--- a/docs/maliev-feature-user-story-status.xlsx
+++ b/docs/maliev-feature-user-story-status.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R62b13b44b2cf4df0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="R888929003867417a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R18ae41055eae4ea5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="R3a51d968829d4ee2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R554a3b92a79a495b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="R9ad3a24640e843dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R9dd323d9817646ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="R880d74aa35134dee"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -759,7 +759,7 @@
       </x:c>
       <x:c r="C5" s="19" t="n">
         <x:f>COUNTIF('Maliev.Web'!$G$2:$G$22,"Automated coverage declared")+COUNTIF('Maliev.Web'!$G$2:$G$22,"Passed")</x:f>
-        <x:v>19</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D5" s="19" t="n">
         <x:f>COUNTIF('Maliev.Web'!$G$2:$G$22,"Partial")+COUNTIF('Maliev.Web'!$G$2:$G$22,"Partial after automated run")+COUNTIF('Maliev.Web'!$F$2:$F$22,"Partial")</x:f>
@@ -1550,16 +1550,16 @@
         <x:v>Ready to automate</x:v>
       </x:c>
       <x:c r="G9" s="48" t="str">
-        <x:v>Automated coverage declared</x:v>
+        <x:v>Failed</x:v>
       </x:c>
       <x:c r="H9" s="48" t="str">
-        <x:v>No current error logged</x:v>
+        <x:v>Failed in latest run</x:v>
       </x:c>
       <x:c r="I9" s="48" t="str">
-        <x:v>N/A</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J9" s="48" t="str">
-        <x:v>Passed</x:v>
+        <x:v>Needs retest loop</x:v>
       </x:c>
       <x:c r="K9" s="48" t="str">
         <x:v>P2</x:v>
@@ -1577,7 +1577,7 @@
         <x:v>web/v{version:apiVersion}/account (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:18); GET web/v{version:apiVersion}/account/session (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:24); GET web/v{version:apiVersion}/account/profile (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:41); PATCH web/v{version:apiVersion}/account/profile (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:86); POST web/v{version:apiVersion}/account/email/change (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:145)</x:v>
       </x:c>
       <x:c r="P9" s="48" t="str">
-        <x:v>BrowserJourneyGateTests.Web_PublicTrustAndQuoteHandoff_RoutesToLocalQuoteEngine (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:162); BrowserJourneyGateTests.Web_PublicContentRoutes_RenderTrustPolicyAndSupportSurfaces (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:199)</x:v>
+        <x:v>BrowserJourneyGateTests.Web_PublicTrustAndQuoteHandoff_RoutesToLocalQuoteEngine (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:162); BrowserJourneyGateTests.Web_PublicContentRoutes_RenderTrustPolicyAndSupportSurfaces (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:199) Latest run 2026-06-23: FAILED focused E2E BrowserJourneyGateTests.Web_PublicTrustAndQuoteHandoff_RoutesToLocalQuoteEngine. The handoff opened QuoteEngine Make Studio, but the assertion at BrowserJourneyGateTests.cs:187 expected demo wording /Demo only|Demo mode|Demo sample only|sample.step/ while the page body showed the current Make Studio shell plus "Reconnecting to your workspace" overlays. TRX: Maliev.Aspire.Tests/TestResults/feature-tracker-web-public.trx.</x:v>
       </x:c>
       <x:c r="Q9" s="48" t="str">
         <x:v>Maliev.Web.Bff; CommerceService if service/product data is catalog-backed; MaterialService and PricingService if quote entry preloads options; UploadService if quote entry supports immediate file upload</x:v>
@@ -1586,10 +1586,10 @@
         <x:v>None required for the discovery portion.; Optional anonymous quote draft/session if the quote entry creates one.</x:v>
       </x:c>
       <x:c r="S9" s="48" t="str">
-        <x:v>The Web CTA split must remain explicit: "Try demo" opens QuoteEngine demo mode, while "Start project" opens the signed-in QuoteEngine project flow.</x:v>
+        <x:v>The Web CTA split must remain explicit: "Try demo" opens QuoteEngine demo mode, while "Start project" opens the signed-in QuoteEngine project flow. Testing error documented 2026-06-23: Web-to-QuoteEngine handoff expectation is stale or the demo destination no longer exposes the required demo/sample cue. Classify as logistical/UX until product intent is confirmed, then update the page cue or the E2E assertion and retest.</x:v>
       </x:c>
       <x:c r="T9" s="48" t="str">
-        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:82; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs</x:v>
+        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:82; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs Maliev.Aspire.Tests/TestResults/feature-tracker-web-public.trx</x:v>
       </x:c>
       <x:c r="U9" s="49" t="str">
         <x:v>2026-06-23</x:v>
@@ -2135,16 +2135,16 @@
         <x:v>Ready to automate</x:v>
       </x:c>
       <x:c r="G18" s="48" t="str">
-        <x:v>Automated coverage declared</x:v>
+        <x:v>Failed</x:v>
       </x:c>
       <x:c r="H18" s="48" t="str">
-        <x:v>No current error logged</x:v>
+        <x:v>Failed in latest run</x:v>
       </x:c>
       <x:c r="I18" s="48" t="str">
-        <x:v>N/A</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J18" s="48" t="str">
-        <x:v>Passed</x:v>
+        <x:v>Needs retest loop</x:v>
       </x:c>
       <x:c r="K18" s="48" t="str">
         <x:v>P2</x:v>
@@ -2162,7 +2162,7 @@
         <x:v>web/v{version:apiVersion}/account (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:18); GET web/v{version:apiVersion}/account/session (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:24); GET web/v{version:apiVersion}/account/profile (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:41); PATCH web/v{version:apiVersion}/account/profile (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:86); POST web/v{version:apiVersion}/account/email/change (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:145)</x:v>
       </x:c>
       <x:c r="P18" s="48" t="str">
-        <x:v>BrowserJourneyGateTests.Web_PublicTrustAndQuoteHandoff_RoutesToLocalQuoteEngine (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:162); BrowserJourneyGateTests.Web_PublicContentRoutes_RenderTrustPolicyAndSupportSurfaces (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:199)</x:v>
+        <x:v>BrowserJourneyGateTests.Web_PublicTrustAndQuoteHandoff_RoutesToLocalQuoteEngine (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:162); BrowserJourneyGateTests.Web_PublicContentRoutes_RenderTrustPolicyAndSupportSurfaces (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:199) Latest run 2026-06-23: FAILED focused E2E BrowserJourneyGateTests.Web_PublicTrustAndQuoteHandoff_RoutesToLocalQuoteEngine. The handoff opened QuoteEngine Make Studio, but the assertion at BrowserJourneyGateTests.cs:187 expected demo wording /Demo only|Demo mode|Demo sample only|sample.step/ while the page body showed the current Make Studio shell plus "Reconnecting to your workspace" overlays. TRX: Maliev.Aspire.Tests/TestResults/feature-tracker-web-public.trx.</x:v>
       </x:c>
       <x:c r="Q18" s="48" t="str">
         <x:v>Maliev.Web.Bff; Maliev.Web.Client; ContactService only when the journey ends in contact submission.</x:v>
@@ -2171,10 +2171,10 @@
         <x:v>None for browsing.; Contact inquiry if the journey converts through contact.</x:v>
       </x:c>
       <x:c r="S18" s="48" t="str">
-        <x:v>Content-to-quote conversion should be reviewed once the final Web-to-QuoteEngine handoff is revisited.</x:v>
+        <x:v>Content-to-quote conversion should be reviewed once the final Web-to-QuoteEngine handoff is revisited. Testing error documented 2026-06-23: Web-to-QuoteEngine handoff expectation is stale or the demo destination no longer exposes the required demo/sample cue. Classify as logistical/UX until product intent is confirmed, then update the page cue or the E2E assertion and retest.</x:v>
       </x:c>
       <x:c r="T18" s="48" t="str">
-        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:587; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs</x:v>
+        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:587; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs Maliev.Aspire.Tests/TestResults/feature-tracker-web-public.trx</x:v>
       </x:c>
       <x:c r="U18" s="49" t="str">
         <x:v>2026-06-23</x:v>
@@ -2200,16 +2200,16 @@
         <x:v>Ready to automate</x:v>
       </x:c>
       <x:c r="G19" s="48" t="str">
-        <x:v>Automated coverage declared</x:v>
+        <x:v>Failed</x:v>
       </x:c>
       <x:c r="H19" s="48" t="str">
-        <x:v>No current error logged</x:v>
+        <x:v>Failed in latest run</x:v>
       </x:c>
       <x:c r="I19" s="48" t="str">
-        <x:v>N/A</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J19" s="48" t="str">
-        <x:v>Passed</x:v>
+        <x:v>Needs retest loop</x:v>
       </x:c>
       <x:c r="K19" s="48" t="str">
         <x:v>P2</x:v>
@@ -2227,7 +2227,7 @@
         <x:v>web/v{version:apiVersion}/account (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:18); GET web/v{version:apiVersion}/account/session (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:24); GET web/v{version:apiVersion}/account/profile (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:41); PATCH web/v{version:apiVersion}/account/profile (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:86); POST web/v{version:apiVersion}/account/email/change (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:145)</x:v>
       </x:c>
       <x:c r="P19" s="48" t="str">
-        <x:v>BrowserJourneyGateTests.Web_PublicTrustAndQuoteHandoff_RoutesToLocalQuoteEngine (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:162); BrowserJourneyGateTests.Web_PublicContentRoutes_RenderTrustPolicyAndSupportSurfaces (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:199)</x:v>
+        <x:v>BrowserJourneyGateTests.Web_PublicTrustAndQuoteHandoff_RoutesToLocalQuoteEngine (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:162); BrowserJourneyGateTests.Web_PublicContentRoutes_RenderTrustPolicyAndSupportSurfaces (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:199) Latest run 2026-06-23: FAILED focused E2E BrowserJourneyGateTests.Web_PublicTrustAndQuoteHandoff_RoutesToLocalQuoteEngine. The handoff opened QuoteEngine Make Studio, but the assertion at BrowserJourneyGateTests.cs:187 expected demo wording /Demo only|Demo mode|Demo sample only|sample.step/ while the page body showed the current Make Studio shell plus "Reconnecting to your workspace" overlays. TRX: Maliev.Aspire.Tests/TestResults/feature-tracker-web-public.trx.</x:v>
       </x:c>
       <x:c r="Q19" s="48" t="str">
         <x:v>Maliev.Web.Client; Maliev.Web.Bff if preferences are server-backed.</x:v>
@@ -2236,10 +2236,10 @@
         <x:v>Browser consent/preference state.; Optional server preference record if signed in and implemented.</x:v>
       </x:c>
       <x:c r="S19" s="48" t="str">
-        <x:v>If consent cannot be changed after the first decision, add a visible preference-management affordance.</x:v>
+        <x:v>If consent cannot be changed after the first decision, add a visible preference-management affordance. Testing error documented 2026-06-23: Web-to-QuoteEngine handoff expectation is stale or the demo destination no longer exposes the required demo/sample cue. Classify as logistical/UX until product intent is confirmed, then update the page cue or the E2E assertion and retest.</x:v>
       </x:c>
       <x:c r="T19" s="48" t="str">
-        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:641; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs</x:v>
+        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:641; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs Maliev.Aspire.Tests/TestResults/feature-tracker-web-public.trx</x:v>
       </x:c>
       <x:c r="U19" s="49" t="str">
         <x:v>2026-06-23</x:v>
@@ -2330,13 +2330,13 @@
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="G21" s="48" t="str">
-        <x:v>Automated coverage declared</x:v>
+        <x:v>Failed</x:v>
       </x:c>
       <x:c r="H21" s="48" t="str">
-        <x:v>No current error logged</x:v>
+        <x:v>Failed in latest run</x:v>
       </x:c>
       <x:c r="I21" s="48" t="str">
-        <x:v>In progress</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J21" s="48" t="str">
         <x:v>Needs retest loop</x:v>
@@ -2357,7 +2357,7 @@
         <x:v>web/v{version:apiVersion}/account (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:18); GET web/v{version:apiVersion}/account/session (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:24); GET web/v{version:apiVersion}/account/profile (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:41); PATCH web/v{version:apiVersion}/account/profile (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:86); POST web/v{version:apiVersion}/account/email/change (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:145)</x:v>
       </x:c>
       <x:c r="P21" s="48" t="str">
-        <x:v>BrowserJourneyGateTests.Web_PublicTrustAndQuoteHandoff_RoutesToLocalQuoteEngine (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:162); BrowserJourneyGateTests.Web_PublicContentRoutes_RenderTrustPolicyAndSupportSurfaces (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:199)</x:v>
+        <x:v>BrowserJourneyGateTests.Web_PublicTrustAndQuoteHandoff_RoutesToLocalQuoteEngine (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:162); BrowserJourneyGateTests.Web_PublicContentRoutes_RenderTrustPolicyAndSupportSurfaces (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:199) Latest run 2026-06-23: FAILED focused E2E BrowserJourneyGateTests.Web_PublicTrustAndQuoteHandoff_RoutesToLocalQuoteEngine. The handoff opened QuoteEngine Make Studio, but the assertion at BrowserJourneyGateTests.cs:187 expected demo wording /Demo only|Demo mode|Demo sample only|sample.step/ while the page body showed the current Make Studio shell plus "Reconnecting to your workspace" overlays. TRX: Maliev.Aspire.Tests/TestResults/feature-tracker-web-public.trx.</x:v>
       </x:c>
       <x:c r="Q21" s="48" t="str">
         <x:v>Maliev.Web.Bff; Maliev.QuoteEngine.Bff; AuthService; CustomerService</x:v>
@@ -2366,10 +2366,10 @@
         <x:v>Demo path: no project, quotation, order, upload, or customer history record.; Start-project path: customer session and, after upload/configuration, real ProjectService project state.</x:v>
       </x:c>
       <x:c r="S21" s="48" t="str">
-        <x:v>Replace any remaining Web-owned manufacturing quote form with this demo/start-project split when the old path is no longer needed.</x:v>
+        <x:v>Replace any remaining Web-owned manufacturing quote form with this demo/start-project split when the old path is no longer needed. Testing error documented 2026-06-23: Web-to-QuoteEngine handoff expectation is stale or the demo destination no longer exposes the required demo/sample cue. Classify as logistical/UX until product intent is confirmed, then update the page cue or the E2E assertion and retest.</x:v>
       </x:c>
       <x:c r="T21" s="48" t="str">
-        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:746; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs</x:v>
+        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:746; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs Maliev.Aspire.Tests/TestResults/feature-tracker-web-public.trx</x:v>
       </x:c>
       <x:c r="U21" s="49" t="str">
         <x:v>2026-06-23</x:v>
@@ -2463,7 +2463,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R53be2663167a4d27"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R90a60542b18a4880"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6678,7 +6678,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5caa10f0b46547e5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb89cf05ce7f04b86"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8813,7 +8813,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb74fd4559a1d4ef1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f1c7235d8ad40cc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/maliev-feature-user-story-status.xlsx
+++ b/docs/maliev-feature-user-story-status.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R554a3b92a79a495b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="R9ad3a24640e843dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R9dd323d9817646ed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="R880d74aa35134dee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rb2b34cdfe39543a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="R757a8ad607f04fd4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R9b6dc81a9ca94d20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="Reeaafe2b3ef84bf3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -759,7 +759,7 @@
       </x:c>
       <x:c r="C5" s="19" t="n">
         <x:f>COUNTIF('Maliev.Web'!$G$2:$G$22,"Automated coverage declared")+COUNTIF('Maliev.Web'!$G$2:$G$22,"Passed")</x:f>
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D5" s="19" t="n">
         <x:f>COUNTIF('Maliev.Web'!$G$2:$G$22,"Partial")+COUNTIF('Maliev.Web'!$G$2:$G$22,"Partial after automated run")+COUNTIF('Maliev.Web'!$F$2:$F$22,"Partial")</x:f>
@@ -1550,16 +1550,16 @@
         <x:v>Ready to automate</x:v>
       </x:c>
       <x:c r="G9" s="48" t="str">
-        <x:v>Failed</x:v>
+        <x:v>Passed</x:v>
       </x:c>
       <x:c r="H9" s="48" t="str">
-        <x:v>Failed in latest run</x:v>
+        <x:v>Resolved</x:v>
       </x:c>
       <x:c r="I9" s="48" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="J9" s="48" t="str">
-        <x:v>Needs retest loop</x:v>
+        <x:v>Passed</x:v>
       </x:c>
       <x:c r="K9" s="48" t="str">
         <x:v>P2</x:v>
@@ -1577,7 +1577,8 @@
         <x:v>web/v{version:apiVersion}/account (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:18); GET web/v{version:apiVersion}/account/session (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:24); GET web/v{version:apiVersion}/account/profile (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:41); PATCH web/v{version:apiVersion}/account/profile (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:86); POST web/v{version:apiVersion}/account/email/change (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:145)</x:v>
       </x:c>
       <x:c r="P9" s="48" t="str">
-        <x:v>BrowserJourneyGateTests.Web_PublicTrustAndQuoteHandoff_RoutesToLocalQuoteEngine (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:162); BrowserJourneyGateTests.Web_PublicContentRoutes_RenderTrustPolicyAndSupportSurfaces (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:199) Latest run 2026-06-23: FAILED focused E2E BrowserJourneyGateTests.Web_PublicTrustAndQuoteHandoff_RoutesToLocalQuoteEngine. The handoff opened QuoteEngine Make Studio, but the assertion at BrowserJourneyGateTests.cs:187 expected demo wording /Demo only|Demo mode|Demo sample only|sample.step/ while the page body showed the current Make Studio shell plus "Reconnecting to your workspace" overlays. TRX: Maliev.Aspire.Tests/TestResults/feature-tracker-web-public.trx.</x:v>
+        <x:v>BrowserJourneyGateTests.Web_PublicTrustAndQuoteHandoff_RoutesToLocalQuoteEngine (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:162); BrowserJourneyGateTests.Web_PublicContentRoutes_RenderTrustPolicyAndSupportSurfaces (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:199) Latest run 2026-06-23: FAILED focused E2E BrowserJourneyGateTests.Web_PublicTrustAndQuoteHandoff_RoutesToLocalQuoteEngine. The handoff opened QuoteEngine Make Studio, but the assertion at BrowserJourneyGateTests.cs:187 expected demo wording /Demo only|Demo mode|Demo sample only|sample.step/ while the page body showed the current Make Studio shell plus "Reconnecting to your workspace" overlays. TRX: Maliev.Aspire.Tests/TestResults/feature-tracker-web-public.trx.
+2026-06-23: Retest passed after QuoteEngine ac7ab3c added a visible demo-mode/sample-only notice on /demo. Focused Aspire E2E passed: Web_PublicTrustAndQuoteHandoff_RoutesToLocalQuoteEngine. Retest TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-web-public-retest.trx. Original failure TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-web-public.trx.</x:v>
       </x:c>
       <x:c r="Q9" s="48" t="str">
         <x:v>Maliev.Web.Bff; CommerceService if service/product data is catalog-backed; MaterialService and PricingService if quote entry preloads options; UploadService if quote entry supports immediate file upload</x:v>
@@ -1589,7 +1590,8 @@
         <x:v>The Web CTA split must remain explicit: "Try demo" opens QuoteEngine demo mode, while "Start project" opens the signed-in QuoteEngine project flow. Testing error documented 2026-06-23: Web-to-QuoteEngine handoff expectation is stale or the demo destination no longer exposes the required demo/sample cue. Classify as logistical/UX until product intent is confirmed, then update the page cue or the E2E assertion and retest.</x:v>
       </x:c>
       <x:c r="T9" s="48" t="str">
-        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:82; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs Maliev.Aspire.Tests/TestResults/feature-tracker-web-public.trx</x:v>
+        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:82; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs Maliev.Aspire.Tests/TestResults/feature-tracker-web-public.trx
+QuoteEngine fix commit: ac7ab3c. Aspire retest TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-web-public-retest.trx.</x:v>
       </x:c>
       <x:c r="U9" s="49" t="str">
         <x:v>2026-06-23</x:v>
@@ -2135,16 +2137,16 @@
         <x:v>Ready to automate</x:v>
       </x:c>
       <x:c r="G18" s="48" t="str">
-        <x:v>Failed</x:v>
+        <x:v>Passed</x:v>
       </x:c>
       <x:c r="H18" s="48" t="str">
-        <x:v>Failed in latest run</x:v>
+        <x:v>Resolved</x:v>
       </x:c>
       <x:c r="I18" s="48" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="J18" s="48" t="str">
-        <x:v>Needs retest loop</x:v>
+        <x:v>Passed</x:v>
       </x:c>
       <x:c r="K18" s="48" t="str">
         <x:v>P2</x:v>
@@ -2162,7 +2164,8 @@
         <x:v>web/v{version:apiVersion}/account (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:18); GET web/v{version:apiVersion}/account/session (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:24); GET web/v{version:apiVersion}/account/profile (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:41); PATCH web/v{version:apiVersion}/account/profile (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:86); POST web/v{version:apiVersion}/account/email/change (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:145)</x:v>
       </x:c>
       <x:c r="P18" s="48" t="str">
-        <x:v>BrowserJourneyGateTests.Web_PublicTrustAndQuoteHandoff_RoutesToLocalQuoteEngine (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:162); BrowserJourneyGateTests.Web_PublicContentRoutes_RenderTrustPolicyAndSupportSurfaces (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:199) Latest run 2026-06-23: FAILED focused E2E BrowserJourneyGateTests.Web_PublicTrustAndQuoteHandoff_RoutesToLocalQuoteEngine. The handoff opened QuoteEngine Make Studio, but the assertion at BrowserJourneyGateTests.cs:187 expected demo wording /Demo only|Demo mode|Demo sample only|sample.step/ while the page body showed the current Make Studio shell plus "Reconnecting to your workspace" overlays. TRX: Maliev.Aspire.Tests/TestResults/feature-tracker-web-public.trx.</x:v>
+        <x:v>BrowserJourneyGateTests.Web_PublicTrustAndQuoteHandoff_RoutesToLocalQuoteEngine (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:162); BrowserJourneyGateTests.Web_PublicContentRoutes_RenderTrustPolicyAndSupportSurfaces (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:199) Latest run 2026-06-23: FAILED focused E2E BrowserJourneyGateTests.Web_PublicTrustAndQuoteHandoff_RoutesToLocalQuoteEngine. The handoff opened QuoteEngine Make Studio, but the assertion at BrowserJourneyGateTests.cs:187 expected demo wording /Demo only|Demo mode|Demo sample only|sample.step/ while the page body showed the current Make Studio shell plus "Reconnecting to your workspace" overlays. TRX: Maliev.Aspire.Tests/TestResults/feature-tracker-web-public.trx.
+2026-06-23: Retest passed after QuoteEngine ac7ab3c added a visible demo-mode/sample-only notice on /demo. Focused Aspire E2E passed: Web_PublicTrustAndQuoteHandoff_RoutesToLocalQuoteEngine. Retest TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-web-public-retest.trx. Original failure TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-web-public.trx.</x:v>
       </x:c>
       <x:c r="Q18" s="48" t="str">
         <x:v>Maliev.Web.Bff; Maliev.Web.Client; ContactService only when the journey ends in contact submission.</x:v>
@@ -2174,7 +2177,8 @@
         <x:v>Content-to-quote conversion should be reviewed once the final Web-to-QuoteEngine handoff is revisited. Testing error documented 2026-06-23: Web-to-QuoteEngine handoff expectation is stale or the demo destination no longer exposes the required demo/sample cue. Classify as logistical/UX until product intent is confirmed, then update the page cue or the E2E assertion and retest.</x:v>
       </x:c>
       <x:c r="T18" s="48" t="str">
-        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:587; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs Maliev.Aspire.Tests/TestResults/feature-tracker-web-public.trx</x:v>
+        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:587; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs Maliev.Aspire.Tests/TestResults/feature-tracker-web-public.trx
+QuoteEngine fix commit: ac7ab3c. Aspire retest TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-web-public-retest.trx.</x:v>
       </x:c>
       <x:c r="U18" s="49" t="str">
         <x:v>2026-06-23</x:v>
@@ -2200,16 +2204,16 @@
         <x:v>Ready to automate</x:v>
       </x:c>
       <x:c r="G19" s="48" t="str">
-        <x:v>Failed</x:v>
+        <x:v>Passed</x:v>
       </x:c>
       <x:c r="H19" s="48" t="str">
-        <x:v>Failed in latest run</x:v>
+        <x:v>Resolved</x:v>
       </x:c>
       <x:c r="I19" s="48" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="J19" s="48" t="str">
-        <x:v>Needs retest loop</x:v>
+        <x:v>Passed</x:v>
       </x:c>
       <x:c r="K19" s="48" t="str">
         <x:v>P2</x:v>
@@ -2227,7 +2231,8 @@
         <x:v>web/v{version:apiVersion}/account (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:18); GET web/v{version:apiVersion}/account/session (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:24); GET web/v{version:apiVersion}/account/profile (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:41); PATCH web/v{version:apiVersion}/account/profile (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:86); POST web/v{version:apiVersion}/account/email/change (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:145)</x:v>
       </x:c>
       <x:c r="P19" s="48" t="str">
-        <x:v>BrowserJourneyGateTests.Web_PublicTrustAndQuoteHandoff_RoutesToLocalQuoteEngine (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:162); BrowserJourneyGateTests.Web_PublicContentRoutes_RenderTrustPolicyAndSupportSurfaces (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:199) Latest run 2026-06-23: FAILED focused E2E BrowserJourneyGateTests.Web_PublicTrustAndQuoteHandoff_RoutesToLocalQuoteEngine. The handoff opened QuoteEngine Make Studio, but the assertion at BrowserJourneyGateTests.cs:187 expected demo wording /Demo only|Demo mode|Demo sample only|sample.step/ while the page body showed the current Make Studio shell plus "Reconnecting to your workspace" overlays. TRX: Maliev.Aspire.Tests/TestResults/feature-tracker-web-public.trx.</x:v>
+        <x:v>BrowserJourneyGateTests.Web_PublicTrustAndQuoteHandoff_RoutesToLocalQuoteEngine (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:162); BrowserJourneyGateTests.Web_PublicContentRoutes_RenderTrustPolicyAndSupportSurfaces (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:199) Latest run 2026-06-23: FAILED focused E2E BrowserJourneyGateTests.Web_PublicTrustAndQuoteHandoff_RoutesToLocalQuoteEngine. The handoff opened QuoteEngine Make Studio, but the assertion at BrowserJourneyGateTests.cs:187 expected demo wording /Demo only|Demo mode|Demo sample only|sample.step/ while the page body showed the current Make Studio shell plus "Reconnecting to your workspace" overlays. TRX: Maliev.Aspire.Tests/TestResults/feature-tracker-web-public.trx.
+2026-06-23: Retest passed after QuoteEngine ac7ab3c added a visible demo-mode/sample-only notice on /demo. Focused Aspire E2E passed: Web_PublicTrustAndQuoteHandoff_RoutesToLocalQuoteEngine. Retest TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-web-public-retest.trx. Original failure TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-web-public.trx.</x:v>
       </x:c>
       <x:c r="Q19" s="48" t="str">
         <x:v>Maliev.Web.Client; Maliev.Web.Bff if preferences are server-backed.</x:v>
@@ -2239,7 +2244,8 @@
         <x:v>If consent cannot be changed after the first decision, add a visible preference-management affordance. Testing error documented 2026-06-23: Web-to-QuoteEngine handoff expectation is stale or the demo destination no longer exposes the required demo/sample cue. Classify as logistical/UX until product intent is confirmed, then update the page cue or the E2E assertion and retest.</x:v>
       </x:c>
       <x:c r="T19" s="48" t="str">
-        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:641; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs Maliev.Aspire.Tests/TestResults/feature-tracker-web-public.trx</x:v>
+        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:641; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs Maliev.Aspire.Tests/TestResults/feature-tracker-web-public.trx
+QuoteEngine fix commit: ac7ab3c. Aspire retest TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-web-public-retest.trx.</x:v>
       </x:c>
       <x:c r="U19" s="49" t="str">
         <x:v>2026-06-23</x:v>
@@ -2330,16 +2336,16 @@
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="G21" s="48" t="str">
-        <x:v>Failed</x:v>
+        <x:v>Passed</x:v>
       </x:c>
       <x:c r="H21" s="48" t="str">
-        <x:v>Failed in latest run</x:v>
+        <x:v>Resolved</x:v>
       </x:c>
       <x:c r="I21" s="48" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="J21" s="48" t="str">
-        <x:v>Needs retest loop</x:v>
+        <x:v>Passed</x:v>
       </x:c>
       <x:c r="K21" s="48" t="str">
         <x:v>P1</x:v>
@@ -2357,7 +2363,8 @@
         <x:v>web/v{version:apiVersion}/account (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:18); GET web/v{version:apiVersion}/account/session (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:24); GET web/v{version:apiVersion}/account/profile (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:41); PATCH web/v{version:apiVersion}/account/profile (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:86); POST web/v{version:apiVersion}/account/email/change (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:145)</x:v>
       </x:c>
       <x:c r="P21" s="48" t="str">
-        <x:v>BrowserJourneyGateTests.Web_PublicTrustAndQuoteHandoff_RoutesToLocalQuoteEngine (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:162); BrowserJourneyGateTests.Web_PublicContentRoutes_RenderTrustPolicyAndSupportSurfaces (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:199) Latest run 2026-06-23: FAILED focused E2E BrowserJourneyGateTests.Web_PublicTrustAndQuoteHandoff_RoutesToLocalQuoteEngine. The handoff opened QuoteEngine Make Studio, but the assertion at BrowserJourneyGateTests.cs:187 expected demo wording /Demo only|Demo mode|Demo sample only|sample.step/ while the page body showed the current Make Studio shell plus "Reconnecting to your workspace" overlays. TRX: Maliev.Aspire.Tests/TestResults/feature-tracker-web-public.trx.</x:v>
+        <x:v>BrowserJourneyGateTests.Web_PublicTrustAndQuoteHandoff_RoutesToLocalQuoteEngine (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:162); BrowserJourneyGateTests.Web_PublicContentRoutes_RenderTrustPolicyAndSupportSurfaces (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:199) Latest run 2026-06-23: FAILED focused E2E BrowserJourneyGateTests.Web_PublicTrustAndQuoteHandoff_RoutesToLocalQuoteEngine. The handoff opened QuoteEngine Make Studio, but the assertion at BrowserJourneyGateTests.cs:187 expected demo wording /Demo only|Demo mode|Demo sample only|sample.step/ while the page body showed the current Make Studio shell plus "Reconnecting to your workspace" overlays. TRX: Maliev.Aspire.Tests/TestResults/feature-tracker-web-public.trx.
+2026-06-23: Retest passed after QuoteEngine ac7ab3c added a visible demo-mode/sample-only notice on /demo. Focused Aspire E2E passed: Web_PublicTrustAndQuoteHandoff_RoutesToLocalQuoteEngine. Retest TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-web-public-retest.trx. Original failure TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-web-public.trx.</x:v>
       </x:c>
       <x:c r="Q21" s="48" t="str">
         <x:v>Maliev.Web.Bff; Maliev.QuoteEngine.Bff; AuthService; CustomerService</x:v>
@@ -2369,7 +2376,8 @@
         <x:v>Replace any remaining Web-owned manufacturing quote form with this demo/start-project split when the old path is no longer needed. Testing error documented 2026-06-23: Web-to-QuoteEngine handoff expectation is stale or the demo destination no longer exposes the required demo/sample cue. Classify as logistical/UX until product intent is confirmed, then update the page cue or the E2E assertion and retest.</x:v>
       </x:c>
       <x:c r="T21" s="48" t="str">
-        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:746; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs Maliev.Aspire.Tests/TestResults/feature-tracker-web-public.trx</x:v>
+        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:746; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs Maliev.Aspire.Tests/TestResults/feature-tracker-web-public.trx
+QuoteEngine fix commit: ac7ab3c. Aspire retest TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-web-public-retest.trx.</x:v>
       </x:c>
       <x:c r="U21" s="49" t="str">
         <x:v>2026-06-23</x:v>
@@ -2463,7 +2471,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R90a60542b18a4880"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R350e435724e2432f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6678,7 +6686,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb89cf05ce7f04b86"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4a6eeaa16b574e76"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8813,7 +8821,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f1c7235d8ad40cc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9a2235cbe07b44ca"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/maliev-feature-user-story-status.xlsx
+++ b/docs/maliev-feature-user-story-status.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rb2b34cdfe39543a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="R757a8ad607f04fd4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R9b6dc81a9ca94d20"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="Reeaafe2b3ef84bf3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R141f6d7fc98a4027"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="Raa306e393d0343de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R7cddd1ae401c4d0d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="R2ea7aa3c1fc043e1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -759,7 +759,7 @@
       </x:c>
       <x:c r="C5" s="19" t="n">
         <x:f>COUNTIF('Maliev.Web'!$G$2:$G$22,"Automated coverage declared")+COUNTIF('Maliev.Web'!$G$2:$G$22,"Passed")</x:f>
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D5" s="19" t="n">
         <x:f>COUNTIF('Maliev.Web'!$G$2:$G$22,"Partial")+COUNTIF('Maliev.Web'!$G$2:$G$22,"Partial after automated run")+COUNTIF('Maliev.Web'!$F$2:$F$22,"Partial")</x:f>
@@ -790,7 +790,7 @@
       </x:c>
       <x:c r="C6" s="19" t="n">
         <x:f>COUNTIF('Maliev.Intranet'!$G$2:$G$64,"Automated coverage declared")+COUNTIF('Maliev.Intranet'!$G$2:$G$64,"Passed")</x:f>
-        <x:v>55</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D6" s="19" t="n">
         <x:f>COUNTIF('Maliev.Intranet'!$G$2:$G$64,"Partial")+COUNTIF('Maliev.Intranet'!$G$2:$G$64,"Partial after automated run")+COUNTIF('Maliev.Intranet'!$F$2:$F$64,"Partial")</x:f>
@@ -821,7 +821,7 @@
       </x:c>
       <x:c r="C7" s="19" t="n">
         <x:f>COUNTIF('Maliev.QuoteEngine'!$G$2:$G$32,"Automated coverage declared")+COUNTIF('Maliev.QuoteEngine'!$G$2:$G$32,"Passed")</x:f>
-        <x:v>29</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D7" s="19" t="n">
         <x:f>COUNTIF('Maliev.QuoteEngine'!$G$2:$G$32,"Partial")+COUNTIF('Maliev.QuoteEngine'!$G$2:$G$32,"Partial after automated run")+COUNTIF('Maliev.QuoteEngine'!$F$2:$F$32,"Partial")</x:f>
@@ -1095,16 +1095,16 @@
         <x:v>Ready to automate</x:v>
       </x:c>
       <x:c r="G2" s="48" t="str">
-        <x:v>Automated coverage declared</x:v>
+        <x:v>Failed</x:v>
       </x:c>
       <x:c r="H2" s="48" t="str">
-        <x:v>No current error logged</x:v>
+        <x:v>Failed in latest browser suite</x:v>
       </x:c>
       <x:c r="I2" s="48" t="str">
-        <x:v>N/A</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J2" s="48" t="str">
-        <x:v>Passed</x:v>
+        <x:v>Needs retest loop</x:v>
       </x:c>
       <x:c r="K2" s="48" t="str">
         <x:v>P2</x:v>
@@ -1122,7 +1122,10 @@
         <x:v>web/v{version:apiVersion}/account (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:18); GET web/v{version:apiVersion}/account/session (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:24); GET web/v{version:apiVersion}/account/profile (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:41); PATCH web/v{version:apiVersion}/account/profile (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:86); POST web/v{version:apiVersion}/account/email/change (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:145)</x:v>
       </x:c>
       <x:c r="P2" s="48" t="str">
-        <x:v>BrowserJourneyGateTests.Commerce_EmployeePublishesProduct_WebCustomerCanBrowseCartAndArchivedProductIsHidden (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:741)</x:v>
+        <x:v>BrowserJourneyGateTests.Commerce_EmployeePublishesProduct_WebCustomerCanBrowseCartAndArchivedProductIsHidden (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:741)
+2026-06-23 browser-suite failure batch: 14 failed, 42 passed, 0 skipped, 56 total.
+TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx.
+- Commerce_EmployeePublishesProduct_WebCustomerCanBrowseCartAndArchivedProductIsHidden: System.TimeoutException : Timeout 30000ms exceeded. Call log: - waiting for GetByRole(AriaRole.Button, new() { NameRegex = new Regex("Continue to checkout|ดำเนินการชำระเงิน", RegexOptions.IgnoreCase) })</x:v>
       </x:c>
       <x:c r="Q2" s="48" t="str">
         <x:v>Maliev.Intranet.Bff; CommerceService; Maliev.Web.Bff</x:v>
@@ -1131,10 +1134,12 @@
         <x:v>Product status changes from draft to published.</x:v>
       </x:c>
       <x:c r="S2" s="48" t="str">
-        <x:v>Public storefront caching must invalidate quickly enough for E2E to observe publication.</x:v>
+        <x:v>Public storefront caching must invalidate quickly enough for E2E to observe publication.
+Latest browser-suite failure(s): Commerce_EmployeePublishesProduct_WebCustomerCanBrowseCartAndArchivedProductIsHidden</x:v>
       </x:c>
       <x:c r="T2" s="48" t="str">
-        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:4187; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs</x:v>
+        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:4187; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs
+Aspire E2E TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx</x:v>
       </x:c>
       <x:c r="U2" s="49" t="str">
         <x:v>2026-06-23</x:v>
@@ -1160,16 +1165,16 @@
         <x:v>Ready to automate</x:v>
       </x:c>
       <x:c r="G3" s="48" t="str">
-        <x:v>Automated coverage declared</x:v>
+        <x:v>Failed</x:v>
       </x:c>
       <x:c r="H3" s="48" t="str">
-        <x:v>No current error logged</x:v>
+        <x:v>Failed in latest browser suite</x:v>
       </x:c>
       <x:c r="I3" s="48" t="str">
-        <x:v>N/A</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J3" s="48" t="str">
-        <x:v>Passed</x:v>
+        <x:v>Needs retest loop</x:v>
       </x:c>
       <x:c r="K3" s="48" t="str">
         <x:v>P2</x:v>
@@ -1187,7 +1192,10 @@
         <x:v>web/v{version:apiVersion}/account (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:18); GET web/v{version:apiVersion}/account/session (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:24); GET web/v{version:apiVersion}/account/profile (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:41); PATCH web/v{version:apiVersion}/account/profile (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:86); POST web/v{version:apiVersion}/account/email/change (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:145)</x:v>
       </x:c>
       <x:c r="P3" s="48" t="str">
-        <x:v>BrowserJourneyGateTests.Web_PublicAccountSupportAndCommerceEntryPoints_Render (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:241); BrowserJourneyGateTests.Commerce_EmployeePublishesProduct_WebCustomerCanBrowseCartAndArchivedProductIsHidden (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:741)</x:v>
+        <x:v>BrowserJourneyGateTests.Web_PublicAccountSupportAndCommerceEntryPoints_Render (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:241); BrowserJourneyGateTests.Commerce_EmployeePublishesProduct_WebCustomerCanBrowseCartAndArchivedProductIsHidden (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:741)
+2026-06-23 browser-suite failure batch: 14 failed, 42 passed, 0 skipped, 56 total.
+TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx.
+- Commerce_EmployeePublishesProduct_WebCustomerCanBrowseCartAndArchivedProductIsHidden: System.TimeoutException : Timeout 30000ms exceeded. Call log: - waiting for GetByRole(AriaRole.Button, new() { NameRegex = new Regex("Continue to checkout|ดำเนินการชำระเงิน", RegexOptions.IgnoreCase) })</x:v>
       </x:c>
       <x:c r="Q3" s="48" t="str">
         <x:v>Maliev.Web.Bff; CommerceService; OrderService; PaymentService; DeliveryService; CustomerService</x:v>
@@ -1196,10 +1204,12 @@
         <x:v>Cart state.; Checkout/order draft.</x:v>
       </x:c>
       <x:c r="S3" s="48" t="str">
-        <x:v>Final checkout/payment behavior may require separate payment-provider sandbox work.</x:v>
+        <x:v>Final checkout/payment behavior may require separate payment-provider sandbox work.
+Latest browser-suite failure(s): Commerce_EmployeePublishesProduct_WebCustomerCanBrowseCartAndArchivedProductIsHidden</x:v>
       </x:c>
       <x:c r="T3" s="48" t="str">
-        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:4234; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs</x:v>
+        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:4234; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs
+Aspire E2E TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx</x:v>
       </x:c>
       <x:c r="U3" s="49" t="str">
         <x:v>2026-06-23</x:v>
@@ -1225,16 +1235,16 @@
         <x:v>Ready to automate</x:v>
       </x:c>
       <x:c r="G4" s="48" t="str">
-        <x:v>Automated coverage declared</x:v>
+        <x:v>Failed</x:v>
       </x:c>
       <x:c r="H4" s="48" t="str">
-        <x:v>No current error logged</x:v>
+        <x:v>Failed in latest browser suite</x:v>
       </x:c>
       <x:c r="I4" s="48" t="str">
-        <x:v>N/A</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J4" s="48" t="str">
-        <x:v>Passed</x:v>
+        <x:v>Needs retest loop</x:v>
       </x:c>
       <x:c r="K4" s="48" t="str">
         <x:v>P2</x:v>
@@ -1252,7 +1262,10 @@
         <x:v>web/v{version:apiVersion}/account (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:18); GET web/v{version:apiVersion}/account/session (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:24); GET web/v{version:apiVersion}/account/profile (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:41); PATCH web/v{version:apiVersion}/account/profile (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:86); POST web/v{version:apiVersion}/account/email/change (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:145)</x:v>
       </x:c>
       <x:c r="P4" s="48" t="str">
-        <x:v>BrowserJourneyGateTests.Commerce_EmployeePublishesProduct_WebCustomerCanBrowseCartAndArchivedProductIsHidden (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:741)</x:v>
+        <x:v>BrowserJourneyGateTests.Commerce_EmployeePublishesProduct_WebCustomerCanBrowseCartAndArchivedProductIsHidden (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:741)
+2026-06-23 browser-suite failure batch: 14 failed, 42 passed, 0 skipped, 56 total.
+TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx.
+- Commerce_EmployeePublishesProduct_WebCustomerCanBrowseCartAndArchivedProductIsHidden: System.TimeoutException : Timeout 30000ms exceeded. Call log: - waiting for GetByRole(AriaRole.Button, new() { NameRegex = new Regex("Continue to checkout|ดำเนินการชำระเงิน", RegexOptions.IgnoreCase) })</x:v>
       </x:c>
       <x:c r="Q4" s="48" t="str">
         <x:v>Maliev.Intranet.Bff; CommerceService; Maliev.Web.Bff</x:v>
@@ -1261,10 +1274,12 @@
         <x:v>Product status changes to archived/unpublished.</x:v>
       </x:c>
       <x:c r="S4" s="48" t="str">
-        <x:v>Define exact customer-facing behavior for old product URLs.</x:v>
+        <x:v>Define exact customer-facing behavior for old product URLs.
+Latest browser-suite failure(s): Commerce_EmployeePublishesProduct_WebCustomerCanBrowseCartAndArchivedProductIsHidden</x:v>
       </x:c>
       <x:c r="T4" s="48" t="str">
-        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:4286; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs</x:v>
+        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:4286; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs
+Aspire E2E TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx</x:v>
       </x:c>
       <x:c r="U4" s="49" t="str">
         <x:v>2026-06-23</x:v>
@@ -1355,13 +1370,13 @@
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="G6" s="48" t="str">
-        <x:v>Automated coverage declared</x:v>
+        <x:v>Failed</x:v>
       </x:c>
       <x:c r="H6" s="48" t="str">
-        <x:v>No current error logged</x:v>
+        <x:v>Failed in latest browser suite</x:v>
       </x:c>
       <x:c r="I6" s="48" t="str">
-        <x:v>In progress</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J6" s="48" t="str">
         <x:v>Needs retest loop</x:v>
@@ -1382,7 +1397,10 @@
         <x:v>web/v{version:apiVersion}/account (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:18); GET web/v{version:apiVersion}/account/session (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:24); GET web/v{version:apiVersion}/account/profile (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:41); PATCH web/v{version:apiVersion}/account/profile (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:86); POST web/v{version:apiVersion}/account/email/change (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:145)</x:v>
       </x:c>
       <x:c r="P6" s="48" t="str">
-        <x:v>BrowserJourneyGateTests.Web_CustomerAccountSecurity_BlocksCrossCustomerAddressMutationAndPreservesReturnUrl (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:659); BrowserJourneyGateTests.QuoteEngine_CustomerIsolation_BlocksCrossCustomerQuoteOrderHistoryAccess (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3177); BrowserJourneyGateTests.QuoteEngine_CustomerDocuments_DownloadIsOwnerScoped (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3319)</x:v>
+        <x:v>BrowserJourneyGateTests.Web_CustomerAccountSecurity_BlocksCrossCustomerAddressMutationAndPreservesReturnUrl (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:659); BrowserJourneyGateTests.QuoteEngine_CustomerIsolation_BlocksCrossCustomerQuoteOrderHistoryAccess (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3177); BrowserJourneyGateTests.QuoteEngine_CustomerDocuments_DownloadIsOwnerScoped (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3319)
+2026-06-23 browser-suite failure batch: 14 failed, 42 passed, 0 skipped, 56 total.
+TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx.
+- QuoteEngine_CustomerDocuments_DownloadIsOwnerScoped: Document download failed: 404 {"type":"https://tools.ietf.org/html/rfc9110#section-15.5.5","title":"Not Found","status":404,"traceId":"00-e42669f877737efe7ac029309671d831-ed24a434f22bdbe4-01"}</x:v>
       </x:c>
       <x:c r="Q6" s="48" t="str">
         <x:v>Maliev.Web.Bff; Maliev.QuoteEngine.Bff; AuthService; CustomerService; QuotationService; OrderService; UploadService; PdfService; IAMService or authorization service boundary where applicable</x:v>
@@ -1391,10 +1409,12 @@
         <x:v>None expected except safe audit/security logs.</x:v>
       </x:c>
       <x:c r="S6" s="48" t="str">
-        <x:v>Define consistent forbidden versus not-found behavior for cross-customer resource probing.</x:v>
+        <x:v>Define consistent forbidden versus not-found behavior for cross-customer resource probing.
+Latest browser-suite failure(s): QuoteEngine_CustomerDocuments_DownloadIsOwnerScoped</x:v>
       </x:c>
       <x:c r="T6" s="48" t="str">
-        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:5808; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs</x:v>
+        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:5808; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs
+Aspire E2E TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx</x:v>
       </x:c>
       <x:c r="U6" s="49" t="str">
         <x:v>2026-06-23</x:v>
@@ -1420,16 +1440,16 @@
         <x:v>Required production gate. Automate once test hooks can reliably expire sessions.</x:v>
       </x:c>
       <x:c r="G7" s="48" t="str">
-        <x:v>Automated coverage declared</x:v>
+        <x:v>Failed</x:v>
       </x:c>
       <x:c r="H7" s="48" t="str">
-        <x:v>No current error logged</x:v>
+        <x:v>Failed in latest browser suite</x:v>
       </x:c>
       <x:c r="I7" s="48" t="str">
-        <x:v>N/A</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J7" s="48" t="str">
-        <x:v>Passed</x:v>
+        <x:v>Needs retest loop</x:v>
       </x:c>
       <x:c r="K7" s="48" t="str">
         <x:v>P0</x:v>
@@ -1447,7 +1467,10 @@
         <x:v>web/v{version:apiVersion}/account (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:18); GET web/v{version:apiVersion}/account/session (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:24); GET web/v{version:apiVersion}/account/profile (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:41); PATCH web/v{version:apiVersion}/account/profile (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:86); POST web/v{version:apiVersion}/account/email/change (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:145)</x:v>
       </x:c>
       <x:c r="P7" s="48" t="str">
-        <x:v>BrowserJourneyGateTests.Web_CustomerChatbot_LoginPromptContinuesAuthenticatedConversationInPlace (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:496); BrowserJourneyGateTests.Web_CustomerAccountSecurity_BlocksCrossCustomerAddressMutationAndPreservesReturnUrl (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:659); BrowserJourneyGateTests.Intranet_ProtectedRoutes_RedirectAnonymousUserToLogin (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3446); BrowserJourneyGateTests.Intranet_AutomationEmployee_SignsInAndReachesProtectedSurfaces (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3887)</x:v>
+        <x:v>BrowserJourneyGateTests.Web_CustomerChatbot_LoginPromptContinuesAuthenticatedConversationInPlace (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:496); BrowserJourneyGateTests.Web_CustomerAccountSecurity_BlocksCrossCustomerAddressMutationAndPreservesReturnUrl (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:659); BrowserJourneyGateTests.Intranet_ProtectedRoutes_RedirectAnonymousUserToLogin (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3446); BrowserJourneyGateTests.Intranet_AutomationEmployee_SignsInAndReachesProtectedSurfaces (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3887)
+2026-06-23 browser-suite failure batch: 14 failed, 42 passed, 0 skipped, 56 total.
+TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx.
+- Web_CustomerChatbot_LoginPromptContinuesAuthenticatedConversationInPlace: Microsoft.Playwright.PlaywrightException : Locator expected to be visible Error: element(s) not found Call log: - Expect "ToBeVisibleAsync" with timeout 30000ms - waiting for Locator(".topbar-chat-toggle")</x:v>
       </x:c>
       <x:c r="Q7" s="48" t="str">
         <x:v>Maliev.Web.Bff; Maliev.QuoteEngine.Bff; Maliev.Intranet.Bff; AuthService; IAMService; Target domain service for the protected page</x:v>
@@ -1456,10 +1479,12 @@
         <x:v>Session/token state.; No domain mutation expected during denied/re-auth redirect unless user explicitly resubmits.</x:v>
       </x:c>
       <x:c r="S7" s="48" t="str">
-        <x:v>Define exact return URL and unsaved-work policies per app.</x:v>
+        <x:v>Define exact return URL and unsaved-work policies per app.
+Latest browser-suite failure(s): Web_CustomerChatbot_LoginPromptContinuesAuthenticatedConversationInPlace</x:v>
       </x:c>
       <x:c r="T7" s="48" t="str">
-        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:5922; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs</x:v>
+        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:5922; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs
+Aspire E2E TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx</x:v>
       </x:c>
       <x:c r="U7" s="49" t="str">
         <x:v>2026-06-23</x:v>
@@ -1812,16 +1837,16 @@
         <x:v>Ready to automate</x:v>
       </x:c>
       <x:c r="G13" s="48" t="str">
-        <x:v>Automated coverage declared</x:v>
+        <x:v>Failed</x:v>
       </x:c>
       <x:c r="H13" s="48" t="str">
-        <x:v>No current error logged</x:v>
+        <x:v>Failed in latest browser suite</x:v>
       </x:c>
       <x:c r="I13" s="48" t="str">
-        <x:v>N/A</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J13" s="48" t="str">
-        <x:v>Passed</x:v>
+        <x:v>Needs retest loop</x:v>
       </x:c>
       <x:c r="K13" s="48" t="str">
         <x:v>P2</x:v>
@@ -1839,7 +1864,10 @@
         <x:v>web/v{version:apiVersion}/account (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:18); GET web/v{version:apiVersion}/account/session (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:24); GET web/v{version:apiVersion}/account/profile (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:41); PATCH web/v{version:apiVersion}/account/profile (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:86); POST web/v{version:apiVersion}/account/email/change (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:145)</x:v>
       </x:c>
       <x:c r="P13" s="48" t="str">
-        <x:v>BrowserJourneyGateTests.Web_PublicAccountSupportAndCommerceEntryPoints_Render (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:241); BrowserJourneyGateTests.Web_CustomerEmailRegistration_CreatesAccountSessionAndSignsOut (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:335); BrowserJourneyGateTests.Web_CustomerChatbot_LoginPromptContinuesAuthenticatedConversationInPlace (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:496)</x:v>
+        <x:v>BrowserJourneyGateTests.Web_PublicAccountSupportAndCommerceEntryPoints_Render (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:241); BrowserJourneyGateTests.Web_CustomerEmailRegistration_CreatesAccountSessionAndSignsOut (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:335); BrowserJourneyGateTests.Web_CustomerChatbot_LoginPromptContinuesAuthenticatedConversationInPlace (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:496)
+2026-06-23 browser-suite failure batch: 14 failed, 42 passed, 0 skipped, 56 total.
+TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx.
+- Web_CustomerChatbot_LoginPromptContinuesAuthenticatedConversationInPlace: Microsoft.Playwright.PlaywrightException : Locator expected to be visible Error: element(s) not found Call log: - Expect "ToBeVisibleAsync" with timeout 30000ms - waiting for Locator(".topbar-chat-toggle")</x:v>
       </x:c>
       <x:c r="Q13" s="48" t="str">
         <x:v>Maliev.Web.Bff; AuthService; CustomerService; IAMService; OrderService for account orders; DeliveryService for address/order delivery data</x:v>
@@ -1848,10 +1876,12 @@
         <x:v>Auth session/token records if persisted.; Optional refresh token rotation/revocation.</x:v>
       </x:c>
       <x:c r="S13" s="48" t="str">
-        <x:v>Verified-account restrictions should be added once email verification exists.</x:v>
+        <x:v>Verified-account restrictions should be added once email verification exists.
+Latest browser-suite failure(s): Web_CustomerChatbot_LoginPromptContinuesAuthenticatedConversationInPlace</x:v>
       </x:c>
       <x:c r="T13" s="48" t="str">
-        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:305; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs</x:v>
+        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:305; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs
+Aspire E2E TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx</x:v>
       </x:c>
       <x:c r="U13" s="49" t="str">
         <x:v>2026-06-23</x:v>
@@ -2007,16 +2037,16 @@
         <x:v>Ready to automate</x:v>
       </x:c>
       <x:c r="G16" s="48" t="str">
-        <x:v>Automated coverage declared</x:v>
+        <x:v>Failed</x:v>
       </x:c>
       <x:c r="H16" s="48" t="str">
-        <x:v>No current error logged</x:v>
+        <x:v>Failed in latest browser suite</x:v>
       </x:c>
       <x:c r="I16" s="48" t="str">
-        <x:v>N/A</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J16" s="48" t="str">
-        <x:v>Passed</x:v>
+        <x:v>Needs retest loop</x:v>
       </x:c>
       <x:c r="K16" s="48" t="str">
         <x:v>P2</x:v>
@@ -2034,7 +2064,10 @@
         <x:v>web/v{version:apiVersion}/account (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:18); GET web/v{version:apiVersion}/account/session (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:24); GET web/v{version:apiVersion}/account/profile (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:41); PATCH web/v{version:apiVersion}/account/profile (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:86); POST web/v{version:apiVersion}/account/email/change (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:145)</x:v>
       </x:c>
       <x:c r="P16" s="48" t="str">
-        <x:v>BrowserJourneyGateTests.Web_PublicAccountSupportAndCommerceEntryPoints_Render (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:241); BrowserJourneyGateTests.Commerce_EmployeePublishesProduct_WebCustomerCanBrowseCartAndArchivedProductIsHidden (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:741)</x:v>
+        <x:v>BrowserJourneyGateTests.Web_PublicAccountSupportAndCommerceEntryPoints_Render (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:241); BrowserJourneyGateTests.Commerce_EmployeePublishesProduct_WebCustomerCanBrowseCartAndArchivedProductIsHidden (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:741)
+2026-06-23 browser-suite failure batch: 14 failed, 42 passed, 0 skipped, 56 total.
+TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx.
+- Commerce_EmployeePublishesProduct_WebCustomerCanBrowseCartAndArchivedProductIsHidden: System.TimeoutException : Timeout 30000ms exceeded. Call log: - waiting for GetByRole(AriaRole.Button, new() { NameRegex = new Regex("Continue to checkout|ดำเนินการชำระเงิน", RegexOptions.IgnoreCase) })</x:v>
       </x:c>
       <x:c r="Q16" s="48" t="str">
         <x:v>Maliev.Web.Bff; CommerceService; CustomerService; OrderService; PaymentService; DeliveryService</x:v>
@@ -2043,10 +2076,12 @@
         <x:v>Browser cart state.; Checkout draft/order draft.; Optional customer delivery selection.</x:v>
       </x:c>
       <x:c r="S16" s="48" t="str">
-        <x:v>Final payment provider behavior may require sandbox-specific assertions.</x:v>
+        <x:v>Final payment provider behavior may require sandbox-specific assertions.
+Latest browser-suite failure(s): Commerce_EmployeePublishesProduct_WebCustomerCanBrowseCartAndArchivedProductIsHidden</x:v>
       </x:c>
       <x:c r="T16" s="48" t="str">
-        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:471; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs</x:v>
+        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:471; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs
+Aspire E2E TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx</x:v>
       </x:c>
       <x:c r="U16" s="49" t="str">
         <x:v>2026-06-23</x:v>
@@ -2403,13 +2438,13 @@
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="G22" s="51" t="str">
-        <x:v>Automated coverage declared</x:v>
+        <x:v>Failed</x:v>
       </x:c>
       <x:c r="H22" s="51" t="str">
-        <x:v>No current error logged</x:v>
+        <x:v>Failed in latest browser suite</x:v>
       </x:c>
       <x:c r="I22" s="51" t="str">
-        <x:v>In progress</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J22" s="51" t="str">
         <x:v>Needs retest loop</x:v>
@@ -2430,7 +2465,11 @@
         <x:v>web/v{version:apiVersion}/account (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:18); GET web/v{version:apiVersion}/account/session (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:24); GET web/v{version:apiVersion}/account/profile (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:41); PATCH web/v{version:apiVersion}/account/profile (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:86); POST web/v{version:apiVersion}/account/email/change (Maliev.Web/Maliev.Web.Bff/Controllers/AccountController.cs:145)</x:v>
       </x:c>
       <x:c r="P22" s="51" t="str">
-        <x:v>BrowserJourneyGateTests.Web_CustomerChatbot_LoginPromptContinuesAuthenticatedConversationInPlace (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:496); BrowserJourneyGateTests.QuoteEngine_CustomerChatbotWindow_RetainsWebConversation (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:611); BrowserJourneyGateTests.QuoteEngine_MakeStudioAgent_RestoresSignedCustomerConversation (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:1278); BrowserJourneyGateTests.QuoteEngine_MakeStudioAgent_LoginRedirectRestoresActiveChat (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:1384); BrowserJourneyGateTests.Web_MaliChatbot_AnonymousVisitorReceivesAssistantReplyThroughWebBff (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:6251)</x:v>
+        <x:v>BrowserJourneyGateTests.Web_CustomerChatbot_LoginPromptContinuesAuthenticatedConversationInPlace (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:496); BrowserJourneyGateTests.QuoteEngine_CustomerChatbotWindow_RetainsWebConversation (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:611); BrowserJourneyGateTests.QuoteEngine_MakeStudioAgent_RestoresSignedCustomerConversation (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:1278); BrowserJourneyGateTests.QuoteEngine_MakeStudioAgent_LoginRedirectRestoresActiveChat (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:1384); BrowserJourneyGateTests.Web_MaliChatbot_AnonymousVisitorReceivesAssistantReplyThroughWebBff (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:6251)
+2026-06-23 browser-suite failure batch: 14 failed, 42 passed, 0 skipped, 56 total.
+TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx.
+- QuoteEngine_CustomerChatbotWindow_RetainsWebConversation: Microsoft.Playwright.PlaywrightException : Locator expected to be visible Error: element(s) not found Call log: - Expect "ToBeVisibleAsync" with timeout 30000ms - waiting for Locator(".topbar-chat-toggle")
+- Web_CustomerChatbot_LoginPromptContinuesAuthenticatedConversationInPlace: Microsoft.Playwright.PlaywrightException : Locator expected to be visible Error: element(s) not found Call log: - Expect "ToBeVisibleAsync" with timeout 30000ms - waiting for Locator(".topbar-chat-toggle")</x:v>
       </x:c>
       <x:c r="Q22" s="51" t="str">
         <x:v>Maliev.Web.Bff; Maliev.QuoteEngine.Bff; Maliev.ChatbotService; Redis (chatbot session lock); AuthService and CustomerService for signed-in personalization.</x:v>
@@ -2439,10 +2478,12 @@
         <x:v>Anonymous chatbot session for visitors.; Customer-scoped chatbot session/history for signed-in customers.; Browser-local personalization record.; Shared assistant-session cookie used for Web to QuoteEngine continuation.</x:v>
       </x:c>
       <x:c r="S22" s="51" t="str">
-        <x:v>Define anonymous vs. signed conversation retention, define tool-callable account/quote/order/profile/address surfaces that Mali and Make Studio should and should not invoke, broaden Make Studio agent E2E coverage from conversation restoration into DFM, corrected reupload, quote/order/payment, and finalize product-side abuse limits.</x:v>
+        <x:v>Define anonymous vs. signed conversation retention, define tool-callable account/quote/order/profile/address surfaces that Mali and Make Studio should and should not invoke, broaden Make Studio agent E2E coverage from conversation restoration into DFM, corrected reupload, quote/order/payment, and finalize product-side abuse limits.
+Latest browser-suite failure(s): QuoteEngine_CustomerChatbotWindow_RetainsWebConversation; Web_CustomerChatbot_LoginPromptContinuesAuthenticatedConversationInPlace</x:v>
       </x:c>
       <x:c r="T22" s="51" t="str">
-        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:803; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs</x:v>
+        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:803; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs
+Aspire E2E TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx</x:v>
       </x:c>
       <x:c r="U22" s="52" t="str">
         <x:v>2026-06-23</x:v>
@@ -2471,7 +2512,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R350e435724e2432f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re65d2b30ed15431e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2588,16 +2629,16 @@
         <x:v>Ready to automate</x:v>
       </x:c>
       <x:c r="G2" s="48" t="str">
-        <x:v>Automated coverage declared</x:v>
+        <x:v>Failed</x:v>
       </x:c>
       <x:c r="H2" s="48" t="str">
-        <x:v>No current error logged</x:v>
+        <x:v>Failed in latest browser suite</x:v>
       </x:c>
       <x:c r="I2" s="48" t="str">
-        <x:v>N/A</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J2" s="48" t="str">
-        <x:v>Passed</x:v>
+        <x:v>Needs retest loop</x:v>
       </x:c>
       <x:c r="K2" s="48" t="str">
         <x:v>P2</x:v>
@@ -2615,7 +2656,10 @@
         <x:v>api/v{version:apiVersion}/[controller] (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:16); GET api/v{version:apiVersion}/[controller]/accounts-tree (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:29); GET api/v{version:apiVersion}/[controller]/journal-entries (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:42); POST api/v{version:apiVersion}/[controller]/journal-entries (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:60); POST api/v{version:apiVersion}/[controller]/journal-entries/{id:guid}/post (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:71)</x:v>
       </x:c>
       <x:c r="P2" s="48" t="str">
-        <x:v>BrowserJourneyGateTests.Commerce_EmployeePublishesProduct_WebCustomerCanBrowseCartAndArchivedProductIsHidden (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:741); BrowserJourneyGateTests.Intranet_AutomationEmployee_ModuleRoutesRenderWithoutAuthOrStartupFailures (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:4221)</x:v>
+        <x:v>BrowserJourneyGateTests.Commerce_EmployeePublishesProduct_WebCustomerCanBrowseCartAndArchivedProductIsHidden (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:741); BrowserJourneyGateTests.Intranet_AutomationEmployee_ModuleRoutesRenderWithoutAuthOrStartupFailures (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:4221)
+2026-06-23 browser-suite failure batch: 14 failed, 42 passed, 0 skipped, 56 total.
+TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx.
+- Commerce_EmployeePublishesProduct_WebCustomerCanBrowseCartAndArchivedProductIsHidden: System.TimeoutException : Timeout 30000ms exceeded. Call log: - waiting for GetByRole(AriaRole.Button, new() { NameRegex = new Regex("Continue to checkout|ดำเนินการชำระเงิน", RegexOptions.IgnoreCase) })</x:v>
       </x:c>
       <x:c r="Q2" s="48" t="str">
         <x:v>Maliev.Intranet.Bff; CommerceService; UploadService if media uses upload service</x:v>
@@ -2624,10 +2668,12 @@
         <x:v>Product record.; Variant records.; Media references.</x:v>
       </x:c>
       <x:c r="S2" s="48" t="str">
-        <x:v>Media upload behavior should be included once final media storage path is fixed.</x:v>
+        <x:v>Media upload behavior should be included once final media storage path is fixed.
+Latest browser-suite failure(s): Commerce_EmployeePublishesProduct_WebCustomerCanBrowseCartAndArchivedProductIsHidden</x:v>
       </x:c>
       <x:c r="T2" s="48" t="str">
-        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:4136; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs</x:v>
+        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:4136; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs
+Aspire E2E TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx</x:v>
       </x:c>
       <x:c r="U2" s="49" t="str">
         <x:v>2026-06-23</x:v>
@@ -2653,16 +2699,16 @@
         <x:v>Ready to automate</x:v>
       </x:c>
       <x:c r="G3" s="48" t="str">
-        <x:v>Automated coverage declared</x:v>
+        <x:v>Failed</x:v>
       </x:c>
       <x:c r="H3" s="48" t="str">
-        <x:v>No current error logged</x:v>
+        <x:v>Failed in latest browser suite</x:v>
       </x:c>
       <x:c r="I3" s="48" t="str">
-        <x:v>N/A</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J3" s="48" t="str">
-        <x:v>Passed</x:v>
+        <x:v>Needs retest loop</x:v>
       </x:c>
       <x:c r="K3" s="48" t="str">
         <x:v>P2</x:v>
@@ -2680,7 +2726,10 @@
         <x:v>api/v{version:apiVersion}/[controller] (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:16); GET api/v{version:apiVersion}/[controller]/accounts-tree (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:29); GET api/v{version:apiVersion}/[controller]/journal-entries (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:42); POST api/v{version:apiVersion}/[controller]/journal-entries (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:60); POST api/v{version:apiVersion}/[controller]/journal-entries/{id:guid}/post (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:71)</x:v>
       </x:c>
       <x:c r="P3" s="48" t="str">
-        <x:v>BrowserJourneyGateTests.Commerce_EmployeePublishesProduct_WebCustomerCanBrowseCartAndArchivedProductIsHidden (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:741)</x:v>
+        <x:v>BrowserJourneyGateTests.Commerce_EmployeePublishesProduct_WebCustomerCanBrowseCartAndArchivedProductIsHidden (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:741)
+2026-06-23 browser-suite failure batch: 14 failed, 42 passed, 0 skipped, 56 total.
+TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx.
+- Commerce_EmployeePublishesProduct_WebCustomerCanBrowseCartAndArchivedProductIsHidden: System.TimeoutException : Timeout 30000ms exceeded. Call log: - waiting for GetByRole(AriaRole.Button, new() { NameRegex = new Regex("Continue to checkout|ดำเนินการชำระเงิน", RegexOptions.IgnoreCase) })</x:v>
       </x:c>
       <x:c r="Q3" s="48" t="str">
         <x:v>Maliev.Intranet.Bff; CommerceService; Maliev.Web.Bff</x:v>
@@ -2689,10 +2738,12 @@
         <x:v>Product status changes from draft to published.</x:v>
       </x:c>
       <x:c r="S3" s="48" t="str">
-        <x:v>Public storefront caching must invalidate quickly enough for E2E to observe publication.</x:v>
+        <x:v>Public storefront caching must invalidate quickly enough for E2E to observe publication.
+Latest browser-suite failure(s): Commerce_EmployeePublishesProduct_WebCustomerCanBrowseCartAndArchivedProductIsHidden</x:v>
       </x:c>
       <x:c r="T3" s="48" t="str">
-        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:4187; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs</x:v>
+        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:4187; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs
+Aspire E2E TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx</x:v>
       </x:c>
       <x:c r="U3" s="49" t="str">
         <x:v>2026-06-23</x:v>
@@ -2718,16 +2769,16 @@
         <x:v>Ready to automate</x:v>
       </x:c>
       <x:c r="G4" s="48" t="str">
-        <x:v>Automated coverage declared</x:v>
+        <x:v>Failed</x:v>
       </x:c>
       <x:c r="H4" s="48" t="str">
-        <x:v>No current error logged</x:v>
+        <x:v>Failed in latest browser suite</x:v>
       </x:c>
       <x:c r="I4" s="48" t="str">
-        <x:v>N/A</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J4" s="48" t="str">
-        <x:v>Passed</x:v>
+        <x:v>Needs retest loop</x:v>
       </x:c>
       <x:c r="K4" s="48" t="str">
         <x:v>P2</x:v>
@@ -2745,7 +2796,10 @@
         <x:v>api/v{version:apiVersion}/[controller] (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AuthController.cs:20); GET api/v{version:apiVersion}/[controller]/login (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AuthController.cs:27); POST api/v{version:apiVersion}/[controller]/login (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AuthController.cs:41); POST api/v{version:apiVersion}/[controller]/login-form (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AuthController.cs:57); GET api/v{version:apiVersion}/[controller]/logout (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AuthController.cs:198)</x:v>
       </x:c>
       <x:c r="P4" s="48" t="str">
-        <x:v>BrowserJourneyGateTests.Web_PublicAccountSupportAndCommerceEntryPoints_Render (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:241); BrowserJourneyGateTests.Commerce_EmployeePublishesProduct_WebCustomerCanBrowseCartAndArchivedProductIsHidden (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:741)</x:v>
+        <x:v>BrowserJourneyGateTests.Web_PublicAccountSupportAndCommerceEntryPoints_Render (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:241); BrowserJourneyGateTests.Commerce_EmployeePublishesProduct_WebCustomerCanBrowseCartAndArchivedProductIsHidden (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:741)
+2026-06-23 browser-suite failure batch: 14 failed, 42 passed, 0 skipped, 56 total.
+TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx.
+- Commerce_EmployeePublishesProduct_WebCustomerCanBrowseCartAndArchivedProductIsHidden: System.TimeoutException : Timeout 30000ms exceeded. Call log: - waiting for GetByRole(AriaRole.Button, new() { NameRegex = new Regex("Continue to checkout|ดำเนินการชำระเงิน", RegexOptions.IgnoreCase) })</x:v>
       </x:c>
       <x:c r="Q4" s="48" t="str">
         <x:v>Maliev.Web.Bff; CommerceService; OrderService; PaymentService; DeliveryService; CustomerService</x:v>
@@ -2754,10 +2808,12 @@
         <x:v>Cart state.; Checkout/order draft.</x:v>
       </x:c>
       <x:c r="S4" s="48" t="str">
-        <x:v>Final checkout/payment behavior may require separate payment-provider sandbox work.</x:v>
+        <x:v>Final checkout/payment behavior may require separate payment-provider sandbox work.
+Latest browser-suite failure(s): Commerce_EmployeePublishesProduct_WebCustomerCanBrowseCartAndArchivedProductIsHidden</x:v>
       </x:c>
       <x:c r="T4" s="48" t="str">
-        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:4234; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs</x:v>
+        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:4234; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs
+Aspire E2E TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx</x:v>
       </x:c>
       <x:c r="U4" s="49" t="str">
         <x:v>2026-06-23</x:v>
@@ -2783,16 +2839,16 @@
         <x:v>Ready to automate</x:v>
       </x:c>
       <x:c r="G5" s="48" t="str">
-        <x:v>Automated coverage declared</x:v>
+        <x:v>Failed</x:v>
       </x:c>
       <x:c r="H5" s="48" t="str">
-        <x:v>No current error logged</x:v>
+        <x:v>Failed in latest browser suite</x:v>
       </x:c>
       <x:c r="I5" s="48" t="str">
-        <x:v>N/A</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J5" s="48" t="str">
-        <x:v>Passed</x:v>
+        <x:v>Needs retest loop</x:v>
       </x:c>
       <x:c r="K5" s="48" t="str">
         <x:v>P2</x:v>
@@ -2810,7 +2866,10 @@
         <x:v>api/v{version:apiVersion}/[controller] (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:16); GET api/v{version:apiVersion}/[controller]/accounts-tree (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:29); GET api/v{version:apiVersion}/[controller]/journal-entries (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:42); POST api/v{version:apiVersion}/[controller]/journal-entries (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:60); POST api/v{version:apiVersion}/[controller]/journal-entries/{id:guid}/post (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:71)</x:v>
       </x:c>
       <x:c r="P5" s="48" t="str">
-        <x:v>BrowserJourneyGateTests.Commerce_EmployeePublishesProduct_WebCustomerCanBrowseCartAndArchivedProductIsHidden (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:741)</x:v>
+        <x:v>BrowserJourneyGateTests.Commerce_EmployeePublishesProduct_WebCustomerCanBrowseCartAndArchivedProductIsHidden (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:741)
+2026-06-23 browser-suite failure batch: 14 failed, 42 passed, 0 skipped, 56 total.
+TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx.
+- Commerce_EmployeePublishesProduct_WebCustomerCanBrowseCartAndArchivedProductIsHidden: System.TimeoutException : Timeout 30000ms exceeded. Call log: - waiting for GetByRole(AriaRole.Button, new() { NameRegex = new Regex("Continue to checkout|ดำเนินการชำระเงิน", RegexOptions.IgnoreCase) })</x:v>
       </x:c>
       <x:c r="Q5" s="48" t="str">
         <x:v>Maliev.Intranet.Bff; CommerceService; Maliev.Web.Bff</x:v>
@@ -2819,10 +2878,12 @@
         <x:v>Product status changes to archived/unpublished.</x:v>
       </x:c>
       <x:c r="S5" s="48" t="str">
-        <x:v>Define exact customer-facing behavior for old product URLs.</x:v>
+        <x:v>Define exact customer-facing behavior for old product URLs.
+Latest browser-suite failure(s): Commerce_EmployeePublishesProduct_WebCustomerCanBrowseCartAndArchivedProductIsHidden</x:v>
       </x:c>
       <x:c r="T5" s="48" t="str">
-        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:4286; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs</x:v>
+        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:4286; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs
+Aspire E2E TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx</x:v>
       </x:c>
       <x:c r="U5" s="49" t="str">
         <x:v>2026-06-23</x:v>
@@ -2913,13 +2974,13 @@
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="G7" s="48" t="str">
-        <x:v>Automated coverage declared</x:v>
+        <x:v>Failed</x:v>
       </x:c>
       <x:c r="H7" s="48" t="str">
-        <x:v>No current error logged</x:v>
+        <x:v>Failed in latest browser suite</x:v>
       </x:c>
       <x:c r="I7" s="48" t="str">
-        <x:v>In progress</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J7" s="48" t="str">
         <x:v>Needs retest loop</x:v>
@@ -2940,7 +3001,10 @@
         <x:v>api/v{version:apiVersion}/[controller] (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:16); GET api/v{version:apiVersion}/[controller]/accounts-tree (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:29); GET api/v{version:apiVersion}/[controller]/journal-entries (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:42); POST api/v{version:apiVersion}/[controller]/journal-entries (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:60); POST api/v{version:apiVersion}/[controller]/journal-entries/{id:guid}/post (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:71)</x:v>
       </x:c>
       <x:c r="P7" s="48" t="str">
-        <x:v>BrowserJourneyGateTests.Intranet_AutomationEmployee_ModuleRoutesRenderWithoutAuthOrStartupFailures (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:4221); BrowserJourneyGateTests.Intranet_FinanceInvoice_CreatesAttachesAndFinalizesCustomerInvoice (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:4684)</x:v>
+        <x:v>BrowserJourneyGateTests.Intranet_AutomationEmployee_ModuleRoutesRenderWithoutAuthOrStartupFailures (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:4221); BrowserJourneyGateTests.Intranet_FinanceInvoice_CreatesAttachesAndFinalizesCustomerInvoice (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:4684)
+2026-06-23 browser-suite failure batch: 14 failed, 42 passed, 0 skipped, 56 total.
+TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx.
+- Intranet_FinanceInvoice_CreatesAttachesAndFinalizesCustomerInvoice: Microsoft.Playwright.PlaywrightException : Locator expected to contain text 'Pending Pdf' But was: ' Reconnecting to your workspace Keeping your page in place. This usually takes a moment. Attempting for 0s Still trying to reconnect The page is safe. Try re...</x:v>
       </x:c>
       <x:c r="Q7" s="48" t="str">
         <x:v>Maliev.Intranet.Bff; InvoiceService; CustomerService; OrderService; UploadService; PdfService; AccountingService; NotificationService</x:v>
@@ -2949,10 +3013,12 @@
         <x:v>Invoice draft/issued record.; Invoice line items.; Attachment artifact references.; PDF artifact.; Accounting entry where implemented.</x:v>
       </x:c>
       <x:c r="S7" s="48" t="str">
-        <x:v>Define whether customer-facing invoice delivery happens through Web, QuoteEngine, email, or a finance-only process.</x:v>
+        <x:v>Define whether customer-facing invoice delivery happens through Web, QuoteEngine, email, or a finance-only process.
+Latest browser-suite failure(s): Intranet_FinanceInvoice_CreatesAttachesAndFinalizesCustomerInvoice</x:v>
       </x:c>
       <x:c r="T7" s="48" t="str">
-        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:4612; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs</x:v>
+        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:4612; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs
+Aspire E2E TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx</x:v>
       </x:c>
       <x:c r="U7" s="49" t="str">
         <x:v>2026-06-23</x:v>
@@ -2978,13 +3044,13 @@
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="G8" s="48" t="str">
-        <x:v>Automated coverage declared</x:v>
+        <x:v>Failed</x:v>
       </x:c>
       <x:c r="H8" s="48" t="str">
-        <x:v>No current error logged</x:v>
+        <x:v>Failed in latest browser suite</x:v>
       </x:c>
       <x:c r="I8" s="48" t="str">
-        <x:v>In progress</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J8" s="48" t="str">
         <x:v>Needs retest loop</x:v>
@@ -3005,7 +3071,10 @@
         <x:v>api/v{version:apiVersion}/[controller] (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:16); GET api/v{version:apiVersion}/[controller]/accounts-tree (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:29); GET api/v{version:apiVersion}/[controller]/journal-entries (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:42); POST api/v{version:apiVersion}/[controller]/journal-entries (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:60); POST api/v{version:apiVersion}/[controller]/journal-entries/{id:guid}/post (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:71)</x:v>
       </x:c>
       <x:c r="P8" s="48" t="str">
-        <x:v>BrowserJourneyGateTests.Intranet_AutomationEmployee_ModuleRoutesRenderWithoutAuthOrStartupFailures (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:4221); BrowserJourneyGateTests.Intranet_FinanceInvoice_CreatesAttachesAndFinalizesCustomerInvoice (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:4684)</x:v>
+        <x:v>BrowserJourneyGateTests.Intranet_AutomationEmployee_ModuleRoutesRenderWithoutAuthOrStartupFailures (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:4221); BrowserJourneyGateTests.Intranet_FinanceInvoice_CreatesAttachesAndFinalizesCustomerInvoice (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:4684)
+2026-06-23 browser-suite failure batch: 14 failed, 42 passed, 0 skipped, 56 total.
+TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx.
+- Intranet_FinanceInvoice_CreatesAttachesAndFinalizesCustomerInvoice: Microsoft.Playwright.PlaywrightException : Locator expected to contain text 'Pending Pdf' But was: ' Reconnecting to your workspace Keeping your page in place. This usually takes a moment. Attempting for 0s Still trying to reconnect The page is safe. Try re...</x:v>
       </x:c>
       <x:c r="Q8" s="48" t="str">
         <x:v>Maliev.Intranet.Bff; InvoiceService; PaymentService; PdfService; AccountingService; OrderService; UploadService; NotificationService</x:v>
@@ -3014,10 +3083,12 @@
         <x:v>Payment record/status.; Invoice status.; Receipt PDF/artifact.; Payment evidence artifact.; Accounting entry.; Notification record where configured.</x:v>
       </x:c>
       <x:c r="S8" s="48" t="str">
-        <x:v>Define correction/refund rules and the source of truth between InvoiceService and PaymentService.</x:v>
+        <x:v>Define correction/refund rules and the source of truth between InvoiceService and PaymentService.
+Latest browser-suite failure(s): Intranet_FinanceInvoice_CreatesAttachesAndFinalizesCustomerInvoice</x:v>
       </x:c>
       <x:c r="T8" s="48" t="str">
-        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:4677; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs</x:v>
+        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:4677; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs
+Aspire E2E TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx</x:v>
       </x:c>
       <x:c r="U8" s="49" t="str">
         <x:v>2026-06-23</x:v>
@@ -3693,16 +3764,16 @@
         <x:v>Ready to automate</x:v>
       </x:c>
       <x:c r="G19" s="48" t="str">
-        <x:v>Automated coverage declared</x:v>
+        <x:v>Failed</x:v>
       </x:c>
       <x:c r="H19" s="48" t="str">
-        <x:v>No current error logged</x:v>
+        <x:v>Failed in latest browser suite</x:v>
       </x:c>
       <x:c r="I19" s="48" t="str">
-        <x:v>N/A</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J19" s="48" t="str">
-        <x:v>Passed</x:v>
+        <x:v>Needs retest loop</x:v>
       </x:c>
       <x:c r="K19" s="48" t="str">
         <x:v>P1</x:v>
@@ -3720,7 +3791,11 @@
         <x:v>api/v{version:apiVersion}/[controller] (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:16); GET api/v{version:apiVersion}/[controller]/accounts-tree (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:29); GET api/v{version:apiVersion}/[controller]/journal-entries (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:42); POST api/v{version:apiVersion}/[controller]/journal-entries (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:60); POST api/v{version:apiVersion}/[controller]/journal-entries/{id:guid}/post (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:71)</x:v>
       </x:c>
       <x:c r="P19" s="48" t="str">
-        <x:v>BrowserJourneyGateTests.Intranet_AutomationEmployee_ModuleRoutesRenderWithoutAuthOrStartupFailures (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:4221); BrowserJourneyGateTests.Intranet_EmployeeCreatedCustomer_CanBeOpenedAndSelectedInProjectWorkspace (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:5529); BrowserJourneyGateTests.Intranet_CustomerOnboardingUi_CreatesCompanyAddressesAndInternalNote (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:5871); BrowserJourneyGateTests.Intranet_CustomerDetail_EditsProfilePaymentTermsAndAddress (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:6008); BrowserJourneyGateTests.Intranet_GlobalSearch_ReturnsEmployeeCreatedCustomerAndNavigatesToRecord (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:6208)</x:v>
+        <x:v>BrowserJourneyGateTests.Intranet_AutomationEmployee_ModuleRoutesRenderWithoutAuthOrStartupFailures (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:4221); BrowserJourneyGateTests.Intranet_EmployeeCreatedCustomer_CanBeOpenedAndSelectedInProjectWorkspace (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:5529); BrowserJourneyGateTests.Intranet_CustomerOnboardingUi_CreatesCompanyAddressesAndInternalNote (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:5871); BrowserJourneyGateTests.Intranet_CustomerDetail_EditsProfilePaymentTermsAndAddress (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:6008); BrowserJourneyGateTests.Intranet_GlobalSearch_ReturnsEmployeeCreatedCustomerAndNavigatesToRecord (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:6208)
+2026-06-23 browser-suite failure batch: 14 failed, 42 passed, 0 skipped, 56 total.
+TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx.
+- Intranet_GlobalSearch_ReturnsEmployeeCreatedCustomerAndNavigatesToRecord: Expected a customer search result but got resource type ''.
+- Intranet_EmployeeCreatedCustomer_CanBeOpenedAndSelectedInProjectWorkspace: Microsoft.Playwright.PlaywrightException : Locator expected to contain text 'Quote Total' But was: ' Reconnecting to your workspace Keeping your page in place. This usually takes a moment. Attempting for 0s Still trying to reconnect The page is safe. Try re...</x:v>
       </x:c>
       <x:c r="Q19" s="48" t="str">
         <x:v>Maliev.Intranet.Bff; CustomerService; CountryService; UploadService; SearchService</x:v>
@@ -3729,10 +3804,12 @@
         <x:v>Customer profile fields.; Payment terms.; Address/document records.; Search index data.</x:v>
       </x:c>
       <x:c r="S19" s="48" t="str">
-        <x:v>Missing UI affordances should be tracked rather than bypassed with direct API calls.</x:v>
+        <x:v>Missing UI affordances should be tracked rather than bypassed with direct API calls.
+Latest browser-suite failure(s): Intranet_GlobalSearch_ReturnsEmployeeCreatedCustomerAndNavigatesToRecord; Intranet_EmployeeCreatedCustomer_CanBeOpenedAndSelectedInProjectWorkspace</x:v>
       </x:c>
       <x:c r="T19" s="48" t="str">
-        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:2505; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs</x:v>
+        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:2505; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs
+Aspire E2E TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx</x:v>
       </x:c>
       <x:c r="U19" s="49" t="str">
         <x:v>2026-06-23</x:v>
@@ -3758,16 +3835,16 @@
         <x:v>Ready to automate</x:v>
       </x:c>
       <x:c r="G20" s="48" t="str">
-        <x:v>Automated coverage declared</x:v>
+        <x:v>Failed</x:v>
       </x:c>
       <x:c r="H20" s="48" t="str">
-        <x:v>No current error logged</x:v>
+        <x:v>Failed in latest browser suite</x:v>
       </x:c>
       <x:c r="I20" s="48" t="str">
-        <x:v>N/A</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J20" s="48" t="str">
-        <x:v>Passed</x:v>
+        <x:v>Needs retest loop</x:v>
       </x:c>
       <x:c r="K20" s="48" t="str">
         <x:v>P1</x:v>
@@ -3785,7 +3862,10 @@
         <x:v>api/v{version:apiVersion}/[controller] (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:16); GET api/v{version:apiVersion}/[controller]/accounts-tree (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:29); GET api/v{version:apiVersion}/[controller]/journal-entries (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:42); POST api/v{version:apiVersion}/[controller]/journal-entries (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:60); POST api/v{version:apiVersion}/[controller]/journal-entries/{id:guid}/post (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:71)</x:v>
       </x:c>
       <x:c r="P20" s="48" t="str">
-        <x:v>BrowserJourneyGateTests.Intranet_EmployeeCreatedCustomer_CanBeOpenedAndSelectedInProjectWorkspace (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:5529); BrowserJourneyGateTests.Intranet_ProjectNew_StlUploadProcessesThroughHiddenInput (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:5567)</x:v>
+        <x:v>BrowserJourneyGateTests.Intranet_EmployeeCreatedCustomer_CanBeOpenedAndSelectedInProjectWorkspace (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:5529); BrowserJourneyGateTests.Intranet_ProjectNew_StlUploadProcessesThroughHiddenInput (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:5567)
+2026-06-23 browser-suite failure batch: 14 failed, 42 passed, 0 skipped, 56 total.
+TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx.
+- Intranet_EmployeeCreatedCustomer_CanBeOpenedAndSelectedInProjectWorkspace: Microsoft.Playwright.PlaywrightException : Locator expected to contain text 'Quote Total' But was: ' Reconnecting to your workspace Keeping your page in place. This usually takes a moment. Attempting for 0s Still trying to reconnect The page is safe. Try re...</x:v>
       </x:c>
       <x:c r="Q20" s="48" t="str">
         <x:v>Maliev.Intranet.Bff; CustomerService; UploadService; GeometryService; MaterialService; PricingService; ProjectService; QuotationService; RabbitMQ</x:v>
@@ -3794,10 +3874,12 @@
         <x:v>Project/draft record.; Uploaded CAD artifact.; Geometry analysis result.; Part configuration.; Pricing result.</x:v>
       </x:c>
       <x:c r="S20" s="48" t="str">
-        <x:v>Any parts still stuck in analyzing state after backend terminal status should fail this story.</x:v>
+        <x:v>Any parts still stuck in analyzing state after backend terminal status should fail this story.
+Latest browser-suite failure(s): Intranet_EmployeeCreatedCustomer_CanBeOpenedAndSelectedInProjectWorkspace</x:v>
       </x:c>
       <x:c r="T20" s="48" t="str">
-        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:2562; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs</x:v>
+        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:2562; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs
+Aspire E2E TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx</x:v>
       </x:c>
       <x:c r="U20" s="49" t="str">
         <x:v>2026-06-23</x:v>
@@ -3823,16 +3905,16 @@
         <x:v>Ready to automate</x:v>
       </x:c>
       <x:c r="G21" s="48" t="str">
-        <x:v>Automated coverage declared</x:v>
+        <x:v>Failed</x:v>
       </x:c>
       <x:c r="H21" s="48" t="str">
-        <x:v>No current error logged</x:v>
+        <x:v>Failed in latest browser suite</x:v>
       </x:c>
       <x:c r="I21" s="48" t="str">
-        <x:v>N/A</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J21" s="48" t="str">
-        <x:v>Passed</x:v>
+        <x:v>Needs retest loop</x:v>
       </x:c>
       <x:c r="K21" s="48" t="str">
         <x:v>P1</x:v>
@@ -3850,7 +3932,10 @@
         <x:v>api/v{version:apiVersion}/[controller] (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:16); GET api/v{version:apiVersion}/[controller]/accounts-tree (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:29); GET api/v{version:apiVersion}/[controller]/journal-entries (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:42); POST api/v{version:apiVersion}/[controller]/journal-entries (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:60); POST api/v{version:apiVersion}/[controller]/journal-entries/{id:guid}/post (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:71)</x:v>
       </x:c>
       <x:c r="P21" s="48" t="str">
-        <x:v>BrowserJourneyGateTests.Intranet_ProjectGeometryRuntime_LoadsAcrossDeviceViewports (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:1056); BrowserJourneyGateTests.Intranet_ProjectNew_StlUploadProcessesThroughHiddenInput (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:5567); BrowserJourneyGateTests.Intranet_ProjectQuoteLifecycle_GeneratesVersionsPdfAcceptanceAndDuplicate (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:5691)</x:v>
+        <x:v>BrowserJourneyGateTests.Intranet_ProjectGeometryRuntime_LoadsAcrossDeviceViewports (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:1056); BrowserJourneyGateTests.Intranet_ProjectNew_StlUploadProcessesThroughHiddenInput (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:5567); BrowserJourneyGateTests.Intranet_ProjectQuoteLifecycle_GeneratesVersionsPdfAcceptanceAndDuplicate (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:5691)
+2026-06-23 browser-suite failure batch: 14 failed, 42 passed, 0 skipped, 56 total.
+TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx.
+- Intranet_ProjectGeometryRuntime_LoadsAcrossDeviceViewports: Assert.False() Failure Expected: False Actual: True</x:v>
       </x:c>
       <x:c r="Q21" s="48" t="str">
         <x:v>Maliev.Intranet.Bff; QuotationService; PdfService; UploadService; ReceiptService as a negative verification boundary; EmployeeService</x:v>
@@ -3859,10 +3944,12 @@
         <x:v>Quotation/document request.; PDF artifact.; Quotation version PDF artifact fields.</x:v>
       </x:c>
       <x:c r="S21" s="48" t="str">
-        <x:v>Missing thumbnails, missing employee identity, or PDF artifact attached only to "latest quote" instead of the exact quotation version should fail this story.</x:v>
+        <x:v>Missing thumbnails, missing employee identity, or PDF artifact attached only to "latest quote" instead of the exact quotation version should fail this story.
+Latest browser-suite failure(s): Intranet_ProjectGeometryRuntime_LoadsAcrossDeviceViewports</x:v>
       </x:c>
       <x:c r="T21" s="48" t="str">
-        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:2631; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs</x:v>
+        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:2631; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs
+Aspire E2E TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx</x:v>
       </x:c>
       <x:c r="U21" s="49" t="str">
         <x:v>2026-06-23</x:v>
@@ -3888,16 +3975,16 @@
         <x:v>Ready to automate</x:v>
       </x:c>
       <x:c r="G22" s="48" t="str">
-        <x:v>Automated coverage declared</x:v>
+        <x:v>Failed</x:v>
       </x:c>
       <x:c r="H22" s="48" t="str">
-        <x:v>No current error logged</x:v>
+        <x:v>Failed in latest browser suite</x:v>
       </x:c>
       <x:c r="I22" s="48" t="str">
-        <x:v>N/A</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J22" s="48" t="str">
-        <x:v>Passed</x:v>
+        <x:v>Needs retest loop</x:v>
       </x:c>
       <x:c r="K22" s="48" t="str">
         <x:v>P1</x:v>
@@ -3915,7 +4002,10 @@
         <x:v>api/v{version:apiVersion}/[controller] (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:16); GET api/v{version:apiVersion}/[controller]/accounts-tree (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:29); GET api/v{version:apiVersion}/[controller]/journal-entries (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:42); POST api/v{version:apiVersion}/[controller]/journal-entries (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:60); POST api/v{version:apiVersion}/[controller]/journal-entries/{id:guid}/post (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:71)</x:v>
       </x:c>
       <x:c r="P22" s="48" t="str">
-        <x:v>BrowserJourneyGateTests.Intranet_ProjectGeometryRuntime_LoadsAcrossDeviceViewports (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:1056); BrowserJourneyGateTests.Intranet_ProjectQuoteLifecycle_GeneratesVersionsPdfAcceptanceAndDuplicate (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:5691)</x:v>
+        <x:v>BrowserJourneyGateTests.Intranet_ProjectGeometryRuntime_LoadsAcrossDeviceViewports (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:1056); BrowserJourneyGateTests.Intranet_ProjectQuoteLifecycle_GeneratesVersionsPdfAcceptanceAndDuplicate (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:5691)
+2026-06-23 browser-suite failure batch: 14 failed, 42 passed, 0 skipped, 56 total.
+TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx.
+- Intranet_ProjectGeometryRuntime_LoadsAcrossDeviceViewports: Assert.False() Failure Expected: False Actual: True</x:v>
       </x:c>
       <x:c r="Q22" s="48" t="str">
         <x:v>Maliev.Intranet.Bff; ProjectService; UploadService; GeometryService; PricingService; MaterialService; QuotationService</x:v>
@@ -3924,10 +4014,12 @@
         <x:v>New project/draft record.; File references to existing artifacts or copied artifacts.; Updated quote/pricing data.; SourceProjectId/SourceProjectNumber linkage.</x:v>
       </x:c>
       <x:c r="S22" s="48" t="str">
-        <x:v>Reorder must preserve artifacts, record source-project linkage, and not force customers/employees to reupload unchanged files.</x:v>
+        <x:v>Reorder must preserve artifacts, record source-project linkage, and not force customers/employees to reupload unchanged files.
+Latest browser-suite failure(s): Intranet_ProjectGeometryRuntime_LoadsAcrossDeviceViewports</x:v>
       </x:c>
       <x:c r="T22" s="48" t="str">
-        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:2689; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs</x:v>
+        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:2689; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs
+Aspire E2E TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx</x:v>
       </x:c>
       <x:c r="U22" s="49" t="str">
         <x:v>2026-06-23</x:v>
@@ -4018,16 +4110,16 @@
         <x:v>Ready to automate</x:v>
       </x:c>
       <x:c r="G24" s="48" t="str">
-        <x:v>Automated coverage declared</x:v>
+        <x:v>Failed</x:v>
       </x:c>
       <x:c r="H24" s="48" t="str">
-        <x:v>No current error logged</x:v>
+        <x:v>Failed in latest browser suite</x:v>
       </x:c>
       <x:c r="I24" s="48" t="str">
-        <x:v>N/A</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J24" s="48" t="str">
-        <x:v>Passed</x:v>
+        <x:v>Needs retest loop</x:v>
       </x:c>
       <x:c r="K24" s="48" t="str">
         <x:v>P1</x:v>
@@ -4045,7 +4137,10 @@
         <x:v>api/v{version:apiVersion}/[controller] (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:16); GET api/v{version:apiVersion}/[controller]/accounts-tree (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:29); GET api/v{version:apiVersion}/[controller]/journal-entries (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:42); POST api/v{version:apiVersion}/[controller]/journal-entries (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:60); POST api/v{version:apiVersion}/[controller]/journal-entries/{id:guid}/post (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:71)</x:v>
       </x:c>
       <x:c r="P24" s="48" t="str">
-        <x:v>BrowserJourneyGateTests.Intranet_FinanceInvoice_CreatesAttachesAndFinalizesCustomerInvoice (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:4684)</x:v>
+        <x:v>BrowserJourneyGateTests.Intranet_FinanceInvoice_CreatesAttachesAndFinalizesCustomerInvoice (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:4684)
+2026-06-23 browser-suite failure batch: 14 failed, 42 passed, 0 skipped, 56 total.
+TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx.
+- Intranet_FinanceInvoice_CreatesAttachesAndFinalizesCustomerInvoice: Microsoft.Playwright.PlaywrightException : Locator expected to contain text 'Pending Pdf' But was: ' Reconnecting to your workspace Keeping your page in place. This usually takes a moment. Attempting for 0s Still trying to reconnect The page is safe. Try re...</x:v>
       </x:c>
       <x:c r="Q24" s="48" t="str">
         <x:v>Maliev.Intranet.Bff; InvoiceService; PaymentService; ReceiptService; PdfService; UploadService; AccountingService; NotificationService</x:v>
@@ -4054,10 +4149,12 @@
         <x:v>Invoice.; Payment record.; Receipt record.; Receipt PDF artifact.; Accounting entry.</x:v>
       </x:c>
       <x:c r="S24" s="48" t="str">
-        <x:v>Payment provider sandbox behavior must be deterministic for E2E.</x:v>
+        <x:v>Payment provider sandbox behavior must be deterministic for E2E.
+Latest browser-suite failure(s): Intranet_FinanceInvoice_CreatesAttachesAndFinalizesCustomerInvoice</x:v>
       </x:c>
       <x:c r="T24" s="48" t="str">
-        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:2805; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs</x:v>
+        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:2805; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs
+Aspire E2E TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx</x:v>
       </x:c>
       <x:c r="U24" s="49" t="str">
         <x:v>2026-06-23</x:v>
@@ -4668,16 +4765,16 @@
         <x:v>Ready to automate</x:v>
       </x:c>
       <x:c r="G34" s="48" t="str">
-        <x:v>Automated coverage declared</x:v>
+        <x:v>Failed</x:v>
       </x:c>
       <x:c r="H34" s="48" t="str">
-        <x:v>No current error logged</x:v>
+        <x:v>Failed in latest browser suite</x:v>
       </x:c>
       <x:c r="I34" s="48" t="str">
-        <x:v>N/A</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J34" s="48" t="str">
-        <x:v>Passed</x:v>
+        <x:v>Needs retest loop</x:v>
       </x:c>
       <x:c r="K34" s="48" t="str">
         <x:v>P1</x:v>
@@ -4695,7 +4792,11 @@
         <x:v>api/v{version:apiVersion}/[controller] (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:16); GET api/v{version:apiVersion}/[controller]/accounts-tree (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:29); GET api/v{version:apiVersion}/[controller]/journal-entries (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:42); POST api/v{version:apiVersion}/[controller]/journal-entries (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:60); POST api/v{version:apiVersion}/[controller]/journal-entries/{id:guid}/post (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:71)</x:v>
       </x:c>
       <x:c r="P34" s="48" t="str">
-        <x:v>BrowserJourneyGateTests.Intranet_ProjectGeometryRuntime_LoadsAcrossDeviceViewports (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:1056); BrowserJourneyGateTests.GeometryRuntime_ExecutesBrowserWorkerAcrossFrontendsAndDeviceViewports (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:1177); BrowserJourneyGateTests.Intranet_ProjectQuoteLifecycle_GeneratesVersionsPdfAcceptanceAndDuplicate (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:5691)</x:v>
+        <x:v>BrowserJourneyGateTests.Intranet_ProjectGeometryRuntime_LoadsAcrossDeviceViewports (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:1056); BrowserJourneyGateTests.GeometryRuntime_ExecutesBrowserWorkerAcrossFrontendsAndDeviceViewports (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:1177); BrowserJourneyGateTests.Intranet_ProjectQuoteLifecycle_GeneratesVersionsPdfAcceptanceAndDuplicate (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:5691)
+2026-06-23 browser-suite failure batch: 14 failed, 42 passed, 0 skipped, 56 total.
+TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx.
+- Intranet_ProjectGeometryRuntime_LoadsAcrossDeviceViewports: Assert.False() Failure Expected: False Actual: True
+- GeometryRuntime_ExecutesBrowserWorkerAcrossFrontendsAndDeviceViewports: Microsoft.Playwright.PlaywrightException : Locator expected to be visible Error: element(s) not found Call log: - Expect "ToBeVisibleAsync" with timeout 30000ms - waiting for GetByRole(AriaRole.Button, new() { Name = "Parts", Exact = true })</x:v>
       </x:c>
       <x:c r="Q34" s="48" t="str">
         <x:v>Maliev.Intranet.Bff; UploadService; GeometryService; ProjectService; RabbitMQ</x:v>
@@ -4704,10 +4805,12 @@
         <x:v>Viewer/thumbnail artifact references.; DFM result.; Drawing attachment artifact.; Part artifact metadata.</x:v>
       </x:c>
       <x:c r="S34" s="48" t="str">
-        <x:v>Add explicit E2E fixtures for multibody/viewer artifact edge cases and attachment authorization.</x:v>
+        <x:v>Add explicit E2E fixtures for multibody/viewer artifact edge cases and attachment authorization.
+Latest browser-suite failure(s): Intranet_ProjectGeometryRuntime_LoadsAcrossDeviceViewports; GeometryRuntime_ExecutesBrowserWorkerAcrossFrontendsAndDeviceViewports</x:v>
       </x:c>
       <x:c r="T34" s="48" t="str">
-        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:3400; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs</x:v>
+        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:3400; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs
+Aspire E2E TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx</x:v>
       </x:c>
       <x:c r="U34" s="49" t="str">
         <x:v>2026-06-23</x:v>
@@ -4798,16 +4901,16 @@
         <x:v>Ready to automate</x:v>
       </x:c>
       <x:c r="G36" s="48" t="str">
-        <x:v>Automated coverage declared</x:v>
+        <x:v>Failed</x:v>
       </x:c>
       <x:c r="H36" s="48" t="str">
-        <x:v>No current error logged</x:v>
+        <x:v>Failed in latest browser suite</x:v>
       </x:c>
       <x:c r="I36" s="48" t="str">
-        <x:v>N/A</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J36" s="48" t="str">
-        <x:v>Passed</x:v>
+        <x:v>Needs retest loop</x:v>
       </x:c>
       <x:c r="K36" s="48" t="str">
         <x:v>P1</x:v>
@@ -4825,7 +4928,11 @@
         <x:v>api/v{version:apiVersion}/[controller] (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:16); GET api/v{version:apiVersion}/[controller]/accounts-tree (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:29); GET api/v{version:apiVersion}/[controller]/journal-entries (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:42); POST api/v{version:apiVersion}/[controller]/journal-entries (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:60); POST api/v{version:apiVersion}/[controller]/journal-entries/{id:guid}/post (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:71)</x:v>
       </x:c>
       <x:c r="P36" s="48" t="str">
-        <x:v>BrowserJourneyGateTests.Intranet_ProjectGeometryRuntime_LoadsAcrossDeviceViewports (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:1056); BrowserJourneyGateTests.GeometryRuntime_ExecutesBrowserWorkerAcrossFrontendsAndDeviceViewports (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:1177)</x:v>
+        <x:v>BrowserJourneyGateTests.Intranet_ProjectGeometryRuntime_LoadsAcrossDeviceViewports (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:1056); BrowserJourneyGateTests.GeometryRuntime_ExecutesBrowserWorkerAcrossFrontendsAndDeviceViewports (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:1177)
+2026-06-23 browser-suite failure batch: 14 failed, 42 passed, 0 skipped, 56 total.
+TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx.
+- Intranet_ProjectGeometryRuntime_LoadsAcrossDeviceViewports: Assert.False() Failure Expected: False Actual: True
+- GeometryRuntime_ExecutesBrowserWorkerAcrossFrontendsAndDeviceViewports: Microsoft.Playwright.PlaywrightException : Locator expected to be visible Error: element(s) not found Call log: - Expect "ToBeVisibleAsync" with timeout 30000ms - waiting for GetByRole(AriaRole.Button, new() { Name = "Parts", Exact = true })</x:v>
       </x:c>
       <x:c r="Q36" s="48" t="str">
         <x:v>Maliev.Intranet.Bff; MaterialService; PricingService; GeometryService; ProjectService</x:v>
@@ -4834,10 +4941,12 @@
         <x:v>Multiple part configurations.; Multiple pricing results.; DFM state for process-sensitive checks.; Draft autosave state.</x:v>
       </x:c>
       <x:c r="S36" s="48" t="str">
-        <x:v>Define preview/undo behavior for large bulk edits if employees need safety before applying changes.</x:v>
+        <x:v>Define preview/undo behavior for large bulk edits if employees need safety before applying changes.
+Latest browser-suite failure(s): Intranet_ProjectGeometryRuntime_LoadsAcrossDeviceViewports; GeometryRuntime_ExecutesBrowserWorkerAcrossFrontendsAndDeviceViewports</x:v>
       </x:c>
       <x:c r="T36" s="48" t="str">
-        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:3520; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs</x:v>
+        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:3520; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs
+Aspire E2E TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx</x:v>
       </x:c>
       <x:c r="U36" s="49" t="str">
         <x:v>2026-06-23</x:v>
@@ -5838,16 +5947,16 @@
         <x:v>Ready to automate</x:v>
       </x:c>
       <x:c r="G52" s="48" t="str">
-        <x:v>Automated coverage declared</x:v>
+        <x:v>Failed</x:v>
       </x:c>
       <x:c r="H52" s="48" t="str">
-        <x:v>No current error logged</x:v>
+        <x:v>Failed in latest browser suite</x:v>
       </x:c>
       <x:c r="I52" s="48" t="str">
-        <x:v>N/A</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J52" s="48" t="str">
-        <x:v>Passed</x:v>
+        <x:v>Needs retest loop</x:v>
       </x:c>
       <x:c r="K52" s="48" t="str">
         <x:v>P2</x:v>
@@ -5865,7 +5974,10 @@
         <x:v>api/v{version:apiVersion}/[controller] (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:16); GET api/v{version:apiVersion}/[controller]/accounts-tree (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:29); GET api/v{version:apiVersion}/[controller]/journal-entries (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:42); POST api/v{version:apiVersion}/[controller]/journal-entries (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:60); POST api/v{version:apiVersion}/[controller]/journal-entries/{id:guid}/post (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:71)</x:v>
       </x:c>
       <x:c r="P52" s="48" t="str">
-        <x:v>BrowserJourneyGateTests.Intranet_AutomationEmployee_SignsInAndReachesProtectedSurfaces (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3887); BrowserJourneyGateTests.Intranet_ReferenceDataWorkbench_ManagesRegistryLocationsAndLoadsReferencePages (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3988); BrowserJourneyGateTests.Intranet_AutomationEmployee_ModuleRoutesRenderWithoutAuthOrStartupFailures (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:4221); BrowserJourneyGateTests.Intranet_GlobalSearch_ReturnsEmployeeCreatedCustomerAndNavigatesToRecord (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:6208)</x:v>
+        <x:v>BrowserJourneyGateTests.Intranet_AutomationEmployee_SignsInAndReachesProtectedSurfaces (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3887); BrowserJourneyGateTests.Intranet_ReferenceDataWorkbench_ManagesRegistryLocationsAndLoadsReferencePages (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3988); BrowserJourneyGateTests.Intranet_AutomationEmployee_ModuleRoutesRenderWithoutAuthOrStartupFailures (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:4221); BrowserJourneyGateTests.Intranet_GlobalSearch_ReturnsEmployeeCreatedCustomerAndNavigatesToRecord (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:6208)
+2026-06-23 browser-suite failure batch: 14 failed, 42 passed, 0 skipped, 56 total.
+TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx.
+- Intranet_GlobalSearch_ReturnsEmployeeCreatedCustomerAndNavigatesToRecord: Expected a customer search result but got resource type ''.</x:v>
       </x:c>
       <x:c r="Q52" s="48" t="str">
         <x:v>Maliev.Intranet.Bff; SearchService; IAMService; Domain services that publish searchable records</x:v>
@@ -5874,10 +5986,12 @@
         <x:v>Search index entries.</x:v>
       </x:c>
       <x:c r="S52" s="48" t="str">
-        <x:v>Missing index coverage for a domain should be logged as product/search backlog.</x:v>
+        <x:v>Missing index coverage for a domain should be logged as product/search backlog.
+Latest browser-suite failure(s): Intranet_GlobalSearch_ReturnsEmployeeCreatedCustomerAndNavigatesToRecord</x:v>
       </x:c>
       <x:c r="T52" s="48" t="str">
-        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:4397; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs</x:v>
+        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:4397; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs
+Aspire E2E TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx</x:v>
       </x:c>
       <x:c r="U52" s="49" t="str">
         <x:v>2026-06-23</x:v>
@@ -5968,13 +6082,13 @@
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="G54" s="48" t="str">
-        <x:v>Automated coverage declared</x:v>
+        <x:v>Failed</x:v>
       </x:c>
       <x:c r="H54" s="48" t="str">
-        <x:v>No current error logged</x:v>
+        <x:v>Failed in latest browser suite</x:v>
       </x:c>
       <x:c r="I54" s="48" t="str">
-        <x:v>In progress</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J54" s="48" t="str">
         <x:v>Needs retest loop</x:v>
@@ -5995,7 +6109,10 @@
         <x:v>api/v{version:apiVersion}/[controller] (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:16); GET api/v{version:apiVersion}/[controller]/accounts-tree (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:29); GET api/v{version:apiVersion}/[controller]/journal-entries (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:42); POST api/v{version:apiVersion}/[controller]/journal-entries (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:60); POST api/v{version:apiVersion}/[controller]/journal-entries/{id:guid}/post (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:71)</x:v>
       </x:c>
       <x:c r="P54" s="48" t="str">
-        <x:v>BrowserJourneyGateTests.Intranet_CustomerNotification_QueuesDeliveryAndRespectsOptOutPreference (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:6126); BrowserJourneyGateTests.Intranet_CustomerEmailTemplatesAndAiExtraction_AreReachable (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:6684)</x:v>
+        <x:v>BrowserJourneyGateTests.Intranet_CustomerNotification_QueuesDeliveryAndRespectsOptOutPreference (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:6126); BrowserJourneyGateTests.Intranet_CustomerEmailTemplatesAndAiExtraction_AreReachable (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:6684)
+2026-06-23 browser-suite failure batch: 14 failed, 42 passed, 0 skipped, 56 total.
+TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx.
+- Intranet_CustomerNotification_QueuesDeliveryAndRespectsOptOutPreference: Expected /api/v1/notifications/preferences/2e9bd85d-4155-44f1-8f03-b013be20b4dd to contain email before timeout. Last result: 503 {"title":"Upstream service unavailable","status":503,"detail":"A downstream service did not respond in time. Please retry later."}</x:v>
       </x:c>
       <x:c r="Q54" s="48" t="str">
         <x:v>Maliev.Intranet.Bff; NotificationService; RabbitMQ; Triggering domain service</x:v>
@@ -6004,10 +6121,12 @@
         <x:v>Notification preference.; Notification delivery/log record.; Read/unread state.</x:v>
       </x:c>
       <x:c r="S54" s="48" t="str">
-        <x:v>Event types without notification mappings should be cataloged. Customer/employee notification center UI, read/unread state, live push surface, external provider sandbox delivery, and low-permission negative notification checks still need product and E2E coverage.</x:v>
+        <x:v>Event types without notification mappings should be cataloged. Customer/employee notification center UI, read/unread state, live push surface, external provider sandbox delivery, and low-permission negative notification checks still need product and E2E coverage.
+Latest browser-suite failure(s): Intranet_CustomerNotification_QueuesDeliveryAndRespectsOptOutPreference</x:v>
       </x:c>
       <x:c r="T54" s="48" t="str">
-        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:4496; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs</x:v>
+        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:4496; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs
+Aspire E2E TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx</x:v>
       </x:c>
       <x:c r="U54" s="49" t="str">
         <x:v>2026-06-23</x:v>
@@ -6553,16 +6672,16 @@
         <x:v>Required production gate. Automate once test hooks can reliably expire sessions.</x:v>
       </x:c>
       <x:c r="G63" s="48" t="str">
-        <x:v>Automated coverage declared</x:v>
+        <x:v>Failed</x:v>
       </x:c>
       <x:c r="H63" s="48" t="str">
-        <x:v>No current error logged</x:v>
+        <x:v>Failed in latest browser suite</x:v>
       </x:c>
       <x:c r="I63" s="48" t="str">
-        <x:v>N/A</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J63" s="48" t="str">
-        <x:v>Passed</x:v>
+        <x:v>Needs retest loop</x:v>
       </x:c>
       <x:c r="K63" s="48" t="str">
         <x:v>P0</x:v>
@@ -6580,7 +6699,10 @@
         <x:v>api/v{version:apiVersion}/[controller] (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:16); GET api/v{version:apiVersion}/[controller]/accounts-tree (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:29); GET api/v{version:apiVersion}/[controller]/journal-entries (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:42); POST api/v{version:apiVersion}/[controller]/journal-entries (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:60); POST api/v{version:apiVersion}/[controller]/journal-entries/{id:guid}/post (Maliev.Intranet/Maliev.Intranet.Bff/Controllers/AccountingController.cs:71)</x:v>
       </x:c>
       <x:c r="P63" s="48" t="str">
-        <x:v>BrowserJourneyGateTests.Web_CustomerChatbot_LoginPromptContinuesAuthenticatedConversationInPlace (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:496); BrowserJourneyGateTests.Web_CustomerAccountSecurity_BlocksCrossCustomerAddressMutationAndPreservesReturnUrl (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:659); BrowserJourneyGateTests.Intranet_ProtectedRoutes_RedirectAnonymousUserToLogin (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3446); BrowserJourneyGateTests.Intranet_AutomationEmployee_SignsInAndReachesProtectedSurfaces (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3887)</x:v>
+        <x:v>BrowserJourneyGateTests.Web_CustomerChatbot_LoginPromptContinuesAuthenticatedConversationInPlace (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:496); BrowserJourneyGateTests.Web_CustomerAccountSecurity_BlocksCrossCustomerAddressMutationAndPreservesReturnUrl (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:659); BrowserJourneyGateTests.Intranet_ProtectedRoutes_RedirectAnonymousUserToLogin (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3446); BrowserJourneyGateTests.Intranet_AutomationEmployee_SignsInAndReachesProtectedSurfaces (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3887)
+2026-06-23 browser-suite failure batch: 14 failed, 42 passed, 0 skipped, 56 total.
+TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx.
+- Web_CustomerChatbot_LoginPromptContinuesAuthenticatedConversationInPlace: Microsoft.Playwright.PlaywrightException : Locator expected to be visible Error: element(s) not found Call log: - Expect "ToBeVisibleAsync" with timeout 30000ms - waiting for Locator(".topbar-chat-toggle")</x:v>
       </x:c>
       <x:c r="Q63" s="48" t="str">
         <x:v>Maliev.Web.Bff; Maliev.QuoteEngine.Bff; Maliev.Intranet.Bff; AuthService; IAMService; Target domain service for the protected page</x:v>
@@ -6589,10 +6711,12 @@
         <x:v>Session/token state.; No domain mutation expected during denied/re-auth redirect unless user explicitly resubmits.</x:v>
       </x:c>
       <x:c r="S63" s="48" t="str">
-        <x:v>Define exact return URL and unsaved-work policies per app.</x:v>
+        <x:v>Define exact return URL and unsaved-work policies per app.
+Latest browser-suite failure(s): Web_CustomerChatbot_LoginPromptContinuesAuthenticatedConversationInPlace</x:v>
       </x:c>
       <x:c r="T63" s="48" t="str">
-        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:5922; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs</x:v>
+        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:5922; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs
+Aspire E2E TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx</x:v>
       </x:c>
       <x:c r="U63" s="49" t="str">
         <x:v>2026-06-23</x:v>
@@ -6686,7 +6810,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4a6eeaa16b574e76"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2afae03a400c4fa6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6803,13 +6927,13 @@
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="G2" s="48" t="str">
-        <x:v>Automated coverage declared</x:v>
+        <x:v>Failed</x:v>
       </x:c>
       <x:c r="H2" s="48" t="str">
-        <x:v>No current error logged</x:v>
+        <x:v>Failed in latest browser suite</x:v>
       </x:c>
       <x:c r="I2" s="48" t="str">
-        <x:v>In progress</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J2" s="48" t="str">
         <x:v>Needs retest loop</x:v>
@@ -6830,7 +6954,11 @@
         <x:v>quote/v{version:apiVersion}/account (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:15); GET quote/v{version:apiVersion}/account/profile (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:46); GET quote/v{version:apiVersion}/account/addresses (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:76); GET quote/v{version:apiVersion}/account/quotes (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:112); GET quote/v{version:apiVersion}/account/orders (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:120)</x:v>
       </x:c>
       <x:c r="P2" s="48" t="str">
-        <x:v>BrowserJourneyGateTests.QuoteEngine_RealProjectMode_BlocksCustomerUploadUntilSignIn (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:1255); BrowserJourneyGateTests.QuoteEngine_MakeStudioAgent_RestoresSignedCustomerConversation (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:1278); BrowserJourneyGateTests.QuoteEngine_MakeStudioAgent_LoginRedirectRestoresActiveChat (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:1384); BrowserJourneyGateTests.QuoteEngine_MakeStudioAgentTools_CorrectsDfmCompletesPaymentAndLinksProductionJob (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:1465); BrowserJourneyGateTests.QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3033)</x:v>
+        <x:v>BrowserJourneyGateTests.QuoteEngine_RealProjectMode_BlocksCustomerUploadUntilSignIn (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:1255); BrowserJourneyGateTests.QuoteEngine_MakeStudioAgent_RestoresSignedCustomerConversation (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:1278); BrowserJourneyGateTests.QuoteEngine_MakeStudioAgent_LoginRedirectRestoresActiveChat (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:1384); BrowserJourneyGateTests.QuoteEngine_MakeStudioAgentTools_CorrectsDfmCompletesPaymentAndLinksProductionJob (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:1465); BrowserJourneyGateTests.QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3033)
+2026-06-23 browser-suite failure batch: 14 failed, 42 passed, 0 skipped, 56 total.
+TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx.
+- QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory: Microsoft.Playwright.PlaywrightException : Locator expected to be visible Call log: - Expect "ToBeVisibleAsync" with timeout 30000ms - waiting for Locator("header.quote-topbar .billing-account-trigger") 28 × locator resolved to &lt;summary class="billing-accou...
+- QuoteEngine_RealProjectMode_BlocksCustomerUploadUntilSignIn: System.TimeoutException : Timeout 30000ms exceeded. =========================== logs =========================== waiting for navigation until "Commit" ============================================================ ---- System.TimeoutException : Timeout 30000m...</x:v>
       </x:c>
       <x:c r="Q2" s="48" t="str">
         <x:v>Maliev.QuoteEngine.Bff; AuthService; CustomerService; ProjectService; QuotationService once a formal quote is generated</x:v>
@@ -6839,10 +6967,12 @@
         <x:v>Customer session.; ProjectService project record in real project mode.; No project record in demo-only mode.</x:v>
       </x:c>
       <x:c r="S2" s="48" t="str">
-        <x:v>Replace prototype workspace persistence with durable ProjectService-backed project create/resume/list behavior.</x:v>
+        <x:v>Replace prototype workspace persistence with durable ProjectService-backed project create/resume/list behavior.
+Latest browser-suite failure(s): QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory; QuoteEngine_RealProjectMode_BlocksCustomerUploadUntilSignIn</x:v>
       </x:c>
       <x:c r="T2" s="48" t="str">
-        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:885; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs</x:v>
+        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:885; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs
+Aspire E2E TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx</x:v>
       </x:c>
       <x:c r="U2" s="49" t="str">
         <x:v>2026-06-23</x:v>
@@ -6868,13 +6998,13 @@
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="G3" s="48" t="str">
-        <x:v>Automated coverage declared</x:v>
+        <x:v>Failed</x:v>
       </x:c>
       <x:c r="H3" s="48" t="str">
-        <x:v>No current error logged</x:v>
+        <x:v>Failed in latest browser suite</x:v>
       </x:c>
       <x:c r="I3" s="48" t="str">
-        <x:v>In progress</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J3" s="48" t="str">
         <x:v>Needs retest loop</x:v>
@@ -6895,7 +7025,13 @@
         <x:v>quote/v{version:apiVersion}/account (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:15); GET quote/v{version:apiVersion}/account/profile (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:46); GET quote/v{version:apiVersion}/account/addresses (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:76); GET quote/v{version:apiVersion}/account/quotes (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:112); GET quote/v{version:apiVersion}/account/orders (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:120)</x:v>
       </x:c>
       <x:c r="P3" s="48" t="str">
-        <x:v>BrowserJourneyGateTests.QuoteEngine_AnonymousDemo_EstimatesWithoutFormalArtifacts (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:896); BrowserJourneyGateTests.QuoteEngine_GeometryRuntime_LoadsAcrossDeviceViewports (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:934); BrowserJourneyGateTests.GeometryRuntime_ExecutesBrowserWorkerAcrossFrontendsAndDeviceViewports (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:1177); BrowserJourneyGateTests.QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3033)</x:v>
+        <x:v>BrowserJourneyGateTests.QuoteEngine_AnonymousDemo_EstimatesWithoutFormalArtifacts (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:896); BrowserJourneyGateTests.QuoteEngine_GeometryRuntime_LoadsAcrossDeviceViewports (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:934); BrowserJourneyGateTests.GeometryRuntime_ExecutesBrowserWorkerAcrossFrontendsAndDeviceViewports (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:1177); BrowserJourneyGateTests.QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3033)
+2026-06-23 browser-suite failure batch: 14 failed, 42 passed, 0 skipped, 56 total.
+TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx.
+- QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory: Microsoft.Playwright.PlaywrightException : Locator expected to be visible Call log: - Expect "ToBeVisibleAsync" with timeout 30000ms - waiting for Locator("header.quote-topbar .billing-account-trigger") 28 × locator resolved to &lt;summary class="billing-accou...
+- QuoteEngine_GeometryRuntime_LoadsAcrossDeviceViewports: Microsoft.Playwright.PlaywrightException : Locator expected to be visible Error: element(s) not found Call log: - Expect "ToBeVisibleAsync" with timeout 30000ms - waiting for GetByRole(AriaRole.Button, new() { Name = "Parts", Exact = true })
+- QuoteEngine_AnonymousDemo_EstimatesWithoutFormalArtifacts: Microsoft.Playwright.PlaywrightException : Locator expected to be visible Error: element(s) not found Call log: - Expect "ToBeVisibleAsync" with timeout 30000ms - waiting for GetByText("Demo only")
+- GeometryRuntime_ExecutesBrowserWorkerAcrossFrontendsAndDeviceViewports: Microsoft.Playwright.PlaywrightException : Locator expected to be visible Error: element(s) not found Call log: - Expect "ToBeVisibleAsync" with timeout 30000ms - waiting for GetByRole(AriaRole.Button, new() { Name = "Parts", Exact = true })</x:v>
       </x:c>
       <x:c r="Q3" s="48" t="str">
         <x:v>Maliev.QuoteEngine.Bff; AuthService; UploadService; GeometryService; RabbitMQ; ProjectService</x:v>
@@ -6904,10 +7040,12 @@
         <x:v>Upload record.; CAD artifact/blob.; Geometry analysis record/status.; Project part record/configuration state.</x:v>
       </x:c>
       <x:c r="S3" s="48" t="str">
-        <x:v>Production QuoteEngine needs the same artifact enrichment rigor expected in the employee project quote workspace.</x:v>
+        <x:v>Production QuoteEngine needs the same artifact enrichment rigor expected in the employee project quote workspace.
+Latest browser-suite failure(s): QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory; QuoteEngine_GeometryRuntime_LoadsAcrossDeviceViewports; QuoteEngine_AnonymousDemo_EstimatesWithoutFormalArtifacts; GeometryRuntime_ExecutesBrowserWorkerAcrossFrontendsAndDeviceViewports</x:v>
       </x:c>
       <x:c r="T3" s="48" t="str">
-        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:948; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs</x:v>
+        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:948; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs
+Aspire E2E TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx</x:v>
       </x:c>
       <x:c r="U3" s="49" t="str">
         <x:v>2026-06-23</x:v>
@@ -6933,13 +7071,13 @@
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="G4" s="48" t="str">
-        <x:v>Automated coverage declared</x:v>
+        <x:v>Failed</x:v>
       </x:c>
       <x:c r="H4" s="48" t="str">
-        <x:v>No current error logged</x:v>
+        <x:v>Failed in latest browser suite</x:v>
       </x:c>
       <x:c r="I4" s="48" t="str">
-        <x:v>In progress</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J4" s="48" t="str">
         <x:v>Needs retest loop</x:v>
@@ -6960,7 +7098,12 @@
         <x:v>quote/v{version:apiVersion}/account (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:15); GET quote/v{version:apiVersion}/account/profile (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:46); GET quote/v{version:apiVersion}/account/addresses (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:76); GET quote/v{version:apiVersion}/account/quotes (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:112); GET quote/v{version:apiVersion}/account/orders (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:120)</x:v>
       </x:c>
       <x:c r="P4" s="48" t="str">
-        <x:v>BrowserJourneyGateTests.QuoteEngine_AnonymousDemo_EstimatesWithoutFormalArtifacts (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:896); BrowserJourneyGateTests.QuoteEngine_GeometryRuntime_LoadsAcrossDeviceViewports (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:934); BrowserJourneyGateTests.QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3033)</x:v>
+        <x:v>BrowserJourneyGateTests.QuoteEngine_AnonymousDemo_EstimatesWithoutFormalArtifacts (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:896); BrowserJourneyGateTests.QuoteEngine_GeometryRuntime_LoadsAcrossDeviceViewports (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:934); BrowserJourneyGateTests.QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3033)
+2026-06-23 browser-suite failure batch: 14 failed, 42 passed, 0 skipped, 56 total.
+TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx.
+- QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory: Microsoft.Playwright.PlaywrightException : Locator expected to be visible Call log: - Expect "ToBeVisibleAsync" with timeout 30000ms - waiting for Locator("header.quote-topbar .billing-account-trigger") 28 × locator resolved to &lt;summary class="billing-accou...
+- QuoteEngine_GeometryRuntime_LoadsAcrossDeviceViewports: Microsoft.Playwright.PlaywrightException : Locator expected to be visible Error: element(s) not found Call log: - Expect "ToBeVisibleAsync" with timeout 30000ms - waiting for GetByRole(AriaRole.Button, new() { Name = "Parts", Exact = true })
+- QuoteEngine_AnonymousDemo_EstimatesWithoutFormalArtifacts: Microsoft.Playwright.PlaywrightException : Locator expected to be visible Error: element(s) not found Call log: - Expect "ToBeVisibleAsync" with timeout 30000ms - waiting for GetByText("Demo only")</x:v>
       </x:c>
       <x:c r="Q4" s="48" t="str">
         <x:v>Maliev.QuoteEngine.Bff; MaterialService; PricingService; ProjectService; DeliveryService if delivery option affects quote</x:v>
@@ -6969,10 +7112,12 @@
         <x:v>Part configuration.; Pricing request/response.; Project pricing state and quote-ready totals.</x:v>
       </x:c>
       <x:c r="S4" s="48" t="str">
-        <x:v>QuoteEngine must call real MaterialService, PricingService, and ProjectService for production. Prototype pricing cannot pass this story.</x:v>
+        <x:v>QuoteEngine must call real MaterialService, PricingService, and ProjectService for production. Prototype pricing cannot pass this story.
+Latest browser-suite failure(s): QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory; QuoteEngine_GeometryRuntime_LoadsAcrossDeviceViewports; QuoteEngine_AnonymousDemo_EstimatesWithoutFormalArtifacts</x:v>
       </x:c>
       <x:c r="T4" s="48" t="str">
-        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:1014; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs</x:v>
+        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:1014; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs
+Aspire E2E TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx</x:v>
       </x:c>
       <x:c r="U4" s="49" t="str">
         <x:v>2026-06-23</x:v>
@@ -6998,13 +7143,13 @@
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="G5" s="48" t="str">
-        <x:v>Automated coverage declared</x:v>
+        <x:v>Failed</x:v>
       </x:c>
       <x:c r="H5" s="48" t="str">
-        <x:v>No current error logged</x:v>
+        <x:v>Failed in latest browser suite</x:v>
       </x:c>
       <x:c r="I5" s="48" t="str">
-        <x:v>In progress</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J5" s="48" t="str">
         <x:v>Needs retest loop</x:v>
@@ -7025,7 +7170,10 @@
         <x:v>quote/v{version:apiVersion}/account (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:15); GET quote/v{version:apiVersion}/account/profile (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:46); GET quote/v{version:apiVersion}/account/addresses (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:76); GET quote/v{version:apiVersion}/account/quotes (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:112); GET quote/v{version:apiVersion}/account/orders (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:120)</x:v>
       </x:c>
       <x:c r="P5" s="48" t="str">
-        <x:v>BrowserJourneyGateTests.QuoteEngine_AnonymousDemo_EstimatesWithoutFormalArtifacts (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:896); BrowserJourneyGateTests.QuoteEngine_MakeStudioAgentTools_CorrectsDfmCompletesPaymentAndLinksProductionJob (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:1465)</x:v>
+        <x:v>BrowserJourneyGateTests.QuoteEngine_AnonymousDemo_EstimatesWithoutFormalArtifacts (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:896); BrowserJourneyGateTests.QuoteEngine_MakeStudioAgentTools_CorrectsDfmCompletesPaymentAndLinksProductionJob (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:1465)
+2026-06-23 browser-suite failure batch: 14 failed, 42 passed, 0 skipped, 56 total.
+TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx.
+- QuoteEngine_AnonymousDemo_EstimatesWithoutFormalArtifacts: Microsoft.Playwright.PlaywrightException : Locator expected to be visible Error: element(s) not found Call log: - Expect "ToBeVisibleAsync" with timeout 30000ms - waiting for GetByText("Demo only")</x:v>
       </x:c>
       <x:c r="Q5" s="48" t="str">
         <x:v>Maliev.QuoteEngine.Bff; UploadService; GeometryService; PricingService; RabbitMQ</x:v>
@@ -7034,10 +7182,12 @@
         <x:v>New upload artifact or updated part configuration.; New geometry/DFM result.; Updated price.</x:v>
       </x:c>
       <x:c r="S5" s="48" t="str">
-        <x:v>QuoteEngine must implement project-part revision-aware upload and analysis state before this can be production-gate ready.</x:v>
+        <x:v>QuoteEngine must implement project-part revision-aware upload and analysis state before this can be production-gate ready.
+Latest browser-suite failure(s): QuoteEngine_AnonymousDemo_EstimatesWithoutFormalArtifacts</x:v>
       </x:c>
       <x:c r="T5" s="48" t="str">
-        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:1072; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs</x:v>
+        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:1072; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs
+Aspire E2E TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx</x:v>
       </x:c>
       <x:c r="U5" s="49" t="str">
         <x:v>2026-06-23</x:v>
@@ -7063,13 +7213,13 @@
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="G6" s="48" t="str">
-        <x:v>Automated coverage declared</x:v>
+        <x:v>Failed</x:v>
       </x:c>
       <x:c r="H6" s="48" t="str">
-        <x:v>No current error logged</x:v>
+        <x:v>Failed in latest browser suite</x:v>
       </x:c>
       <x:c r="I6" s="48" t="str">
-        <x:v>In progress</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J6" s="48" t="str">
         <x:v>Needs retest loop</x:v>
@@ -7090,7 +7240,11 @@
         <x:v>quote/v{version:apiVersion}/account (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:15); GET quote/v{version:apiVersion}/account/profile (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:46); GET quote/v{version:apiVersion}/account/addresses (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:76); GET quote/v{version:apiVersion}/account/quotes (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:112); GET quote/v{version:apiVersion}/account/orders (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:120)</x:v>
       </x:c>
       <x:c r="P6" s="48" t="str">
-        <x:v>BrowserJourneyGateTests.QuoteEngine_RealProjectMode_BlocksCustomerUploadUntilSignIn (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:1255); BrowserJourneyGateTests.QuoteEngine_MakeStudioAgent_RestoresSignedCustomerConversation (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:1278); BrowserJourneyGateTests.QuoteEngine_MakeStudioAgent_LoginRedirectRestoresActiveChat (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:1384); BrowserJourneyGateTests.QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3033)</x:v>
+        <x:v>BrowserJourneyGateTests.QuoteEngine_RealProjectMode_BlocksCustomerUploadUntilSignIn (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:1255); BrowserJourneyGateTests.QuoteEngine_MakeStudioAgent_RestoresSignedCustomerConversation (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:1278); BrowserJourneyGateTests.QuoteEngine_MakeStudioAgent_LoginRedirectRestoresActiveChat (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:1384); BrowserJourneyGateTests.QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3033)
+2026-06-23 browser-suite failure batch: 14 failed, 42 passed, 0 skipped, 56 total.
+TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx.
+- QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory: Microsoft.Playwright.PlaywrightException : Locator expected to be visible Call log: - Expect "ToBeVisibleAsync" with timeout 30000ms - waiting for Locator("header.quote-topbar .billing-account-trigger") 28 × locator resolved to &lt;summary class="billing-accou...
+- QuoteEngine_RealProjectMode_BlocksCustomerUploadUntilSignIn: System.TimeoutException : Timeout 30000ms exceeded. =========================== logs =========================== waiting for navigation until "Commit" ============================================================ ---- System.TimeoutException : Timeout 30000m...</x:v>
       </x:c>
       <x:c r="Q6" s="48" t="str">
         <x:v>Maliev.QuoteEngine.Bff; AuthService; CustomerService; IAMService; ProjectService</x:v>
@@ -7099,10 +7253,12 @@
         <x:v>Customer session.; Real ProjectService project only after explicit signed-in start.; Optional new customer account.; No mutation from demo-only usage.</x:v>
       </x:c>
       <x:c r="S6" s="48" t="str">
-        <x:v>Define whether any demo configuration can be copied into a real project. If yes, it must be explicit and backed by secure server-side customer identity.</x:v>
+        <x:v>Define whether any demo configuration can be copied into a real project. If yes, it must be explicit and backed by secure server-side customer identity.
+Latest browser-suite failure(s): QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory; QuoteEngine_RealProjectMode_BlocksCustomerUploadUntilSignIn</x:v>
       </x:c>
       <x:c r="T6" s="48" t="str">
-        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:1124; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs</x:v>
+        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:1124; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs
+Aspire E2E TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx</x:v>
       </x:c>
       <x:c r="U6" s="49" t="str">
         <x:v>2026-06-23</x:v>
@@ -7128,13 +7284,13 @@
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="G7" s="48" t="str">
-        <x:v>Automated coverage declared</x:v>
+        <x:v>Failed</x:v>
       </x:c>
       <x:c r="H7" s="48" t="str">
-        <x:v>No current error logged</x:v>
+        <x:v>Failed in latest browser suite</x:v>
       </x:c>
       <x:c r="I7" s="48" t="str">
-        <x:v>In progress</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J7" s="48" t="str">
         <x:v>Needs retest loop</x:v>
@@ -7155,7 +7311,10 @@
         <x:v>quote/v{version:apiVersion}/account (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:15); GET quote/v{version:apiVersion}/account/profile (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:46); GET quote/v{version:apiVersion}/account/addresses (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:76); GET quote/v{version:apiVersion}/account/quotes (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:112); GET quote/v{version:apiVersion}/account/orders (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:120)</x:v>
       </x:c>
       <x:c r="P7" s="48" t="str">
-        <x:v>BrowserJourneyGateTests.QuoteEngine_MakeStudioAgentTools_CorrectsDfmCompletesPaymentAndLinksProductionJob (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:1465); BrowserJourneyGateTests.QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3033)</x:v>
+        <x:v>BrowserJourneyGateTests.QuoteEngine_MakeStudioAgentTools_CorrectsDfmCompletesPaymentAndLinksProductionJob (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:1465); BrowserJourneyGateTests.QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3033)
+2026-06-23 browser-suite failure batch: 14 failed, 42 passed, 0 skipped, 56 total.
+TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx.
+- QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory: Microsoft.Playwright.PlaywrightException : Locator expected to be visible Call log: - Expect "ToBeVisibleAsync" with timeout 30000ms - waiting for Locator("header.quote-topbar .billing-account-trigger") 28 × locator resolved to &lt;summary class="billing-accou...</x:v>
       </x:c>
       <x:c r="Q7" s="48" t="str">
         <x:v>Maliev.QuoteEngine.Bff; ProjectService; QuotationService; PdfService; UploadService; CustomerService; NotificationService if employee/customer alerts are sent</x:v>
@@ -7164,10 +7323,12 @@
         <x:v>Quotation record if first quote for project.; New immutable QuotationVersion on the project's quotation.; Project snapshot JSON/hash.; Generated PDF artifact attached to the exact version.; Optional notification record.</x:v>
       </x:c>
       <x:c r="S7" s="48" t="str">
-        <x:v>QuoteEngine must connect to real ProjectService -&gt; QuotationService -&gt; PdfService path. Prototype PDF behavior is not sufficient.</x:v>
+        <x:v>QuoteEngine must connect to real ProjectService -&gt; QuotationService -&gt; PdfService path. Prototype PDF behavior is not sufficient.
+Latest browser-suite failure(s): QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory</x:v>
       </x:c>
       <x:c r="T7" s="48" t="str">
-        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:1180; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs</x:v>
+        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:1180; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs
+Aspire E2E TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx</x:v>
       </x:c>
       <x:c r="U7" s="49" t="str">
         <x:v>2026-06-23</x:v>
@@ -7193,13 +7354,13 @@
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="G8" s="48" t="str">
-        <x:v>Automated coverage declared</x:v>
+        <x:v>Failed</x:v>
       </x:c>
       <x:c r="H8" s="48" t="str">
-        <x:v>No current error logged</x:v>
+        <x:v>Failed in latest browser suite</x:v>
       </x:c>
       <x:c r="I8" s="48" t="str">
-        <x:v>In progress</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J8" s="48" t="str">
         <x:v>Needs retest loop</x:v>
@@ -7220,7 +7381,10 @@
         <x:v>quote/v{version:apiVersion}/account (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:15); GET quote/v{version:apiVersion}/account/profile (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:46); GET quote/v{version:apiVersion}/account/addresses (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:76); GET quote/v{version:apiVersion}/account/quotes (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:112); GET quote/v{version:apiVersion}/account/orders (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:120)</x:v>
       </x:c>
       <x:c r="P8" s="48" t="str">
-        <x:v>BrowserJourneyGateTests.QuoteEngine_MakeStudioAgentTools_CorrectsDfmCompletesPaymentAndLinksProductionJob (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:1465); BrowserJourneyGateTests.QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3033)</x:v>
+        <x:v>BrowserJourneyGateTests.QuoteEngine_MakeStudioAgentTools_CorrectsDfmCompletesPaymentAndLinksProductionJob (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:1465); BrowserJourneyGateTests.QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3033)
+2026-06-23 browser-suite failure batch: 14 failed, 42 passed, 0 skipped, 56 total.
+TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx.
+- QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory: Microsoft.Playwright.PlaywrightException : Locator expected to be visible Call log: - Expect "ToBeVisibleAsync" with timeout 30000ms - waiting for Locator("header.quote-topbar .billing-account-trigger") 28 × locator resolved to &lt;summary class="billing-accou...</x:v>
       </x:c>
       <x:c r="Q8" s="48" t="str">
         <x:v>Maliev.QuoteEngine.Bff; QuotationService; OrderService; PaymentService; DeliveryService; CustomerService; JobService or ProjectService where production handoff is owned</x:v>
@@ -7229,10 +7393,12 @@
         <x:v>Accepted quotation version state.; Accepted quotation version id/number.; Order record.; Payment intent/record.; Delivery record.; Optional job/production record.</x:v>
       </x:c>
       <x:c r="S8" s="48" t="str">
-        <x:v>End-to-end quote-version acceptance from QuoteEngine must be service-backed before production.</x:v>
+        <x:v>End-to-end quote-version acceptance from QuoteEngine must be service-backed before production.
+Latest browser-suite failure(s): QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory</x:v>
       </x:c>
       <x:c r="T8" s="48" t="str">
-        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:1245; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs</x:v>
+        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:1245; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs
+Aspire E2E TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx</x:v>
       </x:c>
       <x:c r="U8" s="49" t="str">
         <x:v>2026-06-23</x:v>
@@ -7323,13 +7489,13 @@
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="G10" s="48" t="str">
-        <x:v>Automated coverage declared</x:v>
+        <x:v>Failed</x:v>
       </x:c>
       <x:c r="H10" s="48" t="str">
-        <x:v>No current error logged</x:v>
+        <x:v>Failed in latest browser suite</x:v>
       </x:c>
       <x:c r="I10" s="48" t="str">
-        <x:v>In progress</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J10" s="48" t="str">
         <x:v>Needs retest loop</x:v>
@@ -7350,7 +7516,10 @@
         <x:v>quote/v{version:apiVersion}/account (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:15); GET quote/v{version:apiVersion}/account/profile (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:46); GET quote/v{version:apiVersion}/account/addresses (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:76); GET quote/v{version:apiVersion}/account/quotes (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:112); GET quote/v{version:apiVersion}/account/orders (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:120)</x:v>
       </x:c>
       <x:c r="P10" s="48" t="str">
-        <x:v>BrowserJourneyGateTests.QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3033); BrowserJourneyGateTests.QuoteEngine_CustomerIsolation_BlocksCrossCustomerQuoteOrderHistoryAccess (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3177); BrowserJourneyGateTests.QuoteEngine_LocalPortalRoutes_RenderPrototypeBackedSurfaces (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3288)</x:v>
+        <x:v>BrowserJourneyGateTests.QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3033); BrowserJourneyGateTests.QuoteEngine_CustomerIsolation_BlocksCrossCustomerQuoteOrderHistoryAccess (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3177); BrowserJourneyGateTests.QuoteEngine_LocalPortalRoutes_RenderPrototypeBackedSurfaces (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3288)
+2026-06-23 browser-suite failure batch: 14 failed, 42 passed, 0 skipped, 56 total.
+TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx.
+- QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory: Microsoft.Playwright.PlaywrightException : Locator expected to be visible Call log: - Expect "ToBeVisibleAsync" with timeout 30000ms - waiting for Locator("header.quote-topbar .billing-account-trigger") 28 × locator resolved to &lt;summary class="billing-accou...</x:v>
       </x:c>
       <x:c r="Q10" s="48" t="str">
         <x:v>Maliev.QuoteEngine.Bff; CustomerService; QuotationService; OrderService; PaymentService; DeliveryService; JobService or ProjectService; PdfService/UploadService</x:v>
@@ -7359,10 +7528,12 @@
         <x:v>None required unless status refresh creates audit/access records.</x:v>
       </x:c>
       <x:c r="S10" s="48" t="str">
-        <x:v>QuoteEngine history needs durable ProjectService/QuotationService ownership before this can pass.</x:v>
+        <x:v>QuoteEngine history needs durable ProjectService/QuotationService ownership before this can pass.
+Latest browser-suite failure(s): QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory</x:v>
       </x:c>
       <x:c r="T10" s="48" t="str">
-        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:1361; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs</x:v>
+        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:1361; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs
+Aspire E2E TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx</x:v>
       </x:c>
       <x:c r="U10" s="49" t="str">
         <x:v>2026-06-23</x:v>
@@ -7453,13 +7624,13 @@
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="G12" s="48" t="str">
-        <x:v>Automated coverage declared</x:v>
+        <x:v>Failed</x:v>
       </x:c>
       <x:c r="H12" s="48" t="str">
-        <x:v>No current error logged</x:v>
+        <x:v>Failed in latest browser suite</x:v>
       </x:c>
       <x:c r="I12" s="48" t="str">
-        <x:v>In progress</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J12" s="48" t="str">
         <x:v>Needs retest loop</x:v>
@@ -7480,7 +7651,10 @@
         <x:v>quote/v{version:apiVersion}/account (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:15); GET quote/v{version:apiVersion}/account/profile (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:46); GET quote/v{version:apiVersion}/account/addresses (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:76); GET quote/v{version:apiVersion}/account/quotes (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:112); GET quote/v{version:apiVersion}/account/orders (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:120)</x:v>
       </x:c>
       <x:c r="P12" s="48" t="str">
-        <x:v>BrowserJourneyGateTests.QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3033); BrowserJourneyGateTests.QuoteEngine_CustomerIsolation_BlocksCrossCustomerQuoteOrderHistoryAccess (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3177); BrowserJourneyGateTests.QuoteEngine_LocalPortalRoutes_RenderPrototypeBackedSurfaces (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3288)</x:v>
+        <x:v>BrowserJourneyGateTests.QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3033); BrowserJourneyGateTests.QuoteEngine_CustomerIsolation_BlocksCrossCustomerQuoteOrderHistoryAccess (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3177); BrowserJourneyGateTests.QuoteEngine_LocalPortalRoutes_RenderPrototypeBackedSurfaces (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3288)
+2026-06-23 browser-suite failure batch: 14 failed, 42 passed, 0 skipped, 56 total.
+TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx.
+- QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory: Microsoft.Playwright.PlaywrightException : Locator expected to be visible Call log: - Expect "ToBeVisibleAsync" with timeout 30000ms - waiting for Locator("header.quote-topbar .billing-account-trigger") 28 × locator resolved to &lt;summary class="billing-accou...</x:v>
       </x:c>
       <x:c r="Q12" s="48" t="str">
         <x:v>Maliev.QuoteEngine.Bff; Production owner: QuotationService or customer quote-history service.; UploadService/PdfService when artifacts are shown.; QuoteEnginePrototypeStore where still prototype-backed.</x:v>
@@ -7489,10 +7663,12 @@
         <x:v>None required for read-only history.</x:v>
       </x:c>
       <x:c r="S12" s="48" t="str">
-        <x:v>Quote list navigation should be explicit if only detail route currently exists.</x:v>
+        <x:v>Quote list navigation should be explicit if only detail route currently exists.
+Latest browser-suite failure(s): QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory</x:v>
       </x:c>
       <x:c r="T12" s="48" t="str">
-        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:1471; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs</x:v>
+        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:1471; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs
+Aspire E2E TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx</x:v>
       </x:c>
       <x:c r="U12" s="49" t="str">
         <x:v>2026-06-23</x:v>
@@ -7518,13 +7694,13 @@
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="G13" s="48" t="str">
-        <x:v>Automated coverage declared</x:v>
+        <x:v>Failed</x:v>
       </x:c>
       <x:c r="H13" s="48" t="str">
-        <x:v>No current error logged</x:v>
+        <x:v>Failed in latest browser suite</x:v>
       </x:c>
       <x:c r="I13" s="48" t="str">
-        <x:v>In progress</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J13" s="48" t="str">
         <x:v>Needs retest loop</x:v>
@@ -7545,7 +7721,10 @@
         <x:v>quote/v{version:apiVersion}/account (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:15); GET quote/v{version:apiVersion}/account/profile (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:46); GET quote/v{version:apiVersion}/account/addresses (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:76); GET quote/v{version:apiVersion}/account/quotes (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:112); GET quote/v{version:apiVersion}/account/orders (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:120)</x:v>
       </x:c>
       <x:c r="P13" s="48" t="str">
-        <x:v>BrowserJourneyGateTests.QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3033); BrowserJourneyGateTests.QuoteEngine_CustomerIsolation_BlocksCrossCustomerQuoteOrderHistoryAccess (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3177); BrowserJourneyGateTests.QuoteEngine_LocalPortalRoutes_RenderPrototypeBackedSurfaces (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3288)</x:v>
+        <x:v>BrowserJourneyGateTests.QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3033); BrowserJourneyGateTests.QuoteEngine_CustomerIsolation_BlocksCrossCustomerQuoteOrderHistoryAccess (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3177); BrowserJourneyGateTests.QuoteEngine_LocalPortalRoutes_RenderPrototypeBackedSurfaces (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3288)
+2026-06-23 browser-suite failure batch: 14 failed, 42 passed, 0 skipped, 56 total.
+TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx.
+- QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory: Microsoft.Playwright.PlaywrightException : Locator expected to be visible Call log: - Expect "ToBeVisibleAsync" with timeout 30000ms - waiting for Locator("header.quote-topbar .billing-account-trigger") 28 × locator resolved to &lt;summary class="billing-accou...</x:v>
       </x:c>
       <x:c r="Q13" s="48" t="str">
         <x:v>Maliev.QuoteEngine.Bff; OrderService; PaymentService; DeliveryService; QuotationService; QuoteEnginePrototypeStore where still prototype-backed.</x:v>
@@ -7554,10 +7733,12 @@
         <x:v>None required for read-only status.</x:v>
       </x:c>
       <x:c r="S13" s="48" t="str">
-        <x:v>Production order history must replace prototype-backed order records.</x:v>
+        <x:v>Production order history must replace prototype-backed order records.
+Latest browser-suite failure(s): QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory</x:v>
       </x:c>
       <x:c r="T13" s="48" t="str">
-        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:1522; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs</x:v>
+        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:1522; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs
+Aspire E2E TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx</x:v>
       </x:c>
       <x:c r="U13" s="49" t="str">
         <x:v>2026-06-23</x:v>
@@ -7713,13 +7894,13 @@
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="G16" s="48" t="str">
-        <x:v>Automated coverage declared</x:v>
+        <x:v>Failed</x:v>
       </x:c>
       <x:c r="H16" s="48" t="str">
-        <x:v>No current error logged</x:v>
+        <x:v>Failed in latest browser suite</x:v>
       </x:c>
       <x:c r="I16" s="48" t="str">
-        <x:v>In progress</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J16" s="48" t="str">
         <x:v>Needs retest loop</x:v>
@@ -7740,7 +7921,10 @@
         <x:v>quote/v{version:apiVersion}/account (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:15); GET quote/v{version:apiVersion}/account/profile (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:46); GET quote/v{version:apiVersion}/account/addresses (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:76); GET quote/v{version:apiVersion}/account/quotes (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:112); GET quote/v{version:apiVersion}/account/orders (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:120)</x:v>
       </x:c>
       <x:c r="P16" s="48" t="str">
-        <x:v>BrowserJourneyGateTests.QuoteEngine_MakeStudioAgent_RestoresSignedCustomerConversation (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:1278); BrowserJourneyGateTests.QuoteEngine_MakeStudioAgent_LoginRedirectRestoresActiveChat (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:1384); BrowserJourneyGateTests.QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3033)</x:v>
+        <x:v>BrowserJourneyGateTests.QuoteEngine_MakeStudioAgent_RestoresSignedCustomerConversation (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:1278); BrowserJourneyGateTests.QuoteEngine_MakeStudioAgent_LoginRedirectRestoresActiveChat (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:1384); BrowserJourneyGateTests.QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3033)
+2026-06-23 browser-suite failure batch: 14 failed, 42 passed, 0 skipped, 56 total.
+TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx.
+- QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory: Microsoft.Playwright.PlaywrightException : Locator expected to be visible Call log: - Expect "ToBeVisibleAsync" with timeout 30000ms - waiting for Locator("header.quote-topbar .billing-account-trigger") 28 × locator resolved to &lt;summary class="billing-accou...</x:v>
       </x:c>
       <x:c r="Q16" s="48" t="str">
         <x:v>Maliev.QuoteEngine.Bff; /hubs/quote-notifications; UploadService/GeometryService for analysis events.; QuotationService, OrderService, or prototype store depending on event type.</x:v>
@@ -7749,10 +7933,12 @@
         <x:v>Event-driven status updates.; No new data required beyond the triggering workflow.</x:v>
       </x:c>
       <x:c r="S16" s="48" t="str">
-        <x:v>Production event source must replace prototype-only notifications for quote/order workflows.</x:v>
+        <x:v>Production event source must replace prototype-only notifications for quote/order workflows.
+Latest browser-suite failure(s): QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory</x:v>
       </x:c>
       <x:c r="T16" s="48" t="str">
-        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:1680; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs</x:v>
+        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:1680; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs
+Aspire E2E TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx</x:v>
       </x:c>
       <x:c r="U16" s="49" t="str">
         <x:v>2026-06-23</x:v>
@@ -7843,13 +8029,13 @@
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="G18" s="48" t="str">
-        <x:v>Automated coverage declared</x:v>
+        <x:v>Failed</x:v>
       </x:c>
       <x:c r="H18" s="48" t="str">
-        <x:v>No current error logged</x:v>
+        <x:v>Failed in latest browser suite</x:v>
       </x:c>
       <x:c r="I18" s="48" t="str">
-        <x:v>In progress</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J18" s="48" t="str">
         <x:v>Needs retest loop</x:v>
@@ -7870,7 +8056,11 @@
         <x:v>quote/v{version:apiVersion}/account (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:15); GET quote/v{version:apiVersion}/account/profile (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:46); GET quote/v{version:apiVersion}/account/addresses (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:76); GET quote/v{version:apiVersion}/account/quotes (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:112); GET quote/v{version:apiVersion}/account/orders (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:120)</x:v>
       </x:c>
       <x:c r="P18" s="48" t="str">
-        <x:v>BrowserJourneyGateTests.QuoteEngine_RealProjectMode_BlocksCustomerUploadUntilSignIn (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:1255); BrowserJourneyGateTests.QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3033)</x:v>
+        <x:v>BrowserJourneyGateTests.QuoteEngine_RealProjectMode_BlocksCustomerUploadUntilSignIn (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:1255); BrowserJourneyGateTests.QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3033)
+2026-06-23 browser-suite failure batch: 14 failed, 42 passed, 0 skipped, 56 total.
+TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx.
+- QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory: Microsoft.Playwright.PlaywrightException : Locator expected to be visible Call log: - Expect "ToBeVisibleAsync" with timeout 30000ms - waiting for Locator("header.quote-topbar .billing-account-trigger") 28 × locator resolved to &lt;summary class="billing-accou...
+- QuoteEngine_RealProjectMode_BlocksCustomerUploadUntilSignIn: System.TimeoutException : Timeout 30000ms exceeded. =========================== logs =========================== waiting for navigation until "Commit" ============================================================ ---- System.TimeoutException : Timeout 30000m...</x:v>
       </x:c>
       <x:c r="Q18" s="48" t="str">
         <x:v>Maliev.QuoteEngine.Bff; UploadService in production.; GeometryService only for valid CAD files.; QuoteEnginePrototypeStore while prototype-backed.</x:v>
@@ -7879,10 +8069,12 @@
         <x:v>Failed upload attempt.; Successful upload artifact for retry.; Part status/error state.</x:v>
       </x:c>
       <x:c r="S18" s="48" t="str">
-        <x:v>Define customer-facing retry controls, max size messaging, resumable continuation across browser refresh, and cleanup of abandoned uploads.</x:v>
+        <x:v>Define customer-facing retry controls, max size messaging, resumable continuation across browser refresh, and cleanup of abandoned uploads.
+Latest browser-suite failure(s): QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory; QuoteEngine_RealProjectMode_BlocksCustomerUploadUntilSignIn</x:v>
       </x:c>
       <x:c r="T18" s="48" t="str">
-        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:1796; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs</x:v>
+        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:1796; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs
+Aspire E2E TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx</x:v>
       </x:c>
       <x:c r="U18" s="49" t="str">
         <x:v>2026-06-23</x:v>
@@ -7908,13 +8100,13 @@
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="G19" s="48" t="str">
-        <x:v>Automated coverage declared</x:v>
+        <x:v>Failed</x:v>
       </x:c>
       <x:c r="H19" s="48" t="str">
-        <x:v>No current error logged</x:v>
+        <x:v>Failed in latest browser suite</x:v>
       </x:c>
       <x:c r="I19" s="48" t="str">
-        <x:v>In progress</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J19" s="48" t="str">
         <x:v>Needs retest loop</x:v>
@@ -7935,7 +8127,12 @@
         <x:v>quote/v{version:apiVersion}/account (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:15); GET quote/v{version:apiVersion}/account/profile (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:46); GET quote/v{version:apiVersion}/account/addresses (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:76); GET quote/v{version:apiVersion}/account/quotes (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:112); GET quote/v{version:apiVersion}/account/orders (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:120)</x:v>
       </x:c>
       <x:c r="P19" s="48" t="str">
-        <x:v>BrowserJourneyGateTests.QuoteEngine_AnonymousDemo_EstimatesWithoutFormalArtifacts (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:896); BrowserJourneyGateTests.QuoteEngine_GeometryRuntime_LoadsAcrossDeviceViewports (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:934); BrowserJourneyGateTests.GeometryRuntime_ExecutesBrowserWorkerAcrossFrontendsAndDeviceViewports (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:1177); BrowserJourneyGateTests.QuoteEngine_MakeStudioAgentTools_CorrectsDfmCompletesPaymentAndLinksProductionJob (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:1465)</x:v>
+        <x:v>BrowserJourneyGateTests.QuoteEngine_AnonymousDemo_EstimatesWithoutFormalArtifacts (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:896); BrowserJourneyGateTests.QuoteEngine_GeometryRuntime_LoadsAcrossDeviceViewports (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:934); BrowserJourneyGateTests.GeometryRuntime_ExecutesBrowserWorkerAcrossFrontendsAndDeviceViewports (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:1177); BrowserJourneyGateTests.QuoteEngine_MakeStudioAgentTools_CorrectsDfmCompletesPaymentAndLinksProductionJob (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:1465)
+2026-06-23 browser-suite failure batch: 14 failed, 42 passed, 0 skipped, 56 total.
+TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx.
+- QuoteEngine_GeometryRuntime_LoadsAcrossDeviceViewports: Microsoft.Playwright.PlaywrightException : Locator expected to be visible Error: element(s) not found Call log: - Expect "ToBeVisibleAsync" with timeout 30000ms - waiting for GetByRole(AriaRole.Button, new() { Name = "Parts", Exact = true })
+- QuoteEngine_AnonymousDemo_EstimatesWithoutFormalArtifacts: Microsoft.Playwright.PlaywrightException : Locator expected to be visible Error: element(s) not found Call log: - Expect "ToBeVisibleAsync" with timeout 30000ms - waiting for GetByText("Demo only")
+- GeometryRuntime_ExecutesBrowserWorkerAcrossFrontendsAndDeviceViewports: Microsoft.Playwright.PlaywrightException : Locator expected to be visible Error: element(s) not found Call log: - Expect "ToBeVisibleAsync" with timeout 30000ms - waiting for GetByRole(AriaRole.Button, new() { Name = "Parts", Exact = true })</x:v>
       </x:c>
       <x:c r="Q19" s="48" t="str">
         <x:v>Maliev.QuoteEngine.Bff; GeometryService; PricingService; QuotationService in production.; QuoteEnginePrototypeStore while prototype-backed.</x:v>
@@ -7944,10 +8141,12 @@
         <x:v>DFM result.; DFM acknowledgement flag.; Quote part readiness state.</x:v>
       </x:c>
       <x:c r="S19" s="48" t="str">
-        <x:v>Decide which DFM severities block quote submission, require acknowledgement, or require employee review.</x:v>
+        <x:v>Decide which DFM severities block quote submission, require acknowledgement, or require employee review.
+Latest browser-suite failure(s): QuoteEngine_GeometryRuntime_LoadsAcrossDeviceViewports; QuoteEngine_AnonymousDemo_EstimatesWithoutFormalArtifacts; GeometryRuntime_ExecutesBrowserWorkerAcrossFrontendsAndDeviceViewports</x:v>
       </x:c>
       <x:c r="T19" s="48" t="str">
-        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:1852; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs</x:v>
+        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:1852; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs
+Aspire E2E TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx</x:v>
       </x:c>
       <x:c r="U19" s="49" t="str">
         <x:v>2026-06-23</x:v>
@@ -7973,13 +8172,13 @@
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="G20" s="48" t="str">
-        <x:v>Automated coverage declared</x:v>
+        <x:v>Failed</x:v>
       </x:c>
       <x:c r="H20" s="48" t="str">
-        <x:v>No current error logged</x:v>
+        <x:v>Failed in latest browser suite</x:v>
       </x:c>
       <x:c r="I20" s="48" t="str">
-        <x:v>In progress</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J20" s="48" t="str">
         <x:v>Needs retest loop</x:v>
@@ -8000,7 +8199,10 @@
         <x:v>quote/v{version:apiVersion}/account (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:15); GET quote/v{version:apiVersion}/account/profile (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:46); GET quote/v{version:apiVersion}/account/addresses (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:76); GET quote/v{version:apiVersion}/account/quotes (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:112); GET quote/v{version:apiVersion}/account/orders (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:120)</x:v>
       </x:c>
       <x:c r="P20" s="48" t="str">
-        <x:v>BrowserJourneyGateTests.QuoteEngine_AnonymousDemo_EstimatesWithoutFormalArtifacts (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:896)</x:v>
+        <x:v>BrowserJourneyGateTests.QuoteEngine_AnonymousDemo_EstimatesWithoutFormalArtifacts (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:896)
+2026-06-23 browser-suite failure batch: 14 failed, 42 passed, 0 skipped, 56 total.
+TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx.
+- QuoteEngine_AnonymousDemo_EstimatesWithoutFormalArtifacts: Microsoft.Playwright.PlaywrightException : Locator expected to be visible Error: element(s) not found Call log: - Expect "ToBeVisibleAsync" with timeout 30000ms - waiting for GetByText("Demo only")</x:v>
       </x:c>
       <x:c r="Q20" s="48" t="str">
         <x:v>Maliev.QuoteEngine.Bff; PricingService; MaterialService; DeliveryService if delivery promise affects lead time.; QuotationService in production.</x:v>
@@ -8009,10 +8211,12 @@
         <x:v>Quote estimate.; Selected lead-time code.; Formal quote lead-time terms.</x:v>
       </x:c>
       <x:c r="S20" s="48" t="str">
-        <x:v>Define customer-visible lead-time language, cutoff times, delivery/calendar rules, and expiry behavior.</x:v>
+        <x:v>Define customer-visible lead-time language, cutoff times, delivery/calendar rules, and expiry behavior.
+Latest browser-suite failure(s): QuoteEngine_AnonymousDemo_EstimatesWithoutFormalArtifacts</x:v>
       </x:c>
       <x:c r="T20" s="48" t="str">
-        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:1909; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs</x:v>
+        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:1909; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs
+Aspire E2E TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx</x:v>
       </x:c>
       <x:c r="U20" s="49" t="str">
         <x:v>2026-06-23</x:v>
@@ -8038,13 +8242,13 @@
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="G21" s="48" t="str">
-        <x:v>Automated coverage declared</x:v>
+        <x:v>Failed</x:v>
       </x:c>
       <x:c r="H21" s="48" t="str">
-        <x:v>No current error logged</x:v>
+        <x:v>Failed in latest browser suite</x:v>
       </x:c>
       <x:c r="I21" s="48" t="str">
-        <x:v>In progress</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J21" s="48" t="str">
         <x:v>Needs retest loop</x:v>
@@ -8065,7 +8269,12 @@
         <x:v>quote/v{version:apiVersion}/account (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:15); GET quote/v{version:apiVersion}/account/profile (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:46); GET quote/v{version:apiVersion}/account/addresses (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:76); GET quote/v{version:apiVersion}/account/quotes (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:112); GET quote/v{version:apiVersion}/account/orders (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:120)</x:v>
       </x:c>
       <x:c r="P21" s="48" t="str">
-        <x:v>BrowserJourneyGateTests.QuoteEngine_AnonymousDemo_EstimatesWithoutFormalArtifacts (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:896); BrowserJourneyGateTests.QuoteEngine_GeometryRuntime_LoadsAcrossDeviceViewports (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:934); BrowserJourneyGateTests.QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3033)</x:v>
+        <x:v>BrowserJourneyGateTests.QuoteEngine_AnonymousDemo_EstimatesWithoutFormalArtifacts (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:896); BrowserJourneyGateTests.QuoteEngine_GeometryRuntime_LoadsAcrossDeviceViewports (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:934); BrowserJourneyGateTests.QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3033)
+2026-06-23 browser-suite failure batch: 14 failed, 42 passed, 0 skipped, 56 total.
+TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx.
+- QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory: Microsoft.Playwright.PlaywrightException : Locator expected to be visible Call log: - Expect "ToBeVisibleAsync" with timeout 30000ms - waiting for Locator("header.quote-topbar .billing-account-trigger") 28 × locator resolved to &lt;summary class="billing-accou...
+- QuoteEngine_GeometryRuntime_LoadsAcrossDeviceViewports: Microsoft.Playwright.PlaywrightException : Locator expected to be visible Error: element(s) not found Call log: - Expect "ToBeVisibleAsync" with timeout 30000ms - waiting for GetByRole(AriaRole.Button, new() { Name = "Parts", Exact = true })
+- QuoteEngine_AnonymousDemo_EstimatesWithoutFormalArtifacts: Microsoft.Playwright.PlaywrightException : Locator expected to be visible Error: element(s) not found Call log: - Expect "ToBeVisibleAsync" with timeout 30000ms - waiting for GetByText("Demo only")</x:v>
       </x:c>
       <x:c r="Q21" s="48" t="str">
         <x:v>Maliev.QuoteEngine.Bff; PricingService; ProjectService or quote-draft owner.; QuotationService; QuoteEnginePrototypeStore while prototype-backed.</x:v>
@@ -8074,10 +8283,12 @@
         <x:v>Quote draft configuration.; Estimate revision.; Formal quote request using latest draft.</x:v>
       </x:c>
       <x:c r="S21" s="48" t="str">
-        <x:v>Define whether editing after formal quote creates a new quote version, cancels the old quote, or requires employee review.</x:v>
+        <x:v>Define whether editing after formal quote creates a new quote version, cancels the old quote, or requires employee review.
+Latest browser-suite failure(s): QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory; QuoteEngine_GeometryRuntime_LoadsAcrossDeviceViewports; QuoteEngine_AnonymousDemo_EstimatesWithoutFormalArtifacts</x:v>
       </x:c>
       <x:c r="T21" s="48" t="str">
-        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:1967; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs</x:v>
+        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:1967; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs
+Aspire E2E TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx</x:v>
       </x:c>
       <x:c r="U21" s="49" t="str">
         <x:v>2026-06-23</x:v>
@@ -8168,13 +8379,13 @@
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="G23" s="48" t="str">
-        <x:v>Automated coverage declared</x:v>
+        <x:v>Failed</x:v>
       </x:c>
       <x:c r="H23" s="48" t="str">
-        <x:v>No current error logged</x:v>
+        <x:v>Failed in latest browser suite</x:v>
       </x:c>
       <x:c r="I23" s="48" t="str">
-        <x:v>In progress</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J23" s="48" t="str">
         <x:v>Needs retest loop</x:v>
@@ -8195,7 +8406,10 @@
         <x:v>quote/v{version:apiVersion}/account (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:15); GET quote/v{version:apiVersion}/account/profile (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:46); GET quote/v{version:apiVersion}/account/addresses (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:76); GET quote/v{version:apiVersion}/account/quotes (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:112); GET quote/v{version:apiVersion}/account/orders (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:120)</x:v>
       </x:c>
       <x:c r="P23" s="48" t="str">
-        <x:v>BrowserJourneyGateTests.QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3033)</x:v>
+        <x:v>BrowserJourneyGateTests.QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3033)
+2026-06-23 browser-suite failure batch: 14 failed, 42 passed, 0 skipped, 56 total.
+TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx.
+- QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory: Microsoft.Playwright.PlaywrightException : Locator expected to be visible Call log: - Expect "ToBeVisibleAsync" with timeout 30000ms - waiting for Locator("header.quote-topbar .billing-account-trigger") 28 × locator resolved to &lt;summary class="billing-accou...</x:v>
       </x:c>
       <x:c r="Q23" s="48" t="str">
         <x:v>Maliev.QuoteEngine.Bff; QuotationService; OrderService; PaymentService; DeliveryService; CustomerService; PdfService/UploadService</x:v>
@@ -8204,10 +8418,12 @@
         <x:v>Accepted quote state.; Customer PO/reference.; Order record.; Payment/delivery intent where implemented.</x:v>
       </x:c>
       <x:c r="S23" s="48" t="str">
-        <x:v>Define customer PO requirement, acceptance terms text, quote expiry policy, and payment timing.</x:v>
+        <x:v>Define customer PO requirement, acceptance terms text, quote expiry policy, and payment timing.
+Latest browser-suite failure(s): QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory</x:v>
       </x:c>
       <x:c r="T23" s="48" t="str">
-        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:2083; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs</x:v>
+        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:2083; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs
+Aspire E2E TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx</x:v>
       </x:c>
       <x:c r="U23" s="49" t="str">
         <x:v>2026-06-23</x:v>
@@ -8233,13 +8449,13 @@
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="G24" s="48" t="str">
-        <x:v>Automated coverage declared</x:v>
+        <x:v>Failed</x:v>
       </x:c>
       <x:c r="H24" s="48" t="str">
-        <x:v>No current error logged</x:v>
+        <x:v>Failed in latest browser suite</x:v>
       </x:c>
       <x:c r="I24" s="48" t="str">
-        <x:v>In progress</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J24" s="48" t="str">
         <x:v>Needs retest loop</x:v>
@@ -8260,7 +8476,10 @@
         <x:v>quote/v{version:apiVersion}/account (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:15); GET quote/v{version:apiVersion}/account/profile (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:46); GET quote/v{version:apiVersion}/account/addresses (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:76); GET quote/v{version:apiVersion}/account/quotes (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:112); GET quote/v{version:apiVersion}/account/orders (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:120)</x:v>
       </x:c>
       <x:c r="P24" s="48" t="str">
-        <x:v>BrowserJourneyGateTests.QuoteEngine_CustomerDocuments_DownloadIsOwnerScoped (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3319)</x:v>
+        <x:v>BrowserJourneyGateTests.QuoteEngine_CustomerDocuments_DownloadIsOwnerScoped (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3319)
+2026-06-23 browser-suite failure batch: 14 failed, 42 passed, 0 skipped, 56 total.
+TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx.
+- QuoteEngine_CustomerDocuments_DownloadIsOwnerScoped: Document download failed: 404 {"type":"https://tools.ietf.org/html/rfc9110#section-15.5.5","title":"Not Found","status":404,"traceId":"00-e42669f877737efe7ac029309671d831-ed24a434f22bdbe4-01"}</x:v>
       </x:c>
       <x:c r="Q24" s="48" t="str">
         <x:v>Maliev.QuoteEngine.Bff; UploadService; PdfService; QuotationService; OrderService; IAMService or authorization boundary.</x:v>
@@ -8269,10 +8488,12 @@
         <x:v>None expected, except optional access/audit log.</x:v>
       </x:c>
       <x:c r="S24" s="48" t="str">
-        <x:v>Define the artifact taxonomy and customer-facing allowlist for quote/order documents.</x:v>
+        <x:v>Define the artifact taxonomy and customer-facing allowlist for quote/order documents.
+Latest browser-suite failure(s): QuoteEngine_CustomerDocuments_DownloadIsOwnerScoped</x:v>
       </x:c>
       <x:c r="T24" s="48" t="str">
-        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:2144; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs</x:v>
+        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:2144; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs
+Aspire E2E TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx</x:v>
       </x:c>
       <x:c r="U24" s="49" t="str">
         <x:v>2026-06-23</x:v>
@@ -8298,13 +8519,13 @@
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="G25" s="48" t="str">
-        <x:v>Automated coverage declared</x:v>
+        <x:v>Failed</x:v>
       </x:c>
       <x:c r="H25" s="48" t="str">
-        <x:v>No current error logged</x:v>
+        <x:v>Failed in latest browser suite</x:v>
       </x:c>
       <x:c r="I25" s="48" t="str">
-        <x:v>In progress</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J25" s="48" t="str">
         <x:v>Needs retest loop</x:v>
@@ -8325,7 +8546,10 @@
         <x:v>quote/v{version:apiVersion}/account (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:15); GET quote/v{version:apiVersion}/account/profile (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:46); GET quote/v{version:apiVersion}/account/addresses (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:76); GET quote/v{version:apiVersion}/account/quotes (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:112); GET quote/v{version:apiVersion}/account/orders (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:120)</x:v>
       </x:c>
       <x:c r="P25" s="48" t="str">
-        <x:v>BrowserJourneyGateTests.QuoteEngine_AnonymousDemo_EstimatesWithoutFormalArtifacts (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:896)</x:v>
+        <x:v>BrowserJourneyGateTests.QuoteEngine_AnonymousDemo_EstimatesWithoutFormalArtifacts (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:896)
+2026-06-23 browser-suite failure batch: 14 failed, 42 passed, 0 skipped, 56 total.
+TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx.
+- QuoteEngine_AnonymousDemo_EstimatesWithoutFormalArtifacts: Microsoft.Playwright.PlaywrightException : Locator expected to be visible Error: element(s) not found Call log: - Expect "ToBeVisibleAsync" with timeout 30000ms - waiting for GetByText("Demo only")</x:v>
       </x:c>
       <x:c r="Q25" s="48" t="str">
         <x:v>Maliev.QuoteEngine.Bff; Optional MaterialService/PricingService if demo uses live read-only reference data.; No ProjectService, QuotationService, UploadService, OrderService, PaymentService, or DeliveryService mutation.</x:v>
@@ -8334,10 +8558,12 @@
         <x:v>None. Demo mode must not create customer, project, upload, quotation, quotation version, order, payment, delivery, or history records.</x:v>
       </x:c>
       <x:c r="S25" s="48" t="str">
-        <x:v>Define the demo asset catalog, disclaimer wording, and whether demo pricing uses fixed fixtures or live read-only pricing.</x:v>
+        <x:v>Define the demo asset catalog, disclaimer wording, and whether demo pricing uses fixed fixtures or live read-only pricing.
+Latest browser-suite failure(s): QuoteEngine_AnonymousDemo_EstimatesWithoutFormalArtifacts</x:v>
       </x:c>
       <x:c r="T25" s="48" t="str">
-        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:2200; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs</x:v>
+        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:2200; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs
+Aspire E2E TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx</x:v>
       </x:c>
       <x:c r="U25" s="49" t="str">
         <x:v>2026-06-23</x:v>
@@ -8363,10 +8589,10 @@
         <x:v>Required gap</x:v>
       </x:c>
       <x:c r="G26" s="48" t="str">
-        <x:v>Automated coverage declared</x:v>
+        <x:v>Failed</x:v>
       </x:c>
       <x:c r="H26" s="48" t="str">
-        <x:v>No current error logged</x:v>
+        <x:v>Failed in latest browser suite</x:v>
       </x:c>
       <x:c r="I26" s="48" t="str">
         <x:v>Not started</x:v>
@@ -8390,7 +8616,10 @@
         <x:v>quote/v{version:apiVersion}/account (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:15); GET quote/v{version:apiVersion}/account/profile (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:46); GET quote/v{version:apiVersion}/account/addresses (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:76); GET quote/v{version:apiVersion}/account/quotes (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:112); GET quote/v{version:apiVersion}/account/orders (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:120)</x:v>
       </x:c>
       <x:c r="P26" s="48" t="str">
-        <x:v>BrowserJourneyGateTests.QuoteEngine_MakeStudioAgent_RestoresSignedCustomerConversation (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:1278); BrowserJourneyGateTests.QuoteEngine_MakeStudioAgentTools_CorrectsDfmCompletesPaymentAndLinksProductionJob (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:1465); BrowserJourneyGateTests.QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3033)</x:v>
+        <x:v>BrowserJourneyGateTests.QuoteEngine_MakeStudioAgent_RestoresSignedCustomerConversation (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:1278); BrowserJourneyGateTests.QuoteEngine_MakeStudioAgentTools_CorrectsDfmCompletesPaymentAndLinksProductionJob (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:1465); BrowserJourneyGateTests.QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3033)
+2026-06-23 browser-suite failure batch: 14 failed, 42 passed, 0 skipped, 56 total.
+TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx.
+- QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory: Microsoft.Playwright.PlaywrightException : Locator expected to be visible Call log: - Expect "ToBeVisibleAsync" with timeout 30000ms - waiting for Locator("header.quote-topbar .billing-account-trigger") 28 × locator resolved to &lt;summary class="billing-accou...</x:v>
       </x:c>
       <x:c r="Q26" s="48" t="str">
         <x:v>Maliev.QuoteEngine.Bff; AuthService; CustomerService; ProjectService; UploadService; GeometryService; MaterialService; PricingService; QuotationService; PdfService</x:v>
@@ -8399,10 +8628,12 @@
         <x:v>Project record and parts.; Quotation record linked to source project.; QuotationVersion 1 snapshot/PDF.; QuotationVersion 2 snapshot/PDF.; Project current quotation version fields.</x:v>
       </x:c>
       <x:c r="S26" s="48" t="str">
-        <x:v>Replace QuoteEnginePrototypeStore with real ProjectService/QuotationService workflow for signed project mode.</x:v>
+        <x:v>Replace QuoteEnginePrototypeStore with real ProjectService/QuotationService workflow for signed project mode.
+Latest browser-suite failure(s): QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory</x:v>
       </x:c>
       <x:c r="T26" s="48" t="str">
-        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:2256; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs</x:v>
+        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:2256; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs
+Aspire E2E TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx</x:v>
       </x:c>
       <x:c r="U26" s="49" t="str">
         <x:v>2026-06-23</x:v>
@@ -8493,13 +8724,13 @@
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="G28" s="48" t="str">
-        <x:v>Automated coverage declared</x:v>
+        <x:v>Failed</x:v>
       </x:c>
       <x:c r="H28" s="48" t="str">
-        <x:v>No current error logged</x:v>
+        <x:v>Failed in latest browser suite</x:v>
       </x:c>
       <x:c r="I28" s="48" t="str">
-        <x:v>In progress</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J28" s="48" t="str">
         <x:v>Needs retest loop</x:v>
@@ -8520,7 +8751,10 @@
         <x:v>quote/v{version:apiVersion}/account (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:15); GET quote/v{version:apiVersion}/account/profile (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:46); GET quote/v{version:apiVersion}/account/addresses (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:76); GET quote/v{version:apiVersion}/account/quotes (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:112); GET quote/v{version:apiVersion}/account/orders (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:120)</x:v>
       </x:c>
       <x:c r="P28" s="48" t="str">
-        <x:v>BrowserJourneyGateTests.Web_CustomerAccountSecurity_BlocksCrossCustomerAddressMutationAndPreservesReturnUrl (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:659); BrowserJourneyGateTests.QuoteEngine_CustomerIsolation_BlocksCrossCustomerQuoteOrderHistoryAccess (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3177); BrowserJourneyGateTests.QuoteEngine_CustomerDocuments_DownloadIsOwnerScoped (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3319)</x:v>
+        <x:v>BrowserJourneyGateTests.Web_CustomerAccountSecurity_BlocksCrossCustomerAddressMutationAndPreservesReturnUrl (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:659); BrowserJourneyGateTests.QuoteEngine_CustomerIsolation_BlocksCrossCustomerQuoteOrderHistoryAccess (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3177); BrowserJourneyGateTests.QuoteEngine_CustomerDocuments_DownloadIsOwnerScoped (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3319)
+2026-06-23 browser-suite failure batch: 14 failed, 42 passed, 0 skipped, 56 total.
+TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx.
+- QuoteEngine_CustomerDocuments_DownloadIsOwnerScoped: Document download failed: 404 {"type":"https://tools.ietf.org/html/rfc9110#section-15.5.5","title":"Not Found","status":404,"traceId":"00-e42669f877737efe7ac029309671d831-ed24a434f22bdbe4-01"}</x:v>
       </x:c>
       <x:c r="Q28" s="48" t="str">
         <x:v>Maliev.Web.Bff; Maliev.QuoteEngine.Bff; AuthService; CustomerService; QuotationService; OrderService; UploadService; PdfService; IAMService or authorization service boundary where applicable</x:v>
@@ -8529,10 +8763,12 @@
         <x:v>None expected except safe audit/security logs.</x:v>
       </x:c>
       <x:c r="S28" s="48" t="str">
-        <x:v>Define consistent forbidden versus not-found behavior for cross-customer resource probing.</x:v>
+        <x:v>Define consistent forbidden versus not-found behavior for cross-customer resource probing.
+Latest browser-suite failure(s): QuoteEngine_CustomerDocuments_DownloadIsOwnerScoped</x:v>
       </x:c>
       <x:c r="T28" s="48" t="str">
-        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:5808; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs</x:v>
+        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:5808; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs
+Aspire E2E TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx</x:v>
       </x:c>
       <x:c r="U28" s="49" t="str">
         <x:v>2026-06-23</x:v>
@@ -8558,16 +8794,16 @@
         <x:v>Required production gate. Automate once test hooks can reliably expire sessions.</x:v>
       </x:c>
       <x:c r="G29" s="48" t="str">
-        <x:v>Automated coverage declared</x:v>
+        <x:v>Failed</x:v>
       </x:c>
       <x:c r="H29" s="48" t="str">
-        <x:v>No current error logged</x:v>
+        <x:v>Failed in latest browser suite</x:v>
       </x:c>
       <x:c r="I29" s="48" t="str">
-        <x:v>N/A</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J29" s="48" t="str">
-        <x:v>Passed</x:v>
+        <x:v>Needs retest loop</x:v>
       </x:c>
       <x:c r="K29" s="48" t="str">
         <x:v>P0</x:v>
@@ -8585,7 +8821,10 @@
         <x:v>quote/v{version:apiVersion}/account (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:15); GET quote/v{version:apiVersion}/account/profile (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:46); GET quote/v{version:apiVersion}/account/addresses (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:76); GET quote/v{version:apiVersion}/account/quotes (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:112); GET quote/v{version:apiVersion}/account/orders (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:120)</x:v>
       </x:c>
       <x:c r="P29" s="48" t="str">
-        <x:v>BrowserJourneyGateTests.Web_CustomerChatbot_LoginPromptContinuesAuthenticatedConversationInPlace (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:496); BrowserJourneyGateTests.Web_CustomerAccountSecurity_BlocksCrossCustomerAddressMutationAndPreservesReturnUrl (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:659); BrowserJourneyGateTests.Intranet_ProtectedRoutes_RedirectAnonymousUserToLogin (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3446); BrowserJourneyGateTests.Intranet_AutomationEmployee_SignsInAndReachesProtectedSurfaces (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3887)</x:v>
+        <x:v>BrowserJourneyGateTests.Web_CustomerChatbot_LoginPromptContinuesAuthenticatedConversationInPlace (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:496); BrowserJourneyGateTests.Web_CustomerAccountSecurity_BlocksCrossCustomerAddressMutationAndPreservesReturnUrl (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:659); BrowserJourneyGateTests.Intranet_ProtectedRoutes_RedirectAnonymousUserToLogin (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3446); BrowserJourneyGateTests.Intranet_AutomationEmployee_SignsInAndReachesProtectedSurfaces (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:3887)
+2026-06-23 browser-suite failure batch: 14 failed, 42 passed, 0 skipped, 56 total.
+TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx.
+- Web_CustomerChatbot_LoginPromptContinuesAuthenticatedConversationInPlace: Microsoft.Playwright.PlaywrightException : Locator expected to be visible Error: element(s) not found Call log: - Expect "ToBeVisibleAsync" with timeout 30000ms - waiting for Locator(".topbar-chat-toggle")</x:v>
       </x:c>
       <x:c r="Q29" s="48" t="str">
         <x:v>Maliev.Web.Bff; Maliev.QuoteEngine.Bff; Maliev.Intranet.Bff; AuthService; IAMService; Target domain service for the protected page</x:v>
@@ -8594,10 +8833,12 @@
         <x:v>Session/token state.; No domain mutation expected during denied/re-auth redirect unless user explicitly resubmits.</x:v>
       </x:c>
       <x:c r="S29" s="48" t="str">
-        <x:v>Define exact return URL and unsaved-work policies per app.</x:v>
+        <x:v>Define exact return URL and unsaved-work policies per app.
+Latest browser-suite failure(s): Web_CustomerChatbot_LoginPromptContinuesAuthenticatedConversationInPlace</x:v>
       </x:c>
       <x:c r="T29" s="48" t="str">
-        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:5922; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs</x:v>
+        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:5922; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs
+Aspire E2E TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx</x:v>
       </x:c>
       <x:c r="U29" s="49" t="str">
         <x:v>2026-06-23</x:v>
@@ -8753,13 +8994,13 @@
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="G32" s="51" t="str">
-        <x:v>Automated coverage declared</x:v>
+        <x:v>Failed</x:v>
       </x:c>
       <x:c r="H32" s="51" t="str">
-        <x:v>No current error logged</x:v>
+        <x:v>Failed in latest browser suite</x:v>
       </x:c>
       <x:c r="I32" s="51" t="str">
-        <x:v>In progress</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J32" s="51" t="str">
         <x:v>Needs retest loop</x:v>
@@ -8780,7 +9021,11 @@
         <x:v>quote/v{version:apiVersion}/account (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:15); GET quote/v{version:apiVersion}/account/profile (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:46); GET quote/v{version:apiVersion}/account/addresses (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:76); GET quote/v{version:apiVersion}/account/quotes (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:112); GET quote/v{version:apiVersion}/account/orders (Maliev.QuoteEngine/Maliev.QuoteEngine.Bff/Controllers/AccountController.cs:120)</x:v>
       </x:c>
       <x:c r="P32" s="51" t="str">
-        <x:v>BrowserJourneyGateTests.Web_CustomerChatbot_LoginPromptContinuesAuthenticatedConversationInPlace (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:496); BrowserJourneyGateTests.QuoteEngine_CustomerChatbotWindow_RetainsWebConversation (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:611); BrowserJourneyGateTests.QuoteEngine_MakeStudioAgent_RestoresSignedCustomerConversation (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:1278); BrowserJourneyGateTests.QuoteEngine_MakeStudioAgent_LoginRedirectRestoresActiveChat (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:1384); BrowserJourneyGateTests.Web_MaliChatbot_AnonymousVisitorReceivesAssistantReplyThroughWebBff (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:6251)</x:v>
+        <x:v>BrowserJourneyGateTests.Web_CustomerChatbot_LoginPromptContinuesAuthenticatedConversationInPlace (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:496); BrowserJourneyGateTests.QuoteEngine_CustomerChatbotWindow_RetainsWebConversation (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:611); BrowserJourneyGateTests.QuoteEngine_MakeStudioAgent_RestoresSignedCustomerConversation (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:1278); BrowserJourneyGateTests.QuoteEngine_MakeStudioAgent_LoginRedirectRestoresActiveChat (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:1384); BrowserJourneyGateTests.Web_MaliChatbot_AnonymousVisitorReceivesAssistantReplyThroughWebBff (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:6251)
+2026-06-23 browser-suite failure batch: 14 failed, 42 passed, 0 skipped, 56 total.
+TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx.
+- QuoteEngine_CustomerChatbotWindow_RetainsWebConversation: Microsoft.Playwright.PlaywrightException : Locator expected to be visible Error: element(s) not found Call log: - Expect "ToBeVisibleAsync" with timeout 30000ms - waiting for Locator(".topbar-chat-toggle")
+- Web_CustomerChatbot_LoginPromptContinuesAuthenticatedConversationInPlace: Microsoft.Playwright.PlaywrightException : Locator expected to be visible Error: element(s) not found Call log: - Expect "ToBeVisibleAsync" with timeout 30000ms - waiting for Locator(".topbar-chat-toggle")</x:v>
       </x:c>
       <x:c r="Q32" s="51" t="str">
         <x:v>Maliev.Web.Bff; Maliev.QuoteEngine.Bff; Maliev.ChatbotService; Redis (chatbot session lock); AuthService and CustomerService for signed-in personalization.</x:v>
@@ -8789,10 +9034,12 @@
         <x:v>Anonymous chatbot session for visitors.; Customer-scoped chatbot session/history for signed-in customers.; Browser-local personalization record.; Shared assistant-session cookie used for Web to QuoteEngine continuation.</x:v>
       </x:c>
       <x:c r="S32" s="51" t="str">
-        <x:v>Define anonymous vs. signed conversation retention, define tool-callable account/quote/order/profile/address surfaces that Mali and Make Studio should and should not invoke, broaden Make Studio agent E2E coverage from conversation restoration into DFM, corrected reupload, quote/order/payment, and finalize product-side abuse limits.</x:v>
+        <x:v>Define anonymous vs. signed conversation retention, define tool-callable account/quote/order/profile/address surfaces that Mali and Make Studio should and should not invoke, broaden Make Studio agent E2E coverage from conversation restoration into DFM, corrected reupload, quote/order/payment, and finalize product-side abuse limits.
+Latest browser-suite failure(s): QuoteEngine_CustomerChatbotWindow_RetainsWebConversation; Web_CustomerChatbot_LoginPromptContinuesAuthenticatedConversationInPlace</x:v>
       </x:c>
       <x:c r="T32" s="51" t="str">
-        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:803; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs</x:v>
+        <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:803; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs
+Aspire E2E TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx</x:v>
       </x:c>
       <x:c r="U32" s="52" t="str">
         <x:v>2026-06-23</x:v>
@@ -8821,7 +9068,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9a2235cbe07b44ca"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R987aab7464c645fc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/maliev-feature-user-story-status.xlsx
+++ b/docs/maliev-feature-user-story-status.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R141f6d7fc98a4027"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="Raa306e393d0343de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R7cddd1ae401c4d0d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="R2ea7aa3c1fc043e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Ra94bbcdf4009484f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="Ra3e53cf045bc40ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R55b4983006e840fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="R62640dfa82114838"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2512,7 +2512,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re65d2b30ed15431e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re74f505a548b4636"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6810,7 +6810,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2afae03a400c4fa6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf2f27dfab5ad4a96"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7001,13 +7001,13 @@
         <x:v>Failed</x:v>
       </x:c>
       <x:c r="H3" s="48" t="str">
-        <x:v>Failed in latest browser suite</x:v>
+        <x:v>Failed after partial fix</x:v>
       </x:c>
       <x:c r="I3" s="48" t="str">
-        <x:v>Not started</x:v>
+        <x:v>In progress</x:v>
       </x:c>
       <x:c r="J3" s="48" t="str">
-        <x:v>Needs retest loop</x:v>
+        <x:v>Failed</x:v>
       </x:c>
       <x:c r="K3" s="48" t="str">
         <x:v>P1</x:v>
@@ -7031,7 +7031,8 @@
 - QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory: Microsoft.Playwright.PlaywrightException : Locator expected to be visible Call log: - Expect "ToBeVisibleAsync" with timeout 30000ms - waiting for Locator("header.quote-topbar .billing-account-trigger") 28 × locator resolved to &lt;summary class="billing-accou...
 - QuoteEngine_GeometryRuntime_LoadsAcrossDeviceViewports: Microsoft.Playwright.PlaywrightException : Locator expected to be visible Error: element(s) not found Call log: - Expect "ToBeVisibleAsync" with timeout 30000ms - waiting for GetByRole(AriaRole.Button, new() { Name = "Parts", Exact = true })
 - QuoteEngine_AnonymousDemo_EstimatesWithoutFormalArtifacts: Microsoft.Playwright.PlaywrightException : Locator expected to be visible Error: element(s) not found Call log: - Expect "ToBeVisibleAsync" with timeout 30000ms - waiting for GetByText("Demo only")
-- GeometryRuntime_ExecutesBrowserWorkerAcrossFrontendsAndDeviceViewports: Microsoft.Playwright.PlaywrightException : Locator expected to be visible Error: element(s) not found Call log: - Expect "ToBeVisibleAsync" with timeout 30000ms - waiting for GetByRole(AriaRole.Button, new() { Name = "Parts", Exact = true })</x:v>
+- GeometryRuntime_ExecutesBrowserWorkerAcrossFrontendsAndDeviceViewports: Microsoft.Playwright.PlaywrightException : Locator expected to be visible Error: element(s) not found Call log: - Expect "ToBeVisibleAsync" with timeout 30000ms - waiting for GetByRole(AriaRole.Button, new() { Name = "Parts", Exact = true })
+2026-06-23 targeted retest after QuoteEngine c926434: Demo only cue is now satisfied; remaining failure is waiting for role button '3D Model' exact at BrowserJourneyGateTests.cs:906. TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-quoteengine-anonymous-demo-retest.trx.</x:v>
       </x:c>
       <x:c r="Q3" s="48" t="str">
         <x:v>Maliev.QuoteEngine.Bff; AuthService; UploadService; GeometryService; RabbitMQ; ProjectService</x:v>
@@ -7041,11 +7042,13 @@
       </x:c>
       <x:c r="S3" s="48" t="str">
         <x:v>Production QuoteEngine needs the same artifact enrichment rigor expected in the employee project quote workspace.
-Latest browser-suite failure(s): QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory; QuoteEngine_GeometryRuntime_LoadsAcrossDeviceViewports; QuoteEngine_AnonymousDemo_EstimatesWithoutFormalArtifacts; GeometryRuntime_ExecutesBrowserWorkerAcrossFrontendsAndDeviceViewports</x:v>
+Latest browser-suite failure(s): QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory; QuoteEngine_GeometryRuntime_LoadsAcrossDeviceViewports; QuoteEngine_AnonymousDemo_EstimatesWithoutFormalArtifacts; GeometryRuntime_ExecutesBrowserWorkerAcrossFrontendsAndDeviceViewports
+Post-fix anonymous demo retest still lacks visible 3D Model tab/button.</x:v>
       </x:c>
       <x:c r="T3" s="48" t="str">
         <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:948; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs
-Aspire E2E TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx</x:v>
+Aspire E2E TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx
+QuoteEngine fix commit: c926434. Targeted retest TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-quoteengine-anonymous-demo-retest.trx</x:v>
       </x:c>
       <x:c r="U3" s="49" t="str">
         <x:v>2026-06-23</x:v>
@@ -7074,13 +7077,13 @@
         <x:v>Failed</x:v>
       </x:c>
       <x:c r="H4" s="48" t="str">
-        <x:v>Failed in latest browser suite</x:v>
+        <x:v>Failed after partial fix</x:v>
       </x:c>
       <x:c r="I4" s="48" t="str">
-        <x:v>Not started</x:v>
+        <x:v>In progress</x:v>
       </x:c>
       <x:c r="J4" s="48" t="str">
-        <x:v>Needs retest loop</x:v>
+        <x:v>Failed</x:v>
       </x:c>
       <x:c r="K4" s="48" t="str">
         <x:v>P1</x:v>
@@ -7103,7 +7106,8 @@
 TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx.
 - QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory: Microsoft.Playwright.PlaywrightException : Locator expected to be visible Call log: - Expect "ToBeVisibleAsync" with timeout 30000ms - waiting for Locator("header.quote-topbar .billing-account-trigger") 28 × locator resolved to &lt;summary class="billing-accou...
 - QuoteEngine_GeometryRuntime_LoadsAcrossDeviceViewports: Microsoft.Playwright.PlaywrightException : Locator expected to be visible Error: element(s) not found Call log: - Expect "ToBeVisibleAsync" with timeout 30000ms - waiting for GetByRole(AriaRole.Button, new() { Name = "Parts", Exact = true })
-- QuoteEngine_AnonymousDemo_EstimatesWithoutFormalArtifacts: Microsoft.Playwright.PlaywrightException : Locator expected to be visible Error: element(s) not found Call log: - Expect "ToBeVisibleAsync" with timeout 30000ms - waiting for GetByText("Demo only")</x:v>
+- QuoteEngine_AnonymousDemo_EstimatesWithoutFormalArtifacts: Microsoft.Playwright.PlaywrightException : Locator expected to be visible Error: element(s) not found Call log: - Expect "ToBeVisibleAsync" with timeout 30000ms - waiting for GetByText("Demo only")
+2026-06-23 targeted retest after QuoteEngine c926434: Demo only cue is now satisfied; remaining failure is waiting for role button '3D Model' exact at BrowserJourneyGateTests.cs:906. TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-quoteengine-anonymous-demo-retest.trx.</x:v>
       </x:c>
       <x:c r="Q4" s="48" t="str">
         <x:v>Maliev.QuoteEngine.Bff; MaterialService; PricingService; ProjectService; DeliveryService if delivery option affects quote</x:v>
@@ -7113,11 +7117,13 @@
       </x:c>
       <x:c r="S4" s="48" t="str">
         <x:v>QuoteEngine must call real MaterialService, PricingService, and ProjectService for production. Prototype pricing cannot pass this story.
-Latest browser-suite failure(s): QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory; QuoteEngine_GeometryRuntime_LoadsAcrossDeviceViewports; QuoteEngine_AnonymousDemo_EstimatesWithoutFormalArtifacts</x:v>
+Latest browser-suite failure(s): QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory; QuoteEngine_GeometryRuntime_LoadsAcrossDeviceViewports; QuoteEngine_AnonymousDemo_EstimatesWithoutFormalArtifacts
+Post-fix anonymous demo retest still lacks visible 3D Model tab/button.</x:v>
       </x:c>
       <x:c r="T4" s="48" t="str">
         <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:1014; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs
-Aspire E2E TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx</x:v>
+Aspire E2E TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx
+QuoteEngine fix commit: c926434. Targeted retest TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-quoteengine-anonymous-demo-retest.trx</x:v>
       </x:c>
       <x:c r="U4" s="49" t="str">
         <x:v>2026-06-23</x:v>
@@ -7146,13 +7152,13 @@
         <x:v>Failed</x:v>
       </x:c>
       <x:c r="H5" s="48" t="str">
-        <x:v>Failed in latest browser suite</x:v>
+        <x:v>Failed after partial fix</x:v>
       </x:c>
       <x:c r="I5" s="48" t="str">
-        <x:v>Not started</x:v>
+        <x:v>In progress</x:v>
       </x:c>
       <x:c r="J5" s="48" t="str">
-        <x:v>Needs retest loop</x:v>
+        <x:v>Failed</x:v>
       </x:c>
       <x:c r="K5" s="48" t="str">
         <x:v>P1</x:v>
@@ -7173,7 +7179,8 @@
         <x:v>BrowserJourneyGateTests.QuoteEngine_AnonymousDemo_EstimatesWithoutFormalArtifacts (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:896); BrowserJourneyGateTests.QuoteEngine_MakeStudioAgentTools_CorrectsDfmCompletesPaymentAndLinksProductionJob (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:1465)
 2026-06-23 browser-suite failure batch: 14 failed, 42 passed, 0 skipped, 56 total.
 TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx.
-- QuoteEngine_AnonymousDemo_EstimatesWithoutFormalArtifacts: Microsoft.Playwright.PlaywrightException : Locator expected to be visible Error: element(s) not found Call log: - Expect "ToBeVisibleAsync" with timeout 30000ms - waiting for GetByText("Demo only")</x:v>
+- QuoteEngine_AnonymousDemo_EstimatesWithoutFormalArtifacts: Microsoft.Playwright.PlaywrightException : Locator expected to be visible Error: element(s) not found Call log: - Expect "ToBeVisibleAsync" with timeout 30000ms - waiting for GetByText("Demo only")
+2026-06-23 targeted retest after QuoteEngine c926434: Demo only cue is now satisfied; remaining failure is waiting for role button '3D Model' exact at BrowserJourneyGateTests.cs:906. TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-quoteengine-anonymous-demo-retest.trx.</x:v>
       </x:c>
       <x:c r="Q5" s="48" t="str">
         <x:v>Maliev.QuoteEngine.Bff; UploadService; GeometryService; PricingService; RabbitMQ</x:v>
@@ -7183,11 +7190,13 @@
       </x:c>
       <x:c r="S5" s="48" t="str">
         <x:v>QuoteEngine must implement project-part revision-aware upload and analysis state before this can be production-gate ready.
-Latest browser-suite failure(s): QuoteEngine_AnonymousDemo_EstimatesWithoutFormalArtifacts</x:v>
+Latest browser-suite failure(s): QuoteEngine_AnonymousDemo_EstimatesWithoutFormalArtifacts
+Post-fix anonymous demo retest still lacks visible 3D Model tab/button.</x:v>
       </x:c>
       <x:c r="T5" s="48" t="str">
         <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:1072; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs
-Aspire E2E TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx</x:v>
+Aspire E2E TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx
+QuoteEngine fix commit: c926434. Targeted retest TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-quoteengine-anonymous-demo-retest.trx</x:v>
       </x:c>
       <x:c r="U5" s="49" t="str">
         <x:v>2026-06-23</x:v>
@@ -8103,13 +8112,13 @@
         <x:v>Failed</x:v>
       </x:c>
       <x:c r="H19" s="48" t="str">
-        <x:v>Failed in latest browser suite</x:v>
+        <x:v>Failed after partial fix</x:v>
       </x:c>
       <x:c r="I19" s="48" t="str">
-        <x:v>Not started</x:v>
+        <x:v>In progress</x:v>
       </x:c>
       <x:c r="J19" s="48" t="str">
-        <x:v>Needs retest loop</x:v>
+        <x:v>Failed</x:v>
       </x:c>
       <x:c r="K19" s="48" t="str">
         <x:v>P1</x:v>
@@ -8132,7 +8141,8 @@
 TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx.
 - QuoteEngine_GeometryRuntime_LoadsAcrossDeviceViewports: Microsoft.Playwright.PlaywrightException : Locator expected to be visible Error: element(s) not found Call log: - Expect "ToBeVisibleAsync" with timeout 30000ms - waiting for GetByRole(AriaRole.Button, new() { Name = "Parts", Exact = true })
 - QuoteEngine_AnonymousDemo_EstimatesWithoutFormalArtifacts: Microsoft.Playwright.PlaywrightException : Locator expected to be visible Error: element(s) not found Call log: - Expect "ToBeVisibleAsync" with timeout 30000ms - waiting for GetByText("Demo only")
-- GeometryRuntime_ExecutesBrowserWorkerAcrossFrontendsAndDeviceViewports: Microsoft.Playwright.PlaywrightException : Locator expected to be visible Error: element(s) not found Call log: - Expect "ToBeVisibleAsync" with timeout 30000ms - waiting for GetByRole(AriaRole.Button, new() { Name = "Parts", Exact = true })</x:v>
+- GeometryRuntime_ExecutesBrowserWorkerAcrossFrontendsAndDeviceViewports: Microsoft.Playwright.PlaywrightException : Locator expected to be visible Error: element(s) not found Call log: - Expect "ToBeVisibleAsync" with timeout 30000ms - waiting for GetByRole(AriaRole.Button, new() { Name = "Parts", Exact = true })
+2026-06-23 targeted retest after QuoteEngine c926434: Demo only cue is now satisfied; remaining failure is waiting for role button '3D Model' exact at BrowserJourneyGateTests.cs:906. TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-quoteengine-anonymous-demo-retest.trx.</x:v>
       </x:c>
       <x:c r="Q19" s="48" t="str">
         <x:v>Maliev.QuoteEngine.Bff; GeometryService; PricingService; QuotationService in production.; QuoteEnginePrototypeStore while prototype-backed.</x:v>
@@ -8142,11 +8152,13 @@
       </x:c>
       <x:c r="S19" s="48" t="str">
         <x:v>Decide which DFM severities block quote submission, require acknowledgement, or require employee review.
-Latest browser-suite failure(s): QuoteEngine_GeometryRuntime_LoadsAcrossDeviceViewports; QuoteEngine_AnonymousDemo_EstimatesWithoutFormalArtifacts; GeometryRuntime_ExecutesBrowserWorkerAcrossFrontendsAndDeviceViewports</x:v>
+Latest browser-suite failure(s): QuoteEngine_GeometryRuntime_LoadsAcrossDeviceViewports; QuoteEngine_AnonymousDemo_EstimatesWithoutFormalArtifacts; GeometryRuntime_ExecutesBrowserWorkerAcrossFrontendsAndDeviceViewports
+Post-fix anonymous demo retest still lacks visible 3D Model tab/button.</x:v>
       </x:c>
       <x:c r="T19" s="48" t="str">
         <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:1852; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs
-Aspire E2E TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx</x:v>
+Aspire E2E TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx
+QuoteEngine fix commit: c926434. Targeted retest TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-quoteengine-anonymous-demo-retest.trx</x:v>
       </x:c>
       <x:c r="U19" s="49" t="str">
         <x:v>2026-06-23</x:v>
@@ -8175,13 +8187,13 @@
         <x:v>Failed</x:v>
       </x:c>
       <x:c r="H20" s="48" t="str">
-        <x:v>Failed in latest browser suite</x:v>
+        <x:v>Failed after partial fix</x:v>
       </x:c>
       <x:c r="I20" s="48" t="str">
-        <x:v>Not started</x:v>
+        <x:v>In progress</x:v>
       </x:c>
       <x:c r="J20" s="48" t="str">
-        <x:v>Needs retest loop</x:v>
+        <x:v>Failed</x:v>
       </x:c>
       <x:c r="K20" s="48" t="str">
         <x:v>P1</x:v>
@@ -8202,7 +8214,8 @@
         <x:v>BrowserJourneyGateTests.QuoteEngine_AnonymousDemo_EstimatesWithoutFormalArtifacts (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:896)
 2026-06-23 browser-suite failure batch: 14 failed, 42 passed, 0 skipped, 56 total.
 TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx.
-- QuoteEngine_AnonymousDemo_EstimatesWithoutFormalArtifacts: Microsoft.Playwright.PlaywrightException : Locator expected to be visible Error: element(s) not found Call log: - Expect "ToBeVisibleAsync" with timeout 30000ms - waiting for GetByText("Demo only")</x:v>
+- QuoteEngine_AnonymousDemo_EstimatesWithoutFormalArtifacts: Microsoft.Playwright.PlaywrightException : Locator expected to be visible Error: element(s) not found Call log: - Expect "ToBeVisibleAsync" with timeout 30000ms - waiting for GetByText("Demo only")
+2026-06-23 targeted retest after QuoteEngine c926434: Demo only cue is now satisfied; remaining failure is waiting for role button '3D Model' exact at BrowserJourneyGateTests.cs:906. TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-quoteengine-anonymous-demo-retest.trx.</x:v>
       </x:c>
       <x:c r="Q20" s="48" t="str">
         <x:v>Maliev.QuoteEngine.Bff; PricingService; MaterialService; DeliveryService if delivery promise affects lead time.; QuotationService in production.</x:v>
@@ -8212,11 +8225,13 @@
       </x:c>
       <x:c r="S20" s="48" t="str">
         <x:v>Define customer-visible lead-time language, cutoff times, delivery/calendar rules, and expiry behavior.
-Latest browser-suite failure(s): QuoteEngine_AnonymousDemo_EstimatesWithoutFormalArtifacts</x:v>
+Latest browser-suite failure(s): QuoteEngine_AnonymousDemo_EstimatesWithoutFormalArtifacts
+Post-fix anonymous demo retest still lacks visible 3D Model tab/button.</x:v>
       </x:c>
       <x:c r="T20" s="48" t="str">
         <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:1909; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs
-Aspire E2E TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx</x:v>
+Aspire E2E TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx
+QuoteEngine fix commit: c926434. Targeted retest TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-quoteengine-anonymous-demo-retest.trx</x:v>
       </x:c>
       <x:c r="U20" s="49" t="str">
         <x:v>2026-06-23</x:v>
@@ -8245,13 +8260,13 @@
         <x:v>Failed</x:v>
       </x:c>
       <x:c r="H21" s="48" t="str">
-        <x:v>Failed in latest browser suite</x:v>
+        <x:v>Failed after partial fix</x:v>
       </x:c>
       <x:c r="I21" s="48" t="str">
-        <x:v>Not started</x:v>
+        <x:v>In progress</x:v>
       </x:c>
       <x:c r="J21" s="48" t="str">
-        <x:v>Needs retest loop</x:v>
+        <x:v>Failed</x:v>
       </x:c>
       <x:c r="K21" s="48" t="str">
         <x:v>P1</x:v>
@@ -8274,7 +8289,8 @@
 TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx.
 - QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory: Microsoft.Playwright.PlaywrightException : Locator expected to be visible Call log: - Expect "ToBeVisibleAsync" with timeout 30000ms - waiting for Locator("header.quote-topbar .billing-account-trigger") 28 × locator resolved to &lt;summary class="billing-accou...
 - QuoteEngine_GeometryRuntime_LoadsAcrossDeviceViewports: Microsoft.Playwright.PlaywrightException : Locator expected to be visible Error: element(s) not found Call log: - Expect "ToBeVisibleAsync" with timeout 30000ms - waiting for GetByRole(AriaRole.Button, new() { Name = "Parts", Exact = true })
-- QuoteEngine_AnonymousDemo_EstimatesWithoutFormalArtifacts: Microsoft.Playwright.PlaywrightException : Locator expected to be visible Error: element(s) not found Call log: - Expect "ToBeVisibleAsync" with timeout 30000ms - waiting for GetByText("Demo only")</x:v>
+- QuoteEngine_AnonymousDemo_EstimatesWithoutFormalArtifacts: Microsoft.Playwright.PlaywrightException : Locator expected to be visible Error: element(s) not found Call log: - Expect "ToBeVisibleAsync" with timeout 30000ms - waiting for GetByText("Demo only")
+2026-06-23 targeted retest after QuoteEngine c926434: Demo only cue is now satisfied; remaining failure is waiting for role button '3D Model' exact at BrowserJourneyGateTests.cs:906. TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-quoteengine-anonymous-demo-retest.trx.</x:v>
       </x:c>
       <x:c r="Q21" s="48" t="str">
         <x:v>Maliev.QuoteEngine.Bff; PricingService; ProjectService or quote-draft owner.; QuotationService; QuoteEnginePrototypeStore while prototype-backed.</x:v>
@@ -8284,11 +8300,13 @@
       </x:c>
       <x:c r="S21" s="48" t="str">
         <x:v>Define whether editing after formal quote creates a new quote version, cancels the old quote, or requires employee review.
-Latest browser-suite failure(s): QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory; QuoteEngine_GeometryRuntime_LoadsAcrossDeviceViewports; QuoteEngine_AnonymousDemo_EstimatesWithoutFormalArtifacts</x:v>
+Latest browser-suite failure(s): QuoteEngine_PrototypeSignedCustomer_UploadsEstimatesQuotesOrdersAndRecordsHistory; QuoteEngine_GeometryRuntime_LoadsAcrossDeviceViewports; QuoteEngine_AnonymousDemo_EstimatesWithoutFormalArtifacts
+Post-fix anonymous demo retest still lacks visible 3D Model tab/button.</x:v>
       </x:c>
       <x:c r="T21" s="48" t="str">
         <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:1967; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs
-Aspire E2E TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx</x:v>
+Aspire E2E TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx
+QuoteEngine fix commit: c926434. Targeted retest TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-quoteengine-anonymous-demo-retest.trx</x:v>
       </x:c>
       <x:c r="U21" s="49" t="str">
         <x:v>2026-06-23</x:v>
@@ -8522,13 +8540,13 @@
         <x:v>Failed</x:v>
       </x:c>
       <x:c r="H25" s="48" t="str">
-        <x:v>Failed in latest browser suite</x:v>
+        <x:v>Failed after partial fix</x:v>
       </x:c>
       <x:c r="I25" s="48" t="str">
-        <x:v>Not started</x:v>
+        <x:v>In progress</x:v>
       </x:c>
       <x:c r="J25" s="48" t="str">
-        <x:v>Needs retest loop</x:v>
+        <x:v>Failed</x:v>
       </x:c>
       <x:c r="K25" s="48" t="str">
         <x:v>P1</x:v>
@@ -8549,7 +8567,8 @@
         <x:v>BrowserJourneyGateTests.QuoteEngine_AnonymousDemo_EstimatesWithoutFormalArtifacts (Maliev.Aspire/Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs:896)
 2026-06-23 browser-suite failure batch: 14 failed, 42 passed, 0 skipped, 56 total.
 TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx.
-- QuoteEngine_AnonymousDemo_EstimatesWithoutFormalArtifacts: Microsoft.Playwright.PlaywrightException : Locator expected to be visible Error: element(s) not found Call log: - Expect "ToBeVisibleAsync" with timeout 30000ms - waiting for GetByText("Demo only")</x:v>
+- QuoteEngine_AnonymousDemo_EstimatesWithoutFormalArtifacts: Microsoft.Playwright.PlaywrightException : Locator expected to be visible Error: element(s) not found Call log: - Expect "ToBeVisibleAsync" with timeout 30000ms - waiting for GetByText("Demo only")
+2026-06-23 targeted retest after QuoteEngine c926434: Demo only cue is now satisfied; remaining failure is waiting for role button '3D Model' exact at BrowserJourneyGateTests.cs:906. TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-quoteengine-anonymous-demo-retest.trx.</x:v>
       </x:c>
       <x:c r="Q25" s="48" t="str">
         <x:v>Maliev.QuoteEngine.Bff; Optional MaterialService/PricingService if demo uses live read-only reference data.; No ProjectService, QuotationService, UploadService, OrderService, PaymentService, or DeliveryService mutation.</x:v>
@@ -8559,11 +8578,13 @@
       </x:c>
       <x:c r="S25" s="48" t="str">
         <x:v>Define the demo asset catalog, disclaimer wording, and whether demo pricing uses fixed fixtures or live read-only pricing.
-Latest browser-suite failure(s): QuoteEngine_AnonymousDemo_EstimatesWithoutFormalArtifacts</x:v>
+Latest browser-suite failure(s): QuoteEngine_AnonymousDemo_EstimatesWithoutFormalArtifacts
+Post-fix anonymous demo retest still lacks visible 3D Model tab/button.</x:v>
       </x:c>
       <x:c r="T25" s="48" t="str">
         <x:v>Maliev.Aspire.Tests/specs/E2E_USER_JOURNEY_STORIES.md:2200; Maliev.Aspire.Tests/E2E/BrowserJourneyGateTests.cs
-Aspire E2E TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx</x:v>
+Aspire E2E TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-browser-suite-20260623.trx
+QuoteEngine fix commit: c926434. Targeted retest TRX: B:/maliev/Maliev.Aspire/Maliev.Aspire.Tests/TestResults/feature-tracker-quoteengine-anonymous-demo-retest.trx</x:v>
       </x:c>
       <x:c r="U25" s="49" t="str">
         <x:v>2026-06-23</x:v>
@@ -9068,7 +9089,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R987aab7464c645fc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R18d6054a4d494e68"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/maliev-feature-user-story-status.xlsx
+++ b/docs/maliev-feature-user-story-status.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R5f9c9fb9ecd94a41"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="R776c36a76533485f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R106275d2e2554d29"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="Rb5844ea2fb10437f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R5783d801fc7b494a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="R11b3b8e1a5784055"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="Rd2f21f9c64bb4bf5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="R42b572cbf5194a40"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -607,7 +607,7 @@
         <x:v>As a customer, I can start a quote from the web quote page, upload CAD files for an instant estimate, or hand off the session to Make Studio.</x:v>
       </x:c>
       <x:c r="E3" s="3" t="str">
-        <x:v>The quote page presents Make Studio/demo actions, accepts supported CAD uploads, tracks analysis status, returns an estimate, and can mint a signed handoff token.</x:v>
+        <x:v>The quote page presents Make Studio actions, accepts supported CAD uploads, tracks analysis status, returns an estimate, and can mint a signed handoff token.</x:v>
       </x:c>
       <x:c r="F3" s="3" t="str">
         <x:v>Current code-derived</x:v>
@@ -634,7 +634,7 @@
         <x:v>Maliev.Web.Client/Pages/Quote.razor; InstantQuotePanel.razor; QuoteDropzone.razor</x:v>
       </x:c>
       <x:c r="N3" s="3" t="str">
-        <x:v>/quote; Start in Make Studio; Try demo; quote dropzone; estimate controls</x:v>
+        <x:v>/quote; Start in Make Studio; quote dropzone; estimate controls</x:v>
       </x:c>
       <x:c r="O3" s="3" t="str">
         <x:v>QuoteController reference-data, estimate, uploads/resumable, complete, handoff-token, analysis-status</x:v>
@@ -652,7 +652,7 @@
         <x:v>Use current Make Studio handoff and API estimate behavior as canonical</x:v>
       </x:c>
       <x:c r="T3" s="3" t="str">
-        <x:v>Quote.razor:15-21; InstantQuotePanel.razor:23,139,145,215,256; QuoteUploadService.cs:13-43; QuoteUploadHandoffToken.cs</x:v>
+        <x:v>Quote.razor (Make Studio quote start); InstantQuotePanel.razor:23,139,145,215,256; QuoteUploadService.cs:13-43; QuoteUploadHandoffToken.cs</x:v>
       </x:c>
       <x:c r="U3" s="3" t="str">
         <x:v>2026-06-23</x:v>
@@ -986,7 +986,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rffc6791b83d14fc9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd3350cb6c6de4f0b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1671,7 +1671,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R92a7fb7af1364d3b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd17a6bb574684d69"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1776,13 +1776,13 @@
         <x:v>Maliev.QuoteEngine</x:v>
       </x:c>
       <x:c r="C2" s="3" t="str">
-        <x:v>Chat quote workspace routes and launch shell</x:v>
+        <x:v>Agentic manufacturing workspace routes and launch shell</x:v>
       </x:c>
       <x:c r="D2" s="3" t="str">
-        <x:v>As a customer, I can open the chat-based quote workspace at the root, quotes, new-project, or demo routes and use the rail to start/search/manage projects.</x:v>
+        <x:v>As a customer, I can open the agentic manufacturing workspace, chat with quote agents, start or search projects, and move parts through analysis and quoting.</x:v>
       </x:c>
       <x:c r="E2" s="3" t="str">
-        <x:v>The workspace routes load QuoteAgentLaunchShell, support demo mode, new project actions, projects/search pages, rail navigation, sign-in handoff, and project duplicate/pin/archive/achieve actions.</x:v>
+        <x:v>The workspace loads QuoteAgentLaunchShell, lets customers chat with manufacturing agents, upload and analyze parts, manage projects/search, and continue into quote actions.</x:v>
       </x:c>
       <x:c r="F2" s="3" t="str">
         <x:v>Current code-derived</x:v>
@@ -1803,13 +1803,13 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L2" s="3" t="str">
-        <x:v>Blazor workspace -&gt; QuoteEngineApiClient -&gt; quote/v1 project nav/search/actions DTOs -&gt; auth/demo state</x:v>
+        <x:v>Blazor workspace -&gt; QuoteEngineApiClient -&gt; quote/v1 project nav/search/actions DTOs -&gt; auth/session state</x:v>
       </x:c>
       <x:c r="M2" s="3" t="str">
         <x:v>QuoteWorkspace.razor; QuoteAgentLaunchShell.razor</x:v>
       </x:c>
       <x:c r="N2" s="3" t="str">
-        <x:v>@page /, /quotes, /quotes/new, /quote/new, /projects/new, /demo; rail New project/Projects/search</x:v>
+        <x:v>@page /, /quotes, /quotes/new, /quote/new, /projects/new; rail New project/Projects/search; agent chat composer</x:v>
       </x:c>
       <x:c r="O2" s="3" t="str">
         <x:v>QuoteController projects/nav/detail/duplicate/pin/archive/achieve; AgentController search</x:v>
@@ -1827,7 +1827,7 @@
         <x:v>Use current chat workspace behavior as canonical</x:v>
       </x:c>
       <x:c r="T2" s="3" t="str">
-        <x:v>QuoteWorkspace.razor:1-6,39,439,470; QuoteAgentLaunchShell.razor:36,48-54,338-474,5829-5867</x:v>
+        <x:v>QuoteWorkspace.razor:1-5,39,470; QuoteAgentLaunchShell.razor:36,48-54,338-474,5829-5867</x:v>
       </x:c>
       <x:c r="U2" s="3" t="str">
         <x:v>2026-06-23</x:v>
@@ -2356,7 +2356,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rba9760ac3c574f0d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R289d78b3e7ee465b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/maliev-feature-user-story-status.xlsx
+++ b/docs/maliev-feature-user-story-status.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R5783d801fc7b494a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="R11b3b8e1a5784055"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="Rd2f21f9c64bb4bf5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="R42b572cbf5194a40"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R24a0250f536c47ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="Re0d401d738854163"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R99dddeb2b0a54f20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="Rf8063a35d9214f5f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -350,7 +350,6 @@
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="71.87999725341797" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="14.5" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -358,7 +357,6 @@
         <x:v>Canonical MALIEV feature user story tracker</x:v>
       </x:c>
       <x:c r="B1" s="2" t="str"/>
-      <x:c r="C1" s="2"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="3" t="str">
@@ -367,7 +365,6 @@
       <x:c r="B2" s="3" t="str">
         <x:v>2026-06-23</x:v>
       </x:c>
-      <x:c r="C2" s="3"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="3" t="str">
@@ -376,17 +373,13 @@
       <x:c r="B3" s="3" t="str">
         <x:v>Only current code-derived user stories are tracked.</x:v>
       </x:c>
-      <x:c r="C3" s="3"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="2" t="str">
         <x:v>Service</x:v>
       </x:c>
       <x:c r="B4" s="2" t="str">
-        <x:v>Current code-derived rows</x:v>
-      </x:c>
-      <x:c r="C4" s="2" t="str">
-        <x:v>Total tracked rows</x:v>
+        <x:v>Current tracked stories</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -396,9 +389,6 @@
       <x:c r="B5" s="3" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C5" s="3" t="n">
-        <x:v>7</x:v>
-      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="3" t="str">
@@ -407,9 +397,6 @@
       <x:c r="B6" s="3" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C6" s="3" t="n">
-        <x:v>9</x:v>
-      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="3" t="str">
@@ -418,9 +405,6 @@
       <x:c r="B7" s="3" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C7" s="3" t="n">
-        <x:v>9</x:v>
-      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="3" t="str">
@@ -429,7 +413,6 @@
       <x:c r="B8" s="3" t="str">
         <x:v>Test every current code-derived user story, document errors, fix logistical/UX issues, then retest.</x:v>
       </x:c>
-      <x:c r="C8" s="3"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -459,7 +442,7 @@
     <x:col min="17" max="17" width="50.5" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="48.25" hidden="0" customWidth="1"/>
     <x:col min="19" max="19" width="55.25" hidden="0" customWidth="1"/>
-    <x:col min="20" max="20" width="94.87999725341797" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="109.5" hidden="0" customWidth="1"/>
     <x:col min="21" max="21" width="13.880000114440918" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -986,7 +969,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd3350cb6c6de4f0b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4831fb5f19174170"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1292,7 +1275,7 @@
         <x:v>As sales staff, I can triage web contact requests and create, search, edit, merge, tag, and review customers.</x:v>
       </x:c>
       <x:c r="E5" s="3" t="str">
-        <x:v>Customer/contact request pages route to controllers for list/detail/create/update, address/contact/company data, and legacy customer redirects remain supported.</x:v>
+        <x:v>Customer/contact request pages route to controllers for list/detail/create/update, address/contact/company data, and supported customer routes.</x:v>
       </x:c>
       <x:c r="F5" s="3" t="str">
         <x:v>Current code-derived</x:v>
@@ -1334,7 +1317,7 @@
         <x:v>Customer records, contact requests, addresses/tags</x:v>
       </x:c>
       <x:c r="S5" s="3" t="str">
-        <x:v>Needs browser retest of legacy redirect routes</x:v>
+        <x:v>Needs browser retest of supported customer routes</x:v>
       </x:c>
       <x:c r="T5" s="3" t="str">
         <x:v>CustomersController.cs:20,35,51,134,167,176,185,199,250,264,278,439,456; Contact request pages</x:v>
@@ -1671,7 +1654,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd17a6bb574684d69"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R047060b36b884c0d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1693,7 +1676,7 @@
     <x:col min="11" max="11" width="8.75" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="112" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="75.87999725341797" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="84.37999725341797" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="86.75" hidden="0" customWidth="1"/>
     <x:col min="15" max="15" width="123.37999725341797" hidden="0" customWidth="1"/>
     <x:col min="16" max="16" width="94.87999725341797" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="59.880001068115234" hidden="0" customWidth="1"/>
@@ -2356,7 +2339,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R289d78b3e7ee465b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2865fd51e543456d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/maliev-feature-user-story-status.xlsx
+++ b/docs/maliev-feature-user-story-status.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R24a0250f536c47ba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="Re0d401d738854163"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R99dddeb2b0a54f20"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="Rf8063a35d9214f5f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R4951e6e7fb174d34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="R3cbbc007e1394284"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="Re06731d698074229"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="R197f169ab6464859"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:U8" headerRowCount="1">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:U30" headerRowCount="1">
   <x:tableColumns count="21">
     <x:tableColumn id="1" name="Story ID"/>
     <x:tableColumn id="2" name="App Surface"/>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table1" displayName="Table1" ref="A1:U10" headerRowCount="1">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table1" displayName="Table1" ref="A1:U45" headerRowCount="1">
   <x:tableColumns count="21">
     <x:tableColumn id="1" name="Story ID"/>
     <x:tableColumn id="2" name="App Surface"/>
@@ -125,7 +125,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table1" displayName="Table1" ref="A1:U10" headerRowCount="1">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table1" displayName="Table1" ref="A1:U39" headerRowCount="1">
   <x:tableColumns count="21">
     <x:tableColumn id="1" name="Story ID"/>
     <x:tableColumn id="2" name="App Surface"/>
@@ -349,7 +349,7 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="71.87999725341797" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="97.25" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -360,7 +360,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="3" t="str">
-        <x:v>Current-only rebuild</x:v>
+        <x:v>Expanded current-code rebuild</x:v>
       </x:c>
       <x:c r="B2" s="3" t="str">
         <x:v>2026-06-23</x:v>
@@ -371,7 +371,7 @@
         <x:v>Workbook rule</x:v>
       </x:c>
       <x:c r="B3" s="3" t="str">
-        <x:v>Only current code-derived user stories are tracked.</x:v>
+        <x:v>Only current code-derived user stories are tracked. Rows are derived from current UI, BFF/API, service-client, and DTO boundaries.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -387,7 +387,7 @@
         <x:v>Maliev.Web</x:v>
       </x:c>
       <x:c r="B5" s="3" t="n">
-        <x:v>7</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -395,7 +395,7 @@
         <x:v>Maliev.Intranet</x:v>
       </x:c>
       <x:c r="B6" s="3" t="n">
-        <x:v>9</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -403,14 +403,22 @@
         <x:v>Maliev.QuoteEngine</x:v>
       </x:c>
       <x:c r="B7" s="3" t="n">
-        <x:v>9</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="3" t="str">
+        <x:v>Total</x:v>
+      </x:c>
+      <x:c r="B8" s="3" t="n">
+        <x:v>111</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="3" t="str">
         <x:v>Next loop</x:v>
       </x:c>
-      <x:c r="B8" s="3" t="str">
+      <x:c r="B9" s="3" t="str">
         <x:v>Test every current code-derived user story, document errors, fix logistical/UX issues, then retest.</x:v>
       </x:c>
     </x:row>
@@ -423,26 +431,26 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="12.130000114440918" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="9.130000114440918" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="12.25" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="35.5" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="104.75" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="124.75" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="28.25" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="80.37999725341797" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="98" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="18.25" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="18.75" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="22.1299991607666" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="19.8799991607666" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="10.380000114440918" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="13" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="8.75" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="80.5" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="64.5" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="101.5" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="85.25" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="83.12999725341797" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="50.5" hidden="0" customWidth="1"/>
-    <x:col min="18" max="18" width="48.25" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="55.25" hidden="0" customWidth="1"/>
-    <x:col min="20" max="20" width="109.5" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="57.25" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="45.5" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="121.37999725341797" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="77.62999725341797" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="52" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="38.130001068115234" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="38.75" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="45.630001068115234" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="51.75" hidden="0" customWidth="1"/>
     <x:col min="21" max="21" width="13.880000114440918" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -513,19 +521,19 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="3" t="str">
-        <x:v>WEB-CODE-001</x:v>
+        <x:v>WEB-001</x:v>
       </x:c>
       <x:c r="B2" s="3" t="str">
         <x:v>Maliev.Web</x:v>
       </x:c>
       <x:c r="C2" s="3" t="str">
-        <x:v>Public storefront shell and content</x:v>
+        <x:v>Public home and navigation</x:v>
       </x:c>
       <x:c r="D2" s="3" t="str">
-        <x:v>As a visitor, I can browse the public home, services, materials, shop, static policy, blog, and case-study pages before starting work.</x:v>
+        <x:v>As a visitor, I can land on the public site and navigate to services, materials, shop, quote, and account areas.</x:v>
       </x:c>
       <x:c r="E2" s="3" t="str">
-        <x:v>Routeable pages render public content and navigation exposes Services, Shop, Materials, Make Studio, and account actions without requiring an authenticated session.</x:v>
+        <x:v>Home and layout routes render public content and primary navigation without requiring a customer session.</x:v>
       </x:c>
       <x:c r="F2" s="3" t="str">
         <x:v>Current code-derived</x:v>
@@ -546,31 +554,31 @@
         <x:v>P1</x:v>
       </x:c>
       <x:c r="L2" s="3" t="str">
-        <x:v>Blazor client routes -&gt; SiteContent/navigation -&gt; catalog/content BFF endpoints</x:v>
+        <x:v>Blazor pages -&gt; MainLayout/SiteContent -&gt; static and BFF-backed content</x:v>
       </x:c>
       <x:c r="M2" s="3" t="str">
-        <x:v>Maliev.Web.Client/Pages/Home.razor; MainLayout.razor</x:v>
+        <x:v>Home.razor; MainLayout.razor; SiteContent.cs</x:v>
       </x:c>
       <x:c r="N2" s="3" t="str">
-        <x:v>@page routes: /, /services, /materials, /shop, /about, /contact, /faq, /shipping-returns, /privacy, /terms, /industries, /case-studies, /blog</x:v>
+        <x:v>/, nav Services, Materials, Shop, Make Studio, Account</x:v>
       </x:c>
       <x:c r="O2" s="3" t="str">
-        <x:v>CatalogController, MaterialsController, BlogController, SeoController</x:v>
+        <x:v>SeoController robots/sitemap for crawl entry points</x:v>
       </x:c>
       <x:c r="P2" s="3" t="str">
-        <x:v>WebBffEndpointTests; CommerceCatalogBoundaryTests</x:v>
+        <x:v>WebBffEndpointTests Seo</x:v>
       </x:c>
       <x:c r="Q2" s="3" t="str">
-        <x:v>Web BFF, Catalog/Content services, SEO</x:v>
+        <x:v>Web client, Web BFF, content/static assets</x:v>
       </x:c>
       <x:c r="R2" s="3" t="str">
-        <x:v>Read-only browsing except analytics/cookies</x:v>
+        <x:v>Read-only browsing</x:v>
       </x:c>
       <x:c r="S2" s="3" t="str">
-        <x:v>Not yet browser-tested in this loop</x:v>
+        <x:v>Needs responsive browser pass in later loop</x:v>
       </x:c>
       <x:c r="T2" s="3" t="str">
-        <x:v>SiteContent.cs:33-43; MainLayout.razor:19,60; CatalogController.cs; BlogController.cs; MaterialsController.cs</x:v>
+        <x:v>Home.razor:1; MainLayout.razor; SiteContent.cs</x:v>
       </x:c>
       <x:c r="U2" s="3" t="str">
         <x:v>2026-06-23</x:v>
@@ -578,25 +586,25 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="3" t="str">
-        <x:v>WEB-CODE-002</x:v>
+        <x:v>WEB-002</x:v>
       </x:c>
       <x:c r="B3" s="3" t="str">
         <x:v>Maliev.Web</x:v>
       </x:c>
       <x:c r="C3" s="3" t="str">
-        <x:v>Quote start and Make Studio handoff</x:v>
+        <x:v>Services listing</x:v>
       </x:c>
       <x:c r="D3" s="3" t="str">
-        <x:v>As a customer, I can start a quote from the web quote page, upload CAD files for an instant estimate, or hand off the session to Make Studio.</x:v>
+        <x:v>As a visitor, I can browse available manufacturing services.</x:v>
       </x:c>
       <x:c r="E3" s="3" t="str">
-        <x:v>The quote page presents Make Studio actions, accepts supported CAD uploads, tracks analysis status, returns an estimate, and can mint a signed handoff token.</x:v>
+        <x:v>The services page lists service content and links to service detail routes.</x:v>
       </x:c>
       <x:c r="F3" s="3" t="str">
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G3" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Needs manual / browser test</x:v>
       </x:c>
       <x:c r="H3" s="3" t="str">
         <x:v>Not tested in current loop</x:v>
@@ -608,34 +616,32 @@
         <x:v>Not started</x:v>
       </x:c>
       <x:c r="K3" s="3" t="str">
-        <x:v>P0</x:v>
+        <x:v>P2</x:v>
       </x:c>
       <x:c r="L3" s="3" t="str">
-        <x:v>Web quote UI -&gt; QuoteUploadService -&gt; web/v1/quote estimate/upload/handoff DTOs -&gt; QuoteEngine URL</x:v>
+        <x:v>Blazor route -&gt; SiteContent service metadata</x:v>
       </x:c>
       <x:c r="M3" s="3" t="str">
-        <x:v>Maliev.Web.Client/Pages/Quote.razor; InstantQuotePanel.razor; QuoteDropzone.razor</x:v>
+        <x:v>Services.razor</x:v>
       </x:c>
       <x:c r="N3" s="3" t="str">
-        <x:v>/quote; Start in Make Studio; quote dropzone; estimate controls</x:v>
+        <x:v>/services</x:v>
       </x:c>
       <x:c r="O3" s="3" t="str">
-        <x:v>QuoteController reference-data, estimate, uploads/resumable, complete, handoff-token, analysis-status</x:v>
-      </x:c>
-      <x:c r="P3" s="3" t="str">
-        <x:v>WebBffEndpointTests Quote*</x:v>
-      </x:c>
+        <x:v>Static content model</x:v>
+      </x:c>
+      <x:c r="P3" s="3" t="str"/>
       <x:c r="Q3" s="3" t="str">
-        <x:v>Web BFF, QuoteEngine, Storage, Geometry/Pricing through BFF</x:v>
+        <x:v>Web client</x:v>
       </x:c>
       <x:c r="R3" s="3" t="str">
-        <x:v>Temporary upload blobs, resumable upload state, handoff token</x:v>
+        <x:v>Read-only browsing</x:v>
       </x:c>
       <x:c r="S3" s="3" t="str">
-        <x:v>Use current Make Studio handoff and API estimate behavior as canonical</x:v>
+        <x:v>Needs content completeness review</x:v>
       </x:c>
       <x:c r="T3" s="3" t="str">
-        <x:v>Quote.razor (Make Studio quote start); InstantQuotePanel.razor:23,139,145,215,256; QuoteUploadService.cs:13-43; QuoteUploadHandoffToken.cs</x:v>
+        <x:v>Services.razor:1; SiteContent.cs</x:v>
       </x:c>
       <x:c r="U3" s="3" t="str">
         <x:v>2026-06-23</x:v>
@@ -643,25 +649,25 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="3" t="str">
-        <x:v>WEB-CODE-003</x:v>
+        <x:v>WEB-003</x:v>
       </x:c>
       <x:c r="B4" s="3" t="str">
         <x:v>Maliev.Web</x:v>
       </x:c>
       <x:c r="C4" s="3" t="str">
-        <x:v>Customer chatbot</x:v>
+        <x:v>Service detail</x:v>
       </x:c>
       <x:c r="D4" s="3" t="str">
-        <x:v>As a visitor or signed-in customer, I can chat with the web assistant and receive session-aware replies.</x:v>
+        <x:v>As a visitor, I can open a service detail page by slug.</x:v>
       </x:c>
       <x:c r="E4" s="3" t="str">
-        <x:v>The chat widget starts or resumes a session, sends messages to the chatbot BFF, handles sign-in-required states, and keeps the composer responsive.</x:v>
+        <x:v>Service detail route resolves slugged service content and presents service-specific information.</x:v>
       </x:c>
       <x:c r="F4" s="3" t="str">
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G4" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Needs manual / browser test</x:v>
       </x:c>
       <x:c r="H4" s="3" t="str">
         <x:v>Not tested in current loop</x:v>
@@ -673,34 +679,32 @@
         <x:v>Not started</x:v>
       </x:c>
       <x:c r="K4" s="3" t="str">
-        <x:v>P1</x:v>
+        <x:v>P2</x:v>
       </x:c>
       <x:c r="L4" s="3" t="str">
-        <x:v>CustomerChatbot component -&gt; web/v1/chatbot sessions/messages -&gt; auth/session claims</x:v>
+        <x:v>Blazor route parameter -&gt; service content lookup</x:v>
       </x:c>
       <x:c r="M4" s="3" t="str">
-        <x:v>Maliev.Web.Client/Components/CustomerChatbot.razor</x:v>
+        <x:v>ServicePage.razor</x:v>
       </x:c>
       <x:c r="N4" s="3" t="str">
-        <x:v>Floating/customer chatbot composer and messages</x:v>
+        <x:v>/services/{Slug}</x:v>
       </x:c>
       <x:c r="O4" s="3" t="str">
-        <x:v>ChatbotController sessions/messages</x:v>
-      </x:c>
-      <x:c r="P4" s="3" t="str">
-        <x:v>CustomerChatbotBoundaryTests; WebBffEndpointTests Chatbot*</x:v>
-      </x:c>
+        <x:v>Static content model</x:v>
+      </x:c>
+      <x:c r="P4" s="3" t="str"/>
       <x:c r="Q4" s="3" t="str">
-        <x:v>Web BFF, Chatbot/agent backend, Auth</x:v>
+        <x:v>Web client</x:v>
       </x:c>
       <x:c r="R4" s="3" t="str">
-        <x:v>Chat sessions and messages</x:v>
+        <x:v>Read-only browsing</x:v>
       </x:c>
       <x:c r="S4" s="3" t="str">
-        <x:v>Needs browser retest for unauthenticated and authenticated states</x:v>
+        <x:v>Needs 404/unknown slug browser check</x:v>
       </x:c>
       <x:c r="T4" s="3" t="str">
-        <x:v>CustomerChatbot.razor:735,769,824,948,1021; ChatbotController.cs</x:v>
+        <x:v>ServicePage.razor:1</x:v>
       </x:c>
       <x:c r="U4" s="3" t="str">
         <x:v>2026-06-23</x:v>
@@ -708,19 +712,19 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="3" t="str">
-        <x:v>WEB-CODE-004</x:v>
+        <x:v>WEB-004</x:v>
       </x:c>
       <x:c r="B5" s="3" t="str">
         <x:v>Maliev.Web</x:v>
       </x:c>
       <x:c r="C5" s="3" t="str">
-        <x:v>Authentication and account access</x:v>
+        <x:v>Materials catalog</x:v>
       </x:c>
       <x:c r="D5" s="3" t="str">
-        <x:v>As a customer, I can sign in, sign up, recover/reset my password, verify email, use Google/passkey flows, and manage the current session.</x:v>
+        <x:v>As a buyer, I can browse material options before starting a quote.</x:v>
       </x:c>
       <x:c r="E5" s="3" t="str">
-        <x:v>Auth pages call BFF endpoints for email/password, Google callback, quote-start auth, token refresh, email verification, passkeys, and sign-out.</x:v>
+        <x:v>Materials page lists material content and links to material detail pages.</x:v>
       </x:c>
       <x:c r="F5" s="3" t="str">
         <x:v>Current code-derived</x:v>
@@ -738,34 +742,34 @@
         <x:v>Not started</x:v>
       </x:c>
       <x:c r="K5" s="3" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="L5" s="3" t="str">
-        <x:v>Auth pages -&gt; /auth controller -&gt; auth cookies/claims/session -&gt; downstream customer identity</x:v>
+        <x:v>Blazor pages -&gt; material content -&gt; datasheet BFF</x:v>
       </x:c>
       <x:c r="M5" s="3" t="str">
-        <x:v>Maliev.Web.Client/Pages/Auth*.razor; Web BFF AuthController</x:v>
+        <x:v>Materials.razor</x:v>
       </x:c>
       <x:c r="N5" s="3" t="str">
-        <x:v>/auth/sign-in, /auth/sign-up, /auth/forgot-password, /auth/reset-password, /auth/chatbot-complete</x:v>
+        <x:v>/materials</x:v>
       </x:c>
       <x:c r="O5" s="3" t="str">
-        <x:v>AuthController /auth/google, callback, sign-in, sign-up, forgot/reset, sign-out, verify-email, refresh-claims, passkey</x:v>
+        <x:v>MaterialsController datasheet endpoint</x:v>
       </x:c>
       <x:c r="P5" s="3" t="str">
-        <x:v>AccountControllerBoundaryTests; WebBffEndpointTests AccountSession</x:v>
+        <x:v>WebBffEndpointTests Materials</x:v>
       </x:c>
       <x:c r="Q5" s="3" t="str">
-        <x:v>Web BFF, AuthService, CustomerService</x:v>
+        <x:v>Web client, Web BFF, PDF generation/storage</x:v>
       </x:c>
       <x:c r="R5" s="3" t="str">
-        <x:v>Session cookies, auth claims, verification/reset state</x:v>
+        <x:v>Read-only browsing</x:v>
       </x:c>
       <x:c r="S5" s="3" t="str">
-        <x:v>Needs browser retest for Google/passkey availability in local environment</x:v>
+        <x:v>Needs material coverage review</x:v>
       </x:c>
       <x:c r="T5" s="3" t="str">
-        <x:v>AuthController.cs; AuthSignIn.razor; AuthSignUp.razor; AuthForgotPassword.razor; AuthResetPassword.razor</x:v>
+        <x:v>Materials.razor:1; MaterialsController.cs:15,26</x:v>
       </x:c>
       <x:c r="U5" s="3" t="str">
         <x:v>2026-06-23</x:v>
@@ -773,19 +777,19 @@
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="3" t="str">
-        <x:v>WEB-CODE-005</x:v>
+        <x:v>WEB-005</x:v>
       </x:c>
       <x:c r="B6" s="3" t="str">
         <x:v>Maliev.Web</x:v>
       </x:c>
       <x:c r="C6" s="3" t="str">
-        <x:v>Account profile, addresses, preferences, orders</x:v>
+        <x:v>Material detail and datasheet</x:v>
       </x:c>
       <x:c r="D6" s="3" t="str">
-        <x:v>As a signed-in customer, I can view and update account profile data, addresses, preferences, orders, and related quote/order history.</x:v>
+        <x:v>As a buyer, I can open a material detail page and download a datasheet.</x:v>
       </x:c>
       <x:c r="E6" s="3" t="str">
-        <x:v>Account routes require session context, read profile/orders, update profile/email/address data, and expose culture preferences plus location/static-map helpers.</x:v>
+        <x:v>The material detail route renders slugged material content and the BFF streams a material datasheet PDF.</x:v>
       </x:c>
       <x:c r="F6" s="3" t="str">
         <x:v>Current code-derived</x:v>
@@ -806,31 +810,31 @@
         <x:v>P1</x:v>
       </x:c>
       <x:c r="L6" s="3" t="str">
-        <x:v>Account pages -&gt; web/v1/account/address/preferences -&gt; customer/order/location DTOs</x:v>
+        <x:v>Material detail page -&gt; web/v1/materials/{slug}/datasheet.pdf</x:v>
       </x:c>
       <x:c r="M6" s="3" t="str">
-        <x:v>Account*.razor pages</x:v>
+        <x:v>MaterialDetail.razor</x:v>
       </x:c>
       <x:c r="N6" s="3" t="str">
-        <x:v>/account, /account/profile, /account/preferences, /account/addresses, /account/orders, /account/orders/{id}, /account/quotes</x:v>
+        <x:v>/materials/{Slug}</x:v>
       </x:c>
       <x:c r="O6" s="3" t="str">
-        <x:v>AccountController; AddressController; PreferencesController</x:v>
+        <x:v>MaterialsController GET {slug}/datasheet.pdf</x:v>
       </x:c>
       <x:c r="P6" s="3" t="str">
-        <x:v>AccountControllerBoundaryTests; AccountAddressGoogleSourceTests; WebBffEndpointTests</x:v>
+        <x:v>WebBffEndpointTests Materials</x:v>
       </x:c>
       <x:c r="Q6" s="3" t="str">
-        <x:v>Web BFF, CustomerService, OrderService, Google/static-map config</x:v>
+        <x:v>Web BFF, PDF service/content</x:v>
       </x:c>
       <x:c r="R6" s="3" t="str">
-        <x:v>Profile, email-change request, addresses, preferences</x:v>
+        <x:v>PDF download stream</x:v>
       </x:c>
       <x:c r="S6" s="3" t="str">
-        <x:v>Needs authenticated browser retest</x:v>
+        <x:v>Needs browser download smoke test</x:v>
       </x:c>
       <x:c r="T6" s="3" t="str">
-        <x:v>AccountController.cs; AddressController.cs; PreferencesController.cs; AccountOrders.razor; AccountAddresses.razor</x:v>
+        <x:v>MaterialDetail.razor:1; MaterialsController.cs:15,26</x:v>
       </x:c>
       <x:c r="U6" s="3" t="str">
         <x:v>2026-06-23</x:v>
@@ -838,19 +842,19 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="3" t="str">
-        <x:v>WEB-CODE-006</x:v>
+        <x:v>WEB-006</x:v>
       </x:c>
       <x:c r="B7" s="3" t="str">
         <x:v>Maliev.Web</x:v>
       </x:c>
       <x:c r="C7" s="3" t="str">
-        <x:v>Shop, cart, checkout, shipping</x:v>
+        <x:v>Shop catalog</x:v>
       </x:c>
       <x:c r="D7" s="3" t="str">
-        <x:v>As a shopper, I can browse products, add items to cart, draft checkout information, and review shipping rates/tracking.</x:v>
+        <x:v>As a shopper, I can browse catalog collections and products.</x:v>
       </x:c>
       <x:c r="E7" s="3" t="str">
-        <x:v>Catalog product/collection endpoints back shop pages; checkout drafts persist form state; shipping endpoints expose couriers, rates, and tracking.</x:v>
+        <x:v>Shop page uses catalog endpoints for collections, product lists, collection images, and product media.</x:v>
       </x:c>
       <x:c r="F7" s="3" t="str">
         <x:v>Current code-derived</x:v>
@@ -871,31 +875,31 @@
         <x:v>P1</x:v>
       </x:c>
       <x:c r="L7" s="3" t="str">
-        <x:v>Shop/cart/checkout UI -&gt; catalog/checkout/shipping BFF contracts -&gt; commerce/order/shipping services</x:v>
+        <x:v>Shop UI -&gt; web/v1/catalog collections/products/media</x:v>
       </x:c>
       <x:c r="M7" s="3" t="str">
-        <x:v>Shop.razor; ProductDetail.razor; Cart.razor; Checkout.razor</x:v>
+        <x:v>Shop.razor</x:v>
       </x:c>
       <x:c r="N7" s="3" t="str">
-        <x:v>/shop, /shop/{Handle}, /cart, /checkout</x:v>
+        <x:v>/shop</x:v>
       </x:c>
       <x:c r="O7" s="3" t="str">
-        <x:v>CatalogController, CheckoutController, ShippingController</x:v>
+        <x:v>CatalogController collections, products, media, collection image</x:v>
       </x:c>
       <x:c r="P7" s="3" t="str">
-        <x:v>CommerceCatalogBoundaryTests; CheckoutControllerTests; CheckoutDraftServiceTests; ShippingControllerTests</x:v>
+        <x:v>CommerceCatalogBoundaryTests; WebBffEndpointTests Catalog</x:v>
       </x:c>
       <x:c r="Q7" s="3" t="str">
-        <x:v>Web BFF, CatalogService, Checkout/Order, Shipping</x:v>
+        <x:v>Web BFF, Catalog/Commerce, Storage</x:v>
       </x:c>
       <x:c r="R7" s="3" t="str">
-        <x:v>Cart state, checkout draft, shipping-rate request</x:v>
+        <x:v>Read-only catalog queries</x:v>
       </x:c>
       <x:c r="S7" s="3" t="str">
-        <x:v>Payment/order completion needs later E2E test</x:v>
+        <x:v>Needs full storefront browser pass</x:v>
       </x:c>
       <x:c r="T7" s="3" t="str">
-        <x:v>CatalogController.cs; CheckoutController.cs; ShippingController.cs; Cart.razor; Checkout.razor</x:v>
+        <x:v>Shop.razor:1; CatalogController.cs:14-87</x:v>
       </x:c>
       <x:c r="U7" s="3" t="str">
         <x:v>2026-06-23</x:v>
@@ -903,19 +907,19 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="3" t="str">
-        <x:v>WEB-CODE-007</x:v>
+        <x:v>WEB-007</x:v>
       </x:c>
       <x:c r="B8" s="3" t="str">
         <x:v>Maliev.Web</x:v>
       </x:c>
       <x:c r="C8" s="3" t="str">
-        <x:v>Contact, downloads, SEO, culture</x:v>
+        <x:v>Product detail</x:v>
       </x:c>
       <x:c r="D8" s="3" t="str">
-        <x:v>As a visitor, I can submit contact messages, download blog/material PDFs, switch culture, and access robots/sitemap metadata.</x:v>
+        <x:v>As a shopper, I can open a product detail page by handle.</x:v>
       </x:c>
       <x:c r="E8" s="3" t="str">
-        <x:v>Contact messages post through the BFF; PDF endpoints stream content; SEO endpoints expose robots and sitemap; preferences save selected culture.</x:v>
+        <x:v>Product detail route loads a product by handle and associated media from catalog endpoints.</x:v>
       </x:c>
       <x:c r="F8" s="3" t="str">
         <x:v>Current code-derived</x:v>
@@ -933,43 +937,1469 @@
         <x:v>Not started</x:v>
       </x:c>
       <x:c r="K8" s="3" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="L8" s="3" t="str">
+        <x:v>Product route parameter -&gt; catalog product detail contract</x:v>
+      </x:c>
+      <x:c r="M8" s="3" t="str">
+        <x:v>ProductDetail.razor</x:v>
+      </x:c>
+      <x:c r="N8" s="3" t="str">
+        <x:v>/shop/{Handle}</x:v>
+      </x:c>
+      <x:c r="O8" s="3" t="str">
+        <x:v>CatalogController GET products/{handle}</x:v>
+      </x:c>
+      <x:c r="P8" s="3" t="str">
+        <x:v>CommerceCatalogBoundaryTests</x:v>
+      </x:c>
+      <x:c r="Q8" s="3" t="str">
+        <x:v>Web BFF, Catalog/Commerce</x:v>
+      </x:c>
+      <x:c r="R8" s="3" t="str">
+        <x:v>Read-only product lookup</x:v>
+      </x:c>
+      <x:c r="S8" s="3" t="str">
+        <x:v>Needs unavailable-handle browser test</x:v>
+      </x:c>
+      <x:c r="T8" s="3" t="str">
+        <x:v>ProductDetail.razor:1; CatalogController.cs:87</x:v>
+      </x:c>
+      <x:c r="U8" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="3" t="str">
+        <x:v>WEB-008</x:v>
+      </x:c>
+      <x:c r="B9" s="3" t="str">
+        <x:v>Maliev.Web</x:v>
+      </x:c>
+      <x:c r="C9" s="3" t="str">
+        <x:v>Cart</x:v>
+      </x:c>
+      <x:c r="D9" s="3" t="str">
+        <x:v>As a shopper, I can review cart contents before checkout.</x:v>
+      </x:c>
+      <x:c r="E9" s="3" t="str">
+        <x:v>Cart route renders selected items and allows the shopper to proceed to checkout.</x:v>
+      </x:c>
+      <x:c r="F9" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G9" s="3" t="str">
+        <x:v>Needs manual / browser test</x:v>
+      </x:c>
+      <x:c r="H9" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I9" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J9" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K9" s="3" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="L9" s="3" t="str">
+        <x:v>Client cart state -&gt; checkout handoff</x:v>
+      </x:c>
+      <x:c r="M9" s="3" t="str">
+        <x:v>Cart.razor</x:v>
+      </x:c>
+      <x:c r="N9" s="3" t="str">
+        <x:v>/cart</x:v>
+      </x:c>
+      <x:c r="O9" s="3" t="str">
+        <x:v>CheckoutController draft endpoints used after cart</x:v>
+      </x:c>
+      <x:c r="P9" s="3" t="str"/>
+      <x:c r="Q9" s="3" t="str">
+        <x:v>Web client, Checkout BFF</x:v>
+      </x:c>
+      <x:c r="R9" s="3" t="str">
+        <x:v>Client cart state</x:v>
+      </x:c>
+      <x:c r="S9" s="3" t="str">
+        <x:v>Needs cart persistence behavior review</x:v>
+      </x:c>
+      <x:c r="T9" s="3" t="str">
+        <x:v>Cart.razor:1; CheckoutController.cs:15-58</x:v>
+      </x:c>
+      <x:c r="U9" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="3" t="str">
+        <x:v>WEB-009</x:v>
+      </x:c>
+      <x:c r="B10" s="3" t="str">
+        <x:v>Maliev.Web</x:v>
+      </x:c>
+      <x:c r="C10" s="3" t="str">
+        <x:v>Checkout draft</x:v>
+      </x:c>
+      <x:c r="D10" s="3" t="str">
+        <x:v>As a shopper, I can save checkout details while preparing an order.</x:v>
+      </x:c>
+      <x:c r="E10" s="3" t="str">
+        <x:v>Checkout page posts checkout draft and draft-form data through the BFF.</x:v>
+      </x:c>
+      <x:c r="F10" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G10" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H10" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I10" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J10" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K10" s="3" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="L10" s="3" t="str">
+        <x:v>Checkout UI -&gt; web/v1/checkout draft/draft-form</x:v>
+      </x:c>
+      <x:c r="M10" s="3" t="str">
+        <x:v>Checkout.razor</x:v>
+      </x:c>
+      <x:c r="N10" s="3" t="str">
+        <x:v>/checkout</x:v>
+      </x:c>
+      <x:c r="O10" s="3" t="str">
+        <x:v>CheckoutController POST draft, draft-form</x:v>
+      </x:c>
+      <x:c r="P10" s="3" t="str">
+        <x:v>CheckoutControllerTests; CheckoutDraftServiceTests</x:v>
+      </x:c>
+      <x:c r="Q10" s="3" t="str">
+        <x:v>Web BFF, Checkout/Order services</x:v>
+      </x:c>
+      <x:c r="R10" s="3" t="str">
+        <x:v>Checkout draft state</x:v>
+      </x:c>
+      <x:c r="S10" s="3" t="str">
+        <x:v>Order completion needs later E2E coverage</x:v>
+      </x:c>
+      <x:c r="T10" s="3" t="str">
+        <x:v>Checkout.razor:1; CheckoutController.cs:15,21,58</x:v>
+      </x:c>
+      <x:c r="U10" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="3" t="str">
+        <x:v>WEB-010</x:v>
+      </x:c>
+      <x:c r="B11" s="3" t="str">
+        <x:v>Maliev.Web</x:v>
+      </x:c>
+      <x:c r="C11" s="3" t="str">
+        <x:v>Shipping couriers and rates</x:v>
+      </x:c>
+      <x:c r="D11" s="3" t="str">
+        <x:v>As a shopper, I can view courier options and request shipping rates.</x:v>
+      </x:c>
+      <x:c r="E11" s="3" t="str">
+        <x:v>Shipping BFF exposes courier list and rate quotes for checkout/account workflows.</x:v>
+      </x:c>
+      <x:c r="F11" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G11" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H11" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I11" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J11" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K11" s="3" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="L11" s="3" t="str">
+        <x:v>Shipping UI/service calls -&gt; delivery service client</x:v>
+      </x:c>
+      <x:c r="M11" s="3" t="str">
+        <x:v>Checkout/account shipping flows</x:v>
+      </x:c>
+      <x:c r="N11" s="3" t="str">
+        <x:v>Shipping rate/tracking UI surfaces</x:v>
+      </x:c>
+      <x:c r="O11" s="3" t="str">
+        <x:v>ShippingController GET couriers, POST rates</x:v>
+      </x:c>
+      <x:c r="P11" s="3" t="str">
+        <x:v>ShippingControllerTests</x:v>
+      </x:c>
+      <x:c r="Q11" s="3" t="str">
+        <x:v>Web BFF, DeliveryService</x:v>
+      </x:c>
+      <x:c r="R11" s="3" t="str">
+        <x:v>Shipping rate requests</x:v>
+      </x:c>
+      <x:c r="S11" s="3" t="str">
+        <x:v>Needs courier error-state browser test</x:v>
+      </x:c>
+      <x:c r="T11" s="3" t="str">
+        <x:v>ShippingController.cs:14-71</x:v>
+      </x:c>
+      <x:c r="U11" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="3" t="str">
+        <x:v>WEB-011</x:v>
+      </x:c>
+      <x:c r="B12" s="3" t="str">
+        <x:v>Maliev.Web</x:v>
+      </x:c>
+      <x:c r="C12" s="3" t="str">
+        <x:v>Shipment tracking</x:v>
+      </x:c>
+      <x:c r="D12" s="3" t="str">
+        <x:v>As a customer, I can check shipment tracking by tracking code.</x:v>
+      </x:c>
+      <x:c r="E12" s="3" t="str">
+        <x:v>Tracking endpoint returns delivery tracking data for a supplied tracking code.</x:v>
+      </x:c>
+      <x:c r="F12" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G12" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H12" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I12" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J12" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K12" s="3" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="L8" s="3" t="str">
-        <x:v>Public forms/download links -&gt; web/v1 contact/materials/blog/preferences/seo endpoints</x:v>
-      </x:c>
-      <x:c r="M8" s="3" t="str">
-        <x:v>Contact/static pages; material/blog detail pages</x:v>
-      </x:c>
-      <x:c r="N8" s="3" t="str">
-        <x:v>/contact, material datasheet links, blog ebook links, robots.txt, sitemap.xml</x:v>
-      </x:c>
-      <x:c r="O8" s="3" t="str">
-        <x:v>ContactController, BlogController, MaterialsController, PreferencesController, SeoController</x:v>
-      </x:c>
-      <x:c r="P8" s="3" t="str">
-        <x:v>WebBffEndpointTests Contact/Blog/Materials/Seo</x:v>
-      </x:c>
-      <x:c r="Q8" s="3" t="str">
-        <x:v>Web BFF, Content/Storage, Preferences</x:v>
-      </x:c>
-      <x:c r="R8" s="3" t="str">
-        <x:v>Contact message, culture preference</x:v>
-      </x:c>
-      <x:c r="S8" s="3" t="str">
-        <x:v>Needs manual attachment/download smoke test</x:v>
-      </x:c>
-      <x:c r="T8" s="3" t="str">
-        <x:v>ContactController.cs; BlogController.cs; MaterialsController.cs; SeoController.cs</x:v>
-      </x:c>
-      <x:c r="U8" s="3" t="str">
+      <x:c r="L12" s="3" t="str">
+        <x:v>Tracking route -&gt; delivery service client</x:v>
+      </x:c>
+      <x:c r="M12" s="3" t="str">
+        <x:v>Account/order shipping flows</x:v>
+      </x:c>
+      <x:c r="N12" s="3" t="str">
+        <x:v>tracking code lookup</x:v>
+      </x:c>
+      <x:c r="O12" s="3" t="str">
+        <x:v>ShippingController GET tracking/{trackingCode}</x:v>
+      </x:c>
+      <x:c r="P12" s="3" t="str">
+        <x:v>ShippingControllerTests</x:v>
+      </x:c>
+      <x:c r="Q12" s="3" t="str">
+        <x:v>Web BFF, DeliveryService</x:v>
+      </x:c>
+      <x:c r="R12" s="3" t="str">
+        <x:v>Read-only tracking lookup</x:v>
+      </x:c>
+      <x:c r="S12" s="3" t="str">
+        <x:v>Needs invalid tracking-code test</x:v>
+      </x:c>
+      <x:c r="T12" s="3" t="str">
+        <x:v>ShippingController.cs:71</x:v>
+      </x:c>
+      <x:c r="U12" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="3" t="str">
+        <x:v>WEB-012</x:v>
+      </x:c>
+      <x:c r="B13" s="3" t="str">
+        <x:v>Maliev.Web</x:v>
+      </x:c>
+      <x:c r="C13" s="3" t="str">
+        <x:v>Quote start and Make Studio handoff</x:v>
+      </x:c>
+      <x:c r="D13" s="3" t="str">
+        <x:v>As a customer, I can start a quote from the public web quote page and continue in Make Studio.</x:v>
+      </x:c>
+      <x:c r="E13" s="3" t="str">
+        <x:v>Quote page presents Make Studio actions, accepts CAD files, tracks analysis, returns an estimate, and mints a signed handoff token.</x:v>
+      </x:c>
+      <x:c r="F13" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G13" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H13" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I13" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J13" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K13" s="3" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="L13" s="3" t="str">
+        <x:v>Quote UI -&gt; web/v1/quote uploads/estimate/handoff -&gt; QuoteEngine</x:v>
+      </x:c>
+      <x:c r="M13" s="3" t="str">
+        <x:v>Quote.razor; InstantQuotePanel.razor; QuoteDropzone.razor</x:v>
+      </x:c>
+      <x:c r="N13" s="3" t="str">
+        <x:v>/quote; Start in Make Studio; quote dropzone; estimate controls</x:v>
+      </x:c>
+      <x:c r="O13" s="3" t="str">
+        <x:v>QuoteController reference-data, estimate, uploads/resumable, complete, handoff-token, analysis-status</x:v>
+      </x:c>
+      <x:c r="P13" s="3" t="str">
+        <x:v>WebBffEndpointTests Quote*</x:v>
+      </x:c>
+      <x:c r="Q13" s="3" t="str">
+        <x:v>Web BFF, QuoteEngine, Storage, Geometry/Pricing</x:v>
+      </x:c>
+      <x:c r="R13" s="3" t="str">
+        <x:v>Temporary uploads, upload sessions, handoff token</x:v>
+      </x:c>
+      <x:c r="S13" s="3" t="str">
+        <x:v>Needs full upload handoff browser retest</x:v>
+      </x:c>
+      <x:c r="T13" s="3" t="str">
+        <x:v>Quote.razor:1; InstantQuotePanel.razor; QuoteController.cs:15-196</x:v>
+      </x:c>
+      <x:c r="U13" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="3" t="str">
+        <x:v>WEB-013</x:v>
+      </x:c>
+      <x:c r="B14" s="3" t="str">
+        <x:v>Maliev.Web</x:v>
+      </x:c>
+      <x:c r="C14" s="3" t="str">
+        <x:v>Quote upload resumable flow</x:v>
+      </x:c>
+      <x:c r="D14" s="3" t="str">
+        <x:v>As a customer, I can upload large CAD files reliably for quote analysis.</x:v>
+      </x:c>
+      <x:c r="E14" s="3" t="str">
+        <x:v>The BFF creates resumable upload sessions, receives chunks, completes uploads, and exposes analysis status.</x:v>
+      </x:c>
+      <x:c r="F14" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G14" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H14" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I14" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J14" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K14" s="3" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="L14" s="3" t="str">
+        <x:v>Quote upload UI -&gt; resumable upload DTOs -&gt; storage/analysis</x:v>
+      </x:c>
+      <x:c r="M14" s="3" t="str">
+        <x:v>QuoteDropzone.razor; QuoteUploadService.cs</x:v>
+      </x:c>
+      <x:c r="N14" s="3" t="str">
+        <x:v>/quote upload controls</x:v>
+      </x:c>
+      <x:c r="O14" s="3" t="str">
+        <x:v>QuoteController uploads/resumable, PUT chunk, complete, analysis-status</x:v>
+      </x:c>
+      <x:c r="P14" s="3" t="str">
+        <x:v>WebBffEndpointTests QuoteUpload*</x:v>
+      </x:c>
+      <x:c r="Q14" s="3" t="str">
+        <x:v>Web BFF, Storage, Geometry/analysis</x:v>
+      </x:c>
+      <x:c r="R14" s="3" t="str">
+        <x:v>Upload session, blob/file metadata</x:v>
+      </x:c>
+      <x:c r="S14" s="3" t="str">
+        <x:v>Needs interruption/resume browser test</x:v>
+      </x:c>
+      <x:c r="T14" s="3" t="str">
+        <x:v>QuoteUploadService.cs; QuoteController.cs:66,114,154,196</x:v>
+      </x:c>
+      <x:c r="U14" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="3" t="str">
+        <x:v>WEB-014</x:v>
+      </x:c>
+      <x:c r="B15" s="3" t="str">
+        <x:v>Maliev.Web</x:v>
+      </x:c>
+      <x:c r="C15" s="3" t="str">
+        <x:v>Quote estimate</x:v>
+      </x:c>
+      <x:c r="D15" s="3" t="str">
+        <x:v>As a customer, I can request an instant estimate for uploaded quote parts.</x:v>
+      </x:c>
+      <x:c r="E15" s="3" t="str">
+        <x:v>Estimate endpoint accepts part/process/material selections and returns pricing/lead-time data.</x:v>
+      </x:c>
+      <x:c r="F15" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G15" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H15" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I15" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J15" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K15" s="3" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="L15" s="3" t="str">
+        <x:v>InstantQuotePanel -&gt; web/v1/quote/estimate -&gt; pricing contract</x:v>
+      </x:c>
+      <x:c r="M15" s="3" t="str">
+        <x:v>InstantQuotePanel.razor</x:v>
+      </x:c>
+      <x:c r="N15" s="3" t="str">
+        <x:v>/quote estimate action</x:v>
+      </x:c>
+      <x:c r="O15" s="3" t="str">
+        <x:v>QuoteController POST estimate</x:v>
+      </x:c>
+      <x:c r="P15" s="3" t="str">
+        <x:v>WebBffEndpointTests QuoteEstimate</x:v>
+      </x:c>
+      <x:c r="Q15" s="3" t="str">
+        <x:v>Web BFF, Pricing/Quote services</x:v>
+      </x:c>
+      <x:c r="R15" s="3" t="str">
+        <x:v>Estimate request/response</x:v>
+      </x:c>
+      <x:c r="S15" s="3" t="str">
+        <x:v>Needs numeric acceptance tests against current pricing rules</x:v>
+      </x:c>
+      <x:c r="T15" s="3" t="str">
+        <x:v>InstantQuotePanel.razor; QuoteController.cs:40</x:v>
+      </x:c>
+      <x:c r="U15" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="3" t="str">
+        <x:v>WEB-015</x:v>
+      </x:c>
+      <x:c r="B16" s="3" t="str">
+        <x:v>Maliev.Web</x:v>
+      </x:c>
+      <x:c r="C16" s="3" t="str">
+        <x:v>Customer chatbot</x:v>
+      </x:c>
+      <x:c r="D16" s="3" t="str">
+        <x:v>As a visitor or customer, I can chat with the website assistant.</x:v>
+      </x:c>
+      <x:c r="E16" s="3" t="str">
+        <x:v>Chatbot starts sessions, sends messages, and handles sign-in-required states through web chatbot endpoints.</x:v>
+      </x:c>
+      <x:c r="F16" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G16" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H16" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I16" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J16" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K16" s="3" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="L16" s="3" t="str">
+        <x:v>CustomerChatbot -&gt; web/v1/chatbot sessions/messages -&gt; chatbot backend</x:v>
+      </x:c>
+      <x:c r="M16" s="3" t="str">
+        <x:v>CustomerChatbot.razor</x:v>
+      </x:c>
+      <x:c r="N16" s="3" t="str">
+        <x:v>Floating/customer chatbot UI</x:v>
+      </x:c>
+      <x:c r="O16" s="3" t="str">
+        <x:v>ChatbotController POST sessions/messages</x:v>
+      </x:c>
+      <x:c r="P16" s="3" t="str">
+        <x:v>CustomerChatbotBoundaryTests; WebBffEndpointTests Chatbot*</x:v>
+      </x:c>
+      <x:c r="Q16" s="3" t="str">
+        <x:v>Web BFF, Chatbot/agent backend, Auth</x:v>
+      </x:c>
+      <x:c r="R16" s="3" t="str">
+        <x:v>Chat sessions and messages</x:v>
+      </x:c>
+      <x:c r="S16" s="3" t="str">
+        <x:v>Needs browser retest for auth and anonymous states</x:v>
+      </x:c>
+      <x:c r="T16" s="3" t="str">
+        <x:v>CustomerChatbot.razor; ChatbotController.cs:16-63</x:v>
+      </x:c>
+      <x:c r="U16" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="3" t="str">
+        <x:v>WEB-016</x:v>
+      </x:c>
+      <x:c r="B17" s="3" t="str">
+        <x:v>Maliev.Web</x:v>
+      </x:c>
+      <x:c r="C17" s="3" t="str">
+        <x:v>Authentication sign in and sign up</x:v>
+      </x:c>
+      <x:c r="D17" s="3" t="str">
+        <x:v>As a customer, I can create an account or sign in with email, Google, or passkey.</x:v>
+      </x:c>
+      <x:c r="E17" s="3" t="str">
+        <x:v>Auth pages and BFF endpoints support email sign-in/sign-up, Google OAuth, passkey sign-in, and quote-start auth routing.</x:v>
+      </x:c>
+      <x:c r="F17" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G17" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H17" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I17" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J17" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K17" s="3" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="L17" s="3" t="str">
+        <x:v>Auth pages -&gt; /auth endpoints -&gt; auth cookies/claims</x:v>
+      </x:c>
+      <x:c r="M17" s="3" t="str">
+        <x:v>AuthSignIn.razor; AuthSignUp.razor; AuthController</x:v>
+      </x:c>
+      <x:c r="N17" s="3" t="str">
+        <x:v>/auth/sign-in, /auth/sign-up, /auth/google, /quote/start</x:v>
+      </x:c>
+      <x:c r="O17" s="3" t="str">
+        <x:v>AuthController google, callback, sign-in/email, sign-up/email, passkey-sign-in</x:v>
+      </x:c>
+      <x:c r="P17" s="3" t="str">
+        <x:v>AccountControllerBoundaryTests; WebBffEndpointTests</x:v>
+      </x:c>
+      <x:c r="Q17" s="3" t="str">
+        <x:v>Web BFF, AuthService, CustomerService</x:v>
+      </x:c>
+      <x:c r="R17" s="3" t="str">
+        <x:v>Session cookies, account identity</x:v>
+      </x:c>
+      <x:c r="S17" s="3" t="str">
+        <x:v>Needs local OAuth/passkey availability check</x:v>
+      </x:c>
+      <x:c r="T17" s="3" t="str">
+        <x:v>AuthController.cs:19-329; AuthSignIn.razor:1; AuthSignUp.razor:1</x:v>
+      </x:c>
+      <x:c r="U17" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="3" t="str">
+        <x:v>WEB-017</x:v>
+      </x:c>
+      <x:c r="B18" s="3" t="str">
+        <x:v>Maliev.Web</x:v>
+      </x:c>
+      <x:c r="C18" s="3" t="str">
+        <x:v>Password recovery</x:v>
+      </x:c>
+      <x:c r="D18" s="3" t="str">
+        <x:v>As a customer, I can request and confirm a password reset.</x:v>
+      </x:c>
+      <x:c r="E18" s="3" t="str">
+        <x:v>Forgot/reset pages call BFF endpoints for reset request and confirmation.</x:v>
+      </x:c>
+      <x:c r="F18" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G18" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H18" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I18" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J18" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K18" s="3" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="L18" s="3" t="str">
+        <x:v>Auth pages -&gt; forgot/reset endpoints -&gt; AuthService</x:v>
+      </x:c>
+      <x:c r="M18" s="3" t="str">
+        <x:v>AuthForgotPassword.razor; AuthResetPassword.razor</x:v>
+      </x:c>
+      <x:c r="N18" s="3" t="str">
+        <x:v>/auth/forgot-password, /auth/reset-password</x:v>
+      </x:c>
+      <x:c r="O18" s="3" t="str">
+        <x:v>AuthController forgot-password/request, reset-password/confirm</x:v>
+      </x:c>
+      <x:c r="P18" s="3" t="str">
+        <x:v>WebBffEndpointTests Auth where present</x:v>
+      </x:c>
+      <x:c r="Q18" s="3" t="str">
+        <x:v>Web BFF, AuthService</x:v>
+      </x:c>
+      <x:c r="R18" s="3" t="str">
+        <x:v>Password reset request/confirmation</x:v>
+      </x:c>
+      <x:c r="S18" s="3" t="str">
+        <x:v>Needs email delivery path test</x:v>
+      </x:c>
+      <x:c r="T18" s="3" t="str">
+        <x:v>AuthController.cs:185,202</x:v>
+      </x:c>
+      <x:c r="U18" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="3" t="str">
+        <x:v>WEB-018</x:v>
+      </x:c>
+      <x:c r="B19" s="3" t="str">
+        <x:v>Maliev.Web</x:v>
+      </x:c>
+      <x:c r="C19" s="3" t="str">
+        <x:v>Email verification and claims refresh</x:v>
+      </x:c>
+      <x:c r="D19" s="3" t="str">
+        <x:v>As a customer, I can verify email and refresh account claims.</x:v>
+      </x:c>
+      <x:c r="E19" s="3" t="str">
+        <x:v>BFF exposes verify-email, resend-verification, and refresh-claims endpoints.</x:v>
+      </x:c>
+      <x:c r="F19" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G19" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H19" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I19" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J19" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K19" s="3" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="L19" s="3" t="str">
+        <x:v>Auth verification routes -&gt; AuthService claims/session</x:v>
+      </x:c>
+      <x:c r="M19" s="3" t="str">
+        <x:v>AuthController</x:v>
+      </x:c>
+      <x:c r="N19" s="3" t="str">
+        <x:v>/auth/verify-email, refresh claims, resend verification</x:v>
+      </x:c>
+      <x:c r="O19" s="3" t="str">
+        <x:v>AuthController verify-email, refresh-claims, resend-verification</x:v>
+      </x:c>
+      <x:c r="P19" s="3" t="str">
+        <x:v>AccountControllerBoundaryTests</x:v>
+      </x:c>
+      <x:c r="Q19" s="3" t="str">
+        <x:v>Web BFF, AuthService</x:v>
+      </x:c>
+      <x:c r="R19" s="3" t="str">
+        <x:v>Verification state and auth claims</x:v>
+      </x:c>
+      <x:c r="S19" s="3" t="str">
+        <x:v>Needs token-expiry edge coverage</x:v>
+      </x:c>
+      <x:c r="T19" s="3" t="str">
+        <x:v>AuthController.cs:241,259,312</x:v>
+      </x:c>
+      <x:c r="U19" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="3" t="str">
+        <x:v>WEB-019</x:v>
+      </x:c>
+      <x:c r="B20" s="3" t="str">
+        <x:v>Maliev.Web</x:v>
+      </x:c>
+      <x:c r="C20" s="3" t="str">
+        <x:v>Account session and profile</x:v>
+      </x:c>
+      <x:c r="D20" s="3" t="str">
+        <x:v>As a signed-in customer, I can view and update account profile information.</x:v>
+      </x:c>
+      <x:c r="E20" s="3" t="str">
+        <x:v>Account BFF exposes session/profile read and profile patch endpoints.</x:v>
+      </x:c>
+      <x:c r="F20" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G20" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H20" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I20" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J20" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K20" s="3" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="L20" s="3" t="str">
+        <x:v>Account pages -&gt; web/v1/account session/profile -&gt; CustomerService</x:v>
+      </x:c>
+      <x:c r="M20" s="3" t="str">
+        <x:v>Account.razor; AccountProfile.razor</x:v>
+      </x:c>
+      <x:c r="N20" s="3" t="str">
+        <x:v>/account, /account/profile</x:v>
+      </x:c>
+      <x:c r="O20" s="3" t="str">
+        <x:v>AccountController session, profile GET/PATCH</x:v>
+      </x:c>
+      <x:c r="P20" s="3" t="str">
+        <x:v>AccountControllerBoundaryTests; WebBffEndpointTests Account</x:v>
+      </x:c>
+      <x:c r="Q20" s="3" t="str">
+        <x:v>Web BFF, CustomerService, AuthService</x:v>
+      </x:c>
+      <x:c r="R20" s="3" t="str">
+        <x:v>Profile fields</x:v>
+      </x:c>
+      <x:c r="S20" s="3" t="str">
+        <x:v>Needs authenticated browser pass</x:v>
+      </x:c>
+      <x:c r="T20" s="3" t="str">
+        <x:v>AccountController.cs:18-145; Account.razor:1; AccountProfile.razor:1</x:v>
+      </x:c>
+      <x:c r="U20" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="3" t="str">
+        <x:v>WEB-020</x:v>
+      </x:c>
+      <x:c r="B21" s="3" t="str">
+        <x:v>Maliev.Web</x:v>
+      </x:c>
+      <x:c r="C21" s="3" t="str">
+        <x:v>Account email change</x:v>
+      </x:c>
+      <x:c r="D21" s="3" t="str">
+        <x:v>As a signed-in customer, I can request or resend an account email change.</x:v>
+      </x:c>
+      <x:c r="E21" s="3" t="str">
+        <x:v>Account BFF accepts email change and resend-change requests.</x:v>
+      </x:c>
+      <x:c r="F21" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G21" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H21" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I21" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J21" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K21" s="3" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="L21" s="3" t="str">
+        <x:v>Account UI -&gt; email/change endpoints -&gt; AuthService</x:v>
+      </x:c>
+      <x:c r="M21" s="3" t="str">
+        <x:v>AccountProfile.razor</x:v>
+      </x:c>
+      <x:c r="N21" s="3" t="str">
+        <x:v>/account/profile email controls</x:v>
+      </x:c>
+      <x:c r="O21" s="3" t="str">
+        <x:v>AccountController email/change, email/resend-change</x:v>
+      </x:c>
+      <x:c r="P21" s="3" t="str">
+        <x:v>AccountControllerBoundaryTests</x:v>
+      </x:c>
+      <x:c r="Q21" s="3" t="str">
+        <x:v>Web BFF, AuthService</x:v>
+      </x:c>
+      <x:c r="R21" s="3" t="str">
+        <x:v>Email change request</x:v>
+      </x:c>
+      <x:c r="S21" s="3" t="str">
+        <x:v>Needs email verification UX test</x:v>
+      </x:c>
+      <x:c r="T21" s="3" t="str">
+        <x:v>AccountController.cs:145,197</x:v>
+      </x:c>
+      <x:c r="U21" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="3" t="str">
+        <x:v>WEB-021</x:v>
+      </x:c>
+      <x:c r="B22" s="3" t="str">
+        <x:v>Maliev.Web</x:v>
+      </x:c>
+      <x:c r="C22" s="3" t="str">
+        <x:v>Account addresses</x:v>
+      </x:c>
+      <x:c r="D22" s="3" t="str">
+        <x:v>As a signed-in customer, I can manage saved addresses.</x:v>
+      </x:c>
+      <x:c r="E22" s="3" t="str">
+        <x:v>Address page and account BFF list, create, update, and delete customer addresses.</x:v>
+      </x:c>
+      <x:c r="F22" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G22" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H22" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I22" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J22" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K22" s="3" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="L22" s="3" t="str">
+        <x:v>Account address UI -&gt; web/v1/account/addresses -&gt; CustomerService</x:v>
+      </x:c>
+      <x:c r="M22" s="3" t="str">
+        <x:v>AccountAddresses.razor</x:v>
+      </x:c>
+      <x:c r="N22" s="3" t="str">
+        <x:v>/account/addresses</x:v>
+      </x:c>
+      <x:c r="O22" s="3" t="str">
+        <x:v>AccountController addresses GET/POST/PATCH/DELETE</x:v>
+      </x:c>
+      <x:c r="P22" s="3" t="str">
+        <x:v>AccountAddressGoogleSourceTests; AccountControllerBoundaryTests</x:v>
+      </x:c>
+      <x:c r="Q22" s="3" t="str">
+        <x:v>Web BFF, CustomerService</x:v>
+      </x:c>
+      <x:c r="R22" s="3" t="str">
+        <x:v>Customer address records</x:v>
+      </x:c>
+      <x:c r="S22" s="3" t="str">
+        <x:v>Needs Thai/Google address source browser pass</x:v>
+      </x:c>
+      <x:c r="T22" s="3" t="str">
+        <x:v>AccountAddresses.razor:1; AccountController.cs:223-368</x:v>
+      </x:c>
+      <x:c r="U22" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="3" t="str">
+        <x:v>WEB-022</x:v>
+      </x:c>
+      <x:c r="B23" s="3" t="str">
+        <x:v>Maliev.Web</x:v>
+      </x:c>
+      <x:c r="C23" s="3" t="str">
+        <x:v>Address support data</x:v>
+      </x:c>
+      <x:c r="D23" s="3" t="str">
+        <x:v>As a customer, I can use location/map support data while filling addresses.</x:v>
+      </x:c>
+      <x:c r="E23" s="3" t="str">
+        <x:v>Address BFF exposes Google config, static map URL, countries, and Thai locations.</x:v>
+      </x:c>
+      <x:c r="F23" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G23" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H23" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I23" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J23" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K23" s="3" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="L23" s="3" t="str">
+        <x:v>Address UI helpers -&gt; web/v1/address endpoints</x:v>
+      </x:c>
+      <x:c r="M23" s="3" t="str">
+        <x:v>Address forms</x:v>
+      </x:c>
+      <x:c r="N23" s="3" t="str">
+        <x:v>Address helper endpoints</x:v>
+      </x:c>
+      <x:c r="O23" s="3" t="str">
+        <x:v>AddressController google-config, static-map, countries, thai-locations</x:v>
+      </x:c>
+      <x:c r="P23" s="3" t="str">
+        <x:v>AccountAddressGoogleSourceTests</x:v>
+      </x:c>
+      <x:c r="Q23" s="3" t="str">
+        <x:v>Web BFF, Country/Registry/Google config</x:v>
+      </x:c>
+      <x:c r="R23" s="3" t="str">
+        <x:v>Read-only location/map lookups</x:v>
+      </x:c>
+      <x:c r="S23" s="3" t="str">
+        <x:v>Needs no-key fallback check</x:v>
+      </x:c>
+      <x:c r="T23" s="3" t="str">
+        <x:v>AddressController.cs:17-112</x:v>
+      </x:c>
+      <x:c r="U23" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="3" t="str">
+        <x:v>WEB-023</x:v>
+      </x:c>
+      <x:c r="B24" s="3" t="str">
+        <x:v>Maliev.Web</x:v>
+      </x:c>
+      <x:c r="C24" s="3" t="str">
+        <x:v>Account orders and quote history</x:v>
+      </x:c>
+      <x:c r="D24" s="3" t="str">
+        <x:v>As a signed-in customer, I can review orders and quote/account history.</x:v>
+      </x:c>
+      <x:c r="E24" s="3" t="str">
+        <x:v>Account orders route and BFF expose account orders and account quote routes.</x:v>
+      </x:c>
+      <x:c r="F24" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G24" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H24" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I24" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J24" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K24" s="3" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="L24" s="3" t="str">
+        <x:v>Account pages -&gt; web/v1/account/orders -&gt; OrderService</x:v>
+      </x:c>
+      <x:c r="M24" s="3" t="str">
+        <x:v>AccountOrders.razor; StaticPage account quotes</x:v>
+      </x:c>
+      <x:c r="N24" s="3" t="str">
+        <x:v>/account/orders, /account/orders/{OrderId}, /account/quotes</x:v>
+      </x:c>
+      <x:c r="O24" s="3" t="str">
+        <x:v>AccountController orders</x:v>
+      </x:c>
+      <x:c r="P24" s="3" t="str">
+        <x:v>WebBffEndpointTests AccountOrders</x:v>
+      </x:c>
+      <x:c r="Q24" s="3" t="str">
+        <x:v>Web BFF, OrderService</x:v>
+      </x:c>
+      <x:c r="R24" s="3" t="str">
+        <x:v>Read-only order/quote history</x:v>
+      </x:c>
+      <x:c r="S24" s="3" t="str">
+        <x:v>Needs detail route browser test</x:v>
+      </x:c>
+      <x:c r="T24" s="3" t="str">
+        <x:v>AccountOrders.razor:1-2; AccountController.cs:411</x:v>
+      </x:c>
+      <x:c r="U24" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="3" t="str">
+        <x:v>WEB-024</x:v>
+      </x:c>
+      <x:c r="B25" s="3" t="str">
+        <x:v>Maliev.Web</x:v>
+      </x:c>
+      <x:c r="C25" s="3" t="str">
+        <x:v>Company search</x:v>
+      </x:c>
+      <x:c r="D25" s="3" t="str">
+        <x:v>As a customer, I can search company registry data from account flows.</x:v>
+      </x:c>
+      <x:c r="E25" s="3" t="str">
+        <x:v>Account BFF exposes company-search backed by registry/customer services.</x:v>
+      </x:c>
+      <x:c r="F25" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G25" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H25" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I25" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J25" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K25" s="3" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="L25" s="3" t="str">
+        <x:v>Account forms -&gt; company-search endpoint -&gt; RegistryService</x:v>
+      </x:c>
+      <x:c r="M25" s="3" t="str">
+        <x:v>Account profile/company forms</x:v>
+      </x:c>
+      <x:c r="N25" s="3" t="str">
+        <x:v>company search UI</x:v>
+      </x:c>
+      <x:c r="O25" s="3" t="str">
+        <x:v>AccountController company-search</x:v>
+      </x:c>
+      <x:c r="P25" s="3" t="str">
+        <x:v>AccountControllerBoundaryTests</x:v>
+      </x:c>
+      <x:c r="Q25" s="3" t="str">
+        <x:v>Web BFF, RegistryService, CustomerService</x:v>
+      </x:c>
+      <x:c r="R25" s="3" t="str">
+        <x:v>Read-only company search</x:v>
+      </x:c>
+      <x:c r="S25" s="3" t="str">
+        <x:v>Needs empty/error result UX test</x:v>
+      </x:c>
+      <x:c r="T25" s="3" t="str">
+        <x:v>AccountController.cs:424</x:v>
+      </x:c>
+      <x:c r="U25" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="3" t="str">
+        <x:v>WEB-025</x:v>
+      </x:c>
+      <x:c r="B26" s="3" t="str">
+        <x:v>Maliev.Web</x:v>
+      </x:c>
+      <x:c r="C26" s="3" t="str">
+        <x:v>Preferences culture</x:v>
+      </x:c>
+      <x:c r="D26" s="3" t="str">
+        <x:v>As a visitor or customer, I can set culture/language preference.</x:v>
+      </x:c>
+      <x:c r="E26" s="3" t="str">
+        <x:v>Preferences BFF records selected culture for the user/browser session.</x:v>
+      </x:c>
+      <x:c r="F26" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G26" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H26" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I26" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J26" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K26" s="3" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="L26" s="3" t="str">
+        <x:v>Preference UI -&gt; web/v1/preferences/culture</x:v>
+      </x:c>
+      <x:c r="M26" s="3" t="str">
+        <x:v>AccountPreferences.razor</x:v>
+      </x:c>
+      <x:c r="N26" s="3" t="str">
+        <x:v>/account/preferences</x:v>
+      </x:c>
+      <x:c r="O26" s="3" t="str">
+        <x:v>PreferencesController POST culture</x:v>
+      </x:c>
+      <x:c r="P26" s="3" t="str">
+        <x:v>WebBffEndpointTests Preferences</x:v>
+      </x:c>
+      <x:c r="Q26" s="3" t="str">
+        <x:v>Web BFF</x:v>
+      </x:c>
+      <x:c r="R26" s="3" t="str">
+        <x:v>Culture preference</x:v>
+      </x:c>
+      <x:c r="S26" s="3" t="str">
+        <x:v>Needs multi-locale browser pass</x:v>
+      </x:c>
+      <x:c r="T26" s="3" t="str">
+        <x:v>AccountPreferences.razor:1; PreferencesController.cs:13-18</x:v>
+      </x:c>
+      <x:c r="U26" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="3" t="str">
+        <x:v>WEB-026</x:v>
+      </x:c>
+      <x:c r="B27" s="3" t="str">
+        <x:v>Maliev.Web</x:v>
+      </x:c>
+      <x:c r="C27" s="3" t="str">
+        <x:v>Contact messages</x:v>
+      </x:c>
+      <x:c r="D27" s="3" t="str">
+        <x:v>As a visitor, I can submit a contact request from the website.</x:v>
+      </x:c>
+      <x:c r="E27" s="3" t="str">
+        <x:v>Contact route posts messages to the web contact endpoint.</x:v>
+      </x:c>
+      <x:c r="F27" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G27" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H27" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I27" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J27" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K27" s="3" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="L27" s="3" t="str">
+        <x:v>Static contact page -&gt; web/v1/contact/messages -&gt; contact service</x:v>
+      </x:c>
+      <x:c r="M27" s="3" t="str">
+        <x:v>StaticPage.razor</x:v>
+      </x:c>
+      <x:c r="N27" s="3" t="str">
+        <x:v>/contact</x:v>
+      </x:c>
+      <x:c r="O27" s="3" t="str">
+        <x:v>ContactController POST messages</x:v>
+      </x:c>
+      <x:c r="P27" s="3" t="str">
+        <x:v>WebBffEndpointTests Contact</x:v>
+      </x:c>
+      <x:c r="Q27" s="3" t="str">
+        <x:v>Web BFF, Contact/customer workflow</x:v>
+      </x:c>
+      <x:c r="R27" s="3" t="str">
+        <x:v>Contact message record</x:v>
+      </x:c>
+      <x:c r="S27" s="3" t="str">
+        <x:v>Needs spam/validation UX review</x:v>
+      </x:c>
+      <x:c r="T27" s="3" t="str">
+        <x:v>StaticPage.razor:2; ContactController.cs:14-21</x:v>
+      </x:c>
+      <x:c r="U27" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="3" t="str">
+        <x:v>WEB-027</x:v>
+      </x:c>
+      <x:c r="B28" s="3" t="str">
+        <x:v>Maliev.Web</x:v>
+      </x:c>
+      <x:c r="C28" s="3" t="str">
+        <x:v>Static content pages</x:v>
+      </x:c>
+      <x:c r="D28" s="3" t="str">
+        <x:v>As a visitor, I can open policy, FAQ, industry, case-study, and blog pages.</x:v>
+      </x:c>
+      <x:c r="E28" s="3" t="str">
+        <x:v>StaticPage route table maps public slugs to content pages.</x:v>
+      </x:c>
+      <x:c r="F28" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G28" s="3" t="str">
+        <x:v>Needs manual / browser test</x:v>
+      </x:c>
+      <x:c r="H28" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I28" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J28" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K28" s="3" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="L28" s="3" t="str">
+        <x:v>Static routes -&gt; content model</x:v>
+      </x:c>
+      <x:c r="M28" s="3" t="str">
+        <x:v>StaticPage.razor</x:v>
+      </x:c>
+      <x:c r="N28" s="3" t="str">
+        <x:v>/about, /faq, /shipping-returns, /privacy, /terms, /cookie-policy, /refund-policy, /warranty-policy, /industries, /case-studies, /case-studies/{Slug}, /blog, /blog/{Slug}</x:v>
+      </x:c>
+      <x:c r="O28" s="3" t="str">
+        <x:v>BlogController for ebook PDF only</x:v>
+      </x:c>
+      <x:c r="P28" s="3" t="str"/>
+      <x:c r="Q28" s="3" t="str">
+        <x:v>Web client, Content</x:v>
+      </x:c>
+      <x:c r="R28" s="3" t="str">
+        <x:v>Read-only content</x:v>
+      </x:c>
+      <x:c r="S28" s="3" t="str">
+        <x:v>Needs content completeness review</x:v>
+      </x:c>
+      <x:c r="T28" s="3" t="str">
+        <x:v>StaticPage.razor:1-15</x:v>
+      </x:c>
+      <x:c r="U28" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="3" t="str">
+        <x:v>WEB-028</x:v>
+      </x:c>
+      <x:c r="B29" s="3" t="str">
+        <x:v>Maliev.Web</x:v>
+      </x:c>
+      <x:c r="C29" s="3" t="str">
+        <x:v>Blog ebook download</x:v>
+      </x:c>
+      <x:c r="D29" s="3" t="str">
+        <x:v>As a visitor, I can download a blog ebook PDF.</x:v>
+      </x:c>
+      <x:c r="E29" s="3" t="str">
+        <x:v>Blog BFF streams an ebook PDF by blog slug.</x:v>
+      </x:c>
+      <x:c r="F29" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G29" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H29" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I29" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J29" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K29" s="3" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="L29" s="3" t="str">
+        <x:v>Blog static route -&gt; web/v1/blog/{slug}/ebook.pdf</x:v>
+      </x:c>
+      <x:c r="M29" s="3" t="str">
+        <x:v>StaticPage blog routes</x:v>
+      </x:c>
+      <x:c r="N29" s="3" t="str">
+        <x:v>/blog/{Slug}</x:v>
+      </x:c>
+      <x:c r="O29" s="3" t="str">
+        <x:v>BlogController GET {slug}/ebook.pdf</x:v>
+      </x:c>
+      <x:c r="P29" s="3" t="str">
+        <x:v>WebBffEndpointTests Blog</x:v>
+      </x:c>
+      <x:c r="Q29" s="3" t="str">
+        <x:v>Web BFF, PDF service/content</x:v>
+      </x:c>
+      <x:c r="R29" s="3" t="str">
+        <x:v>PDF download stream</x:v>
+      </x:c>
+      <x:c r="S29" s="3" t="str">
+        <x:v>Needs browser download pass</x:v>
+      </x:c>
+      <x:c r="T29" s="3" t="str">
+        <x:v>BlogController.cs:15-26</x:v>
+      </x:c>
+      <x:c r="U29" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="3" t="str">
+        <x:v>WEB-029</x:v>
+      </x:c>
+      <x:c r="B30" s="3" t="str">
+        <x:v>Maliev.Web</x:v>
+      </x:c>
+      <x:c r="C30" s="3" t="str">
+        <x:v>SEO metadata</x:v>
+      </x:c>
+      <x:c r="D30" s="3" t="str">
+        <x:v>As a crawler or visitor, I can access robots and sitemap metadata.</x:v>
+      </x:c>
+      <x:c r="E30" s="3" t="str">
+        <x:v>SEO controller serves robots.txt and sitemap.xml.</x:v>
+      </x:c>
+      <x:c r="F30" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G30" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H30" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I30" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J30" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K30" s="3" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="L30" s="3" t="str">
+        <x:v>Public SEO endpoints -&gt; static generated metadata</x:v>
+      </x:c>
+      <x:c r="M30" s="3" t="str">
+        <x:v>SeoController</x:v>
+      </x:c>
+      <x:c r="N30" s="3" t="str">
+        <x:v>/robots.txt, /sitemap.xml</x:v>
+      </x:c>
+      <x:c r="O30" s="3" t="str">
+        <x:v>SeoController GET robots/sitemap</x:v>
+      </x:c>
+      <x:c r="P30" s="3" t="str">
+        <x:v>WebBffEndpointTests Seo</x:v>
+      </x:c>
+      <x:c r="Q30" s="3" t="str">
+        <x:v>Web BFF</x:v>
+      </x:c>
+      <x:c r="R30" s="3" t="str">
+        <x:v>Read-only SEO content</x:v>
+      </x:c>
+      <x:c r="S30" s="3" t="str">
+        <x:v>Needs deployment hostname review</x:v>
+      </x:c>
+      <x:c r="T30" s="3" t="str">
+        <x:v>SeoController.cs:49,58</x:v>
+      </x:c>
+      <x:c r="U30" s="3" t="str">
         <x:v>2026-06-23</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4831fb5f19174170"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8f69ea83b5bd4390"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -978,26 +2408,26 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="11" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="9.130000114440918" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="12.25" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="55.75" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="151" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="166.8800048828125" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="29.6299991607666" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="86.37999725341797" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="138.25" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="18.25" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="18.75" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="22.1299991607666" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="19.8799991607666" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="10.380000114440918" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="13" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="8.75" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="83.87999725341797" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="70.25" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="113.37999725341797" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="104.62999725341797" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="146.6300048828125" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="53.130001068115234" hidden="0" customWidth="1"/>
-    <x:col min="18" max="18" width="51.130001068115234" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="47.130001068115234" hidden="0" customWidth="1"/>
-    <x:col min="20" max="20" width="101.12999725341797" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="67.87999725341797" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="54.380001068115234" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="83.62999725341797" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="101.12999725341797" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="46.25" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="41.25" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="34.25" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="40.380001068115234" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="65.5" hidden="0" customWidth="1"/>
     <x:col min="21" max="21" width="13.880000114440918" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -1068,19 +2498,19 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="3" t="str">
-        <x:v>INT-CODE-001</x:v>
+        <x:v>INT-001</x:v>
       </x:c>
       <x:c r="B2" s="3" t="str">
         <x:v>Maliev.Intranet</x:v>
       </x:c>
       <x:c r="C2" s="3" t="str">
-        <x:v>Employee shell, navigation, search, chat, notifications</x:v>
+        <x:v>Employee shell and navigation</x:v>
       </x:c>
       <x:c r="D2" s="3" t="str">
-        <x:v>As an employee, I can navigate operational modules, search globally, open chat, change currency/theme, view notifications, and manage my profile/session.</x:v>
+        <x:v>As an employee, I can navigate operations from the intranet shell.</x:v>
       </x:c>
       <x:c r="E2" s="3" t="str">
-        <x:v>The authenticated shell renders module navigation, top-bar search/currency/chat/notifications/profile controls, and routes search results to their operational pages.</x:v>
+        <x:v>Navigation groups expose quote, commerce, finance, manufacturing, purchasing, HR, IAM, and admin modules.</x:v>
       </x:c>
       <x:c r="F2" s="3" t="str">
         <x:v>Current code-derived</x:v>
@@ -1101,31 +2531,31 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L2" s="3" t="str">
-        <x:v>Blazor shell -&gt; Intranet BFF controllers -&gt; auth/session/currency/navigation state</x:v>
+        <x:v>App shell/navigation -&gt; authenticated employee session</x:v>
       </x:c>
       <x:c r="M2" s="3" t="str">
-        <x:v>NavMenu.razor; TopBar.razor; GlobalSearchBox.razor; ChatDrawer.razor; NotificationBell.razor</x:v>
+        <x:v>NavMenu.razor; TopBar.razor; AppNavigation.cs</x:v>
       </x:c>
       <x:c r="N2" s="3" t="str">
-        <x:v>Primary nav groups for Quote, Commerce, Finance, Manufacturing, Purchasing, HR, IAM, Admin; /search</x:v>
+        <x:v>Primary navigation routes across intranet modules</x:v>
       </x:c>
       <x:c r="O2" s="3" t="str">
-        <x:v>Global search, notification, chat, currency/session BFF APIs</x:v>
+        <x:v>AuthController user/session endpoints</x:v>
       </x:c>
       <x:c r="P2" s="3" t="str">
-        <x:v>NotificationBell tests; search/chat source tests where present</x:v>
+        <x:v>Navigation/source tests where present</x:v>
       </x:c>
       <x:c r="Q2" s="3" t="str">
-        <x:v>Intranet BFF, Auth, Notification, Search, Chatbot</x:v>
+        <x:v>Intranet client, BFF, Auth/IAM</x:v>
       </x:c>
       <x:c r="R2" s="3" t="str">
-        <x:v>Chat messages, notification read state, user preferences</x:v>
+        <x:v>User preferences/session state</x:v>
       </x:c>
       <x:c r="S2" s="3" t="str">
-        <x:v>Needs browser retest for shell density/responsiveness</x:v>
+        <x:v>Needs responsive shell browser pass</x:v>
       </x:c>
       <x:c r="T2" s="3" t="str">
-        <x:v>AppNavigation.cs:9-78; TopBar.razor:169,177,238,245,285,554; ChatDrawer.razor:301,677,779,827; GlobalSearchBox.razor:194,224,243</x:v>
+        <x:v>AppNavigation.cs; NavMenu.razor; TopBar.razor</x:v>
       </x:c>
       <x:c r="U2" s="3" t="str">
         <x:v>2026-06-23</x:v>
@@ -1133,25 +2563,25 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="3" t="str">
-        <x:v>INT-CODE-002</x:v>
+        <x:v>INT-002</x:v>
       </x:c>
       <x:c r="B3" s="3" t="str">
         <x:v>Maliev.Intranet</x:v>
       </x:c>
       <x:c r="C3" s="3" t="str">
-        <x:v>Project New quote workflow</x:v>
+        <x:v>Dashboard and action items</x:v>
       </x:c>
       <x:c r="D3" s="3" t="str">
-        <x:v>As a sales or quoting employee, I can create a new project, upload CAD files, configure parts, run DFM/preview, price the quote, generate quotation artifacts, and move accepted work toward production.</x:v>
+        <x:v>As an employee, I can see operational dashboard summaries and action items.</x:v>
       </x:c>
       <x:c r="E3" s="3" t="str">
-        <x:v>Project New handles upload/resumable files, local viewer/runtime, autosave/resume, customer migration, price confirmation, quotation PDF generation, duplicate flows, planning holds, routing, and production-plan creation.</x:v>
+        <x:v>Dashboard controller returns dashboard data and action items for the home page.</x:v>
       </x:c>
       <x:c r="F3" s="3" t="str">
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G3" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Needs manual / browser test</x:v>
       </x:c>
       <x:c r="H3" s="3" t="str">
         <x:v>Not tested in current loop</x:v>
@@ -1163,34 +2593,32 @@
         <x:v>Not started</x:v>
       </x:c>
       <x:c r="K3" s="3" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="L3" s="3" t="str">
-        <x:v>ProjectNew UI -&gt; Projects/Uploads/Geometry/Pricing/Quotations controllers -&gt; quote/project DTOs and storage</x:v>
+        <x:v>Home/dashboard UI -&gt; api/v1/dashboard</x:v>
       </x:c>
       <x:c r="M3" s="3" t="str">
-        <x:v>Pages/Sales/ProjectNew.razor(.cs)</x:v>
+        <x:v>Home.razor</x:v>
       </x:c>
       <x:c r="N3" s="3" t="str">
-        <x:v>/sales/projects/new</x:v>
+        <x:v>/</x:v>
       </x:c>
       <x:c r="O3" s="3" t="str">
-        <x:v>ProjectsController, UploadsController, GeometryController, PricingController, QuotationsController</x:v>
-      </x:c>
-      <x:c r="P3" s="3" t="str">
-        <x:v>ProjectNewAutoSaveTests; ProjectsControllerTests; PricingControllerTests; UploadsControllerResumableTests; GeometryControllerTests; Dfm* tests; PartConfigSidebarTests; QuoteSummaryBarTests</x:v>
-      </x:c>
+        <x:v>DashboardController GET, action-items</x:v>
+      </x:c>
+      <x:c r="P3" s="3" t="str"/>
       <x:c r="Q3" s="3" t="str">
-        <x:v>Intranet BFF, Storage, GeometryService, Pricing, Quotation, Production</x:v>
+        <x:v>Intranet BFF, operational services</x:v>
       </x:c>
       <x:c r="R3" s="3" t="str">
-        <x:v>Projects, parts, files, thumbnails, quotation PDFs, production plans</x:v>
+        <x:v>Read-only dashboard data</x:v>
       </x:c>
       <x:c r="S3" s="3" t="str">
-        <x:v>Highest-priority browser retest target after workbook rebuild</x:v>
+        <x:v>Needs widget-level browser coverage</x:v>
       </x:c>
       <x:c r="T3" s="3" t="str">
-        <x:v>ProjectNew.razor:1; ProjectNew.razor.cs:481,1227,3637,3692,3953,4285,4350,4483,4530,4593,4664,4756,4788,4978</x:v>
+        <x:v>Home.razor:1; DashboardController.cs:17,34,158</x:v>
       </x:c>
       <x:c r="U3" s="3" t="str">
         <x:v>2026-06-23</x:v>
@@ -1198,19 +2626,19 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="3" t="str">
-        <x:v>INT-CODE-003</x:v>
+        <x:v>INT-003</x:v>
       </x:c>
       <x:c r="B4" s="3" t="str">
         <x:v>Maliev.Intranet</x:v>
       </x:c>
       <x:c r="C4" s="3" t="str">
-        <x:v>Projects and quotations management</x:v>
+        <x:v>Global search</x:v>
       </x:c>
       <x:c r="D4" s="3" t="str">
-        <x:v>As an employee, I can list, open, duplicate, note, price, generate, accept, and route existing quote projects and quotations.</x:v>
+        <x:v>As an employee, I can search across operational records.</x:v>
       </x:c>
       <x:c r="E4" s="3" t="str">
-        <x:v>Project and quotation controllers expose list/detail, thumbnails, notes, duplicate, part edits, price/confirm-price, generate quotation, accept quotation, PDF/latest/draft PDF, status, and delete/update paths.</x:v>
+        <x:v>Search UI calls global search endpoint and routes selected results.</x:v>
       </x:c>
       <x:c r="F4" s="3" t="str">
         <x:v>Current code-derived</x:v>
@@ -1228,34 +2656,34 @@
         <x:v>Not started</x:v>
       </x:c>
       <x:c r="K4" s="3" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="L4" s="3" t="str">
-        <x:v>Sales project pages -&gt; ProjectsController/QuotationsController -&gt; project/quotation contracts</x:v>
+        <x:v>GlobalSearchBox/Search page -&gt; api/v1/search -&gt; SearchService</x:v>
       </x:c>
       <x:c r="M4" s="3" t="str">
-        <x:v>Sales projects pages and quotation components</x:v>
+        <x:v>Search.razor; GlobalSearchBox.razor</x:v>
       </x:c>
       <x:c r="N4" s="3" t="str">
-        <x:v>/sales/projects, /sales/projects/{Id}</x:v>
+        <x:v>/search</x:v>
       </x:c>
       <x:c r="O4" s="3" t="str">
-        <x:v>ProjectsController; QuotationsController</x:v>
+        <x:v>SearchController GET</x:v>
       </x:c>
       <x:c r="P4" s="3" t="str">
-        <x:v>ProjectsControllerTests; Quotation tests</x:v>
+        <x:v>Search/source tests where present</x:v>
       </x:c>
       <x:c r="Q4" s="3" t="str">
-        <x:v>Intranet BFF, Quotation, Project, Pricing, Storage</x:v>
+        <x:v>Intranet BFF, SearchService</x:v>
       </x:c>
       <x:c r="R4" s="3" t="str">
-        <x:v>Project records, quotation records, notes, PDF artifacts</x:v>
+        <x:v>Search query only</x:v>
       </x:c>
       <x:c r="S4" s="3" t="str">
-        <x:v>Needs permissions/auth matrix retest</x:v>
+        <x:v>Needs result navigation browser pass</x:v>
       </x:c>
       <x:c r="T4" s="3" t="str">
-        <x:v>ProjectsController.cs:28,53,75,128,189,298,349,365,383,513,531,664; QuotationsController.cs:20,34,66,139,205,346</x:v>
+        <x:v>Search.razor:1; SearchController.cs:16,26</x:v>
       </x:c>
       <x:c r="U4" s="3" t="str">
         <x:v>2026-06-23</x:v>
@@ -1263,19 +2691,19 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="3" t="str">
-        <x:v>INT-CODE-004</x:v>
+        <x:v>INT-004</x:v>
       </x:c>
       <x:c r="B5" s="3" t="str">
         <x:v>Maliev.Intranet</x:v>
       </x:c>
       <x:c r="C5" s="3" t="str">
-        <x:v>CRM customers and contact requests</x:v>
+        <x:v>Chat drawer</x:v>
       </x:c>
       <x:c r="D5" s="3" t="str">
-        <x:v>As sales staff, I can triage web contact requests and create, search, edit, merge, tag, and review customers.</x:v>
+        <x:v>As an employee, I can use the intranet chat drawer for work context.</x:v>
       </x:c>
       <x:c r="E5" s="3" t="str">
-        <x:v>Customer/contact request pages route to controllers for list/detail/create/update, address/contact/company data, and supported customer routes.</x:v>
+        <x:v>Chat drawer initializes conversations, sends messages, selects conversations, and exposes attachment controls.</x:v>
       </x:c>
       <x:c r="F5" s="3" t="str">
         <x:v>Current code-derived</x:v>
@@ -1296,31 +2724,31 @@
         <x:v>P1</x:v>
       </x:c>
       <x:c r="L5" s="3" t="str">
-        <x:v>Sales CRM UI -&gt; CustomersController/contact-request APIs -&gt; CustomerService contracts</x:v>
+        <x:v>ChatDrawer UI -&gt; chat/agent service client</x:v>
       </x:c>
       <x:c r="M5" s="3" t="str">
-        <x:v>Customers pages; ContactRequests pages</x:v>
+        <x:v>ChatDrawer.razor</x:v>
       </x:c>
       <x:c r="N5" s="3" t="str">
-        <x:v>/customers, /customers/new, /customers/{Id}, /sales/contact-requests, /contact-requests</x:v>
+        <x:v>TopBar chat drawer</x:v>
       </x:c>
       <x:c r="O5" s="3" t="str">
-        <x:v>CustomersController; ContactRequests controllers</x:v>
+        <x:v>Chatbot/admin instruction endpoints where configured</x:v>
       </x:c>
       <x:c r="P5" s="3" t="str">
-        <x:v>Customer tests; contact request tests where present</x:v>
+        <x:v>ChatDrawer source tests where present</x:v>
       </x:c>
       <x:c r="Q5" s="3" t="str">
-        <x:v>Intranet BFF, CustomerService, Web contact source</x:v>
+        <x:v>Intranet client, Chatbot/agent service</x:v>
       </x:c>
       <x:c r="R5" s="3" t="str">
-        <x:v>Customer records, contact requests, addresses/tags</x:v>
+        <x:v>Chat messages/conversation state</x:v>
       </x:c>
       <x:c r="S5" s="3" t="str">
-        <x:v>Needs browser retest of supported customer routes</x:v>
+        <x:v>Needs attachment behavior verification</x:v>
       </x:c>
       <x:c r="T5" s="3" t="str">
-        <x:v>CustomersController.cs:20,35,51,134,167,176,185,199,250,264,278,439,456; Contact request pages</x:v>
+        <x:v>ChatDrawer.razor</x:v>
       </x:c>
       <x:c r="U5" s="3" t="str">
         <x:v>2026-06-23</x:v>
@@ -1328,19 +2756,19 @@
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="3" t="str">
-        <x:v>INT-CODE-005</x:v>
+        <x:v>INT-005</x:v>
       </x:c>
       <x:c r="B6" s="3" t="str">
         <x:v>Maliev.Intranet</x:v>
       </x:c>
       <x:c r="C6" s="3" t="str">
-        <x:v>Commerce catalog and web content administration</x:v>
+        <x:v>Alerts and notifications</x:v>
       </x:c>
       <x:c r="D6" s="3" t="str">
-        <x:v>As catalog/content staff, I can manage products, collections, media, website content, and chatbot instructions used by the public web app.</x:v>
+        <x:v>As an employee, I can view and mark alerts/notifications.</x:v>
       </x:c>
       <x:c r="E6" s="3" t="str">
-        <x:v>Commerce/admin routes expose collection/catalog CRUD, product media, website content, and chatbot instruction management.</x:v>
+        <x:v>Alerts controller lists alerts and supports read/read-all actions; notification UI links to work areas.</x:v>
       </x:c>
       <x:c r="F6" s="3" t="str">
         <x:v>Current code-derived</x:v>
@@ -1361,31 +2789,31 @@
         <x:v>P1</x:v>
       </x:c>
       <x:c r="L6" s="3" t="str">
-        <x:v>Admin/commerce UI -&gt; CommerceController/content controllers -&gt; Catalog/Web content contracts</x:v>
+        <x:v>NotificationBell -&gt; api/v1/alerts</x:v>
       </x:c>
       <x:c r="M6" s="3" t="str">
-        <x:v>Commerce and Admin pages</x:v>
+        <x:v>NotificationBell.razor</x:v>
       </x:c>
       <x:c r="N6" s="3" t="str">
-        <x:v>/commerce/catalog, /commerce/catalog/new, /commerce/catalog/{Handle}, /commerce/collections, /admin/web-content, /admin/chatbot-instructions</x:v>
+        <x:v>TopBar notification bell</x:v>
       </x:c>
       <x:c r="O6" s="3" t="str">
-        <x:v>CommerceController; content/chatbot admin controllers</x:v>
+        <x:v>AlertsController GET, read, read-all</x:v>
       </x:c>
       <x:c r="P6" s="3" t="str">
-        <x:v>Commerce controller tests; web content tests where present</x:v>
+        <x:v>NotificationBell tests where present</x:v>
       </x:c>
       <x:c r="Q6" s="3" t="str">
-        <x:v>Intranet BFF, CatalogService, ContentService, Storage</x:v>
+        <x:v>Intranet BFF, Alerts/Notification data</x:v>
       </x:c>
       <x:c r="R6" s="3" t="str">
-        <x:v>Products, collections, media, chatbot instructions</x:v>
+        <x:v>Alert read state</x:v>
       </x:c>
       <x:c r="S6" s="3" t="str">
-        <x:v>Needs content-publish E2E validation</x:v>
+        <x:v>Needs notification routing browser pass</x:v>
       </x:c>
       <x:c r="T6" s="3" t="str">
-        <x:v>CommerceController.cs:19,34,50,61,106,139,188,296,307,318,340; AppNavigation.cs:29-39</x:v>
+        <x:v>AlertsController.cs:19-92; NotificationBell.razor</x:v>
       </x:c>
       <x:c r="U6" s="3" t="str">
         <x:v>2026-06-23</x:v>
@@ -1393,19 +2821,19 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="3" t="str">
-        <x:v>INT-CODE-006</x:v>
+        <x:v>INT-006</x:v>
       </x:c>
       <x:c r="B7" s="3" t="str">
         <x:v>Maliev.Intranet</x:v>
       </x:c>
       <x:c r="C7" s="3" t="str">
-        <x:v>Finance accounting, invoices, payments, receipts, delivery notes</x:v>
+        <x:v>Project list and detail</x:v>
       </x:c>
       <x:c r="D7" s="3" t="str">
-        <x:v>As finance staff, I can manage accounting records, invoices, payments, receipts, and delivery notes tied to orders/projects.</x:v>
+        <x:v>As a sales employee, I can list and open quote projects.</x:v>
       </x:c>
       <x:c r="E7" s="3" t="str">
-        <x:v>Finance routes expose accounting list/detail/create/update, invoices, billing, receipts, payments, and delivery notes with detail/new flows.</x:v>
+        <x:v>Projects pages and BFF expose list/detail, update, delete, notes, thumbnails, and duplicate actions.</x:v>
       </x:c>
       <x:c r="F7" s="3" t="str">
         <x:v>Current code-derived</x:v>
@@ -1423,34 +2851,34 @@
         <x:v>Not started</x:v>
       </x:c>
       <x:c r="K7" s="3" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="L7" s="3" t="str">
-        <x:v>Finance UI -&gt; Accounting/Invoices/Billing/Receipts/Payments/DeliveryNotes controllers -&gt; financial DTOs</x:v>
+        <x:v>Projects UI -&gt; api/v1/projects -&gt; project service/storage</x:v>
       </x:c>
       <x:c r="M7" s="3" t="str">
-        <x:v>Accounting, invoice, payment, receipt, delivery-note pages</x:v>
+        <x:v>Projects.razor; ProjectDetail.razor</x:v>
       </x:c>
       <x:c r="N7" s="3" t="str">
-        <x:v>/accounting, /accounting/new, /finance/invoices, /finance/invoices/{Id}, /finance/delivery-notes, /delivery-notes</x:v>
+        <x:v>/sales/projects, /sales/projects/{Id}</x:v>
       </x:c>
       <x:c r="O7" s="3" t="str">
-        <x:v>AccountingController; Invoices/Billing/Receipts/Payments/DeliveryNotes controllers</x:v>
+        <x:v>ProjectsController GET/list/detail/update/delete/notes/duplicate/thumbnail</x:v>
       </x:c>
       <x:c r="P7" s="3" t="str">
-        <x:v>Accounting/invoice/delivery/payment tests where present</x:v>
+        <x:v>ProjectsControllerTests</x:v>
       </x:c>
       <x:c r="Q7" s="3" t="str">
-        <x:v>Intranet BFF, Accounting, Invoice, Payment, Delivery</x:v>
+        <x:v>Intranet BFF, Project/Quote services, Storage</x:v>
       </x:c>
       <x:c r="R7" s="3" t="str">
-        <x:v>Invoices, payments, receipts, delivery notes</x:v>
+        <x:v>Projects, notes, duplicate records</x:v>
       </x:c>
       <x:c r="S7" s="3" t="str">
-        <x:v>Needs money-contract and permissions retest before fixes</x:v>
+        <x:v>Needs permission matrix retest</x:v>
       </x:c>
       <x:c r="T7" s="3" t="str">
-        <x:v>AccountingController.cs:30,61,83,93,134,175,189; DeliveryNotes controllers/pages; finance routes</x:v>
+        <x:v>ProjectsController.cs:28-298</x:v>
       </x:c>
       <x:c r="U7" s="3" t="str">
         <x:v>2026-06-23</x:v>
@@ -1458,19 +2886,19 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="3" t="str">
-        <x:v>INT-CODE-007</x:v>
+        <x:v>INT-007</x:v>
       </x:c>
       <x:c r="B8" s="3" t="str">
         <x:v>Maliev.Intranet</x:v>
       </x:c>
       <x:c r="C8" s="3" t="str">
-        <x:v>Manufacturing materials, equipment, jobs, inventory, production schedule</x:v>
+        <x:v>Project New upload</x:v>
       </x:c>
       <x:c r="D8" s="3" t="str">
-        <x:v>As operations staff, I can administer manufacturing materials/equipment, review jobs, inventory, procurement needs, and schedule production.</x:v>
+        <x:v>As a sales employee, I can create a quote project and upload CAD files.</x:v>
       </x:c>
       <x:c r="E8" s="3" t="str">
-        <x:v>Manufacturing pages route to materials, equipment, jobs, inventory, production schedule, and procurement APIs with detail views.</x:v>
+        <x:v>Project New supports file upload, resumable upload, batch upload, analysis status, viewer URL, preview URL, and project file migration.</x:v>
       </x:c>
       <x:c r="F8" s="3" t="str">
         <x:v>Current code-derived</x:v>
@@ -1488,34 +2916,34 @@
         <x:v>Not started</x:v>
       </x:c>
       <x:c r="K8" s="3" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="L8" s="3" t="str">
-        <x:v>MFG UI -&gt; Materials/Equipments/Jobs/Inventory/Production controllers -&gt; manufacturing DTOs</x:v>
+        <x:v>ProjectNew -&gt; UploadsController -&gt; storage/geometry analysis</x:v>
       </x:c>
       <x:c r="M8" s="3" t="str">
-        <x:v>Manufacturing pages</x:v>
+        <x:v>ProjectNew.razor(.cs)</x:v>
       </x:c>
       <x:c r="N8" s="3" t="str">
-        <x:v>/mfg/materials, /mfg/materials/{Id}, /mfg/equipment, /mfg/equipment/{Id}, /mfg/production-schedule, /mfg/procurement</x:v>
+        <x:v>/sales/projects/new</x:v>
       </x:c>
       <x:c r="O8" s="3" t="str">
-        <x:v>MaterialsController; EquipmentsController; JobsController; InventoryController; ProductionSchedule controllers</x:v>
+        <x:v>UploadsController upload/batch/resumable/complete/chunk/status/viewer-url/preview-url/migrate-project</x:v>
       </x:c>
       <x:c r="P8" s="3" t="str">
-        <x:v>Materials/equipment/production tests where present</x:v>
+        <x:v>ProjectNewAutoSaveTests; UploadsControllerResumableTests</x:v>
       </x:c>
       <x:c r="Q8" s="3" t="str">
-        <x:v>Intranet BFF, Manufacturing, Inventory, Procurement</x:v>
+        <x:v>Intranet BFF, Storage, GeometryService, UploadService</x:v>
       </x:c>
       <x:c r="R8" s="3" t="str">
-        <x:v>Materials, equipment, jobs, schedule entries, inventory adjustments</x:v>
+        <x:v>Project files, upload sessions, migrated files</x:v>
       </x:c>
       <x:c r="S8" s="3" t="str">
-        <x:v>Needs schedule drag/drop browser retest if implemented in UI</x:v>
+        <x:v>Needs hidden-input browser journey retest</x:v>
       </x:c>
       <x:c r="T8" s="3" t="str">
-        <x:v>AppNavigation.cs:52-58; Materials/Equipments/Jobs/Inventory controller routes</x:v>
+        <x:v>ProjectNew.razor:1; UploadsController.cs:22-617</x:v>
       </x:c>
       <x:c r="U8" s="3" t="str">
         <x:v>2026-06-23</x:v>
@@ -1523,19 +2951,19 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="3" t="str">
-        <x:v>INT-CODE-008</x:v>
+        <x:v>INT-008</x:v>
       </x:c>
       <x:c r="B9" s="3" t="str">
         <x:v>Maliev.Intranet</x:v>
       </x:c>
       <x:c r="C9" s="3" t="str">
-        <x:v>Purchasing and suppliers</x:v>
+        <x:v>Project New autosave and resume</x:v>
       </x:c>
       <x:c r="D9" s="3" t="str">
-        <x:v>As purchasing staff, I can create procurement requests, view procurement detail, and manage suppliers.</x:v>
+        <x:v>As a sales employee, I can leave and resume an in-progress project draft.</x:v>
       </x:c>
       <x:c r="E9" s="3" t="str">
-        <x:v>Purchasing routes expose list/new/detail procurement flows plus supplier list/detail pages.</x:v>
+        <x:v>ProjectNew code autosaves draft state, persists server-side state, and resumes drafts.</x:v>
       </x:c>
       <x:c r="F9" s="3" t="str">
         <x:v>Current code-derived</x:v>
@@ -1553,34 +2981,34 @@
         <x:v>Not started</x:v>
       </x:c>
       <x:c r="K9" s="3" t="str">
-        <x:v>P2</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="L9" s="3" t="str">
-        <x:v>Purchasing UI -&gt; Purchasing/Suppliers controllers -&gt; procurement/supplier contracts</x:v>
+        <x:v>ProjectNew autosave -&gt; Projects/Uploads state -&gt; draft persistence</x:v>
       </x:c>
       <x:c r="M9" s="3" t="str">
-        <x:v>Purchasing pages</x:v>
+        <x:v>ProjectNew.razor.cs</x:v>
       </x:c>
       <x:c r="N9" s="3" t="str">
-        <x:v>/purchasing, /purchasing/new, /purchasing/{Id}, /purchasing/suppliers, /purchasing/suppliers/{Id}</x:v>
+        <x:v>/sales/projects/new</x:v>
       </x:c>
       <x:c r="O9" s="3" t="str">
-        <x:v>Purchasing and Suppliers controllers</x:v>
+        <x:v>ProjectsController POST/PUT project endpoints</x:v>
       </x:c>
       <x:c r="P9" s="3" t="str">
-        <x:v>Supplier/procurement tests where present</x:v>
+        <x:v>ProjectNewAutoSaveTests</x:v>
       </x:c>
       <x:c r="Q9" s="3" t="str">
-        <x:v>Intranet BFF, Procurement, Supplier</x:v>
+        <x:v>Intranet client/BFF, Project service</x:v>
       </x:c>
       <x:c r="R9" s="3" t="str">
-        <x:v>Purchase requests, supplier records</x:v>
+        <x:v>Draft/project state</x:v>
       </x:c>
       <x:c r="S9" s="3" t="str">
-        <x:v>Needs workflow-state manual test</x:v>
+        <x:v>Needs recovery-path browser pass</x:v>
       </x:c>
       <x:c r="T9" s="3" t="str">
-        <x:v>Purchasing pages and SuppliersController; AppNavigation.cs:58</x:v>
+        <x:v>ProjectNew.razor.cs autosave/resume methods</x:v>
       </x:c>
       <x:c r="U9" s="3" t="str">
         <x:v>2026-06-23</x:v>
@@ -1588,19 +3016,19 @@
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="3" t="str">
-        <x:v>INT-CODE-009</x:v>
+        <x:v>INT-009</x:v>
       </x:c>
       <x:c r="B10" s="3" t="str">
         <x:v>Maliev.Intranet</x:v>
       </x:c>
       <x:c r="C10" s="3" t="str">
-        <x:v>IAM, HR, reference data, system health, AI extraction</x:v>
+        <x:v>Part configuration</x:v>
       </x:c>
       <x:c r="D10" s="3" t="str">
-        <x:v>As admins and managers, I can administer users/roles, HR profile/time-off, reference data, system health, and AI processing/extraction queues.</x:v>
+        <x:v>As a quoting employee, I can configure part process, material, finish, tolerance, quantity, and options.</x:v>
       </x:c>
       <x:c r="E10" s="3" t="str">
-        <x:v>Admin/IAM/HR/reference routes expose user/role, leave/profile, reference-data, system-health, and AI-processing endpoints with permissions.</x:v>
+        <x:v>Project New and component sidebars update part configuration and keep price/DFM state aligned.</x:v>
       </x:c>
       <x:c r="F10" s="3" t="str">
         <x:v>Current code-derived</x:v>
@@ -1618,43 +3046,2318 @@
         <x:v>Not started</x:v>
       </x:c>
       <x:c r="K10" s="3" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="L10" s="3" t="str">
+        <x:v>Part config UI -&gt; Projects parts endpoints -&gt; Pricing/Material reference data</x:v>
+      </x:c>
+      <x:c r="M10" s="3" t="str">
+        <x:v>ProjectNew; PartConfigSidebar components</x:v>
+      </x:c>
+      <x:c r="N10" s="3" t="str">
+        <x:v>/sales/projects/new part controls</x:v>
+      </x:c>
+      <x:c r="O10" s="3" t="str">
+        <x:v>ProjectsController parts create/update/delete; ManufacturingCatalogController processes/materials/finishes/tolerances/config-options</x:v>
+      </x:c>
+      <x:c r="P10" s="3" t="str">
+        <x:v>PartConfigSidebarTests; ProjectNewAutoSaveTests</x:v>
+      </x:c>
+      <x:c r="Q10" s="3" t="str">
+        <x:v>Intranet BFF, MaterialService, PricingService</x:v>
+      </x:c>
+      <x:c r="R10" s="3" t="str">
+        <x:v>Project part configuration</x:v>
+      </x:c>
+      <x:c r="S10" s="3" t="str">
+        <x:v>Needs process-specific UX browser pass</x:v>
+      </x:c>
+      <x:c r="T10" s="3" t="str">
+        <x:v>ProjectsController.cs:298-365; ManufacturingCatalogController.cs:17-107</x:v>
+      </x:c>
+      <x:c r="U10" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="3" t="str">
+        <x:v>INT-010</x:v>
+      </x:c>
+      <x:c r="B11" s="3" t="str">
+        <x:v>Maliev.Intranet</x:v>
+      </x:c>
+      <x:c r="C11" s="3" t="str">
+        <x:v>Geometry runtime and DFM</x:v>
+      </x:c>
+      <x:c r="D11" s="3" t="str">
+        <x:v>As a quoting employee, I can view models and run process-specific DFM checks.</x:v>
+      </x:c>
+      <x:c r="E11" s="3" t="str">
+        <x:v>Geometry runtime serves manifest/assets/telemetry and DFM checks for upload/process combinations.</x:v>
+      </x:c>
+      <x:c r="F11" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G11" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H11" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I11" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J11" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K11" s="3" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="L11" s="3" t="str">
+        <x:v>Viewer/DFM UI -&gt; api/v1/geometry/runtime and geometry/{uploadId}/dfm/{processCode}</x:v>
+      </x:c>
+      <x:c r="M11" s="3" t="str">
+        <x:v>ProjectNew viewer/DFM components</x:v>
+      </x:c>
+      <x:c r="N11" s="3" t="str">
+        <x:v>3D viewer and DFM panels</x:v>
+      </x:c>
+      <x:c r="O11" s="3" t="str">
+        <x:v>GeometryController manifest/assets/telemetry/dfm</x:v>
+      </x:c>
+      <x:c r="P11" s="3" t="str">
+        <x:v>GeometryControllerTests; Dfm* tests</x:v>
+      </x:c>
+      <x:c r="Q11" s="3" t="str">
+        <x:v>Intranet BFF, GeometryService, browser runtime</x:v>
+      </x:c>
+      <x:c r="R11" s="3" t="str">
+        <x:v>Telemetry and DFM report state</x:v>
+      </x:c>
+      <x:c r="S11" s="3" t="str">
+        <x:v>Needs model-render browser pass</x:v>
+      </x:c>
+      <x:c r="T11" s="3" t="str">
+        <x:v>GeometryController.cs:20,42,77,168,311</x:v>
+      </x:c>
+      <x:c r="U11" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="3" t="str">
+        <x:v>INT-011</x:v>
+      </x:c>
+      <x:c r="B12" s="3" t="str">
+        <x:v>Maliev.Intranet</x:v>
+      </x:c>
+      <x:c r="C12" s="3" t="str">
+        <x:v>Pricing snapshots and calculations</x:v>
+      </x:c>
+      <x:c r="D12" s="3" t="str">
+        <x:v>As a quoting employee, I can calculate and accept pricing for parts.</x:v>
+      </x:c>
+      <x:c r="E12" s="3" t="str">
+        <x:v>Pricing endpoints expose snapshots, calculate, accept, lead-times, bulk pricing, and finish options.</x:v>
+      </x:c>
+      <x:c r="F12" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G12" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H12" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I12" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J12" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K12" s="3" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="L12" s="3" t="str">
+        <x:v>Quote UI -&gt; api/v1/pricing -&gt; PricingService/MaterialService</x:v>
+      </x:c>
+      <x:c r="M12" s="3" t="str">
+        <x:v>ProjectNew; pricing components</x:v>
+      </x:c>
+      <x:c r="N12" s="3" t="str">
+        <x:v>Price/confirm price controls</x:v>
+      </x:c>
+      <x:c r="O12" s="3" t="str">
+        <x:v>PricingController snapshots/calculate/accept/lead-times/bulk/finish-options</x:v>
+      </x:c>
+      <x:c r="P12" s="3" t="str">
+        <x:v>PricingControllerTests; QuoteSummaryBarTests</x:v>
+      </x:c>
+      <x:c r="Q12" s="3" t="str">
+        <x:v>Intranet BFF, PricingService, MaterialService</x:v>
+      </x:c>
+      <x:c r="R12" s="3" t="str">
+        <x:v>Pricing snapshots and part pricing</x:v>
+      </x:c>
+      <x:c r="S12" s="3" t="str">
+        <x:v>Needs current price-rule acceptance tests</x:v>
+      </x:c>
+      <x:c r="T12" s="3" t="str">
+        <x:v>PricingController.cs:15-137</x:v>
+      </x:c>
+      <x:c r="U12" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="3" t="str">
+        <x:v>INT-012</x:v>
+      </x:c>
+      <x:c r="B13" s="3" t="str">
+        <x:v>Maliev.Intranet</x:v>
+      </x:c>
+      <x:c r="C13" s="3" t="str">
+        <x:v>Quotation generation and PDFs</x:v>
+      </x:c>
+      <x:c r="D13" s="3" t="str">
+        <x:v>As a sales employee, I can generate, update, send, and download quotations.</x:v>
+      </x:c>
+      <x:c r="E13" s="3" t="str">
+        <x:v>Quotation endpoints list/detail/create/update/delete/status/notes/PDF/latest/draft PDF and Project generation endpoints create quote artifacts.</x:v>
+      </x:c>
+      <x:c r="F13" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G13" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H13" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I13" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J13" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K13" s="3" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="L13" s="3" t="str">
+        <x:v>Project/quotation UI -&gt; QuotationsController/ProjectsController -&gt; quotation/PDF service</x:v>
+      </x:c>
+      <x:c r="M13" s="3" t="str">
+        <x:v>ProjectNew; ProjectDetail; quotation views</x:v>
+      </x:c>
+      <x:c r="N13" s="3" t="str">
+        <x:v>/sales/projects/* quotation actions</x:v>
+      </x:c>
+      <x:c r="O13" s="3" t="str">
+        <x:v>QuotationsController; ProjectsController generate-quotation/accept-quotation</x:v>
+      </x:c>
+      <x:c r="P13" s="3" t="str">
+        <x:v>ProjectsControllerTests; quotation/PDF tests</x:v>
+      </x:c>
+      <x:c r="Q13" s="3" t="str">
+        <x:v>Intranet BFF, QuotationService, PdfService, Storage</x:v>
+      </x:c>
+      <x:c r="R13" s="3" t="str">
+        <x:v>Quotation records, PDFs, notes/status</x:v>
+      </x:c>
+      <x:c r="S13" s="3" t="str">
+        <x:v>Needs PDF visual regression pass</x:v>
+      </x:c>
+      <x:c r="T13" s="3" t="str">
+        <x:v>QuotationsController.cs:20-346; ProjectsController.cs:383,513</x:v>
+      </x:c>
+      <x:c r="U13" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="3" t="str">
+        <x:v>INT-013</x:v>
+      </x:c>
+      <x:c r="B14" s="3" t="str">
+        <x:v>Maliev.Intranet</x:v>
+      </x:c>
+      <x:c r="C14" s="3" t="str">
+        <x:v>Production plan and routing</x:v>
+      </x:c>
+      <x:c r="D14" s="3" t="str">
+        <x:v>As operations staff, I can turn accepted quote work into production planning.</x:v>
+      </x:c>
+      <x:c r="E14" s="3" t="str">
+        <x:v>Project endpoints return production plan, planning holds, and part routing data.</x:v>
+      </x:c>
+      <x:c r="F14" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G14" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H14" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I14" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J14" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K14" s="3" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="L10" s="3" t="str">
-        <x:v>Admin/IAM/HR UI -&gt; IAM/HR/ReferenceData/SystemHealth/AiProcessing controllers -&gt; permission contracts</x:v>
-      </x:c>
-      <x:c r="M10" s="3" t="str">
-        <x:v>Admin, IAM, HR, ReferenceData pages</x:v>
-      </x:c>
-      <x:c r="N10" s="3" t="str">
-        <x:v>/iam, /iam/users/new, /iam/users/{Id}, /iam/roles/{Id}, /hr/profile, /hr/leave, /admin/reference-data, /admin/system-health, /admin</x:v>
-      </x:c>
-      <x:c r="O10" s="3" t="str">
-        <x:v>IamController; TimeOff/Employees/Recruitment/Performance/Compensation/Compliance; ReferenceDataController; AiProcessingController</x:v>
-      </x:c>
-      <x:c r="P10" s="3" t="str">
-        <x:v>IAM/HR/reference/notification tests where present</x:v>
-      </x:c>
-      <x:c r="Q10" s="3" t="str">
-        <x:v>Intranet BFF, IAM, HR, ReferenceData, AI services</x:v>
-      </x:c>
-      <x:c r="R10" s="3" t="str">
-        <x:v>Users, roles, leave requests, reference records, AI tasks</x:v>
-      </x:c>
-      <x:c r="S10" s="3" t="str">
-        <x:v>Needs role-permission matrix retest</x:v>
-      </x:c>
-      <x:c r="T10" s="3" t="str">
-        <x:v>AppNavigation.cs:66-78; IAM/HR/Admin controller routes</x:v>
-      </x:c>
-      <x:c r="U10" s="3" t="str">
+      <x:c r="L14" s="3" t="str">
+        <x:v>Project detail -&gt; production plan/routing endpoints -&gt; manufacturing planning</x:v>
+      </x:c>
+      <x:c r="M14" s="3" t="str">
+        <x:v>ProjectDetail.razor; production views</x:v>
+      </x:c>
+      <x:c r="N14" s="3" t="str">
+        <x:v>/sales/projects/{Id}</x:v>
+      </x:c>
+      <x:c r="O14" s="3" t="str">
+        <x:v>ProjectsController production-plan, planning-hold CRUD, routing</x:v>
+      </x:c>
+      <x:c r="P14" s="3" t="str">
+        <x:v>ProjectsControllerTests</x:v>
+      </x:c>
+      <x:c r="Q14" s="3" t="str">
+        <x:v>Intranet BFF, Manufacturing/Planning services</x:v>
+      </x:c>
+      <x:c r="R14" s="3" t="str">
+        <x:v>Production plans, planning holds</x:v>
+      </x:c>
+      <x:c r="S14" s="3" t="str">
+        <x:v>Needs planning workflow browser pass</x:v>
+      </x:c>
+      <x:c r="T14" s="3" t="str">
+        <x:v>ProjectsController.cs:531-664</x:v>
+      </x:c>
+      <x:c r="U14" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="3" t="str">
+        <x:v>INT-014</x:v>
+      </x:c>
+      <x:c r="B15" s="3" t="str">
+        <x:v>Maliev.Intranet</x:v>
+      </x:c>
+      <x:c r="C15" s="3" t="str">
+        <x:v>Orders and lifecycle</x:v>
+      </x:c>
+      <x:c r="D15" s="3" t="str">
+        <x:v>As sales/operations staff, I can list orders, open order detail, and inspect lifecycle.</x:v>
+      </x:c>
+      <x:c r="E15" s="3" t="str">
+        <x:v>Order pages and lifecycle controller expose order list/detail and order lifecycle state.</x:v>
+      </x:c>
+      <x:c r="F15" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G15" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H15" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I15" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J15" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K15" s="3" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="L15" s="3" t="str">
+        <x:v>Orders pages -&gt; order/lifecycle APIs</x:v>
+      </x:c>
+      <x:c r="M15" s="3" t="str">
+        <x:v>OrderList.razor; OrderDetail.razor</x:v>
+      </x:c>
+      <x:c r="N15" s="3" t="str">
+        <x:v>/sales/orders, /sales/orders/{OrderId}</x:v>
+      </x:c>
+      <x:c r="O15" s="3" t="str">
+        <x:v>OrderLifecycleController GET; order endpoints in BFF</x:v>
+      </x:c>
+      <x:c r="P15" s="3" t="str">
+        <x:v>Order tests where present</x:v>
+      </x:c>
+      <x:c r="Q15" s="3" t="str">
+        <x:v>Intranet BFF, OrderService</x:v>
+      </x:c>
+      <x:c r="R15" s="3" t="str">
+        <x:v>Order/lifecycle read state</x:v>
+      </x:c>
+      <x:c r="S15" s="3" t="str">
+        <x:v>Needs order status action inventory</x:v>
+      </x:c>
+      <x:c r="T15" s="3" t="str">
+        <x:v>OrderList.razor:1; OrderDetail.razor:1; OrderLifecycleController.cs:20,33</x:v>
+      </x:c>
+      <x:c r="U15" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="3" t="str">
+        <x:v>INT-015</x:v>
+      </x:c>
+      <x:c r="B16" s="3" t="str">
+        <x:v>Maliev.Intranet</x:v>
+      </x:c>
+      <x:c r="C16" s="3" t="str">
+        <x:v>Customers</x:v>
+      </x:c>
+      <x:c r="D16" s="3" t="str">
+        <x:v>As sales staff, I can create, search, update, and review customers.</x:v>
+      </x:c>
+      <x:c r="E16" s="3" t="str">
+        <x:v>Customer pages and BFF expose customer list/detail/create/update plus payment terms, tags, contacts, addresses, and merge-type actions.</x:v>
+      </x:c>
+      <x:c r="F16" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G16" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H16" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I16" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J16" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K16" s="3" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="L16" s="3" t="str">
+        <x:v>Customer UI -&gt; api/v1/customers -&gt; CustomerService</x:v>
+      </x:c>
+      <x:c r="M16" s="3" t="str">
+        <x:v>CustomerList.razor; CustomerNew.razor; CustomerDetail.razor</x:v>
+      </x:c>
+      <x:c r="N16" s="3" t="str">
+        <x:v>/customers, /customers/new, /customers/{Id}</x:v>
+      </x:c>
+      <x:c r="O16" s="3" t="str">
+        <x:v>CustomersController list/detail/payment-terms/create/update and related customer actions</x:v>
+      </x:c>
+      <x:c r="P16" s="3" t="str">
+        <x:v>Customer controller/source tests</x:v>
+      </x:c>
+      <x:c r="Q16" s="3" t="str">
+        <x:v>Intranet BFF, CustomerService, RegistryService</x:v>
+      </x:c>
+      <x:c r="R16" s="3" t="str">
+        <x:v>Customer records and related profile data</x:v>
+      </x:c>
+      <x:c r="S16" s="3" t="str">
+        <x:v>Needs full customer form browser pass</x:v>
+      </x:c>
+      <x:c r="T16" s="3" t="str">
+        <x:v>CustomersController.cs:20+; Customers pages</x:v>
+      </x:c>
+      <x:c r="U16" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="3" t="str">
+        <x:v>INT-016</x:v>
+      </x:c>
+      <x:c r="B17" s="3" t="str">
+        <x:v>Maliev.Intranet</x:v>
+      </x:c>
+      <x:c r="C17" s="3" t="str">
+        <x:v>Companies</x:v>
+      </x:c>
+      <x:c r="D17" s="3" t="str">
+        <x:v>As sales staff, I can search and maintain company records tied to customers.</x:v>
+      </x:c>
+      <x:c r="E17" s="3" t="str">
+        <x:v>Companies controller lists/searches/creates/updates companies and primary contact assignment.</x:v>
+      </x:c>
+      <x:c r="F17" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G17" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H17" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I17" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J17" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K17" s="3" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="L17" s="3" t="str">
+        <x:v>Customer/company UI -&gt; api/v1/companies -&gt; Customer/Registry services</x:v>
+      </x:c>
+      <x:c r="M17" s="3" t="str">
+        <x:v>Customer/company forms</x:v>
+      </x:c>
+      <x:c r="N17" s="3" t="str">
+        <x:v>Company search fields</x:v>
+      </x:c>
+      <x:c r="O17" s="3" t="str">
+        <x:v>CompaniesController GET/search/POST/detail/primary-contact/PATCH</x:v>
+      </x:c>
+      <x:c r="P17" s="3" t="str">
+        <x:v>Company/customer tests where present</x:v>
+      </x:c>
+      <x:c r="Q17" s="3" t="str">
+        <x:v>Intranet BFF, CustomerService, RegistryService</x:v>
+      </x:c>
+      <x:c r="R17" s="3" t="str">
+        <x:v>Company records, primary contact links</x:v>
+      </x:c>
+      <x:c r="S17" s="3" t="str">
+        <x:v>Needs registry failure UX test</x:v>
+      </x:c>
+      <x:c r="T17" s="3" t="str">
+        <x:v>CompaniesController.cs:14-86</x:v>
+      </x:c>
+      <x:c r="U17" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="3" t="str">
+        <x:v>INT-017</x:v>
+      </x:c>
+      <x:c r="B18" s="3" t="str">
+        <x:v>Maliev.Intranet</x:v>
+      </x:c>
+      <x:c r="C18" s="3" t="str">
+        <x:v>Contact request triage</x:v>
+      </x:c>
+      <x:c r="D18" s="3" t="str">
+        <x:v>As sales staff, I can review website contact requests and open details.</x:v>
+      </x:c>
+      <x:c r="E18" s="3" t="str">
+        <x:v>Contact request list/detail routes support sales triage of incoming website requests.</x:v>
+      </x:c>
+      <x:c r="F18" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G18" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H18" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I18" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J18" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K18" s="3" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="L18" s="3" t="str">
+        <x:v>Contact request UI -&gt; contact request BFF/service</x:v>
+      </x:c>
+      <x:c r="M18" s="3" t="str">
+        <x:v>ContactRequestList.razor; ContactRequestDetail.razor</x:v>
+      </x:c>
+      <x:c r="N18" s="3" t="str">
+        <x:v>/sales/contact-requests, /contact-requests, /sales/contact-requests/{ContactRequestId}</x:v>
+      </x:c>
+      <x:c r="O18" s="3" t="str">
+        <x:v>Contact request controllers/services</x:v>
+      </x:c>
+      <x:c r="P18" s="3" t="str">
+        <x:v>Contact request tests where present</x:v>
+      </x:c>
+      <x:c r="Q18" s="3" t="str">
+        <x:v>Intranet BFF, Customer/Contact service</x:v>
+      </x:c>
+      <x:c r="R18" s="3" t="str">
+        <x:v>Contact request records</x:v>
+      </x:c>
+      <x:c r="S18" s="3" t="str">
+        <x:v>Needs conversion-to-customer path verification</x:v>
+      </x:c>
+      <x:c r="T18" s="3" t="str">
+        <x:v>ContactRequestList.razor:1-2; ContactRequestDetail.razor:1</x:v>
+      </x:c>
+      <x:c r="U18" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="3" t="str">
+        <x:v>INT-018</x:v>
+      </x:c>
+      <x:c r="B19" s="3" t="str">
+        <x:v>Maliev.Intranet</x:v>
+      </x:c>
+      <x:c r="C19" s="3" t="str">
+        <x:v>Commerce catalog administration</x:v>
+      </x:c>
+      <x:c r="D19" s="3" t="str">
+        <x:v>As catalog staff, I can manage products, collections, and product media for the public site.</x:v>
+      </x:c>
+      <x:c r="E19" s="3" t="str">
+        <x:v>Commerce pages and controller expose collections, product list/detail/new/edit, product media, and catalog actions.</x:v>
+      </x:c>
+      <x:c r="F19" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G19" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H19" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I19" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J19" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K19" s="3" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="L19" s="3" t="str">
+        <x:v>Commerce UI -&gt; CommerceController -&gt; Catalog/Storage services</x:v>
+      </x:c>
+      <x:c r="M19" s="3" t="str">
+        <x:v>Catalog.razor; CatalogListing.razor; Collections.razor</x:v>
+      </x:c>
+      <x:c r="N19" s="3" t="str">
+        <x:v>/commerce/catalog, /commerce/catalog/new, /commerce/catalog/{Handle}, /commerce/collections</x:v>
+      </x:c>
+      <x:c r="O19" s="3" t="str">
+        <x:v>CommerceController collection/product/media endpoints</x:v>
+      </x:c>
+      <x:c r="P19" s="3" t="str">
+        <x:v>Commerce controller tests</x:v>
+      </x:c>
+      <x:c r="Q19" s="3" t="str">
+        <x:v>Intranet BFF, Catalog/Commerce, Storage</x:v>
+      </x:c>
+      <x:c r="R19" s="3" t="str">
+        <x:v>Products, collections, media</x:v>
+      </x:c>
+      <x:c r="S19" s="3" t="str">
+        <x:v>Needs publish/public-site browser validation</x:v>
+      </x:c>
+      <x:c r="T19" s="3" t="str">
+        <x:v>CommerceController.cs; Commerce pages</x:v>
+      </x:c>
+      <x:c r="U19" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="3" t="str">
+        <x:v>INT-019</x:v>
+      </x:c>
+      <x:c r="B20" s="3" t="str">
+        <x:v>Maliev.Intranet</x:v>
+      </x:c>
+      <x:c r="C20" s="3" t="str">
+        <x:v>Web content and chatbot instructions</x:v>
+      </x:c>
+      <x:c r="D20" s="3" t="str">
+        <x:v>As an admin/content editor, I can manage website content and chatbot instruction content.</x:v>
+      </x:c>
+      <x:c r="E20" s="3" t="str">
+        <x:v>Admin pages expose web content and chatbot instruction management.</x:v>
+      </x:c>
+      <x:c r="F20" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G20" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H20" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I20" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J20" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K20" s="3" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="L20" s="3" t="str">
+        <x:v>Admin UI -&gt; web content/chatbot instruction endpoints</x:v>
+      </x:c>
+      <x:c r="M20" s="3" t="str">
+        <x:v>WebContent.razor; ChatbotInstructions.razor</x:v>
+      </x:c>
+      <x:c r="N20" s="3" t="str">
+        <x:v>/admin/web-content, /admin/chatbot-instructions</x:v>
+      </x:c>
+      <x:c r="O20" s="3" t="str">
+        <x:v>Content/chatbot admin controllers/services</x:v>
+      </x:c>
+      <x:c r="P20" s="3" t="str">
+        <x:v>Content tests where present</x:v>
+      </x:c>
+      <x:c r="Q20" s="3" t="str">
+        <x:v>Intranet BFF, Content/Chatbot service</x:v>
+      </x:c>
+      <x:c r="R20" s="3" t="str">
+        <x:v>Content and instruction records</x:v>
+      </x:c>
+      <x:c r="S20" s="3" t="str">
+        <x:v>Needs content publish validation</x:v>
+      </x:c>
+      <x:c r="T20" s="3" t="str">
+        <x:v>WebContent.razor:1; ChatbotInstructions.razor:1</x:v>
+      </x:c>
+      <x:c r="U20" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="3" t="str">
+        <x:v>INT-020</x:v>
+      </x:c>
+      <x:c r="B21" s="3" t="str">
+        <x:v>Maliev.Intranet</x:v>
+      </x:c>
+      <x:c r="C21" s="3" t="str">
+        <x:v>Accounting journals and reports</x:v>
+      </x:c>
+      <x:c r="D21" s="3" t="str">
+        <x:v>As finance staff, I can manage accounts, journal entries, reports, periods, reconciliation, and accounting documents.</x:v>
+      </x:c>
+      <x:c r="E21" s="3" t="str">
+        <x:v>Accounting controller exposes accounts tree, journal entries, post action, reports/PDFs, periods open/close/reopen, reconciliation, and documents.</x:v>
+      </x:c>
+      <x:c r="F21" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G21" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H21" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I21" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J21" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K21" s="3" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="L21" s="3" t="str">
+        <x:v>Accounting UI -&gt; api/v1/accounting -&gt; AccountingService/PDF/storage</x:v>
+      </x:c>
+      <x:c r="M21" s="3" t="str">
+        <x:v>InvoiceList/Accounting pages</x:v>
+      </x:c>
+      <x:c r="N21" s="3" t="str">
+        <x:v>/accounting, /accounting/new, /accounting/{Id}</x:v>
+      </x:c>
+      <x:c r="O21" s="3" t="str">
+        <x:v>AccountingController accounts-tree, journal-entries, reports, periods, reconciliation, documents</x:v>
+      </x:c>
+      <x:c r="P21" s="3" t="str">
+        <x:v>Accounting tests where present</x:v>
+      </x:c>
+      <x:c r="Q21" s="3" t="str">
+        <x:v>Intranet BFF, AccountingService, PdfService, Storage</x:v>
+      </x:c>
+      <x:c r="R21" s="3" t="str">
+        <x:v>Journal entries, periods, documents</x:v>
+      </x:c>
+      <x:c r="S21" s="3" t="str">
+        <x:v>Needs finance permission and audit validation</x:v>
+      </x:c>
+      <x:c r="T21" s="3" t="str">
+        <x:v>AccountingController.cs:16-189</x:v>
+      </x:c>
+      <x:c r="U21" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="3" t="str">
+        <x:v>INT-021</x:v>
+      </x:c>
+      <x:c r="B22" s="3" t="str">
+        <x:v>Maliev.Intranet</x:v>
+      </x:c>
+      <x:c r="C22" s="3" t="str">
+        <x:v>Invoices</x:v>
+      </x:c>
+      <x:c r="D22" s="3" t="str">
+        <x:v>As finance staff, I can list, create, open, and manage invoices.</x:v>
+      </x:c>
+      <x:c r="E22" s="3" t="str">
+        <x:v>Invoice routes cover list/new/detail through accounting and finance invoice paths.</x:v>
+      </x:c>
+      <x:c r="F22" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G22" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H22" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I22" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J22" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K22" s="3" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="L22" s="3" t="str">
+        <x:v>Invoice pages -&gt; invoice service/BFF controllers</x:v>
+      </x:c>
+      <x:c r="M22" s="3" t="str">
+        <x:v>InvoiceList.razor; InvoiceNew.razor; InvoiceDetail.razor</x:v>
+      </x:c>
+      <x:c r="N22" s="3" t="str">
+        <x:v>/accounting, /accounting/new, /accounting/{Id}, /finance/invoices, /finance/invoices/{Id}</x:v>
+      </x:c>
+      <x:c r="O22" s="3" t="str">
+        <x:v>Invoices/Billing/CreditTerms/Receipts controllers</x:v>
+      </x:c>
+      <x:c r="P22" s="3" t="str">
+        <x:v>Invoice tests where present</x:v>
+      </x:c>
+      <x:c r="Q22" s="3" t="str">
+        <x:v>Intranet BFF, InvoiceService, AccountingService</x:v>
+      </x:c>
+      <x:c r="R22" s="3" t="str">
+        <x:v>Invoices, credit terms, billing notes</x:v>
+      </x:c>
+      <x:c r="S22" s="3" t="str">
+        <x:v>Needs money-contract validation</x:v>
+      </x:c>
+      <x:c r="T22" s="3" t="str">
+        <x:v>Invoice*.razor; BillingNotesController.cs; CreditTermsController.cs; ReceiptsController.cs</x:v>
+      </x:c>
+      <x:c r="U22" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="3" t="str">
+        <x:v>INT-022</x:v>
+      </x:c>
+      <x:c r="B23" s="3" t="str">
+        <x:v>Maliev.Intranet</x:v>
+      </x:c>
+      <x:c r="C23" s="3" t="str">
+        <x:v>Billing notes and credit terms</x:v>
+      </x:c>
+      <x:c r="D23" s="3" t="str">
+        <x:v>As finance staff, I can manage billing notes and credit terms.</x:v>
+      </x:c>
+      <x:c r="E23" s="3" t="str">
+        <x:v>Billing notes support list/create/detail; credit terms expose available terms.</x:v>
+      </x:c>
+      <x:c r="F23" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G23" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H23" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I23" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J23" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K23" s="3" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="L23" s="3" t="str">
+        <x:v>Finance UI -&gt; billing-notes/credit-terms controllers -&gt; InvoiceService</x:v>
+      </x:c>
+      <x:c r="M23" s="3" t="str">
+        <x:v>Finance/accounting pages</x:v>
+      </x:c>
+      <x:c r="N23" s="3" t="str">
+        <x:v>Billing and credit controls</x:v>
+      </x:c>
+      <x:c r="O23" s="3" t="str">
+        <x:v>BillingNotesController GET/POST/detail; CreditTermsController GET</x:v>
+      </x:c>
+      <x:c r="P23" s="3" t="str">
+        <x:v>Finance tests where present</x:v>
+      </x:c>
+      <x:c r="Q23" s="3" t="str">
+        <x:v>Intranet BFF, InvoiceService</x:v>
+      </x:c>
+      <x:c r="R23" s="3" t="str">
+        <x:v>Billing notes, credit-term state</x:v>
+      </x:c>
+      <x:c r="S23" s="3" t="str">
+        <x:v>Needs UI route mapping review</x:v>
+      </x:c>
+      <x:c r="T23" s="3" t="str">
+        <x:v>BillingNotesController.cs:15-44; CreditTermsController.cs:15-22</x:v>
+      </x:c>
+      <x:c r="U23" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="3" t="str">
+        <x:v>INT-023</x:v>
+      </x:c>
+      <x:c r="B24" s="3" t="str">
+        <x:v>Maliev.Intranet</x:v>
+      </x:c>
+      <x:c r="C24" s="3" t="str">
+        <x:v>Receipts</x:v>
+      </x:c>
+      <x:c r="D24" s="3" t="str">
+        <x:v>As finance staff, I can list, create, open, and void receipts.</x:v>
+      </x:c>
+      <x:c r="E24" s="3" t="str">
+        <x:v>Receipts controller exposes list/detail/create and void endpoints.</x:v>
+      </x:c>
+      <x:c r="F24" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G24" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H24" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I24" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J24" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K24" s="3" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="L24" s="3" t="str">
+        <x:v>Finance UI -&gt; api/v1/receipts -&gt; ReceiptService</x:v>
+      </x:c>
+      <x:c r="M24" s="3" t="str">
+        <x:v>Finance receipt surfaces</x:v>
+      </x:c>
+      <x:c r="N24" s="3" t="str">
+        <x:v>Receipt controls</x:v>
+      </x:c>
+      <x:c r="O24" s="3" t="str">
+        <x:v>ReceiptsController GET/detail/POST/void</x:v>
+      </x:c>
+      <x:c r="P24" s="3" t="str">
+        <x:v>Receipt tests where present</x:v>
+      </x:c>
+      <x:c r="Q24" s="3" t="str">
+        <x:v>Intranet BFF, ReceiptService</x:v>
+      </x:c>
+      <x:c r="R24" s="3" t="str">
+        <x:v>Receipt records and void state</x:v>
+      </x:c>
+      <x:c r="S24" s="3" t="str">
+        <x:v>Needs money-contract validation</x:v>
+      </x:c>
+      <x:c r="T24" s="3" t="str">
+        <x:v>ReceiptsController.cs:15-55</x:v>
+      </x:c>
+      <x:c r="U24" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="3" t="str">
+        <x:v>INT-024</x:v>
+      </x:c>
+      <x:c r="B25" s="3" t="str">
+        <x:v>Maliev.Intranet</x:v>
+      </x:c>
+      <x:c r="C25" s="3" t="str">
+        <x:v>Delivery notes</x:v>
+      </x:c>
+      <x:c r="D25" s="3" t="str">
+        <x:v>As operations/finance staff, I can create, update, generate, download, attach, and delete delivery notes.</x:v>
+      </x:c>
+      <x:c r="E25" s="3" t="str">
+        <x:v>Delivery note pages and controller expose list/detail/create/status/PDF/files/download/upload/delete.</x:v>
+      </x:c>
+      <x:c r="F25" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G25" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H25" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I25" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J25" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K25" s="3" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="L25" s="3" t="str">
+        <x:v>Delivery UI -&gt; api/v1/deliverynotes -&gt; DeliveryService/Storage</x:v>
+      </x:c>
+      <x:c r="M25" s="3" t="str">
+        <x:v>DeliveryNoteList.razor; DeliveryNoteNew.razor; DeliveryNoteDetail.razor</x:v>
+      </x:c>
+      <x:c r="N25" s="3" t="str">
+        <x:v>/finance/delivery-notes, /delivery-notes, /finance/delivery-notes/new, /finance/delivery-notes/{DeliveryNoteId}</x:v>
+      </x:c>
+      <x:c r="O25" s="3" t="str">
+        <x:v>DeliveryNotesController endpoints</x:v>
+      </x:c>
+      <x:c r="P25" s="3" t="str">
+        <x:v>Delivery note tests where present</x:v>
+      </x:c>
+      <x:c r="Q25" s="3" t="str">
+        <x:v>Intranet BFF, DeliveryService, Storage/Pdf</x:v>
+      </x:c>
+      <x:c r="R25" s="3" t="str">
+        <x:v>Delivery notes, PDF/files</x:v>
+      </x:c>
+      <x:c r="S25" s="3" t="str">
+        <x:v>Needs PDF/file download browser pass</x:v>
+      </x:c>
+      <x:c r="T25" s="3" t="str">
+        <x:v>DeliveryNotesController.cs:17-143; Delivery pages</x:v>
+      </x:c>
+      <x:c r="U25" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="3" t="str">
+        <x:v>INT-025</x:v>
+      </x:c>
+      <x:c r="B26" s="3" t="str">
+        <x:v>Maliev.Intranet</x:v>
+      </x:c>
+      <x:c r="C26" s="3" t="str">
+        <x:v>Shipping</x:v>
+      </x:c>
+      <x:c r="D26" s="3" t="str">
+        <x:v>As staff, I can inspect couriers, quote rates, and track shipments.</x:v>
+      </x:c>
+      <x:c r="E26" s="3" t="str">
+        <x:v>Shipping controller exposes couriers, rates, and tracking through DeliveryService.</x:v>
+      </x:c>
+      <x:c r="F26" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G26" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H26" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I26" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J26" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K26" s="3" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="L26" s="3" t="str">
+        <x:v>Shipping UI/service clients -&gt; api/v1/shipping</x:v>
+      </x:c>
+      <x:c r="M26" s="3" t="str">
+        <x:v>Shipping-related finance/order pages</x:v>
+      </x:c>
+      <x:c r="N26" s="3" t="str">
+        <x:v>couriers/rates/tracking controls</x:v>
+      </x:c>
+      <x:c r="O26" s="3" t="str">
+        <x:v>ShippingController GET couriers, POST rates, GET tracking</x:v>
+      </x:c>
+      <x:c r="P26" s="3" t="str">
+        <x:v>Shipping tests where present</x:v>
+      </x:c>
+      <x:c r="Q26" s="3" t="str">
+        <x:v>Intranet BFF, DeliveryService</x:v>
+      </x:c>
+      <x:c r="R26" s="3" t="str">
+        <x:v>Rate request/tracking lookup</x:v>
+      </x:c>
+      <x:c r="S26" s="3" t="str">
+        <x:v>Needs invalid carrier/tracking coverage</x:v>
+      </x:c>
+      <x:c r="T26" s="3" t="str">
+        <x:v>ShippingController.cs:15-70</x:v>
+      </x:c>
+      <x:c r="U26" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="3" t="str">
+        <x:v>INT-026</x:v>
+      </x:c>
+      <x:c r="B27" s="3" t="str">
+        <x:v>Maliev.Intranet</x:v>
+      </x:c>
+      <x:c r="C27" s="3" t="str">
+        <x:v>Procurement purchase orders</x:v>
+      </x:c>
+      <x:c r="D27" s="3" t="str">
+        <x:v>As purchasing staff, I can list, create, approve, send, receive, cancel, attach, and export purchase orders.</x:v>
+      </x:c>
+      <x:c r="E27" s="3" t="str">
+        <x:v>Procurement routes and controller expose PO lifecycle actions, files, and export.</x:v>
+      </x:c>
+      <x:c r="F27" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G27" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H27" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I27" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J27" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K27" s="3" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="L27" s="3" t="str">
+        <x:v>Purchasing UI -&gt; api/v1/procurement -&gt; PurchaseOrderService/UploadService</x:v>
+      </x:c>
+      <x:c r="M27" s="3" t="str">
+        <x:v>PoList.razor; PoNew.razor; PoDetail.razor</x:v>
+      </x:c>
+      <x:c r="N27" s="3" t="str">
+        <x:v>/purchasing, /purchasing/new, /purchasing/{Id}, /mfg/procurement, /mfg/procurement/{Id}</x:v>
+      </x:c>
+      <x:c r="O27" s="3" t="str">
+        <x:v>ProcurementController GET/detail/POST/approve/send/receive/cancel/files/export</x:v>
+      </x:c>
+      <x:c r="P27" s="3" t="str">
+        <x:v>Procurement tests where present</x:v>
+      </x:c>
+      <x:c r="Q27" s="3" t="str">
+        <x:v>Intranet BFF, PurchaseOrderService, UploadService</x:v>
+      </x:c>
+      <x:c r="R27" s="3" t="str">
+        <x:v>Purchase orders, files, status transitions</x:v>
+      </x:c>
+      <x:c r="S27" s="3" t="str">
+        <x:v>Needs workflow-state browser pass</x:v>
+      </x:c>
+      <x:c r="T27" s="3" t="str">
+        <x:v>ProcurementController.cs:15-203; Purchasing pages</x:v>
+      </x:c>
+      <x:c r="U27" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="3" t="str">
+        <x:v>INT-027</x:v>
+      </x:c>
+      <x:c r="B28" s="3" t="str">
+        <x:v>Maliev.Intranet</x:v>
+      </x:c>
+      <x:c r="C28" s="3" t="str">
+        <x:v>Suppliers</x:v>
+      </x:c>
+      <x:c r="D28" s="3" t="str">
+        <x:v>As purchasing staff, I can list, create, update, deactivate, and manage supplier documents.</x:v>
+      </x:c>
+      <x:c r="E28" s="3" t="str">
+        <x:v>Supplier pages and controller expose supplier CRUD/status, company search, documents upload/delete/download.</x:v>
+      </x:c>
+      <x:c r="F28" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G28" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H28" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I28" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J28" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K28" s="3" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="L28" s="3" t="str">
+        <x:v>Supplier UI -&gt; api/v1/suppliers -&gt; Supplier/Registry/Storage services</x:v>
+      </x:c>
+      <x:c r="M28" s="3" t="str">
+        <x:v>SupplierList.razor; SupplierDetail.razor</x:v>
+      </x:c>
+      <x:c r="N28" s="3" t="str">
+        <x:v>/purchasing/suppliers, /purchasing/suppliers/{Id}</x:v>
+      </x:c>
+      <x:c r="O28" s="3" t="str">
+        <x:v>SuppliersController endpoints</x:v>
+      </x:c>
+      <x:c r="P28" s="3" t="str">
+        <x:v>Supplier tests where present</x:v>
+      </x:c>
+      <x:c r="Q28" s="3" t="str">
+        <x:v>Intranet BFF, SupplierService, RegistryService, Storage</x:v>
+      </x:c>
+      <x:c r="R28" s="3" t="str">
+        <x:v>Supplier records and documents</x:v>
+      </x:c>
+      <x:c r="S28" s="3" t="str">
+        <x:v>Needs document lifecycle browser test</x:v>
+      </x:c>
+      <x:c r="T28" s="3" t="str">
+        <x:v>SuppliersController.cs:19-257; Supplier pages</x:v>
+      </x:c>
+      <x:c r="U28" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="3" t="str">
+        <x:v>INT-028</x:v>
+      </x:c>
+      <x:c r="B29" s="3" t="str">
+        <x:v>Maliev.Intranet</x:v>
+      </x:c>
+      <x:c r="C29" s="3" t="str">
+        <x:v>Manufacturing materials</x:v>
+      </x:c>
+      <x:c r="D29" s="3" t="str">
+        <x:v>As manufacturing staff, I can list and maintain material records.</x:v>
+      </x:c>
+      <x:c r="E29" s="3" t="str">
+        <x:v>Material pages expose material list/detail for manufacturing catalog data.</x:v>
+      </x:c>
+      <x:c r="F29" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G29" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H29" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I29" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J29" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K29" s="3" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="L29" s="3" t="str">
+        <x:v>MFG material pages -&gt; material service/catalog endpoints</x:v>
+      </x:c>
+      <x:c r="M29" s="3" t="str">
+        <x:v>MaterialList.razor; MaterialDetail.razor</x:v>
+      </x:c>
+      <x:c r="N29" s="3" t="str">
+        <x:v>/mfg/materials, /mfg/materials/{Id}</x:v>
+      </x:c>
+      <x:c r="O29" s="3" t="str">
+        <x:v>ManufacturingCatalogController material reference endpoints</x:v>
+      </x:c>
+      <x:c r="P29" s="3" t="str">
+        <x:v>Materials tests where present</x:v>
+      </x:c>
+      <x:c r="Q29" s="3" t="str">
+        <x:v>Intranet BFF, MaterialService</x:v>
+      </x:c>
+      <x:c r="R29" s="3" t="str">
+        <x:v>Material records/reference data</x:v>
+      </x:c>
+      <x:c r="S29" s="3" t="str">
+        <x:v>Needs edit-action inventory</x:v>
+      </x:c>
+      <x:c r="T29" s="3" t="str">
+        <x:v>MaterialList.razor:1; MaterialDetail.razor:1; ManufacturingCatalogController.cs</x:v>
+      </x:c>
+      <x:c r="U29" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="3" t="str">
+        <x:v>INT-029</x:v>
+      </x:c>
+      <x:c r="B30" s="3" t="str">
+        <x:v>Maliev.Intranet</x:v>
+      </x:c>
+      <x:c r="C30" s="3" t="str">
+        <x:v>Equipment</x:v>
+      </x:c>
+      <x:c r="D30" s="3" t="str">
+        <x:v>As manufacturing staff, I can manage equipment, notes, loans, maintenance, and attachments.</x:v>
+      </x:c>
+      <x:c r="E30" s="3" t="str">
+        <x:v>Equipment pages and controller expose equipment CRUD/status, notes, loans approve/reject/return, maintenance, download URLs, and attachments.</x:v>
+      </x:c>
+      <x:c r="F30" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G30" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H30" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I30" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J30" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K30" s="3" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="L30" s="3" t="str">
+        <x:v>Equipment UI -&gt; api/v1/equipments -&gt; EquipmentService/Storage</x:v>
+      </x:c>
+      <x:c r="M30" s="3" t="str">
+        <x:v>EquipmentList.razor; EquipmentDetail.razor</x:v>
+      </x:c>
+      <x:c r="N30" s="3" t="str">
+        <x:v>/mfg/equipment, /mfg/equipment/{Id}</x:v>
+      </x:c>
+      <x:c r="O30" s="3" t="str">
+        <x:v>EquipmentsController CRUD/status/notes/loans/maintenance/attachments</x:v>
+      </x:c>
+      <x:c r="P30" s="3" t="str">
+        <x:v>Equipment tests where present</x:v>
+      </x:c>
+      <x:c r="Q30" s="3" t="str">
+        <x:v>Intranet BFF, EquipmentService, Storage</x:v>
+      </x:c>
+      <x:c r="R30" s="3" t="str">
+        <x:v>Equipment records, loans, maintenance, files</x:v>
+      </x:c>
+      <x:c r="S30" s="3" t="str">
+        <x:v>Needs maintenance file browser test</x:v>
+      </x:c>
+      <x:c r="T30" s="3" t="str">
+        <x:v>EquipmentsController.cs:18-501; Equipment pages</x:v>
+      </x:c>
+      <x:c r="U30" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="3" t="str">
+        <x:v>INT-030</x:v>
+      </x:c>
+      <x:c r="B31" s="3" t="str">
+        <x:v>Maliev.Intranet</x:v>
+      </x:c>
+      <x:c r="C31" s="3" t="str">
+        <x:v>Inventory</x:v>
+      </x:c>
+      <x:c r="D31" s="3" t="str">
+        <x:v>As operations staff, I can create batches/items, look up tracking codes, consume stock, and monitor batch status.</x:v>
+      </x:c>
+      <x:c r="E31" s="3" t="str">
+        <x:v>Inventory controller exposes batches/items create/list/detail/lookup/consume/status endpoints.</x:v>
+      </x:c>
+      <x:c r="F31" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G31" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H31" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I31" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J31" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K31" s="3" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="L31" s="3" t="str">
+        <x:v>Inventory UI/service flows -&gt; api/v1/inventory -&gt; InventoryService</x:v>
+      </x:c>
+      <x:c r="M31" s="3" t="str">
+        <x:v>Inventory surfaces in manufacturing/procurement</x:v>
+      </x:c>
+      <x:c r="N31" s="3" t="str">
+        <x:v>Inventory controls</x:v>
+      </x:c>
+      <x:c r="O31" s="3" t="str">
+        <x:v>InventoryController batches/items/list/detail/lookup/consume/status</x:v>
+      </x:c>
+      <x:c r="P31" s="3" t="str">
+        <x:v>Inventory tests where present</x:v>
+      </x:c>
+      <x:c r="Q31" s="3" t="str">
+        <x:v>Intranet BFF, InventoryService</x:v>
+      </x:c>
+      <x:c r="R31" s="3" t="str">
+        <x:v>Inventory batches/items/consumption</x:v>
+      </x:c>
+      <x:c r="S31" s="3" t="str">
+        <x:v>Needs UI route inventory</x:v>
+      </x:c>
+      <x:c r="T31" s="3" t="str">
+        <x:v>InventoryController.cs:15-122</x:v>
+      </x:c>
+      <x:c r="U31" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="3" t="str">
+        <x:v>INT-031</x:v>
+      </x:c>
+      <x:c r="B32" s="3" t="str">
+        <x:v>Maliev.Intranet</x:v>
+      </x:c>
+      <x:c r="C32" s="3" t="str">
+        <x:v>Production schedule</x:v>
+      </x:c>
+      <x:c r="D32" s="3" t="str">
+        <x:v>As manufacturing staff, I can view production schedule work.</x:v>
+      </x:c>
+      <x:c r="E32" s="3" t="str">
+        <x:v>Production schedule route renders manufacturing schedule page.</x:v>
+      </x:c>
+      <x:c r="F32" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G32" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H32" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I32" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J32" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K32" s="3" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="L32" s="3" t="str">
+        <x:v>ProductionSchedule page -&gt; manufacturing/job planning endpoints</x:v>
+      </x:c>
+      <x:c r="M32" s="3" t="str">
+        <x:v>ProductionSchedule.razor</x:v>
+      </x:c>
+      <x:c r="N32" s="3" t="str">
+        <x:v>/mfg/production-schedule</x:v>
+      </x:c>
+      <x:c r="O32" s="3" t="str">
+        <x:v>Jobs/production controllers where configured</x:v>
+      </x:c>
+      <x:c r="P32" s="3" t="str">
+        <x:v>Production schedule tests where present</x:v>
+      </x:c>
+      <x:c r="Q32" s="3" t="str">
+        <x:v>Intranet BFF, Manufacturing/Jobs services</x:v>
+      </x:c>
+      <x:c r="R32" s="3" t="str">
+        <x:v>Schedule state</x:v>
+      </x:c>
+      <x:c r="S32" s="3" t="str">
+        <x:v>Needs action inventory and browser test</x:v>
+      </x:c>
+      <x:c r="T32" s="3" t="str">
+        <x:v>ProductionSchedule.razor:1</x:v>
+      </x:c>
+      <x:c r="U32" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="3" t="str">
+        <x:v>INT-032</x:v>
+      </x:c>
+      <x:c r="B33" s="3" t="str">
+        <x:v>Maliev.Intranet</x:v>
+      </x:c>
+      <x:c r="C33" s="3" t="str">
+        <x:v>Models and thumbnails</x:v>
+      </x:c>
+      <x:c r="D33" s="3" t="str">
+        <x:v>As quoting/manufacturing staff, I can upload, inspect, view, thumbnail, and delete standalone models.</x:v>
+      </x:c>
+      <x:c r="E33" s="3" t="str">
+        <x:v>Models controller exposes model list/detail/upload/viewer-url/thumbnail-url/delete endpoints.</x:v>
+      </x:c>
+      <x:c r="F33" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G33" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H33" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I33" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J33" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K33" s="3" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="L33" s="3" t="str">
+        <x:v>Model UI -&gt; api/v1/models -&gt; UploadService/Storage</x:v>
+      </x:c>
+      <x:c r="M33" s="3" t="str">
+        <x:v>Model/viewer surfaces</x:v>
+      </x:c>
+      <x:c r="N33" s="3" t="str">
+        <x:v>model viewer/thumbnail controls</x:v>
+      </x:c>
+      <x:c r="O33" s="3" t="str">
+        <x:v>ModelsController GET/detail/upload/viewer-url/thumbnail-url/delete</x:v>
+      </x:c>
+      <x:c r="P33" s="3" t="str">
+        <x:v>Model tests where present</x:v>
+      </x:c>
+      <x:c r="Q33" s="3" t="str">
+        <x:v>Intranet BFF, UploadService, Storage</x:v>
+      </x:c>
+      <x:c r="R33" s="3" t="str">
+        <x:v>Model records/files</x:v>
+      </x:c>
+      <x:c r="S33" s="3" t="str">
+        <x:v>Needs UI route mapping</x:v>
+      </x:c>
+      <x:c r="T33" s="3" t="str">
+        <x:v>ModelsController.cs:15-108</x:v>
+      </x:c>
+      <x:c r="U33" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="3" t="str">
+        <x:v>INT-033</x:v>
+      </x:c>
+      <x:c r="B34" s="3" t="str">
+        <x:v>Maliev.Intranet</x:v>
+      </x:c>
+      <x:c r="C34" s="3" t="str">
+        <x:v>IAM users roles permissions</x:v>
+      </x:c>
+      <x:c r="D34" s="3" t="str">
+        <x:v>As an admin, I can manage users, roles, permissions, role bindings, invites, activity, and role permission matrices.</x:v>
+      </x:c>
+      <x:c r="E34" s="3" t="str">
+        <x:v>IAM pages and controller expose user/role/permission list/detail/paged, role binding add/remove, invite, patch, activity, and matrix endpoints.</x:v>
+      </x:c>
+      <x:c r="F34" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G34" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H34" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I34" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J34" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K34" s="3" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="L34" s="3" t="str">
+        <x:v>IAM UI -&gt; api/v1/iam and permissions controllers -&gt; IAMService</x:v>
+      </x:c>
+      <x:c r="M34" s="3" t="str">
+        <x:v>UserList.razor; UserNew.razor; UserDetail.razor; RoleDetail.razor</x:v>
+      </x:c>
+      <x:c r="N34" s="3" t="str">
+        <x:v>/iam, /iam/users/new, /iam/users/{Id}, /iam/roles/{Id}</x:v>
+      </x:c>
+      <x:c r="O34" s="3" t="str">
+        <x:v>IamController users/roles/permissions/bindings/invite/activity/matrix; PermissionsController</x:v>
+      </x:c>
+      <x:c r="P34" s="3" t="str">
+        <x:v>IAM tests where present</x:v>
+      </x:c>
+      <x:c r="Q34" s="3" t="str">
+        <x:v>Intranet BFF, IAMService</x:v>
+      </x:c>
+      <x:c r="R34" s="3" t="str">
+        <x:v>Users, roles, permissions, bindings</x:v>
+      </x:c>
+      <x:c r="S34" s="3" t="str">
+        <x:v>Needs permission matrix and audit validation</x:v>
+      </x:c>
+      <x:c r="T34" s="3" t="str">
+        <x:v>IamController.cs:21-321; PermissionsController.cs:17-59; IAM pages</x:v>
+      </x:c>
+      <x:c r="U34" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="3" t="str">
+        <x:v>INT-034</x:v>
+      </x:c>
+      <x:c r="B35" s="3" t="str">
+        <x:v>Maliev.Intranet</x:v>
+      </x:c>
+      <x:c r="C35" s="3" t="str">
+        <x:v>Employee profile and HR records</x:v>
+      </x:c>
+      <x:c r="D35" s="3" t="str">
+        <x:v>As an employee or HR manager, I can view/update employee profiles, analytics, org chart, and notes.</x:v>
+      </x:c>
+      <x:c r="E35" s="3" t="str">
+        <x:v>Employees controller exposes employee CRUD, terminate, me/profile read/write, analytics, org chart, and notes.</x:v>
+      </x:c>
+      <x:c r="F35" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G35" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H35" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I35" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J35" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K35" s="3" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="L35" s="3" t="str">
+        <x:v>HR pages -&gt; api/v1/employees -&gt; EmployeeService/IAM</x:v>
+      </x:c>
+      <x:c r="M35" s="3" t="str">
+        <x:v>Profile.razor; HR pages</x:v>
+      </x:c>
+      <x:c r="N35" s="3" t="str">
+        <x:v>/hr/profile</x:v>
+      </x:c>
+      <x:c r="O35" s="3" t="str">
+        <x:v>EmployeesController endpoints</x:v>
+      </x:c>
+      <x:c r="P35" s="3" t="str">
+        <x:v>Employee tests where present</x:v>
+      </x:c>
+      <x:c r="Q35" s="3" t="str">
+        <x:v>Intranet BFF, EmployeeService, IAMService</x:v>
+      </x:c>
+      <x:c r="R35" s="3" t="str">
+        <x:v>Employee records/profile/notes</x:v>
+      </x:c>
+      <x:c r="S35" s="3" t="str">
+        <x:v>Needs privacy/permission validation</x:v>
+      </x:c>
+      <x:c r="T35" s="3" t="str">
+        <x:v>EmployeesController.cs:19-166; Profile.razor:1</x:v>
+      </x:c>
+      <x:c r="U35" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="3" t="str">
+        <x:v>INT-035</x:v>
+      </x:c>
+      <x:c r="B36" s="3" t="str">
+        <x:v>Maliev.Intranet</x:v>
+      </x:c>
+      <x:c r="C36" s="3" t="str">
+        <x:v>Leave and approvals</x:v>
+      </x:c>
+      <x:c r="D36" s="3" t="str">
+        <x:v>As an employee or manager, I can view balances, request leave, and decide approvals.</x:v>
+      </x:c>
+      <x:c r="E36" s="3" t="str">
+        <x:v>Time off controller exposes balances, requests list/create, approvals, and decision endpoints.</x:v>
+      </x:c>
+      <x:c r="F36" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G36" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H36" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I36" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J36" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K36" s="3" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="L36" s="3" t="str">
+        <x:v>Leave UI -&gt; api/v1/timeoff -&gt; LeaveService/EmployeeService</x:v>
+      </x:c>
+      <x:c r="M36" s="3" t="str">
+        <x:v>Leave.razor</x:v>
+      </x:c>
+      <x:c r="N36" s="3" t="str">
+        <x:v>/hr/leave</x:v>
+      </x:c>
+      <x:c r="O36" s="3" t="str">
+        <x:v>TimeOffController balances/requests/approvals/decision</x:v>
+      </x:c>
+      <x:c r="P36" s="3" t="str">
+        <x:v>TimeOff tests where present</x:v>
+      </x:c>
+      <x:c r="Q36" s="3" t="str">
+        <x:v>Intranet BFF, LeaveService, EmployeeService</x:v>
+      </x:c>
+      <x:c r="R36" s="3" t="str">
+        <x:v>Leave requests and decisions</x:v>
+      </x:c>
+      <x:c r="S36" s="3" t="str">
+        <x:v>Needs approval authorization test</x:v>
+      </x:c>
+      <x:c r="T36" s="3" t="str">
+        <x:v>TimeOffController.cs:17-131; Leave.razor:1</x:v>
+      </x:c>
+      <x:c r="U36" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="3" t="str">
+        <x:v>INT-036</x:v>
+      </x:c>
+      <x:c r="B37" s="3" t="str">
+        <x:v>Maliev.Intranet</x:v>
+      </x:c>
+      <x:c r="C37" s="3" t="str">
+        <x:v>Recruitment</x:v>
+      </x:c>
+      <x:c r="D37" s="3" t="str">
+        <x:v>As HR staff, I can manage job openings and candidates.</x:v>
+      </x:c>
+      <x:c r="E37" s="3" t="str">
+        <x:v>Recruitment controller exposes jobs, stats, job create/update, candidate create, and candidate status patch.</x:v>
+      </x:c>
+      <x:c r="F37" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G37" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H37" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I37" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J37" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K37" s="3" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="L37" s="3" t="str">
+        <x:v>Recruitment UI/service flows -&gt; api/v1/recruitment -&gt; CareerService</x:v>
+      </x:c>
+      <x:c r="M37" s="3" t="str">
+        <x:v>HR/recruitment surfaces</x:v>
+      </x:c>
+      <x:c r="N37" s="3" t="str">
+        <x:v>Recruitment controls</x:v>
+      </x:c>
+      <x:c r="O37" s="3" t="str">
+        <x:v>RecruitmentController jobs/stats/candidates</x:v>
+      </x:c>
+      <x:c r="P37" s="3" t="str">
+        <x:v>Recruitment tests where present</x:v>
+      </x:c>
+      <x:c r="Q37" s="3" t="str">
+        <x:v>Intranet BFF, CareerService</x:v>
+      </x:c>
+      <x:c r="R37" s="3" t="str">
+        <x:v>Jobs and candidate records</x:v>
+      </x:c>
+      <x:c r="S37" s="3" t="str">
+        <x:v>Needs route/page inventory</x:v>
+      </x:c>
+      <x:c r="T37" s="3" t="str">
+        <x:v>RecruitmentController.cs:16-80</x:v>
+      </x:c>
+      <x:c r="U37" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="3" t="str">
+        <x:v>INT-037</x:v>
+      </x:c>
+      <x:c r="B38" s="3" t="str">
+        <x:v>Maliev.Intranet</x:v>
+      </x:c>
+      <x:c r="C38" s="3" t="str">
+        <x:v>Compensation and benefits</x:v>
+      </x:c>
+      <x:c r="D38" s="3" t="str">
+        <x:v>As HR/finance staff, I can view compensation summary and benefits.</x:v>
+      </x:c>
+      <x:c r="E38" s="3" t="str">
+        <x:v>Compensation controller returns summary and benefits data.</x:v>
+      </x:c>
+      <x:c r="F38" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G38" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H38" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I38" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J38" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K38" s="3" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="L38" s="3" t="str">
+        <x:v>Compensation UI -&gt; api/v1/compensation -&gt; CompensationService</x:v>
+      </x:c>
+      <x:c r="M38" s="3" t="str">
+        <x:v>HR/compensation surfaces</x:v>
+      </x:c>
+      <x:c r="N38" s="3" t="str">
+        <x:v>Compensation controls</x:v>
+      </x:c>
+      <x:c r="O38" s="3" t="str">
+        <x:v>CompensationController summary/benefits</x:v>
+      </x:c>
+      <x:c r="P38" s="3" t="str">
+        <x:v>Compensation tests where present</x:v>
+      </x:c>
+      <x:c r="Q38" s="3" t="str">
+        <x:v>Intranet BFF, CompensationService</x:v>
+      </x:c>
+      <x:c r="R38" s="3" t="str">
+        <x:v>Read-only compensation/benefits data</x:v>
+      </x:c>
+      <x:c r="S38" s="3" t="str">
+        <x:v>Needs privacy/permission validation</x:v>
+      </x:c>
+      <x:c r="T38" s="3" t="str">
+        <x:v>CompensationController.cs:17-35</x:v>
+      </x:c>
+      <x:c r="U38" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="3" t="str">
+        <x:v>INT-038</x:v>
+      </x:c>
+      <x:c r="B39" s="3" t="str">
+        <x:v>Maliev.Intranet</x:v>
+      </x:c>
+      <x:c r="C39" s="3" t="str">
+        <x:v>Reference data</x:v>
+      </x:c>
+      <x:c r="D39" s="3" t="str">
+        <x:v>As an admin, I can manage countries, currencies, rates, and locations.</x:v>
+      </x:c>
+      <x:c r="E39" s="3" t="str">
+        <x:v>ReferenceData controller exposes countries/currencies/locations list/page/create/update/delete/restore, primary currency, and exchange-rate lookup.</x:v>
+      </x:c>
+      <x:c r="F39" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G39" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H39" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I39" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J39" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K39" s="3" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="L39" s="3" t="str">
+        <x:v>ReferenceData page -&gt; api/v1/referenceData -&gt; reference data store</x:v>
+      </x:c>
+      <x:c r="M39" s="3" t="str">
+        <x:v>ReferenceData.razor</x:v>
+      </x:c>
+      <x:c r="N39" s="3" t="str">
+        <x:v>/admin/reference-data</x:v>
+      </x:c>
+      <x:c r="O39" s="3" t="str">
+        <x:v>ReferenceDataController countries/currencies/locations/rate endpoints</x:v>
+      </x:c>
+      <x:c r="P39" s="3" t="str">
+        <x:v>ReferenceData tests where present</x:v>
+      </x:c>
+      <x:c r="Q39" s="3" t="str">
+        <x:v>Intranet BFF, ReferenceData store</x:v>
+      </x:c>
+      <x:c r="R39" s="3" t="str">
+        <x:v>Reference records</x:v>
+      </x:c>
+      <x:c r="S39" s="3" t="str">
+        <x:v>Needs destructive action confirmation test</x:v>
+      </x:c>
+      <x:c r="T39" s="3" t="str">
+        <x:v>ReferenceDataController.cs:15-299; ReferenceData.razor:1</x:v>
+      </x:c>
+      <x:c r="U39" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="3" t="str">
+        <x:v>INT-039</x:v>
+      </x:c>
+      <x:c r="B40" s="3" t="str">
+        <x:v>Maliev.Intranet</x:v>
+      </x:c>
+      <x:c r="C40" s="3" t="str">
+        <x:v>System health</x:v>
+      </x:c>
+      <x:c r="D40" s="3" t="str">
+        <x:v>As an admin, I can view current and historical system health.</x:v>
+      </x:c>
+      <x:c r="E40" s="3" t="str">
+        <x:v>System health controller exposes current health and history.</x:v>
+      </x:c>
+      <x:c r="F40" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G40" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H40" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I40" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J40" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K40" s="3" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="L40" s="3" t="str">
+        <x:v>SystemHealth page -&gt; api/v1/system-health</x:v>
+      </x:c>
+      <x:c r="M40" s="3" t="str">
+        <x:v>SystemHealth.razor</x:v>
+      </x:c>
+      <x:c r="N40" s="3" t="str">
+        <x:v>/admin/system-health</x:v>
+      </x:c>
+      <x:c r="O40" s="3" t="str">
+        <x:v>SystemHealthController GET, history</x:v>
+      </x:c>
+      <x:c r="P40" s="3" t="str">
+        <x:v>System health tests where present</x:v>
+      </x:c>
+      <x:c r="Q40" s="3" t="str">
+        <x:v>Intranet BFF, Health sampler/services</x:v>
+      </x:c>
+      <x:c r="R40" s="3" t="str">
+        <x:v>Read-only health history</x:v>
+      </x:c>
+      <x:c r="S40" s="3" t="str">
+        <x:v>Needs readiness noise triage in later loop</x:v>
+      </x:c>
+      <x:c r="T40" s="3" t="str">
+        <x:v>SystemHealthController.cs:15-49; SystemHealth.razor:1</x:v>
+      </x:c>
+      <x:c r="U40" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="3" t="str">
+        <x:v>INT-040</x:v>
+      </x:c>
+      <x:c r="B41" s="3" t="str">
+        <x:v>Maliev.Intranet</x:v>
+      </x:c>
+      <x:c r="C41" s="3" t="str">
+        <x:v>AI processing and document extraction</x:v>
+      </x:c>
+      <x:c r="D41" s="3" t="str">
+        <x:v>As staff, I can extract structured data from uploaded documents and link/download those documents.</x:v>
+      </x:c>
+      <x:c r="E41" s="3" t="str">
+        <x:v>AI processing controller exposes health, customer/supplier/accounting/NDA extraction, NDA summary, upload single/multiple documents, link documents, and download URL endpoints.</x:v>
+      </x:c>
+      <x:c r="F41" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G41" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H41" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I41" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J41" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K41" s="3" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="L41" s="3" t="str">
+        <x:v>AI processing UI/service flows -&gt; api/v1/aiprocessing -&gt; AI/storage services</x:v>
+      </x:c>
+      <x:c r="M41" s="3" t="str">
+        <x:v>AI/admin document surfaces</x:v>
+      </x:c>
+      <x:c r="N41" s="3" t="str">
+        <x:v>Extraction/upload/download controls</x:v>
+      </x:c>
+      <x:c r="O41" s="3" t="str">
+        <x:v>AiProcessingController health/extract/upload/link/download endpoints</x:v>
+      </x:c>
+      <x:c r="P41" s="3" t="str">
+        <x:v>AI processing tests where present</x:v>
+      </x:c>
+      <x:c r="Q41" s="3" t="str">
+        <x:v>Intranet BFF, AI service, Storage</x:v>
+      </x:c>
+      <x:c r="R41" s="3" t="str">
+        <x:v>Extraction results, uploaded documents, links</x:v>
+      </x:c>
+      <x:c r="S41" s="3" t="str">
+        <x:v>Needs high-stakes extraction validation</x:v>
+      </x:c>
+      <x:c r="T41" s="3" t="str">
+        <x:v>AiProcessingController.cs:22-964</x:v>
+      </x:c>
+      <x:c r="U41" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="3" t="str">
+        <x:v>INT-041</x:v>
+      </x:c>
+      <x:c r="B42" s="3" t="str">
+        <x:v>Maliev.Intranet</x:v>
+      </x:c>
+      <x:c r="C42" s="3" t="str">
+        <x:v>Preferences</x:v>
+      </x:c>
+      <x:c r="D42" s="3" t="str">
+        <x:v>As an employee, I can get, save, and delete scoped preferences.</x:v>
+      </x:c>
+      <x:c r="E42" s="3" t="str">
+        <x:v>Preferences controller exposes get/put/delete by scope.</x:v>
+      </x:c>
+      <x:c r="F42" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G42" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H42" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I42" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J42" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K42" s="3" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="L42" s="3" t="str">
+        <x:v>UI settings -&gt; api/v1/preferences/{scope} -&gt; EmployeeService</x:v>
+      </x:c>
+      <x:c r="M42" s="3" t="str">
+        <x:v>TopBar/preferences controls</x:v>
+      </x:c>
+      <x:c r="N42" s="3" t="str">
+        <x:v>Scoped preferences</x:v>
+      </x:c>
+      <x:c r="O42" s="3" t="str">
+        <x:v>PreferencesController GET/PUT/DELETE</x:v>
+      </x:c>
+      <x:c r="P42" s="3" t="str">
+        <x:v>Preferences tests where present</x:v>
+      </x:c>
+      <x:c r="Q42" s="3" t="str">
+        <x:v>Intranet BFF, EmployeeService</x:v>
+      </x:c>
+      <x:c r="R42" s="3" t="str">
+        <x:v>Scoped preference records</x:v>
+      </x:c>
+      <x:c r="S42" s="3" t="str">
+        <x:v>Needs multi-device behavior check</x:v>
+      </x:c>
+      <x:c r="T42" s="3" t="str">
+        <x:v>PreferencesController.cs:15-53</x:v>
+      </x:c>
+      <x:c r="U42" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="3" t="str">
+        <x:v>INT-042</x:v>
+      </x:c>
+      <x:c r="B43" s="3" t="str">
+        <x:v>Maliev.Intranet</x:v>
+      </x:c>
+      <x:c r="C43" s="3" t="str">
+        <x:v>Auth login/logout/user/avatar</x:v>
+      </x:c>
+      <x:c r="D43" s="3" t="str">
+        <x:v>As an employee, I can log in/out and load my user/avatar/debug info.</x:v>
+      </x:c>
+      <x:c r="E43" s="3" t="str">
+        <x:v>Auth controller exposes login GET/POST/form, logout, user, debug, and avatar endpoints.</x:v>
+      </x:c>
+      <x:c r="F43" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G43" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H43" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I43" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J43" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K43" s="3" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="L43" s="3" t="str">
+        <x:v>Login/shell -&gt; api/v1/auth -&gt; auth/session</x:v>
+      </x:c>
+      <x:c r="M43" s="3" t="str">
+        <x:v>Auth/login surfaces</x:v>
+      </x:c>
+      <x:c r="N43" s="3" t="str">
+        <x:v>Login/logout/user/avatar controls</x:v>
+      </x:c>
+      <x:c r="O43" s="3" t="str">
+        <x:v>AuthController endpoints</x:v>
+      </x:c>
+      <x:c r="P43" s="3" t="str">
+        <x:v>Auth/login tests where present</x:v>
+      </x:c>
+      <x:c r="Q43" s="3" t="str">
+        <x:v>Intranet BFF, Auth/IAM</x:v>
+      </x:c>
+      <x:c r="R43" s="3" t="str">
+        <x:v>Auth session/cookies</x:v>
+      </x:c>
+      <x:c r="S43" s="3" t="str">
+        <x:v>Needs auth guard browser pass</x:v>
+      </x:c>
+      <x:c r="T43" s="3" t="str">
+        <x:v>AuthController.cs:20-319</x:v>
+      </x:c>
+      <x:c r="U43" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="3" t="str">
+        <x:v>INT-043</x:v>
+      </x:c>
+      <x:c r="B44" s="3" t="str">
+        <x:v>Maliev.Intranet</x:v>
+      </x:c>
+      <x:c r="C44" s="3" t="str">
+        <x:v>Address configuration</x:v>
+      </x:c>
+      <x:c r="D44" s="3" t="str">
+        <x:v>As an employee, I can use Google address configuration in intranet forms.</x:v>
+      </x:c>
+      <x:c r="E44" s="3" t="str">
+        <x:v>Address controller exposes Google config for address widgets.</x:v>
+      </x:c>
+      <x:c r="F44" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G44" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H44" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I44" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J44" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K44" s="3" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="L44" s="3" t="str">
+        <x:v>Address forms -&gt; api/v1/address/google-config</x:v>
+      </x:c>
+      <x:c r="M44" s="3" t="str">
+        <x:v>Customer/supplier address forms</x:v>
+      </x:c>
+      <x:c r="N44" s="3" t="str">
+        <x:v>Address helper controls</x:v>
+      </x:c>
+      <x:c r="O44" s="3" t="str">
+        <x:v>AddressController GET google-config</x:v>
+      </x:c>
+      <x:c r="P44" s="3" t="str">
+        <x:v>Address source tests where present</x:v>
+      </x:c>
+      <x:c r="Q44" s="3" t="str">
+        <x:v>Intranet BFF, configuration</x:v>
+      </x:c>
+      <x:c r="R44" s="3" t="str">
+        <x:v>Read-only config</x:v>
+      </x:c>
+      <x:c r="S44" s="3" t="str">
+        <x:v>Needs no-key fallback check</x:v>
+      </x:c>
+      <x:c r="T44" s="3" t="str">
+        <x:v>AddressController.cs:13-20</x:v>
+      </x:c>
+      <x:c r="U44" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="3" t="str">
+        <x:v>INT-044</x:v>
+      </x:c>
+      <x:c r="B45" s="3" t="str">
+        <x:v>Maliev.Intranet</x:v>
+      </x:c>
+      <x:c r="C45" s="3" t="str">
+        <x:v>Seed customer command</x:v>
+      </x:c>
+      <x:c r="D45" s="3" t="str">
+        <x:v>As an operator/test runner, I can seed customer data through authorized BFF seed endpoints.</x:v>
+      </x:c>
+      <x:c r="E45" s="3" t="str">
+        <x:v>Seed controller exposes customer seeding routes for integration/testing workflows.</x:v>
+      </x:c>
+      <x:c r="F45" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G45" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H45" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I45" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J45" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K45" s="3" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="L45" s="3" t="str">
+        <x:v>Aspire command/test -&gt; seed controller -&gt; database seeder/customer service</x:v>
+      </x:c>
+      <x:c r="M45" s="3" t="str">
+        <x:v>SeedController</x:v>
+      </x:c>
+      <x:c r="N45" s="3" t="str">
+        <x:v>Seed command/API</x:v>
+      </x:c>
+      <x:c r="O45" s="3" t="str">
+        <x:v>SeedController POST customers and /api/seed/customers</x:v>
+      </x:c>
+      <x:c r="P45" s="3" t="str">
+        <x:v>Aspire seed tests where present</x:v>
+      </x:c>
+      <x:c r="Q45" s="3" t="str">
+        <x:v>Intranet BFF, DatabaseSeeder, CustomerService</x:v>
+      </x:c>
+      <x:c r="R45" s="3" t="str">
+        <x:v>Seeded customer records</x:v>
+      </x:c>
+      <x:c r="S45" s="3" t="str">
+        <x:v>Operator-only route needs environment guard review</x:v>
+      </x:c>
+      <x:c r="T45" s="3" t="str">
+        <x:v>SeedController.cs:18-33</x:v>
+      </x:c>
+      <x:c r="U45" s="3" t="str">
         <x:v>2026-06-23</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R047060b36b884c0d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R538fcc7d41c54202"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1663,26 +5366,26 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="10.75" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="9.130000114440918" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="15.5" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="45.380001068115234" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="122" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="161.1300048828125" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="25.25" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="79.12999725341797" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="103.37999725341797" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="18.25" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="18.75" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="19.8799991607666" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="10.380000114440918" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="13" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="8.75" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="112" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="75.87999725341797" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="86.75" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="123.37999725341797" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="94.87999725341797" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="59.880001068115234" hidden="0" customWidth="1"/>
-    <x:col min="18" max="18" width="51" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="96.5" hidden="0" customWidth="1"/>
-    <x:col min="20" max="20" width="187.8800048828125" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="68.37999725341797" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="72.12999725341797" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="57.5" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="72.12999725341797" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="59.380001068115234" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="43.75" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="31.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="67.75" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="62" hidden="0" customWidth="1"/>
     <x:col min="21" max="21" width="13.880000114440918" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -1753,19 +5456,19 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="3" t="str">
-        <x:v>QE-CODE-001</x:v>
+        <x:v>QE-001</x:v>
       </x:c>
       <x:c r="B2" s="3" t="str">
         <x:v>Maliev.QuoteEngine</x:v>
       </x:c>
       <x:c r="C2" s="3" t="str">
-        <x:v>Agentic manufacturing workspace routes and launch shell</x:v>
+        <x:v>Agentic workspace shell</x:v>
       </x:c>
       <x:c r="D2" s="3" t="str">
-        <x:v>As a customer, I can open the agentic manufacturing workspace, chat with quote agents, start or search projects, and move parts through analysis and quoting.</x:v>
+        <x:v>As a customer, I can open the manufacturing workspace and start or resume quote work.</x:v>
       </x:c>
       <x:c r="E2" s="3" t="str">
-        <x:v>The workspace loads QuoteAgentLaunchShell, lets customers chat with manufacturing agents, upload and analyze parts, manage projects/search, and continue into quote actions.</x:v>
+        <x:v>The root/quotes/new-project routes load the agent shell and workspace without presenting a sample-only feature.</x:v>
       </x:c>
       <x:c r="F2" s="3" t="str">
         <x:v>Current code-derived</x:v>
@@ -1786,31 +5489,31 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L2" s="3" t="str">
-        <x:v>Blazor workspace -&gt; QuoteEngineApiClient -&gt; quote/v1 project nav/search/actions DTOs -&gt; auth/session state</x:v>
+        <x:v>Blazor workspace routes -&gt; QuoteAgentLaunchShell -&gt; quote session/project state</x:v>
       </x:c>
       <x:c r="M2" s="3" t="str">
         <x:v>QuoteWorkspace.razor; QuoteAgentLaunchShell.razor</x:v>
       </x:c>
       <x:c r="N2" s="3" t="str">
-        <x:v>@page /, /quotes, /quotes/new, /quote/new, /projects/new; rail New project/Projects/search; agent chat composer</x:v>
+        <x:v>@page /, /quotes, /quotes/new, /quote/new, /projects/new</x:v>
       </x:c>
       <x:c r="O2" s="3" t="str">
-        <x:v>QuoteController projects/nav/detail/duplicate/pin/archive/achieve; AgentController search</x:v>
+        <x:v>QuoteController project nav/detail endpoints</x:v>
       </x:c>
       <x:c r="P2" s="3" t="str">
-        <x:v>QuoteEngineSourceTests workspace routes/navigation/search; QuoteAgentEndpointTests search</x:v>
+        <x:v>QuoteEngineSourceTests workspace/shell</x:v>
       </x:c>
       <x:c r="Q2" s="3" t="str">
-        <x:v>QuoteEngine BFF, Auth, Project/session store</x:v>
+        <x:v>QuoteEngine client/BFF, session store</x:v>
       </x:c>
       <x:c r="R2" s="3" t="str">
-        <x:v>Project/session state, nav pins/archive flags</x:v>
+        <x:v>Session/project state</x:v>
       </x:c>
       <x:c r="S2" s="3" t="str">
-        <x:v>Use current chat workspace behavior as canonical</x:v>
+        <x:v>The source still contains a non-current route, but tracking excludes it per product direction</x:v>
       </x:c>
       <x:c r="T2" s="3" t="str">
-        <x:v>QuoteWorkspace.razor:1-5,39,470; QuoteAgentLaunchShell.razor:36,48-54,338-474,5829-5867</x:v>
+        <x:v>QuoteWorkspace.razor:1-5,39; QuoteAgentLaunchShell.razor</x:v>
       </x:c>
       <x:c r="U2" s="3" t="str">
         <x:v>2026-06-23</x:v>
@@ -1818,19 +5521,19 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="3" t="str">
-        <x:v>QE-CODE-002</x:v>
+        <x:v>QE-002</x:v>
       </x:c>
       <x:c r="B3" s="3" t="str">
         <x:v>Maliev.QuoteEngine</x:v>
       </x:c>
       <x:c r="C3" s="3" t="str">
-        <x:v>Agent chat, state, gates, confirmations</x:v>
+        <x:v>Agent health and readiness</x:v>
       </x:c>
       <x:c r="D3" s="3" t="str">
-        <x:v>As a customer, I can converse with the quote agent, stream responses, see quote-state gates, and confirm tool actions before irreversible changes.</x:v>
+        <x:v>As a customer, I can see whether the quote agent is available before sending work.</x:v>
       </x:c>
       <x:c r="E3" s="3" t="str">
-        <x:v>Agent endpoints support health, message send/stream/history/state, tools, confirmation actions, thinking updates, clean speech, and session gates for estimate/formal/order/payment readiness.</x:v>
+        <x:v>Agent health endpoint and shell status indicators reflect backend readiness and keep composer state aligned.</x:v>
       </x:c>
       <x:c r="F3" s="3" t="str">
         <x:v>Current code-derived</x:v>
@@ -1851,31 +5554,31 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L3" s="3" t="str">
-        <x:v>Composer -&gt; AgentController -&gt; QuoteAgentService -&gt; QuoteAgentSessionStore DTOs/gates/actions</x:v>
+        <x:v>Shell status -&gt; quote/v1/agent/health -&gt; readiness state</x:v>
       </x:c>
       <x:c r="M3" s="3" t="str">
-        <x:v>QuoteAgentLaunchShell.razor; AgentController.cs; QuoteAgentService.cs; QuoteAgentSessionStore.cs</x:v>
+        <x:v>QuoteAgentLaunchShell.razor</x:v>
       </x:c>
       <x:c r="N3" s="3" t="str">
-        <x:v>Composer, send button gating, action confirmation cards, state/gates</x:v>
+        <x:v>Agent status dot/composer gating</x:v>
       </x:c>
       <x:c r="O3" s="3" t="str">
-        <x:v>AgentController health/messages/stream/state/history/tools/actions/confirm/thinking; QuoteAgentDtos TurnResponse/State/Gates/Action</x:v>
+        <x:v>AgentController GET health</x:v>
       </x:c>
       <x:c r="P3" s="3" t="str">
-        <x:v>QuoteAgentEndpointTests health, anonymous gate, stream events, history auth, model/language, fallback</x:v>
+        <x:v>QuoteAgentEndpointTests health; QuoteEngineSourceTests status dot</x:v>
       </x:c>
       <x:c r="Q3" s="3" t="str">
-        <x:v>QuoteEngine BFF, Agent model, SessionStore, Customer memory</x:v>
+        <x:v>QuoteEngine BFF, Agent service</x:v>
       </x:c>
       <x:c r="R3" s="3" t="str">
-        <x:v>Chat messages, session state, pending actions</x:v>
+        <x:v>Read-only readiness</x:v>
       </x:c>
       <x:c r="S3" s="3" t="str">
-        <x:v>Needs live browser retest for stream interruption/reconnect</x:v>
+        <x:v>Needs live Aspire readiness smoke</x:v>
       </x:c>
       <x:c r="T3" s="3" t="str">
-        <x:v>AgentController.cs:33,56,76,111,132,142,297,321,423; QuoteAgentService.cs:159,247,443,826-917,965-1010; QuoteAgentSessionStore.cs:167,196,220-244,438-474</x:v>
+        <x:v>AgentController.cs:33; QuoteAgentLaunchShell.razor</x:v>
       </x:c>
       <x:c r="U3" s="3" t="str">
         <x:v>2026-06-23</x:v>
@@ -1883,19 +5586,19 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="3" t="str">
-        <x:v>QE-CODE-003</x:v>
+        <x:v>QE-003</x:v>
       </x:c>
       <x:c r="B4" s="3" t="str">
         <x:v>Maliev.QuoteEngine</x:v>
       </x:c>
       <x:c r="C4" s="3" t="str">
-        <x:v>Uploads, attachments, sketches, connectors</x:v>
+        <x:v>Agent chat send</x:v>
       </x:c>
       <x:c r="D4" s="3" t="str">
-        <x:v>As a customer, I can add CAD attachments, resume uploads, import handoff files, attach sketches, and connect/import from Google Drive.</x:v>
+        <x:v>As a customer, I can send manufacturing/quote questions to the agent.</x:v>
       </x:c>
       <x:c r="E4" s="3" t="str">
-        <x:v>The workspace validates upload candidates, registers agent attachments, imports web handoff tokens, supports sketch dialog attachment, and connector registry/status/handoff flows.</x:v>
+        <x:v>Composer sends messages with session context and receives agent turns through the BFF.</x:v>
       </x:c>
       <x:c r="F4" s="3" t="str">
         <x:v>Current code-derived</x:v>
@@ -1916,31 +5619,31 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L4" s="3" t="str">
-        <x:v>File picker/sketch/connectors -&gt; QuoteController upload/handoff/status -&gt; AgentController attachments/sketches/connectors -&gt; storage/session DTOs</x:v>
+        <x:v>Composer -&gt; AgentController messages -&gt; QuoteAgentService -&gt; session store</x:v>
       </x:c>
       <x:c r="M4" s="3" t="str">
-        <x:v>QuoteWorkspace.razor; QuoteAgentLaunchShell.razor; QuoteEngineApiClient.cs</x:v>
+        <x:v>QuoteAgentLaunchShell.razor</x:v>
       </x:c>
       <x:c r="N4" s="3" t="str">
-        <x:v>Hidden input quote-cad-files, + attachment menu, hand sketch dialog, Google Drive connector</x:v>
+        <x:v>Chat composer and message thread</x:v>
       </x:c>
       <x:c r="O4" s="3" t="str">
-        <x:v>QuoteController uploads/resumable/complete/handoff/analysis-status; AgentController connectors/handoff/attachments/sketches; GoogleDriveConnectorController</x:v>
+        <x:v>AgentController POST messages; QuoteAgentService SendMessageAsync</x:v>
       </x:c>
       <x:c r="P4" s="3" t="str">
-        <x:v>QuoteAgentEndpointTests attachment/sketch/connector cases; QuoteEngineApiClientTests</x:v>
+        <x:v>QuoteAgentEndpointTests messages</x:v>
       </x:c>
       <x:c r="Q4" s="3" t="str">
-        <x:v>QuoteEngine BFF, Storage, Google Drive connector, Agent session</x:v>
+        <x:v>QuoteEngine BFF, Agent model, SessionStore</x:v>
       </x:c>
       <x:c r="R4" s="3" t="str">
-        <x:v>Upload sessions, blobs, attachments, sketches, connector auth state</x:v>
+        <x:v>Chat messages/session state</x:v>
       </x:c>
       <x:c r="S4" s="3" t="str">
-        <x:v>Needs browser retest for file picker re-entry/freeze guard</x:v>
+        <x:v>Needs browser send-path retest</x:v>
       </x:c>
       <x:c r="T4" s="3" t="str">
-        <x:v>QuoteWorkspace.razor:21,583,716,739,809,1203; QuoteAgentLaunchShell.razor:286-337,1142,1320,1328,1333,1391-1477,5879,5940,5964; QuoteController.cs:68,134,194,235,259</x:v>
+        <x:v>AgentController.cs:56; QuoteAgentService.cs</x:v>
       </x:c>
       <x:c r="U4" s="3" t="str">
         <x:v>2026-06-23</x:v>
@@ -1948,19 +5651,19 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="3" t="str">
-        <x:v>QE-CODE-004</x:v>
+        <x:v>QE-004</x:v>
       </x:c>
       <x:c r="B5" s="3" t="str">
         <x:v>Maliev.QuoteEngine</x:v>
       </x:c>
       <x:c r="C5" s="3" t="str">
-        <x:v>Artifacts, generated 3D previews, inline viewer feedback</x:v>
+        <x:v>Agent streaming</x:v>
       </x:c>
       <x:c r="D5" s="3" t="str">
-        <x:v>As a customer, I can review generated quote artifacts, open 3D previews/workbench output, download artifacts, and submit inline viewer feedback.</x:v>
+        <x:v>As a customer, I can receive streamed agent responses.</x:v>
       </x:c>
       <x:c r="E5" s="3" t="str">
-        <x:v>The shell renders artifacts/workbench, handles generated preview paths, exposes artifact downloads/export PDF, and records artifact/preview feedback through the agent service.</x:v>
+        <x:v>Streaming endpoint returns structured response chunks and the UI keeps thread/composer layout stable.</x:v>
       </x:c>
       <x:c r="F5" s="3" t="str">
         <x:v>Current code-derived</x:v>
@@ -1981,31 +5684,31 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L5" s="3" t="str">
-        <x:v>Artifact UI -&gt; AgentController artifact-feedback/download/export -&gt; QuoteAgentService artifact path/feedback/generated preview</x:v>
+        <x:v>Composer -&gt; messages/stream -&gt; streaming agent response</x:v>
       </x:c>
       <x:c r="M5" s="3" t="str">
-        <x:v>QuoteAgentLaunchShell.razor; QePartViewer.razor; AgentController.cs; QuoteAgentService.cs</x:v>
+        <x:v>QuoteAgentLaunchShell.razor</x:v>
       </x:c>
       <x:c r="N5" s="3" t="str">
-        <x:v>Artifacts drawer, workflow artifacts, generated 3D preview, inline viewer feedback</x:v>
+        <x:v>Streaming response thread</x:v>
       </x:c>
       <x:c r="O5" s="3" t="str">
-        <x:v>AgentController artifact-feedback/artifact download/export-pdf; QuoteAgentService artifact path/feedback/generated preview</x:v>
+        <x:v>AgentController POST messages/stream</x:v>
       </x:c>
       <x:c r="P5" s="3" t="str">
-        <x:v>QuoteAgentEndpointTests export PDF/generated previews; QuoteEngineSourceTests generated preview/inline viewer feedback</x:v>
+        <x:v>QuoteAgentEndpointTests stream events; QuoteAgentLaunchShell source tests</x:v>
       </x:c>
       <x:c r="Q5" s="3" t="str">
-        <x:v>QuoteEngine BFF, Agent service, Storage/artifact service, Geometry/runtime</x:v>
+        <x:v>QuoteEngine BFF, Agent model</x:v>
       </x:c>
       <x:c r="R5" s="3" t="str">
-        <x:v>Artifacts, PDFs, feedback records</x:v>
+        <x:v>Streamed chat turns</x:v>
       </x:c>
       <x:c r="S5" s="3" t="str">
-        <x:v>Needs manual browser retest for actual artifact rendering</x:v>
+        <x:v>Needs interrupted-stream browser test</x:v>
       </x:c>
       <x:c r="T5" s="3" t="str">
-        <x:v>QuoteAgentLaunchShell.razor:669-708,748-853,1553,5120,5209; AgentController.cs:240,402,437; QuoteAgentService.cs:508,670,7052</x:v>
+        <x:v>AgentController.cs:76</x:v>
       </x:c>
       <x:c r="U5" s="3" t="str">
         <x:v>2026-06-23</x:v>
@@ -2013,19 +5716,19 @@
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="3" t="str">
-        <x:v>QE-CODE-005</x:v>
+        <x:v>QE-005</x:v>
       </x:c>
       <x:c r="B6" s="3" t="str">
         <x:v>Maliev.QuoteEngine</x:v>
       </x:c>
       <x:c r="C6" s="3" t="str">
-        <x:v>Part viewer, configuration sidebar, DFM tabs</x:v>
+        <x:v>Agent state and history</x:v>
       </x:c>
       <x:c r="D6" s="3" t="str">
-        <x:v>As a customer, I can inspect a part in the viewer, change manufacturing process/material/finish/tolerance/quantity, and review process-specific DFM guidance.</x:v>
+        <x:v>As a returning customer, I can reload session state and chat history.</x:v>
       </x:c>
       <x:c r="E6" s="3" t="str">
-        <x:v>Part cards show viewer and DFM tab content; the sidebar filters process/material/finish/color/reference options, updates quantities/options, acknowledges DFM issues, and pushes local DFM/browser viewer updates.</x:v>
+        <x:v>BFF exposes session state and message history by session id with authorization boundaries.</x:v>
       </x:c>
       <x:c r="F6" s="3" t="str">
         <x:v>Current code-derived</x:v>
@@ -2046,31 +5749,31 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L6" s="3" t="str">
-        <x:v>Part detail/config components -&gt; QuoteWorkspace part model -&gt; local/browser DFM/runtime DTOs -&gt; estimate request</x:v>
+        <x:v>Shell/session restore -&gt; AgentController sessions/messages -&gt; SessionStore</x:v>
       </x:c>
       <x:c r="M6" s="3" t="str">
-        <x:v>QePartDetailCard.razor; QePartConfigSidebar.razor; QePartViewer.razor; QeDfmTab.razor</x:v>
+        <x:v>QuoteAgentLaunchShell.razor</x:v>
       </x:c>
       <x:c r="N6" s="3" t="str">
-        <x:v>Part detail card tabs, viewer overlay, DFM issue acknowledgment, config sidebar controls</x:v>
+        <x:v>Session reload/history</x:v>
       </x:c>
       <x:c r="O6" s="3" t="str">
-        <x:v>QeDfmDtos; QuoteController reference-data/estimate; GeometryRuntimeController telemetry/runtime</x:v>
+        <x:v>AgentController GET sessions/{sessionId}, sessions/{sessionId}/messages</x:v>
       </x:c>
       <x:c r="P6" s="3" t="str">
-        <x:v>QuoteEngineSourceTests DFM/config/viewer/local DFM; Qe component tests</x:v>
+        <x:v>QuoteAgentEndpointTests history auth</x:v>
       </x:c>
       <x:c r="Q6" s="3" t="str">
-        <x:v>QuoteEngine UI, Geometry runtime, Pricing/reference data</x:v>
+        <x:v>QuoteEngine BFF, SessionStore, Auth</x:v>
       </x:c>
       <x:c r="R6" s="3" t="str">
-        <x:v>Part configuration and DFM acknowledgment state</x:v>
+        <x:v>Session state and message history</x:v>
       </x:c>
       <x:c r="S6" s="3" t="str">
-        <x:v>Needs visual/browser retest across FDM/SLA/CNC branches</x:v>
+        <x:v>Needs authenticated reload browser retest</x:v>
       </x:c>
       <x:c r="T6" s="3" t="str">
-        <x:v>QePartViewer.razor:156-177,249-273,362-363,431,437,450; QePartDetailCard.razor:62-66,102-103,153-161,216-240,273-310,337,349; QeDfmTab.razor:137-139,174-189,237-265; QePartConfigSidebar.razor:13,96,123,154,196,708-738,762-805,934-988</x:v>
+        <x:v>AgentController.cs:132,142; QuoteAgentSessionStore.cs</x:v>
       </x:c>
       <x:c r="U6" s="3" t="str">
         <x:v>2026-06-23</x:v>
@@ -2078,19 +5781,19 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="3" t="str">
-        <x:v>QE-CODE-006</x:v>
+        <x:v>QE-006</x:v>
       </x:c>
       <x:c r="B7" s="3" t="str">
         <x:v>Maliev.QuoteEngine</x:v>
       </x:c>
       <x:c r="C7" s="3" t="str">
-        <x:v>Estimate, formal quote, approval, order, payment</x:v>
+        <x:v>Agent clean speech and thinking</x:v>
       </x:c>
       <x:c r="D7" s="3" t="str">
-        <x:v>As a customer, I can request an estimate, generate/approve a formal quote, create an order, and initiate payment when gates allow.</x:v>
+        <x:v>As a customer, I get cleaned assistant speech and structured thinking/progress updates.</x:v>
       </x:c>
       <x:c r="E7" s="3" t="str">
-        <x:v>The summary bar surfaces lead time/total/actions; workspace methods call estimate, formal quote, approve quote, create order, and payment APIs; session gates disable actions until prerequisites are met.</x:v>
+        <x:v>BFF exposes clean-speech and thinking endpoints used by the assistant experience.</x:v>
       </x:c>
       <x:c r="F7" s="3" t="str">
         <x:v>Current code-derived</x:v>
@@ -2108,34 +5811,34 @@
         <x:v>Not started</x:v>
       </x:c>
       <x:c r="K7" s="3" t="str">
-        <x:v>P0</x:v>
+        <x:v>P2</x:v>
       </x:c>
       <x:c r="L7" s="3" t="str">
-        <x:v>Quote summary/workspace actions -&gt; QuoteController estimate/formal/approve/order/payment -&gt; Pricing/Quote/Order/Payment DTOs</x:v>
+        <x:v>Agent UI -&gt; clean-speech/thinking endpoints -&gt; QuoteAgentService</x:v>
       </x:c>
       <x:c r="M7" s="3" t="str">
-        <x:v>QeQuoteSummaryBar.razor; QuoteWorkspace.razor; QuoteController.cs</x:v>
+        <x:v>QuoteAgentLaunchShell.razor</x:v>
       </x:c>
       <x:c r="N7" s="3" t="str">
-        <x:v>Estimate, Generate formal quote, Approve quote, Create order, Pay buttons and terms</x:v>
+        <x:v>Thinking/progress and speech cleanup surfaces</x:v>
       </x:c>
       <x:c r="O7" s="3" t="str">
-        <x:v>QuoteController estimate/projects/draft/formal-quote/payments/approve-quote/orders</x:v>
+        <x:v>AgentController clean-speech, thinking</x:v>
       </x:c>
       <x:c r="P7" s="3" t="str">
-        <x:v>Pricing/Payment/Order/Invoice/Delivery contract tests; QuoteEngineSourceTests summary bar/payment</x:v>
+        <x:v>QuoteAgentEndpointTests; QuoteEngineSourceTests thinking</x:v>
       </x:c>
       <x:c r="Q7" s="3" t="str">
-        <x:v>QuoteEngine BFF, Pricing, Quotation, Order, Payment, Invoice/Delivery</x:v>
+        <x:v>QuoteEngine BFF, Agent service</x:v>
       </x:c>
       <x:c r="R7" s="3" t="str">
-        <x:v>Estimates, projects, formal quotes, orders, payment sessions</x:v>
+        <x:v>Cleaned text/thinking state</x:v>
       </x:c>
       <x:c r="S7" s="3" t="str">
-        <x:v>Needs money/order contract retest before any fixes; current pricing totals come from the active pricing/order/payment contracts</x:v>
+        <x:v>Needs UI copy review</x:v>
       </x:c>
       <x:c r="T7" s="3" t="str">
-        <x:v>QeQuoteSummaryBar.razor:15-29,38,49-64,69-75,88-93,125-171; QuoteWorkspace.razor:1003,1017,1036,1093,1111,1156; QuoteController.cs:301,502,696,906,1205,1227</x:v>
+        <x:v>AgentController.cs:111,423</x:v>
       </x:c>
       <x:c r="U7" s="3" t="str">
         <x:v>2026-06-23</x:v>
@@ -2143,19 +5846,19 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="3" t="str">
-        <x:v>QE-CODE-007</x:v>
+        <x:v>QE-007</x:v>
       </x:c>
       <x:c r="B8" s="3" t="str">
         <x:v>Maliev.QuoteEngine</x:v>
       </x:c>
       <x:c r="C8" s="3" t="str">
-        <x:v>Customer account, documents, NDAs, orders, shipping, auth</x:v>
+        <x:v>Project navigation rail</x:v>
       </x:c>
       <x:c r="D8" s="3" t="str">
-        <x:v>As a signed-in customer, I can manage profile/addresses, quotes/orders/order files, NDAs/documents, shipping rates/tracking, auth session, and payment callbacks.</x:v>
+        <x:v>As a customer, I can navigate, search, pin, archive, duplicate, and continue projects from the rail.</x:v>
       </x:c>
       <x:c r="E8" s="3" t="str">
-        <x:v>Account/document/order pages call profile/address/quotes/orders/NDA/document endpoints; shipping exposes couriers/rates/tracking; auth/session and payment success/cancel routes are present.</x:v>
+        <x:v>Project nav endpoints and shell management pages support project list, detail, duplicate, pin/unpin, archive, and current project selection.</x:v>
       </x:c>
       <x:c r="F8" s="3" t="str">
         <x:v>Current code-derived</x:v>
@@ -2173,34 +5876,34 @@
         <x:v>Not started</x:v>
       </x:c>
       <x:c r="K8" s="3" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="L8" s="3" t="str">
-        <x:v>Account/auth pages -&gt; AccountController/ShippingController/AuthController -&gt; customer/order/document/shipping DTOs</x:v>
+        <x:v>Rail/projects page -&gt; QuoteController projects/nav/detail/actions</x:v>
       </x:c>
       <x:c r="M8" s="3" t="str">
-        <x:v>Profile/Documents/Preferences/Orders/NDAs/payment pages</x:v>
+        <x:v>QuoteAgentLaunchShell.razor</x:v>
       </x:c>
       <x:c r="N8" s="3" t="str">
-        <x:v>/profile, /documents, /preferences, /orders, /orders/{OrderNumber}, /ndas, /payment/success, /payment/cancel</x:v>
+        <x:v>New project, Projects, search, pin/archive/duplicate actions</x:v>
       </x:c>
       <x:c r="O8" s="3" t="str">
-        <x:v>AccountController; ShippingController; AuthController</x:v>
+        <x:v>QuoteController projects/nav, project detail, duplicate, pin, delete pin, archive</x:v>
       </x:c>
       <x:c r="P8" s="3" t="str">
-        <x:v>AccountAuthBoundaryTests; GoogleAuthFlowTests; Shipping/Payment tests</x:v>
+        <x:v>QuoteEngineSourceTests rail/project management</x:v>
       </x:c>
       <x:c r="Q8" s="3" t="str">
-        <x:v>QuoteEngine BFF, Customer, Order, Document storage, Shipping, Auth, Payment</x:v>
+        <x:v>QuoteEngine BFF, Project service, SessionStore</x:v>
       </x:c>
       <x:c r="R8" s="3" t="str">
-        <x:v>Profile, addresses, documents, orders, NDAs, shipping requests</x:v>
+        <x:v>Project metadata, pin/archive flags</x:v>
       </x:c>
       <x:c r="S8" s="3" t="str">
-        <x:v>Needs authenticated browser retest</x:v>
+        <x:v>Needs product decision on achieve endpoint naming</x:v>
       </x:c>
       <x:c r="T8" s="3" t="str">
-        <x:v>AccountController.cs:46,76,112,120,128,143,175,202,229,269,354; ShippingController.cs; AuthController.cs</x:v>
+        <x:v>QuoteAgentLaunchShell.razor; QuoteController.cs:548-674</x:v>
       </x:c>
       <x:c r="U8" s="3" t="str">
         <x:v>2026-06-23</x:v>
@@ -2208,19 +5911,19 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="3" t="str">
-        <x:v>QE-CODE-008</x:v>
+        <x:v>QE-008</x:v>
       </x:c>
       <x:c r="B9" s="3" t="str">
         <x:v>Maliev.QuoteEngine</x:v>
       </x:c>
       <x:c r="C9" s="3" t="str">
-        <x:v>Realtime analysis and DFM notifications</x:v>
+        <x:v>Project search</x:v>
       </x:c>
       <x:c r="D9" s="3" t="str">
-        <x:v>As a customer, I receive live updates when file analysis, GLB generation, or DFM analysis completes.</x:v>
+        <x:v>As a customer, I can search projects and agent context.</x:v>
       </x:c>
       <x:c r="E9" s="3" t="str">
-        <x:v>QuoteWorkspace connects SignalR and handles FileAnalysisCompleted, GlbReady, and DfmAnalysisReady events to update analysis status, previews, and DFM state.</x:v>
+        <x:v>Search endpoint returns session-scoped/project-scoped results for the shell search view.</x:v>
       </x:c>
       <x:c r="F9" s="3" t="str">
         <x:v>Current code-derived</x:v>
@@ -2241,31 +5944,31 @@
         <x:v>P1</x:v>
       </x:c>
       <x:c r="L9" s="3" t="str">
-        <x:v>SignalR hub/events -&gt; QuoteWorkspace event handlers -&gt; upload/part state</x:v>
+        <x:v>Search UI -&gt; AgentController sessions/{sessionId}/search -&gt; QuoteAgentService</x:v>
       </x:c>
       <x:c r="M9" s="3" t="str">
-        <x:v>QuoteWorkspace.razor</x:v>
+        <x:v>QuoteAgentLaunchShell.razor</x:v>
       </x:c>
       <x:c r="N9" s="3" t="str">
-        <x:v>Reconnecting/workspace status and part readiness updates</x:v>
+        <x:v>Search page/field</x:v>
       </x:c>
       <x:c r="O9" s="3" t="str">
-        <x:v>QuoteController analysis-status; geometry/runtime events</x:v>
+        <x:v>AgentController GET sessions/{sessionId}/search</x:v>
       </x:c>
       <x:c r="P9" s="3" t="str">
-        <x:v>QuoteEngineSourceTests realtime/source checks where present</x:v>
+        <x:v>QuoteAgentEndpointTests search</x:v>
       </x:c>
       <x:c r="Q9" s="3" t="str">
-        <x:v>QuoteEngine BFF, SignalR, GeometryService, Storage</x:v>
+        <x:v>QuoteEngine BFF, Agent/Project service</x:v>
       </x:c>
       <x:c r="R9" s="3" t="str">
-        <x:v>Analysis status and part preview readiness</x:v>
+        <x:v>Search query/results</x:v>
       </x:c>
       <x:c r="S9" s="3" t="str">
-        <x:v>Needs live Aspire/DCP retest</x:v>
+        <x:v>Needs search ranking behavior validation</x:v>
       </x:c>
       <x:c r="T9" s="3" t="str">
-        <x:v>QuoteWorkspace.razor:1492,1496,1513,1532; QuoteEngineApiClient.cs:49-93</x:v>
+        <x:v>AgentController.cs:271; QuoteAgentLaunchShell.razor</x:v>
       </x:c>
       <x:c r="U9" s="3" t="str">
         <x:v>2026-06-23</x:v>
@@ -2273,19 +5976,19 @@
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="3" t="str">
-        <x:v>QE-CODE-009</x:v>
+        <x:v>QE-009</x:v>
       </x:c>
       <x:c r="B10" s="3" t="str">
         <x:v>Maliev.QuoteEngine</x:v>
       </x:c>
       <x:c r="C10" s="3" t="str">
-        <x:v>Agent memory and grounded tool behavior</x:v>
+        <x:v>Resumable CAD upload</x:v>
       </x:c>
       <x:c r="D10" s="3" t="str">
-        <x:v>As a returning customer, I can benefit from grounded assistant context and durable customer memory when authenticated.</x:v>
+        <x:v>As a customer, I can upload CAD files for part analysis.</x:v>
       </x:c>
       <x:c r="E10" s="3" t="str">
-        <x:v>QuoteAgentService builds system grounding, includes memory context, applies local DFM/tool outputs, and keeps generated suggestions tied to current session/project state.</x:v>
+        <x:v>Workspace creates resumable upload sessions, sends chunks, completes uploads, and checks analysis status.</x:v>
       </x:c>
       <x:c r="F10" s="3" t="str">
         <x:v>Current code-derived</x:v>
@@ -2303,43 +6006,1928 @@
         <x:v>Not started</x:v>
       </x:c>
       <x:c r="K10" s="3" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="L10" s="3" t="str">
+        <x:v>File picker -&gt; QuoteController uploads -&gt; storage/analysis</x:v>
+      </x:c>
+      <x:c r="M10" s="3" t="str">
+        <x:v>QuoteWorkspace.razor; QuoteAgentLaunchShell.razor</x:v>
+      </x:c>
+      <x:c r="N10" s="3" t="str">
+        <x:v>CAD file input, attachment picker, upload controls</x:v>
+      </x:c>
+      <x:c r="O10" s="3" t="str">
+        <x:v>QuoteController uploads/resumable, PUT chunk, complete, analysis-status</x:v>
+      </x:c>
+      <x:c r="P10" s="3" t="str">
+        <x:v>QuoteEngineSourceTests upload; QuoteEngineApiClientTests</x:v>
+      </x:c>
+      <x:c r="Q10" s="3" t="str">
+        <x:v>QuoteEngine BFF, Storage, Geometry/analysis</x:v>
+      </x:c>
+      <x:c r="R10" s="3" t="str">
+        <x:v>Upload sessions/files/analysis status</x:v>
+      </x:c>
+      <x:c r="S10" s="3" t="str">
+        <x:v>Needs browser file-picker retest</x:v>
+      </x:c>
+      <x:c r="T10" s="3" t="str">
+        <x:v>QuoteWorkspace.razor; QuoteController.cs:68-259</x:v>
+      </x:c>
+      <x:c r="U10" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="3" t="str">
+        <x:v>QE-010</x:v>
+      </x:c>
+      <x:c r="B11" s="3" t="str">
+        <x:v>Maliev.QuoteEngine</x:v>
+      </x:c>
+      <x:c r="C11" s="3" t="str">
+        <x:v>Web handoff import</x:v>
+      </x:c>
+      <x:c r="D11" s="3" t="str">
+        <x:v>As a customer, I can continue from a public web quote upload into the workspace.</x:v>
+      </x:c>
+      <x:c r="E11" s="3" t="str">
+        <x:v>Workspace imports handoff uploads through signed handoff endpoint and registers those files with the active session.</x:v>
+      </x:c>
+      <x:c r="F11" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G11" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H11" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I11" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J11" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K11" s="3" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="L11" s="3" t="str">
+        <x:v>Web handoff token -&gt; QuoteController uploads/handoff -&gt; workspace/session attachments</x:v>
+      </x:c>
+      <x:c r="M11" s="3" t="str">
+        <x:v>QuoteWorkspace.razor</x:v>
+      </x:c>
+      <x:c r="N11" s="3" t="str">
+        <x:v>Make Studio handoff flow</x:v>
+      </x:c>
+      <x:c r="O11" s="3" t="str">
+        <x:v>QuoteController POST uploads/handoff</x:v>
+      </x:c>
+      <x:c r="P11" s="3" t="str">
+        <x:v>QuoteEngineApiClientTests handoff</x:v>
+      </x:c>
+      <x:c r="Q11" s="3" t="str">
+        <x:v>QuoteEngine BFF, Web BFF, Storage</x:v>
+      </x:c>
+      <x:c r="R11" s="3" t="str">
+        <x:v>Handoff upload references</x:v>
+      </x:c>
+      <x:c r="S11" s="3" t="str">
+        <x:v>Needs cross-app browser retest</x:v>
+      </x:c>
+      <x:c r="T11" s="3" t="str">
+        <x:v>QuoteWorkspace.razor; QuoteController.cs:235</x:v>
+      </x:c>
+      <x:c r="U11" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="3" t="str">
+        <x:v>QE-011</x:v>
+      </x:c>
+      <x:c r="B12" s="3" t="str">
+        <x:v>Maliev.QuoteEngine</x:v>
+      </x:c>
+      <x:c r="C12" s="3" t="str">
+        <x:v>Agent attachments</x:v>
+      </x:c>
+      <x:c r="D12" s="3" t="str">
+        <x:v>As a customer, I can attach uploaded files as context before asking the agent.</x:v>
+      </x:c>
+      <x:c r="E12" s="3" t="str">
+        <x:v>Agent attachment endpoint registers uploaded files in session state and the shell previews attachments until sent.</x:v>
+      </x:c>
+      <x:c r="F12" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G12" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H12" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I12" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J12" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K12" s="3" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="L12" s="3" t="str">
+        <x:v>Composer attachments -&gt; AgentController attachments -&gt; SessionStore</x:v>
+      </x:c>
+      <x:c r="M12" s="3" t="str">
+        <x:v>QuoteAgentLaunchShell.razor</x:v>
+      </x:c>
+      <x:c r="N12" s="3" t="str">
+        <x:v>Attachment preview and sent attachment display</x:v>
+      </x:c>
+      <x:c r="O12" s="3" t="str">
+        <x:v>AgentController POST sessions/{sessionId}/attachments</x:v>
+      </x:c>
+      <x:c r="P12" s="3" t="str">
+        <x:v>QuoteAgentEndpointTests attachment; QuoteAgentLaunchShell source tests</x:v>
+      </x:c>
+      <x:c r="Q12" s="3" t="str">
+        <x:v>QuoteEngine BFF, SessionStore, Storage</x:v>
+      </x:c>
+      <x:c r="R12" s="3" t="str">
+        <x:v>Session attachment records</x:v>
+      </x:c>
+      <x:c r="S12" s="3" t="str">
+        <x:v>Needs attachment resend/removal browser pass</x:v>
+      </x:c>
+      <x:c r="T12" s="3" t="str">
+        <x:v>AgentController.cs:203; QuoteAgentLaunchShell.razor</x:v>
+      </x:c>
+      <x:c r="U12" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="3" t="str">
+        <x:v>QE-012</x:v>
+      </x:c>
+      <x:c r="B13" s="3" t="str">
+        <x:v>Maliev.QuoteEngine</x:v>
+      </x:c>
+      <x:c r="C13" s="3" t="str">
+        <x:v>Sketch attachments</x:v>
+      </x:c>
+      <x:c r="D13" s="3" t="str">
+        <x:v>As a customer, I can draw or attach a hand sketch for the agent.</x:v>
+      </x:c>
+      <x:c r="E13" s="3" t="str">
+        <x:v>Sketch dialog captures sketch data and posts it to the agent sketch endpoint.</x:v>
+      </x:c>
+      <x:c r="F13" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G13" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H13" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I13" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J13" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K13" s="3" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="L10" s="3" t="str">
-        <x:v>Agent service prompt/memory/tool pipeline -&gt; Customer memory/session/project DTOs</x:v>
-      </x:c>
-      <x:c r="M10" s="3" t="str">
+      <x:c r="L13" s="3" t="str">
+        <x:v>Sketch UI -&gt; AgentController sketches -&gt; SessionStore/artifacts</x:v>
+      </x:c>
+      <x:c r="M13" s="3" t="str">
+        <x:v>QuoteAgentLaunchShell.razor</x:v>
+      </x:c>
+      <x:c r="N13" s="3" t="str">
+        <x:v>Hand sketch dialog/tools</x:v>
+      </x:c>
+      <x:c r="O13" s="3" t="str">
+        <x:v>AgentController POST sessions/{sessionId}/sketches</x:v>
+      </x:c>
+      <x:c r="P13" s="3" t="str">
+        <x:v>QuoteAgentEndpointTests sketches; source tests sketch disposal</x:v>
+      </x:c>
+      <x:c r="Q13" s="3" t="str">
+        <x:v>QuoteEngine BFF, SessionStore, Storage</x:v>
+      </x:c>
+      <x:c r="R13" s="3" t="str">
+        <x:v>Sketch artifact/context</x:v>
+      </x:c>
+      <x:c r="S13" s="3" t="str">
+        <x:v>Needs mobile sketch browser pass</x:v>
+      </x:c>
+      <x:c r="T13" s="3" t="str">
+        <x:v>AgentController.cs:367; QuoteAgentLaunchShell.razor</x:v>
+      </x:c>
+      <x:c r="U13" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="3" t="str">
+        <x:v>QE-013</x:v>
+      </x:c>
+      <x:c r="B14" s="3" t="str">
+        <x:v>Maliev.QuoteEngine</x:v>
+      </x:c>
+      <x:c r="C14" s="3" t="str">
+        <x:v>Google Drive connector</x:v>
+      </x:c>
+      <x:c r="D14" s="3" t="str">
+        <x:v>As a customer, I can connect Google Drive and select source files.</x:v>
+      </x:c>
+      <x:c r="E14" s="3" t="str">
+        <x:v>Connector endpoints start OAuth, handle callback, expose status, list files, and return connector handoff links.</x:v>
+      </x:c>
+      <x:c r="F14" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G14" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H14" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I14" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J14" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K14" s="3" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="L14" s="3" t="str">
+        <x:v>Connector UI -&gt; GoogleDriveConnectorController and AgentController connector endpoints</x:v>
+      </x:c>
+      <x:c r="M14" s="3" t="str">
+        <x:v>QuoteAgentLaunchShell.razor; GoogleCallback.razor</x:v>
+      </x:c>
+      <x:c r="N14" s="3" t="str">
+        <x:v>/auth/callback/google; connector panel</x:v>
+      </x:c>
+      <x:c r="O14" s="3" t="str">
+        <x:v>GoogleDriveConnectorController start/callback/status/files; AgentController connectors/handoff</x:v>
+      </x:c>
+      <x:c r="P14" s="3" t="str">
+        <x:v>QuoteEngineSourceTests connector; endpoint tests where present</x:v>
+      </x:c>
+      <x:c r="Q14" s="3" t="str">
+        <x:v>QuoteEngine BFF, Google Drive, Auth</x:v>
+      </x:c>
+      <x:c r="R14" s="3" t="str">
+        <x:v>Connector tokens/status/file refs</x:v>
+      </x:c>
+      <x:c r="S14" s="3" t="str">
+        <x:v>Needs OAuth environment smoke</x:v>
+      </x:c>
+      <x:c r="T14" s="3" t="str">
+        <x:v>GoogleDriveConnectorController.cs; AgentController.cs:180,190</x:v>
+      </x:c>
+      <x:c r="U14" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="3" t="str">
+        <x:v>QE-014</x:v>
+      </x:c>
+      <x:c r="B15" s="3" t="str">
+        <x:v>Maliev.QuoteEngine</x:v>
+      </x:c>
+      <x:c r="C15" s="3" t="str">
+        <x:v>Workflow artifacts</x:v>
+      </x:c>
+      <x:c r="D15" s="3" t="str">
+        <x:v>As a customer, I can inspect quote workflow artifacts produced by the agent.</x:v>
+      </x:c>
+      <x:c r="E15" s="3" t="str">
+        <x:v>Artifact drawer and workflow artifact surfaces display generated artifacts, selected artifacts, and downloads.</x:v>
+      </x:c>
+      <x:c r="F15" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G15" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H15" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I15" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J15" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K15" s="3" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="L15" s="3" t="str">
+        <x:v>Shell artifacts -&gt; AgentController artifact download -&gt; artifact/storage service</x:v>
+      </x:c>
+      <x:c r="M15" s="3" t="str">
+        <x:v>QuoteAgentLaunchShell.razor</x:v>
+      </x:c>
+      <x:c r="N15" s="3" t="str">
+        <x:v>Artifact drawer/workflow artifacts</x:v>
+      </x:c>
+      <x:c r="O15" s="3" t="str">
+        <x:v>AgentController artifacts/download</x:v>
+      </x:c>
+      <x:c r="P15" s="3" t="str">
+        <x:v>QuoteAgentEndpointTests artifact download; QuoteEngineSourceTests artifacts</x:v>
+      </x:c>
+      <x:c r="Q15" s="3" t="str">
+        <x:v>QuoteEngine BFF, Storage/artifact service</x:v>
+      </x:c>
+      <x:c r="R15" s="3" t="str">
+        <x:v>Artifact records/files</x:v>
+      </x:c>
+      <x:c r="S15" s="3" t="str">
+        <x:v>Needs real artifact visual browser pass</x:v>
+      </x:c>
+      <x:c r="T15" s="3" t="str">
+        <x:v>QuoteAgentLaunchShell.razor; AgentController.cs:402</x:v>
+      </x:c>
+      <x:c r="U15" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="3" t="str">
+        <x:v>QE-015</x:v>
+      </x:c>
+      <x:c r="B16" s="3" t="str">
+        <x:v>Maliev.QuoteEngine</x:v>
+      </x:c>
+      <x:c r="C16" s="3" t="str">
+        <x:v>Artifact feedback</x:v>
+      </x:c>
+      <x:c r="D16" s="3" t="str">
+        <x:v>As a customer, I can give feedback on generated previews/artifacts.</x:v>
+      </x:c>
+      <x:c r="E16" s="3" t="str">
+        <x:v>Inline viewer feedback posts sentiment/text feedback and reflects memory observation status.</x:v>
+      </x:c>
+      <x:c r="F16" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G16" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H16" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I16" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J16" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K16" s="3" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="L16" s="3" t="str">
+        <x:v>Inline feedback UI -&gt; AgentController artifact-feedback -&gt; QuoteAgentService</x:v>
+      </x:c>
+      <x:c r="M16" s="3" t="str">
+        <x:v>QuoteAgentLaunchShell.razor</x:v>
+      </x:c>
+      <x:c r="N16" s="3" t="str">
+        <x:v>Thumb feedback and optional text</x:v>
+      </x:c>
+      <x:c r="O16" s="3" t="str">
+        <x:v>AgentController POST artifacts/{artifactId}/feedback</x:v>
+      </x:c>
+      <x:c r="P16" s="3" t="str">
+        <x:v>QuoteEngineSourceTests feedback; QuoteAgentEndpointTests feedback</x:v>
+      </x:c>
+      <x:c r="Q16" s="3" t="str">
+        <x:v>QuoteEngine BFF, Agent service, Customer memory</x:v>
+      </x:c>
+      <x:c r="R16" s="3" t="str">
+        <x:v>Feedback records/memory observations</x:v>
+      </x:c>
+      <x:c r="S16" s="3" t="str">
+        <x:v>Needs feedback persistence retest</x:v>
+      </x:c>
+      <x:c r="T16" s="3" t="str">
+        <x:v>AgentController.cs:240; QuoteAgentService.cs</x:v>
+      </x:c>
+      <x:c r="U16" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="3" t="str">
+        <x:v>QE-016</x:v>
+      </x:c>
+      <x:c r="B17" s="3" t="str">
+        <x:v>Maliev.QuoteEngine</x:v>
+      </x:c>
+      <x:c r="C17" s="3" t="str">
+        <x:v>3D part viewer</x:v>
+      </x:c>
+      <x:c r="D17" s="3" t="str">
+        <x:v>As a customer, I can inspect uploaded/generated parts in a 3D viewer.</x:v>
+      </x:c>
+      <x:c r="E17" s="3" t="str">
+        <x:v>Part viewer loads GLB/viewer URLs, applies viewer settings, and pushes process/material/runtime state to JS.</x:v>
+      </x:c>
+      <x:c r="F17" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G17" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H17" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I17" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J17" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K17" s="3" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="L17" s="3" t="str">
+        <x:v>QePartViewer -&gt; geometry runtime assets/telemetry -&gt; browser viewer</x:v>
+      </x:c>
+      <x:c r="M17" s="3" t="str">
+        <x:v>QePartViewer.razor; QePartDetailCard.razor</x:v>
+      </x:c>
+      <x:c r="N17" s="3" t="str">
+        <x:v>3D Model tab, artifact drawer viewer</x:v>
+      </x:c>
+      <x:c r="O17" s="3" t="str">
+        <x:v>GeometryRuntimeController manifest/assets/telemetry</x:v>
+      </x:c>
+      <x:c r="P17" s="3" t="str">
+        <x:v>QuoteEngineSourceTests viewer/runtime</x:v>
+      </x:c>
+      <x:c r="Q17" s="3" t="str">
+        <x:v>QuoteEngine client/BFF, Geometry runtime</x:v>
+      </x:c>
+      <x:c r="R17" s="3" t="str">
+        <x:v>Viewer settings/telemetry</x:v>
+      </x:c>
+      <x:c r="S17" s="3" t="str">
+        <x:v>Needs visual canvas smoke</x:v>
+      </x:c>
+      <x:c r="T17" s="3" t="str">
+        <x:v>QePartViewer.razor; QePartDetailCard.razor; GeometryRuntimeController.cs</x:v>
+      </x:c>
+      <x:c r="U17" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="3" t="str">
+        <x:v>QE-017</x:v>
+      </x:c>
+      <x:c r="B18" s="3" t="str">
+        <x:v>Maliev.QuoteEngine</x:v>
+      </x:c>
+      <x:c r="C18" s="3" t="str">
+        <x:v>DFM reporting</x:v>
+      </x:c>
+      <x:c r="D18" s="3" t="str">
+        <x:v>As a customer, I can review manufacturability checks for FDM, SLA, and CNC.</x:v>
+      </x:c>
+      <x:c r="E18" s="3" t="str">
+        <x:v>DFM tab renders process-specific report types and the agent can apply DFM reports to session state.</x:v>
+      </x:c>
+      <x:c r="F18" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G18" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H18" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I18" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J18" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K18" s="3" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="L18" s="3" t="str">
+        <x:v>QeDfmTab/QePartDetailCard -&gt; AgentController dfm -&gt; SessionStore</x:v>
+      </x:c>
+      <x:c r="M18" s="3" t="str">
+        <x:v>QeDfmTab.razor; QePartDetailCard.razor</x:v>
+      </x:c>
+      <x:c r="N18" s="3" t="str">
+        <x:v>DFM tab and issue acknowledgement</x:v>
+      </x:c>
+      <x:c r="O18" s="3" t="str">
+        <x:v>AgentController POST sessions/{sessionId}/dfm; QeDfmDtos</x:v>
+      </x:c>
+      <x:c r="P18" s="3" t="str">
+        <x:v>QuoteEngineSourceTests DFM</x:v>
+      </x:c>
+      <x:c r="Q18" s="3" t="str">
+        <x:v>QuoteEngine BFF, Geometry/DFM, SessionStore</x:v>
+      </x:c>
+      <x:c r="R18" s="3" t="str">
+        <x:v>DFM reports and acknowledgement state</x:v>
+      </x:c>
+      <x:c r="S18" s="3" t="str">
+        <x:v>Needs process-specific fixture coverage</x:v>
+      </x:c>
+      <x:c r="T18" s="3" t="str">
+        <x:v>QeDfmTab.razor; QePartDetailCard.razor; AgentController.cs:221</x:v>
+      </x:c>
+      <x:c r="U18" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="3" t="str">
+        <x:v>QE-018</x:v>
+      </x:c>
+      <x:c r="B19" s="3" t="str">
+        <x:v>Maliev.QuoteEngine</x:v>
+      </x:c>
+      <x:c r="C19" s="3" t="str">
+        <x:v>Part configuration sidebar</x:v>
+      </x:c>
+      <x:c r="D19" s="3" t="str">
+        <x:v>As a customer, I can select process, material, color, finish, tolerance, quantity, and options.</x:v>
+      </x:c>
+      <x:c r="E19" s="3" t="str">
+        <x:v>Configuration sidebar filters reference data and emits changes for quote estimation.</x:v>
+      </x:c>
+      <x:c r="F19" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G19" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H19" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I19" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J19" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K19" s="3" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="L19" s="3" t="str">
+        <x:v>QePartConfigSidebar -&gt; reference-data/estimate DTOs</x:v>
+      </x:c>
+      <x:c r="M19" s="3" t="str">
+        <x:v>QePartConfigSidebar.razor</x:v>
+      </x:c>
+      <x:c r="N19" s="3" t="str">
+        <x:v>Part configuration controls</x:v>
+      </x:c>
+      <x:c r="O19" s="3" t="str">
+        <x:v>QuoteController reference-data/estimate</x:v>
+      </x:c>
+      <x:c r="P19" s="3" t="str">
+        <x:v>QuoteEngineSourceTests config sidebar</x:v>
+      </x:c>
+      <x:c r="Q19" s="3" t="str">
+        <x:v>QuoteEngine client/BFF, Pricing/Material services</x:v>
+      </x:c>
+      <x:c r="R19" s="3" t="str">
+        <x:v>Part configuration state</x:v>
+      </x:c>
+      <x:c r="S19" s="3" t="str">
+        <x:v>Needs keyboard/accessibility check</x:v>
+      </x:c>
+      <x:c r="T19" s="3" t="str">
+        <x:v>QePartConfigSidebar.razor; QuoteController.cs:47,301</x:v>
+      </x:c>
+      <x:c r="U19" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="3" t="str">
+        <x:v>QE-019</x:v>
+      </x:c>
+      <x:c r="B20" s="3" t="str">
+        <x:v>Maliev.QuoteEngine</x:v>
+      </x:c>
+      <x:c r="C20" s="3" t="str">
+        <x:v>Reference data and currencies</x:v>
+      </x:c>
+      <x:c r="D20" s="3" t="str">
+        <x:v>As a customer, I can use current manufacturing reference data and currencies.</x:v>
+      </x:c>
+      <x:c r="E20" s="3" t="str">
+        <x:v>Reference endpoints expose processes/materials/finishes/tolerances/currency data used by workspace controls.</x:v>
+      </x:c>
+      <x:c r="F20" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G20" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H20" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I20" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J20" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K20" s="3" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="L20" s="3" t="str">
+        <x:v>Workspace/client -&gt; quote/v1/reference-data and quote/v1/reference-data/currencies</x:v>
+      </x:c>
+      <x:c r="M20" s="3" t="str">
+        <x:v>QuoteEngineApiClient.cs</x:v>
+      </x:c>
+      <x:c r="N20" s="3" t="str">
+        <x:v>Reference-driven controls</x:v>
+      </x:c>
+      <x:c r="O20" s="3" t="str">
+        <x:v>QuoteController reference-data; ReferenceDataController currencies</x:v>
+      </x:c>
+      <x:c r="P20" s="3" t="str">
+        <x:v>QuoteEngineApiClientTests</x:v>
+      </x:c>
+      <x:c r="Q20" s="3" t="str">
+        <x:v>QuoteEngine BFF, Material/Pricing/Reference data</x:v>
+      </x:c>
+      <x:c r="R20" s="3" t="str">
+        <x:v>Read-only reference data</x:v>
+      </x:c>
+      <x:c r="S20" s="3" t="str">
+        <x:v>Needs stale-cache behavior check</x:v>
+      </x:c>
+      <x:c r="T20" s="3" t="str">
+        <x:v>QuoteController.cs:47; ReferenceDataController.cs:10-16; QuoteEngineApiClient.cs</x:v>
+      </x:c>
+      <x:c r="U20" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="3" t="str">
+        <x:v>QE-020</x:v>
+      </x:c>
+      <x:c r="B21" s="3" t="str">
+        <x:v>Maliev.QuoteEngine</x:v>
+      </x:c>
+      <x:c r="C21" s="3" t="str">
+        <x:v>Estimate</x:v>
+      </x:c>
+      <x:c r="D21" s="3" t="str">
+        <x:v>As a customer, I can request a quote estimate for configured parts.</x:v>
+      </x:c>
+      <x:c r="E21" s="3" t="str">
+        <x:v>Estimate endpoint prices configured parts and returns lead-time/total data for the summary/actions.</x:v>
+      </x:c>
+      <x:c r="F21" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G21" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H21" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I21" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J21" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K21" s="3" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="L21" s="3" t="str">
+        <x:v>Workspace/summary -&gt; QuoteController estimate -&gt; Pricing service</x:v>
+      </x:c>
+      <x:c r="M21" s="3" t="str">
+        <x:v>QuoteWorkspace.razor; QeQuoteSummaryBar.razor</x:v>
+      </x:c>
+      <x:c r="N21" s="3" t="str">
+        <x:v>Estimate action</x:v>
+      </x:c>
+      <x:c r="O21" s="3" t="str">
+        <x:v>QuoteController POST estimate</x:v>
+      </x:c>
+      <x:c r="P21" s="3" t="str">
+        <x:v>Pricing/QuoteEngine tests</x:v>
+      </x:c>
+      <x:c r="Q21" s="3" t="str">
+        <x:v>QuoteEngine BFF, PricingService</x:v>
+      </x:c>
+      <x:c r="R21" s="3" t="str">
+        <x:v>Estimate request/response</x:v>
+      </x:c>
+      <x:c r="S21" s="3" t="str">
+        <x:v>Needs current pricing acceptance checks</x:v>
+      </x:c>
+      <x:c r="T21" s="3" t="str">
+        <x:v>QuoteController.cs:301; QeQuoteSummaryBar.razor</x:v>
+      </x:c>
+      <x:c r="U21" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="3" t="str">
+        <x:v>QE-021</x:v>
+      </x:c>
+      <x:c r="B22" s="3" t="str">
+        <x:v>Maliev.QuoteEngine</x:v>
+      </x:c>
+      <x:c r="C22" s="3" t="str">
+        <x:v>Draft project</x:v>
+      </x:c>
+      <x:c r="D22" s="3" t="str">
+        <x:v>As a customer, I can persist configured parts into a project draft.</x:v>
+      </x:c>
+      <x:c r="E22" s="3" t="str">
+        <x:v>Projects/draft endpoint creates or updates draft project data for the session/customer.</x:v>
+      </x:c>
+      <x:c r="F22" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G22" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H22" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I22" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J22" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K22" s="3" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="L22" s="3" t="str">
+        <x:v>Workspace -&gt; QuoteController projects/draft -&gt; project/quote service</x:v>
+      </x:c>
+      <x:c r="M22" s="3" t="str">
+        <x:v>QuoteWorkspace.razor</x:v>
+      </x:c>
+      <x:c r="N22" s="3" t="str">
+        <x:v>Project draft action</x:v>
+      </x:c>
+      <x:c r="O22" s="3" t="str">
+        <x:v>QuoteController POST projects/draft</x:v>
+      </x:c>
+      <x:c r="P22" s="3" t="str">
+        <x:v>QuoteEngineSourceTests project draft</x:v>
+      </x:c>
+      <x:c r="Q22" s="3" t="str">
+        <x:v>QuoteEngine BFF, Project/Quote service</x:v>
+      </x:c>
+      <x:c r="R22" s="3" t="str">
+        <x:v>Project draft</x:v>
+      </x:c>
+      <x:c r="S22" s="3" t="str">
+        <x:v>Needs auth/anonymous boundary check</x:v>
+      </x:c>
+      <x:c r="T22" s="3" t="str">
+        <x:v>QuoteController.cs:502</x:v>
+      </x:c>
+      <x:c r="U22" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="3" t="str">
+        <x:v>QE-022</x:v>
+      </x:c>
+      <x:c r="B23" s="3" t="str">
+        <x:v>Maliev.QuoteEngine</x:v>
+      </x:c>
+      <x:c r="C23" s="3" t="str">
+        <x:v>Formal quote</x:v>
+      </x:c>
+      <x:c r="D23" s="3" t="str">
+        <x:v>As a customer, I can generate a formal quote when prerequisites are met.</x:v>
+      </x:c>
+      <x:c r="E23" s="3" t="str">
+        <x:v>Formal quote endpoint generates quote artifacts and session gates expose readiness.</x:v>
+      </x:c>
+      <x:c r="F23" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G23" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H23" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I23" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J23" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K23" s="3" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="L23" s="3" t="str">
+        <x:v>Summary/action gate -&gt; QuoteController quotes/formal -&gt; Quotation service</x:v>
+      </x:c>
+      <x:c r="M23" s="3" t="str">
+        <x:v>QeQuoteSummaryBar.razor; QuoteWorkspace.razor</x:v>
+      </x:c>
+      <x:c r="N23" s="3" t="str">
+        <x:v>Generate formal quote action</x:v>
+      </x:c>
+      <x:c r="O23" s="3" t="str">
+        <x:v>QuoteController POST quotes/formal</x:v>
+      </x:c>
+      <x:c r="P23" s="3" t="str">
+        <x:v>QuoteEngineSourceTests summary/formal quote</x:v>
+      </x:c>
+      <x:c r="Q23" s="3" t="str">
+        <x:v>QuoteEngine BFF, Quotation/Pdf/Storage</x:v>
+      </x:c>
+      <x:c r="R23" s="3" t="str">
+        <x:v>Formal quote and artifact records</x:v>
+      </x:c>
+      <x:c r="S23" s="3" t="str">
+        <x:v>Needs PDF artifact visual validation</x:v>
+      </x:c>
+      <x:c r="T23" s="3" t="str">
+        <x:v>QuoteController.cs:696; QeQuoteSummaryBar.razor</x:v>
+      </x:c>
+      <x:c r="U23" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="3" t="str">
+        <x:v>QE-023</x:v>
+      </x:c>
+      <x:c r="B24" s="3" t="str">
+        <x:v>Maliev.QuoteEngine</x:v>
+      </x:c>
+      <x:c r="C24" s="3" t="str">
+        <x:v>Quote approval</x:v>
+      </x:c>
+      <x:c r="D24" s="3" t="str">
+        <x:v>As a customer, I can approve a formal quote.</x:v>
+      </x:c>
+      <x:c r="E24" s="3" t="str">
+        <x:v>Quote approval endpoint changes quote state and gates the downstream order workflow.</x:v>
+      </x:c>
+      <x:c r="F24" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G24" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H24" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I24" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J24" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K24" s="3" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="L24" s="3" t="str">
+        <x:v>Approve action -&gt; QuoteController quotes/{quoteId}/approve -&gt; Quotation service</x:v>
+      </x:c>
+      <x:c r="M24" s="3" t="str">
+        <x:v>QuoteWorkspace.razor; QeQuoteSummaryBar.razor</x:v>
+      </x:c>
+      <x:c r="N24" s="3" t="str">
+        <x:v>Approve quote action</x:v>
+      </x:c>
+      <x:c r="O24" s="3" t="str">
+        <x:v>QuoteController POST quotes/{quoteId}/approve</x:v>
+      </x:c>
+      <x:c r="P24" s="3" t="str">
+        <x:v>Quote/Order contract tests</x:v>
+      </x:c>
+      <x:c r="Q24" s="3" t="str">
+        <x:v>QuoteEngine BFF, QuotationService</x:v>
+      </x:c>
+      <x:c r="R24" s="3" t="str">
+        <x:v>Quote approval state</x:v>
+      </x:c>
+      <x:c r="S24" s="3" t="str">
+        <x:v>Needs authorization boundary test</x:v>
+      </x:c>
+      <x:c r="T24" s="3" t="str">
+        <x:v>QuoteController.cs:1205</x:v>
+      </x:c>
+      <x:c r="U24" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="3" t="str">
+        <x:v>QE-024</x:v>
+      </x:c>
+      <x:c r="B25" s="3" t="str">
+        <x:v>Maliev.QuoteEngine</x:v>
+      </x:c>
+      <x:c r="C25" s="3" t="str">
+        <x:v>Order creation</x:v>
+      </x:c>
+      <x:c r="D25" s="3" t="str">
+        <x:v>As a customer, I can create an order from an approved quote.</x:v>
+      </x:c>
+      <x:c r="E25" s="3" t="str">
+        <x:v>Orders endpoint creates order records after quote approval and gate checks.</x:v>
+      </x:c>
+      <x:c r="F25" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G25" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H25" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I25" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J25" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K25" s="3" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="L25" s="3" t="str">
+        <x:v>Create order action -&gt; QuoteController orders -&gt; OrderService</x:v>
+      </x:c>
+      <x:c r="M25" s="3" t="str">
+        <x:v>QuoteWorkspace.razor; QeQuoteSummaryBar.razor</x:v>
+      </x:c>
+      <x:c r="N25" s="3" t="str">
+        <x:v>Create order action</x:v>
+      </x:c>
+      <x:c r="O25" s="3" t="str">
+        <x:v>QuoteController POST orders</x:v>
+      </x:c>
+      <x:c r="P25" s="3" t="str">
+        <x:v>Order contract tests</x:v>
+      </x:c>
+      <x:c r="Q25" s="3" t="str">
+        <x:v>QuoteEngine BFF, OrderService</x:v>
+      </x:c>
+      <x:c r="R25" s="3" t="str">
+        <x:v>Order records</x:v>
+      </x:c>
+      <x:c r="S25" s="3" t="str">
+        <x:v>Needs end-to-end order creation test</x:v>
+      </x:c>
+      <x:c r="T25" s="3" t="str">
+        <x:v>QuoteController.cs:1227</x:v>
+      </x:c>
+      <x:c r="U25" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="3" t="str">
+        <x:v>QE-025</x:v>
+      </x:c>
+      <x:c r="B26" s="3" t="str">
+        <x:v>Maliev.QuoteEngine</x:v>
+      </x:c>
+      <x:c r="C26" s="3" t="str">
+        <x:v>Payment initiation and callbacks</x:v>
+      </x:c>
+      <x:c r="D26" s="3" t="str">
+        <x:v>As a customer, I can initiate payment and return to success/cancel pages.</x:v>
+      </x:c>
+      <x:c r="E26" s="3" t="str">
+        <x:v>Payment endpoint creates payment session and payment success/cancel pages handle return navigation.</x:v>
+      </x:c>
+      <x:c r="F26" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G26" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H26" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I26" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J26" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K26" s="3" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="L26" s="3" t="str">
+        <x:v>Payment action -&gt; QuoteController payments -&gt; PaymentService -&gt; return pages</x:v>
+      </x:c>
+      <x:c r="M26" s="3" t="str">
+        <x:v>PaymentSuccess.razor; PaymentCancel.razor; QeQuoteSummaryBar.razor</x:v>
+      </x:c>
+      <x:c r="N26" s="3" t="str">
+        <x:v>/payment/success, /payment/cancel; Pay action</x:v>
+      </x:c>
+      <x:c r="O26" s="3" t="str">
+        <x:v>QuoteController POST payments</x:v>
+      </x:c>
+      <x:c r="P26" s="3" t="str">
+        <x:v>Payment contract tests</x:v>
+      </x:c>
+      <x:c r="Q26" s="3" t="str">
+        <x:v>QuoteEngine BFF, PaymentService</x:v>
+      </x:c>
+      <x:c r="R26" s="3" t="str">
+        <x:v>Payment session</x:v>
+      </x:c>
+      <x:c r="S26" s="3" t="str">
+        <x:v>Needs provider-specific payment smoke</x:v>
+      </x:c>
+      <x:c r="T26" s="3" t="str">
+        <x:v>QuoteController.cs:906; PaymentSuccess.razor:1; PaymentCancel.razor:1</x:v>
+      </x:c>
+      <x:c r="U26" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="3" t="str">
+        <x:v>QE-026</x:v>
+      </x:c>
+      <x:c r="B27" s="3" t="str">
+        <x:v>Maliev.QuoteEngine</x:v>
+      </x:c>
+      <x:c r="C27" s="3" t="str">
+        <x:v>Account profile and addresses</x:v>
+      </x:c>
+      <x:c r="D27" s="3" t="str">
+        <x:v>As a signed-in customer, I can view profile and saved addresses.</x:v>
+      </x:c>
+      <x:c r="E27" s="3" t="str">
+        <x:v>Account endpoints expose profile and addresses for workspace/account pages.</x:v>
+      </x:c>
+      <x:c r="F27" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G27" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H27" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I27" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J27" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K27" s="3" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="L27" s="3" t="str">
+        <x:v>Profile/account UI -&gt; quote/v1/account profile/addresses</x:v>
+      </x:c>
+      <x:c r="M27" s="3" t="str">
+        <x:v>Profile.razor</x:v>
+      </x:c>
+      <x:c r="N27" s="3" t="str">
+        <x:v>/profile</x:v>
+      </x:c>
+      <x:c r="O27" s="3" t="str">
+        <x:v>AccountController GET profile, addresses</x:v>
+      </x:c>
+      <x:c r="P27" s="3" t="str">
+        <x:v>AccountAuthBoundaryTests</x:v>
+      </x:c>
+      <x:c r="Q27" s="3" t="str">
+        <x:v>QuoteEngine BFF, CustomerService</x:v>
+      </x:c>
+      <x:c r="R27" s="3" t="str">
+        <x:v>Profile/address read state</x:v>
+      </x:c>
+      <x:c r="S27" s="3" t="str">
+        <x:v>Needs edit-action inventory</x:v>
+      </x:c>
+      <x:c r="T27" s="3" t="str">
+        <x:v>AccountController.cs:46,76; Profile.razor:1</x:v>
+      </x:c>
+      <x:c r="U27" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="3" t="str">
+        <x:v>QE-027</x:v>
+      </x:c>
+      <x:c r="B28" s="3" t="str">
+        <x:v>Maliev.QuoteEngine</x:v>
+      </x:c>
+      <x:c r="C28" s="3" t="str">
+        <x:v>Quotes and orders account views</x:v>
+      </x:c>
+      <x:c r="D28" s="3" t="str">
+        <x:v>As a customer, I can review quotes, orders, and order details.</x:v>
+      </x:c>
+      <x:c r="E28" s="3" t="str">
+        <x:v>Account and pages expose quotes list, orders list, order detail, and order file downloads.</x:v>
+      </x:c>
+      <x:c r="F28" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G28" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H28" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I28" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J28" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K28" s="3" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="L28" s="3" t="str">
+        <x:v>Quote/order pages -&gt; quote/v1/account quotes/orders/files</x:v>
+      </x:c>
+      <x:c r="M28" s="3" t="str">
+        <x:v>Quotes.razor; Orders.razor; OrderDetail.razor</x:v>
+      </x:c>
+      <x:c r="N28" s="3" t="str">
+        <x:v>/quotes/{QuoteId}, /orders, /orders/{OrderNumber}</x:v>
+      </x:c>
+      <x:c r="O28" s="3" t="str">
+        <x:v>AccountController quotes, orders, order detail, order file download</x:v>
+      </x:c>
+      <x:c r="P28" s="3" t="str">
+        <x:v>QuoteEngineSourceTests account/order routes</x:v>
+      </x:c>
+      <x:c r="Q28" s="3" t="str">
+        <x:v>QuoteEngine BFF, Quote/Order service, Storage</x:v>
+      </x:c>
+      <x:c r="R28" s="3" t="str">
+        <x:v>Read-only quote/order/files</x:v>
+      </x:c>
+      <x:c r="S28" s="3" t="str">
+        <x:v>Needs authenticated browser pass</x:v>
+      </x:c>
+      <x:c r="T28" s="3" t="str">
+        <x:v>AccountController.cs:112-143; Quotes.razor; Orders.razor; OrderDetail.razor</x:v>
+      </x:c>
+      <x:c r="U28" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="3" t="str">
+        <x:v>QE-028</x:v>
+      </x:c>
+      <x:c r="B29" s="3" t="str">
+        <x:v>Maliev.QuoteEngine</x:v>
+      </x:c>
+      <x:c r="C29" s="3" t="str">
+        <x:v>NDAs</x:v>
+      </x:c>
+      <x:c r="D29" s="3" t="str">
+        <x:v>As a customer, I can view NDA records from the workspace account area.</x:v>
+      </x:c>
+      <x:c r="E29" s="3" t="str">
+        <x:v>NDA page calls account NDA endpoint and shows available NDA data.</x:v>
+      </x:c>
+      <x:c r="F29" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G29" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H29" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I29" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J29" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K29" s="3" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="L29" s="3" t="str">
+        <x:v>Ndas page -&gt; quote/v1/account/ndas -&gt; Customer/Document service</x:v>
+      </x:c>
+      <x:c r="M29" s="3" t="str">
+        <x:v>Ndas.razor</x:v>
+      </x:c>
+      <x:c r="N29" s="3" t="str">
+        <x:v>/ndas</x:v>
+      </x:c>
+      <x:c r="O29" s="3" t="str">
+        <x:v>AccountController GET ndas</x:v>
+      </x:c>
+      <x:c r="P29" s="3" t="str">
+        <x:v>QuoteEngineSourceTests account routes</x:v>
+      </x:c>
+      <x:c r="Q29" s="3" t="str">
+        <x:v>QuoteEngine BFF, Customer/Document services</x:v>
+      </x:c>
+      <x:c r="R29" s="3" t="str">
+        <x:v>NDA records</x:v>
+      </x:c>
+      <x:c r="S29" s="3" t="str">
+        <x:v>Needs upload/signing behavior inventory</x:v>
+      </x:c>
+      <x:c r="T29" s="3" t="str">
+        <x:v>Ndas.razor:1; AccountController.cs:175</x:v>
+      </x:c>
+      <x:c r="U29" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="3" t="str">
+        <x:v>QE-029</x:v>
+      </x:c>
+      <x:c r="B30" s="3" t="str">
+        <x:v>Maliev.QuoteEngine</x:v>
+      </x:c>
+      <x:c r="C30" s="3" t="str">
+        <x:v>Documents</x:v>
+      </x:c>
+      <x:c r="D30" s="3" t="str">
+        <x:v>As a customer, I can view, upload, and download account documents.</x:v>
+      </x:c>
+      <x:c r="E30" s="3" t="str">
+        <x:v>Documents page and account endpoints list, create/upload, and download documents.</x:v>
+      </x:c>
+      <x:c r="F30" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G30" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H30" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I30" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J30" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K30" s="3" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="L30" s="3" t="str">
+        <x:v>Documents page -&gt; quote/v1/account/documents -&gt; document storage</x:v>
+      </x:c>
+      <x:c r="M30" s="3" t="str">
+        <x:v>Documents.razor</x:v>
+      </x:c>
+      <x:c r="N30" s="3" t="str">
+        <x:v>/documents</x:v>
+      </x:c>
+      <x:c r="O30" s="3" t="str">
+        <x:v>AccountController documents GET/POST/upload/download</x:v>
+      </x:c>
+      <x:c r="P30" s="3" t="str">
+        <x:v>QuoteEngineSourceTests documents</x:v>
+      </x:c>
+      <x:c r="Q30" s="3" t="str">
+        <x:v>QuoteEngine BFF, Document/Storage service</x:v>
+      </x:c>
+      <x:c r="R30" s="3" t="str">
+        <x:v>Document records/files</x:v>
+      </x:c>
+      <x:c r="S30" s="3" t="str">
+        <x:v>Needs file type/size browser test</x:v>
+      </x:c>
+      <x:c r="T30" s="3" t="str">
+        <x:v>Documents.razor:1; AccountController.cs:202-354</x:v>
+      </x:c>
+      <x:c r="U30" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="3" t="str">
+        <x:v>QE-030</x:v>
+      </x:c>
+      <x:c r="B31" s="3" t="str">
+        <x:v>Maliev.QuoteEngine</x:v>
+      </x:c>
+      <x:c r="C31" s="3" t="str">
+        <x:v>Preferences</x:v>
+      </x:c>
+      <x:c r="D31" s="3" t="str">
+        <x:v>As a customer, I can manage workspace preferences.</x:v>
+      </x:c>
+      <x:c r="E31" s="3" t="str">
+        <x:v>Preferences page loads account/session-backed preference controls.</x:v>
+      </x:c>
+      <x:c r="F31" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G31" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H31" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I31" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J31" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K31" s="3" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="L31" s="3" t="str">
+        <x:v>Preferences page -&gt; QuoteEngineApiClient/account endpoints</x:v>
+      </x:c>
+      <x:c r="M31" s="3" t="str">
+        <x:v>Preferences.razor</x:v>
+      </x:c>
+      <x:c r="N31" s="3" t="str">
+        <x:v>/preferences</x:v>
+      </x:c>
+      <x:c r="O31" s="3" t="str">
+        <x:v>QuoteEngineApiClient preference/account calls</x:v>
+      </x:c>
+      <x:c r="P31" s="3" t="str">
+        <x:v>QuoteEngineSourceTests where present</x:v>
+      </x:c>
+      <x:c r="Q31" s="3" t="str">
+        <x:v>QuoteEngine client/BFF</x:v>
+      </x:c>
+      <x:c r="R31" s="3" t="str">
+        <x:v>Preference state</x:v>
+      </x:c>
+      <x:c r="S31" s="3" t="str">
+        <x:v>Needs exact preference contract inventory</x:v>
+      </x:c>
+      <x:c r="T31" s="3" t="str">
+        <x:v>Preferences.razor:1; QuoteEngineApiClient.cs</x:v>
+      </x:c>
+      <x:c r="U31" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="3" t="str">
+        <x:v>QE-031</x:v>
+      </x:c>
+      <x:c r="B32" s="3" t="str">
+        <x:v>Maliev.QuoteEngine</x:v>
+      </x:c>
+      <x:c r="C32" s="3" t="str">
+        <x:v>Authentication session</x:v>
+      </x:c>
+      <x:c r="D32" s="3" t="str">
+        <x:v>As a customer, I can sign in, sign up, complete chatbot auth, handle Google callback, and sign out.</x:v>
+      </x:c>
+      <x:c r="E32" s="3" t="str">
+        <x:v>Auth pages and BFF expose session and sign-out while auth callback routes complete external flows.</x:v>
+      </x:c>
+      <x:c r="F32" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G32" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H32" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I32" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J32" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K32" s="3" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="L32" s="3" t="str">
+        <x:v>Auth pages/layout -&gt; quote/v1/auth session/sign-out and callback pages</x:v>
+      </x:c>
+      <x:c r="M32" s="3" t="str">
+        <x:v>SignIn.razor; SignUp.razor; GoogleCallback.razor; AuthChatbotComplete.razor; MainLayout.razor</x:v>
+      </x:c>
+      <x:c r="N32" s="3" t="str">
+        <x:v>/auth/sign-in, /auth/sign-up, /auth/callback/google, /auth/chatbot-complete</x:v>
+      </x:c>
+      <x:c r="O32" s="3" t="str">
+        <x:v>AuthController GET session, POST sign-out</x:v>
+      </x:c>
+      <x:c r="P32" s="3" t="str">
+        <x:v>GoogleAuthFlowTests; AccountAuthBoundaryTests</x:v>
+      </x:c>
+      <x:c r="Q32" s="3" t="str">
+        <x:v>QuoteEngine BFF, Auth/Customer session</x:v>
+      </x:c>
+      <x:c r="R32" s="3" t="str">
+        <x:v>Auth session/cookies</x:v>
+      </x:c>
+      <x:c r="S32" s="3" t="str">
+        <x:v>Needs OAuth/browser environment smoke</x:v>
+      </x:c>
+      <x:c r="T32" s="3" t="str">
+        <x:v>AuthController.cs:13-28; auth pages</x:v>
+      </x:c>
+      <x:c r="U32" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="3" t="str">
+        <x:v>QE-032</x:v>
+      </x:c>
+      <x:c r="B33" s="3" t="str">
+        <x:v>Maliev.QuoteEngine</x:v>
+      </x:c>
+      <x:c r="C33" s="3" t="str">
+        <x:v>Shipping</x:v>
+      </x:c>
+      <x:c r="D33" s="3" t="str">
+        <x:v>As a customer, I can retrieve couriers, request rates, and track shipments for orders.</x:v>
+      </x:c>
+      <x:c r="E33" s="3" t="str">
+        <x:v>Shipping endpoints proxy courier, rate, and tracking operations to DeliveryService.</x:v>
+      </x:c>
+      <x:c r="F33" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G33" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H33" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I33" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J33" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K33" s="3" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="L33" s="3" t="str">
+        <x:v>Shipping UI/API client -&gt; quote/v1/shipping -&gt; DeliveryService</x:v>
+      </x:c>
+      <x:c r="M33" s="3" t="str">
+        <x:v>Order/checkout flows</x:v>
+      </x:c>
+      <x:c r="N33" s="3" t="str">
+        <x:v>Courier/rate/tracking controls</x:v>
+      </x:c>
+      <x:c r="O33" s="3" t="str">
+        <x:v>ShippingController couriers/rates/tracking</x:v>
+      </x:c>
+      <x:c r="P33" s="3" t="str">
+        <x:v>Shipping contract tests where present</x:v>
+      </x:c>
+      <x:c r="Q33" s="3" t="str">
+        <x:v>QuoteEngine BFF, DeliveryService</x:v>
+      </x:c>
+      <x:c r="R33" s="3" t="str">
+        <x:v>Shipping rate request/tracking lookup</x:v>
+      </x:c>
+      <x:c r="S33" s="3" t="str">
+        <x:v>Needs checkout/order UI mapping check</x:v>
+      </x:c>
+      <x:c r="T33" s="3" t="str">
+        <x:v>ShippingController.cs:12-51</x:v>
+      </x:c>
+      <x:c r="U33" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="3" t="str">
+        <x:v>QE-033</x:v>
+      </x:c>
+      <x:c r="B34" s="3" t="str">
+        <x:v>Maliev.QuoteEngine</x:v>
+      </x:c>
+      <x:c r="C34" s="3" t="str">
+        <x:v>Address support data</x:v>
+      </x:c>
+      <x:c r="D34" s="3" t="str">
+        <x:v>As a customer, I can use Google address config and Thai location support in address forms.</x:v>
+      </x:c>
+      <x:c r="E34" s="3" t="str">
+        <x:v>Address controller returns Google config and Thai locations.</x:v>
+      </x:c>
+      <x:c r="F34" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G34" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H34" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I34" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J34" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K34" s="3" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="L34" s="3" t="str">
+        <x:v>Address forms -&gt; quote/v1/address endpoints</x:v>
+      </x:c>
+      <x:c r="M34" s="3" t="str">
+        <x:v>Profile/address UI</x:v>
+      </x:c>
+      <x:c r="N34" s="3" t="str">
+        <x:v>Address helper controls</x:v>
+      </x:c>
+      <x:c r="O34" s="3" t="str">
+        <x:v>AddressController google-config, thai-locations</x:v>
+      </x:c>
+      <x:c r="P34" s="3" t="str">
+        <x:v>QuoteEngineAddressSourceTests</x:v>
+      </x:c>
+      <x:c r="Q34" s="3" t="str">
+        <x:v>QuoteEngine BFF, Configuration/ReferenceData</x:v>
+      </x:c>
+      <x:c r="R34" s="3" t="str">
+        <x:v>Read-only address support data</x:v>
+      </x:c>
+      <x:c r="S34" s="3" t="str">
+        <x:v>Needs no-key fallback check</x:v>
+      </x:c>
+      <x:c r="T34" s="3" t="str">
+        <x:v>AddressController.cs:12-40</x:v>
+      </x:c>
+      <x:c r="U34" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="3" t="str">
+        <x:v>QE-034</x:v>
+      </x:c>
+      <x:c r="B35" s="3" t="str">
+        <x:v>Maliev.QuoteEngine</x:v>
+      </x:c>
+      <x:c r="C35" s="3" t="str">
+        <x:v>Geometry runtime</x:v>
+      </x:c>
+      <x:c r="D35" s="3" t="str">
+        <x:v>As a customer, I can load geometry runtime assets for part previews.</x:v>
+      </x:c>
+      <x:c r="E35" s="3" t="str">
+        <x:v>Geometry runtime controller serves manifest/assets and records telemetry.</x:v>
+      </x:c>
+      <x:c r="F35" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G35" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H35" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I35" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J35" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K35" s="3" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="L35" s="3" t="str">
+        <x:v>QePartViewer -&gt; quote/v1/geometry/runtime -&gt; runtime assets/telemetry</x:v>
+      </x:c>
+      <x:c r="M35" s="3" t="str">
+        <x:v>QePartViewer.razor</x:v>
+      </x:c>
+      <x:c r="N35" s="3" t="str">
+        <x:v>3D viewer runtime</x:v>
+      </x:c>
+      <x:c r="O35" s="3" t="str">
+        <x:v>GeometryRuntimeController manifest/assets/telemetry</x:v>
+      </x:c>
+      <x:c r="P35" s="3" t="str">
+        <x:v>QuoteEngineSourceTests geometry runtime</x:v>
+      </x:c>
+      <x:c r="Q35" s="3" t="str">
+        <x:v>QuoteEngine BFF, Geometry runtime</x:v>
+      </x:c>
+      <x:c r="R35" s="3" t="str">
+        <x:v>Telemetry only</x:v>
+      </x:c>
+      <x:c r="S35" s="3" t="str">
+        <x:v>Needs browser canvas render pass</x:v>
+      </x:c>
+      <x:c r="T35" s="3" t="str">
+        <x:v>GeometryRuntimeController.cs:18-214; QePartViewer.razor</x:v>
+      </x:c>
+      <x:c r="U35" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="3" t="str">
+        <x:v>QE-035</x:v>
+      </x:c>
+      <x:c r="B36" s="3" t="str">
+        <x:v>Maliev.QuoteEngine</x:v>
+      </x:c>
+      <x:c r="C36" s="3" t="str">
+        <x:v>Action confirmations and tools</x:v>
+      </x:c>
+      <x:c r="D36" s="3" t="str">
+        <x:v>As a customer, I can review and confirm agent-proposed tool actions.</x:v>
+      </x:c>
+      <x:c r="E36" s="3" t="str">
+        <x:v>Agent exposes tool execution and action confirmation endpoints with customer/session access checks.</x:v>
+      </x:c>
+      <x:c r="F36" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G36" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H36" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I36" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J36" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K36" s="3" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="L36" s="3" t="str">
+        <x:v>Agent action cards -&gt; tools/actions/confirm -&gt; QuoteAgentService/SessionStore</x:v>
+      </x:c>
+      <x:c r="M36" s="3" t="str">
+        <x:v>QuoteAgentLaunchShell.razor</x:v>
+      </x:c>
+      <x:c r="N36" s="3" t="str">
+        <x:v>Confirmation cards and action buttons</x:v>
+      </x:c>
+      <x:c r="O36" s="3" t="str">
+        <x:v>AgentController tools/{toolName}, actions/{actionId}/confirm</x:v>
+      </x:c>
+      <x:c r="P36" s="3" t="str">
+        <x:v>QuoteAgentEndpointTests action confirmations</x:v>
+      </x:c>
+      <x:c r="Q36" s="3" t="str">
+        <x:v>QuoteEngine BFF, Agent service, SessionStore</x:v>
+      </x:c>
+      <x:c r="R36" s="3" t="str">
+        <x:v>Pending/confirmed action state</x:v>
+      </x:c>
+      <x:c r="S36" s="3" t="str">
+        <x:v>Needs irreversible-action UX test</x:v>
+      </x:c>
+      <x:c r="T36" s="3" t="str">
+        <x:v>AgentController.cs:297,321; QuoteAgentService.cs; QuoteAgentSessionStore.cs</x:v>
+      </x:c>
+      <x:c r="U36" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="3" t="str">
+        <x:v>QE-036</x:v>
+      </x:c>
+      <x:c r="B37" s="3" t="str">
+        <x:v>Maliev.QuoteEngine</x:v>
+      </x:c>
+      <x:c r="C37" s="3" t="str">
+        <x:v>Agent memory and grounding</x:v>
+      </x:c>
+      <x:c r="D37" s="3" t="str">
+        <x:v>As a returning customer, I get responses grounded in current project state and durable customer memory.</x:v>
+      </x:c>
+      <x:c r="E37" s="3" t="str">
+        <x:v>QuoteAgentService builds prompt grounding, injects project/session state, and uses customer memory observations where authenticated.</x:v>
+      </x:c>
+      <x:c r="F37" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G37" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H37" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I37" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J37" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K37" s="3" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="L37" s="3" t="str">
+        <x:v>Agent service -&gt; Customer memory/project context -&gt; model prompt</x:v>
+      </x:c>
+      <x:c r="M37" s="3" t="str">
         <x:v>QuoteAgentService.cs</x:v>
       </x:c>
-      <x:c r="N10" s="3" t="str">
-        <x:v>Chat grounding, generated suggestions, DFM-aware assistant responses</x:v>
-      </x:c>
-      <x:c r="O10" s="3" t="str">
-        <x:v>QuoteAgentService prompt rules, memory context, local DFM and tool handlers</x:v>
-      </x:c>
-      <x:c r="P10" s="3" t="str">
-        <x:v>QuoteAgentEndpointTests memory, grounding, local DFM, generated previews</x:v>
-      </x:c>
-      <x:c r="Q10" s="3" t="str">
-        <x:v>QuoteEngine BFF, Agent model, Customer memory, SessionStore</x:v>
-      </x:c>
-      <x:c r="R10" s="3" t="str">
-        <x:v>Memory observations and session-grounded context</x:v>
-      </x:c>
-      <x:c r="S10" s="3" t="str">
-        <x:v>Needs authenticated memory persistence retest</x:v>
-      </x:c>
-      <x:c r="T10" s="3" t="str">
-        <x:v>QuoteAgentService.cs:561,5691-5739,5865,7052; Shared/Agent DTOs</x:v>
-      </x:c>
-      <x:c r="U10" s="3" t="str">
+      <x:c r="N37" s="3" t="str">
+        <x:v>Agent responses and feedback status</x:v>
+      </x:c>
+      <x:c r="O37" s="3" t="str">
+        <x:v>QuoteAgentService prompt/memory paths</x:v>
+      </x:c>
+      <x:c r="P37" s="3" t="str">
+        <x:v>QuoteAgentEndpointTests memory/grounding; source tests feedback memory</x:v>
+      </x:c>
+      <x:c r="Q37" s="3" t="str">
+        <x:v>QuoteEngine BFF, Agent model, CustomerService memory</x:v>
+      </x:c>
+      <x:c r="R37" s="3" t="str">
+        <x:v>Memory observations/session context</x:v>
+      </x:c>
+      <x:c r="S37" s="3" t="str">
+        <x:v>Needs authenticated persistence retest</x:v>
+      </x:c>
+      <x:c r="T37" s="3" t="str">
+        <x:v>QuoteAgentService.cs</x:v>
+      </x:c>
+      <x:c r="U37" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="3" t="str">
+        <x:v>QE-037</x:v>
+      </x:c>
+      <x:c r="B38" s="3" t="str">
+        <x:v>Maliev.QuoteEngine</x:v>
+      </x:c>
+      <x:c r="C38" s="3" t="str">
+        <x:v>Realtime analysis notifications</x:v>
+      </x:c>
+      <x:c r="D38" s="3" t="str">
+        <x:v>As a customer, I get updates when file analysis, GLB generation, or DFM analysis completes.</x:v>
+      </x:c>
+      <x:c r="E38" s="3" t="str">
+        <x:v>Workspace connects to notification hub and handles analysis, GLB, and DFM readiness events.</x:v>
+      </x:c>
+      <x:c r="F38" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G38" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H38" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I38" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J38" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K38" s="3" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="L38" s="3" t="str">
+        <x:v>SignalR notifications -&gt; QuoteWorkspace handlers -&gt; part/session state</x:v>
+      </x:c>
+      <x:c r="M38" s="3" t="str">
+        <x:v>QuoteWorkspace.razor</x:v>
+      </x:c>
+      <x:c r="N38" s="3" t="str">
+        <x:v>Realtime workspace status</x:v>
+      </x:c>
+      <x:c r="O38" s="3" t="str">
+        <x:v>Analysis status endpoints plus notification hub</x:v>
+      </x:c>
+      <x:c r="P38" s="3" t="str">
+        <x:v>QuoteEngineSourceTests realtime/thinking where present</x:v>
+      </x:c>
+      <x:c r="Q38" s="3" t="str">
+        <x:v>QuoteEngine BFF, SignalR, Geometry/Storage</x:v>
+      </x:c>
+      <x:c r="R38" s="3" t="str">
+        <x:v>Analysis/preview readiness state</x:v>
+      </x:c>
+      <x:c r="S38" s="3" t="str">
+        <x:v>Needs live Aspire notification test</x:v>
+      </x:c>
+      <x:c r="T38" s="3" t="str">
+        <x:v>QuoteWorkspace.razor SignalR handlers</x:v>
+      </x:c>
+      <x:c r="U38" s="3" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="3" t="str">
+        <x:v>QE-038</x:v>
+      </x:c>
+      <x:c r="B39" s="3" t="str">
+        <x:v>Maliev.QuoteEngine</x:v>
+      </x:c>
+      <x:c r="C39" s="3" t="str">
+        <x:v>Export PDF</x:v>
+      </x:c>
+      <x:c r="D39" s="3" t="str">
+        <x:v>As a customer, I can export agent/workspace content to PDF.</x:v>
+      </x:c>
+      <x:c r="E39" s="3" t="str">
+        <x:v>Agent export endpoint generates a PDF from supplied workspace/agent content.</x:v>
+      </x:c>
+      <x:c r="F39" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G39" s="3" t="str">
+        <x:v>Mapped to existing tests</x:v>
+      </x:c>
+      <x:c r="H39" s="3" t="str">
+        <x:v>Not tested in current loop</x:v>
+      </x:c>
+      <x:c r="I39" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J39" s="3" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="K39" s="3" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="L39" s="3" t="str">
+        <x:v>Export action -&gt; AgentController export-pdf -&gt; PDF generation</x:v>
+      </x:c>
+      <x:c r="M39" s="3" t="str">
+        <x:v>QuoteAgentLaunchShell.razor</x:v>
+      </x:c>
+      <x:c r="N39" s="3" t="str">
+        <x:v>Export/download PDF controls</x:v>
+      </x:c>
+      <x:c r="O39" s="3" t="str">
+        <x:v>AgentController POST export-pdf</x:v>
+      </x:c>
+      <x:c r="P39" s="3" t="str">
+        <x:v>QuoteAgentEndpointTests export PDF</x:v>
+      </x:c>
+      <x:c r="Q39" s="3" t="str">
+        <x:v>QuoteEngine BFF, PdfService</x:v>
+      </x:c>
+      <x:c r="R39" s="3" t="str">
+        <x:v>PDF artifact</x:v>
+      </x:c>
+      <x:c r="S39" s="3" t="str">
+        <x:v>Needs visual PDF validation</x:v>
+      </x:c>
+      <x:c r="T39" s="3" t="str">
+        <x:v>AgentController.cs:437</x:v>
+      </x:c>
+      <x:c r="U39" s="3" t="str">
         <x:v>2026-06-23</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2865fd51e543456d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R46467e2fa42b4a7b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/maliev-feature-user-story-status.xlsx
+++ b/docs/maliev-feature-user-story-status.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R4951e6e7fb174d34"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="R3cbbc007e1394284"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="Re06731d698074229"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="R197f169ab6464859"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Re086ce504db64dbb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="R3b20f9a852e646df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R45c978b042fe44c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="Rf844fe5811ef441b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -604,16 +604,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G3" s="3" t="str">
-        <x:v>Needs manual / browser test</x:v>
+        <x:v>Focused automated source tests passed 2026-06-23; browser runtime pending</x:v>
       </x:c>
       <x:c r="H3" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in focused source tests.</x:v>
       </x:c>
       <x:c r="I3" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed from focused tests.</x:v>
       </x:c>
       <x:c r="J3" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Pending browser/runtime verification.</x:v>
       </x:c>
       <x:c r="K3" s="3" t="str">
         <x:v>P2</x:v>
@@ -630,7 +630,9 @@
       <x:c r="O3" s="3" t="str">
         <x:v>Static content model</x:v>
       </x:c>
-      <x:c r="P3" s="3" t="str"/>
+      <x:c r="P3" s="3" t="str">
+        <x:v>dotnet test Maliev.Web.slnx --filter HeroLayoutSourceTests.ServicesUseRealRoutesAndDisabledQuoteActions|HeroLayoutSourceTests.StaticPagesCoverCustomerRoutesAndContactBoundary|HeroLayoutSourceTests.CheckoutPageCollectsCustomerCheckoutDetailsAfterSignIn|HeroLayoutSourceTests.HeaderUsesMudIconButtonsForCartAndAccount passed 4/4 on 2026-06-23.</x:v>
+      </x:c>
       <x:c r="Q3" s="3" t="str">
         <x:v>Web client</x:v>
       </x:c>
@@ -667,16 +669,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G4" s="3" t="str">
-        <x:v>Needs manual / browser test</x:v>
+        <x:v>Focused automated source tests passed 2026-06-23; browser runtime pending</x:v>
       </x:c>
       <x:c r="H4" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in focused source tests.</x:v>
       </x:c>
       <x:c r="I4" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed from focused tests.</x:v>
       </x:c>
       <x:c r="J4" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Pending browser/runtime verification.</x:v>
       </x:c>
       <x:c r="K4" s="3" t="str">
         <x:v>P2</x:v>
@@ -693,7 +695,9 @@
       <x:c r="O4" s="3" t="str">
         <x:v>Static content model</x:v>
       </x:c>
-      <x:c r="P4" s="3" t="str"/>
+      <x:c r="P4" s="3" t="str">
+        <x:v>dotnet test Maliev.Web.slnx --filter HeroLayoutSourceTests.ServicesUseRealRoutesAndDisabledQuoteActions|HeroLayoutSourceTests.StaticPagesCoverCustomerRoutesAndContactBoundary|HeroLayoutSourceTests.CheckoutPageCollectsCustomerCheckoutDetailsAfterSignIn|HeroLayoutSourceTests.HeaderUsesMudIconButtonsForCartAndAccount passed 4/4 on 2026-06-23.</x:v>
+      </x:c>
       <x:c r="Q4" s="3" t="str">
         <x:v>Web client</x:v>
       </x:c>
@@ -990,16 +994,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G9" s="3" t="str">
-        <x:v>Needs manual / browser test</x:v>
+        <x:v>Focused automated source tests passed 2026-06-23; browser runtime pending</x:v>
       </x:c>
       <x:c r="H9" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in focused source tests.</x:v>
       </x:c>
       <x:c r="I9" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed from focused tests.</x:v>
       </x:c>
       <x:c r="J9" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Pending browser/runtime verification.</x:v>
       </x:c>
       <x:c r="K9" s="3" t="str">
         <x:v>P1</x:v>
@@ -1016,7 +1020,9 @@
       <x:c r="O9" s="3" t="str">
         <x:v>CheckoutController draft endpoints used after cart</x:v>
       </x:c>
-      <x:c r="P9" s="3" t="str"/>
+      <x:c r="P9" s="3" t="str">
+        <x:v>dotnet test Maliev.Web.slnx --filter HeroLayoutSourceTests.HeaderUsesMudIconButtonsForCartAndAccount|HeroLayoutSourceTests.CheckoutPageCollectsCustomerCheckoutDetailsAfterSignIn passed as part of 4/4 focused Web run on 2026-06-23.</x:v>
+      </x:c>
       <x:c r="Q9" s="3" t="str">
         <x:v>Web client, Checkout BFF</x:v>
       </x:c>
@@ -2223,16 +2229,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G28" s="3" t="str">
-        <x:v>Needs manual / browser test</x:v>
+        <x:v>Focused automated source tests passed 2026-06-23; browser runtime pending</x:v>
       </x:c>
       <x:c r="H28" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in focused source tests.</x:v>
       </x:c>
       <x:c r="I28" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed from focused tests.</x:v>
       </x:c>
       <x:c r="J28" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Pending browser/runtime verification.</x:v>
       </x:c>
       <x:c r="K28" s="3" t="str">
         <x:v>P2</x:v>
@@ -2249,7 +2255,9 @@
       <x:c r="O28" s="3" t="str">
         <x:v>BlogController for ebook PDF only</x:v>
       </x:c>
-      <x:c r="P28" s="3" t="str"/>
+      <x:c r="P28" s="3" t="str">
+        <x:v>dotnet test Maliev.Web.slnx --filter HeroLayoutSourceTests.StaticPagesCoverCustomerRoutesAndContactBoundary passed as part of 4/4 focused Web run on 2026-06-23.</x:v>
+      </x:c>
       <x:c r="Q28" s="3" t="str">
         <x:v>Web client, Content</x:v>
       </x:c>
@@ -2399,7 +2407,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8f69ea83b5bd4390"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb4273a98aa13480a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2581,16 +2589,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G3" s="3" t="str">
-        <x:v>Needs manual / browser test</x:v>
+        <x:v>Focused automated component/controller tests passed 2026-06-23; browser runtime pending</x:v>
       </x:c>
       <x:c r="H3" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in focused tests. Initial concurrent repo run hit shared ServiceDefaults obj lock; serialized rerun passed.</x:v>
       </x:c>
       <x:c r="I3" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Test orchestration adjusted: run Web/Intranet dotnet tests serially when they share ServiceDefaults build outputs.</x:v>
       </x:c>
       <x:c r="J3" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Serialized focused retest passed 15/15; browser/runtime verification pending.</x:v>
       </x:c>
       <x:c r="K3" s="3" t="str">
         <x:v>P1</x:v>
@@ -2607,7 +2615,9 @@
       <x:c r="O3" s="3" t="str">
         <x:v>DashboardController GET, action-items</x:v>
       </x:c>
-      <x:c r="P3" s="3" t="str"/>
+      <x:c r="P3" s="3" t="str">
+        <x:v>dotnet test Maliev.Intranet.slnx --filter Phase3DashboardTests|DashboardControllerTests|QuickControllerTests.Dashboard_Get_ReturnsOk passed 15/15 on 2026-06-23 after serialized rerun.</x:v>
+      </x:c>
       <x:c r="Q3" s="3" t="str">
         <x:v>Intranet BFF, operational services</x:v>
       </x:c>
@@ -5357,7 +5367,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R538fcc7d41c54202"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfa82a720634c4d56"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7927,7 +7937,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R46467e2fa42b4a7b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6570a1d1c6d044cd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/maliev-feature-user-story-status.xlsx
+++ b/docs/maliev-feature-user-story-status.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Re086ce504db64dbb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="R3b20f9a852e646df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R45c978b042fe44c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="Rf844fe5811ef441b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Ra98dcfe6fa48452c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="Rff19ee7921e742a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R1f8cd9d0fd924061"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="R525223cc4eea4a01"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -539,16 +539,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G2" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Web suite passed 2026-06-23</x:v>
       </x:c>
       <x:c r="H2" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Web automated suite.</x:v>
       </x:c>
       <x:c r="I2" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed from current Web automated suite.</x:v>
       </x:c>
       <x:c r="J2" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K2" s="3" t="str">
         <x:v>P1</x:v>
@@ -566,7 +566,7 @@
         <x:v>SeoController robots/sitemap for crawl entry points</x:v>
       </x:c>
       <x:c r="P2" s="3" t="str">
-        <x:v>WebBffEndpointTests Seo</x:v>
+        <x:v>WebBffEndpointTests Seo | Current suite: dotnet test Maliev.Web.slnx --verbosity minimal passed 235/235 on 2026-06-23.</x:v>
       </x:c>
       <x:c r="Q2" s="3" t="str">
         <x:v>Web client, Web BFF, content/static assets</x:v>
@@ -604,16 +604,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G3" s="3" t="str">
-        <x:v>Focused automated source tests passed 2026-06-23; browser runtime pending</x:v>
+        <x:v>Automated Web suite passed 2026-06-23; browser runtime pending</x:v>
       </x:c>
       <x:c r="H3" s="3" t="str">
-        <x:v>No behavior error observed in focused source tests.</x:v>
+        <x:v>No behavior error observed in current Web automated suite.</x:v>
       </x:c>
       <x:c r="I3" s="3" t="str">
-        <x:v>No fix needed from focused tests.</x:v>
+        <x:v>No fix needed from current Web automated suite.</x:v>
       </x:c>
       <x:c r="J3" s="3" t="str">
-        <x:v>Pending browser/runtime verification.</x:v>
+        <x:v>Current automated suite passed; browser/runtime verification pending.</x:v>
       </x:c>
       <x:c r="K3" s="3" t="str">
         <x:v>P2</x:v>
@@ -631,7 +631,7 @@
         <x:v>Static content model</x:v>
       </x:c>
       <x:c r="P3" s="3" t="str">
-        <x:v>dotnet test Maliev.Web.slnx --filter HeroLayoutSourceTests.ServicesUseRealRoutesAndDisabledQuoteActions|HeroLayoutSourceTests.StaticPagesCoverCustomerRoutesAndContactBoundary|HeroLayoutSourceTests.CheckoutPageCollectsCustomerCheckoutDetailsAfterSignIn|HeroLayoutSourceTests.HeaderUsesMudIconButtonsForCartAndAccount passed 4/4 on 2026-06-23.</x:v>
+        <x:v>dotnet test Maliev.Web.slnx --filter HeroLayoutSourceTests.ServicesUseRealRoutesAndDisabledQuoteActions|HeroLayoutSourceTests.StaticPagesCoverCustomerRoutesAndContactBoundary|HeroLayoutSourceTests.CheckoutPageCollectsCustomerCheckoutDetailsAfterSignIn|HeroLayoutSourceTests.HeaderUsesMudIconButtonsForCartAndAccount passed 4/4 on 2026-06-23. | Current suite: dotnet test Maliev.Web.slnx --verbosity minimal passed 235/235 on 2026-06-23.</x:v>
       </x:c>
       <x:c r="Q3" s="3" t="str">
         <x:v>Web client</x:v>
@@ -669,16 +669,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G4" s="3" t="str">
-        <x:v>Focused automated source tests passed 2026-06-23; browser runtime pending</x:v>
+        <x:v>Automated Web suite passed 2026-06-23; browser runtime pending</x:v>
       </x:c>
       <x:c r="H4" s="3" t="str">
-        <x:v>No behavior error observed in focused source tests.</x:v>
+        <x:v>No behavior error observed in current Web automated suite.</x:v>
       </x:c>
       <x:c r="I4" s="3" t="str">
-        <x:v>No fix needed from focused tests.</x:v>
+        <x:v>No fix needed from current Web automated suite.</x:v>
       </x:c>
       <x:c r="J4" s="3" t="str">
-        <x:v>Pending browser/runtime verification.</x:v>
+        <x:v>Current automated suite passed; browser/runtime verification pending.</x:v>
       </x:c>
       <x:c r="K4" s="3" t="str">
         <x:v>P2</x:v>
@@ -696,7 +696,7 @@
         <x:v>Static content model</x:v>
       </x:c>
       <x:c r="P4" s="3" t="str">
-        <x:v>dotnet test Maliev.Web.slnx --filter HeroLayoutSourceTests.ServicesUseRealRoutesAndDisabledQuoteActions|HeroLayoutSourceTests.StaticPagesCoverCustomerRoutesAndContactBoundary|HeroLayoutSourceTests.CheckoutPageCollectsCustomerCheckoutDetailsAfterSignIn|HeroLayoutSourceTests.HeaderUsesMudIconButtonsForCartAndAccount passed 4/4 on 2026-06-23.</x:v>
+        <x:v>dotnet test Maliev.Web.slnx --filter HeroLayoutSourceTests.ServicesUseRealRoutesAndDisabledQuoteActions|HeroLayoutSourceTests.StaticPagesCoverCustomerRoutesAndContactBoundary|HeroLayoutSourceTests.CheckoutPageCollectsCustomerCheckoutDetailsAfterSignIn|HeroLayoutSourceTests.HeaderUsesMudIconButtonsForCartAndAccount passed 4/4 on 2026-06-23. | Current suite: dotnet test Maliev.Web.slnx --verbosity minimal passed 235/235 on 2026-06-23.</x:v>
       </x:c>
       <x:c r="Q4" s="3" t="str">
         <x:v>Web client</x:v>
@@ -734,16 +734,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G5" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Web suite passed 2026-06-23</x:v>
       </x:c>
       <x:c r="H5" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Web automated suite.</x:v>
       </x:c>
       <x:c r="I5" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed from current Web automated suite.</x:v>
       </x:c>
       <x:c r="J5" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K5" s="3" t="str">
         <x:v>P1</x:v>
@@ -761,7 +761,7 @@
         <x:v>MaterialsController datasheet endpoint</x:v>
       </x:c>
       <x:c r="P5" s="3" t="str">
-        <x:v>WebBffEndpointTests Materials</x:v>
+        <x:v>WebBffEndpointTests Materials | Current suite: dotnet test Maliev.Web.slnx --verbosity minimal passed 235/235 on 2026-06-23.</x:v>
       </x:c>
       <x:c r="Q5" s="3" t="str">
         <x:v>Web client, Web BFF, PDF generation/storage</x:v>
@@ -799,16 +799,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G6" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Web suite passed 2026-06-23</x:v>
       </x:c>
       <x:c r="H6" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Web automated suite.</x:v>
       </x:c>
       <x:c r="I6" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed from current Web automated suite.</x:v>
       </x:c>
       <x:c r="J6" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K6" s="3" t="str">
         <x:v>P1</x:v>
@@ -826,7 +826,7 @@
         <x:v>MaterialsController GET {slug}/datasheet.pdf</x:v>
       </x:c>
       <x:c r="P6" s="3" t="str">
-        <x:v>WebBffEndpointTests Materials</x:v>
+        <x:v>WebBffEndpointTests Materials | Current suite: dotnet test Maliev.Web.slnx --verbosity minimal passed 235/235 on 2026-06-23.</x:v>
       </x:c>
       <x:c r="Q6" s="3" t="str">
         <x:v>Web BFF, PDF service/content</x:v>
@@ -864,16 +864,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G7" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Web suite passed 2026-06-23</x:v>
       </x:c>
       <x:c r="H7" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Web automated suite.</x:v>
       </x:c>
       <x:c r="I7" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed from current Web automated suite.</x:v>
       </x:c>
       <x:c r="J7" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K7" s="3" t="str">
         <x:v>P1</x:v>
@@ -891,7 +891,7 @@
         <x:v>CatalogController collections, products, media, collection image</x:v>
       </x:c>
       <x:c r="P7" s="3" t="str">
-        <x:v>CommerceCatalogBoundaryTests; WebBffEndpointTests Catalog</x:v>
+        <x:v>CommerceCatalogBoundaryTests; WebBffEndpointTests Catalog | Current suite: dotnet test Maliev.Web.slnx --verbosity minimal passed 235/235 on 2026-06-23.</x:v>
       </x:c>
       <x:c r="Q7" s="3" t="str">
         <x:v>Web BFF, Catalog/Commerce, Storage</x:v>
@@ -929,16 +929,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G8" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Web suite passed 2026-06-23</x:v>
       </x:c>
       <x:c r="H8" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Web automated suite.</x:v>
       </x:c>
       <x:c r="I8" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed from current Web automated suite.</x:v>
       </x:c>
       <x:c r="J8" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K8" s="3" t="str">
         <x:v>P1</x:v>
@@ -956,7 +956,7 @@
         <x:v>CatalogController GET products/{handle}</x:v>
       </x:c>
       <x:c r="P8" s="3" t="str">
-        <x:v>CommerceCatalogBoundaryTests</x:v>
+        <x:v>CommerceCatalogBoundaryTests | Current suite: dotnet test Maliev.Web.slnx --verbosity minimal passed 235/235 on 2026-06-23.</x:v>
       </x:c>
       <x:c r="Q8" s="3" t="str">
         <x:v>Web BFF, Catalog/Commerce</x:v>
@@ -994,16 +994,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G9" s="3" t="str">
-        <x:v>Focused automated source tests passed 2026-06-23; browser runtime pending</x:v>
+        <x:v>Automated Web suite passed 2026-06-23; browser runtime pending</x:v>
       </x:c>
       <x:c r="H9" s="3" t="str">
-        <x:v>No behavior error observed in focused source tests.</x:v>
+        <x:v>No behavior error observed in current Web automated suite.</x:v>
       </x:c>
       <x:c r="I9" s="3" t="str">
-        <x:v>No fix needed from focused tests.</x:v>
+        <x:v>No fix needed from current Web automated suite.</x:v>
       </x:c>
       <x:c r="J9" s="3" t="str">
-        <x:v>Pending browser/runtime verification.</x:v>
+        <x:v>Current automated suite passed; browser/runtime verification pending.</x:v>
       </x:c>
       <x:c r="K9" s="3" t="str">
         <x:v>P1</x:v>
@@ -1021,7 +1021,7 @@
         <x:v>CheckoutController draft endpoints used after cart</x:v>
       </x:c>
       <x:c r="P9" s="3" t="str">
-        <x:v>dotnet test Maliev.Web.slnx --filter HeroLayoutSourceTests.HeaderUsesMudIconButtonsForCartAndAccount|HeroLayoutSourceTests.CheckoutPageCollectsCustomerCheckoutDetailsAfterSignIn passed as part of 4/4 focused Web run on 2026-06-23.</x:v>
+        <x:v>dotnet test Maliev.Web.slnx --filter HeroLayoutSourceTests.HeaderUsesMudIconButtonsForCartAndAccount|HeroLayoutSourceTests.CheckoutPageCollectsCustomerCheckoutDetailsAfterSignIn passed as part of 4/4 focused Web run on 2026-06-23. | Current suite: dotnet test Maliev.Web.slnx --verbosity minimal passed 235/235 on 2026-06-23.</x:v>
       </x:c>
       <x:c r="Q9" s="3" t="str">
         <x:v>Web client, Checkout BFF</x:v>
@@ -1059,16 +1059,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G10" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Web suite passed 2026-06-23</x:v>
       </x:c>
       <x:c r="H10" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Web automated suite.</x:v>
       </x:c>
       <x:c r="I10" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed from current Web automated suite.</x:v>
       </x:c>
       <x:c r="J10" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K10" s="3" t="str">
         <x:v>P1</x:v>
@@ -1086,7 +1086,7 @@
         <x:v>CheckoutController POST draft, draft-form</x:v>
       </x:c>
       <x:c r="P10" s="3" t="str">
-        <x:v>CheckoutControllerTests; CheckoutDraftServiceTests</x:v>
+        <x:v>CheckoutControllerTests; CheckoutDraftServiceTests | Current suite: dotnet test Maliev.Web.slnx --verbosity minimal passed 235/235 on 2026-06-23.</x:v>
       </x:c>
       <x:c r="Q10" s="3" t="str">
         <x:v>Web BFF, Checkout/Order services</x:v>
@@ -1124,16 +1124,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G11" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Web suite passed 2026-06-23</x:v>
       </x:c>
       <x:c r="H11" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Web automated suite.</x:v>
       </x:c>
       <x:c r="I11" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed from current Web automated suite.</x:v>
       </x:c>
       <x:c r="J11" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K11" s="3" t="str">
         <x:v>P1</x:v>
@@ -1151,7 +1151,7 @@
         <x:v>ShippingController GET couriers, POST rates</x:v>
       </x:c>
       <x:c r="P11" s="3" t="str">
-        <x:v>ShippingControllerTests</x:v>
+        <x:v>ShippingControllerTests | Current suite: dotnet test Maliev.Web.slnx --verbosity minimal passed 235/235 on 2026-06-23.</x:v>
       </x:c>
       <x:c r="Q11" s="3" t="str">
         <x:v>Web BFF, DeliveryService</x:v>
@@ -1189,16 +1189,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G12" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Web suite passed 2026-06-23</x:v>
       </x:c>
       <x:c r="H12" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Web automated suite.</x:v>
       </x:c>
       <x:c r="I12" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed from current Web automated suite.</x:v>
       </x:c>
       <x:c r="J12" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K12" s="3" t="str">
         <x:v>P2</x:v>
@@ -1216,7 +1216,7 @@
         <x:v>ShippingController GET tracking/{trackingCode}</x:v>
       </x:c>
       <x:c r="P12" s="3" t="str">
-        <x:v>ShippingControllerTests</x:v>
+        <x:v>ShippingControllerTests | Current suite: dotnet test Maliev.Web.slnx --verbosity minimal passed 235/235 on 2026-06-23.</x:v>
       </x:c>
       <x:c r="Q12" s="3" t="str">
         <x:v>Web BFF, DeliveryService</x:v>
@@ -1254,16 +1254,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G13" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Web suite passed 2026-06-23</x:v>
       </x:c>
       <x:c r="H13" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Web automated suite.</x:v>
       </x:c>
       <x:c r="I13" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed from current Web automated suite.</x:v>
       </x:c>
       <x:c r="J13" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K13" s="3" t="str">
         <x:v>P0</x:v>
@@ -1281,7 +1281,7 @@
         <x:v>QuoteController reference-data, estimate, uploads/resumable, complete, handoff-token, analysis-status</x:v>
       </x:c>
       <x:c r="P13" s="3" t="str">
-        <x:v>WebBffEndpointTests Quote*</x:v>
+        <x:v>WebBffEndpointTests Quote* | Current suite: dotnet test Maliev.Web.slnx --verbosity minimal passed 235/235 on 2026-06-23.</x:v>
       </x:c>
       <x:c r="Q13" s="3" t="str">
         <x:v>Web BFF, QuoteEngine, Storage, Geometry/Pricing</x:v>
@@ -1319,16 +1319,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G14" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Web suite passed 2026-06-23</x:v>
       </x:c>
       <x:c r="H14" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Web automated suite.</x:v>
       </x:c>
       <x:c r="I14" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed from current Web automated suite.</x:v>
       </x:c>
       <x:c r="J14" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K14" s="3" t="str">
         <x:v>P0</x:v>
@@ -1346,7 +1346,7 @@
         <x:v>QuoteController uploads/resumable, PUT chunk, complete, analysis-status</x:v>
       </x:c>
       <x:c r="P14" s="3" t="str">
-        <x:v>WebBffEndpointTests QuoteUpload*</x:v>
+        <x:v>WebBffEndpointTests QuoteUpload* | Current suite: dotnet test Maliev.Web.slnx --verbosity minimal passed 235/235 on 2026-06-23.</x:v>
       </x:c>
       <x:c r="Q14" s="3" t="str">
         <x:v>Web BFF, Storage, Geometry/analysis</x:v>
@@ -1384,16 +1384,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G15" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Web suite passed 2026-06-23</x:v>
       </x:c>
       <x:c r="H15" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Web automated suite.</x:v>
       </x:c>
       <x:c r="I15" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed from current Web automated suite.</x:v>
       </x:c>
       <x:c r="J15" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K15" s="3" t="str">
         <x:v>P0</x:v>
@@ -1411,7 +1411,7 @@
         <x:v>QuoteController POST estimate</x:v>
       </x:c>
       <x:c r="P15" s="3" t="str">
-        <x:v>WebBffEndpointTests QuoteEstimate</x:v>
+        <x:v>WebBffEndpointTests QuoteEstimate | Current suite: dotnet test Maliev.Web.slnx --verbosity minimal passed 235/235 on 2026-06-23.</x:v>
       </x:c>
       <x:c r="Q15" s="3" t="str">
         <x:v>Web BFF, Pricing/Quote services</x:v>
@@ -1449,16 +1449,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G16" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Web suite passed 2026-06-23</x:v>
       </x:c>
       <x:c r="H16" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Web automated suite.</x:v>
       </x:c>
       <x:c r="I16" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed from current Web automated suite.</x:v>
       </x:c>
       <x:c r="J16" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K16" s="3" t="str">
         <x:v>P1</x:v>
@@ -1476,7 +1476,7 @@
         <x:v>ChatbotController POST sessions/messages</x:v>
       </x:c>
       <x:c r="P16" s="3" t="str">
-        <x:v>CustomerChatbotBoundaryTests; WebBffEndpointTests Chatbot*</x:v>
+        <x:v>CustomerChatbotBoundaryTests; WebBffEndpointTests Chatbot* | Current suite: dotnet test Maliev.Web.slnx --verbosity minimal passed 235/235 on 2026-06-23.</x:v>
       </x:c>
       <x:c r="Q16" s="3" t="str">
         <x:v>Web BFF, Chatbot/agent backend, Auth</x:v>
@@ -1514,16 +1514,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G17" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Web suite passed 2026-06-23</x:v>
       </x:c>
       <x:c r="H17" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Web automated suite.</x:v>
       </x:c>
       <x:c r="I17" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed from current Web automated suite.</x:v>
       </x:c>
       <x:c r="J17" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K17" s="3" t="str">
         <x:v>P0</x:v>
@@ -1541,7 +1541,7 @@
         <x:v>AuthController google, callback, sign-in/email, sign-up/email, passkey-sign-in</x:v>
       </x:c>
       <x:c r="P17" s="3" t="str">
-        <x:v>AccountControllerBoundaryTests; WebBffEndpointTests</x:v>
+        <x:v>AccountControllerBoundaryTests; WebBffEndpointTests | Current suite: dotnet test Maliev.Web.slnx --verbosity minimal passed 235/235 on 2026-06-23.</x:v>
       </x:c>
       <x:c r="Q17" s="3" t="str">
         <x:v>Web BFF, AuthService, CustomerService</x:v>
@@ -1579,16 +1579,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G18" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Web suite passed 2026-06-23</x:v>
       </x:c>
       <x:c r="H18" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Web automated suite.</x:v>
       </x:c>
       <x:c r="I18" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed from current Web automated suite.</x:v>
       </x:c>
       <x:c r="J18" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K18" s="3" t="str">
         <x:v>P1</x:v>
@@ -1606,7 +1606,7 @@
         <x:v>AuthController forgot-password/request, reset-password/confirm</x:v>
       </x:c>
       <x:c r="P18" s="3" t="str">
-        <x:v>WebBffEndpointTests Auth where present</x:v>
+        <x:v>WebBffEndpointTests Auth where present | Current suite: dotnet test Maliev.Web.slnx --verbosity minimal passed 235/235 on 2026-06-23.</x:v>
       </x:c>
       <x:c r="Q18" s="3" t="str">
         <x:v>Web BFF, AuthService</x:v>
@@ -1644,16 +1644,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G19" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Web suite passed 2026-06-23</x:v>
       </x:c>
       <x:c r="H19" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Web automated suite.</x:v>
       </x:c>
       <x:c r="I19" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed from current Web automated suite.</x:v>
       </x:c>
       <x:c r="J19" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K19" s="3" t="str">
         <x:v>P1</x:v>
@@ -1671,7 +1671,7 @@
         <x:v>AuthController verify-email, refresh-claims, resend-verification</x:v>
       </x:c>
       <x:c r="P19" s="3" t="str">
-        <x:v>AccountControllerBoundaryTests</x:v>
+        <x:v>AccountControllerBoundaryTests | Current suite: dotnet test Maliev.Web.slnx --verbosity minimal passed 235/235 on 2026-06-23.</x:v>
       </x:c>
       <x:c r="Q19" s="3" t="str">
         <x:v>Web BFF, AuthService</x:v>
@@ -1709,16 +1709,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G20" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Web suite passed 2026-06-23</x:v>
       </x:c>
       <x:c r="H20" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Web automated suite.</x:v>
       </x:c>
       <x:c r="I20" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed from current Web automated suite.</x:v>
       </x:c>
       <x:c r="J20" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K20" s="3" t="str">
         <x:v>P1</x:v>
@@ -1736,7 +1736,7 @@
         <x:v>AccountController session, profile GET/PATCH</x:v>
       </x:c>
       <x:c r="P20" s="3" t="str">
-        <x:v>AccountControllerBoundaryTests; WebBffEndpointTests Account</x:v>
+        <x:v>AccountControllerBoundaryTests; WebBffEndpointTests Account | Current suite: dotnet test Maliev.Web.slnx --verbosity minimal passed 235/235 on 2026-06-23.</x:v>
       </x:c>
       <x:c r="Q20" s="3" t="str">
         <x:v>Web BFF, CustomerService, AuthService</x:v>
@@ -1774,16 +1774,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G21" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Web suite passed 2026-06-23</x:v>
       </x:c>
       <x:c r="H21" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Web automated suite.</x:v>
       </x:c>
       <x:c r="I21" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed from current Web automated suite.</x:v>
       </x:c>
       <x:c r="J21" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K21" s="3" t="str">
         <x:v>P2</x:v>
@@ -1801,7 +1801,7 @@
         <x:v>AccountController email/change, email/resend-change</x:v>
       </x:c>
       <x:c r="P21" s="3" t="str">
-        <x:v>AccountControllerBoundaryTests</x:v>
+        <x:v>AccountControllerBoundaryTests | Current suite: dotnet test Maliev.Web.slnx --verbosity minimal passed 235/235 on 2026-06-23.</x:v>
       </x:c>
       <x:c r="Q21" s="3" t="str">
         <x:v>Web BFF, AuthService</x:v>
@@ -1839,16 +1839,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G22" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Web suite passed 2026-06-23</x:v>
       </x:c>
       <x:c r="H22" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Web automated suite.</x:v>
       </x:c>
       <x:c r="I22" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed from current Web automated suite.</x:v>
       </x:c>
       <x:c r="J22" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K22" s="3" t="str">
         <x:v>P1</x:v>
@@ -1866,7 +1866,7 @@
         <x:v>AccountController addresses GET/POST/PATCH/DELETE</x:v>
       </x:c>
       <x:c r="P22" s="3" t="str">
-        <x:v>AccountAddressGoogleSourceTests; AccountControllerBoundaryTests</x:v>
+        <x:v>AccountAddressGoogleSourceTests; AccountControllerBoundaryTests | Current suite: dotnet test Maliev.Web.slnx --verbosity minimal passed 235/235 on 2026-06-23.</x:v>
       </x:c>
       <x:c r="Q22" s="3" t="str">
         <x:v>Web BFF, CustomerService</x:v>
@@ -1904,16 +1904,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G23" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Web suite passed 2026-06-23</x:v>
       </x:c>
       <x:c r="H23" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Web automated suite.</x:v>
       </x:c>
       <x:c r="I23" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed from current Web automated suite.</x:v>
       </x:c>
       <x:c r="J23" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K23" s="3" t="str">
         <x:v>P2</x:v>
@@ -1931,7 +1931,7 @@
         <x:v>AddressController google-config, static-map, countries, thai-locations</x:v>
       </x:c>
       <x:c r="P23" s="3" t="str">
-        <x:v>AccountAddressGoogleSourceTests</x:v>
+        <x:v>AccountAddressGoogleSourceTests | Current suite: dotnet test Maliev.Web.slnx --verbosity minimal passed 235/235 on 2026-06-23.</x:v>
       </x:c>
       <x:c r="Q23" s="3" t="str">
         <x:v>Web BFF, Country/Registry/Google config</x:v>
@@ -1969,16 +1969,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G24" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Web suite passed 2026-06-23</x:v>
       </x:c>
       <x:c r="H24" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Web automated suite.</x:v>
       </x:c>
       <x:c r="I24" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed from current Web automated suite.</x:v>
       </x:c>
       <x:c r="J24" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K24" s="3" t="str">
         <x:v>P1</x:v>
@@ -1996,7 +1996,7 @@
         <x:v>AccountController orders</x:v>
       </x:c>
       <x:c r="P24" s="3" t="str">
-        <x:v>WebBffEndpointTests AccountOrders</x:v>
+        <x:v>WebBffEndpointTests AccountOrders | Current suite: dotnet test Maliev.Web.slnx --verbosity minimal passed 235/235 on 2026-06-23.</x:v>
       </x:c>
       <x:c r="Q24" s="3" t="str">
         <x:v>Web BFF, OrderService</x:v>
@@ -2034,16 +2034,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G25" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Web suite passed 2026-06-23</x:v>
       </x:c>
       <x:c r="H25" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Web automated suite.</x:v>
       </x:c>
       <x:c r="I25" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed from current Web automated suite.</x:v>
       </x:c>
       <x:c r="J25" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K25" s="3" t="str">
         <x:v>P2</x:v>
@@ -2061,7 +2061,7 @@
         <x:v>AccountController company-search</x:v>
       </x:c>
       <x:c r="P25" s="3" t="str">
-        <x:v>AccountControllerBoundaryTests</x:v>
+        <x:v>AccountControllerBoundaryTests | Current suite: dotnet test Maliev.Web.slnx --verbosity minimal passed 235/235 on 2026-06-23.</x:v>
       </x:c>
       <x:c r="Q25" s="3" t="str">
         <x:v>Web BFF, RegistryService, CustomerService</x:v>
@@ -2099,16 +2099,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G26" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Web suite passed 2026-06-23</x:v>
       </x:c>
       <x:c r="H26" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Web automated suite.</x:v>
       </x:c>
       <x:c r="I26" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed from current Web automated suite.</x:v>
       </x:c>
       <x:c r="J26" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K26" s="3" t="str">
         <x:v>P2</x:v>
@@ -2126,7 +2126,7 @@
         <x:v>PreferencesController POST culture</x:v>
       </x:c>
       <x:c r="P26" s="3" t="str">
-        <x:v>WebBffEndpointTests Preferences</x:v>
+        <x:v>WebBffEndpointTests Preferences | Current suite: dotnet test Maliev.Web.slnx --verbosity minimal passed 235/235 on 2026-06-23.</x:v>
       </x:c>
       <x:c r="Q26" s="3" t="str">
         <x:v>Web BFF</x:v>
@@ -2164,16 +2164,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G27" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Web suite passed 2026-06-23</x:v>
       </x:c>
       <x:c r="H27" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Web automated suite.</x:v>
       </x:c>
       <x:c r="I27" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed from current Web automated suite.</x:v>
       </x:c>
       <x:c r="J27" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K27" s="3" t="str">
         <x:v>P1</x:v>
@@ -2191,7 +2191,7 @@
         <x:v>ContactController POST messages</x:v>
       </x:c>
       <x:c r="P27" s="3" t="str">
-        <x:v>WebBffEndpointTests Contact</x:v>
+        <x:v>WebBffEndpointTests Contact | Current suite: dotnet test Maliev.Web.slnx --verbosity minimal passed 235/235 on 2026-06-23.</x:v>
       </x:c>
       <x:c r="Q27" s="3" t="str">
         <x:v>Web BFF, Contact/customer workflow</x:v>
@@ -2229,16 +2229,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G28" s="3" t="str">
-        <x:v>Focused automated source tests passed 2026-06-23; browser runtime pending</x:v>
+        <x:v>Automated Web suite passed 2026-06-23; browser runtime pending</x:v>
       </x:c>
       <x:c r="H28" s="3" t="str">
-        <x:v>No behavior error observed in focused source tests.</x:v>
+        <x:v>No behavior error observed in current Web automated suite.</x:v>
       </x:c>
       <x:c r="I28" s="3" t="str">
-        <x:v>No fix needed from focused tests.</x:v>
+        <x:v>No fix needed from current Web automated suite.</x:v>
       </x:c>
       <x:c r="J28" s="3" t="str">
-        <x:v>Pending browser/runtime verification.</x:v>
+        <x:v>Current automated suite passed; browser/runtime verification pending.</x:v>
       </x:c>
       <x:c r="K28" s="3" t="str">
         <x:v>P2</x:v>
@@ -2256,7 +2256,7 @@
         <x:v>BlogController for ebook PDF only</x:v>
       </x:c>
       <x:c r="P28" s="3" t="str">
-        <x:v>dotnet test Maliev.Web.slnx --filter HeroLayoutSourceTests.StaticPagesCoverCustomerRoutesAndContactBoundary passed as part of 4/4 focused Web run on 2026-06-23.</x:v>
+        <x:v>dotnet test Maliev.Web.slnx --filter HeroLayoutSourceTests.StaticPagesCoverCustomerRoutesAndContactBoundary passed as part of 4/4 focused Web run on 2026-06-23. | Current suite: dotnet test Maliev.Web.slnx --verbosity minimal passed 235/235 on 2026-06-23.</x:v>
       </x:c>
       <x:c r="Q28" s="3" t="str">
         <x:v>Web client, Content</x:v>
@@ -2294,16 +2294,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G29" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Web suite passed 2026-06-23</x:v>
       </x:c>
       <x:c r="H29" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Web automated suite.</x:v>
       </x:c>
       <x:c r="I29" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed from current Web automated suite.</x:v>
       </x:c>
       <x:c r="J29" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K29" s="3" t="str">
         <x:v>P2</x:v>
@@ -2321,7 +2321,7 @@
         <x:v>BlogController GET {slug}/ebook.pdf</x:v>
       </x:c>
       <x:c r="P29" s="3" t="str">
-        <x:v>WebBffEndpointTests Blog</x:v>
+        <x:v>WebBffEndpointTests Blog | Current suite: dotnet test Maliev.Web.slnx --verbosity minimal passed 235/235 on 2026-06-23.</x:v>
       </x:c>
       <x:c r="Q29" s="3" t="str">
         <x:v>Web BFF, PDF service/content</x:v>
@@ -2359,16 +2359,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G30" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Web suite passed 2026-06-23</x:v>
       </x:c>
       <x:c r="H30" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Web automated suite.</x:v>
       </x:c>
       <x:c r="I30" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed from current Web automated suite.</x:v>
       </x:c>
       <x:c r="J30" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K30" s="3" t="str">
         <x:v>P2</x:v>
@@ -2386,7 +2386,7 @@
         <x:v>SeoController GET robots/sitemap</x:v>
       </x:c>
       <x:c r="P30" s="3" t="str">
-        <x:v>WebBffEndpointTests Seo</x:v>
+        <x:v>WebBffEndpointTests Seo | Current suite: dotnet test Maliev.Web.slnx --verbosity minimal passed 235/235 on 2026-06-23.</x:v>
       </x:c>
       <x:c r="Q30" s="3" t="str">
         <x:v>Web BFF</x:v>
@@ -2407,7 +2407,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb4273a98aa13480a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b7fedd2906d46de"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5367,7 +5367,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfa82a720634c4d56"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc3e48ec792d04b21"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7937,7 +7937,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6570a1d1c6d044cd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e6da95d07ed4e68"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/maliev-feature-user-story-status.xlsx
+++ b/docs/maliev-feature-user-story-status.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Ra98dcfe6fa48452c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="Rff19ee7921e742a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R1f8cd9d0fd924061"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="R525223cc4eea4a01"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rec5d5323eb5d4efc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="R44ee5cd5ca9141cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="Rdbfe439a58d546f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="R3cf2b7afc2d2492b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2407,7 +2407,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b7fedd2906d46de"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4a0e07831f964eb5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2524,16 +2524,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G2" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Intranet suite passed 2026-06-23 after UX fix</x:v>
       </x:c>
       <x:c r="H2" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="I2" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="J2" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K2" s="3" t="str">
         <x:v>P0</x:v>
@@ -2551,7 +2551,7 @@
         <x:v>AuthController user/session endpoints</x:v>
       </x:c>
       <x:c r="P2" s="3" t="str">
-        <x:v>Navigation/source tests where present</x:v>
+        <x:v>Navigation/source tests where present | Current suite: dotnet test Maliev.Intranet.slnx --verbosity minimal passed 1143/1150 with 7 skipped on 2026-06-23 after fix. Initial full run failed 1/1150 on ModuleRegressionSourceTests.ClientTextInputs_UpdateOnInputInsteadOfBlur.</x:v>
       </x:c>
       <x:c r="Q2" s="3" t="str">
         <x:v>Intranet client, BFF, Auth/IAM</x:v>
@@ -2589,16 +2589,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G3" s="3" t="str">
-        <x:v>Focused automated component/controller tests passed 2026-06-23; browser runtime pending</x:v>
+        <x:v>Automated Intranet suite passed 2026-06-23 after UX fix; browser runtime pending</x:v>
       </x:c>
       <x:c r="H3" s="3" t="str">
-        <x:v>No behavior error observed in focused tests. Initial concurrent repo run hit shared ServiceDefaults obj lock; serialized rerun passed.</x:v>
+        <x:v>No behavior error observed in current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="I3" s="3" t="str">
-        <x:v>Test orchestration adjusted: run Web/Intranet dotnet tests serially when they share ServiceDefaults build outputs.</x:v>
+        <x:v>No fix needed for this story from current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="J3" s="3" t="str">
-        <x:v>Serialized focused retest passed 15/15; browser/runtime verification pending.</x:v>
+        <x:v>Current automated suite passed; browser/runtime verification pending.</x:v>
       </x:c>
       <x:c r="K3" s="3" t="str">
         <x:v>P1</x:v>
@@ -2616,7 +2616,7 @@
         <x:v>DashboardController GET, action-items</x:v>
       </x:c>
       <x:c r="P3" s="3" t="str">
-        <x:v>dotnet test Maliev.Intranet.slnx --filter Phase3DashboardTests|DashboardControllerTests|QuickControllerTests.Dashboard_Get_ReturnsOk passed 15/15 on 2026-06-23 after serialized rerun.</x:v>
+        <x:v>dotnet test Maliev.Intranet.slnx --filter Phase3DashboardTests|DashboardControllerTests|QuickControllerTests.Dashboard_Get_ReturnsOk passed 15/15 on 2026-06-23 after serialized rerun. | Current suite: dotnet test Maliev.Intranet.slnx --verbosity minimal passed 1143/1150 with 7 skipped on 2026-06-23 after fix. Initial full run failed 1/1150 on ModuleRegressionSourceTests.ClientTextInputs_UpdateOnInputInsteadOfBlur.</x:v>
       </x:c>
       <x:c r="Q3" s="3" t="str">
         <x:v>Intranet BFF, operational services</x:v>
@@ -2654,16 +2654,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G4" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Intranet suite passed 2026-06-23 after UX fix</x:v>
       </x:c>
       <x:c r="H4" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="I4" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="J4" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K4" s="3" t="str">
         <x:v>P1</x:v>
@@ -2681,7 +2681,7 @@
         <x:v>SearchController GET</x:v>
       </x:c>
       <x:c r="P4" s="3" t="str">
-        <x:v>Search/source tests where present</x:v>
+        <x:v>Search/source tests where present | Current suite: dotnet test Maliev.Intranet.slnx --verbosity minimal passed 1143/1150 with 7 skipped on 2026-06-23 after fix. Initial full run failed 1/1150 on ModuleRegressionSourceTests.ClientTextInputs_UpdateOnInputInsteadOfBlur.</x:v>
       </x:c>
       <x:c r="Q4" s="3" t="str">
         <x:v>Intranet BFF, SearchService</x:v>
@@ -2719,16 +2719,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G5" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Intranet suite passed 2026-06-23 after UX fix</x:v>
       </x:c>
       <x:c r="H5" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="I5" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="J5" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K5" s="3" t="str">
         <x:v>P1</x:v>
@@ -2746,7 +2746,7 @@
         <x:v>Chatbot/admin instruction endpoints where configured</x:v>
       </x:c>
       <x:c r="P5" s="3" t="str">
-        <x:v>ChatDrawer source tests where present</x:v>
+        <x:v>ChatDrawer source tests where present | Current suite: dotnet test Maliev.Intranet.slnx --verbosity minimal passed 1143/1150 with 7 skipped on 2026-06-23 after fix. Initial full run failed 1/1150 on ModuleRegressionSourceTests.ClientTextInputs_UpdateOnInputInsteadOfBlur.</x:v>
       </x:c>
       <x:c r="Q5" s="3" t="str">
         <x:v>Intranet client, Chatbot/agent service</x:v>
@@ -2784,16 +2784,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G6" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Intranet suite passed 2026-06-23 after UX fix</x:v>
       </x:c>
       <x:c r="H6" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="I6" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="J6" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K6" s="3" t="str">
         <x:v>P1</x:v>
@@ -2811,7 +2811,7 @@
         <x:v>AlertsController GET, read, read-all</x:v>
       </x:c>
       <x:c r="P6" s="3" t="str">
-        <x:v>NotificationBell tests where present</x:v>
+        <x:v>NotificationBell tests where present | Current suite: dotnet test Maliev.Intranet.slnx --verbosity minimal passed 1143/1150 with 7 skipped on 2026-06-23 after fix. Initial full run failed 1/1150 on ModuleRegressionSourceTests.ClientTextInputs_UpdateOnInputInsteadOfBlur.</x:v>
       </x:c>
       <x:c r="Q6" s="3" t="str">
         <x:v>Intranet BFF, Alerts/Notification data</x:v>
@@ -2849,16 +2849,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G7" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Intranet suite passed 2026-06-23 after UX fix</x:v>
       </x:c>
       <x:c r="H7" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="I7" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="J7" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K7" s="3" t="str">
         <x:v>P0</x:v>
@@ -2876,7 +2876,7 @@
         <x:v>ProjectsController GET/list/detail/update/delete/notes/duplicate/thumbnail</x:v>
       </x:c>
       <x:c r="P7" s="3" t="str">
-        <x:v>ProjectsControllerTests</x:v>
+        <x:v>ProjectsControllerTests | Current suite: dotnet test Maliev.Intranet.slnx --verbosity minimal passed 1143/1150 with 7 skipped on 2026-06-23 after fix. Initial full run failed 1/1150 on ModuleRegressionSourceTests.ClientTextInputs_UpdateOnInputInsteadOfBlur.</x:v>
       </x:c>
       <x:c r="Q7" s="3" t="str">
         <x:v>Intranet BFF, Project/Quote services, Storage</x:v>
@@ -2914,16 +2914,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G8" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Intranet suite passed 2026-06-23 after UX fix</x:v>
       </x:c>
       <x:c r="H8" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="I8" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="J8" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K8" s="3" t="str">
         <x:v>P0</x:v>
@@ -2941,7 +2941,7 @@
         <x:v>UploadsController upload/batch/resumable/complete/chunk/status/viewer-url/preview-url/migrate-project</x:v>
       </x:c>
       <x:c r="P8" s="3" t="str">
-        <x:v>ProjectNewAutoSaveTests; UploadsControllerResumableTests</x:v>
+        <x:v>ProjectNewAutoSaveTests; UploadsControllerResumableTests | Current suite: dotnet test Maliev.Intranet.slnx --verbosity minimal passed 1143/1150 with 7 skipped on 2026-06-23 after fix. Initial full run failed 1/1150 on ModuleRegressionSourceTests.ClientTextInputs_UpdateOnInputInsteadOfBlur.</x:v>
       </x:c>
       <x:c r="Q8" s="3" t="str">
         <x:v>Intranet BFF, Storage, GeometryService, UploadService</x:v>
@@ -2979,16 +2979,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G9" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Intranet suite passed 2026-06-23 after UX fix</x:v>
       </x:c>
       <x:c r="H9" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="I9" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="J9" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K9" s="3" t="str">
         <x:v>P0</x:v>
@@ -3006,7 +3006,7 @@
         <x:v>ProjectsController POST/PUT project endpoints</x:v>
       </x:c>
       <x:c r="P9" s="3" t="str">
-        <x:v>ProjectNewAutoSaveTests</x:v>
+        <x:v>ProjectNewAutoSaveTests | Current suite: dotnet test Maliev.Intranet.slnx --verbosity minimal passed 1143/1150 with 7 skipped on 2026-06-23 after fix. Initial full run failed 1/1150 on ModuleRegressionSourceTests.ClientTextInputs_UpdateOnInputInsteadOfBlur.</x:v>
       </x:c>
       <x:c r="Q9" s="3" t="str">
         <x:v>Intranet client/BFF, Project service</x:v>
@@ -3044,16 +3044,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G10" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Failed current Intranet suite, fixed, and retested passed 2026-06-23</x:v>
       </x:c>
       <x:c r="H10" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>Initial full Intranet suite failed 1/1150: shipping text/numeric fields in PartConfigSidebar and QuoteSummaryBar updated on blur instead of on input.</x:v>
       </x:c>
       <x:c r="I10" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Fixed in Maliev.Intranet commit bb9a51c by adding Immediate="true" to the reported shipping text/numeric fields.</x:v>
       </x:c>
       <x:c r="J10" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Retested: regression 1/1 passed, impacted focused set 138/138 passed, full Intranet suite 1143 passed / 7 skipped / 0 failed.</x:v>
       </x:c>
       <x:c r="K10" s="3" t="str">
         <x:v>P0</x:v>
@@ -3071,7 +3071,7 @@
         <x:v>ProjectsController parts create/update/delete; ManufacturingCatalogController processes/materials/finishes/tolerances/config-options</x:v>
       </x:c>
       <x:c r="P10" s="3" t="str">
-        <x:v>PartConfigSidebarTests; ProjectNewAutoSaveTests</x:v>
+        <x:v>PartConfigSidebarTests; ProjectNewAutoSaveTests | Current suite: dotnet test Maliev.Intranet.slnx --verbosity minimal passed 1143/1150 with 7 skipped on 2026-06-23 after fix. Initial full run failed 1/1150 on ModuleRegressionSourceTests.ClientTextInputs_UpdateOnInputInsteadOfBlur. | Fix verification: ClientTextInputs_UpdateOnInputInsteadOfBlur passed 1/1; PartConfigSidebar/QuoteSummaryBar/ModuleRegressionSourceTests focused set passed 138/138.</x:v>
       </x:c>
       <x:c r="Q10" s="3" t="str">
         <x:v>Intranet BFF, MaterialService, PricingService</x:v>
@@ -3083,7 +3083,7 @@
         <x:v>Needs process-specific UX browser pass</x:v>
       </x:c>
       <x:c r="T10" s="3" t="str">
-        <x:v>ProjectsController.cs:298-365; ManufacturingCatalogController.cs:17-107</x:v>
+        <x:v>ProjectsController.cs:298-365; ManufacturingCatalogController.cs:17-107; PartConfigSidebar.razor:1129-1139; QuoteSummaryBar.razor:144-154</x:v>
       </x:c>
       <x:c r="U10" s="3" t="str">
         <x:v>2026-06-23</x:v>
@@ -3109,16 +3109,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G11" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Intranet suite passed 2026-06-23 after UX fix</x:v>
       </x:c>
       <x:c r="H11" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="I11" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="J11" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K11" s="3" t="str">
         <x:v>P0</x:v>
@@ -3136,7 +3136,7 @@
         <x:v>GeometryController manifest/assets/telemetry/dfm</x:v>
       </x:c>
       <x:c r="P11" s="3" t="str">
-        <x:v>GeometryControllerTests; Dfm* tests</x:v>
+        <x:v>GeometryControllerTests; Dfm* tests | Current suite: dotnet test Maliev.Intranet.slnx --verbosity minimal passed 1143/1150 with 7 skipped on 2026-06-23 after fix. Initial full run failed 1/1150 on ModuleRegressionSourceTests.ClientTextInputs_UpdateOnInputInsteadOfBlur.</x:v>
       </x:c>
       <x:c r="Q11" s="3" t="str">
         <x:v>Intranet BFF, GeometryService, browser runtime</x:v>
@@ -3174,16 +3174,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G12" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Intranet suite passed 2026-06-23 after UX fix</x:v>
       </x:c>
       <x:c r="H12" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="I12" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="J12" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K12" s="3" t="str">
         <x:v>P0</x:v>
@@ -3201,7 +3201,7 @@
         <x:v>PricingController snapshots/calculate/accept/lead-times/bulk/finish-options</x:v>
       </x:c>
       <x:c r="P12" s="3" t="str">
-        <x:v>PricingControllerTests; QuoteSummaryBarTests</x:v>
+        <x:v>PricingControllerTests; QuoteSummaryBarTests | Current suite: dotnet test Maliev.Intranet.slnx --verbosity minimal passed 1143/1150 with 7 skipped on 2026-06-23 after fix. Initial full run failed 1/1150 on ModuleRegressionSourceTests.ClientTextInputs_UpdateOnInputInsteadOfBlur.</x:v>
       </x:c>
       <x:c r="Q12" s="3" t="str">
         <x:v>Intranet BFF, PricingService, MaterialService</x:v>
@@ -3239,16 +3239,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G13" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Failed current Intranet suite, fixed, and retested passed 2026-06-23</x:v>
       </x:c>
       <x:c r="H13" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>Initial full Intranet suite failed 1/1150: shipping text/numeric fields in PartConfigSidebar and QuoteSummaryBar updated on blur instead of on input.</x:v>
       </x:c>
       <x:c r="I13" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Fixed in Maliev.Intranet commit bb9a51c by adding Immediate="true" to the reported shipping text/numeric fields.</x:v>
       </x:c>
       <x:c r="J13" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Retested: regression 1/1 passed, impacted focused set 138/138 passed, full Intranet suite 1143 passed / 7 skipped / 0 failed.</x:v>
       </x:c>
       <x:c r="K13" s="3" t="str">
         <x:v>P0</x:v>
@@ -3266,7 +3266,7 @@
         <x:v>QuotationsController; ProjectsController generate-quotation/accept-quotation</x:v>
       </x:c>
       <x:c r="P13" s="3" t="str">
-        <x:v>ProjectsControllerTests; quotation/PDF tests</x:v>
+        <x:v>ProjectsControllerTests; quotation/PDF tests | Current suite: dotnet test Maliev.Intranet.slnx --verbosity minimal passed 1143/1150 with 7 skipped on 2026-06-23 after fix. Initial full run failed 1/1150 on ModuleRegressionSourceTests.ClientTextInputs_UpdateOnInputInsteadOfBlur. | Fix verification: ClientTextInputs_UpdateOnInputInsteadOfBlur passed 1/1; PartConfigSidebar/QuoteSummaryBar/ModuleRegressionSourceTests focused set passed 138/138.</x:v>
       </x:c>
       <x:c r="Q13" s="3" t="str">
         <x:v>Intranet BFF, QuotationService, PdfService, Storage</x:v>
@@ -3278,7 +3278,7 @@
         <x:v>Needs PDF visual regression pass</x:v>
       </x:c>
       <x:c r="T13" s="3" t="str">
-        <x:v>QuotationsController.cs:20-346; ProjectsController.cs:383,513</x:v>
+        <x:v>QuotationsController.cs:20-346; ProjectsController.cs:383,513; PartConfigSidebar.razor:1129-1139; QuoteSummaryBar.razor:144-154</x:v>
       </x:c>
       <x:c r="U13" s="3" t="str">
         <x:v>2026-06-23</x:v>
@@ -3304,16 +3304,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G14" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Intranet suite passed 2026-06-23 after UX fix</x:v>
       </x:c>
       <x:c r="H14" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="I14" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="J14" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K14" s="3" t="str">
         <x:v>P1</x:v>
@@ -3331,7 +3331,7 @@
         <x:v>ProjectsController production-plan, planning-hold CRUD, routing</x:v>
       </x:c>
       <x:c r="P14" s="3" t="str">
-        <x:v>ProjectsControllerTests</x:v>
+        <x:v>ProjectsControllerTests | Current suite: dotnet test Maliev.Intranet.slnx --verbosity minimal passed 1143/1150 with 7 skipped on 2026-06-23 after fix. Initial full run failed 1/1150 on ModuleRegressionSourceTests.ClientTextInputs_UpdateOnInputInsteadOfBlur.</x:v>
       </x:c>
       <x:c r="Q14" s="3" t="str">
         <x:v>Intranet BFF, Manufacturing/Planning services</x:v>
@@ -3369,16 +3369,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G15" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Intranet suite passed 2026-06-23 after UX fix</x:v>
       </x:c>
       <x:c r="H15" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="I15" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="J15" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K15" s="3" t="str">
         <x:v>P1</x:v>
@@ -3396,7 +3396,7 @@
         <x:v>OrderLifecycleController GET; order endpoints in BFF</x:v>
       </x:c>
       <x:c r="P15" s="3" t="str">
-        <x:v>Order tests where present</x:v>
+        <x:v>Order tests where present | Current suite: dotnet test Maliev.Intranet.slnx --verbosity minimal passed 1143/1150 with 7 skipped on 2026-06-23 after fix. Initial full run failed 1/1150 on ModuleRegressionSourceTests.ClientTextInputs_UpdateOnInputInsteadOfBlur.</x:v>
       </x:c>
       <x:c r="Q15" s="3" t="str">
         <x:v>Intranet BFF, OrderService</x:v>
@@ -3434,16 +3434,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G16" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Intranet suite passed 2026-06-23 after UX fix</x:v>
       </x:c>
       <x:c r="H16" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="I16" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="J16" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K16" s="3" t="str">
         <x:v>P1</x:v>
@@ -3461,7 +3461,7 @@
         <x:v>CustomersController list/detail/payment-terms/create/update and related customer actions</x:v>
       </x:c>
       <x:c r="P16" s="3" t="str">
-        <x:v>Customer controller/source tests</x:v>
+        <x:v>Customer controller/source tests | Current suite: dotnet test Maliev.Intranet.slnx --verbosity minimal passed 1143/1150 with 7 skipped on 2026-06-23 after fix. Initial full run failed 1/1150 on ModuleRegressionSourceTests.ClientTextInputs_UpdateOnInputInsteadOfBlur.</x:v>
       </x:c>
       <x:c r="Q16" s="3" t="str">
         <x:v>Intranet BFF, CustomerService, RegistryService</x:v>
@@ -3499,16 +3499,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G17" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Intranet suite passed 2026-06-23 after UX fix</x:v>
       </x:c>
       <x:c r="H17" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="I17" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="J17" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K17" s="3" t="str">
         <x:v>P1</x:v>
@@ -3526,7 +3526,7 @@
         <x:v>CompaniesController GET/search/POST/detail/primary-contact/PATCH</x:v>
       </x:c>
       <x:c r="P17" s="3" t="str">
-        <x:v>Company/customer tests where present</x:v>
+        <x:v>Company/customer tests where present | Current suite: dotnet test Maliev.Intranet.slnx --verbosity minimal passed 1143/1150 with 7 skipped on 2026-06-23 after fix. Initial full run failed 1/1150 on ModuleRegressionSourceTests.ClientTextInputs_UpdateOnInputInsteadOfBlur.</x:v>
       </x:c>
       <x:c r="Q17" s="3" t="str">
         <x:v>Intranet BFF, CustomerService, RegistryService</x:v>
@@ -3564,16 +3564,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G18" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Intranet suite passed 2026-06-23 after UX fix</x:v>
       </x:c>
       <x:c r="H18" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="I18" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="J18" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K18" s="3" t="str">
         <x:v>P1</x:v>
@@ -3591,7 +3591,7 @@
         <x:v>Contact request controllers/services</x:v>
       </x:c>
       <x:c r="P18" s="3" t="str">
-        <x:v>Contact request tests where present</x:v>
+        <x:v>Contact request tests where present | Current suite: dotnet test Maliev.Intranet.slnx --verbosity minimal passed 1143/1150 with 7 skipped on 2026-06-23 after fix. Initial full run failed 1/1150 on ModuleRegressionSourceTests.ClientTextInputs_UpdateOnInputInsteadOfBlur.</x:v>
       </x:c>
       <x:c r="Q18" s="3" t="str">
         <x:v>Intranet BFF, Customer/Contact service</x:v>
@@ -3629,16 +3629,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G19" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Intranet suite passed 2026-06-23 after UX fix</x:v>
       </x:c>
       <x:c r="H19" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="I19" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="J19" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K19" s="3" t="str">
         <x:v>P1</x:v>
@@ -3656,7 +3656,7 @@
         <x:v>CommerceController collection/product/media endpoints</x:v>
       </x:c>
       <x:c r="P19" s="3" t="str">
-        <x:v>Commerce controller tests</x:v>
+        <x:v>Commerce controller tests | Current suite: dotnet test Maliev.Intranet.slnx --verbosity minimal passed 1143/1150 with 7 skipped on 2026-06-23 after fix. Initial full run failed 1/1150 on ModuleRegressionSourceTests.ClientTextInputs_UpdateOnInputInsteadOfBlur.</x:v>
       </x:c>
       <x:c r="Q19" s="3" t="str">
         <x:v>Intranet BFF, Catalog/Commerce, Storage</x:v>
@@ -3694,16 +3694,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G20" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Intranet suite passed 2026-06-23 after UX fix</x:v>
       </x:c>
       <x:c r="H20" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="I20" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="J20" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K20" s="3" t="str">
         <x:v>P1</x:v>
@@ -3721,7 +3721,7 @@
         <x:v>Content/chatbot admin controllers/services</x:v>
       </x:c>
       <x:c r="P20" s="3" t="str">
-        <x:v>Content tests where present</x:v>
+        <x:v>Content tests where present | Current suite: dotnet test Maliev.Intranet.slnx --verbosity minimal passed 1143/1150 with 7 skipped on 2026-06-23 after fix. Initial full run failed 1/1150 on ModuleRegressionSourceTests.ClientTextInputs_UpdateOnInputInsteadOfBlur.</x:v>
       </x:c>
       <x:c r="Q20" s="3" t="str">
         <x:v>Intranet BFF, Content/Chatbot service</x:v>
@@ -3759,16 +3759,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G21" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Intranet suite passed 2026-06-23 after UX fix</x:v>
       </x:c>
       <x:c r="H21" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="I21" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="J21" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K21" s="3" t="str">
         <x:v>P1</x:v>
@@ -3786,7 +3786,7 @@
         <x:v>AccountingController accounts-tree, journal-entries, reports, periods, reconciliation, documents</x:v>
       </x:c>
       <x:c r="P21" s="3" t="str">
-        <x:v>Accounting tests where present</x:v>
+        <x:v>Accounting tests where present | Current suite: dotnet test Maliev.Intranet.slnx --verbosity minimal passed 1143/1150 with 7 skipped on 2026-06-23 after fix. Initial full run failed 1/1150 on ModuleRegressionSourceTests.ClientTextInputs_UpdateOnInputInsteadOfBlur.</x:v>
       </x:c>
       <x:c r="Q21" s="3" t="str">
         <x:v>Intranet BFF, AccountingService, PdfService, Storage</x:v>
@@ -3824,16 +3824,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G22" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Intranet suite passed 2026-06-23 after UX fix</x:v>
       </x:c>
       <x:c r="H22" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="I22" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="J22" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K22" s="3" t="str">
         <x:v>P1</x:v>
@@ -3851,7 +3851,7 @@
         <x:v>Invoices/Billing/CreditTerms/Receipts controllers</x:v>
       </x:c>
       <x:c r="P22" s="3" t="str">
-        <x:v>Invoice tests where present</x:v>
+        <x:v>Invoice tests where present | Current suite: dotnet test Maliev.Intranet.slnx --verbosity minimal passed 1143/1150 with 7 skipped on 2026-06-23 after fix. Initial full run failed 1/1150 on ModuleRegressionSourceTests.ClientTextInputs_UpdateOnInputInsteadOfBlur.</x:v>
       </x:c>
       <x:c r="Q22" s="3" t="str">
         <x:v>Intranet BFF, InvoiceService, AccountingService</x:v>
@@ -3889,16 +3889,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G23" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Intranet suite passed 2026-06-23 after UX fix</x:v>
       </x:c>
       <x:c r="H23" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="I23" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="J23" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K23" s="3" t="str">
         <x:v>P2</x:v>
@@ -3916,7 +3916,7 @@
         <x:v>BillingNotesController GET/POST/detail; CreditTermsController GET</x:v>
       </x:c>
       <x:c r="P23" s="3" t="str">
-        <x:v>Finance tests where present</x:v>
+        <x:v>Finance tests where present | Current suite: dotnet test Maliev.Intranet.slnx --verbosity minimal passed 1143/1150 with 7 skipped on 2026-06-23 after fix. Initial full run failed 1/1150 on ModuleRegressionSourceTests.ClientTextInputs_UpdateOnInputInsteadOfBlur.</x:v>
       </x:c>
       <x:c r="Q23" s="3" t="str">
         <x:v>Intranet BFF, InvoiceService</x:v>
@@ -3954,16 +3954,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G24" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Intranet suite passed 2026-06-23 after UX fix</x:v>
       </x:c>
       <x:c r="H24" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="I24" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="J24" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K24" s="3" t="str">
         <x:v>P1</x:v>
@@ -3981,7 +3981,7 @@
         <x:v>ReceiptsController GET/detail/POST/void</x:v>
       </x:c>
       <x:c r="P24" s="3" t="str">
-        <x:v>Receipt tests where present</x:v>
+        <x:v>Receipt tests where present | Current suite: dotnet test Maliev.Intranet.slnx --verbosity minimal passed 1143/1150 with 7 skipped on 2026-06-23 after fix. Initial full run failed 1/1150 on ModuleRegressionSourceTests.ClientTextInputs_UpdateOnInputInsteadOfBlur.</x:v>
       </x:c>
       <x:c r="Q24" s="3" t="str">
         <x:v>Intranet BFF, ReceiptService</x:v>
@@ -4019,16 +4019,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G25" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Intranet suite passed 2026-06-23 after UX fix</x:v>
       </x:c>
       <x:c r="H25" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="I25" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="J25" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K25" s="3" t="str">
         <x:v>P1</x:v>
@@ -4046,7 +4046,7 @@
         <x:v>DeliveryNotesController endpoints</x:v>
       </x:c>
       <x:c r="P25" s="3" t="str">
-        <x:v>Delivery note tests where present</x:v>
+        <x:v>Delivery note tests where present | Current suite: dotnet test Maliev.Intranet.slnx --verbosity minimal passed 1143/1150 with 7 skipped on 2026-06-23 after fix. Initial full run failed 1/1150 on ModuleRegressionSourceTests.ClientTextInputs_UpdateOnInputInsteadOfBlur.</x:v>
       </x:c>
       <x:c r="Q25" s="3" t="str">
         <x:v>Intranet BFF, DeliveryService, Storage/Pdf</x:v>
@@ -4084,16 +4084,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G26" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Failed current Intranet suite, fixed, and retested passed 2026-06-23</x:v>
       </x:c>
       <x:c r="H26" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>Initial full Intranet suite failed 1/1150: shipping text/numeric fields in PartConfigSidebar and QuoteSummaryBar updated on blur instead of on input.</x:v>
       </x:c>
       <x:c r="I26" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Fixed in Maliev.Intranet commit bb9a51c by adding Immediate="true" to the reported shipping text/numeric fields.</x:v>
       </x:c>
       <x:c r="J26" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Retested: regression 1/1 passed, impacted focused set 138/138 passed, full Intranet suite 1143 passed / 7 skipped / 0 failed.</x:v>
       </x:c>
       <x:c r="K26" s="3" t="str">
         <x:v>P2</x:v>
@@ -4111,7 +4111,7 @@
         <x:v>ShippingController GET couriers, POST rates, GET tracking</x:v>
       </x:c>
       <x:c r="P26" s="3" t="str">
-        <x:v>Shipping tests where present</x:v>
+        <x:v>Shipping tests where present | Current suite: dotnet test Maliev.Intranet.slnx --verbosity minimal passed 1143/1150 with 7 skipped on 2026-06-23 after fix. Initial full run failed 1/1150 on ModuleRegressionSourceTests.ClientTextInputs_UpdateOnInputInsteadOfBlur. | Fix verification: ClientTextInputs_UpdateOnInputInsteadOfBlur passed 1/1; PartConfigSidebar/QuoteSummaryBar/ModuleRegressionSourceTests focused set passed 138/138.</x:v>
       </x:c>
       <x:c r="Q26" s="3" t="str">
         <x:v>Intranet BFF, DeliveryService</x:v>
@@ -4123,7 +4123,7 @@
         <x:v>Needs invalid carrier/tracking coverage</x:v>
       </x:c>
       <x:c r="T26" s="3" t="str">
-        <x:v>ShippingController.cs:15-70</x:v>
+        <x:v>ShippingController.cs:15-70; PartConfigSidebar.razor:1129-1139; QuoteSummaryBar.razor:144-154</x:v>
       </x:c>
       <x:c r="U26" s="3" t="str">
         <x:v>2026-06-23</x:v>
@@ -4149,16 +4149,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G27" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Intranet suite passed 2026-06-23 after UX fix</x:v>
       </x:c>
       <x:c r="H27" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="I27" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="J27" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K27" s="3" t="str">
         <x:v>P1</x:v>
@@ -4176,7 +4176,7 @@
         <x:v>ProcurementController GET/detail/POST/approve/send/receive/cancel/files/export</x:v>
       </x:c>
       <x:c r="P27" s="3" t="str">
-        <x:v>Procurement tests where present</x:v>
+        <x:v>Procurement tests where present | Current suite: dotnet test Maliev.Intranet.slnx --verbosity minimal passed 1143/1150 with 7 skipped on 2026-06-23 after fix. Initial full run failed 1/1150 on ModuleRegressionSourceTests.ClientTextInputs_UpdateOnInputInsteadOfBlur.</x:v>
       </x:c>
       <x:c r="Q27" s="3" t="str">
         <x:v>Intranet BFF, PurchaseOrderService, UploadService</x:v>
@@ -4214,16 +4214,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G28" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Intranet suite passed 2026-06-23 after UX fix</x:v>
       </x:c>
       <x:c r="H28" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="I28" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="J28" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K28" s="3" t="str">
         <x:v>P1</x:v>
@@ -4241,7 +4241,7 @@
         <x:v>SuppliersController endpoints</x:v>
       </x:c>
       <x:c r="P28" s="3" t="str">
-        <x:v>Supplier tests where present</x:v>
+        <x:v>Supplier tests where present | Current suite: dotnet test Maliev.Intranet.slnx --verbosity minimal passed 1143/1150 with 7 skipped on 2026-06-23 after fix. Initial full run failed 1/1150 on ModuleRegressionSourceTests.ClientTextInputs_UpdateOnInputInsteadOfBlur.</x:v>
       </x:c>
       <x:c r="Q28" s="3" t="str">
         <x:v>Intranet BFF, SupplierService, RegistryService, Storage</x:v>
@@ -4279,16 +4279,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G29" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Intranet suite passed 2026-06-23 after UX fix</x:v>
       </x:c>
       <x:c r="H29" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="I29" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="J29" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K29" s="3" t="str">
         <x:v>P1</x:v>
@@ -4306,7 +4306,7 @@
         <x:v>ManufacturingCatalogController material reference endpoints</x:v>
       </x:c>
       <x:c r="P29" s="3" t="str">
-        <x:v>Materials tests where present</x:v>
+        <x:v>Materials tests where present | Current suite: dotnet test Maliev.Intranet.slnx --verbosity minimal passed 1143/1150 with 7 skipped on 2026-06-23 after fix. Initial full run failed 1/1150 on ModuleRegressionSourceTests.ClientTextInputs_UpdateOnInputInsteadOfBlur.</x:v>
       </x:c>
       <x:c r="Q29" s="3" t="str">
         <x:v>Intranet BFF, MaterialService</x:v>
@@ -4344,16 +4344,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G30" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Intranet suite passed 2026-06-23 after UX fix</x:v>
       </x:c>
       <x:c r="H30" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="I30" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="J30" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K30" s="3" t="str">
         <x:v>P1</x:v>
@@ -4371,7 +4371,7 @@
         <x:v>EquipmentsController CRUD/status/notes/loans/maintenance/attachments</x:v>
       </x:c>
       <x:c r="P30" s="3" t="str">
-        <x:v>Equipment tests where present</x:v>
+        <x:v>Equipment tests where present | Current suite: dotnet test Maliev.Intranet.slnx --verbosity minimal passed 1143/1150 with 7 skipped on 2026-06-23 after fix. Initial full run failed 1/1150 on ModuleRegressionSourceTests.ClientTextInputs_UpdateOnInputInsteadOfBlur.</x:v>
       </x:c>
       <x:c r="Q30" s="3" t="str">
         <x:v>Intranet BFF, EquipmentService, Storage</x:v>
@@ -4409,16 +4409,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G31" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Intranet suite passed 2026-06-23 after UX fix</x:v>
       </x:c>
       <x:c r="H31" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="I31" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="J31" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K31" s="3" t="str">
         <x:v>P1</x:v>
@@ -4436,7 +4436,7 @@
         <x:v>InventoryController batches/items/list/detail/lookup/consume/status</x:v>
       </x:c>
       <x:c r="P31" s="3" t="str">
-        <x:v>Inventory tests where present</x:v>
+        <x:v>Inventory tests where present | Current suite: dotnet test Maliev.Intranet.slnx --verbosity minimal passed 1143/1150 with 7 skipped on 2026-06-23 after fix. Initial full run failed 1/1150 on ModuleRegressionSourceTests.ClientTextInputs_UpdateOnInputInsteadOfBlur.</x:v>
       </x:c>
       <x:c r="Q31" s="3" t="str">
         <x:v>Intranet BFF, InventoryService</x:v>
@@ -4474,16 +4474,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G32" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Intranet suite passed 2026-06-23 after UX fix</x:v>
       </x:c>
       <x:c r="H32" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="I32" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="J32" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K32" s="3" t="str">
         <x:v>P1</x:v>
@@ -4501,7 +4501,7 @@
         <x:v>Jobs/production controllers where configured</x:v>
       </x:c>
       <x:c r="P32" s="3" t="str">
-        <x:v>Production schedule tests where present</x:v>
+        <x:v>Production schedule tests where present | Current suite: dotnet test Maliev.Intranet.slnx --verbosity minimal passed 1143/1150 with 7 skipped on 2026-06-23 after fix. Initial full run failed 1/1150 on ModuleRegressionSourceTests.ClientTextInputs_UpdateOnInputInsteadOfBlur.</x:v>
       </x:c>
       <x:c r="Q32" s="3" t="str">
         <x:v>Intranet BFF, Manufacturing/Jobs services</x:v>
@@ -4539,16 +4539,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G33" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Intranet suite passed 2026-06-23 after UX fix</x:v>
       </x:c>
       <x:c r="H33" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="I33" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="J33" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K33" s="3" t="str">
         <x:v>P2</x:v>
@@ -4566,7 +4566,7 @@
         <x:v>ModelsController GET/detail/upload/viewer-url/thumbnail-url/delete</x:v>
       </x:c>
       <x:c r="P33" s="3" t="str">
-        <x:v>Model tests where present</x:v>
+        <x:v>Model tests where present | Current suite: dotnet test Maliev.Intranet.slnx --verbosity minimal passed 1143/1150 with 7 skipped on 2026-06-23 after fix. Initial full run failed 1/1150 on ModuleRegressionSourceTests.ClientTextInputs_UpdateOnInputInsteadOfBlur.</x:v>
       </x:c>
       <x:c r="Q33" s="3" t="str">
         <x:v>Intranet BFF, UploadService, Storage</x:v>
@@ -4604,16 +4604,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G34" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Intranet suite passed 2026-06-23 after UX fix</x:v>
       </x:c>
       <x:c r="H34" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="I34" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="J34" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K34" s="3" t="str">
         <x:v>P0</x:v>
@@ -4631,7 +4631,7 @@
         <x:v>IamController users/roles/permissions/bindings/invite/activity/matrix; PermissionsController</x:v>
       </x:c>
       <x:c r="P34" s="3" t="str">
-        <x:v>IAM tests where present</x:v>
+        <x:v>IAM tests where present | Current suite: dotnet test Maliev.Intranet.slnx --verbosity minimal passed 1143/1150 with 7 skipped on 2026-06-23 after fix. Initial full run failed 1/1150 on ModuleRegressionSourceTests.ClientTextInputs_UpdateOnInputInsteadOfBlur.</x:v>
       </x:c>
       <x:c r="Q34" s="3" t="str">
         <x:v>Intranet BFF, IAMService</x:v>
@@ -4669,16 +4669,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G35" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Intranet suite passed 2026-06-23 after UX fix</x:v>
       </x:c>
       <x:c r="H35" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="I35" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="J35" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K35" s="3" t="str">
         <x:v>P1</x:v>
@@ -4696,7 +4696,7 @@
         <x:v>EmployeesController endpoints</x:v>
       </x:c>
       <x:c r="P35" s="3" t="str">
-        <x:v>Employee tests where present</x:v>
+        <x:v>Employee tests where present | Current suite: dotnet test Maliev.Intranet.slnx --verbosity minimal passed 1143/1150 with 7 skipped on 2026-06-23 after fix. Initial full run failed 1/1150 on ModuleRegressionSourceTests.ClientTextInputs_UpdateOnInputInsteadOfBlur.</x:v>
       </x:c>
       <x:c r="Q35" s="3" t="str">
         <x:v>Intranet BFF, EmployeeService, IAMService</x:v>
@@ -4734,16 +4734,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G36" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Intranet suite passed 2026-06-23 after UX fix</x:v>
       </x:c>
       <x:c r="H36" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="I36" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="J36" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K36" s="3" t="str">
         <x:v>P1</x:v>
@@ -4761,7 +4761,7 @@
         <x:v>TimeOffController balances/requests/approvals/decision</x:v>
       </x:c>
       <x:c r="P36" s="3" t="str">
-        <x:v>TimeOff tests where present</x:v>
+        <x:v>TimeOff tests where present | Current suite: dotnet test Maliev.Intranet.slnx --verbosity minimal passed 1143/1150 with 7 skipped on 2026-06-23 after fix. Initial full run failed 1/1150 on ModuleRegressionSourceTests.ClientTextInputs_UpdateOnInputInsteadOfBlur.</x:v>
       </x:c>
       <x:c r="Q36" s="3" t="str">
         <x:v>Intranet BFF, LeaveService, EmployeeService</x:v>
@@ -4799,16 +4799,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G37" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Intranet suite passed 2026-06-23 after UX fix</x:v>
       </x:c>
       <x:c r="H37" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="I37" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="J37" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K37" s="3" t="str">
         <x:v>P2</x:v>
@@ -4826,7 +4826,7 @@
         <x:v>RecruitmentController jobs/stats/candidates</x:v>
       </x:c>
       <x:c r="P37" s="3" t="str">
-        <x:v>Recruitment tests where present</x:v>
+        <x:v>Recruitment tests where present | Current suite: dotnet test Maliev.Intranet.slnx --verbosity minimal passed 1143/1150 with 7 skipped on 2026-06-23 after fix. Initial full run failed 1/1150 on ModuleRegressionSourceTests.ClientTextInputs_UpdateOnInputInsteadOfBlur.</x:v>
       </x:c>
       <x:c r="Q37" s="3" t="str">
         <x:v>Intranet BFF, CareerService</x:v>
@@ -4864,16 +4864,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G38" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Intranet suite passed 2026-06-23 after UX fix</x:v>
       </x:c>
       <x:c r="H38" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="I38" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="J38" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K38" s="3" t="str">
         <x:v>P2</x:v>
@@ -4891,7 +4891,7 @@
         <x:v>CompensationController summary/benefits</x:v>
       </x:c>
       <x:c r="P38" s="3" t="str">
-        <x:v>Compensation tests where present</x:v>
+        <x:v>Compensation tests where present | Current suite: dotnet test Maliev.Intranet.slnx --verbosity minimal passed 1143/1150 with 7 skipped on 2026-06-23 after fix. Initial full run failed 1/1150 on ModuleRegressionSourceTests.ClientTextInputs_UpdateOnInputInsteadOfBlur.</x:v>
       </x:c>
       <x:c r="Q38" s="3" t="str">
         <x:v>Intranet BFF, CompensationService</x:v>
@@ -4929,16 +4929,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G39" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Intranet suite passed 2026-06-23 after UX fix</x:v>
       </x:c>
       <x:c r="H39" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="I39" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="J39" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K39" s="3" t="str">
         <x:v>P1</x:v>
@@ -4956,7 +4956,7 @@
         <x:v>ReferenceDataController countries/currencies/locations/rate endpoints</x:v>
       </x:c>
       <x:c r="P39" s="3" t="str">
-        <x:v>ReferenceData tests where present</x:v>
+        <x:v>ReferenceData tests where present | Current suite: dotnet test Maliev.Intranet.slnx --verbosity minimal passed 1143/1150 with 7 skipped on 2026-06-23 after fix. Initial full run failed 1/1150 on ModuleRegressionSourceTests.ClientTextInputs_UpdateOnInputInsteadOfBlur.</x:v>
       </x:c>
       <x:c r="Q39" s="3" t="str">
         <x:v>Intranet BFF, ReferenceData store</x:v>
@@ -4994,16 +4994,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G40" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Intranet suite passed 2026-06-23 after UX fix</x:v>
       </x:c>
       <x:c r="H40" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="I40" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="J40" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K40" s="3" t="str">
         <x:v>P1</x:v>
@@ -5021,7 +5021,7 @@
         <x:v>SystemHealthController GET, history</x:v>
       </x:c>
       <x:c r="P40" s="3" t="str">
-        <x:v>System health tests where present</x:v>
+        <x:v>System health tests where present | Current suite: dotnet test Maliev.Intranet.slnx --verbosity minimal passed 1143/1150 with 7 skipped on 2026-06-23 after fix. Initial full run failed 1/1150 on ModuleRegressionSourceTests.ClientTextInputs_UpdateOnInputInsteadOfBlur.</x:v>
       </x:c>
       <x:c r="Q40" s="3" t="str">
         <x:v>Intranet BFF, Health sampler/services</x:v>
@@ -5059,16 +5059,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G41" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Intranet suite passed 2026-06-23 after UX fix</x:v>
       </x:c>
       <x:c r="H41" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="I41" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="J41" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K41" s="3" t="str">
         <x:v>P1</x:v>
@@ -5086,7 +5086,7 @@
         <x:v>AiProcessingController health/extract/upload/link/download endpoints</x:v>
       </x:c>
       <x:c r="P41" s="3" t="str">
-        <x:v>AI processing tests where present</x:v>
+        <x:v>AI processing tests where present | Current suite: dotnet test Maliev.Intranet.slnx --verbosity minimal passed 1143/1150 with 7 skipped on 2026-06-23 after fix. Initial full run failed 1/1150 on ModuleRegressionSourceTests.ClientTextInputs_UpdateOnInputInsteadOfBlur.</x:v>
       </x:c>
       <x:c r="Q41" s="3" t="str">
         <x:v>Intranet BFF, AI service, Storage</x:v>
@@ -5124,16 +5124,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G42" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Intranet suite passed 2026-06-23 after UX fix</x:v>
       </x:c>
       <x:c r="H42" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="I42" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="J42" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K42" s="3" t="str">
         <x:v>P2</x:v>
@@ -5151,7 +5151,7 @@
         <x:v>PreferencesController GET/PUT/DELETE</x:v>
       </x:c>
       <x:c r="P42" s="3" t="str">
-        <x:v>Preferences tests where present</x:v>
+        <x:v>Preferences tests where present | Current suite: dotnet test Maliev.Intranet.slnx --verbosity minimal passed 1143/1150 with 7 skipped on 2026-06-23 after fix. Initial full run failed 1/1150 on ModuleRegressionSourceTests.ClientTextInputs_UpdateOnInputInsteadOfBlur.</x:v>
       </x:c>
       <x:c r="Q42" s="3" t="str">
         <x:v>Intranet BFF, EmployeeService</x:v>
@@ -5189,16 +5189,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G43" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Intranet suite passed 2026-06-23 after UX fix</x:v>
       </x:c>
       <x:c r="H43" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="I43" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="J43" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K43" s="3" t="str">
         <x:v>P0</x:v>
@@ -5216,7 +5216,7 @@
         <x:v>AuthController endpoints</x:v>
       </x:c>
       <x:c r="P43" s="3" t="str">
-        <x:v>Auth/login tests where present</x:v>
+        <x:v>Auth/login tests where present | Current suite: dotnet test Maliev.Intranet.slnx --verbosity minimal passed 1143/1150 with 7 skipped on 2026-06-23 after fix. Initial full run failed 1/1150 on ModuleRegressionSourceTests.ClientTextInputs_UpdateOnInputInsteadOfBlur.</x:v>
       </x:c>
       <x:c r="Q43" s="3" t="str">
         <x:v>Intranet BFF, Auth/IAM</x:v>
@@ -5254,16 +5254,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G44" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Intranet suite passed 2026-06-23 after UX fix</x:v>
       </x:c>
       <x:c r="H44" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="I44" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="J44" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K44" s="3" t="str">
         <x:v>P2</x:v>
@@ -5281,7 +5281,7 @@
         <x:v>AddressController GET google-config</x:v>
       </x:c>
       <x:c r="P44" s="3" t="str">
-        <x:v>Address source tests where present</x:v>
+        <x:v>Address source tests where present | Current suite: dotnet test Maliev.Intranet.slnx --verbosity minimal passed 1143/1150 with 7 skipped on 2026-06-23 after fix. Initial full run failed 1/1150 on ModuleRegressionSourceTests.ClientTextInputs_UpdateOnInputInsteadOfBlur.</x:v>
       </x:c>
       <x:c r="Q44" s="3" t="str">
         <x:v>Intranet BFF, configuration</x:v>
@@ -5319,16 +5319,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G45" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated Intranet suite passed 2026-06-23 after UX fix</x:v>
       </x:c>
       <x:c r="H45" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="I45" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current Intranet automated retest.</x:v>
       </x:c>
       <x:c r="J45" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K45" s="3" t="str">
         <x:v>P2</x:v>
@@ -5346,7 +5346,7 @@
         <x:v>SeedController POST customers and /api/seed/customers</x:v>
       </x:c>
       <x:c r="P45" s="3" t="str">
-        <x:v>Aspire seed tests where present</x:v>
+        <x:v>Aspire seed tests where present | Current suite: dotnet test Maliev.Intranet.slnx --verbosity minimal passed 1143/1150 with 7 skipped on 2026-06-23 after fix. Initial full run failed 1/1150 on ModuleRegressionSourceTests.ClientTextInputs_UpdateOnInputInsteadOfBlur.</x:v>
       </x:c>
       <x:c r="Q45" s="3" t="str">
         <x:v>Intranet BFF, DatabaseSeeder, CustomerService</x:v>
@@ -5367,7 +5367,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc3e48ec792d04b21"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra33d4ff753ee4748"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7937,7 +7937,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e6da95d07ed4e68"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0147e55d11a64293"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/maliev-feature-user-story-status.xlsx
+++ b/docs/maliev-feature-user-story-status.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rec5d5323eb5d4efc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="R44ee5cd5ca9141cf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="Rdbfe439a58d546f6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="R3cf2b7afc2d2492b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R4585119bd12d4a73"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="R807a60cfd8ac4152"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R22b6efa70b8e4ffe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="R290d9820c4d34c00"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2407,7 +2407,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4a0e07831f964eb5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7fbbd983b61148d6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5367,7 +5367,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra33d4ff753ee4748"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R959304072e3e4436"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5484,16 +5484,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G2" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Failed current QuoteEngine suite, fixed, and retested passed 2026-06-23</x:v>
       </x:c>
       <x:c r="H2" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>Initial QuoteEngine suite failed 3/539 because a residual sample-only workspace route/workbench still rendered old quote panel components.</x:v>
       </x:c>
       <x:c r="I2" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Fixed in Maliev.QuoteEngine commit e0c263f by removing the sample-only workspace route, workbench, notice, and public fallback exception.</x:v>
       </x:c>
       <x:c r="J2" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Retested: source tests 180/180 passed, full QuoteEngine suite 539/539 passed, targeted route/workbench marker scan clean.</x:v>
       </x:c>
       <x:c r="K2" s="3" t="str">
         <x:v>P0</x:v>
@@ -5511,7 +5511,7 @@
         <x:v>QuoteController project nav/detail endpoints</x:v>
       </x:c>
       <x:c r="P2" s="3" t="str">
-        <x:v>QuoteEngineSourceTests workspace/shell</x:v>
+        <x:v>QuoteEngineSourceTests workspace/shell | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations. | Fix verification: QuoteEngineSourceTests passed 180/180; targeted scan found no sample-only workspace route/workbench markers in client workspace or BFF fallback route.</x:v>
       </x:c>
       <x:c r="Q2" s="3" t="str">
         <x:v>QuoteEngine client/BFF, session store</x:v>
@@ -5523,7 +5523,7 @@
         <x:v>The source still contains a non-current route, but tracking excludes it per product direction</x:v>
       </x:c>
       <x:c r="T2" s="3" t="str">
-        <x:v>QuoteWorkspace.razor:1-5,39; QuoteAgentLaunchShell.razor</x:v>
+        <x:v>QuoteWorkspace.razor:1-5,39; QuoteAgentLaunchShell.razor; Program.cs public route fallback; QuoteWorkspace.razor routes; QuoteAgentLaunchShell.razor</x:v>
       </x:c>
       <x:c r="U2" s="3" t="str">
         <x:v>2026-06-23</x:v>
@@ -5549,16 +5549,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G3" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated QuoteEngine suite passed 2026-06-23 after workspace cleanup</x:v>
       </x:c>
       <x:c r="H3" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="I3" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="J3" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K3" s="3" t="str">
         <x:v>P0</x:v>
@@ -5576,7 +5576,7 @@
         <x:v>AgentController GET health</x:v>
       </x:c>
       <x:c r="P3" s="3" t="str">
-        <x:v>QuoteAgentEndpointTests health; QuoteEngineSourceTests status dot</x:v>
+        <x:v>QuoteAgentEndpointTests health; QuoteEngineSourceTests status dot | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:v>
       </x:c>
       <x:c r="Q3" s="3" t="str">
         <x:v>QuoteEngine BFF, Agent service</x:v>
@@ -5614,16 +5614,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G4" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated QuoteEngine suite passed 2026-06-23 after workspace cleanup</x:v>
       </x:c>
       <x:c r="H4" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="I4" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="J4" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K4" s="3" t="str">
         <x:v>P0</x:v>
@@ -5641,7 +5641,7 @@
         <x:v>AgentController POST messages; QuoteAgentService SendMessageAsync</x:v>
       </x:c>
       <x:c r="P4" s="3" t="str">
-        <x:v>QuoteAgentEndpointTests messages</x:v>
+        <x:v>QuoteAgentEndpointTests messages | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:v>
       </x:c>
       <x:c r="Q4" s="3" t="str">
         <x:v>QuoteEngine BFF, Agent model, SessionStore</x:v>
@@ -5679,16 +5679,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G5" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated QuoteEngine suite passed 2026-06-23 after workspace cleanup</x:v>
       </x:c>
       <x:c r="H5" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="I5" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="J5" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K5" s="3" t="str">
         <x:v>P0</x:v>
@@ -5706,7 +5706,7 @@
         <x:v>AgentController POST messages/stream</x:v>
       </x:c>
       <x:c r="P5" s="3" t="str">
-        <x:v>QuoteAgentEndpointTests stream events; QuoteAgentLaunchShell source tests</x:v>
+        <x:v>QuoteAgentEndpointTests stream events; QuoteAgentLaunchShell source tests | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:v>
       </x:c>
       <x:c r="Q5" s="3" t="str">
         <x:v>QuoteEngine BFF, Agent model</x:v>
@@ -5744,16 +5744,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G6" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated QuoteEngine suite passed 2026-06-23 after workspace cleanup</x:v>
       </x:c>
       <x:c r="H6" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="I6" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="J6" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K6" s="3" t="str">
         <x:v>P0</x:v>
@@ -5771,7 +5771,7 @@
         <x:v>AgentController GET sessions/{sessionId}, sessions/{sessionId}/messages</x:v>
       </x:c>
       <x:c r="P6" s="3" t="str">
-        <x:v>QuoteAgentEndpointTests history auth</x:v>
+        <x:v>QuoteAgentEndpointTests history auth | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:v>
       </x:c>
       <x:c r="Q6" s="3" t="str">
         <x:v>QuoteEngine BFF, SessionStore, Auth</x:v>
@@ -5809,16 +5809,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G7" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated QuoteEngine suite passed 2026-06-23 after workspace cleanup</x:v>
       </x:c>
       <x:c r="H7" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="I7" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="J7" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K7" s="3" t="str">
         <x:v>P2</x:v>
@@ -5836,7 +5836,7 @@
         <x:v>AgentController clean-speech, thinking</x:v>
       </x:c>
       <x:c r="P7" s="3" t="str">
-        <x:v>QuoteAgentEndpointTests; QuoteEngineSourceTests thinking</x:v>
+        <x:v>QuoteAgentEndpointTests; QuoteEngineSourceTests thinking | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:v>
       </x:c>
       <x:c r="Q7" s="3" t="str">
         <x:v>QuoteEngine BFF, Agent service</x:v>
@@ -5874,16 +5874,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G8" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated QuoteEngine suite passed 2026-06-23 after workspace cleanup</x:v>
       </x:c>
       <x:c r="H8" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="I8" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="J8" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K8" s="3" t="str">
         <x:v>P0</x:v>
@@ -5901,7 +5901,7 @@
         <x:v>QuoteController projects/nav, project detail, duplicate, pin, delete pin, archive</x:v>
       </x:c>
       <x:c r="P8" s="3" t="str">
-        <x:v>QuoteEngineSourceTests rail/project management</x:v>
+        <x:v>QuoteEngineSourceTests rail/project management | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:v>
       </x:c>
       <x:c r="Q8" s="3" t="str">
         <x:v>QuoteEngine BFF, Project service, SessionStore</x:v>
@@ -5939,16 +5939,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G9" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated QuoteEngine suite passed 2026-06-23 after workspace cleanup</x:v>
       </x:c>
       <x:c r="H9" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="I9" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="J9" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K9" s="3" t="str">
         <x:v>P1</x:v>
@@ -5966,7 +5966,7 @@
         <x:v>AgentController GET sessions/{sessionId}/search</x:v>
       </x:c>
       <x:c r="P9" s="3" t="str">
-        <x:v>QuoteAgentEndpointTests search</x:v>
+        <x:v>QuoteAgentEndpointTests search | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:v>
       </x:c>
       <x:c r="Q9" s="3" t="str">
         <x:v>QuoteEngine BFF, Agent/Project service</x:v>
@@ -6004,16 +6004,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G10" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated QuoteEngine suite passed 2026-06-23 after workspace cleanup</x:v>
       </x:c>
       <x:c r="H10" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="I10" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="J10" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K10" s="3" t="str">
         <x:v>P0</x:v>
@@ -6031,7 +6031,7 @@
         <x:v>QuoteController uploads/resumable, PUT chunk, complete, analysis-status</x:v>
       </x:c>
       <x:c r="P10" s="3" t="str">
-        <x:v>QuoteEngineSourceTests upload; QuoteEngineApiClientTests</x:v>
+        <x:v>QuoteEngineSourceTests upload; QuoteEngineApiClientTests | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:v>
       </x:c>
       <x:c r="Q10" s="3" t="str">
         <x:v>QuoteEngine BFF, Storage, Geometry/analysis</x:v>
@@ -6069,16 +6069,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G11" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated QuoteEngine suite passed 2026-06-23 after workspace cleanup</x:v>
       </x:c>
       <x:c r="H11" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="I11" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="J11" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K11" s="3" t="str">
         <x:v>P0</x:v>
@@ -6096,7 +6096,7 @@
         <x:v>QuoteController POST uploads/handoff</x:v>
       </x:c>
       <x:c r="P11" s="3" t="str">
-        <x:v>QuoteEngineApiClientTests handoff</x:v>
+        <x:v>QuoteEngineApiClientTests handoff | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:v>
       </x:c>
       <x:c r="Q11" s="3" t="str">
         <x:v>QuoteEngine BFF, Web BFF, Storage</x:v>
@@ -6134,16 +6134,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G12" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated QuoteEngine suite passed 2026-06-23 after workspace cleanup</x:v>
       </x:c>
       <x:c r="H12" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="I12" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="J12" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K12" s="3" t="str">
         <x:v>P0</x:v>
@@ -6161,7 +6161,7 @@
         <x:v>AgentController POST sessions/{sessionId}/attachments</x:v>
       </x:c>
       <x:c r="P12" s="3" t="str">
-        <x:v>QuoteAgentEndpointTests attachment; QuoteAgentLaunchShell source tests</x:v>
+        <x:v>QuoteAgentEndpointTests attachment; QuoteAgentLaunchShell source tests | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:v>
       </x:c>
       <x:c r="Q12" s="3" t="str">
         <x:v>QuoteEngine BFF, SessionStore, Storage</x:v>
@@ -6199,16 +6199,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G13" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated QuoteEngine suite passed 2026-06-23 after workspace cleanup</x:v>
       </x:c>
       <x:c r="H13" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="I13" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="J13" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K13" s="3" t="str">
         <x:v>P1</x:v>
@@ -6226,7 +6226,7 @@
         <x:v>AgentController POST sessions/{sessionId}/sketches</x:v>
       </x:c>
       <x:c r="P13" s="3" t="str">
-        <x:v>QuoteAgentEndpointTests sketches; source tests sketch disposal</x:v>
+        <x:v>QuoteAgentEndpointTests sketches; source tests sketch disposal | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:v>
       </x:c>
       <x:c r="Q13" s="3" t="str">
         <x:v>QuoteEngine BFF, SessionStore, Storage</x:v>
@@ -6264,16 +6264,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G14" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated QuoteEngine suite passed 2026-06-23 after workspace cleanup</x:v>
       </x:c>
       <x:c r="H14" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="I14" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="J14" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K14" s="3" t="str">
         <x:v>P1</x:v>
@@ -6291,7 +6291,7 @@
         <x:v>GoogleDriveConnectorController start/callback/status/files; AgentController connectors/handoff</x:v>
       </x:c>
       <x:c r="P14" s="3" t="str">
-        <x:v>QuoteEngineSourceTests connector; endpoint tests where present</x:v>
+        <x:v>QuoteEngineSourceTests connector; endpoint tests where present | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:v>
       </x:c>
       <x:c r="Q14" s="3" t="str">
         <x:v>QuoteEngine BFF, Google Drive, Auth</x:v>
@@ -6329,16 +6329,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G15" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated QuoteEngine suite passed 2026-06-23 after workspace cleanup</x:v>
       </x:c>
       <x:c r="H15" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="I15" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="J15" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K15" s="3" t="str">
         <x:v>P0</x:v>
@@ -6356,7 +6356,7 @@
         <x:v>AgentController artifacts/download</x:v>
       </x:c>
       <x:c r="P15" s="3" t="str">
-        <x:v>QuoteAgentEndpointTests artifact download; QuoteEngineSourceTests artifacts</x:v>
+        <x:v>QuoteAgentEndpointTests artifact download; QuoteEngineSourceTests artifacts | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:v>
       </x:c>
       <x:c r="Q15" s="3" t="str">
         <x:v>QuoteEngine BFF, Storage/artifact service</x:v>
@@ -6394,16 +6394,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G16" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated QuoteEngine suite passed 2026-06-23 after workspace cleanup</x:v>
       </x:c>
       <x:c r="H16" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="I16" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="J16" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K16" s="3" t="str">
         <x:v>P1</x:v>
@@ -6421,7 +6421,7 @@
         <x:v>AgentController POST artifacts/{artifactId}/feedback</x:v>
       </x:c>
       <x:c r="P16" s="3" t="str">
-        <x:v>QuoteEngineSourceTests feedback; QuoteAgentEndpointTests feedback</x:v>
+        <x:v>QuoteEngineSourceTests feedback; QuoteAgentEndpointTests feedback | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:v>
       </x:c>
       <x:c r="Q16" s="3" t="str">
         <x:v>QuoteEngine BFF, Agent service, Customer memory</x:v>
@@ -6459,16 +6459,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G17" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated QuoteEngine suite passed 2026-06-23 after workspace cleanup</x:v>
       </x:c>
       <x:c r="H17" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="I17" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="J17" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K17" s="3" t="str">
         <x:v>P0</x:v>
@@ -6486,7 +6486,7 @@
         <x:v>GeometryRuntimeController manifest/assets/telemetry</x:v>
       </x:c>
       <x:c r="P17" s="3" t="str">
-        <x:v>QuoteEngineSourceTests viewer/runtime</x:v>
+        <x:v>QuoteEngineSourceTests viewer/runtime | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:v>
       </x:c>
       <x:c r="Q17" s="3" t="str">
         <x:v>QuoteEngine client/BFF, Geometry runtime</x:v>
@@ -6524,16 +6524,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G18" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated QuoteEngine suite passed 2026-06-23 after workspace cleanup</x:v>
       </x:c>
       <x:c r="H18" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="I18" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="J18" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K18" s="3" t="str">
         <x:v>P0</x:v>
@@ -6551,7 +6551,7 @@
         <x:v>AgentController POST sessions/{sessionId}/dfm; QeDfmDtos</x:v>
       </x:c>
       <x:c r="P18" s="3" t="str">
-        <x:v>QuoteEngineSourceTests DFM</x:v>
+        <x:v>QuoteEngineSourceTests DFM | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:v>
       </x:c>
       <x:c r="Q18" s="3" t="str">
         <x:v>QuoteEngine BFF, Geometry/DFM, SessionStore</x:v>
@@ -6589,16 +6589,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G19" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated QuoteEngine suite passed 2026-06-23 after workspace cleanup</x:v>
       </x:c>
       <x:c r="H19" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="I19" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="J19" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K19" s="3" t="str">
         <x:v>P0</x:v>
@@ -6616,7 +6616,7 @@
         <x:v>QuoteController reference-data/estimate</x:v>
       </x:c>
       <x:c r="P19" s="3" t="str">
-        <x:v>QuoteEngineSourceTests config sidebar</x:v>
+        <x:v>QuoteEngineSourceTests config sidebar | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:v>
       </x:c>
       <x:c r="Q19" s="3" t="str">
         <x:v>QuoteEngine client/BFF, Pricing/Material services</x:v>
@@ -6654,16 +6654,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G20" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated QuoteEngine suite passed 2026-06-23 after workspace cleanup</x:v>
       </x:c>
       <x:c r="H20" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="I20" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="J20" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K20" s="3" t="str">
         <x:v>P1</x:v>
@@ -6681,7 +6681,7 @@
         <x:v>QuoteController reference-data; ReferenceDataController currencies</x:v>
       </x:c>
       <x:c r="P20" s="3" t="str">
-        <x:v>QuoteEngineApiClientTests</x:v>
+        <x:v>QuoteEngineApiClientTests | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:v>
       </x:c>
       <x:c r="Q20" s="3" t="str">
         <x:v>QuoteEngine BFF, Material/Pricing/Reference data</x:v>
@@ -6719,16 +6719,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G21" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated QuoteEngine suite passed 2026-06-23 after workspace cleanup</x:v>
       </x:c>
       <x:c r="H21" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="I21" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="J21" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K21" s="3" t="str">
         <x:v>P0</x:v>
@@ -6746,7 +6746,7 @@
         <x:v>QuoteController POST estimate</x:v>
       </x:c>
       <x:c r="P21" s="3" t="str">
-        <x:v>Pricing/QuoteEngine tests</x:v>
+        <x:v>Pricing/QuoteEngine tests | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:v>
       </x:c>
       <x:c r="Q21" s="3" t="str">
         <x:v>QuoteEngine BFF, PricingService</x:v>
@@ -6784,16 +6784,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G22" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated QuoteEngine suite passed 2026-06-23 after workspace cleanup</x:v>
       </x:c>
       <x:c r="H22" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="I22" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="J22" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K22" s="3" t="str">
         <x:v>P0</x:v>
@@ -6811,7 +6811,7 @@
         <x:v>QuoteController POST projects/draft</x:v>
       </x:c>
       <x:c r="P22" s="3" t="str">
-        <x:v>QuoteEngineSourceTests project draft</x:v>
+        <x:v>QuoteEngineSourceTests project draft | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:v>
       </x:c>
       <x:c r="Q22" s="3" t="str">
         <x:v>QuoteEngine BFF, Project/Quote service</x:v>
@@ -6849,16 +6849,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G23" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated QuoteEngine suite passed 2026-06-23 after workspace cleanup</x:v>
       </x:c>
       <x:c r="H23" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="I23" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="J23" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K23" s="3" t="str">
         <x:v>P0</x:v>
@@ -6876,7 +6876,7 @@
         <x:v>QuoteController POST quotes/formal</x:v>
       </x:c>
       <x:c r="P23" s="3" t="str">
-        <x:v>QuoteEngineSourceTests summary/formal quote</x:v>
+        <x:v>QuoteEngineSourceTests summary/formal quote | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:v>
       </x:c>
       <x:c r="Q23" s="3" t="str">
         <x:v>QuoteEngine BFF, Quotation/Pdf/Storage</x:v>
@@ -6914,16 +6914,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G24" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated QuoteEngine suite passed 2026-06-23 after workspace cleanup</x:v>
       </x:c>
       <x:c r="H24" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="I24" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="J24" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K24" s="3" t="str">
         <x:v>P0</x:v>
@@ -6941,7 +6941,7 @@
         <x:v>QuoteController POST quotes/{quoteId}/approve</x:v>
       </x:c>
       <x:c r="P24" s="3" t="str">
-        <x:v>Quote/Order contract tests</x:v>
+        <x:v>Quote/Order contract tests | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:v>
       </x:c>
       <x:c r="Q24" s="3" t="str">
         <x:v>QuoteEngine BFF, QuotationService</x:v>
@@ -6979,16 +6979,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G25" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated QuoteEngine suite passed 2026-06-23 after workspace cleanup</x:v>
       </x:c>
       <x:c r="H25" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="I25" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="J25" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K25" s="3" t="str">
         <x:v>P0</x:v>
@@ -7006,7 +7006,7 @@
         <x:v>QuoteController POST orders</x:v>
       </x:c>
       <x:c r="P25" s="3" t="str">
-        <x:v>Order contract tests</x:v>
+        <x:v>Order contract tests | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:v>
       </x:c>
       <x:c r="Q25" s="3" t="str">
         <x:v>QuoteEngine BFF, OrderService</x:v>
@@ -7044,16 +7044,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G26" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated QuoteEngine suite passed 2026-06-23 after workspace cleanup</x:v>
       </x:c>
       <x:c r="H26" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="I26" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="J26" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K26" s="3" t="str">
         <x:v>P0</x:v>
@@ -7071,7 +7071,7 @@
         <x:v>QuoteController POST payments</x:v>
       </x:c>
       <x:c r="P26" s="3" t="str">
-        <x:v>Payment contract tests</x:v>
+        <x:v>Payment contract tests | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:v>
       </x:c>
       <x:c r="Q26" s="3" t="str">
         <x:v>QuoteEngine BFF, PaymentService</x:v>
@@ -7109,16 +7109,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G27" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated QuoteEngine suite passed 2026-06-23 after workspace cleanup</x:v>
       </x:c>
       <x:c r="H27" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="I27" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="J27" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K27" s="3" t="str">
         <x:v>P1</x:v>
@@ -7136,7 +7136,7 @@
         <x:v>AccountController GET profile, addresses</x:v>
       </x:c>
       <x:c r="P27" s="3" t="str">
-        <x:v>AccountAuthBoundaryTests</x:v>
+        <x:v>AccountAuthBoundaryTests | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:v>
       </x:c>
       <x:c r="Q27" s="3" t="str">
         <x:v>QuoteEngine BFF, CustomerService</x:v>
@@ -7174,16 +7174,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G28" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated QuoteEngine suite passed 2026-06-23 after workspace cleanup</x:v>
       </x:c>
       <x:c r="H28" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="I28" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="J28" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K28" s="3" t="str">
         <x:v>P1</x:v>
@@ -7201,7 +7201,7 @@
         <x:v>AccountController quotes, orders, order detail, order file download</x:v>
       </x:c>
       <x:c r="P28" s="3" t="str">
-        <x:v>QuoteEngineSourceTests account/order routes</x:v>
+        <x:v>QuoteEngineSourceTests account/order routes | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:v>
       </x:c>
       <x:c r="Q28" s="3" t="str">
         <x:v>QuoteEngine BFF, Quote/Order service, Storage</x:v>
@@ -7239,16 +7239,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G29" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated QuoteEngine suite passed 2026-06-23 after workspace cleanup</x:v>
       </x:c>
       <x:c r="H29" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="I29" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="J29" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K29" s="3" t="str">
         <x:v>P2</x:v>
@@ -7266,7 +7266,7 @@
         <x:v>AccountController GET ndas</x:v>
       </x:c>
       <x:c r="P29" s="3" t="str">
-        <x:v>QuoteEngineSourceTests account routes</x:v>
+        <x:v>QuoteEngineSourceTests account routes | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:v>
       </x:c>
       <x:c r="Q29" s="3" t="str">
         <x:v>QuoteEngine BFF, Customer/Document services</x:v>
@@ -7304,16 +7304,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G30" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated QuoteEngine suite passed 2026-06-23 after workspace cleanup</x:v>
       </x:c>
       <x:c r="H30" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="I30" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="J30" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K30" s="3" t="str">
         <x:v>P1</x:v>
@@ -7331,7 +7331,7 @@
         <x:v>AccountController documents GET/POST/upload/download</x:v>
       </x:c>
       <x:c r="P30" s="3" t="str">
-        <x:v>QuoteEngineSourceTests documents</x:v>
+        <x:v>QuoteEngineSourceTests documents | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:v>
       </x:c>
       <x:c r="Q30" s="3" t="str">
         <x:v>QuoteEngine BFF, Document/Storage service</x:v>
@@ -7369,16 +7369,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G31" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated QuoteEngine suite passed 2026-06-23 after workspace cleanup</x:v>
       </x:c>
       <x:c r="H31" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="I31" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="J31" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K31" s="3" t="str">
         <x:v>P2</x:v>
@@ -7396,7 +7396,7 @@
         <x:v>QuoteEngineApiClient preference/account calls</x:v>
       </x:c>
       <x:c r="P31" s="3" t="str">
-        <x:v>QuoteEngineSourceTests where present</x:v>
+        <x:v>QuoteEngineSourceTests where present | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:v>
       </x:c>
       <x:c r="Q31" s="3" t="str">
         <x:v>QuoteEngine client/BFF</x:v>
@@ -7434,16 +7434,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G32" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated QuoteEngine suite passed 2026-06-23 after workspace cleanup</x:v>
       </x:c>
       <x:c r="H32" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="I32" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="J32" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K32" s="3" t="str">
         <x:v>P0</x:v>
@@ -7461,7 +7461,7 @@
         <x:v>AuthController GET session, POST sign-out</x:v>
       </x:c>
       <x:c r="P32" s="3" t="str">
-        <x:v>GoogleAuthFlowTests; AccountAuthBoundaryTests</x:v>
+        <x:v>GoogleAuthFlowTests; AccountAuthBoundaryTests | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:v>
       </x:c>
       <x:c r="Q32" s="3" t="str">
         <x:v>QuoteEngine BFF, Auth/Customer session</x:v>
@@ -7499,16 +7499,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G33" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated QuoteEngine suite passed 2026-06-23 after workspace cleanup</x:v>
       </x:c>
       <x:c r="H33" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="I33" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="J33" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K33" s="3" t="str">
         <x:v>P1</x:v>
@@ -7526,7 +7526,7 @@
         <x:v>ShippingController couriers/rates/tracking</x:v>
       </x:c>
       <x:c r="P33" s="3" t="str">
-        <x:v>Shipping contract tests where present</x:v>
+        <x:v>Shipping contract tests where present | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:v>
       </x:c>
       <x:c r="Q33" s="3" t="str">
         <x:v>QuoteEngine BFF, DeliveryService</x:v>
@@ -7564,16 +7564,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G34" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated QuoteEngine suite passed 2026-06-23 after workspace cleanup</x:v>
       </x:c>
       <x:c r="H34" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="I34" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="J34" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K34" s="3" t="str">
         <x:v>P2</x:v>
@@ -7591,7 +7591,7 @@
         <x:v>AddressController google-config, thai-locations</x:v>
       </x:c>
       <x:c r="P34" s="3" t="str">
-        <x:v>QuoteEngineAddressSourceTests</x:v>
+        <x:v>QuoteEngineAddressSourceTests | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:v>
       </x:c>
       <x:c r="Q34" s="3" t="str">
         <x:v>QuoteEngine BFF, Configuration/ReferenceData</x:v>
@@ -7629,16 +7629,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G35" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated QuoteEngine suite passed 2026-06-23 after workspace cleanup</x:v>
       </x:c>
       <x:c r="H35" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="I35" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="J35" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K35" s="3" t="str">
         <x:v>P1</x:v>
@@ -7656,7 +7656,7 @@
         <x:v>GeometryRuntimeController manifest/assets/telemetry</x:v>
       </x:c>
       <x:c r="P35" s="3" t="str">
-        <x:v>QuoteEngineSourceTests geometry runtime</x:v>
+        <x:v>QuoteEngineSourceTests geometry runtime | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:v>
       </x:c>
       <x:c r="Q35" s="3" t="str">
         <x:v>QuoteEngine BFF, Geometry runtime</x:v>
@@ -7694,16 +7694,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G36" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated QuoteEngine suite passed 2026-06-23 after workspace cleanup</x:v>
       </x:c>
       <x:c r="H36" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="I36" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="J36" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K36" s="3" t="str">
         <x:v>P0</x:v>
@@ -7721,7 +7721,7 @@
         <x:v>AgentController tools/{toolName}, actions/{actionId}/confirm</x:v>
       </x:c>
       <x:c r="P36" s="3" t="str">
-        <x:v>QuoteAgentEndpointTests action confirmations</x:v>
+        <x:v>QuoteAgentEndpointTests action confirmations | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:v>
       </x:c>
       <x:c r="Q36" s="3" t="str">
         <x:v>QuoteEngine BFF, Agent service, SessionStore</x:v>
@@ -7759,16 +7759,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G37" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated QuoteEngine suite passed 2026-06-23 after workspace cleanup</x:v>
       </x:c>
       <x:c r="H37" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="I37" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="J37" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K37" s="3" t="str">
         <x:v>P1</x:v>
@@ -7786,7 +7786,7 @@
         <x:v>QuoteAgentService prompt/memory paths</x:v>
       </x:c>
       <x:c r="P37" s="3" t="str">
-        <x:v>QuoteAgentEndpointTests memory/grounding; source tests feedback memory</x:v>
+        <x:v>QuoteAgentEndpointTests memory/grounding; source tests feedback memory | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:v>
       </x:c>
       <x:c r="Q37" s="3" t="str">
         <x:v>QuoteEngine BFF, Agent model, CustomerService memory</x:v>
@@ -7824,16 +7824,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G38" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated QuoteEngine suite passed 2026-06-23 after workspace cleanup</x:v>
       </x:c>
       <x:c r="H38" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="I38" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="J38" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K38" s="3" t="str">
         <x:v>P1</x:v>
@@ -7851,7 +7851,7 @@
         <x:v>Analysis status endpoints plus notification hub</x:v>
       </x:c>
       <x:c r="P38" s="3" t="str">
-        <x:v>QuoteEngineSourceTests realtime/thinking where present</x:v>
+        <x:v>QuoteEngineSourceTests realtime/thinking where present | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:v>
       </x:c>
       <x:c r="Q38" s="3" t="str">
         <x:v>QuoteEngine BFF, SignalR, Geometry/Storage</x:v>
@@ -7889,16 +7889,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G39" s="3" t="str">
-        <x:v>Mapped to existing tests</x:v>
+        <x:v>Automated QuoteEngine suite passed 2026-06-23 after workspace cleanup</x:v>
       </x:c>
       <x:c r="H39" s="3" t="str">
-        <x:v>Not tested in current loop</x:v>
+        <x:v>No behavior error observed in current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="I39" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>No fix needed for this story from current QuoteEngine automated retest.</x:v>
       </x:c>
       <x:c r="J39" s="3" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Current automated suite passed.</x:v>
       </x:c>
       <x:c r="K39" s="3" t="str">
         <x:v>P2</x:v>
@@ -7916,7 +7916,7 @@
         <x:v>AgentController POST export-pdf</x:v>
       </x:c>
       <x:c r="P39" s="3" t="str">
-        <x:v>QuoteAgentEndpointTests export PDF</x:v>
+        <x:v>QuoteAgentEndpointTests export PDF | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:v>
       </x:c>
       <x:c r="Q39" s="3" t="str">
         <x:v>QuoteEngine BFF, PdfService</x:v>
@@ -7937,7 +7937,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0147e55d11a64293"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R298253f1e71d496e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/maliev-feature-user-story-status.xlsx
+++ b/docs/maliev-feature-user-story-status.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R4585119bd12d4a73"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="R807a60cfd8ac4152"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R22b6efa70b8e4ffe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="R290d9820c4d34c00"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R8e272da5a73f48d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="Rb2db60ebe6ef439c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="Rd5dc25427a094fd9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="Rcbf3e1afc5644b07"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -419,7 +419,7 @@
         <x:v>Next loop</x:v>
       </x:c>
       <x:c r="B9" s="3" t="str">
-        <x:v>Test every current code-derived user story, document errors, fix logistical/UX issues, then retest.</x:v>
+        <x:v>Continue Intranet dashboard browser pass via Aspire-configured runtime, then continue story-by-story behavior testing and retesting.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -604,16 +604,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G3" s="3" t="str">
-        <x:v>Automated Web suite passed 2026-06-23; browser runtime pending</x:v>
+        <x:v>Automated Web suite passed 2026-06-23; browser route check passed 2026-06-23</x:v>
       </x:c>
       <x:c r="H3" s="3" t="str">
-        <x:v>No behavior error observed in current Web automated suite.</x:v>
+        <x:v>Browser check passed: /services returned HTTP 200, rendered services content, and reported no page errors.</x:v>
       </x:c>
       <x:c r="I3" s="3" t="str">
-        <x:v>No fix needed from current Web automated suite.</x:v>
+        <x:v>No Web code fix needed for this story.</x:v>
       </x:c>
       <x:c r="J3" s="3" t="str">
-        <x:v>Current automated suite passed; browser/runtime verification pending.</x:v>
+        <x:v>Retested in 16-route Web browser pass on 2026-06-23; route passed with no page errors.</x:v>
       </x:c>
       <x:c r="K3" s="3" t="str">
         <x:v>P2</x:v>
@@ -631,7 +631,7 @@
         <x:v>Static content model</x:v>
       </x:c>
       <x:c r="P3" s="3" t="str">
-        <x:v>dotnet test Maliev.Web.slnx --filter HeroLayoutSourceTests.ServicesUseRealRoutesAndDisabledQuoteActions|HeroLayoutSourceTests.StaticPagesCoverCustomerRoutesAndContactBoundary|HeroLayoutSourceTests.CheckoutPageCollectsCustomerCheckoutDetailsAfterSignIn|HeroLayoutSourceTests.HeaderUsesMudIconButtonsForCartAndAccount passed 4/4 on 2026-06-23. | Current suite: dotnet test Maliev.Web.slnx --verbosity minimal passed 235/235 on 2026-06-23.</x:v>
+        <x:v>Browser evidence: Playwright browser route check against Maliev.Web.Bff http profile on 2026-06-23 covered /services, /services/3d-printing, /cart, and 13 static/content routes; final retest passed 16/16 with no page errors.</x:v>
       </x:c>
       <x:c r="Q3" s="3" t="str">
         <x:v>Web client</x:v>
@@ -669,16 +669,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G4" s="3" t="str">
-        <x:v>Automated Web suite passed 2026-06-23; browser runtime pending</x:v>
+        <x:v>Automated Web suite passed 2026-06-23; browser route check failed, fixed, and retested passed 2026-06-23</x:v>
       </x:c>
       <x:c r="H4" s="3" t="str">
-        <x:v>No behavior error observed in current Web automated suite.</x:v>
+        <x:v>Initial browser check: /services/3d-printing returned HTTP 200 and rendered the page, but threw TypeError in babylonjs.loaders.min.js while duplicate Babylon runtime scripts were appended.</x:v>
       </x:c>
       <x:c r="I4" s="3" t="str">
-        <x:v>No fix needed from current Web automated suite.</x:v>
+        <x:v>Fixed manufacturing-gizmo runtime guards to share canvas instances and Babylon script promises through globalThis.__malievManufacturingGizmo.</x:v>
       </x:c>
       <x:c r="J4" s="3" t="str">
-        <x:v>Current automated suite passed; browser/runtime verification pending.</x:v>
+        <x:v>Retested focused regression 1/1 passed; reran 16-route Web browser pass 16/16 passed; /services/3d-printing had no page errors and duplicate-script probe showed one Babylon core and one loader script.</x:v>
       </x:c>
       <x:c r="K4" s="3" t="str">
         <x:v>P2</x:v>
@@ -696,7 +696,7 @@
         <x:v>Static content model</x:v>
       </x:c>
       <x:c r="P4" s="3" t="str">
-        <x:v>dotnet test Maliev.Web.slnx --filter HeroLayoutSourceTests.ServicesUseRealRoutesAndDisabledQuoteActions|HeroLayoutSourceTests.StaticPagesCoverCustomerRoutesAndContactBoundary|HeroLayoutSourceTests.CheckoutPageCollectsCustomerCheckoutDetailsAfterSignIn|HeroLayoutSourceTests.HeaderUsesMudIconButtonsForCartAndAccount passed 4/4 on 2026-06-23. | Current suite: dotnet test Maliev.Web.slnx --verbosity minimal passed 235/235 on 2026-06-23.</x:v>
+        <x:v>Browser evidence: Playwright browser route check against Maliev.Web.Bff http profile on 2026-06-23 covered /services, /services/3d-printing, /cart, and 13 static/content routes; final retest passed 16/16 with no page errors. Regression: dotnet test Maliev.Web.slnx --filter "FullyQualifiedName~ManufacturingGizmoRuntimeSourceTests" --verbosity minimal passed 1/1 after failing before the JS runtime fix.</x:v>
       </x:c>
       <x:c r="Q4" s="3" t="str">
         <x:v>Web client</x:v>
@@ -708,7 +708,7 @@
         <x:v>Needs 404/unknown slug browser check</x:v>
       </x:c>
       <x:c r="T4" s="3" t="str">
-        <x:v>ServicePage.razor:1</x:v>
+        <x:v>ServicePage.razor:1; manufacturing-gizmo.js:1-8,215-247; ManufacturingGizmoRuntimeSourceTests.cs</x:v>
       </x:c>
       <x:c r="U4" s="3" t="str">
         <x:v>2026-06-23</x:v>
@@ -994,16 +994,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G9" s="3" t="str">
-        <x:v>Automated Web suite passed 2026-06-23; browser runtime pending</x:v>
+        <x:v>Automated Web suite passed 2026-06-23; browser route check passed 2026-06-23</x:v>
       </x:c>
       <x:c r="H9" s="3" t="str">
-        <x:v>No behavior error observed in current Web automated suite.</x:v>
+        <x:v>Browser check passed: /cart returned HTTP 200, rendered cart content, and reported no page errors.</x:v>
       </x:c>
       <x:c r="I9" s="3" t="str">
-        <x:v>No fix needed from current Web automated suite.</x:v>
+        <x:v>No Web code fix needed for this story.</x:v>
       </x:c>
       <x:c r="J9" s="3" t="str">
-        <x:v>Current automated suite passed; browser/runtime verification pending.</x:v>
+        <x:v>Retested in 16-route Web browser pass on 2026-06-23; route passed with no page errors.</x:v>
       </x:c>
       <x:c r="K9" s="3" t="str">
         <x:v>P1</x:v>
@@ -1021,7 +1021,7 @@
         <x:v>CheckoutController draft endpoints used after cart</x:v>
       </x:c>
       <x:c r="P9" s="3" t="str">
-        <x:v>dotnet test Maliev.Web.slnx --filter HeroLayoutSourceTests.HeaderUsesMudIconButtonsForCartAndAccount|HeroLayoutSourceTests.CheckoutPageCollectsCustomerCheckoutDetailsAfterSignIn passed as part of 4/4 focused Web run on 2026-06-23. | Current suite: dotnet test Maliev.Web.slnx --verbosity minimal passed 235/235 on 2026-06-23.</x:v>
+        <x:v>Browser evidence: Playwright browser route check against Maliev.Web.Bff http profile on 2026-06-23 covered /services, /services/3d-printing, /cart, and 13 static/content routes; final retest passed 16/16 with no page errors.</x:v>
       </x:c>
       <x:c r="Q9" s="3" t="str">
         <x:v>Web client, Checkout BFF</x:v>
@@ -2229,16 +2229,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G28" s="3" t="str">
-        <x:v>Automated Web suite passed 2026-06-23; browser runtime pending</x:v>
+        <x:v>Automated Web suite passed 2026-06-23; browser route check passed 2026-06-23</x:v>
       </x:c>
       <x:c r="H28" s="3" t="str">
-        <x:v>No behavior error observed in current Web automated suite.</x:v>
+        <x:v>Browser check passed: about, FAQ, policy, industry, case-study, and blog routes returned HTTP 200 and reported no page errors.</x:v>
       </x:c>
       <x:c r="I28" s="3" t="str">
-        <x:v>No fix needed from current Web automated suite.</x:v>
+        <x:v>No Web code fix needed for this story.</x:v>
       </x:c>
       <x:c r="J28" s="3" t="str">
-        <x:v>Current automated suite passed; browser/runtime verification pending.</x:v>
+        <x:v>Retested in 16-route Web browser pass on 2026-06-23; all covered static/content routes passed with no page errors.</x:v>
       </x:c>
       <x:c r="K28" s="3" t="str">
         <x:v>P2</x:v>
@@ -2256,7 +2256,7 @@
         <x:v>BlogController for ebook PDF only</x:v>
       </x:c>
       <x:c r="P28" s="3" t="str">
-        <x:v>dotnet test Maliev.Web.slnx --filter HeroLayoutSourceTests.StaticPagesCoverCustomerRoutesAndContactBoundary passed as part of 4/4 focused Web run on 2026-06-23. | Current suite: dotnet test Maliev.Web.slnx --verbosity minimal passed 235/235 on 2026-06-23.</x:v>
+        <x:v>Browser evidence: Playwright browser route check against Maliev.Web.Bff http profile on 2026-06-23 covered /services, /services/3d-printing, /cart, and 13 static/content routes; final retest passed 16/16 with no page errors.</x:v>
       </x:c>
       <x:c r="Q28" s="3" t="str">
         <x:v>Web client, Content</x:v>
@@ -2407,7 +2407,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7fbbd983b61148d6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4a4370cd90e94e1b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2589,16 +2589,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G3" s="3" t="str">
-        <x:v>Automated Intranet suite passed 2026-06-23 after UX fix; browser runtime pending</x:v>
+        <x:v>Automated Intranet suite passed 2026-06-23 after UX fix; standalone browser startup blocked 2026-06-23</x:v>
       </x:c>
       <x:c r="H3" s="3" t="str">
-        <x:v>No behavior error observed in current Intranet automated retest.</x:v>
+        <x:v>Browser check did not reach /: standalone dotnet run for Maliev.Intranet.Bff terminated before listening because IntranetDbContext connection string was not configured.</x:v>
       </x:c>
       <x:c r="I3" s="3" t="str">
-        <x:v>No fix needed for this story from current Intranet automated retest.</x:v>
+        <x:v>No dashboard UX fix applied in this slice; route needs Aspire-configured runtime with IntranetDbContext before browser verification.</x:v>
       </x:c>
       <x:c r="J3" s="3" t="str">
-        <x:v>Current automated suite passed; browser/runtime verification pending.</x:v>
+        <x:v>Not browser-rendered in standalone mode; startup blocker captured from current run. Automated dashboard/controller tests remain passed.</x:v>
       </x:c>
       <x:c r="K3" s="3" t="str">
         <x:v>P1</x:v>
@@ -5367,7 +5367,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R959304072e3e4436"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc1ec56bbf2fc4287"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7937,7 +7937,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R298253f1e71d496e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R97c79c73d9d14e7e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/maliev-feature-user-story-status.xlsx
+++ b/docs/maliev-feature-user-story-status.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R84826f258dea4c1d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="R612a23bdfc764b64"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="Rd76d5e8c74ac4ce6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="R27796b1ecd8f4f15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Recba917fce4e47a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="Rd28cc1ae787c42ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R8bd7a0686ffc465d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="R9b3c2a324e4f4f0d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3227,39 +3227,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">ClientConfigController.cs:14-46; DiagnosticsController.cs:15-25</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">INT-051</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Not-found handling</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">As an employee, I can recover when an intranet route does not exist.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Not-found page explains the missing content and links back to the dashboard.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Blazor fallback route -&gt; dashboard recovery link</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">NotFound.razor</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">/not-found</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">None; client recovery page only</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Intranet client</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Needs browser recovery-route pass.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">NotFound.razor:1</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">QE-001</x:t>
@@ -7238,7 +7205,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R499cf8b8082d473e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4b883387c6dd487a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10587,74 +10554,74 @@
       </x:c>
     </x:row>
     <x:row r="52" ht="51.29999923706055" hidden="0">
-      <x:c r="A52" s="3" t="s">
-        <x:v>1072</x:v>
-      </x:c>
-      <x:c r="B52" s="3" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C52" s="3" t="s">
-        <x:v>1073</x:v>
-      </x:c>
-      <x:c r="D52" s="3" t="s">
-        <x:v>1074</x:v>
-      </x:c>
-      <x:c r="E52" s="3" t="s">
-        <x:v>1075</x:v>
-      </x:c>
-      <x:c r="F52" s="3" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="G52" s="3" t="s">
-        <x:v>1001</x:v>
-      </x:c>
-      <x:c r="H52" s="3" t="s">
-        <x:v>1002</x:v>
-      </x:c>
-      <x:c r="I52" s="3" t="s">
-        <x:v>1003</x:v>
-      </x:c>
-      <x:c r="J52" s="3" t="s">
-        <x:v>1004</x:v>
-      </x:c>
-      <x:c r="K52" s="3" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="L52" s="3" t="s">
-        <x:v>1076</x:v>
-      </x:c>
-      <x:c r="M52" s="3" t="s">
-        <x:v>1077</x:v>
-      </x:c>
-      <x:c r="N52" s="3" t="s">
-        <x:v>1078</x:v>
-      </x:c>
-      <x:c r="O52" s="3" t="s">
-        <x:v>1079</x:v>
-      </x:c>
-      <x:c r="P52" s="3" t="s">
-        <x:v>1009</x:v>
-      </x:c>
-      <x:c r="Q52" s="3" t="s">
-        <x:v>1080</x:v>
-      </x:c>
-      <x:c r="R52" s="3" t="s">
-        <x:v>418</x:v>
-      </x:c>
-      <x:c r="S52" s="3" t="s">
-        <x:v>1081</x:v>
-      </x:c>
-      <x:c r="T52" s="3" t="s">
-        <x:v>1082</x:v>
-      </x:c>
-      <x:c r="U52" s="3" t="s">
-        <x:v>2</x:v>
+      <x:c r="A52" s="3" t="str">
+        <x:v>INT-051</x:v>
+      </x:c>
+      <x:c r="B52" s="3" t="str">
+        <x:v>Maliev.Intranet</x:v>
+      </x:c>
+      <x:c r="C52" s="3" t="str">
+        <x:v>Not-found handling</x:v>
+      </x:c>
+      <x:c r="D52" s="3" t="str">
+        <x:v>As an employee, I can recover when an intranet route does not exist.</x:v>
+      </x:c>
+      <x:c r="E52" s="3" t="str">
+        <x:v>Not-found page explains the missing content and links back to the dashboard.</x:v>
+      </x:c>
+      <x:c r="F52" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G52" s="3" t="str">
+        <x:v>Behavior test failed, fixed, and retested passed 2026-06-23.</x:v>
+      </x:c>
+      <x:c r="H52" s="3" t="str">
+        <x:v>Source behavior check found unknown client routes used the Router inline fallback text instead of the existing designed /not-found recovery page.</x:v>
+      </x:c>
+      <x:c r="I52" s="3" t="str">
+        <x:v>Fixed in Maliev.Intranet commit 379913b by rendering Maliev.Intranet.Client.Pages.NotFound from Routes.razor &lt;NotFound&gt; fallback and adding a source regression.</x:v>
+      </x:c>
+      <x:c r="J52" s="3" t="str">
+        <x:v>Retested focused not-found source regressions 2/2 passed.</x:v>
+      </x:c>
+      <x:c r="K52" s="3" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="L52" s="3" t="str">
+        <x:v>Blazor fallback route -&gt; dashboard recovery link</x:v>
+      </x:c>
+      <x:c r="M52" s="3" t="str">
+        <x:v>NotFound.razor</x:v>
+      </x:c>
+      <x:c r="N52" s="3" t="str">
+        <x:v>/not-found</x:v>
+      </x:c>
+      <x:c r="O52" s="3" t="str">
+        <x:v>None; client recovery page only</x:v>
+      </x:c>
+      <x:c r="P52" s="3" t="str">
+        <x:v>Focused test: dotnet test Maliev.Intranet.slnx --filter "FullyQualifiedName~ModuleRegressionSourceTests.NotFoundPage_UsesAnimatedSearchingEyes|FullyQualifiedName~ModuleRegressionSourceTests.RouterFallback_UsesNotFoundRecoveryPage" --verbosity minimal passed 2/2 on 2026-06-23. Test build compiled Intranet Client, BFF, and Tests projects.</x:v>
+      </x:c>
+      <x:c r="Q52" s="3" t="str">
+        <x:v>Intranet client</x:v>
+      </x:c>
+      <x:c r="R52" s="3" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="S52" s="3" t="str">
+        <x:v>No remaining INT-051 source fallback gap from this focused retest; full authenticated browser unknown-route pass still needed when Aspire/browser tooling is available.</x:v>
+      </x:c>
+      <x:c r="T52" s="3" t="str">
+        <x:v>Routes.razor:30-34; NotFound.razor:1; ModuleRegressionSourceTests.cs:211,225</x:v>
+      </x:c>
+      <x:c r="U52" s="3" t="str">
+        <x:v>2026-06-23</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc68b04f535744e2d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2c18b4856e2c44ea"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10754,64 +10721,64 @@
     </x:row>
     <x:row r="2" ht="149.25" hidden="0">
       <x:c r="A2" s="3" t="s">
-        <x:v>1083</x:v>
+        <x:v>1072</x:v>
       </x:c>
       <x:c r="B2" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C2" s="3" t="s">
-        <x:v>1084</x:v>
+        <x:v>1073</x:v>
       </x:c>
       <x:c r="D2" s="3" t="s">
-        <x:v>1085</x:v>
+        <x:v>1074</x:v>
       </x:c>
       <x:c r="E2" s="3" t="s">
-        <x:v>1086</x:v>
+        <x:v>1075</x:v>
       </x:c>
       <x:c r="F2" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G2" s="3" t="s">
-        <x:v>1087</x:v>
+        <x:v>1076</x:v>
       </x:c>
       <x:c r="H2" s="3" t="s">
-        <x:v>1088</x:v>
+        <x:v>1077</x:v>
       </x:c>
       <x:c r="I2" s="3" t="s">
-        <x:v>1089</x:v>
+        <x:v>1078</x:v>
       </x:c>
       <x:c r="J2" s="3" t="s">
-        <x:v>1090</x:v>
+        <x:v>1079</x:v>
       </x:c>
       <x:c r="K2" s="3" t="s">
         <x:v>188</x:v>
       </x:c>
       <x:c r="L2" s="3" t="s">
-        <x:v>1091</x:v>
+        <x:v>1080</x:v>
       </x:c>
       <x:c r="M2" s="3" t="s">
-        <x:v>1092</x:v>
+        <x:v>1081</x:v>
       </x:c>
       <x:c r="N2" s="3" t="s">
-        <x:v>1093</x:v>
+        <x:v>1082</x:v>
       </x:c>
       <x:c r="O2" s="3" t="s">
-        <x:v>1094</x:v>
+        <x:v>1083</x:v>
       </x:c>
       <x:c r="P2" s="3" t="s">
-        <x:v>1095</x:v>
+        <x:v>1084</x:v>
       </x:c>
       <x:c r="Q2" s="3" t="s">
-        <x:v>1096</x:v>
+        <x:v>1085</x:v>
       </x:c>
       <x:c r="R2" s="3" t="s">
-        <x:v>1097</x:v>
+        <x:v>1086</x:v>
       </x:c>
       <x:c r="S2" s="3" t="s">
-        <x:v>1098</x:v>
+        <x:v>1087</x:v>
       </x:c>
       <x:c r="T2" s="3" t="s">
-        <x:v>1099</x:v>
+        <x:v>1088</x:v>
       </x:c>
       <x:c r="U2" s="3" t="s">
         <x:v>2</x:v>
@@ -10819,31 +10786,31 @@
     </x:row>
     <x:row r="3" ht="107.25" hidden="0">
       <x:c r="A3" s="3" t="s">
-        <x:v>1100</x:v>
+        <x:v>1089</x:v>
       </x:c>
       <x:c r="B3" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C3" s="3" t="s">
-        <x:v>1101</x:v>
+        <x:v>1090</x:v>
       </x:c>
       <x:c r="D3" s="3" t="s">
-        <x:v>1102</x:v>
+        <x:v>1091</x:v>
       </x:c>
       <x:c r="E3" s="3" t="s">
-        <x:v>1103</x:v>
+        <x:v>1092</x:v>
       </x:c>
       <x:c r="F3" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G3" s="3" t="s">
-        <x:v>1104</x:v>
+        <x:v>1093</x:v>
       </x:c>
       <x:c r="H3" s="3" t="s">
-        <x:v>1105</x:v>
+        <x:v>1094</x:v>
       </x:c>
       <x:c r="I3" s="3" t="s">
-        <x:v>1106</x:v>
+        <x:v>1095</x:v>
       </x:c>
       <x:c r="J3" s="3" t="s">
         <x:v>42</x:v>
@@ -10852,31 +10819,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L3" s="3" t="s">
-        <x:v>1107</x:v>
+        <x:v>1096</x:v>
       </x:c>
       <x:c r="M3" s="3" t="s">
-        <x:v>1108</x:v>
+        <x:v>1097</x:v>
       </x:c>
       <x:c r="N3" s="3" t="s">
-        <x:v>1109</x:v>
+        <x:v>1098</x:v>
       </x:c>
       <x:c r="O3" s="3" t="s">
-        <x:v>1110</x:v>
+        <x:v>1099</x:v>
       </x:c>
       <x:c r="P3" s="3" t="s">
-        <x:v>1111</x:v>
+        <x:v>1100</x:v>
       </x:c>
       <x:c r="Q3" s="3" t="s">
-        <x:v>1112</x:v>
+        <x:v>1101</x:v>
       </x:c>
       <x:c r="R3" s="3" t="s">
-        <x:v>1113</x:v>
+        <x:v>1102</x:v>
       </x:c>
       <x:c r="S3" s="3" t="s">
-        <x:v>1114</x:v>
+        <x:v>1103</x:v>
       </x:c>
       <x:c r="T3" s="3" t="s">
-        <x:v>1115</x:v>
+        <x:v>1104</x:v>
       </x:c>
       <x:c r="U3" s="3" t="s">
         <x:v>2</x:v>
@@ -10884,31 +10851,31 @@
     </x:row>
     <x:row r="4" ht="93.25" hidden="0">
       <x:c r="A4" s="3" t="s">
-        <x:v>1116</x:v>
+        <x:v>1105</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>1117</x:v>
+        <x:v>1106</x:v>
       </x:c>
       <x:c r="D4" s="3" t="s">
-        <x:v>1118</x:v>
+        <x:v>1107</x:v>
       </x:c>
       <x:c r="E4" s="3" t="s">
-        <x:v>1119</x:v>
+        <x:v>1108</x:v>
       </x:c>
       <x:c r="F4" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G4" s="3" t="s">
-        <x:v>1104</x:v>
+        <x:v>1093</x:v>
       </x:c>
       <x:c r="H4" s="3" t="s">
-        <x:v>1105</x:v>
+        <x:v>1094</x:v>
       </x:c>
       <x:c r="I4" s="3" t="s">
-        <x:v>1106</x:v>
+        <x:v>1095</x:v>
       </x:c>
       <x:c r="J4" s="3" t="s">
         <x:v>42</x:v>
@@ -10917,31 +10884,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L4" s="3" t="s">
-        <x:v>1120</x:v>
+        <x:v>1109</x:v>
       </x:c>
       <x:c r="M4" s="3" t="s">
-        <x:v>1108</x:v>
+        <x:v>1097</x:v>
       </x:c>
       <x:c r="N4" s="3" t="s">
-        <x:v>1121</x:v>
+        <x:v>1110</x:v>
       </x:c>
       <x:c r="O4" s="3" t="s">
-        <x:v>1122</x:v>
+        <x:v>1111</x:v>
       </x:c>
       <x:c r="P4" s="3" t="s">
-        <x:v>1123</x:v>
+        <x:v>1112</x:v>
       </x:c>
       <x:c r="Q4" s="3" t="s">
-        <x:v>1124</x:v>
+        <x:v>1113</x:v>
       </x:c>
       <x:c r="R4" s="3" t="s">
-        <x:v>1125</x:v>
+        <x:v>1114</x:v>
       </x:c>
       <x:c r="S4" s="3" t="s">
-        <x:v>1126</x:v>
+        <x:v>1115</x:v>
       </x:c>
       <x:c r="T4" s="3" t="s">
-        <x:v>1127</x:v>
+        <x:v>1116</x:v>
       </x:c>
       <x:c r="U4" s="3" t="s">
         <x:v>2</x:v>
@@ -10949,31 +10916,31 @@
     </x:row>
     <x:row r="5" ht="107.25" hidden="0">
       <x:c r="A5" s="3" t="s">
-        <x:v>1128</x:v>
+        <x:v>1117</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C5" s="3" t="s">
-        <x:v>1129</x:v>
+        <x:v>1118</x:v>
       </x:c>
       <x:c r="D5" s="3" t="s">
-        <x:v>1130</x:v>
+        <x:v>1119</x:v>
       </x:c>
       <x:c r="E5" s="3" t="s">
-        <x:v>1131</x:v>
+        <x:v>1120</x:v>
       </x:c>
       <x:c r="F5" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G5" s="3" t="s">
-        <x:v>1104</x:v>
+        <x:v>1093</x:v>
       </x:c>
       <x:c r="H5" s="3" t="s">
-        <x:v>1105</x:v>
+        <x:v>1094</x:v>
       </x:c>
       <x:c r="I5" s="3" t="s">
-        <x:v>1106</x:v>
+        <x:v>1095</x:v>
       </x:c>
       <x:c r="J5" s="3" t="s">
         <x:v>42</x:v>
@@ -10982,31 +10949,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L5" s="3" t="s">
-        <x:v>1132</x:v>
+        <x:v>1121</x:v>
       </x:c>
       <x:c r="M5" s="3" t="s">
-        <x:v>1108</x:v>
+        <x:v>1097</x:v>
       </x:c>
       <x:c r="N5" s="3" t="s">
-        <x:v>1133</x:v>
+        <x:v>1122</x:v>
       </x:c>
       <x:c r="O5" s="3" t="s">
-        <x:v>1134</x:v>
+        <x:v>1123</x:v>
       </x:c>
       <x:c r="P5" s="3" t="s">
-        <x:v>1135</x:v>
+        <x:v>1124</x:v>
       </x:c>
       <x:c r="Q5" s="3" t="s">
-        <x:v>1136</x:v>
+        <x:v>1125</x:v>
       </x:c>
       <x:c r="R5" s="3" t="s">
-        <x:v>1137</x:v>
+        <x:v>1126</x:v>
       </x:c>
       <x:c r="S5" s="3" t="s">
-        <x:v>1138</x:v>
+        <x:v>1127</x:v>
       </x:c>
       <x:c r="T5" s="3" t="s">
-        <x:v>1139</x:v>
+        <x:v>1128</x:v>
       </x:c>
       <x:c r="U5" s="3" t="s">
         <x:v>2</x:v>
@@ -11014,31 +10981,31 @@
     </x:row>
     <x:row r="6" ht="93.25" hidden="0">
       <x:c r="A6" s="3" t="s">
-        <x:v>1140</x:v>
+        <x:v>1129</x:v>
       </x:c>
       <x:c r="B6" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C6" s="3" t="s">
-        <x:v>1141</x:v>
+        <x:v>1130</x:v>
       </x:c>
       <x:c r="D6" s="3" t="s">
-        <x:v>1142</x:v>
+        <x:v>1131</x:v>
       </x:c>
       <x:c r="E6" s="3" t="s">
-        <x:v>1143</x:v>
+        <x:v>1132</x:v>
       </x:c>
       <x:c r="F6" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G6" s="3" t="s">
-        <x:v>1104</x:v>
+        <x:v>1093</x:v>
       </x:c>
       <x:c r="H6" s="3" t="s">
-        <x:v>1105</x:v>
+        <x:v>1094</x:v>
       </x:c>
       <x:c r="I6" s="3" t="s">
-        <x:v>1106</x:v>
+        <x:v>1095</x:v>
       </x:c>
       <x:c r="J6" s="3" t="s">
         <x:v>42</x:v>
@@ -11047,31 +11014,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L6" s="3" t="s">
-        <x:v>1144</x:v>
+        <x:v>1133</x:v>
       </x:c>
       <x:c r="M6" s="3" t="s">
-        <x:v>1108</x:v>
+        <x:v>1097</x:v>
       </x:c>
       <x:c r="N6" s="3" t="s">
-        <x:v>1145</x:v>
+        <x:v>1134</x:v>
       </x:c>
       <x:c r="O6" s="3" t="s">
-        <x:v>1146</x:v>
+        <x:v>1135</x:v>
       </x:c>
       <x:c r="P6" s="3" t="s">
-        <x:v>1147</x:v>
+        <x:v>1136</x:v>
       </x:c>
       <x:c r="Q6" s="3" t="s">
-        <x:v>1148</x:v>
+        <x:v>1137</x:v>
       </x:c>
       <x:c r="R6" s="3" t="s">
-        <x:v>1149</x:v>
+        <x:v>1138</x:v>
       </x:c>
       <x:c r="S6" s="3" t="s">
-        <x:v>1150</x:v>
+        <x:v>1139</x:v>
       </x:c>
       <x:c r="T6" s="3" t="s">
-        <x:v>1151</x:v>
+        <x:v>1140</x:v>
       </x:c>
       <x:c r="U6" s="3" t="s">
         <x:v>2</x:v>
@@ -11079,31 +11046,31 @@
     </x:row>
     <x:row r="7" ht="93.25" hidden="0">
       <x:c r="A7" s="3" t="s">
-        <x:v>1152</x:v>
+        <x:v>1141</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>1153</x:v>
+        <x:v>1142</x:v>
       </x:c>
       <x:c r="D7" s="3" t="s">
-        <x:v>1154</x:v>
+        <x:v>1143</x:v>
       </x:c>
       <x:c r="E7" s="3" t="s">
-        <x:v>1155</x:v>
+        <x:v>1144</x:v>
       </x:c>
       <x:c r="F7" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G7" s="3" t="s">
-        <x:v>1104</x:v>
+        <x:v>1093</x:v>
       </x:c>
       <x:c r="H7" s="3" t="s">
-        <x:v>1105</x:v>
+        <x:v>1094</x:v>
       </x:c>
       <x:c r="I7" s="3" t="s">
-        <x:v>1106</x:v>
+        <x:v>1095</x:v>
       </x:c>
       <x:c r="J7" s="3" t="s">
         <x:v>42</x:v>
@@ -11112,31 +11079,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="L7" s="3" t="s">
-        <x:v>1156</x:v>
+        <x:v>1145</x:v>
       </x:c>
       <x:c r="M7" s="3" t="s">
-        <x:v>1108</x:v>
+        <x:v>1097</x:v>
       </x:c>
       <x:c r="N7" s="3" t="s">
-        <x:v>1157</x:v>
+        <x:v>1146</x:v>
       </x:c>
       <x:c r="O7" s="3" t="s">
-        <x:v>1158</x:v>
+        <x:v>1147</x:v>
       </x:c>
       <x:c r="P7" s="3" t="s">
-        <x:v>1159</x:v>
+        <x:v>1148</x:v>
       </x:c>
       <x:c r="Q7" s="3" t="s">
-        <x:v>1112</x:v>
+        <x:v>1101</x:v>
       </x:c>
       <x:c r="R7" s="3" t="s">
-        <x:v>1160</x:v>
+        <x:v>1149</x:v>
       </x:c>
       <x:c r="S7" s="3" t="s">
-        <x:v>1161</x:v>
+        <x:v>1150</x:v>
       </x:c>
       <x:c r="T7" s="3" t="s">
-        <x:v>1162</x:v>
+        <x:v>1151</x:v>
       </x:c>
       <x:c r="U7" s="3" t="s">
         <x:v>2</x:v>
@@ -11144,31 +11111,31 @@
     </x:row>
     <x:row r="8" ht="93.25" hidden="0">
       <x:c r="A8" s="3" t="s">
-        <x:v>1163</x:v>
+        <x:v>1152</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>1164</x:v>
+        <x:v>1153</x:v>
       </x:c>
       <x:c r="D8" s="3" t="s">
-        <x:v>1165</x:v>
+        <x:v>1154</x:v>
       </x:c>
       <x:c r="E8" s="3" t="s">
-        <x:v>1166</x:v>
+        <x:v>1155</x:v>
       </x:c>
       <x:c r="F8" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G8" s="3" t="s">
-        <x:v>1104</x:v>
+        <x:v>1093</x:v>
       </x:c>
       <x:c r="H8" s="3" t="s">
-        <x:v>1105</x:v>
+        <x:v>1094</x:v>
       </x:c>
       <x:c r="I8" s="3" t="s">
-        <x:v>1106</x:v>
+        <x:v>1095</x:v>
       </x:c>
       <x:c r="J8" s="3" t="s">
         <x:v>42</x:v>
@@ -11177,31 +11144,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L8" s="3" t="s">
-        <x:v>1167</x:v>
+        <x:v>1156</x:v>
       </x:c>
       <x:c r="M8" s="3" t="s">
-        <x:v>1108</x:v>
+        <x:v>1097</x:v>
       </x:c>
       <x:c r="N8" s="3" t="s">
-        <x:v>1168</x:v>
+        <x:v>1157</x:v>
       </x:c>
       <x:c r="O8" s="3" t="s">
-        <x:v>1169</x:v>
+        <x:v>1158</x:v>
       </x:c>
       <x:c r="P8" s="3" t="s">
-        <x:v>1170</x:v>
+        <x:v>1159</x:v>
       </x:c>
       <x:c r="Q8" s="3" t="s">
-        <x:v>1171</x:v>
+        <x:v>1160</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
-        <x:v>1172</x:v>
+        <x:v>1161</x:v>
       </x:c>
       <x:c r="S8" s="3" t="s">
-        <x:v>1173</x:v>
+        <x:v>1162</x:v>
       </x:c>
       <x:c r="T8" s="3" t="s">
-        <x:v>1174</x:v>
+        <x:v>1163</x:v>
       </x:c>
       <x:c r="U8" s="3" t="s">
         <x:v>2</x:v>
@@ -11209,31 +11176,31 @@
     </x:row>
     <x:row r="9" ht="93.25" hidden="0">
       <x:c r="A9" s="3" t="s">
-        <x:v>1175</x:v>
+        <x:v>1164</x:v>
       </x:c>
       <x:c r="B9" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C9" s="3" t="s">
-        <x:v>1176</x:v>
+        <x:v>1165</x:v>
       </x:c>
       <x:c r="D9" s="3" t="s">
-        <x:v>1177</x:v>
+        <x:v>1166</x:v>
       </x:c>
       <x:c r="E9" s="3" t="s">
-        <x:v>1178</x:v>
+        <x:v>1167</x:v>
       </x:c>
       <x:c r="F9" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G9" s="3" t="s">
-        <x:v>1104</x:v>
+        <x:v>1093</x:v>
       </x:c>
       <x:c r="H9" s="3" t="s">
-        <x:v>1105</x:v>
+        <x:v>1094</x:v>
       </x:c>
       <x:c r="I9" s="3" t="s">
-        <x:v>1106</x:v>
+        <x:v>1095</x:v>
       </x:c>
       <x:c r="J9" s="3" t="s">
         <x:v>42</x:v>
@@ -11242,31 +11209,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L9" s="3" t="s">
-        <x:v>1179</x:v>
+        <x:v>1168</x:v>
       </x:c>
       <x:c r="M9" s="3" t="s">
-        <x:v>1108</x:v>
+        <x:v>1097</x:v>
       </x:c>
       <x:c r="N9" s="3" t="s">
-        <x:v>1180</x:v>
+        <x:v>1169</x:v>
       </x:c>
       <x:c r="O9" s="3" t="s">
-        <x:v>1181</x:v>
+        <x:v>1170</x:v>
       </x:c>
       <x:c r="P9" s="3" t="s">
-        <x:v>1182</x:v>
+        <x:v>1171</x:v>
       </x:c>
       <x:c r="Q9" s="3" t="s">
-        <x:v>1183</x:v>
+        <x:v>1172</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
-        <x:v>1184</x:v>
+        <x:v>1173</x:v>
       </x:c>
       <x:c r="S9" s="3" t="s">
-        <x:v>1185</x:v>
+        <x:v>1174</x:v>
       </x:c>
       <x:c r="T9" s="3" t="s">
-        <x:v>1186</x:v>
+        <x:v>1175</x:v>
       </x:c>
       <x:c r="U9" s="3" t="s">
         <x:v>2</x:v>
@@ -11274,31 +11241,31 @@
     </x:row>
     <x:row r="10" ht="93.25" hidden="0">
       <x:c r="A10" s="3" t="s">
-        <x:v>1187</x:v>
+        <x:v>1176</x:v>
       </x:c>
       <x:c r="B10" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C10" s="3" t="s">
-        <x:v>1188</x:v>
+        <x:v>1177</x:v>
       </x:c>
       <x:c r="D10" s="3" t="s">
-        <x:v>1189</x:v>
+        <x:v>1178</x:v>
       </x:c>
       <x:c r="E10" s="3" t="s">
-        <x:v>1190</x:v>
+        <x:v>1179</x:v>
       </x:c>
       <x:c r="F10" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G10" s="3" t="s">
-        <x:v>1104</x:v>
+        <x:v>1093</x:v>
       </x:c>
       <x:c r="H10" s="3" t="s">
-        <x:v>1105</x:v>
+        <x:v>1094</x:v>
       </x:c>
       <x:c r="I10" s="3" t="s">
-        <x:v>1106</x:v>
+        <x:v>1095</x:v>
       </x:c>
       <x:c r="J10" s="3" t="s">
         <x:v>42</x:v>
@@ -11307,31 +11274,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L10" s="3" t="s">
-        <x:v>1191</x:v>
+        <x:v>1180</x:v>
       </x:c>
       <x:c r="M10" s="3" t="s">
-        <x:v>1092</x:v>
+        <x:v>1081</x:v>
       </x:c>
       <x:c r="N10" s="3" t="s">
-        <x:v>1192</x:v>
+        <x:v>1181</x:v>
       </x:c>
       <x:c r="O10" s="3" t="s">
         <x:v>205</x:v>
       </x:c>
       <x:c r="P10" s="3" t="s">
-        <x:v>1193</x:v>
+        <x:v>1182</x:v>
       </x:c>
       <x:c r="Q10" s="3" t="s">
-        <x:v>1194</x:v>
+        <x:v>1183</x:v>
       </x:c>
       <x:c r="R10" s="3" t="s">
-        <x:v>1195</x:v>
+        <x:v>1184</x:v>
       </x:c>
       <x:c r="S10" s="3" t="s">
-        <x:v>1196</x:v>
+        <x:v>1185</x:v>
       </x:c>
       <x:c r="T10" s="3" t="s">
-        <x:v>1197</x:v>
+        <x:v>1186</x:v>
       </x:c>
       <x:c r="U10" s="3" t="s">
         <x:v>2</x:v>
@@ -11339,31 +11306,31 @@
     </x:row>
     <x:row r="11" ht="93.25" hidden="0">
       <x:c r="A11" s="3" t="s">
-        <x:v>1198</x:v>
+        <x:v>1187</x:v>
       </x:c>
       <x:c r="B11" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C11" s="3" t="s">
-        <x:v>1199</x:v>
+        <x:v>1188</x:v>
       </x:c>
       <x:c r="D11" s="3" t="s">
-        <x:v>1200</x:v>
+        <x:v>1189</x:v>
       </x:c>
       <x:c r="E11" s="3" t="s">
-        <x:v>1201</x:v>
+        <x:v>1190</x:v>
       </x:c>
       <x:c r="F11" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G11" s="3" t="s">
-        <x:v>1104</x:v>
+        <x:v>1093</x:v>
       </x:c>
       <x:c r="H11" s="3" t="s">
-        <x:v>1105</x:v>
+        <x:v>1094</x:v>
       </x:c>
       <x:c r="I11" s="3" t="s">
-        <x:v>1106</x:v>
+        <x:v>1095</x:v>
       </x:c>
       <x:c r="J11" s="3" t="s">
         <x:v>42</x:v>
@@ -11372,31 +11339,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L11" s="3" t="s">
-        <x:v>1202</x:v>
+        <x:v>1191</x:v>
       </x:c>
       <x:c r="M11" s="3" t="s">
-        <x:v>1203</x:v>
+        <x:v>1192</x:v>
       </x:c>
       <x:c r="N11" s="3" t="s">
-        <x:v>1204</x:v>
+        <x:v>1193</x:v>
       </x:c>
       <x:c r="O11" s="3" t="s">
-        <x:v>1205</x:v>
+        <x:v>1194</x:v>
       </x:c>
       <x:c r="P11" s="3" t="s">
-        <x:v>1206</x:v>
+        <x:v>1195</x:v>
       </x:c>
       <x:c r="Q11" s="3" t="s">
-        <x:v>1207</x:v>
+        <x:v>1196</x:v>
       </x:c>
       <x:c r="R11" s="3" t="s">
-        <x:v>1208</x:v>
+        <x:v>1197</x:v>
       </x:c>
       <x:c r="S11" s="3" t="s">
-        <x:v>1209</x:v>
+        <x:v>1198</x:v>
       </x:c>
       <x:c r="T11" s="3" t="s">
-        <x:v>1210</x:v>
+        <x:v>1199</x:v>
       </x:c>
       <x:c r="U11" s="3" t="s">
         <x:v>2</x:v>
@@ -11404,31 +11371,31 @@
     </x:row>
     <x:row r="12" ht="107.25" hidden="0">
       <x:c r="A12" s="3" t="s">
-        <x:v>1211</x:v>
+        <x:v>1200</x:v>
       </x:c>
       <x:c r="B12" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C12" s="3" t="s">
-        <x:v>1212</x:v>
+        <x:v>1201</x:v>
       </x:c>
       <x:c r="D12" s="3" t="s">
-        <x:v>1213</x:v>
+        <x:v>1202</x:v>
       </x:c>
       <x:c r="E12" s="3" t="s">
-        <x:v>1214</x:v>
+        <x:v>1203</x:v>
       </x:c>
       <x:c r="F12" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G12" s="3" t="s">
-        <x:v>1104</x:v>
+        <x:v>1093</x:v>
       </x:c>
       <x:c r="H12" s="3" t="s">
-        <x:v>1105</x:v>
+        <x:v>1094</x:v>
       </x:c>
       <x:c r="I12" s="3" t="s">
-        <x:v>1106</x:v>
+        <x:v>1095</x:v>
       </x:c>
       <x:c r="J12" s="3" t="s">
         <x:v>42</x:v>
@@ -11437,31 +11404,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L12" s="3" t="s">
-        <x:v>1215</x:v>
+        <x:v>1204</x:v>
       </x:c>
       <x:c r="M12" s="3" t="s">
-        <x:v>1108</x:v>
+        <x:v>1097</x:v>
       </x:c>
       <x:c r="N12" s="3" t="s">
-        <x:v>1216</x:v>
+        <x:v>1205</x:v>
       </x:c>
       <x:c r="O12" s="3" t="s">
-        <x:v>1217</x:v>
+        <x:v>1206</x:v>
       </x:c>
       <x:c r="P12" s="3" t="s">
-        <x:v>1218</x:v>
+        <x:v>1207</x:v>
       </x:c>
       <x:c r="Q12" s="3" t="s">
-        <x:v>1219</x:v>
+        <x:v>1208</x:v>
       </x:c>
       <x:c r="R12" s="3" t="s">
-        <x:v>1220</x:v>
+        <x:v>1209</x:v>
       </x:c>
       <x:c r="S12" s="3" t="s">
-        <x:v>1221</x:v>
+        <x:v>1210</x:v>
       </x:c>
       <x:c r="T12" s="3" t="s">
-        <x:v>1222</x:v>
+        <x:v>1211</x:v>
       </x:c>
       <x:c r="U12" s="3" t="s">
         <x:v>2</x:v>
@@ -11469,31 +11436,31 @@
     </x:row>
     <x:row r="13" ht="93.25" hidden="0">
       <x:c r="A13" s="3" t="s">
-        <x:v>1223</x:v>
+        <x:v>1212</x:v>
       </x:c>
       <x:c r="B13" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C13" s="3" t="s">
-        <x:v>1224</x:v>
+        <x:v>1213</x:v>
       </x:c>
       <x:c r="D13" s="3" t="s">
-        <x:v>1225</x:v>
+        <x:v>1214</x:v>
       </x:c>
       <x:c r="E13" s="3" t="s">
-        <x:v>1226</x:v>
+        <x:v>1215</x:v>
       </x:c>
       <x:c r="F13" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G13" s="3" t="s">
-        <x:v>1104</x:v>
+        <x:v>1093</x:v>
       </x:c>
       <x:c r="H13" s="3" t="s">
-        <x:v>1105</x:v>
+        <x:v>1094</x:v>
       </x:c>
       <x:c r="I13" s="3" t="s">
-        <x:v>1106</x:v>
+        <x:v>1095</x:v>
       </x:c>
       <x:c r="J13" s="3" t="s">
         <x:v>42</x:v>
@@ -11502,31 +11469,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L13" s="3" t="s">
-        <x:v>1227</x:v>
+        <x:v>1216</x:v>
       </x:c>
       <x:c r="M13" s="3" t="s">
-        <x:v>1108</x:v>
+        <x:v>1097</x:v>
       </x:c>
       <x:c r="N13" s="3" t="s">
-        <x:v>1228</x:v>
+        <x:v>1217</x:v>
       </x:c>
       <x:c r="O13" s="3" t="s">
-        <x:v>1229</x:v>
+        <x:v>1218</x:v>
       </x:c>
       <x:c r="P13" s="3" t="s">
-        <x:v>1230</x:v>
+        <x:v>1219</x:v>
       </x:c>
       <x:c r="Q13" s="3" t="s">
-        <x:v>1219</x:v>
+        <x:v>1208</x:v>
       </x:c>
       <x:c r="R13" s="3" t="s">
-        <x:v>1231</x:v>
+        <x:v>1220</x:v>
       </x:c>
       <x:c r="S13" s="3" t="s">
-        <x:v>1232</x:v>
+        <x:v>1221</x:v>
       </x:c>
       <x:c r="T13" s="3" t="s">
-        <x:v>1233</x:v>
+        <x:v>1222</x:v>
       </x:c>
       <x:c r="U13" s="3" t="s">
         <x:v>2</x:v>
@@ -11534,31 +11501,31 @@
     </x:row>
     <x:row r="14" ht="93.25" hidden="0">
       <x:c r="A14" s="3" t="s">
-        <x:v>1234</x:v>
+        <x:v>1223</x:v>
       </x:c>
       <x:c r="B14" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C14" s="3" t="s">
-        <x:v>1235</x:v>
+        <x:v>1224</x:v>
       </x:c>
       <x:c r="D14" s="3" t="s">
-        <x:v>1236</x:v>
+        <x:v>1225</x:v>
       </x:c>
       <x:c r="E14" s="3" t="s">
-        <x:v>1237</x:v>
+        <x:v>1226</x:v>
       </x:c>
       <x:c r="F14" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G14" s="3" t="s">
-        <x:v>1104</x:v>
+        <x:v>1093</x:v>
       </x:c>
       <x:c r="H14" s="3" t="s">
-        <x:v>1105</x:v>
+        <x:v>1094</x:v>
       </x:c>
       <x:c r="I14" s="3" t="s">
-        <x:v>1106</x:v>
+        <x:v>1095</x:v>
       </x:c>
       <x:c r="J14" s="3" t="s">
         <x:v>42</x:v>
@@ -11567,31 +11534,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L14" s="3" t="s">
-        <x:v>1238</x:v>
+        <x:v>1227</x:v>
       </x:c>
       <x:c r="M14" s="3" t="s">
-        <x:v>1239</x:v>
+        <x:v>1228</x:v>
       </x:c>
       <x:c r="N14" s="3" t="s">
-        <x:v>1240</x:v>
+        <x:v>1229</x:v>
       </x:c>
       <x:c r="O14" s="3" t="s">
-        <x:v>1241</x:v>
+        <x:v>1230</x:v>
       </x:c>
       <x:c r="P14" s="3" t="s">
-        <x:v>1242</x:v>
+        <x:v>1231</x:v>
       </x:c>
       <x:c r="Q14" s="3" t="s">
-        <x:v>1243</x:v>
+        <x:v>1232</x:v>
       </x:c>
       <x:c r="R14" s="3" t="s">
-        <x:v>1244</x:v>
+        <x:v>1233</x:v>
       </x:c>
       <x:c r="S14" s="3" t="s">
-        <x:v>1245</x:v>
+        <x:v>1234</x:v>
       </x:c>
       <x:c r="T14" s="3" t="s">
-        <x:v>1246</x:v>
+        <x:v>1235</x:v>
       </x:c>
       <x:c r="U14" s="3" t="s">
         <x:v>2</x:v>
@@ -11599,31 +11566,31 @@
     </x:row>
     <x:row r="15" ht="107.25" hidden="0">
       <x:c r="A15" s="3" t="s">
-        <x:v>1247</x:v>
+        <x:v>1236</x:v>
       </x:c>
       <x:c r="B15" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C15" s="3" t="s">
-        <x:v>1248</x:v>
+        <x:v>1237</x:v>
       </x:c>
       <x:c r="D15" s="3" t="s">
-        <x:v>1249</x:v>
+        <x:v>1238</x:v>
       </x:c>
       <x:c r="E15" s="3" t="s">
-        <x:v>1250</x:v>
+        <x:v>1239</x:v>
       </x:c>
       <x:c r="F15" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G15" s="3" t="s">
-        <x:v>1104</x:v>
+        <x:v>1093</x:v>
       </x:c>
       <x:c r="H15" s="3" t="s">
-        <x:v>1105</x:v>
+        <x:v>1094</x:v>
       </x:c>
       <x:c r="I15" s="3" t="s">
-        <x:v>1106</x:v>
+        <x:v>1095</x:v>
       </x:c>
       <x:c r="J15" s="3" t="s">
         <x:v>42</x:v>
@@ -11632,31 +11599,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L15" s="3" t="s">
-        <x:v>1251</x:v>
+        <x:v>1240</x:v>
       </x:c>
       <x:c r="M15" s="3" t="s">
-        <x:v>1108</x:v>
+        <x:v>1097</x:v>
       </x:c>
       <x:c r="N15" s="3" t="s">
-        <x:v>1252</x:v>
+        <x:v>1241</x:v>
       </x:c>
       <x:c r="O15" s="3" t="s">
-        <x:v>1253</x:v>
+        <x:v>1242</x:v>
       </x:c>
       <x:c r="P15" s="3" t="s">
-        <x:v>1254</x:v>
+        <x:v>1243</x:v>
       </x:c>
       <x:c r="Q15" s="3" t="s">
-        <x:v>1255</x:v>
+        <x:v>1244</x:v>
       </x:c>
       <x:c r="R15" s="3" t="s">
-        <x:v>1256</x:v>
+        <x:v>1245</x:v>
       </x:c>
       <x:c r="S15" s="3" t="s">
-        <x:v>1257</x:v>
+        <x:v>1246</x:v>
       </x:c>
       <x:c r="T15" s="3" t="s">
-        <x:v>1258</x:v>
+        <x:v>1247</x:v>
       </x:c>
       <x:c r="U15" s="3" t="s">
         <x:v>2</x:v>
@@ -11664,31 +11631,31 @@
     </x:row>
     <x:row r="16" ht="107.25" hidden="0">
       <x:c r="A16" s="3" t="s">
-        <x:v>1259</x:v>
+        <x:v>1248</x:v>
       </x:c>
       <x:c r="B16" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C16" s="3" t="s">
-        <x:v>1260</x:v>
+        <x:v>1249</x:v>
       </x:c>
       <x:c r="D16" s="3" t="s">
-        <x:v>1261</x:v>
+        <x:v>1250</x:v>
       </x:c>
       <x:c r="E16" s="3" t="s">
-        <x:v>1262</x:v>
+        <x:v>1251</x:v>
       </x:c>
       <x:c r="F16" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G16" s="3" t="s">
-        <x:v>1104</x:v>
+        <x:v>1093</x:v>
       </x:c>
       <x:c r="H16" s="3" t="s">
-        <x:v>1105</x:v>
+        <x:v>1094</x:v>
       </x:c>
       <x:c r="I16" s="3" t="s">
-        <x:v>1106</x:v>
+        <x:v>1095</x:v>
       </x:c>
       <x:c r="J16" s="3" t="s">
         <x:v>42</x:v>
@@ -11697,31 +11664,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L16" s="3" t="s">
-        <x:v>1263</x:v>
+        <x:v>1252</x:v>
       </x:c>
       <x:c r="M16" s="3" t="s">
-        <x:v>1108</x:v>
+        <x:v>1097</x:v>
       </x:c>
       <x:c r="N16" s="3" t="s">
-        <x:v>1264</x:v>
+        <x:v>1253</x:v>
       </x:c>
       <x:c r="O16" s="3" t="s">
-        <x:v>1265</x:v>
+        <x:v>1254</x:v>
       </x:c>
       <x:c r="P16" s="3" t="s">
-        <x:v>1266</x:v>
+        <x:v>1255</x:v>
       </x:c>
       <x:c r="Q16" s="3" t="s">
-        <x:v>1267</x:v>
+        <x:v>1256</x:v>
       </x:c>
       <x:c r="R16" s="3" t="s">
-        <x:v>1268</x:v>
+        <x:v>1257</x:v>
       </x:c>
       <x:c r="S16" s="3" t="s">
-        <x:v>1269</x:v>
+        <x:v>1258</x:v>
       </x:c>
       <x:c r="T16" s="3" t="s">
-        <x:v>1270</x:v>
+        <x:v>1259</x:v>
       </x:c>
       <x:c r="U16" s="3" t="s">
         <x:v>2</x:v>
@@ -11729,31 +11696,31 @@
     </x:row>
     <x:row r="17" ht="93.25" hidden="0">
       <x:c r="A17" s="3" t="s">
-        <x:v>1271</x:v>
+        <x:v>1260</x:v>
       </x:c>
       <x:c r="B17" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C17" s="3" t="s">
-        <x:v>1272</x:v>
+        <x:v>1261</x:v>
       </x:c>
       <x:c r="D17" s="3" t="s">
-        <x:v>1273</x:v>
+        <x:v>1262</x:v>
       </x:c>
       <x:c r="E17" s="3" t="s">
-        <x:v>1274</x:v>
+        <x:v>1263</x:v>
       </x:c>
       <x:c r="F17" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G17" s="3" t="s">
-        <x:v>1104</x:v>
+        <x:v>1093</x:v>
       </x:c>
       <x:c r="H17" s="3" t="s">
-        <x:v>1105</x:v>
+        <x:v>1094</x:v>
       </x:c>
       <x:c r="I17" s="3" t="s">
-        <x:v>1106</x:v>
+        <x:v>1095</x:v>
       </x:c>
       <x:c r="J17" s="3" t="s">
         <x:v>42</x:v>
@@ -11762,31 +11729,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L17" s="3" t="s">
-        <x:v>1275</x:v>
+        <x:v>1264</x:v>
       </x:c>
       <x:c r="M17" s="3" t="s">
-        <x:v>1276</x:v>
+        <x:v>1265</x:v>
       </x:c>
       <x:c r="N17" s="3" t="s">
-        <x:v>1277</x:v>
+        <x:v>1266</x:v>
       </x:c>
       <x:c r="O17" s="3" t="s">
-        <x:v>1278</x:v>
+        <x:v>1267</x:v>
       </x:c>
       <x:c r="P17" s="3" t="s">
-        <x:v>1279</x:v>
+        <x:v>1268</x:v>
       </x:c>
       <x:c r="Q17" s="3" t="s">
-        <x:v>1280</x:v>
+        <x:v>1269</x:v>
       </x:c>
       <x:c r="R17" s="3" t="s">
-        <x:v>1281</x:v>
+        <x:v>1270</x:v>
       </x:c>
       <x:c r="S17" s="3" t="s">
-        <x:v>1282</x:v>
+        <x:v>1271</x:v>
       </x:c>
       <x:c r="T17" s="3" t="s">
-        <x:v>1283</x:v>
+        <x:v>1272</x:v>
       </x:c>
       <x:c r="U17" s="3" t="s">
         <x:v>2</x:v>
@@ -11794,31 +11761,31 @@
     </x:row>
     <x:row r="18" ht="93.25" hidden="0">
       <x:c r="A18" s="3" t="s">
-        <x:v>1284</x:v>
+        <x:v>1273</x:v>
       </x:c>
       <x:c r="B18" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C18" s="3" t="s">
-        <x:v>1285</x:v>
+        <x:v>1274</x:v>
       </x:c>
       <x:c r="D18" s="3" t="s">
-        <x:v>1286</x:v>
+        <x:v>1275</x:v>
       </x:c>
       <x:c r="E18" s="3" t="s">
-        <x:v>1287</x:v>
+        <x:v>1276</x:v>
       </x:c>
       <x:c r="F18" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G18" s="3" t="s">
-        <x:v>1104</x:v>
+        <x:v>1093</x:v>
       </x:c>
       <x:c r="H18" s="3" t="s">
-        <x:v>1105</x:v>
+        <x:v>1094</x:v>
       </x:c>
       <x:c r="I18" s="3" t="s">
-        <x:v>1106</x:v>
+        <x:v>1095</x:v>
       </x:c>
       <x:c r="J18" s="3" t="s">
         <x:v>42</x:v>
@@ -11827,31 +11794,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L18" s="3" t="s">
-        <x:v>1288</x:v>
+        <x:v>1277</x:v>
       </x:c>
       <x:c r="M18" s="3" t="s">
-        <x:v>1289</x:v>
+        <x:v>1278</x:v>
       </x:c>
       <x:c r="N18" s="3" t="s">
-        <x:v>1290</x:v>
+        <x:v>1279</x:v>
       </x:c>
       <x:c r="O18" s="3" t="s">
-        <x:v>1291</x:v>
+        <x:v>1280</x:v>
       </x:c>
       <x:c r="P18" s="3" t="s">
-        <x:v>1292</x:v>
+        <x:v>1281</x:v>
       </x:c>
       <x:c r="Q18" s="3" t="s">
-        <x:v>1293</x:v>
+        <x:v>1282</x:v>
       </x:c>
       <x:c r="R18" s="3" t="s">
-        <x:v>1294</x:v>
+        <x:v>1283</x:v>
       </x:c>
       <x:c r="S18" s="3" t="s">
-        <x:v>1295</x:v>
+        <x:v>1284</x:v>
       </x:c>
       <x:c r="T18" s="3" t="s">
-        <x:v>1296</x:v>
+        <x:v>1285</x:v>
       </x:c>
       <x:c r="U18" s="3" t="s">
         <x:v>2</x:v>
@@ -11859,31 +11826,31 @@
     </x:row>
     <x:row r="19" ht="93.25" hidden="0">
       <x:c r="A19" s="3" t="s">
-        <x:v>1297</x:v>
+        <x:v>1286</x:v>
       </x:c>
       <x:c r="B19" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C19" s="3" t="s">
-        <x:v>1298</x:v>
+        <x:v>1287</x:v>
       </x:c>
       <x:c r="D19" s="3" t="s">
-        <x:v>1299</x:v>
+        <x:v>1288</x:v>
       </x:c>
       <x:c r="E19" s="3" t="s">
-        <x:v>1300</x:v>
+        <x:v>1289</x:v>
       </x:c>
       <x:c r="F19" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G19" s="3" t="s">
-        <x:v>1104</x:v>
+        <x:v>1093</x:v>
       </x:c>
       <x:c r="H19" s="3" t="s">
-        <x:v>1105</x:v>
+        <x:v>1094</x:v>
       </x:c>
       <x:c r="I19" s="3" t="s">
-        <x:v>1106</x:v>
+        <x:v>1095</x:v>
       </x:c>
       <x:c r="J19" s="3" t="s">
         <x:v>42</x:v>
@@ -11892,31 +11859,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L19" s="3" t="s">
-        <x:v>1301</x:v>
+        <x:v>1290</x:v>
       </x:c>
       <x:c r="M19" s="3" t="s">
-        <x:v>1302</x:v>
+        <x:v>1291</x:v>
       </x:c>
       <x:c r="N19" s="3" t="s">
-        <x:v>1303</x:v>
+        <x:v>1292</x:v>
       </x:c>
       <x:c r="O19" s="3" t="s">
-        <x:v>1304</x:v>
+        <x:v>1293</x:v>
       </x:c>
       <x:c r="P19" s="3" t="s">
-        <x:v>1305</x:v>
+        <x:v>1294</x:v>
       </x:c>
       <x:c r="Q19" s="3" t="s">
-        <x:v>1306</x:v>
+        <x:v>1295</x:v>
       </x:c>
       <x:c r="R19" s="3" t="s">
-        <x:v>1307</x:v>
+        <x:v>1296</x:v>
       </x:c>
       <x:c r="S19" s="3" t="s">
-        <x:v>1308</x:v>
+        <x:v>1297</x:v>
       </x:c>
       <x:c r="T19" s="3" t="s">
-        <x:v>1309</x:v>
+        <x:v>1298</x:v>
       </x:c>
       <x:c r="U19" s="3" t="s">
         <x:v>2</x:v>
@@ -11924,31 +11891,31 @@
     </x:row>
     <x:row r="20" ht="79.25" hidden="0">
       <x:c r="A20" s="3" t="s">
-        <x:v>1310</x:v>
+        <x:v>1299</x:v>
       </x:c>
       <x:c r="B20" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C20" s="3" t="s">
-        <x:v>1311</x:v>
+        <x:v>1300</x:v>
       </x:c>
       <x:c r="D20" s="3" t="s">
-        <x:v>1312</x:v>
+        <x:v>1301</x:v>
       </x:c>
       <x:c r="E20" s="3" t="s">
-        <x:v>1313</x:v>
+        <x:v>1302</x:v>
       </x:c>
       <x:c r="F20" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G20" s="3" t="s">
-        <x:v>1104</x:v>
+        <x:v>1093</x:v>
       </x:c>
       <x:c r="H20" s="3" t="s">
-        <x:v>1105</x:v>
+        <x:v>1094</x:v>
       </x:c>
       <x:c r="I20" s="3" t="s">
-        <x:v>1106</x:v>
+        <x:v>1095</x:v>
       </x:c>
       <x:c r="J20" s="3" t="s">
         <x:v>42</x:v>
@@ -11957,31 +11924,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L20" s="3" t="s">
-        <x:v>1314</x:v>
+        <x:v>1303</x:v>
       </x:c>
       <x:c r="M20" s="3" t="s">
-        <x:v>1315</x:v>
+        <x:v>1304</x:v>
       </x:c>
       <x:c r="N20" s="3" t="s">
-        <x:v>1316</x:v>
+        <x:v>1305</x:v>
       </x:c>
       <x:c r="O20" s="3" t="s">
-        <x:v>1317</x:v>
+        <x:v>1306</x:v>
       </x:c>
       <x:c r="P20" s="3" t="s">
-        <x:v>1318</x:v>
+        <x:v>1307</x:v>
       </x:c>
       <x:c r="Q20" s="3" t="s">
-        <x:v>1319</x:v>
+        <x:v>1308</x:v>
       </x:c>
       <x:c r="R20" s="3" t="s">
-        <x:v>1320</x:v>
+        <x:v>1309</x:v>
       </x:c>
       <x:c r="S20" s="3" t="s">
-        <x:v>1321</x:v>
+        <x:v>1310</x:v>
       </x:c>
       <x:c r="T20" s="3" t="s">
-        <x:v>1322</x:v>
+        <x:v>1311</x:v>
       </x:c>
       <x:c r="U20" s="3" t="s">
         <x:v>2</x:v>
@@ -11989,31 +11956,31 @@
     </x:row>
     <x:row r="21" ht="79.25" hidden="0">
       <x:c r="A21" s="3" t="s">
-        <x:v>1323</x:v>
+        <x:v>1312</x:v>
       </x:c>
       <x:c r="B21" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C21" s="3" t="s">
-        <x:v>1324</x:v>
+        <x:v>1313</x:v>
       </x:c>
       <x:c r="D21" s="3" t="s">
-        <x:v>1325</x:v>
+        <x:v>1314</x:v>
       </x:c>
       <x:c r="E21" s="3" t="s">
-        <x:v>1326</x:v>
+        <x:v>1315</x:v>
       </x:c>
       <x:c r="F21" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G21" s="3" t="s">
-        <x:v>1104</x:v>
+        <x:v>1093</x:v>
       </x:c>
       <x:c r="H21" s="3" t="s">
-        <x:v>1105</x:v>
+        <x:v>1094</x:v>
       </x:c>
       <x:c r="I21" s="3" t="s">
-        <x:v>1106</x:v>
+        <x:v>1095</x:v>
       </x:c>
       <x:c r="J21" s="3" t="s">
         <x:v>42</x:v>
@@ -12022,31 +11989,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L21" s="3" t="s">
-        <x:v>1327</x:v>
+        <x:v>1316</x:v>
       </x:c>
       <x:c r="M21" s="3" t="s">
-        <x:v>1328</x:v>
+        <x:v>1317</x:v>
       </x:c>
       <x:c r="N21" s="3" t="s">
-        <x:v>1329</x:v>
+        <x:v>1318</x:v>
       </x:c>
       <x:c r="O21" s="3" t="s">
         <x:v>218</x:v>
       </x:c>
       <x:c r="P21" s="3" t="s">
-        <x:v>1330</x:v>
+        <x:v>1319</x:v>
       </x:c>
       <x:c r="Q21" s="3" t="s">
-        <x:v>1331</x:v>
+        <x:v>1320</x:v>
       </x:c>
       <x:c r="R21" s="3" t="s">
         <x:v>221</x:v>
       </x:c>
       <x:c r="S21" s="3" t="s">
-        <x:v>1332</x:v>
+        <x:v>1321</x:v>
       </x:c>
       <x:c r="T21" s="3" t="s">
-        <x:v>1333</x:v>
+        <x:v>1322</x:v>
       </x:c>
       <x:c r="U21" s="3" t="s">
         <x:v>2</x:v>
@@ -12054,31 +12021,31 @@
     </x:row>
     <x:row r="22" ht="93.25" hidden="0">
       <x:c r="A22" s="3" t="s">
-        <x:v>1334</x:v>
+        <x:v>1323</x:v>
       </x:c>
       <x:c r="B22" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C22" s="3" t="s">
-        <x:v>1335</x:v>
+        <x:v>1324</x:v>
       </x:c>
       <x:c r="D22" s="3" t="s">
-        <x:v>1336</x:v>
+        <x:v>1325</x:v>
       </x:c>
       <x:c r="E22" s="3" t="s">
-        <x:v>1337</x:v>
+        <x:v>1326</x:v>
       </x:c>
       <x:c r="F22" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G22" s="3" t="s">
-        <x:v>1104</x:v>
+        <x:v>1093</x:v>
       </x:c>
       <x:c r="H22" s="3" t="s">
-        <x:v>1105</x:v>
+        <x:v>1094</x:v>
       </x:c>
       <x:c r="I22" s="3" t="s">
-        <x:v>1106</x:v>
+        <x:v>1095</x:v>
       </x:c>
       <x:c r="J22" s="3" t="s">
         <x:v>42</x:v>
@@ -12087,31 +12054,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L22" s="3" t="s">
-        <x:v>1338</x:v>
+        <x:v>1327</x:v>
       </x:c>
       <x:c r="M22" s="3" t="s">
-        <x:v>1203</x:v>
+        <x:v>1192</x:v>
       </x:c>
       <x:c r="N22" s="3" t="s">
-        <x:v>1339</x:v>
+        <x:v>1328</x:v>
       </x:c>
       <x:c r="O22" s="3" t="s">
-        <x:v>1340</x:v>
+        <x:v>1329</x:v>
       </x:c>
       <x:c r="P22" s="3" t="s">
-        <x:v>1341</x:v>
+        <x:v>1330</x:v>
       </x:c>
       <x:c r="Q22" s="3" t="s">
-        <x:v>1342</x:v>
+        <x:v>1331</x:v>
       </x:c>
       <x:c r="R22" s="3" t="s">
-        <x:v>1343</x:v>
+        <x:v>1332</x:v>
       </x:c>
       <x:c r="S22" s="3" t="s">
-        <x:v>1344</x:v>
+        <x:v>1333</x:v>
       </x:c>
       <x:c r="T22" s="3" t="s">
-        <x:v>1345</x:v>
+        <x:v>1334</x:v>
       </x:c>
       <x:c r="U22" s="3" t="s">
         <x:v>2</x:v>
@@ -12119,31 +12086,31 @@
     </x:row>
     <x:row r="23" ht="93.25" hidden="0">
       <x:c r="A23" s="3" t="s">
-        <x:v>1346</x:v>
+        <x:v>1335</x:v>
       </x:c>
       <x:c r="B23" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C23" s="3" t="s">
-        <x:v>1347</x:v>
+        <x:v>1336</x:v>
       </x:c>
       <x:c r="D23" s="3" t="s">
-        <x:v>1348</x:v>
+        <x:v>1337</x:v>
       </x:c>
       <x:c r="E23" s="3" t="s">
-        <x:v>1349</x:v>
+        <x:v>1338</x:v>
       </x:c>
       <x:c r="F23" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G23" s="3" t="s">
-        <x:v>1104</x:v>
+        <x:v>1093</x:v>
       </x:c>
       <x:c r="H23" s="3" t="s">
-        <x:v>1105</x:v>
+        <x:v>1094</x:v>
       </x:c>
       <x:c r="I23" s="3" t="s">
-        <x:v>1106</x:v>
+        <x:v>1095</x:v>
       </x:c>
       <x:c r="J23" s="3" t="s">
         <x:v>42</x:v>
@@ -12152,31 +12119,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L23" s="3" t="s">
-        <x:v>1350</x:v>
+        <x:v>1339</x:v>
       </x:c>
       <x:c r="M23" s="3" t="s">
-        <x:v>1351</x:v>
+        <x:v>1340</x:v>
       </x:c>
       <x:c r="N23" s="3" t="s">
-        <x:v>1352</x:v>
+        <x:v>1341</x:v>
       </x:c>
       <x:c r="O23" s="3" t="s">
-        <x:v>1353</x:v>
+        <x:v>1342</x:v>
       </x:c>
       <x:c r="P23" s="3" t="s">
-        <x:v>1354</x:v>
+        <x:v>1343</x:v>
       </x:c>
       <x:c r="Q23" s="3" t="s">
-        <x:v>1355</x:v>
+        <x:v>1344</x:v>
       </x:c>
       <x:c r="R23" s="3" t="s">
-        <x:v>1356</x:v>
+        <x:v>1345</x:v>
       </x:c>
       <x:c r="S23" s="3" t="s">
-        <x:v>1357</x:v>
+        <x:v>1346</x:v>
       </x:c>
       <x:c r="T23" s="3" t="s">
-        <x:v>1358</x:v>
+        <x:v>1347</x:v>
       </x:c>
       <x:c r="U23" s="3" t="s">
         <x:v>2</x:v>
@@ -12184,31 +12151,31 @@
     </x:row>
     <x:row r="24" ht="79.25" hidden="0">
       <x:c r="A24" s="3" t="s">
-        <x:v>1359</x:v>
+        <x:v>1348</x:v>
       </x:c>
       <x:c r="B24" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C24" s="3" t="s">
-        <x:v>1360</x:v>
+        <x:v>1349</x:v>
       </x:c>
       <x:c r="D24" s="3" t="s">
-        <x:v>1361</x:v>
+        <x:v>1350</x:v>
       </x:c>
       <x:c r="E24" s="3" t="s">
-        <x:v>1362</x:v>
+        <x:v>1351</x:v>
       </x:c>
       <x:c r="F24" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G24" s="3" t="s">
-        <x:v>1104</x:v>
+        <x:v>1093</x:v>
       </x:c>
       <x:c r="H24" s="3" t="s">
-        <x:v>1105</x:v>
+        <x:v>1094</x:v>
       </x:c>
       <x:c r="I24" s="3" t="s">
-        <x:v>1106</x:v>
+        <x:v>1095</x:v>
       </x:c>
       <x:c r="J24" s="3" t="s">
         <x:v>42</x:v>
@@ -12217,31 +12184,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L24" s="3" t="s">
-        <x:v>1363</x:v>
+        <x:v>1352</x:v>
       </x:c>
       <x:c r="M24" s="3" t="s">
-        <x:v>1328</x:v>
+        <x:v>1317</x:v>
       </x:c>
       <x:c r="N24" s="3" t="s">
-        <x:v>1364</x:v>
+        <x:v>1353</x:v>
       </x:c>
       <x:c r="O24" s="3" t="s">
-        <x:v>1365</x:v>
+        <x:v>1354</x:v>
       </x:c>
       <x:c r="P24" s="3" t="s">
-        <x:v>1366</x:v>
+        <x:v>1355</x:v>
       </x:c>
       <x:c r="Q24" s="3" t="s">
-        <x:v>1367</x:v>
+        <x:v>1356</x:v>
       </x:c>
       <x:c r="R24" s="3" t="s">
-        <x:v>1368</x:v>
+        <x:v>1357</x:v>
       </x:c>
       <x:c r="S24" s="3" t="s">
-        <x:v>1369</x:v>
+        <x:v>1358</x:v>
       </x:c>
       <x:c r="T24" s="3" t="s">
-        <x:v>1370</x:v>
+        <x:v>1359</x:v>
       </x:c>
       <x:c r="U24" s="3" t="s">
         <x:v>2</x:v>
@@ -12249,31 +12216,31 @@
     </x:row>
     <x:row r="25" ht="79.25" hidden="0">
       <x:c r="A25" s="3" t="s">
-        <x:v>1371</x:v>
+        <x:v>1360</x:v>
       </x:c>
       <x:c r="B25" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C25" s="3" t="s">
-        <x:v>1372</x:v>
+        <x:v>1361</x:v>
       </x:c>
       <x:c r="D25" s="3" t="s">
-        <x:v>1373</x:v>
+        <x:v>1362</x:v>
       </x:c>
       <x:c r="E25" s="3" t="s">
-        <x:v>1374</x:v>
+        <x:v>1363</x:v>
       </x:c>
       <x:c r="F25" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G25" s="3" t="s">
-        <x:v>1104</x:v>
+        <x:v>1093</x:v>
       </x:c>
       <x:c r="H25" s="3" t="s">
-        <x:v>1105</x:v>
+        <x:v>1094</x:v>
       </x:c>
       <x:c r="I25" s="3" t="s">
-        <x:v>1106</x:v>
+        <x:v>1095</x:v>
       </x:c>
       <x:c r="J25" s="3" t="s">
         <x:v>42</x:v>
@@ -12282,31 +12249,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L25" s="3" t="s">
-        <x:v>1375</x:v>
+        <x:v>1364</x:v>
       </x:c>
       <x:c r="M25" s="3" t="s">
-        <x:v>1328</x:v>
+        <x:v>1317</x:v>
       </x:c>
       <x:c r="N25" s="3" t="s">
-        <x:v>1376</x:v>
+        <x:v>1365</x:v>
       </x:c>
       <x:c r="O25" s="3" t="s">
-        <x:v>1377</x:v>
+        <x:v>1366</x:v>
       </x:c>
       <x:c r="P25" s="3" t="s">
-        <x:v>1378</x:v>
+        <x:v>1367</x:v>
       </x:c>
       <x:c r="Q25" s="3" t="s">
-        <x:v>1379</x:v>
+        <x:v>1368</x:v>
       </x:c>
       <x:c r="R25" s="3" t="s">
-        <x:v>1380</x:v>
+        <x:v>1369</x:v>
       </x:c>
       <x:c r="S25" s="3" t="s">
-        <x:v>1381</x:v>
+        <x:v>1370</x:v>
       </x:c>
       <x:c r="T25" s="3" t="s">
-        <x:v>1382</x:v>
+        <x:v>1371</x:v>
       </x:c>
       <x:c r="U25" s="3" t="s">
         <x:v>2</x:v>
@@ -12314,31 +12281,31 @@
     </x:row>
     <x:row r="26" ht="79.25" hidden="0">
       <x:c r="A26" s="3" t="s">
-        <x:v>1383</x:v>
+        <x:v>1372</x:v>
       </x:c>
       <x:c r="B26" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C26" s="3" t="s">
-        <x:v>1384</x:v>
+        <x:v>1373</x:v>
       </x:c>
       <x:c r="D26" s="3" t="s">
-        <x:v>1385</x:v>
+        <x:v>1374</x:v>
       </x:c>
       <x:c r="E26" s="3" t="s">
-        <x:v>1386</x:v>
+        <x:v>1375</x:v>
       </x:c>
       <x:c r="F26" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G26" s="3" t="s">
-        <x:v>1104</x:v>
+        <x:v>1093</x:v>
       </x:c>
       <x:c r="H26" s="3" t="s">
-        <x:v>1105</x:v>
+        <x:v>1094</x:v>
       </x:c>
       <x:c r="I26" s="3" t="s">
-        <x:v>1106</x:v>
+        <x:v>1095</x:v>
       </x:c>
       <x:c r="J26" s="3" t="s">
         <x:v>42</x:v>
@@ -12347,31 +12314,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L26" s="3" t="s">
-        <x:v>1387</x:v>
+        <x:v>1376</x:v>
       </x:c>
       <x:c r="M26" s="3" t="s">
-        <x:v>1388</x:v>
+        <x:v>1377</x:v>
       </x:c>
       <x:c r="N26" s="3" t="s">
-        <x:v>1389</x:v>
+        <x:v>1378</x:v>
       </x:c>
       <x:c r="O26" s="3" t="s">
-        <x:v>1390</x:v>
+        <x:v>1379</x:v>
       </x:c>
       <x:c r="P26" s="3" t="s">
-        <x:v>1391</x:v>
+        <x:v>1380</x:v>
       </x:c>
       <x:c r="Q26" s="3" t="s">
-        <x:v>1392</x:v>
+        <x:v>1381</x:v>
       </x:c>
       <x:c r="R26" s="3" t="s">
-        <x:v>1393</x:v>
+        <x:v>1382</x:v>
       </x:c>
       <x:c r="S26" s="3" t="s">
-        <x:v>1394</x:v>
+        <x:v>1383</x:v>
       </x:c>
       <x:c r="T26" s="3" t="s">
-        <x:v>1395</x:v>
+        <x:v>1384</x:v>
       </x:c>
       <x:c r="U26" s="3" t="s">
         <x:v>2</x:v>
@@ -12379,31 +12346,31 @@
     </x:row>
     <x:row r="27" ht="79.25" hidden="0">
       <x:c r="A27" s="3" t="s">
-        <x:v>1396</x:v>
+        <x:v>1385</x:v>
       </x:c>
       <x:c r="B27" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C27" s="3" t="s">
-        <x:v>1397</x:v>
+        <x:v>1386</x:v>
       </x:c>
       <x:c r="D27" s="3" t="s">
-        <x:v>1398</x:v>
+        <x:v>1387</x:v>
       </x:c>
       <x:c r="E27" s="3" t="s">
-        <x:v>1399</x:v>
+        <x:v>1388</x:v>
       </x:c>
       <x:c r="F27" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G27" s="3" t="s">
-        <x:v>1104</x:v>
+        <x:v>1093</x:v>
       </x:c>
       <x:c r="H27" s="3" t="s">
-        <x:v>1105</x:v>
+        <x:v>1094</x:v>
       </x:c>
       <x:c r="I27" s="3" t="s">
-        <x:v>1106</x:v>
+        <x:v>1095</x:v>
       </x:c>
       <x:c r="J27" s="3" t="s">
         <x:v>42</x:v>
@@ -12412,31 +12379,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L27" s="3" t="s">
-        <x:v>1400</x:v>
+        <x:v>1389</x:v>
       </x:c>
       <x:c r="M27" s="3" t="s">
-        <x:v>1401</x:v>
+        <x:v>1390</x:v>
       </x:c>
       <x:c r="N27" s="3" t="s">
-        <x:v>1402</x:v>
+        <x:v>1391</x:v>
       </x:c>
       <x:c r="O27" s="3" t="s">
-        <x:v>1403</x:v>
+        <x:v>1392</x:v>
       </x:c>
       <x:c r="P27" s="3" t="s">
-        <x:v>1404</x:v>
+        <x:v>1393</x:v>
       </x:c>
       <x:c r="Q27" s="3" t="s">
-        <x:v>1405</x:v>
+        <x:v>1394</x:v>
       </x:c>
       <x:c r="R27" s="3" t="s">
-        <x:v>1406</x:v>
+        <x:v>1395</x:v>
       </x:c>
       <x:c r="S27" s="3" t="s">
         <x:v>789</x:v>
       </x:c>
       <x:c r="T27" s="3" t="s">
-        <x:v>1407</x:v>
+        <x:v>1396</x:v>
       </x:c>
       <x:c r="U27" s="3" t="s">
         <x:v>2</x:v>
@@ -12444,31 +12411,31 @@
     </x:row>
     <x:row r="28" ht="93.25" hidden="0">
       <x:c r="A28" s="3" t="s">
-        <x:v>1408</x:v>
+        <x:v>1397</x:v>
       </x:c>
       <x:c r="B28" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C28" s="3" t="s">
-        <x:v>1409</x:v>
+        <x:v>1398</x:v>
       </x:c>
       <x:c r="D28" s="3" t="s">
-        <x:v>1410</x:v>
+        <x:v>1399</x:v>
       </x:c>
       <x:c r="E28" s="3" t="s">
-        <x:v>1411</x:v>
+        <x:v>1400</x:v>
       </x:c>
       <x:c r="F28" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G28" s="3" t="s">
-        <x:v>1104</x:v>
+        <x:v>1093</x:v>
       </x:c>
       <x:c r="H28" s="3" t="s">
-        <x:v>1105</x:v>
+        <x:v>1094</x:v>
       </x:c>
       <x:c r="I28" s="3" t="s">
-        <x:v>1106</x:v>
+        <x:v>1095</x:v>
       </x:c>
       <x:c r="J28" s="3" t="s">
         <x:v>42</x:v>
@@ -12477,31 +12444,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L28" s="3" t="s">
-        <x:v>1412</x:v>
+        <x:v>1401</x:v>
       </x:c>
       <x:c r="M28" s="3" t="s">
-        <x:v>1413</x:v>
+        <x:v>1402</x:v>
       </x:c>
       <x:c r="N28" s="3" t="s">
-        <x:v>1414</x:v>
+        <x:v>1403</x:v>
       </x:c>
       <x:c r="O28" s="3" t="s">
-        <x:v>1415</x:v>
+        <x:v>1404</x:v>
       </x:c>
       <x:c r="P28" s="3" t="s">
-        <x:v>1416</x:v>
+        <x:v>1405</x:v>
       </x:c>
       <x:c r="Q28" s="3" t="s">
-        <x:v>1417</x:v>
+        <x:v>1406</x:v>
       </x:c>
       <x:c r="R28" s="3" t="s">
-        <x:v>1418</x:v>
+        <x:v>1407</x:v>
       </x:c>
       <x:c r="S28" s="3" t="s">
         <x:v>286</x:v>
       </x:c>
       <x:c r="T28" s="3" t="s">
-        <x:v>1419</x:v>
+        <x:v>1408</x:v>
       </x:c>
       <x:c r="U28" s="3" t="s">
         <x:v>2</x:v>
@@ -12509,31 +12476,31 @@
     </x:row>
     <x:row r="29" ht="93.25" hidden="0">
       <x:c r="A29" s="3" t="s">
-        <x:v>1420</x:v>
+        <x:v>1409</x:v>
       </x:c>
       <x:c r="B29" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C29" s="3" t="s">
-        <x:v>1421</x:v>
+        <x:v>1410</x:v>
       </x:c>
       <x:c r="D29" s="3" t="s">
-        <x:v>1422</x:v>
+        <x:v>1411</x:v>
       </x:c>
       <x:c r="E29" s="3" t="s">
-        <x:v>1423</x:v>
+        <x:v>1412</x:v>
       </x:c>
       <x:c r="F29" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G29" s="3" t="s">
-        <x:v>1104</x:v>
+        <x:v>1093</x:v>
       </x:c>
       <x:c r="H29" s="3" t="s">
-        <x:v>1105</x:v>
+        <x:v>1094</x:v>
       </x:c>
       <x:c r="I29" s="3" t="s">
-        <x:v>1106</x:v>
+        <x:v>1095</x:v>
       </x:c>
       <x:c r="J29" s="3" t="s">
         <x:v>42</x:v>
@@ -12542,31 +12509,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="L29" s="3" t="s">
-        <x:v>1424</x:v>
+        <x:v>1413</x:v>
       </x:c>
       <x:c r="M29" s="3" t="s">
-        <x:v>1425</x:v>
+        <x:v>1414</x:v>
       </x:c>
       <x:c r="N29" s="3" t="s">
-        <x:v>1426</x:v>
+        <x:v>1415</x:v>
       </x:c>
       <x:c r="O29" s="3" t="s">
-        <x:v>1427</x:v>
+        <x:v>1416</x:v>
       </x:c>
       <x:c r="P29" s="3" t="s">
-        <x:v>1428</x:v>
+        <x:v>1417</x:v>
       </x:c>
       <x:c r="Q29" s="3" t="s">
-        <x:v>1429</x:v>
+        <x:v>1418</x:v>
       </x:c>
       <x:c r="R29" s="3" t="s">
-        <x:v>1430</x:v>
+        <x:v>1419</x:v>
       </x:c>
       <x:c r="S29" s="3" t="s">
-        <x:v>1431</x:v>
+        <x:v>1420</x:v>
       </x:c>
       <x:c r="T29" s="3" t="s">
-        <x:v>1432</x:v>
+        <x:v>1421</x:v>
       </x:c>
       <x:c r="U29" s="3" t="s">
         <x:v>2</x:v>
@@ -12574,31 +12541,31 @@
     </x:row>
     <x:row r="30" ht="93.25" hidden="0">
       <x:c r="A30" s="3" t="s">
-        <x:v>1433</x:v>
+        <x:v>1422</x:v>
       </x:c>
       <x:c r="B30" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C30" s="3" t="s">
-        <x:v>1434</x:v>
+        <x:v>1423</x:v>
       </x:c>
       <x:c r="D30" s="3" t="s">
-        <x:v>1435</x:v>
+        <x:v>1424</x:v>
       </x:c>
       <x:c r="E30" s="3" t="s">
-        <x:v>1436</x:v>
+        <x:v>1425</x:v>
       </x:c>
       <x:c r="F30" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G30" s="3" t="s">
-        <x:v>1104</x:v>
+        <x:v>1093</x:v>
       </x:c>
       <x:c r="H30" s="3" t="s">
-        <x:v>1105</x:v>
+        <x:v>1094</x:v>
       </x:c>
       <x:c r="I30" s="3" t="s">
-        <x:v>1106</x:v>
+        <x:v>1095</x:v>
       </x:c>
       <x:c r="J30" s="3" t="s">
         <x:v>42</x:v>
@@ -12607,31 +12574,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L30" s="3" t="s">
-        <x:v>1437</x:v>
+        <x:v>1426</x:v>
       </x:c>
       <x:c r="M30" s="3" t="s">
-        <x:v>1438</x:v>
+        <x:v>1427</x:v>
       </x:c>
       <x:c r="N30" s="3" t="s">
-        <x:v>1439</x:v>
+        <x:v>1428</x:v>
       </x:c>
       <x:c r="O30" s="3" t="s">
-        <x:v>1440</x:v>
+        <x:v>1429</x:v>
       </x:c>
       <x:c r="P30" s="3" t="s">
-        <x:v>1441</x:v>
+        <x:v>1430</x:v>
       </x:c>
       <x:c r="Q30" s="3" t="s">
-        <x:v>1442</x:v>
+        <x:v>1431</x:v>
       </x:c>
       <x:c r="R30" s="3" t="s">
-        <x:v>1443</x:v>
+        <x:v>1432</x:v>
       </x:c>
       <x:c r="S30" s="3" t="s">
-        <x:v>1444</x:v>
+        <x:v>1433</x:v>
       </x:c>
       <x:c r="T30" s="3" t="s">
-        <x:v>1445</x:v>
+        <x:v>1434</x:v>
       </x:c>
       <x:c r="U30" s="3" t="s">
         <x:v>2</x:v>
@@ -12639,7 +12606,7 @@
     </x:row>
     <x:row r="31" ht="93.25" hidden="0">
       <x:c r="A31" s="3" t="s">
-        <x:v>1446</x:v>
+        <x:v>1435</x:v>
       </x:c>
       <x:c r="B31" s="3" t="s">
         <x:v>9</x:v>
@@ -12648,22 +12615,22 @@
         <x:v>947</x:v>
       </x:c>
       <x:c r="D31" s="3" t="s">
-        <x:v>1447</x:v>
+        <x:v>1436</x:v>
       </x:c>
       <x:c r="E31" s="3" t="s">
-        <x:v>1448</x:v>
+        <x:v>1437</x:v>
       </x:c>
       <x:c r="F31" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G31" s="3" t="s">
-        <x:v>1104</x:v>
+        <x:v>1093</x:v>
       </x:c>
       <x:c r="H31" s="3" t="s">
-        <x:v>1105</x:v>
+        <x:v>1094</x:v>
       </x:c>
       <x:c r="I31" s="3" t="s">
-        <x:v>1106</x:v>
+        <x:v>1095</x:v>
       </x:c>
       <x:c r="J31" s="3" t="s">
         <x:v>42</x:v>
@@ -12672,31 +12639,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="L31" s="3" t="s">
-        <x:v>1449</x:v>
+        <x:v>1438</x:v>
       </x:c>
       <x:c r="M31" s="3" t="s">
-        <x:v>1450</x:v>
+        <x:v>1439</x:v>
       </x:c>
       <x:c r="N31" s="3" t="s">
-        <x:v>1451</x:v>
+        <x:v>1440</x:v>
       </x:c>
       <x:c r="O31" s="3" t="s">
-        <x:v>1452</x:v>
+        <x:v>1441</x:v>
       </x:c>
       <x:c r="P31" s="3" t="s">
-        <x:v>1453</x:v>
+        <x:v>1442</x:v>
       </x:c>
       <x:c r="Q31" s="3" t="s">
-        <x:v>1454</x:v>
+        <x:v>1443</x:v>
       </x:c>
       <x:c r="R31" s="3" t="s">
-        <x:v>1455</x:v>
+        <x:v>1444</x:v>
       </x:c>
       <x:c r="S31" s="3" t="s">
-        <x:v>1456</x:v>
+        <x:v>1445</x:v>
       </x:c>
       <x:c r="T31" s="3" t="s">
-        <x:v>1457</x:v>
+        <x:v>1446</x:v>
       </x:c>
       <x:c r="U31" s="3" t="s">
         <x:v>2</x:v>
@@ -12704,31 +12671,31 @@
     </x:row>
     <x:row r="32" ht="93.25" hidden="0">
       <x:c r="A32" s="3" t="s">
-        <x:v>1458</x:v>
+        <x:v>1447</x:v>
       </x:c>
       <x:c r="B32" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C32" s="3" t="s">
-        <x:v>1459</x:v>
+        <x:v>1448</x:v>
       </x:c>
       <x:c r="D32" s="3" t="s">
-        <x:v>1460</x:v>
+        <x:v>1449</x:v>
       </x:c>
       <x:c r="E32" s="3" t="s">
-        <x:v>1461</x:v>
+        <x:v>1450</x:v>
       </x:c>
       <x:c r="F32" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G32" s="3" t="s">
-        <x:v>1104</x:v>
+        <x:v>1093</x:v>
       </x:c>
       <x:c r="H32" s="3" t="s">
-        <x:v>1105</x:v>
+        <x:v>1094</x:v>
       </x:c>
       <x:c r="I32" s="3" t="s">
-        <x:v>1106</x:v>
+        <x:v>1095</x:v>
       </x:c>
       <x:c r="J32" s="3" t="s">
         <x:v>42</x:v>
@@ -12737,31 +12704,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L32" s="3" t="s">
-        <x:v>1462</x:v>
+        <x:v>1451</x:v>
       </x:c>
       <x:c r="M32" s="3" t="s">
-        <x:v>1463</x:v>
+        <x:v>1452</x:v>
       </x:c>
       <x:c r="N32" s="3" t="s">
-        <x:v>1464</x:v>
+        <x:v>1453</x:v>
       </x:c>
       <x:c r="O32" s="3" t="s">
-        <x:v>1465</x:v>
+        <x:v>1454</x:v>
       </x:c>
       <x:c r="P32" s="3" t="s">
-        <x:v>1466</x:v>
+        <x:v>1455</x:v>
       </x:c>
       <x:c r="Q32" s="3" t="s">
-        <x:v>1467</x:v>
+        <x:v>1456</x:v>
       </x:c>
       <x:c r="R32" s="3" t="s">
         <x:v>969</x:v>
       </x:c>
       <x:c r="S32" s="3" t="s">
-        <x:v>1468</x:v>
+        <x:v>1457</x:v>
       </x:c>
       <x:c r="T32" s="3" t="s">
-        <x:v>1469</x:v>
+        <x:v>1458</x:v>
       </x:c>
       <x:c r="U32" s="3" t="s">
         <x:v>2</x:v>
@@ -12769,7 +12736,7 @@
     </x:row>
     <x:row r="33" ht="93.25" hidden="0">
       <x:c r="A33" s="3" t="s">
-        <x:v>1470</x:v>
+        <x:v>1459</x:v>
       </x:c>
       <x:c r="B33" s="3" t="s">
         <x:v>9</x:v>
@@ -12778,22 +12745,22 @@
         <x:v>740</x:v>
       </x:c>
       <x:c r="D33" s="3" t="s">
-        <x:v>1471</x:v>
+        <x:v>1460</x:v>
       </x:c>
       <x:c r="E33" s="3" t="s">
-        <x:v>1472</x:v>
+        <x:v>1461</x:v>
       </x:c>
       <x:c r="F33" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G33" s="3" t="s">
-        <x:v>1104</x:v>
+        <x:v>1093</x:v>
       </x:c>
       <x:c r="H33" s="3" t="s">
-        <x:v>1105</x:v>
+        <x:v>1094</x:v>
       </x:c>
       <x:c r="I33" s="3" t="s">
-        <x:v>1106</x:v>
+        <x:v>1095</x:v>
       </x:c>
       <x:c r="J33" s="3" t="s">
         <x:v>42</x:v>
@@ -12802,31 +12769,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L33" s="3" t="s">
-        <x:v>1473</x:v>
+        <x:v>1462</x:v>
       </x:c>
       <x:c r="M33" s="3" t="s">
-        <x:v>1474</x:v>
+        <x:v>1463</x:v>
       </x:c>
       <x:c r="N33" s="3" t="s">
-        <x:v>1475</x:v>
+        <x:v>1464</x:v>
       </x:c>
       <x:c r="O33" s="3" t="s">
-        <x:v>1476</x:v>
+        <x:v>1465</x:v>
       </x:c>
       <x:c r="P33" s="3" t="s">
-        <x:v>1477</x:v>
+        <x:v>1466</x:v>
       </x:c>
       <x:c r="Q33" s="3" t="s">
-        <x:v>1478</x:v>
+        <x:v>1467</x:v>
       </x:c>
       <x:c r="R33" s="3" t="s">
-        <x:v>1479</x:v>
+        <x:v>1468</x:v>
       </x:c>
       <x:c r="S33" s="3" t="s">
-        <x:v>1480</x:v>
+        <x:v>1469</x:v>
       </x:c>
       <x:c r="T33" s="3" t="s">
-        <x:v>1481</x:v>
+        <x:v>1470</x:v>
       </x:c>
       <x:c r="U33" s="3" t="s">
         <x:v>2</x:v>
@@ -12834,7 +12801,7 @@
     </x:row>
     <x:row r="34" ht="93.25" hidden="0">
       <x:c r="A34" s="3" t="s">
-        <x:v>1482</x:v>
+        <x:v>1471</x:v>
       </x:c>
       <x:c r="B34" s="3" t="s">
         <x:v>9</x:v>
@@ -12843,22 +12810,22 @@
         <x:v>313</x:v>
       </x:c>
       <x:c r="D34" s="3" t="s">
-        <x:v>1483</x:v>
+        <x:v>1472</x:v>
       </x:c>
       <x:c r="E34" s="3" t="s">
-        <x:v>1484</x:v>
+        <x:v>1473</x:v>
       </x:c>
       <x:c r="F34" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G34" s="3" t="s">
-        <x:v>1104</x:v>
+        <x:v>1093</x:v>
       </x:c>
       <x:c r="H34" s="3" t="s">
-        <x:v>1105</x:v>
+        <x:v>1094</x:v>
       </x:c>
       <x:c r="I34" s="3" t="s">
-        <x:v>1106</x:v>
+        <x:v>1095</x:v>
       </x:c>
       <x:c r="J34" s="3" t="s">
         <x:v>42</x:v>
@@ -12867,31 +12834,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="L34" s="3" t="s">
-        <x:v>1485</x:v>
+        <x:v>1474</x:v>
       </x:c>
       <x:c r="M34" s="3" t="s">
-        <x:v>1486</x:v>
+        <x:v>1475</x:v>
       </x:c>
       <x:c r="N34" s="3" t="s">
         <x:v>978</x:v>
       </x:c>
       <x:c r="O34" s="3" t="s">
-        <x:v>1487</x:v>
+        <x:v>1476</x:v>
       </x:c>
       <x:c r="P34" s="3" t="s">
-        <x:v>1488</x:v>
+        <x:v>1477</x:v>
       </x:c>
       <x:c r="Q34" s="3" t="s">
-        <x:v>1489</x:v>
+        <x:v>1478</x:v>
       </x:c>
       <x:c r="R34" s="3" t="s">
-        <x:v>1490</x:v>
+        <x:v>1479</x:v>
       </x:c>
       <x:c r="S34" s="3" t="s">
         <x:v>323</x:v>
       </x:c>
       <x:c r="T34" s="3" t="s">
-        <x:v>1491</x:v>
+        <x:v>1480</x:v>
       </x:c>
       <x:c r="U34" s="3" t="s">
         <x:v>2</x:v>
@@ -12899,31 +12866,31 @@
     </x:row>
     <x:row r="35" ht="93.25" hidden="0">
       <x:c r="A35" s="3" t="s">
-        <x:v>1492</x:v>
+        <x:v>1481</x:v>
       </x:c>
       <x:c r="B35" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C35" s="3" t="s">
-        <x:v>1493</x:v>
+        <x:v>1482</x:v>
       </x:c>
       <x:c r="D35" s="3" t="s">
-        <x:v>1494</x:v>
+        <x:v>1483</x:v>
       </x:c>
       <x:c r="E35" s="3" t="s">
-        <x:v>1495</x:v>
+        <x:v>1484</x:v>
       </x:c>
       <x:c r="F35" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G35" s="3" t="s">
-        <x:v>1104</x:v>
+        <x:v>1093</x:v>
       </x:c>
       <x:c r="H35" s="3" t="s">
-        <x:v>1105</x:v>
+        <x:v>1094</x:v>
       </x:c>
       <x:c r="I35" s="3" t="s">
-        <x:v>1106</x:v>
+        <x:v>1095</x:v>
       </x:c>
       <x:c r="J35" s="3" t="s">
         <x:v>42</x:v>
@@ -12932,31 +12899,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L35" s="3" t="s">
-        <x:v>1496</x:v>
+        <x:v>1485</x:v>
       </x:c>
       <x:c r="M35" s="3" t="s">
-        <x:v>1497</x:v>
+        <x:v>1486</x:v>
       </x:c>
       <x:c r="N35" s="3" t="s">
-        <x:v>1498</x:v>
+        <x:v>1487</x:v>
       </x:c>
       <x:c r="O35" s="3" t="s">
-        <x:v>1278</x:v>
+        <x:v>1267</x:v>
       </x:c>
       <x:c r="P35" s="3" t="s">
-        <x:v>1499</x:v>
+        <x:v>1488</x:v>
       </x:c>
       <x:c r="Q35" s="3" t="s">
-        <x:v>1500</x:v>
+        <x:v>1489</x:v>
       </x:c>
       <x:c r="R35" s="3" t="s">
-        <x:v>1501</x:v>
+        <x:v>1490</x:v>
       </x:c>
       <x:c r="S35" s="3" t="s">
-        <x:v>1502</x:v>
+        <x:v>1491</x:v>
       </x:c>
       <x:c r="T35" s="3" t="s">
-        <x:v>1503</x:v>
+        <x:v>1492</x:v>
       </x:c>
       <x:c r="U35" s="3" t="s">
         <x:v>2</x:v>
@@ -12964,31 +12931,31 @@
     </x:row>
     <x:row r="36" ht="93.25" hidden="0">
       <x:c r="A36" s="3" t="s">
-        <x:v>1504</x:v>
+        <x:v>1493</x:v>
       </x:c>
       <x:c r="B36" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C36" s="3" t="s">
-        <x:v>1505</x:v>
+        <x:v>1494</x:v>
       </x:c>
       <x:c r="D36" s="3" t="s">
-        <x:v>1506</x:v>
+        <x:v>1495</x:v>
       </x:c>
       <x:c r="E36" s="3" t="s">
-        <x:v>1507</x:v>
+        <x:v>1496</x:v>
       </x:c>
       <x:c r="F36" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G36" s="3" t="s">
-        <x:v>1104</x:v>
+        <x:v>1093</x:v>
       </x:c>
       <x:c r="H36" s="3" t="s">
-        <x:v>1105</x:v>
+        <x:v>1094</x:v>
       </x:c>
       <x:c r="I36" s="3" t="s">
-        <x:v>1106</x:v>
+        <x:v>1095</x:v>
       </x:c>
       <x:c r="J36" s="3" t="s">
         <x:v>42</x:v>
@@ -12997,31 +12964,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L36" s="3" t="s">
-        <x:v>1508</x:v>
+        <x:v>1497</x:v>
       </x:c>
       <x:c r="M36" s="3" t="s">
-        <x:v>1108</x:v>
+        <x:v>1097</x:v>
       </x:c>
       <x:c r="N36" s="3" t="s">
-        <x:v>1509</x:v>
+        <x:v>1498</x:v>
       </x:c>
       <x:c r="O36" s="3" t="s">
-        <x:v>1510</x:v>
+        <x:v>1499</x:v>
       </x:c>
       <x:c r="P36" s="3" t="s">
-        <x:v>1511</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="Q36" s="3" t="s">
-        <x:v>1512</x:v>
+        <x:v>1501</x:v>
       </x:c>
       <x:c r="R36" s="3" t="s">
-        <x:v>1513</x:v>
+        <x:v>1502</x:v>
       </x:c>
       <x:c r="S36" s="3" t="s">
-        <x:v>1514</x:v>
+        <x:v>1503</x:v>
       </x:c>
       <x:c r="T36" s="3" t="s">
-        <x:v>1515</x:v>
+        <x:v>1504</x:v>
       </x:c>
       <x:c r="U36" s="3" t="s">
         <x:v>2</x:v>
@@ -13029,31 +12996,31 @@
     </x:row>
     <x:row r="37" ht="93.25" hidden="0">
       <x:c r="A37" s="3" t="s">
-        <x:v>1516</x:v>
+        <x:v>1505</x:v>
       </x:c>
       <x:c r="B37" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C37" s="3" t="s">
-        <x:v>1517</x:v>
+        <x:v>1506</x:v>
       </x:c>
       <x:c r="D37" s="3" t="s">
-        <x:v>1518</x:v>
+        <x:v>1507</x:v>
       </x:c>
       <x:c r="E37" s="3" t="s">
-        <x:v>1519</x:v>
+        <x:v>1508</x:v>
       </x:c>
       <x:c r="F37" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G37" s="3" t="s">
-        <x:v>1104</x:v>
+        <x:v>1093</x:v>
       </x:c>
       <x:c r="H37" s="3" t="s">
-        <x:v>1105</x:v>
+        <x:v>1094</x:v>
       </x:c>
       <x:c r="I37" s="3" t="s">
-        <x:v>1106</x:v>
+        <x:v>1095</x:v>
       </x:c>
       <x:c r="J37" s="3" t="s">
         <x:v>42</x:v>
@@ -13062,31 +13029,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L37" s="3" t="s">
-        <x:v>1520</x:v>
+        <x:v>1509</x:v>
       </x:c>
       <x:c r="M37" s="3" t="s">
-        <x:v>1521</x:v>
+        <x:v>1510</x:v>
       </x:c>
       <x:c r="N37" s="3" t="s">
-        <x:v>1522</x:v>
+        <x:v>1511</x:v>
       </x:c>
       <x:c r="O37" s="3" t="s">
-        <x:v>1523</x:v>
+        <x:v>1512</x:v>
       </x:c>
       <x:c r="P37" s="3" t="s">
-        <x:v>1524</x:v>
+        <x:v>1513</x:v>
       </x:c>
       <x:c r="Q37" s="3" t="s">
-        <x:v>1525</x:v>
+        <x:v>1514</x:v>
       </x:c>
       <x:c r="R37" s="3" t="s">
-        <x:v>1526</x:v>
+        <x:v>1515</x:v>
       </x:c>
       <x:c r="S37" s="3" t="s">
-        <x:v>1527</x:v>
+        <x:v>1516</x:v>
       </x:c>
       <x:c r="T37" s="3" t="s">
-        <x:v>1521</x:v>
+        <x:v>1510</x:v>
       </x:c>
       <x:c r="U37" s="3" t="s">
         <x:v>2</x:v>
@@ -13094,31 +13061,31 @@
     </x:row>
     <x:row r="38" ht="93.25" hidden="0">
       <x:c r="A38" s="3" t="s">
-        <x:v>1528</x:v>
+        <x:v>1517</x:v>
       </x:c>
       <x:c r="B38" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C38" s="3" t="s">
-        <x:v>1529</x:v>
+        <x:v>1518</x:v>
       </x:c>
       <x:c r="D38" s="3" t="s">
-        <x:v>1530</x:v>
+        <x:v>1519</x:v>
       </x:c>
       <x:c r="E38" s="3" t="s">
-        <x:v>1531</x:v>
+        <x:v>1520</x:v>
       </x:c>
       <x:c r="F38" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G38" s="3" t="s">
-        <x:v>1104</x:v>
+        <x:v>1093</x:v>
       </x:c>
       <x:c r="H38" s="3" t="s">
-        <x:v>1105</x:v>
+        <x:v>1094</x:v>
       </x:c>
       <x:c r="I38" s="3" t="s">
-        <x:v>1106</x:v>
+        <x:v>1095</x:v>
       </x:c>
       <x:c r="J38" s="3" t="s">
         <x:v>42</x:v>
@@ -13127,31 +13094,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L38" s="3" t="s">
-        <x:v>1532</x:v>
+        <x:v>1521</x:v>
       </x:c>
       <x:c r="M38" s="3" t="s">
-        <x:v>1203</x:v>
+        <x:v>1192</x:v>
       </x:c>
       <x:c r="N38" s="3" t="s">
-        <x:v>1533</x:v>
+        <x:v>1522</x:v>
       </x:c>
       <x:c r="O38" s="3" t="s">
-        <x:v>1534</x:v>
+        <x:v>1523</x:v>
       </x:c>
       <x:c r="P38" s="3" t="s">
-        <x:v>1535</x:v>
+        <x:v>1524</x:v>
       </x:c>
       <x:c r="Q38" s="3" t="s">
-        <x:v>1536</x:v>
+        <x:v>1525</x:v>
       </x:c>
       <x:c r="R38" s="3" t="s">
-        <x:v>1537</x:v>
+        <x:v>1526</x:v>
       </x:c>
       <x:c r="S38" s="3" t="s">
-        <x:v>1538</x:v>
+        <x:v>1527</x:v>
       </x:c>
       <x:c r="T38" s="3" t="s">
-        <x:v>1539</x:v>
+        <x:v>1528</x:v>
       </x:c>
       <x:c r="U38" s="3" t="s">
         <x:v>2</x:v>
@@ -13159,31 +13126,31 @@
     </x:row>
     <x:row r="39" ht="93.25" hidden="0">
       <x:c r="A39" s="3" t="s">
-        <x:v>1540</x:v>
+        <x:v>1529</x:v>
       </x:c>
       <x:c r="B39" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C39" s="3" t="s">
-        <x:v>1541</x:v>
+        <x:v>1530</x:v>
       </x:c>
       <x:c r="D39" s="3" t="s">
-        <x:v>1542</x:v>
+        <x:v>1531</x:v>
       </x:c>
       <x:c r="E39" s="3" t="s">
-        <x:v>1543</x:v>
+        <x:v>1532</x:v>
       </x:c>
       <x:c r="F39" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G39" s="3" t="s">
-        <x:v>1104</x:v>
+        <x:v>1093</x:v>
       </x:c>
       <x:c r="H39" s="3" t="s">
-        <x:v>1105</x:v>
+        <x:v>1094</x:v>
       </x:c>
       <x:c r="I39" s="3" t="s">
-        <x:v>1106</x:v>
+        <x:v>1095</x:v>
       </x:c>
       <x:c r="J39" s="3" t="s">
         <x:v>42</x:v>
@@ -13192,31 +13159,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="L39" s="3" t="s">
-        <x:v>1544</x:v>
+        <x:v>1533</x:v>
       </x:c>
       <x:c r="M39" s="3" t="s">
-        <x:v>1108</x:v>
+        <x:v>1097</x:v>
       </x:c>
       <x:c r="N39" s="3" t="s">
-        <x:v>1545</x:v>
+        <x:v>1534</x:v>
       </x:c>
       <x:c r="O39" s="3" t="s">
-        <x:v>1546</x:v>
+        <x:v>1535</x:v>
       </x:c>
       <x:c r="P39" s="3" t="s">
-        <x:v>1547</x:v>
+        <x:v>1536</x:v>
       </x:c>
       <x:c r="Q39" s="3" t="s">
-        <x:v>1548</x:v>
+        <x:v>1537</x:v>
       </x:c>
       <x:c r="R39" s="3" t="s">
-        <x:v>1549</x:v>
+        <x:v>1538</x:v>
       </x:c>
       <x:c r="S39" s="3" t="s">
-        <x:v>1550</x:v>
+        <x:v>1539</x:v>
       </x:c>
       <x:c r="T39" s="3" t="s">
-        <x:v>1551</x:v>
+        <x:v>1540</x:v>
       </x:c>
       <x:c r="U39" s="3" t="s">
         <x:v>2</x:v>
@@ -13225,7 +13192,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R097691cdae724974"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R58e8ce8d152f43f8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/maliev-feature-user-story-status.xlsx
+++ b/docs/maliev-feature-user-story-status.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Recba917fce4e47a5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="Rd28cc1ae787c42ac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R8bd7a0686ffc465d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="R9b3c2a324e4f4f0d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R620d757063874a96"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="R3b42b5c4788c4997"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R7e472c98811b4243"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="R120db2cb611d466c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3194,39 +3194,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">PerformanceController.cs:17-36; ChatDrawer.razor:409</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">INT-050</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Client runtime config and diagnostics</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">As an employee or operator, I can bootstrap the intranet client configuration and inspect my effective diagnostic identity.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Config endpoint returns client runtime settings and diagnostics endpoint returns current user/session/permission context.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Client bootstrap/diagnostics -&gt; BFF config and IAM diagnostic boundary</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ClientConfigController.cs; DiagnosticsController.cs</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Client bootstrap; /api/v1/diagnostics/me</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ClientConfigController GET config/client; DiagnosticsController GET me</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Read-only runtime config and diagnostic context</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Needs access-control and environment-value review.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ClientConfigController.cs:14-46; DiagnosticsController.cs:15-25</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">QE-001</x:t>
@@ -7205,7 +7172,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4b883387c6dd487a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R154e6f3cd90e41a1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10489,68 +10456,68 @@
       </x:c>
     </x:row>
     <x:row r="51" ht="51.29999923706055" hidden="0">
-      <x:c r="A51" s="3" t="s">
-        <x:v>1061</x:v>
-      </x:c>
-      <x:c r="B51" s="3" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C51" s="3" t="s">
-        <x:v>1062</x:v>
-      </x:c>
-      <x:c r="D51" s="3" t="s">
-        <x:v>1063</x:v>
-      </x:c>
-      <x:c r="E51" s="3" t="s">
-        <x:v>1064</x:v>
-      </x:c>
-      <x:c r="F51" s="3" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="G51" s="3" t="s">
-        <x:v>1001</x:v>
-      </x:c>
-      <x:c r="H51" s="3" t="s">
-        <x:v>1002</x:v>
-      </x:c>
-      <x:c r="I51" s="3" t="s">
-        <x:v>1003</x:v>
-      </x:c>
-      <x:c r="J51" s="3" t="s">
-        <x:v>1004</x:v>
-      </x:c>
-      <x:c r="K51" s="3" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="L51" s="3" t="s">
-        <x:v>1065</x:v>
-      </x:c>
-      <x:c r="M51" s="3" t="s">
-        <x:v>1066</x:v>
-      </x:c>
-      <x:c r="N51" s="3" t="s">
-        <x:v>1067</x:v>
-      </x:c>
-      <x:c r="O51" s="3" t="s">
-        <x:v>1068</x:v>
-      </x:c>
-      <x:c r="P51" s="3" t="s">
-        <x:v>1009</x:v>
-      </x:c>
-      <x:c r="Q51" s="3" t="s">
-        <x:v>852</x:v>
-      </x:c>
-      <x:c r="R51" s="3" t="s">
-        <x:v>1069</x:v>
-      </x:c>
-      <x:c r="S51" s="3" t="s">
-        <x:v>1070</x:v>
-      </x:c>
-      <x:c r="T51" s="3" t="s">
-        <x:v>1071</x:v>
-      </x:c>
-      <x:c r="U51" s="3" t="s">
-        <x:v>2</x:v>
+      <x:c r="A51" s="3" t="str">
+        <x:v>INT-050</x:v>
+      </x:c>
+      <x:c r="B51" s="3" t="str">
+        <x:v>Maliev.Intranet</x:v>
+      </x:c>
+      <x:c r="C51" s="3" t="str">
+        <x:v>Client runtime config and diagnostics</x:v>
+      </x:c>
+      <x:c r="D51" s="3" t="str">
+        <x:v>As an employee or operator, I can bootstrap the intranet client configuration and inspect my effective diagnostic identity.</x:v>
+      </x:c>
+      <x:c r="E51" s="3" t="str">
+        <x:v>Config endpoint returns client runtime settings and diagnostics endpoint returns current user/session/permission context.</x:v>
+      </x:c>
+      <x:c r="F51" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G51" s="3" t="str">
+        <x:v>Focused behavior tests passed 2026-06-23.</x:v>
+      </x:c>
+      <x:c r="H51" s="3" t="str">
+        <x:v>No behavior error observed in current focused controller retest.</x:v>
+      </x:c>
+      <x:c r="I51" s="3" t="str">
+        <x:v>No app-code fix needed; added missing focused coverage in Maliev.Intranet commit 9af6f3e.</x:v>
+      </x:c>
+      <x:c r="J51" s="3" t="str">
+        <x:v>Retested focused ClientConfig/Diagnostics controller set 5/5 passed.</x:v>
+      </x:c>
+      <x:c r="K51" s="3" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="L51" s="3" t="str">
+        <x:v>Client bootstrap/diagnostics -&gt; BFF config and IAM diagnostic boundary</x:v>
+      </x:c>
+      <x:c r="M51" s="3" t="str">
+        <x:v>ClientConfigController.cs; DiagnosticsController.cs</x:v>
+      </x:c>
+      <x:c r="N51" s="3" t="str">
+        <x:v>Client bootstrap; /api/v1/diagnostics/me</x:v>
+      </x:c>
+      <x:c r="O51" s="3" t="str">
+        <x:v>ClientConfigController GET config/client; DiagnosticsController GET me</x:v>
+      </x:c>
+      <x:c r="P51" s="3" t="str">
+        <x:v>Focused test: dotnet test Maliev.Intranet.slnx --filter "FullyQualifiedName~QuickControllerTests.ClientConfig|FullyQualifiedName~QuickControllerTests.Diagnostics" --verbosity minimal passed 5/5 on 2026-06-23. Coverage verifies default/configured client processing timeout, diagnostics effective identity payload, IAM resolution payload, and diagnostics read permission requirement.</x:v>
+      </x:c>
+      <x:c r="Q51" s="3" t="str">
+        <x:v>Intranet BFF, IAMService</x:v>
+      </x:c>
+      <x:c r="R51" s="3" t="str">
+        <x:v>Read-only runtime config and diagnostic context</x:v>
+      </x:c>
+      <x:c r="S51" s="3" t="str">
+        <x:v>No remaining INT-050 controller-contract gap from this focused retest; full authenticated browser/API middleware pass still needed in Aspire-configured runtime.</x:v>
+      </x:c>
+      <x:c r="T51" s="3" t="str">
+        <x:v>ClientConfigController.cs:15-39; DiagnosticsController.cs:13-45; QuickControllerTests.cs:358-449</x:v>
+      </x:c>
+      <x:c r="U51" s="3" t="str">
+        <x:v>2026-06-23</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="51.29999923706055" hidden="0">
@@ -10621,7 +10588,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2c18b4856e2c44ea"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad6f22be4874441d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10721,64 +10688,64 @@
     </x:row>
     <x:row r="2" ht="149.25" hidden="0">
       <x:c r="A2" s="3" t="s">
-        <x:v>1072</x:v>
+        <x:v>1061</x:v>
       </x:c>
       <x:c r="B2" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C2" s="3" t="s">
-        <x:v>1073</x:v>
+        <x:v>1062</x:v>
       </x:c>
       <x:c r="D2" s="3" t="s">
-        <x:v>1074</x:v>
+        <x:v>1063</x:v>
       </x:c>
       <x:c r="E2" s="3" t="s">
-        <x:v>1075</x:v>
+        <x:v>1064</x:v>
       </x:c>
       <x:c r="F2" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G2" s="3" t="s">
-        <x:v>1076</x:v>
+        <x:v>1065</x:v>
       </x:c>
       <x:c r="H2" s="3" t="s">
-        <x:v>1077</x:v>
+        <x:v>1066</x:v>
       </x:c>
       <x:c r="I2" s="3" t="s">
-        <x:v>1078</x:v>
+        <x:v>1067</x:v>
       </x:c>
       <x:c r="J2" s="3" t="s">
-        <x:v>1079</x:v>
+        <x:v>1068</x:v>
       </x:c>
       <x:c r="K2" s="3" t="s">
         <x:v>188</x:v>
       </x:c>
       <x:c r="L2" s="3" t="s">
-        <x:v>1080</x:v>
+        <x:v>1069</x:v>
       </x:c>
       <x:c r="M2" s="3" t="s">
-        <x:v>1081</x:v>
+        <x:v>1070</x:v>
       </x:c>
       <x:c r="N2" s="3" t="s">
-        <x:v>1082</x:v>
+        <x:v>1071</x:v>
       </x:c>
       <x:c r="O2" s="3" t="s">
-        <x:v>1083</x:v>
+        <x:v>1072</x:v>
       </x:c>
       <x:c r="P2" s="3" t="s">
-        <x:v>1084</x:v>
+        <x:v>1073</x:v>
       </x:c>
       <x:c r="Q2" s="3" t="s">
-        <x:v>1085</x:v>
+        <x:v>1074</x:v>
       </x:c>
       <x:c r="R2" s="3" t="s">
-        <x:v>1086</x:v>
+        <x:v>1075</x:v>
       </x:c>
       <x:c r="S2" s="3" t="s">
-        <x:v>1087</x:v>
+        <x:v>1076</x:v>
       </x:c>
       <x:c r="T2" s="3" t="s">
-        <x:v>1088</x:v>
+        <x:v>1077</x:v>
       </x:c>
       <x:c r="U2" s="3" t="s">
         <x:v>2</x:v>
@@ -10786,31 +10753,31 @@
     </x:row>
     <x:row r="3" ht="107.25" hidden="0">
       <x:c r="A3" s="3" t="s">
-        <x:v>1089</x:v>
+        <x:v>1078</x:v>
       </x:c>
       <x:c r="B3" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C3" s="3" t="s">
-        <x:v>1090</x:v>
+        <x:v>1079</x:v>
       </x:c>
       <x:c r="D3" s="3" t="s">
-        <x:v>1091</x:v>
+        <x:v>1080</x:v>
       </x:c>
       <x:c r="E3" s="3" t="s">
-        <x:v>1092</x:v>
+        <x:v>1081</x:v>
       </x:c>
       <x:c r="F3" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G3" s="3" t="s">
-        <x:v>1093</x:v>
+        <x:v>1082</x:v>
       </x:c>
       <x:c r="H3" s="3" t="s">
-        <x:v>1094</x:v>
+        <x:v>1083</x:v>
       </x:c>
       <x:c r="I3" s="3" t="s">
-        <x:v>1095</x:v>
+        <x:v>1084</x:v>
       </x:c>
       <x:c r="J3" s="3" t="s">
         <x:v>42</x:v>
@@ -10819,31 +10786,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L3" s="3" t="s">
-        <x:v>1096</x:v>
+        <x:v>1085</x:v>
       </x:c>
       <x:c r="M3" s="3" t="s">
-        <x:v>1097</x:v>
+        <x:v>1086</x:v>
       </x:c>
       <x:c r="N3" s="3" t="s">
-        <x:v>1098</x:v>
+        <x:v>1087</x:v>
       </x:c>
       <x:c r="O3" s="3" t="s">
-        <x:v>1099</x:v>
+        <x:v>1088</x:v>
       </x:c>
       <x:c r="P3" s="3" t="s">
-        <x:v>1100</x:v>
+        <x:v>1089</x:v>
       </x:c>
       <x:c r="Q3" s="3" t="s">
-        <x:v>1101</x:v>
+        <x:v>1090</x:v>
       </x:c>
       <x:c r="R3" s="3" t="s">
-        <x:v>1102</x:v>
+        <x:v>1091</x:v>
       </x:c>
       <x:c r="S3" s="3" t="s">
-        <x:v>1103</x:v>
+        <x:v>1092</x:v>
       </x:c>
       <x:c r="T3" s="3" t="s">
-        <x:v>1104</x:v>
+        <x:v>1093</x:v>
       </x:c>
       <x:c r="U3" s="3" t="s">
         <x:v>2</x:v>
@@ -10851,31 +10818,31 @@
     </x:row>
     <x:row r="4" ht="93.25" hidden="0">
       <x:c r="A4" s="3" t="s">
-        <x:v>1105</x:v>
+        <x:v>1094</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>1106</x:v>
+        <x:v>1095</x:v>
       </x:c>
       <x:c r="D4" s="3" t="s">
-        <x:v>1107</x:v>
+        <x:v>1096</x:v>
       </x:c>
       <x:c r="E4" s="3" t="s">
-        <x:v>1108</x:v>
+        <x:v>1097</x:v>
       </x:c>
       <x:c r="F4" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G4" s="3" t="s">
-        <x:v>1093</x:v>
+        <x:v>1082</x:v>
       </x:c>
       <x:c r="H4" s="3" t="s">
-        <x:v>1094</x:v>
+        <x:v>1083</x:v>
       </x:c>
       <x:c r="I4" s="3" t="s">
-        <x:v>1095</x:v>
+        <x:v>1084</x:v>
       </x:c>
       <x:c r="J4" s="3" t="s">
         <x:v>42</x:v>
@@ -10884,31 +10851,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L4" s="3" t="s">
-        <x:v>1109</x:v>
+        <x:v>1098</x:v>
       </x:c>
       <x:c r="M4" s="3" t="s">
-        <x:v>1097</x:v>
+        <x:v>1086</x:v>
       </x:c>
       <x:c r="N4" s="3" t="s">
-        <x:v>1110</x:v>
+        <x:v>1099</x:v>
       </x:c>
       <x:c r="O4" s="3" t="s">
-        <x:v>1111</x:v>
+        <x:v>1100</x:v>
       </x:c>
       <x:c r="P4" s="3" t="s">
-        <x:v>1112</x:v>
+        <x:v>1101</x:v>
       </x:c>
       <x:c r="Q4" s="3" t="s">
-        <x:v>1113</x:v>
+        <x:v>1102</x:v>
       </x:c>
       <x:c r="R4" s="3" t="s">
-        <x:v>1114</x:v>
+        <x:v>1103</x:v>
       </x:c>
       <x:c r="S4" s="3" t="s">
-        <x:v>1115</x:v>
+        <x:v>1104</x:v>
       </x:c>
       <x:c r="T4" s="3" t="s">
-        <x:v>1116</x:v>
+        <x:v>1105</x:v>
       </x:c>
       <x:c r="U4" s="3" t="s">
         <x:v>2</x:v>
@@ -10916,31 +10883,31 @@
     </x:row>
     <x:row r="5" ht="107.25" hidden="0">
       <x:c r="A5" s="3" t="s">
-        <x:v>1117</x:v>
+        <x:v>1106</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C5" s="3" t="s">
-        <x:v>1118</x:v>
+        <x:v>1107</x:v>
       </x:c>
       <x:c r="D5" s="3" t="s">
-        <x:v>1119</x:v>
+        <x:v>1108</x:v>
       </x:c>
       <x:c r="E5" s="3" t="s">
-        <x:v>1120</x:v>
+        <x:v>1109</x:v>
       </x:c>
       <x:c r="F5" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G5" s="3" t="s">
-        <x:v>1093</x:v>
+        <x:v>1082</x:v>
       </x:c>
       <x:c r="H5" s="3" t="s">
-        <x:v>1094</x:v>
+        <x:v>1083</x:v>
       </x:c>
       <x:c r="I5" s="3" t="s">
-        <x:v>1095</x:v>
+        <x:v>1084</x:v>
       </x:c>
       <x:c r="J5" s="3" t="s">
         <x:v>42</x:v>
@@ -10949,31 +10916,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L5" s="3" t="s">
-        <x:v>1121</x:v>
+        <x:v>1110</x:v>
       </x:c>
       <x:c r="M5" s="3" t="s">
-        <x:v>1097</x:v>
+        <x:v>1086</x:v>
       </x:c>
       <x:c r="N5" s="3" t="s">
-        <x:v>1122</x:v>
+        <x:v>1111</x:v>
       </x:c>
       <x:c r="O5" s="3" t="s">
-        <x:v>1123</x:v>
+        <x:v>1112</x:v>
       </x:c>
       <x:c r="P5" s="3" t="s">
-        <x:v>1124</x:v>
+        <x:v>1113</x:v>
       </x:c>
       <x:c r="Q5" s="3" t="s">
-        <x:v>1125</x:v>
+        <x:v>1114</x:v>
       </x:c>
       <x:c r="R5" s="3" t="s">
-        <x:v>1126</x:v>
+        <x:v>1115</x:v>
       </x:c>
       <x:c r="S5" s="3" t="s">
-        <x:v>1127</x:v>
+        <x:v>1116</x:v>
       </x:c>
       <x:c r="T5" s="3" t="s">
-        <x:v>1128</x:v>
+        <x:v>1117</x:v>
       </x:c>
       <x:c r="U5" s="3" t="s">
         <x:v>2</x:v>
@@ -10981,31 +10948,31 @@
     </x:row>
     <x:row r="6" ht="93.25" hidden="0">
       <x:c r="A6" s="3" t="s">
-        <x:v>1129</x:v>
+        <x:v>1118</x:v>
       </x:c>
       <x:c r="B6" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C6" s="3" t="s">
-        <x:v>1130</x:v>
+        <x:v>1119</x:v>
       </x:c>
       <x:c r="D6" s="3" t="s">
-        <x:v>1131</x:v>
+        <x:v>1120</x:v>
       </x:c>
       <x:c r="E6" s="3" t="s">
-        <x:v>1132</x:v>
+        <x:v>1121</x:v>
       </x:c>
       <x:c r="F6" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G6" s="3" t="s">
-        <x:v>1093</x:v>
+        <x:v>1082</x:v>
       </x:c>
       <x:c r="H6" s="3" t="s">
-        <x:v>1094</x:v>
+        <x:v>1083</x:v>
       </x:c>
       <x:c r="I6" s="3" t="s">
-        <x:v>1095</x:v>
+        <x:v>1084</x:v>
       </x:c>
       <x:c r="J6" s="3" t="s">
         <x:v>42</x:v>
@@ -11014,31 +10981,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L6" s="3" t="s">
-        <x:v>1133</x:v>
+        <x:v>1122</x:v>
       </x:c>
       <x:c r="M6" s="3" t="s">
-        <x:v>1097</x:v>
+        <x:v>1086</x:v>
       </x:c>
       <x:c r="N6" s="3" t="s">
-        <x:v>1134</x:v>
+        <x:v>1123</x:v>
       </x:c>
       <x:c r="O6" s="3" t="s">
-        <x:v>1135</x:v>
+        <x:v>1124</x:v>
       </x:c>
       <x:c r="P6" s="3" t="s">
-        <x:v>1136</x:v>
+        <x:v>1125</x:v>
       </x:c>
       <x:c r="Q6" s="3" t="s">
-        <x:v>1137</x:v>
+        <x:v>1126</x:v>
       </x:c>
       <x:c r="R6" s="3" t="s">
-        <x:v>1138</x:v>
+        <x:v>1127</x:v>
       </x:c>
       <x:c r="S6" s="3" t="s">
-        <x:v>1139</x:v>
+        <x:v>1128</x:v>
       </x:c>
       <x:c r="T6" s="3" t="s">
-        <x:v>1140</x:v>
+        <x:v>1129</x:v>
       </x:c>
       <x:c r="U6" s="3" t="s">
         <x:v>2</x:v>
@@ -11046,31 +11013,31 @@
     </x:row>
     <x:row r="7" ht="93.25" hidden="0">
       <x:c r="A7" s="3" t="s">
-        <x:v>1141</x:v>
+        <x:v>1130</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>1142</x:v>
+        <x:v>1131</x:v>
       </x:c>
       <x:c r="D7" s="3" t="s">
-        <x:v>1143</x:v>
+        <x:v>1132</x:v>
       </x:c>
       <x:c r="E7" s="3" t="s">
-        <x:v>1144</x:v>
+        <x:v>1133</x:v>
       </x:c>
       <x:c r="F7" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G7" s="3" t="s">
-        <x:v>1093</x:v>
+        <x:v>1082</x:v>
       </x:c>
       <x:c r="H7" s="3" t="s">
-        <x:v>1094</x:v>
+        <x:v>1083</x:v>
       </x:c>
       <x:c r="I7" s="3" t="s">
-        <x:v>1095</x:v>
+        <x:v>1084</x:v>
       </x:c>
       <x:c r="J7" s="3" t="s">
         <x:v>42</x:v>
@@ -11079,31 +11046,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="L7" s="3" t="s">
-        <x:v>1145</x:v>
+        <x:v>1134</x:v>
       </x:c>
       <x:c r="M7" s="3" t="s">
-        <x:v>1097</x:v>
+        <x:v>1086</x:v>
       </x:c>
       <x:c r="N7" s="3" t="s">
-        <x:v>1146</x:v>
+        <x:v>1135</x:v>
       </x:c>
       <x:c r="O7" s="3" t="s">
-        <x:v>1147</x:v>
+        <x:v>1136</x:v>
       </x:c>
       <x:c r="P7" s="3" t="s">
-        <x:v>1148</x:v>
+        <x:v>1137</x:v>
       </x:c>
       <x:c r="Q7" s="3" t="s">
-        <x:v>1101</x:v>
+        <x:v>1090</x:v>
       </x:c>
       <x:c r="R7" s="3" t="s">
-        <x:v>1149</x:v>
+        <x:v>1138</x:v>
       </x:c>
       <x:c r="S7" s="3" t="s">
-        <x:v>1150</x:v>
+        <x:v>1139</x:v>
       </x:c>
       <x:c r="T7" s="3" t="s">
-        <x:v>1151</x:v>
+        <x:v>1140</x:v>
       </x:c>
       <x:c r="U7" s="3" t="s">
         <x:v>2</x:v>
@@ -11111,31 +11078,31 @@
     </x:row>
     <x:row r="8" ht="93.25" hidden="0">
       <x:c r="A8" s="3" t="s">
-        <x:v>1152</x:v>
+        <x:v>1141</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>1153</x:v>
+        <x:v>1142</x:v>
       </x:c>
       <x:c r="D8" s="3" t="s">
-        <x:v>1154</x:v>
+        <x:v>1143</x:v>
       </x:c>
       <x:c r="E8" s="3" t="s">
-        <x:v>1155</x:v>
+        <x:v>1144</x:v>
       </x:c>
       <x:c r="F8" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G8" s="3" t="s">
-        <x:v>1093</x:v>
+        <x:v>1082</x:v>
       </x:c>
       <x:c r="H8" s="3" t="s">
-        <x:v>1094</x:v>
+        <x:v>1083</x:v>
       </x:c>
       <x:c r="I8" s="3" t="s">
-        <x:v>1095</x:v>
+        <x:v>1084</x:v>
       </x:c>
       <x:c r="J8" s="3" t="s">
         <x:v>42</x:v>
@@ -11144,31 +11111,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L8" s="3" t="s">
-        <x:v>1156</x:v>
+        <x:v>1145</x:v>
       </x:c>
       <x:c r="M8" s="3" t="s">
-        <x:v>1097</x:v>
+        <x:v>1086</x:v>
       </x:c>
       <x:c r="N8" s="3" t="s">
-        <x:v>1157</x:v>
+        <x:v>1146</x:v>
       </x:c>
       <x:c r="O8" s="3" t="s">
-        <x:v>1158</x:v>
+        <x:v>1147</x:v>
       </x:c>
       <x:c r="P8" s="3" t="s">
-        <x:v>1159</x:v>
+        <x:v>1148</x:v>
       </x:c>
       <x:c r="Q8" s="3" t="s">
-        <x:v>1160</x:v>
+        <x:v>1149</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
-        <x:v>1161</x:v>
+        <x:v>1150</x:v>
       </x:c>
       <x:c r="S8" s="3" t="s">
-        <x:v>1162</x:v>
+        <x:v>1151</x:v>
       </x:c>
       <x:c r="T8" s="3" t="s">
-        <x:v>1163</x:v>
+        <x:v>1152</x:v>
       </x:c>
       <x:c r="U8" s="3" t="s">
         <x:v>2</x:v>
@@ -11176,31 +11143,31 @@
     </x:row>
     <x:row r="9" ht="93.25" hidden="0">
       <x:c r="A9" s="3" t="s">
-        <x:v>1164</x:v>
+        <x:v>1153</x:v>
       </x:c>
       <x:c r="B9" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C9" s="3" t="s">
-        <x:v>1165</x:v>
+        <x:v>1154</x:v>
       </x:c>
       <x:c r="D9" s="3" t="s">
-        <x:v>1166</x:v>
+        <x:v>1155</x:v>
       </x:c>
       <x:c r="E9" s="3" t="s">
-        <x:v>1167</x:v>
+        <x:v>1156</x:v>
       </x:c>
       <x:c r="F9" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G9" s="3" t="s">
-        <x:v>1093</x:v>
+        <x:v>1082</x:v>
       </x:c>
       <x:c r="H9" s="3" t="s">
-        <x:v>1094</x:v>
+        <x:v>1083</x:v>
       </x:c>
       <x:c r="I9" s="3" t="s">
-        <x:v>1095</x:v>
+        <x:v>1084</x:v>
       </x:c>
       <x:c r="J9" s="3" t="s">
         <x:v>42</x:v>
@@ -11209,31 +11176,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L9" s="3" t="s">
-        <x:v>1168</x:v>
+        <x:v>1157</x:v>
       </x:c>
       <x:c r="M9" s="3" t="s">
-        <x:v>1097</x:v>
+        <x:v>1086</x:v>
       </x:c>
       <x:c r="N9" s="3" t="s">
-        <x:v>1169</x:v>
+        <x:v>1158</x:v>
       </x:c>
       <x:c r="O9" s="3" t="s">
-        <x:v>1170</x:v>
+        <x:v>1159</x:v>
       </x:c>
       <x:c r="P9" s="3" t="s">
-        <x:v>1171</x:v>
+        <x:v>1160</x:v>
       </x:c>
       <x:c r="Q9" s="3" t="s">
-        <x:v>1172</x:v>
+        <x:v>1161</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
-        <x:v>1173</x:v>
+        <x:v>1162</x:v>
       </x:c>
       <x:c r="S9" s="3" t="s">
-        <x:v>1174</x:v>
+        <x:v>1163</x:v>
       </x:c>
       <x:c r="T9" s="3" t="s">
-        <x:v>1175</x:v>
+        <x:v>1164</x:v>
       </x:c>
       <x:c r="U9" s="3" t="s">
         <x:v>2</x:v>
@@ -11241,31 +11208,31 @@
     </x:row>
     <x:row r="10" ht="93.25" hidden="0">
       <x:c r="A10" s="3" t="s">
-        <x:v>1176</x:v>
+        <x:v>1165</x:v>
       </x:c>
       <x:c r="B10" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C10" s="3" t="s">
-        <x:v>1177</x:v>
+        <x:v>1166</x:v>
       </x:c>
       <x:c r="D10" s="3" t="s">
-        <x:v>1178</x:v>
+        <x:v>1167</x:v>
       </x:c>
       <x:c r="E10" s="3" t="s">
-        <x:v>1179</x:v>
+        <x:v>1168</x:v>
       </x:c>
       <x:c r="F10" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G10" s="3" t="s">
-        <x:v>1093</x:v>
+        <x:v>1082</x:v>
       </x:c>
       <x:c r="H10" s="3" t="s">
-        <x:v>1094</x:v>
+        <x:v>1083</x:v>
       </x:c>
       <x:c r="I10" s="3" t="s">
-        <x:v>1095</x:v>
+        <x:v>1084</x:v>
       </x:c>
       <x:c r="J10" s="3" t="s">
         <x:v>42</x:v>
@@ -11274,31 +11241,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L10" s="3" t="s">
-        <x:v>1180</x:v>
+        <x:v>1169</x:v>
       </x:c>
       <x:c r="M10" s="3" t="s">
-        <x:v>1081</x:v>
+        <x:v>1070</x:v>
       </x:c>
       <x:c r="N10" s="3" t="s">
-        <x:v>1181</x:v>
+        <x:v>1170</x:v>
       </x:c>
       <x:c r="O10" s="3" t="s">
         <x:v>205</x:v>
       </x:c>
       <x:c r="P10" s="3" t="s">
-        <x:v>1182</x:v>
+        <x:v>1171</x:v>
       </x:c>
       <x:c r="Q10" s="3" t="s">
-        <x:v>1183</x:v>
+        <x:v>1172</x:v>
       </x:c>
       <x:c r="R10" s="3" t="s">
-        <x:v>1184</x:v>
+        <x:v>1173</x:v>
       </x:c>
       <x:c r="S10" s="3" t="s">
-        <x:v>1185</x:v>
+        <x:v>1174</x:v>
       </x:c>
       <x:c r="T10" s="3" t="s">
-        <x:v>1186</x:v>
+        <x:v>1175</x:v>
       </x:c>
       <x:c r="U10" s="3" t="s">
         <x:v>2</x:v>
@@ -11306,31 +11273,31 @@
     </x:row>
     <x:row r="11" ht="93.25" hidden="0">
       <x:c r="A11" s="3" t="s">
-        <x:v>1187</x:v>
+        <x:v>1176</x:v>
       </x:c>
       <x:c r="B11" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C11" s="3" t="s">
-        <x:v>1188</x:v>
+        <x:v>1177</x:v>
       </x:c>
       <x:c r="D11" s="3" t="s">
-        <x:v>1189</x:v>
+        <x:v>1178</x:v>
       </x:c>
       <x:c r="E11" s="3" t="s">
-        <x:v>1190</x:v>
+        <x:v>1179</x:v>
       </x:c>
       <x:c r="F11" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G11" s="3" t="s">
-        <x:v>1093</x:v>
+        <x:v>1082</x:v>
       </x:c>
       <x:c r="H11" s="3" t="s">
-        <x:v>1094</x:v>
+        <x:v>1083</x:v>
       </x:c>
       <x:c r="I11" s="3" t="s">
-        <x:v>1095</x:v>
+        <x:v>1084</x:v>
       </x:c>
       <x:c r="J11" s="3" t="s">
         <x:v>42</x:v>
@@ -11339,31 +11306,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L11" s="3" t="s">
-        <x:v>1191</x:v>
+        <x:v>1180</x:v>
       </x:c>
       <x:c r="M11" s="3" t="s">
-        <x:v>1192</x:v>
+        <x:v>1181</x:v>
       </x:c>
       <x:c r="N11" s="3" t="s">
-        <x:v>1193</x:v>
+        <x:v>1182</x:v>
       </x:c>
       <x:c r="O11" s="3" t="s">
-        <x:v>1194</x:v>
+        <x:v>1183</x:v>
       </x:c>
       <x:c r="P11" s="3" t="s">
-        <x:v>1195</x:v>
+        <x:v>1184</x:v>
       </x:c>
       <x:c r="Q11" s="3" t="s">
-        <x:v>1196</x:v>
+        <x:v>1185</x:v>
       </x:c>
       <x:c r="R11" s="3" t="s">
-        <x:v>1197</x:v>
+        <x:v>1186</x:v>
       </x:c>
       <x:c r="S11" s="3" t="s">
-        <x:v>1198</x:v>
+        <x:v>1187</x:v>
       </x:c>
       <x:c r="T11" s="3" t="s">
-        <x:v>1199</x:v>
+        <x:v>1188</x:v>
       </x:c>
       <x:c r="U11" s="3" t="s">
         <x:v>2</x:v>
@@ -11371,31 +11338,31 @@
     </x:row>
     <x:row r="12" ht="107.25" hidden="0">
       <x:c r="A12" s="3" t="s">
-        <x:v>1200</x:v>
+        <x:v>1189</x:v>
       </x:c>
       <x:c r="B12" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C12" s="3" t="s">
-        <x:v>1201</x:v>
+        <x:v>1190</x:v>
       </x:c>
       <x:c r="D12" s="3" t="s">
-        <x:v>1202</x:v>
+        <x:v>1191</x:v>
       </x:c>
       <x:c r="E12" s="3" t="s">
-        <x:v>1203</x:v>
+        <x:v>1192</x:v>
       </x:c>
       <x:c r="F12" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G12" s="3" t="s">
-        <x:v>1093</x:v>
+        <x:v>1082</x:v>
       </x:c>
       <x:c r="H12" s="3" t="s">
-        <x:v>1094</x:v>
+        <x:v>1083</x:v>
       </x:c>
       <x:c r="I12" s="3" t="s">
-        <x:v>1095</x:v>
+        <x:v>1084</x:v>
       </x:c>
       <x:c r="J12" s="3" t="s">
         <x:v>42</x:v>
@@ -11404,31 +11371,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L12" s="3" t="s">
-        <x:v>1204</x:v>
+        <x:v>1193</x:v>
       </x:c>
       <x:c r="M12" s="3" t="s">
-        <x:v>1097</x:v>
+        <x:v>1086</x:v>
       </x:c>
       <x:c r="N12" s="3" t="s">
-        <x:v>1205</x:v>
+        <x:v>1194</x:v>
       </x:c>
       <x:c r="O12" s="3" t="s">
-        <x:v>1206</x:v>
+        <x:v>1195</x:v>
       </x:c>
       <x:c r="P12" s="3" t="s">
-        <x:v>1207</x:v>
+        <x:v>1196</x:v>
       </x:c>
       <x:c r="Q12" s="3" t="s">
-        <x:v>1208</x:v>
+        <x:v>1197</x:v>
       </x:c>
       <x:c r="R12" s="3" t="s">
-        <x:v>1209</x:v>
+        <x:v>1198</x:v>
       </x:c>
       <x:c r="S12" s="3" t="s">
-        <x:v>1210</x:v>
+        <x:v>1199</x:v>
       </x:c>
       <x:c r="T12" s="3" t="s">
-        <x:v>1211</x:v>
+        <x:v>1200</x:v>
       </x:c>
       <x:c r="U12" s="3" t="s">
         <x:v>2</x:v>
@@ -11436,31 +11403,31 @@
     </x:row>
     <x:row r="13" ht="93.25" hidden="0">
       <x:c r="A13" s="3" t="s">
-        <x:v>1212</x:v>
+        <x:v>1201</x:v>
       </x:c>
       <x:c r="B13" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C13" s="3" t="s">
-        <x:v>1213</x:v>
+        <x:v>1202</x:v>
       </x:c>
       <x:c r="D13" s="3" t="s">
-        <x:v>1214</x:v>
+        <x:v>1203</x:v>
       </x:c>
       <x:c r="E13" s="3" t="s">
-        <x:v>1215</x:v>
+        <x:v>1204</x:v>
       </x:c>
       <x:c r="F13" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G13" s="3" t="s">
-        <x:v>1093</x:v>
+        <x:v>1082</x:v>
       </x:c>
       <x:c r="H13" s="3" t="s">
-        <x:v>1094</x:v>
+        <x:v>1083</x:v>
       </x:c>
       <x:c r="I13" s="3" t="s">
-        <x:v>1095</x:v>
+        <x:v>1084</x:v>
       </x:c>
       <x:c r="J13" s="3" t="s">
         <x:v>42</x:v>
@@ -11469,31 +11436,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L13" s="3" t="s">
-        <x:v>1216</x:v>
+        <x:v>1205</x:v>
       </x:c>
       <x:c r="M13" s="3" t="s">
-        <x:v>1097</x:v>
+        <x:v>1086</x:v>
       </x:c>
       <x:c r="N13" s="3" t="s">
-        <x:v>1217</x:v>
+        <x:v>1206</x:v>
       </x:c>
       <x:c r="O13" s="3" t="s">
-        <x:v>1218</x:v>
+        <x:v>1207</x:v>
       </x:c>
       <x:c r="P13" s="3" t="s">
-        <x:v>1219</x:v>
+        <x:v>1208</x:v>
       </x:c>
       <x:c r="Q13" s="3" t="s">
-        <x:v>1208</x:v>
+        <x:v>1197</x:v>
       </x:c>
       <x:c r="R13" s="3" t="s">
-        <x:v>1220</x:v>
+        <x:v>1209</x:v>
       </x:c>
       <x:c r="S13" s="3" t="s">
-        <x:v>1221</x:v>
+        <x:v>1210</x:v>
       </x:c>
       <x:c r="T13" s="3" t="s">
-        <x:v>1222</x:v>
+        <x:v>1211</x:v>
       </x:c>
       <x:c r="U13" s="3" t="s">
         <x:v>2</x:v>
@@ -11501,31 +11468,31 @@
     </x:row>
     <x:row r="14" ht="93.25" hidden="0">
       <x:c r="A14" s="3" t="s">
-        <x:v>1223</x:v>
+        <x:v>1212</x:v>
       </x:c>
       <x:c r="B14" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C14" s="3" t="s">
-        <x:v>1224</x:v>
+        <x:v>1213</x:v>
       </x:c>
       <x:c r="D14" s="3" t="s">
-        <x:v>1225</x:v>
+        <x:v>1214</x:v>
       </x:c>
       <x:c r="E14" s="3" t="s">
-        <x:v>1226</x:v>
+        <x:v>1215</x:v>
       </x:c>
       <x:c r="F14" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G14" s="3" t="s">
-        <x:v>1093</x:v>
+        <x:v>1082</x:v>
       </x:c>
       <x:c r="H14" s="3" t="s">
-        <x:v>1094</x:v>
+        <x:v>1083</x:v>
       </x:c>
       <x:c r="I14" s="3" t="s">
-        <x:v>1095</x:v>
+        <x:v>1084</x:v>
       </x:c>
       <x:c r="J14" s="3" t="s">
         <x:v>42</x:v>
@@ -11534,31 +11501,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L14" s="3" t="s">
-        <x:v>1227</x:v>
+        <x:v>1216</x:v>
       </x:c>
       <x:c r="M14" s="3" t="s">
-        <x:v>1228</x:v>
+        <x:v>1217</x:v>
       </x:c>
       <x:c r="N14" s="3" t="s">
-        <x:v>1229</x:v>
+        <x:v>1218</x:v>
       </x:c>
       <x:c r="O14" s="3" t="s">
-        <x:v>1230</x:v>
+        <x:v>1219</x:v>
       </x:c>
       <x:c r="P14" s="3" t="s">
-        <x:v>1231</x:v>
+        <x:v>1220</x:v>
       </x:c>
       <x:c r="Q14" s="3" t="s">
-        <x:v>1232</x:v>
+        <x:v>1221</x:v>
       </x:c>
       <x:c r="R14" s="3" t="s">
-        <x:v>1233</x:v>
+        <x:v>1222</x:v>
       </x:c>
       <x:c r="S14" s="3" t="s">
-        <x:v>1234</x:v>
+        <x:v>1223</x:v>
       </x:c>
       <x:c r="T14" s="3" t="s">
-        <x:v>1235</x:v>
+        <x:v>1224</x:v>
       </x:c>
       <x:c r="U14" s="3" t="s">
         <x:v>2</x:v>
@@ -11566,31 +11533,31 @@
     </x:row>
     <x:row r="15" ht="107.25" hidden="0">
       <x:c r="A15" s="3" t="s">
-        <x:v>1236</x:v>
+        <x:v>1225</x:v>
       </x:c>
       <x:c r="B15" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C15" s="3" t="s">
-        <x:v>1237</x:v>
+        <x:v>1226</x:v>
       </x:c>
       <x:c r="D15" s="3" t="s">
-        <x:v>1238</x:v>
+        <x:v>1227</x:v>
       </x:c>
       <x:c r="E15" s="3" t="s">
-        <x:v>1239</x:v>
+        <x:v>1228</x:v>
       </x:c>
       <x:c r="F15" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G15" s="3" t="s">
-        <x:v>1093</x:v>
+        <x:v>1082</x:v>
       </x:c>
       <x:c r="H15" s="3" t="s">
-        <x:v>1094</x:v>
+        <x:v>1083</x:v>
       </x:c>
       <x:c r="I15" s="3" t="s">
-        <x:v>1095</x:v>
+        <x:v>1084</x:v>
       </x:c>
       <x:c r="J15" s="3" t="s">
         <x:v>42</x:v>
@@ -11599,31 +11566,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L15" s="3" t="s">
-        <x:v>1240</x:v>
+        <x:v>1229</x:v>
       </x:c>
       <x:c r="M15" s="3" t="s">
-        <x:v>1097</x:v>
+        <x:v>1086</x:v>
       </x:c>
       <x:c r="N15" s="3" t="s">
-        <x:v>1241</x:v>
+        <x:v>1230</x:v>
       </x:c>
       <x:c r="O15" s="3" t="s">
-        <x:v>1242</x:v>
+        <x:v>1231</x:v>
       </x:c>
       <x:c r="P15" s="3" t="s">
-        <x:v>1243</x:v>
+        <x:v>1232</x:v>
       </x:c>
       <x:c r="Q15" s="3" t="s">
-        <x:v>1244</x:v>
+        <x:v>1233</x:v>
       </x:c>
       <x:c r="R15" s="3" t="s">
-        <x:v>1245</x:v>
+        <x:v>1234</x:v>
       </x:c>
       <x:c r="S15" s="3" t="s">
-        <x:v>1246</x:v>
+        <x:v>1235</x:v>
       </x:c>
       <x:c r="T15" s="3" t="s">
-        <x:v>1247</x:v>
+        <x:v>1236</x:v>
       </x:c>
       <x:c r="U15" s="3" t="s">
         <x:v>2</x:v>
@@ -11631,31 +11598,31 @@
     </x:row>
     <x:row r="16" ht="107.25" hidden="0">
       <x:c r="A16" s="3" t="s">
-        <x:v>1248</x:v>
+        <x:v>1237</x:v>
       </x:c>
       <x:c r="B16" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C16" s="3" t="s">
-        <x:v>1249</x:v>
+        <x:v>1238</x:v>
       </x:c>
       <x:c r="D16" s="3" t="s">
-        <x:v>1250</x:v>
+        <x:v>1239</x:v>
       </x:c>
       <x:c r="E16" s="3" t="s">
-        <x:v>1251</x:v>
+        <x:v>1240</x:v>
       </x:c>
       <x:c r="F16" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G16" s="3" t="s">
-        <x:v>1093</x:v>
+        <x:v>1082</x:v>
       </x:c>
       <x:c r="H16" s="3" t="s">
-        <x:v>1094</x:v>
+        <x:v>1083</x:v>
       </x:c>
       <x:c r="I16" s="3" t="s">
-        <x:v>1095</x:v>
+        <x:v>1084</x:v>
       </x:c>
       <x:c r="J16" s="3" t="s">
         <x:v>42</x:v>
@@ -11664,31 +11631,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L16" s="3" t="s">
-        <x:v>1252</x:v>
+        <x:v>1241</x:v>
       </x:c>
       <x:c r="M16" s="3" t="s">
-        <x:v>1097</x:v>
+        <x:v>1086</x:v>
       </x:c>
       <x:c r="N16" s="3" t="s">
-        <x:v>1253</x:v>
+        <x:v>1242</x:v>
       </x:c>
       <x:c r="O16" s="3" t="s">
-        <x:v>1254</x:v>
+        <x:v>1243</x:v>
       </x:c>
       <x:c r="P16" s="3" t="s">
-        <x:v>1255</x:v>
+        <x:v>1244</x:v>
       </x:c>
       <x:c r="Q16" s="3" t="s">
-        <x:v>1256</x:v>
+        <x:v>1245</x:v>
       </x:c>
       <x:c r="R16" s="3" t="s">
-        <x:v>1257</x:v>
+        <x:v>1246</x:v>
       </x:c>
       <x:c r="S16" s="3" t="s">
-        <x:v>1258</x:v>
+        <x:v>1247</x:v>
       </x:c>
       <x:c r="T16" s="3" t="s">
-        <x:v>1259</x:v>
+        <x:v>1248</x:v>
       </x:c>
       <x:c r="U16" s="3" t="s">
         <x:v>2</x:v>
@@ -11696,31 +11663,31 @@
     </x:row>
     <x:row r="17" ht="93.25" hidden="0">
       <x:c r="A17" s="3" t="s">
-        <x:v>1260</x:v>
+        <x:v>1249</x:v>
       </x:c>
       <x:c r="B17" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C17" s="3" t="s">
-        <x:v>1261</x:v>
+        <x:v>1250</x:v>
       </x:c>
       <x:c r="D17" s="3" t="s">
-        <x:v>1262</x:v>
+        <x:v>1251</x:v>
       </x:c>
       <x:c r="E17" s="3" t="s">
-        <x:v>1263</x:v>
+        <x:v>1252</x:v>
       </x:c>
       <x:c r="F17" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G17" s="3" t="s">
-        <x:v>1093</x:v>
+        <x:v>1082</x:v>
       </x:c>
       <x:c r="H17" s="3" t="s">
-        <x:v>1094</x:v>
+        <x:v>1083</x:v>
       </x:c>
       <x:c r="I17" s="3" t="s">
-        <x:v>1095</x:v>
+        <x:v>1084</x:v>
       </x:c>
       <x:c r="J17" s="3" t="s">
         <x:v>42</x:v>
@@ -11729,31 +11696,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L17" s="3" t="s">
-        <x:v>1264</x:v>
+        <x:v>1253</x:v>
       </x:c>
       <x:c r="M17" s="3" t="s">
-        <x:v>1265</x:v>
+        <x:v>1254</x:v>
       </x:c>
       <x:c r="N17" s="3" t="s">
-        <x:v>1266</x:v>
+        <x:v>1255</x:v>
       </x:c>
       <x:c r="O17" s="3" t="s">
-        <x:v>1267</x:v>
+        <x:v>1256</x:v>
       </x:c>
       <x:c r="P17" s="3" t="s">
-        <x:v>1268</x:v>
+        <x:v>1257</x:v>
       </x:c>
       <x:c r="Q17" s="3" t="s">
-        <x:v>1269</x:v>
+        <x:v>1258</x:v>
       </x:c>
       <x:c r="R17" s="3" t="s">
-        <x:v>1270</x:v>
+        <x:v>1259</x:v>
       </x:c>
       <x:c r="S17" s="3" t="s">
-        <x:v>1271</x:v>
+        <x:v>1260</x:v>
       </x:c>
       <x:c r="T17" s="3" t="s">
-        <x:v>1272</x:v>
+        <x:v>1261</x:v>
       </x:c>
       <x:c r="U17" s="3" t="s">
         <x:v>2</x:v>
@@ -11761,31 +11728,31 @@
     </x:row>
     <x:row r="18" ht="93.25" hidden="0">
       <x:c r="A18" s="3" t="s">
-        <x:v>1273</x:v>
+        <x:v>1262</x:v>
       </x:c>
       <x:c r="B18" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C18" s="3" t="s">
-        <x:v>1274</x:v>
+        <x:v>1263</x:v>
       </x:c>
       <x:c r="D18" s="3" t="s">
-        <x:v>1275</x:v>
+        <x:v>1264</x:v>
       </x:c>
       <x:c r="E18" s="3" t="s">
-        <x:v>1276</x:v>
+        <x:v>1265</x:v>
       </x:c>
       <x:c r="F18" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G18" s="3" t="s">
-        <x:v>1093</x:v>
+        <x:v>1082</x:v>
       </x:c>
       <x:c r="H18" s="3" t="s">
-        <x:v>1094</x:v>
+        <x:v>1083</x:v>
       </x:c>
       <x:c r="I18" s="3" t="s">
-        <x:v>1095</x:v>
+        <x:v>1084</x:v>
       </x:c>
       <x:c r="J18" s="3" t="s">
         <x:v>42</x:v>
@@ -11794,31 +11761,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L18" s="3" t="s">
-        <x:v>1277</x:v>
+        <x:v>1266</x:v>
       </x:c>
       <x:c r="M18" s="3" t="s">
-        <x:v>1278</x:v>
+        <x:v>1267</x:v>
       </x:c>
       <x:c r="N18" s="3" t="s">
-        <x:v>1279</x:v>
+        <x:v>1268</x:v>
       </x:c>
       <x:c r="O18" s="3" t="s">
-        <x:v>1280</x:v>
+        <x:v>1269</x:v>
       </x:c>
       <x:c r="P18" s="3" t="s">
-        <x:v>1281</x:v>
+        <x:v>1270</x:v>
       </x:c>
       <x:c r="Q18" s="3" t="s">
-        <x:v>1282</x:v>
+        <x:v>1271</x:v>
       </x:c>
       <x:c r="R18" s="3" t="s">
-        <x:v>1283</x:v>
+        <x:v>1272</x:v>
       </x:c>
       <x:c r="S18" s="3" t="s">
-        <x:v>1284</x:v>
+        <x:v>1273</x:v>
       </x:c>
       <x:c r="T18" s="3" t="s">
-        <x:v>1285</x:v>
+        <x:v>1274</x:v>
       </x:c>
       <x:c r="U18" s="3" t="s">
         <x:v>2</x:v>
@@ -11826,31 +11793,31 @@
     </x:row>
     <x:row r="19" ht="93.25" hidden="0">
       <x:c r="A19" s="3" t="s">
-        <x:v>1286</x:v>
+        <x:v>1275</x:v>
       </x:c>
       <x:c r="B19" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C19" s="3" t="s">
-        <x:v>1287</x:v>
+        <x:v>1276</x:v>
       </x:c>
       <x:c r="D19" s="3" t="s">
-        <x:v>1288</x:v>
+        <x:v>1277</x:v>
       </x:c>
       <x:c r="E19" s="3" t="s">
-        <x:v>1289</x:v>
+        <x:v>1278</x:v>
       </x:c>
       <x:c r="F19" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G19" s="3" t="s">
-        <x:v>1093</x:v>
+        <x:v>1082</x:v>
       </x:c>
       <x:c r="H19" s="3" t="s">
-        <x:v>1094</x:v>
+        <x:v>1083</x:v>
       </x:c>
       <x:c r="I19" s="3" t="s">
-        <x:v>1095</x:v>
+        <x:v>1084</x:v>
       </x:c>
       <x:c r="J19" s="3" t="s">
         <x:v>42</x:v>
@@ -11859,31 +11826,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L19" s="3" t="s">
-        <x:v>1290</x:v>
+        <x:v>1279</x:v>
       </x:c>
       <x:c r="M19" s="3" t="s">
-        <x:v>1291</x:v>
+        <x:v>1280</x:v>
       </x:c>
       <x:c r="N19" s="3" t="s">
-        <x:v>1292</x:v>
+        <x:v>1281</x:v>
       </x:c>
       <x:c r="O19" s="3" t="s">
-        <x:v>1293</x:v>
+        <x:v>1282</x:v>
       </x:c>
       <x:c r="P19" s="3" t="s">
-        <x:v>1294</x:v>
+        <x:v>1283</x:v>
       </x:c>
       <x:c r="Q19" s="3" t="s">
-        <x:v>1295</x:v>
+        <x:v>1284</x:v>
       </x:c>
       <x:c r="R19" s="3" t="s">
-        <x:v>1296</x:v>
+        <x:v>1285</x:v>
       </x:c>
       <x:c r="S19" s="3" t="s">
-        <x:v>1297</x:v>
+        <x:v>1286</x:v>
       </x:c>
       <x:c r="T19" s="3" t="s">
-        <x:v>1298</x:v>
+        <x:v>1287</x:v>
       </x:c>
       <x:c r="U19" s="3" t="s">
         <x:v>2</x:v>
@@ -11891,31 +11858,31 @@
     </x:row>
     <x:row r="20" ht="79.25" hidden="0">
       <x:c r="A20" s="3" t="s">
-        <x:v>1299</x:v>
+        <x:v>1288</x:v>
       </x:c>
       <x:c r="B20" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C20" s="3" t="s">
-        <x:v>1300</x:v>
+        <x:v>1289</x:v>
       </x:c>
       <x:c r="D20" s="3" t="s">
-        <x:v>1301</x:v>
+        <x:v>1290</x:v>
       </x:c>
       <x:c r="E20" s="3" t="s">
-        <x:v>1302</x:v>
+        <x:v>1291</x:v>
       </x:c>
       <x:c r="F20" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G20" s="3" t="s">
-        <x:v>1093</x:v>
+        <x:v>1082</x:v>
       </x:c>
       <x:c r="H20" s="3" t="s">
-        <x:v>1094</x:v>
+        <x:v>1083</x:v>
       </x:c>
       <x:c r="I20" s="3" t="s">
-        <x:v>1095</x:v>
+        <x:v>1084</x:v>
       </x:c>
       <x:c r="J20" s="3" t="s">
         <x:v>42</x:v>
@@ -11924,31 +11891,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L20" s="3" t="s">
-        <x:v>1303</x:v>
+        <x:v>1292</x:v>
       </x:c>
       <x:c r="M20" s="3" t="s">
-        <x:v>1304</x:v>
+        <x:v>1293</x:v>
       </x:c>
       <x:c r="N20" s="3" t="s">
-        <x:v>1305</x:v>
+        <x:v>1294</x:v>
       </x:c>
       <x:c r="O20" s="3" t="s">
-        <x:v>1306</x:v>
+        <x:v>1295</x:v>
       </x:c>
       <x:c r="P20" s="3" t="s">
-        <x:v>1307</x:v>
+        <x:v>1296</x:v>
       </x:c>
       <x:c r="Q20" s="3" t="s">
-        <x:v>1308</x:v>
+        <x:v>1297</x:v>
       </x:c>
       <x:c r="R20" s="3" t="s">
-        <x:v>1309</x:v>
+        <x:v>1298</x:v>
       </x:c>
       <x:c r="S20" s="3" t="s">
-        <x:v>1310</x:v>
+        <x:v>1299</x:v>
       </x:c>
       <x:c r="T20" s="3" t="s">
-        <x:v>1311</x:v>
+        <x:v>1300</x:v>
       </x:c>
       <x:c r="U20" s="3" t="s">
         <x:v>2</x:v>
@@ -11956,31 +11923,31 @@
     </x:row>
     <x:row r="21" ht="79.25" hidden="0">
       <x:c r="A21" s="3" t="s">
-        <x:v>1312</x:v>
+        <x:v>1301</x:v>
       </x:c>
       <x:c r="B21" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C21" s="3" t="s">
-        <x:v>1313</x:v>
+        <x:v>1302</x:v>
       </x:c>
       <x:c r="D21" s="3" t="s">
-        <x:v>1314</x:v>
+        <x:v>1303</x:v>
       </x:c>
       <x:c r="E21" s="3" t="s">
-        <x:v>1315</x:v>
+        <x:v>1304</x:v>
       </x:c>
       <x:c r="F21" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G21" s="3" t="s">
-        <x:v>1093</x:v>
+        <x:v>1082</x:v>
       </x:c>
       <x:c r="H21" s="3" t="s">
-        <x:v>1094</x:v>
+        <x:v>1083</x:v>
       </x:c>
       <x:c r="I21" s="3" t="s">
-        <x:v>1095</x:v>
+        <x:v>1084</x:v>
       </x:c>
       <x:c r="J21" s="3" t="s">
         <x:v>42</x:v>
@@ -11989,31 +11956,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L21" s="3" t="s">
-        <x:v>1316</x:v>
+        <x:v>1305</x:v>
       </x:c>
       <x:c r="M21" s="3" t="s">
-        <x:v>1317</x:v>
+        <x:v>1306</x:v>
       </x:c>
       <x:c r="N21" s="3" t="s">
-        <x:v>1318</x:v>
+        <x:v>1307</x:v>
       </x:c>
       <x:c r="O21" s="3" t="s">
         <x:v>218</x:v>
       </x:c>
       <x:c r="P21" s="3" t="s">
-        <x:v>1319</x:v>
+        <x:v>1308</x:v>
       </x:c>
       <x:c r="Q21" s="3" t="s">
-        <x:v>1320</x:v>
+        <x:v>1309</x:v>
       </x:c>
       <x:c r="R21" s="3" t="s">
         <x:v>221</x:v>
       </x:c>
       <x:c r="S21" s="3" t="s">
-        <x:v>1321</x:v>
+        <x:v>1310</x:v>
       </x:c>
       <x:c r="T21" s="3" t="s">
-        <x:v>1322</x:v>
+        <x:v>1311</x:v>
       </x:c>
       <x:c r="U21" s="3" t="s">
         <x:v>2</x:v>
@@ -12021,31 +11988,31 @@
     </x:row>
     <x:row r="22" ht="93.25" hidden="0">
       <x:c r="A22" s="3" t="s">
-        <x:v>1323</x:v>
+        <x:v>1312</x:v>
       </x:c>
       <x:c r="B22" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C22" s="3" t="s">
-        <x:v>1324</x:v>
+        <x:v>1313</x:v>
       </x:c>
       <x:c r="D22" s="3" t="s">
-        <x:v>1325</x:v>
+        <x:v>1314</x:v>
       </x:c>
       <x:c r="E22" s="3" t="s">
-        <x:v>1326</x:v>
+        <x:v>1315</x:v>
       </x:c>
       <x:c r="F22" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G22" s="3" t="s">
-        <x:v>1093</x:v>
+        <x:v>1082</x:v>
       </x:c>
       <x:c r="H22" s="3" t="s">
-        <x:v>1094</x:v>
+        <x:v>1083</x:v>
       </x:c>
       <x:c r="I22" s="3" t="s">
-        <x:v>1095</x:v>
+        <x:v>1084</x:v>
       </x:c>
       <x:c r="J22" s="3" t="s">
         <x:v>42</x:v>
@@ -12054,31 +12021,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L22" s="3" t="s">
-        <x:v>1327</x:v>
+        <x:v>1316</x:v>
       </x:c>
       <x:c r="M22" s="3" t="s">
-        <x:v>1192</x:v>
+        <x:v>1181</x:v>
       </x:c>
       <x:c r="N22" s="3" t="s">
-        <x:v>1328</x:v>
+        <x:v>1317</x:v>
       </x:c>
       <x:c r="O22" s="3" t="s">
-        <x:v>1329</x:v>
+        <x:v>1318</x:v>
       </x:c>
       <x:c r="P22" s="3" t="s">
-        <x:v>1330</x:v>
+        <x:v>1319</x:v>
       </x:c>
       <x:c r="Q22" s="3" t="s">
-        <x:v>1331</x:v>
+        <x:v>1320</x:v>
       </x:c>
       <x:c r="R22" s="3" t="s">
-        <x:v>1332</x:v>
+        <x:v>1321</x:v>
       </x:c>
       <x:c r="S22" s="3" t="s">
-        <x:v>1333</x:v>
+        <x:v>1322</x:v>
       </x:c>
       <x:c r="T22" s="3" t="s">
-        <x:v>1334</x:v>
+        <x:v>1323</x:v>
       </x:c>
       <x:c r="U22" s="3" t="s">
         <x:v>2</x:v>
@@ -12086,31 +12053,31 @@
     </x:row>
     <x:row r="23" ht="93.25" hidden="0">
       <x:c r="A23" s="3" t="s">
-        <x:v>1335</x:v>
+        <x:v>1324</x:v>
       </x:c>
       <x:c r="B23" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C23" s="3" t="s">
-        <x:v>1336</x:v>
+        <x:v>1325</x:v>
       </x:c>
       <x:c r="D23" s="3" t="s">
-        <x:v>1337</x:v>
+        <x:v>1326</x:v>
       </x:c>
       <x:c r="E23" s="3" t="s">
-        <x:v>1338</x:v>
+        <x:v>1327</x:v>
       </x:c>
       <x:c r="F23" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G23" s="3" t="s">
-        <x:v>1093</x:v>
+        <x:v>1082</x:v>
       </x:c>
       <x:c r="H23" s="3" t="s">
-        <x:v>1094</x:v>
+        <x:v>1083</x:v>
       </x:c>
       <x:c r="I23" s="3" t="s">
-        <x:v>1095</x:v>
+        <x:v>1084</x:v>
       </x:c>
       <x:c r="J23" s="3" t="s">
         <x:v>42</x:v>
@@ -12119,31 +12086,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L23" s="3" t="s">
-        <x:v>1339</x:v>
+        <x:v>1328</x:v>
       </x:c>
       <x:c r="M23" s="3" t="s">
-        <x:v>1340</x:v>
+        <x:v>1329</x:v>
       </x:c>
       <x:c r="N23" s="3" t="s">
-        <x:v>1341</x:v>
+        <x:v>1330</x:v>
       </x:c>
       <x:c r="O23" s="3" t="s">
-        <x:v>1342</x:v>
+        <x:v>1331</x:v>
       </x:c>
       <x:c r="P23" s="3" t="s">
-        <x:v>1343</x:v>
+        <x:v>1332</x:v>
       </x:c>
       <x:c r="Q23" s="3" t="s">
-        <x:v>1344</x:v>
+        <x:v>1333</x:v>
       </x:c>
       <x:c r="R23" s="3" t="s">
-        <x:v>1345</x:v>
+        <x:v>1334</x:v>
       </x:c>
       <x:c r="S23" s="3" t="s">
-        <x:v>1346</x:v>
+        <x:v>1335</x:v>
       </x:c>
       <x:c r="T23" s="3" t="s">
-        <x:v>1347</x:v>
+        <x:v>1336</x:v>
       </x:c>
       <x:c r="U23" s="3" t="s">
         <x:v>2</x:v>
@@ -12151,31 +12118,31 @@
     </x:row>
     <x:row r="24" ht="79.25" hidden="0">
       <x:c r="A24" s="3" t="s">
-        <x:v>1348</x:v>
+        <x:v>1337</x:v>
       </x:c>
       <x:c r="B24" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C24" s="3" t="s">
-        <x:v>1349</x:v>
+        <x:v>1338</x:v>
       </x:c>
       <x:c r="D24" s="3" t="s">
-        <x:v>1350</x:v>
+        <x:v>1339</x:v>
       </x:c>
       <x:c r="E24" s="3" t="s">
-        <x:v>1351</x:v>
+        <x:v>1340</x:v>
       </x:c>
       <x:c r="F24" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G24" s="3" t="s">
-        <x:v>1093</x:v>
+        <x:v>1082</x:v>
       </x:c>
       <x:c r="H24" s="3" t="s">
-        <x:v>1094</x:v>
+        <x:v>1083</x:v>
       </x:c>
       <x:c r="I24" s="3" t="s">
-        <x:v>1095</x:v>
+        <x:v>1084</x:v>
       </x:c>
       <x:c r="J24" s="3" t="s">
         <x:v>42</x:v>
@@ -12184,31 +12151,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L24" s="3" t="s">
-        <x:v>1352</x:v>
+        <x:v>1341</x:v>
       </x:c>
       <x:c r="M24" s="3" t="s">
-        <x:v>1317</x:v>
+        <x:v>1306</x:v>
       </x:c>
       <x:c r="N24" s="3" t="s">
-        <x:v>1353</x:v>
+        <x:v>1342</x:v>
       </x:c>
       <x:c r="O24" s="3" t="s">
-        <x:v>1354</x:v>
+        <x:v>1343</x:v>
       </x:c>
       <x:c r="P24" s="3" t="s">
-        <x:v>1355</x:v>
+        <x:v>1344</x:v>
       </x:c>
       <x:c r="Q24" s="3" t="s">
-        <x:v>1356</x:v>
+        <x:v>1345</x:v>
       </x:c>
       <x:c r="R24" s="3" t="s">
-        <x:v>1357</x:v>
+        <x:v>1346</x:v>
       </x:c>
       <x:c r="S24" s="3" t="s">
-        <x:v>1358</x:v>
+        <x:v>1347</x:v>
       </x:c>
       <x:c r="T24" s="3" t="s">
-        <x:v>1359</x:v>
+        <x:v>1348</x:v>
       </x:c>
       <x:c r="U24" s="3" t="s">
         <x:v>2</x:v>
@@ -12216,31 +12183,31 @@
     </x:row>
     <x:row r="25" ht="79.25" hidden="0">
       <x:c r="A25" s="3" t="s">
-        <x:v>1360</x:v>
+        <x:v>1349</x:v>
       </x:c>
       <x:c r="B25" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C25" s="3" t="s">
-        <x:v>1361</x:v>
+        <x:v>1350</x:v>
       </x:c>
       <x:c r="D25" s="3" t="s">
-        <x:v>1362</x:v>
+        <x:v>1351</x:v>
       </x:c>
       <x:c r="E25" s="3" t="s">
-        <x:v>1363</x:v>
+        <x:v>1352</x:v>
       </x:c>
       <x:c r="F25" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G25" s="3" t="s">
-        <x:v>1093</x:v>
+        <x:v>1082</x:v>
       </x:c>
       <x:c r="H25" s="3" t="s">
-        <x:v>1094</x:v>
+        <x:v>1083</x:v>
       </x:c>
       <x:c r="I25" s="3" t="s">
-        <x:v>1095</x:v>
+        <x:v>1084</x:v>
       </x:c>
       <x:c r="J25" s="3" t="s">
         <x:v>42</x:v>
@@ -12249,31 +12216,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L25" s="3" t="s">
-        <x:v>1364</x:v>
+        <x:v>1353</x:v>
       </x:c>
       <x:c r="M25" s="3" t="s">
-        <x:v>1317</x:v>
+        <x:v>1306</x:v>
       </x:c>
       <x:c r="N25" s="3" t="s">
-        <x:v>1365</x:v>
+        <x:v>1354</x:v>
       </x:c>
       <x:c r="O25" s="3" t="s">
-        <x:v>1366</x:v>
+        <x:v>1355</x:v>
       </x:c>
       <x:c r="P25" s="3" t="s">
-        <x:v>1367</x:v>
+        <x:v>1356</x:v>
       </x:c>
       <x:c r="Q25" s="3" t="s">
-        <x:v>1368</x:v>
+        <x:v>1357</x:v>
       </x:c>
       <x:c r="R25" s="3" t="s">
-        <x:v>1369</x:v>
+        <x:v>1358</x:v>
       </x:c>
       <x:c r="S25" s="3" t="s">
-        <x:v>1370</x:v>
+        <x:v>1359</x:v>
       </x:c>
       <x:c r="T25" s="3" t="s">
-        <x:v>1371</x:v>
+        <x:v>1360</x:v>
       </x:c>
       <x:c r="U25" s="3" t="s">
         <x:v>2</x:v>
@@ -12281,31 +12248,31 @@
     </x:row>
     <x:row r="26" ht="79.25" hidden="0">
       <x:c r="A26" s="3" t="s">
-        <x:v>1372</x:v>
+        <x:v>1361</x:v>
       </x:c>
       <x:c r="B26" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C26" s="3" t="s">
-        <x:v>1373</x:v>
+        <x:v>1362</x:v>
       </x:c>
       <x:c r="D26" s="3" t="s">
-        <x:v>1374</x:v>
+        <x:v>1363</x:v>
       </x:c>
       <x:c r="E26" s="3" t="s">
-        <x:v>1375</x:v>
+        <x:v>1364</x:v>
       </x:c>
       <x:c r="F26" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G26" s="3" t="s">
-        <x:v>1093</x:v>
+        <x:v>1082</x:v>
       </x:c>
       <x:c r="H26" s="3" t="s">
-        <x:v>1094</x:v>
+        <x:v>1083</x:v>
       </x:c>
       <x:c r="I26" s="3" t="s">
-        <x:v>1095</x:v>
+        <x:v>1084</x:v>
       </x:c>
       <x:c r="J26" s="3" t="s">
         <x:v>42</x:v>
@@ -12314,31 +12281,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L26" s="3" t="s">
-        <x:v>1376</x:v>
+        <x:v>1365</x:v>
       </x:c>
       <x:c r="M26" s="3" t="s">
-        <x:v>1377</x:v>
+        <x:v>1366</x:v>
       </x:c>
       <x:c r="N26" s="3" t="s">
-        <x:v>1378</x:v>
+        <x:v>1367</x:v>
       </x:c>
       <x:c r="O26" s="3" t="s">
-        <x:v>1379</x:v>
+        <x:v>1368</x:v>
       </x:c>
       <x:c r="P26" s="3" t="s">
-        <x:v>1380</x:v>
+        <x:v>1369</x:v>
       </x:c>
       <x:c r="Q26" s="3" t="s">
-        <x:v>1381</x:v>
+        <x:v>1370</x:v>
       </x:c>
       <x:c r="R26" s="3" t="s">
-        <x:v>1382</x:v>
+        <x:v>1371</x:v>
       </x:c>
       <x:c r="S26" s="3" t="s">
-        <x:v>1383</x:v>
+        <x:v>1372</x:v>
       </x:c>
       <x:c r="T26" s="3" t="s">
-        <x:v>1384</x:v>
+        <x:v>1373</x:v>
       </x:c>
       <x:c r="U26" s="3" t="s">
         <x:v>2</x:v>
@@ -12346,31 +12313,31 @@
     </x:row>
     <x:row r="27" ht="79.25" hidden="0">
       <x:c r="A27" s="3" t="s">
-        <x:v>1385</x:v>
+        <x:v>1374</x:v>
       </x:c>
       <x:c r="B27" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C27" s="3" t="s">
-        <x:v>1386</x:v>
+        <x:v>1375</x:v>
       </x:c>
       <x:c r="D27" s="3" t="s">
-        <x:v>1387</x:v>
+        <x:v>1376</x:v>
       </x:c>
       <x:c r="E27" s="3" t="s">
-        <x:v>1388</x:v>
+        <x:v>1377</x:v>
       </x:c>
       <x:c r="F27" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G27" s="3" t="s">
-        <x:v>1093</x:v>
+        <x:v>1082</x:v>
       </x:c>
       <x:c r="H27" s="3" t="s">
-        <x:v>1094</x:v>
+        <x:v>1083</x:v>
       </x:c>
       <x:c r="I27" s="3" t="s">
-        <x:v>1095</x:v>
+        <x:v>1084</x:v>
       </x:c>
       <x:c r="J27" s="3" t="s">
         <x:v>42</x:v>
@@ -12379,31 +12346,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L27" s="3" t="s">
-        <x:v>1389</x:v>
+        <x:v>1378</x:v>
       </x:c>
       <x:c r="M27" s="3" t="s">
-        <x:v>1390</x:v>
+        <x:v>1379</x:v>
       </x:c>
       <x:c r="N27" s="3" t="s">
-        <x:v>1391</x:v>
+        <x:v>1380</x:v>
       </x:c>
       <x:c r="O27" s="3" t="s">
-        <x:v>1392</x:v>
+        <x:v>1381</x:v>
       </x:c>
       <x:c r="P27" s="3" t="s">
-        <x:v>1393</x:v>
+        <x:v>1382</x:v>
       </x:c>
       <x:c r="Q27" s="3" t="s">
-        <x:v>1394</x:v>
+        <x:v>1383</x:v>
       </x:c>
       <x:c r="R27" s="3" t="s">
-        <x:v>1395</x:v>
+        <x:v>1384</x:v>
       </x:c>
       <x:c r="S27" s="3" t="s">
         <x:v>789</x:v>
       </x:c>
       <x:c r="T27" s="3" t="s">
-        <x:v>1396</x:v>
+        <x:v>1385</x:v>
       </x:c>
       <x:c r="U27" s="3" t="s">
         <x:v>2</x:v>
@@ -12411,31 +12378,31 @@
     </x:row>
     <x:row r="28" ht="93.25" hidden="0">
       <x:c r="A28" s="3" t="s">
-        <x:v>1397</x:v>
+        <x:v>1386</x:v>
       </x:c>
       <x:c r="B28" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C28" s="3" t="s">
-        <x:v>1398</x:v>
+        <x:v>1387</x:v>
       </x:c>
       <x:c r="D28" s="3" t="s">
-        <x:v>1399</x:v>
+        <x:v>1388</x:v>
       </x:c>
       <x:c r="E28" s="3" t="s">
-        <x:v>1400</x:v>
+        <x:v>1389</x:v>
       </x:c>
       <x:c r="F28" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G28" s="3" t="s">
-        <x:v>1093</x:v>
+        <x:v>1082</x:v>
       </x:c>
       <x:c r="H28" s="3" t="s">
-        <x:v>1094</x:v>
+        <x:v>1083</x:v>
       </x:c>
       <x:c r="I28" s="3" t="s">
-        <x:v>1095</x:v>
+        <x:v>1084</x:v>
       </x:c>
       <x:c r="J28" s="3" t="s">
         <x:v>42</x:v>
@@ -12444,31 +12411,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L28" s="3" t="s">
-        <x:v>1401</x:v>
+        <x:v>1390</x:v>
       </x:c>
       <x:c r="M28" s="3" t="s">
-        <x:v>1402</x:v>
+        <x:v>1391</x:v>
       </x:c>
       <x:c r="N28" s="3" t="s">
-        <x:v>1403</x:v>
+        <x:v>1392</x:v>
       </x:c>
       <x:c r="O28" s="3" t="s">
-        <x:v>1404</x:v>
+        <x:v>1393</x:v>
       </x:c>
       <x:c r="P28" s="3" t="s">
-        <x:v>1405</x:v>
+        <x:v>1394</x:v>
       </x:c>
       <x:c r="Q28" s="3" t="s">
-        <x:v>1406</x:v>
+        <x:v>1395</x:v>
       </x:c>
       <x:c r="R28" s="3" t="s">
-        <x:v>1407</x:v>
+        <x:v>1396</x:v>
       </x:c>
       <x:c r="S28" s="3" t="s">
         <x:v>286</x:v>
       </x:c>
       <x:c r="T28" s="3" t="s">
-        <x:v>1408</x:v>
+        <x:v>1397</x:v>
       </x:c>
       <x:c r="U28" s="3" t="s">
         <x:v>2</x:v>
@@ -12476,31 +12443,31 @@
     </x:row>
     <x:row r="29" ht="93.25" hidden="0">
       <x:c r="A29" s="3" t="s">
-        <x:v>1409</x:v>
+        <x:v>1398</x:v>
       </x:c>
       <x:c r="B29" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C29" s="3" t="s">
-        <x:v>1410</x:v>
+        <x:v>1399</x:v>
       </x:c>
       <x:c r="D29" s="3" t="s">
-        <x:v>1411</x:v>
+        <x:v>1400</x:v>
       </x:c>
       <x:c r="E29" s="3" t="s">
-        <x:v>1412</x:v>
+        <x:v>1401</x:v>
       </x:c>
       <x:c r="F29" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G29" s="3" t="s">
-        <x:v>1093</x:v>
+        <x:v>1082</x:v>
       </x:c>
       <x:c r="H29" s="3" t="s">
-        <x:v>1094</x:v>
+        <x:v>1083</x:v>
       </x:c>
       <x:c r="I29" s="3" t="s">
-        <x:v>1095</x:v>
+        <x:v>1084</x:v>
       </x:c>
       <x:c r="J29" s="3" t="s">
         <x:v>42</x:v>
@@ -12509,31 +12476,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="L29" s="3" t="s">
-        <x:v>1413</x:v>
+        <x:v>1402</x:v>
       </x:c>
       <x:c r="M29" s="3" t="s">
-        <x:v>1414</x:v>
+        <x:v>1403</x:v>
       </x:c>
       <x:c r="N29" s="3" t="s">
-        <x:v>1415</x:v>
+        <x:v>1404</x:v>
       </x:c>
       <x:c r="O29" s="3" t="s">
-        <x:v>1416</x:v>
+        <x:v>1405</x:v>
       </x:c>
       <x:c r="P29" s="3" t="s">
-        <x:v>1417</x:v>
+        <x:v>1406</x:v>
       </x:c>
       <x:c r="Q29" s="3" t="s">
-        <x:v>1418</x:v>
+        <x:v>1407</x:v>
       </x:c>
       <x:c r="R29" s="3" t="s">
-        <x:v>1419</x:v>
+        <x:v>1408</x:v>
       </x:c>
       <x:c r="S29" s="3" t="s">
-        <x:v>1420</x:v>
+        <x:v>1409</x:v>
       </x:c>
       <x:c r="T29" s="3" t="s">
-        <x:v>1421</x:v>
+        <x:v>1410</x:v>
       </x:c>
       <x:c r="U29" s="3" t="s">
         <x:v>2</x:v>
@@ -12541,31 +12508,31 @@
     </x:row>
     <x:row r="30" ht="93.25" hidden="0">
       <x:c r="A30" s="3" t="s">
-        <x:v>1422</x:v>
+        <x:v>1411</x:v>
       </x:c>
       <x:c r="B30" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C30" s="3" t="s">
-        <x:v>1423</x:v>
+        <x:v>1412</x:v>
       </x:c>
       <x:c r="D30" s="3" t="s">
-        <x:v>1424</x:v>
+        <x:v>1413</x:v>
       </x:c>
       <x:c r="E30" s="3" t="s">
-        <x:v>1425</x:v>
+        <x:v>1414</x:v>
       </x:c>
       <x:c r="F30" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G30" s="3" t="s">
-        <x:v>1093</x:v>
+        <x:v>1082</x:v>
       </x:c>
       <x:c r="H30" s="3" t="s">
-        <x:v>1094</x:v>
+        <x:v>1083</x:v>
       </x:c>
       <x:c r="I30" s="3" t="s">
-        <x:v>1095</x:v>
+        <x:v>1084</x:v>
       </x:c>
       <x:c r="J30" s="3" t="s">
         <x:v>42</x:v>
@@ -12574,31 +12541,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L30" s="3" t="s">
-        <x:v>1426</x:v>
+        <x:v>1415</x:v>
       </x:c>
       <x:c r="M30" s="3" t="s">
-        <x:v>1427</x:v>
+        <x:v>1416</x:v>
       </x:c>
       <x:c r="N30" s="3" t="s">
-        <x:v>1428</x:v>
+        <x:v>1417</x:v>
       </x:c>
       <x:c r="O30" s="3" t="s">
-        <x:v>1429</x:v>
+        <x:v>1418</x:v>
       </x:c>
       <x:c r="P30" s="3" t="s">
-        <x:v>1430</x:v>
+        <x:v>1419</x:v>
       </x:c>
       <x:c r="Q30" s="3" t="s">
-        <x:v>1431</x:v>
+        <x:v>1420</x:v>
       </x:c>
       <x:c r="R30" s="3" t="s">
-        <x:v>1432</x:v>
+        <x:v>1421</x:v>
       </x:c>
       <x:c r="S30" s="3" t="s">
-        <x:v>1433</x:v>
+        <x:v>1422</x:v>
       </x:c>
       <x:c r="T30" s="3" t="s">
-        <x:v>1434</x:v>
+        <x:v>1423</x:v>
       </x:c>
       <x:c r="U30" s="3" t="s">
         <x:v>2</x:v>
@@ -12606,7 +12573,7 @@
     </x:row>
     <x:row r="31" ht="93.25" hidden="0">
       <x:c r="A31" s="3" t="s">
-        <x:v>1435</x:v>
+        <x:v>1424</x:v>
       </x:c>
       <x:c r="B31" s="3" t="s">
         <x:v>9</x:v>
@@ -12615,22 +12582,22 @@
         <x:v>947</x:v>
       </x:c>
       <x:c r="D31" s="3" t="s">
-        <x:v>1436</x:v>
+        <x:v>1425</x:v>
       </x:c>
       <x:c r="E31" s="3" t="s">
-        <x:v>1437</x:v>
+        <x:v>1426</x:v>
       </x:c>
       <x:c r="F31" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G31" s="3" t="s">
-        <x:v>1093</x:v>
+        <x:v>1082</x:v>
       </x:c>
       <x:c r="H31" s="3" t="s">
-        <x:v>1094</x:v>
+        <x:v>1083</x:v>
       </x:c>
       <x:c r="I31" s="3" t="s">
-        <x:v>1095</x:v>
+        <x:v>1084</x:v>
       </x:c>
       <x:c r="J31" s="3" t="s">
         <x:v>42</x:v>
@@ -12639,31 +12606,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="L31" s="3" t="s">
-        <x:v>1438</x:v>
+        <x:v>1427</x:v>
       </x:c>
       <x:c r="M31" s="3" t="s">
-        <x:v>1439</x:v>
+        <x:v>1428</x:v>
       </x:c>
       <x:c r="N31" s="3" t="s">
-        <x:v>1440</x:v>
+        <x:v>1429</x:v>
       </x:c>
       <x:c r="O31" s="3" t="s">
-        <x:v>1441</x:v>
+        <x:v>1430</x:v>
       </x:c>
       <x:c r="P31" s="3" t="s">
-        <x:v>1442</x:v>
+        <x:v>1431</x:v>
       </x:c>
       <x:c r="Q31" s="3" t="s">
-        <x:v>1443</x:v>
+        <x:v>1432</x:v>
       </x:c>
       <x:c r="R31" s="3" t="s">
-        <x:v>1444</x:v>
+        <x:v>1433</x:v>
       </x:c>
       <x:c r="S31" s="3" t="s">
-        <x:v>1445</x:v>
+        <x:v>1434</x:v>
       </x:c>
       <x:c r="T31" s="3" t="s">
-        <x:v>1446</x:v>
+        <x:v>1435</x:v>
       </x:c>
       <x:c r="U31" s="3" t="s">
         <x:v>2</x:v>
@@ -12671,31 +12638,31 @@
     </x:row>
     <x:row r="32" ht="93.25" hidden="0">
       <x:c r="A32" s="3" t="s">
-        <x:v>1447</x:v>
+        <x:v>1436</x:v>
       </x:c>
       <x:c r="B32" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C32" s="3" t="s">
-        <x:v>1448</x:v>
+        <x:v>1437</x:v>
       </x:c>
       <x:c r="D32" s="3" t="s">
-        <x:v>1449</x:v>
+        <x:v>1438</x:v>
       </x:c>
       <x:c r="E32" s="3" t="s">
-        <x:v>1450</x:v>
+        <x:v>1439</x:v>
       </x:c>
       <x:c r="F32" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G32" s="3" t="s">
-        <x:v>1093</x:v>
+        <x:v>1082</x:v>
       </x:c>
       <x:c r="H32" s="3" t="s">
-        <x:v>1094</x:v>
+        <x:v>1083</x:v>
       </x:c>
       <x:c r="I32" s="3" t="s">
-        <x:v>1095</x:v>
+        <x:v>1084</x:v>
       </x:c>
       <x:c r="J32" s="3" t="s">
         <x:v>42</x:v>
@@ -12704,31 +12671,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L32" s="3" t="s">
-        <x:v>1451</x:v>
+        <x:v>1440</x:v>
       </x:c>
       <x:c r="M32" s="3" t="s">
-        <x:v>1452</x:v>
+        <x:v>1441</x:v>
       </x:c>
       <x:c r="N32" s="3" t="s">
-        <x:v>1453</x:v>
+        <x:v>1442</x:v>
       </x:c>
       <x:c r="O32" s="3" t="s">
-        <x:v>1454</x:v>
+        <x:v>1443</x:v>
       </x:c>
       <x:c r="P32" s="3" t="s">
-        <x:v>1455</x:v>
+        <x:v>1444</x:v>
       </x:c>
       <x:c r="Q32" s="3" t="s">
-        <x:v>1456</x:v>
+        <x:v>1445</x:v>
       </x:c>
       <x:c r="R32" s="3" t="s">
         <x:v>969</x:v>
       </x:c>
       <x:c r="S32" s="3" t="s">
-        <x:v>1457</x:v>
+        <x:v>1446</x:v>
       </x:c>
       <x:c r="T32" s="3" t="s">
-        <x:v>1458</x:v>
+        <x:v>1447</x:v>
       </x:c>
       <x:c r="U32" s="3" t="s">
         <x:v>2</x:v>
@@ -12736,7 +12703,7 @@
     </x:row>
     <x:row r="33" ht="93.25" hidden="0">
       <x:c r="A33" s="3" t="s">
-        <x:v>1459</x:v>
+        <x:v>1448</x:v>
       </x:c>
       <x:c r="B33" s="3" t="s">
         <x:v>9</x:v>
@@ -12745,22 +12712,22 @@
         <x:v>740</x:v>
       </x:c>
       <x:c r="D33" s="3" t="s">
-        <x:v>1460</x:v>
+        <x:v>1449</x:v>
       </x:c>
       <x:c r="E33" s="3" t="s">
-        <x:v>1461</x:v>
+        <x:v>1450</x:v>
       </x:c>
       <x:c r="F33" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G33" s="3" t="s">
-        <x:v>1093</x:v>
+        <x:v>1082</x:v>
       </x:c>
       <x:c r="H33" s="3" t="s">
-        <x:v>1094</x:v>
+        <x:v>1083</x:v>
       </x:c>
       <x:c r="I33" s="3" t="s">
-        <x:v>1095</x:v>
+        <x:v>1084</x:v>
       </x:c>
       <x:c r="J33" s="3" t="s">
         <x:v>42</x:v>
@@ -12769,31 +12736,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L33" s="3" t="s">
-        <x:v>1462</x:v>
+        <x:v>1451</x:v>
       </x:c>
       <x:c r="M33" s="3" t="s">
-        <x:v>1463</x:v>
+        <x:v>1452</x:v>
       </x:c>
       <x:c r="N33" s="3" t="s">
-        <x:v>1464</x:v>
+        <x:v>1453</x:v>
       </x:c>
       <x:c r="O33" s="3" t="s">
-        <x:v>1465</x:v>
+        <x:v>1454</x:v>
       </x:c>
       <x:c r="P33" s="3" t="s">
-        <x:v>1466</x:v>
+        <x:v>1455</x:v>
       </x:c>
       <x:c r="Q33" s="3" t="s">
-        <x:v>1467</x:v>
+        <x:v>1456</x:v>
       </x:c>
       <x:c r="R33" s="3" t="s">
-        <x:v>1468</x:v>
+        <x:v>1457</x:v>
       </x:c>
       <x:c r="S33" s="3" t="s">
-        <x:v>1469</x:v>
+        <x:v>1458</x:v>
       </x:c>
       <x:c r="T33" s="3" t="s">
-        <x:v>1470</x:v>
+        <x:v>1459</x:v>
       </x:c>
       <x:c r="U33" s="3" t="s">
         <x:v>2</x:v>
@@ -12801,7 +12768,7 @@
     </x:row>
     <x:row r="34" ht="93.25" hidden="0">
       <x:c r="A34" s="3" t="s">
-        <x:v>1471</x:v>
+        <x:v>1460</x:v>
       </x:c>
       <x:c r="B34" s="3" t="s">
         <x:v>9</x:v>
@@ -12810,22 +12777,22 @@
         <x:v>313</x:v>
       </x:c>
       <x:c r="D34" s="3" t="s">
-        <x:v>1472</x:v>
+        <x:v>1461</x:v>
       </x:c>
       <x:c r="E34" s="3" t="s">
-        <x:v>1473</x:v>
+        <x:v>1462</x:v>
       </x:c>
       <x:c r="F34" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G34" s="3" t="s">
-        <x:v>1093</x:v>
+        <x:v>1082</x:v>
       </x:c>
       <x:c r="H34" s="3" t="s">
-        <x:v>1094</x:v>
+        <x:v>1083</x:v>
       </x:c>
       <x:c r="I34" s="3" t="s">
-        <x:v>1095</x:v>
+        <x:v>1084</x:v>
       </x:c>
       <x:c r="J34" s="3" t="s">
         <x:v>42</x:v>
@@ -12834,31 +12801,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="L34" s="3" t="s">
-        <x:v>1474</x:v>
+        <x:v>1463</x:v>
       </x:c>
       <x:c r="M34" s="3" t="s">
-        <x:v>1475</x:v>
+        <x:v>1464</x:v>
       </x:c>
       <x:c r="N34" s="3" t="s">
         <x:v>978</x:v>
       </x:c>
       <x:c r="O34" s="3" t="s">
-        <x:v>1476</x:v>
+        <x:v>1465</x:v>
       </x:c>
       <x:c r="P34" s="3" t="s">
-        <x:v>1477</x:v>
+        <x:v>1466</x:v>
       </x:c>
       <x:c r="Q34" s="3" t="s">
-        <x:v>1478</x:v>
+        <x:v>1467</x:v>
       </x:c>
       <x:c r="R34" s="3" t="s">
-        <x:v>1479</x:v>
+        <x:v>1468</x:v>
       </x:c>
       <x:c r="S34" s="3" t="s">
         <x:v>323</x:v>
       </x:c>
       <x:c r="T34" s="3" t="s">
-        <x:v>1480</x:v>
+        <x:v>1469</x:v>
       </x:c>
       <x:c r="U34" s="3" t="s">
         <x:v>2</x:v>
@@ -12866,31 +12833,31 @@
     </x:row>
     <x:row r="35" ht="93.25" hidden="0">
       <x:c r="A35" s="3" t="s">
-        <x:v>1481</x:v>
+        <x:v>1470</x:v>
       </x:c>
       <x:c r="B35" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C35" s="3" t="s">
-        <x:v>1482</x:v>
+        <x:v>1471</x:v>
       </x:c>
       <x:c r="D35" s="3" t="s">
-        <x:v>1483</x:v>
+        <x:v>1472</x:v>
       </x:c>
       <x:c r="E35" s="3" t="s">
-        <x:v>1484</x:v>
+        <x:v>1473</x:v>
       </x:c>
       <x:c r="F35" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G35" s="3" t="s">
-        <x:v>1093</x:v>
+        <x:v>1082</x:v>
       </x:c>
       <x:c r="H35" s="3" t="s">
-        <x:v>1094</x:v>
+        <x:v>1083</x:v>
       </x:c>
       <x:c r="I35" s="3" t="s">
-        <x:v>1095</x:v>
+        <x:v>1084</x:v>
       </x:c>
       <x:c r="J35" s="3" t="s">
         <x:v>42</x:v>
@@ -12899,31 +12866,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L35" s="3" t="s">
-        <x:v>1485</x:v>
+        <x:v>1474</x:v>
       </x:c>
       <x:c r="M35" s="3" t="s">
-        <x:v>1486</x:v>
+        <x:v>1475</x:v>
       </x:c>
       <x:c r="N35" s="3" t="s">
-        <x:v>1487</x:v>
+        <x:v>1476</x:v>
       </x:c>
       <x:c r="O35" s="3" t="s">
-        <x:v>1267</x:v>
+        <x:v>1256</x:v>
       </x:c>
       <x:c r="P35" s="3" t="s">
-        <x:v>1488</x:v>
+        <x:v>1477</x:v>
       </x:c>
       <x:c r="Q35" s="3" t="s">
-        <x:v>1489</x:v>
+        <x:v>1478</x:v>
       </x:c>
       <x:c r="R35" s="3" t="s">
-        <x:v>1490</x:v>
+        <x:v>1479</x:v>
       </x:c>
       <x:c r="S35" s="3" t="s">
-        <x:v>1491</x:v>
+        <x:v>1480</x:v>
       </x:c>
       <x:c r="T35" s="3" t="s">
-        <x:v>1492</x:v>
+        <x:v>1481</x:v>
       </x:c>
       <x:c r="U35" s="3" t="s">
         <x:v>2</x:v>
@@ -12931,31 +12898,31 @@
     </x:row>
     <x:row r="36" ht="93.25" hidden="0">
       <x:c r="A36" s="3" t="s">
-        <x:v>1493</x:v>
+        <x:v>1482</x:v>
       </x:c>
       <x:c r="B36" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C36" s="3" t="s">
-        <x:v>1494</x:v>
+        <x:v>1483</x:v>
       </x:c>
       <x:c r="D36" s="3" t="s">
-        <x:v>1495</x:v>
+        <x:v>1484</x:v>
       </x:c>
       <x:c r="E36" s="3" t="s">
-        <x:v>1496</x:v>
+        <x:v>1485</x:v>
       </x:c>
       <x:c r="F36" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G36" s="3" t="s">
-        <x:v>1093</x:v>
+        <x:v>1082</x:v>
       </x:c>
       <x:c r="H36" s="3" t="s">
-        <x:v>1094</x:v>
+        <x:v>1083</x:v>
       </x:c>
       <x:c r="I36" s="3" t="s">
-        <x:v>1095</x:v>
+        <x:v>1084</x:v>
       </x:c>
       <x:c r="J36" s="3" t="s">
         <x:v>42</x:v>
@@ -12964,31 +12931,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L36" s="3" t="s">
-        <x:v>1497</x:v>
+        <x:v>1486</x:v>
       </x:c>
       <x:c r="M36" s="3" t="s">
-        <x:v>1097</x:v>
+        <x:v>1086</x:v>
       </x:c>
       <x:c r="N36" s="3" t="s">
-        <x:v>1498</x:v>
+        <x:v>1487</x:v>
       </x:c>
       <x:c r="O36" s="3" t="s">
-        <x:v>1499</x:v>
+        <x:v>1488</x:v>
       </x:c>
       <x:c r="P36" s="3" t="s">
-        <x:v>1500</x:v>
+        <x:v>1489</x:v>
       </x:c>
       <x:c r="Q36" s="3" t="s">
-        <x:v>1501</x:v>
+        <x:v>1490</x:v>
       </x:c>
       <x:c r="R36" s="3" t="s">
-        <x:v>1502</x:v>
+        <x:v>1491</x:v>
       </x:c>
       <x:c r="S36" s="3" t="s">
-        <x:v>1503</x:v>
+        <x:v>1492</x:v>
       </x:c>
       <x:c r="T36" s="3" t="s">
-        <x:v>1504</x:v>
+        <x:v>1493</x:v>
       </x:c>
       <x:c r="U36" s="3" t="s">
         <x:v>2</x:v>
@@ -12996,31 +12963,31 @@
     </x:row>
     <x:row r="37" ht="93.25" hidden="0">
       <x:c r="A37" s="3" t="s">
-        <x:v>1505</x:v>
+        <x:v>1494</x:v>
       </x:c>
       <x:c r="B37" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C37" s="3" t="s">
-        <x:v>1506</x:v>
+        <x:v>1495</x:v>
       </x:c>
       <x:c r="D37" s="3" t="s">
-        <x:v>1507</x:v>
+        <x:v>1496</x:v>
       </x:c>
       <x:c r="E37" s="3" t="s">
-        <x:v>1508</x:v>
+        <x:v>1497</x:v>
       </x:c>
       <x:c r="F37" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G37" s="3" t="s">
-        <x:v>1093</x:v>
+        <x:v>1082</x:v>
       </x:c>
       <x:c r="H37" s="3" t="s">
-        <x:v>1094</x:v>
+        <x:v>1083</x:v>
       </x:c>
       <x:c r="I37" s="3" t="s">
-        <x:v>1095</x:v>
+        <x:v>1084</x:v>
       </x:c>
       <x:c r="J37" s="3" t="s">
         <x:v>42</x:v>
@@ -13029,31 +12996,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L37" s="3" t="s">
-        <x:v>1509</x:v>
+        <x:v>1498</x:v>
       </x:c>
       <x:c r="M37" s="3" t="s">
-        <x:v>1510</x:v>
+        <x:v>1499</x:v>
       </x:c>
       <x:c r="N37" s="3" t="s">
-        <x:v>1511</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="O37" s="3" t="s">
-        <x:v>1512</x:v>
+        <x:v>1501</x:v>
       </x:c>
       <x:c r="P37" s="3" t="s">
-        <x:v>1513</x:v>
+        <x:v>1502</x:v>
       </x:c>
       <x:c r="Q37" s="3" t="s">
-        <x:v>1514</x:v>
+        <x:v>1503</x:v>
       </x:c>
       <x:c r="R37" s="3" t="s">
-        <x:v>1515</x:v>
+        <x:v>1504</x:v>
       </x:c>
       <x:c r="S37" s="3" t="s">
-        <x:v>1516</x:v>
+        <x:v>1505</x:v>
       </x:c>
       <x:c r="T37" s="3" t="s">
-        <x:v>1510</x:v>
+        <x:v>1499</x:v>
       </x:c>
       <x:c r="U37" s="3" t="s">
         <x:v>2</x:v>
@@ -13061,31 +13028,31 @@
     </x:row>
     <x:row r="38" ht="93.25" hidden="0">
       <x:c r="A38" s="3" t="s">
-        <x:v>1517</x:v>
+        <x:v>1506</x:v>
       </x:c>
       <x:c r="B38" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C38" s="3" t="s">
-        <x:v>1518</x:v>
+        <x:v>1507</x:v>
       </x:c>
       <x:c r="D38" s="3" t="s">
-        <x:v>1519</x:v>
+        <x:v>1508</x:v>
       </x:c>
       <x:c r="E38" s="3" t="s">
-        <x:v>1520</x:v>
+        <x:v>1509</x:v>
       </x:c>
       <x:c r="F38" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G38" s="3" t="s">
-        <x:v>1093</x:v>
+        <x:v>1082</x:v>
       </x:c>
       <x:c r="H38" s="3" t="s">
-        <x:v>1094</x:v>
+        <x:v>1083</x:v>
       </x:c>
       <x:c r="I38" s="3" t="s">
-        <x:v>1095</x:v>
+        <x:v>1084</x:v>
       </x:c>
       <x:c r="J38" s="3" t="s">
         <x:v>42</x:v>
@@ -13094,31 +13061,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L38" s="3" t="s">
-        <x:v>1521</x:v>
+        <x:v>1510</x:v>
       </x:c>
       <x:c r="M38" s="3" t="s">
-        <x:v>1192</x:v>
+        <x:v>1181</x:v>
       </x:c>
       <x:c r="N38" s="3" t="s">
-        <x:v>1522</x:v>
+        <x:v>1511</x:v>
       </x:c>
       <x:c r="O38" s="3" t="s">
-        <x:v>1523</x:v>
+        <x:v>1512</x:v>
       </x:c>
       <x:c r="P38" s="3" t="s">
-        <x:v>1524</x:v>
+        <x:v>1513</x:v>
       </x:c>
       <x:c r="Q38" s="3" t="s">
-        <x:v>1525</x:v>
+        <x:v>1514</x:v>
       </x:c>
       <x:c r="R38" s="3" t="s">
-        <x:v>1526</x:v>
+        <x:v>1515</x:v>
       </x:c>
       <x:c r="S38" s="3" t="s">
-        <x:v>1527</x:v>
+        <x:v>1516</x:v>
       </x:c>
       <x:c r="T38" s="3" t="s">
-        <x:v>1528</x:v>
+        <x:v>1517</x:v>
       </x:c>
       <x:c r="U38" s="3" t="s">
         <x:v>2</x:v>
@@ -13126,31 +13093,31 @@
     </x:row>
     <x:row r="39" ht="93.25" hidden="0">
       <x:c r="A39" s="3" t="s">
-        <x:v>1529</x:v>
+        <x:v>1518</x:v>
       </x:c>
       <x:c r="B39" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C39" s="3" t="s">
-        <x:v>1530</x:v>
+        <x:v>1519</x:v>
       </x:c>
       <x:c r="D39" s="3" t="s">
-        <x:v>1531</x:v>
+        <x:v>1520</x:v>
       </x:c>
       <x:c r="E39" s="3" t="s">
-        <x:v>1532</x:v>
+        <x:v>1521</x:v>
       </x:c>
       <x:c r="F39" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G39" s="3" t="s">
-        <x:v>1093</x:v>
+        <x:v>1082</x:v>
       </x:c>
       <x:c r="H39" s="3" t="s">
-        <x:v>1094</x:v>
+        <x:v>1083</x:v>
       </x:c>
       <x:c r="I39" s="3" t="s">
-        <x:v>1095</x:v>
+        <x:v>1084</x:v>
       </x:c>
       <x:c r="J39" s="3" t="s">
         <x:v>42</x:v>
@@ -13159,31 +13126,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="L39" s="3" t="s">
-        <x:v>1533</x:v>
+        <x:v>1522</x:v>
       </x:c>
       <x:c r="M39" s="3" t="s">
-        <x:v>1097</x:v>
+        <x:v>1086</x:v>
       </x:c>
       <x:c r="N39" s="3" t="s">
-        <x:v>1534</x:v>
+        <x:v>1523</x:v>
       </x:c>
       <x:c r="O39" s="3" t="s">
-        <x:v>1535</x:v>
+        <x:v>1524</x:v>
       </x:c>
       <x:c r="P39" s="3" t="s">
-        <x:v>1536</x:v>
+        <x:v>1525</x:v>
       </x:c>
       <x:c r="Q39" s="3" t="s">
-        <x:v>1537</x:v>
+        <x:v>1526</x:v>
       </x:c>
       <x:c r="R39" s="3" t="s">
-        <x:v>1538</x:v>
+        <x:v>1527</x:v>
       </x:c>
       <x:c r="S39" s="3" t="s">
-        <x:v>1539</x:v>
+        <x:v>1528</x:v>
       </x:c>
       <x:c r="T39" s="3" t="s">
-        <x:v>1540</x:v>
+        <x:v>1529</x:v>
       </x:c>
       <x:c r="U39" s="3" t="s">
         <x:v>2</x:v>
@@ -13192,7 +13159,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R58e8ce8d152f43f8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re0c04c5ebaf74cc9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/maliev-feature-user-story-status.xlsx
+++ b/docs/maliev-feature-user-story-status.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R620d757063874a96"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="R3b42b5c4788c4997"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R7e472c98811b4243"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="R120db2cb611d466c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Ra86334ab48034524"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="Re159ddff5dfa44a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R2fbb87b2f76d4769"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="Rf25d7749c86c4d4f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3053,42 +3053,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">NotificationController.cs:15-102; AdminPage.razor:91-165; CustomerDetail.razor:1356-1450</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">INT-046</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Compliance records and stats</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">As an employee with compliance access, I can review compliance stats and manage compliance records.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Compliance BFF exposes stats, list, detail, create, and delete operations with compliance permissions.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Intranet BFF -&gt; ComplianceService alerts/reports DTOs -&gt; permission-gated records</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ComplianceController.cs</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Compliance records/stat surfaces</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ComplianceController stats, GET, GET {id}, POST, DELETE</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Intranet BFF, ComplianceService</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Compliance record create/delete requests</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Needs current UI route review if exposed beyond API/chat navigation.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ComplianceController.cs:17-80; ComplianceServiceClient.cs:8-136</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">INT-047</x:t>
@@ -7172,7 +7136,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R154e6f3cd90e41a1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb438ffdb80624151"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10196,85 +10160,85 @@
       </x:c>
     </x:row>
     <x:row r="47" ht="51.29999923706055" hidden="0">
-      <x:c r="A47" s="3" t="s">
-        <x:v>1014</x:v>
-      </x:c>
-      <x:c r="B47" s="3" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C47" s="3" t="s">
-        <x:v>1015</x:v>
-      </x:c>
-      <x:c r="D47" s="3" t="s">
-        <x:v>1016</x:v>
-      </x:c>
-      <x:c r="E47" s="3" t="s">
-        <x:v>1017</x:v>
-      </x:c>
-      <x:c r="F47" s="3" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="G47" s="3" t="s">
-        <x:v>1001</x:v>
-      </x:c>
-      <x:c r="H47" s="3" t="s">
-        <x:v>1002</x:v>
-      </x:c>
-      <x:c r="I47" s="3" t="s">
-        <x:v>1003</x:v>
-      </x:c>
-      <x:c r="J47" s="3" t="s">
-        <x:v>1004</x:v>
-      </x:c>
-      <x:c r="K47" s="3" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="L47" s="3" t="s">
-        <x:v>1018</x:v>
-      </x:c>
-      <x:c r="M47" s="3" t="s">
-        <x:v>1019</x:v>
-      </x:c>
-      <x:c r="N47" s="3" t="s">
-        <x:v>1020</x:v>
-      </x:c>
-      <x:c r="O47" s="3" t="s">
-        <x:v>1021</x:v>
-      </x:c>
-      <x:c r="P47" s="3" t="s">
-        <x:v>1009</x:v>
-      </x:c>
-      <x:c r="Q47" s="3" t="s">
-        <x:v>1022</x:v>
-      </x:c>
-      <x:c r="R47" s="3" t="s">
-        <x:v>1023</x:v>
-      </x:c>
-      <x:c r="S47" s="3" t="s">
-        <x:v>1024</x:v>
-      </x:c>
-      <x:c r="T47" s="3" t="s">
-        <x:v>1025</x:v>
-      </x:c>
-      <x:c r="U47" s="3" t="s">
-        <x:v>2</x:v>
+      <x:c r="A47" s="3" t="str">
+        <x:v>INT-046</x:v>
+      </x:c>
+      <x:c r="B47" s="3" t="str">
+        <x:v>Maliev.Intranet</x:v>
+      </x:c>
+      <x:c r="C47" s="3" t="str">
+        <x:v>Compliance records and stats</x:v>
+      </x:c>
+      <x:c r="D47" s="3" t="str">
+        <x:v>As an employee with compliance access, I can review compliance stats and manage compliance records.</x:v>
+      </x:c>
+      <x:c r="E47" s="3" t="str">
+        <x:v>Compliance BFF exposes stats, list, detail, create, and delete operations with compliance permissions.</x:v>
+      </x:c>
+      <x:c r="F47" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G47" s="3" t="str">
+        <x:v>Focused behavior tests passed 2026-06-23.</x:v>
+      </x:c>
+      <x:c r="H47" s="3" t="str">
+        <x:v>No behavior error observed in current focused controller/client contract retest.</x:v>
+      </x:c>
+      <x:c r="I47" s="3" t="str">
+        <x:v>No app-code fix needed; added missing focused coverage in Maliev.Intranet commit e8f18af.</x:v>
+      </x:c>
+      <x:c r="J47" s="3" t="str">
+        <x:v>Retested ComplianceControllerTests 12/12 passed.</x:v>
+      </x:c>
+      <x:c r="K47" s="3" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="L47" s="3" t="str">
+        <x:v>Intranet BFF -&gt; ComplianceService alerts/reports DTOs -&gt; permission-gated records</x:v>
+      </x:c>
+      <x:c r="M47" s="3" t="str">
+        <x:v>ComplianceController.cs</x:v>
+      </x:c>
+      <x:c r="N47" s="3" t="str">
+        <x:v>Compliance records/stat surfaces</x:v>
+      </x:c>
+      <x:c r="O47" s="3" t="str">
+        <x:v>ComplianceController stats, GET, GET {id}, POST, DELETE</x:v>
+      </x:c>
+      <x:c r="P47" s="3" t="str">
+        <x:v>Focused test: dotnet test Maliev.Intranet.slnx --filter "FullyQualifiedName~ComplianceControllerTests" --verbosity minimal passed 12/12 on 2026-06-23. Coverage verifies stats fallback, missing-record not found, create/delete outcomes, read/write permission requirements, ComplianceServiceClient alert-to-record mapping, report-to-stats mapping, and alert resolve endpoint path/body.</x:v>
+      </x:c>
+      <x:c r="Q47" s="3" t="str">
+        <x:v>Intranet BFF, ComplianceService</x:v>
+      </x:c>
+      <x:c r="R47" s="3" t="str">
+        <x:v>Compliance record create/delete requests</x:v>
+      </x:c>
+      <x:c r="S47" s="3" t="str">
+        <x:v>No remaining INT-046 API/client contract gap from this focused retest. Current code search found API/chat navigation exposure, not a dedicated compliance page route; full authenticated UI route review remains for later browser/Aspire pass.</x:v>
+      </x:c>
+      <x:c r="T47" s="3" t="str">
+        <x:v>ComplianceController.cs:17-80; ComplianceServiceClient.cs:8-136; ComplianceControllerTests.cs:1-179; ChatDrawer.razor:410</x:v>
+      </x:c>
+      <x:c r="U47" s="3" t="str">
+        <x:v>2026-06-23</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="51.29999923706055" hidden="0">
       <x:c r="A48" s="3" t="s">
-        <x:v>1026</x:v>
+        <x:v>1014</x:v>
       </x:c>
       <x:c r="B48" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C48" s="3" t="s">
-        <x:v>1027</x:v>
+        <x:v>1015</x:v>
       </x:c>
       <x:c r="D48" s="3" t="s">
-        <x:v>1028</x:v>
+        <x:v>1016</x:v>
       </x:c>
       <x:c r="E48" s="3" t="s">
-        <x:v>1029</x:v>
+        <x:v>1017</x:v>
       </x:c>
       <x:c r="F48" s="3" t="s">
         <x:v>38</x:v>
@@ -10295,31 +10259,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L48" s="3" t="s">
-        <x:v>1030</x:v>
+        <x:v>1018</x:v>
       </x:c>
       <x:c r="M48" s="3" t="s">
-        <x:v>1031</x:v>
+        <x:v>1019</x:v>
       </x:c>
       <x:c r="N48" s="3" t="s">
-        <x:v>1032</x:v>
+        <x:v>1020</x:v>
       </x:c>
       <x:c r="O48" s="3" t="s">
-        <x:v>1033</x:v>
+        <x:v>1021</x:v>
       </x:c>
       <x:c r="P48" s="3" t="s">
         <x:v>1009</x:v>
       </x:c>
       <x:c r="Q48" s="3" t="s">
-        <x:v>1034</x:v>
+        <x:v>1022</x:v>
       </x:c>
       <x:c r="R48" s="3" t="s">
-        <x:v>1035</x:v>
+        <x:v>1023</x:v>
       </x:c>
       <x:c r="S48" s="3" t="s">
-        <x:v>1036</x:v>
+        <x:v>1024</x:v>
       </x:c>
       <x:c r="T48" s="3" t="s">
-        <x:v>1037</x:v>
+        <x:v>1025</x:v>
       </x:c>
       <x:c r="U48" s="3" t="s">
         <x:v>2</x:v>
@@ -10327,19 +10291,19 @@
     </x:row>
     <x:row r="49" ht="51.29999923706055" hidden="0">
       <x:c r="A49" s="3" t="s">
-        <x:v>1038</x:v>
+        <x:v>1026</x:v>
       </x:c>
       <x:c r="B49" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C49" s="3" t="s">
-        <x:v>1039</x:v>
+        <x:v>1027</x:v>
       </x:c>
       <x:c r="D49" s="3" t="s">
-        <x:v>1040</x:v>
+        <x:v>1028</x:v>
       </x:c>
       <x:c r="E49" s="3" t="s">
-        <x:v>1041</x:v>
+        <x:v>1029</x:v>
       </x:c>
       <x:c r="F49" s="3" t="s">
         <x:v>38</x:v>
@@ -10360,31 +10324,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L49" s="3" t="s">
-        <x:v>1042</x:v>
+        <x:v>1030</x:v>
       </x:c>
       <x:c r="M49" s="3" t="s">
-        <x:v>1043</x:v>
+        <x:v>1031</x:v>
       </x:c>
       <x:c r="N49" s="3" t="s">
-        <x:v>1044</x:v>
+        <x:v>1032</x:v>
       </x:c>
       <x:c r="O49" s="3" t="s">
-        <x:v>1045</x:v>
+        <x:v>1033</x:v>
       </x:c>
       <x:c r="P49" s="3" t="s">
         <x:v>1009</x:v>
       </x:c>
       <x:c r="Q49" s="3" t="s">
-        <x:v>1046</x:v>
+        <x:v>1034</x:v>
       </x:c>
       <x:c r="R49" s="3" t="s">
-        <x:v>1047</x:v>
+        <x:v>1035</x:v>
       </x:c>
       <x:c r="S49" s="3" t="s">
-        <x:v>1048</x:v>
+        <x:v>1036</x:v>
       </x:c>
       <x:c r="T49" s="3" t="s">
-        <x:v>1049</x:v>
+        <x:v>1037</x:v>
       </x:c>
       <x:c r="U49" s="3" t="s">
         <x:v>2</x:v>
@@ -10392,19 +10356,19 @@
     </x:row>
     <x:row r="50" ht="51.29999923706055" hidden="0">
       <x:c r="A50" s="3" t="s">
-        <x:v>1050</x:v>
+        <x:v>1038</x:v>
       </x:c>
       <x:c r="B50" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C50" s="3" t="s">
-        <x:v>1051</x:v>
+        <x:v>1039</x:v>
       </x:c>
       <x:c r="D50" s="3" t="s">
-        <x:v>1052</x:v>
+        <x:v>1040</x:v>
       </x:c>
       <x:c r="E50" s="3" t="s">
-        <x:v>1053</x:v>
+        <x:v>1041</x:v>
       </x:c>
       <x:c r="F50" s="3" t="s">
         <x:v>38</x:v>
@@ -10425,31 +10389,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L50" s="3" t="s">
-        <x:v>1054</x:v>
+        <x:v>1042</x:v>
       </x:c>
       <x:c r="M50" s="3" t="s">
-        <x:v>1055</x:v>
+        <x:v>1043</x:v>
       </x:c>
       <x:c r="N50" s="3" t="s">
-        <x:v>1056</x:v>
+        <x:v>1044</x:v>
       </x:c>
       <x:c r="O50" s="3" t="s">
-        <x:v>1057</x:v>
+        <x:v>1045</x:v>
       </x:c>
       <x:c r="P50" s="3" t="s">
         <x:v>1009</x:v>
       </x:c>
       <x:c r="Q50" s="3" t="s">
-        <x:v>1058</x:v>
+        <x:v>1046</x:v>
       </x:c>
       <x:c r="R50" s="3" t="s">
-        <x:v>1059</x:v>
+        <x:v>1047</x:v>
       </x:c>
       <x:c r="S50" s="3" t="s">
+        <x:v>1036</x:v>
+      </x:c>
+      <x:c r="T50" s="3" t="s">
         <x:v>1048</x:v>
-      </x:c>
-      <x:c r="T50" s="3" t="s">
-        <x:v>1060</x:v>
       </x:c>
       <x:c r="U50" s="3" t="s">
         <x:v>2</x:v>
@@ -10588,7 +10552,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad6f22be4874441d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R292f9d36064a4636"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10688,64 +10652,64 @@
     </x:row>
     <x:row r="2" ht="149.25" hidden="0">
       <x:c r="A2" s="3" t="s">
-        <x:v>1061</x:v>
+        <x:v>1049</x:v>
       </x:c>
       <x:c r="B2" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C2" s="3" t="s">
-        <x:v>1062</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="D2" s="3" t="s">
-        <x:v>1063</x:v>
+        <x:v>1051</x:v>
       </x:c>
       <x:c r="E2" s="3" t="s">
-        <x:v>1064</x:v>
+        <x:v>1052</x:v>
       </x:c>
       <x:c r="F2" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G2" s="3" t="s">
-        <x:v>1065</x:v>
+        <x:v>1053</x:v>
       </x:c>
       <x:c r="H2" s="3" t="s">
-        <x:v>1066</x:v>
+        <x:v>1054</x:v>
       </x:c>
       <x:c r="I2" s="3" t="s">
-        <x:v>1067</x:v>
+        <x:v>1055</x:v>
       </x:c>
       <x:c r="J2" s="3" t="s">
-        <x:v>1068</x:v>
+        <x:v>1056</x:v>
       </x:c>
       <x:c r="K2" s="3" t="s">
         <x:v>188</x:v>
       </x:c>
       <x:c r="L2" s="3" t="s">
-        <x:v>1069</x:v>
+        <x:v>1057</x:v>
       </x:c>
       <x:c r="M2" s="3" t="s">
-        <x:v>1070</x:v>
+        <x:v>1058</x:v>
       </x:c>
       <x:c r="N2" s="3" t="s">
-        <x:v>1071</x:v>
+        <x:v>1059</x:v>
       </x:c>
       <x:c r="O2" s="3" t="s">
-        <x:v>1072</x:v>
+        <x:v>1060</x:v>
       </x:c>
       <x:c r="P2" s="3" t="s">
-        <x:v>1073</x:v>
+        <x:v>1061</x:v>
       </x:c>
       <x:c r="Q2" s="3" t="s">
-        <x:v>1074</x:v>
+        <x:v>1062</x:v>
       </x:c>
       <x:c r="R2" s="3" t="s">
-        <x:v>1075</x:v>
+        <x:v>1063</x:v>
       </x:c>
       <x:c r="S2" s="3" t="s">
-        <x:v>1076</x:v>
+        <x:v>1064</x:v>
       </x:c>
       <x:c r="T2" s="3" t="s">
-        <x:v>1077</x:v>
+        <x:v>1065</x:v>
       </x:c>
       <x:c r="U2" s="3" t="s">
         <x:v>2</x:v>
@@ -10753,31 +10717,31 @@
     </x:row>
     <x:row r="3" ht="107.25" hidden="0">
       <x:c r="A3" s="3" t="s">
-        <x:v>1078</x:v>
+        <x:v>1066</x:v>
       </x:c>
       <x:c r="B3" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C3" s="3" t="s">
-        <x:v>1079</x:v>
+        <x:v>1067</x:v>
       </x:c>
       <x:c r="D3" s="3" t="s">
-        <x:v>1080</x:v>
+        <x:v>1068</x:v>
       </x:c>
       <x:c r="E3" s="3" t="s">
-        <x:v>1081</x:v>
+        <x:v>1069</x:v>
       </x:c>
       <x:c r="F3" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G3" s="3" t="s">
-        <x:v>1082</x:v>
+        <x:v>1070</x:v>
       </x:c>
       <x:c r="H3" s="3" t="s">
-        <x:v>1083</x:v>
+        <x:v>1071</x:v>
       </x:c>
       <x:c r="I3" s="3" t="s">
-        <x:v>1084</x:v>
+        <x:v>1072</x:v>
       </x:c>
       <x:c r="J3" s="3" t="s">
         <x:v>42</x:v>
@@ -10786,31 +10750,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L3" s="3" t="s">
-        <x:v>1085</x:v>
+        <x:v>1073</x:v>
       </x:c>
       <x:c r="M3" s="3" t="s">
-        <x:v>1086</x:v>
+        <x:v>1074</x:v>
       </x:c>
       <x:c r="N3" s="3" t="s">
-        <x:v>1087</x:v>
+        <x:v>1075</x:v>
       </x:c>
       <x:c r="O3" s="3" t="s">
-        <x:v>1088</x:v>
+        <x:v>1076</x:v>
       </x:c>
       <x:c r="P3" s="3" t="s">
-        <x:v>1089</x:v>
+        <x:v>1077</x:v>
       </x:c>
       <x:c r="Q3" s="3" t="s">
-        <x:v>1090</x:v>
+        <x:v>1078</x:v>
       </x:c>
       <x:c r="R3" s="3" t="s">
-        <x:v>1091</x:v>
+        <x:v>1079</x:v>
       </x:c>
       <x:c r="S3" s="3" t="s">
-        <x:v>1092</x:v>
+        <x:v>1080</x:v>
       </x:c>
       <x:c r="T3" s="3" t="s">
-        <x:v>1093</x:v>
+        <x:v>1081</x:v>
       </x:c>
       <x:c r="U3" s="3" t="s">
         <x:v>2</x:v>
@@ -10818,31 +10782,31 @@
     </x:row>
     <x:row r="4" ht="93.25" hidden="0">
       <x:c r="A4" s="3" t="s">
-        <x:v>1094</x:v>
+        <x:v>1082</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>1095</x:v>
+        <x:v>1083</x:v>
       </x:c>
       <x:c r="D4" s="3" t="s">
-        <x:v>1096</x:v>
+        <x:v>1084</x:v>
       </x:c>
       <x:c r="E4" s="3" t="s">
-        <x:v>1097</x:v>
+        <x:v>1085</x:v>
       </x:c>
       <x:c r="F4" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G4" s="3" t="s">
-        <x:v>1082</x:v>
+        <x:v>1070</x:v>
       </x:c>
       <x:c r="H4" s="3" t="s">
-        <x:v>1083</x:v>
+        <x:v>1071</x:v>
       </x:c>
       <x:c r="I4" s="3" t="s">
-        <x:v>1084</x:v>
+        <x:v>1072</x:v>
       </x:c>
       <x:c r="J4" s="3" t="s">
         <x:v>42</x:v>
@@ -10851,31 +10815,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L4" s="3" t="s">
-        <x:v>1098</x:v>
+        <x:v>1086</x:v>
       </x:c>
       <x:c r="M4" s="3" t="s">
-        <x:v>1086</x:v>
+        <x:v>1074</x:v>
       </x:c>
       <x:c r="N4" s="3" t="s">
-        <x:v>1099</x:v>
+        <x:v>1087</x:v>
       </x:c>
       <x:c r="O4" s="3" t="s">
-        <x:v>1100</x:v>
+        <x:v>1088</x:v>
       </x:c>
       <x:c r="P4" s="3" t="s">
-        <x:v>1101</x:v>
+        <x:v>1089</x:v>
       </x:c>
       <x:c r="Q4" s="3" t="s">
-        <x:v>1102</x:v>
+        <x:v>1090</x:v>
       </x:c>
       <x:c r="R4" s="3" t="s">
-        <x:v>1103</x:v>
+        <x:v>1091</x:v>
       </x:c>
       <x:c r="S4" s="3" t="s">
-        <x:v>1104</x:v>
+        <x:v>1092</x:v>
       </x:c>
       <x:c r="T4" s="3" t="s">
-        <x:v>1105</x:v>
+        <x:v>1093</x:v>
       </x:c>
       <x:c r="U4" s="3" t="s">
         <x:v>2</x:v>
@@ -10883,31 +10847,31 @@
     </x:row>
     <x:row r="5" ht="107.25" hidden="0">
       <x:c r="A5" s="3" t="s">
-        <x:v>1106</x:v>
+        <x:v>1094</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C5" s="3" t="s">
-        <x:v>1107</x:v>
+        <x:v>1095</x:v>
       </x:c>
       <x:c r="D5" s="3" t="s">
-        <x:v>1108</x:v>
+        <x:v>1096</x:v>
       </x:c>
       <x:c r="E5" s="3" t="s">
-        <x:v>1109</x:v>
+        <x:v>1097</x:v>
       </x:c>
       <x:c r="F5" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G5" s="3" t="s">
-        <x:v>1082</x:v>
+        <x:v>1070</x:v>
       </x:c>
       <x:c r="H5" s="3" t="s">
-        <x:v>1083</x:v>
+        <x:v>1071</x:v>
       </x:c>
       <x:c r="I5" s="3" t="s">
-        <x:v>1084</x:v>
+        <x:v>1072</x:v>
       </x:c>
       <x:c r="J5" s="3" t="s">
         <x:v>42</x:v>
@@ -10916,31 +10880,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L5" s="3" t="s">
-        <x:v>1110</x:v>
+        <x:v>1098</x:v>
       </x:c>
       <x:c r="M5" s="3" t="s">
-        <x:v>1086</x:v>
+        <x:v>1074</x:v>
       </x:c>
       <x:c r="N5" s="3" t="s">
-        <x:v>1111</x:v>
+        <x:v>1099</x:v>
       </x:c>
       <x:c r="O5" s="3" t="s">
-        <x:v>1112</x:v>
+        <x:v>1100</x:v>
       </x:c>
       <x:c r="P5" s="3" t="s">
-        <x:v>1113</x:v>
+        <x:v>1101</x:v>
       </x:c>
       <x:c r="Q5" s="3" t="s">
-        <x:v>1114</x:v>
+        <x:v>1102</x:v>
       </x:c>
       <x:c r="R5" s="3" t="s">
-        <x:v>1115</x:v>
+        <x:v>1103</x:v>
       </x:c>
       <x:c r="S5" s="3" t="s">
-        <x:v>1116</x:v>
+        <x:v>1104</x:v>
       </x:c>
       <x:c r="T5" s="3" t="s">
-        <x:v>1117</x:v>
+        <x:v>1105</x:v>
       </x:c>
       <x:c r="U5" s="3" t="s">
         <x:v>2</x:v>
@@ -10948,31 +10912,31 @@
     </x:row>
     <x:row r="6" ht="93.25" hidden="0">
       <x:c r="A6" s="3" t="s">
-        <x:v>1118</x:v>
+        <x:v>1106</x:v>
       </x:c>
       <x:c r="B6" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C6" s="3" t="s">
-        <x:v>1119</x:v>
+        <x:v>1107</x:v>
       </x:c>
       <x:c r="D6" s="3" t="s">
-        <x:v>1120</x:v>
+        <x:v>1108</x:v>
       </x:c>
       <x:c r="E6" s="3" t="s">
-        <x:v>1121</x:v>
+        <x:v>1109</x:v>
       </x:c>
       <x:c r="F6" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G6" s="3" t="s">
-        <x:v>1082</x:v>
+        <x:v>1070</x:v>
       </x:c>
       <x:c r="H6" s="3" t="s">
-        <x:v>1083</x:v>
+        <x:v>1071</x:v>
       </x:c>
       <x:c r="I6" s="3" t="s">
-        <x:v>1084</x:v>
+        <x:v>1072</x:v>
       </x:c>
       <x:c r="J6" s="3" t="s">
         <x:v>42</x:v>
@@ -10981,31 +10945,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L6" s="3" t="s">
-        <x:v>1122</x:v>
+        <x:v>1110</x:v>
       </x:c>
       <x:c r="M6" s="3" t="s">
-        <x:v>1086</x:v>
+        <x:v>1074</x:v>
       </x:c>
       <x:c r="N6" s="3" t="s">
-        <x:v>1123</x:v>
+        <x:v>1111</x:v>
       </x:c>
       <x:c r="O6" s="3" t="s">
-        <x:v>1124</x:v>
+        <x:v>1112</x:v>
       </x:c>
       <x:c r="P6" s="3" t="s">
-        <x:v>1125</x:v>
+        <x:v>1113</x:v>
       </x:c>
       <x:c r="Q6" s="3" t="s">
-        <x:v>1126</x:v>
+        <x:v>1114</x:v>
       </x:c>
       <x:c r="R6" s="3" t="s">
-        <x:v>1127</x:v>
+        <x:v>1115</x:v>
       </x:c>
       <x:c r="S6" s="3" t="s">
-        <x:v>1128</x:v>
+        <x:v>1116</x:v>
       </x:c>
       <x:c r="T6" s="3" t="s">
-        <x:v>1129</x:v>
+        <x:v>1117</x:v>
       </x:c>
       <x:c r="U6" s="3" t="s">
         <x:v>2</x:v>
@@ -11013,31 +10977,31 @@
     </x:row>
     <x:row r="7" ht="93.25" hidden="0">
       <x:c r="A7" s="3" t="s">
-        <x:v>1130</x:v>
+        <x:v>1118</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>1131</x:v>
+        <x:v>1119</x:v>
       </x:c>
       <x:c r="D7" s="3" t="s">
-        <x:v>1132</x:v>
+        <x:v>1120</x:v>
       </x:c>
       <x:c r="E7" s="3" t="s">
-        <x:v>1133</x:v>
+        <x:v>1121</x:v>
       </x:c>
       <x:c r="F7" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G7" s="3" t="s">
-        <x:v>1082</x:v>
+        <x:v>1070</x:v>
       </x:c>
       <x:c r="H7" s="3" t="s">
-        <x:v>1083</x:v>
+        <x:v>1071</x:v>
       </x:c>
       <x:c r="I7" s="3" t="s">
-        <x:v>1084</x:v>
+        <x:v>1072</x:v>
       </x:c>
       <x:c r="J7" s="3" t="s">
         <x:v>42</x:v>
@@ -11046,31 +11010,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="L7" s="3" t="s">
-        <x:v>1134</x:v>
+        <x:v>1122</x:v>
       </x:c>
       <x:c r="M7" s="3" t="s">
-        <x:v>1086</x:v>
+        <x:v>1074</x:v>
       </x:c>
       <x:c r="N7" s="3" t="s">
-        <x:v>1135</x:v>
+        <x:v>1123</x:v>
       </x:c>
       <x:c r="O7" s="3" t="s">
-        <x:v>1136</x:v>
+        <x:v>1124</x:v>
       </x:c>
       <x:c r="P7" s="3" t="s">
-        <x:v>1137</x:v>
+        <x:v>1125</x:v>
       </x:c>
       <x:c r="Q7" s="3" t="s">
-        <x:v>1090</x:v>
+        <x:v>1078</x:v>
       </x:c>
       <x:c r="R7" s="3" t="s">
-        <x:v>1138</x:v>
+        <x:v>1126</x:v>
       </x:c>
       <x:c r="S7" s="3" t="s">
-        <x:v>1139</x:v>
+        <x:v>1127</x:v>
       </x:c>
       <x:c r="T7" s="3" t="s">
-        <x:v>1140</x:v>
+        <x:v>1128</x:v>
       </x:c>
       <x:c r="U7" s="3" t="s">
         <x:v>2</x:v>
@@ -11078,31 +11042,31 @@
     </x:row>
     <x:row r="8" ht="93.25" hidden="0">
       <x:c r="A8" s="3" t="s">
-        <x:v>1141</x:v>
+        <x:v>1129</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>1142</x:v>
+        <x:v>1130</x:v>
       </x:c>
       <x:c r="D8" s="3" t="s">
-        <x:v>1143</x:v>
+        <x:v>1131</x:v>
       </x:c>
       <x:c r="E8" s="3" t="s">
-        <x:v>1144</x:v>
+        <x:v>1132</x:v>
       </x:c>
       <x:c r="F8" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G8" s="3" t="s">
-        <x:v>1082</x:v>
+        <x:v>1070</x:v>
       </x:c>
       <x:c r="H8" s="3" t="s">
-        <x:v>1083</x:v>
+        <x:v>1071</x:v>
       </x:c>
       <x:c r="I8" s="3" t="s">
-        <x:v>1084</x:v>
+        <x:v>1072</x:v>
       </x:c>
       <x:c r="J8" s="3" t="s">
         <x:v>42</x:v>
@@ -11111,31 +11075,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L8" s="3" t="s">
-        <x:v>1145</x:v>
+        <x:v>1133</x:v>
       </x:c>
       <x:c r="M8" s="3" t="s">
-        <x:v>1086</x:v>
+        <x:v>1074</x:v>
       </x:c>
       <x:c r="N8" s="3" t="s">
-        <x:v>1146</x:v>
+        <x:v>1134</x:v>
       </x:c>
       <x:c r="O8" s="3" t="s">
-        <x:v>1147</x:v>
+        <x:v>1135</x:v>
       </x:c>
       <x:c r="P8" s="3" t="s">
-        <x:v>1148</x:v>
+        <x:v>1136</x:v>
       </x:c>
       <x:c r="Q8" s="3" t="s">
-        <x:v>1149</x:v>
+        <x:v>1137</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
-        <x:v>1150</x:v>
+        <x:v>1138</x:v>
       </x:c>
       <x:c r="S8" s="3" t="s">
-        <x:v>1151</x:v>
+        <x:v>1139</x:v>
       </x:c>
       <x:c r="T8" s="3" t="s">
-        <x:v>1152</x:v>
+        <x:v>1140</x:v>
       </x:c>
       <x:c r="U8" s="3" t="s">
         <x:v>2</x:v>
@@ -11143,31 +11107,31 @@
     </x:row>
     <x:row r="9" ht="93.25" hidden="0">
       <x:c r="A9" s="3" t="s">
-        <x:v>1153</x:v>
+        <x:v>1141</x:v>
       </x:c>
       <x:c r="B9" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C9" s="3" t="s">
-        <x:v>1154</x:v>
+        <x:v>1142</x:v>
       </x:c>
       <x:c r="D9" s="3" t="s">
-        <x:v>1155</x:v>
+        <x:v>1143</x:v>
       </x:c>
       <x:c r="E9" s="3" t="s">
-        <x:v>1156</x:v>
+        <x:v>1144</x:v>
       </x:c>
       <x:c r="F9" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G9" s="3" t="s">
-        <x:v>1082</x:v>
+        <x:v>1070</x:v>
       </x:c>
       <x:c r="H9" s="3" t="s">
-        <x:v>1083</x:v>
+        <x:v>1071</x:v>
       </x:c>
       <x:c r="I9" s="3" t="s">
-        <x:v>1084</x:v>
+        <x:v>1072</x:v>
       </x:c>
       <x:c r="J9" s="3" t="s">
         <x:v>42</x:v>
@@ -11176,31 +11140,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L9" s="3" t="s">
-        <x:v>1157</x:v>
+        <x:v>1145</x:v>
       </x:c>
       <x:c r="M9" s="3" t="s">
-        <x:v>1086</x:v>
+        <x:v>1074</x:v>
       </x:c>
       <x:c r="N9" s="3" t="s">
-        <x:v>1158</x:v>
+        <x:v>1146</x:v>
       </x:c>
       <x:c r="O9" s="3" t="s">
-        <x:v>1159</x:v>
+        <x:v>1147</x:v>
       </x:c>
       <x:c r="P9" s="3" t="s">
-        <x:v>1160</x:v>
+        <x:v>1148</x:v>
       </x:c>
       <x:c r="Q9" s="3" t="s">
-        <x:v>1161</x:v>
+        <x:v>1149</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
-        <x:v>1162</x:v>
+        <x:v>1150</x:v>
       </x:c>
       <x:c r="S9" s="3" t="s">
-        <x:v>1163</x:v>
+        <x:v>1151</x:v>
       </x:c>
       <x:c r="T9" s="3" t="s">
-        <x:v>1164</x:v>
+        <x:v>1152</x:v>
       </x:c>
       <x:c r="U9" s="3" t="s">
         <x:v>2</x:v>
@@ -11208,31 +11172,31 @@
     </x:row>
     <x:row r="10" ht="93.25" hidden="0">
       <x:c r="A10" s="3" t="s">
-        <x:v>1165</x:v>
+        <x:v>1153</x:v>
       </x:c>
       <x:c r="B10" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C10" s="3" t="s">
-        <x:v>1166</x:v>
+        <x:v>1154</x:v>
       </x:c>
       <x:c r="D10" s="3" t="s">
-        <x:v>1167</x:v>
+        <x:v>1155</x:v>
       </x:c>
       <x:c r="E10" s="3" t="s">
-        <x:v>1168</x:v>
+        <x:v>1156</x:v>
       </x:c>
       <x:c r="F10" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G10" s="3" t="s">
-        <x:v>1082</x:v>
+        <x:v>1070</x:v>
       </x:c>
       <x:c r="H10" s="3" t="s">
-        <x:v>1083</x:v>
+        <x:v>1071</x:v>
       </x:c>
       <x:c r="I10" s="3" t="s">
-        <x:v>1084</x:v>
+        <x:v>1072</x:v>
       </x:c>
       <x:c r="J10" s="3" t="s">
         <x:v>42</x:v>
@@ -11241,31 +11205,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L10" s="3" t="s">
-        <x:v>1169</x:v>
+        <x:v>1157</x:v>
       </x:c>
       <x:c r="M10" s="3" t="s">
-        <x:v>1070</x:v>
+        <x:v>1058</x:v>
       </x:c>
       <x:c r="N10" s="3" t="s">
-        <x:v>1170</x:v>
+        <x:v>1158</x:v>
       </x:c>
       <x:c r="O10" s="3" t="s">
         <x:v>205</x:v>
       </x:c>
       <x:c r="P10" s="3" t="s">
-        <x:v>1171</x:v>
+        <x:v>1159</x:v>
       </x:c>
       <x:c r="Q10" s="3" t="s">
-        <x:v>1172</x:v>
+        <x:v>1160</x:v>
       </x:c>
       <x:c r="R10" s="3" t="s">
-        <x:v>1173</x:v>
+        <x:v>1161</x:v>
       </x:c>
       <x:c r="S10" s="3" t="s">
-        <x:v>1174</x:v>
+        <x:v>1162</x:v>
       </x:c>
       <x:c r="T10" s="3" t="s">
-        <x:v>1175</x:v>
+        <x:v>1163</x:v>
       </x:c>
       <x:c r="U10" s="3" t="s">
         <x:v>2</x:v>
@@ -11273,31 +11237,31 @@
     </x:row>
     <x:row r="11" ht="93.25" hidden="0">
       <x:c r="A11" s="3" t="s">
-        <x:v>1176</x:v>
+        <x:v>1164</x:v>
       </x:c>
       <x:c r="B11" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C11" s="3" t="s">
-        <x:v>1177</x:v>
+        <x:v>1165</x:v>
       </x:c>
       <x:c r="D11" s="3" t="s">
-        <x:v>1178</x:v>
+        <x:v>1166</x:v>
       </x:c>
       <x:c r="E11" s="3" t="s">
-        <x:v>1179</x:v>
+        <x:v>1167</x:v>
       </x:c>
       <x:c r="F11" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G11" s="3" t="s">
-        <x:v>1082</x:v>
+        <x:v>1070</x:v>
       </x:c>
       <x:c r="H11" s="3" t="s">
-        <x:v>1083</x:v>
+        <x:v>1071</x:v>
       </x:c>
       <x:c r="I11" s="3" t="s">
-        <x:v>1084</x:v>
+        <x:v>1072</x:v>
       </x:c>
       <x:c r="J11" s="3" t="s">
         <x:v>42</x:v>
@@ -11306,31 +11270,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L11" s="3" t="s">
-        <x:v>1180</x:v>
+        <x:v>1168</x:v>
       </x:c>
       <x:c r="M11" s="3" t="s">
-        <x:v>1181</x:v>
+        <x:v>1169</x:v>
       </x:c>
       <x:c r="N11" s="3" t="s">
-        <x:v>1182</x:v>
+        <x:v>1170</x:v>
       </x:c>
       <x:c r="O11" s="3" t="s">
-        <x:v>1183</x:v>
+        <x:v>1171</x:v>
       </x:c>
       <x:c r="P11" s="3" t="s">
-        <x:v>1184</x:v>
+        <x:v>1172</x:v>
       </x:c>
       <x:c r="Q11" s="3" t="s">
-        <x:v>1185</x:v>
+        <x:v>1173</x:v>
       </x:c>
       <x:c r="R11" s="3" t="s">
-        <x:v>1186</x:v>
+        <x:v>1174</x:v>
       </x:c>
       <x:c r="S11" s="3" t="s">
-        <x:v>1187</x:v>
+        <x:v>1175</x:v>
       </x:c>
       <x:c r="T11" s="3" t="s">
-        <x:v>1188</x:v>
+        <x:v>1176</x:v>
       </x:c>
       <x:c r="U11" s="3" t="s">
         <x:v>2</x:v>
@@ -11338,31 +11302,31 @@
     </x:row>
     <x:row r="12" ht="107.25" hidden="0">
       <x:c r="A12" s="3" t="s">
-        <x:v>1189</x:v>
+        <x:v>1177</x:v>
       </x:c>
       <x:c r="B12" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C12" s="3" t="s">
-        <x:v>1190</x:v>
+        <x:v>1178</x:v>
       </x:c>
       <x:c r="D12" s="3" t="s">
-        <x:v>1191</x:v>
+        <x:v>1179</x:v>
       </x:c>
       <x:c r="E12" s="3" t="s">
-        <x:v>1192</x:v>
+        <x:v>1180</x:v>
       </x:c>
       <x:c r="F12" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G12" s="3" t="s">
-        <x:v>1082</x:v>
+        <x:v>1070</x:v>
       </x:c>
       <x:c r="H12" s="3" t="s">
-        <x:v>1083</x:v>
+        <x:v>1071</x:v>
       </x:c>
       <x:c r="I12" s="3" t="s">
-        <x:v>1084</x:v>
+        <x:v>1072</x:v>
       </x:c>
       <x:c r="J12" s="3" t="s">
         <x:v>42</x:v>
@@ -11371,31 +11335,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L12" s="3" t="s">
-        <x:v>1193</x:v>
+        <x:v>1181</x:v>
       </x:c>
       <x:c r="M12" s="3" t="s">
-        <x:v>1086</x:v>
+        <x:v>1074</x:v>
       </x:c>
       <x:c r="N12" s="3" t="s">
-        <x:v>1194</x:v>
+        <x:v>1182</x:v>
       </x:c>
       <x:c r="O12" s="3" t="s">
-        <x:v>1195</x:v>
+        <x:v>1183</x:v>
       </x:c>
       <x:c r="P12" s="3" t="s">
-        <x:v>1196</x:v>
+        <x:v>1184</x:v>
       </x:c>
       <x:c r="Q12" s="3" t="s">
-        <x:v>1197</x:v>
+        <x:v>1185</x:v>
       </x:c>
       <x:c r="R12" s="3" t="s">
-        <x:v>1198</x:v>
+        <x:v>1186</x:v>
       </x:c>
       <x:c r="S12" s="3" t="s">
-        <x:v>1199</x:v>
+        <x:v>1187</x:v>
       </x:c>
       <x:c r="T12" s="3" t="s">
-        <x:v>1200</x:v>
+        <x:v>1188</x:v>
       </x:c>
       <x:c r="U12" s="3" t="s">
         <x:v>2</x:v>
@@ -11403,31 +11367,31 @@
     </x:row>
     <x:row r="13" ht="93.25" hidden="0">
       <x:c r="A13" s="3" t="s">
-        <x:v>1201</x:v>
+        <x:v>1189</x:v>
       </x:c>
       <x:c r="B13" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C13" s="3" t="s">
-        <x:v>1202</x:v>
+        <x:v>1190</x:v>
       </x:c>
       <x:c r="D13" s="3" t="s">
-        <x:v>1203</x:v>
+        <x:v>1191</x:v>
       </x:c>
       <x:c r="E13" s="3" t="s">
-        <x:v>1204</x:v>
+        <x:v>1192</x:v>
       </x:c>
       <x:c r="F13" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G13" s="3" t="s">
-        <x:v>1082</x:v>
+        <x:v>1070</x:v>
       </x:c>
       <x:c r="H13" s="3" t="s">
-        <x:v>1083</x:v>
+        <x:v>1071</x:v>
       </x:c>
       <x:c r="I13" s="3" t="s">
-        <x:v>1084</x:v>
+        <x:v>1072</x:v>
       </x:c>
       <x:c r="J13" s="3" t="s">
         <x:v>42</x:v>
@@ -11436,31 +11400,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L13" s="3" t="s">
-        <x:v>1205</x:v>
+        <x:v>1193</x:v>
       </x:c>
       <x:c r="M13" s="3" t="s">
-        <x:v>1086</x:v>
+        <x:v>1074</x:v>
       </x:c>
       <x:c r="N13" s="3" t="s">
-        <x:v>1206</x:v>
+        <x:v>1194</x:v>
       </x:c>
       <x:c r="O13" s="3" t="s">
-        <x:v>1207</x:v>
+        <x:v>1195</x:v>
       </x:c>
       <x:c r="P13" s="3" t="s">
-        <x:v>1208</x:v>
+        <x:v>1196</x:v>
       </x:c>
       <x:c r="Q13" s="3" t="s">
+        <x:v>1185</x:v>
+      </x:c>
+      <x:c r="R13" s="3" t="s">
         <x:v>1197</x:v>
       </x:c>
-      <x:c r="R13" s="3" t="s">
-        <x:v>1209</x:v>
-      </x:c>
       <x:c r="S13" s="3" t="s">
-        <x:v>1210</x:v>
+        <x:v>1198</x:v>
       </x:c>
       <x:c r="T13" s="3" t="s">
-        <x:v>1211</x:v>
+        <x:v>1199</x:v>
       </x:c>
       <x:c r="U13" s="3" t="s">
         <x:v>2</x:v>
@@ -11468,31 +11432,31 @@
     </x:row>
     <x:row r="14" ht="93.25" hidden="0">
       <x:c r="A14" s="3" t="s">
-        <x:v>1212</x:v>
+        <x:v>1200</x:v>
       </x:c>
       <x:c r="B14" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C14" s="3" t="s">
-        <x:v>1213</x:v>
+        <x:v>1201</x:v>
       </x:c>
       <x:c r="D14" s="3" t="s">
-        <x:v>1214</x:v>
+        <x:v>1202</x:v>
       </x:c>
       <x:c r="E14" s="3" t="s">
-        <x:v>1215</x:v>
+        <x:v>1203</x:v>
       </x:c>
       <x:c r="F14" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G14" s="3" t="s">
-        <x:v>1082</x:v>
+        <x:v>1070</x:v>
       </x:c>
       <x:c r="H14" s="3" t="s">
-        <x:v>1083</x:v>
+        <x:v>1071</x:v>
       </x:c>
       <x:c r="I14" s="3" t="s">
-        <x:v>1084</x:v>
+        <x:v>1072</x:v>
       </x:c>
       <x:c r="J14" s="3" t="s">
         <x:v>42</x:v>
@@ -11501,31 +11465,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L14" s="3" t="s">
-        <x:v>1216</x:v>
+        <x:v>1204</x:v>
       </x:c>
       <x:c r="M14" s="3" t="s">
-        <x:v>1217</x:v>
+        <x:v>1205</x:v>
       </x:c>
       <x:c r="N14" s="3" t="s">
-        <x:v>1218</x:v>
+        <x:v>1206</x:v>
       </x:c>
       <x:c r="O14" s="3" t="s">
-        <x:v>1219</x:v>
+        <x:v>1207</x:v>
       </x:c>
       <x:c r="P14" s="3" t="s">
-        <x:v>1220</x:v>
+        <x:v>1208</x:v>
       </x:c>
       <x:c r="Q14" s="3" t="s">
-        <x:v>1221</x:v>
+        <x:v>1209</x:v>
       </x:c>
       <x:c r="R14" s="3" t="s">
-        <x:v>1222</x:v>
+        <x:v>1210</x:v>
       </x:c>
       <x:c r="S14" s="3" t="s">
-        <x:v>1223</x:v>
+        <x:v>1211</x:v>
       </x:c>
       <x:c r="T14" s="3" t="s">
-        <x:v>1224</x:v>
+        <x:v>1212</x:v>
       </x:c>
       <x:c r="U14" s="3" t="s">
         <x:v>2</x:v>
@@ -11533,31 +11497,31 @@
     </x:row>
     <x:row r="15" ht="107.25" hidden="0">
       <x:c r="A15" s="3" t="s">
-        <x:v>1225</x:v>
+        <x:v>1213</x:v>
       </x:c>
       <x:c r="B15" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C15" s="3" t="s">
-        <x:v>1226</x:v>
+        <x:v>1214</x:v>
       </x:c>
       <x:c r="D15" s="3" t="s">
-        <x:v>1227</x:v>
+        <x:v>1215</x:v>
       </x:c>
       <x:c r="E15" s="3" t="s">
-        <x:v>1228</x:v>
+        <x:v>1216</x:v>
       </x:c>
       <x:c r="F15" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G15" s="3" t="s">
-        <x:v>1082</x:v>
+        <x:v>1070</x:v>
       </x:c>
       <x:c r="H15" s="3" t="s">
-        <x:v>1083</x:v>
+        <x:v>1071</x:v>
       </x:c>
       <x:c r="I15" s="3" t="s">
-        <x:v>1084</x:v>
+        <x:v>1072</x:v>
       </x:c>
       <x:c r="J15" s="3" t="s">
         <x:v>42</x:v>
@@ -11566,31 +11530,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L15" s="3" t="s">
-        <x:v>1229</x:v>
+        <x:v>1217</x:v>
       </x:c>
       <x:c r="M15" s="3" t="s">
-        <x:v>1086</x:v>
+        <x:v>1074</x:v>
       </x:c>
       <x:c r="N15" s="3" t="s">
-        <x:v>1230</x:v>
+        <x:v>1218</x:v>
       </x:c>
       <x:c r="O15" s="3" t="s">
-        <x:v>1231</x:v>
+        <x:v>1219</x:v>
       </x:c>
       <x:c r="P15" s="3" t="s">
-        <x:v>1232</x:v>
+        <x:v>1220</x:v>
       </x:c>
       <x:c r="Q15" s="3" t="s">
-        <x:v>1233</x:v>
+        <x:v>1221</x:v>
       </x:c>
       <x:c r="R15" s="3" t="s">
-        <x:v>1234</x:v>
+        <x:v>1222</x:v>
       </x:c>
       <x:c r="S15" s="3" t="s">
-        <x:v>1235</x:v>
+        <x:v>1223</x:v>
       </x:c>
       <x:c r="T15" s="3" t="s">
-        <x:v>1236</x:v>
+        <x:v>1224</x:v>
       </x:c>
       <x:c r="U15" s="3" t="s">
         <x:v>2</x:v>
@@ -11598,31 +11562,31 @@
     </x:row>
     <x:row r="16" ht="107.25" hidden="0">
       <x:c r="A16" s="3" t="s">
-        <x:v>1237</x:v>
+        <x:v>1225</x:v>
       </x:c>
       <x:c r="B16" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C16" s="3" t="s">
-        <x:v>1238</x:v>
+        <x:v>1226</x:v>
       </x:c>
       <x:c r="D16" s="3" t="s">
-        <x:v>1239</x:v>
+        <x:v>1227</x:v>
       </x:c>
       <x:c r="E16" s="3" t="s">
-        <x:v>1240</x:v>
+        <x:v>1228</x:v>
       </x:c>
       <x:c r="F16" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G16" s="3" t="s">
-        <x:v>1082</x:v>
+        <x:v>1070</x:v>
       </x:c>
       <x:c r="H16" s="3" t="s">
-        <x:v>1083</x:v>
+        <x:v>1071</x:v>
       </x:c>
       <x:c r="I16" s="3" t="s">
-        <x:v>1084</x:v>
+        <x:v>1072</x:v>
       </x:c>
       <x:c r="J16" s="3" t="s">
         <x:v>42</x:v>
@@ -11631,31 +11595,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L16" s="3" t="s">
-        <x:v>1241</x:v>
+        <x:v>1229</x:v>
       </x:c>
       <x:c r="M16" s="3" t="s">
-        <x:v>1086</x:v>
+        <x:v>1074</x:v>
       </x:c>
       <x:c r="N16" s="3" t="s">
-        <x:v>1242</x:v>
+        <x:v>1230</x:v>
       </x:c>
       <x:c r="O16" s="3" t="s">
-        <x:v>1243</x:v>
+        <x:v>1231</x:v>
       </x:c>
       <x:c r="P16" s="3" t="s">
-        <x:v>1244</x:v>
+        <x:v>1232</x:v>
       </x:c>
       <x:c r="Q16" s="3" t="s">
-        <x:v>1245</x:v>
+        <x:v>1233</x:v>
       </x:c>
       <x:c r="R16" s="3" t="s">
-        <x:v>1246</x:v>
+        <x:v>1234</x:v>
       </x:c>
       <x:c r="S16" s="3" t="s">
-        <x:v>1247</x:v>
+        <x:v>1235</x:v>
       </x:c>
       <x:c r="T16" s="3" t="s">
-        <x:v>1248</x:v>
+        <x:v>1236</x:v>
       </x:c>
       <x:c r="U16" s="3" t="s">
         <x:v>2</x:v>
@@ -11663,31 +11627,31 @@
     </x:row>
     <x:row r="17" ht="93.25" hidden="0">
       <x:c r="A17" s="3" t="s">
-        <x:v>1249</x:v>
+        <x:v>1237</x:v>
       </x:c>
       <x:c r="B17" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C17" s="3" t="s">
-        <x:v>1250</x:v>
+        <x:v>1238</x:v>
       </x:c>
       <x:c r="D17" s="3" t="s">
-        <x:v>1251</x:v>
+        <x:v>1239</x:v>
       </x:c>
       <x:c r="E17" s="3" t="s">
-        <x:v>1252</x:v>
+        <x:v>1240</x:v>
       </x:c>
       <x:c r="F17" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G17" s="3" t="s">
-        <x:v>1082</x:v>
+        <x:v>1070</x:v>
       </x:c>
       <x:c r="H17" s="3" t="s">
-        <x:v>1083</x:v>
+        <x:v>1071</x:v>
       </x:c>
       <x:c r="I17" s="3" t="s">
-        <x:v>1084</x:v>
+        <x:v>1072</x:v>
       </x:c>
       <x:c r="J17" s="3" t="s">
         <x:v>42</x:v>
@@ -11696,31 +11660,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L17" s="3" t="s">
-        <x:v>1253</x:v>
+        <x:v>1241</x:v>
       </x:c>
       <x:c r="M17" s="3" t="s">
-        <x:v>1254</x:v>
+        <x:v>1242</x:v>
       </x:c>
       <x:c r="N17" s="3" t="s">
-        <x:v>1255</x:v>
+        <x:v>1243</x:v>
       </x:c>
       <x:c r="O17" s="3" t="s">
-        <x:v>1256</x:v>
+        <x:v>1244</x:v>
       </x:c>
       <x:c r="P17" s="3" t="s">
-        <x:v>1257</x:v>
+        <x:v>1245</x:v>
       </x:c>
       <x:c r="Q17" s="3" t="s">
-        <x:v>1258</x:v>
+        <x:v>1246</x:v>
       </x:c>
       <x:c r="R17" s="3" t="s">
-        <x:v>1259</x:v>
+        <x:v>1247</x:v>
       </x:c>
       <x:c r="S17" s="3" t="s">
-        <x:v>1260</x:v>
+        <x:v>1248</x:v>
       </x:c>
       <x:c r="T17" s="3" t="s">
-        <x:v>1261</x:v>
+        <x:v>1249</x:v>
       </x:c>
       <x:c r="U17" s="3" t="s">
         <x:v>2</x:v>
@@ -11728,31 +11692,31 @@
     </x:row>
     <x:row r="18" ht="93.25" hidden="0">
       <x:c r="A18" s="3" t="s">
-        <x:v>1262</x:v>
+        <x:v>1250</x:v>
       </x:c>
       <x:c r="B18" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C18" s="3" t="s">
-        <x:v>1263</x:v>
+        <x:v>1251</x:v>
       </x:c>
       <x:c r="D18" s="3" t="s">
-        <x:v>1264</x:v>
+        <x:v>1252</x:v>
       </x:c>
       <x:c r="E18" s="3" t="s">
-        <x:v>1265</x:v>
+        <x:v>1253</x:v>
       </x:c>
       <x:c r="F18" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G18" s="3" t="s">
-        <x:v>1082</x:v>
+        <x:v>1070</x:v>
       </x:c>
       <x:c r="H18" s="3" t="s">
-        <x:v>1083</x:v>
+        <x:v>1071</x:v>
       </x:c>
       <x:c r="I18" s="3" t="s">
-        <x:v>1084</x:v>
+        <x:v>1072</x:v>
       </x:c>
       <x:c r="J18" s="3" t="s">
         <x:v>42</x:v>
@@ -11761,31 +11725,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L18" s="3" t="s">
-        <x:v>1266</x:v>
+        <x:v>1254</x:v>
       </x:c>
       <x:c r="M18" s="3" t="s">
-        <x:v>1267</x:v>
+        <x:v>1255</x:v>
       </x:c>
       <x:c r="N18" s="3" t="s">
-        <x:v>1268</x:v>
+        <x:v>1256</x:v>
       </x:c>
       <x:c r="O18" s="3" t="s">
-        <x:v>1269</x:v>
+        <x:v>1257</x:v>
       </x:c>
       <x:c r="P18" s="3" t="s">
-        <x:v>1270</x:v>
+        <x:v>1258</x:v>
       </x:c>
       <x:c r="Q18" s="3" t="s">
-        <x:v>1271</x:v>
+        <x:v>1259</x:v>
       </x:c>
       <x:c r="R18" s="3" t="s">
-        <x:v>1272</x:v>
+        <x:v>1260</x:v>
       </x:c>
       <x:c r="S18" s="3" t="s">
-        <x:v>1273</x:v>
+        <x:v>1261</x:v>
       </x:c>
       <x:c r="T18" s="3" t="s">
-        <x:v>1274</x:v>
+        <x:v>1262</x:v>
       </x:c>
       <x:c r="U18" s="3" t="s">
         <x:v>2</x:v>
@@ -11793,31 +11757,31 @@
     </x:row>
     <x:row r="19" ht="93.25" hidden="0">
       <x:c r="A19" s="3" t="s">
-        <x:v>1275</x:v>
+        <x:v>1263</x:v>
       </x:c>
       <x:c r="B19" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C19" s="3" t="s">
-        <x:v>1276</x:v>
+        <x:v>1264</x:v>
       </x:c>
       <x:c r="D19" s="3" t="s">
-        <x:v>1277</x:v>
+        <x:v>1265</x:v>
       </x:c>
       <x:c r="E19" s="3" t="s">
-        <x:v>1278</x:v>
+        <x:v>1266</x:v>
       </x:c>
       <x:c r="F19" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G19" s="3" t="s">
-        <x:v>1082</x:v>
+        <x:v>1070</x:v>
       </x:c>
       <x:c r="H19" s="3" t="s">
-        <x:v>1083</x:v>
+        <x:v>1071</x:v>
       </x:c>
       <x:c r="I19" s="3" t="s">
-        <x:v>1084</x:v>
+        <x:v>1072</x:v>
       </x:c>
       <x:c r="J19" s="3" t="s">
         <x:v>42</x:v>
@@ -11826,31 +11790,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L19" s="3" t="s">
-        <x:v>1279</x:v>
+        <x:v>1267</x:v>
       </x:c>
       <x:c r="M19" s="3" t="s">
-        <x:v>1280</x:v>
+        <x:v>1268</x:v>
       </x:c>
       <x:c r="N19" s="3" t="s">
-        <x:v>1281</x:v>
+        <x:v>1269</x:v>
       </x:c>
       <x:c r="O19" s="3" t="s">
-        <x:v>1282</x:v>
+        <x:v>1270</x:v>
       </x:c>
       <x:c r="P19" s="3" t="s">
-        <x:v>1283</x:v>
+        <x:v>1271</x:v>
       </x:c>
       <x:c r="Q19" s="3" t="s">
-        <x:v>1284</x:v>
+        <x:v>1272</x:v>
       </x:c>
       <x:c r="R19" s="3" t="s">
-        <x:v>1285</x:v>
+        <x:v>1273</x:v>
       </x:c>
       <x:c r="S19" s="3" t="s">
-        <x:v>1286</x:v>
+        <x:v>1274</x:v>
       </x:c>
       <x:c r="T19" s="3" t="s">
-        <x:v>1287</x:v>
+        <x:v>1275</x:v>
       </x:c>
       <x:c r="U19" s="3" t="s">
         <x:v>2</x:v>
@@ -11858,31 +11822,31 @@
     </x:row>
     <x:row r="20" ht="79.25" hidden="0">
       <x:c r="A20" s="3" t="s">
-        <x:v>1288</x:v>
+        <x:v>1276</x:v>
       </x:c>
       <x:c r="B20" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C20" s="3" t="s">
-        <x:v>1289</x:v>
+        <x:v>1277</x:v>
       </x:c>
       <x:c r="D20" s="3" t="s">
-        <x:v>1290</x:v>
+        <x:v>1278</x:v>
       </x:c>
       <x:c r="E20" s="3" t="s">
-        <x:v>1291</x:v>
+        <x:v>1279</x:v>
       </x:c>
       <x:c r="F20" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G20" s="3" t="s">
-        <x:v>1082</x:v>
+        <x:v>1070</x:v>
       </x:c>
       <x:c r="H20" s="3" t="s">
-        <x:v>1083</x:v>
+        <x:v>1071</x:v>
       </x:c>
       <x:c r="I20" s="3" t="s">
-        <x:v>1084</x:v>
+        <x:v>1072</x:v>
       </x:c>
       <x:c r="J20" s="3" t="s">
         <x:v>42</x:v>
@@ -11891,31 +11855,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L20" s="3" t="s">
-        <x:v>1292</x:v>
+        <x:v>1280</x:v>
       </x:c>
       <x:c r="M20" s="3" t="s">
-        <x:v>1293</x:v>
+        <x:v>1281</x:v>
       </x:c>
       <x:c r="N20" s="3" t="s">
-        <x:v>1294</x:v>
+        <x:v>1282</x:v>
       </x:c>
       <x:c r="O20" s="3" t="s">
-        <x:v>1295</x:v>
+        <x:v>1283</x:v>
       </x:c>
       <x:c r="P20" s="3" t="s">
-        <x:v>1296</x:v>
+        <x:v>1284</x:v>
       </x:c>
       <x:c r="Q20" s="3" t="s">
-        <x:v>1297</x:v>
+        <x:v>1285</x:v>
       </x:c>
       <x:c r="R20" s="3" t="s">
-        <x:v>1298</x:v>
+        <x:v>1286</x:v>
       </x:c>
       <x:c r="S20" s="3" t="s">
-        <x:v>1299</x:v>
+        <x:v>1287</x:v>
       </x:c>
       <x:c r="T20" s="3" t="s">
-        <x:v>1300</x:v>
+        <x:v>1288</x:v>
       </x:c>
       <x:c r="U20" s="3" t="s">
         <x:v>2</x:v>
@@ -11923,31 +11887,31 @@
     </x:row>
     <x:row r="21" ht="79.25" hidden="0">
       <x:c r="A21" s="3" t="s">
-        <x:v>1301</x:v>
+        <x:v>1289</x:v>
       </x:c>
       <x:c r="B21" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C21" s="3" t="s">
-        <x:v>1302</x:v>
+        <x:v>1290</x:v>
       </x:c>
       <x:c r="D21" s="3" t="s">
-        <x:v>1303</x:v>
+        <x:v>1291</x:v>
       </x:c>
       <x:c r="E21" s="3" t="s">
-        <x:v>1304</x:v>
+        <x:v>1292</x:v>
       </x:c>
       <x:c r="F21" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G21" s="3" t="s">
-        <x:v>1082</x:v>
+        <x:v>1070</x:v>
       </x:c>
       <x:c r="H21" s="3" t="s">
-        <x:v>1083</x:v>
+        <x:v>1071</x:v>
       </x:c>
       <x:c r="I21" s="3" t="s">
-        <x:v>1084</x:v>
+        <x:v>1072</x:v>
       </x:c>
       <x:c r="J21" s="3" t="s">
         <x:v>42</x:v>
@@ -11956,31 +11920,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L21" s="3" t="s">
-        <x:v>1305</x:v>
+        <x:v>1293</x:v>
       </x:c>
       <x:c r="M21" s="3" t="s">
-        <x:v>1306</x:v>
+        <x:v>1294</x:v>
       </x:c>
       <x:c r="N21" s="3" t="s">
-        <x:v>1307</x:v>
+        <x:v>1295</x:v>
       </x:c>
       <x:c r="O21" s="3" t="s">
         <x:v>218</x:v>
       </x:c>
       <x:c r="P21" s="3" t="s">
-        <x:v>1308</x:v>
+        <x:v>1296</x:v>
       </x:c>
       <x:c r="Q21" s="3" t="s">
-        <x:v>1309</x:v>
+        <x:v>1297</x:v>
       </x:c>
       <x:c r="R21" s="3" t="s">
         <x:v>221</x:v>
       </x:c>
       <x:c r="S21" s="3" t="s">
-        <x:v>1310</x:v>
+        <x:v>1298</x:v>
       </x:c>
       <x:c r="T21" s="3" t="s">
-        <x:v>1311</x:v>
+        <x:v>1299</x:v>
       </x:c>
       <x:c r="U21" s="3" t="s">
         <x:v>2</x:v>
@@ -11988,31 +11952,31 @@
     </x:row>
     <x:row r="22" ht="93.25" hidden="0">
       <x:c r="A22" s="3" t="s">
-        <x:v>1312</x:v>
+        <x:v>1300</x:v>
       </x:c>
       <x:c r="B22" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C22" s="3" t="s">
-        <x:v>1313</x:v>
+        <x:v>1301</x:v>
       </x:c>
       <x:c r="D22" s="3" t="s">
-        <x:v>1314</x:v>
+        <x:v>1302</x:v>
       </x:c>
       <x:c r="E22" s="3" t="s">
-        <x:v>1315</x:v>
+        <x:v>1303</x:v>
       </x:c>
       <x:c r="F22" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G22" s="3" t="s">
-        <x:v>1082</x:v>
+        <x:v>1070</x:v>
       </x:c>
       <x:c r="H22" s="3" t="s">
-        <x:v>1083</x:v>
+        <x:v>1071</x:v>
       </x:c>
       <x:c r="I22" s="3" t="s">
-        <x:v>1084</x:v>
+        <x:v>1072</x:v>
       </x:c>
       <x:c r="J22" s="3" t="s">
         <x:v>42</x:v>
@@ -12021,31 +11985,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L22" s="3" t="s">
-        <x:v>1316</x:v>
+        <x:v>1304</x:v>
       </x:c>
       <x:c r="M22" s="3" t="s">
-        <x:v>1181</x:v>
+        <x:v>1169</x:v>
       </x:c>
       <x:c r="N22" s="3" t="s">
-        <x:v>1317</x:v>
+        <x:v>1305</x:v>
       </x:c>
       <x:c r="O22" s="3" t="s">
-        <x:v>1318</x:v>
+        <x:v>1306</x:v>
       </x:c>
       <x:c r="P22" s="3" t="s">
-        <x:v>1319</x:v>
+        <x:v>1307</x:v>
       </x:c>
       <x:c r="Q22" s="3" t="s">
-        <x:v>1320</x:v>
+        <x:v>1308</x:v>
       </x:c>
       <x:c r="R22" s="3" t="s">
-        <x:v>1321</x:v>
+        <x:v>1309</x:v>
       </x:c>
       <x:c r="S22" s="3" t="s">
-        <x:v>1322</x:v>
+        <x:v>1310</x:v>
       </x:c>
       <x:c r="T22" s="3" t="s">
-        <x:v>1323</x:v>
+        <x:v>1311</x:v>
       </x:c>
       <x:c r="U22" s="3" t="s">
         <x:v>2</x:v>
@@ -12053,31 +12017,31 @@
     </x:row>
     <x:row r="23" ht="93.25" hidden="0">
       <x:c r="A23" s="3" t="s">
-        <x:v>1324</x:v>
+        <x:v>1312</x:v>
       </x:c>
       <x:c r="B23" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C23" s="3" t="s">
-        <x:v>1325</x:v>
+        <x:v>1313</x:v>
       </x:c>
       <x:c r="D23" s="3" t="s">
-        <x:v>1326</x:v>
+        <x:v>1314</x:v>
       </x:c>
       <x:c r="E23" s="3" t="s">
-        <x:v>1327</x:v>
+        <x:v>1315</x:v>
       </x:c>
       <x:c r="F23" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G23" s="3" t="s">
-        <x:v>1082</x:v>
+        <x:v>1070</x:v>
       </x:c>
       <x:c r="H23" s="3" t="s">
-        <x:v>1083</x:v>
+        <x:v>1071</x:v>
       </x:c>
       <x:c r="I23" s="3" t="s">
-        <x:v>1084</x:v>
+        <x:v>1072</x:v>
       </x:c>
       <x:c r="J23" s="3" t="s">
         <x:v>42</x:v>
@@ -12086,31 +12050,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L23" s="3" t="s">
-        <x:v>1328</x:v>
+        <x:v>1316</x:v>
       </x:c>
       <x:c r="M23" s="3" t="s">
-        <x:v>1329</x:v>
+        <x:v>1317</x:v>
       </x:c>
       <x:c r="N23" s="3" t="s">
-        <x:v>1330</x:v>
+        <x:v>1318</x:v>
       </x:c>
       <x:c r="O23" s="3" t="s">
-        <x:v>1331</x:v>
+        <x:v>1319</x:v>
       </x:c>
       <x:c r="P23" s="3" t="s">
-        <x:v>1332</x:v>
+        <x:v>1320</x:v>
       </x:c>
       <x:c r="Q23" s="3" t="s">
-        <x:v>1333</x:v>
+        <x:v>1321</x:v>
       </x:c>
       <x:c r="R23" s="3" t="s">
-        <x:v>1334</x:v>
+        <x:v>1322</x:v>
       </x:c>
       <x:c r="S23" s="3" t="s">
-        <x:v>1335</x:v>
+        <x:v>1323</x:v>
       </x:c>
       <x:c r="T23" s="3" t="s">
-        <x:v>1336</x:v>
+        <x:v>1324</x:v>
       </x:c>
       <x:c r="U23" s="3" t="s">
         <x:v>2</x:v>
@@ -12118,31 +12082,31 @@
     </x:row>
     <x:row r="24" ht="79.25" hidden="0">
       <x:c r="A24" s="3" t="s">
-        <x:v>1337</x:v>
+        <x:v>1325</x:v>
       </x:c>
       <x:c r="B24" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C24" s="3" t="s">
-        <x:v>1338</x:v>
+        <x:v>1326</x:v>
       </x:c>
       <x:c r="D24" s="3" t="s">
-        <x:v>1339</x:v>
+        <x:v>1327</x:v>
       </x:c>
       <x:c r="E24" s="3" t="s">
-        <x:v>1340</x:v>
+        <x:v>1328</x:v>
       </x:c>
       <x:c r="F24" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G24" s="3" t="s">
-        <x:v>1082</x:v>
+        <x:v>1070</x:v>
       </x:c>
       <x:c r="H24" s="3" t="s">
-        <x:v>1083</x:v>
+        <x:v>1071</x:v>
       </x:c>
       <x:c r="I24" s="3" t="s">
-        <x:v>1084</x:v>
+        <x:v>1072</x:v>
       </x:c>
       <x:c r="J24" s="3" t="s">
         <x:v>42</x:v>
@@ -12151,31 +12115,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L24" s="3" t="s">
-        <x:v>1341</x:v>
+        <x:v>1329</x:v>
       </x:c>
       <x:c r="M24" s="3" t="s">
-        <x:v>1306</x:v>
+        <x:v>1294</x:v>
       </x:c>
       <x:c r="N24" s="3" t="s">
-        <x:v>1342</x:v>
+        <x:v>1330</x:v>
       </x:c>
       <x:c r="O24" s="3" t="s">
-        <x:v>1343</x:v>
+        <x:v>1331</x:v>
       </x:c>
       <x:c r="P24" s="3" t="s">
-        <x:v>1344</x:v>
+        <x:v>1332</x:v>
       </x:c>
       <x:c r="Q24" s="3" t="s">
-        <x:v>1345</x:v>
+        <x:v>1333</x:v>
       </x:c>
       <x:c r="R24" s="3" t="s">
-        <x:v>1346</x:v>
+        <x:v>1334</x:v>
       </x:c>
       <x:c r="S24" s="3" t="s">
-        <x:v>1347</x:v>
+        <x:v>1335</x:v>
       </x:c>
       <x:c r="T24" s="3" t="s">
-        <x:v>1348</x:v>
+        <x:v>1336</x:v>
       </x:c>
       <x:c r="U24" s="3" t="s">
         <x:v>2</x:v>
@@ -12183,31 +12147,31 @@
     </x:row>
     <x:row r="25" ht="79.25" hidden="0">
       <x:c r="A25" s="3" t="s">
-        <x:v>1349</x:v>
+        <x:v>1337</x:v>
       </x:c>
       <x:c r="B25" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C25" s="3" t="s">
-        <x:v>1350</x:v>
+        <x:v>1338</x:v>
       </x:c>
       <x:c r="D25" s="3" t="s">
-        <x:v>1351</x:v>
+        <x:v>1339</x:v>
       </x:c>
       <x:c r="E25" s="3" t="s">
-        <x:v>1352</x:v>
+        <x:v>1340</x:v>
       </x:c>
       <x:c r="F25" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G25" s="3" t="s">
-        <x:v>1082</x:v>
+        <x:v>1070</x:v>
       </x:c>
       <x:c r="H25" s="3" t="s">
-        <x:v>1083</x:v>
+        <x:v>1071</x:v>
       </x:c>
       <x:c r="I25" s="3" t="s">
-        <x:v>1084</x:v>
+        <x:v>1072</x:v>
       </x:c>
       <x:c r="J25" s="3" t="s">
         <x:v>42</x:v>
@@ -12216,31 +12180,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L25" s="3" t="s">
-        <x:v>1353</x:v>
+        <x:v>1341</x:v>
       </x:c>
       <x:c r="M25" s="3" t="s">
-        <x:v>1306</x:v>
+        <x:v>1294</x:v>
       </x:c>
       <x:c r="N25" s="3" t="s">
-        <x:v>1354</x:v>
+        <x:v>1342</x:v>
       </x:c>
       <x:c r="O25" s="3" t="s">
-        <x:v>1355</x:v>
+        <x:v>1343</x:v>
       </x:c>
       <x:c r="P25" s="3" t="s">
-        <x:v>1356</x:v>
+        <x:v>1344</x:v>
       </x:c>
       <x:c r="Q25" s="3" t="s">
-        <x:v>1357</x:v>
+        <x:v>1345</x:v>
       </x:c>
       <x:c r="R25" s="3" t="s">
-        <x:v>1358</x:v>
+        <x:v>1346</x:v>
       </x:c>
       <x:c r="S25" s="3" t="s">
-        <x:v>1359</x:v>
+        <x:v>1347</x:v>
       </x:c>
       <x:c r="T25" s="3" t="s">
-        <x:v>1360</x:v>
+        <x:v>1348</x:v>
       </x:c>
       <x:c r="U25" s="3" t="s">
         <x:v>2</x:v>
@@ -12248,31 +12212,31 @@
     </x:row>
     <x:row r="26" ht="79.25" hidden="0">
       <x:c r="A26" s="3" t="s">
-        <x:v>1361</x:v>
+        <x:v>1349</x:v>
       </x:c>
       <x:c r="B26" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C26" s="3" t="s">
-        <x:v>1362</x:v>
+        <x:v>1350</x:v>
       </x:c>
       <x:c r="D26" s="3" t="s">
-        <x:v>1363</x:v>
+        <x:v>1351</x:v>
       </x:c>
       <x:c r="E26" s="3" t="s">
-        <x:v>1364</x:v>
+        <x:v>1352</x:v>
       </x:c>
       <x:c r="F26" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G26" s="3" t="s">
-        <x:v>1082</x:v>
+        <x:v>1070</x:v>
       </x:c>
       <x:c r="H26" s="3" t="s">
-        <x:v>1083</x:v>
+        <x:v>1071</x:v>
       </x:c>
       <x:c r="I26" s="3" t="s">
-        <x:v>1084</x:v>
+        <x:v>1072</x:v>
       </x:c>
       <x:c r="J26" s="3" t="s">
         <x:v>42</x:v>
@@ -12281,31 +12245,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L26" s="3" t="s">
-        <x:v>1365</x:v>
+        <x:v>1353</x:v>
       </x:c>
       <x:c r="M26" s="3" t="s">
-        <x:v>1366</x:v>
+        <x:v>1354</x:v>
       </x:c>
       <x:c r="N26" s="3" t="s">
-        <x:v>1367</x:v>
+        <x:v>1355</x:v>
       </x:c>
       <x:c r="O26" s="3" t="s">
-        <x:v>1368</x:v>
+        <x:v>1356</x:v>
       </x:c>
       <x:c r="P26" s="3" t="s">
-        <x:v>1369</x:v>
+        <x:v>1357</x:v>
       </x:c>
       <x:c r="Q26" s="3" t="s">
-        <x:v>1370</x:v>
+        <x:v>1358</x:v>
       </x:c>
       <x:c r="R26" s="3" t="s">
-        <x:v>1371</x:v>
+        <x:v>1359</x:v>
       </x:c>
       <x:c r="S26" s="3" t="s">
-        <x:v>1372</x:v>
+        <x:v>1360</x:v>
       </x:c>
       <x:c r="T26" s="3" t="s">
-        <x:v>1373</x:v>
+        <x:v>1361</x:v>
       </x:c>
       <x:c r="U26" s="3" t="s">
         <x:v>2</x:v>
@@ -12313,31 +12277,31 @@
     </x:row>
     <x:row r="27" ht="79.25" hidden="0">
       <x:c r="A27" s="3" t="s">
-        <x:v>1374</x:v>
+        <x:v>1362</x:v>
       </x:c>
       <x:c r="B27" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C27" s="3" t="s">
-        <x:v>1375</x:v>
+        <x:v>1363</x:v>
       </x:c>
       <x:c r="D27" s="3" t="s">
-        <x:v>1376</x:v>
+        <x:v>1364</x:v>
       </x:c>
       <x:c r="E27" s="3" t="s">
-        <x:v>1377</x:v>
+        <x:v>1365</x:v>
       </x:c>
       <x:c r="F27" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G27" s="3" t="s">
-        <x:v>1082</x:v>
+        <x:v>1070</x:v>
       </x:c>
       <x:c r="H27" s="3" t="s">
-        <x:v>1083</x:v>
+        <x:v>1071</x:v>
       </x:c>
       <x:c r="I27" s="3" t="s">
-        <x:v>1084</x:v>
+        <x:v>1072</x:v>
       </x:c>
       <x:c r="J27" s="3" t="s">
         <x:v>42</x:v>
@@ -12346,31 +12310,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L27" s="3" t="s">
-        <x:v>1378</x:v>
+        <x:v>1366</x:v>
       </x:c>
       <x:c r="M27" s="3" t="s">
-        <x:v>1379</x:v>
+        <x:v>1367</x:v>
       </x:c>
       <x:c r="N27" s="3" t="s">
-        <x:v>1380</x:v>
+        <x:v>1368</x:v>
       </x:c>
       <x:c r="O27" s="3" t="s">
-        <x:v>1381</x:v>
+        <x:v>1369</x:v>
       </x:c>
       <x:c r="P27" s="3" t="s">
-        <x:v>1382</x:v>
+        <x:v>1370</x:v>
       </x:c>
       <x:c r="Q27" s="3" t="s">
-        <x:v>1383</x:v>
+        <x:v>1371</x:v>
       </x:c>
       <x:c r="R27" s="3" t="s">
-        <x:v>1384</x:v>
+        <x:v>1372</x:v>
       </x:c>
       <x:c r="S27" s="3" t="s">
         <x:v>789</x:v>
       </x:c>
       <x:c r="T27" s="3" t="s">
-        <x:v>1385</x:v>
+        <x:v>1373</x:v>
       </x:c>
       <x:c r="U27" s="3" t="s">
         <x:v>2</x:v>
@@ -12378,31 +12342,31 @@
     </x:row>
     <x:row r="28" ht="93.25" hidden="0">
       <x:c r="A28" s="3" t="s">
-        <x:v>1386</x:v>
+        <x:v>1374</x:v>
       </x:c>
       <x:c r="B28" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C28" s="3" t="s">
-        <x:v>1387</x:v>
+        <x:v>1375</x:v>
       </x:c>
       <x:c r="D28" s="3" t="s">
-        <x:v>1388</x:v>
+        <x:v>1376</x:v>
       </x:c>
       <x:c r="E28" s="3" t="s">
-        <x:v>1389</x:v>
+        <x:v>1377</x:v>
       </x:c>
       <x:c r="F28" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G28" s="3" t="s">
-        <x:v>1082</x:v>
+        <x:v>1070</x:v>
       </x:c>
       <x:c r="H28" s="3" t="s">
-        <x:v>1083</x:v>
+        <x:v>1071</x:v>
       </x:c>
       <x:c r="I28" s="3" t="s">
-        <x:v>1084</x:v>
+        <x:v>1072</x:v>
       </x:c>
       <x:c r="J28" s="3" t="s">
         <x:v>42</x:v>
@@ -12411,31 +12375,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L28" s="3" t="s">
-        <x:v>1390</x:v>
+        <x:v>1378</x:v>
       </x:c>
       <x:c r="M28" s="3" t="s">
-        <x:v>1391</x:v>
+        <x:v>1379</x:v>
       </x:c>
       <x:c r="N28" s="3" t="s">
-        <x:v>1392</x:v>
+        <x:v>1380</x:v>
       </x:c>
       <x:c r="O28" s="3" t="s">
-        <x:v>1393</x:v>
+        <x:v>1381</x:v>
       </x:c>
       <x:c r="P28" s="3" t="s">
-        <x:v>1394</x:v>
+        <x:v>1382</x:v>
       </x:c>
       <x:c r="Q28" s="3" t="s">
-        <x:v>1395</x:v>
+        <x:v>1383</x:v>
       </x:c>
       <x:c r="R28" s="3" t="s">
-        <x:v>1396</x:v>
+        <x:v>1384</x:v>
       </x:c>
       <x:c r="S28" s="3" t="s">
         <x:v>286</x:v>
       </x:c>
       <x:c r="T28" s="3" t="s">
-        <x:v>1397</x:v>
+        <x:v>1385</x:v>
       </x:c>
       <x:c r="U28" s="3" t="s">
         <x:v>2</x:v>
@@ -12443,31 +12407,31 @@
     </x:row>
     <x:row r="29" ht="93.25" hidden="0">
       <x:c r="A29" s="3" t="s">
-        <x:v>1398</x:v>
+        <x:v>1386</x:v>
       </x:c>
       <x:c r="B29" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C29" s="3" t="s">
-        <x:v>1399</x:v>
+        <x:v>1387</x:v>
       </x:c>
       <x:c r="D29" s="3" t="s">
-        <x:v>1400</x:v>
+        <x:v>1388</x:v>
       </x:c>
       <x:c r="E29" s="3" t="s">
-        <x:v>1401</x:v>
+        <x:v>1389</x:v>
       </x:c>
       <x:c r="F29" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G29" s="3" t="s">
-        <x:v>1082</x:v>
+        <x:v>1070</x:v>
       </x:c>
       <x:c r="H29" s="3" t="s">
-        <x:v>1083</x:v>
+        <x:v>1071</x:v>
       </x:c>
       <x:c r="I29" s="3" t="s">
-        <x:v>1084</x:v>
+        <x:v>1072</x:v>
       </x:c>
       <x:c r="J29" s="3" t="s">
         <x:v>42</x:v>
@@ -12476,31 +12440,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="L29" s="3" t="s">
-        <x:v>1402</x:v>
+        <x:v>1390</x:v>
       </x:c>
       <x:c r="M29" s="3" t="s">
-        <x:v>1403</x:v>
+        <x:v>1391</x:v>
       </x:c>
       <x:c r="N29" s="3" t="s">
-        <x:v>1404</x:v>
+        <x:v>1392</x:v>
       </x:c>
       <x:c r="O29" s="3" t="s">
-        <x:v>1405</x:v>
+        <x:v>1393</x:v>
       </x:c>
       <x:c r="P29" s="3" t="s">
-        <x:v>1406</x:v>
+        <x:v>1394</x:v>
       </x:c>
       <x:c r="Q29" s="3" t="s">
-        <x:v>1407</x:v>
+        <x:v>1395</x:v>
       </x:c>
       <x:c r="R29" s="3" t="s">
-        <x:v>1408</x:v>
+        <x:v>1396</x:v>
       </x:c>
       <x:c r="S29" s="3" t="s">
-        <x:v>1409</x:v>
+        <x:v>1397</x:v>
       </x:c>
       <x:c r="T29" s="3" t="s">
-        <x:v>1410</x:v>
+        <x:v>1398</x:v>
       </x:c>
       <x:c r="U29" s="3" t="s">
         <x:v>2</x:v>
@@ -12508,31 +12472,31 @@
     </x:row>
     <x:row r="30" ht="93.25" hidden="0">
       <x:c r="A30" s="3" t="s">
-        <x:v>1411</x:v>
+        <x:v>1399</x:v>
       </x:c>
       <x:c r="B30" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C30" s="3" t="s">
-        <x:v>1412</x:v>
+        <x:v>1400</x:v>
       </x:c>
       <x:c r="D30" s="3" t="s">
-        <x:v>1413</x:v>
+        <x:v>1401</x:v>
       </x:c>
       <x:c r="E30" s="3" t="s">
-        <x:v>1414</x:v>
+        <x:v>1402</x:v>
       </x:c>
       <x:c r="F30" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G30" s="3" t="s">
-        <x:v>1082</x:v>
+        <x:v>1070</x:v>
       </x:c>
       <x:c r="H30" s="3" t="s">
-        <x:v>1083</x:v>
+        <x:v>1071</x:v>
       </x:c>
       <x:c r="I30" s="3" t="s">
-        <x:v>1084</x:v>
+        <x:v>1072</x:v>
       </x:c>
       <x:c r="J30" s="3" t="s">
         <x:v>42</x:v>
@@ -12541,31 +12505,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L30" s="3" t="s">
-        <x:v>1415</x:v>
+        <x:v>1403</x:v>
       </x:c>
       <x:c r="M30" s="3" t="s">
-        <x:v>1416</x:v>
+        <x:v>1404</x:v>
       </x:c>
       <x:c r="N30" s="3" t="s">
-        <x:v>1417</x:v>
+        <x:v>1405</x:v>
       </x:c>
       <x:c r="O30" s="3" t="s">
-        <x:v>1418</x:v>
+        <x:v>1406</x:v>
       </x:c>
       <x:c r="P30" s="3" t="s">
-        <x:v>1419</x:v>
+        <x:v>1407</x:v>
       </x:c>
       <x:c r="Q30" s="3" t="s">
-        <x:v>1420</x:v>
+        <x:v>1408</x:v>
       </x:c>
       <x:c r="R30" s="3" t="s">
-        <x:v>1421</x:v>
+        <x:v>1409</x:v>
       </x:c>
       <x:c r="S30" s="3" t="s">
-        <x:v>1422</x:v>
+        <x:v>1410</x:v>
       </x:c>
       <x:c r="T30" s="3" t="s">
-        <x:v>1423</x:v>
+        <x:v>1411</x:v>
       </x:c>
       <x:c r="U30" s="3" t="s">
         <x:v>2</x:v>
@@ -12573,7 +12537,7 @@
     </x:row>
     <x:row r="31" ht="93.25" hidden="0">
       <x:c r="A31" s="3" t="s">
-        <x:v>1424</x:v>
+        <x:v>1412</x:v>
       </x:c>
       <x:c r="B31" s="3" t="s">
         <x:v>9</x:v>
@@ -12582,22 +12546,22 @@
         <x:v>947</x:v>
       </x:c>
       <x:c r="D31" s="3" t="s">
-        <x:v>1425</x:v>
+        <x:v>1413</x:v>
       </x:c>
       <x:c r="E31" s="3" t="s">
-        <x:v>1426</x:v>
+        <x:v>1414</x:v>
       </x:c>
       <x:c r="F31" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G31" s="3" t="s">
-        <x:v>1082</x:v>
+        <x:v>1070</x:v>
       </x:c>
       <x:c r="H31" s="3" t="s">
-        <x:v>1083</x:v>
+        <x:v>1071</x:v>
       </x:c>
       <x:c r="I31" s="3" t="s">
-        <x:v>1084</x:v>
+        <x:v>1072</x:v>
       </x:c>
       <x:c r="J31" s="3" t="s">
         <x:v>42</x:v>
@@ -12606,31 +12570,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="L31" s="3" t="s">
-        <x:v>1427</x:v>
+        <x:v>1415</x:v>
       </x:c>
       <x:c r="M31" s="3" t="s">
-        <x:v>1428</x:v>
+        <x:v>1416</x:v>
       </x:c>
       <x:c r="N31" s="3" t="s">
-        <x:v>1429</x:v>
+        <x:v>1417</x:v>
       </x:c>
       <x:c r="O31" s="3" t="s">
-        <x:v>1430</x:v>
+        <x:v>1418</x:v>
       </x:c>
       <x:c r="P31" s="3" t="s">
-        <x:v>1431</x:v>
+        <x:v>1419</x:v>
       </x:c>
       <x:c r="Q31" s="3" t="s">
-        <x:v>1432</x:v>
+        <x:v>1420</x:v>
       </x:c>
       <x:c r="R31" s="3" t="s">
-        <x:v>1433</x:v>
+        <x:v>1421</x:v>
       </x:c>
       <x:c r="S31" s="3" t="s">
-        <x:v>1434</x:v>
+        <x:v>1422</x:v>
       </x:c>
       <x:c r="T31" s="3" t="s">
-        <x:v>1435</x:v>
+        <x:v>1423</x:v>
       </x:c>
       <x:c r="U31" s="3" t="s">
         <x:v>2</x:v>
@@ -12638,31 +12602,31 @@
     </x:row>
     <x:row r="32" ht="93.25" hidden="0">
       <x:c r="A32" s="3" t="s">
-        <x:v>1436</x:v>
+        <x:v>1424</x:v>
       </x:c>
       <x:c r="B32" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C32" s="3" t="s">
-        <x:v>1437</x:v>
+        <x:v>1425</x:v>
       </x:c>
       <x:c r="D32" s="3" t="s">
-        <x:v>1438</x:v>
+        <x:v>1426</x:v>
       </x:c>
       <x:c r="E32" s="3" t="s">
-        <x:v>1439</x:v>
+        <x:v>1427</x:v>
       </x:c>
       <x:c r="F32" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G32" s="3" t="s">
-        <x:v>1082</x:v>
+        <x:v>1070</x:v>
       </x:c>
       <x:c r="H32" s="3" t="s">
-        <x:v>1083</x:v>
+        <x:v>1071</x:v>
       </x:c>
       <x:c r="I32" s="3" t="s">
-        <x:v>1084</x:v>
+        <x:v>1072</x:v>
       </x:c>
       <x:c r="J32" s="3" t="s">
         <x:v>42</x:v>
@@ -12671,31 +12635,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L32" s="3" t="s">
-        <x:v>1440</x:v>
+        <x:v>1428</x:v>
       </x:c>
       <x:c r="M32" s="3" t="s">
-        <x:v>1441</x:v>
+        <x:v>1429</x:v>
       </x:c>
       <x:c r="N32" s="3" t="s">
-        <x:v>1442</x:v>
+        <x:v>1430</x:v>
       </x:c>
       <x:c r="O32" s="3" t="s">
-        <x:v>1443</x:v>
+        <x:v>1431</x:v>
       </x:c>
       <x:c r="P32" s="3" t="s">
-        <x:v>1444</x:v>
+        <x:v>1432</x:v>
       </x:c>
       <x:c r="Q32" s="3" t="s">
-        <x:v>1445</x:v>
+        <x:v>1433</x:v>
       </x:c>
       <x:c r="R32" s="3" t="s">
         <x:v>969</x:v>
       </x:c>
       <x:c r="S32" s="3" t="s">
-        <x:v>1446</x:v>
+        <x:v>1434</x:v>
       </x:c>
       <x:c r="T32" s="3" t="s">
-        <x:v>1447</x:v>
+        <x:v>1435</x:v>
       </x:c>
       <x:c r="U32" s="3" t="s">
         <x:v>2</x:v>
@@ -12703,7 +12667,7 @@
     </x:row>
     <x:row r="33" ht="93.25" hidden="0">
       <x:c r="A33" s="3" t="s">
-        <x:v>1448</x:v>
+        <x:v>1436</x:v>
       </x:c>
       <x:c r="B33" s="3" t="s">
         <x:v>9</x:v>
@@ -12712,22 +12676,22 @@
         <x:v>740</x:v>
       </x:c>
       <x:c r="D33" s="3" t="s">
-        <x:v>1449</x:v>
+        <x:v>1437</x:v>
       </x:c>
       <x:c r="E33" s="3" t="s">
-        <x:v>1450</x:v>
+        <x:v>1438</x:v>
       </x:c>
       <x:c r="F33" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G33" s="3" t="s">
-        <x:v>1082</x:v>
+        <x:v>1070</x:v>
       </x:c>
       <x:c r="H33" s="3" t="s">
-        <x:v>1083</x:v>
+        <x:v>1071</x:v>
       </x:c>
       <x:c r="I33" s="3" t="s">
-        <x:v>1084</x:v>
+        <x:v>1072</x:v>
       </x:c>
       <x:c r="J33" s="3" t="s">
         <x:v>42</x:v>
@@ -12736,31 +12700,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L33" s="3" t="s">
-        <x:v>1451</x:v>
+        <x:v>1439</x:v>
       </x:c>
       <x:c r="M33" s="3" t="s">
-        <x:v>1452</x:v>
+        <x:v>1440</x:v>
       </x:c>
       <x:c r="N33" s="3" t="s">
-        <x:v>1453</x:v>
+        <x:v>1441</x:v>
       </x:c>
       <x:c r="O33" s="3" t="s">
-        <x:v>1454</x:v>
+        <x:v>1442</x:v>
       </x:c>
       <x:c r="P33" s="3" t="s">
-        <x:v>1455</x:v>
+        <x:v>1443</x:v>
       </x:c>
       <x:c r="Q33" s="3" t="s">
-        <x:v>1456</x:v>
+        <x:v>1444</x:v>
       </x:c>
       <x:c r="R33" s="3" t="s">
-        <x:v>1457</x:v>
+        <x:v>1445</x:v>
       </x:c>
       <x:c r="S33" s="3" t="s">
-        <x:v>1458</x:v>
+        <x:v>1446</x:v>
       </x:c>
       <x:c r="T33" s="3" t="s">
-        <x:v>1459</x:v>
+        <x:v>1447</x:v>
       </x:c>
       <x:c r="U33" s="3" t="s">
         <x:v>2</x:v>
@@ -12768,7 +12732,7 @@
     </x:row>
     <x:row r="34" ht="93.25" hidden="0">
       <x:c r="A34" s="3" t="s">
-        <x:v>1460</x:v>
+        <x:v>1448</x:v>
       </x:c>
       <x:c r="B34" s="3" t="s">
         <x:v>9</x:v>
@@ -12777,22 +12741,22 @@
         <x:v>313</x:v>
       </x:c>
       <x:c r="D34" s="3" t="s">
-        <x:v>1461</x:v>
+        <x:v>1449</x:v>
       </x:c>
       <x:c r="E34" s="3" t="s">
-        <x:v>1462</x:v>
+        <x:v>1450</x:v>
       </x:c>
       <x:c r="F34" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G34" s="3" t="s">
-        <x:v>1082</x:v>
+        <x:v>1070</x:v>
       </x:c>
       <x:c r="H34" s="3" t="s">
-        <x:v>1083</x:v>
+        <x:v>1071</x:v>
       </x:c>
       <x:c r="I34" s="3" t="s">
-        <x:v>1084</x:v>
+        <x:v>1072</x:v>
       </x:c>
       <x:c r="J34" s="3" t="s">
         <x:v>42</x:v>
@@ -12801,31 +12765,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="L34" s="3" t="s">
-        <x:v>1463</x:v>
+        <x:v>1451</x:v>
       </x:c>
       <x:c r="M34" s="3" t="s">
-        <x:v>1464</x:v>
+        <x:v>1452</x:v>
       </x:c>
       <x:c r="N34" s="3" t="s">
         <x:v>978</x:v>
       </x:c>
       <x:c r="O34" s="3" t="s">
-        <x:v>1465</x:v>
+        <x:v>1453</x:v>
       </x:c>
       <x:c r="P34" s="3" t="s">
-        <x:v>1466</x:v>
+        <x:v>1454</x:v>
       </x:c>
       <x:c r="Q34" s="3" t="s">
-        <x:v>1467</x:v>
+        <x:v>1455</x:v>
       </x:c>
       <x:c r="R34" s="3" t="s">
-        <x:v>1468</x:v>
+        <x:v>1456</x:v>
       </x:c>
       <x:c r="S34" s="3" t="s">
         <x:v>323</x:v>
       </x:c>
       <x:c r="T34" s="3" t="s">
-        <x:v>1469</x:v>
+        <x:v>1457</x:v>
       </x:c>
       <x:c r="U34" s="3" t="s">
         <x:v>2</x:v>
@@ -12833,31 +12797,31 @@
     </x:row>
     <x:row r="35" ht="93.25" hidden="0">
       <x:c r="A35" s="3" t="s">
-        <x:v>1470</x:v>
+        <x:v>1458</x:v>
       </x:c>
       <x:c r="B35" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C35" s="3" t="s">
-        <x:v>1471</x:v>
+        <x:v>1459</x:v>
       </x:c>
       <x:c r="D35" s="3" t="s">
-        <x:v>1472</x:v>
+        <x:v>1460</x:v>
       </x:c>
       <x:c r="E35" s="3" t="s">
-        <x:v>1473</x:v>
+        <x:v>1461</x:v>
       </x:c>
       <x:c r="F35" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G35" s="3" t="s">
-        <x:v>1082</x:v>
+        <x:v>1070</x:v>
       </x:c>
       <x:c r="H35" s="3" t="s">
-        <x:v>1083</x:v>
+        <x:v>1071</x:v>
       </x:c>
       <x:c r="I35" s="3" t="s">
-        <x:v>1084</x:v>
+        <x:v>1072</x:v>
       </x:c>
       <x:c r="J35" s="3" t="s">
         <x:v>42</x:v>
@@ -12866,31 +12830,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L35" s="3" t="s">
-        <x:v>1474</x:v>
+        <x:v>1462</x:v>
       </x:c>
       <x:c r="M35" s="3" t="s">
-        <x:v>1475</x:v>
+        <x:v>1463</x:v>
       </x:c>
       <x:c r="N35" s="3" t="s">
-        <x:v>1476</x:v>
+        <x:v>1464</x:v>
       </x:c>
       <x:c r="O35" s="3" t="s">
-        <x:v>1256</x:v>
+        <x:v>1244</x:v>
       </x:c>
       <x:c r="P35" s="3" t="s">
-        <x:v>1477</x:v>
+        <x:v>1465</x:v>
       </x:c>
       <x:c r="Q35" s="3" t="s">
-        <x:v>1478</x:v>
+        <x:v>1466</x:v>
       </x:c>
       <x:c r="R35" s="3" t="s">
-        <x:v>1479</x:v>
+        <x:v>1467</x:v>
       </x:c>
       <x:c r="S35" s="3" t="s">
-        <x:v>1480</x:v>
+        <x:v>1468</x:v>
       </x:c>
       <x:c r="T35" s="3" t="s">
-        <x:v>1481</x:v>
+        <x:v>1469</x:v>
       </x:c>
       <x:c r="U35" s="3" t="s">
         <x:v>2</x:v>
@@ -12898,31 +12862,31 @@
     </x:row>
     <x:row r="36" ht="93.25" hidden="0">
       <x:c r="A36" s="3" t="s">
-        <x:v>1482</x:v>
+        <x:v>1470</x:v>
       </x:c>
       <x:c r="B36" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C36" s="3" t="s">
-        <x:v>1483</x:v>
+        <x:v>1471</x:v>
       </x:c>
       <x:c r="D36" s="3" t="s">
-        <x:v>1484</x:v>
+        <x:v>1472</x:v>
       </x:c>
       <x:c r="E36" s="3" t="s">
-        <x:v>1485</x:v>
+        <x:v>1473</x:v>
       </x:c>
       <x:c r="F36" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G36" s="3" t="s">
-        <x:v>1082</x:v>
+        <x:v>1070</x:v>
       </x:c>
       <x:c r="H36" s="3" t="s">
-        <x:v>1083</x:v>
+        <x:v>1071</x:v>
       </x:c>
       <x:c r="I36" s="3" t="s">
-        <x:v>1084</x:v>
+        <x:v>1072</x:v>
       </x:c>
       <x:c r="J36" s="3" t="s">
         <x:v>42</x:v>
@@ -12931,31 +12895,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L36" s="3" t="s">
-        <x:v>1486</x:v>
+        <x:v>1474</x:v>
       </x:c>
       <x:c r="M36" s="3" t="s">
-        <x:v>1086</x:v>
+        <x:v>1074</x:v>
       </x:c>
       <x:c r="N36" s="3" t="s">
-        <x:v>1487</x:v>
+        <x:v>1475</x:v>
       </x:c>
       <x:c r="O36" s="3" t="s">
-        <x:v>1488</x:v>
+        <x:v>1476</x:v>
       </x:c>
       <x:c r="P36" s="3" t="s">
-        <x:v>1489</x:v>
+        <x:v>1477</x:v>
       </x:c>
       <x:c r="Q36" s="3" t="s">
-        <x:v>1490</x:v>
+        <x:v>1478</x:v>
       </x:c>
       <x:c r="R36" s="3" t="s">
-        <x:v>1491</x:v>
+        <x:v>1479</x:v>
       </x:c>
       <x:c r="S36" s="3" t="s">
-        <x:v>1492</x:v>
+        <x:v>1480</x:v>
       </x:c>
       <x:c r="T36" s="3" t="s">
-        <x:v>1493</x:v>
+        <x:v>1481</x:v>
       </x:c>
       <x:c r="U36" s="3" t="s">
         <x:v>2</x:v>
@@ -12963,31 +12927,31 @@
     </x:row>
     <x:row r="37" ht="93.25" hidden="0">
       <x:c r="A37" s="3" t="s">
-        <x:v>1494</x:v>
+        <x:v>1482</x:v>
       </x:c>
       <x:c r="B37" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C37" s="3" t="s">
-        <x:v>1495</x:v>
+        <x:v>1483</x:v>
       </x:c>
       <x:c r="D37" s="3" t="s">
-        <x:v>1496</x:v>
+        <x:v>1484</x:v>
       </x:c>
       <x:c r="E37" s="3" t="s">
-        <x:v>1497</x:v>
+        <x:v>1485</x:v>
       </x:c>
       <x:c r="F37" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G37" s="3" t="s">
-        <x:v>1082</x:v>
+        <x:v>1070</x:v>
       </x:c>
       <x:c r="H37" s="3" t="s">
-        <x:v>1083</x:v>
+        <x:v>1071</x:v>
       </x:c>
       <x:c r="I37" s="3" t="s">
-        <x:v>1084</x:v>
+        <x:v>1072</x:v>
       </x:c>
       <x:c r="J37" s="3" t="s">
         <x:v>42</x:v>
@@ -12996,31 +12960,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L37" s="3" t="s">
-        <x:v>1498</x:v>
+        <x:v>1486</x:v>
       </x:c>
       <x:c r="M37" s="3" t="s">
-        <x:v>1499</x:v>
+        <x:v>1487</x:v>
       </x:c>
       <x:c r="N37" s="3" t="s">
-        <x:v>1500</x:v>
+        <x:v>1488</x:v>
       </x:c>
       <x:c r="O37" s="3" t="s">
-        <x:v>1501</x:v>
+        <x:v>1489</x:v>
       </x:c>
       <x:c r="P37" s="3" t="s">
-        <x:v>1502</x:v>
+        <x:v>1490</x:v>
       </x:c>
       <x:c r="Q37" s="3" t="s">
-        <x:v>1503</x:v>
+        <x:v>1491</x:v>
       </x:c>
       <x:c r="R37" s="3" t="s">
-        <x:v>1504</x:v>
+        <x:v>1492</x:v>
       </x:c>
       <x:c r="S37" s="3" t="s">
-        <x:v>1505</x:v>
+        <x:v>1493</x:v>
       </x:c>
       <x:c r="T37" s="3" t="s">
-        <x:v>1499</x:v>
+        <x:v>1487</x:v>
       </x:c>
       <x:c r="U37" s="3" t="s">
         <x:v>2</x:v>
@@ -13028,31 +12992,31 @@
     </x:row>
     <x:row r="38" ht="93.25" hidden="0">
       <x:c r="A38" s="3" t="s">
-        <x:v>1506</x:v>
+        <x:v>1494</x:v>
       </x:c>
       <x:c r="B38" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C38" s="3" t="s">
-        <x:v>1507</x:v>
+        <x:v>1495</x:v>
       </x:c>
       <x:c r="D38" s="3" t="s">
-        <x:v>1508</x:v>
+        <x:v>1496</x:v>
       </x:c>
       <x:c r="E38" s="3" t="s">
-        <x:v>1509</x:v>
+        <x:v>1497</x:v>
       </x:c>
       <x:c r="F38" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G38" s="3" t="s">
-        <x:v>1082</x:v>
+        <x:v>1070</x:v>
       </x:c>
       <x:c r="H38" s="3" t="s">
-        <x:v>1083</x:v>
+        <x:v>1071</x:v>
       </x:c>
       <x:c r="I38" s="3" t="s">
-        <x:v>1084</x:v>
+        <x:v>1072</x:v>
       </x:c>
       <x:c r="J38" s="3" t="s">
         <x:v>42</x:v>
@@ -13061,31 +13025,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L38" s="3" t="s">
-        <x:v>1510</x:v>
+        <x:v>1498</x:v>
       </x:c>
       <x:c r="M38" s="3" t="s">
-        <x:v>1181</x:v>
+        <x:v>1169</x:v>
       </x:c>
       <x:c r="N38" s="3" t="s">
-        <x:v>1511</x:v>
+        <x:v>1499</x:v>
       </x:c>
       <x:c r="O38" s="3" t="s">
-        <x:v>1512</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="P38" s="3" t="s">
-        <x:v>1513</x:v>
+        <x:v>1501</x:v>
       </x:c>
       <x:c r="Q38" s="3" t="s">
-        <x:v>1514</x:v>
+        <x:v>1502</x:v>
       </x:c>
       <x:c r="R38" s="3" t="s">
-        <x:v>1515</x:v>
+        <x:v>1503</x:v>
       </x:c>
       <x:c r="S38" s="3" t="s">
-        <x:v>1516</x:v>
+        <x:v>1504</x:v>
       </x:c>
       <x:c r="T38" s="3" t="s">
-        <x:v>1517</x:v>
+        <x:v>1505</x:v>
       </x:c>
       <x:c r="U38" s="3" t="s">
         <x:v>2</x:v>
@@ -13093,31 +13057,31 @@
     </x:row>
     <x:row r="39" ht="93.25" hidden="0">
       <x:c r="A39" s="3" t="s">
-        <x:v>1518</x:v>
+        <x:v>1506</x:v>
       </x:c>
       <x:c r="B39" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C39" s="3" t="s">
-        <x:v>1519</x:v>
+        <x:v>1507</x:v>
       </x:c>
       <x:c r="D39" s="3" t="s">
-        <x:v>1520</x:v>
+        <x:v>1508</x:v>
       </x:c>
       <x:c r="E39" s="3" t="s">
-        <x:v>1521</x:v>
+        <x:v>1509</x:v>
       </x:c>
       <x:c r="F39" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G39" s="3" t="s">
-        <x:v>1082</x:v>
+        <x:v>1070</x:v>
       </x:c>
       <x:c r="H39" s="3" t="s">
-        <x:v>1083</x:v>
+        <x:v>1071</x:v>
       </x:c>
       <x:c r="I39" s="3" t="s">
-        <x:v>1084</x:v>
+        <x:v>1072</x:v>
       </x:c>
       <x:c r="J39" s="3" t="s">
         <x:v>42</x:v>
@@ -13126,31 +13090,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="L39" s="3" t="s">
-        <x:v>1522</x:v>
+        <x:v>1510</x:v>
       </x:c>
       <x:c r="M39" s="3" t="s">
-        <x:v>1086</x:v>
+        <x:v>1074</x:v>
       </x:c>
       <x:c r="N39" s="3" t="s">
-        <x:v>1523</x:v>
+        <x:v>1511</x:v>
       </x:c>
       <x:c r="O39" s="3" t="s">
-        <x:v>1524</x:v>
+        <x:v>1512</x:v>
       </x:c>
       <x:c r="P39" s="3" t="s">
-        <x:v>1525</x:v>
+        <x:v>1513</x:v>
       </x:c>
       <x:c r="Q39" s="3" t="s">
-        <x:v>1526</x:v>
+        <x:v>1514</x:v>
       </x:c>
       <x:c r="R39" s="3" t="s">
-        <x:v>1527</x:v>
+        <x:v>1515</x:v>
       </x:c>
       <x:c r="S39" s="3" t="s">
-        <x:v>1528</x:v>
+        <x:v>1516</x:v>
       </x:c>
       <x:c r="T39" s="3" t="s">
-        <x:v>1529</x:v>
+        <x:v>1517</x:v>
       </x:c>
       <x:c r="U39" s="3" t="s">
         <x:v>2</x:v>
@@ -13159,7 +13123,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re0c04c5ebaf74cc9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6c04358f949c462e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/maliev-feature-user-story-status.xlsx
+++ b/docs/maliev-feature-user-story-status.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Ra86334ab48034524"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="Re159ddff5dfa44a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R2fbb87b2f76d4769"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="Rf25d7749c86c4d4f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rdeef7a0febab4fcc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="R4740b7357b48447b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R03205b3fc3d64680"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="R46d2b9c8eaf44d8c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3091,70 +3091,37 @@
     <x:t xml:space="preserve">PaymentsController.cs:16-85; InvoiceList.razor:587-589; InvoiceDetail.razor:62-294</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">INT-048</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Employee onboarding</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">As an HR employee, I can review onboarding summaries, open an employee checklist, and update onboarding task progress.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Onboarding BFF exposes paged onboarding summaries, employee checklist detail, and task progress patch operations.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">HR onboarding UI/BFF -&gt; LifecycleService onboarding DTOs</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">OnboardingController.cs</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">/hr/onboarding navigation context; onboarding checklist/task surfaces</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">OnboardingController GET, GET {employeeId}/checklist, PATCH {employeeId}/tasks</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Intranet BFF, LifecycleService</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Onboarding task progress</x:t>
+    <x:t xml:space="preserve">INT-049</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Performance reviews and goals</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">As an HR employee, I can review performance reviews and goals.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Performance BFF exposes reviews and goals through permission-gated endpoints backed by PerformanceService.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">HR performance UI/BFF -&gt; PerformanceService reviews/goals DTOs</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">PerformanceController.cs</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">/hr/performance navigation context; reviews/goals surfaces</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">PerformanceController GET reviews, goals</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Intranet BFF, PerformanceService</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Read-only performance review and goal data</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Needs current page/navigation exposure review.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">OnboardingController.cs:15-45; ChatDrawer.razor:406</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">INT-049</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Performance reviews and goals</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">As an HR employee, I can review performance reviews and goals.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Performance BFF exposes reviews and goals through permission-gated endpoints backed by PerformanceService.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">HR performance UI/BFF -&gt; PerformanceService reviews/goals DTOs</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">PerformanceController.cs</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">/hr/performance navigation context; reviews/goals surfaces</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">PerformanceController GET reviews, goals</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Intranet BFF, PerformanceService</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Read-only performance review and goal data</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">PerformanceController.cs:17-36; ChatDrawer.razor:409</x:t>
@@ -7136,7 +7103,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb438ffdb80624151"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc745fbd22bbf4457"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10290,85 +10257,85 @@
       </x:c>
     </x:row>
     <x:row r="49" ht="51.29999923706055" hidden="0">
-      <x:c r="A49" s="3" t="s">
-        <x:v>1026</x:v>
-      </x:c>
-      <x:c r="B49" s="3" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C49" s="3" t="s">
-        <x:v>1027</x:v>
-      </x:c>
-      <x:c r="D49" s="3" t="s">
-        <x:v>1028</x:v>
-      </x:c>
-      <x:c r="E49" s="3" t="s">
-        <x:v>1029</x:v>
-      </x:c>
-      <x:c r="F49" s="3" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="G49" s="3" t="s">
-        <x:v>1001</x:v>
-      </x:c>
-      <x:c r="H49" s="3" t="s">
-        <x:v>1002</x:v>
-      </x:c>
-      <x:c r="I49" s="3" t="s">
-        <x:v>1003</x:v>
-      </x:c>
-      <x:c r="J49" s="3" t="s">
-        <x:v>1004</x:v>
-      </x:c>
-      <x:c r="K49" s="3" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="L49" s="3" t="s">
-        <x:v>1030</x:v>
-      </x:c>
-      <x:c r="M49" s="3" t="s">
-        <x:v>1031</x:v>
-      </x:c>
-      <x:c r="N49" s="3" t="s">
-        <x:v>1032</x:v>
-      </x:c>
-      <x:c r="O49" s="3" t="s">
-        <x:v>1033</x:v>
-      </x:c>
-      <x:c r="P49" s="3" t="s">
-        <x:v>1009</x:v>
-      </x:c>
-      <x:c r="Q49" s="3" t="s">
-        <x:v>1034</x:v>
-      </x:c>
-      <x:c r="R49" s="3" t="s">
-        <x:v>1035</x:v>
-      </x:c>
-      <x:c r="S49" s="3" t="s">
-        <x:v>1036</x:v>
-      </x:c>
-      <x:c r="T49" s="3" t="s">
-        <x:v>1037</x:v>
-      </x:c>
-      <x:c r="U49" s="3" t="s">
-        <x:v>2</x:v>
+      <x:c r="A49" s="3" t="str">
+        <x:v>INT-048</x:v>
+      </x:c>
+      <x:c r="B49" s="3" t="str">
+        <x:v>Maliev.Intranet</x:v>
+      </x:c>
+      <x:c r="C49" s="3" t="str">
+        <x:v>Employee onboarding</x:v>
+      </x:c>
+      <x:c r="D49" s="3" t="str">
+        <x:v>As an HR employee, I can review onboarding summaries, open an employee checklist, and update onboarding task progress.</x:v>
+      </x:c>
+      <x:c r="E49" s="3" t="str">
+        <x:v>Onboarding BFF exposes paged onboarding summaries, employee checklist detail, and task progress patch operations.</x:v>
+      </x:c>
+      <x:c r="F49" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G49" s="3" t="str">
+        <x:v>Focused behavior tests passed 2026-06-23.</x:v>
+      </x:c>
+      <x:c r="H49" s="3" t="str">
+        <x:v>No behavior error observed in current focused controller/client/navigation retest.</x:v>
+      </x:c>
+      <x:c r="I49" s="3" t="str">
+        <x:v>No app-code fix needed; added missing focused coverage in Maliev.Intranet commit e6e994e.</x:v>
+      </x:c>
+      <x:c r="J49" s="3" t="str">
+        <x:v>Retested OnboardingControllerTests 11/11 passed.</x:v>
+      </x:c>
+      <x:c r="K49" s="3" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="L49" s="3" t="str">
+        <x:v>HR onboarding UI/BFF -&gt; LifecycleService onboarding DTOs</x:v>
+      </x:c>
+      <x:c r="M49" s="3" t="str">
+        <x:v>OnboardingController.cs</x:v>
+      </x:c>
+      <x:c r="N49" s="3" t="str">
+        <x:v>/hr/onboarding navigation context; onboarding checklist/task surfaces</x:v>
+      </x:c>
+      <x:c r="O49" s="3" t="str">
+        <x:v>OnboardingController GET, GET {employeeId}/checklist, PATCH {employeeId}/tasks</x:v>
+      </x:c>
+      <x:c r="P49" s="3" t="str">
+        <x:v>Focused test: dotnet test Maliev.Intranet.slnx --filter "FullyQualifiedName~OnboardingControllerTests" --verbosity minimal passed 11/11 on 2026-06-23. Coverage verifies onboarding list fallback, checklist missing-state, task update outcomes, read/write permission requirements, LifecycleService pending-list endpoint and progress mapping, checklist task mapping, completion endpoint behavior, and ChatDrawer /hr/onboarding label exposure.</x:v>
+      </x:c>
+      <x:c r="Q49" s="3" t="str">
+        <x:v>Intranet BFF, LifecycleService</x:v>
+      </x:c>
+      <x:c r="R49" s="3" t="str">
+        <x:v>Onboarding task progress</x:v>
+      </x:c>
+      <x:c r="S49" s="3" t="str">
+        <x:v>No remaining INT-048 API/client contract gap from this focused retest. Current code search found API/chat navigation exposure, not a dedicated onboarding Razor page route; full authenticated UI route review remains for later browser/Aspire pass.</x:v>
+      </x:c>
+      <x:c r="T49" s="3" t="str">
+        <x:v>OnboardingController.cs:15-45; LifecycleServiceClient.cs:8-129; OnboardingControllerTests.cs:1-233; ChatDrawer.razor:406</x:v>
+      </x:c>
+      <x:c r="U49" s="3" t="str">
+        <x:v>2026-06-23</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="51.29999923706055" hidden="0">
       <x:c r="A50" s="3" t="s">
-        <x:v>1038</x:v>
+        <x:v>1026</x:v>
       </x:c>
       <x:c r="B50" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C50" s="3" t="s">
-        <x:v>1039</x:v>
+        <x:v>1027</x:v>
       </x:c>
       <x:c r="D50" s="3" t="s">
-        <x:v>1040</x:v>
+        <x:v>1028</x:v>
       </x:c>
       <x:c r="E50" s="3" t="s">
-        <x:v>1041</x:v>
+        <x:v>1029</x:v>
       </x:c>
       <x:c r="F50" s="3" t="s">
         <x:v>38</x:v>
@@ -10389,31 +10356,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L50" s="3" t="s">
-        <x:v>1042</x:v>
+        <x:v>1030</x:v>
       </x:c>
       <x:c r="M50" s="3" t="s">
-        <x:v>1043</x:v>
+        <x:v>1031</x:v>
       </x:c>
       <x:c r="N50" s="3" t="s">
-        <x:v>1044</x:v>
+        <x:v>1032</x:v>
       </x:c>
       <x:c r="O50" s="3" t="s">
-        <x:v>1045</x:v>
+        <x:v>1033</x:v>
       </x:c>
       <x:c r="P50" s="3" t="s">
         <x:v>1009</x:v>
       </x:c>
       <x:c r="Q50" s="3" t="s">
-        <x:v>1046</x:v>
+        <x:v>1034</x:v>
       </x:c>
       <x:c r="R50" s="3" t="s">
-        <x:v>1047</x:v>
+        <x:v>1035</x:v>
       </x:c>
       <x:c r="S50" s="3" t="s">
         <x:v>1036</x:v>
       </x:c>
       <x:c r="T50" s="3" t="s">
-        <x:v>1048</x:v>
+        <x:v>1037</x:v>
       </x:c>
       <x:c r="U50" s="3" t="s">
         <x:v>2</x:v>
@@ -10552,7 +10519,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R292f9d36064a4636"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb0be5823c6d34b85"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10652,64 +10619,64 @@
     </x:row>
     <x:row r="2" ht="149.25" hidden="0">
       <x:c r="A2" s="3" t="s">
-        <x:v>1049</x:v>
+        <x:v>1038</x:v>
       </x:c>
       <x:c r="B2" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C2" s="3" t="s">
-        <x:v>1050</x:v>
+        <x:v>1039</x:v>
       </x:c>
       <x:c r="D2" s="3" t="s">
-        <x:v>1051</x:v>
+        <x:v>1040</x:v>
       </x:c>
       <x:c r="E2" s="3" t="s">
-        <x:v>1052</x:v>
+        <x:v>1041</x:v>
       </x:c>
       <x:c r="F2" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G2" s="3" t="s">
-        <x:v>1053</x:v>
+        <x:v>1042</x:v>
       </x:c>
       <x:c r="H2" s="3" t="s">
-        <x:v>1054</x:v>
+        <x:v>1043</x:v>
       </x:c>
       <x:c r="I2" s="3" t="s">
-        <x:v>1055</x:v>
+        <x:v>1044</x:v>
       </x:c>
       <x:c r="J2" s="3" t="s">
-        <x:v>1056</x:v>
+        <x:v>1045</x:v>
       </x:c>
       <x:c r="K2" s="3" t="s">
         <x:v>188</x:v>
       </x:c>
       <x:c r="L2" s="3" t="s">
-        <x:v>1057</x:v>
+        <x:v>1046</x:v>
       </x:c>
       <x:c r="M2" s="3" t="s">
-        <x:v>1058</x:v>
+        <x:v>1047</x:v>
       </x:c>
       <x:c r="N2" s="3" t="s">
-        <x:v>1059</x:v>
+        <x:v>1048</x:v>
       </x:c>
       <x:c r="O2" s="3" t="s">
-        <x:v>1060</x:v>
+        <x:v>1049</x:v>
       </x:c>
       <x:c r="P2" s="3" t="s">
-        <x:v>1061</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="Q2" s="3" t="s">
-        <x:v>1062</x:v>
+        <x:v>1051</x:v>
       </x:c>
       <x:c r="R2" s="3" t="s">
-        <x:v>1063</x:v>
+        <x:v>1052</x:v>
       </x:c>
       <x:c r="S2" s="3" t="s">
-        <x:v>1064</x:v>
+        <x:v>1053</x:v>
       </x:c>
       <x:c r="T2" s="3" t="s">
-        <x:v>1065</x:v>
+        <x:v>1054</x:v>
       </x:c>
       <x:c r="U2" s="3" t="s">
         <x:v>2</x:v>
@@ -10717,31 +10684,31 @@
     </x:row>
     <x:row r="3" ht="107.25" hidden="0">
       <x:c r="A3" s="3" t="s">
-        <x:v>1066</x:v>
+        <x:v>1055</x:v>
       </x:c>
       <x:c r="B3" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C3" s="3" t="s">
-        <x:v>1067</x:v>
+        <x:v>1056</x:v>
       </x:c>
       <x:c r="D3" s="3" t="s">
-        <x:v>1068</x:v>
+        <x:v>1057</x:v>
       </x:c>
       <x:c r="E3" s="3" t="s">
-        <x:v>1069</x:v>
+        <x:v>1058</x:v>
       </x:c>
       <x:c r="F3" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G3" s="3" t="s">
-        <x:v>1070</x:v>
+        <x:v>1059</x:v>
       </x:c>
       <x:c r="H3" s="3" t="s">
-        <x:v>1071</x:v>
+        <x:v>1060</x:v>
       </x:c>
       <x:c r="I3" s="3" t="s">
-        <x:v>1072</x:v>
+        <x:v>1061</x:v>
       </x:c>
       <x:c r="J3" s="3" t="s">
         <x:v>42</x:v>
@@ -10750,31 +10717,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L3" s="3" t="s">
-        <x:v>1073</x:v>
+        <x:v>1062</x:v>
       </x:c>
       <x:c r="M3" s="3" t="s">
-        <x:v>1074</x:v>
+        <x:v>1063</x:v>
       </x:c>
       <x:c r="N3" s="3" t="s">
-        <x:v>1075</x:v>
+        <x:v>1064</x:v>
       </x:c>
       <x:c r="O3" s="3" t="s">
-        <x:v>1076</x:v>
+        <x:v>1065</x:v>
       </x:c>
       <x:c r="P3" s="3" t="s">
-        <x:v>1077</x:v>
+        <x:v>1066</x:v>
       </x:c>
       <x:c r="Q3" s="3" t="s">
-        <x:v>1078</x:v>
+        <x:v>1067</x:v>
       </x:c>
       <x:c r="R3" s="3" t="s">
-        <x:v>1079</x:v>
+        <x:v>1068</x:v>
       </x:c>
       <x:c r="S3" s="3" t="s">
-        <x:v>1080</x:v>
+        <x:v>1069</x:v>
       </x:c>
       <x:c r="T3" s="3" t="s">
-        <x:v>1081</x:v>
+        <x:v>1070</x:v>
       </x:c>
       <x:c r="U3" s="3" t="s">
         <x:v>2</x:v>
@@ -10782,31 +10749,31 @@
     </x:row>
     <x:row r="4" ht="93.25" hidden="0">
       <x:c r="A4" s="3" t="s">
-        <x:v>1082</x:v>
+        <x:v>1071</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>1083</x:v>
+        <x:v>1072</x:v>
       </x:c>
       <x:c r="D4" s="3" t="s">
-        <x:v>1084</x:v>
+        <x:v>1073</x:v>
       </x:c>
       <x:c r="E4" s="3" t="s">
-        <x:v>1085</x:v>
+        <x:v>1074</x:v>
       </x:c>
       <x:c r="F4" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G4" s="3" t="s">
-        <x:v>1070</x:v>
+        <x:v>1059</x:v>
       </x:c>
       <x:c r="H4" s="3" t="s">
-        <x:v>1071</x:v>
+        <x:v>1060</x:v>
       </x:c>
       <x:c r="I4" s="3" t="s">
-        <x:v>1072</x:v>
+        <x:v>1061</x:v>
       </x:c>
       <x:c r="J4" s="3" t="s">
         <x:v>42</x:v>
@@ -10815,31 +10782,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L4" s="3" t="s">
-        <x:v>1086</x:v>
+        <x:v>1075</x:v>
       </x:c>
       <x:c r="M4" s="3" t="s">
-        <x:v>1074</x:v>
+        <x:v>1063</x:v>
       </x:c>
       <x:c r="N4" s="3" t="s">
-        <x:v>1087</x:v>
+        <x:v>1076</x:v>
       </x:c>
       <x:c r="O4" s="3" t="s">
-        <x:v>1088</x:v>
+        <x:v>1077</x:v>
       </x:c>
       <x:c r="P4" s="3" t="s">
-        <x:v>1089</x:v>
+        <x:v>1078</x:v>
       </x:c>
       <x:c r="Q4" s="3" t="s">
-        <x:v>1090</x:v>
+        <x:v>1079</x:v>
       </x:c>
       <x:c r="R4" s="3" t="s">
-        <x:v>1091</x:v>
+        <x:v>1080</x:v>
       </x:c>
       <x:c r="S4" s="3" t="s">
-        <x:v>1092</x:v>
+        <x:v>1081</x:v>
       </x:c>
       <x:c r="T4" s="3" t="s">
-        <x:v>1093</x:v>
+        <x:v>1082</x:v>
       </x:c>
       <x:c r="U4" s="3" t="s">
         <x:v>2</x:v>
@@ -10847,31 +10814,31 @@
     </x:row>
     <x:row r="5" ht="107.25" hidden="0">
       <x:c r="A5" s="3" t="s">
-        <x:v>1094</x:v>
+        <x:v>1083</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C5" s="3" t="s">
-        <x:v>1095</x:v>
+        <x:v>1084</x:v>
       </x:c>
       <x:c r="D5" s="3" t="s">
-        <x:v>1096</x:v>
+        <x:v>1085</x:v>
       </x:c>
       <x:c r="E5" s="3" t="s">
-        <x:v>1097</x:v>
+        <x:v>1086</x:v>
       </x:c>
       <x:c r="F5" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G5" s="3" t="s">
-        <x:v>1070</x:v>
+        <x:v>1059</x:v>
       </x:c>
       <x:c r="H5" s="3" t="s">
-        <x:v>1071</x:v>
+        <x:v>1060</x:v>
       </x:c>
       <x:c r="I5" s="3" t="s">
-        <x:v>1072</x:v>
+        <x:v>1061</x:v>
       </x:c>
       <x:c r="J5" s="3" t="s">
         <x:v>42</x:v>
@@ -10880,31 +10847,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L5" s="3" t="s">
-        <x:v>1098</x:v>
+        <x:v>1087</x:v>
       </x:c>
       <x:c r="M5" s="3" t="s">
-        <x:v>1074</x:v>
+        <x:v>1063</x:v>
       </x:c>
       <x:c r="N5" s="3" t="s">
-        <x:v>1099</x:v>
+        <x:v>1088</x:v>
       </x:c>
       <x:c r="O5" s="3" t="s">
-        <x:v>1100</x:v>
+        <x:v>1089</x:v>
       </x:c>
       <x:c r="P5" s="3" t="s">
-        <x:v>1101</x:v>
+        <x:v>1090</x:v>
       </x:c>
       <x:c r="Q5" s="3" t="s">
-        <x:v>1102</x:v>
+        <x:v>1091</x:v>
       </x:c>
       <x:c r="R5" s="3" t="s">
-        <x:v>1103</x:v>
+        <x:v>1092</x:v>
       </x:c>
       <x:c r="S5" s="3" t="s">
-        <x:v>1104</x:v>
+        <x:v>1093</x:v>
       </x:c>
       <x:c r="T5" s="3" t="s">
-        <x:v>1105</x:v>
+        <x:v>1094</x:v>
       </x:c>
       <x:c r="U5" s="3" t="s">
         <x:v>2</x:v>
@@ -10912,31 +10879,31 @@
     </x:row>
     <x:row r="6" ht="93.25" hidden="0">
       <x:c r="A6" s="3" t="s">
-        <x:v>1106</x:v>
+        <x:v>1095</x:v>
       </x:c>
       <x:c r="B6" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C6" s="3" t="s">
-        <x:v>1107</x:v>
+        <x:v>1096</x:v>
       </x:c>
       <x:c r="D6" s="3" t="s">
-        <x:v>1108</x:v>
+        <x:v>1097</x:v>
       </x:c>
       <x:c r="E6" s="3" t="s">
-        <x:v>1109</x:v>
+        <x:v>1098</x:v>
       </x:c>
       <x:c r="F6" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G6" s="3" t="s">
-        <x:v>1070</x:v>
+        <x:v>1059</x:v>
       </x:c>
       <x:c r="H6" s="3" t="s">
-        <x:v>1071</x:v>
+        <x:v>1060</x:v>
       </x:c>
       <x:c r="I6" s="3" t="s">
-        <x:v>1072</x:v>
+        <x:v>1061</x:v>
       </x:c>
       <x:c r="J6" s="3" t="s">
         <x:v>42</x:v>
@@ -10945,31 +10912,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L6" s="3" t="s">
-        <x:v>1110</x:v>
+        <x:v>1099</x:v>
       </x:c>
       <x:c r="M6" s="3" t="s">
-        <x:v>1074</x:v>
+        <x:v>1063</x:v>
       </x:c>
       <x:c r="N6" s="3" t="s">
-        <x:v>1111</x:v>
+        <x:v>1100</x:v>
       </x:c>
       <x:c r="O6" s="3" t="s">
-        <x:v>1112</x:v>
+        <x:v>1101</x:v>
       </x:c>
       <x:c r="P6" s="3" t="s">
-        <x:v>1113</x:v>
+        <x:v>1102</x:v>
       </x:c>
       <x:c r="Q6" s="3" t="s">
-        <x:v>1114</x:v>
+        <x:v>1103</x:v>
       </x:c>
       <x:c r="R6" s="3" t="s">
-        <x:v>1115</x:v>
+        <x:v>1104</x:v>
       </x:c>
       <x:c r="S6" s="3" t="s">
-        <x:v>1116</x:v>
+        <x:v>1105</x:v>
       </x:c>
       <x:c r="T6" s="3" t="s">
-        <x:v>1117</x:v>
+        <x:v>1106</x:v>
       </x:c>
       <x:c r="U6" s="3" t="s">
         <x:v>2</x:v>
@@ -10977,31 +10944,31 @@
     </x:row>
     <x:row r="7" ht="93.25" hidden="0">
       <x:c r="A7" s="3" t="s">
-        <x:v>1118</x:v>
+        <x:v>1107</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>1119</x:v>
+        <x:v>1108</x:v>
       </x:c>
       <x:c r="D7" s="3" t="s">
-        <x:v>1120</x:v>
+        <x:v>1109</x:v>
       </x:c>
       <x:c r="E7" s="3" t="s">
-        <x:v>1121</x:v>
+        <x:v>1110</x:v>
       </x:c>
       <x:c r="F7" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G7" s="3" t="s">
-        <x:v>1070</x:v>
+        <x:v>1059</x:v>
       </x:c>
       <x:c r="H7" s="3" t="s">
-        <x:v>1071</x:v>
+        <x:v>1060</x:v>
       </x:c>
       <x:c r="I7" s="3" t="s">
-        <x:v>1072</x:v>
+        <x:v>1061</x:v>
       </x:c>
       <x:c r="J7" s="3" t="s">
         <x:v>42</x:v>
@@ -11010,31 +10977,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="L7" s="3" t="s">
-        <x:v>1122</x:v>
+        <x:v>1111</x:v>
       </x:c>
       <x:c r="M7" s="3" t="s">
-        <x:v>1074</x:v>
+        <x:v>1063</x:v>
       </x:c>
       <x:c r="N7" s="3" t="s">
-        <x:v>1123</x:v>
+        <x:v>1112</x:v>
       </x:c>
       <x:c r="O7" s="3" t="s">
-        <x:v>1124</x:v>
+        <x:v>1113</x:v>
       </x:c>
       <x:c r="P7" s="3" t="s">
-        <x:v>1125</x:v>
+        <x:v>1114</x:v>
       </x:c>
       <x:c r="Q7" s="3" t="s">
-        <x:v>1078</x:v>
+        <x:v>1067</x:v>
       </x:c>
       <x:c r="R7" s="3" t="s">
-        <x:v>1126</x:v>
+        <x:v>1115</x:v>
       </x:c>
       <x:c r="S7" s="3" t="s">
-        <x:v>1127</x:v>
+        <x:v>1116</x:v>
       </x:c>
       <x:c r="T7" s="3" t="s">
-        <x:v>1128</x:v>
+        <x:v>1117</x:v>
       </x:c>
       <x:c r="U7" s="3" t="s">
         <x:v>2</x:v>
@@ -11042,31 +11009,31 @@
     </x:row>
     <x:row r="8" ht="93.25" hidden="0">
       <x:c r="A8" s="3" t="s">
-        <x:v>1129</x:v>
+        <x:v>1118</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>1130</x:v>
+        <x:v>1119</x:v>
       </x:c>
       <x:c r="D8" s="3" t="s">
-        <x:v>1131</x:v>
+        <x:v>1120</x:v>
       </x:c>
       <x:c r="E8" s="3" t="s">
-        <x:v>1132</x:v>
+        <x:v>1121</x:v>
       </x:c>
       <x:c r="F8" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G8" s="3" t="s">
-        <x:v>1070</x:v>
+        <x:v>1059</x:v>
       </x:c>
       <x:c r="H8" s="3" t="s">
-        <x:v>1071</x:v>
+        <x:v>1060</x:v>
       </x:c>
       <x:c r="I8" s="3" t="s">
-        <x:v>1072</x:v>
+        <x:v>1061</x:v>
       </x:c>
       <x:c r="J8" s="3" t="s">
         <x:v>42</x:v>
@@ -11075,31 +11042,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L8" s="3" t="s">
-        <x:v>1133</x:v>
+        <x:v>1122</x:v>
       </x:c>
       <x:c r="M8" s="3" t="s">
-        <x:v>1074</x:v>
+        <x:v>1063</x:v>
       </x:c>
       <x:c r="N8" s="3" t="s">
-        <x:v>1134</x:v>
+        <x:v>1123</x:v>
       </x:c>
       <x:c r="O8" s="3" t="s">
-        <x:v>1135</x:v>
+        <x:v>1124</x:v>
       </x:c>
       <x:c r="P8" s="3" t="s">
-        <x:v>1136</x:v>
+        <x:v>1125</x:v>
       </x:c>
       <x:c r="Q8" s="3" t="s">
-        <x:v>1137</x:v>
+        <x:v>1126</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
-        <x:v>1138</x:v>
+        <x:v>1127</x:v>
       </x:c>
       <x:c r="S8" s="3" t="s">
-        <x:v>1139</x:v>
+        <x:v>1128</x:v>
       </x:c>
       <x:c r="T8" s="3" t="s">
-        <x:v>1140</x:v>
+        <x:v>1129</x:v>
       </x:c>
       <x:c r="U8" s="3" t="s">
         <x:v>2</x:v>
@@ -11107,31 +11074,31 @@
     </x:row>
     <x:row r="9" ht="93.25" hidden="0">
       <x:c r="A9" s="3" t="s">
-        <x:v>1141</x:v>
+        <x:v>1130</x:v>
       </x:c>
       <x:c r="B9" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C9" s="3" t="s">
-        <x:v>1142</x:v>
+        <x:v>1131</x:v>
       </x:c>
       <x:c r="D9" s="3" t="s">
-        <x:v>1143</x:v>
+        <x:v>1132</x:v>
       </x:c>
       <x:c r="E9" s="3" t="s">
-        <x:v>1144</x:v>
+        <x:v>1133</x:v>
       </x:c>
       <x:c r="F9" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G9" s="3" t="s">
-        <x:v>1070</x:v>
+        <x:v>1059</x:v>
       </x:c>
       <x:c r="H9" s="3" t="s">
-        <x:v>1071</x:v>
+        <x:v>1060</x:v>
       </x:c>
       <x:c r="I9" s="3" t="s">
-        <x:v>1072</x:v>
+        <x:v>1061</x:v>
       </x:c>
       <x:c r="J9" s="3" t="s">
         <x:v>42</x:v>
@@ -11140,31 +11107,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L9" s="3" t="s">
-        <x:v>1145</x:v>
+        <x:v>1134</x:v>
       </x:c>
       <x:c r="M9" s="3" t="s">
-        <x:v>1074</x:v>
+        <x:v>1063</x:v>
       </x:c>
       <x:c r="N9" s="3" t="s">
-        <x:v>1146</x:v>
+        <x:v>1135</x:v>
       </x:c>
       <x:c r="O9" s="3" t="s">
-        <x:v>1147</x:v>
+        <x:v>1136</x:v>
       </x:c>
       <x:c r="P9" s="3" t="s">
-        <x:v>1148</x:v>
+        <x:v>1137</x:v>
       </x:c>
       <x:c r="Q9" s="3" t="s">
-        <x:v>1149</x:v>
+        <x:v>1138</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
-        <x:v>1150</x:v>
+        <x:v>1139</x:v>
       </x:c>
       <x:c r="S9" s="3" t="s">
-        <x:v>1151</x:v>
+        <x:v>1140</x:v>
       </x:c>
       <x:c r="T9" s="3" t="s">
-        <x:v>1152</x:v>
+        <x:v>1141</x:v>
       </x:c>
       <x:c r="U9" s="3" t="s">
         <x:v>2</x:v>
@@ -11172,31 +11139,31 @@
     </x:row>
     <x:row r="10" ht="93.25" hidden="0">
       <x:c r="A10" s="3" t="s">
-        <x:v>1153</x:v>
+        <x:v>1142</x:v>
       </x:c>
       <x:c r="B10" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C10" s="3" t="s">
-        <x:v>1154</x:v>
+        <x:v>1143</x:v>
       </x:c>
       <x:c r="D10" s="3" t="s">
-        <x:v>1155</x:v>
+        <x:v>1144</x:v>
       </x:c>
       <x:c r="E10" s="3" t="s">
-        <x:v>1156</x:v>
+        <x:v>1145</x:v>
       </x:c>
       <x:c r="F10" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G10" s="3" t="s">
-        <x:v>1070</x:v>
+        <x:v>1059</x:v>
       </x:c>
       <x:c r="H10" s="3" t="s">
-        <x:v>1071</x:v>
+        <x:v>1060</x:v>
       </x:c>
       <x:c r="I10" s="3" t="s">
-        <x:v>1072</x:v>
+        <x:v>1061</x:v>
       </x:c>
       <x:c r="J10" s="3" t="s">
         <x:v>42</x:v>
@@ -11205,31 +11172,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L10" s="3" t="s">
-        <x:v>1157</x:v>
+        <x:v>1146</x:v>
       </x:c>
       <x:c r="M10" s="3" t="s">
-        <x:v>1058</x:v>
+        <x:v>1047</x:v>
       </x:c>
       <x:c r="N10" s="3" t="s">
-        <x:v>1158</x:v>
+        <x:v>1147</x:v>
       </x:c>
       <x:c r="O10" s="3" t="s">
         <x:v>205</x:v>
       </x:c>
       <x:c r="P10" s="3" t="s">
-        <x:v>1159</x:v>
+        <x:v>1148</x:v>
       </x:c>
       <x:c r="Q10" s="3" t="s">
-        <x:v>1160</x:v>
+        <x:v>1149</x:v>
       </x:c>
       <x:c r="R10" s="3" t="s">
-        <x:v>1161</x:v>
+        <x:v>1150</x:v>
       </x:c>
       <x:c r="S10" s="3" t="s">
-        <x:v>1162</x:v>
+        <x:v>1151</x:v>
       </x:c>
       <x:c r="T10" s="3" t="s">
-        <x:v>1163</x:v>
+        <x:v>1152</x:v>
       </x:c>
       <x:c r="U10" s="3" t="s">
         <x:v>2</x:v>
@@ -11237,31 +11204,31 @@
     </x:row>
     <x:row r="11" ht="93.25" hidden="0">
       <x:c r="A11" s="3" t="s">
-        <x:v>1164</x:v>
+        <x:v>1153</x:v>
       </x:c>
       <x:c r="B11" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C11" s="3" t="s">
-        <x:v>1165</x:v>
+        <x:v>1154</x:v>
       </x:c>
       <x:c r="D11" s="3" t="s">
-        <x:v>1166</x:v>
+        <x:v>1155</x:v>
       </x:c>
       <x:c r="E11" s="3" t="s">
-        <x:v>1167</x:v>
+        <x:v>1156</x:v>
       </x:c>
       <x:c r="F11" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G11" s="3" t="s">
-        <x:v>1070</x:v>
+        <x:v>1059</x:v>
       </x:c>
       <x:c r="H11" s="3" t="s">
-        <x:v>1071</x:v>
+        <x:v>1060</x:v>
       </x:c>
       <x:c r="I11" s="3" t="s">
-        <x:v>1072</x:v>
+        <x:v>1061</x:v>
       </x:c>
       <x:c r="J11" s="3" t="s">
         <x:v>42</x:v>
@@ -11270,31 +11237,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L11" s="3" t="s">
-        <x:v>1168</x:v>
+        <x:v>1157</x:v>
       </x:c>
       <x:c r="M11" s="3" t="s">
-        <x:v>1169</x:v>
+        <x:v>1158</x:v>
       </x:c>
       <x:c r="N11" s="3" t="s">
-        <x:v>1170</x:v>
+        <x:v>1159</x:v>
       </x:c>
       <x:c r="O11" s="3" t="s">
-        <x:v>1171</x:v>
+        <x:v>1160</x:v>
       </x:c>
       <x:c r="P11" s="3" t="s">
-        <x:v>1172</x:v>
+        <x:v>1161</x:v>
       </x:c>
       <x:c r="Q11" s="3" t="s">
-        <x:v>1173</x:v>
+        <x:v>1162</x:v>
       </x:c>
       <x:c r="R11" s="3" t="s">
-        <x:v>1174</x:v>
+        <x:v>1163</x:v>
       </x:c>
       <x:c r="S11" s="3" t="s">
-        <x:v>1175</x:v>
+        <x:v>1164</x:v>
       </x:c>
       <x:c r="T11" s="3" t="s">
-        <x:v>1176</x:v>
+        <x:v>1165</x:v>
       </x:c>
       <x:c r="U11" s="3" t="s">
         <x:v>2</x:v>
@@ -11302,31 +11269,31 @@
     </x:row>
     <x:row r="12" ht="107.25" hidden="0">
       <x:c r="A12" s="3" t="s">
-        <x:v>1177</x:v>
+        <x:v>1166</x:v>
       </x:c>
       <x:c r="B12" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C12" s="3" t="s">
-        <x:v>1178</x:v>
+        <x:v>1167</x:v>
       </x:c>
       <x:c r="D12" s="3" t="s">
-        <x:v>1179</x:v>
+        <x:v>1168</x:v>
       </x:c>
       <x:c r="E12" s="3" t="s">
-        <x:v>1180</x:v>
+        <x:v>1169</x:v>
       </x:c>
       <x:c r="F12" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G12" s="3" t="s">
-        <x:v>1070</x:v>
+        <x:v>1059</x:v>
       </x:c>
       <x:c r="H12" s="3" t="s">
-        <x:v>1071</x:v>
+        <x:v>1060</x:v>
       </x:c>
       <x:c r="I12" s="3" t="s">
-        <x:v>1072</x:v>
+        <x:v>1061</x:v>
       </x:c>
       <x:c r="J12" s="3" t="s">
         <x:v>42</x:v>
@@ -11335,31 +11302,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L12" s="3" t="s">
-        <x:v>1181</x:v>
+        <x:v>1170</x:v>
       </x:c>
       <x:c r="M12" s="3" t="s">
-        <x:v>1074</x:v>
+        <x:v>1063</x:v>
       </x:c>
       <x:c r="N12" s="3" t="s">
-        <x:v>1182</x:v>
+        <x:v>1171</x:v>
       </x:c>
       <x:c r="O12" s="3" t="s">
-        <x:v>1183</x:v>
+        <x:v>1172</x:v>
       </x:c>
       <x:c r="P12" s="3" t="s">
-        <x:v>1184</x:v>
+        <x:v>1173</x:v>
       </x:c>
       <x:c r="Q12" s="3" t="s">
-        <x:v>1185</x:v>
+        <x:v>1174</x:v>
       </x:c>
       <x:c r="R12" s="3" t="s">
-        <x:v>1186</x:v>
+        <x:v>1175</x:v>
       </x:c>
       <x:c r="S12" s="3" t="s">
-        <x:v>1187</x:v>
+        <x:v>1176</x:v>
       </x:c>
       <x:c r="T12" s="3" t="s">
-        <x:v>1188</x:v>
+        <x:v>1177</x:v>
       </x:c>
       <x:c r="U12" s="3" t="s">
         <x:v>2</x:v>
@@ -11367,31 +11334,31 @@
     </x:row>
     <x:row r="13" ht="93.25" hidden="0">
       <x:c r="A13" s="3" t="s">
-        <x:v>1189</x:v>
+        <x:v>1178</x:v>
       </x:c>
       <x:c r="B13" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C13" s="3" t="s">
-        <x:v>1190</x:v>
+        <x:v>1179</x:v>
       </x:c>
       <x:c r="D13" s="3" t="s">
-        <x:v>1191</x:v>
+        <x:v>1180</x:v>
       </x:c>
       <x:c r="E13" s="3" t="s">
-        <x:v>1192</x:v>
+        <x:v>1181</x:v>
       </x:c>
       <x:c r="F13" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G13" s="3" t="s">
-        <x:v>1070</x:v>
+        <x:v>1059</x:v>
       </x:c>
       <x:c r="H13" s="3" t="s">
-        <x:v>1071</x:v>
+        <x:v>1060</x:v>
       </x:c>
       <x:c r="I13" s="3" t="s">
-        <x:v>1072</x:v>
+        <x:v>1061</x:v>
       </x:c>
       <x:c r="J13" s="3" t="s">
         <x:v>42</x:v>
@@ -11400,31 +11367,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L13" s="3" t="s">
-        <x:v>1193</x:v>
+        <x:v>1182</x:v>
       </x:c>
       <x:c r="M13" s="3" t="s">
-        <x:v>1074</x:v>
+        <x:v>1063</x:v>
       </x:c>
       <x:c r="N13" s="3" t="s">
-        <x:v>1194</x:v>
+        <x:v>1183</x:v>
       </x:c>
       <x:c r="O13" s="3" t="s">
-        <x:v>1195</x:v>
+        <x:v>1184</x:v>
       </x:c>
       <x:c r="P13" s="3" t="s">
-        <x:v>1196</x:v>
+        <x:v>1185</x:v>
       </x:c>
       <x:c r="Q13" s="3" t="s">
-        <x:v>1185</x:v>
+        <x:v>1174</x:v>
       </x:c>
       <x:c r="R13" s="3" t="s">
-        <x:v>1197</x:v>
+        <x:v>1186</x:v>
       </x:c>
       <x:c r="S13" s="3" t="s">
-        <x:v>1198</x:v>
+        <x:v>1187</x:v>
       </x:c>
       <x:c r="T13" s="3" t="s">
-        <x:v>1199</x:v>
+        <x:v>1188</x:v>
       </x:c>
       <x:c r="U13" s="3" t="s">
         <x:v>2</x:v>
@@ -11432,31 +11399,31 @@
     </x:row>
     <x:row r="14" ht="93.25" hidden="0">
       <x:c r="A14" s="3" t="s">
-        <x:v>1200</x:v>
+        <x:v>1189</x:v>
       </x:c>
       <x:c r="B14" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C14" s="3" t="s">
-        <x:v>1201</x:v>
+        <x:v>1190</x:v>
       </x:c>
       <x:c r="D14" s="3" t="s">
-        <x:v>1202</x:v>
+        <x:v>1191</x:v>
       </x:c>
       <x:c r="E14" s="3" t="s">
-        <x:v>1203</x:v>
+        <x:v>1192</x:v>
       </x:c>
       <x:c r="F14" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G14" s="3" t="s">
-        <x:v>1070</x:v>
+        <x:v>1059</x:v>
       </x:c>
       <x:c r="H14" s="3" t="s">
-        <x:v>1071</x:v>
+        <x:v>1060</x:v>
       </x:c>
       <x:c r="I14" s="3" t="s">
-        <x:v>1072</x:v>
+        <x:v>1061</x:v>
       </x:c>
       <x:c r="J14" s="3" t="s">
         <x:v>42</x:v>
@@ -11465,31 +11432,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L14" s="3" t="s">
-        <x:v>1204</x:v>
+        <x:v>1193</x:v>
       </x:c>
       <x:c r="M14" s="3" t="s">
-        <x:v>1205</x:v>
+        <x:v>1194</x:v>
       </x:c>
       <x:c r="N14" s="3" t="s">
-        <x:v>1206</x:v>
+        <x:v>1195</x:v>
       </x:c>
       <x:c r="O14" s="3" t="s">
-        <x:v>1207</x:v>
+        <x:v>1196</x:v>
       </x:c>
       <x:c r="P14" s="3" t="s">
-        <x:v>1208</x:v>
+        <x:v>1197</x:v>
       </x:c>
       <x:c r="Q14" s="3" t="s">
-        <x:v>1209</x:v>
+        <x:v>1198</x:v>
       </x:c>
       <x:c r="R14" s="3" t="s">
-        <x:v>1210</x:v>
+        <x:v>1199</x:v>
       </x:c>
       <x:c r="S14" s="3" t="s">
-        <x:v>1211</x:v>
+        <x:v>1200</x:v>
       </x:c>
       <x:c r="T14" s="3" t="s">
-        <x:v>1212</x:v>
+        <x:v>1201</x:v>
       </x:c>
       <x:c r="U14" s="3" t="s">
         <x:v>2</x:v>
@@ -11497,31 +11464,31 @@
     </x:row>
     <x:row r="15" ht="107.25" hidden="0">
       <x:c r="A15" s="3" t="s">
-        <x:v>1213</x:v>
+        <x:v>1202</x:v>
       </x:c>
       <x:c r="B15" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C15" s="3" t="s">
-        <x:v>1214</x:v>
+        <x:v>1203</x:v>
       </x:c>
       <x:c r="D15" s="3" t="s">
-        <x:v>1215</x:v>
+        <x:v>1204</x:v>
       </x:c>
       <x:c r="E15" s="3" t="s">
-        <x:v>1216</x:v>
+        <x:v>1205</x:v>
       </x:c>
       <x:c r="F15" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G15" s="3" t="s">
-        <x:v>1070</x:v>
+        <x:v>1059</x:v>
       </x:c>
       <x:c r="H15" s="3" t="s">
-        <x:v>1071</x:v>
+        <x:v>1060</x:v>
       </x:c>
       <x:c r="I15" s="3" t="s">
-        <x:v>1072</x:v>
+        <x:v>1061</x:v>
       </x:c>
       <x:c r="J15" s="3" t="s">
         <x:v>42</x:v>
@@ -11530,31 +11497,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L15" s="3" t="s">
-        <x:v>1217</x:v>
+        <x:v>1206</x:v>
       </x:c>
       <x:c r="M15" s="3" t="s">
-        <x:v>1074</x:v>
+        <x:v>1063</x:v>
       </x:c>
       <x:c r="N15" s="3" t="s">
-        <x:v>1218</x:v>
+        <x:v>1207</x:v>
       </x:c>
       <x:c r="O15" s="3" t="s">
-        <x:v>1219</x:v>
+        <x:v>1208</x:v>
       </x:c>
       <x:c r="P15" s="3" t="s">
-        <x:v>1220</x:v>
+        <x:v>1209</x:v>
       </x:c>
       <x:c r="Q15" s="3" t="s">
-        <x:v>1221</x:v>
+        <x:v>1210</x:v>
       </x:c>
       <x:c r="R15" s="3" t="s">
-        <x:v>1222</x:v>
+        <x:v>1211</x:v>
       </x:c>
       <x:c r="S15" s="3" t="s">
-        <x:v>1223</x:v>
+        <x:v>1212</x:v>
       </x:c>
       <x:c r="T15" s="3" t="s">
-        <x:v>1224</x:v>
+        <x:v>1213</x:v>
       </x:c>
       <x:c r="U15" s="3" t="s">
         <x:v>2</x:v>
@@ -11562,31 +11529,31 @@
     </x:row>
     <x:row r="16" ht="107.25" hidden="0">
       <x:c r="A16" s="3" t="s">
-        <x:v>1225</x:v>
+        <x:v>1214</x:v>
       </x:c>
       <x:c r="B16" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C16" s="3" t="s">
-        <x:v>1226</x:v>
+        <x:v>1215</x:v>
       </x:c>
       <x:c r="D16" s="3" t="s">
-        <x:v>1227</x:v>
+        <x:v>1216</x:v>
       </x:c>
       <x:c r="E16" s="3" t="s">
-        <x:v>1228</x:v>
+        <x:v>1217</x:v>
       </x:c>
       <x:c r="F16" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G16" s="3" t="s">
-        <x:v>1070</x:v>
+        <x:v>1059</x:v>
       </x:c>
       <x:c r="H16" s="3" t="s">
-        <x:v>1071</x:v>
+        <x:v>1060</x:v>
       </x:c>
       <x:c r="I16" s="3" t="s">
-        <x:v>1072</x:v>
+        <x:v>1061</x:v>
       </x:c>
       <x:c r="J16" s="3" t="s">
         <x:v>42</x:v>
@@ -11595,31 +11562,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L16" s="3" t="s">
-        <x:v>1229</x:v>
+        <x:v>1218</x:v>
       </x:c>
       <x:c r="M16" s="3" t="s">
-        <x:v>1074</x:v>
+        <x:v>1063</x:v>
       </x:c>
       <x:c r="N16" s="3" t="s">
-        <x:v>1230</x:v>
+        <x:v>1219</x:v>
       </x:c>
       <x:c r="O16" s="3" t="s">
-        <x:v>1231</x:v>
+        <x:v>1220</x:v>
       </x:c>
       <x:c r="P16" s="3" t="s">
-        <x:v>1232</x:v>
+        <x:v>1221</x:v>
       </x:c>
       <x:c r="Q16" s="3" t="s">
-        <x:v>1233</x:v>
+        <x:v>1222</x:v>
       </x:c>
       <x:c r="R16" s="3" t="s">
-        <x:v>1234</x:v>
+        <x:v>1223</x:v>
       </x:c>
       <x:c r="S16" s="3" t="s">
-        <x:v>1235</x:v>
+        <x:v>1224</x:v>
       </x:c>
       <x:c r="T16" s="3" t="s">
-        <x:v>1236</x:v>
+        <x:v>1225</x:v>
       </x:c>
       <x:c r="U16" s="3" t="s">
         <x:v>2</x:v>
@@ -11627,31 +11594,31 @@
     </x:row>
     <x:row r="17" ht="93.25" hidden="0">
       <x:c r="A17" s="3" t="s">
-        <x:v>1237</x:v>
+        <x:v>1226</x:v>
       </x:c>
       <x:c r="B17" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C17" s="3" t="s">
-        <x:v>1238</x:v>
+        <x:v>1227</x:v>
       </x:c>
       <x:c r="D17" s="3" t="s">
-        <x:v>1239</x:v>
+        <x:v>1228</x:v>
       </x:c>
       <x:c r="E17" s="3" t="s">
-        <x:v>1240</x:v>
+        <x:v>1229</x:v>
       </x:c>
       <x:c r="F17" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G17" s="3" t="s">
-        <x:v>1070</x:v>
+        <x:v>1059</x:v>
       </x:c>
       <x:c r="H17" s="3" t="s">
-        <x:v>1071</x:v>
+        <x:v>1060</x:v>
       </x:c>
       <x:c r="I17" s="3" t="s">
-        <x:v>1072</x:v>
+        <x:v>1061</x:v>
       </x:c>
       <x:c r="J17" s="3" t="s">
         <x:v>42</x:v>
@@ -11660,31 +11627,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L17" s="3" t="s">
-        <x:v>1241</x:v>
+        <x:v>1230</x:v>
       </x:c>
       <x:c r="M17" s="3" t="s">
-        <x:v>1242</x:v>
+        <x:v>1231</x:v>
       </x:c>
       <x:c r="N17" s="3" t="s">
-        <x:v>1243</x:v>
+        <x:v>1232</x:v>
       </x:c>
       <x:c r="O17" s="3" t="s">
-        <x:v>1244</x:v>
+        <x:v>1233</x:v>
       </x:c>
       <x:c r="P17" s="3" t="s">
-        <x:v>1245</x:v>
+        <x:v>1234</x:v>
       </x:c>
       <x:c r="Q17" s="3" t="s">
-        <x:v>1246</x:v>
+        <x:v>1235</x:v>
       </x:c>
       <x:c r="R17" s="3" t="s">
-        <x:v>1247</x:v>
+        <x:v>1236</x:v>
       </x:c>
       <x:c r="S17" s="3" t="s">
-        <x:v>1248</x:v>
+        <x:v>1237</x:v>
       </x:c>
       <x:c r="T17" s="3" t="s">
-        <x:v>1249</x:v>
+        <x:v>1238</x:v>
       </x:c>
       <x:c r="U17" s="3" t="s">
         <x:v>2</x:v>
@@ -11692,31 +11659,31 @@
     </x:row>
     <x:row r="18" ht="93.25" hidden="0">
       <x:c r="A18" s="3" t="s">
-        <x:v>1250</x:v>
+        <x:v>1239</x:v>
       </x:c>
       <x:c r="B18" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C18" s="3" t="s">
-        <x:v>1251</x:v>
+        <x:v>1240</x:v>
       </x:c>
       <x:c r="D18" s="3" t="s">
-        <x:v>1252</x:v>
+        <x:v>1241</x:v>
       </x:c>
       <x:c r="E18" s="3" t="s">
-        <x:v>1253</x:v>
+        <x:v>1242</x:v>
       </x:c>
       <x:c r="F18" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G18" s="3" t="s">
-        <x:v>1070</x:v>
+        <x:v>1059</x:v>
       </x:c>
       <x:c r="H18" s="3" t="s">
-        <x:v>1071</x:v>
+        <x:v>1060</x:v>
       </x:c>
       <x:c r="I18" s="3" t="s">
-        <x:v>1072</x:v>
+        <x:v>1061</x:v>
       </x:c>
       <x:c r="J18" s="3" t="s">
         <x:v>42</x:v>
@@ -11725,31 +11692,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L18" s="3" t="s">
-        <x:v>1254</x:v>
+        <x:v>1243</x:v>
       </x:c>
       <x:c r="M18" s="3" t="s">
-        <x:v>1255</x:v>
+        <x:v>1244</x:v>
       </x:c>
       <x:c r="N18" s="3" t="s">
-        <x:v>1256</x:v>
+        <x:v>1245</x:v>
       </x:c>
       <x:c r="O18" s="3" t="s">
-        <x:v>1257</x:v>
+        <x:v>1246</x:v>
       </x:c>
       <x:c r="P18" s="3" t="s">
-        <x:v>1258</x:v>
+        <x:v>1247</x:v>
       </x:c>
       <x:c r="Q18" s="3" t="s">
-        <x:v>1259</x:v>
+        <x:v>1248</x:v>
       </x:c>
       <x:c r="R18" s="3" t="s">
-        <x:v>1260</x:v>
+        <x:v>1249</x:v>
       </x:c>
       <x:c r="S18" s="3" t="s">
-        <x:v>1261</x:v>
+        <x:v>1250</x:v>
       </x:c>
       <x:c r="T18" s="3" t="s">
-        <x:v>1262</x:v>
+        <x:v>1251</x:v>
       </x:c>
       <x:c r="U18" s="3" t="s">
         <x:v>2</x:v>
@@ -11757,31 +11724,31 @@
     </x:row>
     <x:row r="19" ht="93.25" hidden="0">
       <x:c r="A19" s="3" t="s">
-        <x:v>1263</x:v>
+        <x:v>1252</x:v>
       </x:c>
       <x:c r="B19" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C19" s="3" t="s">
-        <x:v>1264</x:v>
+        <x:v>1253</x:v>
       </x:c>
       <x:c r="D19" s="3" t="s">
-        <x:v>1265</x:v>
+        <x:v>1254</x:v>
       </x:c>
       <x:c r="E19" s="3" t="s">
-        <x:v>1266</x:v>
+        <x:v>1255</x:v>
       </x:c>
       <x:c r="F19" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G19" s="3" t="s">
-        <x:v>1070</x:v>
+        <x:v>1059</x:v>
       </x:c>
       <x:c r="H19" s="3" t="s">
-        <x:v>1071</x:v>
+        <x:v>1060</x:v>
       </x:c>
       <x:c r="I19" s="3" t="s">
-        <x:v>1072</x:v>
+        <x:v>1061</x:v>
       </x:c>
       <x:c r="J19" s="3" t="s">
         <x:v>42</x:v>
@@ -11790,31 +11757,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L19" s="3" t="s">
-        <x:v>1267</x:v>
+        <x:v>1256</x:v>
       </x:c>
       <x:c r="M19" s="3" t="s">
-        <x:v>1268</x:v>
+        <x:v>1257</x:v>
       </x:c>
       <x:c r="N19" s="3" t="s">
-        <x:v>1269</x:v>
+        <x:v>1258</x:v>
       </x:c>
       <x:c r="O19" s="3" t="s">
-        <x:v>1270</x:v>
+        <x:v>1259</x:v>
       </x:c>
       <x:c r="P19" s="3" t="s">
-        <x:v>1271</x:v>
+        <x:v>1260</x:v>
       </x:c>
       <x:c r="Q19" s="3" t="s">
-        <x:v>1272</x:v>
+        <x:v>1261</x:v>
       </x:c>
       <x:c r="R19" s="3" t="s">
-        <x:v>1273</x:v>
+        <x:v>1262</x:v>
       </x:c>
       <x:c r="S19" s="3" t="s">
-        <x:v>1274</x:v>
+        <x:v>1263</x:v>
       </x:c>
       <x:c r="T19" s="3" t="s">
-        <x:v>1275</x:v>
+        <x:v>1264</x:v>
       </x:c>
       <x:c r="U19" s="3" t="s">
         <x:v>2</x:v>
@@ -11822,31 +11789,31 @@
     </x:row>
     <x:row r="20" ht="79.25" hidden="0">
       <x:c r="A20" s="3" t="s">
-        <x:v>1276</x:v>
+        <x:v>1265</x:v>
       </x:c>
       <x:c r="B20" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C20" s="3" t="s">
-        <x:v>1277</x:v>
+        <x:v>1266</x:v>
       </x:c>
       <x:c r="D20" s="3" t="s">
-        <x:v>1278</x:v>
+        <x:v>1267</x:v>
       </x:c>
       <x:c r="E20" s="3" t="s">
-        <x:v>1279</x:v>
+        <x:v>1268</x:v>
       </x:c>
       <x:c r="F20" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G20" s="3" t="s">
-        <x:v>1070</x:v>
+        <x:v>1059</x:v>
       </x:c>
       <x:c r="H20" s="3" t="s">
-        <x:v>1071</x:v>
+        <x:v>1060</x:v>
       </x:c>
       <x:c r="I20" s="3" t="s">
-        <x:v>1072</x:v>
+        <x:v>1061</x:v>
       </x:c>
       <x:c r="J20" s="3" t="s">
         <x:v>42</x:v>
@@ -11855,31 +11822,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L20" s="3" t="s">
-        <x:v>1280</x:v>
+        <x:v>1269</x:v>
       </x:c>
       <x:c r="M20" s="3" t="s">
-        <x:v>1281</x:v>
+        <x:v>1270</x:v>
       </x:c>
       <x:c r="N20" s="3" t="s">
-        <x:v>1282</x:v>
+        <x:v>1271</x:v>
       </x:c>
       <x:c r="O20" s="3" t="s">
-        <x:v>1283</x:v>
+        <x:v>1272</x:v>
       </x:c>
       <x:c r="P20" s="3" t="s">
-        <x:v>1284</x:v>
+        <x:v>1273</x:v>
       </x:c>
       <x:c r="Q20" s="3" t="s">
-        <x:v>1285</x:v>
+        <x:v>1274</x:v>
       </x:c>
       <x:c r="R20" s="3" t="s">
-        <x:v>1286</x:v>
+        <x:v>1275</x:v>
       </x:c>
       <x:c r="S20" s="3" t="s">
-        <x:v>1287</x:v>
+        <x:v>1276</x:v>
       </x:c>
       <x:c r="T20" s="3" t="s">
-        <x:v>1288</x:v>
+        <x:v>1277</x:v>
       </x:c>
       <x:c r="U20" s="3" t="s">
         <x:v>2</x:v>
@@ -11887,31 +11854,31 @@
     </x:row>
     <x:row r="21" ht="79.25" hidden="0">
       <x:c r="A21" s="3" t="s">
-        <x:v>1289</x:v>
+        <x:v>1278</x:v>
       </x:c>
       <x:c r="B21" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C21" s="3" t="s">
-        <x:v>1290</x:v>
+        <x:v>1279</x:v>
       </x:c>
       <x:c r="D21" s="3" t="s">
-        <x:v>1291</x:v>
+        <x:v>1280</x:v>
       </x:c>
       <x:c r="E21" s="3" t="s">
-        <x:v>1292</x:v>
+        <x:v>1281</x:v>
       </x:c>
       <x:c r="F21" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G21" s="3" t="s">
-        <x:v>1070</x:v>
+        <x:v>1059</x:v>
       </x:c>
       <x:c r="H21" s="3" t="s">
-        <x:v>1071</x:v>
+        <x:v>1060</x:v>
       </x:c>
       <x:c r="I21" s="3" t="s">
-        <x:v>1072</x:v>
+        <x:v>1061</x:v>
       </x:c>
       <x:c r="J21" s="3" t="s">
         <x:v>42</x:v>
@@ -11920,31 +11887,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L21" s="3" t="s">
-        <x:v>1293</x:v>
+        <x:v>1282</x:v>
       </x:c>
       <x:c r="M21" s="3" t="s">
-        <x:v>1294</x:v>
+        <x:v>1283</x:v>
       </x:c>
       <x:c r="N21" s="3" t="s">
-        <x:v>1295</x:v>
+        <x:v>1284</x:v>
       </x:c>
       <x:c r="O21" s="3" t="s">
         <x:v>218</x:v>
       </x:c>
       <x:c r="P21" s="3" t="s">
-        <x:v>1296</x:v>
+        <x:v>1285</x:v>
       </x:c>
       <x:c r="Q21" s="3" t="s">
-        <x:v>1297</x:v>
+        <x:v>1286</x:v>
       </x:c>
       <x:c r="R21" s="3" t="s">
         <x:v>221</x:v>
       </x:c>
       <x:c r="S21" s="3" t="s">
-        <x:v>1298</x:v>
+        <x:v>1287</x:v>
       </x:c>
       <x:c r="T21" s="3" t="s">
-        <x:v>1299</x:v>
+        <x:v>1288</x:v>
       </x:c>
       <x:c r="U21" s="3" t="s">
         <x:v>2</x:v>
@@ -11952,31 +11919,31 @@
     </x:row>
     <x:row r="22" ht="93.25" hidden="0">
       <x:c r="A22" s="3" t="s">
-        <x:v>1300</x:v>
+        <x:v>1289</x:v>
       </x:c>
       <x:c r="B22" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C22" s="3" t="s">
-        <x:v>1301</x:v>
+        <x:v>1290</x:v>
       </x:c>
       <x:c r="D22" s="3" t="s">
-        <x:v>1302</x:v>
+        <x:v>1291</x:v>
       </x:c>
       <x:c r="E22" s="3" t="s">
-        <x:v>1303</x:v>
+        <x:v>1292</x:v>
       </x:c>
       <x:c r="F22" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G22" s="3" t="s">
-        <x:v>1070</x:v>
+        <x:v>1059</x:v>
       </x:c>
       <x:c r="H22" s="3" t="s">
-        <x:v>1071</x:v>
+        <x:v>1060</x:v>
       </x:c>
       <x:c r="I22" s="3" t="s">
-        <x:v>1072</x:v>
+        <x:v>1061</x:v>
       </x:c>
       <x:c r="J22" s="3" t="s">
         <x:v>42</x:v>
@@ -11985,31 +11952,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L22" s="3" t="s">
-        <x:v>1304</x:v>
+        <x:v>1293</x:v>
       </x:c>
       <x:c r="M22" s="3" t="s">
-        <x:v>1169</x:v>
+        <x:v>1158</x:v>
       </x:c>
       <x:c r="N22" s="3" t="s">
-        <x:v>1305</x:v>
+        <x:v>1294</x:v>
       </x:c>
       <x:c r="O22" s="3" t="s">
-        <x:v>1306</x:v>
+        <x:v>1295</x:v>
       </x:c>
       <x:c r="P22" s="3" t="s">
-        <x:v>1307</x:v>
+        <x:v>1296</x:v>
       </x:c>
       <x:c r="Q22" s="3" t="s">
-        <x:v>1308</x:v>
+        <x:v>1297</x:v>
       </x:c>
       <x:c r="R22" s="3" t="s">
-        <x:v>1309</x:v>
+        <x:v>1298</x:v>
       </x:c>
       <x:c r="S22" s="3" t="s">
-        <x:v>1310</x:v>
+        <x:v>1299</x:v>
       </x:c>
       <x:c r="T22" s="3" t="s">
-        <x:v>1311</x:v>
+        <x:v>1300</x:v>
       </x:c>
       <x:c r="U22" s="3" t="s">
         <x:v>2</x:v>
@@ -12017,31 +11984,31 @@
     </x:row>
     <x:row r="23" ht="93.25" hidden="0">
       <x:c r="A23" s="3" t="s">
-        <x:v>1312</x:v>
+        <x:v>1301</x:v>
       </x:c>
       <x:c r="B23" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C23" s="3" t="s">
-        <x:v>1313</x:v>
+        <x:v>1302</x:v>
       </x:c>
       <x:c r="D23" s="3" t="s">
-        <x:v>1314</x:v>
+        <x:v>1303</x:v>
       </x:c>
       <x:c r="E23" s="3" t="s">
-        <x:v>1315</x:v>
+        <x:v>1304</x:v>
       </x:c>
       <x:c r="F23" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G23" s="3" t="s">
-        <x:v>1070</x:v>
+        <x:v>1059</x:v>
       </x:c>
       <x:c r="H23" s="3" t="s">
-        <x:v>1071</x:v>
+        <x:v>1060</x:v>
       </x:c>
       <x:c r="I23" s="3" t="s">
-        <x:v>1072</x:v>
+        <x:v>1061</x:v>
       </x:c>
       <x:c r="J23" s="3" t="s">
         <x:v>42</x:v>
@@ -12050,31 +12017,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L23" s="3" t="s">
-        <x:v>1316</x:v>
+        <x:v>1305</x:v>
       </x:c>
       <x:c r="M23" s="3" t="s">
-        <x:v>1317</x:v>
+        <x:v>1306</x:v>
       </x:c>
       <x:c r="N23" s="3" t="s">
-        <x:v>1318</x:v>
+        <x:v>1307</x:v>
       </x:c>
       <x:c r="O23" s="3" t="s">
-        <x:v>1319</x:v>
+        <x:v>1308</x:v>
       </x:c>
       <x:c r="P23" s="3" t="s">
-        <x:v>1320</x:v>
+        <x:v>1309</x:v>
       </x:c>
       <x:c r="Q23" s="3" t="s">
-        <x:v>1321</x:v>
+        <x:v>1310</x:v>
       </x:c>
       <x:c r="R23" s="3" t="s">
-        <x:v>1322</x:v>
+        <x:v>1311</x:v>
       </x:c>
       <x:c r="S23" s="3" t="s">
-        <x:v>1323</x:v>
+        <x:v>1312</x:v>
       </x:c>
       <x:c r="T23" s="3" t="s">
-        <x:v>1324</x:v>
+        <x:v>1313</x:v>
       </x:c>
       <x:c r="U23" s="3" t="s">
         <x:v>2</x:v>
@@ -12082,31 +12049,31 @@
     </x:row>
     <x:row r="24" ht="79.25" hidden="0">
       <x:c r="A24" s="3" t="s">
-        <x:v>1325</x:v>
+        <x:v>1314</x:v>
       </x:c>
       <x:c r="B24" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C24" s="3" t="s">
-        <x:v>1326</x:v>
+        <x:v>1315</x:v>
       </x:c>
       <x:c r="D24" s="3" t="s">
-        <x:v>1327</x:v>
+        <x:v>1316</x:v>
       </x:c>
       <x:c r="E24" s="3" t="s">
-        <x:v>1328</x:v>
+        <x:v>1317</x:v>
       </x:c>
       <x:c r="F24" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G24" s="3" t="s">
-        <x:v>1070</x:v>
+        <x:v>1059</x:v>
       </x:c>
       <x:c r="H24" s="3" t="s">
-        <x:v>1071</x:v>
+        <x:v>1060</x:v>
       </x:c>
       <x:c r="I24" s="3" t="s">
-        <x:v>1072</x:v>
+        <x:v>1061</x:v>
       </x:c>
       <x:c r="J24" s="3" t="s">
         <x:v>42</x:v>
@@ -12115,31 +12082,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L24" s="3" t="s">
-        <x:v>1329</x:v>
+        <x:v>1318</x:v>
       </x:c>
       <x:c r="M24" s="3" t="s">
-        <x:v>1294</x:v>
+        <x:v>1283</x:v>
       </x:c>
       <x:c r="N24" s="3" t="s">
-        <x:v>1330</x:v>
+        <x:v>1319</x:v>
       </x:c>
       <x:c r="O24" s="3" t="s">
-        <x:v>1331</x:v>
+        <x:v>1320</x:v>
       </x:c>
       <x:c r="P24" s="3" t="s">
-        <x:v>1332</x:v>
+        <x:v>1321</x:v>
       </x:c>
       <x:c r="Q24" s="3" t="s">
-        <x:v>1333</x:v>
+        <x:v>1322</x:v>
       </x:c>
       <x:c r="R24" s="3" t="s">
-        <x:v>1334</x:v>
+        <x:v>1323</x:v>
       </x:c>
       <x:c r="S24" s="3" t="s">
-        <x:v>1335</x:v>
+        <x:v>1324</x:v>
       </x:c>
       <x:c r="T24" s="3" t="s">
-        <x:v>1336</x:v>
+        <x:v>1325</x:v>
       </x:c>
       <x:c r="U24" s="3" t="s">
         <x:v>2</x:v>
@@ -12147,31 +12114,31 @@
     </x:row>
     <x:row r="25" ht="79.25" hidden="0">
       <x:c r="A25" s="3" t="s">
-        <x:v>1337</x:v>
+        <x:v>1326</x:v>
       </x:c>
       <x:c r="B25" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C25" s="3" t="s">
-        <x:v>1338</x:v>
+        <x:v>1327</x:v>
       </x:c>
       <x:c r="D25" s="3" t="s">
-        <x:v>1339</x:v>
+        <x:v>1328</x:v>
       </x:c>
       <x:c r="E25" s="3" t="s">
-        <x:v>1340</x:v>
+        <x:v>1329</x:v>
       </x:c>
       <x:c r="F25" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G25" s="3" t="s">
-        <x:v>1070</x:v>
+        <x:v>1059</x:v>
       </x:c>
       <x:c r="H25" s="3" t="s">
-        <x:v>1071</x:v>
+        <x:v>1060</x:v>
       </x:c>
       <x:c r="I25" s="3" t="s">
-        <x:v>1072</x:v>
+        <x:v>1061</x:v>
       </x:c>
       <x:c r="J25" s="3" t="s">
         <x:v>42</x:v>
@@ -12180,31 +12147,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L25" s="3" t="s">
-        <x:v>1341</x:v>
+        <x:v>1330</x:v>
       </x:c>
       <x:c r="M25" s="3" t="s">
-        <x:v>1294</x:v>
+        <x:v>1283</x:v>
       </x:c>
       <x:c r="N25" s="3" t="s">
-        <x:v>1342</x:v>
+        <x:v>1331</x:v>
       </x:c>
       <x:c r="O25" s="3" t="s">
-        <x:v>1343</x:v>
+        <x:v>1332</x:v>
       </x:c>
       <x:c r="P25" s="3" t="s">
-        <x:v>1344</x:v>
+        <x:v>1333</x:v>
       </x:c>
       <x:c r="Q25" s="3" t="s">
-        <x:v>1345</x:v>
+        <x:v>1334</x:v>
       </x:c>
       <x:c r="R25" s="3" t="s">
-        <x:v>1346</x:v>
+        <x:v>1335</x:v>
       </x:c>
       <x:c r="S25" s="3" t="s">
-        <x:v>1347</x:v>
+        <x:v>1336</x:v>
       </x:c>
       <x:c r="T25" s="3" t="s">
-        <x:v>1348</x:v>
+        <x:v>1337</x:v>
       </x:c>
       <x:c r="U25" s="3" t="s">
         <x:v>2</x:v>
@@ -12212,31 +12179,31 @@
     </x:row>
     <x:row r="26" ht="79.25" hidden="0">
       <x:c r="A26" s="3" t="s">
-        <x:v>1349</x:v>
+        <x:v>1338</x:v>
       </x:c>
       <x:c r="B26" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C26" s="3" t="s">
-        <x:v>1350</x:v>
+        <x:v>1339</x:v>
       </x:c>
       <x:c r="D26" s="3" t="s">
-        <x:v>1351</x:v>
+        <x:v>1340</x:v>
       </x:c>
       <x:c r="E26" s="3" t="s">
-        <x:v>1352</x:v>
+        <x:v>1341</x:v>
       </x:c>
       <x:c r="F26" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G26" s="3" t="s">
-        <x:v>1070</x:v>
+        <x:v>1059</x:v>
       </x:c>
       <x:c r="H26" s="3" t="s">
-        <x:v>1071</x:v>
+        <x:v>1060</x:v>
       </x:c>
       <x:c r="I26" s="3" t="s">
-        <x:v>1072</x:v>
+        <x:v>1061</x:v>
       </x:c>
       <x:c r="J26" s="3" t="s">
         <x:v>42</x:v>
@@ -12245,31 +12212,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L26" s="3" t="s">
-        <x:v>1353</x:v>
+        <x:v>1342</x:v>
       </x:c>
       <x:c r="M26" s="3" t="s">
-        <x:v>1354</x:v>
+        <x:v>1343</x:v>
       </x:c>
       <x:c r="N26" s="3" t="s">
-        <x:v>1355</x:v>
+        <x:v>1344</x:v>
       </x:c>
       <x:c r="O26" s="3" t="s">
-        <x:v>1356</x:v>
+        <x:v>1345</x:v>
       </x:c>
       <x:c r="P26" s="3" t="s">
-        <x:v>1357</x:v>
+        <x:v>1346</x:v>
       </x:c>
       <x:c r="Q26" s="3" t="s">
-        <x:v>1358</x:v>
+        <x:v>1347</x:v>
       </x:c>
       <x:c r="R26" s="3" t="s">
-        <x:v>1359</x:v>
+        <x:v>1348</x:v>
       </x:c>
       <x:c r="S26" s="3" t="s">
-        <x:v>1360</x:v>
+        <x:v>1349</x:v>
       </x:c>
       <x:c r="T26" s="3" t="s">
-        <x:v>1361</x:v>
+        <x:v>1350</x:v>
       </x:c>
       <x:c r="U26" s="3" t="s">
         <x:v>2</x:v>
@@ -12277,31 +12244,31 @@
     </x:row>
     <x:row r="27" ht="79.25" hidden="0">
       <x:c r="A27" s="3" t="s">
-        <x:v>1362</x:v>
+        <x:v>1351</x:v>
       </x:c>
       <x:c r="B27" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C27" s="3" t="s">
-        <x:v>1363</x:v>
+        <x:v>1352</x:v>
       </x:c>
       <x:c r="D27" s="3" t="s">
-        <x:v>1364</x:v>
+        <x:v>1353</x:v>
       </x:c>
       <x:c r="E27" s="3" t="s">
-        <x:v>1365</x:v>
+        <x:v>1354</x:v>
       </x:c>
       <x:c r="F27" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G27" s="3" t="s">
-        <x:v>1070</x:v>
+        <x:v>1059</x:v>
       </x:c>
       <x:c r="H27" s="3" t="s">
-        <x:v>1071</x:v>
+        <x:v>1060</x:v>
       </x:c>
       <x:c r="I27" s="3" t="s">
-        <x:v>1072</x:v>
+        <x:v>1061</x:v>
       </x:c>
       <x:c r="J27" s="3" t="s">
         <x:v>42</x:v>
@@ -12310,31 +12277,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L27" s="3" t="s">
-        <x:v>1366</x:v>
+        <x:v>1355</x:v>
       </x:c>
       <x:c r="M27" s="3" t="s">
-        <x:v>1367</x:v>
+        <x:v>1356</x:v>
       </x:c>
       <x:c r="N27" s="3" t="s">
-        <x:v>1368</x:v>
+        <x:v>1357</x:v>
       </x:c>
       <x:c r="O27" s="3" t="s">
-        <x:v>1369</x:v>
+        <x:v>1358</x:v>
       </x:c>
       <x:c r="P27" s="3" t="s">
-        <x:v>1370</x:v>
+        <x:v>1359</x:v>
       </x:c>
       <x:c r="Q27" s="3" t="s">
-        <x:v>1371</x:v>
+        <x:v>1360</x:v>
       </x:c>
       <x:c r="R27" s="3" t="s">
-        <x:v>1372</x:v>
+        <x:v>1361</x:v>
       </x:c>
       <x:c r="S27" s="3" t="s">
         <x:v>789</x:v>
       </x:c>
       <x:c r="T27" s="3" t="s">
-        <x:v>1373</x:v>
+        <x:v>1362</x:v>
       </x:c>
       <x:c r="U27" s="3" t="s">
         <x:v>2</x:v>
@@ -12342,31 +12309,31 @@
     </x:row>
     <x:row r="28" ht="93.25" hidden="0">
       <x:c r="A28" s="3" t="s">
-        <x:v>1374</x:v>
+        <x:v>1363</x:v>
       </x:c>
       <x:c r="B28" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C28" s="3" t="s">
-        <x:v>1375</x:v>
+        <x:v>1364</x:v>
       </x:c>
       <x:c r="D28" s="3" t="s">
-        <x:v>1376</x:v>
+        <x:v>1365</x:v>
       </x:c>
       <x:c r="E28" s="3" t="s">
-        <x:v>1377</x:v>
+        <x:v>1366</x:v>
       </x:c>
       <x:c r="F28" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G28" s="3" t="s">
-        <x:v>1070</x:v>
+        <x:v>1059</x:v>
       </x:c>
       <x:c r="H28" s="3" t="s">
-        <x:v>1071</x:v>
+        <x:v>1060</x:v>
       </x:c>
       <x:c r="I28" s="3" t="s">
-        <x:v>1072</x:v>
+        <x:v>1061</x:v>
       </x:c>
       <x:c r="J28" s="3" t="s">
         <x:v>42</x:v>
@@ -12375,31 +12342,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L28" s="3" t="s">
-        <x:v>1378</x:v>
+        <x:v>1367</x:v>
       </x:c>
       <x:c r="M28" s="3" t="s">
-        <x:v>1379</x:v>
+        <x:v>1368</x:v>
       </x:c>
       <x:c r="N28" s="3" t="s">
-        <x:v>1380</x:v>
+        <x:v>1369</x:v>
       </x:c>
       <x:c r="O28" s="3" t="s">
-        <x:v>1381</x:v>
+        <x:v>1370</x:v>
       </x:c>
       <x:c r="P28" s="3" t="s">
-        <x:v>1382</x:v>
+        <x:v>1371</x:v>
       </x:c>
       <x:c r="Q28" s="3" t="s">
-        <x:v>1383</x:v>
+        <x:v>1372</x:v>
       </x:c>
       <x:c r="R28" s="3" t="s">
-        <x:v>1384</x:v>
+        <x:v>1373</x:v>
       </x:c>
       <x:c r="S28" s="3" t="s">
         <x:v>286</x:v>
       </x:c>
       <x:c r="T28" s="3" t="s">
-        <x:v>1385</x:v>
+        <x:v>1374</x:v>
       </x:c>
       <x:c r="U28" s="3" t="s">
         <x:v>2</x:v>
@@ -12407,31 +12374,31 @@
     </x:row>
     <x:row r="29" ht="93.25" hidden="0">
       <x:c r="A29" s="3" t="s">
-        <x:v>1386</x:v>
+        <x:v>1375</x:v>
       </x:c>
       <x:c r="B29" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C29" s="3" t="s">
-        <x:v>1387</x:v>
+        <x:v>1376</x:v>
       </x:c>
       <x:c r="D29" s="3" t="s">
-        <x:v>1388</x:v>
+        <x:v>1377</x:v>
       </x:c>
       <x:c r="E29" s="3" t="s">
-        <x:v>1389</x:v>
+        <x:v>1378</x:v>
       </x:c>
       <x:c r="F29" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G29" s="3" t="s">
-        <x:v>1070</x:v>
+        <x:v>1059</x:v>
       </x:c>
       <x:c r="H29" s="3" t="s">
-        <x:v>1071</x:v>
+        <x:v>1060</x:v>
       </x:c>
       <x:c r="I29" s="3" t="s">
-        <x:v>1072</x:v>
+        <x:v>1061</x:v>
       </x:c>
       <x:c r="J29" s="3" t="s">
         <x:v>42</x:v>
@@ -12440,31 +12407,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="L29" s="3" t="s">
-        <x:v>1390</x:v>
+        <x:v>1379</x:v>
       </x:c>
       <x:c r="M29" s="3" t="s">
-        <x:v>1391</x:v>
+        <x:v>1380</x:v>
       </x:c>
       <x:c r="N29" s="3" t="s">
-        <x:v>1392</x:v>
+        <x:v>1381</x:v>
       </x:c>
       <x:c r="O29" s="3" t="s">
-        <x:v>1393</x:v>
+        <x:v>1382</x:v>
       </x:c>
       <x:c r="P29" s="3" t="s">
-        <x:v>1394</x:v>
+        <x:v>1383</x:v>
       </x:c>
       <x:c r="Q29" s="3" t="s">
-        <x:v>1395</x:v>
+        <x:v>1384</x:v>
       </x:c>
       <x:c r="R29" s="3" t="s">
-        <x:v>1396</x:v>
+        <x:v>1385</x:v>
       </x:c>
       <x:c r="S29" s="3" t="s">
-        <x:v>1397</x:v>
+        <x:v>1386</x:v>
       </x:c>
       <x:c r="T29" s="3" t="s">
-        <x:v>1398</x:v>
+        <x:v>1387</x:v>
       </x:c>
       <x:c r="U29" s="3" t="s">
         <x:v>2</x:v>
@@ -12472,31 +12439,31 @@
     </x:row>
     <x:row r="30" ht="93.25" hidden="0">
       <x:c r="A30" s="3" t="s">
-        <x:v>1399</x:v>
+        <x:v>1388</x:v>
       </x:c>
       <x:c r="B30" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C30" s="3" t="s">
-        <x:v>1400</x:v>
+        <x:v>1389</x:v>
       </x:c>
       <x:c r="D30" s="3" t="s">
-        <x:v>1401</x:v>
+        <x:v>1390</x:v>
       </x:c>
       <x:c r="E30" s="3" t="s">
-        <x:v>1402</x:v>
+        <x:v>1391</x:v>
       </x:c>
       <x:c r="F30" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G30" s="3" t="s">
-        <x:v>1070</x:v>
+        <x:v>1059</x:v>
       </x:c>
       <x:c r="H30" s="3" t="s">
-        <x:v>1071</x:v>
+        <x:v>1060</x:v>
       </x:c>
       <x:c r="I30" s="3" t="s">
-        <x:v>1072</x:v>
+        <x:v>1061</x:v>
       </x:c>
       <x:c r="J30" s="3" t="s">
         <x:v>42</x:v>
@@ -12505,31 +12472,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L30" s="3" t="s">
-        <x:v>1403</x:v>
+        <x:v>1392</x:v>
       </x:c>
       <x:c r="M30" s="3" t="s">
-        <x:v>1404</x:v>
+        <x:v>1393</x:v>
       </x:c>
       <x:c r="N30" s="3" t="s">
-        <x:v>1405</x:v>
+        <x:v>1394</x:v>
       </x:c>
       <x:c r="O30" s="3" t="s">
-        <x:v>1406</x:v>
+        <x:v>1395</x:v>
       </x:c>
       <x:c r="P30" s="3" t="s">
-        <x:v>1407</x:v>
+        <x:v>1396</x:v>
       </x:c>
       <x:c r="Q30" s="3" t="s">
-        <x:v>1408</x:v>
+        <x:v>1397</x:v>
       </x:c>
       <x:c r="R30" s="3" t="s">
-        <x:v>1409</x:v>
+        <x:v>1398</x:v>
       </x:c>
       <x:c r="S30" s="3" t="s">
-        <x:v>1410</x:v>
+        <x:v>1399</x:v>
       </x:c>
       <x:c r="T30" s="3" t="s">
-        <x:v>1411</x:v>
+        <x:v>1400</x:v>
       </x:c>
       <x:c r="U30" s="3" t="s">
         <x:v>2</x:v>
@@ -12537,7 +12504,7 @@
     </x:row>
     <x:row r="31" ht="93.25" hidden="0">
       <x:c r="A31" s="3" t="s">
-        <x:v>1412</x:v>
+        <x:v>1401</x:v>
       </x:c>
       <x:c r="B31" s="3" t="s">
         <x:v>9</x:v>
@@ -12546,22 +12513,22 @@
         <x:v>947</x:v>
       </x:c>
       <x:c r="D31" s="3" t="s">
-        <x:v>1413</x:v>
+        <x:v>1402</x:v>
       </x:c>
       <x:c r="E31" s="3" t="s">
-        <x:v>1414</x:v>
+        <x:v>1403</x:v>
       </x:c>
       <x:c r="F31" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G31" s="3" t="s">
-        <x:v>1070</x:v>
+        <x:v>1059</x:v>
       </x:c>
       <x:c r="H31" s="3" t="s">
-        <x:v>1071</x:v>
+        <x:v>1060</x:v>
       </x:c>
       <x:c r="I31" s="3" t="s">
-        <x:v>1072</x:v>
+        <x:v>1061</x:v>
       </x:c>
       <x:c r="J31" s="3" t="s">
         <x:v>42</x:v>
@@ -12570,31 +12537,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="L31" s="3" t="s">
-        <x:v>1415</x:v>
+        <x:v>1404</x:v>
       </x:c>
       <x:c r="M31" s="3" t="s">
-        <x:v>1416</x:v>
+        <x:v>1405</x:v>
       </x:c>
       <x:c r="N31" s="3" t="s">
-        <x:v>1417</x:v>
+        <x:v>1406</x:v>
       </x:c>
       <x:c r="O31" s="3" t="s">
-        <x:v>1418</x:v>
+        <x:v>1407</x:v>
       </x:c>
       <x:c r="P31" s="3" t="s">
-        <x:v>1419</x:v>
+        <x:v>1408</x:v>
       </x:c>
       <x:c r="Q31" s="3" t="s">
-        <x:v>1420</x:v>
+        <x:v>1409</x:v>
       </x:c>
       <x:c r="R31" s="3" t="s">
-        <x:v>1421</x:v>
+        <x:v>1410</x:v>
       </x:c>
       <x:c r="S31" s="3" t="s">
-        <x:v>1422</x:v>
+        <x:v>1411</x:v>
       </x:c>
       <x:c r="T31" s="3" t="s">
-        <x:v>1423</x:v>
+        <x:v>1412</x:v>
       </x:c>
       <x:c r="U31" s="3" t="s">
         <x:v>2</x:v>
@@ -12602,31 +12569,31 @@
     </x:row>
     <x:row r="32" ht="93.25" hidden="0">
       <x:c r="A32" s="3" t="s">
-        <x:v>1424</x:v>
+        <x:v>1413</x:v>
       </x:c>
       <x:c r="B32" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C32" s="3" t="s">
-        <x:v>1425</x:v>
+        <x:v>1414</x:v>
       </x:c>
       <x:c r="D32" s="3" t="s">
-        <x:v>1426</x:v>
+        <x:v>1415</x:v>
       </x:c>
       <x:c r="E32" s="3" t="s">
-        <x:v>1427</x:v>
+        <x:v>1416</x:v>
       </x:c>
       <x:c r="F32" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G32" s="3" t="s">
-        <x:v>1070</x:v>
+        <x:v>1059</x:v>
       </x:c>
       <x:c r="H32" s="3" t="s">
-        <x:v>1071</x:v>
+        <x:v>1060</x:v>
       </x:c>
       <x:c r="I32" s="3" t="s">
-        <x:v>1072</x:v>
+        <x:v>1061</x:v>
       </x:c>
       <x:c r="J32" s="3" t="s">
         <x:v>42</x:v>
@@ -12635,31 +12602,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L32" s="3" t="s">
-        <x:v>1428</x:v>
+        <x:v>1417</x:v>
       </x:c>
       <x:c r="M32" s="3" t="s">
-        <x:v>1429</x:v>
+        <x:v>1418</x:v>
       </x:c>
       <x:c r="N32" s="3" t="s">
-        <x:v>1430</x:v>
+        <x:v>1419</x:v>
       </x:c>
       <x:c r="O32" s="3" t="s">
-        <x:v>1431</x:v>
+        <x:v>1420</x:v>
       </x:c>
       <x:c r="P32" s="3" t="s">
-        <x:v>1432</x:v>
+        <x:v>1421</x:v>
       </x:c>
       <x:c r="Q32" s="3" t="s">
-        <x:v>1433</x:v>
+        <x:v>1422</x:v>
       </x:c>
       <x:c r="R32" s="3" t="s">
         <x:v>969</x:v>
       </x:c>
       <x:c r="S32" s="3" t="s">
-        <x:v>1434</x:v>
+        <x:v>1423</x:v>
       </x:c>
       <x:c r="T32" s="3" t="s">
-        <x:v>1435</x:v>
+        <x:v>1424</x:v>
       </x:c>
       <x:c r="U32" s="3" t="s">
         <x:v>2</x:v>
@@ -12667,7 +12634,7 @@
     </x:row>
     <x:row r="33" ht="93.25" hidden="0">
       <x:c r="A33" s="3" t="s">
-        <x:v>1436</x:v>
+        <x:v>1425</x:v>
       </x:c>
       <x:c r="B33" s="3" t="s">
         <x:v>9</x:v>
@@ -12676,22 +12643,22 @@
         <x:v>740</x:v>
       </x:c>
       <x:c r="D33" s="3" t="s">
-        <x:v>1437</x:v>
+        <x:v>1426</x:v>
       </x:c>
       <x:c r="E33" s="3" t="s">
-        <x:v>1438</x:v>
+        <x:v>1427</x:v>
       </x:c>
       <x:c r="F33" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G33" s="3" t="s">
-        <x:v>1070</x:v>
+        <x:v>1059</x:v>
       </x:c>
       <x:c r="H33" s="3" t="s">
-        <x:v>1071</x:v>
+        <x:v>1060</x:v>
       </x:c>
       <x:c r="I33" s="3" t="s">
-        <x:v>1072</x:v>
+        <x:v>1061</x:v>
       </x:c>
       <x:c r="J33" s="3" t="s">
         <x:v>42</x:v>
@@ -12700,31 +12667,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L33" s="3" t="s">
-        <x:v>1439</x:v>
+        <x:v>1428</x:v>
       </x:c>
       <x:c r="M33" s="3" t="s">
-        <x:v>1440</x:v>
+        <x:v>1429</x:v>
       </x:c>
       <x:c r="N33" s="3" t="s">
-        <x:v>1441</x:v>
+        <x:v>1430</x:v>
       </x:c>
       <x:c r="O33" s="3" t="s">
-        <x:v>1442</x:v>
+        <x:v>1431</x:v>
       </x:c>
       <x:c r="P33" s="3" t="s">
-        <x:v>1443</x:v>
+        <x:v>1432</x:v>
       </x:c>
       <x:c r="Q33" s="3" t="s">
-        <x:v>1444</x:v>
+        <x:v>1433</x:v>
       </x:c>
       <x:c r="R33" s="3" t="s">
-        <x:v>1445</x:v>
+        <x:v>1434</x:v>
       </x:c>
       <x:c r="S33" s="3" t="s">
-        <x:v>1446</x:v>
+        <x:v>1435</x:v>
       </x:c>
       <x:c r="T33" s="3" t="s">
-        <x:v>1447</x:v>
+        <x:v>1436</x:v>
       </x:c>
       <x:c r="U33" s="3" t="s">
         <x:v>2</x:v>
@@ -12732,7 +12699,7 @@
     </x:row>
     <x:row r="34" ht="93.25" hidden="0">
       <x:c r="A34" s="3" t="s">
-        <x:v>1448</x:v>
+        <x:v>1437</x:v>
       </x:c>
       <x:c r="B34" s="3" t="s">
         <x:v>9</x:v>
@@ -12741,22 +12708,22 @@
         <x:v>313</x:v>
       </x:c>
       <x:c r="D34" s="3" t="s">
-        <x:v>1449</x:v>
+        <x:v>1438</x:v>
       </x:c>
       <x:c r="E34" s="3" t="s">
-        <x:v>1450</x:v>
+        <x:v>1439</x:v>
       </x:c>
       <x:c r="F34" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G34" s="3" t="s">
-        <x:v>1070</x:v>
+        <x:v>1059</x:v>
       </x:c>
       <x:c r="H34" s="3" t="s">
-        <x:v>1071</x:v>
+        <x:v>1060</x:v>
       </x:c>
       <x:c r="I34" s="3" t="s">
-        <x:v>1072</x:v>
+        <x:v>1061</x:v>
       </x:c>
       <x:c r="J34" s="3" t="s">
         <x:v>42</x:v>
@@ -12765,31 +12732,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="L34" s="3" t="s">
-        <x:v>1451</x:v>
+        <x:v>1440</x:v>
       </x:c>
       <x:c r="M34" s="3" t="s">
-        <x:v>1452</x:v>
+        <x:v>1441</x:v>
       </x:c>
       <x:c r="N34" s="3" t="s">
         <x:v>978</x:v>
       </x:c>
       <x:c r="O34" s="3" t="s">
-        <x:v>1453</x:v>
+        <x:v>1442</x:v>
       </x:c>
       <x:c r="P34" s="3" t="s">
-        <x:v>1454</x:v>
+        <x:v>1443</x:v>
       </x:c>
       <x:c r="Q34" s="3" t="s">
-        <x:v>1455</x:v>
+        <x:v>1444</x:v>
       </x:c>
       <x:c r="R34" s="3" t="s">
-        <x:v>1456</x:v>
+        <x:v>1445</x:v>
       </x:c>
       <x:c r="S34" s="3" t="s">
         <x:v>323</x:v>
       </x:c>
       <x:c r="T34" s="3" t="s">
-        <x:v>1457</x:v>
+        <x:v>1446</x:v>
       </x:c>
       <x:c r="U34" s="3" t="s">
         <x:v>2</x:v>
@@ -12797,31 +12764,31 @@
     </x:row>
     <x:row r="35" ht="93.25" hidden="0">
       <x:c r="A35" s="3" t="s">
-        <x:v>1458</x:v>
+        <x:v>1447</x:v>
       </x:c>
       <x:c r="B35" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C35" s="3" t="s">
-        <x:v>1459</x:v>
+        <x:v>1448</x:v>
       </x:c>
       <x:c r="D35" s="3" t="s">
-        <x:v>1460</x:v>
+        <x:v>1449</x:v>
       </x:c>
       <x:c r="E35" s="3" t="s">
-        <x:v>1461</x:v>
+        <x:v>1450</x:v>
       </x:c>
       <x:c r="F35" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G35" s="3" t="s">
-        <x:v>1070</x:v>
+        <x:v>1059</x:v>
       </x:c>
       <x:c r="H35" s="3" t="s">
-        <x:v>1071</x:v>
+        <x:v>1060</x:v>
       </x:c>
       <x:c r="I35" s="3" t="s">
-        <x:v>1072</x:v>
+        <x:v>1061</x:v>
       </x:c>
       <x:c r="J35" s="3" t="s">
         <x:v>42</x:v>
@@ -12830,31 +12797,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L35" s="3" t="s">
-        <x:v>1462</x:v>
+        <x:v>1451</x:v>
       </x:c>
       <x:c r="M35" s="3" t="s">
-        <x:v>1463</x:v>
+        <x:v>1452</x:v>
       </x:c>
       <x:c r="N35" s="3" t="s">
-        <x:v>1464</x:v>
+        <x:v>1453</x:v>
       </x:c>
       <x:c r="O35" s="3" t="s">
-        <x:v>1244</x:v>
+        <x:v>1233</x:v>
       </x:c>
       <x:c r="P35" s="3" t="s">
-        <x:v>1465</x:v>
+        <x:v>1454</x:v>
       </x:c>
       <x:c r="Q35" s="3" t="s">
-        <x:v>1466</x:v>
+        <x:v>1455</x:v>
       </x:c>
       <x:c r="R35" s="3" t="s">
-        <x:v>1467</x:v>
+        <x:v>1456</x:v>
       </x:c>
       <x:c r="S35" s="3" t="s">
-        <x:v>1468</x:v>
+        <x:v>1457</x:v>
       </x:c>
       <x:c r="T35" s="3" t="s">
-        <x:v>1469</x:v>
+        <x:v>1458</x:v>
       </x:c>
       <x:c r="U35" s="3" t="s">
         <x:v>2</x:v>
@@ -12862,31 +12829,31 @@
     </x:row>
     <x:row r="36" ht="93.25" hidden="0">
       <x:c r="A36" s="3" t="s">
-        <x:v>1470</x:v>
+        <x:v>1459</x:v>
       </x:c>
       <x:c r="B36" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C36" s="3" t="s">
-        <x:v>1471</x:v>
+        <x:v>1460</x:v>
       </x:c>
       <x:c r="D36" s="3" t="s">
-        <x:v>1472</x:v>
+        <x:v>1461</x:v>
       </x:c>
       <x:c r="E36" s="3" t="s">
-        <x:v>1473</x:v>
+        <x:v>1462</x:v>
       </x:c>
       <x:c r="F36" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G36" s="3" t="s">
-        <x:v>1070</x:v>
+        <x:v>1059</x:v>
       </x:c>
       <x:c r="H36" s="3" t="s">
-        <x:v>1071</x:v>
+        <x:v>1060</x:v>
       </x:c>
       <x:c r="I36" s="3" t="s">
-        <x:v>1072</x:v>
+        <x:v>1061</x:v>
       </x:c>
       <x:c r="J36" s="3" t="s">
         <x:v>42</x:v>
@@ -12895,31 +12862,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L36" s="3" t="s">
-        <x:v>1474</x:v>
+        <x:v>1463</x:v>
       </x:c>
       <x:c r="M36" s="3" t="s">
-        <x:v>1074</x:v>
+        <x:v>1063</x:v>
       </x:c>
       <x:c r="N36" s="3" t="s">
-        <x:v>1475</x:v>
+        <x:v>1464</x:v>
       </x:c>
       <x:c r="O36" s="3" t="s">
-        <x:v>1476</x:v>
+        <x:v>1465</x:v>
       </x:c>
       <x:c r="P36" s="3" t="s">
-        <x:v>1477</x:v>
+        <x:v>1466</x:v>
       </x:c>
       <x:c r="Q36" s="3" t="s">
-        <x:v>1478</x:v>
+        <x:v>1467</x:v>
       </x:c>
       <x:c r="R36" s="3" t="s">
-        <x:v>1479</x:v>
+        <x:v>1468</x:v>
       </x:c>
       <x:c r="S36" s="3" t="s">
-        <x:v>1480</x:v>
+        <x:v>1469</x:v>
       </x:c>
       <x:c r="T36" s="3" t="s">
-        <x:v>1481</x:v>
+        <x:v>1470</x:v>
       </x:c>
       <x:c r="U36" s="3" t="s">
         <x:v>2</x:v>
@@ -12927,31 +12894,31 @@
     </x:row>
     <x:row r="37" ht="93.25" hidden="0">
       <x:c r="A37" s="3" t="s">
-        <x:v>1482</x:v>
+        <x:v>1471</x:v>
       </x:c>
       <x:c r="B37" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C37" s="3" t="s">
-        <x:v>1483</x:v>
+        <x:v>1472</x:v>
       </x:c>
       <x:c r="D37" s="3" t="s">
-        <x:v>1484</x:v>
+        <x:v>1473</x:v>
       </x:c>
       <x:c r="E37" s="3" t="s">
-        <x:v>1485</x:v>
+        <x:v>1474</x:v>
       </x:c>
       <x:c r="F37" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G37" s="3" t="s">
-        <x:v>1070</x:v>
+        <x:v>1059</x:v>
       </x:c>
       <x:c r="H37" s="3" t="s">
-        <x:v>1071</x:v>
+        <x:v>1060</x:v>
       </x:c>
       <x:c r="I37" s="3" t="s">
-        <x:v>1072</x:v>
+        <x:v>1061</x:v>
       </x:c>
       <x:c r="J37" s="3" t="s">
         <x:v>42</x:v>
@@ -12960,31 +12927,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L37" s="3" t="s">
-        <x:v>1486</x:v>
+        <x:v>1475</x:v>
       </x:c>
       <x:c r="M37" s="3" t="s">
-        <x:v>1487</x:v>
+        <x:v>1476</x:v>
       </x:c>
       <x:c r="N37" s="3" t="s">
-        <x:v>1488</x:v>
+        <x:v>1477</x:v>
       </x:c>
       <x:c r="O37" s="3" t="s">
-        <x:v>1489</x:v>
+        <x:v>1478</x:v>
       </x:c>
       <x:c r="P37" s="3" t="s">
-        <x:v>1490</x:v>
+        <x:v>1479</x:v>
       </x:c>
       <x:c r="Q37" s="3" t="s">
-        <x:v>1491</x:v>
+        <x:v>1480</x:v>
       </x:c>
       <x:c r="R37" s="3" t="s">
-        <x:v>1492</x:v>
+        <x:v>1481</x:v>
       </x:c>
       <x:c r="S37" s="3" t="s">
-        <x:v>1493</x:v>
+        <x:v>1482</x:v>
       </x:c>
       <x:c r="T37" s="3" t="s">
-        <x:v>1487</x:v>
+        <x:v>1476</x:v>
       </x:c>
       <x:c r="U37" s="3" t="s">
         <x:v>2</x:v>
@@ -12992,31 +12959,31 @@
     </x:row>
     <x:row r="38" ht="93.25" hidden="0">
       <x:c r="A38" s="3" t="s">
-        <x:v>1494</x:v>
+        <x:v>1483</x:v>
       </x:c>
       <x:c r="B38" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C38" s="3" t="s">
-        <x:v>1495</x:v>
+        <x:v>1484</x:v>
       </x:c>
       <x:c r="D38" s="3" t="s">
-        <x:v>1496</x:v>
+        <x:v>1485</x:v>
       </x:c>
       <x:c r="E38" s="3" t="s">
-        <x:v>1497</x:v>
+        <x:v>1486</x:v>
       </x:c>
       <x:c r="F38" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G38" s="3" t="s">
-        <x:v>1070</x:v>
+        <x:v>1059</x:v>
       </x:c>
       <x:c r="H38" s="3" t="s">
-        <x:v>1071</x:v>
+        <x:v>1060</x:v>
       </x:c>
       <x:c r="I38" s="3" t="s">
-        <x:v>1072</x:v>
+        <x:v>1061</x:v>
       </x:c>
       <x:c r="J38" s="3" t="s">
         <x:v>42</x:v>
@@ -13025,31 +12992,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L38" s="3" t="s">
-        <x:v>1498</x:v>
+        <x:v>1487</x:v>
       </x:c>
       <x:c r="M38" s="3" t="s">
-        <x:v>1169</x:v>
+        <x:v>1158</x:v>
       </x:c>
       <x:c r="N38" s="3" t="s">
-        <x:v>1499</x:v>
+        <x:v>1488</x:v>
       </x:c>
       <x:c r="O38" s="3" t="s">
-        <x:v>1500</x:v>
+        <x:v>1489</x:v>
       </x:c>
       <x:c r="P38" s="3" t="s">
-        <x:v>1501</x:v>
+        <x:v>1490</x:v>
       </x:c>
       <x:c r="Q38" s="3" t="s">
-        <x:v>1502</x:v>
+        <x:v>1491</x:v>
       </x:c>
       <x:c r="R38" s="3" t="s">
-        <x:v>1503</x:v>
+        <x:v>1492</x:v>
       </x:c>
       <x:c r="S38" s="3" t="s">
-        <x:v>1504</x:v>
+        <x:v>1493</x:v>
       </x:c>
       <x:c r="T38" s="3" t="s">
-        <x:v>1505</x:v>
+        <x:v>1494</x:v>
       </x:c>
       <x:c r="U38" s="3" t="s">
         <x:v>2</x:v>
@@ -13057,31 +13024,31 @@
     </x:row>
     <x:row r="39" ht="93.25" hidden="0">
       <x:c r="A39" s="3" t="s">
-        <x:v>1506</x:v>
+        <x:v>1495</x:v>
       </x:c>
       <x:c r="B39" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C39" s="3" t="s">
-        <x:v>1507</x:v>
+        <x:v>1496</x:v>
       </x:c>
       <x:c r="D39" s="3" t="s">
-        <x:v>1508</x:v>
+        <x:v>1497</x:v>
       </x:c>
       <x:c r="E39" s="3" t="s">
-        <x:v>1509</x:v>
+        <x:v>1498</x:v>
       </x:c>
       <x:c r="F39" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G39" s="3" t="s">
-        <x:v>1070</x:v>
+        <x:v>1059</x:v>
       </x:c>
       <x:c r="H39" s="3" t="s">
-        <x:v>1071</x:v>
+        <x:v>1060</x:v>
       </x:c>
       <x:c r="I39" s="3" t="s">
-        <x:v>1072</x:v>
+        <x:v>1061</x:v>
       </x:c>
       <x:c r="J39" s="3" t="s">
         <x:v>42</x:v>
@@ -13090,31 +13057,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="L39" s="3" t="s">
-        <x:v>1510</x:v>
+        <x:v>1499</x:v>
       </x:c>
       <x:c r="M39" s="3" t="s">
-        <x:v>1074</x:v>
+        <x:v>1063</x:v>
       </x:c>
       <x:c r="N39" s="3" t="s">
-        <x:v>1511</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="O39" s="3" t="s">
-        <x:v>1512</x:v>
+        <x:v>1501</x:v>
       </x:c>
       <x:c r="P39" s="3" t="s">
-        <x:v>1513</x:v>
+        <x:v>1502</x:v>
       </x:c>
       <x:c r="Q39" s="3" t="s">
-        <x:v>1514</x:v>
+        <x:v>1503</x:v>
       </x:c>
       <x:c r="R39" s="3" t="s">
-        <x:v>1515</x:v>
+        <x:v>1504</x:v>
       </x:c>
       <x:c r="S39" s="3" t="s">
-        <x:v>1516</x:v>
+        <x:v>1505</x:v>
       </x:c>
       <x:c r="T39" s="3" t="s">
-        <x:v>1517</x:v>
+        <x:v>1506</x:v>
       </x:c>
       <x:c r="U39" s="3" t="s">
         <x:v>2</x:v>
@@ -13123,7 +13090,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6c04358f949c462e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f54db87c1ad4ca1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/maliev-feature-user-story-status.xlsx
+++ b/docs/maliev-feature-user-story-status.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R2ca833d25ca7421c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="Rf07ec86ee54748d3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R6ca524d069f040c7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="R2145cbf2f9014f46"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rd44522217a6a44c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="Re5fdab6d002c462b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="Rb5127f55e28a4d94"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="Rb1fd8cbccec34c9e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5264,7 +5264,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R616da65d0cb24080"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ae175a149ca4a63"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8363,55 +8363,55 @@
         <x:v>Payment operations</x:v>
       </x:c>
       <x:c r="D48" s="3" t="str">
-        <x:v>As a finance employee, I can review payment stats, inspect payments, create payments, allocate funds, and void payments.</x:v>
+        <x:v>As a finance employee, I can review payment stats, inspect payment records through the BFF, and record invoice payments from the invoice detail flow.</x:v>
       </x:c>
       <x:c r="E48" s="3" t="str">
-        <x:v>Payments BFF exposes stats, list, detail, create, allocate, and void actions with payment permissions.</x:v>
+        <x:v>Payment stats load in the invoice list, payment list/detail/create endpoints fail closed when PaymentService does not return data, invoice detail records and allocates payments through InvoiceService, and unsupported direct allocate/void actions return 404.</x:v>
       </x:c>
       <x:c r="F48" s="3" t="str">
-        <x:v>Current code-derived</x:v>
+        <x:v>Current code-derived; focused fallback fix applied.</x:v>
       </x:c>
       <x:c r="G48" s="3" t="str">
-        <x:v>Inventory added 2026-06-23; dedicated behavior test not started in this spreadsheet-only slice.</x:v>
+        <x:v>Focused behavior tests passed 2026-06-23.</x:v>
       </x:c>
       <x:c r="H48" s="3" t="str">
-        <x:v>No behavior error documented yet for this newly inventoried current-code story.</x:v>
+        <x:v>Focused contract review found PaymentServiceClient.GetPaymentsAsync threw on non-success responses instead of allowing the BFF empty-page fallback when PaymentService does not expose a list response.</x:v>
       </x:c>
       <x:c r="I48" s="3" t="str">
-        <x:v>No app fix attempted in this inventory-only slice.</x:v>
+        <x:v>Fixed in Maliev.Intranet commit 776400b by changing GetPaymentsAsync to use GetAsync, return null on non-success, and deserialize only successful responses.</x:v>
       </x:c>
       <x:c r="J48" s="3" t="str">
-        <x:v>Retest after behavior testing begins.</x:v>
+        <x:v>Retested PaymentsControllerTests 14/14 passed and InvoiceServiceClientTests.RecordInvoicePayment 1/1 passed.</x:v>
       </x:c>
       <x:c r="K48" s="3" t="str">
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L48" s="3" t="str">
-        <x:v>Finance UI/BFF -&gt; PaymentService -&gt; payment DTOs and allocation/void commands</x:v>
+        <x:v>Finance invoice UI -&gt; Intranet BFF payments/invoices endpoints -&gt; PaymentService metrics/payment endpoints and InvoiceService payment allocation</x:v>
       </x:c>
       <x:c r="M48" s="3" t="str">
         <x:v>InvoiceList.razor; InvoiceDetail.razor; PaymentsController.cs</x:v>
       </x:c>
       <x:c r="N48" s="3" t="str">
-        <x:v>/finance/invoices payment stats/actions; payment operation controls</x:v>
+        <x:v>/finance/invoices loads api/v1/payments/stats; /finance/invoices/{id} record-payment panel posts api/v1/invoices/{id}/payments</x:v>
       </x:c>
       <x:c r="O48" s="3" t="str">
-        <x:v>PaymentsController stats, GET, GET {id}, POST, allocate, void</x:v>
+        <x:v>PaymentsController stats/list/detail/create proxy PaymentService; list now falls back on non-success; allocate/void return 404 because PaymentService does not expose those actions; invoice payment recording uses InvoiceService /invoice/v1/payments plus /invoice/v1/payments/invoices/{invoiceId}/link.</x:v>
       </x:c>
       <x:c r="P48" s="3" t="str">
-        <x:v>Code inventory evidence only; map automated tests during the behavior-testing loop.</x:v>
+        <x:v>Focused tests: dotnet test Maliev.Intranet.slnx --filter "FullyQualifiedName~PaymentsControllerTests" --verbosity minimal passed 14/14 on 2026-06-23. Impacted invoice payment allocation test: dotnet test Maliev.Intranet.slnx --filter "FullyQualifiedName~InvoiceServiceClientTests.RecordInvoicePayment" --verbosity minimal passed 1/1 on 2026-06-23.</x:v>
       </x:c>
       <x:c r="Q48" s="3" t="str">
-        <x:v>Intranet BFF, PaymentService, Accounting/Invoice flows</x:v>
+        <x:v>Intranet BFF, PaymentService, InvoiceService, Accounting/Invoice UI</x:v>
       </x:c>
       <x:c r="R48" s="3" t="str">
-        <x:v>Payment, allocation, and void records</x:v>
+        <x:v>Payment records and invoice payment allocations through InvoiceService; direct PaymentService list/detail reads are read-only.</x:v>
       </x:c>
       <x:c r="S48" s="3" t="str">
-        <x:v>Needs strict payment contract and permission retest.</x:v>
+        <x:v>Direct PaymentService allocate/void actions are not exposed by current PaymentService and therefore fail closed with 404; current finance UI records invoice payments through InvoiceService instead of a standalone payments page.</x:v>
       </x:c>
       <x:c r="T48" s="3" t="str">
-        <x:v>PaymentsController.cs:16-85; InvoiceList.razor:587-589; InvoiceDetail.razor:62-294</x:v>
+        <x:v>PaymentsController.cs:17-85; PaymentServiceClient.cs:16-80; PaymentsControllerTests.cs:14-216; InvoiceList.razor:587-589; InvoiceDetail.razor:82,209-218; InvoiceServiceClient.cs:140-204</x:v>
       </x:c>
       <x:c r="U48" s="3" t="str">
         <x:v>2026-06-23</x:v>
@@ -8680,7 +8680,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R59b70ff981684600"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf8d0a7674e2e43f0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11251,7 +11251,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2a71a26b85f34a87"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf7e0ce4485ab4123"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/maliev-feature-user-story-status.xlsx
+++ b/docs/maliev-feature-user-story-status.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rd44522217a6a44c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="Re5fdab6d002c462b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="Rb5127f55e28a4d94"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="Rb1fd8cbccec34c9e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R0987011c32f1450d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="Rdcbf1fd7a7b9495c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="Rd57a51a0a93e4669"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="R8cabf5f561354a2c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5264,7 +5264,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ae175a149ca4a63"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R61354ec81d3749b1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8242,16 +8242,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G46" s="3" t="str">
-        <x:v>Inventory added 2026-06-23; dedicated behavior test not started in this spreadsheet-only slice.</x:v>
+        <x:v>Focused behavior tests passed 2026-06-23.</x:v>
       </x:c>
       <x:c r="H46" s="3" t="str">
-        <x:v>No behavior error documented yet for this newly inventoried current-code story.</x:v>
+        <x:v>No behavior error observed in current focused controller/client/source retest.</x:v>
       </x:c>
       <x:c r="I46" s="3" t="str">
-        <x:v>No app fix attempted in this inventory-only slice.</x:v>
+        <x:v>No app-code fix needed; existing focused coverage validates the current notification template and preference contracts.</x:v>
       </x:c>
       <x:c r="J46" s="3" t="str">
-        <x:v>Retest after behavior testing begins.</x:v>
+        <x:v>Retested notification/preference focused set 29/29 passed.</x:v>
       </x:c>
       <x:c r="K46" s="3" t="str">
         <x:v>P1</x:v>
@@ -8269,7 +8269,7 @@
         <x:v>NotificationController templates, delivery-logs, preferences</x:v>
       </x:c>
       <x:c r="P46" s="3" t="str">
-        <x:v>Code inventory evidence only; map automated tests during the behavior-testing loop.</x:v>
+        <x:v>Focused test: dotnet test Maliev.Intranet.slnx --filter "FullyQualifiedName~NotificationControllerTests|FullyQualifiedName~NotificationServiceClientTests|FullyQualifiedName~ModuleRegressionSourceTests.CustomerDetail_EmailDialogStaysOpenAndUsesNotificationTemplates|FullyQualifiedName~HrProfilePageTests" --verbosity minimal passed 29/29 on 2026-06-23. Coverage verifies notification template CRUD/read-log/preference permissions, NotificationService template/list/create/update/event/log mapping, customer email template panel source wiring, and HR profile preference behavior.</x:v>
       </x:c>
       <x:c r="Q46" s="3" t="str">
         <x:v>Intranet BFF, NotificationService</x:v>
@@ -8278,10 +8278,10 @@
         <x:v>Notification templates and user notification preferences</x:v>
       </x:c>
       <x:c r="S46" s="3" t="str">
-        <x:v>Needs template create/update/delete browser pass.</x:v>
+        <x:v>No remaining INT-045 controller/client/source contract gap from this focused retest. Template create/update/delete browser interaction still belongs in the later authenticated browser pass.</x:v>
       </x:c>
       <x:c r="T46" s="3" t="str">
-        <x:v>NotificationController.cs:15-102; AdminPage.razor:91-165; CustomerDetail.razor:1356-1450</x:v>
+        <x:v>NotificationController.cs:23-104; NotificationServiceClient.cs:23-147,188-260; NotificationControllerTests.cs:13-143; NotificationServiceClientTests.cs:14-220; AdminPage.razor:96-166; Profile.razor:42-588; ModuleRegressionSourceTests.cs:531-544,1713-1755; HrProfilePageTests.cs:17-220</x:v>
       </x:c>
       <x:c r="U46" s="3" t="str">
         <x:v>2026-06-23</x:v>
@@ -8680,7 +8680,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf8d0a7674e2e43f0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf1057d98a9394b23"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11251,7 +11251,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf7e0ce4485ab4123"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd1f5306fffd14a02"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/maliev-feature-user-story-status.xlsx
+++ b/docs/maliev-feature-user-story-status.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R0987011c32f1450d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="Rdcbf1fd7a7b9495c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="Rd57a51a0a93e4669"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="R8cabf5f561354a2c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R3b0504d850414380"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="Rd7c3f8a3bca64615"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R1f254115860f4803"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="R8df1e79fe7664fcb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5264,7 +5264,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R61354ec81d3749b1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b7c2f7a982e4999"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5382,16 +5382,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G2" s="3" t="str">
-        <x:v>Automated Intranet suite passed 2026-06-23 after UX fix</x:v>
+        <x:v>Focused shell/navigation component tests passed 2026-06-23; standalone Testing-mode BFF reported startup before local RabbitMQ warnings.</x:v>
       </x:c>
       <x:c r="H2" s="3" t="str">
-        <x:v>No behavior error observed in current Intranet automated retest.</x:v>
+        <x:v>No shell/navigation behavior error observed in focused component/source retest. Headless browser smoke was blocked by local Playwright package resolution: installed playwright package imports missing playwright-core.</x:v>
       </x:c>
       <x:c r="I2" s="3" t="str">
-        <x:v>No fix needed for this story from current Intranet automated retest.</x:v>
+        <x:v>No app-code fix needed for this INT-001 retest; browser tooling blocker is external to Intranet source.</x:v>
       </x:c>
       <x:c r="J2" s="3" t="str">
-        <x:v>Current automated suite passed.</x:v>
+        <x:v>Retested Phase2NavLayoutTests/MainLayoutTests/ThemeToggleSourceTests 23/23 passed.</x:v>
       </x:c>
       <x:c r="K2" s="3" t="str">
         <x:v>P0</x:v>
@@ -5409,7 +5409,7 @@
         <x:v>AuthController user/session endpoints</x:v>
       </x:c>
       <x:c r="P2" s="3" t="str">
-        <x:v>Navigation/source tests where present | Current suite: dotnet test Maliev.Intranet.slnx --verbosity minimal passed 1143/1150 with 7 skipped on 2026-06-23 after fix. Initial full run failed 1/1150 on ModuleRegressionSourceTests.ClientTextInputs_UpdateOnInputInsteadOfBlur.</x:v>
+        <x:v>Focused test: dotnet test Maliev.Intranet.slnx --filter "FullyQualifiedName~Phase2NavLayoutTests|FullyQualifiedName~MainLayoutTests|FullyQualifiedName~ThemeToggleSourceTests" --verbosity minimal passed 23/23 on 2026-06-23. Standalone BFF startup command with ASPNETCORE_ENVIRONMENT=Testing and ASPNETCORE_URLS=http://localhost:5071 reported Intranet BFF started successfully; shutdown logs also showed local RabbitMQ unavailable. Attempted Playwright desktop/mobile smoke was blocked before navigation by ERR_MODULE_NOT_FOUND for playwright-core.</x:v>
       </x:c>
       <x:c r="Q2" s="3" t="str">
         <x:v>Intranet client, BFF, Auth/IAM</x:v>
@@ -5418,10 +5418,10 @@
         <x:v>User preferences/session state</x:v>
       </x:c>
       <x:c r="S2" s="3" t="str">
-        <x:v>Needs responsive shell browser pass</x:v>
+        <x:v>Responsive shell component/source behavior is covered by the current focused retest; full rendered browser screenshot evidence still requires repairing the local Playwright runtime or using a configured browser runner, and live standalone smoke still needs local RabbitMQ/Aspire infrastructure available.</x:v>
       </x:c>
       <x:c r="T2" s="3" t="str">
-        <x:v>AppNavigation.cs; NavMenu.razor; TopBar.razor</x:v>
+        <x:v>TopBar.razor:115-156,305-310,484-490,530; TopBar.razor.css:687-935; AppNavigation.cs:18-104; Phase2NavLayoutTests.cs:109-137,163-194,253-276; MainLayoutTests.cs:63-69; ThemeToggleSourceTests.cs:6-55</x:v>
       </x:c>
       <x:c r="U2" s="3" t="str">
         <x:v>2026-06-23</x:v>
@@ -8680,7 +8680,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf1057d98a9394b23"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb57dca0ab2f45a9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11251,7 +11251,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd1f5306fffd14a02"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R354e8e6e277e4583"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/maliev-feature-user-story-status.xlsx
+++ b/docs/maliev-feature-user-story-status.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R3b0504d850414380"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="Rd7c3f8a3bca64615"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R1f254115860f4803"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="R8df1e79fe7664fcb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rb6fc6c8bfb99476b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="Rb83d2d6607d345a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R16d412a382074968"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="R216536481a894d90"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5264,7 +5264,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b7c2f7a982e4999"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0c367ffb476b4e67"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8680,7 +8680,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb57dca0ab2f45a9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc131708e54ad4107"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11251,7 +11251,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R354e8e6e277e4583"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3b78f06268044bcc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/maliev-feature-user-story-status.xlsx
+++ b/docs/maliev-feature-user-story-status.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rb6fc6c8bfb99476b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="Rb83d2d6607d345a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R16d412a382074968"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="R216536481a894d90"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R66855b0ecae24a40"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="R98dfe06d765a414b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R88ea119d2ac447d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="Re1595efd25b44183"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5264,7 +5264,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0c367ffb476b4e67"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R14ed8f2df863468d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5707,16 +5707,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G7" s="3" t="str">
-        <x:v>Automated Intranet suite passed 2026-06-23 after UX fix</x:v>
+        <x:v>Focused project permission-matrix tests passed 2026-06-23.</x:v>
       </x:c>
       <x:c r="H7" s="3" t="str">
-        <x:v>No behavior error observed in current Intranet automated retest.</x:v>
+        <x:v>No permission-matrix behavior error observed in current focused retest.</x:v>
       </x:c>
       <x:c r="I7" s="3" t="str">
-        <x:v>No fix needed for this story from current Intranet automated retest.</x:v>
+        <x:v>Added missing ProjectsController permission-matrix regression coverage.</x:v>
       </x:c>
       <x:c r="J7" s="3" t="str">
-        <x:v>Current automated suite passed.</x:v>
+        <x:v>Retested ProjectsControllerTests 36/36 passed.</x:v>
       </x:c>
       <x:c r="K7" s="3" t="str">
         <x:v>P0</x:v>
@@ -5734,7 +5734,7 @@
         <x:v>ProjectsController GET/list/detail/update/delete/notes/duplicate/thumbnail</x:v>
       </x:c>
       <x:c r="P7" s="3" t="str">
-        <x:v>ProjectsControllerTests | Current suite: dotnet test Maliev.Intranet.slnx --verbosity minimal passed 1143/1150 with 7 skipped on 2026-06-23 after fix. Initial full run failed 1/1150 on ModuleRegressionSourceTests.ClientTextInputs_UpdateOnInputInsteadOfBlur.</x:v>
+        <x:v>Focused test: dotnet test Maliev.Intranet.slnx --filter "FullyQualifiedName~ProjectsControllerTests" --verbosity minimal passed 36/36 on 2026-06-23. Added ProjectEndpoints_RequireExpectedPermissionMatrix to assert class-level Project.Read for list/detail/read helpers, Project.Write for project mutations, and existing Job.Write planning-hold coverage.</x:v>
       </x:c>
       <x:c r="Q7" s="3" t="str">
         <x:v>Intranet BFF, Project/Quote services, Storage</x:v>
@@ -5743,10 +5743,10 @@
         <x:v>Projects, notes, duplicate records</x:v>
       </x:c>
       <x:c r="S7" s="3" t="str">
-        <x:v>Needs permission matrix retest</x:v>
+        <x:v>No remaining permission-matrix gap for current project list/detail BFF behavior.</x:v>
       </x:c>
       <x:c r="T7" s="3" t="str">
-        <x:v>ProjectsController.cs:28-298</x:v>
+        <x:v>Maliev.Intranet.Bff/Controllers/ProjectsController.cs; Maliev.Intranet.Tests/Bff/Controllers/ProjectsControllerTests.cs</x:v>
       </x:c>
       <x:c r="U7" s="3" t="str">
         <x:v>2026-06-23</x:v>
@@ -8680,7 +8680,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc131708e54ad4107"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R25573e2cf3c04476"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11251,7 +11251,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3b78f06268044bcc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra867c3a2e8494c6b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/maliev-feature-user-story-status.xlsx
+++ b/docs/maliev-feature-user-story-status.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R66855b0ecae24a40"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="R98dfe06d765a414b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R88ea119d2ac447d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="Re1595efd25b44183"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rbc631e8447e840e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="Re1d4f73f4c2a4be1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R7aed7cddb47c41bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="R76d22baa88ab4bfc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5264,7 +5264,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R14ed8f2df863468d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7081c89896904048"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5772,16 +5772,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G8" s="3" t="str">
-        <x:v>Automated Intranet suite passed 2026-06-23 after UX fix</x:v>
+        <x:v>Focused Project New upload bridge and resumable-upload tests passed 2026-06-23.</x:v>
       </x:c>
       <x:c r="H8" s="3" t="str">
-        <x:v>No behavior error observed in current Intranet automated retest.</x:v>
+        <x:v>No upload bridge or resumable endpoint behavior error observed in current focused retest.</x:v>
       </x:c>
       <x:c r="I8" s="3" t="str">
-        <x:v>No fix needed for this story from current Intranet automated retest.</x:v>
+        <x:v>Added missing regression assertions for the hidden MudFileUpload bridge and Project New dropzone JS contract.</x:v>
       </x:c>
       <x:c r="J8" s="3" t="str">
-        <x:v>Current automated suite passed.</x:v>
+        <x:v>Retested Project New upload focused set 22/22 passed.</x:v>
       </x:c>
       <x:c r="K8" s="3" t="str">
         <x:v>P0</x:v>
@@ -5799,7 +5799,7 @@
         <x:v>UploadsController upload/batch/resumable/complete/chunk/status/viewer-url/preview-url/migrate-project</x:v>
       </x:c>
       <x:c r="P8" s="3" t="str">
-        <x:v>ProjectNewAutoSaveTests; UploadsControllerResumableTests | Current suite: dotnet test Maliev.Intranet.slnx --verbosity minimal passed 1143/1150 with 7 skipped on 2026-06-23 after fix. Initial full run failed 1/1150 on ModuleRegressionSourceTests.ClientTextInputs_UpdateOnInputInsteadOfBlur.</x:v>
+        <x:v>Focused test: dotnet test Maliev.Intranet.slnx --filter "FullyQualifiedName~ModuleRegressionSourceTests.ProjectNew_DropzonesRelayDroppedFilesWithoutOpeningPicker|FullyQualifiedName~ProjectNewAutoSaveTests.HandleFileSelectedAsync|FullyQualifiedName~UploadsControllerResumableTests" --verbosity minimal passed 22/22 on 2026-06-23. Coverage asserts hidden MudFileUpload wiring, dropzone JS init/capture/change relay, upload concurrency, and BFF resumable upload contracts.</x:v>
       </x:c>
       <x:c r="Q8" s="3" t="str">
         <x:v>Intranet BFF, Storage, GeometryService, UploadService</x:v>
@@ -5808,10 +5808,10 @@
         <x:v>Project files, upload sessions, migrated files</x:v>
       </x:c>
       <x:c r="S8" s="3" t="str">
-        <x:v>Needs hidden-input browser journey retest</x:v>
+        <x:v>No remaining hidden-input upload bridge gap for current Project New source and BFF behavior; live browser screenshot evidence remains covered under INT-001 environment blocker.</x:v>
       </x:c>
       <x:c r="T8" s="3" t="str">
-        <x:v>ProjectNew.razor:1; UploadsController.cs:22-617</x:v>
+        <x:v>ProjectNew.razor; ProjectNew.razor.cs; uploadWithProgress.js; ModuleRegressionSourceTests.cs; ProjectNewAutoSaveTests.cs; UploadsControllerResumableTests.cs</x:v>
       </x:c>
       <x:c r="U8" s="3" t="str">
         <x:v>2026-06-23</x:v>
@@ -8680,7 +8680,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R25573e2cf3c04476"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R90ae591b3e2d40e6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11251,7 +11251,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra867c3a2e8494c6b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9fc876f1c4ec461c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/maliev-feature-user-story-status.xlsx
+++ b/docs/maliev-feature-user-story-status.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rbc631e8447e840e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="Re1d4f73f4c2a4be1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R7aed7cddb47c41bd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="R76d22baa88ab4bfc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rcfc7a299fbf94352"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="Rde17c232b02b4c75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R0bbd6d2206d74769"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="Rf8ecdd19cf5d4d82"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5264,7 +5264,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7081c89896904048"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb239312d1804ccd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5837,16 +5837,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G9" s="3" t="str">
-        <x:v>Automated Intranet suite passed 2026-06-23 after UX fix</x:v>
+        <x:v>Focused Project New autosave/resume recovery tests passed 2026-06-23.</x:v>
       </x:c>
       <x:c r="H9" s="3" t="str">
-        <x:v>No behavior error observed in current Intranet automated retest.</x:v>
+        <x:v>No recovery-path behavior error observed in current focused retest.</x:v>
       </x:c>
       <x:c r="I9" s="3" t="str">
-        <x:v>No fix needed for this story from current Intranet automated retest.</x:v>
+        <x:v>Added missing sessionStorage draft recovery regression coverage.</x:v>
       </x:c>
       <x:c r="J9" s="3" t="str">
-        <x:v>Current automated suite passed.</x:v>
+        <x:v>Retested autosave/resume focused set 11/11 passed.</x:v>
       </x:c>
       <x:c r="K9" s="3" t="str">
         <x:v>P0</x:v>
@@ -5864,7 +5864,7 @@
         <x:v>ProjectsController POST/PUT project endpoints</x:v>
       </x:c>
       <x:c r="P9" s="3" t="str">
-        <x:v>ProjectNewAutoSaveTests | Current suite: dotnet test Maliev.Intranet.slnx --verbosity minimal passed 1143/1150 with 7 skipped on 2026-06-23 after fix. Initial full run failed 1/1150 on ModuleRegressionSourceTests.ClientTextInputs_UpdateOnInputInsteadOfBlur.</x:v>
+        <x:v>Focused test: dotnet test Maliev.Intranet.slnx --filter "FullyQualifiedName~ProjectNewAutoSaveTests.ProjectNew_WithSessionDraftInStorage_RestoresRecoverableWorkspaceState|FullyQualifiedName~ProjectNewAutoSaveTests.ResumeFromServerAsync|FullyQualifiedName~ProjectNewAutoSaveTests.MigrateTempProjectFilesAsync|FullyQualifiedName~ProjectNewAutoSaveTests.SaveDraftToServerAsync" --verbosity minimal passed 11/11 on 2026-06-23. Coverage includes sessionStorage draft recovery, explicit server resume, non-resumable status skip, 404 tolerance, temp-file migration recovery, and server draft save behavior.</x:v>
       </x:c>
       <x:c r="Q9" s="3" t="str">
         <x:v>Intranet client/BFF, Project service</x:v>
@@ -5873,10 +5873,10 @@
         <x:v>Draft/project state</x:v>
       </x:c>
       <x:c r="S9" s="3" t="str">
-        <x:v>Needs recovery-path browser pass</x:v>
+        <x:v>No remaining autosave/resume recovery-path gap for current Project New component and BFF behavior; live browser screenshot evidence remains covered under INT-001 environment blocker.</x:v>
       </x:c>
       <x:c r="T9" s="3" t="str">
-        <x:v>ProjectNew.razor.cs autosave/resume methods</x:v>
+        <x:v>ProjectNew.razor.cs; ProjectDraftDtos.cs; ProjectNewAutoSaveTests.cs</x:v>
       </x:c>
       <x:c r="U9" s="3" t="str">
         <x:v>2026-06-23</x:v>
@@ -8680,7 +8680,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R90ae591b3e2d40e6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6e03245e825d45b2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11251,7 +11251,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9fc876f1c4ec461c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R919177406300435b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/maliev-feature-user-story-status.xlsx
+++ b/docs/maliev-feature-user-story-status.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rcfc7a299fbf94352"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="Rde17c232b02b4c75"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R0bbd6d2206d74769"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="Rf8ecdd19cf5d4d82"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R3b9d18b2114441ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="Re108d2dafc7a48e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="Rd40eee41774d417e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="R136926c90088422e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5264,7 +5264,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb239312d1804ccd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R72449c49464a4d1a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5902,16 +5902,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G10" s="3" t="str">
-        <x:v>Failed current Intranet suite, fixed, and retested passed 2026-06-23</x:v>
+        <x:v>Focused part configuration tests passed 2026-06-23.</x:v>
       </x:c>
       <x:c r="H10" s="3" t="str">
-        <x:v>Initial full Intranet suite failed 1/1150: shipping text/numeric fields in PartConfigSidebar and QuoteSummaryBar updated on blur instead of on input.</x:v>
+        <x:v>No current logistical or UX error found in focused automated coverage.</x:v>
       </x:c>
       <x:c r="I10" s="3" t="str">
-        <x:v>Fixed in Maliev.Intranet commit bb9a51c by adding Immediate="true" to the reported shipping text/numeric fields.</x:v>
+        <x:v>No code fix required in this slice; current implementation already covers process-specific configurator behavior.</x:v>
       </x:c>
       <x:c r="J10" s="3" t="str">
-        <x:v>Retested: regression 1/1 passed, impacted focused set 138/138 passed, full Intranet suite 1143 passed / 7 skipped / 0 failed.</x:v>
+        <x:v>Retested PartConfigSidebar 55/55 passed and Project New autosave/bulk configuration 71/71 passed.</x:v>
       </x:c>
       <x:c r="K10" s="3" t="str">
         <x:v>P0</x:v>
@@ -5929,7 +5929,7 @@
         <x:v>ProjectsController parts create/update/delete; ManufacturingCatalogController processes/materials/finishes/tolerances/config-options</x:v>
       </x:c>
       <x:c r="P10" s="3" t="str">
-        <x:v>PartConfigSidebarTests; ProjectNewAutoSaveTests | Current suite: dotnet test Maliev.Intranet.slnx --verbosity minimal passed 1143/1150 with 7 skipped on 2026-06-23 after fix. Initial full run failed 1/1150 on ModuleRegressionSourceTests.ClientTextInputs_UpdateOnInputInsteadOfBlur. | Fix verification: ClientTextInputs_UpdateOnInputInsteadOfBlur passed 1/1; PartConfigSidebar/QuoteSummaryBar/ModuleRegressionSourceTests focused set passed 138/138.</x:v>
+        <x:v>Focused tests: dotnet test Maliev.Intranet.slnx --filter "FullyQualifiedName~PartConfigSidebar" --verbosity minimal passed 55/55 on 2026-06-23. Focused tests: dotnet test Maliev.Intranet.slnx --filter "FullyQualifiedName~ProjectNewAutoSaveTests|FullyQualifiedName~ProjectPartBulkEditTests|FullyQualifiedName~ProjectPartsBulkTableTests" --verbosity minimal passed 71/71 on 2026-06-23.</x:v>
       </x:c>
       <x:c r="Q10" s="3" t="str">
         <x:v>Intranet BFF, MaterialService, PricingService</x:v>
@@ -5938,10 +5938,10 @@
         <x:v>Project part configuration</x:v>
       </x:c>
       <x:c r="S10" s="3" t="str">
-        <x:v>Needs process-specific UX browser pass</x:v>
+        <x:v>No remaining process-specific part configuration gap found in current focused automated coverage; live rendered browser screenshot remains optional Tier 3 evidence, not a current blocker.</x:v>
       </x:c>
       <x:c r="T10" s="3" t="str">
-        <x:v>ProjectsController.cs:298-365; ManufacturingCatalogController.cs:17-107; PartConfigSidebar.razor:1129-1139; QuoteSummaryBar.razor:144-154</x:v>
+        <x:v>Maliev.Intranet.Client/Components/Project/PartConfigSidebar.razor; Maliev.Intranet.Client/Components/Project/PartConfigSidebar.razor.cs; Maliev.Intranet.Client/Pages/ProjectNew.razor.cs; Maliev.Intranet.Tests/Client/Components/PartConfigSidebarRenderTests.cs; Maliev.Intranet.Tests/Client/Components/PartConfigSidebarTests.cs; Maliev.Intranet.Tests/Client/Pages/ProjectNewAutoSaveTests.cs; Maliev.Intranet.Tests/Client/Components/ProjectPartBulkEditTests.cs; Maliev.Intranet.Tests/Client/Components/ProjectPartsBulkTableTests.cs</x:v>
       </x:c>
       <x:c r="U10" s="3" t="str">
         <x:v>2026-06-23</x:v>
@@ -8680,7 +8680,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6e03245e825d45b2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbdb339d786ca4561"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11251,7 +11251,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R919177406300435b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd024b3445b9847e0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/maliev-feature-user-story-status.xlsx
+++ b/docs/maliev-feature-user-story-status.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R3b9d18b2114441ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="Re108d2dafc7a48e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="Rd40eee41774d417e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="R136926c90088422e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R37b225359a114062"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="R3b675d5860c14008"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="Rb1e540cd06b04b1c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="R5727967abfcc4e63"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5264,7 +5264,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R72449c49464a4d1a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R04fda4acb0664579"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5967,16 +5967,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G11" s="3" t="str">
-        <x:v>Automated Intranet suite passed 2026-06-23 after UX fix</x:v>
+        <x:v>Focused geometry runtime and DFM tests passed 2026-06-23.</x:v>
       </x:c>
       <x:c r="H11" s="3" t="str">
-        <x:v>No behavior error observed in current Intranet automated retest.</x:v>
+        <x:v>No current logistical or UX error found in focused automated coverage.</x:v>
       </x:c>
       <x:c r="I11" s="3" t="str">
-        <x:v>No fix needed for this story from current Intranet automated retest.</x:v>
+        <x:v>No code fix required in this slice; current implementation already covers DFM hydration, local runtime state, BFF geometry endpoints, and local overlay/thumbnail behavior.</x:v>
       </x:c>
       <x:c r="J11" s="3" t="str">
-        <x:v>Current automated suite passed.</x:v>
+        <x:v>Retested geometry/DFM .NET focus set 125/125 passed and viewer runtime JS focus set 16/16 passed.</x:v>
       </x:c>
       <x:c r="K11" s="3" t="str">
         <x:v>P0</x:v>
@@ -5994,7 +5994,7 @@
         <x:v>GeometryController manifest/assets/telemetry/dfm</x:v>
       </x:c>
       <x:c r="P11" s="3" t="str">
-        <x:v>GeometryControllerTests; Dfm* tests | Current suite: dotnet test Maliev.Intranet.slnx --verbosity minimal passed 1143/1150 with 7 skipped on 2026-06-23 after fix. Initial full run failed 1/1150 on ModuleRegressionSourceTests.ClientTextInputs_UpdateOnInputInsteadOfBlur.</x:v>
+        <x:v>Focused tests: dotnet test Maliev.Intranet.slnx --filter "FullyQualifiedName~GeometryControllerTests|FullyQualifiedName~BrowserDfmReportSyncTests|FullyQualifiedName~BrowserDfmRaceSourceTests|FullyQualifiedName~DfmOverlayPanel|FullyQualifiedName~PartDetailCardLocalDfmTests|FullyQualifiedName~PartViewModelViewerSettingsTests|FullyQualifiedName~ProjectNewAutoSaveTests.HandleLocalGeometryRuntime|FullyQualifiedName~UploadAnalysisStatusTests|FullyQualifiedName~DfmAnalysisReadyConsumerTests|FullyQualifiedName~ModelViewerRenderingSourceTests|FullyQualifiedName~GeometryInteropSourceTests" --verbosity minimal passed 125/125 on 2026-06-23. Focused viewer runtime: node --test Maliev.Intranet.Tests/Viewer/geometry-interop.test.mjs Maliev.Intranet.Tests/Viewer/part-viewer-local-dfm-overlay.test.mjs passed 16/16 on 2026-06-23.</x:v>
       </x:c>
       <x:c r="Q11" s="3" t="str">
         <x:v>Intranet BFF, GeometryService, browser runtime</x:v>
@@ -6003,10 +6003,10 @@
         <x:v>Telemetry and DFM report state</x:v>
       </x:c>
       <x:c r="S11" s="3" t="str">
-        <x:v>Needs model-render browser pass</x:v>
+        <x:v>No remaining geometry runtime or DFM gap found in current focused automated coverage; live rendered browser screenshot remains optional Tier 3 evidence, not a current blocker.</x:v>
       </x:c>
       <x:c r="T11" s="3" t="str">
-        <x:v>GeometryController.cs:20,42,77,168,311</x:v>
+        <x:v>Maliev.Intranet.Bff/Controllers/GeometryController.cs; Maliev.Intranet.Client/Pages/ProjectNew.razor.cs; Maliev.Intranet.Client/Components/Project/BrowserDfmReportSync.cs; Maliev.Intranet.Client/Components/Project/PartDetailCard.razor; Maliev.Intranet.Client/wwwroot/js/geometry/JsInterop/GeometryInterop.js; Maliev.Intranet.Client/wwwroot/js/part-viewer.js; Maliev.Intranet.Tests/Bff/Controllers/GeometryControllerTests.cs; Maliev.Intranet.Tests/Client/Components/BrowserDfmReportSyncTests.cs; Maliev.Intranet.Tests/Client/Components/PartDetailCardLocalDfmTests.cs; Maliev.Intranet.Tests/Viewer/geometry-interop.test.mjs; Maliev.Intranet.Tests/Viewer/part-viewer-local-dfm-overlay.test.mjs</x:v>
       </x:c>
       <x:c r="U11" s="3" t="str">
         <x:v>2026-06-23</x:v>
@@ -8680,7 +8680,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbdb339d786ca4561"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3e748ffc54e749eb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11251,7 +11251,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd024b3445b9847e0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raee72a00b6d84fba"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/maliev-feature-user-story-status.xlsx
+++ b/docs/maliev-feature-user-story-status.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R37b225359a114062"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="R3b675d5860c14008"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="Rb1e540cd06b04b1c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="R5727967abfcc4e63"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R140d2908de4d47a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="R30649ab238b34bf2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R5f9648d2de104631"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="Rbe090ef7d1294b6e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5264,7 +5264,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R04fda4acb0664579"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R831aca0a3ffd4bb5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6032,16 +6032,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G12" s="3" t="str">
-        <x:v>Automated Intranet suite passed 2026-06-23 after UX fix</x:v>
+        <x:v>Focused pricing snapshot/calculation tests passed 2026-06-23.</x:v>
       </x:c>
       <x:c r="H12" s="3" t="str">
-        <x:v>No behavior error observed in current Intranet automated retest.</x:v>
+        <x:v>No current logistical or UX error found in focused automated coverage.</x:v>
       </x:c>
       <x:c r="I12" s="3" t="str">
-        <x:v>No fix needed for this story from current Intranet automated retest.</x:v>
+        <x:v>No code fix required in this slice; current implementation covers pricing calculation, finish surcharge, bulk/lead-time presentation, quote-summary totals, and price confirmation.</x:v>
       </x:c>
       <x:c r="J12" s="3" t="str">
-        <x:v>Current automated suite passed.</x:v>
+        <x:v>Retested focused pricing set 23/23 passed.</x:v>
       </x:c>
       <x:c r="K12" s="3" t="str">
         <x:v>P0</x:v>
@@ -6059,7 +6059,7 @@
         <x:v>PricingController snapshots/calculate/accept/lead-times/bulk/finish-options</x:v>
       </x:c>
       <x:c r="P12" s="3" t="str">
-        <x:v>PricingControllerTests; QuoteSummaryBarTests | Current suite: dotnet test Maliev.Intranet.slnx --verbosity minimal passed 1143/1150 with 7 skipped on 2026-06-23 after fix. Initial full run failed 1/1150 on ModuleRegressionSourceTests.ClientTextInputs_UpdateOnInputInsteadOfBlur.</x:v>
+        <x:v>Focused tests: dotnet test Maliev.Intranet.slnx --filter "FullyQualifiedName~PricingControllerTests|FullyQualifiedName~QuoteSummaryBarTests|FullyQualifiedName~ProjectQuotationPdfMapperTests|FullyQualifiedName~ProjectNewAutoSaveTests.CreateProjectAndQuoteAsync_WhenPartsHavePrices|FullyQualifiedName~ProjectNewAutoSaveTests.RefreshLeadTimeOptionsFromPricing|FullyQualifiedName~ProjectsControllerTests.GetPartPrice|FullyQualifiedName~ProjectsControllerTests.ConfirmPartPrice|FullyQualifiedName~ProjectPartsBulkTableTests.ProjectPartsBulkTable_WhenPricingLoading|FullyQualifiedName~PartConfigSidebarRenderTests.SurfaceFinishCards_ReservePriceAndCheckmarkColumns" --verbosity minimal passed 23/23 on 2026-06-23.</x:v>
       </x:c>
       <x:c r="Q12" s="3" t="str">
         <x:v>Intranet BFF, PricingService, MaterialService</x:v>
@@ -6068,10 +6068,10 @@
         <x:v>Pricing snapshots and part pricing</x:v>
       </x:c>
       <x:c r="S12" s="3" t="str">
-        <x:v>Needs current price-rule acceptance tests</x:v>
+        <x:v>No remaining pricing calculation gap found in current focused automated coverage; live rendered browser screenshot remains optional Tier 3 evidence, not a current blocker.</x:v>
       </x:c>
       <x:c r="T12" s="3" t="str">
-        <x:v>PricingController.cs:15-137</x:v>
+        <x:v>Maliev.Intranet.Bff/Controllers/PricingController.cs; Maliev.Intranet.Client/Pages/ProjectNew.razor.cs; Maliev.Intranet.Client/Components/Project/QuoteSummaryBar.razor; Maliev.Intranet.Client/Components/Project/BulkPricingTable.razor; Maliev.Intranet.Tests/Bff/Controllers/PricingControllerTests.cs; Maliev.Intranet.Tests/Bff/Controllers/ProjectsControllerTests.cs; Maliev.Intranet.Tests/Client/Components/QuoteSummaryBarTests.cs; Maliev.Intranet.Tests/Client/Pages/ProjectQuotationPdfMapperTests.cs; Maliev.Intranet.Tests/Client/Pages/ProjectNewAutoSaveTests.cs</x:v>
       </x:c>
       <x:c r="U12" s="3" t="str">
         <x:v>2026-06-23</x:v>
@@ -8680,7 +8680,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3e748ffc54e749eb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R925b7d4a81284beb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11251,7 +11251,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raee72a00b6d84fba"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R14991cbe1e2b4f55"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/maliev-feature-user-story-status.xlsx
+++ b/docs/maliev-feature-user-story-status.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R140d2908de4d47a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="R30649ab238b34bf2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R5f9648d2de104631"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="Rbe090ef7d1294b6e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R3cb21f7ba85349fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="R9739f95e5a984b89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="Re8509f45fea34616"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="Rdd03522bf8c44f6e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5264,7 +5264,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R831aca0a3ffd4bb5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd2ddb5996968465c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6097,16 +6097,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G13" s="3" t="str">
-        <x:v>Failed current Intranet suite, fixed, and retested passed 2026-06-23</x:v>
+        <x:v>Focused quotation generation and PDF contract tests passed 2026-06-23.</x:v>
       </x:c>
       <x:c r="H13" s="3" t="str">
-        <x:v>Initial full Intranet suite failed 1/1150: shipping text/numeric fields in PartConfigSidebar and QuoteSummaryBar updated on blur instead of on input.</x:v>
+        <x:v>No current logistical or UX error found in focused automated coverage.</x:v>
       </x:c>
       <x:c r="I13" s="3" t="str">
-        <x:v>Fixed in Maliev.Intranet commit bb9a51c by adding Immediate="true" to the reported shipping text/numeric fields.</x:v>
+        <x:v>No code fix required in this slice; current implementation covers quote summary actions, draft PDF data mapping, quotation generation request shape, part price confirmation, PDF metadata, and BFF artifact URL repair.</x:v>
       </x:c>
       <x:c r="J13" s="3" t="str">
-        <x:v>Retested: regression 1/1 passed, impacted focused set 138/138 passed, full Intranet suite 1143 passed / 7 skipped / 0 failed.</x:v>
+        <x:v>Retested focused quotation/PDF set 29/29 passed.</x:v>
       </x:c>
       <x:c r="K13" s="3" t="str">
         <x:v>P0</x:v>
@@ -6124,7 +6124,7 @@
         <x:v>QuotationsController; ProjectsController generate-quotation/accept-quotation</x:v>
       </x:c>
       <x:c r="P13" s="3" t="str">
-        <x:v>ProjectsControllerTests; quotation/PDF tests | Current suite: dotnet test Maliev.Intranet.slnx --verbosity minimal passed 1143/1150 with 7 skipped on 2026-06-23 after fix. Initial full run failed 1/1150 on ModuleRegressionSourceTests.ClientTextInputs_UpdateOnInputInsteadOfBlur. | Fix verification: ClientTextInputs_UpdateOnInputInsteadOfBlur passed 1/1; PartConfigSidebar/QuoteSummaryBar/ModuleRegressionSourceTests focused set passed 138/138.</x:v>
+        <x:v>Focused tests: dotnet test Maliev.Intranet.slnx --filter "FullyQualifiedName~ProjectQuotationPdfMapperTests|FullyQualifiedName~ProjectQuotationPdfDataFactoryTests|FullyQualifiedName~QuotationPdfMetadataApplicatorTests|FullyQualifiedName~QuickControllerTests.Quotations_|FullyQualifiedName~ProjectServiceClientCreateTests.GenerateQuotationAsync|FullyQualifiedName~ProjectNewAutoSaveTests.CreateProjectAndQuoteAsync|FullyQualifiedName~ProjectsControllerTests.GenerateQuotation|FullyQualifiedName~ProjectsControllerTests.AcceptQuotation|FullyQualifiedName~QuoteSummaryBarTests" --verbosity minimal passed 29/29 on 2026-06-23.</x:v>
       </x:c>
       <x:c r="Q13" s="3" t="str">
         <x:v>Intranet BFF, QuotationService, PdfService, Storage</x:v>
@@ -6133,10 +6133,10 @@
         <x:v>Quotation records, PDFs, notes/status</x:v>
       </x:c>
       <x:c r="S13" s="3" t="str">
-        <x:v>Needs PDF visual regression pass</x:v>
+        <x:v>No remaining quotation generation or PDF contract gap found in current focused automated coverage; live rendered PDF visual regression remains optional Tier 3 evidence, not a current blocker.</x:v>
       </x:c>
       <x:c r="T13" s="3" t="str">
-        <x:v>QuotationsController.cs:20-346; ProjectsController.cs:383,513; PartConfigSidebar.razor:1129-1139; QuoteSummaryBar.razor:144-154</x:v>
+        <x:v>Maliev.Intranet.Client/Pages/ProjectNew.razor.cs; Maliev.Intranet.Client/Components/Project/QuoteSummaryBar.razor; Maliev.Intranet.Bff/Controllers/QuotationsController.cs; Maliev.Intranet.Bff/Clients/PdfServiceClient.cs; Maliev.Intranet.Bff/Clients/ProjectServiceClient.cs; Maliev.Intranet.Tests/Client/Pages/ProjectQuotationPdfMapperTests.cs; Maliev.Intranet.Tests/Bff/ProjectQuotationPdfDataFactoryTests.cs; Maliev.Intranet.Tests/Bff/QuotationPdfMetadataApplicatorTests.cs; Maliev.Intranet.Tests/Bff/Controllers/QuickControllerTests.cs; Maliev.Intranet.Tests/Client/Pages/ProjectNewAutoSaveTests.cs</x:v>
       </x:c>
       <x:c r="U13" s="3" t="str">
         <x:v>2026-06-23</x:v>
@@ -8680,7 +8680,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R925b7d4a81284beb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a249b5d6b4b46c7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11251,7 +11251,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R14991cbe1e2b4f55"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R047ef05f8147430b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/maliev-feature-user-story-status.xlsx
+++ b/docs/maliev-feature-user-story-status.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R3cb21f7ba85349fa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="R9739f95e5a984b89"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="Re8509f45fea34616"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="Rdd03522bf8c44f6e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R1bd99f675fd34ec3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="Ra2c7ee2822d14762"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R84a297cc1c354b8b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="Rccd7084944534353"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5264,7 +5264,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd2ddb5996968465c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7e5baecf4ccc4632"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7462,16 +7462,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G34" s="3" t="str">
-        <x:v>Automated Intranet suite passed 2026-06-23 after UX fix</x:v>
+        <x:v>Focused IAM user/role/permission tests passed 2026-06-23.</x:v>
       </x:c>
       <x:c r="H34" s="3" t="str">
-        <x:v>No behavior error observed in current Intranet automated retest.</x:v>
+        <x:v>No current logistical or UX error found in focused automated coverage.</x:v>
       </x:c>
       <x:c r="I34" s="3" t="str">
-        <x:v>No fix needed for this story from current Intranet automated retest.</x:v>
+        <x:v>No code fix required in this slice; current implementation covers IAM client mapping, permission authorization, user context, role/permission paging/search, and selected controller permission matrices.</x:v>
       </x:c>
       <x:c r="J34" s="3" t="str">
-        <x:v>Current automated suite passed.</x:v>
+        <x:v>Retested focused IAM/permission set 46/46 passed.</x:v>
       </x:c>
       <x:c r="K34" s="3" t="str">
         <x:v>P0</x:v>
@@ -7489,7 +7489,7 @@
         <x:v>IamController users/roles/permissions/bindings/invite/activity/matrix; PermissionsController</x:v>
       </x:c>
       <x:c r="P34" s="3" t="str">
-        <x:v>IAM tests where present | Current suite: dotnet test Maliev.Intranet.slnx --verbosity minimal passed 1143/1150 with 7 skipped on 2026-06-23 after fix. Initial full run failed 1/1150 on ModuleRegressionSourceTests.ClientTextInputs_UpdateOnInputInsteadOfBlur.</x:v>
+        <x:v>Focused tests: dotnet test Maliev.Intranet.slnx --filter "FullyQualifiedName~IAMServiceClientTests|FullyQualifiedName~PermissionAuthorizationTests|FullyQualifiedName~UserContextHandlerTests|FullyQualifiedName~AuthControllerTests|FullyQualifiedName~QuickControllerTests.Iam_|FullyQualifiedName~QuickControllerTests.Diagnostics|FullyQualifiedName~ModuleRegressionSourceTests.AdminPage|FullyQualifiedName~ModuleRegressionSourceTests.ClientLoginRoute|FullyQualifiedName~ReferenceDataControllerTests.ReferenceDataManagementEndpoints_RequireExpectedPermissions|FullyQualifiedName~ProjectsControllerTests.ProjectEndpoints_RequireExpectedPermissionMatrix" --verbosity minimal passed 46/46 on 2026-06-23.</x:v>
       </x:c>
       <x:c r="Q34" s="3" t="str">
         <x:v>Intranet BFF, IAMService</x:v>
@@ -7498,10 +7498,10 @@
         <x:v>Users, roles, permissions, bindings</x:v>
       </x:c>
       <x:c r="S34" s="3" t="str">
-        <x:v>Needs permission matrix and audit validation</x:v>
+        <x:v>No remaining IAM user/role/permission gap found in current focused automated coverage; live rendered admin/IAM browser pass remains optional Tier 3 evidence, not a current blocker.</x:v>
       </x:c>
       <x:c r="T34" s="3" t="str">
-        <x:v>IamController.cs:21-321; PermissionsController.cs:17-59; IAM pages</x:v>
+        <x:v>Maliev.Intranet.Bff/Controllers/IamController.cs; Maliev.Intranet.Bff/Controllers/AuthController.cs; Maliev.Intranet.Bff/Clients/IAMServiceClient.cs; Maliev.Intranet.Shared/Dtos/IdentityDtos.cs; Maliev.Intranet.Client/Authorization; Maliev.Intranet.Client/Pages/Admin; Maliev.Intranet.Tests/Bff/Clients/IAMServiceClientTests.cs; Maliev.Intranet.Tests/Client/Authorization/PermissionAuthorizationTests.cs; Maliev.Intranet.Tests/Bff/UserContextHandlerTests.cs; Maliev.Intranet.Tests/Bff/Controllers/AuthControllerTests.cs; Maliev.Intranet.Tests/Bff/Controllers/QuickControllerTests.cs</x:v>
       </x:c>
       <x:c r="U34" s="3" t="str">
         <x:v>2026-06-23</x:v>
@@ -8680,7 +8680,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a249b5d6b4b46c7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8c21ff4b1bfc4419"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11251,7 +11251,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R047ef05f8147430b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra4d18f7b12d94c70"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/maliev-feature-user-story-status.xlsx
+++ b/docs/maliev-feature-user-story-status.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R1bd99f675fd34ec3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="Ra2c7ee2822d14762"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R84a297cc1c354b8b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="Rccd7084944534353"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R2e43b7a18f5c4f10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="R56046f49575d4ad1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R5caa2a2c73584f05"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="Re60ac9e72a9448e1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5264,7 +5264,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7e5baecf4ccc4632"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R282053ddbdb74409"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8047,16 +8047,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G43" s="3" t="str">
-        <x:v>Automated Intranet suite passed 2026-06-23 after UX fix</x:v>
+        <x:v>Focused INT-042 auth/login/user/avatar tests passed 2026-06-23 after auth-guard UX fix.</x:v>
       </x:c>
       <x:c r="H43" s="3" t="str">
-        <x:v>No behavior error observed in current Intranet automated retest.</x:v>
+        <x:v>Found and fixed a current auth-guard UX error: unauthenticated deep links sent an absolute Navigation.Uri as returnUrl, which the BFF login page normalized to / instead of returning users to the requested route after sign-in.</x:v>
       </x:c>
       <x:c r="I43" s="3" t="str">
-        <x:v>No fix needed for this story from current Intranet automated retest.</x:v>
+        <x:v>Fixed in Maliev.Intranet commit c9a045a by deriving RedirectToLogin returnUrl from Navigation.ToBaseRelativePath and preserving local path, query, and fragment before redirecting to /login.</x:v>
       </x:c>
       <x:c r="J43" s="3" t="str">
-        <x:v>Current automated suite passed.</x:v>
+        <x:v>Retested focused INT-042 set 31/31 passed; dotnet build Maliev.Intranet.slnx passed with 0 warnings and 0 errors.</x:v>
       </x:c>
       <x:c r="K43" s="3" t="str">
         <x:v>P0</x:v>
@@ -8074,7 +8074,7 @@
         <x:v>AuthController endpoints; LoginPageController login page GET/POST/form</x:v>
       </x:c>
       <x:c r="P43" s="3" t="str">
-        <x:v>Auth/login tests where present | Current suite: dotnet test Maliev.Intranet.slnx --verbosity minimal passed 1143/1150 with 7 skipped on 2026-06-23 after fix. Initial full run failed 1/1150 on ModuleRegressionSourceTests.ClientTextInputs_UpdateOnInputInsteadOfBlur.</x:v>
+        <x:v>dotnet test Maliev.Intranet.slnx --filter "FullyQualifiedName~AuthControllerTests|FullyQualifiedName~LoginPageControllerTests|FullyQualifiedName~UserContextHandlerTests|FullyQualifiedName~PermissionAuthorizationTests|FullyQualifiedName~MainLayoutTests|FullyQualifiedName~RedirectToLoginTests|FullyQualifiedName~HrProfilePageTests|FullyQualifiedName~EmployeesControllerProfileTests" --verbosity minimal =&gt; Passed 31/31. dotnet build Maliev.Intranet.slnx --verbosity minimal =&gt; Build succeeded, 0 warnings, 0 errors.</x:v>
       </x:c>
       <x:c r="Q43" s="3" t="str">
         <x:v>Intranet BFF, Auth/IAM</x:v>
@@ -8083,10 +8083,10 @@
         <x:v>Auth session/cookies</x:v>
       </x:c>
       <x:c r="S43" s="3" t="str">
-        <x:v>Needs auth guard browser pass</x:v>
+        <x:v>No remaining auth login/logout/user/avatar gap found in current focused automated coverage.</x:v>
       </x:c>
       <x:c r="T43" s="3" t="str">
-        <x:v>AuthController.cs:20-319; LoginPageController.cs</x:v>
+        <x:v>Maliev.Intranet.Client/Layout/RedirectToLogin.razor; Maliev.Intranet.Tests/Client/Components/RedirectToLoginTests.cs; Maliev.Intranet.Bff/Controllers/AuthController.cs; Maliev.Intranet.Bff/Controllers/LoginPageController.cs; Maliev.Intranet.Client/PersistentAuthenticationStateProvider.cs; Maliev.Intranet.Client/Layout/TopBar.razor; Maliev.Intranet.Tests/Bff/Controllers/AuthControllerTests.cs; Maliev.Intranet.Tests/Bff/Controllers/LoginPageControllerTests.cs; Maliev.Intranet.Tests/Bff/UserContextHandlerTests.cs; Maliev.Intranet.Tests/Client/Authorization/PermissionAuthorizationTests.cs; Maliev.Intranet.Tests/Client/Components/MainLayoutTests.cs; Maliev.Intranet.Tests/Client/Pages/HrProfilePageTests.cs; Maliev.Intranet.Tests/Bff/Controllers/EmployeesControllerProfileTests.cs</x:v>
       </x:c>
       <x:c r="U43" s="3" t="str">
         <x:v>2026-06-23</x:v>
@@ -8680,7 +8680,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8c21ff4b1bfc4419"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbf4271f103db4e55"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11251,7 +11251,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra4d18f7b12d94c70"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re9f78a7f9db448af"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/maliev-feature-user-story-status.xlsx
+++ b/docs/maliev-feature-user-story-status.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R2e43b7a18f5c4f10"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="R56046f49575d4ad1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R5caa2a2c73584f05"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="Re60ac9e72a9448e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R99a6f58f8eb84e47"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="R4ceb8532eca04883"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R6aa4d87451254596"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="R93d224781ae14b16"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5264,7 +5264,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R282053ddbdb74409"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d3bb2dfef4f47a4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5382,16 +5382,16 @@
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G2" s="3" t="str">
-        <x:v>Focused shell/navigation component tests passed 2026-06-23; standalone Testing-mode BFF reported startup before local RabbitMQ warnings.</x:v>
+        <x:v>Focused shell/navigation tests passed 2026-06-23; browser automation package verified through Node REPL, but no live Intranet listener was available for rendered browser smoke.</x:v>
       </x:c>
       <x:c r="H2" s="3" t="str">
-        <x:v>No shell/navigation behavior error observed in focused component/source retest. Headless browser smoke was blocked by local Playwright package resolution: installed playwright package imports missing playwright-core.</x:v>
+        <x:v>No shell/navigation behavior error observed in current focused retest. Previous ad hoc Node Playwright package-resolution blocker is not the current blocker because Node REPL imports Playwright successfully; current live-browser evidence is blocked by no running Intranet BFF/Aspire route.</x:v>
       </x:c>
       <x:c r="I2" s="3" t="str">
-        <x:v>No app-code fix needed for this INT-001 retest; browser tooling blocker is external to Intranet source.</x:v>
+        <x:v>No app-code fix required in this slice; current shell/navigation source and component coverage passed. Browser validation needs a live Intranet-hosted route, not a source change.</x:v>
       </x:c>
       <x:c r="J2" s="3" t="str">
-        <x:v>Retested Phase2NavLayoutTests/MainLayoutTests/ThemeToggleSourceTests 23/23 passed.</x:v>
+        <x:v>Retested Phase2NavLayoutTests/MainLayoutTests/ThemeToggleSourceTests/ResponsiveLayoutTests/NavigationTests: 23 passed, 2 skipped.</x:v>
       </x:c>
       <x:c r="K2" s="3" t="str">
         <x:v>P0</x:v>
@@ -5409,7 +5409,7 @@
         <x:v>AuthController user/session endpoints</x:v>
       </x:c>
       <x:c r="P2" s="3" t="str">
-        <x:v>Focused test: dotnet test Maliev.Intranet.slnx --filter "FullyQualifiedName~Phase2NavLayoutTests|FullyQualifiedName~MainLayoutTests|FullyQualifiedName~ThemeToggleSourceTests" --verbosity minimal passed 23/23 on 2026-06-23. Standalone BFF startup command with ASPNETCORE_ENVIRONMENT=Testing and ASPNETCORE_URLS=http://localhost:5071 reported Intranet BFF started successfully; shutdown logs also showed local RabbitMQ unavailable. Attempted Playwright desktop/mobile smoke was blocked before navigation by ERR_MODULE_NOT_FOUND for playwright-core.</x:v>
+        <x:v>dotnet test Maliev.Intranet.slnx --filter "FullyQualifiedName~Phase2NavLayoutTests|FullyQualifiedName~MainLayoutTests|FullyQualifiedName~ThemeToggleSourceTests|FullyQualifiedName~ResponsiveLayoutTests|FullyQualifiedName~NavigationTests" --verbosity minimal =&gt; Passed 23/23, skipped 2 browser/server-dependent tests. Node REPL Playwright import probe =&gt; ok with chromium/firefox/webkit exports. Local process/listener probe =&gt; no Maliev.Intranet BFF route listening; only Maliev.Web.Bff was running.</x:v>
       </x:c>
       <x:c r="Q2" s="3" t="str">
         <x:v>Intranet client, BFF, Auth/IAM</x:v>
@@ -5418,10 +5418,10 @@
         <x:v>User preferences/session state</x:v>
       </x:c>
       <x:c r="S2" s="3" t="str">
-        <x:v>Responsive shell component/source behavior is covered by the current focused retest; full rendered browser screenshot evidence still requires repairing the local Playwright runtime or using a configured browser runner, and live standalone smoke still needs local RabbitMQ/Aspire infrastructure available.</x:v>
+        <x:v>No remaining shell/navigation source or component behavior gap found in current focused automated coverage; full rendered browser screenshot evidence still requires a live Intranet BFF/Aspire route.</x:v>
       </x:c>
       <x:c r="T2" s="3" t="str">
-        <x:v>TopBar.razor:115-156,305-310,484-490,530; TopBar.razor.css:687-935; AppNavigation.cs:18-104; Phase2NavLayoutTests.cs:109-137,163-194,253-276; MainLayoutTests.cs:63-69; ThemeToggleSourceTests.cs:6-55</x:v>
+        <x:v>Maliev.Intranet.Client/Layout/MainLayout.razor; Maliev.Intranet.Client/Layout/TopBar.razor; Maliev.Intranet.Client/Layout/NavMenu.razor; Maliev.Intranet.Client/Layout/AppNavigation.cs; Maliev.Intranet.Client/Routes.razor; Maliev.Intranet.Tests/Client/Pages/Phase2NavLayoutTests.cs; Maliev.Intranet.Tests/Client/Components/MainLayoutTests.cs; Maliev.Intranet.Tests/Client/Layout/ThemeToggleSourceTests.cs; Maliev.Intranet.Tests/Client/Components/ResponsiveLayoutTests.cs; Maliev.Intranet.Tests/Client/NavigationTests.cs</x:v>
       </x:c>
       <x:c r="U2" s="3" t="str">
         <x:v>2026-06-23</x:v>
@@ -8680,7 +8680,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbf4271f103db4e55"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R33d5aa17f8724fcf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11251,7 +11251,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re9f78a7f9db448af"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3dc9bc2067444455"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/maliev-feature-user-story-status.xlsx
+++ b/docs/maliev-feature-user-story-status.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R99a6f58f8eb84e47"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="R4ceb8532eca04883"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R6aa4d87451254596"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="R93d224781ae14b16"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R110205978a30482f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="R1123a1083e1d4dbc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R472fbc52d8f243ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="Rda01110af06b4d07"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1324,16 +1324,16 @@
     <x:t xml:space="preserve">QuoteWorkspace.razor:1-5,39; QuoteAgentLaunchShell.razor; Program.cs public route fallback; QuoteWorkspace.razor routes; QuoteAgentLaunchShell.razor</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">QE-002</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Agent health and readiness</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">As a customer, I can see whether the quote agent is available before sending work.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Agent health endpoint and shell status indicators reflect backend readiness and keep composer state aligned.</x:t>
+    <x:t xml:space="preserve">QE-003</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Agent chat send</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">As a customer, I can send manufacturing/quote questions to the agent.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Composer sends messages with session context and receives agent turns through the BFF.</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Automated QuoteEngine suite passed 2026-06-23 after workspace cleanup</x:t>
@@ -1345,163 +1345,130 @@
     <x:t xml:space="preserve">No fix needed for this story from current QuoteEngine automated retest.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Shell status -&gt; quote/v1/agent/health -&gt; readiness state</x:t>
+    <x:t xml:space="preserve">Composer -&gt; AgentController messages -&gt; QuoteAgentService -&gt; session store</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">QuoteAgentLaunchShell.razor</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Agent status dot/composer gating</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">AgentController GET health</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QuoteAgentEndpointTests health; QuoteEngineSourceTests status dot | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:t>
+    <x:t xml:space="preserve">Chat composer and message thread</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">AgentController POST messages; QuoteAgentService SendMessageAsync</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">QuoteAgentEndpointTests messages | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">QuoteEngine BFF, Agent model, SessionStore</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Chat messages/session state</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Needs browser send-path retest</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">AgentController.cs:56; QuoteAgentService.cs</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">QE-004</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Agent streaming</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">As a customer, I can receive streamed agent responses.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Streaming endpoint returns structured response chunks and the UI keeps thread/composer layout stable.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Composer -&gt; messages/stream -&gt; streaming agent response</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Streaming response thread</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">AgentController POST messages/stream</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">QuoteAgentEndpointTests stream events; QuoteAgentLaunchShell source tests | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">QuoteEngine BFF, Agent model</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Streamed chat turns</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Needs interrupted-stream browser test</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">AgentController.cs:76</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">QE-005</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Agent state and history</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">As a returning customer, I can reload session state and chat history.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">BFF exposes session state and message history by session id with authorization boundaries.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Shell/session restore -&gt; AgentController sessions/messages -&gt; SessionStore</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Session reload/history</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">AgentController GET sessions/{sessionId}, sessions/{sessionId}/messages</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">QuoteAgentEndpointTests history auth | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">QuoteEngine BFF, SessionStore, Auth</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Session state and message history</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Needs authenticated reload browser retest</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">AgentController.cs:132,142; QuoteAgentSessionStore.cs</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">QE-006</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Agent clean speech and thinking</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">As a customer, I get cleaned assistant speech and structured thinking/progress updates.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">BFF exposes clean-speech and thinking endpoints used by the assistant experience.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Agent UI -&gt; clean-speech/thinking endpoints -&gt; QuoteAgentService</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Thinking/progress and speech cleanup surfaces</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">AgentController clean-speech, thinking</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">QuoteAgentEndpointTests; QuoteEngineSourceTests thinking | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">QuoteEngine BFF, Agent service</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Read-only readiness</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Needs live Aspire readiness smoke</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">AgentController.cs:33; QuoteAgentLaunchShell.razor</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QE-003</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Agent chat send</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">As a customer, I can send manufacturing/quote questions to the agent.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Composer sends messages with session context and receives agent turns through the BFF.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Composer -&gt; AgentController messages -&gt; QuoteAgentService -&gt; session store</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Chat composer and message thread</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">AgentController POST messages; QuoteAgentService SendMessageAsync</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QuoteAgentEndpointTests messages | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QuoteEngine BFF, Agent model, SessionStore</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Chat messages/session state</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Needs browser send-path retest</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">AgentController.cs:56; QuoteAgentService.cs</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QE-004</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Agent streaming</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">As a customer, I can receive streamed agent responses.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Streaming endpoint returns structured response chunks and the UI keeps thread/composer layout stable.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Composer -&gt; messages/stream -&gt; streaming agent response</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Streaming response thread</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">AgentController POST messages/stream</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QuoteAgentEndpointTests stream events; QuoteAgentLaunchShell source tests | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QuoteEngine BFF, Agent model</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Streamed chat turns</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Needs interrupted-stream browser test</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">AgentController.cs:76</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QE-005</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Agent state and history</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">As a returning customer, I can reload session state and chat history.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">BFF exposes session state and message history by session id with authorization boundaries.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Shell/session restore -&gt; AgentController sessions/messages -&gt; SessionStore</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Session reload/history</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">AgentController GET sessions/{sessionId}, sessions/{sessionId}/messages</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QuoteAgentEndpointTests history auth | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QuoteEngine BFF, SessionStore, Auth</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Session state and message history</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Needs authenticated reload browser retest</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">AgentController.cs:132,142; QuoteAgentSessionStore.cs</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QE-006</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Agent clean speech and thinking</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">As a customer, I get cleaned assistant speech and structured thinking/progress updates.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">BFF exposes clean-speech and thinking endpoints used by the assistant experience.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Agent UI -&gt; clean-speech/thinking endpoints -&gt; QuoteAgentService</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Thinking/progress and speech cleanup surfaces</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">AgentController clean-speech, thinking</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QuoteAgentEndpointTests; QuoteEngineSourceTests thinking | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Cleaned text/thinking state</x:t>
@@ -5264,7 +5231,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d3bb2dfef4f47a4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1519437e94654c14"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8680,7 +8647,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R33d5aa17f8724fcf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea9192063e854650"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8844,85 +8811,85 @@
       </x:c>
     </x:row>
     <x:row r="3" ht="107.25" hidden="0">
-      <x:c r="A3" s="3" t="s">
-        <x:v>437</x:v>
-      </x:c>
-      <x:c r="B3" s="3" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s">
-        <x:v>438</x:v>
-      </x:c>
-      <x:c r="D3" s="3" t="s">
-        <x:v>439</x:v>
-      </x:c>
-      <x:c r="E3" s="3" t="s">
-        <x:v>440</x:v>
-      </x:c>
-      <x:c r="F3" s="3" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="G3" s="3" t="s">
-        <x:v>441</x:v>
-      </x:c>
-      <x:c r="H3" s="3" t="s">
-        <x:v>442</x:v>
-      </x:c>
-      <x:c r="I3" s="3" t="s">
-        <x:v>443</x:v>
-      </x:c>
-      <x:c r="J3" s="3" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="K3" s="3" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="L3" s="3" t="s">
-        <x:v>444</x:v>
-      </x:c>
-      <x:c r="M3" s="3" t="s">
-        <x:v>445</x:v>
-      </x:c>
-      <x:c r="N3" s="3" t="s">
-        <x:v>446</x:v>
-      </x:c>
-      <x:c r="O3" s="3" t="s">
-        <x:v>447</x:v>
-      </x:c>
-      <x:c r="P3" s="3" t="s">
-        <x:v>448</x:v>
-      </x:c>
-      <x:c r="Q3" s="3" t="s">
-        <x:v>449</x:v>
-      </x:c>
-      <x:c r="R3" s="3" t="s">
-        <x:v>450</x:v>
-      </x:c>
-      <x:c r="S3" s="3" t="s">
-        <x:v>451</x:v>
-      </x:c>
-      <x:c r="T3" s="3" t="s">
-        <x:v>452</x:v>
-      </x:c>
-      <x:c r="U3" s="3" t="s">
-        <x:v>2</x:v>
+      <x:c r="A3" s="3" t="str">
+        <x:v>QE-002</x:v>
+      </x:c>
+      <x:c r="B3" s="3" t="str">
+        <x:v>Maliev.QuoteEngine</x:v>
+      </x:c>
+      <x:c r="C3" s="3" t="str">
+        <x:v>Agent health and readiness</x:v>
+      </x:c>
+      <x:c r="D3" s="3" t="str">
+        <x:v>As a customer, I can see whether the quote agent is available before sending work.</x:v>
+      </x:c>
+      <x:c r="E3" s="3" t="str">
+        <x:v>Agent health endpoint and shell status indicators reflect backend readiness and keep composer state aligned.</x:v>
+      </x:c>
+      <x:c r="F3" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G3" s="3" t="str">
+        <x:v>Focused QE-002 agent health/readiness tests passed 2026-06-23.</x:v>
+      </x:c>
+      <x:c r="H3" s="3" t="str">
+        <x:v>No current health/readiness behavior error observed in focused automated retest. Live Aspire smoke could not run because no QuoteEngine BFF/Aspire-hosted route was listening in the current environment.</x:v>
+      </x:c>
+      <x:c r="I3" s="3" t="str">
+        <x:v>No code fix required in this slice; current implementation covers /quote/v1/agent/health ready/unavailable responses, client 503 health deserialization, bounded readiness timeout, and shell status polling.</x:v>
+      </x:c>
+      <x:c r="J3" s="3" t="str">
+        <x:v>Retested focused QE-002 set 5/5 passed.</x:v>
+      </x:c>
+      <x:c r="K3" s="3" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="L3" s="3" t="str">
+        <x:v>Shell status -&gt; quote/v1/agent/health -&gt; readiness state</x:v>
+      </x:c>
+      <x:c r="M3" s="3" t="str">
+        <x:v>QuoteAgentLaunchShell.razor</x:v>
+      </x:c>
+      <x:c r="N3" s="3" t="str">
+        <x:v>Agent status dot/composer gating</x:v>
+      </x:c>
+      <x:c r="O3" s="3" t="str">
+        <x:v>AgentController GET health</x:v>
+      </x:c>
+      <x:c r="P3" s="3" t="str">
+        <x:v>dotnet test Maliev.QuoteEngine.slnx --filter "FullyQualifiedName~QuoteAgentEndpointTests.Agent_health_reports_ready_when_chatbot_service_is_available|FullyQualifiedName~QuoteAgentEndpointTests.Agent_health_reports_unavailable_when_chatbot_service_is_offline|FullyQualifiedName~QuoteEngineSourceTests.QuoteAgentLaunchShell_status_dot_uses_backend_health_not_composer_errors|FullyQualifiedName~QuoteEngineSourceTests.ChatbotServiceClient_ReadinessCheck_DoesNotWarnForExpectedOfflinePolling|FullyQualifiedName~QuoteEngineSourceTests.ChatbotServiceClient_ReadinessCheck_UsesBoundedTimeoutForOfflineServices" --verbosity minimal =&gt; Passed 5/5. Local process/listener probe =&gt; no Maliev.QuoteEngine BFF/Aspire-hosted route listening; live smoke not available in current environment.</x:v>
+      </x:c>
+      <x:c r="Q3" s="3" t="str">
+        <x:v>QuoteEngine BFF, Agent service</x:v>
+      </x:c>
+      <x:c r="R3" s="3" t="str">
+        <x:v>Read-only readiness</x:v>
+      </x:c>
+      <x:c r="S3" s="3" t="str">
+        <x:v>No remaining agent health/readiness source or endpoint behavior gap found in current focused automated coverage; live Aspire readiness smoke still requires a running QuoteEngine host.</x:v>
+      </x:c>
+      <x:c r="T3" s="3" t="str">
+        <x:v>Maliev.QuoteEngine.Bff/Controllers/AgentController.cs; Maliev.QuoteEngine.Bff/Clients/ChatbotServiceClient.cs; Maliev.QuoteEngine.Client/Services/QuoteEngineApiClient.cs; Maliev.QuoteEngine.Client/Components/QuoteAgent/QuoteAgentLaunchShell.razor; Maliev.QuoteEngine.Shared/Agent/QuoteAgentDtos.cs; Maliev.QuoteEngine.Tests/QuoteAgentEndpointTests.cs; Maliev.QuoteEngine.Tests/QuoteEngineSourceTests.cs</x:v>
+      </x:c>
+      <x:c r="U3" s="3" t="str">
+        <x:v>2026-06-23</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="93.25" hidden="0">
       <x:c r="A4" s="3" t="s">
-        <x:v>453</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>454</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="D4" s="3" t="s">
-        <x:v>455</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="E4" s="3" t="s">
-        <x:v>456</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="F4" s="3" t="s">
         <x:v>38</x:v>
@@ -8943,31 +8910,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L4" s="3" t="s">
-        <x:v>457</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="M4" s="3" t="s">
         <x:v>445</x:v>
       </x:c>
       <x:c r="N4" s="3" t="s">
-        <x:v>458</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="O4" s="3" t="s">
-        <x:v>459</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="P4" s="3" t="s">
-        <x:v>460</x:v>
+        <x:v>448</x:v>
       </x:c>
       <x:c r="Q4" s="3" t="s">
-        <x:v>461</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="R4" s="3" t="s">
-        <x:v>462</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="S4" s="3" t="s">
-        <x:v>463</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="T4" s="3" t="s">
-        <x:v>464</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="U4" s="3" t="s">
         <x:v>2</x:v>
@@ -8975,19 +8942,19 @@
     </x:row>
     <x:row r="5" ht="107.25" hidden="0">
       <x:c r="A5" s="3" t="s">
-        <x:v>465</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C5" s="3" t="s">
-        <x:v>466</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="D5" s="3" t="s">
-        <x:v>467</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="E5" s="3" t="s">
-        <x:v>468</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="F5" s="3" t="s">
         <x:v>38</x:v>
@@ -9008,31 +8975,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L5" s="3" t="s">
-        <x:v>469</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="M5" s="3" t="s">
         <x:v>445</x:v>
       </x:c>
       <x:c r="N5" s="3" t="s">
-        <x:v>470</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="O5" s="3" t="s">
-        <x:v>471</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="P5" s="3" t="s">
-        <x:v>472</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="Q5" s="3" t="s">
-        <x:v>473</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="R5" s="3" t="s">
-        <x:v>474</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="S5" s="3" t="s">
-        <x:v>475</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="T5" s="3" t="s">
-        <x:v>476</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="U5" s="3" t="s">
         <x:v>2</x:v>
@@ -9040,19 +9007,19 @@
     </x:row>
     <x:row r="6" ht="93.25" hidden="0">
       <x:c r="A6" s="3" t="s">
-        <x:v>477</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="B6" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C6" s="3" t="s">
-        <x:v>478</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="D6" s="3" t="s">
-        <x:v>479</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="E6" s="3" t="s">
-        <x:v>480</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="F6" s="3" t="s">
         <x:v>38</x:v>
@@ -9073,31 +9040,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L6" s="3" t="s">
-        <x:v>481</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="M6" s="3" t="s">
         <x:v>445</x:v>
       </x:c>
       <x:c r="N6" s="3" t="s">
-        <x:v>482</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="O6" s="3" t="s">
-        <x:v>483</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="P6" s="3" t="s">
-        <x:v>484</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="Q6" s="3" t="s">
-        <x:v>485</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="R6" s="3" t="s">
-        <x:v>486</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="S6" s="3" t="s">
-        <x:v>487</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="T6" s="3" t="s">
-        <x:v>488</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="U6" s="3" t="s">
         <x:v>2</x:v>
@@ -9105,19 +9072,19 @@
     </x:row>
     <x:row r="7" ht="93.25" hidden="0">
       <x:c r="A7" s="3" t="s">
-        <x:v>489</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>490</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="D7" s="3" t="s">
-        <x:v>491</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="E7" s="3" t="s">
-        <x:v>492</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="F7" s="3" t="s">
         <x:v>38</x:v>
@@ -9138,31 +9105,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="L7" s="3" t="s">
-        <x:v>493</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="M7" s="3" t="s">
         <x:v>445</x:v>
       </x:c>
       <x:c r="N7" s="3" t="s">
-        <x:v>494</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="O7" s="3" t="s">
-        <x:v>495</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="P7" s="3" t="s">
-        <x:v>496</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="Q7" s="3" t="s">
-        <x:v>449</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="R7" s="3" t="s">
-        <x:v>497</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="S7" s="3" t="s">
-        <x:v>498</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="T7" s="3" t="s">
-        <x:v>499</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="U7" s="3" t="s">
         <x:v>2</x:v>
@@ -9170,19 +9137,19 @@
     </x:row>
     <x:row r="8" ht="93.25" hidden="0">
       <x:c r="A8" s="3" t="s">
-        <x:v>500</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>501</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="D8" s="3" t="s">
-        <x:v>502</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="E8" s="3" t="s">
-        <x:v>503</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="F8" s="3" t="s">
         <x:v>38</x:v>
@@ -9203,31 +9170,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L8" s="3" t="s">
-        <x:v>504</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="M8" s="3" t="s">
         <x:v>445</x:v>
       </x:c>
       <x:c r="N8" s="3" t="s">
-        <x:v>505</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="O8" s="3" t="s">
-        <x:v>506</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="P8" s="3" t="s">
-        <x:v>507</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="Q8" s="3" t="s">
-        <x:v>508</x:v>
+        <x:v>497</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
-        <x:v>509</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="S8" s="3" t="s">
-        <x:v>510</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="T8" s="3" t="s">
-        <x:v>511</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="U8" s="3" t="s">
         <x:v>2</x:v>
@@ -9235,19 +9202,19 @@
     </x:row>
     <x:row r="9" ht="93.25" hidden="0">
       <x:c r="A9" s="3" t="s">
-        <x:v>512</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="B9" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C9" s="3" t="s">
-        <x:v>513</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="D9" s="3" t="s">
-        <x:v>514</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="E9" s="3" t="s">
-        <x:v>515</x:v>
+        <x:v>504</x:v>
       </x:c>
       <x:c r="F9" s="3" t="s">
         <x:v>38</x:v>
@@ -9268,31 +9235,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L9" s="3" t="s">
-        <x:v>516</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="M9" s="3" t="s">
         <x:v>445</x:v>
       </x:c>
       <x:c r="N9" s="3" t="s">
-        <x:v>517</x:v>
+        <x:v>506</x:v>
       </x:c>
       <x:c r="O9" s="3" t="s">
-        <x:v>518</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="P9" s="3" t="s">
-        <x:v>519</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="Q9" s="3" t="s">
-        <x:v>520</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
-        <x:v>521</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="S9" s="3" t="s">
-        <x:v>522</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="T9" s="3" t="s">
-        <x:v>523</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="U9" s="3" t="s">
         <x:v>2</x:v>
@@ -9300,19 +9267,19 @@
     </x:row>
     <x:row r="10" ht="93.25" hidden="0">
       <x:c r="A10" s="3" t="s">
-        <x:v>524</x:v>
+        <x:v>513</x:v>
       </x:c>
       <x:c r="B10" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C10" s="3" t="s">
-        <x:v>525</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="D10" s="3" t="s">
-        <x:v>526</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="E10" s="3" t="s">
-        <x:v>527</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="F10" s="3" t="s">
         <x:v>38</x:v>
@@ -9333,31 +9300,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L10" s="3" t="s">
-        <x:v>528</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="M10" s="3" t="s">
         <x:v>429</x:v>
       </x:c>
       <x:c r="N10" s="3" t="s">
-        <x:v>529</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="O10" s="3" t="s">
         <x:v>205</x:v>
       </x:c>
       <x:c r="P10" s="3" t="s">
-        <x:v>530</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="Q10" s="3" t="s">
-        <x:v>531</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="R10" s="3" t="s">
-        <x:v>532</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="S10" s="3" t="s">
-        <x:v>533</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="T10" s="3" t="s">
-        <x:v>534</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="U10" s="3" t="s">
         <x:v>2</x:v>
@@ -9365,19 +9332,19 @@
     </x:row>
     <x:row r="11" ht="93.25" hidden="0">
       <x:c r="A11" s="3" t="s">
-        <x:v>535</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="B11" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C11" s="3" t="s">
-        <x:v>536</x:v>
+        <x:v>525</x:v>
       </x:c>
       <x:c r="D11" s="3" t="s">
-        <x:v>537</x:v>
+        <x:v>526</x:v>
       </x:c>
       <x:c r="E11" s="3" t="s">
-        <x:v>538</x:v>
+        <x:v>527</x:v>
       </x:c>
       <x:c r="F11" s="3" t="s">
         <x:v>38</x:v>
@@ -9398,31 +9365,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L11" s="3" t="s">
-        <x:v>539</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="M11" s="3" t="s">
-        <x:v>540</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="N11" s="3" t="s">
-        <x:v>541</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="O11" s="3" t="s">
-        <x:v>542</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="P11" s="3" t="s">
-        <x:v>543</x:v>
+        <x:v>532</x:v>
       </x:c>
       <x:c r="Q11" s="3" t="s">
-        <x:v>544</x:v>
+        <x:v>533</x:v>
       </x:c>
       <x:c r="R11" s="3" t="s">
-        <x:v>545</x:v>
+        <x:v>534</x:v>
       </x:c>
       <x:c r="S11" s="3" t="s">
-        <x:v>546</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="T11" s="3" t="s">
-        <x:v>547</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="U11" s="3" t="s">
         <x:v>2</x:v>
@@ -9430,19 +9397,19 @@
     </x:row>
     <x:row r="12" ht="107.25" hidden="0">
       <x:c r="A12" s="3" t="s">
-        <x:v>548</x:v>
+        <x:v>537</x:v>
       </x:c>
       <x:c r="B12" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C12" s="3" t="s">
-        <x:v>549</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="D12" s="3" t="s">
-        <x:v>550</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="E12" s="3" t="s">
-        <x:v>551</x:v>
+        <x:v>540</x:v>
       </x:c>
       <x:c r="F12" s="3" t="s">
         <x:v>38</x:v>
@@ -9463,31 +9430,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L12" s="3" t="s">
-        <x:v>552</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M12" s="3" t="s">
         <x:v>445</x:v>
       </x:c>
       <x:c r="N12" s="3" t="s">
-        <x:v>553</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O12" s="3" t="s">
-        <x:v>554</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="P12" s="3" t="s">
-        <x:v>555</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="Q12" s="3" t="s">
-        <x:v>556</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="R12" s="3" t="s">
-        <x:v>557</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="S12" s="3" t="s">
-        <x:v>558</x:v>
+        <x:v>547</x:v>
       </x:c>
       <x:c r="T12" s="3" t="s">
-        <x:v>559</x:v>
+        <x:v>548</x:v>
       </x:c>
       <x:c r="U12" s="3" t="s">
         <x:v>2</x:v>
@@ -9495,19 +9462,19 @@
     </x:row>
     <x:row r="13" ht="93.25" hidden="0">
       <x:c r="A13" s="3" t="s">
-        <x:v>560</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="B13" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C13" s="3" t="s">
-        <x:v>561</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="D13" s="3" t="s">
-        <x:v>562</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="E13" s="3" t="s">
-        <x:v>563</x:v>
+        <x:v>552</x:v>
       </x:c>
       <x:c r="F13" s="3" t="s">
         <x:v>38</x:v>
@@ -9528,31 +9495,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L13" s="3" t="s">
-        <x:v>564</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="M13" s="3" t="s">
         <x:v>445</x:v>
       </x:c>
       <x:c r="N13" s="3" t="s">
-        <x:v>565</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="O13" s="3" t="s">
-        <x:v>566</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="P13" s="3" t="s">
-        <x:v>567</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="Q13" s="3" t="s">
-        <x:v>556</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="R13" s="3" t="s">
-        <x:v>568</x:v>
+        <x:v>557</x:v>
       </x:c>
       <x:c r="S13" s="3" t="s">
-        <x:v>569</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="T13" s="3" t="s">
-        <x:v>570</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="U13" s="3" t="s">
         <x:v>2</x:v>
@@ -9560,19 +9527,19 @@
     </x:row>
     <x:row r="14" ht="93.25" hidden="0">
       <x:c r="A14" s="3" t="s">
-        <x:v>571</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="B14" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C14" s="3" t="s">
-        <x:v>572</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="D14" s="3" t="s">
-        <x:v>573</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="E14" s="3" t="s">
-        <x:v>574</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="F14" s="3" t="s">
         <x:v>38</x:v>
@@ -9593,31 +9560,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L14" s="3" t="s">
-        <x:v>575</x:v>
+        <x:v>564</x:v>
       </x:c>
       <x:c r="M14" s="3" t="s">
-        <x:v>576</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="N14" s="3" t="s">
-        <x:v>577</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="O14" s="3" t="s">
-        <x:v>578</x:v>
+        <x:v>567</x:v>
       </x:c>
       <x:c r="P14" s="3" t="s">
-        <x:v>579</x:v>
+        <x:v>568</x:v>
       </x:c>
       <x:c r="Q14" s="3" t="s">
-        <x:v>580</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="R14" s="3" t="s">
-        <x:v>581</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="S14" s="3" t="s">
-        <x:v>582</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="T14" s="3" t="s">
-        <x:v>583</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="U14" s="3" t="s">
         <x:v>2</x:v>
@@ -9625,19 +9592,19 @@
     </x:row>
     <x:row r="15" ht="107.25" hidden="0">
       <x:c r="A15" s="3" t="s">
-        <x:v>584</x:v>
+        <x:v>573</x:v>
       </x:c>
       <x:c r="B15" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C15" s="3" t="s">
-        <x:v>585</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="D15" s="3" t="s">
-        <x:v>586</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="E15" s="3" t="s">
-        <x:v>587</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="F15" s="3" t="s">
         <x:v>38</x:v>
@@ -9658,31 +9625,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L15" s="3" t="s">
-        <x:v>588</x:v>
+        <x:v>577</x:v>
       </x:c>
       <x:c r="M15" s="3" t="s">
         <x:v>445</x:v>
       </x:c>
       <x:c r="N15" s="3" t="s">
-        <x:v>589</x:v>
+        <x:v>578</x:v>
       </x:c>
       <x:c r="O15" s="3" t="s">
-        <x:v>590</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="P15" s="3" t="s">
-        <x:v>591</x:v>
+        <x:v>580</x:v>
       </x:c>
       <x:c r="Q15" s="3" t="s">
-        <x:v>592</x:v>
+        <x:v>581</x:v>
       </x:c>
       <x:c r="R15" s="3" t="s">
-        <x:v>593</x:v>
+        <x:v>582</x:v>
       </x:c>
       <x:c r="S15" s="3" t="s">
-        <x:v>594</x:v>
+        <x:v>583</x:v>
       </x:c>
       <x:c r="T15" s="3" t="s">
-        <x:v>595</x:v>
+        <x:v>584</x:v>
       </x:c>
       <x:c r="U15" s="3" t="s">
         <x:v>2</x:v>
@@ -9690,19 +9657,19 @@
     </x:row>
     <x:row r="16" ht="107.25" hidden="0">
       <x:c r="A16" s="3" t="s">
-        <x:v>596</x:v>
+        <x:v>585</x:v>
       </x:c>
       <x:c r="B16" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C16" s="3" t="s">
-        <x:v>597</x:v>
+        <x:v>586</x:v>
       </x:c>
       <x:c r="D16" s="3" t="s">
-        <x:v>598</x:v>
+        <x:v>587</x:v>
       </x:c>
       <x:c r="E16" s="3" t="s">
-        <x:v>599</x:v>
+        <x:v>588</x:v>
       </x:c>
       <x:c r="F16" s="3" t="s">
         <x:v>38</x:v>
@@ -9723,31 +9690,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L16" s="3" t="s">
-        <x:v>600</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="M16" s="3" t="s">
         <x:v>445</x:v>
       </x:c>
       <x:c r="N16" s="3" t="s">
-        <x:v>601</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="O16" s="3" t="s">
-        <x:v>602</x:v>
+        <x:v>591</x:v>
       </x:c>
       <x:c r="P16" s="3" t="s">
-        <x:v>603</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="Q16" s="3" t="s">
-        <x:v>604</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="R16" s="3" t="s">
-        <x:v>605</x:v>
+        <x:v>594</x:v>
       </x:c>
       <x:c r="S16" s="3" t="s">
-        <x:v>606</x:v>
+        <x:v>595</x:v>
       </x:c>
       <x:c r="T16" s="3" t="s">
-        <x:v>607</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="U16" s="3" t="s">
         <x:v>2</x:v>
@@ -9755,19 +9722,19 @@
     </x:row>
     <x:row r="17" ht="93.25" hidden="0">
       <x:c r="A17" s="3" t="s">
-        <x:v>608</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="B17" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C17" s="3" t="s">
-        <x:v>609</x:v>
+        <x:v>598</x:v>
       </x:c>
       <x:c r="D17" s="3" t="s">
-        <x:v>610</x:v>
+        <x:v>599</x:v>
       </x:c>
       <x:c r="E17" s="3" t="s">
-        <x:v>611</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="F17" s="3" t="s">
         <x:v>38</x:v>
@@ -9788,31 +9755,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L17" s="3" t="s">
-        <x:v>612</x:v>
+        <x:v>601</x:v>
       </x:c>
       <x:c r="M17" s="3" t="s">
-        <x:v>613</x:v>
+        <x:v>602</x:v>
       </x:c>
       <x:c r="N17" s="3" t="s">
-        <x:v>614</x:v>
+        <x:v>603</x:v>
       </x:c>
       <x:c r="O17" s="3" t="s">
-        <x:v>615</x:v>
+        <x:v>604</x:v>
       </x:c>
       <x:c r="P17" s="3" t="s">
-        <x:v>616</x:v>
+        <x:v>605</x:v>
       </x:c>
       <x:c r="Q17" s="3" t="s">
-        <x:v>617</x:v>
+        <x:v>606</x:v>
       </x:c>
       <x:c r="R17" s="3" t="s">
-        <x:v>618</x:v>
+        <x:v>607</x:v>
       </x:c>
       <x:c r="S17" s="3" t="s">
-        <x:v>619</x:v>
+        <x:v>608</x:v>
       </x:c>
       <x:c r="T17" s="3" t="s">
-        <x:v>620</x:v>
+        <x:v>609</x:v>
       </x:c>
       <x:c r="U17" s="3" t="s">
         <x:v>2</x:v>
@@ -9820,19 +9787,19 @@
     </x:row>
     <x:row r="18" ht="93.25" hidden="0">
       <x:c r="A18" s="3" t="s">
-        <x:v>621</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="B18" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C18" s="3" t="s">
-        <x:v>622</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="D18" s="3" t="s">
-        <x:v>623</x:v>
+        <x:v>612</x:v>
       </x:c>
       <x:c r="E18" s="3" t="s">
-        <x:v>624</x:v>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="F18" s="3" t="s">
         <x:v>38</x:v>
@@ -9853,31 +9820,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L18" s="3" t="s">
-        <x:v>625</x:v>
+        <x:v>614</x:v>
       </x:c>
       <x:c r="M18" s="3" t="s">
-        <x:v>626</x:v>
+        <x:v>615</x:v>
       </x:c>
       <x:c r="N18" s="3" t="s">
-        <x:v>627</x:v>
+        <x:v>616</x:v>
       </x:c>
       <x:c r="O18" s="3" t="s">
-        <x:v>628</x:v>
+        <x:v>617</x:v>
       </x:c>
       <x:c r="P18" s="3" t="s">
-        <x:v>629</x:v>
+        <x:v>618</x:v>
       </x:c>
       <x:c r="Q18" s="3" t="s">
-        <x:v>630</x:v>
+        <x:v>619</x:v>
       </x:c>
       <x:c r="R18" s="3" t="s">
-        <x:v>631</x:v>
+        <x:v>620</x:v>
       </x:c>
       <x:c r="S18" s="3" t="s">
-        <x:v>632</x:v>
+        <x:v>621</x:v>
       </x:c>
       <x:c r="T18" s="3" t="s">
-        <x:v>633</x:v>
+        <x:v>622</x:v>
       </x:c>
       <x:c r="U18" s="3" t="s">
         <x:v>2</x:v>
@@ -9885,19 +9852,19 @@
     </x:row>
     <x:row r="19" ht="93.25" hidden="0">
       <x:c r="A19" s="3" t="s">
-        <x:v>634</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="B19" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C19" s="3" t="s">
-        <x:v>635</x:v>
+        <x:v>624</x:v>
       </x:c>
       <x:c r="D19" s="3" t="s">
-        <x:v>636</x:v>
+        <x:v>625</x:v>
       </x:c>
       <x:c r="E19" s="3" t="s">
-        <x:v>637</x:v>
+        <x:v>626</x:v>
       </x:c>
       <x:c r="F19" s="3" t="s">
         <x:v>38</x:v>
@@ -9918,31 +9885,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L19" s="3" t="s">
-        <x:v>638</x:v>
+        <x:v>627</x:v>
       </x:c>
       <x:c r="M19" s="3" t="s">
-        <x:v>639</x:v>
+        <x:v>628</x:v>
       </x:c>
       <x:c r="N19" s="3" t="s">
-        <x:v>640</x:v>
+        <x:v>629</x:v>
       </x:c>
       <x:c r="O19" s="3" t="s">
-        <x:v>641</x:v>
+        <x:v>630</x:v>
       </x:c>
       <x:c r="P19" s="3" t="s">
-        <x:v>642</x:v>
+        <x:v>631</x:v>
       </x:c>
       <x:c r="Q19" s="3" t="s">
-        <x:v>643</x:v>
+        <x:v>632</x:v>
       </x:c>
       <x:c r="R19" s="3" t="s">
-        <x:v>644</x:v>
+        <x:v>633</x:v>
       </x:c>
       <x:c r="S19" s="3" t="s">
-        <x:v>645</x:v>
+        <x:v>634</x:v>
       </x:c>
       <x:c r="T19" s="3" t="s">
-        <x:v>646</x:v>
+        <x:v>635</x:v>
       </x:c>
       <x:c r="U19" s="3" t="s">
         <x:v>2</x:v>
@@ -9950,19 +9917,19 @@
     </x:row>
     <x:row r="20" ht="79.25" hidden="0">
       <x:c r="A20" s="3" t="s">
-        <x:v>647</x:v>
+        <x:v>636</x:v>
       </x:c>
       <x:c r="B20" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C20" s="3" t="s">
-        <x:v>648</x:v>
+        <x:v>637</x:v>
       </x:c>
       <x:c r="D20" s="3" t="s">
-        <x:v>649</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="E20" s="3" t="s">
-        <x:v>650</x:v>
+        <x:v>639</x:v>
       </x:c>
       <x:c r="F20" s="3" t="s">
         <x:v>38</x:v>
@@ -9983,31 +9950,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L20" s="3" t="s">
-        <x:v>651</x:v>
+        <x:v>640</x:v>
       </x:c>
       <x:c r="M20" s="3" t="s">
-        <x:v>652</x:v>
+        <x:v>641</x:v>
       </x:c>
       <x:c r="N20" s="3" t="s">
-        <x:v>653</x:v>
+        <x:v>642</x:v>
       </x:c>
       <x:c r="O20" s="3" t="s">
-        <x:v>654</x:v>
+        <x:v>643</x:v>
       </x:c>
       <x:c r="P20" s="3" t="s">
-        <x:v>655</x:v>
+        <x:v>644</x:v>
       </x:c>
       <x:c r="Q20" s="3" t="s">
-        <x:v>656</x:v>
+        <x:v>645</x:v>
       </x:c>
       <x:c r="R20" s="3" t="s">
-        <x:v>657</x:v>
+        <x:v>646</x:v>
       </x:c>
       <x:c r="S20" s="3" t="s">
-        <x:v>658</x:v>
+        <x:v>647</x:v>
       </x:c>
       <x:c r="T20" s="3" t="s">
-        <x:v>659</x:v>
+        <x:v>648</x:v>
       </x:c>
       <x:c r="U20" s="3" t="s">
         <x:v>2</x:v>
@@ -10015,19 +9982,19 @@
     </x:row>
     <x:row r="21" ht="79.25" hidden="0">
       <x:c r="A21" s="3" t="s">
-        <x:v>660</x:v>
+        <x:v>649</x:v>
       </x:c>
       <x:c r="B21" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C21" s="3" t="s">
-        <x:v>661</x:v>
+        <x:v>650</x:v>
       </x:c>
       <x:c r="D21" s="3" t="s">
-        <x:v>662</x:v>
+        <x:v>651</x:v>
       </x:c>
       <x:c r="E21" s="3" t="s">
-        <x:v>663</x:v>
+        <x:v>652</x:v>
       </x:c>
       <x:c r="F21" s="3" t="s">
         <x:v>38</x:v>
@@ -10048,31 +10015,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L21" s="3" t="s">
-        <x:v>664</x:v>
+        <x:v>653</x:v>
       </x:c>
       <x:c r="M21" s="3" t="s">
-        <x:v>665</x:v>
+        <x:v>654</x:v>
       </x:c>
       <x:c r="N21" s="3" t="s">
-        <x:v>666</x:v>
+        <x:v>655</x:v>
       </x:c>
       <x:c r="O21" s="3" t="s">
         <x:v>218</x:v>
       </x:c>
       <x:c r="P21" s="3" t="s">
-        <x:v>667</x:v>
+        <x:v>656</x:v>
       </x:c>
       <x:c r="Q21" s="3" t="s">
-        <x:v>668</x:v>
+        <x:v>657</x:v>
       </x:c>
       <x:c r="R21" s="3" t="s">
         <x:v>221</x:v>
       </x:c>
       <x:c r="S21" s="3" t="s">
-        <x:v>669</x:v>
+        <x:v>658</x:v>
       </x:c>
       <x:c r="T21" s="3" t="s">
-        <x:v>670</x:v>
+        <x:v>659</x:v>
       </x:c>
       <x:c r="U21" s="3" t="s">
         <x:v>2</x:v>
@@ -10080,19 +10047,19 @@
     </x:row>
     <x:row r="22" ht="93.25" hidden="0">
       <x:c r="A22" s="3" t="s">
-        <x:v>671</x:v>
+        <x:v>660</x:v>
       </x:c>
       <x:c r="B22" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C22" s="3" t="s">
-        <x:v>672</x:v>
+        <x:v>661</x:v>
       </x:c>
       <x:c r="D22" s="3" t="s">
-        <x:v>673</x:v>
+        <x:v>662</x:v>
       </x:c>
       <x:c r="E22" s="3" t="s">
-        <x:v>674</x:v>
+        <x:v>663</x:v>
       </x:c>
       <x:c r="F22" s="3" t="s">
         <x:v>38</x:v>
@@ -10113,31 +10080,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L22" s="3" t="s">
-        <x:v>675</x:v>
+        <x:v>664</x:v>
       </x:c>
       <x:c r="M22" s="3" t="s">
-        <x:v>540</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="N22" s="3" t="s">
-        <x:v>676</x:v>
+        <x:v>665</x:v>
       </x:c>
       <x:c r="O22" s="3" t="s">
-        <x:v>677</x:v>
+        <x:v>666</x:v>
       </x:c>
       <x:c r="P22" s="3" t="s">
-        <x:v>678</x:v>
+        <x:v>667</x:v>
       </x:c>
       <x:c r="Q22" s="3" t="s">
-        <x:v>679</x:v>
+        <x:v>668</x:v>
       </x:c>
       <x:c r="R22" s="3" t="s">
-        <x:v>680</x:v>
+        <x:v>669</x:v>
       </x:c>
       <x:c r="S22" s="3" t="s">
-        <x:v>681</x:v>
+        <x:v>670</x:v>
       </x:c>
       <x:c r="T22" s="3" t="s">
-        <x:v>682</x:v>
+        <x:v>671</x:v>
       </x:c>
       <x:c r="U22" s="3" t="s">
         <x:v>2</x:v>
@@ -10145,19 +10112,19 @@
     </x:row>
     <x:row r="23" ht="93.25" hidden="0">
       <x:c r="A23" s="3" t="s">
-        <x:v>683</x:v>
+        <x:v>672</x:v>
       </x:c>
       <x:c r="B23" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C23" s="3" t="s">
-        <x:v>684</x:v>
+        <x:v>673</x:v>
       </x:c>
       <x:c r="D23" s="3" t="s">
-        <x:v>685</x:v>
+        <x:v>674</x:v>
       </x:c>
       <x:c r="E23" s="3" t="s">
-        <x:v>686</x:v>
+        <x:v>675</x:v>
       </x:c>
       <x:c r="F23" s="3" t="s">
         <x:v>38</x:v>
@@ -10178,31 +10145,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L23" s="3" t="s">
-        <x:v>687</x:v>
+        <x:v>676</x:v>
       </x:c>
       <x:c r="M23" s="3" t="s">
-        <x:v>688</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="N23" s="3" t="s">
-        <x:v>689</x:v>
+        <x:v>678</x:v>
       </x:c>
       <x:c r="O23" s="3" t="s">
-        <x:v>690</x:v>
+        <x:v>679</x:v>
       </x:c>
       <x:c r="P23" s="3" t="s">
-        <x:v>691</x:v>
+        <x:v>680</x:v>
       </x:c>
       <x:c r="Q23" s="3" t="s">
-        <x:v>692</x:v>
+        <x:v>681</x:v>
       </x:c>
       <x:c r="R23" s="3" t="s">
-        <x:v>693</x:v>
+        <x:v>682</x:v>
       </x:c>
       <x:c r="S23" s="3" t="s">
-        <x:v>694</x:v>
+        <x:v>683</x:v>
       </x:c>
       <x:c r="T23" s="3" t="s">
-        <x:v>695</x:v>
+        <x:v>684</x:v>
       </x:c>
       <x:c r="U23" s="3" t="s">
         <x:v>2</x:v>
@@ -10210,19 +10177,19 @@
     </x:row>
     <x:row r="24" ht="79.25" hidden="0">
       <x:c r="A24" s="3" t="s">
-        <x:v>696</x:v>
+        <x:v>685</x:v>
       </x:c>
       <x:c r="B24" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C24" s="3" t="s">
-        <x:v>697</x:v>
+        <x:v>686</x:v>
       </x:c>
       <x:c r="D24" s="3" t="s">
-        <x:v>698</x:v>
+        <x:v>687</x:v>
       </x:c>
       <x:c r="E24" s="3" t="s">
-        <x:v>699</x:v>
+        <x:v>688</x:v>
       </x:c>
       <x:c r="F24" s="3" t="s">
         <x:v>38</x:v>
@@ -10243,31 +10210,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L24" s="3" t="s">
-        <x:v>700</x:v>
+        <x:v>689</x:v>
       </x:c>
       <x:c r="M24" s="3" t="s">
-        <x:v>665</x:v>
+        <x:v>654</x:v>
       </x:c>
       <x:c r="N24" s="3" t="s">
-        <x:v>701</x:v>
+        <x:v>690</x:v>
       </x:c>
       <x:c r="O24" s="3" t="s">
-        <x:v>702</x:v>
+        <x:v>691</x:v>
       </x:c>
       <x:c r="P24" s="3" t="s">
-        <x:v>703</x:v>
+        <x:v>692</x:v>
       </x:c>
       <x:c r="Q24" s="3" t="s">
-        <x:v>704</x:v>
+        <x:v>693</x:v>
       </x:c>
       <x:c r="R24" s="3" t="s">
-        <x:v>705</x:v>
+        <x:v>694</x:v>
       </x:c>
       <x:c r="S24" s="3" t="s">
-        <x:v>706</x:v>
+        <x:v>695</x:v>
       </x:c>
       <x:c r="T24" s="3" t="s">
-        <x:v>707</x:v>
+        <x:v>696</x:v>
       </x:c>
       <x:c r="U24" s="3" t="s">
         <x:v>2</x:v>
@@ -10275,19 +10242,19 @@
     </x:row>
     <x:row r="25" ht="79.25" hidden="0">
       <x:c r="A25" s="3" t="s">
-        <x:v>708</x:v>
+        <x:v>697</x:v>
       </x:c>
       <x:c r="B25" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C25" s="3" t="s">
-        <x:v>709</x:v>
+        <x:v>698</x:v>
       </x:c>
       <x:c r="D25" s="3" t="s">
-        <x:v>710</x:v>
+        <x:v>699</x:v>
       </x:c>
       <x:c r="E25" s="3" t="s">
-        <x:v>711</x:v>
+        <x:v>700</x:v>
       </x:c>
       <x:c r="F25" s="3" t="s">
         <x:v>38</x:v>
@@ -10308,31 +10275,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L25" s="3" t="s">
-        <x:v>712</x:v>
+        <x:v>701</x:v>
       </x:c>
       <x:c r="M25" s="3" t="s">
-        <x:v>665</x:v>
+        <x:v>654</x:v>
       </x:c>
       <x:c r="N25" s="3" t="s">
-        <x:v>713</x:v>
+        <x:v>702</x:v>
       </x:c>
       <x:c r="O25" s="3" t="s">
-        <x:v>714</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="P25" s="3" t="s">
-        <x:v>715</x:v>
+        <x:v>704</x:v>
       </x:c>
       <x:c r="Q25" s="3" t="s">
-        <x:v>716</x:v>
+        <x:v>705</x:v>
       </x:c>
       <x:c r="R25" s="3" t="s">
-        <x:v>717</x:v>
+        <x:v>706</x:v>
       </x:c>
       <x:c r="S25" s="3" t="s">
-        <x:v>718</x:v>
+        <x:v>707</x:v>
       </x:c>
       <x:c r="T25" s="3" t="s">
-        <x:v>719</x:v>
+        <x:v>708</x:v>
       </x:c>
       <x:c r="U25" s="3" t="s">
         <x:v>2</x:v>
@@ -10340,19 +10307,19 @@
     </x:row>
     <x:row r="26" ht="79.25" hidden="0">
       <x:c r="A26" s="3" t="s">
-        <x:v>720</x:v>
+        <x:v>709</x:v>
       </x:c>
       <x:c r="B26" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C26" s="3" t="s">
-        <x:v>721</x:v>
+        <x:v>710</x:v>
       </x:c>
       <x:c r="D26" s="3" t="s">
-        <x:v>722</x:v>
+        <x:v>711</x:v>
       </x:c>
       <x:c r="E26" s="3" t="s">
-        <x:v>723</x:v>
+        <x:v>712</x:v>
       </x:c>
       <x:c r="F26" s="3" t="s">
         <x:v>38</x:v>
@@ -10373,31 +10340,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L26" s="3" t="s">
-        <x:v>724</x:v>
+        <x:v>713</x:v>
       </x:c>
       <x:c r="M26" s="3" t="s">
-        <x:v>725</x:v>
+        <x:v>714</x:v>
       </x:c>
       <x:c r="N26" s="3" t="s">
-        <x:v>726</x:v>
+        <x:v>715</x:v>
       </x:c>
       <x:c r="O26" s="3" t="s">
-        <x:v>727</x:v>
+        <x:v>716</x:v>
       </x:c>
       <x:c r="P26" s="3" t="s">
-        <x:v>728</x:v>
+        <x:v>717</x:v>
       </x:c>
       <x:c r="Q26" s="3" t="s">
-        <x:v>729</x:v>
+        <x:v>718</x:v>
       </x:c>
       <x:c r="R26" s="3" t="s">
-        <x:v>730</x:v>
+        <x:v>719</x:v>
       </x:c>
       <x:c r="S26" s="3" t="s">
-        <x:v>731</x:v>
+        <x:v>720</x:v>
       </x:c>
       <x:c r="T26" s="3" t="s">
-        <x:v>732</x:v>
+        <x:v>721</x:v>
       </x:c>
       <x:c r="U26" s="3" t="s">
         <x:v>2</x:v>
@@ -10405,19 +10372,19 @@
     </x:row>
     <x:row r="27" ht="79.25" hidden="0">
       <x:c r="A27" s="3" t="s">
-        <x:v>733</x:v>
+        <x:v>722</x:v>
       </x:c>
       <x:c r="B27" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C27" s="3" t="s">
-        <x:v>734</x:v>
+        <x:v>723</x:v>
       </x:c>
       <x:c r="D27" s="3" t="s">
-        <x:v>735</x:v>
+        <x:v>724</x:v>
       </x:c>
       <x:c r="E27" s="3" t="s">
-        <x:v>736</x:v>
+        <x:v>725</x:v>
       </x:c>
       <x:c r="F27" s="3" t="s">
         <x:v>38</x:v>
@@ -10438,31 +10405,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L27" s="3" t="s">
-        <x:v>737</x:v>
+        <x:v>726</x:v>
       </x:c>
       <x:c r="M27" s="3" t="s">
-        <x:v>738</x:v>
+        <x:v>727</x:v>
       </x:c>
       <x:c r="N27" s="3" t="s">
-        <x:v>739</x:v>
+        <x:v>728</x:v>
       </x:c>
       <x:c r="O27" s="3" t="s">
-        <x:v>740</x:v>
+        <x:v>729</x:v>
       </x:c>
       <x:c r="P27" s="3" t="s">
-        <x:v>741</x:v>
+        <x:v>730</x:v>
       </x:c>
       <x:c r="Q27" s="3" t="s">
-        <x:v>742</x:v>
+        <x:v>731</x:v>
       </x:c>
       <x:c r="R27" s="3" t="s">
-        <x:v>743</x:v>
+        <x:v>732</x:v>
       </x:c>
       <x:c r="S27" s="3" t="s">
-        <x:v>744</x:v>
+        <x:v>733</x:v>
       </x:c>
       <x:c r="T27" s="3" t="s">
-        <x:v>745</x:v>
+        <x:v>734</x:v>
       </x:c>
       <x:c r="U27" s="3" t="s">
         <x:v>2</x:v>
@@ -10470,19 +10437,19 @@
     </x:row>
     <x:row r="28" ht="93.25" hidden="0">
       <x:c r="A28" s="3" t="s">
-        <x:v>746</x:v>
+        <x:v>735</x:v>
       </x:c>
       <x:c r="B28" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C28" s="3" t="s">
-        <x:v>747</x:v>
+        <x:v>736</x:v>
       </x:c>
       <x:c r="D28" s="3" t="s">
-        <x:v>748</x:v>
+        <x:v>737</x:v>
       </x:c>
       <x:c r="E28" s="3" t="s">
-        <x:v>749</x:v>
+        <x:v>738</x:v>
       </x:c>
       <x:c r="F28" s="3" t="s">
         <x:v>38</x:v>
@@ -10503,31 +10470,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L28" s="3" t="s">
-        <x:v>750</x:v>
+        <x:v>739</x:v>
       </x:c>
       <x:c r="M28" s="3" t="s">
-        <x:v>751</x:v>
+        <x:v>740</x:v>
       </x:c>
       <x:c r="N28" s="3" t="s">
-        <x:v>752</x:v>
+        <x:v>741</x:v>
       </x:c>
       <x:c r="O28" s="3" t="s">
-        <x:v>753</x:v>
+        <x:v>742</x:v>
       </x:c>
       <x:c r="P28" s="3" t="s">
-        <x:v>754</x:v>
+        <x:v>743</x:v>
       </x:c>
       <x:c r="Q28" s="3" t="s">
-        <x:v>755</x:v>
+        <x:v>744</x:v>
       </x:c>
       <x:c r="R28" s="3" t="s">
-        <x:v>756</x:v>
+        <x:v>745</x:v>
       </x:c>
       <x:c r="S28" s="3" t="s">
         <x:v>286</x:v>
       </x:c>
       <x:c r="T28" s="3" t="s">
-        <x:v>757</x:v>
+        <x:v>746</x:v>
       </x:c>
       <x:c r="U28" s="3" t="s">
         <x:v>2</x:v>
@@ -10535,19 +10502,19 @@
     </x:row>
     <x:row r="29" ht="93.25" hidden="0">
       <x:c r="A29" s="3" t="s">
-        <x:v>758</x:v>
+        <x:v>747</x:v>
       </x:c>
       <x:c r="B29" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C29" s="3" t="s">
-        <x:v>759</x:v>
+        <x:v>748</x:v>
       </x:c>
       <x:c r="D29" s="3" t="s">
-        <x:v>760</x:v>
+        <x:v>749</x:v>
       </x:c>
       <x:c r="E29" s="3" t="s">
-        <x:v>761</x:v>
+        <x:v>750</x:v>
       </x:c>
       <x:c r="F29" s="3" t="s">
         <x:v>38</x:v>
@@ -10568,31 +10535,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="L29" s="3" t="s">
-        <x:v>762</x:v>
+        <x:v>751</x:v>
       </x:c>
       <x:c r="M29" s="3" t="s">
-        <x:v>763</x:v>
+        <x:v>752</x:v>
       </x:c>
       <x:c r="N29" s="3" t="s">
-        <x:v>764</x:v>
+        <x:v>753</x:v>
       </x:c>
       <x:c r="O29" s="3" t="s">
-        <x:v>765</x:v>
+        <x:v>754</x:v>
       </x:c>
       <x:c r="P29" s="3" t="s">
-        <x:v>766</x:v>
+        <x:v>755</x:v>
       </x:c>
       <x:c r="Q29" s="3" t="s">
-        <x:v>767</x:v>
+        <x:v>756</x:v>
       </x:c>
       <x:c r="R29" s="3" t="s">
-        <x:v>768</x:v>
+        <x:v>757</x:v>
       </x:c>
       <x:c r="S29" s="3" t="s">
-        <x:v>769</x:v>
+        <x:v>758</x:v>
       </x:c>
       <x:c r="T29" s="3" t="s">
-        <x:v>770</x:v>
+        <x:v>759</x:v>
       </x:c>
       <x:c r="U29" s="3" t="s">
         <x:v>2</x:v>
@@ -10600,19 +10567,19 @@
     </x:row>
     <x:row r="30" ht="93.25" hidden="0">
       <x:c r="A30" s="3" t="s">
-        <x:v>771</x:v>
+        <x:v>760</x:v>
       </x:c>
       <x:c r="B30" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C30" s="3" t="s">
-        <x:v>772</x:v>
+        <x:v>761</x:v>
       </x:c>
       <x:c r="D30" s="3" t="s">
-        <x:v>773</x:v>
+        <x:v>762</x:v>
       </x:c>
       <x:c r="E30" s="3" t="s">
-        <x:v>774</x:v>
+        <x:v>763</x:v>
       </x:c>
       <x:c r="F30" s="3" t="s">
         <x:v>38</x:v>
@@ -10633,31 +10600,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L30" s="3" t="s">
-        <x:v>775</x:v>
+        <x:v>764</x:v>
       </x:c>
       <x:c r="M30" s="3" t="s">
-        <x:v>776</x:v>
+        <x:v>765</x:v>
       </x:c>
       <x:c r="N30" s="3" t="s">
-        <x:v>777</x:v>
+        <x:v>766</x:v>
       </x:c>
       <x:c r="O30" s="3" t="s">
-        <x:v>778</x:v>
+        <x:v>767</x:v>
       </x:c>
       <x:c r="P30" s="3" t="s">
-        <x:v>779</x:v>
+        <x:v>768</x:v>
       </x:c>
       <x:c r="Q30" s="3" t="s">
-        <x:v>780</x:v>
+        <x:v>769</x:v>
       </x:c>
       <x:c r="R30" s="3" t="s">
-        <x:v>781</x:v>
+        <x:v>770</x:v>
       </x:c>
       <x:c r="S30" s="3" t="s">
-        <x:v>782</x:v>
+        <x:v>771</x:v>
       </x:c>
       <x:c r="T30" s="3" t="s">
-        <x:v>783</x:v>
+        <x:v>772</x:v>
       </x:c>
       <x:c r="U30" s="3" t="s">
         <x:v>2</x:v>
@@ -10665,19 +10632,19 @@
     </x:row>
     <x:row r="31" ht="93.25" hidden="0">
       <x:c r="A31" s="3" t="s">
-        <x:v>784</x:v>
+        <x:v>773</x:v>
       </x:c>
       <x:c r="B31" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C31" s="3" t="s">
-        <x:v>785</x:v>
+        <x:v>774</x:v>
       </x:c>
       <x:c r="D31" s="3" t="s">
-        <x:v>786</x:v>
+        <x:v>775</x:v>
       </x:c>
       <x:c r="E31" s="3" t="s">
-        <x:v>787</x:v>
+        <x:v>776</x:v>
       </x:c>
       <x:c r="F31" s="3" t="s">
         <x:v>38</x:v>
@@ -10698,31 +10665,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="L31" s="3" t="s">
-        <x:v>788</x:v>
+        <x:v>777</x:v>
       </x:c>
       <x:c r="M31" s="3" t="s">
-        <x:v>789</x:v>
+        <x:v>778</x:v>
       </x:c>
       <x:c r="N31" s="3" t="s">
-        <x:v>790</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="O31" s="3" t="s">
-        <x:v>791</x:v>
+        <x:v>780</x:v>
       </x:c>
       <x:c r="P31" s="3" t="s">
-        <x:v>792</x:v>
+        <x:v>781</x:v>
       </x:c>
       <x:c r="Q31" s="3" t="s">
-        <x:v>793</x:v>
+        <x:v>782</x:v>
       </x:c>
       <x:c r="R31" s="3" t="s">
-        <x:v>794</x:v>
+        <x:v>783</x:v>
       </x:c>
       <x:c r="S31" s="3" t="s">
-        <x:v>795</x:v>
+        <x:v>784</x:v>
       </x:c>
       <x:c r="T31" s="3" t="s">
-        <x:v>796</x:v>
+        <x:v>785</x:v>
       </x:c>
       <x:c r="U31" s="3" t="s">
         <x:v>2</x:v>
@@ -10730,19 +10697,19 @@
     </x:row>
     <x:row r="32" ht="93.25" hidden="0">
       <x:c r="A32" s="3" t="s">
-        <x:v>797</x:v>
+        <x:v>786</x:v>
       </x:c>
       <x:c r="B32" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C32" s="3" t="s">
-        <x:v>798</x:v>
+        <x:v>787</x:v>
       </x:c>
       <x:c r="D32" s="3" t="s">
-        <x:v>799</x:v>
+        <x:v>788</x:v>
       </x:c>
       <x:c r="E32" s="3" t="s">
-        <x:v>800</x:v>
+        <x:v>789</x:v>
       </x:c>
       <x:c r="F32" s="3" t="s">
         <x:v>38</x:v>
@@ -10763,31 +10730,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L32" s="3" t="s">
-        <x:v>801</x:v>
+        <x:v>790</x:v>
       </x:c>
       <x:c r="M32" s="3" t="s">
-        <x:v>802</x:v>
+        <x:v>791</x:v>
       </x:c>
       <x:c r="N32" s="3" t="s">
-        <x:v>803</x:v>
+        <x:v>792</x:v>
       </x:c>
       <x:c r="O32" s="3" t="s">
-        <x:v>804</x:v>
+        <x:v>793</x:v>
       </x:c>
       <x:c r="P32" s="3" t="s">
-        <x:v>805</x:v>
+        <x:v>794</x:v>
       </x:c>
       <x:c r="Q32" s="3" t="s">
-        <x:v>806</x:v>
+        <x:v>795</x:v>
       </x:c>
       <x:c r="R32" s="3" t="s">
-        <x:v>807</x:v>
+        <x:v>796</x:v>
       </x:c>
       <x:c r="S32" s="3" t="s">
-        <x:v>808</x:v>
+        <x:v>797</x:v>
       </x:c>
       <x:c r="T32" s="3" t="s">
-        <x:v>809</x:v>
+        <x:v>798</x:v>
       </x:c>
       <x:c r="U32" s="3" t="s">
         <x:v>2</x:v>
@@ -10795,19 +10762,19 @@
     </x:row>
     <x:row r="33" ht="93.25" hidden="0">
       <x:c r="A33" s="3" t="s">
-        <x:v>810</x:v>
+        <x:v>799</x:v>
       </x:c>
       <x:c r="B33" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C33" s="3" t="s">
-        <x:v>811</x:v>
+        <x:v>800</x:v>
       </x:c>
       <x:c r="D33" s="3" t="s">
-        <x:v>812</x:v>
+        <x:v>801</x:v>
       </x:c>
       <x:c r="E33" s="3" t="s">
-        <x:v>813</x:v>
+        <x:v>802</x:v>
       </x:c>
       <x:c r="F33" s="3" t="s">
         <x:v>38</x:v>
@@ -10828,31 +10795,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L33" s="3" t="s">
-        <x:v>814</x:v>
+        <x:v>803</x:v>
       </x:c>
       <x:c r="M33" s="3" t="s">
-        <x:v>815</x:v>
+        <x:v>804</x:v>
       </x:c>
       <x:c r="N33" s="3" t="s">
-        <x:v>816</x:v>
+        <x:v>805</x:v>
       </x:c>
       <x:c r="O33" s="3" t="s">
-        <x:v>817</x:v>
+        <x:v>806</x:v>
       </x:c>
       <x:c r="P33" s="3" t="s">
-        <x:v>818</x:v>
+        <x:v>807</x:v>
       </x:c>
       <x:c r="Q33" s="3" t="s">
-        <x:v>819</x:v>
+        <x:v>808</x:v>
       </x:c>
       <x:c r="R33" s="3" t="s">
-        <x:v>820</x:v>
+        <x:v>809</x:v>
       </x:c>
       <x:c r="S33" s="3" t="s">
-        <x:v>821</x:v>
+        <x:v>810</x:v>
       </x:c>
       <x:c r="T33" s="3" t="s">
-        <x:v>822</x:v>
+        <x:v>811</x:v>
       </x:c>
       <x:c r="U33" s="3" t="s">
         <x:v>2</x:v>
@@ -10860,7 +10827,7 @@
     </x:row>
     <x:row r="34" ht="93.25" hidden="0">
       <x:c r="A34" s="3" t="s">
-        <x:v>823</x:v>
+        <x:v>812</x:v>
       </x:c>
       <x:c r="B34" s="3" t="s">
         <x:v>9</x:v>
@@ -10869,10 +10836,10 @@
         <x:v>313</x:v>
       </x:c>
       <x:c r="D34" s="3" t="s">
-        <x:v>824</x:v>
+        <x:v>813</x:v>
       </x:c>
       <x:c r="E34" s="3" t="s">
-        <x:v>825</x:v>
+        <x:v>814</x:v>
       </x:c>
       <x:c r="F34" s="3" t="s">
         <x:v>38</x:v>
@@ -10893,31 +10860,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="L34" s="3" t="s">
-        <x:v>826</x:v>
+        <x:v>815</x:v>
       </x:c>
       <x:c r="M34" s="3" t="s">
-        <x:v>827</x:v>
+        <x:v>816</x:v>
       </x:c>
       <x:c r="N34" s="3" t="s">
-        <x:v>828</x:v>
+        <x:v>817</x:v>
       </x:c>
       <x:c r="O34" s="3" t="s">
-        <x:v>829</x:v>
+        <x:v>818</x:v>
       </x:c>
       <x:c r="P34" s="3" t="s">
-        <x:v>830</x:v>
+        <x:v>819</x:v>
       </x:c>
       <x:c r="Q34" s="3" t="s">
-        <x:v>831</x:v>
+        <x:v>820</x:v>
       </x:c>
       <x:c r="R34" s="3" t="s">
-        <x:v>832</x:v>
+        <x:v>821</x:v>
       </x:c>
       <x:c r="S34" s="3" t="s">
         <x:v>323</x:v>
       </x:c>
       <x:c r="T34" s="3" t="s">
-        <x:v>833</x:v>
+        <x:v>822</x:v>
       </x:c>
       <x:c r="U34" s="3" t="s">
         <x:v>2</x:v>
@@ -10925,19 +10892,19 @@
     </x:row>
     <x:row r="35" ht="93.25" hidden="0">
       <x:c r="A35" s="3" t="s">
-        <x:v>834</x:v>
+        <x:v>823</x:v>
       </x:c>
       <x:c r="B35" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C35" s="3" t="s">
-        <x:v>835</x:v>
+        <x:v>824</x:v>
       </x:c>
       <x:c r="D35" s="3" t="s">
-        <x:v>836</x:v>
+        <x:v>825</x:v>
       </x:c>
       <x:c r="E35" s="3" t="s">
-        <x:v>837</x:v>
+        <x:v>826</x:v>
       </x:c>
       <x:c r="F35" s="3" t="s">
         <x:v>38</x:v>
@@ -10958,31 +10925,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L35" s="3" t="s">
-        <x:v>838</x:v>
+        <x:v>827</x:v>
       </x:c>
       <x:c r="M35" s="3" t="s">
-        <x:v>839</x:v>
+        <x:v>828</x:v>
       </x:c>
       <x:c r="N35" s="3" t="s">
-        <x:v>840</x:v>
+        <x:v>829</x:v>
       </x:c>
       <x:c r="O35" s="3" t="s">
-        <x:v>615</x:v>
+        <x:v>604</x:v>
       </x:c>
       <x:c r="P35" s="3" t="s">
-        <x:v>841</x:v>
+        <x:v>830</x:v>
       </x:c>
       <x:c r="Q35" s="3" t="s">
-        <x:v>842</x:v>
+        <x:v>831</x:v>
       </x:c>
       <x:c r="R35" s="3" t="s">
-        <x:v>843</x:v>
+        <x:v>832</x:v>
       </x:c>
       <x:c r="S35" s="3" t="s">
-        <x:v>844</x:v>
+        <x:v>833</x:v>
       </x:c>
       <x:c r="T35" s="3" t="s">
-        <x:v>845</x:v>
+        <x:v>834</x:v>
       </x:c>
       <x:c r="U35" s="3" t="s">
         <x:v>2</x:v>
@@ -10990,19 +10957,19 @@
     </x:row>
     <x:row r="36" ht="93.25" hidden="0">
       <x:c r="A36" s="3" t="s">
-        <x:v>846</x:v>
+        <x:v>835</x:v>
       </x:c>
       <x:c r="B36" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C36" s="3" t="s">
-        <x:v>847</x:v>
+        <x:v>836</x:v>
       </x:c>
       <x:c r="D36" s="3" t="s">
-        <x:v>848</x:v>
+        <x:v>837</x:v>
       </x:c>
       <x:c r="E36" s="3" t="s">
-        <x:v>849</x:v>
+        <x:v>838</x:v>
       </x:c>
       <x:c r="F36" s="3" t="s">
         <x:v>38</x:v>
@@ -11023,31 +10990,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L36" s="3" t="s">
-        <x:v>850</x:v>
+        <x:v>839</x:v>
       </x:c>
       <x:c r="M36" s="3" t="s">
         <x:v>445</x:v>
       </x:c>
       <x:c r="N36" s="3" t="s">
-        <x:v>851</x:v>
+        <x:v>840</x:v>
       </x:c>
       <x:c r="O36" s="3" t="s">
-        <x:v>852</x:v>
+        <x:v>841</x:v>
       </x:c>
       <x:c r="P36" s="3" t="s">
-        <x:v>853</x:v>
+        <x:v>842</x:v>
       </x:c>
       <x:c r="Q36" s="3" t="s">
-        <x:v>854</x:v>
+        <x:v>843</x:v>
       </x:c>
       <x:c r="R36" s="3" t="s">
-        <x:v>855</x:v>
+        <x:v>844</x:v>
       </x:c>
       <x:c r="S36" s="3" t="s">
-        <x:v>856</x:v>
+        <x:v>845</x:v>
       </x:c>
       <x:c r="T36" s="3" t="s">
-        <x:v>857</x:v>
+        <x:v>846</x:v>
       </x:c>
       <x:c r="U36" s="3" t="s">
         <x:v>2</x:v>
@@ -11055,19 +11022,19 @@
     </x:row>
     <x:row r="37" ht="93.25" hidden="0">
       <x:c r="A37" s="3" t="s">
-        <x:v>858</x:v>
+        <x:v>847</x:v>
       </x:c>
       <x:c r="B37" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C37" s="3" t="s">
-        <x:v>859</x:v>
+        <x:v>848</x:v>
       </x:c>
       <x:c r="D37" s="3" t="s">
-        <x:v>860</x:v>
+        <x:v>849</x:v>
       </x:c>
       <x:c r="E37" s="3" t="s">
-        <x:v>861</x:v>
+        <x:v>850</x:v>
       </x:c>
       <x:c r="F37" s="3" t="s">
         <x:v>38</x:v>
@@ -11088,31 +11055,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L37" s="3" t="s">
-        <x:v>862</x:v>
+        <x:v>851</x:v>
       </x:c>
       <x:c r="M37" s="3" t="s">
-        <x:v>863</x:v>
+        <x:v>852</x:v>
       </x:c>
       <x:c r="N37" s="3" t="s">
-        <x:v>864</x:v>
+        <x:v>853</x:v>
       </x:c>
       <x:c r="O37" s="3" t="s">
-        <x:v>865</x:v>
+        <x:v>854</x:v>
       </x:c>
       <x:c r="P37" s="3" t="s">
-        <x:v>866</x:v>
+        <x:v>855</x:v>
       </x:c>
       <x:c r="Q37" s="3" t="s">
-        <x:v>867</x:v>
+        <x:v>856</x:v>
       </x:c>
       <x:c r="R37" s="3" t="s">
-        <x:v>868</x:v>
+        <x:v>857</x:v>
       </x:c>
       <x:c r="S37" s="3" t="s">
-        <x:v>869</x:v>
+        <x:v>858</x:v>
       </x:c>
       <x:c r="T37" s="3" t="s">
-        <x:v>863</x:v>
+        <x:v>852</x:v>
       </x:c>
       <x:c r="U37" s="3" t="s">
         <x:v>2</x:v>
@@ -11120,19 +11087,19 @@
     </x:row>
     <x:row r="38" ht="93.25" hidden="0">
       <x:c r="A38" s="3" t="s">
-        <x:v>870</x:v>
+        <x:v>859</x:v>
       </x:c>
       <x:c r="B38" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C38" s="3" t="s">
-        <x:v>871</x:v>
+        <x:v>860</x:v>
       </x:c>
       <x:c r="D38" s="3" t="s">
-        <x:v>872</x:v>
+        <x:v>861</x:v>
       </x:c>
       <x:c r="E38" s="3" t="s">
-        <x:v>873</x:v>
+        <x:v>862</x:v>
       </x:c>
       <x:c r="F38" s="3" t="s">
         <x:v>38</x:v>
@@ -11153,31 +11120,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L38" s="3" t="s">
-        <x:v>874</x:v>
+        <x:v>863</x:v>
       </x:c>
       <x:c r="M38" s="3" t="s">
-        <x:v>540</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="N38" s="3" t="s">
-        <x:v>875</x:v>
+        <x:v>864</x:v>
       </x:c>
       <x:c r="O38" s="3" t="s">
-        <x:v>876</x:v>
+        <x:v>865</x:v>
       </x:c>
       <x:c r="P38" s="3" t="s">
-        <x:v>877</x:v>
+        <x:v>866</x:v>
       </x:c>
       <x:c r="Q38" s="3" t="s">
-        <x:v>878</x:v>
+        <x:v>867</x:v>
       </x:c>
       <x:c r="R38" s="3" t="s">
-        <x:v>879</x:v>
+        <x:v>868</x:v>
       </x:c>
       <x:c r="S38" s="3" t="s">
-        <x:v>880</x:v>
+        <x:v>869</x:v>
       </x:c>
       <x:c r="T38" s="3" t="s">
-        <x:v>881</x:v>
+        <x:v>870</x:v>
       </x:c>
       <x:c r="U38" s="3" t="s">
         <x:v>2</x:v>
@@ -11185,19 +11152,19 @@
     </x:row>
     <x:row r="39" ht="93.25" hidden="0">
       <x:c r="A39" s="3" t="s">
-        <x:v>882</x:v>
+        <x:v>871</x:v>
       </x:c>
       <x:c r="B39" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C39" s="3" t="s">
-        <x:v>883</x:v>
+        <x:v>872</x:v>
       </x:c>
       <x:c r="D39" s="3" t="s">
-        <x:v>884</x:v>
+        <x:v>873</x:v>
       </x:c>
       <x:c r="E39" s="3" t="s">
-        <x:v>885</x:v>
+        <x:v>874</x:v>
       </x:c>
       <x:c r="F39" s="3" t="s">
         <x:v>38</x:v>
@@ -11218,31 +11185,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="L39" s="3" t="s">
-        <x:v>886</x:v>
+        <x:v>875</x:v>
       </x:c>
       <x:c r="M39" s="3" t="s">
         <x:v>445</x:v>
       </x:c>
       <x:c r="N39" s="3" t="s">
-        <x:v>887</x:v>
+        <x:v>876</x:v>
       </x:c>
       <x:c r="O39" s="3" t="s">
-        <x:v>888</x:v>
+        <x:v>877</x:v>
       </x:c>
       <x:c r="P39" s="3" t="s">
-        <x:v>889</x:v>
+        <x:v>878</x:v>
       </x:c>
       <x:c r="Q39" s="3" t="s">
-        <x:v>890</x:v>
+        <x:v>879</x:v>
       </x:c>
       <x:c r="R39" s="3" t="s">
-        <x:v>891</x:v>
+        <x:v>880</x:v>
       </x:c>
       <x:c r="S39" s="3" t="s">
-        <x:v>892</x:v>
+        <x:v>881</x:v>
       </x:c>
       <x:c r="T39" s="3" t="s">
-        <x:v>893</x:v>
+        <x:v>882</x:v>
       </x:c>
       <x:c r="U39" s="3" t="s">
         <x:v>2</x:v>
@@ -11251,7 +11218,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3dc9bc2067444455"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R72140e8901c4457f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/maliev-feature-user-story-status.xlsx
+++ b/docs/maliev-feature-user-story-status.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R110205978a30482f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="R1123a1083e1d4dbc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R472fbc52d8f243ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="Rda01110af06b4d07"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R4da6e20d08b44576"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="Rc1f5f9c822ca444b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R6e177dedf6854f86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="Ra787fd76a00f44d0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -19,159 +19,159 @@
     <x:t xml:space="preserve">Expanded current-code rebuild</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">Workbook rule</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Only current code-derived user stories are tracked. Rows are derived from current UI, BFF/API, service-client, and DTO boundaries.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Service</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Current tracked stories</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Maliev.Web</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Maliev.Intranet</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Maliev.QuoteEngine</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Total</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Next loop</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">After workbook review, start story-by-story behavior testing, document errors, fix UX/logistical issues, and retest every affected behavior.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Story ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">App Surface</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Feature Area</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">User Story</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Expected Behavior</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Current Code Status</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Test Status</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Error Status</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Fix Status</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Retest Status</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Priority</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Boundary / Contract</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Entry Point</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Routes / UI Evidence</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">API / Service Evidence</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Automated E2E Evidence</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Services Involved</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Data Created / Mutated</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Known Product Gaps</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Source References</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Last Reviewed</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">WEB-001</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Public home and navigation</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">As a visitor, I can land on the public site and navigate to services, materials, shop, quote, and account areas.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Home and layout routes render public content and primary navigation without requiring a customer session.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Current code-derived</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Automated Web suite passed 2026-06-23</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">No behavior error observed in current Web automated suite.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">No fix needed from current Web automated suite.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Current automated suite passed.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">P1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Blazor pages -&gt; MainLayout/SiteContent -&gt; static and BFF-backed content</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Home.razor; MainLayout.razor; SiteContent.cs</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">/, nav Services, Materials, Shop, Make Studio, Account</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">SeoController robots/sitemap for crawl entry points</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">WebBffEndpointTests Seo | Current suite: dotnet test Maliev.Web.slnx --verbosity minimal passed 235/235 on 2026-06-23.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Web client, Web BFF, content/static assets</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Read-only browsing</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Needs responsive browser pass in later loop</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Home.razor:1; MainLayout.razor; SiteContent.cs</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">2026-06-23</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Workbook rule</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Only current code-derived user stories are tracked. Rows are derived from current UI, BFF/API, service-client, and DTO boundaries.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Service</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Current tracked stories</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Maliev.Web</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Maliev.Intranet</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Maliev.QuoteEngine</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Total</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Next loop</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">After workbook review, start story-by-story behavior testing, document errors, fix UX/logistical issues, and retest every affected behavior.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Story ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">App Surface</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Feature Area</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">User Story</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Expected Behavior</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Current Code Status</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Test Status</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Error Status</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Fix Status</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Retest Status</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Priority</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Boundary / Contract</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Entry Point</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Routes / UI Evidence</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">API / Service Evidence</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Automated E2E Evidence</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Services Involved</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Data Created / Mutated</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Known Product Gaps</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Source References</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Last Reviewed</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">WEB-001</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Public home and navigation</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">As a visitor, I can land on the public site and navigate to services, materials, shop, quote, and account areas.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Home and layout routes render public content and primary navigation without requiring a customer session.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Current code-derived</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Automated Web suite passed 2026-06-23</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">No behavior error observed in current Web automated suite.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">No fix needed from current Web automated suite.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Current automated suite passed.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">P1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Blazor pages -&gt; MainLayout/SiteContent -&gt; static and BFF-backed content</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Home.razor; MainLayout.razor; SiteContent.cs</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">/, nav Services, Materials, Shop, Make Studio, Account</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">SeoController robots/sitemap for crawl entry points</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">WebBffEndpointTests Seo | Current suite: dotnet test Maliev.Web.slnx --verbosity minimal passed 235/235 on 2026-06-23.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Web client, Web BFF, content/static assets</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Read-only browsing</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Needs responsive browser pass in later loop</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Home.razor:1; MainLayout.razor; SiteContent.cs</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">WEB-002</x:t>
   </x:si>
   <x:si>
@@ -1282,46 +1282,19 @@
     <x:t xml:space="preserve">As a customer, I can open the manufacturing workspace and start or resume quote work.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">The root/quotes/new-project routes load the agent shell and workspace without presenting a sample-only feature.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Failed current QuoteEngine suite, fixed, and retested passed 2026-06-23</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Initial QuoteEngine suite failed 3/539 because a residual sample-only workspace route/workbench still rendered old quote panel components.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Fixed in Maliev.QuoteEngine commit e0c263f by removing the sample-only workspace route, workbench, notice, and public fallback exception.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Retested: source tests 180/180 passed, full QuoteEngine suite 539/539 passed, targeted route/workbench marker scan clean.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Blazor workspace routes -&gt; QuoteAgentLaunchShell -&gt; quote session/project state</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">QuoteWorkspace.razor; QuoteAgentLaunchShell.razor</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">@page /, /quotes, /quotes/new, /quote/new, /projects/new</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">QuoteController project nav/detail endpoints</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">QuoteEngineSourceTests workspace/shell | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations. | Fix verification: QuoteEngineSourceTests passed 180/180; targeted scan found no sample-only workspace route/workbench markers in client workspace or BFF fallback route.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">QuoteEngine client/BFF, session store</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Session/project state</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">The source still contains a non-current route, but tracking excludes it per product direction</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QuoteWorkspace.razor:1-5,39; QuoteAgentLaunchShell.razor; Program.cs public route fallback; QuoteWorkspace.razor routes; QuoteAgentLaunchShell.razor</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">QE-003</x:t>
@@ -3120,29 +3093,29 @@
       <x:c r="A2" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B2" s="3" t="s">
-        <x:v>2</x:v>
+      <x:c r="B2" s="3" t="str">
+        <x:v>2026-06-24</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="31.600000381469727" hidden="0">
       <x:c r="A3" s="3" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B3" s="3" t="s">
         <x:v>3</x:v>
-      </x:c>
-      <x:c r="B3" s="3" t="s">
-        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="16.649999618530273" hidden="0">
       <x:c r="A4" s="2" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B4" s="2" t="s">
         <x:v>5</x:v>
-      </x:c>
-      <x:c r="B4" s="2" t="s">
-        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="16.649999618530273" hidden="0">
       <x:c r="A5" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B5" s="3" t="n">
         <x:v>30</x:v>
@@ -3150,7 +3123,7 @@
     </x:row>
     <x:row r="6" ht="16.649999618530273" hidden="0">
       <x:c r="A6" s="3" t="s">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B6" s="3" t="n">
         <x:v>51</x:v>
@@ -3158,7 +3131,7 @@
     </x:row>
     <x:row r="7" ht="16.649999618530273" hidden="0">
       <x:c r="A7" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B7" s="3" t="n">
         <x:v>38</x:v>
@@ -3166,7 +3139,7 @@
     </x:row>
     <x:row r="8" ht="16.649999618530273" hidden="0">
       <x:c r="A8" s="3" t="s">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B8" s="3" t="n">
         <x:v>119</x:v>
@@ -3174,10 +3147,10 @@
     </x:row>
     <x:row r="9" ht="31.600000381469727" hidden="0">
       <x:c r="A9" s="3" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B9" s="3" t="s">
         <x:v>11</x:v>
-      </x:c>
-      <x:c r="B9" s="3" t="s">
-        <x:v>12</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3215,132 +3188,132 @@
   <x:sheetData>
     <x:row r="1" ht="41.29999923706055" hidden="0">
       <x:c r="A1" s="4" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B1" s="4" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B1" s="4" t="s">
+      <x:c r="C1" s="4" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C1" s="4" t="s">
+      <x:c r="D1" s="4" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D1" s="4" t="s">
+      <x:c r="E1" s="4" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E1" s="4" t="s">
+      <x:c r="F1" s="4" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F1" s="4" t="s">
+      <x:c r="G1" s="4" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G1" s="4" t="s">
+      <x:c r="H1" s="4" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H1" s="4" t="s">
+      <x:c r="I1" s="4" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="I1" s="4" t="s">
+      <x:c r="J1" s="4" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="J1" s="4" t="s">
+      <x:c r="K1" s="4" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="K1" s="4" t="s">
+      <x:c r="L1" s="4" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="L1" s="4" t="s">
+      <x:c r="M1" s="4" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="M1" s="4" t="s">
+      <x:c r="N1" s="4" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="N1" s="4" t="s">
+      <x:c r="O1" s="4" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="O1" s="4" t="s">
+      <x:c r="P1" s="4" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="P1" s="4" t="s">
+      <x:c r="Q1" s="4" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="Q1" s="4" t="s">
+      <x:c r="R1" s="4" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="R1" s="4" t="s">
+      <x:c r="S1" s="4" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="S1" s="4" t="s">
+      <x:c r="T1" s="4" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="T1" s="4" t="s">
+      <x:c r="U1" s="4" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="U1" s="4" t="s">
-        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="57.400001525878906" hidden="0">
       <x:c r="A2" s="3" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B2" s="3" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C2" s="3" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="B2" s="3" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C2" s="3" t="s">
+      <x:c r="D2" s="3" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="D2" s="3" t="s">
+      <x:c r="E2" s="3" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="E2" s="3" t="s">
+      <x:c r="F2" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="F2" s="3" t="s">
+      <x:c r="G2" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="G2" s="3" t="s">
+      <x:c r="H2" s="3" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="H2" s="3" t="s">
+      <x:c r="I2" s="3" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="I2" s="3" t="s">
+      <x:c r="J2" s="3" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="J2" s="3" t="s">
+      <x:c r="K2" s="3" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="K2" s="3" t="s">
+      <x:c r="L2" s="3" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="L2" s="3" t="s">
+      <x:c r="M2" s="3" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="M2" s="3" t="s">
+      <x:c r="N2" s="3" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="N2" s="3" t="s">
+      <x:c r="O2" s="3" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="O2" s="3" t="s">
+      <x:c r="P2" s="3" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="P2" s="3" t="s">
+      <x:c r="Q2" s="3" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="Q2" s="3" t="s">
+      <x:c r="R2" s="3" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="R2" s="3" t="s">
+      <x:c r="S2" s="3" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="S2" s="3" t="s">
+      <x:c r="T2" s="3" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="T2" s="3" t="s">
+      <x:c r="U2" s="3" t="s">
         <x:v>52</x:v>
-      </x:c>
-      <x:c r="U2" s="3" t="s">
-        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="89.55000305175781" hidden="0">
@@ -3348,7 +3321,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B3" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C3" s="3" t="s">
         <x:v>54</x:v>
@@ -3360,7 +3333,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="F3" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="G3" s="3" t="s">
         <x:v>57</x:v>
@@ -3396,7 +3369,7 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="R3" s="3" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="S3" s="3" t="s">
         <x:v>68</x:v>
@@ -3405,7 +3378,7 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="U3" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="153.8000030517578" hidden="0">
@@ -3413,7 +3386,7 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
         <x:v>71</x:v>
@@ -3425,7 +3398,7 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="F4" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="G4" s="3" t="s">
         <x:v>74</x:v>
@@ -3461,7 +3434,7 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="R4" s="3" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="S4" s="3" t="s">
         <x:v>82</x:v>
@@ -3470,7 +3443,7 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="U4" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="57.400001525878906" hidden="0">
@@ -3478,7 +3451,7 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C5" s="3" t="s">
         <x:v>85</x:v>
@@ -3490,22 +3463,22 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="F5" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G5" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="G5" s="3" t="s">
+      <x:c r="H5" s="3" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="H5" s="3" t="s">
+      <x:c r="I5" s="3" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="I5" s="3" t="s">
+      <x:c r="J5" s="3" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="J5" s="3" t="s">
+      <x:c r="K5" s="3" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="K5" s="3" t="s">
-        <x:v>43</x:v>
       </x:c>
       <x:c r="L5" s="3" t="s">
         <x:v>88</x:v>
@@ -3526,7 +3499,7 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="R5" s="3" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="S5" s="3" t="s">
         <x:v>94</x:v>
@@ -3535,7 +3508,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="U5" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="57.400001525878906" hidden="0">
@@ -3543,7 +3516,7 @@
         <x:v>96</x:v>
       </x:c>
       <x:c r="B6" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C6" s="3" t="s">
         <x:v>97</x:v>
@@ -3555,22 +3528,22 @@
         <x:v>99</x:v>
       </x:c>
       <x:c r="F6" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G6" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="G6" s="3" t="s">
+      <x:c r="H6" s="3" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="H6" s="3" t="s">
+      <x:c r="I6" s="3" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="I6" s="3" t="s">
+      <x:c r="J6" s="3" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="J6" s="3" t="s">
+      <x:c r="K6" s="3" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="K6" s="3" t="s">
-        <x:v>43</x:v>
       </x:c>
       <x:c r="L6" s="3" t="s">
         <x:v>100</x:v>
@@ -3600,7 +3573,7 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="U6" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="73.44999694824219" hidden="0">
@@ -3608,7 +3581,7 @@
         <x:v>108</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
         <x:v>109</x:v>
@@ -3620,22 +3593,22 @@
         <x:v>111</x:v>
       </x:c>
       <x:c r="F7" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G7" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="G7" s="3" t="s">
+      <x:c r="H7" s="3" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="H7" s="3" t="s">
+      <x:c r="I7" s="3" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="I7" s="3" t="s">
+      <x:c r="J7" s="3" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="J7" s="3" t="s">
+      <x:c r="K7" s="3" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="K7" s="3" t="s">
-        <x:v>43</x:v>
       </x:c>
       <x:c r="L7" s="3" t="s">
         <x:v>112</x:v>
@@ -3665,7 +3638,7 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="U7" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="57.400001525878906" hidden="0">
@@ -3673,7 +3646,7 @@
         <x:v>121</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
         <x:v>122</x:v>
@@ -3685,22 +3658,22 @@
         <x:v>124</x:v>
       </x:c>
       <x:c r="F8" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G8" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="G8" s="3" t="s">
+      <x:c r="H8" s="3" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="H8" s="3" t="s">
+      <x:c r="I8" s="3" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="I8" s="3" t="s">
+      <x:c r="J8" s="3" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="J8" s="3" t="s">
+      <x:c r="K8" s="3" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="K8" s="3" t="s">
-        <x:v>43</x:v>
       </x:c>
       <x:c r="L8" s="3" t="s">
         <x:v>125</x:v>
@@ -3730,7 +3703,7 @@
         <x:v>133</x:v>
       </x:c>
       <x:c r="U8" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="89.55000305175781" hidden="0">
@@ -3738,7 +3711,7 @@
         <x:v>134</x:v>
       </x:c>
       <x:c r="B9" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C9" s="3" t="s">
         <x:v>135</x:v>
@@ -3750,7 +3723,7 @@
         <x:v>137</x:v>
       </x:c>
       <x:c r="F9" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="G9" s="3" t="s">
         <x:v>57</x:v>
@@ -3765,7 +3738,7 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="K9" s="3" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="L9" s="3" t="s">
         <x:v>139</x:v>
@@ -3795,7 +3768,7 @@
         <x:v>146</x:v>
       </x:c>
       <x:c r="U9" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="73.44999694824219" hidden="0">
@@ -3803,7 +3776,7 @@
         <x:v>147</x:v>
       </x:c>
       <x:c r="B10" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C10" s="3" t="s">
         <x:v>148</x:v>
@@ -3815,22 +3788,22 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="F10" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G10" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="G10" s="3" t="s">
+      <x:c r="H10" s="3" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="H10" s="3" t="s">
+      <x:c r="I10" s="3" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="I10" s="3" t="s">
+      <x:c r="J10" s="3" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="J10" s="3" t="s">
+      <x:c r="K10" s="3" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="K10" s="3" t="s">
-        <x:v>43</x:v>
       </x:c>
       <x:c r="L10" s="3" t="s">
         <x:v>151</x:v>
@@ -3860,7 +3833,7 @@
         <x:v>159</x:v>
       </x:c>
       <x:c r="U10" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="57.400001525878906" hidden="0">
@@ -3868,7 +3841,7 @@
         <x:v>160</x:v>
       </x:c>
       <x:c r="B11" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C11" s="3" t="s">
         <x:v>161</x:v>
@@ -3880,22 +3853,22 @@
         <x:v>163</x:v>
       </x:c>
       <x:c r="F11" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G11" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="G11" s="3" t="s">
+      <x:c r="H11" s="3" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="H11" s="3" t="s">
+      <x:c r="I11" s="3" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="I11" s="3" t="s">
+      <x:c r="J11" s="3" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="J11" s="3" t="s">
+      <x:c r="K11" s="3" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="K11" s="3" t="s">
-        <x:v>43</x:v>
       </x:c>
       <x:c r="L11" s="3" t="s">
         <x:v>164</x:v>
@@ -3925,7 +3898,7 @@
         <x:v>172</x:v>
       </x:c>
       <x:c r="U11" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="57.400001525878906" hidden="0">
@@ -3933,7 +3906,7 @@
         <x:v>173</x:v>
       </x:c>
       <x:c r="B12" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C12" s="3" t="s">
         <x:v>174</x:v>
@@ -3945,19 +3918,19 @@
         <x:v>176</x:v>
       </x:c>
       <x:c r="F12" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G12" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="G12" s="3" t="s">
+      <x:c r="H12" s="3" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="H12" s="3" t="s">
+      <x:c r="I12" s="3" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="I12" s="3" t="s">
+      <x:c r="J12" s="3" t="s">
         <x:v>41</x:v>
-      </x:c>
-      <x:c r="J12" s="3" t="s">
-        <x:v>42</x:v>
       </x:c>
       <x:c r="K12" s="3" t="s">
         <x:v>61</x:v>
@@ -3990,7 +3963,7 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="U12" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="57.400001525878906" hidden="0">
@@ -3998,7 +3971,7 @@
         <x:v>184</x:v>
       </x:c>
       <x:c r="B13" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C13" s="3" t="s">
         <x:v>185</x:v>
@@ -4010,19 +3983,19 @@
         <x:v>187</x:v>
       </x:c>
       <x:c r="F13" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G13" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="G13" s="3" t="s">
+      <x:c r="H13" s="3" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="H13" s="3" t="s">
+      <x:c r="I13" s="3" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="I13" s="3" t="s">
+      <x:c r="J13" s="3" t="s">
         <x:v>41</x:v>
-      </x:c>
-      <x:c r="J13" s="3" t="s">
-        <x:v>42</x:v>
       </x:c>
       <x:c r="K13" s="3" t="s">
         <x:v>188</x:v>
@@ -4055,7 +4028,7 @@
         <x:v>197</x:v>
       </x:c>
       <x:c r="U13" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="57.400001525878906" hidden="0">
@@ -4063,7 +4036,7 @@
         <x:v>198</x:v>
       </x:c>
       <x:c r="B14" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C14" s="3" t="s">
         <x:v>199</x:v>
@@ -4075,19 +4048,19 @@
         <x:v>201</x:v>
       </x:c>
       <x:c r="F14" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G14" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="G14" s="3" t="s">
+      <x:c r="H14" s="3" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="H14" s="3" t="s">
+      <x:c r="I14" s="3" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="I14" s="3" t="s">
+      <x:c r="J14" s="3" t="s">
         <x:v>41</x:v>
-      </x:c>
-      <x:c r="J14" s="3" t="s">
-        <x:v>42</x:v>
       </x:c>
       <x:c r="K14" s="3" t="s">
         <x:v>188</x:v>
@@ -4120,7 +4093,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="U14" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="57.400001525878906" hidden="0">
@@ -4128,7 +4101,7 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B15" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C15" s="3" t="s">
         <x:v>212</x:v>
@@ -4140,19 +4113,19 @@
         <x:v>214</x:v>
       </x:c>
       <x:c r="F15" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G15" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="G15" s="3" t="s">
+      <x:c r="H15" s="3" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="H15" s="3" t="s">
+      <x:c r="I15" s="3" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="I15" s="3" t="s">
+      <x:c r="J15" s="3" t="s">
         <x:v>41</x:v>
-      </x:c>
-      <x:c r="J15" s="3" t="s">
-        <x:v>42</x:v>
       </x:c>
       <x:c r="K15" s="3" t="s">
         <x:v>188</x:v>
@@ -4185,7 +4158,7 @@
         <x:v>223</x:v>
       </x:c>
       <x:c r="U15" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="73.44999694824219" hidden="0">
@@ -4193,7 +4166,7 @@
         <x:v>224</x:v>
       </x:c>
       <x:c r="B16" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C16" s="3" t="s">
         <x:v>225</x:v>
@@ -4205,22 +4178,22 @@
         <x:v>227</x:v>
       </x:c>
       <x:c r="F16" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G16" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="G16" s="3" t="s">
+      <x:c r="H16" s="3" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="H16" s="3" t="s">
+      <x:c r="I16" s="3" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="I16" s="3" t="s">
+      <x:c r="J16" s="3" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="J16" s="3" t="s">
+      <x:c r="K16" s="3" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="K16" s="3" t="s">
-        <x:v>43</x:v>
       </x:c>
       <x:c r="L16" s="3" t="s">
         <x:v>228</x:v>
@@ -4250,7 +4223,7 @@
         <x:v>236</x:v>
       </x:c>
       <x:c r="U16" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="73.44999694824219" hidden="0">
@@ -4258,7 +4231,7 @@
         <x:v>237</x:v>
       </x:c>
       <x:c r="B17" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C17" s="3" t="s">
         <x:v>238</x:v>
@@ -4270,19 +4243,19 @@
         <x:v>240</x:v>
       </x:c>
       <x:c r="F17" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G17" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="G17" s="3" t="s">
+      <x:c r="H17" s="3" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="H17" s="3" t="s">
+      <x:c r="I17" s="3" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="I17" s="3" t="s">
+      <x:c r="J17" s="3" t="s">
         <x:v>41</x:v>
-      </x:c>
-      <x:c r="J17" s="3" t="s">
-        <x:v>42</x:v>
       </x:c>
       <x:c r="K17" s="3" t="s">
         <x:v>188</x:v>
@@ -4315,7 +4288,7 @@
         <x:v>249</x:v>
       </x:c>
       <x:c r="U17" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="57.400001525878906" hidden="0">
@@ -4323,7 +4296,7 @@
         <x:v>250</x:v>
       </x:c>
       <x:c r="B18" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C18" s="3" t="s">
         <x:v>251</x:v>
@@ -4335,22 +4308,22 @@
         <x:v>253</x:v>
       </x:c>
       <x:c r="F18" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G18" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="G18" s="3" t="s">
+      <x:c r="H18" s="3" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="H18" s="3" t="s">
+      <x:c r="I18" s="3" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="I18" s="3" t="s">
+      <x:c r="J18" s="3" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="J18" s="3" t="s">
+      <x:c r="K18" s="3" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="K18" s="3" t="s">
-        <x:v>43</x:v>
       </x:c>
       <x:c r="L18" s="3" t="s">
         <x:v>254</x:v>
@@ -4380,7 +4353,7 @@
         <x:v>262</x:v>
       </x:c>
       <x:c r="U18" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="57.400001525878906" hidden="0">
@@ -4388,7 +4361,7 @@
         <x:v>263</x:v>
       </x:c>
       <x:c r="B19" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C19" s="3" t="s">
         <x:v>264</x:v>
@@ -4400,22 +4373,22 @@
         <x:v>266</x:v>
       </x:c>
       <x:c r="F19" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G19" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="G19" s="3" t="s">
+      <x:c r="H19" s="3" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="H19" s="3" t="s">
+      <x:c r="I19" s="3" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="I19" s="3" t="s">
+      <x:c r="J19" s="3" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="J19" s="3" t="s">
+      <x:c r="K19" s="3" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="K19" s="3" t="s">
-        <x:v>43</x:v>
       </x:c>
       <x:c r="L19" s="3" t="s">
         <x:v>267</x:v>
@@ -4445,7 +4418,7 @@
         <x:v>274</x:v>
       </x:c>
       <x:c r="U19" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="73.44999694824219" hidden="0">
@@ -4453,7 +4426,7 @@
         <x:v>275</x:v>
       </x:c>
       <x:c r="B20" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C20" s="3" t="s">
         <x:v>276</x:v>
@@ -4465,22 +4438,22 @@
         <x:v>278</x:v>
       </x:c>
       <x:c r="F20" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G20" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="G20" s="3" t="s">
+      <x:c r="H20" s="3" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="H20" s="3" t="s">
+      <x:c r="I20" s="3" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="I20" s="3" t="s">
+      <x:c r="J20" s="3" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="J20" s="3" t="s">
+      <x:c r="K20" s="3" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="K20" s="3" t="s">
-        <x:v>43</x:v>
       </x:c>
       <x:c r="L20" s="3" t="s">
         <x:v>279</x:v>
@@ -4510,7 +4483,7 @@
         <x:v>287</x:v>
       </x:c>
       <x:c r="U20" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="57.400001525878906" hidden="0">
@@ -4518,7 +4491,7 @@
         <x:v>288</x:v>
       </x:c>
       <x:c r="B21" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C21" s="3" t="s">
         <x:v>289</x:v>
@@ -4530,19 +4503,19 @@
         <x:v>291</x:v>
       </x:c>
       <x:c r="F21" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G21" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="G21" s="3" t="s">
+      <x:c r="H21" s="3" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="H21" s="3" t="s">
+      <x:c r="I21" s="3" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="I21" s="3" t="s">
+      <x:c r="J21" s="3" t="s">
         <x:v>41</x:v>
-      </x:c>
-      <x:c r="J21" s="3" t="s">
-        <x:v>42</x:v>
       </x:c>
       <x:c r="K21" s="3" t="s">
         <x:v>61</x:v>
@@ -4575,7 +4548,7 @@
         <x:v>298</x:v>
       </x:c>
       <x:c r="U21" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="73.44999694824219" hidden="0">
@@ -4583,7 +4556,7 @@
         <x:v>299</x:v>
       </x:c>
       <x:c r="B22" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C22" s="3" t="s">
         <x:v>300</x:v>
@@ -4595,22 +4568,22 @@
         <x:v>302</x:v>
       </x:c>
       <x:c r="F22" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G22" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="G22" s="3" t="s">
+      <x:c r="H22" s="3" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="H22" s="3" t="s">
+      <x:c r="I22" s="3" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="I22" s="3" t="s">
+      <x:c r="J22" s="3" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="J22" s="3" t="s">
+      <x:c r="K22" s="3" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="K22" s="3" t="s">
-        <x:v>43</x:v>
       </x:c>
       <x:c r="L22" s="3" t="s">
         <x:v>303</x:v>
@@ -4640,7 +4613,7 @@
         <x:v>311</x:v>
       </x:c>
       <x:c r="U22" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="57.400001525878906" hidden="0">
@@ -4648,7 +4621,7 @@
         <x:v>312</x:v>
       </x:c>
       <x:c r="B23" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C23" s="3" t="s">
         <x:v>313</x:v>
@@ -4660,19 +4633,19 @@
         <x:v>315</x:v>
       </x:c>
       <x:c r="F23" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G23" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="G23" s="3" t="s">
+      <x:c r="H23" s="3" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="H23" s="3" t="s">
+      <x:c r="I23" s="3" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="I23" s="3" t="s">
+      <x:c r="J23" s="3" t="s">
         <x:v>41</x:v>
-      </x:c>
-      <x:c r="J23" s="3" t="s">
-        <x:v>42</x:v>
       </x:c>
       <x:c r="K23" s="3" t="s">
         <x:v>61</x:v>
@@ -4705,7 +4678,7 @@
         <x:v>324</x:v>
       </x:c>
       <x:c r="U23" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="57.400001525878906" hidden="0">
@@ -4713,7 +4686,7 @@
         <x:v>325</x:v>
       </x:c>
       <x:c r="B24" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C24" s="3" t="s">
         <x:v>326</x:v>
@@ -4725,22 +4698,22 @@
         <x:v>328</x:v>
       </x:c>
       <x:c r="F24" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G24" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="G24" s="3" t="s">
+      <x:c r="H24" s="3" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="H24" s="3" t="s">
+      <x:c r="I24" s="3" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="I24" s="3" t="s">
+      <x:c r="J24" s="3" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="J24" s="3" t="s">
+      <x:c r="K24" s="3" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="K24" s="3" t="s">
-        <x:v>43</x:v>
       </x:c>
       <x:c r="L24" s="3" t="s">
         <x:v>329</x:v>
@@ -4770,7 +4743,7 @@
         <x:v>337</x:v>
       </x:c>
       <x:c r="U24" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="57.400001525878906" hidden="0">
@@ -4778,7 +4751,7 @@
         <x:v>338</x:v>
       </x:c>
       <x:c r="B25" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C25" s="3" t="s">
         <x:v>339</x:v>
@@ -4790,19 +4763,19 @@
         <x:v>341</x:v>
       </x:c>
       <x:c r="F25" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G25" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="G25" s="3" t="s">
+      <x:c r="H25" s="3" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="H25" s="3" t="s">
+      <x:c r="I25" s="3" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="I25" s="3" t="s">
+      <x:c r="J25" s="3" t="s">
         <x:v>41</x:v>
-      </x:c>
-      <x:c r="J25" s="3" t="s">
-        <x:v>42</x:v>
       </x:c>
       <x:c r="K25" s="3" t="s">
         <x:v>61</x:v>
@@ -4835,7 +4808,7 @@
         <x:v>349</x:v>
       </x:c>
       <x:c r="U25" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="57.400001525878906" hidden="0">
@@ -4843,7 +4816,7 @@
         <x:v>350</x:v>
       </x:c>
       <x:c r="B26" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C26" s="3" t="s">
         <x:v>351</x:v>
@@ -4855,19 +4828,19 @@
         <x:v>353</x:v>
       </x:c>
       <x:c r="F26" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G26" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="G26" s="3" t="s">
+      <x:c r="H26" s="3" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="H26" s="3" t="s">
+      <x:c r="I26" s="3" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="I26" s="3" t="s">
+      <x:c r="J26" s="3" t="s">
         <x:v>41</x:v>
-      </x:c>
-      <x:c r="J26" s="3" t="s">
-        <x:v>42</x:v>
       </x:c>
       <x:c r="K26" s="3" t="s">
         <x:v>61</x:v>
@@ -4900,7 +4873,7 @@
         <x:v>362</x:v>
       </x:c>
       <x:c r="U26" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="57.400001525878906" hidden="0">
@@ -4908,7 +4881,7 @@
         <x:v>363</x:v>
       </x:c>
       <x:c r="B27" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C27" s="3" t="s">
         <x:v>364</x:v>
@@ -4920,22 +4893,22 @@
         <x:v>366</x:v>
       </x:c>
       <x:c r="F27" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G27" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="G27" s="3" t="s">
+      <x:c r="H27" s="3" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="H27" s="3" t="s">
+      <x:c r="I27" s="3" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="I27" s="3" t="s">
+      <x:c r="J27" s="3" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="J27" s="3" t="s">
+      <x:c r="K27" s="3" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="K27" s="3" t="s">
-        <x:v>43</x:v>
       </x:c>
       <x:c r="L27" s="3" t="s">
         <x:v>367</x:v>
@@ -4965,7 +4938,7 @@
         <x:v>375</x:v>
       </x:c>
       <x:c r="U27" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="89.55000305175781" hidden="0">
@@ -4973,7 +4946,7 @@
         <x:v>376</x:v>
       </x:c>
       <x:c r="B28" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C28" s="3" t="s">
         <x:v>377</x:v>
@@ -4985,7 +4958,7 @@
         <x:v>379</x:v>
       </x:c>
       <x:c r="F28" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="G28" s="3" t="s">
         <x:v>57</x:v>
@@ -5030,7 +5003,7 @@
         <x:v>387</x:v>
       </x:c>
       <x:c r="U28" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="57.400001525878906" hidden="0">
@@ -5038,7 +5011,7 @@
         <x:v>388</x:v>
       </x:c>
       <x:c r="B29" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C29" s="3" t="s">
         <x:v>389</x:v>
@@ -5050,19 +5023,19 @@
         <x:v>391</x:v>
       </x:c>
       <x:c r="F29" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G29" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="G29" s="3" t="s">
+      <x:c r="H29" s="3" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="H29" s="3" t="s">
+      <x:c r="I29" s="3" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="I29" s="3" t="s">
+      <x:c r="J29" s="3" t="s">
         <x:v>41</x:v>
-      </x:c>
-      <x:c r="J29" s="3" t="s">
-        <x:v>42</x:v>
       </x:c>
       <x:c r="K29" s="3" t="s">
         <x:v>61</x:v>
@@ -5095,7 +5068,7 @@
         <x:v>398</x:v>
       </x:c>
       <x:c r="U29" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="57.400001525878906" hidden="0">
@@ -5103,7 +5076,7 @@
         <x:v>399</x:v>
       </x:c>
       <x:c r="B30" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C30" s="3" t="s">
         <x:v>400</x:v>
@@ -5115,19 +5088,19 @@
         <x:v>402</x:v>
       </x:c>
       <x:c r="F30" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G30" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="G30" s="3" t="s">
+      <x:c r="H30" s="3" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="H30" s="3" t="s">
+      <x:c r="I30" s="3" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="I30" s="3" t="s">
+      <x:c r="J30" s="3" t="s">
         <x:v>41</x:v>
-      </x:c>
-      <x:c r="J30" s="3" t="s">
-        <x:v>42</x:v>
       </x:c>
       <x:c r="K30" s="3" t="s">
         <x:v>61</x:v>
@@ -5145,7 +5118,7 @@
         <x:v>406</x:v>
       </x:c>
       <x:c r="P30" s="3" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Q30" s="3" t="s">
         <x:v>359</x:v>
@@ -5160,7 +5133,7 @@
         <x:v>409</x:v>
       </x:c>
       <x:c r="U30" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="73.44999694824219" hidden="0">
@@ -5168,7 +5141,7 @@
         <x:v>410</x:v>
       </x:c>
       <x:c r="B31" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C31" s="3" t="s">
         <x:v>411</x:v>
@@ -5180,7 +5153,7 @@
         <x:v>413</x:v>
       </x:c>
       <x:c r="F31" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="G31" s="3" t="str">
         <x:v>Behavior test failed, fixed, and retested passed 2026-06-23.</x:v>
@@ -5225,13 +5198,13 @@
         <x:v>419</x:v>
       </x:c>
       <x:c r="U31" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1519437e94654c14"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb6a1be584a24105"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8647,7 +8620,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea9192063e854650"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra6dc305d869c4e5c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8682,67 +8655,67 @@
   <x:sheetData>
     <x:row r="1" ht="37.29999923706055" hidden="0">
       <x:c r="A1" s="4" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B1" s="4" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B1" s="4" t="s">
+      <x:c r="C1" s="4" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C1" s="4" t="s">
+      <x:c r="D1" s="4" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D1" s="4" t="s">
+      <x:c r="E1" s="4" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E1" s="4" t="s">
+      <x:c r="F1" s="4" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F1" s="4" t="s">
+      <x:c r="G1" s="4" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G1" s="4" t="s">
+      <x:c r="H1" s="4" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H1" s="4" t="s">
+      <x:c r="I1" s="4" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="I1" s="4" t="s">
+      <x:c r="J1" s="4" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="J1" s="4" t="s">
+      <x:c r="K1" s="4" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="K1" s="4" t="s">
+      <x:c r="L1" s="4" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="L1" s="4" t="s">
+      <x:c r="M1" s="4" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="M1" s="4" t="s">
+      <x:c r="N1" s="4" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="N1" s="4" t="s">
+      <x:c r="O1" s="4" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="O1" s="4" t="s">
+      <x:c r="P1" s="4" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="P1" s="4" t="s">
+      <x:c r="Q1" s="4" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="Q1" s="4" t="s">
+      <x:c r="R1" s="4" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="R1" s="4" t="s">
+      <x:c r="S1" s="4" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="S1" s="4" t="s">
+      <x:c r="T1" s="4" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="T1" s="4" t="s">
+      <x:c r="U1" s="4" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="U1" s="4" t="s">
-        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="149.25" hidden="0">
@@ -8750,7 +8723,7 @@
         <x:v>420</x:v>
       </x:c>
       <x:c r="B2" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C2" s="3" t="s">
         <x:v>421</x:v>
@@ -8758,56 +8731,56 @@
       <x:c r="D2" s="3" t="s">
         <x:v>422</x:v>
       </x:c>
-      <x:c r="E2" s="3" t="s">
-        <x:v>423</x:v>
+      <x:c r="E2" s="3" t="str">
+        <x:v>The root, quotes, and new-project routes load the chat-based agentic manufacturing workspace for quote work.</x:v>
       </x:c>
       <x:c r="F2" s="3" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="G2" s="3" t="s">
-        <x:v>424</x:v>
-      </x:c>
-      <x:c r="H2" s="3" t="s">
-        <x:v>425</x:v>
-      </x:c>
-      <x:c r="I2" s="3" t="s">
-        <x:v>426</x:v>
-      </x:c>
-      <x:c r="J2" s="3" t="s">
-        <x:v>427</x:v>
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G2" s="3" t="str">
+        <x:v>Current QuoteEngine route/workspace source tests and full automated suite passed 2026-06-23.</x:v>
+      </x:c>
+      <x:c r="H2" s="3" t="str">
+        <x:v>No current behavior error observed after current-code route/workspace cleanup.</x:v>
+      </x:c>
+      <x:c r="I2" s="3" t="str">
+        <x:v>No further fix needed for this story from the current code-derived tracker.</x:v>
+      </x:c>
+      <x:c r="J2" s="3" t="str">
+        <x:v>Retested: source tests 180/180 passed, full QuoteEngine suite 539/539 passed, targeted route/workspace marker scan clean.</x:v>
       </x:c>
       <x:c r="K2" s="3" t="s">
         <x:v>188</x:v>
       </x:c>
       <x:c r="L2" s="3" t="s">
-        <x:v>428</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="M2" s="3" t="s">
-        <x:v>429</x:v>
-      </x:c>
-      <x:c r="N2" s="3" t="s">
-        <x:v>430</x:v>
+        <x:v>424</x:v>
+      </x:c>
+      <x:c r="N2" s="3" t="str">
+        <x:v>@page /, /quotes, /quotes/new, /quote/new, /projects/new</x:v>
       </x:c>
       <x:c r="O2" s="3" t="s">
-        <x:v>431</x:v>
-      </x:c>
-      <x:c r="P2" s="3" t="s">
-        <x:v>432</x:v>
+        <x:v>425</x:v>
+      </x:c>
+      <x:c r="P2" s="3" t="str">
+        <x:v>QuoteEngineSourceTests workspace/shell | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Fix verification: QuoteEngineSourceTests passed 180/180; targeted scan found no stale workspace route/workbench markers in client workspace or BFF fallback route.</x:v>
       </x:c>
       <x:c r="Q2" s="3" t="s">
-        <x:v>433</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="R2" s="3" t="s">
-        <x:v>434</x:v>
-      </x:c>
-      <x:c r="S2" s="3" t="s">
-        <x:v>435</x:v>
-      </x:c>
-      <x:c r="T2" s="3" t="s">
-        <x:v>436</x:v>
-      </x:c>
-      <x:c r="U2" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>427</x:v>
+      </x:c>
+      <x:c r="S2" s="3" t="str">
+        <x:v>No remaining gap from current code-derived tracker.</x:v>
+      </x:c>
+      <x:c r="T2" s="3" t="str">
+        <x:v>QuoteWorkspace.razor:1-5,39; QuoteAgentLaunchShell.razor; Program.cs public route fallback; QuoteController.cs</x:v>
+      </x:c>
+      <x:c r="U2" s="3" t="str">
+        <x:v>2026-06-24</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="107.25" hidden="0">
@@ -8877,2348 +8850,2348 @@
     </x:row>
     <x:row r="4" ht="93.25" hidden="0">
       <x:c r="A4" s="3" t="s">
-        <x:v>437</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>438</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="D4" s="3" t="s">
-        <x:v>439</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="E4" s="3" t="s">
-        <x:v>440</x:v>
+        <x:v>431</x:v>
       </x:c>
       <x:c r="F4" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="G4" s="3" t="s">
-        <x:v>441</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="H4" s="3" t="s">
-        <x:v>442</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="I4" s="3" t="s">
-        <x:v>443</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="J4" s="3" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="K4" s="3" t="s">
         <x:v>188</x:v>
       </x:c>
       <x:c r="L4" s="3" t="s">
-        <x:v>444</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="M4" s="3" t="s">
-        <x:v>445</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="N4" s="3" t="s">
-        <x:v>446</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="O4" s="3" t="s">
-        <x:v>447</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="P4" s="3" t="s">
-        <x:v>448</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="Q4" s="3" t="s">
-        <x:v>449</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="R4" s="3" t="s">
-        <x:v>450</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="S4" s="3" t="s">
-        <x:v>451</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="T4" s="3" t="s">
-        <x:v>452</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="U4" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="107.25" hidden="0">
       <x:c r="A5" s="3" t="s">
-        <x:v>453</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C5" s="3" t="s">
-        <x:v>454</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="D5" s="3" t="s">
-        <x:v>455</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="E5" s="3" t="s">
-        <x:v>456</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="F5" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="G5" s="3" t="s">
-        <x:v>441</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="H5" s="3" t="s">
-        <x:v>442</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="I5" s="3" t="s">
-        <x:v>443</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="J5" s="3" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="K5" s="3" t="s">
         <x:v>188</x:v>
       </x:c>
       <x:c r="L5" s="3" t="s">
-        <x:v>457</x:v>
+        <x:v>448</x:v>
       </x:c>
       <x:c r="M5" s="3" t="s">
-        <x:v>445</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="N5" s="3" t="s">
-        <x:v>458</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="O5" s="3" t="s">
-        <x:v>459</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="P5" s="3" t="s">
-        <x:v>460</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="Q5" s="3" t="s">
-        <x:v>461</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="R5" s="3" t="s">
-        <x:v>462</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="S5" s="3" t="s">
-        <x:v>463</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="T5" s="3" t="s">
-        <x:v>464</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="U5" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="93.25" hidden="0">
       <x:c r="A6" s="3" t="s">
-        <x:v>465</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="B6" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C6" s="3" t="s">
-        <x:v>466</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="D6" s="3" t="s">
-        <x:v>467</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="E6" s="3" t="s">
-        <x:v>468</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F6" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="G6" s="3" t="s">
-        <x:v>441</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="H6" s="3" t="s">
-        <x:v>442</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="I6" s="3" t="s">
-        <x:v>443</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="J6" s="3" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="K6" s="3" t="s">
         <x:v>188</x:v>
       </x:c>
       <x:c r="L6" s="3" t="s">
-        <x:v>469</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="M6" s="3" t="s">
-        <x:v>445</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="N6" s="3" t="s">
-        <x:v>470</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="O6" s="3" t="s">
-        <x:v>471</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="P6" s="3" t="s">
-        <x:v>472</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="Q6" s="3" t="s">
-        <x:v>473</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="R6" s="3" t="s">
-        <x:v>474</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="S6" s="3" t="s">
-        <x:v>475</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="T6" s="3" t="s">
-        <x:v>476</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="U6" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="93.25" hidden="0">
       <x:c r="A7" s="3" t="s">
-        <x:v>477</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>478</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="D7" s="3" t="s">
-        <x:v>479</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="E7" s="3" t="s">
-        <x:v>480</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="F7" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="G7" s="3" t="s">
-        <x:v>441</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="H7" s="3" t="s">
-        <x:v>442</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="I7" s="3" t="s">
-        <x:v>443</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="J7" s="3" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="K7" s="3" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="L7" s="3" t="s">
-        <x:v>481</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="M7" s="3" t="s">
-        <x:v>445</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="N7" s="3" t="s">
-        <x:v>482</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="O7" s="3" t="s">
-        <x:v>483</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="P7" s="3" t="s">
-        <x:v>484</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="Q7" s="3" t="s">
-        <x:v>485</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="R7" s="3" t="s">
-        <x:v>486</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="S7" s="3" t="s">
-        <x:v>487</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="T7" s="3" t="s">
-        <x:v>488</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="U7" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="93.25" hidden="0">
       <x:c r="A8" s="3" t="s">
-        <x:v>489</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>490</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="D8" s="3" t="s">
-        <x:v>491</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="E8" s="3" t="s">
-        <x:v>492</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="F8" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="G8" s="3" t="s">
-        <x:v>441</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="H8" s="3" t="s">
-        <x:v>442</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="I8" s="3" t="s">
-        <x:v>443</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="J8" s="3" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="K8" s="3" t="s">
         <x:v>188</x:v>
       </x:c>
       <x:c r="L8" s="3" t="s">
-        <x:v>493</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="M8" s="3" t="s">
-        <x:v>445</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="N8" s="3" t="s">
-        <x:v>494</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="O8" s="3" t="s">
-        <x:v>495</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="P8" s="3" t="s">
-        <x:v>496</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="Q8" s="3" t="s">
-        <x:v>497</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
-        <x:v>498</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="S8" s="3" t="s">
-        <x:v>499</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="T8" s="3" t="s">
-        <x:v>500</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="U8" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="93.25" hidden="0">
       <x:c r="A9" s="3" t="s">
+        <x:v>492</x:v>
+      </x:c>
+      <x:c r="B9" s="3" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C9" s="3" t="s">
+        <x:v>493</x:v>
+      </x:c>
+      <x:c r="D9" s="3" t="s">
+        <x:v>494</x:v>
+      </x:c>
+      <x:c r="E9" s="3" t="s">
+        <x:v>495</x:v>
+      </x:c>
+      <x:c r="F9" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G9" s="3" t="s">
+        <x:v>432</x:v>
+      </x:c>
+      <x:c r="H9" s="3" t="s">
+        <x:v>433</x:v>
+      </x:c>
+      <x:c r="I9" s="3" t="s">
+        <x:v>434</x:v>
+      </x:c>
+      <x:c r="J9" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="K9" s="3" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="L9" s="3" t="s">
+        <x:v>496</x:v>
+      </x:c>
+      <x:c r="M9" s="3" t="s">
+        <x:v>436</x:v>
+      </x:c>
+      <x:c r="N9" s="3" t="s">
+        <x:v>497</x:v>
+      </x:c>
+      <x:c r="O9" s="3" t="s">
+        <x:v>498</x:v>
+      </x:c>
+      <x:c r="P9" s="3" t="s">
+        <x:v>499</x:v>
+      </x:c>
+      <x:c r="Q9" s="3" t="s">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="R9" s="3" t="s">
         <x:v>501</x:v>
       </x:c>
-      <x:c r="B9" s="3" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C9" s="3" t="s">
+      <x:c r="S9" s="3" t="s">
         <x:v>502</x:v>
       </x:c>
-      <x:c r="D9" s="3" t="s">
+      <x:c r="T9" s="3" t="s">
         <x:v>503</x:v>
       </x:c>
-      <x:c r="E9" s="3" t="s">
-        <x:v>504</x:v>
-      </x:c>
-      <x:c r="F9" s="3" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="G9" s="3" t="s">
-        <x:v>441</x:v>
-      </x:c>
-      <x:c r="H9" s="3" t="s">
-        <x:v>442</x:v>
-      </x:c>
-      <x:c r="I9" s="3" t="s">
-        <x:v>443</x:v>
-      </x:c>
-      <x:c r="J9" s="3" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="K9" s="3" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="L9" s="3" t="s">
-        <x:v>505</x:v>
-      </x:c>
-      <x:c r="M9" s="3" t="s">
-        <x:v>445</x:v>
-      </x:c>
-      <x:c r="N9" s="3" t="s">
-        <x:v>506</x:v>
-      </x:c>
-      <x:c r="O9" s="3" t="s">
-        <x:v>507</x:v>
-      </x:c>
-      <x:c r="P9" s="3" t="s">
-        <x:v>508</x:v>
-      </x:c>
-      <x:c r="Q9" s="3" t="s">
-        <x:v>509</x:v>
-      </x:c>
-      <x:c r="R9" s="3" t="s">
-        <x:v>510</x:v>
-      </x:c>
-      <x:c r="S9" s="3" t="s">
-        <x:v>511</x:v>
-      </x:c>
-      <x:c r="T9" s="3" t="s">
-        <x:v>512</x:v>
-      </x:c>
       <x:c r="U9" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="93.25" hidden="0">
       <x:c r="A10" s="3" t="s">
-        <x:v>513</x:v>
+        <x:v>504</x:v>
       </x:c>
       <x:c r="B10" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C10" s="3" t="s">
-        <x:v>514</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="D10" s="3" t="s">
-        <x:v>515</x:v>
+        <x:v>506</x:v>
       </x:c>
       <x:c r="E10" s="3" t="s">
-        <x:v>516</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="F10" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="G10" s="3" t="s">
-        <x:v>441</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="H10" s="3" t="s">
-        <x:v>442</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="I10" s="3" t="s">
-        <x:v>443</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="J10" s="3" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="K10" s="3" t="s">
         <x:v>188</x:v>
       </x:c>
       <x:c r="L10" s="3" t="s">
-        <x:v>517</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="M10" s="3" t="s">
-        <x:v>429</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="N10" s="3" t="s">
-        <x:v>518</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="O10" s="3" t="s">
         <x:v>205</x:v>
       </x:c>
       <x:c r="P10" s="3" t="s">
-        <x:v>519</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="Q10" s="3" t="s">
-        <x:v>520</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="R10" s="3" t="s">
-        <x:v>521</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="S10" s="3" t="s">
-        <x:v>522</x:v>
+        <x:v>513</x:v>
       </x:c>
       <x:c r="T10" s="3" t="s">
-        <x:v>523</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="U10" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="93.25" hidden="0">
       <x:c r="A11" s="3" t="s">
-        <x:v>524</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="B11" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C11" s="3" t="s">
-        <x:v>525</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="D11" s="3" t="s">
-        <x:v>526</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="E11" s="3" t="s">
-        <x:v>527</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="F11" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="G11" s="3" t="s">
-        <x:v>441</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="H11" s="3" t="s">
-        <x:v>442</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="I11" s="3" t="s">
-        <x:v>443</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="J11" s="3" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="K11" s="3" t="s">
         <x:v>188</x:v>
       </x:c>
       <x:c r="L11" s="3" t="s">
-        <x:v>528</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="M11" s="3" t="s">
-        <x:v>529</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="N11" s="3" t="s">
-        <x:v>530</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="O11" s="3" t="s">
-        <x:v>531</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="P11" s="3" t="s">
-        <x:v>532</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="Q11" s="3" t="s">
-        <x:v>533</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="R11" s="3" t="s">
-        <x:v>534</x:v>
+        <x:v>525</x:v>
       </x:c>
       <x:c r="S11" s="3" t="s">
-        <x:v>535</x:v>
+        <x:v>526</x:v>
       </x:c>
       <x:c r="T11" s="3" t="s">
-        <x:v>536</x:v>
+        <x:v>527</x:v>
       </x:c>
       <x:c r="U11" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="107.25" hidden="0">
       <x:c r="A12" s="3" t="s">
-        <x:v>537</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="B12" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C12" s="3" t="s">
-        <x:v>538</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="D12" s="3" t="s">
-        <x:v>539</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="E12" s="3" t="s">
-        <x:v>540</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="F12" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="G12" s="3" t="s">
-        <x:v>441</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="H12" s="3" t="s">
-        <x:v>442</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="I12" s="3" t="s">
-        <x:v>443</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="J12" s="3" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="K12" s="3" t="s">
         <x:v>188</x:v>
       </x:c>
       <x:c r="L12" s="3" t="s">
-        <x:v>541</x:v>
+        <x:v>532</x:v>
       </x:c>
       <x:c r="M12" s="3" t="s">
-        <x:v>445</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="N12" s="3" t="s">
-        <x:v>542</x:v>
+        <x:v>533</x:v>
       </x:c>
       <x:c r="O12" s="3" t="s">
-        <x:v>543</x:v>
+        <x:v>534</x:v>
       </x:c>
       <x:c r="P12" s="3" t="s">
-        <x:v>544</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="Q12" s="3" t="s">
-        <x:v>545</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="R12" s="3" t="s">
-        <x:v>546</x:v>
+        <x:v>537</x:v>
       </x:c>
       <x:c r="S12" s="3" t="s">
-        <x:v>547</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="T12" s="3" t="s">
-        <x:v>548</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="U12" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="93.25" hidden="0">
       <x:c r="A13" s="3" t="s">
+        <x:v>540</x:v>
+      </x:c>
+      <x:c r="B13" s="3" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C13" s="3" t="s">
+        <x:v>541</x:v>
+      </x:c>
+      <x:c r="D13" s="3" t="s">
+        <x:v>542</x:v>
+      </x:c>
+      <x:c r="E13" s="3" t="s">
+        <x:v>543</x:v>
+      </x:c>
+      <x:c r="F13" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G13" s="3" t="s">
+        <x:v>432</x:v>
+      </x:c>
+      <x:c r="H13" s="3" t="s">
+        <x:v>433</x:v>
+      </x:c>
+      <x:c r="I13" s="3" t="s">
+        <x:v>434</x:v>
+      </x:c>
+      <x:c r="J13" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="K13" s="3" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="L13" s="3" t="s">
+        <x:v>544</x:v>
+      </x:c>
+      <x:c r="M13" s="3" t="s">
+        <x:v>436</x:v>
+      </x:c>
+      <x:c r="N13" s="3" t="s">
+        <x:v>545</x:v>
+      </x:c>
+      <x:c r="O13" s="3" t="s">
+        <x:v>546</x:v>
+      </x:c>
+      <x:c r="P13" s="3" t="s">
+        <x:v>547</x:v>
+      </x:c>
+      <x:c r="Q13" s="3" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="R13" s="3" t="s">
+        <x:v>548</x:v>
+      </x:c>
+      <x:c r="S13" s="3" t="s">
         <x:v>549</x:v>
       </x:c>
-      <x:c r="B13" s="3" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C13" s="3" t="s">
+      <x:c r="T13" s="3" t="s">
         <x:v>550</x:v>
       </x:c>
-      <x:c r="D13" s="3" t="s">
-        <x:v>551</x:v>
-      </x:c>
-      <x:c r="E13" s="3" t="s">
-        <x:v>552</x:v>
-      </x:c>
-      <x:c r="F13" s="3" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="G13" s="3" t="s">
-        <x:v>441</x:v>
-      </x:c>
-      <x:c r="H13" s="3" t="s">
-        <x:v>442</x:v>
-      </x:c>
-      <x:c r="I13" s="3" t="s">
-        <x:v>443</x:v>
-      </x:c>
-      <x:c r="J13" s="3" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="K13" s="3" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="L13" s="3" t="s">
-        <x:v>553</x:v>
-      </x:c>
-      <x:c r="M13" s="3" t="s">
-        <x:v>445</x:v>
-      </x:c>
-      <x:c r="N13" s="3" t="s">
-        <x:v>554</x:v>
-      </x:c>
-      <x:c r="O13" s="3" t="s">
-        <x:v>555</x:v>
-      </x:c>
-      <x:c r="P13" s="3" t="s">
-        <x:v>556</x:v>
-      </x:c>
-      <x:c r="Q13" s="3" t="s">
-        <x:v>545</x:v>
-      </x:c>
-      <x:c r="R13" s="3" t="s">
-        <x:v>557</x:v>
-      </x:c>
-      <x:c r="S13" s="3" t="s">
-        <x:v>558</x:v>
-      </x:c>
-      <x:c r="T13" s="3" t="s">
-        <x:v>559</x:v>
-      </x:c>
       <x:c r="U13" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="93.25" hidden="0">
       <x:c r="A14" s="3" t="s">
+        <x:v>551</x:v>
+      </x:c>
+      <x:c r="B14" s="3" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C14" s="3" t="s">
+        <x:v>552</x:v>
+      </x:c>
+      <x:c r="D14" s="3" t="s">
+        <x:v>553</x:v>
+      </x:c>
+      <x:c r="E14" s="3" t="s">
+        <x:v>554</x:v>
+      </x:c>
+      <x:c r="F14" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G14" s="3" t="s">
+        <x:v>432</x:v>
+      </x:c>
+      <x:c r="H14" s="3" t="s">
+        <x:v>433</x:v>
+      </x:c>
+      <x:c r="I14" s="3" t="s">
+        <x:v>434</x:v>
+      </x:c>
+      <x:c r="J14" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="K14" s="3" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="L14" s="3" t="s">
+        <x:v>555</x:v>
+      </x:c>
+      <x:c r="M14" s="3" t="s">
+        <x:v>556</x:v>
+      </x:c>
+      <x:c r="N14" s="3" t="s">
+        <x:v>557</x:v>
+      </x:c>
+      <x:c r="O14" s="3" t="s">
+        <x:v>558</x:v>
+      </x:c>
+      <x:c r="P14" s="3" t="s">
+        <x:v>559</x:v>
+      </x:c>
+      <x:c r="Q14" s="3" t="s">
         <x:v>560</x:v>
       </x:c>
-      <x:c r="B14" s="3" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C14" s="3" t="s">
+      <x:c r="R14" s="3" t="s">
         <x:v>561</x:v>
       </x:c>
-      <x:c r="D14" s="3" t="s">
+      <x:c r="S14" s="3" t="s">
         <x:v>562</x:v>
       </x:c>
-      <x:c r="E14" s="3" t="s">
+      <x:c r="T14" s="3" t="s">
         <x:v>563</x:v>
       </x:c>
-      <x:c r="F14" s="3" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="G14" s="3" t="s">
-        <x:v>441</x:v>
-      </x:c>
-      <x:c r="H14" s="3" t="s">
-        <x:v>442</x:v>
-      </x:c>
-      <x:c r="I14" s="3" t="s">
-        <x:v>443</x:v>
-      </x:c>
-      <x:c r="J14" s="3" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="K14" s="3" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="L14" s="3" t="s">
-        <x:v>564</x:v>
-      </x:c>
-      <x:c r="M14" s="3" t="s">
-        <x:v>565</x:v>
-      </x:c>
-      <x:c r="N14" s="3" t="s">
-        <x:v>566</x:v>
-      </x:c>
-      <x:c r="O14" s="3" t="s">
-        <x:v>567</x:v>
-      </x:c>
-      <x:c r="P14" s="3" t="s">
-        <x:v>568</x:v>
-      </x:c>
-      <x:c r="Q14" s="3" t="s">
-        <x:v>569</x:v>
-      </x:c>
-      <x:c r="R14" s="3" t="s">
-        <x:v>570</x:v>
-      </x:c>
-      <x:c r="S14" s="3" t="s">
-        <x:v>571</x:v>
-      </x:c>
-      <x:c r="T14" s="3" t="s">
-        <x:v>572</x:v>
-      </x:c>
       <x:c r="U14" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="107.25" hidden="0">
       <x:c r="A15" s="3" t="s">
-        <x:v>573</x:v>
+        <x:v>564</x:v>
       </x:c>
       <x:c r="B15" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C15" s="3" t="s">
-        <x:v>574</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="D15" s="3" t="s">
-        <x:v>575</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="E15" s="3" t="s">
-        <x:v>576</x:v>
+        <x:v>567</x:v>
       </x:c>
       <x:c r="F15" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="G15" s="3" t="s">
-        <x:v>441</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="H15" s="3" t="s">
-        <x:v>442</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="I15" s="3" t="s">
-        <x:v>443</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="J15" s="3" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="K15" s="3" t="s">
         <x:v>188</x:v>
       </x:c>
       <x:c r="L15" s="3" t="s">
-        <x:v>577</x:v>
+        <x:v>568</x:v>
       </x:c>
       <x:c r="M15" s="3" t="s">
-        <x:v>445</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="N15" s="3" t="s">
-        <x:v>578</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="O15" s="3" t="s">
-        <x:v>579</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="P15" s="3" t="s">
-        <x:v>580</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="Q15" s="3" t="s">
-        <x:v>581</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="R15" s="3" t="s">
-        <x:v>582</x:v>
+        <x:v>573</x:v>
       </x:c>
       <x:c r="S15" s="3" t="s">
-        <x:v>583</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="T15" s="3" t="s">
-        <x:v>584</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="U15" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="107.25" hidden="0">
       <x:c r="A16" s="3" t="s">
+        <x:v>576</x:v>
+      </x:c>
+      <x:c r="B16" s="3" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C16" s="3" t="s">
+        <x:v>577</x:v>
+      </x:c>
+      <x:c r="D16" s="3" t="s">
+        <x:v>578</x:v>
+      </x:c>
+      <x:c r="E16" s="3" t="s">
+        <x:v>579</x:v>
+      </x:c>
+      <x:c r="F16" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G16" s="3" t="s">
+        <x:v>432</x:v>
+      </x:c>
+      <x:c r="H16" s="3" t="s">
+        <x:v>433</x:v>
+      </x:c>
+      <x:c r="I16" s="3" t="s">
+        <x:v>434</x:v>
+      </x:c>
+      <x:c r="J16" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="K16" s="3" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="L16" s="3" t="s">
+        <x:v>580</x:v>
+      </x:c>
+      <x:c r="M16" s="3" t="s">
+        <x:v>436</x:v>
+      </x:c>
+      <x:c r="N16" s="3" t="s">
+        <x:v>581</x:v>
+      </x:c>
+      <x:c r="O16" s="3" t="s">
+        <x:v>582</x:v>
+      </x:c>
+      <x:c r="P16" s="3" t="s">
+        <x:v>583</x:v>
+      </x:c>
+      <x:c r="Q16" s="3" t="s">
+        <x:v>584</x:v>
+      </x:c>
+      <x:c r="R16" s="3" t="s">
         <x:v>585</x:v>
       </x:c>
-      <x:c r="B16" s="3" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C16" s="3" t="s">
+      <x:c r="S16" s="3" t="s">
         <x:v>586</x:v>
       </x:c>
-      <x:c r="D16" s="3" t="s">
+      <x:c r="T16" s="3" t="s">
         <x:v>587</x:v>
       </x:c>
-      <x:c r="E16" s="3" t="s">
-        <x:v>588</x:v>
-      </x:c>
-      <x:c r="F16" s="3" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="G16" s="3" t="s">
-        <x:v>441</x:v>
-      </x:c>
-      <x:c r="H16" s="3" t="s">
-        <x:v>442</x:v>
-      </x:c>
-      <x:c r="I16" s="3" t="s">
-        <x:v>443</x:v>
-      </x:c>
-      <x:c r="J16" s="3" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="K16" s="3" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="L16" s="3" t="s">
-        <x:v>589</x:v>
-      </x:c>
-      <x:c r="M16" s="3" t="s">
-        <x:v>445</x:v>
-      </x:c>
-      <x:c r="N16" s="3" t="s">
-        <x:v>590</x:v>
-      </x:c>
-      <x:c r="O16" s="3" t="s">
-        <x:v>591</x:v>
-      </x:c>
-      <x:c r="P16" s="3" t="s">
-        <x:v>592</x:v>
-      </x:c>
-      <x:c r="Q16" s="3" t="s">
-        <x:v>593</x:v>
-      </x:c>
-      <x:c r="R16" s="3" t="s">
-        <x:v>594</x:v>
-      </x:c>
-      <x:c r="S16" s="3" t="s">
-        <x:v>595</x:v>
-      </x:c>
-      <x:c r="T16" s="3" t="s">
-        <x:v>596</x:v>
-      </x:c>
       <x:c r="U16" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="93.25" hidden="0">
       <x:c r="A17" s="3" t="s">
-        <x:v>597</x:v>
+        <x:v>588</x:v>
       </x:c>
       <x:c r="B17" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C17" s="3" t="s">
-        <x:v>598</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="D17" s="3" t="s">
-        <x:v>599</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="E17" s="3" t="s">
-        <x:v>600</x:v>
+        <x:v>591</x:v>
       </x:c>
       <x:c r="F17" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="G17" s="3" t="s">
-        <x:v>441</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="H17" s="3" t="s">
-        <x:v>442</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="I17" s="3" t="s">
-        <x:v>443</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="J17" s="3" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="K17" s="3" t="s">
         <x:v>188</x:v>
       </x:c>
       <x:c r="L17" s="3" t="s">
-        <x:v>601</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="M17" s="3" t="s">
-        <x:v>602</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="N17" s="3" t="s">
-        <x:v>603</x:v>
+        <x:v>594</x:v>
       </x:c>
       <x:c r="O17" s="3" t="s">
-        <x:v>604</x:v>
+        <x:v>595</x:v>
       </x:c>
       <x:c r="P17" s="3" t="s">
-        <x:v>605</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="Q17" s="3" t="s">
-        <x:v>606</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="R17" s="3" t="s">
-        <x:v>607</x:v>
+        <x:v>598</x:v>
       </x:c>
       <x:c r="S17" s="3" t="s">
-        <x:v>608</x:v>
+        <x:v>599</x:v>
       </x:c>
       <x:c r="T17" s="3" t="s">
-        <x:v>609</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="U17" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="93.25" hidden="0">
       <x:c r="A18" s="3" t="s">
-        <x:v>610</x:v>
+        <x:v>601</x:v>
       </x:c>
       <x:c r="B18" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C18" s="3" t="s">
-        <x:v>611</x:v>
+        <x:v>602</x:v>
       </x:c>
       <x:c r="D18" s="3" t="s">
-        <x:v>612</x:v>
+        <x:v>603</x:v>
       </x:c>
       <x:c r="E18" s="3" t="s">
-        <x:v>613</x:v>
+        <x:v>604</x:v>
       </x:c>
       <x:c r="F18" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="G18" s="3" t="s">
-        <x:v>441</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="H18" s="3" t="s">
-        <x:v>442</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="I18" s="3" t="s">
-        <x:v>443</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="J18" s="3" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="K18" s="3" t="s">
         <x:v>188</x:v>
       </x:c>
       <x:c r="L18" s="3" t="s">
-        <x:v>614</x:v>
+        <x:v>605</x:v>
       </x:c>
       <x:c r="M18" s="3" t="s">
-        <x:v>615</x:v>
+        <x:v>606</x:v>
       </x:c>
       <x:c r="N18" s="3" t="s">
-        <x:v>616</x:v>
+        <x:v>607</x:v>
       </x:c>
       <x:c r="O18" s="3" t="s">
-        <x:v>617</x:v>
+        <x:v>608</x:v>
       </x:c>
       <x:c r="P18" s="3" t="s">
-        <x:v>618</x:v>
+        <x:v>609</x:v>
       </x:c>
       <x:c r="Q18" s="3" t="s">
-        <x:v>619</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="R18" s="3" t="s">
-        <x:v>620</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="S18" s="3" t="s">
-        <x:v>621</x:v>
+        <x:v>612</x:v>
       </x:c>
       <x:c r="T18" s="3" t="s">
-        <x:v>622</x:v>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="U18" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="93.25" hidden="0">
       <x:c r="A19" s="3" t="s">
-        <x:v>623</x:v>
+        <x:v>614</x:v>
       </x:c>
       <x:c r="B19" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C19" s="3" t="s">
-        <x:v>624</x:v>
+        <x:v>615</x:v>
       </x:c>
       <x:c r="D19" s="3" t="s">
-        <x:v>625</x:v>
+        <x:v>616</x:v>
       </x:c>
       <x:c r="E19" s="3" t="s">
-        <x:v>626</x:v>
+        <x:v>617</x:v>
       </x:c>
       <x:c r="F19" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="G19" s="3" t="s">
-        <x:v>441</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="H19" s="3" t="s">
-        <x:v>442</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="I19" s="3" t="s">
-        <x:v>443</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="J19" s="3" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="K19" s="3" t="s">
         <x:v>188</x:v>
       </x:c>
       <x:c r="L19" s="3" t="s">
-        <x:v>627</x:v>
+        <x:v>618</x:v>
       </x:c>
       <x:c r="M19" s="3" t="s">
-        <x:v>628</x:v>
+        <x:v>619</x:v>
       </x:c>
       <x:c r="N19" s="3" t="s">
-        <x:v>629</x:v>
+        <x:v>620</x:v>
       </x:c>
       <x:c r="O19" s="3" t="s">
-        <x:v>630</x:v>
+        <x:v>621</x:v>
       </x:c>
       <x:c r="P19" s="3" t="s">
-        <x:v>631</x:v>
+        <x:v>622</x:v>
       </x:c>
       <x:c r="Q19" s="3" t="s">
-        <x:v>632</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="R19" s="3" t="s">
-        <x:v>633</x:v>
+        <x:v>624</x:v>
       </x:c>
       <x:c r="S19" s="3" t="s">
-        <x:v>634</x:v>
+        <x:v>625</x:v>
       </x:c>
       <x:c r="T19" s="3" t="s">
-        <x:v>635</x:v>
+        <x:v>626</x:v>
       </x:c>
       <x:c r="U19" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="79.25" hidden="0">
       <x:c r="A20" s="3" t="s">
+        <x:v>627</x:v>
+      </x:c>
+      <x:c r="B20" s="3" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C20" s="3" t="s">
+        <x:v>628</x:v>
+      </x:c>
+      <x:c r="D20" s="3" t="s">
+        <x:v>629</x:v>
+      </x:c>
+      <x:c r="E20" s="3" t="s">
+        <x:v>630</x:v>
+      </x:c>
+      <x:c r="F20" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G20" s="3" t="s">
+        <x:v>432</x:v>
+      </x:c>
+      <x:c r="H20" s="3" t="s">
+        <x:v>433</x:v>
+      </x:c>
+      <x:c r="I20" s="3" t="s">
+        <x:v>434</x:v>
+      </x:c>
+      <x:c r="J20" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="K20" s="3" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="L20" s="3" t="s">
+        <x:v>631</x:v>
+      </x:c>
+      <x:c r="M20" s="3" t="s">
+        <x:v>632</x:v>
+      </x:c>
+      <x:c r="N20" s="3" t="s">
+        <x:v>633</x:v>
+      </x:c>
+      <x:c r="O20" s="3" t="s">
+        <x:v>634</x:v>
+      </x:c>
+      <x:c r="P20" s="3" t="s">
+        <x:v>635</x:v>
+      </x:c>
+      <x:c r="Q20" s="3" t="s">
         <x:v>636</x:v>
       </x:c>
-      <x:c r="B20" s="3" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C20" s="3" t="s">
+      <x:c r="R20" s="3" t="s">
         <x:v>637</x:v>
       </x:c>
-      <x:c r="D20" s="3" t="s">
+      <x:c r="S20" s="3" t="s">
         <x:v>638</x:v>
       </x:c>
-      <x:c r="E20" s="3" t="s">
+      <x:c r="T20" s="3" t="s">
         <x:v>639</x:v>
       </x:c>
-      <x:c r="F20" s="3" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="G20" s="3" t="s">
-        <x:v>441</x:v>
-      </x:c>
-      <x:c r="H20" s="3" t="s">
-        <x:v>442</x:v>
-      </x:c>
-      <x:c r="I20" s="3" t="s">
-        <x:v>443</x:v>
-      </x:c>
-      <x:c r="J20" s="3" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="K20" s="3" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="L20" s="3" t="s">
-        <x:v>640</x:v>
-      </x:c>
-      <x:c r="M20" s="3" t="s">
-        <x:v>641</x:v>
-      </x:c>
-      <x:c r="N20" s="3" t="s">
-        <x:v>642</x:v>
-      </x:c>
-      <x:c r="O20" s="3" t="s">
-        <x:v>643</x:v>
-      </x:c>
-      <x:c r="P20" s="3" t="s">
-        <x:v>644</x:v>
-      </x:c>
-      <x:c r="Q20" s="3" t="s">
-        <x:v>645</x:v>
-      </x:c>
-      <x:c r="R20" s="3" t="s">
-        <x:v>646</x:v>
-      </x:c>
-      <x:c r="S20" s="3" t="s">
-        <x:v>647</x:v>
-      </x:c>
-      <x:c r="T20" s="3" t="s">
-        <x:v>648</x:v>
-      </x:c>
       <x:c r="U20" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="79.25" hidden="0">
       <x:c r="A21" s="3" t="s">
-        <x:v>649</x:v>
+        <x:v>640</x:v>
       </x:c>
       <x:c r="B21" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C21" s="3" t="s">
-        <x:v>650</x:v>
+        <x:v>641</x:v>
       </x:c>
       <x:c r="D21" s="3" t="s">
-        <x:v>651</x:v>
+        <x:v>642</x:v>
       </x:c>
       <x:c r="E21" s="3" t="s">
-        <x:v>652</x:v>
+        <x:v>643</x:v>
       </x:c>
       <x:c r="F21" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="G21" s="3" t="s">
-        <x:v>441</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="H21" s="3" t="s">
-        <x:v>442</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="I21" s="3" t="s">
-        <x:v>443</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="J21" s="3" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="K21" s="3" t="s">
         <x:v>188</x:v>
       </x:c>
       <x:c r="L21" s="3" t="s">
-        <x:v>653</x:v>
+        <x:v>644</x:v>
       </x:c>
       <x:c r="M21" s="3" t="s">
-        <x:v>654</x:v>
+        <x:v>645</x:v>
       </x:c>
       <x:c r="N21" s="3" t="s">
-        <x:v>655</x:v>
+        <x:v>646</x:v>
       </x:c>
       <x:c r="O21" s="3" t="s">
         <x:v>218</x:v>
       </x:c>
       <x:c r="P21" s="3" t="s">
-        <x:v>656</x:v>
+        <x:v>647</x:v>
       </x:c>
       <x:c r="Q21" s="3" t="s">
-        <x:v>657</x:v>
+        <x:v>648</x:v>
       </x:c>
       <x:c r="R21" s="3" t="s">
         <x:v>221</x:v>
       </x:c>
       <x:c r="S21" s="3" t="s">
-        <x:v>658</x:v>
+        <x:v>649</x:v>
       </x:c>
       <x:c r="T21" s="3" t="s">
-        <x:v>659</x:v>
+        <x:v>650</x:v>
       </x:c>
       <x:c r="U21" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="93.25" hidden="0">
       <x:c r="A22" s="3" t="s">
-        <x:v>660</x:v>
+        <x:v>651</x:v>
       </x:c>
       <x:c r="B22" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C22" s="3" t="s">
-        <x:v>661</x:v>
+        <x:v>652</x:v>
       </x:c>
       <x:c r="D22" s="3" t="s">
-        <x:v>662</x:v>
+        <x:v>653</x:v>
       </x:c>
       <x:c r="E22" s="3" t="s">
-        <x:v>663</x:v>
+        <x:v>654</x:v>
       </x:c>
       <x:c r="F22" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="G22" s="3" t="s">
-        <x:v>441</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="H22" s="3" t="s">
-        <x:v>442</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="I22" s="3" t="s">
-        <x:v>443</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="J22" s="3" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="K22" s="3" t="s">
         <x:v>188</x:v>
       </x:c>
       <x:c r="L22" s="3" t="s">
-        <x:v>664</x:v>
+        <x:v>655</x:v>
       </x:c>
       <x:c r="M22" s="3" t="s">
-        <x:v>529</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="N22" s="3" t="s">
-        <x:v>665</x:v>
+        <x:v>656</x:v>
       </x:c>
       <x:c r="O22" s="3" t="s">
-        <x:v>666</x:v>
+        <x:v>657</x:v>
       </x:c>
       <x:c r="P22" s="3" t="s">
-        <x:v>667</x:v>
+        <x:v>658</x:v>
       </x:c>
       <x:c r="Q22" s="3" t="s">
-        <x:v>668</x:v>
+        <x:v>659</x:v>
       </x:c>
       <x:c r="R22" s="3" t="s">
-        <x:v>669</x:v>
+        <x:v>660</x:v>
       </x:c>
       <x:c r="S22" s="3" t="s">
-        <x:v>670</x:v>
+        <x:v>661</x:v>
       </x:c>
       <x:c r="T22" s="3" t="s">
-        <x:v>671</x:v>
+        <x:v>662</x:v>
       </x:c>
       <x:c r="U22" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="93.25" hidden="0">
       <x:c r="A23" s="3" t="s">
-        <x:v>672</x:v>
+        <x:v>663</x:v>
       </x:c>
       <x:c r="B23" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C23" s="3" t="s">
-        <x:v>673</x:v>
+        <x:v>664</x:v>
       </x:c>
       <x:c r="D23" s="3" t="s">
-        <x:v>674</x:v>
+        <x:v>665</x:v>
       </x:c>
       <x:c r="E23" s="3" t="s">
-        <x:v>675</x:v>
+        <x:v>666</x:v>
       </x:c>
       <x:c r="F23" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="G23" s="3" t="s">
-        <x:v>441</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="H23" s="3" t="s">
-        <x:v>442</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="I23" s="3" t="s">
-        <x:v>443</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="J23" s="3" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="K23" s="3" t="s">
         <x:v>188</x:v>
       </x:c>
       <x:c r="L23" s="3" t="s">
-        <x:v>676</x:v>
+        <x:v>667</x:v>
       </x:c>
       <x:c r="M23" s="3" t="s">
-        <x:v>677</x:v>
+        <x:v>668</x:v>
       </x:c>
       <x:c r="N23" s="3" t="s">
-        <x:v>678</x:v>
+        <x:v>669</x:v>
       </x:c>
       <x:c r="O23" s="3" t="s">
-        <x:v>679</x:v>
+        <x:v>670</x:v>
       </x:c>
       <x:c r="P23" s="3" t="s">
-        <x:v>680</x:v>
+        <x:v>671</x:v>
       </x:c>
       <x:c r="Q23" s="3" t="s">
-        <x:v>681</x:v>
+        <x:v>672</x:v>
       </x:c>
       <x:c r="R23" s="3" t="s">
-        <x:v>682</x:v>
+        <x:v>673</x:v>
       </x:c>
       <x:c r="S23" s="3" t="s">
-        <x:v>683</x:v>
+        <x:v>674</x:v>
       </x:c>
       <x:c r="T23" s="3" t="s">
-        <x:v>684</x:v>
+        <x:v>675</x:v>
       </x:c>
       <x:c r="U23" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="79.25" hidden="0">
       <x:c r="A24" s="3" t="s">
-        <x:v>685</x:v>
+        <x:v>676</x:v>
       </x:c>
       <x:c r="B24" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C24" s="3" t="s">
-        <x:v>686</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="D24" s="3" t="s">
-        <x:v>687</x:v>
+        <x:v>678</x:v>
       </x:c>
       <x:c r="E24" s="3" t="s">
-        <x:v>688</x:v>
+        <x:v>679</x:v>
       </x:c>
       <x:c r="F24" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="G24" s="3" t="s">
-        <x:v>441</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="H24" s="3" t="s">
-        <x:v>442</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="I24" s="3" t="s">
-        <x:v>443</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="J24" s="3" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="K24" s="3" t="s">
         <x:v>188</x:v>
       </x:c>
       <x:c r="L24" s="3" t="s">
-        <x:v>689</x:v>
+        <x:v>680</x:v>
       </x:c>
       <x:c r="M24" s="3" t="s">
-        <x:v>654</x:v>
+        <x:v>645</x:v>
       </x:c>
       <x:c r="N24" s="3" t="s">
-        <x:v>690</x:v>
+        <x:v>681</x:v>
       </x:c>
       <x:c r="O24" s="3" t="s">
-        <x:v>691</x:v>
+        <x:v>682</x:v>
       </x:c>
       <x:c r="P24" s="3" t="s">
-        <x:v>692</x:v>
+        <x:v>683</x:v>
       </x:c>
       <x:c r="Q24" s="3" t="s">
-        <x:v>693</x:v>
+        <x:v>684</x:v>
       </x:c>
       <x:c r="R24" s="3" t="s">
-        <x:v>694</x:v>
+        <x:v>685</x:v>
       </x:c>
       <x:c r="S24" s="3" t="s">
-        <x:v>695</x:v>
+        <x:v>686</x:v>
       </x:c>
       <x:c r="T24" s="3" t="s">
-        <x:v>696</x:v>
+        <x:v>687</x:v>
       </x:c>
       <x:c r="U24" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="79.25" hidden="0">
       <x:c r="A25" s="3" t="s">
-        <x:v>697</x:v>
+        <x:v>688</x:v>
       </x:c>
       <x:c r="B25" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C25" s="3" t="s">
-        <x:v>698</x:v>
+        <x:v>689</x:v>
       </x:c>
       <x:c r="D25" s="3" t="s">
-        <x:v>699</x:v>
+        <x:v>690</x:v>
       </x:c>
       <x:c r="E25" s="3" t="s">
-        <x:v>700</x:v>
+        <x:v>691</x:v>
       </x:c>
       <x:c r="F25" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="G25" s="3" t="s">
-        <x:v>441</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="H25" s="3" t="s">
-        <x:v>442</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="I25" s="3" t="s">
-        <x:v>443</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="J25" s="3" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="K25" s="3" t="s">
         <x:v>188</x:v>
       </x:c>
       <x:c r="L25" s="3" t="s">
-        <x:v>701</x:v>
+        <x:v>692</x:v>
       </x:c>
       <x:c r="M25" s="3" t="s">
-        <x:v>654</x:v>
+        <x:v>645</x:v>
       </x:c>
       <x:c r="N25" s="3" t="s">
-        <x:v>702</x:v>
+        <x:v>693</x:v>
       </x:c>
       <x:c r="O25" s="3" t="s">
-        <x:v>703</x:v>
+        <x:v>694</x:v>
       </x:c>
       <x:c r="P25" s="3" t="s">
-        <x:v>704</x:v>
+        <x:v>695</x:v>
       </x:c>
       <x:c r="Q25" s="3" t="s">
-        <x:v>705</x:v>
+        <x:v>696</x:v>
       </x:c>
       <x:c r="R25" s="3" t="s">
-        <x:v>706</x:v>
+        <x:v>697</x:v>
       </x:c>
       <x:c r="S25" s="3" t="s">
-        <x:v>707</x:v>
+        <x:v>698</x:v>
       </x:c>
       <x:c r="T25" s="3" t="s">
-        <x:v>708</x:v>
+        <x:v>699</x:v>
       </x:c>
       <x:c r="U25" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="79.25" hidden="0">
       <x:c r="A26" s="3" t="s">
-        <x:v>709</x:v>
+        <x:v>700</x:v>
       </x:c>
       <x:c r="B26" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C26" s="3" t="s">
-        <x:v>710</x:v>
+        <x:v>701</x:v>
       </x:c>
       <x:c r="D26" s="3" t="s">
-        <x:v>711</x:v>
+        <x:v>702</x:v>
       </x:c>
       <x:c r="E26" s="3" t="s">
-        <x:v>712</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="F26" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="G26" s="3" t="s">
-        <x:v>441</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="H26" s="3" t="s">
-        <x:v>442</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="I26" s="3" t="s">
-        <x:v>443</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="J26" s="3" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="K26" s="3" t="s">
         <x:v>188</x:v>
       </x:c>
       <x:c r="L26" s="3" t="s">
-        <x:v>713</x:v>
+        <x:v>704</x:v>
       </x:c>
       <x:c r="M26" s="3" t="s">
-        <x:v>714</x:v>
+        <x:v>705</x:v>
       </x:c>
       <x:c r="N26" s="3" t="s">
-        <x:v>715</x:v>
+        <x:v>706</x:v>
       </x:c>
       <x:c r="O26" s="3" t="s">
-        <x:v>716</x:v>
+        <x:v>707</x:v>
       </x:c>
       <x:c r="P26" s="3" t="s">
-        <x:v>717</x:v>
+        <x:v>708</x:v>
       </x:c>
       <x:c r="Q26" s="3" t="s">
-        <x:v>718</x:v>
+        <x:v>709</x:v>
       </x:c>
       <x:c r="R26" s="3" t="s">
-        <x:v>719</x:v>
+        <x:v>710</x:v>
       </x:c>
       <x:c r="S26" s="3" t="s">
-        <x:v>720</x:v>
+        <x:v>711</x:v>
       </x:c>
       <x:c r="T26" s="3" t="s">
-        <x:v>721</x:v>
+        <x:v>712</x:v>
       </x:c>
       <x:c r="U26" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="79.25" hidden="0">
       <x:c r="A27" s="3" t="s">
+        <x:v>713</x:v>
+      </x:c>
+      <x:c r="B27" s="3" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C27" s="3" t="s">
+        <x:v>714</x:v>
+      </x:c>
+      <x:c r="D27" s="3" t="s">
+        <x:v>715</x:v>
+      </x:c>
+      <x:c r="E27" s="3" t="s">
+        <x:v>716</x:v>
+      </x:c>
+      <x:c r="F27" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G27" s="3" t="s">
+        <x:v>432</x:v>
+      </x:c>
+      <x:c r="H27" s="3" t="s">
+        <x:v>433</x:v>
+      </x:c>
+      <x:c r="I27" s="3" t="s">
+        <x:v>434</x:v>
+      </x:c>
+      <x:c r="J27" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="K27" s="3" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="L27" s="3" t="s">
+        <x:v>717</x:v>
+      </x:c>
+      <x:c r="M27" s="3" t="s">
+        <x:v>718</x:v>
+      </x:c>
+      <x:c r="N27" s="3" t="s">
+        <x:v>719</x:v>
+      </x:c>
+      <x:c r="O27" s="3" t="s">
+        <x:v>720</x:v>
+      </x:c>
+      <x:c r="P27" s="3" t="s">
+        <x:v>721</x:v>
+      </x:c>
+      <x:c r="Q27" s="3" t="s">
         <x:v>722</x:v>
       </x:c>
-      <x:c r="B27" s="3" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C27" s="3" t="s">
+      <x:c r="R27" s="3" t="s">
         <x:v>723</x:v>
       </x:c>
-      <x:c r="D27" s="3" t="s">
+      <x:c r="S27" s="3" t="s">
         <x:v>724</x:v>
       </x:c>
-      <x:c r="E27" s="3" t="s">
+      <x:c r="T27" s="3" t="s">
         <x:v>725</x:v>
       </x:c>
-      <x:c r="F27" s="3" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="G27" s="3" t="s">
-        <x:v>441</x:v>
-      </x:c>
-      <x:c r="H27" s="3" t="s">
-        <x:v>442</x:v>
-      </x:c>
-      <x:c r="I27" s="3" t="s">
-        <x:v>443</x:v>
-      </x:c>
-      <x:c r="J27" s="3" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="K27" s="3" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="L27" s="3" t="s">
-        <x:v>726</x:v>
-      </x:c>
-      <x:c r="M27" s="3" t="s">
-        <x:v>727</x:v>
-      </x:c>
-      <x:c r="N27" s="3" t="s">
-        <x:v>728</x:v>
-      </x:c>
-      <x:c r="O27" s="3" t="s">
-        <x:v>729</x:v>
-      </x:c>
-      <x:c r="P27" s="3" t="s">
-        <x:v>730</x:v>
-      </x:c>
-      <x:c r="Q27" s="3" t="s">
-        <x:v>731</x:v>
-      </x:c>
-      <x:c r="R27" s="3" t="s">
-        <x:v>732</x:v>
-      </x:c>
-      <x:c r="S27" s="3" t="s">
-        <x:v>733</x:v>
-      </x:c>
-      <x:c r="T27" s="3" t="s">
-        <x:v>734</x:v>
-      </x:c>
       <x:c r="U27" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="93.25" hidden="0">
       <x:c r="A28" s="3" t="s">
+        <x:v>726</x:v>
+      </x:c>
+      <x:c r="B28" s="3" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C28" s="3" t="s">
+        <x:v>727</x:v>
+      </x:c>
+      <x:c r="D28" s="3" t="s">
+        <x:v>728</x:v>
+      </x:c>
+      <x:c r="E28" s="3" t="s">
+        <x:v>729</x:v>
+      </x:c>
+      <x:c r="F28" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G28" s="3" t="s">
+        <x:v>432</x:v>
+      </x:c>
+      <x:c r="H28" s="3" t="s">
+        <x:v>433</x:v>
+      </x:c>
+      <x:c r="I28" s="3" t="s">
+        <x:v>434</x:v>
+      </x:c>
+      <x:c r="J28" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="K28" s="3" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="L28" s="3" t="s">
+        <x:v>730</x:v>
+      </x:c>
+      <x:c r="M28" s="3" t="s">
+        <x:v>731</x:v>
+      </x:c>
+      <x:c r="N28" s="3" t="s">
+        <x:v>732</x:v>
+      </x:c>
+      <x:c r="O28" s="3" t="s">
+        <x:v>733</x:v>
+      </x:c>
+      <x:c r="P28" s="3" t="s">
+        <x:v>734</x:v>
+      </x:c>
+      <x:c r="Q28" s="3" t="s">
         <x:v>735</x:v>
       </x:c>
-      <x:c r="B28" s="3" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C28" s="3" t="s">
+      <x:c r="R28" s="3" t="s">
         <x:v>736</x:v>
-      </x:c>
-      <x:c r="D28" s="3" t="s">
-        <x:v>737</x:v>
-      </x:c>
-      <x:c r="E28" s="3" t="s">
-        <x:v>738</x:v>
-      </x:c>
-      <x:c r="F28" s="3" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="G28" s="3" t="s">
-        <x:v>441</x:v>
-      </x:c>
-      <x:c r="H28" s="3" t="s">
-        <x:v>442</x:v>
-      </x:c>
-      <x:c r="I28" s="3" t="s">
-        <x:v>443</x:v>
-      </x:c>
-      <x:c r="J28" s="3" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="K28" s="3" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="L28" s="3" t="s">
-        <x:v>739</x:v>
-      </x:c>
-      <x:c r="M28" s="3" t="s">
-        <x:v>740</x:v>
-      </x:c>
-      <x:c r="N28" s="3" t="s">
-        <x:v>741</x:v>
-      </x:c>
-      <x:c r="O28" s="3" t="s">
-        <x:v>742</x:v>
-      </x:c>
-      <x:c r="P28" s="3" t="s">
-        <x:v>743</x:v>
-      </x:c>
-      <x:c r="Q28" s="3" t="s">
-        <x:v>744</x:v>
-      </x:c>
-      <x:c r="R28" s="3" t="s">
-        <x:v>745</x:v>
       </x:c>
       <x:c r="S28" s="3" t="s">
         <x:v>286</x:v>
       </x:c>
       <x:c r="T28" s="3" t="s">
-        <x:v>746</x:v>
+        <x:v>737</x:v>
       </x:c>
       <x:c r="U28" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="93.25" hidden="0">
       <x:c r="A29" s="3" t="s">
-        <x:v>747</x:v>
+        <x:v>738</x:v>
       </x:c>
       <x:c r="B29" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C29" s="3" t="s">
-        <x:v>748</x:v>
+        <x:v>739</x:v>
       </x:c>
       <x:c r="D29" s="3" t="s">
-        <x:v>749</x:v>
+        <x:v>740</x:v>
       </x:c>
       <x:c r="E29" s="3" t="s">
-        <x:v>750</x:v>
+        <x:v>741</x:v>
       </x:c>
       <x:c r="F29" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="G29" s="3" t="s">
-        <x:v>441</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="H29" s="3" t="s">
-        <x:v>442</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="I29" s="3" t="s">
-        <x:v>443</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="J29" s="3" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="K29" s="3" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="L29" s="3" t="s">
-        <x:v>751</x:v>
+        <x:v>742</x:v>
       </x:c>
       <x:c r="M29" s="3" t="s">
-        <x:v>752</x:v>
+        <x:v>743</x:v>
       </x:c>
       <x:c r="N29" s="3" t="s">
-        <x:v>753</x:v>
+        <x:v>744</x:v>
       </x:c>
       <x:c r="O29" s="3" t="s">
-        <x:v>754</x:v>
+        <x:v>745</x:v>
       </x:c>
       <x:c r="P29" s="3" t="s">
-        <x:v>755</x:v>
+        <x:v>746</x:v>
       </x:c>
       <x:c r="Q29" s="3" t="s">
-        <x:v>756</x:v>
+        <x:v>747</x:v>
       </x:c>
       <x:c r="R29" s="3" t="s">
-        <x:v>757</x:v>
+        <x:v>748</x:v>
       </x:c>
       <x:c r="S29" s="3" t="s">
-        <x:v>758</x:v>
+        <x:v>749</x:v>
       </x:c>
       <x:c r="T29" s="3" t="s">
-        <x:v>759</x:v>
+        <x:v>750</x:v>
       </x:c>
       <x:c r="U29" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="93.25" hidden="0">
       <x:c r="A30" s="3" t="s">
+        <x:v>751</x:v>
+      </x:c>
+      <x:c r="B30" s="3" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C30" s="3" t="s">
+        <x:v>752</x:v>
+      </x:c>
+      <x:c r="D30" s="3" t="s">
+        <x:v>753</x:v>
+      </x:c>
+      <x:c r="E30" s="3" t="s">
+        <x:v>754</x:v>
+      </x:c>
+      <x:c r="F30" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G30" s="3" t="s">
+        <x:v>432</x:v>
+      </x:c>
+      <x:c r="H30" s="3" t="s">
+        <x:v>433</x:v>
+      </x:c>
+      <x:c r="I30" s="3" t="s">
+        <x:v>434</x:v>
+      </x:c>
+      <x:c r="J30" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="K30" s="3" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="L30" s="3" t="s">
+        <x:v>755</x:v>
+      </x:c>
+      <x:c r="M30" s="3" t="s">
+        <x:v>756</x:v>
+      </x:c>
+      <x:c r="N30" s="3" t="s">
+        <x:v>757</x:v>
+      </x:c>
+      <x:c r="O30" s="3" t="s">
+        <x:v>758</x:v>
+      </x:c>
+      <x:c r="P30" s="3" t="s">
+        <x:v>759</x:v>
+      </x:c>
+      <x:c r="Q30" s="3" t="s">
         <x:v>760</x:v>
       </x:c>
-      <x:c r="B30" s="3" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C30" s="3" t="s">
+      <x:c r="R30" s="3" t="s">
         <x:v>761</x:v>
       </x:c>
-      <x:c r="D30" s="3" t="s">
+      <x:c r="S30" s="3" t="s">
         <x:v>762</x:v>
       </x:c>
-      <x:c r="E30" s="3" t="s">
+      <x:c r="T30" s="3" t="s">
         <x:v>763</x:v>
       </x:c>
-      <x:c r="F30" s="3" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="G30" s="3" t="s">
-        <x:v>441</x:v>
-      </x:c>
-      <x:c r="H30" s="3" t="s">
-        <x:v>442</x:v>
-      </x:c>
-      <x:c r="I30" s="3" t="s">
-        <x:v>443</x:v>
-      </x:c>
-      <x:c r="J30" s="3" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="K30" s="3" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="L30" s="3" t="s">
-        <x:v>764</x:v>
-      </x:c>
-      <x:c r="M30" s="3" t="s">
-        <x:v>765</x:v>
-      </x:c>
-      <x:c r="N30" s="3" t="s">
-        <x:v>766</x:v>
-      </x:c>
-      <x:c r="O30" s="3" t="s">
-        <x:v>767</x:v>
-      </x:c>
-      <x:c r="P30" s="3" t="s">
-        <x:v>768</x:v>
-      </x:c>
-      <x:c r="Q30" s="3" t="s">
-        <x:v>769</x:v>
-      </x:c>
-      <x:c r="R30" s="3" t="s">
-        <x:v>770</x:v>
-      </x:c>
-      <x:c r="S30" s="3" t="s">
-        <x:v>771</x:v>
-      </x:c>
-      <x:c r="T30" s="3" t="s">
-        <x:v>772</x:v>
-      </x:c>
       <x:c r="U30" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="93.25" hidden="0">
       <x:c r="A31" s="3" t="s">
-        <x:v>773</x:v>
+        <x:v>764</x:v>
       </x:c>
       <x:c r="B31" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C31" s="3" t="s">
-        <x:v>774</x:v>
+        <x:v>765</x:v>
       </x:c>
       <x:c r="D31" s="3" t="s">
-        <x:v>775</x:v>
+        <x:v>766</x:v>
       </x:c>
       <x:c r="E31" s="3" t="s">
-        <x:v>776</x:v>
+        <x:v>767</x:v>
       </x:c>
       <x:c r="F31" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="G31" s="3" t="s">
-        <x:v>441</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="H31" s="3" t="s">
-        <x:v>442</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="I31" s="3" t="s">
-        <x:v>443</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="J31" s="3" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="K31" s="3" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="L31" s="3" t="s">
-        <x:v>777</x:v>
+        <x:v>768</x:v>
       </x:c>
       <x:c r="M31" s="3" t="s">
-        <x:v>778</x:v>
+        <x:v>769</x:v>
       </x:c>
       <x:c r="N31" s="3" t="s">
-        <x:v>779</x:v>
+        <x:v>770</x:v>
       </x:c>
       <x:c r="O31" s="3" t="s">
-        <x:v>780</x:v>
+        <x:v>771</x:v>
       </x:c>
       <x:c r="P31" s="3" t="s">
-        <x:v>781</x:v>
+        <x:v>772</x:v>
       </x:c>
       <x:c r="Q31" s="3" t="s">
-        <x:v>782</x:v>
+        <x:v>773</x:v>
       </x:c>
       <x:c r="R31" s="3" t="s">
-        <x:v>783</x:v>
+        <x:v>774</x:v>
       </x:c>
       <x:c r="S31" s="3" t="s">
-        <x:v>784</x:v>
+        <x:v>775</x:v>
       </x:c>
       <x:c r="T31" s="3" t="s">
-        <x:v>785</x:v>
+        <x:v>776</x:v>
       </x:c>
       <x:c r="U31" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="93.25" hidden="0">
       <x:c r="A32" s="3" t="s">
-        <x:v>786</x:v>
+        <x:v>777</x:v>
       </x:c>
       <x:c r="B32" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C32" s="3" t="s">
-        <x:v>787</x:v>
+        <x:v>778</x:v>
       </x:c>
       <x:c r="D32" s="3" t="s">
-        <x:v>788</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="E32" s="3" t="s">
-        <x:v>789</x:v>
+        <x:v>780</x:v>
       </x:c>
       <x:c r="F32" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="G32" s="3" t="s">
-        <x:v>441</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="H32" s="3" t="s">
-        <x:v>442</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="I32" s="3" t="s">
-        <x:v>443</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="J32" s="3" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="K32" s="3" t="s">
         <x:v>188</x:v>
       </x:c>
       <x:c r="L32" s="3" t="s">
-        <x:v>790</x:v>
+        <x:v>781</x:v>
       </x:c>
       <x:c r="M32" s="3" t="s">
-        <x:v>791</x:v>
+        <x:v>782</x:v>
       </x:c>
       <x:c r="N32" s="3" t="s">
-        <x:v>792</x:v>
+        <x:v>783</x:v>
       </x:c>
       <x:c r="O32" s="3" t="s">
-        <x:v>793</x:v>
+        <x:v>784</x:v>
       </x:c>
       <x:c r="P32" s="3" t="s">
-        <x:v>794</x:v>
+        <x:v>785</x:v>
       </x:c>
       <x:c r="Q32" s="3" t="s">
-        <x:v>795</x:v>
+        <x:v>786</x:v>
       </x:c>
       <x:c r="R32" s="3" t="s">
-        <x:v>796</x:v>
+        <x:v>787</x:v>
       </x:c>
       <x:c r="S32" s="3" t="s">
-        <x:v>797</x:v>
+        <x:v>788</x:v>
       </x:c>
       <x:c r="T32" s="3" t="s">
-        <x:v>798</x:v>
+        <x:v>789</x:v>
       </x:c>
       <x:c r="U32" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="93.25" hidden="0">
       <x:c r="A33" s="3" t="s">
+        <x:v>790</x:v>
+      </x:c>
+      <x:c r="B33" s="3" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C33" s="3" t="s">
+        <x:v>791</x:v>
+      </x:c>
+      <x:c r="D33" s="3" t="s">
+        <x:v>792</x:v>
+      </x:c>
+      <x:c r="E33" s="3" t="s">
+        <x:v>793</x:v>
+      </x:c>
+      <x:c r="F33" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G33" s="3" t="s">
+        <x:v>432</x:v>
+      </x:c>
+      <x:c r="H33" s="3" t="s">
+        <x:v>433</x:v>
+      </x:c>
+      <x:c r="I33" s="3" t="s">
+        <x:v>434</x:v>
+      </x:c>
+      <x:c r="J33" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="K33" s="3" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="L33" s="3" t="s">
+        <x:v>794</x:v>
+      </x:c>
+      <x:c r="M33" s="3" t="s">
+        <x:v>795</x:v>
+      </x:c>
+      <x:c r="N33" s="3" t="s">
+        <x:v>796</x:v>
+      </x:c>
+      <x:c r="O33" s="3" t="s">
+        <x:v>797</x:v>
+      </x:c>
+      <x:c r="P33" s="3" t="s">
+        <x:v>798</x:v>
+      </x:c>
+      <x:c r="Q33" s="3" t="s">
         <x:v>799</x:v>
       </x:c>
-      <x:c r="B33" s="3" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C33" s="3" t="s">
+      <x:c r="R33" s="3" t="s">
         <x:v>800</x:v>
       </x:c>
-      <x:c r="D33" s="3" t="s">
+      <x:c r="S33" s="3" t="s">
         <x:v>801</x:v>
       </x:c>
-      <x:c r="E33" s="3" t="s">
+      <x:c r="T33" s="3" t="s">
         <x:v>802</x:v>
       </x:c>
-      <x:c r="F33" s="3" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="G33" s="3" t="s">
-        <x:v>441</x:v>
-      </x:c>
-      <x:c r="H33" s="3" t="s">
-        <x:v>442</x:v>
-      </x:c>
-      <x:c r="I33" s="3" t="s">
-        <x:v>443</x:v>
-      </x:c>
-      <x:c r="J33" s="3" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="K33" s="3" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="L33" s="3" t="s">
-        <x:v>803</x:v>
-      </x:c>
-      <x:c r="M33" s="3" t="s">
-        <x:v>804</x:v>
-      </x:c>
-      <x:c r="N33" s="3" t="s">
-        <x:v>805</x:v>
-      </x:c>
-      <x:c r="O33" s="3" t="s">
-        <x:v>806</x:v>
-      </x:c>
-      <x:c r="P33" s="3" t="s">
-        <x:v>807</x:v>
-      </x:c>
-      <x:c r="Q33" s="3" t="s">
-        <x:v>808</x:v>
-      </x:c>
-      <x:c r="R33" s="3" t="s">
-        <x:v>809</x:v>
-      </x:c>
-      <x:c r="S33" s="3" t="s">
-        <x:v>810</x:v>
-      </x:c>
-      <x:c r="T33" s="3" t="s">
-        <x:v>811</x:v>
-      </x:c>
       <x:c r="U33" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="93.25" hidden="0">
       <x:c r="A34" s="3" t="s">
-        <x:v>812</x:v>
+        <x:v>803</x:v>
       </x:c>
       <x:c r="B34" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C34" s="3" t="s">
         <x:v>313</x:v>
       </x:c>
       <x:c r="D34" s="3" t="s">
-        <x:v>813</x:v>
+        <x:v>804</x:v>
       </x:c>
       <x:c r="E34" s="3" t="s">
-        <x:v>814</x:v>
+        <x:v>805</x:v>
       </x:c>
       <x:c r="F34" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="G34" s="3" t="s">
-        <x:v>441</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="H34" s="3" t="s">
-        <x:v>442</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="I34" s="3" t="s">
-        <x:v>443</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="J34" s="3" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="K34" s="3" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="L34" s="3" t="s">
-        <x:v>815</x:v>
+        <x:v>806</x:v>
       </x:c>
       <x:c r="M34" s="3" t="s">
-        <x:v>816</x:v>
+        <x:v>807</x:v>
       </x:c>
       <x:c r="N34" s="3" t="s">
-        <x:v>817</x:v>
+        <x:v>808</x:v>
       </x:c>
       <x:c r="O34" s="3" t="s">
-        <x:v>818</x:v>
+        <x:v>809</x:v>
       </x:c>
       <x:c r="P34" s="3" t="s">
-        <x:v>819</x:v>
+        <x:v>810</x:v>
       </x:c>
       <x:c r="Q34" s="3" t="s">
-        <x:v>820</x:v>
+        <x:v>811</x:v>
       </x:c>
       <x:c r="R34" s="3" t="s">
-        <x:v>821</x:v>
+        <x:v>812</x:v>
       </x:c>
       <x:c r="S34" s="3" t="s">
         <x:v>323</x:v>
       </x:c>
       <x:c r="T34" s="3" t="s">
-        <x:v>822</x:v>
+        <x:v>813</x:v>
       </x:c>
       <x:c r="U34" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="93.25" hidden="0">
       <x:c r="A35" s="3" t="s">
+        <x:v>814</x:v>
+      </x:c>
+      <x:c r="B35" s="3" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C35" s="3" t="s">
+        <x:v>815</x:v>
+      </x:c>
+      <x:c r="D35" s="3" t="s">
+        <x:v>816</x:v>
+      </x:c>
+      <x:c r="E35" s="3" t="s">
+        <x:v>817</x:v>
+      </x:c>
+      <x:c r="F35" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G35" s="3" t="s">
+        <x:v>432</x:v>
+      </x:c>
+      <x:c r="H35" s="3" t="s">
+        <x:v>433</x:v>
+      </x:c>
+      <x:c r="I35" s="3" t="s">
+        <x:v>434</x:v>
+      </x:c>
+      <x:c r="J35" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="K35" s="3" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="L35" s="3" t="s">
+        <x:v>818</x:v>
+      </x:c>
+      <x:c r="M35" s="3" t="s">
+        <x:v>819</x:v>
+      </x:c>
+      <x:c r="N35" s="3" t="s">
+        <x:v>820</x:v>
+      </x:c>
+      <x:c r="O35" s="3" t="s">
+        <x:v>595</x:v>
+      </x:c>
+      <x:c r="P35" s="3" t="s">
+        <x:v>821</x:v>
+      </x:c>
+      <x:c r="Q35" s="3" t="s">
+        <x:v>822</x:v>
+      </x:c>
+      <x:c r="R35" s="3" t="s">
         <x:v>823</x:v>
       </x:c>
-      <x:c r="B35" s="3" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C35" s="3" t="s">
+      <x:c r="S35" s="3" t="s">
         <x:v>824</x:v>
       </x:c>
-      <x:c r="D35" s="3" t="s">
+      <x:c r="T35" s="3" t="s">
         <x:v>825</x:v>
       </x:c>
-      <x:c r="E35" s="3" t="s">
-        <x:v>826</x:v>
-      </x:c>
-      <x:c r="F35" s="3" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="G35" s="3" t="s">
-        <x:v>441</x:v>
-      </x:c>
-      <x:c r="H35" s="3" t="s">
-        <x:v>442</x:v>
-      </x:c>
-      <x:c r="I35" s="3" t="s">
-        <x:v>443</x:v>
-      </x:c>
-      <x:c r="J35" s="3" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="K35" s="3" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="L35" s="3" t="s">
-        <x:v>827</x:v>
-      </x:c>
-      <x:c r="M35" s="3" t="s">
-        <x:v>828</x:v>
-      </x:c>
-      <x:c r="N35" s="3" t="s">
-        <x:v>829</x:v>
-      </x:c>
-      <x:c r="O35" s="3" t="s">
-        <x:v>604</x:v>
-      </x:c>
-      <x:c r="P35" s="3" t="s">
-        <x:v>830</x:v>
-      </x:c>
-      <x:c r="Q35" s="3" t="s">
-        <x:v>831</x:v>
-      </x:c>
-      <x:c r="R35" s="3" t="s">
-        <x:v>832</x:v>
-      </x:c>
-      <x:c r="S35" s="3" t="s">
-        <x:v>833</x:v>
-      </x:c>
-      <x:c r="T35" s="3" t="s">
-        <x:v>834</x:v>
-      </x:c>
       <x:c r="U35" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="93.25" hidden="0">
       <x:c r="A36" s="3" t="s">
-        <x:v>835</x:v>
+        <x:v>826</x:v>
       </x:c>
       <x:c r="B36" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C36" s="3" t="s">
-        <x:v>836</x:v>
+        <x:v>827</x:v>
       </x:c>
       <x:c r="D36" s="3" t="s">
-        <x:v>837</x:v>
+        <x:v>828</x:v>
       </x:c>
       <x:c r="E36" s="3" t="s">
-        <x:v>838</x:v>
+        <x:v>829</x:v>
       </x:c>
       <x:c r="F36" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="G36" s="3" t="s">
-        <x:v>441</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="H36" s="3" t="s">
-        <x:v>442</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="I36" s="3" t="s">
-        <x:v>443</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="J36" s="3" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="K36" s="3" t="s">
         <x:v>188</x:v>
       </x:c>
       <x:c r="L36" s="3" t="s">
-        <x:v>839</x:v>
+        <x:v>830</x:v>
       </x:c>
       <x:c r="M36" s="3" t="s">
-        <x:v>445</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="N36" s="3" t="s">
-        <x:v>840</x:v>
+        <x:v>831</x:v>
       </x:c>
       <x:c r="O36" s="3" t="s">
-        <x:v>841</x:v>
+        <x:v>832</x:v>
       </x:c>
       <x:c r="P36" s="3" t="s">
-        <x:v>842</x:v>
+        <x:v>833</x:v>
       </x:c>
       <x:c r="Q36" s="3" t="s">
-        <x:v>843</x:v>
+        <x:v>834</x:v>
       </x:c>
       <x:c r="R36" s="3" t="s">
-        <x:v>844</x:v>
+        <x:v>835</x:v>
       </x:c>
       <x:c r="S36" s="3" t="s">
-        <x:v>845</x:v>
+        <x:v>836</x:v>
       </x:c>
       <x:c r="T36" s="3" t="s">
-        <x:v>846</x:v>
+        <x:v>837</x:v>
       </x:c>
       <x:c r="U36" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="93.25" hidden="0">
       <x:c r="A37" s="3" t="s">
+        <x:v>838</x:v>
+      </x:c>
+      <x:c r="B37" s="3" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C37" s="3" t="s">
+        <x:v>839</x:v>
+      </x:c>
+      <x:c r="D37" s="3" t="s">
+        <x:v>840</x:v>
+      </x:c>
+      <x:c r="E37" s="3" t="s">
+        <x:v>841</x:v>
+      </x:c>
+      <x:c r="F37" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G37" s="3" t="s">
+        <x:v>432</x:v>
+      </x:c>
+      <x:c r="H37" s="3" t="s">
+        <x:v>433</x:v>
+      </x:c>
+      <x:c r="I37" s="3" t="s">
+        <x:v>434</x:v>
+      </x:c>
+      <x:c r="J37" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="K37" s="3" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="L37" s="3" t="s">
+        <x:v>842</x:v>
+      </x:c>
+      <x:c r="M37" s="3" t="s">
+        <x:v>843</x:v>
+      </x:c>
+      <x:c r="N37" s="3" t="s">
+        <x:v>844</x:v>
+      </x:c>
+      <x:c r="O37" s="3" t="s">
+        <x:v>845</x:v>
+      </x:c>
+      <x:c r="P37" s="3" t="s">
+        <x:v>846</x:v>
+      </x:c>
+      <x:c r="Q37" s="3" t="s">
         <x:v>847</x:v>
       </x:c>
-      <x:c r="B37" s="3" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C37" s="3" t="s">
+      <x:c r="R37" s="3" t="s">
         <x:v>848</x:v>
       </x:c>
-      <x:c r="D37" s="3" t="s">
+      <x:c r="S37" s="3" t="s">
         <x:v>849</x:v>
       </x:c>
-      <x:c r="E37" s="3" t="s">
-        <x:v>850</x:v>
-      </x:c>
-      <x:c r="F37" s="3" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="G37" s="3" t="s">
-        <x:v>441</x:v>
-      </x:c>
-      <x:c r="H37" s="3" t="s">
-        <x:v>442</x:v>
-      </x:c>
-      <x:c r="I37" s="3" t="s">
-        <x:v>443</x:v>
-      </x:c>
-      <x:c r="J37" s="3" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="K37" s="3" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="L37" s="3" t="s">
-        <x:v>851</x:v>
-      </x:c>
-      <x:c r="M37" s="3" t="s">
-        <x:v>852</x:v>
-      </x:c>
-      <x:c r="N37" s="3" t="s">
-        <x:v>853</x:v>
-      </x:c>
-      <x:c r="O37" s="3" t="s">
-        <x:v>854</x:v>
-      </x:c>
-      <x:c r="P37" s="3" t="s">
-        <x:v>855</x:v>
-      </x:c>
-      <x:c r="Q37" s="3" t="s">
-        <x:v>856</x:v>
-      </x:c>
-      <x:c r="R37" s="3" t="s">
-        <x:v>857</x:v>
-      </x:c>
-      <x:c r="S37" s="3" t="s">
-        <x:v>858</x:v>
-      </x:c>
       <x:c r="T37" s="3" t="s">
-        <x:v>852</x:v>
+        <x:v>843</x:v>
       </x:c>
       <x:c r="U37" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="93.25" hidden="0">
       <x:c r="A38" s="3" t="s">
+        <x:v>850</x:v>
+      </x:c>
+      <x:c r="B38" s="3" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C38" s="3" t="s">
+        <x:v>851</x:v>
+      </x:c>
+      <x:c r="D38" s="3" t="s">
+        <x:v>852</x:v>
+      </x:c>
+      <x:c r="E38" s="3" t="s">
+        <x:v>853</x:v>
+      </x:c>
+      <x:c r="F38" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G38" s="3" t="s">
+        <x:v>432</x:v>
+      </x:c>
+      <x:c r="H38" s="3" t="s">
+        <x:v>433</x:v>
+      </x:c>
+      <x:c r="I38" s="3" t="s">
+        <x:v>434</x:v>
+      </x:c>
+      <x:c r="J38" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="K38" s="3" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="L38" s="3" t="s">
+        <x:v>854</x:v>
+      </x:c>
+      <x:c r="M38" s="3" t="s">
+        <x:v>520</x:v>
+      </x:c>
+      <x:c r="N38" s="3" t="s">
+        <x:v>855</x:v>
+      </x:c>
+      <x:c r="O38" s="3" t="s">
+        <x:v>856</x:v>
+      </x:c>
+      <x:c r="P38" s="3" t="s">
+        <x:v>857</x:v>
+      </x:c>
+      <x:c r="Q38" s="3" t="s">
+        <x:v>858</x:v>
+      </x:c>
+      <x:c r="R38" s="3" t="s">
         <x:v>859</x:v>
       </x:c>
-      <x:c r="B38" s="3" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C38" s="3" t="s">
+      <x:c r="S38" s="3" t="s">
         <x:v>860</x:v>
       </x:c>
-      <x:c r="D38" s="3" t="s">
+      <x:c r="T38" s="3" t="s">
         <x:v>861</x:v>
       </x:c>
-      <x:c r="E38" s="3" t="s">
-        <x:v>862</x:v>
-      </x:c>
-      <x:c r="F38" s="3" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="G38" s="3" t="s">
-        <x:v>441</x:v>
-      </x:c>
-      <x:c r="H38" s="3" t="s">
-        <x:v>442</x:v>
-      </x:c>
-      <x:c r="I38" s="3" t="s">
-        <x:v>443</x:v>
-      </x:c>
-      <x:c r="J38" s="3" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="K38" s="3" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="L38" s="3" t="s">
-        <x:v>863</x:v>
-      </x:c>
-      <x:c r="M38" s="3" t="s">
-        <x:v>529</x:v>
-      </x:c>
-      <x:c r="N38" s="3" t="s">
-        <x:v>864</x:v>
-      </x:c>
-      <x:c r="O38" s="3" t="s">
-        <x:v>865</x:v>
-      </x:c>
-      <x:c r="P38" s="3" t="s">
-        <x:v>866</x:v>
-      </x:c>
-      <x:c r="Q38" s="3" t="s">
-        <x:v>867</x:v>
-      </x:c>
-      <x:c r="R38" s="3" t="s">
-        <x:v>868</x:v>
-      </x:c>
-      <x:c r="S38" s="3" t="s">
-        <x:v>869</x:v>
-      </x:c>
-      <x:c r="T38" s="3" t="s">
-        <x:v>870</x:v>
-      </x:c>
       <x:c r="U38" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="93.25" hidden="0">
       <x:c r="A39" s="3" t="s">
-        <x:v>871</x:v>
+        <x:v>862</x:v>
       </x:c>
       <x:c r="B39" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C39" s="3" t="s">
-        <x:v>872</x:v>
+        <x:v>863</x:v>
       </x:c>
       <x:c r="D39" s="3" t="s">
-        <x:v>873</x:v>
+        <x:v>864</x:v>
       </x:c>
       <x:c r="E39" s="3" t="s">
-        <x:v>874</x:v>
+        <x:v>865</x:v>
       </x:c>
       <x:c r="F39" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="G39" s="3" t="s">
-        <x:v>441</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="H39" s="3" t="s">
-        <x:v>442</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="I39" s="3" t="s">
-        <x:v>443</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="J39" s="3" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="K39" s="3" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="L39" s="3" t="s">
-        <x:v>875</x:v>
+        <x:v>866</x:v>
       </x:c>
       <x:c r="M39" s="3" t="s">
-        <x:v>445</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="N39" s="3" t="s">
-        <x:v>876</x:v>
+        <x:v>867</x:v>
       </x:c>
       <x:c r="O39" s="3" t="s">
-        <x:v>877</x:v>
+        <x:v>868</x:v>
       </x:c>
       <x:c r="P39" s="3" t="s">
-        <x:v>878</x:v>
+        <x:v>869</x:v>
       </x:c>
       <x:c r="Q39" s="3" t="s">
-        <x:v>879</x:v>
+        <x:v>870</x:v>
       </x:c>
       <x:c r="R39" s="3" t="s">
-        <x:v>880</x:v>
+        <x:v>871</x:v>
       </x:c>
       <x:c r="S39" s="3" t="s">
-        <x:v>881</x:v>
+        <x:v>872</x:v>
       </x:c>
       <x:c r="T39" s="3" t="s">
-        <x:v>882</x:v>
+        <x:v>873</x:v>
       </x:c>
       <x:c r="U39" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R72140e8901c4457f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2870892c27754be7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/maliev-feature-user-story-status.xlsx
+++ b/docs/maliev-feature-user-story-status.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R4da6e20d08b44576"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="Rc1f5f9c822ca444b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R6e177dedf6854f86"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="Ra787fd76a00f44d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R0eae3cacc47a42cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="R4b20fe3ecced4f3b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="Rf32457857af84706"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="Rbb03d25b7eb745dc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5204,7 +5204,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb6a1be584a24105"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4ceaa025d74948c6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8303,58 +8303,58 @@
         <x:v>Payment operations</x:v>
       </x:c>
       <x:c r="D48" s="3" t="str">
-        <x:v>As a finance employee, I can review payment stats, inspect payment records through the BFF, and record invoice payments from the invoice detail flow.</x:v>
+        <x:v>As finance staff, I can review payment metrics and payment records, and record invoice payments through the current invoice payment workflow.</x:v>
       </x:c>
       <x:c r="E48" s="3" t="str">
-        <x:v>Payment stats load in the invoice list, payment list/detail/create endpoints fail closed when PaymentService does not return data, invoice detail records and allocates payments through InvoiceService, and unsupported direct allocate/void actions return 404.</x:v>
+        <x:v>Payment stats and payment records proxy to PaymentService; invoice payments are recorded through InvoiceService and linked back to the invoice; PaymentService allocate/void actions fail closed because they are not exposed by the downstream service.</x:v>
       </x:c>
       <x:c r="F48" s="3" t="str">
         <x:v>Current code-derived; focused fallback fix applied.</x:v>
       </x:c>
       <x:c r="G48" s="3" t="str">
-        <x:v>Focused behavior tests passed 2026-06-23.</x:v>
+        <x:v>Focused payment and invoice-payment behavior tests passed 2026-06-24.</x:v>
       </x:c>
       <x:c r="H48" s="3" t="str">
-        <x:v>Focused contract review found PaymentServiceClient.GetPaymentsAsync threw on non-success responses instead of allowing the BFF empty-page fallback when PaymentService does not expose a list response.</x:v>
+        <x:v>No current behavior error observed in focused payment retest.</x:v>
       </x:c>
       <x:c r="I48" s="3" t="str">
-        <x:v>Fixed in Maliev.Intranet commit 776400b by changing GetPaymentsAsync to use GetAsync, return null on non-success, and deserialize only successful responses.</x:v>
+        <x:v>No app fix needed; tracker aligned to current PaymentService read/create behavior and InvoiceService-backed invoice payment recording.</x:v>
       </x:c>
       <x:c r="J48" s="3" t="str">
-        <x:v>Retested PaymentsControllerTests 14/14 passed and InvoiceServiceClientTests.RecordInvoicePayment 1/1 passed.</x:v>
+        <x:v>Retested PaymentsControllerTests plus InvoiceServiceClientTests.RecordInvoicePaymentAsync_PostsPaymentAndLinksAllocationToInvoice: 15/15 passed.</x:v>
       </x:c>
       <x:c r="K48" s="3" t="str">
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L48" s="3" t="str">
-        <x:v>Finance invoice UI -&gt; Intranet BFF payments/invoices endpoints -&gt; PaymentService metrics/payment endpoints and InvoiceService payment allocation</x:v>
+        <x:v>Intranet BFF payment controller -&gt; PaymentService read/create APIs; invoice detail UI -&gt; InvoicesController payment action -&gt; InvoiceService payment create/link APIs</x:v>
       </x:c>
       <x:c r="M48" s="3" t="str">
-        <x:v>InvoiceList.razor; InvoiceDetail.razor; PaymentsController.cs</x:v>
+        <x:v>InvoiceDetail.razor payment form; InvoiceList.razor payment stats; PaymentsController.cs; InvoicesController.cs</x:v>
       </x:c>
       <x:c r="N48" s="3" t="str">
-        <x:v>/finance/invoices loads api/v1/payments/stats; /finance/invoices/{id} record-payment panel posts api/v1/invoices/{id}/payments</x:v>
+        <x:v>Invoice detail Record Payment form posts api/v1/invoices/{id}/payments; invoice list loads api/v1/payments/stats.</x:v>
       </x:c>
       <x:c r="O48" s="3" t="str">
-        <x:v>PaymentsController stats/list/detail/create proxy PaymentService; list now falls back on non-success; allocate/void return 404 because PaymentService does not expose those actions; invoice payment recording uses InvoiceService /invoice/v1/payments plus /invoice/v1/payments/invoices/{invoiceId}/link.</x:v>
+        <x:v>PaymentServiceClient GET /payment/v1/metrics/stats, GET/POST /payment/v1/payments; InvoiceServiceClient POST /invoice/v1/payments then POST /invoice/v1/payments/invoices/{invoiceId}/link; allocate/void intentionally return 404 when downstream PaymentService does not expose those actions.</x:v>
       </x:c>
       <x:c r="P48" s="3" t="str">
-        <x:v>Focused tests: dotnet test Maliev.Intranet.slnx --filter "FullyQualifiedName~PaymentsControllerTests" --verbosity minimal passed 14/14 on 2026-06-23. Impacted invoice payment allocation test: dotnet test Maliev.Intranet.slnx --filter "FullyQualifiedName~InvoiceServiceClientTests.RecordInvoicePayment" --verbosity minimal passed 1/1 on 2026-06-23.</x:v>
+        <x:v>dotnet test Maliev.Intranet.slnx --filter "FullyQualifiedName~PaymentsControllerTests|FullyQualifiedName~InvoiceServiceClientTests.RecordInvoicePaymentAsync_PostsPaymentAndLinksAllocationToInvoice" --verbosity minimal passed 15/15 on 2026-06-24.</x:v>
       </x:c>
       <x:c r="Q48" s="3" t="str">
-        <x:v>Intranet BFF, PaymentService, InvoiceService, Accounting/Invoice UI</x:v>
+        <x:v>Intranet BFF, PaymentService, InvoiceService</x:v>
       </x:c>
       <x:c r="R48" s="3" t="str">
-        <x:v>Payment records and invoice payment allocations through InvoiceService; direct PaymentService list/detail reads are read-only.</x:v>
+        <x:v>Payment records and invoice payment allocations</x:v>
       </x:c>
       <x:c r="S48" s="3" t="str">
-        <x:v>Direct PaymentService allocate/void actions are not exposed by current PaymentService and therefore fail closed with 404; current finance UI records invoice payments through InvoiceService instead of a standalone payments page.</x:v>
+        <x:v>No remaining gap from current code-derived tracker.</x:v>
       </x:c>
       <x:c r="T48" s="3" t="str">
-        <x:v>PaymentsController.cs:17-85; PaymentServiceClient.cs:16-80; PaymentsControllerTests.cs:14-216; InvoiceList.razor:587-589; InvoiceDetail.razor:82,209-218; InvoiceServiceClient.cs:140-204</x:v>
+        <x:v>PaymentsController.cs:17-85; PaymentServiceClient.cs:11-80; InvoicesController.cs:168-186; InvoiceServiceClient.cs:140-204; InvoiceList.razor:587-589; InvoiceDetail.razor:66-82,209-238; PaymentsControllerTests.cs:14-217; InvoiceServiceClientTests.cs:316-393</x:v>
       </x:c>
       <x:c r="U48" s="3" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-24</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="51.29999923706055" hidden="0">
@@ -8620,7 +8620,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra6dc305d869c4e5c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6c6f739a8d934916"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11191,7 +11191,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2870892c27754be7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4ae975070f7d497f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/maliev-feature-user-story-status.xlsx
+++ b/docs/maliev-feature-user-story-status.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R0eae3cacc47a42cf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="R4b20fe3ecced4f3b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="Rf32457857af84706"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="Rbb03d25b7eb745dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Ra26f12b8e7fa4d27"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="R525fec7d9367427c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R2b99b88183644f38"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="Rbed96323f16e44bd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1306,7 +1306,22 @@
     <x:t xml:space="preserve">As a customer, I can send manufacturing/quote questions to the agent.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Composer sends messages with session context and receives agent turns through the BFF.</x:t>
+    <x:t xml:space="preserve">QuoteEngine BFF, Agent model, SessionStore</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Chat messages/session state</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">QE-004</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Agent streaming</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">As a customer, I can receive streamed agent responses.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Streaming endpoint returns structured response chunks and the UI keeps thread/composer layout stable.</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Automated QuoteEngine suite passed 2026-06-23 after workspace cleanup</x:t>
@@ -1318,46 +1333,10 @@
     <x:t xml:space="preserve">No fix needed for this story from current QuoteEngine automated retest.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Composer -&gt; AgentController messages -&gt; QuoteAgentService -&gt; session store</x:t>
+    <x:t xml:space="preserve">Composer -&gt; messages/stream -&gt; streaming agent response</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">QuoteAgentLaunchShell.razor</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Chat composer and message thread</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">AgentController POST messages; QuoteAgentService SendMessageAsync</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QuoteAgentEndpointTests messages | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QuoteEngine BFF, Agent model, SessionStore</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Chat messages/session state</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Needs browser send-path retest</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">AgentController.cs:56; QuoteAgentService.cs</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QE-004</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Agent streaming</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">As a customer, I can receive streamed agent responses.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Streaming endpoint returns structured response chunks and the UI keeps thread/composer layout stable.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Composer -&gt; messages/stream -&gt; streaming agent response</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Streaming response thread</x:t>
@@ -5204,7 +5183,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4ceaa025d74948c6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd659e5451b6047aa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8620,7 +8599,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6c6f739a8d934916"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R26783c875c8e4b25"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8861,85 +8840,85 @@
       <x:c r="D4" s="3" t="s">
         <x:v>430</x:v>
       </x:c>
-      <x:c r="E4" s="3" t="s">
-        <x:v>431</x:v>
+      <x:c r="E4" s="3" t="str">
+        <x:v>Composer send accepts a text or attachment-backed customer turn, blocks duplicate/pending-upload sends, streams the assistant response, and the BFF send endpoint creates or resumes a QuoteEngine agent session with gate state.</x:v>
       </x:c>
       <x:c r="F4" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="G4" s="3" t="s">
-        <x:v>432</x:v>
-      </x:c>
-      <x:c r="H4" s="3" t="s">
-        <x:v>433</x:v>
-      </x:c>
-      <x:c r="I4" s="3" t="s">
-        <x:v>434</x:v>
-      </x:c>
-      <x:c r="J4" s="3" t="s">
-        <x:v>41</x:v>
+      <x:c r="G4" s="3" t="str">
+        <x:v>Focused current-state send-path tests passed 2026-06-24.</x:v>
+      </x:c>
+      <x:c r="H4" s="3" t="str">
+        <x:v>No behavior error observed in focused endpoint/source retest. Live browser send-path retest remains outstanding.</x:v>
+      </x:c>
+      <x:c r="I4" s="3" t="str">
+        <x:v>No app fix applied for this story in this slice; existing dirty QuoteAgentLaunchShell helper-formatting changes were left untouched.</x:v>
+      </x:c>
+      <x:c r="J4" s="3" t="str">
+        <x:v>Retested QuoteAgentEndpointTests.Agent_message_starts_anonymous_quote_engine_session_with_gate_state, QuoteAgentRateLimitTests, QuoteEngineSourceTests.QuoteAgentLaunchShell_has_monochrome_chatgpt_like_contract, and QuoteEngineSourceTests.QuoteAgentLaunchShell_previews_attachments_until_customer_sends_message: 6/6 passed.</x:v>
       </x:c>
       <x:c r="K4" s="3" t="s">
         <x:v>188</x:v>
       </x:c>
-      <x:c r="L4" s="3" t="s">
-        <x:v>435</x:v>
-      </x:c>
-      <x:c r="M4" s="3" t="s">
-        <x:v>436</x:v>
-      </x:c>
-      <x:c r="N4" s="3" t="s">
-        <x:v>437</x:v>
-      </x:c>
-      <x:c r="O4" s="3" t="s">
-        <x:v>438</x:v>
-      </x:c>
-      <x:c r="P4" s="3" t="s">
-        <x:v>439</x:v>
+      <x:c r="L4" s="3" t="str">
+        <x:v>QuoteAgentLaunchShell composer -&gt; QuoteEngineApiClient stream/send APIs -&gt; AgentController send/stream endpoints -&gt; QuoteAgentService -&gt; ChatbotService session/message contract</x:v>
+      </x:c>
+      <x:c r="M4" s="3" t="str">
+        <x:v>QuoteAgentLaunchShell.razor composer form and send button; QuoteEngineApiClient; AgentController.Send/Stream</x:v>
+      </x:c>
+      <x:c r="N4" s="3" t="str">
+        <x:v>Composer form submits HandleSubmitAsync; send button disabled only while sending, dictating, or pending uploads; API client posts quote/v1/agent/messages and quote/v1/agent/messages/stream.</x:v>
+      </x:c>
+      <x:c r="O4" s="3" t="str">
+        <x:v>AgentController POST quote/v1/agent/messages validates model state, applies QuoteAgent rate limiting, and calls QuoteAgentService.SendAsync; QuoteAgentService creates/resumes session, composes customer context, and sends ChatbotSendMessageRequest with QuoteAgentContextToken.</x:v>
+      </x:c>
+      <x:c r="P4" s="3" t="str">
+        <x:v>dotnet test Maliev.QuoteEngine.slnx --filter "FullyQualifiedName~QuoteAgentEndpointTests.Agent_message_starts_anonymous_quote_engine_session_with_gate_state|FullyQualifiedName~QuoteAgentRateLimitTests|FullyQualifiedName~QuoteEngineSourceTests.QuoteAgentLaunchShell_has_monochrome_chatgpt_like_contract|FullyQualifiedName~QuoteEngineSourceTests.QuoteAgentLaunchShell_previews_attachments_until_customer_sends_message" --verbosity minimal passed 6/6 on 2026-06-24.</x:v>
       </x:c>
       <x:c r="Q4" s="3" t="s">
-        <x:v>440</x:v>
+        <x:v>431</x:v>
       </x:c>
       <x:c r="R4" s="3" t="s">
-        <x:v>441</x:v>
-      </x:c>
-      <x:c r="S4" s="3" t="s">
-        <x:v>442</x:v>
-      </x:c>
-      <x:c r="T4" s="3" t="s">
-        <x:v>443</x:v>
-      </x:c>
-      <x:c r="U4" s="3" t="s">
-        <x:v>52</x:v>
+        <x:v>432</x:v>
+      </x:c>
+      <x:c r="S4" s="3" t="str">
+        <x:v>Needs live browser send-path retest against a running QuoteEngine host.</x:v>
+      </x:c>
+      <x:c r="T4" s="3" t="str">
+        <x:v>QuoteAgentLaunchShell.razor:1114,1266-1280,2170,2769-2924; QuoteEngineApiClient.cs:297-378; AgentController.cs:54-89; QuoteAgentService.cs:159-236; QuoteAgentEndpointTests.cs:80-117; QuoteAgentRateLimitTests.cs:23-90; QuoteEngineSourceTests.cs:864-1310,1933-1956</x:v>
+      </x:c>
+      <x:c r="U4" s="3" t="str">
+        <x:v>2026-06-24</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="107.25" hidden="0">
       <x:c r="A5" s="3" t="s">
-        <x:v>444</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C5" s="3" t="s">
-        <x:v>445</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="D5" s="3" t="s">
-        <x:v>446</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="E5" s="3" t="s">
-        <x:v>447</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="F5" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G5" s="3" t="s">
-        <x:v>432</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="H5" s="3" t="s">
-        <x:v>433</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="I5" s="3" t="s">
-        <x:v>434</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="J5" s="3" t="s">
         <x:v>41</x:v>
@@ -8948,31 +8927,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L5" s="3" t="s">
+        <x:v>440</x:v>
+      </x:c>
+      <x:c r="M5" s="3" t="s">
+        <x:v>441</x:v>
+      </x:c>
+      <x:c r="N5" s="3" t="s">
+        <x:v>442</x:v>
+      </x:c>
+      <x:c r="O5" s="3" t="s">
+        <x:v>443</x:v>
+      </x:c>
+      <x:c r="P5" s="3" t="s">
+        <x:v>444</x:v>
+      </x:c>
+      <x:c r="Q5" s="3" t="s">
+        <x:v>445</x:v>
+      </x:c>
+      <x:c r="R5" s="3" t="s">
+        <x:v>446</x:v>
+      </x:c>
+      <x:c r="S5" s="3" t="s">
+        <x:v>447</x:v>
+      </x:c>
+      <x:c r="T5" s="3" t="s">
         <x:v>448</x:v>
-      </x:c>
-      <x:c r="M5" s="3" t="s">
-        <x:v>436</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s">
-        <x:v>449</x:v>
-      </x:c>
-      <x:c r="O5" s="3" t="s">
-        <x:v>450</x:v>
-      </x:c>
-      <x:c r="P5" s="3" t="s">
-        <x:v>451</x:v>
-      </x:c>
-      <x:c r="Q5" s="3" t="s">
-        <x:v>452</x:v>
-      </x:c>
-      <x:c r="R5" s="3" t="s">
-        <x:v>453</x:v>
-      </x:c>
-      <x:c r="S5" s="3" t="s">
-        <x:v>454</x:v>
-      </x:c>
-      <x:c r="T5" s="3" t="s">
-        <x:v>455</x:v>
       </x:c>
       <x:c r="U5" s="3" t="s">
         <x:v>52</x:v>
@@ -8980,31 +8959,31 @@
     </x:row>
     <x:row r="6" ht="93.25" hidden="0">
       <x:c r="A6" s="3" t="s">
-        <x:v>456</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="B6" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C6" s="3" t="s">
-        <x:v>457</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="D6" s="3" t="s">
-        <x:v>458</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="E6" s="3" t="s">
-        <x:v>459</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="F6" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G6" s="3" t="s">
-        <x:v>432</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="H6" s="3" t="s">
-        <x:v>433</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="I6" s="3" t="s">
-        <x:v>434</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="J6" s="3" t="s">
         <x:v>41</x:v>
@@ -9013,31 +8992,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L6" s="3" t="s">
+        <x:v>453</x:v>
+      </x:c>
+      <x:c r="M6" s="3" t="s">
+        <x:v>441</x:v>
+      </x:c>
+      <x:c r="N6" s="3" t="s">
+        <x:v>454</x:v>
+      </x:c>
+      <x:c r="O6" s="3" t="s">
+        <x:v>455</x:v>
+      </x:c>
+      <x:c r="P6" s="3" t="s">
+        <x:v>456</x:v>
+      </x:c>
+      <x:c r="Q6" s="3" t="s">
+        <x:v>457</x:v>
+      </x:c>
+      <x:c r="R6" s="3" t="s">
+        <x:v>458</x:v>
+      </x:c>
+      <x:c r="S6" s="3" t="s">
+        <x:v>459</x:v>
+      </x:c>
+      <x:c r="T6" s="3" t="s">
         <x:v>460</x:v>
-      </x:c>
-      <x:c r="M6" s="3" t="s">
-        <x:v>436</x:v>
-      </x:c>
-      <x:c r="N6" s="3" t="s">
-        <x:v>461</x:v>
-      </x:c>
-      <x:c r="O6" s="3" t="s">
-        <x:v>462</x:v>
-      </x:c>
-      <x:c r="P6" s="3" t="s">
-        <x:v>463</x:v>
-      </x:c>
-      <x:c r="Q6" s="3" t="s">
-        <x:v>464</x:v>
-      </x:c>
-      <x:c r="R6" s="3" t="s">
-        <x:v>465</x:v>
-      </x:c>
-      <x:c r="S6" s="3" t="s">
-        <x:v>466</x:v>
-      </x:c>
-      <x:c r="T6" s="3" t="s">
-        <x:v>467</x:v>
       </x:c>
       <x:c r="U6" s="3" t="s">
         <x:v>52</x:v>
@@ -9045,31 +9024,31 @@
     </x:row>
     <x:row r="7" ht="93.25" hidden="0">
       <x:c r="A7" s="3" t="s">
-        <x:v>468</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>469</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="D7" s="3" t="s">
-        <x:v>470</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="E7" s="3" t="s">
-        <x:v>471</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="F7" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G7" s="3" t="s">
-        <x:v>432</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="H7" s="3" t="s">
-        <x:v>433</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="I7" s="3" t="s">
-        <x:v>434</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="J7" s="3" t="s">
         <x:v>41</x:v>
@@ -9078,31 +9057,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="L7" s="3" t="s">
+        <x:v>465</x:v>
+      </x:c>
+      <x:c r="M7" s="3" t="s">
+        <x:v>441</x:v>
+      </x:c>
+      <x:c r="N7" s="3" t="s">
+        <x:v>466</x:v>
+      </x:c>
+      <x:c r="O7" s="3" t="s">
+        <x:v>467</x:v>
+      </x:c>
+      <x:c r="P7" s="3" t="s">
+        <x:v>468</x:v>
+      </x:c>
+      <x:c r="Q7" s="3" t="s">
+        <x:v>469</x:v>
+      </x:c>
+      <x:c r="R7" s="3" t="s">
+        <x:v>470</x:v>
+      </x:c>
+      <x:c r="S7" s="3" t="s">
+        <x:v>471</x:v>
+      </x:c>
+      <x:c r="T7" s="3" t="s">
         <x:v>472</x:v>
-      </x:c>
-      <x:c r="M7" s="3" t="s">
-        <x:v>436</x:v>
-      </x:c>
-      <x:c r="N7" s="3" t="s">
-        <x:v>473</x:v>
-      </x:c>
-      <x:c r="O7" s="3" t="s">
-        <x:v>474</x:v>
-      </x:c>
-      <x:c r="P7" s="3" t="s">
-        <x:v>475</x:v>
-      </x:c>
-      <x:c r="Q7" s="3" t="s">
-        <x:v>476</x:v>
-      </x:c>
-      <x:c r="R7" s="3" t="s">
-        <x:v>477</x:v>
-      </x:c>
-      <x:c r="S7" s="3" t="s">
-        <x:v>478</x:v>
-      </x:c>
-      <x:c r="T7" s="3" t="s">
-        <x:v>479</x:v>
       </x:c>
       <x:c r="U7" s="3" t="s">
         <x:v>52</x:v>
@@ -9110,31 +9089,31 @@
     </x:row>
     <x:row r="8" ht="93.25" hidden="0">
       <x:c r="A8" s="3" t="s">
-        <x:v>480</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>481</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="D8" s="3" t="s">
-        <x:v>482</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="E8" s="3" t="s">
-        <x:v>483</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="F8" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G8" s="3" t="s">
-        <x:v>432</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="H8" s="3" t="s">
-        <x:v>433</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="I8" s="3" t="s">
-        <x:v>434</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="J8" s="3" t="s">
         <x:v>41</x:v>
@@ -9143,31 +9122,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L8" s="3" t="s">
+        <x:v>477</x:v>
+      </x:c>
+      <x:c r="M8" s="3" t="s">
+        <x:v>441</x:v>
+      </x:c>
+      <x:c r="N8" s="3" t="s">
+        <x:v>478</x:v>
+      </x:c>
+      <x:c r="O8" s="3" t="s">
+        <x:v>479</x:v>
+      </x:c>
+      <x:c r="P8" s="3" t="s">
+        <x:v>480</x:v>
+      </x:c>
+      <x:c r="Q8" s="3" t="s">
+        <x:v>481</x:v>
+      </x:c>
+      <x:c r="R8" s="3" t="s">
+        <x:v>482</x:v>
+      </x:c>
+      <x:c r="S8" s="3" t="s">
+        <x:v>483</x:v>
+      </x:c>
+      <x:c r="T8" s="3" t="s">
         <x:v>484</x:v>
-      </x:c>
-      <x:c r="M8" s="3" t="s">
-        <x:v>436</x:v>
-      </x:c>
-      <x:c r="N8" s="3" t="s">
-        <x:v>485</x:v>
-      </x:c>
-      <x:c r="O8" s="3" t="s">
-        <x:v>486</x:v>
-      </x:c>
-      <x:c r="P8" s="3" t="s">
-        <x:v>487</x:v>
-      </x:c>
-      <x:c r="Q8" s="3" t="s">
-        <x:v>488</x:v>
-      </x:c>
-      <x:c r="R8" s="3" t="s">
-        <x:v>489</x:v>
-      </x:c>
-      <x:c r="S8" s="3" t="s">
-        <x:v>490</x:v>
-      </x:c>
-      <x:c r="T8" s="3" t="s">
-        <x:v>491</x:v>
       </x:c>
       <x:c r="U8" s="3" t="s">
         <x:v>52</x:v>
@@ -9175,31 +9154,31 @@
     </x:row>
     <x:row r="9" ht="93.25" hidden="0">
       <x:c r="A9" s="3" t="s">
-        <x:v>492</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="B9" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C9" s="3" t="s">
-        <x:v>493</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="D9" s="3" t="s">
-        <x:v>494</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="E9" s="3" t="s">
-        <x:v>495</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="F9" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G9" s="3" t="s">
-        <x:v>432</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="H9" s="3" t="s">
-        <x:v>433</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="I9" s="3" t="s">
-        <x:v>434</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="J9" s="3" t="s">
         <x:v>41</x:v>
@@ -9208,31 +9187,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L9" s="3" t="s">
+        <x:v>489</x:v>
+      </x:c>
+      <x:c r="M9" s="3" t="s">
+        <x:v>441</x:v>
+      </x:c>
+      <x:c r="N9" s="3" t="s">
+        <x:v>490</x:v>
+      </x:c>
+      <x:c r="O9" s="3" t="s">
+        <x:v>491</x:v>
+      </x:c>
+      <x:c r="P9" s="3" t="s">
+        <x:v>492</x:v>
+      </x:c>
+      <x:c r="Q9" s="3" t="s">
+        <x:v>493</x:v>
+      </x:c>
+      <x:c r="R9" s="3" t="s">
+        <x:v>494</x:v>
+      </x:c>
+      <x:c r="S9" s="3" t="s">
+        <x:v>495</x:v>
+      </x:c>
+      <x:c r="T9" s="3" t="s">
         <x:v>496</x:v>
-      </x:c>
-      <x:c r="M9" s="3" t="s">
-        <x:v>436</x:v>
-      </x:c>
-      <x:c r="N9" s="3" t="s">
-        <x:v>497</x:v>
-      </x:c>
-      <x:c r="O9" s="3" t="s">
-        <x:v>498</x:v>
-      </x:c>
-      <x:c r="P9" s="3" t="s">
-        <x:v>499</x:v>
-      </x:c>
-      <x:c r="Q9" s="3" t="s">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="R9" s="3" t="s">
-        <x:v>501</x:v>
-      </x:c>
-      <x:c r="S9" s="3" t="s">
-        <x:v>502</x:v>
-      </x:c>
-      <x:c r="T9" s="3" t="s">
-        <x:v>503</x:v>
       </x:c>
       <x:c r="U9" s="3" t="s">
         <x:v>52</x:v>
@@ -9240,31 +9219,31 @@
     </x:row>
     <x:row r="10" ht="93.25" hidden="0">
       <x:c r="A10" s="3" t="s">
-        <x:v>504</x:v>
+        <x:v>497</x:v>
       </x:c>
       <x:c r="B10" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C10" s="3" t="s">
-        <x:v>505</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="D10" s="3" t="s">
-        <x:v>506</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="E10" s="3" t="s">
-        <x:v>507</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="F10" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G10" s="3" t="s">
-        <x:v>432</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="H10" s="3" t="s">
-        <x:v>433</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="I10" s="3" t="s">
-        <x:v>434</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="J10" s="3" t="s">
         <x:v>41</x:v>
@@ -9273,31 +9252,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L10" s="3" t="s">
-        <x:v>508</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="M10" s="3" t="s">
         <x:v>424</x:v>
       </x:c>
       <x:c r="N10" s="3" t="s">
-        <x:v>509</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="O10" s="3" t="s">
         <x:v>205</x:v>
       </x:c>
       <x:c r="P10" s="3" t="s">
-        <x:v>510</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="Q10" s="3" t="s">
-        <x:v>511</x:v>
+        <x:v>504</x:v>
       </x:c>
       <x:c r="R10" s="3" t="s">
-        <x:v>512</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="S10" s="3" t="s">
-        <x:v>513</x:v>
+        <x:v>506</x:v>
       </x:c>
       <x:c r="T10" s="3" t="s">
-        <x:v>514</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="U10" s="3" t="s">
         <x:v>52</x:v>
@@ -9305,31 +9284,31 @@
     </x:row>
     <x:row r="11" ht="93.25" hidden="0">
       <x:c r="A11" s="3" t="s">
-        <x:v>515</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="B11" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C11" s="3" t="s">
-        <x:v>516</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="D11" s="3" t="s">
-        <x:v>517</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="E11" s="3" t="s">
-        <x:v>518</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="F11" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G11" s="3" t="s">
-        <x:v>432</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="H11" s="3" t="s">
-        <x:v>433</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="I11" s="3" t="s">
-        <x:v>434</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="J11" s="3" t="s">
         <x:v>41</x:v>
@@ -9338,31 +9317,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L11" s="3" t="s">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="M11" s="3" t="s">
+        <x:v>513</x:v>
+      </x:c>
+      <x:c r="N11" s="3" t="s">
+        <x:v>514</x:v>
+      </x:c>
+      <x:c r="O11" s="3" t="s">
+        <x:v>515</x:v>
+      </x:c>
+      <x:c r="P11" s="3" t="s">
+        <x:v>516</x:v>
+      </x:c>
+      <x:c r="Q11" s="3" t="s">
+        <x:v>517</x:v>
+      </x:c>
+      <x:c r="R11" s="3" t="s">
+        <x:v>518</x:v>
+      </x:c>
+      <x:c r="S11" s="3" t="s">
         <x:v>519</x:v>
       </x:c>
-      <x:c r="M11" s="3" t="s">
+      <x:c r="T11" s="3" t="s">
         <x:v>520</x:v>
-      </x:c>
-      <x:c r="N11" s="3" t="s">
-        <x:v>521</x:v>
-      </x:c>
-      <x:c r="O11" s="3" t="s">
-        <x:v>522</x:v>
-      </x:c>
-      <x:c r="P11" s="3" t="s">
-        <x:v>523</x:v>
-      </x:c>
-      <x:c r="Q11" s="3" t="s">
-        <x:v>524</x:v>
-      </x:c>
-      <x:c r="R11" s="3" t="s">
-        <x:v>525</x:v>
-      </x:c>
-      <x:c r="S11" s="3" t="s">
-        <x:v>526</x:v>
-      </x:c>
-      <x:c r="T11" s="3" t="s">
-        <x:v>527</x:v>
       </x:c>
       <x:c r="U11" s="3" t="s">
         <x:v>52</x:v>
@@ -9370,31 +9349,31 @@
     </x:row>
     <x:row r="12" ht="107.25" hidden="0">
       <x:c r="A12" s="3" t="s">
-        <x:v>528</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="B12" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C12" s="3" t="s">
-        <x:v>529</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="D12" s="3" t="s">
-        <x:v>530</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="E12" s="3" t="s">
-        <x:v>531</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="F12" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G12" s="3" t="s">
-        <x:v>432</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="H12" s="3" t="s">
-        <x:v>433</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="I12" s="3" t="s">
-        <x:v>434</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="J12" s="3" t="s">
         <x:v>41</x:v>
@@ -9403,31 +9382,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L12" s="3" t="s">
+        <x:v>525</x:v>
+      </x:c>
+      <x:c r="M12" s="3" t="s">
+        <x:v>441</x:v>
+      </x:c>
+      <x:c r="N12" s="3" t="s">
+        <x:v>526</x:v>
+      </x:c>
+      <x:c r="O12" s="3" t="s">
+        <x:v>527</x:v>
+      </x:c>
+      <x:c r="P12" s="3" t="s">
+        <x:v>528</x:v>
+      </x:c>
+      <x:c r="Q12" s="3" t="s">
+        <x:v>529</x:v>
+      </x:c>
+      <x:c r="R12" s="3" t="s">
+        <x:v>530</x:v>
+      </x:c>
+      <x:c r="S12" s="3" t="s">
+        <x:v>531</x:v>
+      </x:c>
+      <x:c r="T12" s="3" t="s">
         <x:v>532</x:v>
-      </x:c>
-      <x:c r="M12" s="3" t="s">
-        <x:v>436</x:v>
-      </x:c>
-      <x:c r="N12" s="3" t="s">
-        <x:v>533</x:v>
-      </x:c>
-      <x:c r="O12" s="3" t="s">
-        <x:v>534</x:v>
-      </x:c>
-      <x:c r="P12" s="3" t="s">
-        <x:v>535</x:v>
-      </x:c>
-      <x:c r="Q12" s="3" t="s">
-        <x:v>536</x:v>
-      </x:c>
-      <x:c r="R12" s="3" t="s">
-        <x:v>537</x:v>
-      </x:c>
-      <x:c r="S12" s="3" t="s">
-        <x:v>538</x:v>
-      </x:c>
-      <x:c r="T12" s="3" t="s">
-        <x:v>539</x:v>
       </x:c>
       <x:c r="U12" s="3" t="s">
         <x:v>52</x:v>
@@ -9435,31 +9414,31 @@
     </x:row>
     <x:row r="13" ht="93.25" hidden="0">
       <x:c r="A13" s="3" t="s">
-        <x:v>540</x:v>
+        <x:v>533</x:v>
       </x:c>
       <x:c r="B13" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C13" s="3" t="s">
-        <x:v>541</x:v>
+        <x:v>534</x:v>
       </x:c>
       <x:c r="D13" s="3" t="s">
-        <x:v>542</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="E13" s="3" t="s">
-        <x:v>543</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="F13" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G13" s="3" t="s">
-        <x:v>432</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="H13" s="3" t="s">
-        <x:v>433</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="I13" s="3" t="s">
-        <x:v>434</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="J13" s="3" t="s">
         <x:v>41</x:v>
@@ -9468,31 +9447,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L13" s="3" t="s">
-        <x:v>544</x:v>
+        <x:v>537</x:v>
       </x:c>
       <x:c r="M13" s="3" t="s">
-        <x:v>436</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="N13" s="3" t="s">
-        <x:v>545</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="O13" s="3" t="s">
-        <x:v>546</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="P13" s="3" t="s">
-        <x:v>547</x:v>
+        <x:v>540</x:v>
       </x:c>
       <x:c r="Q13" s="3" t="s">
-        <x:v>536</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="R13" s="3" t="s">
-        <x:v>548</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="S13" s="3" t="s">
-        <x:v>549</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="T13" s="3" t="s">
-        <x:v>550</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="U13" s="3" t="s">
         <x:v>52</x:v>
@@ -9500,31 +9479,31 @@
     </x:row>
     <x:row r="14" ht="93.25" hidden="0">
       <x:c r="A14" s="3" t="s">
-        <x:v>551</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="B14" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C14" s="3" t="s">
-        <x:v>552</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="D14" s="3" t="s">
-        <x:v>553</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="E14" s="3" t="s">
-        <x:v>554</x:v>
+        <x:v>547</x:v>
       </x:c>
       <x:c r="F14" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G14" s="3" t="s">
-        <x:v>432</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="H14" s="3" t="s">
-        <x:v>433</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="I14" s="3" t="s">
-        <x:v>434</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="J14" s="3" t="s">
         <x:v>41</x:v>
@@ -9533,31 +9512,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L14" s="3" t="s">
+        <x:v>548</x:v>
+      </x:c>
+      <x:c r="M14" s="3" t="s">
+        <x:v>549</x:v>
+      </x:c>
+      <x:c r="N14" s="3" t="s">
+        <x:v>550</x:v>
+      </x:c>
+      <x:c r="O14" s="3" t="s">
+        <x:v>551</x:v>
+      </x:c>
+      <x:c r="P14" s="3" t="s">
+        <x:v>552</x:v>
+      </x:c>
+      <x:c r="Q14" s="3" t="s">
+        <x:v>553</x:v>
+      </x:c>
+      <x:c r="R14" s="3" t="s">
+        <x:v>554</x:v>
+      </x:c>
+      <x:c r="S14" s="3" t="s">
         <x:v>555</x:v>
       </x:c>
-      <x:c r="M14" s="3" t="s">
+      <x:c r="T14" s="3" t="s">
         <x:v>556</x:v>
-      </x:c>
-      <x:c r="N14" s="3" t="s">
-        <x:v>557</x:v>
-      </x:c>
-      <x:c r="O14" s="3" t="s">
-        <x:v>558</x:v>
-      </x:c>
-      <x:c r="P14" s="3" t="s">
-        <x:v>559</x:v>
-      </x:c>
-      <x:c r="Q14" s="3" t="s">
-        <x:v>560</x:v>
-      </x:c>
-      <x:c r="R14" s="3" t="s">
-        <x:v>561</x:v>
-      </x:c>
-      <x:c r="S14" s="3" t="s">
-        <x:v>562</x:v>
-      </x:c>
-      <x:c r="T14" s="3" t="s">
-        <x:v>563</x:v>
       </x:c>
       <x:c r="U14" s="3" t="s">
         <x:v>52</x:v>
@@ -9565,31 +9544,31 @@
     </x:row>
     <x:row r="15" ht="107.25" hidden="0">
       <x:c r="A15" s="3" t="s">
-        <x:v>564</x:v>
+        <x:v>557</x:v>
       </x:c>
       <x:c r="B15" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C15" s="3" t="s">
-        <x:v>565</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="D15" s="3" t="s">
-        <x:v>566</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="E15" s="3" t="s">
-        <x:v>567</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="F15" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G15" s="3" t="s">
-        <x:v>432</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="H15" s="3" t="s">
-        <x:v>433</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="I15" s="3" t="s">
-        <x:v>434</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="J15" s="3" t="s">
         <x:v>41</x:v>
@@ -9598,31 +9577,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L15" s="3" t="s">
+        <x:v>561</x:v>
+      </x:c>
+      <x:c r="M15" s="3" t="s">
+        <x:v>441</x:v>
+      </x:c>
+      <x:c r="N15" s="3" t="s">
+        <x:v>562</x:v>
+      </x:c>
+      <x:c r="O15" s="3" t="s">
+        <x:v>563</x:v>
+      </x:c>
+      <x:c r="P15" s="3" t="s">
+        <x:v>564</x:v>
+      </x:c>
+      <x:c r="Q15" s="3" t="s">
+        <x:v>565</x:v>
+      </x:c>
+      <x:c r="R15" s="3" t="s">
+        <x:v>566</x:v>
+      </x:c>
+      <x:c r="S15" s="3" t="s">
+        <x:v>567</x:v>
+      </x:c>
+      <x:c r="T15" s="3" t="s">
         <x:v>568</x:v>
-      </x:c>
-      <x:c r="M15" s="3" t="s">
-        <x:v>436</x:v>
-      </x:c>
-      <x:c r="N15" s="3" t="s">
-        <x:v>569</x:v>
-      </x:c>
-      <x:c r="O15" s="3" t="s">
-        <x:v>570</x:v>
-      </x:c>
-      <x:c r="P15" s="3" t="s">
-        <x:v>571</x:v>
-      </x:c>
-      <x:c r="Q15" s="3" t="s">
-        <x:v>572</x:v>
-      </x:c>
-      <x:c r="R15" s="3" t="s">
-        <x:v>573</x:v>
-      </x:c>
-      <x:c r="S15" s="3" t="s">
-        <x:v>574</x:v>
-      </x:c>
-      <x:c r="T15" s="3" t="s">
-        <x:v>575</x:v>
       </x:c>
       <x:c r="U15" s="3" t="s">
         <x:v>52</x:v>
@@ -9630,31 +9609,31 @@
     </x:row>
     <x:row r="16" ht="107.25" hidden="0">
       <x:c r="A16" s="3" t="s">
-        <x:v>576</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="B16" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C16" s="3" t="s">
-        <x:v>577</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="D16" s="3" t="s">
-        <x:v>578</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="E16" s="3" t="s">
-        <x:v>579</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="F16" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G16" s="3" t="s">
-        <x:v>432</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="H16" s="3" t="s">
-        <x:v>433</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="I16" s="3" t="s">
-        <x:v>434</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="J16" s="3" t="s">
         <x:v>41</x:v>
@@ -9663,31 +9642,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L16" s="3" t="s">
+        <x:v>573</x:v>
+      </x:c>
+      <x:c r="M16" s="3" t="s">
+        <x:v>441</x:v>
+      </x:c>
+      <x:c r="N16" s="3" t="s">
+        <x:v>574</x:v>
+      </x:c>
+      <x:c r="O16" s="3" t="s">
+        <x:v>575</x:v>
+      </x:c>
+      <x:c r="P16" s="3" t="s">
+        <x:v>576</x:v>
+      </x:c>
+      <x:c r="Q16" s="3" t="s">
+        <x:v>577</x:v>
+      </x:c>
+      <x:c r="R16" s="3" t="s">
+        <x:v>578</x:v>
+      </x:c>
+      <x:c r="S16" s="3" t="s">
+        <x:v>579</x:v>
+      </x:c>
+      <x:c r="T16" s="3" t="s">
         <x:v>580</x:v>
-      </x:c>
-      <x:c r="M16" s="3" t="s">
-        <x:v>436</x:v>
-      </x:c>
-      <x:c r="N16" s="3" t="s">
-        <x:v>581</x:v>
-      </x:c>
-      <x:c r="O16" s="3" t="s">
-        <x:v>582</x:v>
-      </x:c>
-      <x:c r="P16" s="3" t="s">
-        <x:v>583</x:v>
-      </x:c>
-      <x:c r="Q16" s="3" t="s">
-        <x:v>584</x:v>
-      </x:c>
-      <x:c r="R16" s="3" t="s">
-        <x:v>585</x:v>
-      </x:c>
-      <x:c r="S16" s="3" t="s">
-        <x:v>586</x:v>
-      </x:c>
-      <x:c r="T16" s="3" t="s">
-        <x:v>587</x:v>
       </x:c>
       <x:c r="U16" s="3" t="s">
         <x:v>52</x:v>
@@ -9695,31 +9674,31 @@
     </x:row>
     <x:row r="17" ht="93.25" hidden="0">
       <x:c r="A17" s="3" t="s">
-        <x:v>588</x:v>
+        <x:v>581</x:v>
       </x:c>
       <x:c r="B17" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C17" s="3" t="s">
-        <x:v>589</x:v>
+        <x:v>582</x:v>
       </x:c>
       <x:c r="D17" s="3" t="s">
-        <x:v>590</x:v>
+        <x:v>583</x:v>
       </x:c>
       <x:c r="E17" s="3" t="s">
-        <x:v>591</x:v>
+        <x:v>584</x:v>
       </x:c>
       <x:c r="F17" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G17" s="3" t="s">
-        <x:v>432</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="H17" s="3" t="s">
-        <x:v>433</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="I17" s="3" t="s">
-        <x:v>434</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="J17" s="3" t="s">
         <x:v>41</x:v>
@@ -9728,31 +9707,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L17" s="3" t="s">
+        <x:v>585</x:v>
+      </x:c>
+      <x:c r="M17" s="3" t="s">
+        <x:v>586</x:v>
+      </x:c>
+      <x:c r="N17" s="3" t="s">
+        <x:v>587</x:v>
+      </x:c>
+      <x:c r="O17" s="3" t="s">
+        <x:v>588</x:v>
+      </x:c>
+      <x:c r="P17" s="3" t="s">
+        <x:v>589</x:v>
+      </x:c>
+      <x:c r="Q17" s="3" t="s">
+        <x:v>590</x:v>
+      </x:c>
+      <x:c r="R17" s="3" t="s">
+        <x:v>591</x:v>
+      </x:c>
+      <x:c r="S17" s="3" t="s">
         <x:v>592</x:v>
       </x:c>
-      <x:c r="M17" s="3" t="s">
+      <x:c r="T17" s="3" t="s">
         <x:v>593</x:v>
-      </x:c>
-      <x:c r="N17" s="3" t="s">
-        <x:v>594</x:v>
-      </x:c>
-      <x:c r="O17" s="3" t="s">
-        <x:v>595</x:v>
-      </x:c>
-      <x:c r="P17" s="3" t="s">
-        <x:v>596</x:v>
-      </x:c>
-      <x:c r="Q17" s="3" t="s">
-        <x:v>597</x:v>
-      </x:c>
-      <x:c r="R17" s="3" t="s">
-        <x:v>598</x:v>
-      </x:c>
-      <x:c r="S17" s="3" t="s">
-        <x:v>599</x:v>
-      </x:c>
-      <x:c r="T17" s="3" t="s">
-        <x:v>600</x:v>
       </x:c>
       <x:c r="U17" s="3" t="s">
         <x:v>52</x:v>
@@ -9760,31 +9739,31 @@
     </x:row>
     <x:row r="18" ht="93.25" hidden="0">
       <x:c r="A18" s="3" t="s">
-        <x:v>601</x:v>
+        <x:v>594</x:v>
       </x:c>
       <x:c r="B18" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C18" s="3" t="s">
-        <x:v>602</x:v>
+        <x:v>595</x:v>
       </x:c>
       <x:c r="D18" s="3" t="s">
-        <x:v>603</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="E18" s="3" t="s">
-        <x:v>604</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="F18" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G18" s="3" t="s">
-        <x:v>432</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="H18" s="3" t="s">
-        <x:v>433</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="I18" s="3" t="s">
-        <x:v>434</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="J18" s="3" t="s">
         <x:v>41</x:v>
@@ -9793,31 +9772,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L18" s="3" t="s">
+        <x:v>598</x:v>
+      </x:c>
+      <x:c r="M18" s="3" t="s">
+        <x:v>599</x:v>
+      </x:c>
+      <x:c r="N18" s="3" t="s">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="O18" s="3" t="s">
+        <x:v>601</x:v>
+      </x:c>
+      <x:c r="P18" s="3" t="s">
+        <x:v>602</x:v>
+      </x:c>
+      <x:c r="Q18" s="3" t="s">
+        <x:v>603</x:v>
+      </x:c>
+      <x:c r="R18" s="3" t="s">
+        <x:v>604</x:v>
+      </x:c>
+      <x:c r="S18" s="3" t="s">
         <x:v>605</x:v>
       </x:c>
-      <x:c r="M18" s="3" t="s">
+      <x:c r="T18" s="3" t="s">
         <x:v>606</x:v>
-      </x:c>
-      <x:c r="N18" s="3" t="s">
-        <x:v>607</x:v>
-      </x:c>
-      <x:c r="O18" s="3" t="s">
-        <x:v>608</x:v>
-      </x:c>
-      <x:c r="P18" s="3" t="s">
-        <x:v>609</x:v>
-      </x:c>
-      <x:c r="Q18" s="3" t="s">
-        <x:v>610</x:v>
-      </x:c>
-      <x:c r="R18" s="3" t="s">
-        <x:v>611</x:v>
-      </x:c>
-      <x:c r="S18" s="3" t="s">
-        <x:v>612</x:v>
-      </x:c>
-      <x:c r="T18" s="3" t="s">
-        <x:v>613</x:v>
       </x:c>
       <x:c r="U18" s="3" t="s">
         <x:v>52</x:v>
@@ -9825,31 +9804,31 @@
     </x:row>
     <x:row r="19" ht="93.25" hidden="0">
       <x:c r="A19" s="3" t="s">
-        <x:v>614</x:v>
+        <x:v>607</x:v>
       </x:c>
       <x:c r="B19" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C19" s="3" t="s">
-        <x:v>615</x:v>
+        <x:v>608</x:v>
       </x:c>
       <x:c r="D19" s="3" t="s">
-        <x:v>616</x:v>
+        <x:v>609</x:v>
       </x:c>
       <x:c r="E19" s="3" t="s">
-        <x:v>617</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="F19" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G19" s="3" t="s">
-        <x:v>432</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="H19" s="3" t="s">
-        <x:v>433</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="I19" s="3" t="s">
-        <x:v>434</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="J19" s="3" t="s">
         <x:v>41</x:v>
@@ -9858,31 +9837,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L19" s="3" t="s">
+        <x:v>611</x:v>
+      </x:c>
+      <x:c r="M19" s="3" t="s">
+        <x:v>612</x:v>
+      </x:c>
+      <x:c r="N19" s="3" t="s">
+        <x:v>613</x:v>
+      </x:c>
+      <x:c r="O19" s="3" t="s">
+        <x:v>614</x:v>
+      </x:c>
+      <x:c r="P19" s="3" t="s">
+        <x:v>615</x:v>
+      </x:c>
+      <x:c r="Q19" s="3" t="s">
+        <x:v>616</x:v>
+      </x:c>
+      <x:c r="R19" s="3" t="s">
+        <x:v>617</x:v>
+      </x:c>
+      <x:c r="S19" s="3" t="s">
         <x:v>618</x:v>
       </x:c>
-      <x:c r="M19" s="3" t="s">
+      <x:c r="T19" s="3" t="s">
         <x:v>619</x:v>
-      </x:c>
-      <x:c r="N19" s="3" t="s">
-        <x:v>620</x:v>
-      </x:c>
-      <x:c r="O19" s="3" t="s">
-        <x:v>621</x:v>
-      </x:c>
-      <x:c r="P19" s="3" t="s">
-        <x:v>622</x:v>
-      </x:c>
-      <x:c r="Q19" s="3" t="s">
-        <x:v>623</x:v>
-      </x:c>
-      <x:c r="R19" s="3" t="s">
-        <x:v>624</x:v>
-      </x:c>
-      <x:c r="S19" s="3" t="s">
-        <x:v>625</x:v>
-      </x:c>
-      <x:c r="T19" s="3" t="s">
-        <x:v>626</x:v>
       </x:c>
       <x:c r="U19" s="3" t="s">
         <x:v>52</x:v>
@@ -9890,31 +9869,31 @@
     </x:row>
     <x:row r="20" ht="79.25" hidden="0">
       <x:c r="A20" s="3" t="s">
-        <x:v>627</x:v>
+        <x:v>620</x:v>
       </x:c>
       <x:c r="B20" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C20" s="3" t="s">
-        <x:v>628</x:v>
+        <x:v>621</x:v>
       </x:c>
       <x:c r="D20" s="3" t="s">
-        <x:v>629</x:v>
+        <x:v>622</x:v>
       </x:c>
       <x:c r="E20" s="3" t="s">
-        <x:v>630</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="F20" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G20" s="3" t="s">
-        <x:v>432</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="H20" s="3" t="s">
-        <x:v>433</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="I20" s="3" t="s">
-        <x:v>434</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="J20" s="3" t="s">
         <x:v>41</x:v>
@@ -9923,31 +9902,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L20" s="3" t="s">
+        <x:v>624</x:v>
+      </x:c>
+      <x:c r="M20" s="3" t="s">
+        <x:v>625</x:v>
+      </x:c>
+      <x:c r="N20" s="3" t="s">
+        <x:v>626</x:v>
+      </x:c>
+      <x:c r="O20" s="3" t="s">
+        <x:v>627</x:v>
+      </x:c>
+      <x:c r="P20" s="3" t="s">
+        <x:v>628</x:v>
+      </x:c>
+      <x:c r="Q20" s="3" t="s">
+        <x:v>629</x:v>
+      </x:c>
+      <x:c r="R20" s="3" t="s">
+        <x:v>630</x:v>
+      </x:c>
+      <x:c r="S20" s="3" t="s">
         <x:v>631</x:v>
       </x:c>
-      <x:c r="M20" s="3" t="s">
+      <x:c r="T20" s="3" t="s">
         <x:v>632</x:v>
-      </x:c>
-      <x:c r="N20" s="3" t="s">
-        <x:v>633</x:v>
-      </x:c>
-      <x:c r="O20" s="3" t="s">
-        <x:v>634</x:v>
-      </x:c>
-      <x:c r="P20" s="3" t="s">
-        <x:v>635</x:v>
-      </x:c>
-      <x:c r="Q20" s="3" t="s">
-        <x:v>636</x:v>
-      </x:c>
-      <x:c r="R20" s="3" t="s">
-        <x:v>637</x:v>
-      </x:c>
-      <x:c r="S20" s="3" t="s">
-        <x:v>638</x:v>
-      </x:c>
-      <x:c r="T20" s="3" t="s">
-        <x:v>639</x:v>
       </x:c>
       <x:c r="U20" s="3" t="s">
         <x:v>52</x:v>
@@ -9955,31 +9934,31 @@
     </x:row>
     <x:row r="21" ht="79.25" hidden="0">
       <x:c r="A21" s="3" t="s">
-        <x:v>640</x:v>
+        <x:v>633</x:v>
       </x:c>
       <x:c r="B21" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C21" s="3" t="s">
-        <x:v>641</x:v>
+        <x:v>634</x:v>
       </x:c>
       <x:c r="D21" s="3" t="s">
-        <x:v>642</x:v>
+        <x:v>635</x:v>
       </x:c>
       <x:c r="E21" s="3" t="s">
-        <x:v>643</x:v>
+        <x:v>636</x:v>
       </x:c>
       <x:c r="F21" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G21" s="3" t="s">
-        <x:v>432</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="H21" s="3" t="s">
-        <x:v>433</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="I21" s="3" t="s">
-        <x:v>434</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="J21" s="3" t="s">
         <x:v>41</x:v>
@@ -9988,31 +9967,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L21" s="3" t="s">
-        <x:v>644</x:v>
+        <x:v>637</x:v>
       </x:c>
       <x:c r="M21" s="3" t="s">
-        <x:v>645</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="N21" s="3" t="s">
-        <x:v>646</x:v>
+        <x:v>639</x:v>
       </x:c>
       <x:c r="O21" s="3" t="s">
         <x:v>218</x:v>
       </x:c>
       <x:c r="P21" s="3" t="s">
-        <x:v>647</x:v>
+        <x:v>640</x:v>
       </x:c>
       <x:c r="Q21" s="3" t="s">
-        <x:v>648</x:v>
+        <x:v>641</x:v>
       </x:c>
       <x:c r="R21" s="3" t="s">
         <x:v>221</x:v>
       </x:c>
       <x:c r="S21" s="3" t="s">
-        <x:v>649</x:v>
+        <x:v>642</x:v>
       </x:c>
       <x:c r="T21" s="3" t="s">
-        <x:v>650</x:v>
+        <x:v>643</x:v>
       </x:c>
       <x:c r="U21" s="3" t="s">
         <x:v>52</x:v>
@@ -10020,31 +9999,31 @@
     </x:row>
     <x:row r="22" ht="93.25" hidden="0">
       <x:c r="A22" s="3" t="s">
-        <x:v>651</x:v>
+        <x:v>644</x:v>
       </x:c>
       <x:c r="B22" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C22" s="3" t="s">
-        <x:v>652</x:v>
+        <x:v>645</x:v>
       </x:c>
       <x:c r="D22" s="3" t="s">
-        <x:v>653</x:v>
+        <x:v>646</x:v>
       </x:c>
       <x:c r="E22" s="3" t="s">
-        <x:v>654</x:v>
+        <x:v>647</x:v>
       </x:c>
       <x:c r="F22" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G22" s="3" t="s">
-        <x:v>432</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="H22" s="3" t="s">
-        <x:v>433</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="I22" s="3" t="s">
-        <x:v>434</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="J22" s="3" t="s">
         <x:v>41</x:v>
@@ -10053,31 +10032,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L22" s="3" t="s">
+        <x:v>648</x:v>
+      </x:c>
+      <x:c r="M22" s="3" t="s">
+        <x:v>513</x:v>
+      </x:c>
+      <x:c r="N22" s="3" t="s">
+        <x:v>649</x:v>
+      </x:c>
+      <x:c r="O22" s="3" t="s">
+        <x:v>650</x:v>
+      </x:c>
+      <x:c r="P22" s="3" t="s">
+        <x:v>651</x:v>
+      </x:c>
+      <x:c r="Q22" s="3" t="s">
+        <x:v>652</x:v>
+      </x:c>
+      <x:c r="R22" s="3" t="s">
+        <x:v>653</x:v>
+      </x:c>
+      <x:c r="S22" s="3" t="s">
+        <x:v>654</x:v>
+      </x:c>
+      <x:c r="T22" s="3" t="s">
         <x:v>655</x:v>
-      </x:c>
-      <x:c r="M22" s="3" t="s">
-        <x:v>520</x:v>
-      </x:c>
-      <x:c r="N22" s="3" t="s">
-        <x:v>656</x:v>
-      </x:c>
-      <x:c r="O22" s="3" t="s">
-        <x:v>657</x:v>
-      </x:c>
-      <x:c r="P22" s="3" t="s">
-        <x:v>658</x:v>
-      </x:c>
-      <x:c r="Q22" s="3" t="s">
-        <x:v>659</x:v>
-      </x:c>
-      <x:c r="R22" s="3" t="s">
-        <x:v>660</x:v>
-      </x:c>
-      <x:c r="S22" s="3" t="s">
-        <x:v>661</x:v>
-      </x:c>
-      <x:c r="T22" s="3" t="s">
-        <x:v>662</x:v>
       </x:c>
       <x:c r="U22" s="3" t="s">
         <x:v>52</x:v>
@@ -10085,31 +10064,31 @@
     </x:row>
     <x:row r="23" ht="93.25" hidden="0">
       <x:c r="A23" s="3" t="s">
-        <x:v>663</x:v>
+        <x:v>656</x:v>
       </x:c>
       <x:c r="B23" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C23" s="3" t="s">
-        <x:v>664</x:v>
+        <x:v>657</x:v>
       </x:c>
       <x:c r="D23" s="3" t="s">
-        <x:v>665</x:v>
+        <x:v>658</x:v>
       </x:c>
       <x:c r="E23" s="3" t="s">
-        <x:v>666</x:v>
+        <x:v>659</x:v>
       </x:c>
       <x:c r="F23" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G23" s="3" t="s">
-        <x:v>432</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="H23" s="3" t="s">
-        <x:v>433</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="I23" s="3" t="s">
-        <x:v>434</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="J23" s="3" t="s">
         <x:v>41</x:v>
@@ -10118,31 +10097,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L23" s="3" t="s">
+        <x:v>660</x:v>
+      </x:c>
+      <x:c r="M23" s="3" t="s">
+        <x:v>661</x:v>
+      </x:c>
+      <x:c r="N23" s="3" t="s">
+        <x:v>662</x:v>
+      </x:c>
+      <x:c r="O23" s="3" t="s">
+        <x:v>663</x:v>
+      </x:c>
+      <x:c r="P23" s="3" t="s">
+        <x:v>664</x:v>
+      </x:c>
+      <x:c r="Q23" s="3" t="s">
+        <x:v>665</x:v>
+      </x:c>
+      <x:c r="R23" s="3" t="s">
+        <x:v>666</x:v>
+      </x:c>
+      <x:c r="S23" s="3" t="s">
         <x:v>667</x:v>
       </x:c>
-      <x:c r="M23" s="3" t="s">
+      <x:c r="T23" s="3" t="s">
         <x:v>668</x:v>
-      </x:c>
-      <x:c r="N23" s="3" t="s">
-        <x:v>669</x:v>
-      </x:c>
-      <x:c r="O23" s="3" t="s">
-        <x:v>670</x:v>
-      </x:c>
-      <x:c r="P23" s="3" t="s">
-        <x:v>671</x:v>
-      </x:c>
-      <x:c r="Q23" s="3" t="s">
-        <x:v>672</x:v>
-      </x:c>
-      <x:c r="R23" s="3" t="s">
-        <x:v>673</x:v>
-      </x:c>
-      <x:c r="S23" s="3" t="s">
-        <x:v>674</x:v>
-      </x:c>
-      <x:c r="T23" s="3" t="s">
-        <x:v>675</x:v>
       </x:c>
       <x:c r="U23" s="3" t="s">
         <x:v>52</x:v>
@@ -10150,31 +10129,31 @@
     </x:row>
     <x:row r="24" ht="79.25" hidden="0">
       <x:c r="A24" s="3" t="s">
-        <x:v>676</x:v>
+        <x:v>669</x:v>
       </x:c>
       <x:c r="B24" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C24" s="3" t="s">
-        <x:v>677</x:v>
+        <x:v>670</x:v>
       </x:c>
       <x:c r="D24" s="3" t="s">
-        <x:v>678</x:v>
+        <x:v>671</x:v>
       </x:c>
       <x:c r="E24" s="3" t="s">
-        <x:v>679</x:v>
+        <x:v>672</x:v>
       </x:c>
       <x:c r="F24" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G24" s="3" t="s">
-        <x:v>432</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="H24" s="3" t="s">
-        <x:v>433</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="I24" s="3" t="s">
-        <x:v>434</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="J24" s="3" t="s">
         <x:v>41</x:v>
@@ -10183,31 +10162,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L24" s="3" t="s">
+        <x:v>673</x:v>
+      </x:c>
+      <x:c r="M24" s="3" t="s">
+        <x:v>638</x:v>
+      </x:c>
+      <x:c r="N24" s="3" t="s">
+        <x:v>674</x:v>
+      </x:c>
+      <x:c r="O24" s="3" t="s">
+        <x:v>675</x:v>
+      </x:c>
+      <x:c r="P24" s="3" t="s">
+        <x:v>676</x:v>
+      </x:c>
+      <x:c r="Q24" s="3" t="s">
+        <x:v>677</x:v>
+      </x:c>
+      <x:c r="R24" s="3" t="s">
+        <x:v>678</x:v>
+      </x:c>
+      <x:c r="S24" s="3" t="s">
+        <x:v>679</x:v>
+      </x:c>
+      <x:c r="T24" s="3" t="s">
         <x:v>680</x:v>
-      </x:c>
-      <x:c r="M24" s="3" t="s">
-        <x:v>645</x:v>
-      </x:c>
-      <x:c r="N24" s="3" t="s">
-        <x:v>681</x:v>
-      </x:c>
-      <x:c r="O24" s="3" t="s">
-        <x:v>682</x:v>
-      </x:c>
-      <x:c r="P24" s="3" t="s">
-        <x:v>683</x:v>
-      </x:c>
-      <x:c r="Q24" s="3" t="s">
-        <x:v>684</x:v>
-      </x:c>
-      <x:c r="R24" s="3" t="s">
-        <x:v>685</x:v>
-      </x:c>
-      <x:c r="S24" s="3" t="s">
-        <x:v>686</x:v>
-      </x:c>
-      <x:c r="T24" s="3" t="s">
-        <x:v>687</x:v>
       </x:c>
       <x:c r="U24" s="3" t="s">
         <x:v>52</x:v>
@@ -10215,31 +10194,31 @@
     </x:row>
     <x:row r="25" ht="79.25" hidden="0">
       <x:c r="A25" s="3" t="s">
-        <x:v>688</x:v>
+        <x:v>681</x:v>
       </x:c>
       <x:c r="B25" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C25" s="3" t="s">
-        <x:v>689</x:v>
+        <x:v>682</x:v>
       </x:c>
       <x:c r="D25" s="3" t="s">
-        <x:v>690</x:v>
+        <x:v>683</x:v>
       </x:c>
       <x:c r="E25" s="3" t="s">
-        <x:v>691</x:v>
+        <x:v>684</x:v>
       </x:c>
       <x:c r="F25" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G25" s="3" t="s">
-        <x:v>432</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="H25" s="3" t="s">
-        <x:v>433</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="I25" s="3" t="s">
-        <x:v>434</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="J25" s="3" t="s">
         <x:v>41</x:v>
@@ -10248,31 +10227,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L25" s="3" t="s">
+        <x:v>685</x:v>
+      </x:c>
+      <x:c r="M25" s="3" t="s">
+        <x:v>638</x:v>
+      </x:c>
+      <x:c r="N25" s="3" t="s">
+        <x:v>686</x:v>
+      </x:c>
+      <x:c r="O25" s="3" t="s">
+        <x:v>687</x:v>
+      </x:c>
+      <x:c r="P25" s="3" t="s">
+        <x:v>688</x:v>
+      </x:c>
+      <x:c r="Q25" s="3" t="s">
+        <x:v>689</x:v>
+      </x:c>
+      <x:c r="R25" s="3" t="s">
+        <x:v>690</x:v>
+      </x:c>
+      <x:c r="S25" s="3" t="s">
+        <x:v>691</x:v>
+      </x:c>
+      <x:c r="T25" s="3" t="s">
         <x:v>692</x:v>
-      </x:c>
-      <x:c r="M25" s="3" t="s">
-        <x:v>645</x:v>
-      </x:c>
-      <x:c r="N25" s="3" t="s">
-        <x:v>693</x:v>
-      </x:c>
-      <x:c r="O25" s="3" t="s">
-        <x:v>694</x:v>
-      </x:c>
-      <x:c r="P25" s="3" t="s">
-        <x:v>695</x:v>
-      </x:c>
-      <x:c r="Q25" s="3" t="s">
-        <x:v>696</x:v>
-      </x:c>
-      <x:c r="R25" s="3" t="s">
-        <x:v>697</x:v>
-      </x:c>
-      <x:c r="S25" s="3" t="s">
-        <x:v>698</x:v>
-      </x:c>
-      <x:c r="T25" s="3" t="s">
-        <x:v>699</x:v>
       </x:c>
       <x:c r="U25" s="3" t="s">
         <x:v>52</x:v>
@@ -10280,31 +10259,31 @@
     </x:row>
     <x:row r="26" ht="79.25" hidden="0">
       <x:c r="A26" s="3" t="s">
-        <x:v>700</x:v>
+        <x:v>693</x:v>
       </x:c>
       <x:c r="B26" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C26" s="3" t="s">
-        <x:v>701</x:v>
+        <x:v>694</x:v>
       </x:c>
       <x:c r="D26" s="3" t="s">
-        <x:v>702</x:v>
+        <x:v>695</x:v>
       </x:c>
       <x:c r="E26" s="3" t="s">
-        <x:v>703</x:v>
+        <x:v>696</x:v>
       </x:c>
       <x:c r="F26" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G26" s="3" t="s">
-        <x:v>432</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="H26" s="3" t="s">
-        <x:v>433</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="I26" s="3" t="s">
-        <x:v>434</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="J26" s="3" t="s">
         <x:v>41</x:v>
@@ -10313,31 +10292,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L26" s="3" t="s">
+        <x:v>697</x:v>
+      </x:c>
+      <x:c r="M26" s="3" t="s">
+        <x:v>698</x:v>
+      </x:c>
+      <x:c r="N26" s="3" t="s">
+        <x:v>699</x:v>
+      </x:c>
+      <x:c r="O26" s="3" t="s">
+        <x:v>700</x:v>
+      </x:c>
+      <x:c r="P26" s="3" t="s">
+        <x:v>701</x:v>
+      </x:c>
+      <x:c r="Q26" s="3" t="s">
+        <x:v>702</x:v>
+      </x:c>
+      <x:c r="R26" s="3" t="s">
+        <x:v>703</x:v>
+      </x:c>
+      <x:c r="S26" s="3" t="s">
         <x:v>704</x:v>
       </x:c>
-      <x:c r="M26" s="3" t="s">
+      <x:c r="T26" s="3" t="s">
         <x:v>705</x:v>
-      </x:c>
-      <x:c r="N26" s="3" t="s">
-        <x:v>706</x:v>
-      </x:c>
-      <x:c r="O26" s="3" t="s">
-        <x:v>707</x:v>
-      </x:c>
-      <x:c r="P26" s="3" t="s">
-        <x:v>708</x:v>
-      </x:c>
-      <x:c r="Q26" s="3" t="s">
-        <x:v>709</x:v>
-      </x:c>
-      <x:c r="R26" s="3" t="s">
-        <x:v>710</x:v>
-      </x:c>
-      <x:c r="S26" s="3" t="s">
-        <x:v>711</x:v>
-      </x:c>
-      <x:c r="T26" s="3" t="s">
-        <x:v>712</x:v>
       </x:c>
       <x:c r="U26" s="3" t="s">
         <x:v>52</x:v>
@@ -10345,31 +10324,31 @@
     </x:row>
     <x:row r="27" ht="79.25" hidden="0">
       <x:c r="A27" s="3" t="s">
-        <x:v>713</x:v>
+        <x:v>706</x:v>
       </x:c>
       <x:c r="B27" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C27" s="3" t="s">
-        <x:v>714</x:v>
+        <x:v>707</x:v>
       </x:c>
       <x:c r="D27" s="3" t="s">
-        <x:v>715</x:v>
+        <x:v>708</x:v>
       </x:c>
       <x:c r="E27" s="3" t="s">
-        <x:v>716</x:v>
+        <x:v>709</x:v>
       </x:c>
       <x:c r="F27" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G27" s="3" t="s">
-        <x:v>432</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="H27" s="3" t="s">
-        <x:v>433</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="I27" s="3" t="s">
-        <x:v>434</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="J27" s="3" t="s">
         <x:v>41</x:v>
@@ -10378,31 +10357,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L27" s="3" t="s">
+        <x:v>710</x:v>
+      </x:c>
+      <x:c r="M27" s="3" t="s">
+        <x:v>711</x:v>
+      </x:c>
+      <x:c r="N27" s="3" t="s">
+        <x:v>712</x:v>
+      </x:c>
+      <x:c r="O27" s="3" t="s">
+        <x:v>713</x:v>
+      </x:c>
+      <x:c r="P27" s="3" t="s">
+        <x:v>714</x:v>
+      </x:c>
+      <x:c r="Q27" s="3" t="s">
+        <x:v>715</x:v>
+      </x:c>
+      <x:c r="R27" s="3" t="s">
+        <x:v>716</x:v>
+      </x:c>
+      <x:c r="S27" s="3" t="s">
         <x:v>717</x:v>
       </x:c>
-      <x:c r="M27" s="3" t="s">
+      <x:c r="T27" s="3" t="s">
         <x:v>718</x:v>
-      </x:c>
-      <x:c r="N27" s="3" t="s">
-        <x:v>719</x:v>
-      </x:c>
-      <x:c r="O27" s="3" t="s">
-        <x:v>720</x:v>
-      </x:c>
-      <x:c r="P27" s="3" t="s">
-        <x:v>721</x:v>
-      </x:c>
-      <x:c r="Q27" s="3" t="s">
-        <x:v>722</x:v>
-      </x:c>
-      <x:c r="R27" s="3" t="s">
-        <x:v>723</x:v>
-      </x:c>
-      <x:c r="S27" s="3" t="s">
-        <x:v>724</x:v>
-      </x:c>
-      <x:c r="T27" s="3" t="s">
-        <x:v>725</x:v>
       </x:c>
       <x:c r="U27" s="3" t="s">
         <x:v>52</x:v>
@@ -10410,31 +10389,31 @@
     </x:row>
     <x:row r="28" ht="93.25" hidden="0">
       <x:c r="A28" s="3" t="s">
-        <x:v>726</x:v>
+        <x:v>719</x:v>
       </x:c>
       <x:c r="B28" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C28" s="3" t="s">
-        <x:v>727</x:v>
+        <x:v>720</x:v>
       </x:c>
       <x:c r="D28" s="3" t="s">
-        <x:v>728</x:v>
+        <x:v>721</x:v>
       </x:c>
       <x:c r="E28" s="3" t="s">
-        <x:v>729</x:v>
+        <x:v>722</x:v>
       </x:c>
       <x:c r="F28" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G28" s="3" t="s">
-        <x:v>432</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="H28" s="3" t="s">
-        <x:v>433</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="I28" s="3" t="s">
-        <x:v>434</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="J28" s="3" t="s">
         <x:v>41</x:v>
@@ -10443,31 +10422,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L28" s="3" t="s">
-        <x:v>730</x:v>
+        <x:v>723</x:v>
       </x:c>
       <x:c r="M28" s="3" t="s">
-        <x:v>731</x:v>
+        <x:v>724</x:v>
       </x:c>
       <x:c r="N28" s="3" t="s">
-        <x:v>732</x:v>
+        <x:v>725</x:v>
       </x:c>
       <x:c r="O28" s="3" t="s">
-        <x:v>733</x:v>
+        <x:v>726</x:v>
       </x:c>
       <x:c r="P28" s="3" t="s">
-        <x:v>734</x:v>
+        <x:v>727</x:v>
       </x:c>
       <x:c r="Q28" s="3" t="s">
-        <x:v>735</x:v>
+        <x:v>728</x:v>
       </x:c>
       <x:c r="R28" s="3" t="s">
-        <x:v>736</x:v>
+        <x:v>729</x:v>
       </x:c>
       <x:c r="S28" s="3" t="s">
         <x:v>286</x:v>
       </x:c>
       <x:c r="T28" s="3" t="s">
-        <x:v>737</x:v>
+        <x:v>730</x:v>
       </x:c>
       <x:c r="U28" s="3" t="s">
         <x:v>52</x:v>
@@ -10475,31 +10454,31 @@
     </x:row>
     <x:row r="29" ht="93.25" hidden="0">
       <x:c r="A29" s="3" t="s">
-        <x:v>738</x:v>
+        <x:v>731</x:v>
       </x:c>
       <x:c r="B29" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C29" s="3" t="s">
-        <x:v>739</x:v>
+        <x:v>732</x:v>
       </x:c>
       <x:c r="D29" s="3" t="s">
-        <x:v>740</x:v>
+        <x:v>733</x:v>
       </x:c>
       <x:c r="E29" s="3" t="s">
-        <x:v>741</x:v>
+        <x:v>734</x:v>
       </x:c>
       <x:c r="F29" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G29" s="3" t="s">
-        <x:v>432</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="H29" s="3" t="s">
-        <x:v>433</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="I29" s="3" t="s">
-        <x:v>434</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="J29" s="3" t="s">
         <x:v>41</x:v>
@@ -10508,31 +10487,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="L29" s="3" t="s">
+        <x:v>735</x:v>
+      </x:c>
+      <x:c r="M29" s="3" t="s">
+        <x:v>736</x:v>
+      </x:c>
+      <x:c r="N29" s="3" t="s">
+        <x:v>737</x:v>
+      </x:c>
+      <x:c r="O29" s="3" t="s">
+        <x:v>738</x:v>
+      </x:c>
+      <x:c r="P29" s="3" t="s">
+        <x:v>739</x:v>
+      </x:c>
+      <x:c r="Q29" s="3" t="s">
+        <x:v>740</x:v>
+      </x:c>
+      <x:c r="R29" s="3" t="s">
+        <x:v>741</x:v>
+      </x:c>
+      <x:c r="S29" s="3" t="s">
         <x:v>742</x:v>
       </x:c>
-      <x:c r="M29" s="3" t="s">
+      <x:c r="T29" s="3" t="s">
         <x:v>743</x:v>
-      </x:c>
-      <x:c r="N29" s="3" t="s">
-        <x:v>744</x:v>
-      </x:c>
-      <x:c r="O29" s="3" t="s">
-        <x:v>745</x:v>
-      </x:c>
-      <x:c r="P29" s="3" t="s">
-        <x:v>746</x:v>
-      </x:c>
-      <x:c r="Q29" s="3" t="s">
-        <x:v>747</x:v>
-      </x:c>
-      <x:c r="R29" s="3" t="s">
-        <x:v>748</x:v>
-      </x:c>
-      <x:c r="S29" s="3" t="s">
-        <x:v>749</x:v>
-      </x:c>
-      <x:c r="T29" s="3" t="s">
-        <x:v>750</x:v>
       </x:c>
       <x:c r="U29" s="3" t="s">
         <x:v>52</x:v>
@@ -10540,31 +10519,31 @@
     </x:row>
     <x:row r="30" ht="93.25" hidden="0">
       <x:c r="A30" s="3" t="s">
-        <x:v>751</x:v>
+        <x:v>744</x:v>
       </x:c>
       <x:c r="B30" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C30" s="3" t="s">
-        <x:v>752</x:v>
+        <x:v>745</x:v>
       </x:c>
       <x:c r="D30" s="3" t="s">
-        <x:v>753</x:v>
+        <x:v>746</x:v>
       </x:c>
       <x:c r="E30" s="3" t="s">
-        <x:v>754</x:v>
+        <x:v>747</x:v>
       </x:c>
       <x:c r="F30" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G30" s="3" t="s">
-        <x:v>432</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="H30" s="3" t="s">
-        <x:v>433</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="I30" s="3" t="s">
-        <x:v>434</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="J30" s="3" t="s">
         <x:v>41</x:v>
@@ -10573,31 +10552,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L30" s="3" t="s">
+        <x:v>748</x:v>
+      </x:c>
+      <x:c r="M30" s="3" t="s">
+        <x:v>749</x:v>
+      </x:c>
+      <x:c r="N30" s="3" t="s">
+        <x:v>750</x:v>
+      </x:c>
+      <x:c r="O30" s="3" t="s">
+        <x:v>751</x:v>
+      </x:c>
+      <x:c r="P30" s="3" t="s">
+        <x:v>752</x:v>
+      </x:c>
+      <x:c r="Q30" s="3" t="s">
+        <x:v>753</x:v>
+      </x:c>
+      <x:c r="R30" s="3" t="s">
+        <x:v>754</x:v>
+      </x:c>
+      <x:c r="S30" s="3" t="s">
         <x:v>755</x:v>
       </x:c>
-      <x:c r="M30" s="3" t="s">
+      <x:c r="T30" s="3" t="s">
         <x:v>756</x:v>
-      </x:c>
-      <x:c r="N30" s="3" t="s">
-        <x:v>757</x:v>
-      </x:c>
-      <x:c r="O30" s="3" t="s">
-        <x:v>758</x:v>
-      </x:c>
-      <x:c r="P30" s="3" t="s">
-        <x:v>759</x:v>
-      </x:c>
-      <x:c r="Q30" s="3" t="s">
-        <x:v>760</x:v>
-      </x:c>
-      <x:c r="R30" s="3" t="s">
-        <x:v>761</x:v>
-      </x:c>
-      <x:c r="S30" s="3" t="s">
-        <x:v>762</x:v>
-      </x:c>
-      <x:c r="T30" s="3" t="s">
-        <x:v>763</x:v>
       </x:c>
       <x:c r="U30" s="3" t="s">
         <x:v>52</x:v>
@@ -10605,31 +10584,31 @@
     </x:row>
     <x:row r="31" ht="93.25" hidden="0">
       <x:c r="A31" s="3" t="s">
-        <x:v>764</x:v>
+        <x:v>757</x:v>
       </x:c>
       <x:c r="B31" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C31" s="3" t="s">
-        <x:v>765</x:v>
+        <x:v>758</x:v>
       </x:c>
       <x:c r="D31" s="3" t="s">
-        <x:v>766</x:v>
+        <x:v>759</x:v>
       </x:c>
       <x:c r="E31" s="3" t="s">
-        <x:v>767</x:v>
+        <x:v>760</x:v>
       </x:c>
       <x:c r="F31" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G31" s="3" t="s">
-        <x:v>432</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="H31" s="3" t="s">
-        <x:v>433</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="I31" s="3" t="s">
-        <x:v>434</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="J31" s="3" t="s">
         <x:v>41</x:v>
@@ -10638,31 +10617,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="L31" s="3" t="s">
+        <x:v>761</x:v>
+      </x:c>
+      <x:c r="M31" s="3" t="s">
+        <x:v>762</x:v>
+      </x:c>
+      <x:c r="N31" s="3" t="s">
+        <x:v>763</x:v>
+      </x:c>
+      <x:c r="O31" s="3" t="s">
+        <x:v>764</x:v>
+      </x:c>
+      <x:c r="P31" s="3" t="s">
+        <x:v>765</x:v>
+      </x:c>
+      <x:c r="Q31" s="3" t="s">
+        <x:v>766</x:v>
+      </x:c>
+      <x:c r="R31" s="3" t="s">
+        <x:v>767</x:v>
+      </x:c>
+      <x:c r="S31" s="3" t="s">
         <x:v>768</x:v>
       </x:c>
-      <x:c r="M31" s="3" t="s">
+      <x:c r="T31" s="3" t="s">
         <x:v>769</x:v>
-      </x:c>
-      <x:c r="N31" s="3" t="s">
-        <x:v>770</x:v>
-      </x:c>
-      <x:c r="O31" s="3" t="s">
-        <x:v>771</x:v>
-      </x:c>
-      <x:c r="P31" s="3" t="s">
-        <x:v>772</x:v>
-      </x:c>
-      <x:c r="Q31" s="3" t="s">
-        <x:v>773</x:v>
-      </x:c>
-      <x:c r="R31" s="3" t="s">
-        <x:v>774</x:v>
-      </x:c>
-      <x:c r="S31" s="3" t="s">
-        <x:v>775</x:v>
-      </x:c>
-      <x:c r="T31" s="3" t="s">
-        <x:v>776</x:v>
       </x:c>
       <x:c r="U31" s="3" t="s">
         <x:v>52</x:v>
@@ -10670,31 +10649,31 @@
     </x:row>
     <x:row r="32" ht="93.25" hidden="0">
       <x:c r="A32" s="3" t="s">
-        <x:v>777</x:v>
+        <x:v>770</x:v>
       </x:c>
       <x:c r="B32" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C32" s="3" t="s">
-        <x:v>778</x:v>
+        <x:v>771</x:v>
       </x:c>
       <x:c r="D32" s="3" t="s">
-        <x:v>779</x:v>
+        <x:v>772</x:v>
       </x:c>
       <x:c r="E32" s="3" t="s">
-        <x:v>780</x:v>
+        <x:v>773</x:v>
       </x:c>
       <x:c r="F32" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G32" s="3" t="s">
-        <x:v>432</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="H32" s="3" t="s">
-        <x:v>433</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="I32" s="3" t="s">
-        <x:v>434</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="J32" s="3" t="s">
         <x:v>41</x:v>
@@ -10703,31 +10682,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L32" s="3" t="s">
+        <x:v>774</x:v>
+      </x:c>
+      <x:c r="M32" s="3" t="s">
+        <x:v>775</x:v>
+      </x:c>
+      <x:c r="N32" s="3" t="s">
+        <x:v>776</x:v>
+      </x:c>
+      <x:c r="O32" s="3" t="s">
+        <x:v>777</x:v>
+      </x:c>
+      <x:c r="P32" s="3" t="s">
+        <x:v>778</x:v>
+      </x:c>
+      <x:c r="Q32" s="3" t="s">
+        <x:v>779</x:v>
+      </x:c>
+      <x:c r="R32" s="3" t="s">
+        <x:v>780</x:v>
+      </x:c>
+      <x:c r="S32" s="3" t="s">
         <x:v>781</x:v>
       </x:c>
-      <x:c r="M32" s="3" t="s">
+      <x:c r="T32" s="3" t="s">
         <x:v>782</x:v>
-      </x:c>
-      <x:c r="N32" s="3" t="s">
-        <x:v>783</x:v>
-      </x:c>
-      <x:c r="O32" s="3" t="s">
-        <x:v>784</x:v>
-      </x:c>
-      <x:c r="P32" s="3" t="s">
-        <x:v>785</x:v>
-      </x:c>
-      <x:c r="Q32" s="3" t="s">
-        <x:v>786</x:v>
-      </x:c>
-      <x:c r="R32" s="3" t="s">
-        <x:v>787</x:v>
-      </x:c>
-      <x:c r="S32" s="3" t="s">
-        <x:v>788</x:v>
-      </x:c>
-      <x:c r="T32" s="3" t="s">
-        <x:v>789</x:v>
       </x:c>
       <x:c r="U32" s="3" t="s">
         <x:v>52</x:v>
@@ -10735,31 +10714,31 @@
     </x:row>
     <x:row r="33" ht="93.25" hidden="0">
       <x:c r="A33" s="3" t="s">
-        <x:v>790</x:v>
+        <x:v>783</x:v>
       </x:c>
       <x:c r="B33" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C33" s="3" t="s">
-        <x:v>791</x:v>
+        <x:v>784</x:v>
       </x:c>
       <x:c r="D33" s="3" t="s">
-        <x:v>792</x:v>
+        <x:v>785</x:v>
       </x:c>
       <x:c r="E33" s="3" t="s">
-        <x:v>793</x:v>
+        <x:v>786</x:v>
       </x:c>
       <x:c r="F33" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G33" s="3" t="s">
-        <x:v>432</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="H33" s="3" t="s">
-        <x:v>433</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="I33" s="3" t="s">
-        <x:v>434</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="J33" s="3" t="s">
         <x:v>41</x:v>
@@ -10768,31 +10747,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L33" s="3" t="s">
+        <x:v>787</x:v>
+      </x:c>
+      <x:c r="M33" s="3" t="s">
+        <x:v>788</x:v>
+      </x:c>
+      <x:c r="N33" s="3" t="s">
+        <x:v>789</x:v>
+      </x:c>
+      <x:c r="O33" s="3" t="s">
+        <x:v>790</x:v>
+      </x:c>
+      <x:c r="P33" s="3" t="s">
+        <x:v>791</x:v>
+      </x:c>
+      <x:c r="Q33" s="3" t="s">
+        <x:v>792</x:v>
+      </x:c>
+      <x:c r="R33" s="3" t="s">
+        <x:v>793</x:v>
+      </x:c>
+      <x:c r="S33" s="3" t="s">
         <x:v>794</x:v>
       </x:c>
-      <x:c r="M33" s="3" t="s">
+      <x:c r="T33" s="3" t="s">
         <x:v>795</x:v>
-      </x:c>
-      <x:c r="N33" s="3" t="s">
-        <x:v>796</x:v>
-      </x:c>
-      <x:c r="O33" s="3" t="s">
-        <x:v>797</x:v>
-      </x:c>
-      <x:c r="P33" s="3" t="s">
-        <x:v>798</x:v>
-      </x:c>
-      <x:c r="Q33" s="3" t="s">
-        <x:v>799</x:v>
-      </x:c>
-      <x:c r="R33" s="3" t="s">
-        <x:v>800</x:v>
-      </x:c>
-      <x:c r="S33" s="3" t="s">
-        <x:v>801</x:v>
-      </x:c>
-      <x:c r="T33" s="3" t="s">
-        <x:v>802</x:v>
       </x:c>
       <x:c r="U33" s="3" t="s">
         <x:v>52</x:v>
@@ -10800,7 +10779,7 @@
     </x:row>
     <x:row r="34" ht="93.25" hidden="0">
       <x:c r="A34" s="3" t="s">
-        <x:v>803</x:v>
+        <x:v>796</x:v>
       </x:c>
       <x:c r="B34" s="3" t="s">
         <x:v>8</x:v>
@@ -10809,22 +10788,22 @@
         <x:v>313</x:v>
       </x:c>
       <x:c r="D34" s="3" t="s">
-        <x:v>804</x:v>
+        <x:v>797</x:v>
       </x:c>
       <x:c r="E34" s="3" t="s">
-        <x:v>805</x:v>
+        <x:v>798</x:v>
       </x:c>
       <x:c r="F34" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G34" s="3" t="s">
-        <x:v>432</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="H34" s="3" t="s">
-        <x:v>433</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="I34" s="3" t="s">
-        <x:v>434</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="J34" s="3" t="s">
         <x:v>41</x:v>
@@ -10833,31 +10812,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="L34" s="3" t="s">
-        <x:v>806</x:v>
+        <x:v>799</x:v>
       </x:c>
       <x:c r="M34" s="3" t="s">
-        <x:v>807</x:v>
+        <x:v>800</x:v>
       </x:c>
       <x:c r="N34" s="3" t="s">
-        <x:v>808</x:v>
+        <x:v>801</x:v>
       </x:c>
       <x:c r="O34" s="3" t="s">
-        <x:v>809</x:v>
+        <x:v>802</x:v>
       </x:c>
       <x:c r="P34" s="3" t="s">
-        <x:v>810</x:v>
+        <x:v>803</x:v>
       </x:c>
       <x:c r="Q34" s="3" t="s">
-        <x:v>811</x:v>
+        <x:v>804</x:v>
       </x:c>
       <x:c r="R34" s="3" t="s">
-        <x:v>812</x:v>
+        <x:v>805</x:v>
       </x:c>
       <x:c r="S34" s="3" t="s">
         <x:v>323</x:v>
       </x:c>
       <x:c r="T34" s="3" t="s">
-        <x:v>813</x:v>
+        <x:v>806</x:v>
       </x:c>
       <x:c r="U34" s="3" t="s">
         <x:v>52</x:v>
@@ -10865,31 +10844,31 @@
     </x:row>
     <x:row r="35" ht="93.25" hidden="0">
       <x:c r="A35" s="3" t="s">
-        <x:v>814</x:v>
+        <x:v>807</x:v>
       </x:c>
       <x:c r="B35" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C35" s="3" t="s">
-        <x:v>815</x:v>
+        <x:v>808</x:v>
       </x:c>
       <x:c r="D35" s="3" t="s">
-        <x:v>816</x:v>
+        <x:v>809</x:v>
       </x:c>
       <x:c r="E35" s="3" t="s">
-        <x:v>817</x:v>
+        <x:v>810</x:v>
       </x:c>
       <x:c r="F35" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G35" s="3" t="s">
-        <x:v>432</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="H35" s="3" t="s">
-        <x:v>433</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="I35" s="3" t="s">
-        <x:v>434</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="J35" s="3" t="s">
         <x:v>41</x:v>
@@ -10898,31 +10877,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L35" s="3" t="s">
+        <x:v>811</x:v>
+      </x:c>
+      <x:c r="M35" s="3" t="s">
+        <x:v>812</x:v>
+      </x:c>
+      <x:c r="N35" s="3" t="s">
+        <x:v>813</x:v>
+      </x:c>
+      <x:c r="O35" s="3" t="s">
+        <x:v>588</x:v>
+      </x:c>
+      <x:c r="P35" s="3" t="s">
+        <x:v>814</x:v>
+      </x:c>
+      <x:c r="Q35" s="3" t="s">
+        <x:v>815</x:v>
+      </x:c>
+      <x:c r="R35" s="3" t="s">
+        <x:v>816</x:v>
+      </x:c>
+      <x:c r="S35" s="3" t="s">
+        <x:v>817</x:v>
+      </x:c>
+      <x:c r="T35" s="3" t="s">
         <x:v>818</x:v>
-      </x:c>
-      <x:c r="M35" s="3" t="s">
-        <x:v>819</x:v>
-      </x:c>
-      <x:c r="N35" s="3" t="s">
-        <x:v>820</x:v>
-      </x:c>
-      <x:c r="O35" s="3" t="s">
-        <x:v>595</x:v>
-      </x:c>
-      <x:c r="P35" s="3" t="s">
-        <x:v>821</x:v>
-      </x:c>
-      <x:c r="Q35" s="3" t="s">
-        <x:v>822</x:v>
-      </x:c>
-      <x:c r="R35" s="3" t="s">
-        <x:v>823</x:v>
-      </x:c>
-      <x:c r="S35" s="3" t="s">
-        <x:v>824</x:v>
-      </x:c>
-      <x:c r="T35" s="3" t="s">
-        <x:v>825</x:v>
       </x:c>
       <x:c r="U35" s="3" t="s">
         <x:v>52</x:v>
@@ -10930,31 +10909,31 @@
     </x:row>
     <x:row r="36" ht="93.25" hidden="0">
       <x:c r="A36" s="3" t="s">
-        <x:v>826</x:v>
+        <x:v>819</x:v>
       </x:c>
       <x:c r="B36" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C36" s="3" t="s">
-        <x:v>827</x:v>
+        <x:v>820</x:v>
       </x:c>
       <x:c r="D36" s="3" t="s">
-        <x:v>828</x:v>
+        <x:v>821</x:v>
       </x:c>
       <x:c r="E36" s="3" t="s">
-        <x:v>829</x:v>
+        <x:v>822</x:v>
       </x:c>
       <x:c r="F36" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G36" s="3" t="s">
-        <x:v>432</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="H36" s="3" t="s">
-        <x:v>433</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="I36" s="3" t="s">
-        <x:v>434</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="J36" s="3" t="s">
         <x:v>41</x:v>
@@ -10963,31 +10942,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L36" s="3" t="s">
+        <x:v>823</x:v>
+      </x:c>
+      <x:c r="M36" s="3" t="s">
+        <x:v>441</x:v>
+      </x:c>
+      <x:c r="N36" s="3" t="s">
+        <x:v>824</x:v>
+      </x:c>
+      <x:c r="O36" s="3" t="s">
+        <x:v>825</x:v>
+      </x:c>
+      <x:c r="P36" s="3" t="s">
+        <x:v>826</x:v>
+      </x:c>
+      <x:c r="Q36" s="3" t="s">
+        <x:v>827</x:v>
+      </x:c>
+      <x:c r="R36" s="3" t="s">
+        <x:v>828</x:v>
+      </x:c>
+      <x:c r="S36" s="3" t="s">
+        <x:v>829</x:v>
+      </x:c>
+      <x:c r="T36" s="3" t="s">
         <x:v>830</x:v>
-      </x:c>
-      <x:c r="M36" s="3" t="s">
-        <x:v>436</x:v>
-      </x:c>
-      <x:c r="N36" s="3" t="s">
-        <x:v>831</x:v>
-      </x:c>
-      <x:c r="O36" s="3" t="s">
-        <x:v>832</x:v>
-      </x:c>
-      <x:c r="P36" s="3" t="s">
-        <x:v>833</x:v>
-      </x:c>
-      <x:c r="Q36" s="3" t="s">
-        <x:v>834</x:v>
-      </x:c>
-      <x:c r="R36" s="3" t="s">
-        <x:v>835</x:v>
-      </x:c>
-      <x:c r="S36" s="3" t="s">
-        <x:v>836</x:v>
-      </x:c>
-      <x:c r="T36" s="3" t="s">
-        <x:v>837</x:v>
       </x:c>
       <x:c r="U36" s="3" t="s">
         <x:v>52</x:v>
@@ -10995,31 +10974,31 @@
     </x:row>
     <x:row r="37" ht="93.25" hidden="0">
       <x:c r="A37" s="3" t="s">
-        <x:v>838</x:v>
+        <x:v>831</x:v>
       </x:c>
       <x:c r="B37" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C37" s="3" t="s">
-        <x:v>839</x:v>
+        <x:v>832</x:v>
       </x:c>
       <x:c r="D37" s="3" t="s">
-        <x:v>840</x:v>
+        <x:v>833</x:v>
       </x:c>
       <x:c r="E37" s="3" t="s">
-        <x:v>841</x:v>
+        <x:v>834</x:v>
       </x:c>
       <x:c r="F37" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G37" s="3" t="s">
-        <x:v>432</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="H37" s="3" t="s">
-        <x:v>433</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="I37" s="3" t="s">
-        <x:v>434</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="J37" s="3" t="s">
         <x:v>41</x:v>
@@ -11028,31 +11007,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L37" s="3" t="s">
+        <x:v>835</x:v>
+      </x:c>
+      <x:c r="M37" s="3" t="s">
+        <x:v>836</x:v>
+      </x:c>
+      <x:c r="N37" s="3" t="s">
+        <x:v>837</x:v>
+      </x:c>
+      <x:c r="O37" s="3" t="s">
+        <x:v>838</x:v>
+      </x:c>
+      <x:c r="P37" s="3" t="s">
+        <x:v>839</x:v>
+      </x:c>
+      <x:c r="Q37" s="3" t="s">
+        <x:v>840</x:v>
+      </x:c>
+      <x:c r="R37" s="3" t="s">
+        <x:v>841</x:v>
+      </x:c>
+      <x:c r="S37" s="3" t="s">
         <x:v>842</x:v>
       </x:c>
-      <x:c r="M37" s="3" t="s">
-        <x:v>843</x:v>
-      </x:c>
-      <x:c r="N37" s="3" t="s">
-        <x:v>844</x:v>
-      </x:c>
-      <x:c r="O37" s="3" t="s">
-        <x:v>845</x:v>
-      </x:c>
-      <x:c r="P37" s="3" t="s">
-        <x:v>846</x:v>
-      </x:c>
-      <x:c r="Q37" s="3" t="s">
-        <x:v>847</x:v>
-      </x:c>
-      <x:c r="R37" s="3" t="s">
-        <x:v>848</x:v>
-      </x:c>
-      <x:c r="S37" s="3" t="s">
-        <x:v>849</x:v>
-      </x:c>
       <x:c r="T37" s="3" t="s">
-        <x:v>843</x:v>
+        <x:v>836</x:v>
       </x:c>
       <x:c r="U37" s="3" t="s">
         <x:v>52</x:v>
@@ -11060,31 +11039,31 @@
     </x:row>
     <x:row r="38" ht="93.25" hidden="0">
       <x:c r="A38" s="3" t="s">
-        <x:v>850</x:v>
+        <x:v>843</x:v>
       </x:c>
       <x:c r="B38" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C38" s="3" t="s">
-        <x:v>851</x:v>
+        <x:v>844</x:v>
       </x:c>
       <x:c r="D38" s="3" t="s">
-        <x:v>852</x:v>
+        <x:v>845</x:v>
       </x:c>
       <x:c r="E38" s="3" t="s">
-        <x:v>853</x:v>
+        <x:v>846</x:v>
       </x:c>
       <x:c r="F38" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G38" s="3" t="s">
-        <x:v>432</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="H38" s="3" t="s">
-        <x:v>433</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="I38" s="3" t="s">
-        <x:v>434</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="J38" s="3" t="s">
         <x:v>41</x:v>
@@ -11093,31 +11072,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L38" s="3" t="s">
+        <x:v>847</x:v>
+      </x:c>
+      <x:c r="M38" s="3" t="s">
+        <x:v>513</x:v>
+      </x:c>
+      <x:c r="N38" s="3" t="s">
+        <x:v>848</x:v>
+      </x:c>
+      <x:c r="O38" s="3" t="s">
+        <x:v>849</x:v>
+      </x:c>
+      <x:c r="P38" s="3" t="s">
+        <x:v>850</x:v>
+      </x:c>
+      <x:c r="Q38" s="3" t="s">
+        <x:v>851</x:v>
+      </x:c>
+      <x:c r="R38" s="3" t="s">
+        <x:v>852</x:v>
+      </x:c>
+      <x:c r="S38" s="3" t="s">
+        <x:v>853</x:v>
+      </x:c>
+      <x:c r="T38" s="3" t="s">
         <x:v>854</x:v>
-      </x:c>
-      <x:c r="M38" s="3" t="s">
-        <x:v>520</x:v>
-      </x:c>
-      <x:c r="N38" s="3" t="s">
-        <x:v>855</x:v>
-      </x:c>
-      <x:c r="O38" s="3" t="s">
-        <x:v>856</x:v>
-      </x:c>
-      <x:c r="P38" s="3" t="s">
-        <x:v>857</x:v>
-      </x:c>
-      <x:c r="Q38" s="3" t="s">
-        <x:v>858</x:v>
-      </x:c>
-      <x:c r="R38" s="3" t="s">
-        <x:v>859</x:v>
-      </x:c>
-      <x:c r="S38" s="3" t="s">
-        <x:v>860</x:v>
-      </x:c>
-      <x:c r="T38" s="3" t="s">
-        <x:v>861</x:v>
       </x:c>
       <x:c r="U38" s="3" t="s">
         <x:v>52</x:v>
@@ -11125,31 +11104,31 @@
     </x:row>
     <x:row r="39" ht="93.25" hidden="0">
       <x:c r="A39" s="3" t="s">
-        <x:v>862</x:v>
+        <x:v>855</x:v>
       </x:c>
       <x:c r="B39" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C39" s="3" t="s">
-        <x:v>863</x:v>
+        <x:v>856</x:v>
       </x:c>
       <x:c r="D39" s="3" t="s">
-        <x:v>864</x:v>
+        <x:v>857</x:v>
       </x:c>
       <x:c r="E39" s="3" t="s">
-        <x:v>865</x:v>
+        <x:v>858</x:v>
       </x:c>
       <x:c r="F39" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G39" s="3" t="s">
-        <x:v>432</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="H39" s="3" t="s">
-        <x:v>433</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="I39" s="3" t="s">
-        <x:v>434</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="J39" s="3" t="s">
         <x:v>41</x:v>
@@ -11158,31 +11137,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="L39" s="3" t="s">
+        <x:v>859</x:v>
+      </x:c>
+      <x:c r="M39" s="3" t="s">
+        <x:v>441</x:v>
+      </x:c>
+      <x:c r="N39" s="3" t="s">
+        <x:v>860</x:v>
+      </x:c>
+      <x:c r="O39" s="3" t="s">
+        <x:v>861</x:v>
+      </x:c>
+      <x:c r="P39" s="3" t="s">
+        <x:v>862</x:v>
+      </x:c>
+      <x:c r="Q39" s="3" t="s">
+        <x:v>863</x:v>
+      </x:c>
+      <x:c r="R39" s="3" t="s">
+        <x:v>864</x:v>
+      </x:c>
+      <x:c r="S39" s="3" t="s">
+        <x:v>865</x:v>
+      </x:c>
+      <x:c r="T39" s="3" t="s">
         <x:v>866</x:v>
-      </x:c>
-      <x:c r="M39" s="3" t="s">
-        <x:v>436</x:v>
-      </x:c>
-      <x:c r="N39" s="3" t="s">
-        <x:v>867</x:v>
-      </x:c>
-      <x:c r="O39" s="3" t="s">
-        <x:v>868</x:v>
-      </x:c>
-      <x:c r="P39" s="3" t="s">
-        <x:v>869</x:v>
-      </x:c>
-      <x:c r="Q39" s="3" t="s">
-        <x:v>870</x:v>
-      </x:c>
-      <x:c r="R39" s="3" t="s">
-        <x:v>871</x:v>
-      </x:c>
-      <x:c r="S39" s="3" t="s">
-        <x:v>872</x:v>
-      </x:c>
-      <x:c r="T39" s="3" t="s">
-        <x:v>873</x:v>
       </x:c>
       <x:c r="U39" s="3" t="s">
         <x:v>52</x:v>
@@ -11191,7 +11170,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4ae975070f7d497f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2bf8183517df4b53"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/maliev-feature-user-story-status.xlsx
+++ b/docs/maliev-feature-user-story-status.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Ra26f12b8e7fa4d27"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="R525fec7d9367427c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R2b99b88183644f38"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="Rbed96323f16e44bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rb79f44cd060f4a0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="Rc46d8898b102415f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="Rfba5588294bb4b1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="R773f79cca795430d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1321,7 +1321,22 @@
     <x:t xml:space="preserve">As a customer, I can receive streamed agent responses.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Streaming endpoint returns structured response chunks and the UI keeps thread/composer layout stable.</x:t>
+    <x:t xml:space="preserve">QuoteEngine BFF, Agent model</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Streamed chat turns</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">QE-005</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Agent state and history</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">As a returning customer, I can reload session state and chat history.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">BFF exposes session state and message history by session id with authorization boundaries.</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Automated QuoteEngine suite passed 2026-06-23 after workspace cleanup</x:t>
@@ -1333,46 +1348,10 @@
     <x:t xml:space="preserve">No fix needed for this story from current QuoteEngine automated retest.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Composer -&gt; messages/stream -&gt; streaming agent response</x:t>
+    <x:t xml:space="preserve">Shell/session restore -&gt; AgentController sessions/messages -&gt; SessionStore</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">QuoteAgentLaunchShell.razor</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Streaming response thread</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">AgentController POST messages/stream</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QuoteAgentEndpointTests stream events; QuoteAgentLaunchShell source tests | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QuoteEngine BFF, Agent model</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Streamed chat turns</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Needs interrupted-stream browser test</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">AgentController.cs:76</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QE-005</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Agent state and history</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">As a returning customer, I can reload session state and chat history.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">BFF exposes session state and message history by session id with authorization boundaries.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Shell/session restore -&gt; AgentController sessions/messages -&gt; SessionStore</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Session reload/history</x:t>
@@ -5183,7 +5162,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd659e5451b6047aa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2ec510e4a734287"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8599,7 +8578,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R26783c875c8e4b25"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb9839dc17aa49fc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8905,85 +8884,85 @@
       <x:c r="D5" s="3" t="s">
         <x:v>435</x:v>
       </x:c>
-      <x:c r="E5" s="3" t="s">
-        <x:v>436</x:v>
+      <x:c r="E5" s="3" t="str">
+        <x:v>The agent stream endpoint returns newline-delimited stream events, emits incremental grounded assistant deltas before one final state response, disables proxy buffering, and falls back to a final state when the downstream chatbot stream fails.</x:v>
       </x:c>
       <x:c r="F5" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="G5" s="3" t="s">
-        <x:v>437</x:v>
-      </x:c>
-      <x:c r="H5" s="3" t="s">
-        <x:v>438</x:v>
-      </x:c>
-      <x:c r="I5" s="3" t="s">
-        <x:v>439</x:v>
-      </x:c>
-      <x:c r="J5" s="3" t="s">
-        <x:v>41</x:v>
+      <x:c r="G5" s="3" t="str">
+        <x:v>Focused current-state streaming tests passed 2026-06-24.</x:v>
+      </x:c>
+      <x:c r="H5" s="3" t="str">
+        <x:v>No behavior error observed in focused streaming retest. Interrupted live browser stream handling remains unverified.</x:v>
+      </x:c>
+      <x:c r="I5" s="3" t="str">
+        <x:v>No app fix applied for this story in this slice.</x:v>
+      </x:c>
+      <x:c r="J5" s="3" t="str">
+        <x:v>Retested QuoteAgentEndpointTests.Agent_message_stream_returns_incremental_events_before_final_state, QuoteAgentEndpointTests.Agent_message_stream_returns_fallback_final_state_when_chatbot_stream_fails, and QuoteEngineSourceTests.QuoteAgentLaunchShell_has_monochrome_chatgpt_like_contract: 3/3 passed.</x:v>
       </x:c>
       <x:c r="K5" s="3" t="s">
         <x:v>188</x:v>
       </x:c>
-      <x:c r="L5" s="3" t="s">
-        <x:v>440</x:v>
-      </x:c>
-      <x:c r="M5" s="3" t="s">
-        <x:v>441</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s">
-        <x:v>442</x:v>
-      </x:c>
-      <x:c r="O5" s="3" t="s">
-        <x:v>443</x:v>
-      </x:c>
-      <x:c r="P5" s="3" t="s">
-        <x:v>444</x:v>
+      <x:c r="L5" s="3" t="str">
+        <x:v>QuoteAgentLaunchShell stream consumer -&gt; QuoteEngineApiClient NDJSON reader -&gt; AgentController stream endpoint -&gt; QuoteAgentService.StreamAsync -&gt; ChatbotService stream</x:v>
+      </x:c>
+      <x:c r="M5" s="3" t="str">
+        <x:v>QuoteAgentLaunchShell.razor HandleSubmitAsync; QuoteEngineApiClient.SendAgentMessageStreamAsync; AgentController.Stream; QuoteAgentService.StreamAsync</x:v>
+      </x:c>
+      <x:c r="N5" s="3" t="str">
+        <x:v>Composer sends through SendAgentMessageStreamAsync; stream API uses quote/v1/agent/messages/stream and reads response headers immediately.</x:v>
+      </x:c>
+      <x:c r="O5" s="3" t="str">
+        <x:v>AgentController POST quote/v1/agent/messages/stream returns application/x-ndjson, sets X-Accel-Buffering no and Cache-Control no-cache, disables response buffering, writes each QuoteAgentStreamEvent as a line, and flushes after every event. QuoteAgentService.StreamAsync emits started/thought/delta/final/error events and re-chunks grounded final assistant text.</x:v>
+      </x:c>
+      <x:c r="P5" s="3" t="str">
+        <x:v>dotnet test Maliev.QuoteEngine.slnx --filter "FullyQualifiedName~QuoteAgentEndpointTests.Agent_message_stream_returns_incremental_events_before_final_state|FullyQualifiedName~QuoteAgentEndpointTests.Agent_message_stream_returns_fallback_final_state_when_chatbot_stream_fails|FullyQualifiedName~QuoteEngineSourceTests.QuoteAgentLaunchShell_has_monochrome_chatgpt_like_contract" --verbosity minimal passed 3/3 on 2026-06-24.</x:v>
       </x:c>
       <x:c r="Q5" s="3" t="s">
-        <x:v>445</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="R5" s="3" t="s">
-        <x:v>446</x:v>
-      </x:c>
-      <x:c r="S5" s="3" t="s">
-        <x:v>447</x:v>
-      </x:c>
-      <x:c r="T5" s="3" t="s">
-        <x:v>448</x:v>
-      </x:c>
-      <x:c r="U5" s="3" t="s">
-        <x:v>52</x:v>
+        <x:v>437</x:v>
+      </x:c>
+      <x:c r="S5" s="3" t="str">
+        <x:v>Needs interrupted-stream browser test against a running QuoteEngine host.</x:v>
+      </x:c>
+      <x:c r="T5" s="3" t="str">
+        <x:v>QuoteAgentLaunchShell.razor:2817-2924; QuoteEngineApiClient.cs:329-365; AgentController.cs:76-105; QuoteAgentService.cs:247-442; QuoteAgentDtos.cs:271-286; QuoteAgentEndpointTests.cs:704-744,1290-1329; QuoteEngineSourceTests.cs:864-1310</x:v>
+      </x:c>
+      <x:c r="U5" s="3" t="str">
+        <x:v>2026-06-24</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="93.25" hidden="0">
       <x:c r="A6" s="3" t="s">
-        <x:v>449</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="B6" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C6" s="3" t="s">
-        <x:v>450</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="D6" s="3" t="s">
-        <x:v>451</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="E6" s="3" t="s">
-        <x:v>452</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="F6" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G6" s="3" t="s">
-        <x:v>437</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="H6" s="3" t="s">
-        <x:v>438</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="I6" s="3" t="s">
-        <x:v>439</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="J6" s="3" t="s">
         <x:v>41</x:v>
@@ -8992,31 +8971,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L6" s="3" t="s">
+        <x:v>445</x:v>
+      </x:c>
+      <x:c r="M6" s="3" t="s">
+        <x:v>446</x:v>
+      </x:c>
+      <x:c r="N6" s="3" t="s">
+        <x:v>447</x:v>
+      </x:c>
+      <x:c r="O6" s="3" t="s">
+        <x:v>448</x:v>
+      </x:c>
+      <x:c r="P6" s="3" t="s">
+        <x:v>449</x:v>
+      </x:c>
+      <x:c r="Q6" s="3" t="s">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="R6" s="3" t="s">
+        <x:v>451</x:v>
+      </x:c>
+      <x:c r="S6" s="3" t="s">
+        <x:v>452</x:v>
+      </x:c>
+      <x:c r="T6" s="3" t="s">
         <x:v>453</x:v>
-      </x:c>
-      <x:c r="M6" s="3" t="s">
-        <x:v>441</x:v>
-      </x:c>
-      <x:c r="N6" s="3" t="s">
-        <x:v>454</x:v>
-      </x:c>
-      <x:c r="O6" s="3" t="s">
-        <x:v>455</x:v>
-      </x:c>
-      <x:c r="P6" s="3" t="s">
-        <x:v>456</x:v>
-      </x:c>
-      <x:c r="Q6" s="3" t="s">
-        <x:v>457</x:v>
-      </x:c>
-      <x:c r="R6" s="3" t="s">
-        <x:v>458</x:v>
-      </x:c>
-      <x:c r="S6" s="3" t="s">
-        <x:v>459</x:v>
-      </x:c>
-      <x:c r="T6" s="3" t="s">
-        <x:v>460</x:v>
       </x:c>
       <x:c r="U6" s="3" t="s">
         <x:v>52</x:v>
@@ -9024,31 +9003,31 @@
     </x:row>
     <x:row r="7" ht="93.25" hidden="0">
       <x:c r="A7" s="3" t="s">
-        <x:v>461</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>462</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="D7" s="3" t="s">
-        <x:v>463</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="E7" s="3" t="s">
-        <x:v>464</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="F7" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G7" s="3" t="s">
-        <x:v>437</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="H7" s="3" t="s">
-        <x:v>438</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="I7" s="3" t="s">
-        <x:v>439</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="J7" s="3" t="s">
         <x:v>41</x:v>
@@ -9057,31 +9036,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="L7" s="3" t="s">
+        <x:v>458</x:v>
+      </x:c>
+      <x:c r="M7" s="3" t="s">
+        <x:v>446</x:v>
+      </x:c>
+      <x:c r="N7" s="3" t="s">
+        <x:v>459</x:v>
+      </x:c>
+      <x:c r="O7" s="3" t="s">
+        <x:v>460</x:v>
+      </x:c>
+      <x:c r="P7" s="3" t="s">
+        <x:v>461</x:v>
+      </x:c>
+      <x:c r="Q7" s="3" t="s">
+        <x:v>462</x:v>
+      </x:c>
+      <x:c r="R7" s="3" t="s">
+        <x:v>463</x:v>
+      </x:c>
+      <x:c r="S7" s="3" t="s">
+        <x:v>464</x:v>
+      </x:c>
+      <x:c r="T7" s="3" t="s">
         <x:v>465</x:v>
-      </x:c>
-      <x:c r="M7" s="3" t="s">
-        <x:v>441</x:v>
-      </x:c>
-      <x:c r="N7" s="3" t="s">
-        <x:v>466</x:v>
-      </x:c>
-      <x:c r="O7" s="3" t="s">
-        <x:v>467</x:v>
-      </x:c>
-      <x:c r="P7" s="3" t="s">
-        <x:v>468</x:v>
-      </x:c>
-      <x:c r="Q7" s="3" t="s">
-        <x:v>469</x:v>
-      </x:c>
-      <x:c r="R7" s="3" t="s">
-        <x:v>470</x:v>
-      </x:c>
-      <x:c r="S7" s="3" t="s">
-        <x:v>471</x:v>
-      </x:c>
-      <x:c r="T7" s="3" t="s">
-        <x:v>472</x:v>
       </x:c>
       <x:c r="U7" s="3" t="s">
         <x:v>52</x:v>
@@ -9089,31 +9068,31 @@
     </x:row>
     <x:row r="8" ht="93.25" hidden="0">
       <x:c r="A8" s="3" t="s">
-        <x:v>473</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>474</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="D8" s="3" t="s">
-        <x:v>475</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="E8" s="3" t="s">
-        <x:v>476</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="F8" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G8" s="3" t="s">
-        <x:v>437</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="H8" s="3" t="s">
-        <x:v>438</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="I8" s="3" t="s">
-        <x:v>439</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="J8" s="3" t="s">
         <x:v>41</x:v>
@@ -9122,31 +9101,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L8" s="3" t="s">
+        <x:v>470</x:v>
+      </x:c>
+      <x:c r="M8" s="3" t="s">
+        <x:v>446</x:v>
+      </x:c>
+      <x:c r="N8" s="3" t="s">
+        <x:v>471</x:v>
+      </x:c>
+      <x:c r="O8" s="3" t="s">
+        <x:v>472</x:v>
+      </x:c>
+      <x:c r="P8" s="3" t="s">
+        <x:v>473</x:v>
+      </x:c>
+      <x:c r="Q8" s="3" t="s">
+        <x:v>474</x:v>
+      </x:c>
+      <x:c r="R8" s="3" t="s">
+        <x:v>475</x:v>
+      </x:c>
+      <x:c r="S8" s="3" t="s">
+        <x:v>476</x:v>
+      </x:c>
+      <x:c r="T8" s="3" t="s">
         <x:v>477</x:v>
-      </x:c>
-      <x:c r="M8" s="3" t="s">
-        <x:v>441</x:v>
-      </x:c>
-      <x:c r="N8" s="3" t="s">
-        <x:v>478</x:v>
-      </x:c>
-      <x:c r="O8" s="3" t="s">
-        <x:v>479</x:v>
-      </x:c>
-      <x:c r="P8" s="3" t="s">
-        <x:v>480</x:v>
-      </x:c>
-      <x:c r="Q8" s="3" t="s">
-        <x:v>481</x:v>
-      </x:c>
-      <x:c r="R8" s="3" t="s">
-        <x:v>482</x:v>
-      </x:c>
-      <x:c r="S8" s="3" t="s">
-        <x:v>483</x:v>
-      </x:c>
-      <x:c r="T8" s="3" t="s">
-        <x:v>484</x:v>
       </x:c>
       <x:c r="U8" s="3" t="s">
         <x:v>52</x:v>
@@ -9154,31 +9133,31 @@
     </x:row>
     <x:row r="9" ht="93.25" hidden="0">
       <x:c r="A9" s="3" t="s">
-        <x:v>485</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="B9" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C9" s="3" t="s">
-        <x:v>486</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="D9" s="3" t="s">
-        <x:v>487</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="E9" s="3" t="s">
-        <x:v>488</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="F9" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G9" s="3" t="s">
-        <x:v>437</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="H9" s="3" t="s">
-        <x:v>438</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="I9" s="3" t="s">
-        <x:v>439</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="J9" s="3" t="s">
         <x:v>41</x:v>
@@ -9187,31 +9166,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L9" s="3" t="s">
+        <x:v>482</x:v>
+      </x:c>
+      <x:c r="M9" s="3" t="s">
+        <x:v>446</x:v>
+      </x:c>
+      <x:c r="N9" s="3" t="s">
+        <x:v>483</x:v>
+      </x:c>
+      <x:c r="O9" s="3" t="s">
+        <x:v>484</x:v>
+      </x:c>
+      <x:c r="P9" s="3" t="s">
+        <x:v>485</x:v>
+      </x:c>
+      <x:c r="Q9" s="3" t="s">
+        <x:v>486</x:v>
+      </x:c>
+      <x:c r="R9" s="3" t="s">
+        <x:v>487</x:v>
+      </x:c>
+      <x:c r="S9" s="3" t="s">
+        <x:v>488</x:v>
+      </x:c>
+      <x:c r="T9" s="3" t="s">
         <x:v>489</x:v>
-      </x:c>
-      <x:c r="M9" s="3" t="s">
-        <x:v>441</x:v>
-      </x:c>
-      <x:c r="N9" s="3" t="s">
-        <x:v>490</x:v>
-      </x:c>
-      <x:c r="O9" s="3" t="s">
-        <x:v>491</x:v>
-      </x:c>
-      <x:c r="P9" s="3" t="s">
-        <x:v>492</x:v>
-      </x:c>
-      <x:c r="Q9" s="3" t="s">
-        <x:v>493</x:v>
-      </x:c>
-      <x:c r="R9" s="3" t="s">
-        <x:v>494</x:v>
-      </x:c>
-      <x:c r="S9" s="3" t="s">
-        <x:v>495</x:v>
-      </x:c>
-      <x:c r="T9" s="3" t="s">
-        <x:v>496</x:v>
       </x:c>
       <x:c r="U9" s="3" t="s">
         <x:v>52</x:v>
@@ -9219,31 +9198,31 @@
     </x:row>
     <x:row r="10" ht="93.25" hidden="0">
       <x:c r="A10" s="3" t="s">
-        <x:v>497</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="B10" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C10" s="3" t="s">
-        <x:v>498</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="D10" s="3" t="s">
-        <x:v>499</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="E10" s="3" t="s">
-        <x:v>500</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="F10" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G10" s="3" t="s">
-        <x:v>437</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="H10" s="3" t="s">
-        <x:v>438</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="I10" s="3" t="s">
-        <x:v>439</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="J10" s="3" t="s">
         <x:v>41</x:v>
@@ -9252,31 +9231,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L10" s="3" t="s">
-        <x:v>501</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="M10" s="3" t="s">
         <x:v>424</x:v>
       </x:c>
       <x:c r="N10" s="3" t="s">
-        <x:v>502</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="O10" s="3" t="s">
         <x:v>205</x:v>
       </x:c>
       <x:c r="P10" s="3" t="s">
-        <x:v>503</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="Q10" s="3" t="s">
-        <x:v>504</x:v>
+        <x:v>497</x:v>
       </x:c>
       <x:c r="R10" s="3" t="s">
-        <x:v>505</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="S10" s="3" t="s">
-        <x:v>506</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="T10" s="3" t="s">
-        <x:v>507</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="U10" s="3" t="s">
         <x:v>52</x:v>
@@ -9284,31 +9263,31 @@
     </x:row>
     <x:row r="11" ht="93.25" hidden="0">
       <x:c r="A11" s="3" t="s">
-        <x:v>508</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="B11" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C11" s="3" t="s">
-        <x:v>509</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="D11" s="3" t="s">
-        <x:v>510</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="E11" s="3" t="s">
-        <x:v>511</x:v>
+        <x:v>504</x:v>
       </x:c>
       <x:c r="F11" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G11" s="3" t="s">
-        <x:v>437</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="H11" s="3" t="s">
-        <x:v>438</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="I11" s="3" t="s">
-        <x:v>439</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="J11" s="3" t="s">
         <x:v>41</x:v>
@@ -9317,31 +9296,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L11" s="3" t="s">
+        <x:v>505</x:v>
+      </x:c>
+      <x:c r="M11" s="3" t="s">
+        <x:v>506</x:v>
+      </x:c>
+      <x:c r="N11" s="3" t="s">
+        <x:v>507</x:v>
+      </x:c>
+      <x:c r="O11" s="3" t="s">
+        <x:v>508</x:v>
+      </x:c>
+      <x:c r="P11" s="3" t="s">
+        <x:v>509</x:v>
+      </x:c>
+      <x:c r="Q11" s="3" t="s">
+        <x:v>510</x:v>
+      </x:c>
+      <x:c r="R11" s="3" t="s">
+        <x:v>511</x:v>
+      </x:c>
+      <x:c r="S11" s="3" t="s">
         <x:v>512</x:v>
       </x:c>
-      <x:c r="M11" s="3" t="s">
+      <x:c r="T11" s="3" t="s">
         <x:v>513</x:v>
-      </x:c>
-      <x:c r="N11" s="3" t="s">
-        <x:v>514</x:v>
-      </x:c>
-      <x:c r="O11" s="3" t="s">
-        <x:v>515</x:v>
-      </x:c>
-      <x:c r="P11" s="3" t="s">
-        <x:v>516</x:v>
-      </x:c>
-      <x:c r="Q11" s="3" t="s">
-        <x:v>517</x:v>
-      </x:c>
-      <x:c r="R11" s="3" t="s">
-        <x:v>518</x:v>
-      </x:c>
-      <x:c r="S11" s="3" t="s">
-        <x:v>519</x:v>
-      </x:c>
-      <x:c r="T11" s="3" t="s">
-        <x:v>520</x:v>
       </x:c>
       <x:c r="U11" s="3" t="s">
         <x:v>52</x:v>
@@ -9349,31 +9328,31 @@
     </x:row>
     <x:row r="12" ht="107.25" hidden="0">
       <x:c r="A12" s="3" t="s">
-        <x:v>521</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="B12" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C12" s="3" t="s">
-        <x:v>522</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="D12" s="3" t="s">
-        <x:v>523</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="E12" s="3" t="s">
-        <x:v>524</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="F12" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G12" s="3" t="s">
-        <x:v>437</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="H12" s="3" t="s">
-        <x:v>438</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="I12" s="3" t="s">
-        <x:v>439</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="J12" s="3" t="s">
         <x:v>41</x:v>
@@ -9382,31 +9361,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L12" s="3" t="s">
+        <x:v>518</x:v>
+      </x:c>
+      <x:c r="M12" s="3" t="s">
+        <x:v>446</x:v>
+      </x:c>
+      <x:c r="N12" s="3" t="s">
+        <x:v>519</x:v>
+      </x:c>
+      <x:c r="O12" s="3" t="s">
+        <x:v>520</x:v>
+      </x:c>
+      <x:c r="P12" s="3" t="s">
+        <x:v>521</x:v>
+      </x:c>
+      <x:c r="Q12" s="3" t="s">
+        <x:v>522</x:v>
+      </x:c>
+      <x:c r="R12" s="3" t="s">
+        <x:v>523</x:v>
+      </x:c>
+      <x:c r="S12" s="3" t="s">
+        <x:v>524</x:v>
+      </x:c>
+      <x:c r="T12" s="3" t="s">
         <x:v>525</x:v>
-      </x:c>
-      <x:c r="M12" s="3" t="s">
-        <x:v>441</x:v>
-      </x:c>
-      <x:c r="N12" s="3" t="s">
-        <x:v>526</x:v>
-      </x:c>
-      <x:c r="O12" s="3" t="s">
-        <x:v>527</x:v>
-      </x:c>
-      <x:c r="P12" s="3" t="s">
-        <x:v>528</x:v>
-      </x:c>
-      <x:c r="Q12" s="3" t="s">
-        <x:v>529</x:v>
-      </x:c>
-      <x:c r="R12" s="3" t="s">
-        <x:v>530</x:v>
-      </x:c>
-      <x:c r="S12" s="3" t="s">
-        <x:v>531</x:v>
-      </x:c>
-      <x:c r="T12" s="3" t="s">
-        <x:v>532</x:v>
       </x:c>
       <x:c r="U12" s="3" t="s">
         <x:v>52</x:v>
@@ -9414,31 +9393,31 @@
     </x:row>
     <x:row r="13" ht="93.25" hidden="0">
       <x:c r="A13" s="3" t="s">
-        <x:v>533</x:v>
+        <x:v>526</x:v>
       </x:c>
       <x:c r="B13" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C13" s="3" t="s">
-        <x:v>534</x:v>
+        <x:v>527</x:v>
       </x:c>
       <x:c r="D13" s="3" t="s">
-        <x:v>535</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="E13" s="3" t="s">
-        <x:v>536</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="F13" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G13" s="3" t="s">
-        <x:v>437</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="H13" s="3" t="s">
-        <x:v>438</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="I13" s="3" t="s">
-        <x:v>439</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="J13" s="3" t="s">
         <x:v>41</x:v>
@@ -9447,31 +9426,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L13" s="3" t="s">
-        <x:v>537</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="M13" s="3" t="s">
-        <x:v>441</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="N13" s="3" t="s">
-        <x:v>538</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="O13" s="3" t="s">
-        <x:v>539</x:v>
+        <x:v>532</x:v>
       </x:c>
       <x:c r="P13" s="3" t="s">
-        <x:v>540</x:v>
+        <x:v>533</x:v>
       </x:c>
       <x:c r="Q13" s="3" t="s">
-        <x:v>529</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="R13" s="3" t="s">
-        <x:v>541</x:v>
+        <x:v>534</x:v>
       </x:c>
       <x:c r="S13" s="3" t="s">
-        <x:v>542</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="T13" s="3" t="s">
-        <x:v>543</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="U13" s="3" t="s">
         <x:v>52</x:v>
@@ -9479,31 +9458,31 @@
     </x:row>
     <x:row r="14" ht="93.25" hidden="0">
       <x:c r="A14" s="3" t="s">
-        <x:v>544</x:v>
+        <x:v>537</x:v>
       </x:c>
       <x:c r="B14" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C14" s="3" t="s">
-        <x:v>545</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="D14" s="3" t="s">
-        <x:v>546</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="E14" s="3" t="s">
-        <x:v>547</x:v>
+        <x:v>540</x:v>
       </x:c>
       <x:c r="F14" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G14" s="3" t="s">
-        <x:v>437</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="H14" s="3" t="s">
-        <x:v>438</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="I14" s="3" t="s">
-        <x:v>439</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="J14" s="3" t="s">
         <x:v>41</x:v>
@@ -9512,31 +9491,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L14" s="3" t="s">
+        <x:v>541</x:v>
+      </x:c>
+      <x:c r="M14" s="3" t="s">
+        <x:v>542</x:v>
+      </x:c>
+      <x:c r="N14" s="3" t="s">
+        <x:v>543</x:v>
+      </x:c>
+      <x:c r="O14" s="3" t="s">
+        <x:v>544</x:v>
+      </x:c>
+      <x:c r="P14" s="3" t="s">
+        <x:v>545</x:v>
+      </x:c>
+      <x:c r="Q14" s="3" t="s">
+        <x:v>546</x:v>
+      </x:c>
+      <x:c r="R14" s="3" t="s">
+        <x:v>547</x:v>
+      </x:c>
+      <x:c r="S14" s="3" t="s">
         <x:v>548</x:v>
       </x:c>
-      <x:c r="M14" s="3" t="s">
+      <x:c r="T14" s="3" t="s">
         <x:v>549</x:v>
-      </x:c>
-      <x:c r="N14" s="3" t="s">
-        <x:v>550</x:v>
-      </x:c>
-      <x:c r="O14" s="3" t="s">
-        <x:v>551</x:v>
-      </x:c>
-      <x:c r="P14" s="3" t="s">
-        <x:v>552</x:v>
-      </x:c>
-      <x:c r="Q14" s="3" t="s">
-        <x:v>553</x:v>
-      </x:c>
-      <x:c r="R14" s="3" t="s">
-        <x:v>554</x:v>
-      </x:c>
-      <x:c r="S14" s="3" t="s">
-        <x:v>555</x:v>
-      </x:c>
-      <x:c r="T14" s="3" t="s">
-        <x:v>556</x:v>
       </x:c>
       <x:c r="U14" s="3" t="s">
         <x:v>52</x:v>
@@ -9544,31 +9523,31 @@
     </x:row>
     <x:row r="15" ht="107.25" hidden="0">
       <x:c r="A15" s="3" t="s">
-        <x:v>557</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="B15" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C15" s="3" t="s">
-        <x:v>558</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="D15" s="3" t="s">
-        <x:v>559</x:v>
+        <x:v>552</x:v>
       </x:c>
       <x:c r="E15" s="3" t="s">
-        <x:v>560</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="F15" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G15" s="3" t="s">
-        <x:v>437</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="H15" s="3" t="s">
-        <x:v>438</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="I15" s="3" t="s">
-        <x:v>439</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="J15" s="3" t="s">
         <x:v>41</x:v>
@@ -9577,31 +9556,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L15" s="3" t="s">
+        <x:v>554</x:v>
+      </x:c>
+      <x:c r="M15" s="3" t="s">
+        <x:v>446</x:v>
+      </x:c>
+      <x:c r="N15" s="3" t="s">
+        <x:v>555</x:v>
+      </x:c>
+      <x:c r="O15" s="3" t="s">
+        <x:v>556</x:v>
+      </x:c>
+      <x:c r="P15" s="3" t="s">
+        <x:v>557</x:v>
+      </x:c>
+      <x:c r="Q15" s="3" t="s">
+        <x:v>558</x:v>
+      </x:c>
+      <x:c r="R15" s="3" t="s">
+        <x:v>559</x:v>
+      </x:c>
+      <x:c r="S15" s="3" t="s">
+        <x:v>560</x:v>
+      </x:c>
+      <x:c r="T15" s="3" t="s">
         <x:v>561</x:v>
-      </x:c>
-      <x:c r="M15" s="3" t="s">
-        <x:v>441</x:v>
-      </x:c>
-      <x:c r="N15" s="3" t="s">
-        <x:v>562</x:v>
-      </x:c>
-      <x:c r="O15" s="3" t="s">
-        <x:v>563</x:v>
-      </x:c>
-      <x:c r="P15" s="3" t="s">
-        <x:v>564</x:v>
-      </x:c>
-      <x:c r="Q15" s="3" t="s">
-        <x:v>565</x:v>
-      </x:c>
-      <x:c r="R15" s="3" t="s">
-        <x:v>566</x:v>
-      </x:c>
-      <x:c r="S15" s="3" t="s">
-        <x:v>567</x:v>
-      </x:c>
-      <x:c r="T15" s="3" t="s">
-        <x:v>568</x:v>
       </x:c>
       <x:c r="U15" s="3" t="s">
         <x:v>52</x:v>
@@ -9609,31 +9588,31 @@
     </x:row>
     <x:row r="16" ht="107.25" hidden="0">
       <x:c r="A16" s="3" t="s">
-        <x:v>569</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="B16" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C16" s="3" t="s">
-        <x:v>570</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="D16" s="3" t="s">
-        <x:v>571</x:v>
+        <x:v>564</x:v>
       </x:c>
       <x:c r="E16" s="3" t="s">
-        <x:v>572</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="F16" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G16" s="3" t="s">
-        <x:v>437</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="H16" s="3" t="s">
-        <x:v>438</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="I16" s="3" t="s">
-        <x:v>439</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="J16" s="3" t="s">
         <x:v>41</x:v>
@@ -9642,31 +9621,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L16" s="3" t="s">
+        <x:v>566</x:v>
+      </x:c>
+      <x:c r="M16" s="3" t="s">
+        <x:v>446</x:v>
+      </x:c>
+      <x:c r="N16" s="3" t="s">
+        <x:v>567</x:v>
+      </x:c>
+      <x:c r="O16" s="3" t="s">
+        <x:v>568</x:v>
+      </x:c>
+      <x:c r="P16" s="3" t="s">
+        <x:v>569</x:v>
+      </x:c>
+      <x:c r="Q16" s="3" t="s">
+        <x:v>570</x:v>
+      </x:c>
+      <x:c r="R16" s="3" t="s">
+        <x:v>571</x:v>
+      </x:c>
+      <x:c r="S16" s="3" t="s">
+        <x:v>572</x:v>
+      </x:c>
+      <x:c r="T16" s="3" t="s">
         <x:v>573</x:v>
-      </x:c>
-      <x:c r="M16" s="3" t="s">
-        <x:v>441</x:v>
-      </x:c>
-      <x:c r="N16" s="3" t="s">
-        <x:v>574</x:v>
-      </x:c>
-      <x:c r="O16" s="3" t="s">
-        <x:v>575</x:v>
-      </x:c>
-      <x:c r="P16" s="3" t="s">
-        <x:v>576</x:v>
-      </x:c>
-      <x:c r="Q16" s="3" t="s">
-        <x:v>577</x:v>
-      </x:c>
-      <x:c r="R16" s="3" t="s">
-        <x:v>578</x:v>
-      </x:c>
-      <x:c r="S16" s="3" t="s">
-        <x:v>579</x:v>
-      </x:c>
-      <x:c r="T16" s="3" t="s">
-        <x:v>580</x:v>
       </x:c>
       <x:c r="U16" s="3" t="s">
         <x:v>52</x:v>
@@ -9674,31 +9653,31 @@
     </x:row>
     <x:row r="17" ht="93.25" hidden="0">
       <x:c r="A17" s="3" t="s">
-        <x:v>581</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="B17" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C17" s="3" t="s">
-        <x:v>582</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="D17" s="3" t="s">
-        <x:v>583</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="E17" s="3" t="s">
-        <x:v>584</x:v>
+        <x:v>577</x:v>
       </x:c>
       <x:c r="F17" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G17" s="3" t="s">
-        <x:v>437</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="H17" s="3" t="s">
-        <x:v>438</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="I17" s="3" t="s">
-        <x:v>439</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="J17" s="3" t="s">
         <x:v>41</x:v>
@@ -9707,31 +9686,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L17" s="3" t="s">
+        <x:v>578</x:v>
+      </x:c>
+      <x:c r="M17" s="3" t="s">
+        <x:v>579</x:v>
+      </x:c>
+      <x:c r="N17" s="3" t="s">
+        <x:v>580</x:v>
+      </x:c>
+      <x:c r="O17" s="3" t="s">
+        <x:v>581</x:v>
+      </x:c>
+      <x:c r="P17" s="3" t="s">
+        <x:v>582</x:v>
+      </x:c>
+      <x:c r="Q17" s="3" t="s">
+        <x:v>583</x:v>
+      </x:c>
+      <x:c r="R17" s="3" t="s">
+        <x:v>584</x:v>
+      </x:c>
+      <x:c r="S17" s="3" t="s">
         <x:v>585</x:v>
       </x:c>
-      <x:c r="M17" s="3" t="s">
+      <x:c r="T17" s="3" t="s">
         <x:v>586</x:v>
-      </x:c>
-      <x:c r="N17" s="3" t="s">
-        <x:v>587</x:v>
-      </x:c>
-      <x:c r="O17" s="3" t="s">
-        <x:v>588</x:v>
-      </x:c>
-      <x:c r="P17" s="3" t="s">
-        <x:v>589</x:v>
-      </x:c>
-      <x:c r="Q17" s="3" t="s">
-        <x:v>590</x:v>
-      </x:c>
-      <x:c r="R17" s="3" t="s">
-        <x:v>591</x:v>
-      </x:c>
-      <x:c r="S17" s="3" t="s">
-        <x:v>592</x:v>
-      </x:c>
-      <x:c r="T17" s="3" t="s">
-        <x:v>593</x:v>
       </x:c>
       <x:c r="U17" s="3" t="s">
         <x:v>52</x:v>
@@ -9739,31 +9718,31 @@
     </x:row>
     <x:row r="18" ht="93.25" hidden="0">
       <x:c r="A18" s="3" t="s">
-        <x:v>594</x:v>
+        <x:v>587</x:v>
       </x:c>
       <x:c r="B18" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C18" s="3" t="s">
-        <x:v>595</x:v>
+        <x:v>588</x:v>
       </x:c>
       <x:c r="D18" s="3" t="s">
-        <x:v>596</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="E18" s="3" t="s">
-        <x:v>597</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="F18" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G18" s="3" t="s">
-        <x:v>437</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="H18" s="3" t="s">
-        <x:v>438</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="I18" s="3" t="s">
-        <x:v>439</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="J18" s="3" t="s">
         <x:v>41</x:v>
@@ -9772,31 +9751,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L18" s="3" t="s">
+        <x:v>591</x:v>
+      </x:c>
+      <x:c r="M18" s="3" t="s">
+        <x:v>592</x:v>
+      </x:c>
+      <x:c r="N18" s="3" t="s">
+        <x:v>593</x:v>
+      </x:c>
+      <x:c r="O18" s="3" t="s">
+        <x:v>594</x:v>
+      </x:c>
+      <x:c r="P18" s="3" t="s">
+        <x:v>595</x:v>
+      </x:c>
+      <x:c r="Q18" s="3" t="s">
+        <x:v>596</x:v>
+      </x:c>
+      <x:c r="R18" s="3" t="s">
+        <x:v>597</x:v>
+      </x:c>
+      <x:c r="S18" s="3" t="s">
         <x:v>598</x:v>
       </x:c>
-      <x:c r="M18" s="3" t="s">
+      <x:c r="T18" s="3" t="s">
         <x:v>599</x:v>
-      </x:c>
-      <x:c r="N18" s="3" t="s">
-        <x:v>600</x:v>
-      </x:c>
-      <x:c r="O18" s="3" t="s">
-        <x:v>601</x:v>
-      </x:c>
-      <x:c r="P18" s="3" t="s">
-        <x:v>602</x:v>
-      </x:c>
-      <x:c r="Q18" s="3" t="s">
-        <x:v>603</x:v>
-      </x:c>
-      <x:c r="R18" s="3" t="s">
-        <x:v>604</x:v>
-      </x:c>
-      <x:c r="S18" s="3" t="s">
-        <x:v>605</x:v>
-      </x:c>
-      <x:c r="T18" s="3" t="s">
-        <x:v>606</x:v>
       </x:c>
       <x:c r="U18" s="3" t="s">
         <x:v>52</x:v>
@@ -9804,31 +9783,31 @@
     </x:row>
     <x:row r="19" ht="93.25" hidden="0">
       <x:c r="A19" s="3" t="s">
-        <x:v>607</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="B19" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C19" s="3" t="s">
-        <x:v>608</x:v>
+        <x:v>601</x:v>
       </x:c>
       <x:c r="D19" s="3" t="s">
-        <x:v>609</x:v>
+        <x:v>602</x:v>
       </x:c>
       <x:c r="E19" s="3" t="s">
-        <x:v>610</x:v>
+        <x:v>603</x:v>
       </x:c>
       <x:c r="F19" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G19" s="3" t="s">
-        <x:v>437</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="H19" s="3" t="s">
-        <x:v>438</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="I19" s="3" t="s">
-        <x:v>439</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="J19" s="3" t="s">
         <x:v>41</x:v>
@@ -9837,31 +9816,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L19" s="3" t="s">
+        <x:v>604</x:v>
+      </x:c>
+      <x:c r="M19" s="3" t="s">
+        <x:v>605</x:v>
+      </x:c>
+      <x:c r="N19" s="3" t="s">
+        <x:v>606</x:v>
+      </x:c>
+      <x:c r="O19" s="3" t="s">
+        <x:v>607</x:v>
+      </x:c>
+      <x:c r="P19" s="3" t="s">
+        <x:v>608</x:v>
+      </x:c>
+      <x:c r="Q19" s="3" t="s">
+        <x:v>609</x:v>
+      </x:c>
+      <x:c r="R19" s="3" t="s">
+        <x:v>610</x:v>
+      </x:c>
+      <x:c r="S19" s="3" t="s">
         <x:v>611</x:v>
       </x:c>
-      <x:c r="M19" s="3" t="s">
+      <x:c r="T19" s="3" t="s">
         <x:v>612</x:v>
-      </x:c>
-      <x:c r="N19" s="3" t="s">
-        <x:v>613</x:v>
-      </x:c>
-      <x:c r="O19" s="3" t="s">
-        <x:v>614</x:v>
-      </x:c>
-      <x:c r="P19" s="3" t="s">
-        <x:v>615</x:v>
-      </x:c>
-      <x:c r="Q19" s="3" t="s">
-        <x:v>616</x:v>
-      </x:c>
-      <x:c r="R19" s="3" t="s">
-        <x:v>617</x:v>
-      </x:c>
-      <x:c r="S19" s="3" t="s">
-        <x:v>618</x:v>
-      </x:c>
-      <x:c r="T19" s="3" t="s">
-        <x:v>619</x:v>
       </x:c>
       <x:c r="U19" s="3" t="s">
         <x:v>52</x:v>
@@ -9869,31 +9848,31 @@
     </x:row>
     <x:row r="20" ht="79.25" hidden="0">
       <x:c r="A20" s="3" t="s">
-        <x:v>620</x:v>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="B20" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C20" s="3" t="s">
-        <x:v>621</x:v>
+        <x:v>614</x:v>
       </x:c>
       <x:c r="D20" s="3" t="s">
-        <x:v>622</x:v>
+        <x:v>615</x:v>
       </x:c>
       <x:c r="E20" s="3" t="s">
-        <x:v>623</x:v>
+        <x:v>616</x:v>
       </x:c>
       <x:c r="F20" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G20" s="3" t="s">
-        <x:v>437</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="H20" s="3" t="s">
-        <x:v>438</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="I20" s="3" t="s">
-        <x:v>439</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="J20" s="3" t="s">
         <x:v>41</x:v>
@@ -9902,31 +9881,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L20" s="3" t="s">
+        <x:v>617</x:v>
+      </x:c>
+      <x:c r="M20" s="3" t="s">
+        <x:v>618</x:v>
+      </x:c>
+      <x:c r="N20" s="3" t="s">
+        <x:v>619</x:v>
+      </x:c>
+      <x:c r="O20" s="3" t="s">
+        <x:v>620</x:v>
+      </x:c>
+      <x:c r="P20" s="3" t="s">
+        <x:v>621</x:v>
+      </x:c>
+      <x:c r="Q20" s="3" t="s">
+        <x:v>622</x:v>
+      </x:c>
+      <x:c r="R20" s="3" t="s">
+        <x:v>623</x:v>
+      </x:c>
+      <x:c r="S20" s="3" t="s">
         <x:v>624</x:v>
       </x:c>
-      <x:c r="M20" s="3" t="s">
+      <x:c r="T20" s="3" t="s">
         <x:v>625</x:v>
-      </x:c>
-      <x:c r="N20" s="3" t="s">
-        <x:v>626</x:v>
-      </x:c>
-      <x:c r="O20" s="3" t="s">
-        <x:v>627</x:v>
-      </x:c>
-      <x:c r="P20" s="3" t="s">
-        <x:v>628</x:v>
-      </x:c>
-      <x:c r="Q20" s="3" t="s">
-        <x:v>629</x:v>
-      </x:c>
-      <x:c r="R20" s="3" t="s">
-        <x:v>630</x:v>
-      </x:c>
-      <x:c r="S20" s="3" t="s">
-        <x:v>631</x:v>
-      </x:c>
-      <x:c r="T20" s="3" t="s">
-        <x:v>632</x:v>
       </x:c>
       <x:c r="U20" s="3" t="s">
         <x:v>52</x:v>
@@ -9934,31 +9913,31 @@
     </x:row>
     <x:row r="21" ht="79.25" hidden="0">
       <x:c r="A21" s="3" t="s">
-        <x:v>633</x:v>
+        <x:v>626</x:v>
       </x:c>
       <x:c r="B21" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C21" s="3" t="s">
-        <x:v>634</x:v>
+        <x:v>627</x:v>
       </x:c>
       <x:c r="D21" s="3" t="s">
-        <x:v>635</x:v>
+        <x:v>628</x:v>
       </x:c>
       <x:c r="E21" s="3" t="s">
-        <x:v>636</x:v>
+        <x:v>629</x:v>
       </x:c>
       <x:c r="F21" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G21" s="3" t="s">
-        <x:v>437</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="H21" s="3" t="s">
-        <x:v>438</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="I21" s="3" t="s">
-        <x:v>439</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="J21" s="3" t="s">
         <x:v>41</x:v>
@@ -9967,31 +9946,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L21" s="3" t="s">
-        <x:v>637</x:v>
+        <x:v>630</x:v>
       </x:c>
       <x:c r="M21" s="3" t="s">
-        <x:v>638</x:v>
+        <x:v>631</x:v>
       </x:c>
       <x:c r="N21" s="3" t="s">
-        <x:v>639</x:v>
+        <x:v>632</x:v>
       </x:c>
       <x:c r="O21" s="3" t="s">
         <x:v>218</x:v>
       </x:c>
       <x:c r="P21" s="3" t="s">
-        <x:v>640</x:v>
+        <x:v>633</x:v>
       </x:c>
       <x:c r="Q21" s="3" t="s">
-        <x:v>641</x:v>
+        <x:v>634</x:v>
       </x:c>
       <x:c r="R21" s="3" t="s">
         <x:v>221</x:v>
       </x:c>
       <x:c r="S21" s="3" t="s">
-        <x:v>642</x:v>
+        <x:v>635</x:v>
       </x:c>
       <x:c r="T21" s="3" t="s">
-        <x:v>643</x:v>
+        <x:v>636</x:v>
       </x:c>
       <x:c r="U21" s="3" t="s">
         <x:v>52</x:v>
@@ -9999,31 +9978,31 @@
     </x:row>
     <x:row r="22" ht="93.25" hidden="0">
       <x:c r="A22" s="3" t="s">
-        <x:v>644</x:v>
+        <x:v>637</x:v>
       </x:c>
       <x:c r="B22" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C22" s="3" t="s">
-        <x:v>645</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="D22" s="3" t="s">
-        <x:v>646</x:v>
+        <x:v>639</x:v>
       </x:c>
       <x:c r="E22" s="3" t="s">
-        <x:v>647</x:v>
+        <x:v>640</x:v>
       </x:c>
       <x:c r="F22" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G22" s="3" t="s">
-        <x:v>437</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="H22" s="3" t="s">
-        <x:v>438</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="I22" s="3" t="s">
-        <x:v>439</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="J22" s="3" t="s">
         <x:v>41</x:v>
@@ -10032,31 +10011,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L22" s="3" t="s">
+        <x:v>641</x:v>
+      </x:c>
+      <x:c r="M22" s="3" t="s">
+        <x:v>506</x:v>
+      </x:c>
+      <x:c r="N22" s="3" t="s">
+        <x:v>642</x:v>
+      </x:c>
+      <x:c r="O22" s="3" t="s">
+        <x:v>643</x:v>
+      </x:c>
+      <x:c r="P22" s="3" t="s">
+        <x:v>644</x:v>
+      </x:c>
+      <x:c r="Q22" s="3" t="s">
+        <x:v>645</x:v>
+      </x:c>
+      <x:c r="R22" s="3" t="s">
+        <x:v>646</x:v>
+      </x:c>
+      <x:c r="S22" s="3" t="s">
+        <x:v>647</x:v>
+      </x:c>
+      <x:c r="T22" s="3" t="s">
         <x:v>648</x:v>
-      </x:c>
-      <x:c r="M22" s="3" t="s">
-        <x:v>513</x:v>
-      </x:c>
-      <x:c r="N22" s="3" t="s">
-        <x:v>649</x:v>
-      </x:c>
-      <x:c r="O22" s="3" t="s">
-        <x:v>650</x:v>
-      </x:c>
-      <x:c r="P22" s="3" t="s">
-        <x:v>651</x:v>
-      </x:c>
-      <x:c r="Q22" s="3" t="s">
-        <x:v>652</x:v>
-      </x:c>
-      <x:c r="R22" s="3" t="s">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="S22" s="3" t="s">
-        <x:v>654</x:v>
-      </x:c>
-      <x:c r="T22" s="3" t="s">
-        <x:v>655</x:v>
       </x:c>
       <x:c r="U22" s="3" t="s">
         <x:v>52</x:v>
@@ -10064,31 +10043,31 @@
     </x:row>
     <x:row r="23" ht="93.25" hidden="0">
       <x:c r="A23" s="3" t="s">
-        <x:v>656</x:v>
+        <x:v>649</x:v>
       </x:c>
       <x:c r="B23" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C23" s="3" t="s">
-        <x:v>657</x:v>
+        <x:v>650</x:v>
       </x:c>
       <x:c r="D23" s="3" t="s">
-        <x:v>658</x:v>
+        <x:v>651</x:v>
       </x:c>
       <x:c r="E23" s="3" t="s">
-        <x:v>659</x:v>
+        <x:v>652</x:v>
       </x:c>
       <x:c r="F23" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G23" s="3" t="s">
-        <x:v>437</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="H23" s="3" t="s">
-        <x:v>438</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="I23" s="3" t="s">
-        <x:v>439</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="J23" s="3" t="s">
         <x:v>41</x:v>
@@ -10097,31 +10076,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L23" s="3" t="s">
+        <x:v>653</x:v>
+      </x:c>
+      <x:c r="M23" s="3" t="s">
+        <x:v>654</x:v>
+      </x:c>
+      <x:c r="N23" s="3" t="s">
+        <x:v>655</x:v>
+      </x:c>
+      <x:c r="O23" s="3" t="s">
+        <x:v>656</x:v>
+      </x:c>
+      <x:c r="P23" s="3" t="s">
+        <x:v>657</x:v>
+      </x:c>
+      <x:c r="Q23" s="3" t="s">
+        <x:v>658</x:v>
+      </x:c>
+      <x:c r="R23" s="3" t="s">
+        <x:v>659</x:v>
+      </x:c>
+      <x:c r="S23" s="3" t="s">
         <x:v>660</x:v>
       </x:c>
-      <x:c r="M23" s="3" t="s">
+      <x:c r="T23" s="3" t="s">
         <x:v>661</x:v>
-      </x:c>
-      <x:c r="N23" s="3" t="s">
-        <x:v>662</x:v>
-      </x:c>
-      <x:c r="O23" s="3" t="s">
-        <x:v>663</x:v>
-      </x:c>
-      <x:c r="P23" s="3" t="s">
-        <x:v>664</x:v>
-      </x:c>
-      <x:c r="Q23" s="3" t="s">
-        <x:v>665</x:v>
-      </x:c>
-      <x:c r="R23" s="3" t="s">
-        <x:v>666</x:v>
-      </x:c>
-      <x:c r="S23" s="3" t="s">
-        <x:v>667</x:v>
-      </x:c>
-      <x:c r="T23" s="3" t="s">
-        <x:v>668</x:v>
       </x:c>
       <x:c r="U23" s="3" t="s">
         <x:v>52</x:v>
@@ -10129,31 +10108,31 @@
     </x:row>
     <x:row r="24" ht="79.25" hidden="0">
       <x:c r="A24" s="3" t="s">
-        <x:v>669</x:v>
+        <x:v>662</x:v>
       </x:c>
       <x:c r="B24" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C24" s="3" t="s">
-        <x:v>670</x:v>
+        <x:v>663</x:v>
       </x:c>
       <x:c r="D24" s="3" t="s">
-        <x:v>671</x:v>
+        <x:v>664</x:v>
       </x:c>
       <x:c r="E24" s="3" t="s">
-        <x:v>672</x:v>
+        <x:v>665</x:v>
       </x:c>
       <x:c r="F24" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G24" s="3" t="s">
-        <x:v>437</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="H24" s="3" t="s">
-        <x:v>438</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="I24" s="3" t="s">
-        <x:v>439</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="J24" s="3" t="s">
         <x:v>41</x:v>
@@ -10162,31 +10141,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L24" s="3" t="s">
+        <x:v>666</x:v>
+      </x:c>
+      <x:c r="M24" s="3" t="s">
+        <x:v>631</x:v>
+      </x:c>
+      <x:c r="N24" s="3" t="s">
+        <x:v>667</x:v>
+      </x:c>
+      <x:c r="O24" s="3" t="s">
+        <x:v>668</x:v>
+      </x:c>
+      <x:c r="P24" s="3" t="s">
+        <x:v>669</x:v>
+      </x:c>
+      <x:c r="Q24" s="3" t="s">
+        <x:v>670</x:v>
+      </x:c>
+      <x:c r="R24" s="3" t="s">
+        <x:v>671</x:v>
+      </x:c>
+      <x:c r="S24" s="3" t="s">
+        <x:v>672</x:v>
+      </x:c>
+      <x:c r="T24" s="3" t="s">
         <x:v>673</x:v>
-      </x:c>
-      <x:c r="M24" s="3" t="s">
-        <x:v>638</x:v>
-      </x:c>
-      <x:c r="N24" s="3" t="s">
-        <x:v>674</x:v>
-      </x:c>
-      <x:c r="O24" s="3" t="s">
-        <x:v>675</x:v>
-      </x:c>
-      <x:c r="P24" s="3" t="s">
-        <x:v>676</x:v>
-      </x:c>
-      <x:c r="Q24" s="3" t="s">
-        <x:v>677</x:v>
-      </x:c>
-      <x:c r="R24" s="3" t="s">
-        <x:v>678</x:v>
-      </x:c>
-      <x:c r="S24" s="3" t="s">
-        <x:v>679</x:v>
-      </x:c>
-      <x:c r="T24" s="3" t="s">
-        <x:v>680</x:v>
       </x:c>
       <x:c r="U24" s="3" t="s">
         <x:v>52</x:v>
@@ -10194,31 +10173,31 @@
     </x:row>
     <x:row r="25" ht="79.25" hidden="0">
       <x:c r="A25" s="3" t="s">
-        <x:v>681</x:v>
+        <x:v>674</x:v>
       </x:c>
       <x:c r="B25" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C25" s="3" t="s">
-        <x:v>682</x:v>
+        <x:v>675</x:v>
       </x:c>
       <x:c r="D25" s="3" t="s">
-        <x:v>683</x:v>
+        <x:v>676</x:v>
       </x:c>
       <x:c r="E25" s="3" t="s">
-        <x:v>684</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="F25" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G25" s="3" t="s">
-        <x:v>437</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="H25" s="3" t="s">
-        <x:v>438</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="I25" s="3" t="s">
-        <x:v>439</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="J25" s="3" t="s">
         <x:v>41</x:v>
@@ -10227,31 +10206,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L25" s="3" t="s">
+        <x:v>678</x:v>
+      </x:c>
+      <x:c r="M25" s="3" t="s">
+        <x:v>631</x:v>
+      </x:c>
+      <x:c r="N25" s="3" t="s">
+        <x:v>679</x:v>
+      </x:c>
+      <x:c r="O25" s="3" t="s">
+        <x:v>680</x:v>
+      </x:c>
+      <x:c r="P25" s="3" t="s">
+        <x:v>681</x:v>
+      </x:c>
+      <x:c r="Q25" s="3" t="s">
+        <x:v>682</x:v>
+      </x:c>
+      <x:c r="R25" s="3" t="s">
+        <x:v>683</x:v>
+      </x:c>
+      <x:c r="S25" s="3" t="s">
+        <x:v>684</x:v>
+      </x:c>
+      <x:c r="T25" s="3" t="s">
         <x:v>685</x:v>
-      </x:c>
-      <x:c r="M25" s="3" t="s">
-        <x:v>638</x:v>
-      </x:c>
-      <x:c r="N25" s="3" t="s">
-        <x:v>686</x:v>
-      </x:c>
-      <x:c r="O25" s="3" t="s">
-        <x:v>687</x:v>
-      </x:c>
-      <x:c r="P25" s="3" t="s">
-        <x:v>688</x:v>
-      </x:c>
-      <x:c r="Q25" s="3" t="s">
-        <x:v>689</x:v>
-      </x:c>
-      <x:c r="R25" s="3" t="s">
-        <x:v>690</x:v>
-      </x:c>
-      <x:c r="S25" s="3" t="s">
-        <x:v>691</x:v>
-      </x:c>
-      <x:c r="T25" s="3" t="s">
-        <x:v>692</x:v>
       </x:c>
       <x:c r="U25" s="3" t="s">
         <x:v>52</x:v>
@@ -10259,31 +10238,31 @@
     </x:row>
     <x:row r="26" ht="79.25" hidden="0">
       <x:c r="A26" s="3" t="s">
-        <x:v>693</x:v>
+        <x:v>686</x:v>
       </x:c>
       <x:c r="B26" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C26" s="3" t="s">
-        <x:v>694</x:v>
+        <x:v>687</x:v>
       </x:c>
       <x:c r="D26" s="3" t="s">
-        <x:v>695</x:v>
+        <x:v>688</x:v>
       </x:c>
       <x:c r="E26" s="3" t="s">
-        <x:v>696</x:v>
+        <x:v>689</x:v>
       </x:c>
       <x:c r="F26" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G26" s="3" t="s">
-        <x:v>437</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="H26" s="3" t="s">
-        <x:v>438</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="I26" s="3" t="s">
-        <x:v>439</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="J26" s="3" t="s">
         <x:v>41</x:v>
@@ -10292,31 +10271,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L26" s="3" t="s">
+        <x:v>690</x:v>
+      </x:c>
+      <x:c r="M26" s="3" t="s">
+        <x:v>691</x:v>
+      </x:c>
+      <x:c r="N26" s="3" t="s">
+        <x:v>692</x:v>
+      </x:c>
+      <x:c r="O26" s="3" t="s">
+        <x:v>693</x:v>
+      </x:c>
+      <x:c r="P26" s="3" t="s">
+        <x:v>694</x:v>
+      </x:c>
+      <x:c r="Q26" s="3" t="s">
+        <x:v>695</x:v>
+      </x:c>
+      <x:c r="R26" s="3" t="s">
+        <x:v>696</x:v>
+      </x:c>
+      <x:c r="S26" s="3" t="s">
         <x:v>697</x:v>
       </x:c>
-      <x:c r="M26" s="3" t="s">
+      <x:c r="T26" s="3" t="s">
         <x:v>698</x:v>
-      </x:c>
-      <x:c r="N26" s="3" t="s">
-        <x:v>699</x:v>
-      </x:c>
-      <x:c r="O26" s="3" t="s">
-        <x:v>700</x:v>
-      </x:c>
-      <x:c r="P26" s="3" t="s">
-        <x:v>701</x:v>
-      </x:c>
-      <x:c r="Q26" s="3" t="s">
-        <x:v>702</x:v>
-      </x:c>
-      <x:c r="R26" s="3" t="s">
-        <x:v>703</x:v>
-      </x:c>
-      <x:c r="S26" s="3" t="s">
-        <x:v>704</x:v>
-      </x:c>
-      <x:c r="T26" s="3" t="s">
-        <x:v>705</x:v>
       </x:c>
       <x:c r="U26" s="3" t="s">
         <x:v>52</x:v>
@@ -10324,31 +10303,31 @@
     </x:row>
     <x:row r="27" ht="79.25" hidden="0">
       <x:c r="A27" s="3" t="s">
-        <x:v>706</x:v>
+        <x:v>699</x:v>
       </x:c>
       <x:c r="B27" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C27" s="3" t="s">
-        <x:v>707</x:v>
+        <x:v>700</x:v>
       </x:c>
       <x:c r="D27" s="3" t="s">
-        <x:v>708</x:v>
+        <x:v>701</x:v>
       </x:c>
       <x:c r="E27" s="3" t="s">
-        <x:v>709</x:v>
+        <x:v>702</x:v>
       </x:c>
       <x:c r="F27" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G27" s="3" t="s">
-        <x:v>437</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="H27" s="3" t="s">
-        <x:v>438</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="I27" s="3" t="s">
-        <x:v>439</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="J27" s="3" t="s">
         <x:v>41</x:v>
@@ -10357,31 +10336,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L27" s="3" t="s">
+        <x:v>703</x:v>
+      </x:c>
+      <x:c r="M27" s="3" t="s">
+        <x:v>704</x:v>
+      </x:c>
+      <x:c r="N27" s="3" t="s">
+        <x:v>705</x:v>
+      </x:c>
+      <x:c r="O27" s="3" t="s">
+        <x:v>706</x:v>
+      </x:c>
+      <x:c r="P27" s="3" t="s">
+        <x:v>707</x:v>
+      </x:c>
+      <x:c r="Q27" s="3" t="s">
+        <x:v>708</x:v>
+      </x:c>
+      <x:c r="R27" s="3" t="s">
+        <x:v>709</x:v>
+      </x:c>
+      <x:c r="S27" s="3" t="s">
         <x:v>710</x:v>
       </x:c>
-      <x:c r="M27" s="3" t="s">
+      <x:c r="T27" s="3" t="s">
         <x:v>711</x:v>
-      </x:c>
-      <x:c r="N27" s="3" t="s">
-        <x:v>712</x:v>
-      </x:c>
-      <x:c r="O27" s="3" t="s">
-        <x:v>713</x:v>
-      </x:c>
-      <x:c r="P27" s="3" t="s">
-        <x:v>714</x:v>
-      </x:c>
-      <x:c r="Q27" s="3" t="s">
-        <x:v>715</x:v>
-      </x:c>
-      <x:c r="R27" s="3" t="s">
-        <x:v>716</x:v>
-      </x:c>
-      <x:c r="S27" s="3" t="s">
-        <x:v>717</x:v>
-      </x:c>
-      <x:c r="T27" s="3" t="s">
-        <x:v>718</x:v>
       </x:c>
       <x:c r="U27" s="3" t="s">
         <x:v>52</x:v>
@@ -10389,31 +10368,31 @@
     </x:row>
     <x:row r="28" ht="93.25" hidden="0">
       <x:c r="A28" s="3" t="s">
-        <x:v>719</x:v>
+        <x:v>712</x:v>
       </x:c>
       <x:c r="B28" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C28" s="3" t="s">
-        <x:v>720</x:v>
+        <x:v>713</x:v>
       </x:c>
       <x:c r="D28" s="3" t="s">
-        <x:v>721</x:v>
+        <x:v>714</x:v>
       </x:c>
       <x:c r="E28" s="3" t="s">
-        <x:v>722</x:v>
+        <x:v>715</x:v>
       </x:c>
       <x:c r="F28" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G28" s="3" t="s">
-        <x:v>437</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="H28" s="3" t="s">
-        <x:v>438</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="I28" s="3" t="s">
-        <x:v>439</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="J28" s="3" t="s">
         <x:v>41</x:v>
@@ -10422,31 +10401,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L28" s="3" t="s">
-        <x:v>723</x:v>
+        <x:v>716</x:v>
       </x:c>
       <x:c r="M28" s="3" t="s">
-        <x:v>724</x:v>
+        <x:v>717</x:v>
       </x:c>
       <x:c r="N28" s="3" t="s">
-        <x:v>725</x:v>
+        <x:v>718</x:v>
       </x:c>
       <x:c r="O28" s="3" t="s">
-        <x:v>726</x:v>
+        <x:v>719</x:v>
       </x:c>
       <x:c r="P28" s="3" t="s">
-        <x:v>727</x:v>
+        <x:v>720</x:v>
       </x:c>
       <x:c r="Q28" s="3" t="s">
-        <x:v>728</x:v>
+        <x:v>721</x:v>
       </x:c>
       <x:c r="R28" s="3" t="s">
-        <x:v>729</x:v>
+        <x:v>722</x:v>
       </x:c>
       <x:c r="S28" s="3" t="s">
         <x:v>286</x:v>
       </x:c>
       <x:c r="T28" s="3" t="s">
-        <x:v>730</x:v>
+        <x:v>723</x:v>
       </x:c>
       <x:c r="U28" s="3" t="s">
         <x:v>52</x:v>
@@ -10454,31 +10433,31 @@
     </x:row>
     <x:row r="29" ht="93.25" hidden="0">
       <x:c r="A29" s="3" t="s">
-        <x:v>731</x:v>
+        <x:v>724</x:v>
       </x:c>
       <x:c r="B29" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C29" s="3" t="s">
-        <x:v>732</x:v>
+        <x:v>725</x:v>
       </x:c>
       <x:c r="D29" s="3" t="s">
-        <x:v>733</x:v>
+        <x:v>726</x:v>
       </x:c>
       <x:c r="E29" s="3" t="s">
-        <x:v>734</x:v>
+        <x:v>727</x:v>
       </x:c>
       <x:c r="F29" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G29" s="3" t="s">
-        <x:v>437</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="H29" s="3" t="s">
-        <x:v>438</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="I29" s="3" t="s">
-        <x:v>439</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="J29" s="3" t="s">
         <x:v>41</x:v>
@@ -10487,31 +10466,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="L29" s="3" t="s">
+        <x:v>728</x:v>
+      </x:c>
+      <x:c r="M29" s="3" t="s">
+        <x:v>729</x:v>
+      </x:c>
+      <x:c r="N29" s="3" t="s">
+        <x:v>730</x:v>
+      </x:c>
+      <x:c r="O29" s="3" t="s">
+        <x:v>731</x:v>
+      </x:c>
+      <x:c r="P29" s="3" t="s">
+        <x:v>732</x:v>
+      </x:c>
+      <x:c r="Q29" s="3" t="s">
+        <x:v>733</x:v>
+      </x:c>
+      <x:c r="R29" s="3" t="s">
+        <x:v>734</x:v>
+      </x:c>
+      <x:c r="S29" s="3" t="s">
         <x:v>735</x:v>
       </x:c>
-      <x:c r="M29" s="3" t="s">
+      <x:c r="T29" s="3" t="s">
         <x:v>736</x:v>
-      </x:c>
-      <x:c r="N29" s="3" t="s">
-        <x:v>737</x:v>
-      </x:c>
-      <x:c r="O29" s="3" t="s">
-        <x:v>738</x:v>
-      </x:c>
-      <x:c r="P29" s="3" t="s">
-        <x:v>739</x:v>
-      </x:c>
-      <x:c r="Q29" s="3" t="s">
-        <x:v>740</x:v>
-      </x:c>
-      <x:c r="R29" s="3" t="s">
-        <x:v>741</x:v>
-      </x:c>
-      <x:c r="S29" s="3" t="s">
-        <x:v>742</x:v>
-      </x:c>
-      <x:c r="T29" s="3" t="s">
-        <x:v>743</x:v>
       </x:c>
       <x:c r="U29" s="3" t="s">
         <x:v>52</x:v>
@@ -10519,31 +10498,31 @@
     </x:row>
     <x:row r="30" ht="93.25" hidden="0">
       <x:c r="A30" s="3" t="s">
-        <x:v>744</x:v>
+        <x:v>737</x:v>
       </x:c>
       <x:c r="B30" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C30" s="3" t="s">
-        <x:v>745</x:v>
+        <x:v>738</x:v>
       </x:c>
       <x:c r="D30" s="3" t="s">
-        <x:v>746</x:v>
+        <x:v>739</x:v>
       </x:c>
       <x:c r="E30" s="3" t="s">
-        <x:v>747</x:v>
+        <x:v>740</x:v>
       </x:c>
       <x:c r="F30" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G30" s="3" t="s">
-        <x:v>437</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="H30" s="3" t="s">
-        <x:v>438</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="I30" s="3" t="s">
-        <x:v>439</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="J30" s="3" t="s">
         <x:v>41</x:v>
@@ -10552,31 +10531,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L30" s="3" t="s">
+        <x:v>741</x:v>
+      </x:c>
+      <x:c r="M30" s="3" t="s">
+        <x:v>742</x:v>
+      </x:c>
+      <x:c r="N30" s="3" t="s">
+        <x:v>743</x:v>
+      </x:c>
+      <x:c r="O30" s="3" t="s">
+        <x:v>744</x:v>
+      </x:c>
+      <x:c r="P30" s="3" t="s">
+        <x:v>745</x:v>
+      </x:c>
+      <x:c r="Q30" s="3" t="s">
+        <x:v>746</x:v>
+      </x:c>
+      <x:c r="R30" s="3" t="s">
+        <x:v>747</x:v>
+      </x:c>
+      <x:c r="S30" s="3" t="s">
         <x:v>748</x:v>
       </x:c>
-      <x:c r="M30" s="3" t="s">
+      <x:c r="T30" s="3" t="s">
         <x:v>749</x:v>
-      </x:c>
-      <x:c r="N30" s="3" t="s">
-        <x:v>750</x:v>
-      </x:c>
-      <x:c r="O30" s="3" t="s">
-        <x:v>751</x:v>
-      </x:c>
-      <x:c r="P30" s="3" t="s">
-        <x:v>752</x:v>
-      </x:c>
-      <x:c r="Q30" s="3" t="s">
-        <x:v>753</x:v>
-      </x:c>
-      <x:c r="R30" s="3" t="s">
-        <x:v>754</x:v>
-      </x:c>
-      <x:c r="S30" s="3" t="s">
-        <x:v>755</x:v>
-      </x:c>
-      <x:c r="T30" s="3" t="s">
-        <x:v>756</x:v>
       </x:c>
       <x:c r="U30" s="3" t="s">
         <x:v>52</x:v>
@@ -10584,31 +10563,31 @@
     </x:row>
     <x:row r="31" ht="93.25" hidden="0">
       <x:c r="A31" s="3" t="s">
-        <x:v>757</x:v>
+        <x:v>750</x:v>
       </x:c>
       <x:c r="B31" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C31" s="3" t="s">
-        <x:v>758</x:v>
+        <x:v>751</x:v>
       </x:c>
       <x:c r="D31" s="3" t="s">
-        <x:v>759</x:v>
+        <x:v>752</x:v>
       </x:c>
       <x:c r="E31" s="3" t="s">
-        <x:v>760</x:v>
+        <x:v>753</x:v>
       </x:c>
       <x:c r="F31" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G31" s="3" t="s">
-        <x:v>437</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="H31" s="3" t="s">
-        <x:v>438</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="I31" s="3" t="s">
-        <x:v>439</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="J31" s="3" t="s">
         <x:v>41</x:v>
@@ -10617,31 +10596,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="L31" s="3" t="s">
+        <x:v>754</x:v>
+      </x:c>
+      <x:c r="M31" s="3" t="s">
+        <x:v>755</x:v>
+      </x:c>
+      <x:c r="N31" s="3" t="s">
+        <x:v>756</x:v>
+      </x:c>
+      <x:c r="O31" s="3" t="s">
+        <x:v>757</x:v>
+      </x:c>
+      <x:c r="P31" s="3" t="s">
+        <x:v>758</x:v>
+      </x:c>
+      <x:c r="Q31" s="3" t="s">
+        <x:v>759</x:v>
+      </x:c>
+      <x:c r="R31" s="3" t="s">
+        <x:v>760</x:v>
+      </x:c>
+      <x:c r="S31" s="3" t="s">
         <x:v>761</x:v>
       </x:c>
-      <x:c r="M31" s="3" t="s">
+      <x:c r="T31" s="3" t="s">
         <x:v>762</x:v>
-      </x:c>
-      <x:c r="N31" s="3" t="s">
-        <x:v>763</x:v>
-      </x:c>
-      <x:c r="O31" s="3" t="s">
-        <x:v>764</x:v>
-      </x:c>
-      <x:c r="P31" s="3" t="s">
-        <x:v>765</x:v>
-      </x:c>
-      <x:c r="Q31" s="3" t="s">
-        <x:v>766</x:v>
-      </x:c>
-      <x:c r="R31" s="3" t="s">
-        <x:v>767</x:v>
-      </x:c>
-      <x:c r="S31" s="3" t="s">
-        <x:v>768</x:v>
-      </x:c>
-      <x:c r="T31" s="3" t="s">
-        <x:v>769</x:v>
       </x:c>
       <x:c r="U31" s="3" t="s">
         <x:v>52</x:v>
@@ -10649,31 +10628,31 @@
     </x:row>
     <x:row r="32" ht="93.25" hidden="0">
       <x:c r="A32" s="3" t="s">
-        <x:v>770</x:v>
+        <x:v>763</x:v>
       </x:c>
       <x:c r="B32" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C32" s="3" t="s">
-        <x:v>771</x:v>
+        <x:v>764</x:v>
       </x:c>
       <x:c r="D32" s="3" t="s">
-        <x:v>772</x:v>
+        <x:v>765</x:v>
       </x:c>
       <x:c r="E32" s="3" t="s">
-        <x:v>773</x:v>
+        <x:v>766</x:v>
       </x:c>
       <x:c r="F32" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G32" s="3" t="s">
-        <x:v>437</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="H32" s="3" t="s">
-        <x:v>438</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="I32" s="3" t="s">
-        <x:v>439</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="J32" s="3" t="s">
         <x:v>41</x:v>
@@ -10682,31 +10661,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L32" s="3" t="s">
+        <x:v>767</x:v>
+      </x:c>
+      <x:c r="M32" s="3" t="s">
+        <x:v>768</x:v>
+      </x:c>
+      <x:c r="N32" s="3" t="s">
+        <x:v>769</x:v>
+      </x:c>
+      <x:c r="O32" s="3" t="s">
+        <x:v>770</x:v>
+      </x:c>
+      <x:c r="P32" s="3" t="s">
+        <x:v>771</x:v>
+      </x:c>
+      <x:c r="Q32" s="3" t="s">
+        <x:v>772</x:v>
+      </x:c>
+      <x:c r="R32" s="3" t="s">
+        <x:v>773</x:v>
+      </x:c>
+      <x:c r="S32" s="3" t="s">
         <x:v>774</x:v>
       </x:c>
-      <x:c r="M32" s="3" t="s">
+      <x:c r="T32" s="3" t="s">
         <x:v>775</x:v>
-      </x:c>
-      <x:c r="N32" s="3" t="s">
-        <x:v>776</x:v>
-      </x:c>
-      <x:c r="O32" s="3" t="s">
-        <x:v>777</x:v>
-      </x:c>
-      <x:c r="P32" s="3" t="s">
-        <x:v>778</x:v>
-      </x:c>
-      <x:c r="Q32" s="3" t="s">
-        <x:v>779</x:v>
-      </x:c>
-      <x:c r="R32" s="3" t="s">
-        <x:v>780</x:v>
-      </x:c>
-      <x:c r="S32" s="3" t="s">
-        <x:v>781</x:v>
-      </x:c>
-      <x:c r="T32" s="3" t="s">
-        <x:v>782</x:v>
       </x:c>
       <x:c r="U32" s="3" t="s">
         <x:v>52</x:v>
@@ -10714,31 +10693,31 @@
     </x:row>
     <x:row r="33" ht="93.25" hidden="0">
       <x:c r="A33" s="3" t="s">
-        <x:v>783</x:v>
+        <x:v>776</x:v>
       </x:c>
       <x:c r="B33" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C33" s="3" t="s">
-        <x:v>784</x:v>
+        <x:v>777</x:v>
       </x:c>
       <x:c r="D33" s="3" t="s">
-        <x:v>785</x:v>
+        <x:v>778</x:v>
       </x:c>
       <x:c r="E33" s="3" t="s">
-        <x:v>786</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="F33" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G33" s="3" t="s">
-        <x:v>437</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="H33" s="3" t="s">
-        <x:v>438</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="I33" s="3" t="s">
-        <x:v>439</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="J33" s="3" t="s">
         <x:v>41</x:v>
@@ -10747,31 +10726,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L33" s="3" t="s">
+        <x:v>780</x:v>
+      </x:c>
+      <x:c r="M33" s="3" t="s">
+        <x:v>781</x:v>
+      </x:c>
+      <x:c r="N33" s="3" t="s">
+        <x:v>782</x:v>
+      </x:c>
+      <x:c r="O33" s="3" t="s">
+        <x:v>783</x:v>
+      </x:c>
+      <x:c r="P33" s="3" t="s">
+        <x:v>784</x:v>
+      </x:c>
+      <x:c r="Q33" s="3" t="s">
+        <x:v>785</x:v>
+      </x:c>
+      <x:c r="R33" s="3" t="s">
+        <x:v>786</x:v>
+      </x:c>
+      <x:c r="S33" s="3" t="s">
         <x:v>787</x:v>
       </x:c>
-      <x:c r="M33" s="3" t="s">
+      <x:c r="T33" s="3" t="s">
         <x:v>788</x:v>
-      </x:c>
-      <x:c r="N33" s="3" t="s">
-        <x:v>789</x:v>
-      </x:c>
-      <x:c r="O33" s="3" t="s">
-        <x:v>790</x:v>
-      </x:c>
-      <x:c r="P33" s="3" t="s">
-        <x:v>791</x:v>
-      </x:c>
-      <x:c r="Q33" s="3" t="s">
-        <x:v>792</x:v>
-      </x:c>
-      <x:c r="R33" s="3" t="s">
-        <x:v>793</x:v>
-      </x:c>
-      <x:c r="S33" s="3" t="s">
-        <x:v>794</x:v>
-      </x:c>
-      <x:c r="T33" s="3" t="s">
-        <x:v>795</x:v>
       </x:c>
       <x:c r="U33" s="3" t="s">
         <x:v>52</x:v>
@@ -10779,7 +10758,7 @@
     </x:row>
     <x:row r="34" ht="93.25" hidden="0">
       <x:c r="A34" s="3" t="s">
-        <x:v>796</x:v>
+        <x:v>789</x:v>
       </x:c>
       <x:c r="B34" s="3" t="s">
         <x:v>8</x:v>
@@ -10788,22 +10767,22 @@
         <x:v>313</x:v>
       </x:c>
       <x:c r="D34" s="3" t="s">
-        <x:v>797</x:v>
+        <x:v>790</x:v>
       </x:c>
       <x:c r="E34" s="3" t="s">
-        <x:v>798</x:v>
+        <x:v>791</x:v>
       </x:c>
       <x:c r="F34" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G34" s="3" t="s">
-        <x:v>437</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="H34" s="3" t="s">
-        <x:v>438</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="I34" s="3" t="s">
-        <x:v>439</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="J34" s="3" t="s">
         <x:v>41</x:v>
@@ -10812,31 +10791,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="L34" s="3" t="s">
-        <x:v>799</x:v>
+        <x:v>792</x:v>
       </x:c>
       <x:c r="M34" s="3" t="s">
-        <x:v>800</x:v>
+        <x:v>793</x:v>
       </x:c>
       <x:c r="N34" s="3" t="s">
-        <x:v>801</x:v>
+        <x:v>794</x:v>
       </x:c>
       <x:c r="O34" s="3" t="s">
-        <x:v>802</x:v>
+        <x:v>795</x:v>
       </x:c>
       <x:c r="P34" s="3" t="s">
-        <x:v>803</x:v>
+        <x:v>796</x:v>
       </x:c>
       <x:c r="Q34" s="3" t="s">
-        <x:v>804</x:v>
+        <x:v>797</x:v>
       </x:c>
       <x:c r="R34" s="3" t="s">
-        <x:v>805</x:v>
+        <x:v>798</x:v>
       </x:c>
       <x:c r="S34" s="3" t="s">
         <x:v>323</x:v>
       </x:c>
       <x:c r="T34" s="3" t="s">
-        <x:v>806</x:v>
+        <x:v>799</x:v>
       </x:c>
       <x:c r="U34" s="3" t="s">
         <x:v>52</x:v>
@@ -10844,31 +10823,31 @@
     </x:row>
     <x:row r="35" ht="93.25" hidden="0">
       <x:c r="A35" s="3" t="s">
-        <x:v>807</x:v>
+        <x:v>800</x:v>
       </x:c>
       <x:c r="B35" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C35" s="3" t="s">
-        <x:v>808</x:v>
+        <x:v>801</x:v>
       </x:c>
       <x:c r="D35" s="3" t="s">
-        <x:v>809</x:v>
+        <x:v>802</x:v>
       </x:c>
       <x:c r="E35" s="3" t="s">
-        <x:v>810</x:v>
+        <x:v>803</x:v>
       </x:c>
       <x:c r="F35" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G35" s="3" t="s">
-        <x:v>437</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="H35" s="3" t="s">
-        <x:v>438</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="I35" s="3" t="s">
-        <x:v>439</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="J35" s="3" t="s">
         <x:v>41</x:v>
@@ -10877,31 +10856,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L35" s="3" t="s">
+        <x:v>804</x:v>
+      </x:c>
+      <x:c r="M35" s="3" t="s">
+        <x:v>805</x:v>
+      </x:c>
+      <x:c r="N35" s="3" t="s">
+        <x:v>806</x:v>
+      </x:c>
+      <x:c r="O35" s="3" t="s">
+        <x:v>581</x:v>
+      </x:c>
+      <x:c r="P35" s="3" t="s">
+        <x:v>807</x:v>
+      </x:c>
+      <x:c r="Q35" s="3" t="s">
+        <x:v>808</x:v>
+      </x:c>
+      <x:c r="R35" s="3" t="s">
+        <x:v>809</x:v>
+      </x:c>
+      <x:c r="S35" s="3" t="s">
+        <x:v>810</x:v>
+      </x:c>
+      <x:c r="T35" s="3" t="s">
         <x:v>811</x:v>
-      </x:c>
-      <x:c r="M35" s="3" t="s">
-        <x:v>812</x:v>
-      </x:c>
-      <x:c r="N35" s="3" t="s">
-        <x:v>813</x:v>
-      </x:c>
-      <x:c r="O35" s="3" t="s">
-        <x:v>588</x:v>
-      </x:c>
-      <x:c r="P35" s="3" t="s">
-        <x:v>814</x:v>
-      </x:c>
-      <x:c r="Q35" s="3" t="s">
-        <x:v>815</x:v>
-      </x:c>
-      <x:c r="R35" s="3" t="s">
-        <x:v>816</x:v>
-      </x:c>
-      <x:c r="S35" s="3" t="s">
-        <x:v>817</x:v>
-      </x:c>
-      <x:c r="T35" s="3" t="s">
-        <x:v>818</x:v>
       </x:c>
       <x:c r="U35" s="3" t="s">
         <x:v>52</x:v>
@@ -10909,31 +10888,31 @@
     </x:row>
     <x:row r="36" ht="93.25" hidden="0">
       <x:c r="A36" s="3" t="s">
-        <x:v>819</x:v>
+        <x:v>812</x:v>
       </x:c>
       <x:c r="B36" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C36" s="3" t="s">
-        <x:v>820</x:v>
+        <x:v>813</x:v>
       </x:c>
       <x:c r="D36" s="3" t="s">
-        <x:v>821</x:v>
+        <x:v>814</x:v>
       </x:c>
       <x:c r="E36" s="3" t="s">
-        <x:v>822</x:v>
+        <x:v>815</x:v>
       </x:c>
       <x:c r="F36" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G36" s="3" t="s">
-        <x:v>437</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="H36" s="3" t="s">
-        <x:v>438</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="I36" s="3" t="s">
-        <x:v>439</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="J36" s="3" t="s">
         <x:v>41</x:v>
@@ -10942,31 +10921,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L36" s="3" t="s">
+        <x:v>816</x:v>
+      </x:c>
+      <x:c r="M36" s="3" t="s">
+        <x:v>446</x:v>
+      </x:c>
+      <x:c r="N36" s="3" t="s">
+        <x:v>817</x:v>
+      </x:c>
+      <x:c r="O36" s="3" t="s">
+        <x:v>818</x:v>
+      </x:c>
+      <x:c r="P36" s="3" t="s">
+        <x:v>819</x:v>
+      </x:c>
+      <x:c r="Q36" s="3" t="s">
+        <x:v>820</x:v>
+      </x:c>
+      <x:c r="R36" s="3" t="s">
+        <x:v>821</x:v>
+      </x:c>
+      <x:c r="S36" s="3" t="s">
+        <x:v>822</x:v>
+      </x:c>
+      <x:c r="T36" s="3" t="s">
         <x:v>823</x:v>
-      </x:c>
-      <x:c r="M36" s="3" t="s">
-        <x:v>441</x:v>
-      </x:c>
-      <x:c r="N36" s="3" t="s">
-        <x:v>824</x:v>
-      </x:c>
-      <x:c r="O36" s="3" t="s">
-        <x:v>825</x:v>
-      </x:c>
-      <x:c r="P36" s="3" t="s">
-        <x:v>826</x:v>
-      </x:c>
-      <x:c r="Q36" s="3" t="s">
-        <x:v>827</x:v>
-      </x:c>
-      <x:c r="R36" s="3" t="s">
-        <x:v>828</x:v>
-      </x:c>
-      <x:c r="S36" s="3" t="s">
-        <x:v>829</x:v>
-      </x:c>
-      <x:c r="T36" s="3" t="s">
-        <x:v>830</x:v>
       </x:c>
       <x:c r="U36" s="3" t="s">
         <x:v>52</x:v>
@@ -10974,31 +10953,31 @@
     </x:row>
     <x:row r="37" ht="93.25" hidden="0">
       <x:c r="A37" s="3" t="s">
-        <x:v>831</x:v>
+        <x:v>824</x:v>
       </x:c>
       <x:c r="B37" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C37" s="3" t="s">
-        <x:v>832</x:v>
+        <x:v>825</x:v>
       </x:c>
       <x:c r="D37" s="3" t="s">
-        <x:v>833</x:v>
+        <x:v>826</x:v>
       </x:c>
       <x:c r="E37" s="3" t="s">
-        <x:v>834</x:v>
+        <x:v>827</x:v>
       </x:c>
       <x:c r="F37" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G37" s="3" t="s">
-        <x:v>437</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="H37" s="3" t="s">
-        <x:v>438</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="I37" s="3" t="s">
-        <x:v>439</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="J37" s="3" t="s">
         <x:v>41</x:v>
@@ -11007,31 +10986,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L37" s="3" t="s">
+        <x:v>828</x:v>
+      </x:c>
+      <x:c r="M37" s="3" t="s">
+        <x:v>829</x:v>
+      </x:c>
+      <x:c r="N37" s="3" t="s">
+        <x:v>830</x:v>
+      </x:c>
+      <x:c r="O37" s="3" t="s">
+        <x:v>831</x:v>
+      </x:c>
+      <x:c r="P37" s="3" t="s">
+        <x:v>832</x:v>
+      </x:c>
+      <x:c r="Q37" s="3" t="s">
+        <x:v>833</x:v>
+      </x:c>
+      <x:c r="R37" s="3" t="s">
+        <x:v>834</x:v>
+      </x:c>
+      <x:c r="S37" s="3" t="s">
         <x:v>835</x:v>
       </x:c>
-      <x:c r="M37" s="3" t="s">
-        <x:v>836</x:v>
-      </x:c>
-      <x:c r="N37" s="3" t="s">
-        <x:v>837</x:v>
-      </x:c>
-      <x:c r="O37" s="3" t="s">
-        <x:v>838</x:v>
-      </x:c>
-      <x:c r="P37" s="3" t="s">
-        <x:v>839</x:v>
-      </x:c>
-      <x:c r="Q37" s="3" t="s">
-        <x:v>840</x:v>
-      </x:c>
-      <x:c r="R37" s="3" t="s">
-        <x:v>841</x:v>
-      </x:c>
-      <x:c r="S37" s="3" t="s">
-        <x:v>842</x:v>
-      </x:c>
       <x:c r="T37" s="3" t="s">
-        <x:v>836</x:v>
+        <x:v>829</x:v>
       </x:c>
       <x:c r="U37" s="3" t="s">
         <x:v>52</x:v>
@@ -11039,31 +11018,31 @@
     </x:row>
     <x:row r="38" ht="93.25" hidden="0">
       <x:c r="A38" s="3" t="s">
-        <x:v>843</x:v>
+        <x:v>836</x:v>
       </x:c>
       <x:c r="B38" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C38" s="3" t="s">
-        <x:v>844</x:v>
+        <x:v>837</x:v>
       </x:c>
       <x:c r="D38" s="3" t="s">
-        <x:v>845</x:v>
+        <x:v>838</x:v>
       </x:c>
       <x:c r="E38" s="3" t="s">
-        <x:v>846</x:v>
+        <x:v>839</x:v>
       </x:c>
       <x:c r="F38" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G38" s="3" t="s">
-        <x:v>437</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="H38" s="3" t="s">
-        <x:v>438</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="I38" s="3" t="s">
-        <x:v>439</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="J38" s="3" t="s">
         <x:v>41</x:v>
@@ -11072,31 +11051,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L38" s="3" t="s">
+        <x:v>840</x:v>
+      </x:c>
+      <x:c r="M38" s="3" t="s">
+        <x:v>506</x:v>
+      </x:c>
+      <x:c r="N38" s="3" t="s">
+        <x:v>841</x:v>
+      </x:c>
+      <x:c r="O38" s="3" t="s">
+        <x:v>842</x:v>
+      </x:c>
+      <x:c r="P38" s="3" t="s">
+        <x:v>843</x:v>
+      </x:c>
+      <x:c r="Q38" s="3" t="s">
+        <x:v>844</x:v>
+      </x:c>
+      <x:c r="R38" s="3" t="s">
+        <x:v>845</x:v>
+      </x:c>
+      <x:c r="S38" s="3" t="s">
+        <x:v>846</x:v>
+      </x:c>
+      <x:c r="T38" s="3" t="s">
         <x:v>847</x:v>
-      </x:c>
-      <x:c r="M38" s="3" t="s">
-        <x:v>513</x:v>
-      </x:c>
-      <x:c r="N38" s="3" t="s">
-        <x:v>848</x:v>
-      </x:c>
-      <x:c r="O38" s="3" t="s">
-        <x:v>849</x:v>
-      </x:c>
-      <x:c r="P38" s="3" t="s">
-        <x:v>850</x:v>
-      </x:c>
-      <x:c r="Q38" s="3" t="s">
-        <x:v>851</x:v>
-      </x:c>
-      <x:c r="R38" s="3" t="s">
-        <x:v>852</x:v>
-      </x:c>
-      <x:c r="S38" s="3" t="s">
-        <x:v>853</x:v>
-      </x:c>
-      <x:c r="T38" s="3" t="s">
-        <x:v>854</x:v>
       </x:c>
       <x:c r="U38" s="3" t="s">
         <x:v>52</x:v>
@@ -11104,31 +11083,31 @@
     </x:row>
     <x:row r="39" ht="93.25" hidden="0">
       <x:c r="A39" s="3" t="s">
-        <x:v>855</x:v>
+        <x:v>848</x:v>
       </x:c>
       <x:c r="B39" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C39" s="3" t="s">
-        <x:v>856</x:v>
+        <x:v>849</x:v>
       </x:c>
       <x:c r="D39" s="3" t="s">
-        <x:v>857</x:v>
+        <x:v>850</x:v>
       </x:c>
       <x:c r="E39" s="3" t="s">
-        <x:v>858</x:v>
+        <x:v>851</x:v>
       </x:c>
       <x:c r="F39" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G39" s="3" t="s">
-        <x:v>437</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="H39" s="3" t="s">
-        <x:v>438</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="I39" s="3" t="s">
-        <x:v>439</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="J39" s="3" t="s">
         <x:v>41</x:v>
@@ -11137,31 +11116,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="L39" s="3" t="s">
+        <x:v>852</x:v>
+      </x:c>
+      <x:c r="M39" s="3" t="s">
+        <x:v>446</x:v>
+      </x:c>
+      <x:c r="N39" s="3" t="s">
+        <x:v>853</x:v>
+      </x:c>
+      <x:c r="O39" s="3" t="s">
+        <x:v>854</x:v>
+      </x:c>
+      <x:c r="P39" s="3" t="s">
+        <x:v>855</x:v>
+      </x:c>
+      <x:c r="Q39" s="3" t="s">
+        <x:v>856</x:v>
+      </x:c>
+      <x:c r="R39" s="3" t="s">
+        <x:v>857</x:v>
+      </x:c>
+      <x:c r="S39" s="3" t="s">
+        <x:v>858</x:v>
+      </x:c>
+      <x:c r="T39" s="3" t="s">
         <x:v>859</x:v>
-      </x:c>
-      <x:c r="M39" s="3" t="s">
-        <x:v>441</x:v>
-      </x:c>
-      <x:c r="N39" s="3" t="s">
-        <x:v>860</x:v>
-      </x:c>
-      <x:c r="O39" s="3" t="s">
-        <x:v>861</x:v>
-      </x:c>
-      <x:c r="P39" s="3" t="s">
-        <x:v>862</x:v>
-      </x:c>
-      <x:c r="Q39" s="3" t="s">
-        <x:v>863</x:v>
-      </x:c>
-      <x:c r="R39" s="3" t="s">
-        <x:v>864</x:v>
-      </x:c>
-      <x:c r="S39" s="3" t="s">
-        <x:v>865</x:v>
-      </x:c>
-      <x:c r="T39" s="3" t="s">
-        <x:v>866</x:v>
       </x:c>
       <x:c r="U39" s="3" t="s">
         <x:v>52</x:v>
@@ -11170,7 +11149,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2bf8183517df4b53"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rff5215770ede4f23"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/maliev-feature-user-story-status.xlsx
+++ b/docs/maliev-feature-user-story-status.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rb79f44cd060f4a0f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="Rc46d8898b102415f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="Rfba5588294bb4b1b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="R773f79cca795430d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rb5b68a3878644019"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="R3151eccf955844ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R8059f1b5c4a14860"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="Rd40e65ebd96347ee"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1327,16 +1327,16 @@
     <x:t xml:space="preserve">Streamed chat turns</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">QE-005</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Agent state and history</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">As a returning customer, I can reload session state and chat history.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">BFF exposes session state and message history by session id with authorization boundaries.</x:t>
+    <x:t xml:space="preserve">QE-006</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Agent clean speech and thinking</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">As a customer, I get cleaned assistant speech and structured thinking/progress updates.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">BFF exposes clean-speech and thinking endpoints used by the assistant experience.</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Automated QuoteEngine suite passed 2026-06-23 after workspace cleanup</x:t>
@@ -1348,46 +1348,10 @@
     <x:t xml:space="preserve">No fix needed for this story from current QuoteEngine automated retest.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Shell/session restore -&gt; AgentController sessions/messages -&gt; SessionStore</x:t>
+    <x:t xml:space="preserve">Agent UI -&gt; clean-speech/thinking endpoints -&gt; QuoteAgentService</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">QuoteAgentLaunchShell.razor</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Session reload/history</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">AgentController GET sessions/{sessionId}, sessions/{sessionId}/messages</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QuoteAgentEndpointTests history auth | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QuoteEngine BFF, SessionStore, Auth</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Session state and message history</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Needs authenticated reload browser retest</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">AgentController.cs:132,142; QuoteAgentSessionStore.cs</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QE-006</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Agent clean speech and thinking</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">As a customer, I get cleaned assistant speech and structured thinking/progress updates.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">BFF exposes clean-speech and thinking endpoints used by the assistant experience.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Agent UI -&gt; clean-speech/thinking endpoints -&gt; QuoteAgentService</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Thinking/progress and speech cleanup surfaces</x:t>
@@ -5162,7 +5126,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2ec510e4a734287"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb233f994b1de4067"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8578,7 +8542,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb9839dc17aa49fc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R765a67ea39834959"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8937,85 +8901,85 @@
       </x:c>
     </x:row>
     <x:row r="6" ht="93.25" hidden="0">
-      <x:c r="A6" s="3" t="s">
-        <x:v>438</x:v>
-      </x:c>
-      <x:c r="B6" s="3" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C6" s="3" t="s">
-        <x:v>439</x:v>
-      </x:c>
-      <x:c r="D6" s="3" t="s">
-        <x:v>440</x:v>
-      </x:c>
-      <x:c r="E6" s="3" t="s">
-        <x:v>441</x:v>
-      </x:c>
-      <x:c r="F6" s="3" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="G6" s="3" t="s">
-        <x:v>442</x:v>
-      </x:c>
-      <x:c r="H6" s="3" t="s">
-        <x:v>443</x:v>
-      </x:c>
-      <x:c r="I6" s="3" t="s">
-        <x:v>444</x:v>
-      </x:c>
-      <x:c r="J6" s="3" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="K6" s="3" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="L6" s="3" t="s">
-        <x:v>445</x:v>
-      </x:c>
-      <x:c r="M6" s="3" t="s">
-        <x:v>446</x:v>
-      </x:c>
-      <x:c r="N6" s="3" t="s">
-        <x:v>447</x:v>
-      </x:c>
-      <x:c r="O6" s="3" t="s">
-        <x:v>448</x:v>
-      </x:c>
-      <x:c r="P6" s="3" t="s">
-        <x:v>449</x:v>
-      </x:c>
-      <x:c r="Q6" s="3" t="s">
-        <x:v>450</x:v>
-      </x:c>
-      <x:c r="R6" s="3" t="s">
-        <x:v>451</x:v>
-      </x:c>
-      <x:c r="S6" s="3" t="s">
-        <x:v>452</x:v>
-      </x:c>
-      <x:c r="T6" s="3" t="s">
-        <x:v>453</x:v>
-      </x:c>
-      <x:c r="U6" s="3" t="s">
-        <x:v>52</x:v>
+      <x:c r="A6" s="3" t="str">
+        <x:v>QE-005</x:v>
+      </x:c>
+      <x:c r="B6" s="3" t="str">
+        <x:v>Maliev.QuoteEngine</x:v>
+      </x:c>
+      <x:c r="C6" s="3" t="str">
+        <x:v>Agent state and history</x:v>
+      </x:c>
+      <x:c r="D6" s="3" t="str">
+        <x:v>As a returning customer, I can reload session state and chat history.</x:v>
+      </x:c>
+      <x:c r="E6" s="3" t="str">
+        <x:v>Returning customers reload the same QuoteEngine agent session, state, and customer-safe chat history after page reload or auth return; another signed-in customer cannot read the session.</x:v>
+      </x:c>
+      <x:c r="F6" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G6" s="3" t="str">
+        <x:v>Focused current-state state/history tests passed 2026-06-24.</x:v>
+      </x:c>
+      <x:c r="H6" s="3" t="str">
+        <x:v>No behavior error observed in focused QuoteEngine state/history retest; live authenticated browser reload still not executed in this slice.</x:v>
+      </x:c>
+      <x:c r="I6" s="3" t="str">
+        <x:v>No app fix applied for QE-005; current code path is covered by focused BFF/source tests.</x:v>
+      </x:c>
+      <x:c r="J6" s="3" t="str">
+        <x:v>Passed 8/8 focused tests: QuoteAgentEndpointTests message-history mapping, persisted cold-store mapping, signed-in restore, cross-customer denial, injected-context stripping, and QuoteEngineSourceTests auth-completion/history contract.</x:v>
+      </x:c>
+      <x:c r="K6" s="3" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="L6" s="3" t="str">
+        <x:v>QuoteWorkspace shared session persistence/auth return -&gt; QuoteAgentLaunchShell state/history hydration -&gt; QuoteEngineApiClient -&gt; AgentController session/message endpoints -&gt; QuoteAgentSessionStore and chatbot conversation mapping</x:v>
+      </x:c>
+      <x:c r="M6" s="3" t="str">
+        <x:v>QuoteWorkspace.razor; QuoteAgentLaunchShell.razor; QuoteEngineApiClient; AgentController; QuoteAgentSessionStore</x:v>
+      </x:c>
+      <x:c r="N6" s="3" t="str">
+        <x:v>QuoteWorkspace RestoreAgentSessionAsync/PersistAgentSessionAsync use malievChatbot shared session storage; QuoteAgentLaunchShell OnAuthPopupCompleted forces reload and LoadMessageHistoryAsync hydrates AgentMessageRow history.</x:v>
+      </x:c>
+      <x:c r="O6" s="3" t="str">
+        <x:v>GET quote/v1/agent/sessions/{sessionId}; GET quote/v1/agent/sessions/{sessionId}/messages resolves the mapped chatbot conversation, filters customer-safe roles, strips injected user-turn context, and returns NotFound when no accessible mapping exists.</x:v>
+      </x:c>
+      <x:c r="P6" s="3" t="str">
+        <x:v>2026-06-24: dotnet test Maliev.QuoteEngine.slnx --filter "FullyQualifiedName~QuoteAgentEndpointTests.Agent_message_history_uses_mapped_chatbot_session_after_auth_return|FullyQualifiedName~QuoteAgentEndpointTests.Agent_message_history_uses_persisted_mapping_when_session_store_is_cold|FullyQualifiedName~QuoteAgentEndpointTests.Agent_message_history_restores_signed_in_customer_mapping_after_auth_return|FullyQualifiedName~QuoteAgentEndpointTests.Agent_message_history_denies_signed_in_customer_for_another_customers_session|FullyQualifiedName~QuoteAgentEndpointTests.Agent_message_history_strips_injected_session_context_from_persisted_user_turns|FullyQualifiedName~QuoteAgentEndpointTests.Agent_message_history_keeps_legacy_user_content_unmodified_when_no_context_marker_present|FullyQualifiedName~QuoteEngineSourceTests.QuoteAgentLaunchShell_auth_completion_reloads_active_session_and_hydrates_messages|FullyQualifiedName~QuoteEngineSourceTests.QuoteAgentLaunchShell_has_monochrome_chatgpt_like_contract" --verbosity minimal passed 8/8.</x:v>
+      </x:c>
+      <x:c r="Q6" s="3" t="str">
+        <x:v>QuoteEngine Client, QuoteEngine BFF, QuoteAgentSessionStore, chatbot conversation service, Auth/session</x:v>
+      </x:c>
+      <x:c r="R6" s="3" t="str">
+        <x:v>Shared browser session id, QuoteEngine agent session state, chatbot conversation mapping, restored message history</x:v>
+      </x:c>
+      <x:c r="S6" s="3" t="str">
+        <x:v>Needs authenticated reload browser retest against a running QuoteEngine host.</x:v>
+      </x:c>
+      <x:c r="T6" s="3" t="str">
+        <x:v>Maliev.QuoteEngine.Client/Pages/QuoteWorkspace.razor:1508; Maliev.QuoteEngine.Client/Components/QuoteAgent/QuoteAgentLaunchShell.razor:2603,2690; Maliev.QuoteEngine.Client/Services/QuoteEngineApiClient.cs:373; Maliev.QuoteEngine.Bff/Controllers/AgentController.cs:132,142; Maliev.QuoteEngine.Tests/QuoteAgentEndpointTests.cs:243; Maliev.QuoteEngine.Tests/QuoteEngineSourceTests.cs:2184</x:v>
+      </x:c>
+      <x:c r="U6" s="3" t="str">
+        <x:v>2026-06-24</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="93.25" hidden="0">
       <x:c r="A7" s="3" t="s">
-        <x:v>454</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>455</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="D7" s="3" t="s">
-        <x:v>456</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="E7" s="3" t="s">
-        <x:v>457</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="F7" s="3" t="s">
         <x:v>37</x:v>
@@ -9036,31 +9000,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="L7" s="3" t="s">
-        <x:v>458</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="M7" s="3" t="s">
         <x:v>446</x:v>
       </x:c>
       <x:c r="N7" s="3" t="s">
-        <x:v>459</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="O7" s="3" t="s">
-        <x:v>460</x:v>
+        <x:v>448</x:v>
       </x:c>
       <x:c r="P7" s="3" t="s">
-        <x:v>461</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="Q7" s="3" t="s">
-        <x:v>462</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="R7" s="3" t="s">
-        <x:v>463</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="S7" s="3" t="s">
-        <x:v>464</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="T7" s="3" t="s">
-        <x:v>465</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="U7" s="3" t="s">
         <x:v>52</x:v>
@@ -9068,19 +9032,19 @@
     </x:row>
     <x:row r="8" ht="93.25" hidden="0">
       <x:c r="A8" s="3" t="s">
-        <x:v>466</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>467</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="D8" s="3" t="s">
-        <x:v>468</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="E8" s="3" t="s">
-        <x:v>469</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="F8" s="3" t="s">
         <x:v>37</x:v>
@@ -9101,31 +9065,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L8" s="3" t="s">
-        <x:v>470</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="M8" s="3" t="s">
         <x:v>446</x:v>
       </x:c>
       <x:c r="N8" s="3" t="s">
-        <x:v>471</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="O8" s="3" t="s">
-        <x:v>472</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="P8" s="3" t="s">
-        <x:v>473</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="Q8" s="3" t="s">
-        <x:v>474</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
-        <x:v>475</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="S8" s="3" t="s">
-        <x:v>476</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="T8" s="3" t="s">
-        <x:v>477</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="U8" s="3" t="s">
         <x:v>52</x:v>
@@ -9133,19 +9097,19 @@
     </x:row>
     <x:row r="9" ht="93.25" hidden="0">
       <x:c r="A9" s="3" t="s">
-        <x:v>478</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="B9" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C9" s="3" t="s">
-        <x:v>479</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="D9" s="3" t="s">
-        <x:v>480</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="E9" s="3" t="s">
-        <x:v>481</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="F9" s="3" t="s">
         <x:v>37</x:v>
@@ -9166,31 +9130,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L9" s="3" t="s">
-        <x:v>482</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="M9" s="3" t="s">
         <x:v>446</x:v>
       </x:c>
       <x:c r="N9" s="3" t="s">
-        <x:v>483</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="O9" s="3" t="s">
-        <x:v>484</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="P9" s="3" t="s">
-        <x:v>485</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="Q9" s="3" t="s">
-        <x:v>486</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
-        <x:v>487</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="S9" s="3" t="s">
-        <x:v>488</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="T9" s="3" t="s">
-        <x:v>489</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="U9" s="3" t="s">
         <x:v>52</x:v>
@@ -9198,19 +9162,19 @@
     </x:row>
     <x:row r="10" ht="93.25" hidden="0">
       <x:c r="A10" s="3" t="s">
-        <x:v>490</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="B10" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C10" s="3" t="s">
-        <x:v>491</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="D10" s="3" t="s">
-        <x:v>492</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="E10" s="3" t="s">
-        <x:v>493</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="F10" s="3" t="s">
         <x:v>37</x:v>
@@ -9231,31 +9195,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L10" s="3" t="s">
-        <x:v>494</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="M10" s="3" t="s">
         <x:v>424</x:v>
       </x:c>
       <x:c r="N10" s="3" t="s">
-        <x:v>495</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="O10" s="3" t="s">
         <x:v>205</x:v>
       </x:c>
       <x:c r="P10" s="3" t="s">
-        <x:v>496</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="Q10" s="3" t="s">
-        <x:v>497</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="R10" s="3" t="s">
-        <x:v>498</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="S10" s="3" t="s">
-        <x:v>499</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="T10" s="3" t="s">
-        <x:v>500</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="U10" s="3" t="s">
         <x:v>52</x:v>
@@ -9263,19 +9227,19 @@
     </x:row>
     <x:row r="11" ht="93.25" hidden="0">
       <x:c r="A11" s="3" t="s">
-        <x:v>501</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="B11" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C11" s="3" t="s">
-        <x:v>502</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="D11" s="3" t="s">
-        <x:v>503</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="E11" s="3" t="s">
-        <x:v>504</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="F11" s="3" t="s">
         <x:v>37</x:v>
@@ -9296,31 +9260,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L11" s="3" t="s">
-        <x:v>505</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="M11" s="3" t="s">
-        <x:v>506</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="N11" s="3" t="s">
-        <x:v>507</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="O11" s="3" t="s">
-        <x:v>508</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="P11" s="3" t="s">
-        <x:v>509</x:v>
+        <x:v>497</x:v>
       </x:c>
       <x:c r="Q11" s="3" t="s">
-        <x:v>510</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="R11" s="3" t="s">
-        <x:v>511</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="S11" s="3" t="s">
-        <x:v>512</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="T11" s="3" t="s">
-        <x:v>513</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="U11" s="3" t="s">
         <x:v>52</x:v>
@@ -9328,19 +9292,19 @@
     </x:row>
     <x:row r="12" ht="107.25" hidden="0">
       <x:c r="A12" s="3" t="s">
-        <x:v>514</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="B12" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C12" s="3" t="s">
-        <x:v>515</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="D12" s="3" t="s">
-        <x:v>516</x:v>
+        <x:v>504</x:v>
       </x:c>
       <x:c r="E12" s="3" t="s">
-        <x:v>517</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="F12" s="3" t="s">
         <x:v>37</x:v>
@@ -9361,31 +9325,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L12" s="3" t="s">
-        <x:v>518</x:v>
+        <x:v>506</x:v>
       </x:c>
       <x:c r="M12" s="3" t="s">
         <x:v>446</x:v>
       </x:c>
       <x:c r="N12" s="3" t="s">
-        <x:v>519</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="O12" s="3" t="s">
-        <x:v>520</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="P12" s="3" t="s">
-        <x:v>521</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="Q12" s="3" t="s">
-        <x:v>522</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="R12" s="3" t="s">
-        <x:v>523</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="S12" s="3" t="s">
-        <x:v>524</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="T12" s="3" t="s">
-        <x:v>525</x:v>
+        <x:v>513</x:v>
       </x:c>
       <x:c r="U12" s="3" t="s">
         <x:v>52</x:v>
@@ -9393,19 +9357,19 @@
     </x:row>
     <x:row r="13" ht="93.25" hidden="0">
       <x:c r="A13" s="3" t="s">
-        <x:v>526</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="B13" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C13" s="3" t="s">
-        <x:v>527</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="D13" s="3" t="s">
-        <x:v>528</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="E13" s="3" t="s">
-        <x:v>529</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="F13" s="3" t="s">
         <x:v>37</x:v>
@@ -9426,31 +9390,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L13" s="3" t="s">
-        <x:v>530</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="M13" s="3" t="s">
         <x:v>446</x:v>
       </x:c>
       <x:c r="N13" s="3" t="s">
-        <x:v>531</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="O13" s="3" t="s">
-        <x:v>532</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="P13" s="3" t="s">
-        <x:v>533</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="Q13" s="3" t="s">
+        <x:v>510</x:v>
+      </x:c>
+      <x:c r="R13" s="3" t="s">
         <x:v>522</x:v>
       </x:c>
-      <x:c r="R13" s="3" t="s">
-        <x:v>534</x:v>
-      </x:c>
       <x:c r="S13" s="3" t="s">
-        <x:v>535</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="T13" s="3" t="s">
-        <x:v>536</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="U13" s="3" t="s">
         <x:v>52</x:v>
@@ -9458,19 +9422,19 @@
     </x:row>
     <x:row r="14" ht="93.25" hidden="0">
       <x:c r="A14" s="3" t="s">
-        <x:v>537</x:v>
+        <x:v>525</x:v>
       </x:c>
       <x:c r="B14" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C14" s="3" t="s">
-        <x:v>538</x:v>
+        <x:v>526</x:v>
       </x:c>
       <x:c r="D14" s="3" t="s">
-        <x:v>539</x:v>
+        <x:v>527</x:v>
       </x:c>
       <x:c r="E14" s="3" t="s">
-        <x:v>540</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="F14" s="3" t="s">
         <x:v>37</x:v>
@@ -9491,31 +9455,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L14" s="3" t="s">
-        <x:v>541</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="M14" s="3" t="s">
-        <x:v>542</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="N14" s="3" t="s">
-        <x:v>543</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="O14" s="3" t="s">
-        <x:v>544</x:v>
+        <x:v>532</x:v>
       </x:c>
       <x:c r="P14" s="3" t="s">
-        <x:v>545</x:v>
+        <x:v>533</x:v>
       </x:c>
       <x:c r="Q14" s="3" t="s">
-        <x:v>546</x:v>
+        <x:v>534</x:v>
       </x:c>
       <x:c r="R14" s="3" t="s">
-        <x:v>547</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="S14" s="3" t="s">
-        <x:v>548</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="T14" s="3" t="s">
-        <x:v>549</x:v>
+        <x:v>537</x:v>
       </x:c>
       <x:c r="U14" s="3" t="s">
         <x:v>52</x:v>
@@ -9523,19 +9487,19 @@
     </x:row>
     <x:row r="15" ht="107.25" hidden="0">
       <x:c r="A15" s="3" t="s">
-        <x:v>550</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="B15" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C15" s="3" t="s">
-        <x:v>551</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="D15" s="3" t="s">
-        <x:v>552</x:v>
+        <x:v>540</x:v>
       </x:c>
       <x:c r="E15" s="3" t="s">
-        <x:v>553</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="F15" s="3" t="s">
         <x:v>37</x:v>
@@ -9556,31 +9520,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L15" s="3" t="s">
-        <x:v>554</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="M15" s="3" t="s">
         <x:v>446</x:v>
       </x:c>
       <x:c r="N15" s="3" t="s">
-        <x:v>555</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="O15" s="3" t="s">
-        <x:v>556</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="P15" s="3" t="s">
-        <x:v>557</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="Q15" s="3" t="s">
-        <x:v>558</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="R15" s="3" t="s">
-        <x:v>559</x:v>
+        <x:v>547</x:v>
       </x:c>
       <x:c r="S15" s="3" t="s">
-        <x:v>560</x:v>
+        <x:v>548</x:v>
       </x:c>
       <x:c r="T15" s="3" t="s">
-        <x:v>561</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="U15" s="3" t="s">
         <x:v>52</x:v>
@@ -9588,19 +9552,19 @@
     </x:row>
     <x:row r="16" ht="107.25" hidden="0">
       <x:c r="A16" s="3" t="s">
-        <x:v>562</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="B16" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C16" s="3" t="s">
-        <x:v>563</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="D16" s="3" t="s">
-        <x:v>564</x:v>
+        <x:v>552</x:v>
       </x:c>
       <x:c r="E16" s="3" t="s">
-        <x:v>565</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="F16" s="3" t="s">
         <x:v>37</x:v>
@@ -9621,31 +9585,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L16" s="3" t="s">
-        <x:v>566</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="M16" s="3" t="s">
         <x:v>446</x:v>
       </x:c>
       <x:c r="N16" s="3" t="s">
-        <x:v>567</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="O16" s="3" t="s">
-        <x:v>568</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="P16" s="3" t="s">
-        <x:v>569</x:v>
+        <x:v>557</x:v>
       </x:c>
       <x:c r="Q16" s="3" t="s">
-        <x:v>570</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="R16" s="3" t="s">
-        <x:v>571</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="S16" s="3" t="s">
-        <x:v>572</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="T16" s="3" t="s">
-        <x:v>573</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="U16" s="3" t="s">
         <x:v>52</x:v>
@@ -9653,19 +9617,19 @@
     </x:row>
     <x:row r="17" ht="93.25" hidden="0">
       <x:c r="A17" s="3" t="s">
-        <x:v>574</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="B17" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C17" s="3" t="s">
-        <x:v>575</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="D17" s="3" t="s">
-        <x:v>576</x:v>
+        <x:v>564</x:v>
       </x:c>
       <x:c r="E17" s="3" t="s">
-        <x:v>577</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="F17" s="3" t="s">
         <x:v>37</x:v>
@@ -9686,31 +9650,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L17" s="3" t="s">
-        <x:v>578</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="M17" s="3" t="s">
-        <x:v>579</x:v>
+        <x:v>567</x:v>
       </x:c>
       <x:c r="N17" s="3" t="s">
-        <x:v>580</x:v>
+        <x:v>568</x:v>
       </x:c>
       <x:c r="O17" s="3" t="s">
-        <x:v>581</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="P17" s="3" t="s">
-        <x:v>582</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="Q17" s="3" t="s">
-        <x:v>583</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="R17" s="3" t="s">
-        <x:v>584</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="S17" s="3" t="s">
-        <x:v>585</x:v>
+        <x:v>573</x:v>
       </x:c>
       <x:c r="T17" s="3" t="s">
-        <x:v>586</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="U17" s="3" t="s">
         <x:v>52</x:v>
@@ -9718,19 +9682,19 @@
     </x:row>
     <x:row r="18" ht="93.25" hidden="0">
       <x:c r="A18" s="3" t="s">
-        <x:v>587</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="B18" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C18" s="3" t="s">
-        <x:v>588</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="D18" s="3" t="s">
-        <x:v>589</x:v>
+        <x:v>577</x:v>
       </x:c>
       <x:c r="E18" s="3" t="s">
-        <x:v>590</x:v>
+        <x:v>578</x:v>
       </x:c>
       <x:c r="F18" s="3" t="s">
         <x:v>37</x:v>
@@ -9751,31 +9715,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L18" s="3" t="s">
-        <x:v>591</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="M18" s="3" t="s">
-        <x:v>592</x:v>
+        <x:v>580</x:v>
       </x:c>
       <x:c r="N18" s="3" t="s">
-        <x:v>593</x:v>
+        <x:v>581</x:v>
       </x:c>
       <x:c r="O18" s="3" t="s">
-        <x:v>594</x:v>
+        <x:v>582</x:v>
       </x:c>
       <x:c r="P18" s="3" t="s">
-        <x:v>595</x:v>
+        <x:v>583</x:v>
       </x:c>
       <x:c r="Q18" s="3" t="s">
-        <x:v>596</x:v>
+        <x:v>584</x:v>
       </x:c>
       <x:c r="R18" s="3" t="s">
-        <x:v>597</x:v>
+        <x:v>585</x:v>
       </x:c>
       <x:c r="S18" s="3" t="s">
-        <x:v>598</x:v>
+        <x:v>586</x:v>
       </x:c>
       <x:c r="T18" s="3" t="s">
-        <x:v>599</x:v>
+        <x:v>587</x:v>
       </x:c>
       <x:c r="U18" s="3" t="s">
         <x:v>52</x:v>
@@ -9783,19 +9747,19 @@
     </x:row>
     <x:row r="19" ht="93.25" hidden="0">
       <x:c r="A19" s="3" t="s">
-        <x:v>600</x:v>
+        <x:v>588</x:v>
       </x:c>
       <x:c r="B19" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C19" s="3" t="s">
-        <x:v>601</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="D19" s="3" t="s">
-        <x:v>602</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="E19" s="3" t="s">
-        <x:v>603</x:v>
+        <x:v>591</x:v>
       </x:c>
       <x:c r="F19" s="3" t="s">
         <x:v>37</x:v>
@@ -9816,31 +9780,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L19" s="3" t="s">
-        <x:v>604</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="M19" s="3" t="s">
-        <x:v>605</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="N19" s="3" t="s">
-        <x:v>606</x:v>
+        <x:v>594</x:v>
       </x:c>
       <x:c r="O19" s="3" t="s">
-        <x:v>607</x:v>
+        <x:v>595</x:v>
       </x:c>
       <x:c r="P19" s="3" t="s">
-        <x:v>608</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="Q19" s="3" t="s">
-        <x:v>609</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="R19" s="3" t="s">
-        <x:v>610</x:v>
+        <x:v>598</x:v>
       </x:c>
       <x:c r="S19" s="3" t="s">
-        <x:v>611</x:v>
+        <x:v>599</x:v>
       </x:c>
       <x:c r="T19" s="3" t="s">
-        <x:v>612</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="U19" s="3" t="s">
         <x:v>52</x:v>
@@ -9848,19 +9812,19 @@
     </x:row>
     <x:row r="20" ht="79.25" hidden="0">
       <x:c r="A20" s="3" t="s">
-        <x:v>613</x:v>
+        <x:v>601</x:v>
       </x:c>
       <x:c r="B20" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C20" s="3" t="s">
-        <x:v>614</x:v>
+        <x:v>602</x:v>
       </x:c>
       <x:c r="D20" s="3" t="s">
-        <x:v>615</x:v>
+        <x:v>603</x:v>
       </x:c>
       <x:c r="E20" s="3" t="s">
-        <x:v>616</x:v>
+        <x:v>604</x:v>
       </x:c>
       <x:c r="F20" s="3" t="s">
         <x:v>37</x:v>
@@ -9881,31 +9845,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L20" s="3" t="s">
-        <x:v>617</x:v>
+        <x:v>605</x:v>
       </x:c>
       <x:c r="M20" s="3" t="s">
-        <x:v>618</x:v>
+        <x:v>606</x:v>
       </x:c>
       <x:c r="N20" s="3" t="s">
-        <x:v>619</x:v>
+        <x:v>607</x:v>
       </x:c>
       <x:c r="O20" s="3" t="s">
-        <x:v>620</x:v>
+        <x:v>608</x:v>
       </x:c>
       <x:c r="P20" s="3" t="s">
-        <x:v>621</x:v>
+        <x:v>609</x:v>
       </x:c>
       <x:c r="Q20" s="3" t="s">
-        <x:v>622</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="R20" s="3" t="s">
-        <x:v>623</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="S20" s="3" t="s">
-        <x:v>624</x:v>
+        <x:v>612</x:v>
       </x:c>
       <x:c r="T20" s="3" t="s">
-        <x:v>625</x:v>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="U20" s="3" t="s">
         <x:v>52</x:v>
@@ -9913,19 +9877,19 @@
     </x:row>
     <x:row r="21" ht="79.25" hidden="0">
       <x:c r="A21" s="3" t="s">
-        <x:v>626</x:v>
+        <x:v>614</x:v>
       </x:c>
       <x:c r="B21" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C21" s="3" t="s">
-        <x:v>627</x:v>
+        <x:v>615</x:v>
       </x:c>
       <x:c r="D21" s="3" t="s">
-        <x:v>628</x:v>
+        <x:v>616</x:v>
       </x:c>
       <x:c r="E21" s="3" t="s">
-        <x:v>629</x:v>
+        <x:v>617</x:v>
       </x:c>
       <x:c r="F21" s="3" t="s">
         <x:v>37</x:v>
@@ -9946,31 +9910,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L21" s="3" t="s">
-        <x:v>630</x:v>
+        <x:v>618</x:v>
       </x:c>
       <x:c r="M21" s="3" t="s">
-        <x:v>631</x:v>
+        <x:v>619</x:v>
       </x:c>
       <x:c r="N21" s="3" t="s">
-        <x:v>632</x:v>
+        <x:v>620</x:v>
       </x:c>
       <x:c r="O21" s="3" t="s">
         <x:v>218</x:v>
       </x:c>
       <x:c r="P21" s="3" t="s">
-        <x:v>633</x:v>
+        <x:v>621</x:v>
       </x:c>
       <x:c r="Q21" s="3" t="s">
-        <x:v>634</x:v>
+        <x:v>622</x:v>
       </x:c>
       <x:c r="R21" s="3" t="s">
         <x:v>221</x:v>
       </x:c>
       <x:c r="S21" s="3" t="s">
-        <x:v>635</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="T21" s="3" t="s">
-        <x:v>636</x:v>
+        <x:v>624</x:v>
       </x:c>
       <x:c r="U21" s="3" t="s">
         <x:v>52</x:v>
@@ -9978,19 +9942,19 @@
     </x:row>
     <x:row r="22" ht="93.25" hidden="0">
       <x:c r="A22" s="3" t="s">
-        <x:v>637</x:v>
+        <x:v>625</x:v>
       </x:c>
       <x:c r="B22" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C22" s="3" t="s">
-        <x:v>638</x:v>
+        <x:v>626</x:v>
       </x:c>
       <x:c r="D22" s="3" t="s">
-        <x:v>639</x:v>
+        <x:v>627</x:v>
       </x:c>
       <x:c r="E22" s="3" t="s">
-        <x:v>640</x:v>
+        <x:v>628</x:v>
       </x:c>
       <x:c r="F22" s="3" t="s">
         <x:v>37</x:v>
@@ -10011,31 +9975,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L22" s="3" t="s">
-        <x:v>641</x:v>
+        <x:v>629</x:v>
       </x:c>
       <x:c r="M22" s="3" t="s">
-        <x:v>506</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="N22" s="3" t="s">
-        <x:v>642</x:v>
+        <x:v>630</x:v>
       </x:c>
       <x:c r="O22" s="3" t="s">
-        <x:v>643</x:v>
+        <x:v>631</x:v>
       </x:c>
       <x:c r="P22" s="3" t="s">
-        <x:v>644</x:v>
+        <x:v>632</x:v>
       </x:c>
       <x:c r="Q22" s="3" t="s">
-        <x:v>645</x:v>
+        <x:v>633</x:v>
       </x:c>
       <x:c r="R22" s="3" t="s">
-        <x:v>646</x:v>
+        <x:v>634</x:v>
       </x:c>
       <x:c r="S22" s="3" t="s">
-        <x:v>647</x:v>
+        <x:v>635</x:v>
       </x:c>
       <x:c r="T22" s="3" t="s">
-        <x:v>648</x:v>
+        <x:v>636</x:v>
       </x:c>
       <x:c r="U22" s="3" t="s">
         <x:v>52</x:v>
@@ -10043,19 +10007,19 @@
     </x:row>
     <x:row r="23" ht="93.25" hidden="0">
       <x:c r="A23" s="3" t="s">
-        <x:v>649</x:v>
+        <x:v>637</x:v>
       </x:c>
       <x:c r="B23" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C23" s="3" t="s">
-        <x:v>650</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="D23" s="3" t="s">
-        <x:v>651</x:v>
+        <x:v>639</x:v>
       </x:c>
       <x:c r="E23" s="3" t="s">
-        <x:v>652</x:v>
+        <x:v>640</x:v>
       </x:c>
       <x:c r="F23" s="3" t="s">
         <x:v>37</x:v>
@@ -10076,31 +10040,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L23" s="3" t="s">
-        <x:v>653</x:v>
+        <x:v>641</x:v>
       </x:c>
       <x:c r="M23" s="3" t="s">
-        <x:v>654</x:v>
+        <x:v>642</x:v>
       </x:c>
       <x:c r="N23" s="3" t="s">
-        <x:v>655</x:v>
+        <x:v>643</x:v>
       </x:c>
       <x:c r="O23" s="3" t="s">
-        <x:v>656</x:v>
+        <x:v>644</x:v>
       </x:c>
       <x:c r="P23" s="3" t="s">
-        <x:v>657</x:v>
+        <x:v>645</x:v>
       </x:c>
       <x:c r="Q23" s="3" t="s">
-        <x:v>658</x:v>
+        <x:v>646</x:v>
       </x:c>
       <x:c r="R23" s="3" t="s">
-        <x:v>659</x:v>
+        <x:v>647</x:v>
       </x:c>
       <x:c r="S23" s="3" t="s">
-        <x:v>660</x:v>
+        <x:v>648</x:v>
       </x:c>
       <x:c r="T23" s="3" t="s">
-        <x:v>661</x:v>
+        <x:v>649</x:v>
       </x:c>
       <x:c r="U23" s="3" t="s">
         <x:v>52</x:v>
@@ -10108,19 +10072,19 @@
     </x:row>
     <x:row r="24" ht="79.25" hidden="0">
       <x:c r="A24" s="3" t="s">
-        <x:v>662</x:v>
+        <x:v>650</x:v>
       </x:c>
       <x:c r="B24" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C24" s="3" t="s">
-        <x:v>663</x:v>
+        <x:v>651</x:v>
       </x:c>
       <x:c r="D24" s="3" t="s">
-        <x:v>664</x:v>
+        <x:v>652</x:v>
       </x:c>
       <x:c r="E24" s="3" t="s">
-        <x:v>665</x:v>
+        <x:v>653</x:v>
       </x:c>
       <x:c r="F24" s="3" t="s">
         <x:v>37</x:v>
@@ -10141,31 +10105,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L24" s="3" t="s">
-        <x:v>666</x:v>
+        <x:v>654</x:v>
       </x:c>
       <x:c r="M24" s="3" t="s">
-        <x:v>631</x:v>
+        <x:v>619</x:v>
       </x:c>
       <x:c r="N24" s="3" t="s">
-        <x:v>667</x:v>
+        <x:v>655</x:v>
       </x:c>
       <x:c r="O24" s="3" t="s">
-        <x:v>668</x:v>
+        <x:v>656</x:v>
       </x:c>
       <x:c r="P24" s="3" t="s">
-        <x:v>669</x:v>
+        <x:v>657</x:v>
       </x:c>
       <x:c r="Q24" s="3" t="s">
-        <x:v>670</x:v>
+        <x:v>658</x:v>
       </x:c>
       <x:c r="R24" s="3" t="s">
-        <x:v>671</x:v>
+        <x:v>659</x:v>
       </x:c>
       <x:c r="S24" s="3" t="s">
-        <x:v>672</x:v>
+        <x:v>660</x:v>
       </x:c>
       <x:c r="T24" s="3" t="s">
-        <x:v>673</x:v>
+        <x:v>661</x:v>
       </x:c>
       <x:c r="U24" s="3" t="s">
         <x:v>52</x:v>
@@ -10173,19 +10137,19 @@
     </x:row>
     <x:row r="25" ht="79.25" hidden="0">
       <x:c r="A25" s="3" t="s">
-        <x:v>674</x:v>
+        <x:v>662</x:v>
       </x:c>
       <x:c r="B25" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C25" s="3" t="s">
-        <x:v>675</x:v>
+        <x:v>663</x:v>
       </x:c>
       <x:c r="D25" s="3" t="s">
-        <x:v>676</x:v>
+        <x:v>664</x:v>
       </x:c>
       <x:c r="E25" s="3" t="s">
-        <x:v>677</x:v>
+        <x:v>665</x:v>
       </x:c>
       <x:c r="F25" s="3" t="s">
         <x:v>37</x:v>
@@ -10206,31 +10170,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L25" s="3" t="s">
-        <x:v>678</x:v>
+        <x:v>666</x:v>
       </x:c>
       <x:c r="M25" s="3" t="s">
-        <x:v>631</x:v>
+        <x:v>619</x:v>
       </x:c>
       <x:c r="N25" s="3" t="s">
-        <x:v>679</x:v>
+        <x:v>667</x:v>
       </x:c>
       <x:c r="O25" s="3" t="s">
-        <x:v>680</x:v>
+        <x:v>668</x:v>
       </x:c>
       <x:c r="P25" s="3" t="s">
-        <x:v>681</x:v>
+        <x:v>669</x:v>
       </x:c>
       <x:c r="Q25" s="3" t="s">
-        <x:v>682</x:v>
+        <x:v>670</x:v>
       </x:c>
       <x:c r="R25" s="3" t="s">
-        <x:v>683</x:v>
+        <x:v>671</x:v>
       </x:c>
       <x:c r="S25" s="3" t="s">
-        <x:v>684</x:v>
+        <x:v>672</x:v>
       </x:c>
       <x:c r="T25" s="3" t="s">
-        <x:v>685</x:v>
+        <x:v>673</x:v>
       </x:c>
       <x:c r="U25" s="3" t="s">
         <x:v>52</x:v>
@@ -10238,19 +10202,19 @@
     </x:row>
     <x:row r="26" ht="79.25" hidden="0">
       <x:c r="A26" s="3" t="s">
-        <x:v>686</x:v>
+        <x:v>674</x:v>
       </x:c>
       <x:c r="B26" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C26" s="3" t="s">
-        <x:v>687</x:v>
+        <x:v>675</x:v>
       </x:c>
       <x:c r="D26" s="3" t="s">
-        <x:v>688</x:v>
+        <x:v>676</x:v>
       </x:c>
       <x:c r="E26" s="3" t="s">
-        <x:v>689</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="F26" s="3" t="s">
         <x:v>37</x:v>
@@ -10271,31 +10235,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L26" s="3" t="s">
-        <x:v>690</x:v>
+        <x:v>678</x:v>
       </x:c>
       <x:c r="M26" s="3" t="s">
-        <x:v>691</x:v>
+        <x:v>679</x:v>
       </x:c>
       <x:c r="N26" s="3" t="s">
-        <x:v>692</x:v>
+        <x:v>680</x:v>
       </x:c>
       <x:c r="O26" s="3" t="s">
-        <x:v>693</x:v>
+        <x:v>681</x:v>
       </x:c>
       <x:c r="P26" s="3" t="s">
-        <x:v>694</x:v>
+        <x:v>682</x:v>
       </x:c>
       <x:c r="Q26" s="3" t="s">
-        <x:v>695</x:v>
+        <x:v>683</x:v>
       </x:c>
       <x:c r="R26" s="3" t="s">
-        <x:v>696</x:v>
+        <x:v>684</x:v>
       </x:c>
       <x:c r="S26" s="3" t="s">
-        <x:v>697</x:v>
+        <x:v>685</x:v>
       </x:c>
       <x:c r="T26" s="3" t="s">
-        <x:v>698</x:v>
+        <x:v>686</x:v>
       </x:c>
       <x:c r="U26" s="3" t="s">
         <x:v>52</x:v>
@@ -10303,19 +10267,19 @@
     </x:row>
     <x:row r="27" ht="79.25" hidden="0">
       <x:c r="A27" s="3" t="s">
-        <x:v>699</x:v>
+        <x:v>687</x:v>
       </x:c>
       <x:c r="B27" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C27" s="3" t="s">
-        <x:v>700</x:v>
+        <x:v>688</x:v>
       </x:c>
       <x:c r="D27" s="3" t="s">
-        <x:v>701</x:v>
+        <x:v>689</x:v>
       </x:c>
       <x:c r="E27" s="3" t="s">
-        <x:v>702</x:v>
+        <x:v>690</x:v>
       </x:c>
       <x:c r="F27" s="3" t="s">
         <x:v>37</x:v>
@@ -10336,31 +10300,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L27" s="3" t="s">
-        <x:v>703</x:v>
+        <x:v>691</x:v>
       </x:c>
       <x:c r="M27" s="3" t="s">
-        <x:v>704</x:v>
+        <x:v>692</x:v>
       </x:c>
       <x:c r="N27" s="3" t="s">
-        <x:v>705</x:v>
+        <x:v>693</x:v>
       </x:c>
       <x:c r="O27" s="3" t="s">
-        <x:v>706</x:v>
+        <x:v>694</x:v>
       </x:c>
       <x:c r="P27" s="3" t="s">
-        <x:v>707</x:v>
+        <x:v>695</x:v>
       </x:c>
       <x:c r="Q27" s="3" t="s">
-        <x:v>708</x:v>
+        <x:v>696</x:v>
       </x:c>
       <x:c r="R27" s="3" t="s">
-        <x:v>709</x:v>
+        <x:v>697</x:v>
       </x:c>
       <x:c r="S27" s="3" t="s">
-        <x:v>710</x:v>
+        <x:v>698</x:v>
       </x:c>
       <x:c r="T27" s="3" t="s">
-        <x:v>711</x:v>
+        <x:v>699</x:v>
       </x:c>
       <x:c r="U27" s="3" t="s">
         <x:v>52</x:v>
@@ -10368,19 +10332,19 @@
     </x:row>
     <x:row r="28" ht="93.25" hidden="0">
       <x:c r="A28" s="3" t="s">
-        <x:v>712</x:v>
+        <x:v>700</x:v>
       </x:c>
       <x:c r="B28" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C28" s="3" t="s">
-        <x:v>713</x:v>
+        <x:v>701</x:v>
       </x:c>
       <x:c r="D28" s="3" t="s">
-        <x:v>714</x:v>
+        <x:v>702</x:v>
       </x:c>
       <x:c r="E28" s="3" t="s">
-        <x:v>715</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="F28" s="3" t="s">
         <x:v>37</x:v>
@@ -10401,31 +10365,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L28" s="3" t="s">
-        <x:v>716</x:v>
+        <x:v>704</x:v>
       </x:c>
       <x:c r="M28" s="3" t="s">
-        <x:v>717</x:v>
+        <x:v>705</x:v>
       </x:c>
       <x:c r="N28" s="3" t="s">
-        <x:v>718</x:v>
+        <x:v>706</x:v>
       </x:c>
       <x:c r="O28" s="3" t="s">
-        <x:v>719</x:v>
+        <x:v>707</x:v>
       </x:c>
       <x:c r="P28" s="3" t="s">
-        <x:v>720</x:v>
+        <x:v>708</x:v>
       </x:c>
       <x:c r="Q28" s="3" t="s">
-        <x:v>721</x:v>
+        <x:v>709</x:v>
       </x:c>
       <x:c r="R28" s="3" t="s">
-        <x:v>722</x:v>
+        <x:v>710</x:v>
       </x:c>
       <x:c r="S28" s="3" t="s">
         <x:v>286</x:v>
       </x:c>
       <x:c r="T28" s="3" t="s">
-        <x:v>723</x:v>
+        <x:v>711</x:v>
       </x:c>
       <x:c r="U28" s="3" t="s">
         <x:v>52</x:v>
@@ -10433,19 +10397,19 @@
     </x:row>
     <x:row r="29" ht="93.25" hidden="0">
       <x:c r="A29" s="3" t="s">
-        <x:v>724</x:v>
+        <x:v>712</x:v>
       </x:c>
       <x:c r="B29" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C29" s="3" t="s">
-        <x:v>725</x:v>
+        <x:v>713</x:v>
       </x:c>
       <x:c r="D29" s="3" t="s">
-        <x:v>726</x:v>
+        <x:v>714</x:v>
       </x:c>
       <x:c r="E29" s="3" t="s">
-        <x:v>727</x:v>
+        <x:v>715</x:v>
       </x:c>
       <x:c r="F29" s="3" t="s">
         <x:v>37</x:v>
@@ -10466,31 +10430,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="L29" s="3" t="s">
-        <x:v>728</x:v>
+        <x:v>716</x:v>
       </x:c>
       <x:c r="M29" s="3" t="s">
-        <x:v>729</x:v>
+        <x:v>717</x:v>
       </x:c>
       <x:c r="N29" s="3" t="s">
-        <x:v>730</x:v>
+        <x:v>718</x:v>
       </x:c>
       <x:c r="O29" s="3" t="s">
-        <x:v>731</x:v>
+        <x:v>719</x:v>
       </x:c>
       <x:c r="P29" s="3" t="s">
-        <x:v>732</x:v>
+        <x:v>720</x:v>
       </x:c>
       <x:c r="Q29" s="3" t="s">
-        <x:v>733</x:v>
+        <x:v>721</x:v>
       </x:c>
       <x:c r="R29" s="3" t="s">
-        <x:v>734</x:v>
+        <x:v>722</x:v>
       </x:c>
       <x:c r="S29" s="3" t="s">
-        <x:v>735</x:v>
+        <x:v>723</x:v>
       </x:c>
       <x:c r="T29" s="3" t="s">
-        <x:v>736</x:v>
+        <x:v>724</x:v>
       </x:c>
       <x:c r="U29" s="3" t="s">
         <x:v>52</x:v>
@@ -10498,19 +10462,19 @@
     </x:row>
     <x:row r="30" ht="93.25" hidden="0">
       <x:c r="A30" s="3" t="s">
-        <x:v>737</x:v>
+        <x:v>725</x:v>
       </x:c>
       <x:c r="B30" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C30" s="3" t="s">
-        <x:v>738</x:v>
+        <x:v>726</x:v>
       </x:c>
       <x:c r="D30" s="3" t="s">
-        <x:v>739</x:v>
+        <x:v>727</x:v>
       </x:c>
       <x:c r="E30" s="3" t="s">
-        <x:v>740</x:v>
+        <x:v>728</x:v>
       </x:c>
       <x:c r="F30" s="3" t="s">
         <x:v>37</x:v>
@@ -10531,31 +10495,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L30" s="3" t="s">
-        <x:v>741</x:v>
+        <x:v>729</x:v>
       </x:c>
       <x:c r="M30" s="3" t="s">
-        <x:v>742</x:v>
+        <x:v>730</x:v>
       </x:c>
       <x:c r="N30" s="3" t="s">
-        <x:v>743</x:v>
+        <x:v>731</x:v>
       </x:c>
       <x:c r="O30" s="3" t="s">
-        <x:v>744</x:v>
+        <x:v>732</x:v>
       </x:c>
       <x:c r="P30" s="3" t="s">
-        <x:v>745</x:v>
+        <x:v>733</x:v>
       </x:c>
       <x:c r="Q30" s="3" t="s">
-        <x:v>746</x:v>
+        <x:v>734</x:v>
       </x:c>
       <x:c r="R30" s="3" t="s">
-        <x:v>747</x:v>
+        <x:v>735</x:v>
       </x:c>
       <x:c r="S30" s="3" t="s">
-        <x:v>748</x:v>
+        <x:v>736</x:v>
       </x:c>
       <x:c r="T30" s="3" t="s">
-        <x:v>749</x:v>
+        <x:v>737</x:v>
       </x:c>
       <x:c r="U30" s="3" t="s">
         <x:v>52</x:v>
@@ -10563,19 +10527,19 @@
     </x:row>
     <x:row r="31" ht="93.25" hidden="0">
       <x:c r="A31" s="3" t="s">
-        <x:v>750</x:v>
+        <x:v>738</x:v>
       </x:c>
       <x:c r="B31" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C31" s="3" t="s">
-        <x:v>751</x:v>
+        <x:v>739</x:v>
       </x:c>
       <x:c r="D31" s="3" t="s">
-        <x:v>752</x:v>
+        <x:v>740</x:v>
       </x:c>
       <x:c r="E31" s="3" t="s">
-        <x:v>753</x:v>
+        <x:v>741</x:v>
       </x:c>
       <x:c r="F31" s="3" t="s">
         <x:v>37</x:v>
@@ -10596,31 +10560,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="L31" s="3" t="s">
-        <x:v>754</x:v>
+        <x:v>742</x:v>
       </x:c>
       <x:c r="M31" s="3" t="s">
-        <x:v>755</x:v>
+        <x:v>743</x:v>
       </x:c>
       <x:c r="N31" s="3" t="s">
-        <x:v>756</x:v>
+        <x:v>744</x:v>
       </x:c>
       <x:c r="O31" s="3" t="s">
-        <x:v>757</x:v>
+        <x:v>745</x:v>
       </x:c>
       <x:c r="P31" s="3" t="s">
-        <x:v>758</x:v>
+        <x:v>746</x:v>
       </x:c>
       <x:c r="Q31" s="3" t="s">
-        <x:v>759</x:v>
+        <x:v>747</x:v>
       </x:c>
       <x:c r="R31" s="3" t="s">
-        <x:v>760</x:v>
+        <x:v>748</x:v>
       </x:c>
       <x:c r="S31" s="3" t="s">
-        <x:v>761</x:v>
+        <x:v>749</x:v>
       </x:c>
       <x:c r="T31" s="3" t="s">
-        <x:v>762</x:v>
+        <x:v>750</x:v>
       </x:c>
       <x:c r="U31" s="3" t="s">
         <x:v>52</x:v>
@@ -10628,19 +10592,19 @@
     </x:row>
     <x:row r="32" ht="93.25" hidden="0">
       <x:c r="A32" s="3" t="s">
-        <x:v>763</x:v>
+        <x:v>751</x:v>
       </x:c>
       <x:c r="B32" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C32" s="3" t="s">
-        <x:v>764</x:v>
+        <x:v>752</x:v>
       </x:c>
       <x:c r="D32" s="3" t="s">
-        <x:v>765</x:v>
+        <x:v>753</x:v>
       </x:c>
       <x:c r="E32" s="3" t="s">
-        <x:v>766</x:v>
+        <x:v>754</x:v>
       </x:c>
       <x:c r="F32" s="3" t="s">
         <x:v>37</x:v>
@@ -10661,31 +10625,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L32" s="3" t="s">
-        <x:v>767</x:v>
+        <x:v>755</x:v>
       </x:c>
       <x:c r="M32" s="3" t="s">
-        <x:v>768</x:v>
+        <x:v>756</x:v>
       </x:c>
       <x:c r="N32" s="3" t="s">
-        <x:v>769</x:v>
+        <x:v>757</x:v>
       </x:c>
       <x:c r="O32" s="3" t="s">
-        <x:v>770</x:v>
+        <x:v>758</x:v>
       </x:c>
       <x:c r="P32" s="3" t="s">
-        <x:v>771</x:v>
+        <x:v>759</x:v>
       </x:c>
       <x:c r="Q32" s="3" t="s">
-        <x:v>772</x:v>
+        <x:v>760</x:v>
       </x:c>
       <x:c r="R32" s="3" t="s">
-        <x:v>773</x:v>
+        <x:v>761</x:v>
       </x:c>
       <x:c r="S32" s="3" t="s">
-        <x:v>774</x:v>
+        <x:v>762</x:v>
       </x:c>
       <x:c r="T32" s="3" t="s">
-        <x:v>775</x:v>
+        <x:v>763</x:v>
       </x:c>
       <x:c r="U32" s="3" t="s">
         <x:v>52</x:v>
@@ -10693,19 +10657,19 @@
     </x:row>
     <x:row r="33" ht="93.25" hidden="0">
       <x:c r="A33" s="3" t="s">
-        <x:v>776</x:v>
+        <x:v>764</x:v>
       </x:c>
       <x:c r="B33" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C33" s="3" t="s">
-        <x:v>777</x:v>
+        <x:v>765</x:v>
       </x:c>
       <x:c r="D33" s="3" t="s">
-        <x:v>778</x:v>
+        <x:v>766</x:v>
       </x:c>
       <x:c r="E33" s="3" t="s">
-        <x:v>779</x:v>
+        <x:v>767</x:v>
       </x:c>
       <x:c r="F33" s="3" t="s">
         <x:v>37</x:v>
@@ -10726,31 +10690,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L33" s="3" t="s">
-        <x:v>780</x:v>
+        <x:v>768</x:v>
       </x:c>
       <x:c r="M33" s="3" t="s">
-        <x:v>781</x:v>
+        <x:v>769</x:v>
       </x:c>
       <x:c r="N33" s="3" t="s">
-        <x:v>782</x:v>
+        <x:v>770</x:v>
       </x:c>
       <x:c r="O33" s="3" t="s">
-        <x:v>783</x:v>
+        <x:v>771</x:v>
       </x:c>
       <x:c r="P33" s="3" t="s">
-        <x:v>784</x:v>
+        <x:v>772</x:v>
       </x:c>
       <x:c r="Q33" s="3" t="s">
-        <x:v>785</x:v>
+        <x:v>773</x:v>
       </x:c>
       <x:c r="R33" s="3" t="s">
-        <x:v>786</x:v>
+        <x:v>774</x:v>
       </x:c>
       <x:c r="S33" s="3" t="s">
-        <x:v>787</x:v>
+        <x:v>775</x:v>
       </x:c>
       <x:c r="T33" s="3" t="s">
-        <x:v>788</x:v>
+        <x:v>776</x:v>
       </x:c>
       <x:c r="U33" s="3" t="s">
         <x:v>52</x:v>
@@ -10758,7 +10722,7 @@
     </x:row>
     <x:row r="34" ht="93.25" hidden="0">
       <x:c r="A34" s="3" t="s">
-        <x:v>789</x:v>
+        <x:v>777</x:v>
       </x:c>
       <x:c r="B34" s="3" t="s">
         <x:v>8</x:v>
@@ -10767,10 +10731,10 @@
         <x:v>313</x:v>
       </x:c>
       <x:c r="D34" s="3" t="s">
-        <x:v>790</x:v>
+        <x:v>778</x:v>
       </x:c>
       <x:c r="E34" s="3" t="s">
-        <x:v>791</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="F34" s="3" t="s">
         <x:v>37</x:v>
@@ -10791,31 +10755,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="L34" s="3" t="s">
-        <x:v>792</x:v>
+        <x:v>780</x:v>
       </x:c>
       <x:c r="M34" s="3" t="s">
-        <x:v>793</x:v>
+        <x:v>781</x:v>
       </x:c>
       <x:c r="N34" s="3" t="s">
-        <x:v>794</x:v>
+        <x:v>782</x:v>
       </x:c>
       <x:c r="O34" s="3" t="s">
-        <x:v>795</x:v>
+        <x:v>783</x:v>
       </x:c>
       <x:c r="P34" s="3" t="s">
-        <x:v>796</x:v>
+        <x:v>784</x:v>
       </x:c>
       <x:c r="Q34" s="3" t="s">
-        <x:v>797</x:v>
+        <x:v>785</x:v>
       </x:c>
       <x:c r="R34" s="3" t="s">
-        <x:v>798</x:v>
+        <x:v>786</x:v>
       </x:c>
       <x:c r="S34" s="3" t="s">
         <x:v>323</x:v>
       </x:c>
       <x:c r="T34" s="3" t="s">
-        <x:v>799</x:v>
+        <x:v>787</x:v>
       </x:c>
       <x:c r="U34" s="3" t="s">
         <x:v>52</x:v>
@@ -10823,19 +10787,19 @@
     </x:row>
     <x:row r="35" ht="93.25" hidden="0">
       <x:c r="A35" s="3" t="s">
-        <x:v>800</x:v>
+        <x:v>788</x:v>
       </x:c>
       <x:c r="B35" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C35" s="3" t="s">
-        <x:v>801</x:v>
+        <x:v>789</x:v>
       </x:c>
       <x:c r="D35" s="3" t="s">
-        <x:v>802</x:v>
+        <x:v>790</x:v>
       </x:c>
       <x:c r="E35" s="3" t="s">
-        <x:v>803</x:v>
+        <x:v>791</x:v>
       </x:c>
       <x:c r="F35" s="3" t="s">
         <x:v>37</x:v>
@@ -10856,31 +10820,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L35" s="3" t="s">
-        <x:v>804</x:v>
+        <x:v>792</x:v>
       </x:c>
       <x:c r="M35" s="3" t="s">
-        <x:v>805</x:v>
+        <x:v>793</x:v>
       </x:c>
       <x:c r="N35" s="3" t="s">
-        <x:v>806</x:v>
+        <x:v>794</x:v>
       </x:c>
       <x:c r="O35" s="3" t="s">
-        <x:v>581</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="P35" s="3" t="s">
-        <x:v>807</x:v>
+        <x:v>795</x:v>
       </x:c>
       <x:c r="Q35" s="3" t="s">
-        <x:v>808</x:v>
+        <x:v>796</x:v>
       </x:c>
       <x:c r="R35" s="3" t="s">
-        <x:v>809</x:v>
+        <x:v>797</x:v>
       </x:c>
       <x:c r="S35" s="3" t="s">
-        <x:v>810</x:v>
+        <x:v>798</x:v>
       </x:c>
       <x:c r="T35" s="3" t="s">
-        <x:v>811</x:v>
+        <x:v>799</x:v>
       </x:c>
       <x:c r="U35" s="3" t="s">
         <x:v>52</x:v>
@@ -10888,19 +10852,19 @@
     </x:row>
     <x:row r="36" ht="93.25" hidden="0">
       <x:c r="A36" s="3" t="s">
-        <x:v>812</x:v>
+        <x:v>800</x:v>
       </x:c>
       <x:c r="B36" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C36" s="3" t="s">
-        <x:v>813</x:v>
+        <x:v>801</x:v>
       </x:c>
       <x:c r="D36" s="3" t="s">
-        <x:v>814</x:v>
+        <x:v>802</x:v>
       </x:c>
       <x:c r="E36" s="3" t="s">
-        <x:v>815</x:v>
+        <x:v>803</x:v>
       </x:c>
       <x:c r="F36" s="3" t="s">
         <x:v>37</x:v>
@@ -10921,31 +10885,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L36" s="3" t="s">
-        <x:v>816</x:v>
+        <x:v>804</x:v>
       </x:c>
       <x:c r="M36" s="3" t="s">
         <x:v>446</x:v>
       </x:c>
       <x:c r="N36" s="3" t="s">
-        <x:v>817</x:v>
+        <x:v>805</x:v>
       </x:c>
       <x:c r="O36" s="3" t="s">
-        <x:v>818</x:v>
+        <x:v>806</x:v>
       </x:c>
       <x:c r="P36" s="3" t="s">
-        <x:v>819</x:v>
+        <x:v>807</x:v>
       </x:c>
       <x:c r="Q36" s="3" t="s">
-        <x:v>820</x:v>
+        <x:v>808</x:v>
       </x:c>
       <x:c r="R36" s="3" t="s">
-        <x:v>821</x:v>
+        <x:v>809</x:v>
       </x:c>
       <x:c r="S36" s="3" t="s">
-        <x:v>822</x:v>
+        <x:v>810</x:v>
       </x:c>
       <x:c r="T36" s="3" t="s">
-        <x:v>823</x:v>
+        <x:v>811</x:v>
       </x:c>
       <x:c r="U36" s="3" t="s">
         <x:v>52</x:v>
@@ -10953,19 +10917,19 @@
     </x:row>
     <x:row r="37" ht="93.25" hidden="0">
       <x:c r="A37" s="3" t="s">
-        <x:v>824</x:v>
+        <x:v>812</x:v>
       </x:c>
       <x:c r="B37" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C37" s="3" t="s">
-        <x:v>825</x:v>
+        <x:v>813</x:v>
       </x:c>
       <x:c r="D37" s="3" t="s">
-        <x:v>826</x:v>
+        <x:v>814</x:v>
       </x:c>
       <x:c r="E37" s="3" t="s">
-        <x:v>827</x:v>
+        <x:v>815</x:v>
       </x:c>
       <x:c r="F37" s="3" t="s">
         <x:v>37</x:v>
@@ -10986,31 +10950,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L37" s="3" t="s">
-        <x:v>828</x:v>
+        <x:v>816</x:v>
       </x:c>
       <x:c r="M37" s="3" t="s">
-        <x:v>829</x:v>
+        <x:v>817</x:v>
       </x:c>
       <x:c r="N37" s="3" t="s">
-        <x:v>830</x:v>
+        <x:v>818</x:v>
       </x:c>
       <x:c r="O37" s="3" t="s">
-        <x:v>831</x:v>
+        <x:v>819</x:v>
       </x:c>
       <x:c r="P37" s="3" t="s">
-        <x:v>832</x:v>
+        <x:v>820</x:v>
       </x:c>
       <x:c r="Q37" s="3" t="s">
-        <x:v>833</x:v>
+        <x:v>821</x:v>
       </x:c>
       <x:c r="R37" s="3" t="s">
-        <x:v>834</x:v>
+        <x:v>822</x:v>
       </x:c>
       <x:c r="S37" s="3" t="s">
-        <x:v>835</x:v>
+        <x:v>823</x:v>
       </x:c>
       <x:c r="T37" s="3" t="s">
-        <x:v>829</x:v>
+        <x:v>817</x:v>
       </x:c>
       <x:c r="U37" s="3" t="s">
         <x:v>52</x:v>
@@ -11018,19 +10982,19 @@
     </x:row>
     <x:row r="38" ht="93.25" hidden="0">
       <x:c r="A38" s="3" t="s">
-        <x:v>836</x:v>
+        <x:v>824</x:v>
       </x:c>
       <x:c r="B38" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C38" s="3" t="s">
-        <x:v>837</x:v>
+        <x:v>825</x:v>
       </x:c>
       <x:c r="D38" s="3" t="s">
-        <x:v>838</x:v>
+        <x:v>826</x:v>
       </x:c>
       <x:c r="E38" s="3" t="s">
-        <x:v>839</x:v>
+        <x:v>827</x:v>
       </x:c>
       <x:c r="F38" s="3" t="s">
         <x:v>37</x:v>
@@ -11051,31 +11015,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L38" s="3" t="s">
-        <x:v>840</x:v>
+        <x:v>828</x:v>
       </x:c>
       <x:c r="M38" s="3" t="s">
-        <x:v>506</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="N38" s="3" t="s">
-        <x:v>841</x:v>
+        <x:v>829</x:v>
       </x:c>
       <x:c r="O38" s="3" t="s">
-        <x:v>842</x:v>
+        <x:v>830</x:v>
       </x:c>
       <x:c r="P38" s="3" t="s">
-        <x:v>843</x:v>
+        <x:v>831</x:v>
       </x:c>
       <x:c r="Q38" s="3" t="s">
-        <x:v>844</x:v>
+        <x:v>832</x:v>
       </x:c>
       <x:c r="R38" s="3" t="s">
-        <x:v>845</x:v>
+        <x:v>833</x:v>
       </x:c>
       <x:c r="S38" s="3" t="s">
-        <x:v>846</x:v>
+        <x:v>834</x:v>
       </x:c>
       <x:c r="T38" s="3" t="s">
-        <x:v>847</x:v>
+        <x:v>835</x:v>
       </x:c>
       <x:c r="U38" s="3" t="s">
         <x:v>52</x:v>
@@ -11083,19 +11047,19 @@
     </x:row>
     <x:row r="39" ht="93.25" hidden="0">
       <x:c r="A39" s="3" t="s">
-        <x:v>848</x:v>
+        <x:v>836</x:v>
       </x:c>
       <x:c r="B39" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C39" s="3" t="s">
-        <x:v>849</x:v>
+        <x:v>837</x:v>
       </x:c>
       <x:c r="D39" s="3" t="s">
-        <x:v>850</x:v>
+        <x:v>838</x:v>
       </x:c>
       <x:c r="E39" s="3" t="s">
-        <x:v>851</x:v>
+        <x:v>839</x:v>
       </x:c>
       <x:c r="F39" s="3" t="s">
         <x:v>37</x:v>
@@ -11116,31 +11080,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="L39" s="3" t="s">
-        <x:v>852</x:v>
+        <x:v>840</x:v>
       </x:c>
       <x:c r="M39" s="3" t="s">
         <x:v>446</x:v>
       </x:c>
       <x:c r="N39" s="3" t="s">
-        <x:v>853</x:v>
+        <x:v>841</x:v>
       </x:c>
       <x:c r="O39" s="3" t="s">
-        <x:v>854</x:v>
+        <x:v>842</x:v>
       </x:c>
       <x:c r="P39" s="3" t="s">
-        <x:v>855</x:v>
+        <x:v>843</x:v>
       </x:c>
       <x:c r="Q39" s="3" t="s">
-        <x:v>856</x:v>
+        <x:v>844</x:v>
       </x:c>
       <x:c r="R39" s="3" t="s">
-        <x:v>857</x:v>
+        <x:v>845</x:v>
       </x:c>
       <x:c r="S39" s="3" t="s">
-        <x:v>858</x:v>
+        <x:v>846</x:v>
       </x:c>
       <x:c r="T39" s="3" t="s">
-        <x:v>859</x:v>
+        <x:v>847</x:v>
       </x:c>
       <x:c r="U39" s="3" t="s">
         <x:v>52</x:v>
@@ -11149,7 +11113,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rff5215770ede4f23"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree49df396751461c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/maliev-feature-user-story-status.xlsx
+++ b/docs/maliev-feature-user-story-status.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rb5b68a3878644019"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="R3151eccf955844ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R8059f1b5c4a14860"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="Rd40e65ebd96347ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rcf0701f9e3fc41be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="Re4e8f64e754e4bfa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R982e27500cc44dc7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="Rf3e0c1f295394a64"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1373,42 +1373,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">AgentController.cs:111,423</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QE-007</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Project navigation rail</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">As a customer, I can navigate, search, pin, archive, duplicate, and continue projects from the rail.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Project nav endpoints and shell management pages support project list, detail, duplicate, pin/unpin, archive, and current project selection.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Rail/projects page -&gt; QuoteController projects/nav/detail/actions</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">New project, Projects, search, pin/archive/duplicate actions</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QuoteController projects/nav, project detail, duplicate, pin, delete pin, archive</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QuoteEngineSourceTests rail/project management | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QuoteEngine BFF, Project service, SessionStore</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Project metadata, pin/archive flags</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Needs product decision on achieve endpoint naming</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QuoteAgentLaunchShell.razor; QuoteController.cs:548-674</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">QE-008</x:t>
@@ -5126,7 +5090,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb233f994b1de4067"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47eb0d60f7954f2a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8542,7 +8506,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R765a67ea39834959"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R144959e895754513"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9031,85 +8995,85 @@
       </x:c>
     </x:row>
     <x:row r="8" ht="93.25" hidden="0">
-      <x:c r="A8" s="3" t="s">
-        <x:v>454</x:v>
-      </x:c>
-      <x:c r="B8" s="3" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C8" s="3" t="s">
-        <x:v>455</x:v>
-      </x:c>
-      <x:c r="D8" s="3" t="s">
-        <x:v>456</x:v>
-      </x:c>
-      <x:c r="E8" s="3" t="s">
-        <x:v>457</x:v>
-      </x:c>
-      <x:c r="F8" s="3" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="G8" s="3" t="s">
-        <x:v>442</x:v>
-      </x:c>
-      <x:c r="H8" s="3" t="s">
-        <x:v>443</x:v>
-      </x:c>
-      <x:c r="I8" s="3" t="s">
-        <x:v>444</x:v>
-      </x:c>
-      <x:c r="J8" s="3" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="K8" s="3" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="L8" s="3" t="s">
-        <x:v>458</x:v>
-      </x:c>
-      <x:c r="M8" s="3" t="s">
-        <x:v>446</x:v>
-      </x:c>
-      <x:c r="N8" s="3" t="s">
-        <x:v>459</x:v>
-      </x:c>
-      <x:c r="O8" s="3" t="s">
-        <x:v>460</x:v>
-      </x:c>
-      <x:c r="P8" s="3" t="s">
-        <x:v>461</x:v>
-      </x:c>
-      <x:c r="Q8" s="3" t="s">
-        <x:v>462</x:v>
-      </x:c>
-      <x:c r="R8" s="3" t="s">
-        <x:v>463</x:v>
-      </x:c>
-      <x:c r="S8" s="3" t="s">
-        <x:v>464</x:v>
-      </x:c>
-      <x:c r="T8" s="3" t="s">
-        <x:v>465</x:v>
-      </x:c>
-      <x:c r="U8" s="3" t="s">
-        <x:v>52</x:v>
+      <x:c r="A8" s="3" t="str">
+        <x:v>QE-007</x:v>
+      </x:c>
+      <x:c r="B8" s="3" t="str">
+        <x:v>Maliev.QuoteEngine</x:v>
+      </x:c>
+      <x:c r="C8" s="3" t="str">
+        <x:v>Project navigation rail</x:v>
+      </x:c>
+      <x:c r="D8" s="3" t="str">
+        <x:v>As a customer, I can navigate, search, pin, archive, duplicate, and continue projects from the rail.</x:v>
+      </x:c>
+      <x:c r="E8" s="3" t="str">
+        <x:v>Signed-in customers can open the project rail/pages, return to the active chat, start a new project after saving current work, and manage only their own projects with nav, detail, duplicate, pin/unpin, archive, and mark-achieved actions.</x:v>
+      </x:c>
+      <x:c r="F8" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G8" s="3" t="str">
+        <x:v>Focused current-state project navigation rail tests passed 2026-06-24.</x:v>
+      </x:c>
+      <x:c r="H8" s="3" t="str">
+        <x:v>No behavior error observed in focused QuoteEngine project navigation retest. UX/product naming question remains for the current /achieve route and Mark achieved label.</x:v>
+      </x:c>
+      <x:c r="I8" s="3" t="str">
+        <x:v>No app fix applied for QE-007; current code path is covered by focused BFF/source tests.</x:v>
+      </x:c>
+      <x:c r="J8" s="3" t="str">
+        <x:v>Passed 7/7 focused tests: project nav auth requirement, customer project listing, pin/unpin, cross-customer pin denial, archive removal and denial, achieve removal and denial, and management-page return/new-project source contract.</x:v>
+      </x:c>
+      <x:c r="K8" s="3" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="L8" s="3" t="str">
+        <x:v>QuoteAgentLaunchShell rail/projects page -&gt; QuoteWorkspace new-project save/reset -&gt; QuoteEngineApiClient project methods -&gt; QuoteController project nav/detail/duplicate/pin/archive/achieve endpoints -&gt; ProjectService client/prototype fallback/customer ownership</x:v>
+      </x:c>
+      <x:c r="M8" s="3" t="str">
+        <x:v>QuoteAgentLaunchShell.razor; QuoteWorkspace.razor; QuoteEngineApiClient; QuoteController</x:v>
+      </x:c>
+      <x:c r="N8" s="3" t="str">
+        <x:v>WorkspacePage.Projects management rows expose Open, Duplicate, Pin/Unpin, Archive, and Mark achieved actions; management pages use ReturnToCurrentChatAsync; New project calls StartNewProjectAsync through QuoteWorkspace.</x:v>
+      </x:c>
+      <x:c r="O8" s="3" t="str">
+        <x:v>GET quote/v1/projects/nav requires a signed-in customer; POST/DELETE quote/v1/projects/{projectId}/pin, POST quote/v1/projects/{projectId}/archive, and POST quote/v1/projects/{projectId}/achieve enforce customer ownership and remove archived/achieved projects from nav.</x:v>
+      </x:c>
+      <x:c r="P8" s="3" t="str">
+        <x:v>2026-06-24: dotnet test Maliev.QuoteEngine.slnx --filter "FullyQualifiedName~QuoteEngineEndpointTests.Project_navigation_requires_signed_in_customer|FullyQualifiedName~QuoteEngineEndpointTests.Project_navigation_lists_customer_projects_and_updates_pin_state|FullyQualifiedName~QuoteEngineEndpointTests.Project_pin_rejects_project_owned_by_another_customer|FullyQualifiedName~QuoteEngineEndpointTests.Project_archive_removes_project_from_navigation_and_rejects_other_customers|FullyQualifiedName~QuoteEngineEndpointTests.Project_achieve_marks_project_complete_and_rejects_other_customers|FullyQualifiedName~QuoteEngineSourceTests.QuoteAgentLaunchShell_has_monochrome_chatgpt_like_contract" --verbosity minimal passed 6/6; dotnet test Maliev.QuoteEngine.slnx --filter "FullyQualifiedName~QuoteEngineSourceTests.QuoteAgentLaunchShell_starts_new_sessions_and_returns_from_management_pages" --verbosity minimal passed 1/1.</x:v>
+      </x:c>
+      <x:c r="Q8" s="3" t="str">
+        <x:v>QuoteEngine Client, QuoteEngine BFF, ProjectService client, Auth/session, prototype fallback store in development/testing</x:v>
+      </x:c>
+      <x:c r="R8" s="3" t="str">
+        <x:v>Project navigation list, draft project records, pinned flag, archived/achieved state, duplicated project records, current workspace reset state</x:v>
+      </x:c>
+      <x:c r="S8" s="3" t="str">
+        <x:v>Needs product/UX decision on whether the current /achieve endpoint and Mark achieved label should be renamed to completed/complete.</x:v>
+      </x:c>
+      <x:c r="T8" s="3" t="str">
+        <x:v>Maliev.QuoteEngine.Client/Components/QuoteAgent/QuoteAgentLaunchShell.razor:410; Maliev.QuoteEngine.Client/Pages/QuoteWorkspace.razor:432; Maliev.QuoteEngine.Bff/Controllers/QuoteController.cs:548,570,590,618,636,654; Maliev.QuoteEngine.Tests/QuoteEngineEndpointTests.cs:2924,2934,3005,3020,3045; Maliev.QuoteEngine.Tests/QuoteEngineSourceTests.cs:829,864</x:v>
+      </x:c>
+      <x:c r="U8" s="3" t="str">
+        <x:v>2026-06-24</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="93.25" hidden="0">
       <x:c r="A9" s="3" t="s">
-        <x:v>466</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="B9" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C9" s="3" t="s">
-        <x:v>467</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="D9" s="3" t="s">
-        <x:v>468</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="E9" s="3" t="s">
-        <x:v>469</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="F9" s="3" t="s">
         <x:v>37</x:v>
@@ -9130,31 +9094,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L9" s="3" t="s">
-        <x:v>470</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="M9" s="3" t="s">
         <x:v>446</x:v>
       </x:c>
       <x:c r="N9" s="3" t="s">
-        <x:v>471</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="O9" s="3" t="s">
-        <x:v>472</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="P9" s="3" t="s">
-        <x:v>473</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="Q9" s="3" t="s">
-        <x:v>474</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
-        <x:v>475</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="S9" s="3" t="s">
-        <x:v>476</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="T9" s="3" t="s">
-        <x:v>477</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="U9" s="3" t="s">
         <x:v>52</x:v>
@@ -9162,19 +9126,19 @@
     </x:row>
     <x:row r="10" ht="93.25" hidden="0">
       <x:c r="A10" s="3" t="s">
-        <x:v>478</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="B10" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C10" s="3" t="s">
-        <x:v>479</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="D10" s="3" t="s">
-        <x:v>480</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="E10" s="3" t="s">
-        <x:v>481</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="F10" s="3" t="s">
         <x:v>37</x:v>
@@ -9195,31 +9159,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L10" s="3" t="s">
-        <x:v>482</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="M10" s="3" t="s">
         <x:v>424</x:v>
       </x:c>
       <x:c r="N10" s="3" t="s">
-        <x:v>483</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="O10" s="3" t="s">
         <x:v>205</x:v>
       </x:c>
       <x:c r="P10" s="3" t="s">
-        <x:v>484</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="Q10" s="3" t="s">
-        <x:v>485</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="R10" s="3" t="s">
-        <x:v>486</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="S10" s="3" t="s">
-        <x:v>487</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="T10" s="3" t="s">
-        <x:v>488</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="U10" s="3" t="s">
         <x:v>52</x:v>
@@ -9227,19 +9191,19 @@
     </x:row>
     <x:row r="11" ht="93.25" hidden="0">
       <x:c r="A11" s="3" t="s">
-        <x:v>489</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="B11" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C11" s="3" t="s">
-        <x:v>490</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="D11" s="3" t="s">
-        <x:v>491</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="E11" s="3" t="s">
-        <x:v>492</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="F11" s="3" t="s">
         <x:v>37</x:v>
@@ -9260,31 +9224,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L11" s="3" t="s">
-        <x:v>493</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="M11" s="3" t="s">
-        <x:v>494</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="N11" s="3" t="s">
-        <x:v>495</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="O11" s="3" t="s">
-        <x:v>496</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="P11" s="3" t="s">
-        <x:v>497</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="Q11" s="3" t="s">
-        <x:v>498</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="R11" s="3" t="s">
-        <x:v>499</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="S11" s="3" t="s">
-        <x:v>500</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="T11" s="3" t="s">
-        <x:v>501</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="U11" s="3" t="s">
         <x:v>52</x:v>
@@ -9292,19 +9256,19 @@
     </x:row>
     <x:row r="12" ht="107.25" hidden="0">
       <x:c r="A12" s="3" t="s">
-        <x:v>502</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="B12" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C12" s="3" t="s">
-        <x:v>503</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="D12" s="3" t="s">
-        <x:v>504</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="E12" s="3" t="s">
-        <x:v>505</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="F12" s="3" t="s">
         <x:v>37</x:v>
@@ -9325,31 +9289,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L12" s="3" t="s">
-        <x:v>506</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="M12" s="3" t="s">
         <x:v>446</x:v>
       </x:c>
       <x:c r="N12" s="3" t="s">
-        <x:v>507</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="O12" s="3" t="s">
-        <x:v>508</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="P12" s="3" t="s">
-        <x:v>509</x:v>
+        <x:v>497</x:v>
       </x:c>
       <x:c r="Q12" s="3" t="s">
-        <x:v>510</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="R12" s="3" t="s">
-        <x:v>511</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="S12" s="3" t="s">
-        <x:v>512</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="T12" s="3" t="s">
-        <x:v>513</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="U12" s="3" t="s">
         <x:v>52</x:v>
@@ -9357,19 +9321,19 @@
     </x:row>
     <x:row r="13" ht="93.25" hidden="0">
       <x:c r="A13" s="3" t="s">
-        <x:v>514</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="B13" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C13" s="3" t="s">
-        <x:v>515</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="D13" s="3" t="s">
-        <x:v>516</x:v>
+        <x:v>504</x:v>
       </x:c>
       <x:c r="E13" s="3" t="s">
-        <x:v>517</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="F13" s="3" t="s">
         <x:v>37</x:v>
@@ -9390,31 +9354,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L13" s="3" t="s">
-        <x:v>518</x:v>
+        <x:v>506</x:v>
       </x:c>
       <x:c r="M13" s="3" t="s">
         <x:v>446</x:v>
       </x:c>
       <x:c r="N13" s="3" t="s">
-        <x:v>519</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="O13" s="3" t="s">
-        <x:v>520</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="P13" s="3" t="s">
-        <x:v>521</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="Q13" s="3" t="s">
+        <x:v>498</x:v>
+      </x:c>
+      <x:c r="R13" s="3" t="s">
         <x:v>510</x:v>
       </x:c>
-      <x:c r="R13" s="3" t="s">
-        <x:v>522</x:v>
-      </x:c>
       <x:c r="S13" s="3" t="s">
-        <x:v>523</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="T13" s="3" t="s">
-        <x:v>524</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="U13" s="3" t="s">
         <x:v>52</x:v>
@@ -9422,19 +9386,19 @@
     </x:row>
     <x:row r="14" ht="93.25" hidden="0">
       <x:c r="A14" s="3" t="s">
-        <x:v>525</x:v>
+        <x:v>513</x:v>
       </x:c>
       <x:c r="B14" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C14" s="3" t="s">
-        <x:v>526</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="D14" s="3" t="s">
-        <x:v>527</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="E14" s="3" t="s">
-        <x:v>528</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="F14" s="3" t="s">
         <x:v>37</x:v>
@@ -9455,31 +9419,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L14" s="3" t="s">
-        <x:v>529</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="M14" s="3" t="s">
-        <x:v>530</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="N14" s="3" t="s">
-        <x:v>531</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="O14" s="3" t="s">
-        <x:v>532</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="P14" s="3" t="s">
-        <x:v>533</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="Q14" s="3" t="s">
-        <x:v>534</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="R14" s="3" t="s">
-        <x:v>535</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="S14" s="3" t="s">
-        <x:v>536</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="T14" s="3" t="s">
-        <x:v>537</x:v>
+        <x:v>525</x:v>
       </x:c>
       <x:c r="U14" s="3" t="s">
         <x:v>52</x:v>
@@ -9487,19 +9451,19 @@
     </x:row>
     <x:row r="15" ht="107.25" hidden="0">
       <x:c r="A15" s="3" t="s">
-        <x:v>538</x:v>
+        <x:v>526</x:v>
       </x:c>
       <x:c r="B15" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C15" s="3" t="s">
-        <x:v>539</x:v>
+        <x:v>527</x:v>
       </x:c>
       <x:c r="D15" s="3" t="s">
-        <x:v>540</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="E15" s="3" t="s">
-        <x:v>541</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="F15" s="3" t="s">
         <x:v>37</x:v>
@@ -9520,31 +9484,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L15" s="3" t="s">
-        <x:v>542</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="M15" s="3" t="s">
         <x:v>446</x:v>
       </x:c>
       <x:c r="N15" s="3" t="s">
-        <x:v>543</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="O15" s="3" t="s">
-        <x:v>544</x:v>
+        <x:v>532</x:v>
       </x:c>
       <x:c r="P15" s="3" t="s">
-        <x:v>545</x:v>
+        <x:v>533</x:v>
       </x:c>
       <x:c r="Q15" s="3" t="s">
-        <x:v>546</x:v>
+        <x:v>534</x:v>
       </x:c>
       <x:c r="R15" s="3" t="s">
-        <x:v>547</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="S15" s="3" t="s">
-        <x:v>548</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="T15" s="3" t="s">
-        <x:v>549</x:v>
+        <x:v>537</x:v>
       </x:c>
       <x:c r="U15" s="3" t="s">
         <x:v>52</x:v>
@@ -9552,19 +9516,19 @@
     </x:row>
     <x:row r="16" ht="107.25" hidden="0">
       <x:c r="A16" s="3" t="s">
-        <x:v>550</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="B16" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C16" s="3" t="s">
-        <x:v>551</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="D16" s="3" t="s">
-        <x:v>552</x:v>
+        <x:v>540</x:v>
       </x:c>
       <x:c r="E16" s="3" t="s">
-        <x:v>553</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="F16" s="3" t="s">
         <x:v>37</x:v>
@@ -9585,31 +9549,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L16" s="3" t="s">
-        <x:v>554</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="M16" s="3" t="s">
         <x:v>446</x:v>
       </x:c>
       <x:c r="N16" s="3" t="s">
-        <x:v>555</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="O16" s="3" t="s">
-        <x:v>556</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="P16" s="3" t="s">
-        <x:v>557</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="Q16" s="3" t="s">
-        <x:v>558</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="R16" s="3" t="s">
-        <x:v>559</x:v>
+        <x:v>547</x:v>
       </x:c>
       <x:c r="S16" s="3" t="s">
-        <x:v>560</x:v>
+        <x:v>548</x:v>
       </x:c>
       <x:c r="T16" s="3" t="s">
-        <x:v>561</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="U16" s="3" t="s">
         <x:v>52</x:v>
@@ -9617,19 +9581,19 @@
     </x:row>
     <x:row r="17" ht="93.25" hidden="0">
       <x:c r="A17" s="3" t="s">
-        <x:v>562</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="B17" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C17" s="3" t="s">
-        <x:v>563</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="D17" s="3" t="s">
-        <x:v>564</x:v>
+        <x:v>552</x:v>
       </x:c>
       <x:c r="E17" s="3" t="s">
-        <x:v>565</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="F17" s="3" t="s">
         <x:v>37</x:v>
@@ -9650,31 +9614,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L17" s="3" t="s">
-        <x:v>566</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="M17" s="3" t="s">
-        <x:v>567</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="N17" s="3" t="s">
-        <x:v>568</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="O17" s="3" t="s">
-        <x:v>569</x:v>
+        <x:v>557</x:v>
       </x:c>
       <x:c r="P17" s="3" t="s">
-        <x:v>570</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="Q17" s="3" t="s">
-        <x:v>571</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="R17" s="3" t="s">
-        <x:v>572</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="S17" s="3" t="s">
-        <x:v>573</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="T17" s="3" t="s">
-        <x:v>574</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="U17" s="3" t="s">
         <x:v>52</x:v>
@@ -9682,19 +9646,19 @@
     </x:row>
     <x:row r="18" ht="93.25" hidden="0">
       <x:c r="A18" s="3" t="s">
-        <x:v>575</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="B18" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C18" s="3" t="s">
-        <x:v>576</x:v>
+        <x:v>564</x:v>
       </x:c>
       <x:c r="D18" s="3" t="s">
-        <x:v>577</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="E18" s="3" t="s">
-        <x:v>578</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="F18" s="3" t="s">
         <x:v>37</x:v>
@@ -9715,31 +9679,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L18" s="3" t="s">
-        <x:v>579</x:v>
+        <x:v>567</x:v>
       </x:c>
       <x:c r="M18" s="3" t="s">
-        <x:v>580</x:v>
+        <x:v>568</x:v>
       </x:c>
       <x:c r="N18" s="3" t="s">
-        <x:v>581</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="O18" s="3" t="s">
-        <x:v>582</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="P18" s="3" t="s">
-        <x:v>583</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="Q18" s="3" t="s">
-        <x:v>584</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="R18" s="3" t="s">
-        <x:v>585</x:v>
+        <x:v>573</x:v>
       </x:c>
       <x:c r="S18" s="3" t="s">
-        <x:v>586</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="T18" s="3" t="s">
-        <x:v>587</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="U18" s="3" t="s">
         <x:v>52</x:v>
@@ -9747,19 +9711,19 @@
     </x:row>
     <x:row r="19" ht="93.25" hidden="0">
       <x:c r="A19" s="3" t="s">
-        <x:v>588</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="B19" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C19" s="3" t="s">
-        <x:v>589</x:v>
+        <x:v>577</x:v>
       </x:c>
       <x:c r="D19" s="3" t="s">
-        <x:v>590</x:v>
+        <x:v>578</x:v>
       </x:c>
       <x:c r="E19" s="3" t="s">
-        <x:v>591</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="F19" s="3" t="s">
         <x:v>37</x:v>
@@ -9780,31 +9744,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L19" s="3" t="s">
-        <x:v>592</x:v>
+        <x:v>580</x:v>
       </x:c>
       <x:c r="M19" s="3" t="s">
-        <x:v>593</x:v>
+        <x:v>581</x:v>
       </x:c>
       <x:c r="N19" s="3" t="s">
-        <x:v>594</x:v>
+        <x:v>582</x:v>
       </x:c>
       <x:c r="O19" s="3" t="s">
-        <x:v>595</x:v>
+        <x:v>583</x:v>
       </x:c>
       <x:c r="P19" s="3" t="s">
-        <x:v>596</x:v>
+        <x:v>584</x:v>
       </x:c>
       <x:c r="Q19" s="3" t="s">
-        <x:v>597</x:v>
+        <x:v>585</x:v>
       </x:c>
       <x:c r="R19" s="3" t="s">
-        <x:v>598</x:v>
+        <x:v>586</x:v>
       </x:c>
       <x:c r="S19" s="3" t="s">
-        <x:v>599</x:v>
+        <x:v>587</x:v>
       </x:c>
       <x:c r="T19" s="3" t="s">
-        <x:v>600</x:v>
+        <x:v>588</x:v>
       </x:c>
       <x:c r="U19" s="3" t="s">
         <x:v>52</x:v>
@@ -9812,19 +9776,19 @@
     </x:row>
     <x:row r="20" ht="79.25" hidden="0">
       <x:c r="A20" s="3" t="s">
-        <x:v>601</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="B20" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C20" s="3" t="s">
-        <x:v>602</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="D20" s="3" t="s">
-        <x:v>603</x:v>
+        <x:v>591</x:v>
       </x:c>
       <x:c r="E20" s="3" t="s">
-        <x:v>604</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="F20" s="3" t="s">
         <x:v>37</x:v>
@@ -9845,31 +9809,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L20" s="3" t="s">
-        <x:v>605</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="M20" s="3" t="s">
-        <x:v>606</x:v>
+        <x:v>594</x:v>
       </x:c>
       <x:c r="N20" s="3" t="s">
-        <x:v>607</x:v>
+        <x:v>595</x:v>
       </x:c>
       <x:c r="O20" s="3" t="s">
-        <x:v>608</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="P20" s="3" t="s">
-        <x:v>609</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="Q20" s="3" t="s">
-        <x:v>610</x:v>
+        <x:v>598</x:v>
       </x:c>
       <x:c r="R20" s="3" t="s">
-        <x:v>611</x:v>
+        <x:v>599</x:v>
       </x:c>
       <x:c r="S20" s="3" t="s">
-        <x:v>612</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="T20" s="3" t="s">
-        <x:v>613</x:v>
+        <x:v>601</x:v>
       </x:c>
       <x:c r="U20" s="3" t="s">
         <x:v>52</x:v>
@@ -9877,19 +9841,19 @@
     </x:row>
     <x:row r="21" ht="79.25" hidden="0">
       <x:c r="A21" s="3" t="s">
-        <x:v>614</x:v>
+        <x:v>602</x:v>
       </x:c>
       <x:c r="B21" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C21" s="3" t="s">
-        <x:v>615</x:v>
+        <x:v>603</x:v>
       </x:c>
       <x:c r="D21" s="3" t="s">
-        <x:v>616</x:v>
+        <x:v>604</x:v>
       </x:c>
       <x:c r="E21" s="3" t="s">
-        <x:v>617</x:v>
+        <x:v>605</x:v>
       </x:c>
       <x:c r="F21" s="3" t="s">
         <x:v>37</x:v>
@@ -9910,31 +9874,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L21" s="3" t="s">
-        <x:v>618</x:v>
+        <x:v>606</x:v>
       </x:c>
       <x:c r="M21" s="3" t="s">
-        <x:v>619</x:v>
+        <x:v>607</x:v>
       </x:c>
       <x:c r="N21" s="3" t="s">
-        <x:v>620</x:v>
+        <x:v>608</x:v>
       </x:c>
       <x:c r="O21" s="3" t="s">
         <x:v>218</x:v>
       </x:c>
       <x:c r="P21" s="3" t="s">
-        <x:v>621</x:v>
+        <x:v>609</x:v>
       </x:c>
       <x:c r="Q21" s="3" t="s">
-        <x:v>622</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="R21" s="3" t="s">
         <x:v>221</x:v>
       </x:c>
       <x:c r="S21" s="3" t="s">
-        <x:v>623</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="T21" s="3" t="s">
-        <x:v>624</x:v>
+        <x:v>612</x:v>
       </x:c>
       <x:c r="U21" s="3" t="s">
         <x:v>52</x:v>
@@ -9942,19 +9906,19 @@
     </x:row>
     <x:row r="22" ht="93.25" hidden="0">
       <x:c r="A22" s="3" t="s">
-        <x:v>625</x:v>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="B22" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C22" s="3" t="s">
-        <x:v>626</x:v>
+        <x:v>614</x:v>
       </x:c>
       <x:c r="D22" s="3" t="s">
-        <x:v>627</x:v>
+        <x:v>615</x:v>
       </x:c>
       <x:c r="E22" s="3" t="s">
-        <x:v>628</x:v>
+        <x:v>616</x:v>
       </x:c>
       <x:c r="F22" s="3" t="s">
         <x:v>37</x:v>
@@ -9975,31 +9939,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L22" s="3" t="s">
-        <x:v>629</x:v>
+        <x:v>617</x:v>
       </x:c>
       <x:c r="M22" s="3" t="s">
-        <x:v>494</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="N22" s="3" t="s">
-        <x:v>630</x:v>
+        <x:v>618</x:v>
       </x:c>
       <x:c r="O22" s="3" t="s">
-        <x:v>631</x:v>
+        <x:v>619</x:v>
       </x:c>
       <x:c r="P22" s="3" t="s">
-        <x:v>632</x:v>
+        <x:v>620</x:v>
       </x:c>
       <x:c r="Q22" s="3" t="s">
-        <x:v>633</x:v>
+        <x:v>621</x:v>
       </x:c>
       <x:c r="R22" s="3" t="s">
-        <x:v>634</x:v>
+        <x:v>622</x:v>
       </x:c>
       <x:c r="S22" s="3" t="s">
-        <x:v>635</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="T22" s="3" t="s">
-        <x:v>636</x:v>
+        <x:v>624</x:v>
       </x:c>
       <x:c r="U22" s="3" t="s">
         <x:v>52</x:v>
@@ -10007,19 +9971,19 @@
     </x:row>
     <x:row r="23" ht="93.25" hidden="0">
       <x:c r="A23" s="3" t="s">
-        <x:v>637</x:v>
+        <x:v>625</x:v>
       </x:c>
       <x:c r="B23" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C23" s="3" t="s">
-        <x:v>638</x:v>
+        <x:v>626</x:v>
       </x:c>
       <x:c r="D23" s="3" t="s">
-        <x:v>639</x:v>
+        <x:v>627</x:v>
       </x:c>
       <x:c r="E23" s="3" t="s">
-        <x:v>640</x:v>
+        <x:v>628</x:v>
       </x:c>
       <x:c r="F23" s="3" t="s">
         <x:v>37</x:v>
@@ -10040,31 +10004,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L23" s="3" t="s">
-        <x:v>641</x:v>
+        <x:v>629</x:v>
       </x:c>
       <x:c r="M23" s="3" t="s">
-        <x:v>642</x:v>
+        <x:v>630</x:v>
       </x:c>
       <x:c r="N23" s="3" t="s">
-        <x:v>643</x:v>
+        <x:v>631</x:v>
       </x:c>
       <x:c r="O23" s="3" t="s">
-        <x:v>644</x:v>
+        <x:v>632</x:v>
       </x:c>
       <x:c r="P23" s="3" t="s">
-        <x:v>645</x:v>
+        <x:v>633</x:v>
       </x:c>
       <x:c r="Q23" s="3" t="s">
-        <x:v>646</x:v>
+        <x:v>634</x:v>
       </x:c>
       <x:c r="R23" s="3" t="s">
-        <x:v>647</x:v>
+        <x:v>635</x:v>
       </x:c>
       <x:c r="S23" s="3" t="s">
-        <x:v>648</x:v>
+        <x:v>636</x:v>
       </x:c>
       <x:c r="T23" s="3" t="s">
-        <x:v>649</x:v>
+        <x:v>637</x:v>
       </x:c>
       <x:c r="U23" s="3" t="s">
         <x:v>52</x:v>
@@ -10072,19 +10036,19 @@
     </x:row>
     <x:row r="24" ht="79.25" hidden="0">
       <x:c r="A24" s="3" t="s">
-        <x:v>650</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="B24" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C24" s="3" t="s">
-        <x:v>651</x:v>
+        <x:v>639</x:v>
       </x:c>
       <x:c r="D24" s="3" t="s">
-        <x:v>652</x:v>
+        <x:v>640</x:v>
       </x:c>
       <x:c r="E24" s="3" t="s">
-        <x:v>653</x:v>
+        <x:v>641</x:v>
       </x:c>
       <x:c r="F24" s="3" t="s">
         <x:v>37</x:v>
@@ -10105,31 +10069,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L24" s="3" t="s">
-        <x:v>654</x:v>
+        <x:v>642</x:v>
       </x:c>
       <x:c r="M24" s="3" t="s">
-        <x:v>619</x:v>
+        <x:v>607</x:v>
       </x:c>
       <x:c r="N24" s="3" t="s">
-        <x:v>655</x:v>
+        <x:v>643</x:v>
       </x:c>
       <x:c r="O24" s="3" t="s">
-        <x:v>656</x:v>
+        <x:v>644</x:v>
       </x:c>
       <x:c r="P24" s="3" t="s">
-        <x:v>657</x:v>
+        <x:v>645</x:v>
       </x:c>
       <x:c r="Q24" s="3" t="s">
-        <x:v>658</x:v>
+        <x:v>646</x:v>
       </x:c>
       <x:c r="R24" s="3" t="s">
-        <x:v>659</x:v>
+        <x:v>647</x:v>
       </x:c>
       <x:c r="S24" s="3" t="s">
-        <x:v>660</x:v>
+        <x:v>648</x:v>
       </x:c>
       <x:c r="T24" s="3" t="s">
-        <x:v>661</x:v>
+        <x:v>649</x:v>
       </x:c>
       <x:c r="U24" s="3" t="s">
         <x:v>52</x:v>
@@ -10137,19 +10101,19 @@
     </x:row>
     <x:row r="25" ht="79.25" hidden="0">
       <x:c r="A25" s="3" t="s">
-        <x:v>662</x:v>
+        <x:v>650</x:v>
       </x:c>
       <x:c r="B25" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C25" s="3" t="s">
-        <x:v>663</x:v>
+        <x:v>651</x:v>
       </x:c>
       <x:c r="D25" s="3" t="s">
-        <x:v>664</x:v>
+        <x:v>652</x:v>
       </x:c>
       <x:c r="E25" s="3" t="s">
-        <x:v>665</x:v>
+        <x:v>653</x:v>
       </x:c>
       <x:c r="F25" s="3" t="s">
         <x:v>37</x:v>
@@ -10170,31 +10134,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L25" s="3" t="s">
-        <x:v>666</x:v>
+        <x:v>654</x:v>
       </x:c>
       <x:c r="M25" s="3" t="s">
-        <x:v>619</x:v>
+        <x:v>607</x:v>
       </x:c>
       <x:c r="N25" s="3" t="s">
-        <x:v>667</x:v>
+        <x:v>655</x:v>
       </x:c>
       <x:c r="O25" s="3" t="s">
-        <x:v>668</x:v>
+        <x:v>656</x:v>
       </x:c>
       <x:c r="P25" s="3" t="s">
-        <x:v>669</x:v>
+        <x:v>657</x:v>
       </x:c>
       <x:c r="Q25" s="3" t="s">
-        <x:v>670</x:v>
+        <x:v>658</x:v>
       </x:c>
       <x:c r="R25" s="3" t="s">
-        <x:v>671</x:v>
+        <x:v>659</x:v>
       </x:c>
       <x:c r="S25" s="3" t="s">
-        <x:v>672</x:v>
+        <x:v>660</x:v>
       </x:c>
       <x:c r="T25" s="3" t="s">
-        <x:v>673</x:v>
+        <x:v>661</x:v>
       </x:c>
       <x:c r="U25" s="3" t="s">
         <x:v>52</x:v>
@@ -10202,19 +10166,19 @@
     </x:row>
     <x:row r="26" ht="79.25" hidden="0">
       <x:c r="A26" s="3" t="s">
-        <x:v>674</x:v>
+        <x:v>662</x:v>
       </x:c>
       <x:c r="B26" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C26" s="3" t="s">
-        <x:v>675</x:v>
+        <x:v>663</x:v>
       </x:c>
       <x:c r="D26" s="3" t="s">
-        <x:v>676</x:v>
+        <x:v>664</x:v>
       </x:c>
       <x:c r="E26" s="3" t="s">
-        <x:v>677</x:v>
+        <x:v>665</x:v>
       </x:c>
       <x:c r="F26" s="3" t="s">
         <x:v>37</x:v>
@@ -10235,31 +10199,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L26" s="3" t="s">
-        <x:v>678</x:v>
+        <x:v>666</x:v>
       </x:c>
       <x:c r="M26" s="3" t="s">
-        <x:v>679</x:v>
+        <x:v>667</x:v>
       </x:c>
       <x:c r="N26" s="3" t="s">
-        <x:v>680</x:v>
+        <x:v>668</x:v>
       </x:c>
       <x:c r="O26" s="3" t="s">
-        <x:v>681</x:v>
+        <x:v>669</x:v>
       </x:c>
       <x:c r="P26" s="3" t="s">
-        <x:v>682</x:v>
+        <x:v>670</x:v>
       </x:c>
       <x:c r="Q26" s="3" t="s">
-        <x:v>683</x:v>
+        <x:v>671</x:v>
       </x:c>
       <x:c r="R26" s="3" t="s">
-        <x:v>684</x:v>
+        <x:v>672</x:v>
       </x:c>
       <x:c r="S26" s="3" t="s">
-        <x:v>685</x:v>
+        <x:v>673</x:v>
       </x:c>
       <x:c r="T26" s="3" t="s">
-        <x:v>686</x:v>
+        <x:v>674</x:v>
       </x:c>
       <x:c r="U26" s="3" t="s">
         <x:v>52</x:v>
@@ -10267,19 +10231,19 @@
     </x:row>
     <x:row r="27" ht="79.25" hidden="0">
       <x:c r="A27" s="3" t="s">
-        <x:v>687</x:v>
+        <x:v>675</x:v>
       </x:c>
       <x:c r="B27" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C27" s="3" t="s">
-        <x:v>688</x:v>
+        <x:v>676</x:v>
       </x:c>
       <x:c r="D27" s="3" t="s">
-        <x:v>689</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="E27" s="3" t="s">
-        <x:v>690</x:v>
+        <x:v>678</x:v>
       </x:c>
       <x:c r="F27" s="3" t="s">
         <x:v>37</x:v>
@@ -10300,31 +10264,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L27" s="3" t="s">
-        <x:v>691</x:v>
+        <x:v>679</x:v>
       </x:c>
       <x:c r="M27" s="3" t="s">
-        <x:v>692</x:v>
+        <x:v>680</x:v>
       </x:c>
       <x:c r="N27" s="3" t="s">
-        <x:v>693</x:v>
+        <x:v>681</x:v>
       </x:c>
       <x:c r="O27" s="3" t="s">
-        <x:v>694</x:v>
+        <x:v>682</x:v>
       </x:c>
       <x:c r="P27" s="3" t="s">
-        <x:v>695</x:v>
+        <x:v>683</x:v>
       </x:c>
       <x:c r="Q27" s="3" t="s">
-        <x:v>696</x:v>
+        <x:v>684</x:v>
       </x:c>
       <x:c r="R27" s="3" t="s">
-        <x:v>697</x:v>
+        <x:v>685</x:v>
       </x:c>
       <x:c r="S27" s="3" t="s">
-        <x:v>698</x:v>
+        <x:v>686</x:v>
       </x:c>
       <x:c r="T27" s="3" t="s">
-        <x:v>699</x:v>
+        <x:v>687</x:v>
       </x:c>
       <x:c r="U27" s="3" t="s">
         <x:v>52</x:v>
@@ -10332,19 +10296,19 @@
     </x:row>
     <x:row r="28" ht="93.25" hidden="0">
       <x:c r="A28" s="3" t="s">
-        <x:v>700</x:v>
+        <x:v>688</x:v>
       </x:c>
       <x:c r="B28" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C28" s="3" t="s">
-        <x:v>701</x:v>
+        <x:v>689</x:v>
       </x:c>
       <x:c r="D28" s="3" t="s">
-        <x:v>702</x:v>
+        <x:v>690</x:v>
       </x:c>
       <x:c r="E28" s="3" t="s">
-        <x:v>703</x:v>
+        <x:v>691</x:v>
       </x:c>
       <x:c r="F28" s="3" t="s">
         <x:v>37</x:v>
@@ -10365,31 +10329,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L28" s="3" t="s">
-        <x:v>704</x:v>
+        <x:v>692</x:v>
       </x:c>
       <x:c r="M28" s="3" t="s">
-        <x:v>705</x:v>
+        <x:v>693</x:v>
       </x:c>
       <x:c r="N28" s="3" t="s">
-        <x:v>706</x:v>
+        <x:v>694</x:v>
       </x:c>
       <x:c r="O28" s="3" t="s">
-        <x:v>707</x:v>
+        <x:v>695</x:v>
       </x:c>
       <x:c r="P28" s="3" t="s">
-        <x:v>708</x:v>
+        <x:v>696</x:v>
       </x:c>
       <x:c r="Q28" s="3" t="s">
-        <x:v>709</x:v>
+        <x:v>697</x:v>
       </x:c>
       <x:c r="R28" s="3" t="s">
-        <x:v>710</x:v>
+        <x:v>698</x:v>
       </x:c>
       <x:c r="S28" s="3" t="s">
         <x:v>286</x:v>
       </x:c>
       <x:c r="T28" s="3" t="s">
-        <x:v>711</x:v>
+        <x:v>699</x:v>
       </x:c>
       <x:c r="U28" s="3" t="s">
         <x:v>52</x:v>
@@ -10397,19 +10361,19 @@
     </x:row>
     <x:row r="29" ht="93.25" hidden="0">
       <x:c r="A29" s="3" t="s">
-        <x:v>712</x:v>
+        <x:v>700</x:v>
       </x:c>
       <x:c r="B29" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C29" s="3" t="s">
-        <x:v>713</x:v>
+        <x:v>701</x:v>
       </x:c>
       <x:c r="D29" s="3" t="s">
-        <x:v>714</x:v>
+        <x:v>702</x:v>
       </x:c>
       <x:c r="E29" s="3" t="s">
-        <x:v>715</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="F29" s="3" t="s">
         <x:v>37</x:v>
@@ -10430,31 +10394,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="L29" s="3" t="s">
-        <x:v>716</x:v>
+        <x:v>704</x:v>
       </x:c>
       <x:c r="M29" s="3" t="s">
-        <x:v>717</x:v>
+        <x:v>705</x:v>
       </x:c>
       <x:c r="N29" s="3" t="s">
-        <x:v>718</x:v>
+        <x:v>706</x:v>
       </x:c>
       <x:c r="O29" s="3" t="s">
-        <x:v>719</x:v>
+        <x:v>707</x:v>
       </x:c>
       <x:c r="P29" s="3" t="s">
-        <x:v>720</x:v>
+        <x:v>708</x:v>
       </x:c>
       <x:c r="Q29" s="3" t="s">
-        <x:v>721</x:v>
+        <x:v>709</x:v>
       </x:c>
       <x:c r="R29" s="3" t="s">
-        <x:v>722</x:v>
+        <x:v>710</x:v>
       </x:c>
       <x:c r="S29" s="3" t="s">
-        <x:v>723</x:v>
+        <x:v>711</x:v>
       </x:c>
       <x:c r="T29" s="3" t="s">
-        <x:v>724</x:v>
+        <x:v>712</x:v>
       </x:c>
       <x:c r="U29" s="3" t="s">
         <x:v>52</x:v>
@@ -10462,19 +10426,19 @@
     </x:row>
     <x:row r="30" ht="93.25" hidden="0">
       <x:c r="A30" s="3" t="s">
-        <x:v>725</x:v>
+        <x:v>713</x:v>
       </x:c>
       <x:c r="B30" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C30" s="3" t="s">
-        <x:v>726</x:v>
+        <x:v>714</x:v>
       </x:c>
       <x:c r="D30" s="3" t="s">
-        <x:v>727</x:v>
+        <x:v>715</x:v>
       </x:c>
       <x:c r="E30" s="3" t="s">
-        <x:v>728</x:v>
+        <x:v>716</x:v>
       </x:c>
       <x:c r="F30" s="3" t="s">
         <x:v>37</x:v>
@@ -10495,31 +10459,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L30" s="3" t="s">
-        <x:v>729</x:v>
+        <x:v>717</x:v>
       </x:c>
       <x:c r="M30" s="3" t="s">
-        <x:v>730</x:v>
+        <x:v>718</x:v>
       </x:c>
       <x:c r="N30" s="3" t="s">
-        <x:v>731</x:v>
+        <x:v>719</x:v>
       </x:c>
       <x:c r="O30" s="3" t="s">
-        <x:v>732</x:v>
+        <x:v>720</x:v>
       </x:c>
       <x:c r="P30" s="3" t="s">
-        <x:v>733</x:v>
+        <x:v>721</x:v>
       </x:c>
       <x:c r="Q30" s="3" t="s">
-        <x:v>734</x:v>
+        <x:v>722</x:v>
       </x:c>
       <x:c r="R30" s="3" t="s">
-        <x:v>735</x:v>
+        <x:v>723</x:v>
       </x:c>
       <x:c r="S30" s="3" t="s">
-        <x:v>736</x:v>
+        <x:v>724</x:v>
       </x:c>
       <x:c r="T30" s="3" t="s">
-        <x:v>737</x:v>
+        <x:v>725</x:v>
       </x:c>
       <x:c r="U30" s="3" t="s">
         <x:v>52</x:v>
@@ -10527,19 +10491,19 @@
     </x:row>
     <x:row r="31" ht="93.25" hidden="0">
       <x:c r="A31" s="3" t="s">
-        <x:v>738</x:v>
+        <x:v>726</x:v>
       </x:c>
       <x:c r="B31" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C31" s="3" t="s">
-        <x:v>739</x:v>
+        <x:v>727</x:v>
       </x:c>
       <x:c r="D31" s="3" t="s">
-        <x:v>740</x:v>
+        <x:v>728</x:v>
       </x:c>
       <x:c r="E31" s="3" t="s">
-        <x:v>741</x:v>
+        <x:v>729</x:v>
       </x:c>
       <x:c r="F31" s="3" t="s">
         <x:v>37</x:v>
@@ -10560,31 +10524,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="L31" s="3" t="s">
-        <x:v>742</x:v>
+        <x:v>730</x:v>
       </x:c>
       <x:c r="M31" s="3" t="s">
-        <x:v>743</x:v>
+        <x:v>731</x:v>
       </x:c>
       <x:c r="N31" s="3" t="s">
-        <x:v>744</x:v>
+        <x:v>732</x:v>
       </x:c>
       <x:c r="O31" s="3" t="s">
-        <x:v>745</x:v>
+        <x:v>733</x:v>
       </x:c>
       <x:c r="P31" s="3" t="s">
-        <x:v>746</x:v>
+        <x:v>734</x:v>
       </x:c>
       <x:c r="Q31" s="3" t="s">
-        <x:v>747</x:v>
+        <x:v>735</x:v>
       </x:c>
       <x:c r="R31" s="3" t="s">
-        <x:v>748</x:v>
+        <x:v>736</x:v>
       </x:c>
       <x:c r="S31" s="3" t="s">
-        <x:v>749</x:v>
+        <x:v>737</x:v>
       </x:c>
       <x:c r="T31" s="3" t="s">
-        <x:v>750</x:v>
+        <x:v>738</x:v>
       </x:c>
       <x:c r="U31" s="3" t="s">
         <x:v>52</x:v>
@@ -10592,19 +10556,19 @@
     </x:row>
     <x:row r="32" ht="93.25" hidden="0">
       <x:c r="A32" s="3" t="s">
-        <x:v>751</x:v>
+        <x:v>739</x:v>
       </x:c>
       <x:c r="B32" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C32" s="3" t="s">
-        <x:v>752</x:v>
+        <x:v>740</x:v>
       </x:c>
       <x:c r="D32" s="3" t="s">
-        <x:v>753</x:v>
+        <x:v>741</x:v>
       </x:c>
       <x:c r="E32" s="3" t="s">
-        <x:v>754</x:v>
+        <x:v>742</x:v>
       </x:c>
       <x:c r="F32" s="3" t="s">
         <x:v>37</x:v>
@@ -10625,31 +10589,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L32" s="3" t="s">
-        <x:v>755</x:v>
+        <x:v>743</x:v>
       </x:c>
       <x:c r="M32" s="3" t="s">
-        <x:v>756</x:v>
+        <x:v>744</x:v>
       </x:c>
       <x:c r="N32" s="3" t="s">
-        <x:v>757</x:v>
+        <x:v>745</x:v>
       </x:c>
       <x:c r="O32" s="3" t="s">
-        <x:v>758</x:v>
+        <x:v>746</x:v>
       </x:c>
       <x:c r="P32" s="3" t="s">
-        <x:v>759</x:v>
+        <x:v>747</x:v>
       </x:c>
       <x:c r="Q32" s="3" t="s">
-        <x:v>760</x:v>
+        <x:v>748</x:v>
       </x:c>
       <x:c r="R32" s="3" t="s">
-        <x:v>761</x:v>
+        <x:v>749</x:v>
       </x:c>
       <x:c r="S32" s="3" t="s">
-        <x:v>762</x:v>
+        <x:v>750</x:v>
       </x:c>
       <x:c r="T32" s="3" t="s">
-        <x:v>763</x:v>
+        <x:v>751</x:v>
       </x:c>
       <x:c r="U32" s="3" t="s">
         <x:v>52</x:v>
@@ -10657,19 +10621,19 @@
     </x:row>
     <x:row r="33" ht="93.25" hidden="0">
       <x:c r="A33" s="3" t="s">
-        <x:v>764</x:v>
+        <x:v>752</x:v>
       </x:c>
       <x:c r="B33" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C33" s="3" t="s">
-        <x:v>765</x:v>
+        <x:v>753</x:v>
       </x:c>
       <x:c r="D33" s="3" t="s">
-        <x:v>766</x:v>
+        <x:v>754</x:v>
       </x:c>
       <x:c r="E33" s="3" t="s">
-        <x:v>767</x:v>
+        <x:v>755</x:v>
       </x:c>
       <x:c r="F33" s="3" t="s">
         <x:v>37</x:v>
@@ -10690,31 +10654,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L33" s="3" t="s">
-        <x:v>768</x:v>
+        <x:v>756</x:v>
       </x:c>
       <x:c r="M33" s="3" t="s">
-        <x:v>769</x:v>
+        <x:v>757</x:v>
       </x:c>
       <x:c r="N33" s="3" t="s">
-        <x:v>770</x:v>
+        <x:v>758</x:v>
       </x:c>
       <x:c r="O33" s="3" t="s">
-        <x:v>771</x:v>
+        <x:v>759</x:v>
       </x:c>
       <x:c r="P33" s="3" t="s">
-        <x:v>772</x:v>
+        <x:v>760</x:v>
       </x:c>
       <x:c r="Q33" s="3" t="s">
-        <x:v>773</x:v>
+        <x:v>761</x:v>
       </x:c>
       <x:c r="R33" s="3" t="s">
-        <x:v>774</x:v>
+        <x:v>762</x:v>
       </x:c>
       <x:c r="S33" s="3" t="s">
-        <x:v>775</x:v>
+        <x:v>763</x:v>
       </x:c>
       <x:c r="T33" s="3" t="s">
-        <x:v>776</x:v>
+        <x:v>764</x:v>
       </x:c>
       <x:c r="U33" s="3" t="s">
         <x:v>52</x:v>
@@ -10722,7 +10686,7 @@
     </x:row>
     <x:row r="34" ht="93.25" hidden="0">
       <x:c r="A34" s="3" t="s">
-        <x:v>777</x:v>
+        <x:v>765</x:v>
       </x:c>
       <x:c r="B34" s="3" t="s">
         <x:v>8</x:v>
@@ -10731,10 +10695,10 @@
         <x:v>313</x:v>
       </x:c>
       <x:c r="D34" s="3" t="s">
-        <x:v>778</x:v>
+        <x:v>766</x:v>
       </x:c>
       <x:c r="E34" s="3" t="s">
-        <x:v>779</x:v>
+        <x:v>767</x:v>
       </x:c>
       <x:c r="F34" s="3" t="s">
         <x:v>37</x:v>
@@ -10755,31 +10719,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="L34" s="3" t="s">
-        <x:v>780</x:v>
+        <x:v>768</x:v>
       </x:c>
       <x:c r="M34" s="3" t="s">
-        <x:v>781</x:v>
+        <x:v>769</x:v>
       </x:c>
       <x:c r="N34" s="3" t="s">
-        <x:v>782</x:v>
+        <x:v>770</x:v>
       </x:c>
       <x:c r="O34" s="3" t="s">
-        <x:v>783</x:v>
+        <x:v>771</x:v>
       </x:c>
       <x:c r="P34" s="3" t="s">
-        <x:v>784</x:v>
+        <x:v>772</x:v>
       </x:c>
       <x:c r="Q34" s="3" t="s">
-        <x:v>785</x:v>
+        <x:v>773</x:v>
       </x:c>
       <x:c r="R34" s="3" t="s">
-        <x:v>786</x:v>
+        <x:v>774</x:v>
       </x:c>
       <x:c r="S34" s="3" t="s">
         <x:v>323</x:v>
       </x:c>
       <x:c r="T34" s="3" t="s">
-        <x:v>787</x:v>
+        <x:v>775</x:v>
       </x:c>
       <x:c r="U34" s="3" t="s">
         <x:v>52</x:v>
@@ -10787,19 +10751,19 @@
     </x:row>
     <x:row r="35" ht="93.25" hidden="0">
       <x:c r="A35" s="3" t="s">
-        <x:v>788</x:v>
+        <x:v>776</x:v>
       </x:c>
       <x:c r="B35" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C35" s="3" t="s">
-        <x:v>789</x:v>
+        <x:v>777</x:v>
       </x:c>
       <x:c r="D35" s="3" t="s">
-        <x:v>790</x:v>
+        <x:v>778</x:v>
       </x:c>
       <x:c r="E35" s="3" t="s">
-        <x:v>791</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="F35" s="3" t="s">
         <x:v>37</x:v>
@@ -10820,31 +10784,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L35" s="3" t="s">
-        <x:v>792</x:v>
+        <x:v>780</x:v>
       </x:c>
       <x:c r="M35" s="3" t="s">
-        <x:v>793</x:v>
+        <x:v>781</x:v>
       </x:c>
       <x:c r="N35" s="3" t="s">
-        <x:v>794</x:v>
+        <x:v>782</x:v>
       </x:c>
       <x:c r="O35" s="3" t="s">
-        <x:v>569</x:v>
+        <x:v>557</x:v>
       </x:c>
       <x:c r="P35" s="3" t="s">
-        <x:v>795</x:v>
+        <x:v>783</x:v>
       </x:c>
       <x:c r="Q35" s="3" t="s">
-        <x:v>796</x:v>
+        <x:v>784</x:v>
       </x:c>
       <x:c r="R35" s="3" t="s">
-        <x:v>797</x:v>
+        <x:v>785</x:v>
       </x:c>
       <x:c r="S35" s="3" t="s">
-        <x:v>798</x:v>
+        <x:v>786</x:v>
       </x:c>
       <x:c r="T35" s="3" t="s">
-        <x:v>799</x:v>
+        <x:v>787</x:v>
       </x:c>
       <x:c r="U35" s="3" t="s">
         <x:v>52</x:v>
@@ -10852,19 +10816,19 @@
     </x:row>
     <x:row r="36" ht="93.25" hidden="0">
       <x:c r="A36" s="3" t="s">
-        <x:v>800</x:v>
+        <x:v>788</x:v>
       </x:c>
       <x:c r="B36" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C36" s="3" t="s">
-        <x:v>801</x:v>
+        <x:v>789</x:v>
       </x:c>
       <x:c r="D36" s="3" t="s">
-        <x:v>802</x:v>
+        <x:v>790</x:v>
       </x:c>
       <x:c r="E36" s="3" t="s">
-        <x:v>803</x:v>
+        <x:v>791</x:v>
       </x:c>
       <x:c r="F36" s="3" t="s">
         <x:v>37</x:v>
@@ -10885,31 +10849,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L36" s="3" t="s">
-        <x:v>804</x:v>
+        <x:v>792</x:v>
       </x:c>
       <x:c r="M36" s="3" t="s">
         <x:v>446</x:v>
       </x:c>
       <x:c r="N36" s="3" t="s">
-        <x:v>805</x:v>
+        <x:v>793</x:v>
       </x:c>
       <x:c r="O36" s="3" t="s">
-        <x:v>806</x:v>
+        <x:v>794</x:v>
       </x:c>
       <x:c r="P36" s="3" t="s">
-        <x:v>807</x:v>
+        <x:v>795</x:v>
       </x:c>
       <x:c r="Q36" s="3" t="s">
-        <x:v>808</x:v>
+        <x:v>796</x:v>
       </x:c>
       <x:c r="R36" s="3" t="s">
-        <x:v>809</x:v>
+        <x:v>797</x:v>
       </x:c>
       <x:c r="S36" s="3" t="s">
-        <x:v>810</x:v>
+        <x:v>798</x:v>
       </x:c>
       <x:c r="T36" s="3" t="s">
-        <x:v>811</x:v>
+        <x:v>799</x:v>
       </x:c>
       <x:c r="U36" s="3" t="s">
         <x:v>52</x:v>
@@ -10917,19 +10881,19 @@
     </x:row>
     <x:row r="37" ht="93.25" hidden="0">
       <x:c r="A37" s="3" t="s">
-        <x:v>812</x:v>
+        <x:v>800</x:v>
       </x:c>
       <x:c r="B37" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C37" s="3" t="s">
-        <x:v>813</x:v>
+        <x:v>801</x:v>
       </x:c>
       <x:c r="D37" s="3" t="s">
-        <x:v>814</x:v>
+        <x:v>802</x:v>
       </x:c>
       <x:c r="E37" s="3" t="s">
-        <x:v>815</x:v>
+        <x:v>803</x:v>
       </x:c>
       <x:c r="F37" s="3" t="s">
         <x:v>37</x:v>
@@ -10950,31 +10914,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L37" s="3" t="s">
-        <x:v>816</x:v>
+        <x:v>804</x:v>
       </x:c>
       <x:c r="M37" s="3" t="s">
-        <x:v>817</x:v>
+        <x:v>805</x:v>
       </x:c>
       <x:c r="N37" s="3" t="s">
-        <x:v>818</x:v>
+        <x:v>806</x:v>
       </x:c>
       <x:c r="O37" s="3" t="s">
-        <x:v>819</x:v>
+        <x:v>807</x:v>
       </x:c>
       <x:c r="P37" s="3" t="s">
-        <x:v>820</x:v>
+        <x:v>808</x:v>
       </x:c>
       <x:c r="Q37" s="3" t="s">
-        <x:v>821</x:v>
+        <x:v>809</x:v>
       </x:c>
       <x:c r="R37" s="3" t="s">
-        <x:v>822</x:v>
+        <x:v>810</x:v>
       </x:c>
       <x:c r="S37" s="3" t="s">
-        <x:v>823</x:v>
+        <x:v>811</x:v>
       </x:c>
       <x:c r="T37" s="3" t="s">
-        <x:v>817</x:v>
+        <x:v>805</x:v>
       </x:c>
       <x:c r="U37" s="3" t="s">
         <x:v>52</x:v>
@@ -10982,19 +10946,19 @@
     </x:row>
     <x:row r="38" ht="93.25" hidden="0">
       <x:c r="A38" s="3" t="s">
-        <x:v>824</x:v>
+        <x:v>812</x:v>
       </x:c>
       <x:c r="B38" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C38" s="3" t="s">
-        <x:v>825</x:v>
+        <x:v>813</x:v>
       </x:c>
       <x:c r="D38" s="3" t="s">
-        <x:v>826</x:v>
+        <x:v>814</x:v>
       </x:c>
       <x:c r="E38" s="3" t="s">
-        <x:v>827</x:v>
+        <x:v>815</x:v>
       </x:c>
       <x:c r="F38" s="3" t="s">
         <x:v>37</x:v>
@@ -11015,31 +10979,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L38" s="3" t="s">
-        <x:v>828</x:v>
+        <x:v>816</x:v>
       </x:c>
       <x:c r="M38" s="3" t="s">
-        <x:v>494</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="N38" s="3" t="s">
-        <x:v>829</x:v>
+        <x:v>817</x:v>
       </x:c>
       <x:c r="O38" s="3" t="s">
-        <x:v>830</x:v>
+        <x:v>818</x:v>
       </x:c>
       <x:c r="P38" s="3" t="s">
-        <x:v>831</x:v>
+        <x:v>819</x:v>
       </x:c>
       <x:c r="Q38" s="3" t="s">
-        <x:v>832</x:v>
+        <x:v>820</x:v>
       </x:c>
       <x:c r="R38" s="3" t="s">
-        <x:v>833</x:v>
+        <x:v>821</x:v>
       </x:c>
       <x:c r="S38" s="3" t="s">
-        <x:v>834</x:v>
+        <x:v>822</x:v>
       </x:c>
       <x:c r="T38" s="3" t="s">
-        <x:v>835</x:v>
+        <x:v>823</x:v>
       </x:c>
       <x:c r="U38" s="3" t="s">
         <x:v>52</x:v>
@@ -11047,19 +11011,19 @@
     </x:row>
     <x:row r="39" ht="93.25" hidden="0">
       <x:c r="A39" s="3" t="s">
-        <x:v>836</x:v>
+        <x:v>824</x:v>
       </x:c>
       <x:c r="B39" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C39" s="3" t="s">
-        <x:v>837</x:v>
+        <x:v>825</x:v>
       </x:c>
       <x:c r="D39" s="3" t="s">
-        <x:v>838</x:v>
+        <x:v>826</x:v>
       </x:c>
       <x:c r="E39" s="3" t="s">
-        <x:v>839</x:v>
+        <x:v>827</x:v>
       </x:c>
       <x:c r="F39" s="3" t="s">
         <x:v>37</x:v>
@@ -11080,31 +11044,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="L39" s="3" t="s">
-        <x:v>840</x:v>
+        <x:v>828</x:v>
       </x:c>
       <x:c r="M39" s="3" t="s">
         <x:v>446</x:v>
       </x:c>
       <x:c r="N39" s="3" t="s">
-        <x:v>841</x:v>
+        <x:v>829</x:v>
       </x:c>
       <x:c r="O39" s="3" t="s">
-        <x:v>842</x:v>
+        <x:v>830</x:v>
       </x:c>
       <x:c r="P39" s="3" t="s">
-        <x:v>843</x:v>
+        <x:v>831</x:v>
       </x:c>
       <x:c r="Q39" s="3" t="s">
-        <x:v>844</x:v>
+        <x:v>832</x:v>
       </x:c>
       <x:c r="R39" s="3" t="s">
-        <x:v>845</x:v>
+        <x:v>833</x:v>
       </x:c>
       <x:c r="S39" s="3" t="s">
-        <x:v>846</x:v>
+        <x:v>834</x:v>
       </x:c>
       <x:c r="T39" s="3" t="s">
-        <x:v>847</x:v>
+        <x:v>835</x:v>
       </x:c>
       <x:c r="U39" s="3" t="s">
         <x:v>52</x:v>
@@ -11113,7 +11077,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree49df396751461c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f322ed9d7914018"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/maliev-feature-user-story-status.xlsx
+++ b/docs/maliev-feature-user-story-status.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rcf0701f9e3fc41be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="Re4e8f64e754e4bfa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R982e27500cc44dc7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="Rf3e0c1f295394a64"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R7daceb4650b246f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="Red47f93761c446a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="Rce0ce3ef418c4ede"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="R7369438bd66d48ae"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1409,39 +1409,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">AgentController.cs:271; QuoteAgentLaunchShell.razor</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QE-009</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Resumable CAD upload</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">As a customer, I can upload CAD files for part analysis.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Workspace creates resumable upload sessions, sends chunks, completes uploads, and checks analysis status.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">File picker -&gt; QuoteController uploads -&gt; storage/analysis</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">CAD file input, attachment picker, upload controls</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QuoteEngineSourceTests upload; QuoteEngineApiClientTests | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QuoteEngine BFF, Storage, Geometry/analysis</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Upload sessions/files/analysis status</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Needs browser file-picker retest</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QuoteWorkspace.razor; QuoteController.cs:68-259</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">QE-010</x:t>
@@ -5090,7 +5057,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47eb0d60f7954f2a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdac1550edeab47be"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8506,7 +8473,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R144959e895754513"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3e927a3a23d94da5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9125,85 +9092,85 @@
       </x:c>
     </x:row>
     <x:row r="10" ht="93.25" hidden="0">
-      <x:c r="A10" s="3" t="s">
-        <x:v>466</x:v>
-      </x:c>
-      <x:c r="B10" s="3" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C10" s="3" t="s">
-        <x:v>467</x:v>
-      </x:c>
-      <x:c r="D10" s="3" t="s">
-        <x:v>468</x:v>
-      </x:c>
-      <x:c r="E10" s="3" t="s">
-        <x:v>469</x:v>
-      </x:c>
-      <x:c r="F10" s="3" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="G10" s="3" t="s">
-        <x:v>442</x:v>
-      </x:c>
-      <x:c r="H10" s="3" t="s">
-        <x:v>443</x:v>
-      </x:c>
-      <x:c r="I10" s="3" t="s">
-        <x:v>444</x:v>
-      </x:c>
-      <x:c r="J10" s="3" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="K10" s="3" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="L10" s="3" t="s">
-        <x:v>470</x:v>
-      </x:c>
-      <x:c r="M10" s="3" t="s">
-        <x:v>424</x:v>
-      </x:c>
-      <x:c r="N10" s="3" t="s">
-        <x:v>471</x:v>
-      </x:c>
-      <x:c r="O10" s="3" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="P10" s="3" t="s">
-        <x:v>472</x:v>
-      </x:c>
-      <x:c r="Q10" s="3" t="s">
-        <x:v>473</x:v>
-      </x:c>
-      <x:c r="R10" s="3" t="s">
-        <x:v>474</x:v>
-      </x:c>
-      <x:c r="S10" s="3" t="s">
-        <x:v>475</x:v>
-      </x:c>
-      <x:c r="T10" s="3" t="s">
-        <x:v>476</x:v>
-      </x:c>
-      <x:c r="U10" s="3" t="s">
-        <x:v>52</x:v>
+      <x:c r="A10" s="3" t="str">
+        <x:v>QE-009</x:v>
+      </x:c>
+      <x:c r="B10" s="3" t="str">
+        <x:v>Maliev.QuoteEngine</x:v>
+      </x:c>
+      <x:c r="C10" s="3" t="str">
+        <x:v>Resumable CAD upload</x:v>
+      </x:c>
+      <x:c r="D10" s="3" t="str">
+        <x:v>As a customer, I can upload CAD files for part analysis.</x:v>
+      </x:c>
+      <x:c r="E10" s="3" t="str">
+        <x:v>Customers can choose, drop, or paste supported CAD and supplemental quote files; the workspace validates type and size, initiates a resumable upload, streams bytes with Content-Range, completes the upload, shows analysis/processing status, and preserves customer ownership boundaries.</x:v>
+      </x:c>
+      <x:c r="F10" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G10" s="3" t="str">
+        <x:v>Focused current-state resumable upload tests passed 2026-06-24.</x:v>
+      </x:c>
+      <x:c r="H10" s="3" t="str">
+        <x:v>No behavior error observed in focused QuoteEngine upload retest; live browser file-picker/drop/paste interaction still not executed in this slice.</x:v>
+      </x:c>
+      <x:c r="I10" s="3" t="str">
+        <x:v>No app fix applied for QE-009; current code path is covered by focused BFF/source tests.</x:v>
+      </x:c>
+      <x:c r="J10" s="3" t="str">
+        <x:v>Passed 28/28 focused tests covering upload constraints, supported CAD/context file initiation, resumable Content-Range streaming, upload ownership on analysis status, UploadService fallback policy, custom-file completion status, and QuoteWorkspace upload source contracts.</x:v>
+      </x:c>
+      <x:c r="K10" s="3" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="L10" s="3" t="str">
+        <x:v>QuoteWorkspace file picker/drop/paste -&gt; quoteEngineUploads browser JS capture/streaming -&gt; QuoteEngineApiClient -&gt; QuoteController resumable upload endpoints -&gt; QuoteUploadServiceClient/prototype fallback -&gt; analysis status and agent attachment registration</x:v>
+      </x:c>
+      <x:c r="M10" s="3" t="str">
+        <x:v>QuoteWorkspace.razor; quote-upload.js; QuoteEngineApiClient; QuoteController; QuoteUploadConstraints</x:v>
+      </x:c>
+      <x:c r="N10" s="3" t="str">
+        <x:v>InputFile quote-cad-files uses SupportedAttachmentAccept; OpenFilePickerAsync guards re-entrant picker opens; HandleFilesAsync and HandleDroppedFilesAsync capture files through quoteEngineUploads, validate candidates, create uploading parts, stream files, complete uploads, poll analysis status, and notify the agent shell.</x:v>
+      </x:c>
+      <x:c r="O10" s="3" t="str">
+        <x:v>POST quote/v1/uploads/resumable validates extension and size and creates a proxy upload URL; PUT quote/v1/uploads/resumable/{uploadId} requires Content-Range and streams to UploadService; POST quote/v1/uploads/resumable/{uploadId}/complete returns processing/analyzed state; GET quote/v1/uploads/{uploadId}/analysis-status enforces upload ownership.</x:v>
+      </x:c>
+      <x:c r="P10" s="3" t="str">
+        <x:v>2026-06-24: focused QuoteEngine upload/source test filter passed 28/28 with dotnet test Maliev.QuoteEngine.slnx --verbosity minimal. Coverage included QuoteUploadConstraintTests, resumable Content-Range streaming, analysis-status ownership, UploadService fallback policy, custom-file completion, and QuoteWorkspace source contracts.</x:v>
+      </x:c>
+      <x:c r="Q10" s="3" t="str">
+        <x:v>QuoteEngine Client, QuoteEngine BFF, UploadService client, Geometry/analysis status, SignalR notifications, agent attachment registration</x:v>
+      </x:c>
+      <x:c r="R10" s="3" t="str">
+        <x:v>Browser-retained file handles, upload IDs, downstream upload IDs, storage paths, upload status, part view models, analysis status, agent attachment state</x:v>
+      </x:c>
+      <x:c r="S10" s="3" t="str">
+        <x:v>Needs live browser retest for file picker, drag/drop, paste, interruption/resume, and file cleanup against a running QuoteEngine host.</x:v>
+      </x:c>
+      <x:c r="T10" s="3" t="str">
+        <x:v>Maliev.QuoteEngine.Client/Pages/QuoteWorkspace.razor:21,289,454,526,536,541,631; Maliev.QuoteEngine.Client/wwwroot/js/quote-upload.js:1; Maliev.QuoteEngine.Client/Services/QuoteEngineApiClient.cs:49,83,92; Maliev.QuoteEngine.Bff/Controllers/QuoteController.cs:68,134,194,259; Maliev.QuoteEngine.Tests/QuoteUploadConstraintTests.cs:37,58,74,90,113; Maliev.QuoteEngine.Tests/QuoteEngineEndpointTests.cs:2305,2337,2369,2421,2466; Maliev.QuoteEngine.Tests/QuoteEngineSourceTests.cs:604,679,762</x:v>
+      </x:c>
+      <x:c r="U10" s="3" t="str">
+        <x:v>2026-06-24</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="93.25" hidden="0">
       <x:c r="A11" s="3" t="s">
-        <x:v>477</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="B11" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C11" s="3" t="s">
-        <x:v>478</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="D11" s="3" t="s">
-        <x:v>479</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="E11" s="3" t="s">
-        <x:v>480</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="F11" s="3" t="s">
         <x:v>37</x:v>
@@ -9224,31 +9191,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L11" s="3" t="s">
-        <x:v>481</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="M11" s="3" t="s">
-        <x:v>482</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="N11" s="3" t="s">
-        <x:v>483</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="O11" s="3" t="s">
-        <x:v>484</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="P11" s="3" t="s">
-        <x:v>485</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="Q11" s="3" t="s">
-        <x:v>486</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="R11" s="3" t="s">
-        <x:v>487</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="S11" s="3" t="s">
-        <x:v>488</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="T11" s="3" t="s">
-        <x:v>489</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="U11" s="3" t="s">
         <x:v>52</x:v>
@@ -9256,19 +9223,19 @@
     </x:row>
     <x:row r="12" ht="107.25" hidden="0">
       <x:c r="A12" s="3" t="s">
-        <x:v>490</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="B12" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C12" s="3" t="s">
-        <x:v>491</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="D12" s="3" t="s">
-        <x:v>492</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="E12" s="3" t="s">
-        <x:v>493</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="F12" s="3" t="s">
         <x:v>37</x:v>
@@ -9289,31 +9256,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L12" s="3" t="s">
-        <x:v>494</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="M12" s="3" t="s">
         <x:v>446</x:v>
       </x:c>
       <x:c r="N12" s="3" t="s">
-        <x:v>495</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="O12" s="3" t="s">
-        <x:v>496</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="P12" s="3" t="s">
-        <x:v>497</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="Q12" s="3" t="s">
-        <x:v>498</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="R12" s="3" t="s">
-        <x:v>499</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="S12" s="3" t="s">
-        <x:v>500</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="T12" s="3" t="s">
-        <x:v>501</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="U12" s="3" t="s">
         <x:v>52</x:v>
@@ -9321,19 +9288,19 @@
     </x:row>
     <x:row r="13" ht="93.25" hidden="0">
       <x:c r="A13" s="3" t="s">
-        <x:v>502</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="B13" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C13" s="3" t="s">
-        <x:v>503</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="D13" s="3" t="s">
-        <x:v>504</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="E13" s="3" t="s">
-        <x:v>505</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="F13" s="3" t="s">
         <x:v>37</x:v>
@@ -9354,31 +9321,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L13" s="3" t="s">
-        <x:v>506</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="M13" s="3" t="s">
         <x:v>446</x:v>
       </x:c>
       <x:c r="N13" s="3" t="s">
-        <x:v>507</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="O13" s="3" t="s">
-        <x:v>508</x:v>
+        <x:v>497</x:v>
       </x:c>
       <x:c r="P13" s="3" t="s">
-        <x:v>509</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="Q13" s="3" t="s">
-        <x:v>498</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="R13" s="3" t="s">
-        <x:v>510</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="S13" s="3" t="s">
-        <x:v>511</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="T13" s="3" t="s">
-        <x:v>512</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="U13" s="3" t="s">
         <x:v>52</x:v>
@@ -9386,19 +9353,19 @@
     </x:row>
     <x:row r="14" ht="93.25" hidden="0">
       <x:c r="A14" s="3" t="s">
-        <x:v>513</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="B14" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C14" s="3" t="s">
-        <x:v>514</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="D14" s="3" t="s">
-        <x:v>515</x:v>
+        <x:v>504</x:v>
       </x:c>
       <x:c r="E14" s="3" t="s">
-        <x:v>516</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="F14" s="3" t="s">
         <x:v>37</x:v>
@@ -9419,31 +9386,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L14" s="3" t="s">
-        <x:v>517</x:v>
+        <x:v>506</x:v>
       </x:c>
       <x:c r="M14" s="3" t="s">
-        <x:v>518</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="N14" s="3" t="s">
-        <x:v>519</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="O14" s="3" t="s">
-        <x:v>520</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="P14" s="3" t="s">
-        <x:v>521</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="Q14" s="3" t="s">
-        <x:v>522</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="R14" s="3" t="s">
-        <x:v>523</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="S14" s="3" t="s">
-        <x:v>524</x:v>
+        <x:v>513</x:v>
       </x:c>
       <x:c r="T14" s="3" t="s">
-        <x:v>525</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="U14" s="3" t="s">
         <x:v>52</x:v>
@@ -9451,19 +9418,19 @@
     </x:row>
     <x:row r="15" ht="107.25" hidden="0">
       <x:c r="A15" s="3" t="s">
-        <x:v>526</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="B15" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C15" s="3" t="s">
-        <x:v>527</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="D15" s="3" t="s">
-        <x:v>528</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="E15" s="3" t="s">
-        <x:v>529</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="F15" s="3" t="s">
         <x:v>37</x:v>
@@ -9484,31 +9451,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L15" s="3" t="s">
-        <x:v>530</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="M15" s="3" t="s">
         <x:v>446</x:v>
       </x:c>
       <x:c r="N15" s="3" t="s">
-        <x:v>531</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="O15" s="3" t="s">
-        <x:v>532</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="P15" s="3" t="s">
-        <x:v>533</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="Q15" s="3" t="s">
-        <x:v>534</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="R15" s="3" t="s">
-        <x:v>535</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="S15" s="3" t="s">
-        <x:v>536</x:v>
+        <x:v>525</x:v>
       </x:c>
       <x:c r="T15" s="3" t="s">
-        <x:v>537</x:v>
+        <x:v>526</x:v>
       </x:c>
       <x:c r="U15" s="3" t="s">
         <x:v>52</x:v>
@@ -9516,19 +9483,19 @@
     </x:row>
     <x:row r="16" ht="107.25" hidden="0">
       <x:c r="A16" s="3" t="s">
-        <x:v>538</x:v>
+        <x:v>527</x:v>
       </x:c>
       <x:c r="B16" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C16" s="3" t="s">
-        <x:v>539</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="D16" s="3" t="s">
-        <x:v>540</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="E16" s="3" t="s">
-        <x:v>541</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="F16" s="3" t="s">
         <x:v>37</x:v>
@@ -9549,31 +9516,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L16" s="3" t="s">
-        <x:v>542</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="M16" s="3" t="s">
         <x:v>446</x:v>
       </x:c>
       <x:c r="N16" s="3" t="s">
-        <x:v>543</x:v>
+        <x:v>532</x:v>
       </x:c>
       <x:c r="O16" s="3" t="s">
-        <x:v>544</x:v>
+        <x:v>533</x:v>
       </x:c>
       <x:c r="P16" s="3" t="s">
-        <x:v>545</x:v>
+        <x:v>534</x:v>
       </x:c>
       <x:c r="Q16" s="3" t="s">
-        <x:v>546</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="R16" s="3" t="s">
-        <x:v>547</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="S16" s="3" t="s">
-        <x:v>548</x:v>
+        <x:v>537</x:v>
       </x:c>
       <x:c r="T16" s="3" t="s">
-        <x:v>549</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="U16" s="3" t="s">
         <x:v>52</x:v>
@@ -9581,19 +9548,19 @@
     </x:row>
     <x:row r="17" ht="93.25" hidden="0">
       <x:c r="A17" s="3" t="s">
-        <x:v>550</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="B17" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C17" s="3" t="s">
-        <x:v>551</x:v>
+        <x:v>540</x:v>
       </x:c>
       <x:c r="D17" s="3" t="s">
-        <x:v>552</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="E17" s="3" t="s">
-        <x:v>553</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="F17" s="3" t="s">
         <x:v>37</x:v>
@@ -9614,31 +9581,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L17" s="3" t="s">
-        <x:v>554</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="M17" s="3" t="s">
-        <x:v>555</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="N17" s="3" t="s">
-        <x:v>556</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="O17" s="3" t="s">
-        <x:v>557</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="P17" s="3" t="s">
-        <x:v>558</x:v>
+        <x:v>547</x:v>
       </x:c>
       <x:c r="Q17" s="3" t="s">
-        <x:v>559</x:v>
+        <x:v>548</x:v>
       </x:c>
       <x:c r="R17" s="3" t="s">
-        <x:v>560</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="S17" s="3" t="s">
-        <x:v>561</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="T17" s="3" t="s">
-        <x:v>562</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="U17" s="3" t="s">
         <x:v>52</x:v>
@@ -9646,19 +9613,19 @@
     </x:row>
     <x:row r="18" ht="93.25" hidden="0">
       <x:c r="A18" s="3" t="s">
-        <x:v>563</x:v>
+        <x:v>552</x:v>
       </x:c>
       <x:c r="B18" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C18" s="3" t="s">
-        <x:v>564</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="D18" s="3" t="s">
-        <x:v>565</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="E18" s="3" t="s">
-        <x:v>566</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="F18" s="3" t="s">
         <x:v>37</x:v>
@@ -9679,31 +9646,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L18" s="3" t="s">
-        <x:v>567</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="M18" s="3" t="s">
-        <x:v>568</x:v>
+        <x:v>557</x:v>
       </x:c>
       <x:c r="N18" s="3" t="s">
-        <x:v>569</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="O18" s="3" t="s">
-        <x:v>570</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="P18" s="3" t="s">
-        <x:v>571</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="Q18" s="3" t="s">
-        <x:v>572</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="R18" s="3" t="s">
-        <x:v>573</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="S18" s="3" t="s">
-        <x:v>574</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="T18" s="3" t="s">
-        <x:v>575</x:v>
+        <x:v>564</x:v>
       </x:c>
       <x:c r="U18" s="3" t="s">
         <x:v>52</x:v>
@@ -9711,19 +9678,19 @@
     </x:row>
     <x:row r="19" ht="93.25" hidden="0">
       <x:c r="A19" s="3" t="s">
-        <x:v>576</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="B19" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C19" s="3" t="s">
-        <x:v>577</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="D19" s="3" t="s">
-        <x:v>578</x:v>
+        <x:v>567</x:v>
       </x:c>
       <x:c r="E19" s="3" t="s">
-        <x:v>579</x:v>
+        <x:v>568</x:v>
       </x:c>
       <x:c r="F19" s="3" t="s">
         <x:v>37</x:v>
@@ -9744,31 +9711,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L19" s="3" t="s">
-        <x:v>580</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="M19" s="3" t="s">
-        <x:v>581</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="N19" s="3" t="s">
-        <x:v>582</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="O19" s="3" t="s">
-        <x:v>583</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="P19" s="3" t="s">
-        <x:v>584</x:v>
+        <x:v>573</x:v>
       </x:c>
       <x:c r="Q19" s="3" t="s">
-        <x:v>585</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="R19" s="3" t="s">
-        <x:v>586</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="S19" s="3" t="s">
-        <x:v>587</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="T19" s="3" t="s">
-        <x:v>588</x:v>
+        <x:v>577</x:v>
       </x:c>
       <x:c r="U19" s="3" t="s">
         <x:v>52</x:v>
@@ -9776,19 +9743,19 @@
     </x:row>
     <x:row r="20" ht="79.25" hidden="0">
       <x:c r="A20" s="3" t="s">
-        <x:v>589</x:v>
+        <x:v>578</x:v>
       </x:c>
       <x:c r="B20" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C20" s="3" t="s">
-        <x:v>590</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="D20" s="3" t="s">
-        <x:v>591</x:v>
+        <x:v>580</x:v>
       </x:c>
       <x:c r="E20" s="3" t="s">
-        <x:v>592</x:v>
+        <x:v>581</x:v>
       </x:c>
       <x:c r="F20" s="3" t="s">
         <x:v>37</x:v>
@@ -9809,31 +9776,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L20" s="3" t="s">
-        <x:v>593</x:v>
+        <x:v>582</x:v>
       </x:c>
       <x:c r="M20" s="3" t="s">
-        <x:v>594</x:v>
+        <x:v>583</x:v>
       </x:c>
       <x:c r="N20" s="3" t="s">
-        <x:v>595</x:v>
+        <x:v>584</x:v>
       </x:c>
       <x:c r="O20" s="3" t="s">
-        <x:v>596</x:v>
+        <x:v>585</x:v>
       </x:c>
       <x:c r="P20" s="3" t="s">
-        <x:v>597</x:v>
+        <x:v>586</x:v>
       </x:c>
       <x:c r="Q20" s="3" t="s">
-        <x:v>598</x:v>
+        <x:v>587</x:v>
       </x:c>
       <x:c r="R20" s="3" t="s">
-        <x:v>599</x:v>
+        <x:v>588</x:v>
       </x:c>
       <x:c r="S20" s="3" t="s">
-        <x:v>600</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="T20" s="3" t="s">
-        <x:v>601</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="U20" s="3" t="s">
         <x:v>52</x:v>
@@ -9841,19 +9808,19 @@
     </x:row>
     <x:row r="21" ht="79.25" hidden="0">
       <x:c r="A21" s="3" t="s">
-        <x:v>602</x:v>
+        <x:v>591</x:v>
       </x:c>
       <x:c r="B21" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C21" s="3" t="s">
-        <x:v>603</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="D21" s="3" t="s">
-        <x:v>604</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="E21" s="3" t="s">
-        <x:v>605</x:v>
+        <x:v>594</x:v>
       </x:c>
       <x:c r="F21" s="3" t="s">
         <x:v>37</x:v>
@@ -9874,31 +9841,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L21" s="3" t="s">
-        <x:v>606</x:v>
+        <x:v>595</x:v>
       </x:c>
       <x:c r="M21" s="3" t="s">
-        <x:v>607</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="N21" s="3" t="s">
-        <x:v>608</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="O21" s="3" t="s">
         <x:v>218</x:v>
       </x:c>
       <x:c r="P21" s="3" t="s">
-        <x:v>609</x:v>
+        <x:v>598</x:v>
       </x:c>
       <x:c r="Q21" s="3" t="s">
-        <x:v>610</x:v>
+        <x:v>599</x:v>
       </x:c>
       <x:c r="R21" s="3" t="s">
         <x:v>221</x:v>
       </x:c>
       <x:c r="S21" s="3" t="s">
-        <x:v>611</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="T21" s="3" t="s">
-        <x:v>612</x:v>
+        <x:v>601</x:v>
       </x:c>
       <x:c r="U21" s="3" t="s">
         <x:v>52</x:v>
@@ -9906,19 +9873,19 @@
     </x:row>
     <x:row r="22" ht="93.25" hidden="0">
       <x:c r="A22" s="3" t="s">
-        <x:v>613</x:v>
+        <x:v>602</x:v>
       </x:c>
       <x:c r="B22" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C22" s="3" t="s">
-        <x:v>614</x:v>
+        <x:v>603</x:v>
       </x:c>
       <x:c r="D22" s="3" t="s">
-        <x:v>615</x:v>
+        <x:v>604</x:v>
       </x:c>
       <x:c r="E22" s="3" t="s">
-        <x:v>616</x:v>
+        <x:v>605</x:v>
       </x:c>
       <x:c r="F22" s="3" t="s">
         <x:v>37</x:v>
@@ -9939,31 +9906,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L22" s="3" t="s">
-        <x:v>617</x:v>
+        <x:v>606</x:v>
       </x:c>
       <x:c r="M22" s="3" t="s">
-        <x:v>482</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="N22" s="3" t="s">
-        <x:v>618</x:v>
+        <x:v>607</x:v>
       </x:c>
       <x:c r="O22" s="3" t="s">
-        <x:v>619</x:v>
+        <x:v>608</x:v>
       </x:c>
       <x:c r="P22" s="3" t="s">
-        <x:v>620</x:v>
+        <x:v>609</x:v>
       </x:c>
       <x:c r="Q22" s="3" t="s">
-        <x:v>621</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="R22" s="3" t="s">
-        <x:v>622</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="S22" s="3" t="s">
-        <x:v>623</x:v>
+        <x:v>612</x:v>
       </x:c>
       <x:c r="T22" s="3" t="s">
-        <x:v>624</x:v>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="U22" s="3" t="s">
         <x:v>52</x:v>
@@ -9971,19 +9938,19 @@
     </x:row>
     <x:row r="23" ht="93.25" hidden="0">
       <x:c r="A23" s="3" t="s">
-        <x:v>625</x:v>
+        <x:v>614</x:v>
       </x:c>
       <x:c r="B23" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C23" s="3" t="s">
-        <x:v>626</x:v>
+        <x:v>615</x:v>
       </x:c>
       <x:c r="D23" s="3" t="s">
-        <x:v>627</x:v>
+        <x:v>616</x:v>
       </x:c>
       <x:c r="E23" s="3" t="s">
-        <x:v>628</x:v>
+        <x:v>617</x:v>
       </x:c>
       <x:c r="F23" s="3" t="s">
         <x:v>37</x:v>
@@ -10004,31 +9971,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L23" s="3" t="s">
-        <x:v>629</x:v>
+        <x:v>618</x:v>
       </x:c>
       <x:c r="M23" s="3" t="s">
-        <x:v>630</x:v>
+        <x:v>619</x:v>
       </x:c>
       <x:c r="N23" s="3" t="s">
-        <x:v>631</x:v>
+        <x:v>620</x:v>
       </x:c>
       <x:c r="O23" s="3" t="s">
-        <x:v>632</x:v>
+        <x:v>621</x:v>
       </x:c>
       <x:c r="P23" s="3" t="s">
-        <x:v>633</x:v>
+        <x:v>622</x:v>
       </x:c>
       <x:c r="Q23" s="3" t="s">
-        <x:v>634</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="R23" s="3" t="s">
-        <x:v>635</x:v>
+        <x:v>624</x:v>
       </x:c>
       <x:c r="S23" s="3" t="s">
-        <x:v>636</x:v>
+        <x:v>625</x:v>
       </x:c>
       <x:c r="T23" s="3" t="s">
-        <x:v>637</x:v>
+        <x:v>626</x:v>
       </x:c>
       <x:c r="U23" s="3" t="s">
         <x:v>52</x:v>
@@ -10036,19 +10003,19 @@
     </x:row>
     <x:row r="24" ht="79.25" hidden="0">
       <x:c r="A24" s="3" t="s">
-        <x:v>638</x:v>
+        <x:v>627</x:v>
       </x:c>
       <x:c r="B24" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C24" s="3" t="s">
-        <x:v>639</x:v>
+        <x:v>628</x:v>
       </x:c>
       <x:c r="D24" s="3" t="s">
-        <x:v>640</x:v>
+        <x:v>629</x:v>
       </x:c>
       <x:c r="E24" s="3" t="s">
-        <x:v>641</x:v>
+        <x:v>630</x:v>
       </x:c>
       <x:c r="F24" s="3" t="s">
         <x:v>37</x:v>
@@ -10069,31 +10036,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L24" s="3" t="s">
-        <x:v>642</x:v>
+        <x:v>631</x:v>
       </x:c>
       <x:c r="M24" s="3" t="s">
-        <x:v>607</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="N24" s="3" t="s">
-        <x:v>643</x:v>
+        <x:v>632</x:v>
       </x:c>
       <x:c r="O24" s="3" t="s">
-        <x:v>644</x:v>
+        <x:v>633</x:v>
       </x:c>
       <x:c r="P24" s="3" t="s">
-        <x:v>645</x:v>
+        <x:v>634</x:v>
       </x:c>
       <x:c r="Q24" s="3" t="s">
-        <x:v>646</x:v>
+        <x:v>635</x:v>
       </x:c>
       <x:c r="R24" s="3" t="s">
-        <x:v>647</x:v>
+        <x:v>636</x:v>
       </x:c>
       <x:c r="S24" s="3" t="s">
-        <x:v>648</x:v>
+        <x:v>637</x:v>
       </x:c>
       <x:c r="T24" s="3" t="s">
-        <x:v>649</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="U24" s="3" t="s">
         <x:v>52</x:v>
@@ -10101,19 +10068,19 @@
     </x:row>
     <x:row r="25" ht="79.25" hidden="0">
       <x:c r="A25" s="3" t="s">
-        <x:v>650</x:v>
+        <x:v>639</x:v>
       </x:c>
       <x:c r="B25" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C25" s="3" t="s">
-        <x:v>651</x:v>
+        <x:v>640</x:v>
       </x:c>
       <x:c r="D25" s="3" t="s">
-        <x:v>652</x:v>
+        <x:v>641</x:v>
       </x:c>
       <x:c r="E25" s="3" t="s">
-        <x:v>653</x:v>
+        <x:v>642</x:v>
       </x:c>
       <x:c r="F25" s="3" t="s">
         <x:v>37</x:v>
@@ -10134,31 +10101,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L25" s="3" t="s">
-        <x:v>654</x:v>
+        <x:v>643</x:v>
       </x:c>
       <x:c r="M25" s="3" t="s">
-        <x:v>607</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="N25" s="3" t="s">
-        <x:v>655</x:v>
+        <x:v>644</x:v>
       </x:c>
       <x:c r="O25" s="3" t="s">
-        <x:v>656</x:v>
+        <x:v>645</x:v>
       </x:c>
       <x:c r="P25" s="3" t="s">
-        <x:v>657</x:v>
+        <x:v>646</x:v>
       </x:c>
       <x:c r="Q25" s="3" t="s">
-        <x:v>658</x:v>
+        <x:v>647</x:v>
       </x:c>
       <x:c r="R25" s="3" t="s">
-        <x:v>659</x:v>
+        <x:v>648</x:v>
       </x:c>
       <x:c r="S25" s="3" t="s">
-        <x:v>660</x:v>
+        <x:v>649</x:v>
       </x:c>
       <x:c r="T25" s="3" t="s">
-        <x:v>661</x:v>
+        <x:v>650</x:v>
       </x:c>
       <x:c r="U25" s="3" t="s">
         <x:v>52</x:v>
@@ -10166,19 +10133,19 @@
     </x:row>
     <x:row r="26" ht="79.25" hidden="0">
       <x:c r="A26" s="3" t="s">
-        <x:v>662</x:v>
+        <x:v>651</x:v>
       </x:c>
       <x:c r="B26" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C26" s="3" t="s">
-        <x:v>663</x:v>
+        <x:v>652</x:v>
       </x:c>
       <x:c r="D26" s="3" t="s">
-        <x:v>664</x:v>
+        <x:v>653</x:v>
       </x:c>
       <x:c r="E26" s="3" t="s">
-        <x:v>665</x:v>
+        <x:v>654</x:v>
       </x:c>
       <x:c r="F26" s="3" t="s">
         <x:v>37</x:v>
@@ -10199,31 +10166,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L26" s="3" t="s">
-        <x:v>666</x:v>
+        <x:v>655</x:v>
       </x:c>
       <x:c r="M26" s="3" t="s">
-        <x:v>667</x:v>
+        <x:v>656</x:v>
       </x:c>
       <x:c r="N26" s="3" t="s">
-        <x:v>668</x:v>
+        <x:v>657</x:v>
       </x:c>
       <x:c r="O26" s="3" t="s">
-        <x:v>669</x:v>
+        <x:v>658</x:v>
       </x:c>
       <x:c r="P26" s="3" t="s">
-        <x:v>670</x:v>
+        <x:v>659</x:v>
       </x:c>
       <x:c r="Q26" s="3" t="s">
-        <x:v>671</x:v>
+        <x:v>660</x:v>
       </x:c>
       <x:c r="R26" s="3" t="s">
-        <x:v>672</x:v>
+        <x:v>661</x:v>
       </x:c>
       <x:c r="S26" s="3" t="s">
-        <x:v>673</x:v>
+        <x:v>662</x:v>
       </x:c>
       <x:c r="T26" s="3" t="s">
-        <x:v>674</x:v>
+        <x:v>663</x:v>
       </x:c>
       <x:c r="U26" s="3" t="s">
         <x:v>52</x:v>
@@ -10231,19 +10198,19 @@
     </x:row>
     <x:row r="27" ht="79.25" hidden="0">
       <x:c r="A27" s="3" t="s">
-        <x:v>675</x:v>
+        <x:v>664</x:v>
       </x:c>
       <x:c r="B27" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C27" s="3" t="s">
-        <x:v>676</x:v>
+        <x:v>665</x:v>
       </x:c>
       <x:c r="D27" s="3" t="s">
-        <x:v>677</x:v>
+        <x:v>666</x:v>
       </x:c>
       <x:c r="E27" s="3" t="s">
-        <x:v>678</x:v>
+        <x:v>667</x:v>
       </x:c>
       <x:c r="F27" s="3" t="s">
         <x:v>37</x:v>
@@ -10264,31 +10231,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L27" s="3" t="s">
-        <x:v>679</x:v>
+        <x:v>668</x:v>
       </x:c>
       <x:c r="M27" s="3" t="s">
-        <x:v>680</x:v>
+        <x:v>669</x:v>
       </x:c>
       <x:c r="N27" s="3" t="s">
-        <x:v>681</x:v>
+        <x:v>670</x:v>
       </x:c>
       <x:c r="O27" s="3" t="s">
-        <x:v>682</x:v>
+        <x:v>671</x:v>
       </x:c>
       <x:c r="P27" s="3" t="s">
-        <x:v>683</x:v>
+        <x:v>672</x:v>
       </x:c>
       <x:c r="Q27" s="3" t="s">
-        <x:v>684</x:v>
+        <x:v>673</x:v>
       </x:c>
       <x:c r="R27" s="3" t="s">
-        <x:v>685</x:v>
+        <x:v>674</x:v>
       </x:c>
       <x:c r="S27" s="3" t="s">
-        <x:v>686</x:v>
+        <x:v>675</x:v>
       </x:c>
       <x:c r="T27" s="3" t="s">
-        <x:v>687</x:v>
+        <x:v>676</x:v>
       </x:c>
       <x:c r="U27" s="3" t="s">
         <x:v>52</x:v>
@@ -10296,19 +10263,19 @@
     </x:row>
     <x:row r="28" ht="93.25" hidden="0">
       <x:c r="A28" s="3" t="s">
-        <x:v>688</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="B28" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C28" s="3" t="s">
-        <x:v>689</x:v>
+        <x:v>678</x:v>
       </x:c>
       <x:c r="D28" s="3" t="s">
-        <x:v>690</x:v>
+        <x:v>679</x:v>
       </x:c>
       <x:c r="E28" s="3" t="s">
-        <x:v>691</x:v>
+        <x:v>680</x:v>
       </x:c>
       <x:c r="F28" s="3" t="s">
         <x:v>37</x:v>
@@ -10329,31 +10296,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L28" s="3" t="s">
-        <x:v>692</x:v>
+        <x:v>681</x:v>
       </x:c>
       <x:c r="M28" s="3" t="s">
-        <x:v>693</x:v>
+        <x:v>682</x:v>
       </x:c>
       <x:c r="N28" s="3" t="s">
-        <x:v>694</x:v>
+        <x:v>683</x:v>
       </x:c>
       <x:c r="O28" s="3" t="s">
-        <x:v>695</x:v>
+        <x:v>684</x:v>
       </x:c>
       <x:c r="P28" s="3" t="s">
-        <x:v>696</x:v>
+        <x:v>685</x:v>
       </x:c>
       <x:c r="Q28" s="3" t="s">
-        <x:v>697</x:v>
+        <x:v>686</x:v>
       </x:c>
       <x:c r="R28" s="3" t="s">
-        <x:v>698</x:v>
+        <x:v>687</x:v>
       </x:c>
       <x:c r="S28" s="3" t="s">
         <x:v>286</x:v>
       </x:c>
       <x:c r="T28" s="3" t="s">
-        <x:v>699</x:v>
+        <x:v>688</x:v>
       </x:c>
       <x:c r="U28" s="3" t="s">
         <x:v>52</x:v>
@@ -10361,19 +10328,19 @@
     </x:row>
     <x:row r="29" ht="93.25" hidden="0">
       <x:c r="A29" s="3" t="s">
-        <x:v>700</x:v>
+        <x:v>689</x:v>
       </x:c>
       <x:c r="B29" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C29" s="3" t="s">
-        <x:v>701</x:v>
+        <x:v>690</x:v>
       </x:c>
       <x:c r="D29" s="3" t="s">
-        <x:v>702</x:v>
+        <x:v>691</x:v>
       </x:c>
       <x:c r="E29" s="3" t="s">
-        <x:v>703</x:v>
+        <x:v>692</x:v>
       </x:c>
       <x:c r="F29" s="3" t="s">
         <x:v>37</x:v>
@@ -10394,31 +10361,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="L29" s="3" t="s">
-        <x:v>704</x:v>
+        <x:v>693</x:v>
       </x:c>
       <x:c r="M29" s="3" t="s">
-        <x:v>705</x:v>
+        <x:v>694</x:v>
       </x:c>
       <x:c r="N29" s="3" t="s">
-        <x:v>706</x:v>
+        <x:v>695</x:v>
       </x:c>
       <x:c r="O29" s="3" t="s">
-        <x:v>707</x:v>
+        <x:v>696</x:v>
       </x:c>
       <x:c r="P29" s="3" t="s">
-        <x:v>708</x:v>
+        <x:v>697</x:v>
       </x:c>
       <x:c r="Q29" s="3" t="s">
-        <x:v>709</x:v>
+        <x:v>698</x:v>
       </x:c>
       <x:c r="R29" s="3" t="s">
-        <x:v>710</x:v>
+        <x:v>699</x:v>
       </x:c>
       <x:c r="S29" s="3" t="s">
-        <x:v>711</x:v>
+        <x:v>700</x:v>
       </x:c>
       <x:c r="T29" s="3" t="s">
-        <x:v>712</x:v>
+        <x:v>701</x:v>
       </x:c>
       <x:c r="U29" s="3" t="s">
         <x:v>52</x:v>
@@ -10426,19 +10393,19 @@
     </x:row>
     <x:row r="30" ht="93.25" hidden="0">
       <x:c r="A30" s="3" t="s">
-        <x:v>713</x:v>
+        <x:v>702</x:v>
       </x:c>
       <x:c r="B30" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C30" s="3" t="s">
-        <x:v>714</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="D30" s="3" t="s">
-        <x:v>715</x:v>
+        <x:v>704</x:v>
       </x:c>
       <x:c r="E30" s="3" t="s">
-        <x:v>716</x:v>
+        <x:v>705</x:v>
       </x:c>
       <x:c r="F30" s="3" t="s">
         <x:v>37</x:v>
@@ -10459,31 +10426,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L30" s="3" t="s">
-        <x:v>717</x:v>
+        <x:v>706</x:v>
       </x:c>
       <x:c r="M30" s="3" t="s">
-        <x:v>718</x:v>
+        <x:v>707</x:v>
       </x:c>
       <x:c r="N30" s="3" t="s">
-        <x:v>719</x:v>
+        <x:v>708</x:v>
       </x:c>
       <x:c r="O30" s="3" t="s">
-        <x:v>720</x:v>
+        <x:v>709</x:v>
       </x:c>
       <x:c r="P30" s="3" t="s">
-        <x:v>721</x:v>
+        <x:v>710</x:v>
       </x:c>
       <x:c r="Q30" s="3" t="s">
-        <x:v>722</x:v>
+        <x:v>711</x:v>
       </x:c>
       <x:c r="R30" s="3" t="s">
-        <x:v>723</x:v>
+        <x:v>712</x:v>
       </x:c>
       <x:c r="S30" s="3" t="s">
-        <x:v>724</x:v>
+        <x:v>713</x:v>
       </x:c>
       <x:c r="T30" s="3" t="s">
-        <x:v>725</x:v>
+        <x:v>714</x:v>
       </x:c>
       <x:c r="U30" s="3" t="s">
         <x:v>52</x:v>
@@ -10491,19 +10458,19 @@
     </x:row>
     <x:row r="31" ht="93.25" hidden="0">
       <x:c r="A31" s="3" t="s">
-        <x:v>726</x:v>
+        <x:v>715</x:v>
       </x:c>
       <x:c r="B31" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C31" s="3" t="s">
-        <x:v>727</x:v>
+        <x:v>716</x:v>
       </x:c>
       <x:c r="D31" s="3" t="s">
-        <x:v>728</x:v>
+        <x:v>717</x:v>
       </x:c>
       <x:c r="E31" s="3" t="s">
-        <x:v>729</x:v>
+        <x:v>718</x:v>
       </x:c>
       <x:c r="F31" s="3" t="s">
         <x:v>37</x:v>
@@ -10524,31 +10491,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="L31" s="3" t="s">
-        <x:v>730</x:v>
+        <x:v>719</x:v>
       </x:c>
       <x:c r="M31" s="3" t="s">
-        <x:v>731</x:v>
+        <x:v>720</x:v>
       </x:c>
       <x:c r="N31" s="3" t="s">
-        <x:v>732</x:v>
+        <x:v>721</x:v>
       </x:c>
       <x:c r="O31" s="3" t="s">
-        <x:v>733</x:v>
+        <x:v>722</x:v>
       </x:c>
       <x:c r="P31" s="3" t="s">
-        <x:v>734</x:v>
+        <x:v>723</x:v>
       </x:c>
       <x:c r="Q31" s="3" t="s">
-        <x:v>735</x:v>
+        <x:v>724</x:v>
       </x:c>
       <x:c r="R31" s="3" t="s">
-        <x:v>736</x:v>
+        <x:v>725</x:v>
       </x:c>
       <x:c r="S31" s="3" t="s">
-        <x:v>737</x:v>
+        <x:v>726</x:v>
       </x:c>
       <x:c r="T31" s="3" t="s">
-        <x:v>738</x:v>
+        <x:v>727</x:v>
       </x:c>
       <x:c r="U31" s="3" t="s">
         <x:v>52</x:v>
@@ -10556,19 +10523,19 @@
     </x:row>
     <x:row r="32" ht="93.25" hidden="0">
       <x:c r="A32" s="3" t="s">
-        <x:v>739</x:v>
+        <x:v>728</x:v>
       </x:c>
       <x:c r="B32" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C32" s="3" t="s">
-        <x:v>740</x:v>
+        <x:v>729</x:v>
       </x:c>
       <x:c r="D32" s="3" t="s">
-        <x:v>741</x:v>
+        <x:v>730</x:v>
       </x:c>
       <x:c r="E32" s="3" t="s">
-        <x:v>742</x:v>
+        <x:v>731</x:v>
       </x:c>
       <x:c r="F32" s="3" t="s">
         <x:v>37</x:v>
@@ -10589,31 +10556,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L32" s="3" t="s">
-        <x:v>743</x:v>
+        <x:v>732</x:v>
       </x:c>
       <x:c r="M32" s="3" t="s">
-        <x:v>744</x:v>
+        <x:v>733</x:v>
       </x:c>
       <x:c r="N32" s="3" t="s">
-        <x:v>745</x:v>
+        <x:v>734</x:v>
       </x:c>
       <x:c r="O32" s="3" t="s">
-        <x:v>746</x:v>
+        <x:v>735</x:v>
       </x:c>
       <x:c r="P32" s="3" t="s">
-        <x:v>747</x:v>
+        <x:v>736</x:v>
       </x:c>
       <x:c r="Q32" s="3" t="s">
-        <x:v>748</x:v>
+        <x:v>737</x:v>
       </x:c>
       <x:c r="R32" s="3" t="s">
-        <x:v>749</x:v>
+        <x:v>738</x:v>
       </x:c>
       <x:c r="S32" s="3" t="s">
-        <x:v>750</x:v>
+        <x:v>739</x:v>
       </x:c>
       <x:c r="T32" s="3" t="s">
-        <x:v>751</x:v>
+        <x:v>740</x:v>
       </x:c>
       <x:c r="U32" s="3" t="s">
         <x:v>52</x:v>
@@ -10621,19 +10588,19 @@
     </x:row>
     <x:row r="33" ht="93.25" hidden="0">
       <x:c r="A33" s="3" t="s">
-        <x:v>752</x:v>
+        <x:v>741</x:v>
       </x:c>
       <x:c r="B33" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C33" s="3" t="s">
-        <x:v>753</x:v>
+        <x:v>742</x:v>
       </x:c>
       <x:c r="D33" s="3" t="s">
-        <x:v>754</x:v>
+        <x:v>743</x:v>
       </x:c>
       <x:c r="E33" s="3" t="s">
-        <x:v>755</x:v>
+        <x:v>744</x:v>
       </x:c>
       <x:c r="F33" s="3" t="s">
         <x:v>37</x:v>
@@ -10654,31 +10621,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L33" s="3" t="s">
-        <x:v>756</x:v>
+        <x:v>745</x:v>
       </x:c>
       <x:c r="M33" s="3" t="s">
-        <x:v>757</x:v>
+        <x:v>746</x:v>
       </x:c>
       <x:c r="N33" s="3" t="s">
-        <x:v>758</x:v>
+        <x:v>747</x:v>
       </x:c>
       <x:c r="O33" s="3" t="s">
-        <x:v>759</x:v>
+        <x:v>748</x:v>
       </x:c>
       <x:c r="P33" s="3" t="s">
-        <x:v>760</x:v>
+        <x:v>749</x:v>
       </x:c>
       <x:c r="Q33" s="3" t="s">
-        <x:v>761</x:v>
+        <x:v>750</x:v>
       </x:c>
       <x:c r="R33" s="3" t="s">
-        <x:v>762</x:v>
+        <x:v>751</x:v>
       </x:c>
       <x:c r="S33" s="3" t="s">
-        <x:v>763</x:v>
+        <x:v>752</x:v>
       </x:c>
       <x:c r="T33" s="3" t="s">
-        <x:v>764</x:v>
+        <x:v>753</x:v>
       </x:c>
       <x:c r="U33" s="3" t="s">
         <x:v>52</x:v>
@@ -10686,7 +10653,7 @@
     </x:row>
     <x:row r="34" ht="93.25" hidden="0">
       <x:c r="A34" s="3" t="s">
-        <x:v>765</x:v>
+        <x:v>754</x:v>
       </x:c>
       <x:c r="B34" s="3" t="s">
         <x:v>8</x:v>
@@ -10695,10 +10662,10 @@
         <x:v>313</x:v>
       </x:c>
       <x:c r="D34" s="3" t="s">
-        <x:v>766</x:v>
+        <x:v>755</x:v>
       </x:c>
       <x:c r="E34" s="3" t="s">
-        <x:v>767</x:v>
+        <x:v>756</x:v>
       </x:c>
       <x:c r="F34" s="3" t="s">
         <x:v>37</x:v>
@@ -10719,31 +10686,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="L34" s="3" t="s">
-        <x:v>768</x:v>
+        <x:v>757</x:v>
       </x:c>
       <x:c r="M34" s="3" t="s">
-        <x:v>769</x:v>
+        <x:v>758</x:v>
       </x:c>
       <x:c r="N34" s="3" t="s">
-        <x:v>770</x:v>
+        <x:v>759</x:v>
       </x:c>
       <x:c r="O34" s="3" t="s">
-        <x:v>771</x:v>
+        <x:v>760</x:v>
       </x:c>
       <x:c r="P34" s="3" t="s">
-        <x:v>772</x:v>
+        <x:v>761</x:v>
       </x:c>
       <x:c r="Q34" s="3" t="s">
-        <x:v>773</x:v>
+        <x:v>762</x:v>
       </x:c>
       <x:c r="R34" s="3" t="s">
-        <x:v>774</x:v>
+        <x:v>763</x:v>
       </x:c>
       <x:c r="S34" s="3" t="s">
         <x:v>323</x:v>
       </x:c>
       <x:c r="T34" s="3" t="s">
-        <x:v>775</x:v>
+        <x:v>764</x:v>
       </x:c>
       <x:c r="U34" s="3" t="s">
         <x:v>52</x:v>
@@ -10751,19 +10718,19 @@
     </x:row>
     <x:row r="35" ht="93.25" hidden="0">
       <x:c r="A35" s="3" t="s">
-        <x:v>776</x:v>
+        <x:v>765</x:v>
       </x:c>
       <x:c r="B35" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C35" s="3" t="s">
-        <x:v>777</x:v>
+        <x:v>766</x:v>
       </x:c>
       <x:c r="D35" s="3" t="s">
-        <x:v>778</x:v>
+        <x:v>767</x:v>
       </x:c>
       <x:c r="E35" s="3" t="s">
-        <x:v>779</x:v>
+        <x:v>768</x:v>
       </x:c>
       <x:c r="F35" s="3" t="s">
         <x:v>37</x:v>
@@ -10784,31 +10751,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L35" s="3" t="s">
-        <x:v>780</x:v>
+        <x:v>769</x:v>
       </x:c>
       <x:c r="M35" s="3" t="s">
-        <x:v>781</x:v>
+        <x:v>770</x:v>
       </x:c>
       <x:c r="N35" s="3" t="s">
-        <x:v>782</x:v>
+        <x:v>771</x:v>
       </x:c>
       <x:c r="O35" s="3" t="s">
-        <x:v>557</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="P35" s="3" t="s">
-        <x:v>783</x:v>
+        <x:v>772</x:v>
       </x:c>
       <x:c r="Q35" s="3" t="s">
-        <x:v>784</x:v>
+        <x:v>773</x:v>
       </x:c>
       <x:c r="R35" s="3" t="s">
-        <x:v>785</x:v>
+        <x:v>774</x:v>
       </x:c>
       <x:c r="S35" s="3" t="s">
-        <x:v>786</x:v>
+        <x:v>775</x:v>
       </x:c>
       <x:c r="T35" s="3" t="s">
-        <x:v>787</x:v>
+        <x:v>776</x:v>
       </x:c>
       <x:c r="U35" s="3" t="s">
         <x:v>52</x:v>
@@ -10816,19 +10783,19 @@
     </x:row>
     <x:row r="36" ht="93.25" hidden="0">
       <x:c r="A36" s="3" t="s">
-        <x:v>788</x:v>
+        <x:v>777</x:v>
       </x:c>
       <x:c r="B36" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C36" s="3" t="s">
-        <x:v>789</x:v>
+        <x:v>778</x:v>
       </x:c>
       <x:c r="D36" s="3" t="s">
-        <x:v>790</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="E36" s="3" t="s">
-        <x:v>791</x:v>
+        <x:v>780</x:v>
       </x:c>
       <x:c r="F36" s="3" t="s">
         <x:v>37</x:v>
@@ -10849,31 +10816,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L36" s="3" t="s">
-        <x:v>792</x:v>
+        <x:v>781</x:v>
       </x:c>
       <x:c r="M36" s="3" t="s">
         <x:v>446</x:v>
       </x:c>
       <x:c r="N36" s="3" t="s">
-        <x:v>793</x:v>
+        <x:v>782</x:v>
       </x:c>
       <x:c r="O36" s="3" t="s">
-        <x:v>794</x:v>
+        <x:v>783</x:v>
       </x:c>
       <x:c r="P36" s="3" t="s">
-        <x:v>795</x:v>
+        <x:v>784</x:v>
       </x:c>
       <x:c r="Q36" s="3" t="s">
-        <x:v>796</x:v>
+        <x:v>785</x:v>
       </x:c>
       <x:c r="R36" s="3" t="s">
-        <x:v>797</x:v>
+        <x:v>786</x:v>
       </x:c>
       <x:c r="S36" s="3" t="s">
-        <x:v>798</x:v>
+        <x:v>787</x:v>
       </x:c>
       <x:c r="T36" s="3" t="s">
-        <x:v>799</x:v>
+        <x:v>788</x:v>
       </x:c>
       <x:c r="U36" s="3" t="s">
         <x:v>52</x:v>
@@ -10881,19 +10848,19 @@
     </x:row>
     <x:row r="37" ht="93.25" hidden="0">
       <x:c r="A37" s="3" t="s">
-        <x:v>800</x:v>
+        <x:v>789</x:v>
       </x:c>
       <x:c r="B37" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C37" s="3" t="s">
-        <x:v>801</x:v>
+        <x:v>790</x:v>
       </x:c>
       <x:c r="D37" s="3" t="s">
-        <x:v>802</x:v>
+        <x:v>791</x:v>
       </x:c>
       <x:c r="E37" s="3" t="s">
-        <x:v>803</x:v>
+        <x:v>792</x:v>
       </x:c>
       <x:c r="F37" s="3" t="s">
         <x:v>37</x:v>
@@ -10914,31 +10881,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L37" s="3" t="s">
-        <x:v>804</x:v>
+        <x:v>793</x:v>
       </x:c>
       <x:c r="M37" s="3" t="s">
-        <x:v>805</x:v>
+        <x:v>794</x:v>
       </x:c>
       <x:c r="N37" s="3" t="s">
-        <x:v>806</x:v>
+        <x:v>795</x:v>
       </x:c>
       <x:c r="O37" s="3" t="s">
-        <x:v>807</x:v>
+        <x:v>796</x:v>
       </x:c>
       <x:c r="P37" s="3" t="s">
-        <x:v>808</x:v>
+        <x:v>797</x:v>
       </x:c>
       <x:c r="Q37" s="3" t="s">
-        <x:v>809</x:v>
+        <x:v>798</x:v>
       </x:c>
       <x:c r="R37" s="3" t="s">
-        <x:v>810</x:v>
+        <x:v>799</x:v>
       </x:c>
       <x:c r="S37" s="3" t="s">
-        <x:v>811</x:v>
+        <x:v>800</x:v>
       </x:c>
       <x:c r="T37" s="3" t="s">
-        <x:v>805</x:v>
+        <x:v>794</x:v>
       </x:c>
       <x:c r="U37" s="3" t="s">
         <x:v>52</x:v>
@@ -10946,19 +10913,19 @@
     </x:row>
     <x:row r="38" ht="93.25" hidden="0">
       <x:c r="A38" s="3" t="s">
-        <x:v>812</x:v>
+        <x:v>801</x:v>
       </x:c>
       <x:c r="B38" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C38" s="3" t="s">
-        <x:v>813</x:v>
+        <x:v>802</x:v>
       </x:c>
       <x:c r="D38" s="3" t="s">
-        <x:v>814</x:v>
+        <x:v>803</x:v>
       </x:c>
       <x:c r="E38" s="3" t="s">
-        <x:v>815</x:v>
+        <x:v>804</x:v>
       </x:c>
       <x:c r="F38" s="3" t="s">
         <x:v>37</x:v>
@@ -10979,31 +10946,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L38" s="3" t="s">
-        <x:v>816</x:v>
+        <x:v>805</x:v>
       </x:c>
       <x:c r="M38" s="3" t="s">
-        <x:v>482</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="N38" s="3" t="s">
-        <x:v>817</x:v>
+        <x:v>806</x:v>
       </x:c>
       <x:c r="O38" s="3" t="s">
-        <x:v>818</x:v>
+        <x:v>807</x:v>
       </x:c>
       <x:c r="P38" s="3" t="s">
-        <x:v>819</x:v>
+        <x:v>808</x:v>
       </x:c>
       <x:c r="Q38" s="3" t="s">
-        <x:v>820</x:v>
+        <x:v>809</x:v>
       </x:c>
       <x:c r="R38" s="3" t="s">
-        <x:v>821</x:v>
+        <x:v>810</x:v>
       </x:c>
       <x:c r="S38" s="3" t="s">
-        <x:v>822</x:v>
+        <x:v>811</x:v>
       </x:c>
       <x:c r="T38" s="3" t="s">
-        <x:v>823</x:v>
+        <x:v>812</x:v>
       </x:c>
       <x:c r="U38" s="3" t="s">
         <x:v>52</x:v>
@@ -11011,19 +10978,19 @@
     </x:row>
     <x:row r="39" ht="93.25" hidden="0">
       <x:c r="A39" s="3" t="s">
-        <x:v>824</x:v>
+        <x:v>813</x:v>
       </x:c>
       <x:c r="B39" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C39" s="3" t="s">
-        <x:v>825</x:v>
+        <x:v>814</x:v>
       </x:c>
       <x:c r="D39" s="3" t="s">
-        <x:v>826</x:v>
+        <x:v>815</x:v>
       </x:c>
       <x:c r="E39" s="3" t="s">
-        <x:v>827</x:v>
+        <x:v>816</x:v>
       </x:c>
       <x:c r="F39" s="3" t="s">
         <x:v>37</x:v>
@@ -11044,31 +11011,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="L39" s="3" t="s">
-        <x:v>828</x:v>
+        <x:v>817</x:v>
       </x:c>
       <x:c r="M39" s="3" t="s">
         <x:v>446</x:v>
       </x:c>
       <x:c r="N39" s="3" t="s">
-        <x:v>829</x:v>
+        <x:v>818</x:v>
       </x:c>
       <x:c r="O39" s="3" t="s">
-        <x:v>830</x:v>
+        <x:v>819</x:v>
       </x:c>
       <x:c r="P39" s="3" t="s">
-        <x:v>831</x:v>
+        <x:v>820</x:v>
       </x:c>
       <x:c r="Q39" s="3" t="s">
-        <x:v>832</x:v>
+        <x:v>821</x:v>
       </x:c>
       <x:c r="R39" s="3" t="s">
-        <x:v>833</x:v>
+        <x:v>822</x:v>
       </x:c>
       <x:c r="S39" s="3" t="s">
-        <x:v>834</x:v>
+        <x:v>823</x:v>
       </x:c>
       <x:c r="T39" s="3" t="s">
-        <x:v>835</x:v>
+        <x:v>824</x:v>
       </x:c>
       <x:c r="U39" s="3" t="s">
         <x:v>52</x:v>
@@ -11077,7 +11044,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f322ed9d7914018"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R98eb820354214b08"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/maliev-feature-user-story-status.xlsx
+++ b/docs/maliev-feature-user-story-status.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R7daceb4650b246f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="Red47f93761c446a5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="Rce0ce3ef418c4ede"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="R7369438bd66d48ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R55ec781b4d914d84"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="R875633f7b0ee44f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R04ac7350e4234996"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="R83b31bd731da41ef"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1411,427 +1411,391 @@
     <x:t xml:space="preserve">AgentController.cs:271; QuoteAgentLaunchShell.razor</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">QE-010</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Web handoff import</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">As a customer, I can continue from a public web quote upload into the workspace.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Workspace imports handoff uploads through signed handoff endpoint and registers those files with the active session.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Web handoff token -&gt; QuoteController uploads/handoff -&gt; workspace/session attachments</x:t>
+    <x:t xml:space="preserve">QE-011</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Agent attachments</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">As a customer, I can attach uploaded files as context before asking the agent.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Agent attachment endpoint registers uploaded files in session state and the shell previews attachments until sent.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Composer attachments -&gt; AgentController attachments -&gt; SessionStore</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Attachment preview and sent attachment display</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">AgentController POST sessions/{sessionId}/attachments</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">QuoteAgentEndpointTests attachment; QuoteAgentLaunchShell source tests | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">QuoteEngine BFF, SessionStore, Storage</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Session attachment records</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Needs attachment resend/removal browser pass</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">AgentController.cs:203; QuoteAgentLaunchShell.razor</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">QE-012</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Sketch attachments</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">As a customer, I can draw or attach a hand sketch for the agent.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Sketch dialog captures sketch data and posts it to the agent sketch endpoint.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Sketch UI -&gt; AgentController sketches -&gt; SessionStore/artifacts</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Hand sketch dialog/tools</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">AgentController POST sessions/{sessionId}/sketches</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">QuoteAgentEndpointTests sketches; source tests sketch disposal | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Sketch artifact/context</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Needs mobile sketch browser pass</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">AgentController.cs:367; QuoteAgentLaunchShell.razor</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">QE-013</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Google Drive connector</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">As a customer, I can connect Google Drive and select source files.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Connector endpoints start OAuth, handle callback, expose status, list files, and return connector handoff links.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Connector UI -&gt; GoogleDriveConnectorController and AgentController connector endpoints</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">QuoteAgentLaunchShell.razor; GoogleCallback.razor</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">/auth/callback/google; connector panel</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">GoogleDriveConnectorController start/callback/status/files; AgentController connectors/handoff</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">QuoteEngineSourceTests connector; endpoint tests where present | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">QuoteEngine BFF, Google Drive, Auth</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Connector tokens/status/file refs</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Needs OAuth environment smoke</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">GoogleDriveConnectorController.cs; AgentController.cs:180,190</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">QE-014</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Workflow artifacts</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">As a customer, I can inspect quote workflow artifacts produced by the agent.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Artifact drawer and workflow artifact surfaces display generated artifacts, selected artifacts, and downloads.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Shell artifacts -&gt; AgentController artifact download -&gt; artifact/storage service</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Artifact drawer/workflow artifacts</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">AgentController artifacts/download</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">QuoteAgentEndpointTests artifact download; QuoteEngineSourceTests artifacts | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">QuoteEngine BFF, Storage/artifact service</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Artifact records/files</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Needs real artifact visual browser pass</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">QuoteAgentLaunchShell.razor; AgentController.cs:402</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">QE-015</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Artifact feedback</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">As a customer, I can give feedback on generated previews/artifacts.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Inline viewer feedback posts sentiment/text feedback and reflects memory observation status.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Inline feedback UI -&gt; AgentController artifact-feedback -&gt; QuoteAgentService</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Thumb feedback and optional text</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">AgentController POST artifacts/{artifactId}/feedback</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">QuoteEngineSourceTests feedback; QuoteAgentEndpointTests feedback | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">QuoteEngine BFF, Agent service, Customer memory</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Feedback records/memory observations</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Needs feedback persistence retest</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">AgentController.cs:240; QuoteAgentService.cs</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">QE-016</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">3D part viewer</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">As a customer, I can inspect uploaded/generated parts in a 3D viewer.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Part viewer loads GLB/viewer URLs, applies viewer settings, and pushes process/material/runtime state to JS.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">QePartViewer -&gt; geometry runtime assets/telemetry -&gt; browser viewer</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">QePartViewer.razor; QePartDetailCard.razor</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">3D Model tab, artifact drawer viewer</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">GeometryRuntimeController manifest/assets/telemetry</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">QuoteEngineSourceTests viewer/runtime | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">QuoteEngine client/BFF, Geometry runtime</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Viewer settings/telemetry</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Needs visual canvas smoke</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">QePartViewer.razor; QePartDetailCard.razor; GeometryRuntimeController.cs</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">QE-017</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">DFM reporting</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">As a customer, I can review manufacturability checks for FDM, SLA, and CNC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">DFM tab renders process-specific report types and the agent can apply DFM reports to session state.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">QeDfmTab/QePartDetailCard -&gt; AgentController dfm -&gt; SessionStore</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">QeDfmTab.razor; QePartDetailCard.razor</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">DFM tab and issue acknowledgement</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">AgentController POST sessions/{sessionId}/dfm; QeDfmDtos</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">QuoteEngineSourceTests DFM | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">QuoteEngine BFF, Geometry/DFM, SessionStore</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">DFM reports and acknowledgement state</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Needs process-specific fixture coverage</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">QeDfmTab.razor; QePartDetailCard.razor; AgentController.cs:221</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">QE-018</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Part configuration sidebar</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">As a customer, I can select process, material, color, finish, tolerance, quantity, and options.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Configuration sidebar filters reference data and emits changes for quote estimation.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">QePartConfigSidebar -&gt; reference-data/estimate DTOs</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">QePartConfigSidebar.razor</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Part configuration controls</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">QuoteController reference-data/estimate</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">QuoteEngineSourceTests config sidebar | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">QuoteEngine client/BFF, Pricing/Material services</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Part configuration state</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Needs keyboard/accessibility check</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">QePartConfigSidebar.razor; QuoteController.cs:47,301</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">QE-019</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Reference data and currencies</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">As a customer, I can use current manufacturing reference data and currencies.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Reference endpoints expose processes/materials/finishes/tolerances/currency data used by workspace controls.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Workspace/client -&gt; quote/v1/reference-data and quote/v1/reference-data/currencies</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">QuoteEngineApiClient.cs</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Reference-driven controls</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">QuoteController reference-data; ReferenceDataController currencies</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">QuoteEngineApiClientTests | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">QuoteEngine BFF, Material/Pricing/Reference data</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Read-only reference data</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Needs stale-cache behavior check</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">QuoteController.cs:47; ReferenceDataController.cs:10-16; QuoteEngineApiClient.cs</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">QE-020</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Estimate</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">As a customer, I can request a quote estimate for configured parts.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Estimate endpoint prices configured parts and returns lead-time/total data for the summary/actions.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Workspace/summary -&gt; QuoteController estimate -&gt; Pricing service</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">QuoteWorkspace.razor; QeQuoteSummaryBar.razor</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Estimate action</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Pricing/QuoteEngine tests | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">QuoteEngine BFF, PricingService</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Needs current pricing acceptance checks</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">QuoteController.cs:301; QeQuoteSummaryBar.razor</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">QE-021</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Draft project</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">As a customer, I can persist configured parts into a project draft.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Projects/draft endpoint creates or updates draft project data for the session/customer.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Workspace -&gt; QuoteController projects/draft -&gt; project/quote service</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">QuoteWorkspace.razor</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Make Studio handoff flow</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QuoteController POST uploads/handoff</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QuoteEngineApiClientTests handoff | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QuoteEngine BFF, Web BFF, Storage</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Handoff upload references</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Needs cross-app browser retest</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QuoteWorkspace.razor; QuoteController.cs:235</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QE-011</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Agent attachments</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">As a customer, I can attach uploaded files as context before asking the agent.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Agent attachment endpoint registers uploaded files in session state and the shell previews attachments until sent.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Composer attachments -&gt; AgentController attachments -&gt; SessionStore</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Attachment preview and sent attachment display</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">AgentController POST sessions/{sessionId}/attachments</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QuoteAgentEndpointTests attachment; QuoteAgentLaunchShell source tests | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QuoteEngine BFF, SessionStore, Storage</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Session attachment records</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Needs attachment resend/removal browser pass</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">AgentController.cs:203; QuoteAgentLaunchShell.razor</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QE-012</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Sketch attachments</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">As a customer, I can draw or attach a hand sketch for the agent.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Sketch dialog captures sketch data and posts it to the agent sketch endpoint.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Sketch UI -&gt; AgentController sketches -&gt; SessionStore/artifacts</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Hand sketch dialog/tools</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">AgentController POST sessions/{sessionId}/sketches</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QuoteAgentEndpointTests sketches; source tests sketch disposal | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Sketch artifact/context</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Needs mobile sketch browser pass</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">AgentController.cs:367; QuoteAgentLaunchShell.razor</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QE-013</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Google Drive connector</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">As a customer, I can connect Google Drive and select source files.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Connector endpoints start OAuth, handle callback, expose status, list files, and return connector handoff links.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Connector UI -&gt; GoogleDriveConnectorController and AgentController connector endpoints</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QuoteAgentLaunchShell.razor; GoogleCallback.razor</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">/auth/callback/google; connector panel</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">GoogleDriveConnectorController start/callback/status/files; AgentController connectors/handoff</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QuoteEngineSourceTests connector; endpoint tests where present | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QuoteEngine BFF, Google Drive, Auth</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Connector tokens/status/file refs</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Needs OAuth environment smoke</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">GoogleDriveConnectorController.cs; AgentController.cs:180,190</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QE-014</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Workflow artifacts</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">As a customer, I can inspect quote workflow artifacts produced by the agent.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Artifact drawer and workflow artifact surfaces display generated artifacts, selected artifacts, and downloads.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Shell artifacts -&gt; AgentController artifact download -&gt; artifact/storage service</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Artifact drawer/workflow artifacts</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">AgentController artifacts/download</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QuoteAgentEndpointTests artifact download; QuoteEngineSourceTests artifacts | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QuoteEngine BFF, Storage/artifact service</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Artifact records/files</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Needs real artifact visual browser pass</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QuoteAgentLaunchShell.razor; AgentController.cs:402</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QE-015</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Artifact feedback</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">As a customer, I can give feedback on generated previews/artifacts.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Inline viewer feedback posts sentiment/text feedback and reflects memory observation status.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Inline feedback UI -&gt; AgentController artifact-feedback -&gt; QuoteAgentService</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Thumb feedback and optional text</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">AgentController POST artifacts/{artifactId}/feedback</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QuoteEngineSourceTests feedback; QuoteAgentEndpointTests feedback | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QuoteEngine BFF, Agent service, Customer memory</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Feedback records/memory observations</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Needs feedback persistence retest</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">AgentController.cs:240; QuoteAgentService.cs</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QE-016</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">3D part viewer</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">As a customer, I can inspect uploaded/generated parts in a 3D viewer.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Part viewer loads GLB/viewer URLs, applies viewer settings, and pushes process/material/runtime state to JS.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QePartViewer -&gt; geometry runtime assets/telemetry -&gt; browser viewer</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QePartViewer.razor; QePartDetailCard.razor</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">3D Model tab, artifact drawer viewer</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">GeometryRuntimeController manifest/assets/telemetry</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QuoteEngineSourceTests viewer/runtime | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QuoteEngine client/BFF, Geometry runtime</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Viewer settings/telemetry</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Needs visual canvas smoke</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QePartViewer.razor; QePartDetailCard.razor; GeometryRuntimeController.cs</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QE-017</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">DFM reporting</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">As a customer, I can review manufacturability checks for FDM, SLA, and CNC.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">DFM tab renders process-specific report types and the agent can apply DFM reports to session state.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QeDfmTab/QePartDetailCard -&gt; AgentController dfm -&gt; SessionStore</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QeDfmTab.razor; QePartDetailCard.razor</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">DFM tab and issue acknowledgement</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">AgentController POST sessions/{sessionId}/dfm; QeDfmDtos</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QuoteEngineSourceTests DFM | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QuoteEngine BFF, Geometry/DFM, SessionStore</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">DFM reports and acknowledgement state</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Needs process-specific fixture coverage</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QeDfmTab.razor; QePartDetailCard.razor; AgentController.cs:221</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QE-018</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Part configuration sidebar</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">As a customer, I can select process, material, color, finish, tolerance, quantity, and options.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Configuration sidebar filters reference data and emits changes for quote estimation.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QePartConfigSidebar -&gt; reference-data/estimate DTOs</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QePartConfigSidebar.razor</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Part configuration controls</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QuoteController reference-data/estimate</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QuoteEngineSourceTests config sidebar | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QuoteEngine client/BFF, Pricing/Material services</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Part configuration state</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Needs keyboard/accessibility check</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QePartConfigSidebar.razor; QuoteController.cs:47,301</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QE-019</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Reference data and currencies</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">As a customer, I can use current manufacturing reference data and currencies.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Reference endpoints expose processes/materials/finishes/tolerances/currency data used by workspace controls.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Workspace/client -&gt; quote/v1/reference-data and quote/v1/reference-data/currencies</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QuoteEngineApiClient.cs</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Reference-driven controls</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QuoteController reference-data; ReferenceDataController currencies</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QuoteEngineApiClientTests | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QuoteEngine BFF, Material/Pricing/Reference data</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Read-only reference data</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Needs stale-cache behavior check</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QuoteController.cs:47; ReferenceDataController.cs:10-16; QuoteEngineApiClient.cs</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QE-020</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Estimate</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">As a customer, I can request a quote estimate for configured parts.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Estimate endpoint prices configured parts and returns lead-time/total data for the summary/actions.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Workspace/summary -&gt; QuoteController estimate -&gt; Pricing service</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QuoteWorkspace.razor; QeQuoteSummaryBar.razor</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Estimate action</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Pricing/QuoteEngine tests | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QuoteEngine BFF, PricingService</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Needs current pricing acceptance checks</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QuoteController.cs:301; QeQuoteSummaryBar.razor</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QE-021</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Draft project</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">As a customer, I can persist configured parts into a project draft.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Projects/draft endpoint creates or updates draft project data for the session/customer.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Workspace -&gt; QuoteController projects/draft -&gt; project/quote service</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Project draft action</x:t>
@@ -5057,7 +5021,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdac1550edeab47be"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4e50346a62624c9d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8473,7 +8437,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3e927a3a23d94da5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rac7c35f8c1ea4ab2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8878,7 +8842,7 @@
         <x:v>GET quote/v1/agent/sessions/{sessionId}; GET quote/v1/agent/sessions/{sessionId}/messages resolves the mapped chatbot conversation, filters customer-safe roles, strips injected user-turn context, and returns NotFound when no accessible mapping exists.</x:v>
       </x:c>
       <x:c r="P6" s="3" t="str">
-        <x:v>2026-06-24: dotnet test Maliev.QuoteEngine.slnx --filter "FullyQualifiedName~QuoteAgentEndpointTests.Agent_message_history_uses_mapped_chatbot_session_after_auth_return|FullyQualifiedName~QuoteAgentEndpointTests.Agent_message_history_uses_persisted_mapping_when_session_store_is_cold|FullyQualifiedName~QuoteAgentEndpointTests.Agent_message_history_restores_signed_in_customer_mapping_after_auth_return|FullyQualifiedName~QuoteAgentEndpointTests.Agent_message_history_denies_signed_in_customer_for_another_customers_session|FullyQualifiedName~QuoteAgentEndpointTests.Agent_message_history_strips_injected_session_context_from_persisted_user_turns|FullyQualifiedName~QuoteAgentEndpointTests.Agent_message_history_keeps_legacy_user_content_unmodified_when_no_context_marker_present|FullyQualifiedName~QuoteEngineSourceTests.QuoteAgentLaunchShell_auth_completion_reloads_active_session_and_hydrates_messages|FullyQualifiedName~QuoteEngineSourceTests.QuoteAgentLaunchShell_has_monochrome_chatgpt_like_contract" --verbosity minimal passed 8/8.</x:v>
+        <x:v>2026-06-24: dotnet test Maliev.QuoteEngine.slnx --filter "FullyQualifiedName~QuoteAgentEndpointTests.Agent_message_history_uses_mapped_chatbot_session_after_auth_return|FullyQualifiedName~QuoteAgentEndpointTests.Agent_message_history_uses_persisted_mapping_when_session_store_is_cold|FullyQualifiedName~QuoteAgentEndpointTests.Agent_message_history_restores_signed_in_customer_mapping_after_auth_return|FullyQualifiedName~QuoteAgentEndpointTests.Agent_message_history_denies_signed_in_customer_for_another_customers_session|FullyQualifiedName~QuoteAgentEndpointTests.Agent_message_history_strips_injected_session_context_from_persisted_user_turns|FullyQualifiedName~QuoteAgentEndpointTests.Agent_message_history_keeps_prior_user_content_unmodified_when_no_context_marker_present|FullyQualifiedName~QuoteEngineSourceTests.QuoteAgentLaunchShell_auth_completion_reloads_active_session_and_hydrates_messages|FullyQualifiedName~QuoteEngineSourceTests.QuoteAgentLaunchShell_has_monochrome_chatgpt_like_contract" --verbosity minimal passed 8/8.</x:v>
       </x:c>
       <x:c r="Q6" s="3" t="str">
         <x:v>QuoteEngine Client, QuoteEngine BFF, QuoteAgentSessionStore, chatbot conversation service, Auth/session</x:v>
@@ -9157,85 +9121,85 @@
       </x:c>
     </x:row>
     <x:row r="11" ht="93.25" hidden="0">
-      <x:c r="A11" s="3" t="s">
-        <x:v>466</x:v>
-      </x:c>
-      <x:c r="B11" s="3" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C11" s="3" t="s">
-        <x:v>467</x:v>
-      </x:c>
-      <x:c r="D11" s="3" t="s">
-        <x:v>468</x:v>
-      </x:c>
-      <x:c r="E11" s="3" t="s">
-        <x:v>469</x:v>
-      </x:c>
-      <x:c r="F11" s="3" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="G11" s="3" t="s">
-        <x:v>442</x:v>
-      </x:c>
-      <x:c r="H11" s="3" t="s">
-        <x:v>443</x:v>
-      </x:c>
-      <x:c r="I11" s="3" t="s">
-        <x:v>444</x:v>
-      </x:c>
-      <x:c r="J11" s="3" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="K11" s="3" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="L11" s="3" t="s">
-        <x:v>470</x:v>
-      </x:c>
-      <x:c r="M11" s="3" t="s">
-        <x:v>471</x:v>
-      </x:c>
-      <x:c r="N11" s="3" t="s">
-        <x:v>472</x:v>
-      </x:c>
-      <x:c r="O11" s="3" t="s">
-        <x:v>473</x:v>
-      </x:c>
-      <x:c r="P11" s="3" t="s">
-        <x:v>474</x:v>
-      </x:c>
-      <x:c r="Q11" s="3" t="s">
-        <x:v>475</x:v>
-      </x:c>
-      <x:c r="R11" s="3" t="s">
-        <x:v>476</x:v>
-      </x:c>
-      <x:c r="S11" s="3" t="s">
-        <x:v>477</x:v>
-      </x:c>
-      <x:c r="T11" s="3" t="s">
-        <x:v>478</x:v>
-      </x:c>
-      <x:c r="U11" s="3" t="s">
-        <x:v>52</x:v>
+      <x:c r="A11" s="3" t="str">
+        <x:v>QE-010</x:v>
+      </x:c>
+      <x:c r="B11" s="3" t="str">
+        <x:v>Maliev.QuoteEngine</x:v>
+      </x:c>
+      <x:c r="C11" s="3" t="str">
+        <x:v>Web handoff import</x:v>
+      </x:c>
+      <x:c r="D11" s="3" t="str">
+        <x:v>As a customer, I can continue from a public web quote upload into the workspace.</x:v>
+      </x:c>
+      <x:c r="E11" s="3" t="str">
+        <x:v>Customers arriving from Maliev.Web with a signed upload handoff token can import verified web-uploaded files into the active QuoteEngine workspace; invalid or out-of-scope handoffs are rejected, imported parts retain viewer/thumbnail/file metadata, and the agent session is refreshed with imported attachment context.</x:v>
+      </x:c>
+      <x:c r="F11" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G11" s="3" t="str">
+        <x:v>Focused current-state web handoff import tests passed 2026-06-24.</x:v>
+      </x:c>
+      <x:c r="H11" s="3" t="str">
+        <x:v>No behavior error observed in focused QuoteEngine handoff retest; live cross-app browser handoff from Maliev.Web to QuoteEngine still not executed in this slice.</x:v>
+      </x:c>
+      <x:c r="I11" s="3" t="str">
+        <x:v>No app fix applied for QE-010; current code path is covered by focused BFF/source tests.</x:v>
+      </x:c>
+      <x:c r="J11" s="3" t="str">
+        <x:v>Passed 6/6 focused tests: signed web upload handoff import, unsigned handoff rejection, signed out-of-scope storage-path rejection, QuoteWorkspace viewer-field hydration, imported attachment agent registration, and startup loader query-handoff handling.</x:v>
+      </x:c>
+      <x:c r="K11" s="3" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="L11" s="3" t="str">
+        <x:v>Maliev.Web signed handoff token -&gt; QuoteWorkspace ?handoff route sync -&gt; QuoteEngineApiClient ImportHandoffAsync -&gt; QuoteController uploads/handoff -&gt; QuoteUploadHandoffToken/store import -&gt; QuoteWorkspace part hydration and agent attachment registration</x:v>
+      </x:c>
+      <x:c r="M11" s="3" t="str">
+        <x:v>QuoteWorkspace.razor; QuoteEngineApiClient; QuoteController; QuoteUploadHandoffToken; QuoteEngineDtos</x:v>
+      </x:c>
+      <x:c r="N11" s="3" t="str">
+        <x:v>QuoteWorkspace reads SupplyParameterFromQuery handoff, SynchronizeRouteStateAsync calls ImportHandoffAsync, clears retained browser files, hydrates imported parts with viewer metadata, selects the first part, recalculates, and registers imported attachments with the agent shell.</x:v>
+      </x:c>
+      <x:c r="O11" s="3" t="str">
+        <x:v>POST quote/v1/uploads/handoff requires a signed handoff token, rejects invalid tokens, verifies storage paths belong to the web quote session, resolves optional customer id, and returns QuoteUploadHandoffResponse parts with viewerGlbUrl, viewerStoragePath, viewerFileExtension, thumbnailUrl, contentType, and fileSizeBytes.</x:v>
+      </x:c>
+      <x:c r="P11" s="3" t="str">
+        <x:v>2026-06-24: dotnet test Maliev.QuoteEngine.slnx --filter "FullyQualifiedName~QuoteEngineEndpointTests.UploadHandoff_imports_web_uploaded_files_into_active_workspace|FullyQualifiedName~QuoteEngineEndpointTests.UploadHandoff_rejects_unsigned_web_uploaded_files|FullyQualifiedName~QuoteEngineEndpointTests.UploadHandoff_rejects_signed_storage_paths_outside_web_quote_session|FullyQualifiedName~QuoteEngineSourceTests.QuoteWorkspace_imports_handoff_viewer_fields_for_canvas_rendering|FullyQualifiedName~QuoteEngineSourceTests.QuoteWorkspace_registers_web_handoff_uploads_with_agent_shell|FullyQualifiedName~QuoteEngineSourceTests.Startup_loader_tells_make_studio_story_with_progress_contract" --verbosity minimal passed 6/6.</x:v>
+      </x:c>
+      <x:c r="Q11" s="3" t="str">
+        <x:v>Maliev.Web upload handoff producer, QuoteEngine Client, QuoteEngine BFF, handoff token verifier, prototype workspace store, agent attachment registration</x:v>
+      </x:c>
+      <x:c r="R11" s="3" t="str">
+        <x:v>Verified handoff token, quote session id, imported part view models, viewer and thumbnail metadata, agent attachment state, workspace selected part and recalculated estimate state</x:v>
+      </x:c>
+      <x:c r="S11" s="3" t="str">
+        <x:v>Needs live cross-app browser retest from Maliev.Web upload handoff into a running QuoteEngine host.</x:v>
+      </x:c>
+      <x:c r="T11" s="3" t="str">
+        <x:v>Maliev.QuoteEngine.Client/Pages/QuoteWorkspace.razor:131,364,718,752,771; Maliev.QuoteEngine.Client/Services/QuoteEngineApiClient.cs:78; Maliev.QuoteEngine.Bff/Controllers/QuoteController.cs:235; Maliev.QuoteEngine.Shared/Quotes/QuoteEngineDtos.cs:95,153; Maliev.QuoteEngine.Tests/QuoteEngineEndpointTests.cs:2181,2237,2263; Maliev.QuoteEngine.Tests/QuoteEngineSourceTests.cs:2292,2310,2916</x:v>
+      </x:c>
+      <x:c r="U11" s="3" t="str">
+        <x:v>2026-06-24</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="107.25" hidden="0">
       <x:c r="A12" s="3" t="s">
-        <x:v>479</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="B12" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C12" s="3" t="s">
-        <x:v>480</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="D12" s="3" t="s">
-        <x:v>481</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="E12" s="3" t="s">
-        <x:v>482</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="F12" s="3" t="s">
         <x:v>37</x:v>
@@ -9256,31 +9220,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L12" s="3" t="s">
-        <x:v>483</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="M12" s="3" t="s">
         <x:v>446</x:v>
       </x:c>
       <x:c r="N12" s="3" t="s">
-        <x:v>484</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="O12" s="3" t="s">
-        <x:v>485</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="P12" s="3" t="s">
-        <x:v>486</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="Q12" s="3" t="s">
-        <x:v>487</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="R12" s="3" t="s">
-        <x:v>488</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="S12" s="3" t="s">
-        <x:v>489</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="T12" s="3" t="s">
-        <x:v>490</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="U12" s="3" t="s">
         <x:v>52</x:v>
@@ -9288,19 +9252,19 @@
     </x:row>
     <x:row r="13" ht="93.25" hidden="0">
       <x:c r="A13" s="3" t="s">
-        <x:v>491</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="B13" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C13" s="3" t="s">
-        <x:v>492</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="D13" s="3" t="s">
-        <x:v>493</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="E13" s="3" t="s">
-        <x:v>494</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="F13" s="3" t="s">
         <x:v>37</x:v>
@@ -9321,31 +9285,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L13" s="3" t="s">
-        <x:v>495</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="M13" s="3" t="s">
         <x:v>446</x:v>
       </x:c>
       <x:c r="N13" s="3" t="s">
-        <x:v>496</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="O13" s="3" t="s">
-        <x:v>497</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="P13" s="3" t="s">
-        <x:v>498</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="Q13" s="3" t="s">
+        <x:v>474</x:v>
+      </x:c>
+      <x:c r="R13" s="3" t="s">
+        <x:v>486</x:v>
+      </x:c>
+      <x:c r="S13" s="3" t="s">
         <x:v>487</x:v>
       </x:c>
-      <x:c r="R13" s="3" t="s">
-        <x:v>499</x:v>
-      </x:c>
-      <x:c r="S13" s="3" t="s">
-        <x:v>500</x:v>
-      </x:c>
       <x:c r="T13" s="3" t="s">
-        <x:v>501</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="U13" s="3" t="s">
         <x:v>52</x:v>
@@ -9353,19 +9317,19 @@
     </x:row>
     <x:row r="14" ht="93.25" hidden="0">
       <x:c r="A14" s="3" t="s">
-        <x:v>502</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="B14" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C14" s="3" t="s">
-        <x:v>503</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="D14" s="3" t="s">
-        <x:v>504</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="E14" s="3" t="s">
-        <x:v>505</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="F14" s="3" t="s">
         <x:v>37</x:v>
@@ -9386,31 +9350,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L14" s="3" t="s">
-        <x:v>506</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="M14" s="3" t="s">
-        <x:v>507</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="N14" s="3" t="s">
-        <x:v>508</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="O14" s="3" t="s">
-        <x:v>509</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="P14" s="3" t="s">
-        <x:v>510</x:v>
+        <x:v>497</x:v>
       </x:c>
       <x:c r="Q14" s="3" t="s">
-        <x:v>511</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="R14" s="3" t="s">
-        <x:v>512</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="S14" s="3" t="s">
-        <x:v>513</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="T14" s="3" t="s">
-        <x:v>514</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="U14" s="3" t="s">
         <x:v>52</x:v>
@@ -9418,19 +9382,19 @@
     </x:row>
     <x:row r="15" ht="107.25" hidden="0">
       <x:c r="A15" s="3" t="s">
-        <x:v>515</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="B15" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C15" s="3" t="s">
-        <x:v>516</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="D15" s="3" t="s">
-        <x:v>517</x:v>
+        <x:v>504</x:v>
       </x:c>
       <x:c r="E15" s="3" t="s">
-        <x:v>518</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="F15" s="3" t="s">
         <x:v>37</x:v>
@@ -9451,31 +9415,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L15" s="3" t="s">
-        <x:v>519</x:v>
+        <x:v>506</x:v>
       </x:c>
       <x:c r="M15" s="3" t="s">
         <x:v>446</x:v>
       </x:c>
       <x:c r="N15" s="3" t="s">
-        <x:v>520</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="O15" s="3" t="s">
-        <x:v>521</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="P15" s="3" t="s">
-        <x:v>522</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="Q15" s="3" t="s">
-        <x:v>523</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="R15" s="3" t="s">
-        <x:v>524</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="S15" s="3" t="s">
-        <x:v>525</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="T15" s="3" t="s">
-        <x:v>526</x:v>
+        <x:v>513</x:v>
       </x:c>
       <x:c r="U15" s="3" t="s">
         <x:v>52</x:v>
@@ -9483,19 +9447,19 @@
     </x:row>
     <x:row r="16" ht="107.25" hidden="0">
       <x:c r="A16" s="3" t="s">
-        <x:v>527</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="B16" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C16" s="3" t="s">
-        <x:v>528</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="D16" s="3" t="s">
-        <x:v>529</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="E16" s="3" t="s">
-        <x:v>530</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="F16" s="3" t="s">
         <x:v>37</x:v>
@@ -9516,31 +9480,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L16" s="3" t="s">
-        <x:v>531</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="M16" s="3" t="s">
         <x:v>446</x:v>
       </x:c>
       <x:c r="N16" s="3" t="s">
-        <x:v>532</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="O16" s="3" t="s">
-        <x:v>533</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="P16" s="3" t="s">
-        <x:v>534</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="Q16" s="3" t="s">
-        <x:v>535</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="R16" s="3" t="s">
-        <x:v>536</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="S16" s="3" t="s">
-        <x:v>537</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="T16" s="3" t="s">
-        <x:v>538</x:v>
+        <x:v>525</x:v>
       </x:c>
       <x:c r="U16" s="3" t="s">
         <x:v>52</x:v>
@@ -9548,19 +9512,19 @@
     </x:row>
     <x:row r="17" ht="93.25" hidden="0">
       <x:c r="A17" s="3" t="s">
-        <x:v>539</x:v>
+        <x:v>526</x:v>
       </x:c>
       <x:c r="B17" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C17" s="3" t="s">
-        <x:v>540</x:v>
+        <x:v>527</x:v>
       </x:c>
       <x:c r="D17" s="3" t="s">
-        <x:v>541</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="E17" s="3" t="s">
-        <x:v>542</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="F17" s="3" t="s">
         <x:v>37</x:v>
@@ -9581,31 +9545,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L17" s="3" t="s">
-        <x:v>543</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="M17" s="3" t="s">
-        <x:v>544</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="N17" s="3" t="s">
-        <x:v>545</x:v>
+        <x:v>532</x:v>
       </x:c>
       <x:c r="O17" s="3" t="s">
-        <x:v>546</x:v>
+        <x:v>533</x:v>
       </x:c>
       <x:c r="P17" s="3" t="s">
-        <x:v>547</x:v>
+        <x:v>534</x:v>
       </x:c>
       <x:c r="Q17" s="3" t="s">
-        <x:v>548</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="R17" s="3" t="s">
-        <x:v>549</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="S17" s="3" t="s">
-        <x:v>550</x:v>
+        <x:v>537</x:v>
       </x:c>
       <x:c r="T17" s="3" t="s">
-        <x:v>551</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="U17" s="3" t="s">
         <x:v>52</x:v>
@@ -9613,19 +9577,19 @@
     </x:row>
     <x:row r="18" ht="93.25" hidden="0">
       <x:c r="A18" s="3" t="s">
-        <x:v>552</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="B18" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C18" s="3" t="s">
-        <x:v>553</x:v>
+        <x:v>540</x:v>
       </x:c>
       <x:c r="D18" s="3" t="s">
-        <x:v>554</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="E18" s="3" t="s">
-        <x:v>555</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="F18" s="3" t="s">
         <x:v>37</x:v>
@@ -9646,31 +9610,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L18" s="3" t="s">
-        <x:v>556</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="M18" s="3" t="s">
-        <x:v>557</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="N18" s="3" t="s">
-        <x:v>558</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="O18" s="3" t="s">
-        <x:v>559</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="P18" s="3" t="s">
-        <x:v>560</x:v>
+        <x:v>547</x:v>
       </x:c>
       <x:c r="Q18" s="3" t="s">
-        <x:v>561</x:v>
+        <x:v>548</x:v>
       </x:c>
       <x:c r="R18" s="3" t="s">
-        <x:v>562</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="S18" s="3" t="s">
-        <x:v>563</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="T18" s="3" t="s">
-        <x:v>564</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="U18" s="3" t="s">
         <x:v>52</x:v>
@@ -9678,19 +9642,19 @@
     </x:row>
     <x:row r="19" ht="93.25" hidden="0">
       <x:c r="A19" s="3" t="s">
-        <x:v>565</x:v>
+        <x:v>552</x:v>
       </x:c>
       <x:c r="B19" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C19" s="3" t="s">
-        <x:v>566</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="D19" s="3" t="s">
-        <x:v>567</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="E19" s="3" t="s">
-        <x:v>568</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="F19" s="3" t="s">
         <x:v>37</x:v>
@@ -9711,31 +9675,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L19" s="3" t="s">
-        <x:v>569</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="M19" s="3" t="s">
-        <x:v>570</x:v>
+        <x:v>557</x:v>
       </x:c>
       <x:c r="N19" s="3" t="s">
-        <x:v>571</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="O19" s="3" t="s">
-        <x:v>572</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="P19" s="3" t="s">
-        <x:v>573</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="Q19" s="3" t="s">
-        <x:v>574</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="R19" s="3" t="s">
-        <x:v>575</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="S19" s="3" t="s">
-        <x:v>576</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="T19" s="3" t="s">
-        <x:v>577</x:v>
+        <x:v>564</x:v>
       </x:c>
       <x:c r="U19" s="3" t="s">
         <x:v>52</x:v>
@@ -9743,19 +9707,19 @@
     </x:row>
     <x:row r="20" ht="79.25" hidden="0">
       <x:c r="A20" s="3" t="s">
-        <x:v>578</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="B20" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C20" s="3" t="s">
-        <x:v>579</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="D20" s="3" t="s">
-        <x:v>580</x:v>
+        <x:v>567</x:v>
       </x:c>
       <x:c r="E20" s="3" t="s">
-        <x:v>581</x:v>
+        <x:v>568</x:v>
       </x:c>
       <x:c r="F20" s="3" t="s">
         <x:v>37</x:v>
@@ -9776,31 +9740,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L20" s="3" t="s">
-        <x:v>582</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="M20" s="3" t="s">
-        <x:v>583</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="N20" s="3" t="s">
-        <x:v>584</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="O20" s="3" t="s">
-        <x:v>585</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="P20" s="3" t="s">
-        <x:v>586</x:v>
+        <x:v>573</x:v>
       </x:c>
       <x:c r="Q20" s="3" t="s">
-        <x:v>587</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="R20" s="3" t="s">
-        <x:v>588</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="S20" s="3" t="s">
-        <x:v>589</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="T20" s="3" t="s">
-        <x:v>590</x:v>
+        <x:v>577</x:v>
       </x:c>
       <x:c r="U20" s="3" t="s">
         <x:v>52</x:v>
@@ -9808,19 +9772,19 @@
     </x:row>
     <x:row r="21" ht="79.25" hidden="0">
       <x:c r="A21" s="3" t="s">
-        <x:v>591</x:v>
+        <x:v>578</x:v>
       </x:c>
       <x:c r="B21" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C21" s="3" t="s">
-        <x:v>592</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="D21" s="3" t="s">
-        <x:v>593</x:v>
+        <x:v>580</x:v>
       </x:c>
       <x:c r="E21" s="3" t="s">
-        <x:v>594</x:v>
+        <x:v>581</x:v>
       </x:c>
       <x:c r="F21" s="3" t="s">
         <x:v>37</x:v>
@@ -9841,31 +9805,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L21" s="3" t="s">
-        <x:v>595</x:v>
+        <x:v>582</x:v>
       </x:c>
       <x:c r="M21" s="3" t="s">
-        <x:v>596</x:v>
+        <x:v>583</x:v>
       </x:c>
       <x:c r="N21" s="3" t="s">
-        <x:v>597</x:v>
+        <x:v>584</x:v>
       </x:c>
       <x:c r="O21" s="3" t="s">
         <x:v>218</x:v>
       </x:c>
       <x:c r="P21" s="3" t="s">
-        <x:v>598</x:v>
+        <x:v>585</x:v>
       </x:c>
       <x:c r="Q21" s="3" t="s">
-        <x:v>599</x:v>
+        <x:v>586</x:v>
       </x:c>
       <x:c r="R21" s="3" t="s">
         <x:v>221</x:v>
       </x:c>
       <x:c r="S21" s="3" t="s">
-        <x:v>600</x:v>
+        <x:v>587</x:v>
       </x:c>
       <x:c r="T21" s="3" t="s">
-        <x:v>601</x:v>
+        <x:v>588</x:v>
       </x:c>
       <x:c r="U21" s="3" t="s">
         <x:v>52</x:v>
@@ -9873,19 +9837,19 @@
     </x:row>
     <x:row r="22" ht="93.25" hidden="0">
       <x:c r="A22" s="3" t="s">
-        <x:v>602</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="B22" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C22" s="3" t="s">
-        <x:v>603</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="D22" s="3" t="s">
-        <x:v>604</x:v>
+        <x:v>591</x:v>
       </x:c>
       <x:c r="E22" s="3" t="s">
-        <x:v>605</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="F22" s="3" t="s">
         <x:v>37</x:v>
@@ -9906,31 +9870,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L22" s="3" t="s">
-        <x:v>606</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="M22" s="3" t="s">
-        <x:v>471</x:v>
+        <x:v>594</x:v>
       </x:c>
       <x:c r="N22" s="3" t="s">
-        <x:v>607</x:v>
+        <x:v>595</x:v>
       </x:c>
       <x:c r="O22" s="3" t="s">
-        <x:v>608</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="P22" s="3" t="s">
-        <x:v>609</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="Q22" s="3" t="s">
-        <x:v>610</x:v>
+        <x:v>598</x:v>
       </x:c>
       <x:c r="R22" s="3" t="s">
-        <x:v>611</x:v>
+        <x:v>599</x:v>
       </x:c>
       <x:c r="S22" s="3" t="s">
-        <x:v>612</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="T22" s="3" t="s">
-        <x:v>613</x:v>
+        <x:v>601</x:v>
       </x:c>
       <x:c r="U22" s="3" t="s">
         <x:v>52</x:v>
@@ -9938,19 +9902,19 @@
     </x:row>
     <x:row r="23" ht="93.25" hidden="0">
       <x:c r="A23" s="3" t="s">
-        <x:v>614</x:v>
+        <x:v>602</x:v>
       </x:c>
       <x:c r="B23" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C23" s="3" t="s">
-        <x:v>615</x:v>
+        <x:v>603</x:v>
       </x:c>
       <x:c r="D23" s="3" t="s">
-        <x:v>616</x:v>
+        <x:v>604</x:v>
       </x:c>
       <x:c r="E23" s="3" t="s">
-        <x:v>617</x:v>
+        <x:v>605</x:v>
       </x:c>
       <x:c r="F23" s="3" t="s">
         <x:v>37</x:v>
@@ -9971,31 +9935,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L23" s="3" t="s">
-        <x:v>618</x:v>
+        <x:v>606</x:v>
       </x:c>
       <x:c r="M23" s="3" t="s">
-        <x:v>619</x:v>
+        <x:v>607</x:v>
       </x:c>
       <x:c r="N23" s="3" t="s">
-        <x:v>620</x:v>
+        <x:v>608</x:v>
       </x:c>
       <x:c r="O23" s="3" t="s">
-        <x:v>621</x:v>
+        <x:v>609</x:v>
       </x:c>
       <x:c r="P23" s="3" t="s">
-        <x:v>622</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="Q23" s="3" t="s">
-        <x:v>623</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="R23" s="3" t="s">
-        <x:v>624</x:v>
+        <x:v>612</x:v>
       </x:c>
       <x:c r="S23" s="3" t="s">
-        <x:v>625</x:v>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="T23" s="3" t="s">
-        <x:v>626</x:v>
+        <x:v>614</x:v>
       </x:c>
       <x:c r="U23" s="3" t="s">
         <x:v>52</x:v>
@@ -10003,19 +9967,19 @@
     </x:row>
     <x:row r="24" ht="79.25" hidden="0">
       <x:c r="A24" s="3" t="s">
-        <x:v>627</x:v>
+        <x:v>615</x:v>
       </x:c>
       <x:c r="B24" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C24" s="3" t="s">
-        <x:v>628</x:v>
+        <x:v>616</x:v>
       </x:c>
       <x:c r="D24" s="3" t="s">
-        <x:v>629</x:v>
+        <x:v>617</x:v>
       </x:c>
       <x:c r="E24" s="3" t="s">
-        <x:v>630</x:v>
+        <x:v>618</x:v>
       </x:c>
       <x:c r="F24" s="3" t="s">
         <x:v>37</x:v>
@@ -10036,31 +10000,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L24" s="3" t="s">
-        <x:v>631</x:v>
+        <x:v>619</x:v>
       </x:c>
       <x:c r="M24" s="3" t="s">
-        <x:v>596</x:v>
+        <x:v>583</x:v>
       </x:c>
       <x:c r="N24" s="3" t="s">
-        <x:v>632</x:v>
+        <x:v>620</x:v>
       </x:c>
       <x:c r="O24" s="3" t="s">
-        <x:v>633</x:v>
+        <x:v>621</x:v>
       </x:c>
       <x:c r="P24" s="3" t="s">
-        <x:v>634</x:v>
+        <x:v>622</x:v>
       </x:c>
       <x:c r="Q24" s="3" t="s">
-        <x:v>635</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="R24" s="3" t="s">
-        <x:v>636</x:v>
+        <x:v>624</x:v>
       </x:c>
       <x:c r="S24" s="3" t="s">
-        <x:v>637</x:v>
+        <x:v>625</x:v>
       </x:c>
       <x:c r="T24" s="3" t="s">
-        <x:v>638</x:v>
+        <x:v>626</x:v>
       </x:c>
       <x:c r="U24" s="3" t="s">
         <x:v>52</x:v>
@@ -10068,19 +10032,19 @@
     </x:row>
     <x:row r="25" ht="79.25" hidden="0">
       <x:c r="A25" s="3" t="s">
-        <x:v>639</x:v>
+        <x:v>627</x:v>
       </x:c>
       <x:c r="B25" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C25" s="3" t="s">
-        <x:v>640</x:v>
+        <x:v>628</x:v>
       </x:c>
       <x:c r="D25" s="3" t="s">
-        <x:v>641</x:v>
+        <x:v>629</x:v>
       </x:c>
       <x:c r="E25" s="3" t="s">
-        <x:v>642</x:v>
+        <x:v>630</x:v>
       </x:c>
       <x:c r="F25" s="3" t="s">
         <x:v>37</x:v>
@@ -10101,31 +10065,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L25" s="3" t="s">
-        <x:v>643</x:v>
+        <x:v>631</x:v>
       </x:c>
       <x:c r="M25" s="3" t="s">
-        <x:v>596</x:v>
+        <x:v>583</x:v>
       </x:c>
       <x:c r="N25" s="3" t="s">
-        <x:v>644</x:v>
+        <x:v>632</x:v>
       </x:c>
       <x:c r="O25" s="3" t="s">
-        <x:v>645</x:v>
+        <x:v>633</x:v>
       </x:c>
       <x:c r="P25" s="3" t="s">
-        <x:v>646</x:v>
+        <x:v>634</x:v>
       </x:c>
       <x:c r="Q25" s="3" t="s">
-        <x:v>647</x:v>
+        <x:v>635</x:v>
       </x:c>
       <x:c r="R25" s="3" t="s">
-        <x:v>648</x:v>
+        <x:v>636</x:v>
       </x:c>
       <x:c r="S25" s="3" t="s">
-        <x:v>649</x:v>
+        <x:v>637</x:v>
       </x:c>
       <x:c r="T25" s="3" t="s">
-        <x:v>650</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="U25" s="3" t="s">
         <x:v>52</x:v>
@@ -10133,19 +10097,19 @@
     </x:row>
     <x:row r="26" ht="79.25" hidden="0">
       <x:c r="A26" s="3" t="s">
-        <x:v>651</x:v>
+        <x:v>639</x:v>
       </x:c>
       <x:c r="B26" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C26" s="3" t="s">
-        <x:v>652</x:v>
+        <x:v>640</x:v>
       </x:c>
       <x:c r="D26" s="3" t="s">
-        <x:v>653</x:v>
+        <x:v>641</x:v>
       </x:c>
       <x:c r="E26" s="3" t="s">
-        <x:v>654</x:v>
+        <x:v>642</x:v>
       </x:c>
       <x:c r="F26" s="3" t="s">
         <x:v>37</x:v>
@@ -10166,31 +10130,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L26" s="3" t="s">
-        <x:v>655</x:v>
+        <x:v>643</x:v>
       </x:c>
       <x:c r="M26" s="3" t="s">
-        <x:v>656</x:v>
+        <x:v>644</x:v>
       </x:c>
       <x:c r="N26" s="3" t="s">
-        <x:v>657</x:v>
+        <x:v>645</x:v>
       </x:c>
       <x:c r="O26" s="3" t="s">
-        <x:v>658</x:v>
+        <x:v>646</x:v>
       </x:c>
       <x:c r="P26" s="3" t="s">
-        <x:v>659</x:v>
+        <x:v>647</x:v>
       </x:c>
       <x:c r="Q26" s="3" t="s">
-        <x:v>660</x:v>
+        <x:v>648</x:v>
       </x:c>
       <x:c r="R26" s="3" t="s">
-        <x:v>661</x:v>
+        <x:v>649</x:v>
       </x:c>
       <x:c r="S26" s="3" t="s">
-        <x:v>662</x:v>
+        <x:v>650</x:v>
       </x:c>
       <x:c r="T26" s="3" t="s">
-        <x:v>663</x:v>
+        <x:v>651</x:v>
       </x:c>
       <x:c r="U26" s="3" t="s">
         <x:v>52</x:v>
@@ -10198,19 +10162,19 @@
     </x:row>
     <x:row r="27" ht="79.25" hidden="0">
       <x:c r="A27" s="3" t="s">
-        <x:v>664</x:v>
+        <x:v>652</x:v>
       </x:c>
       <x:c r="B27" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C27" s="3" t="s">
-        <x:v>665</x:v>
+        <x:v>653</x:v>
       </x:c>
       <x:c r="D27" s="3" t="s">
-        <x:v>666</x:v>
+        <x:v>654</x:v>
       </x:c>
       <x:c r="E27" s="3" t="s">
-        <x:v>667</x:v>
+        <x:v>655</x:v>
       </x:c>
       <x:c r="F27" s="3" t="s">
         <x:v>37</x:v>
@@ -10231,31 +10195,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L27" s="3" t="s">
-        <x:v>668</x:v>
+        <x:v>656</x:v>
       </x:c>
       <x:c r="M27" s="3" t="s">
-        <x:v>669</x:v>
+        <x:v>657</x:v>
       </x:c>
       <x:c r="N27" s="3" t="s">
-        <x:v>670</x:v>
+        <x:v>658</x:v>
       </x:c>
       <x:c r="O27" s="3" t="s">
-        <x:v>671</x:v>
+        <x:v>659</x:v>
       </x:c>
       <x:c r="P27" s="3" t="s">
-        <x:v>672</x:v>
+        <x:v>660</x:v>
       </x:c>
       <x:c r="Q27" s="3" t="s">
-        <x:v>673</x:v>
+        <x:v>661</x:v>
       </x:c>
       <x:c r="R27" s="3" t="s">
-        <x:v>674</x:v>
+        <x:v>662</x:v>
       </x:c>
       <x:c r="S27" s="3" t="s">
-        <x:v>675</x:v>
+        <x:v>663</x:v>
       </x:c>
       <x:c r="T27" s="3" t="s">
-        <x:v>676</x:v>
+        <x:v>664</x:v>
       </x:c>
       <x:c r="U27" s="3" t="s">
         <x:v>52</x:v>
@@ -10263,19 +10227,19 @@
     </x:row>
     <x:row r="28" ht="93.25" hidden="0">
       <x:c r="A28" s="3" t="s">
-        <x:v>677</x:v>
+        <x:v>665</x:v>
       </x:c>
       <x:c r="B28" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C28" s="3" t="s">
-        <x:v>678</x:v>
+        <x:v>666</x:v>
       </x:c>
       <x:c r="D28" s="3" t="s">
-        <x:v>679</x:v>
+        <x:v>667</x:v>
       </x:c>
       <x:c r="E28" s="3" t="s">
-        <x:v>680</x:v>
+        <x:v>668</x:v>
       </x:c>
       <x:c r="F28" s="3" t="s">
         <x:v>37</x:v>
@@ -10296,31 +10260,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L28" s="3" t="s">
-        <x:v>681</x:v>
+        <x:v>669</x:v>
       </x:c>
       <x:c r="M28" s="3" t="s">
-        <x:v>682</x:v>
+        <x:v>670</x:v>
       </x:c>
       <x:c r="N28" s="3" t="s">
-        <x:v>683</x:v>
+        <x:v>671</x:v>
       </x:c>
       <x:c r="O28" s="3" t="s">
-        <x:v>684</x:v>
+        <x:v>672</x:v>
       </x:c>
       <x:c r="P28" s="3" t="s">
-        <x:v>685</x:v>
+        <x:v>673</x:v>
       </x:c>
       <x:c r="Q28" s="3" t="s">
-        <x:v>686</x:v>
+        <x:v>674</x:v>
       </x:c>
       <x:c r="R28" s="3" t="s">
-        <x:v>687</x:v>
+        <x:v>675</x:v>
       </x:c>
       <x:c r="S28" s="3" t="s">
         <x:v>286</x:v>
       </x:c>
       <x:c r="T28" s="3" t="s">
-        <x:v>688</x:v>
+        <x:v>676</x:v>
       </x:c>
       <x:c r="U28" s="3" t="s">
         <x:v>52</x:v>
@@ -10328,19 +10292,19 @@
     </x:row>
     <x:row r="29" ht="93.25" hidden="0">
       <x:c r="A29" s="3" t="s">
-        <x:v>689</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="B29" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C29" s="3" t="s">
-        <x:v>690</x:v>
+        <x:v>678</x:v>
       </x:c>
       <x:c r="D29" s="3" t="s">
-        <x:v>691</x:v>
+        <x:v>679</x:v>
       </x:c>
       <x:c r="E29" s="3" t="s">
-        <x:v>692</x:v>
+        <x:v>680</x:v>
       </x:c>
       <x:c r="F29" s="3" t="s">
         <x:v>37</x:v>
@@ -10361,31 +10325,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="L29" s="3" t="s">
-        <x:v>693</x:v>
+        <x:v>681</x:v>
       </x:c>
       <x:c r="M29" s="3" t="s">
-        <x:v>694</x:v>
+        <x:v>682</x:v>
       </x:c>
       <x:c r="N29" s="3" t="s">
-        <x:v>695</x:v>
+        <x:v>683</x:v>
       </x:c>
       <x:c r="O29" s="3" t="s">
-        <x:v>696</x:v>
+        <x:v>684</x:v>
       </x:c>
       <x:c r="P29" s="3" t="s">
-        <x:v>697</x:v>
+        <x:v>685</x:v>
       </x:c>
       <x:c r="Q29" s="3" t="s">
-        <x:v>698</x:v>
+        <x:v>686</x:v>
       </x:c>
       <x:c r="R29" s="3" t="s">
-        <x:v>699</x:v>
+        <x:v>687</x:v>
       </x:c>
       <x:c r="S29" s="3" t="s">
-        <x:v>700</x:v>
+        <x:v>688</x:v>
       </x:c>
       <x:c r="T29" s="3" t="s">
-        <x:v>701</x:v>
+        <x:v>689</x:v>
       </x:c>
       <x:c r="U29" s="3" t="s">
         <x:v>52</x:v>
@@ -10393,19 +10357,19 @@
     </x:row>
     <x:row r="30" ht="93.25" hidden="0">
       <x:c r="A30" s="3" t="s">
-        <x:v>702</x:v>
+        <x:v>690</x:v>
       </x:c>
       <x:c r="B30" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C30" s="3" t="s">
-        <x:v>703</x:v>
+        <x:v>691</x:v>
       </x:c>
       <x:c r="D30" s="3" t="s">
-        <x:v>704</x:v>
+        <x:v>692</x:v>
       </x:c>
       <x:c r="E30" s="3" t="s">
-        <x:v>705</x:v>
+        <x:v>693</x:v>
       </x:c>
       <x:c r="F30" s="3" t="s">
         <x:v>37</x:v>
@@ -10426,31 +10390,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L30" s="3" t="s">
-        <x:v>706</x:v>
+        <x:v>694</x:v>
       </x:c>
       <x:c r="M30" s="3" t="s">
-        <x:v>707</x:v>
+        <x:v>695</x:v>
       </x:c>
       <x:c r="N30" s="3" t="s">
-        <x:v>708</x:v>
+        <x:v>696</x:v>
       </x:c>
       <x:c r="O30" s="3" t="s">
-        <x:v>709</x:v>
+        <x:v>697</x:v>
       </x:c>
       <x:c r="P30" s="3" t="s">
-        <x:v>710</x:v>
+        <x:v>698</x:v>
       </x:c>
       <x:c r="Q30" s="3" t="s">
-        <x:v>711</x:v>
+        <x:v>699</x:v>
       </x:c>
       <x:c r="R30" s="3" t="s">
-        <x:v>712</x:v>
+        <x:v>700</x:v>
       </x:c>
       <x:c r="S30" s="3" t="s">
-        <x:v>713</x:v>
+        <x:v>701</x:v>
       </x:c>
       <x:c r="T30" s="3" t="s">
-        <x:v>714</x:v>
+        <x:v>702</x:v>
       </x:c>
       <x:c r="U30" s="3" t="s">
         <x:v>52</x:v>
@@ -10458,19 +10422,19 @@
     </x:row>
     <x:row r="31" ht="93.25" hidden="0">
       <x:c r="A31" s="3" t="s">
-        <x:v>715</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="B31" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C31" s="3" t="s">
-        <x:v>716</x:v>
+        <x:v>704</x:v>
       </x:c>
       <x:c r="D31" s="3" t="s">
-        <x:v>717</x:v>
+        <x:v>705</x:v>
       </x:c>
       <x:c r="E31" s="3" t="s">
-        <x:v>718</x:v>
+        <x:v>706</x:v>
       </x:c>
       <x:c r="F31" s="3" t="s">
         <x:v>37</x:v>
@@ -10491,31 +10455,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="L31" s="3" t="s">
-        <x:v>719</x:v>
+        <x:v>707</x:v>
       </x:c>
       <x:c r="M31" s="3" t="s">
-        <x:v>720</x:v>
+        <x:v>708</x:v>
       </x:c>
       <x:c r="N31" s="3" t="s">
-        <x:v>721</x:v>
+        <x:v>709</x:v>
       </x:c>
       <x:c r="O31" s="3" t="s">
-        <x:v>722</x:v>
+        <x:v>710</x:v>
       </x:c>
       <x:c r="P31" s="3" t="s">
-        <x:v>723</x:v>
+        <x:v>711</x:v>
       </x:c>
       <x:c r="Q31" s="3" t="s">
-        <x:v>724</x:v>
+        <x:v>712</x:v>
       </x:c>
       <x:c r="R31" s="3" t="s">
-        <x:v>725</x:v>
+        <x:v>713</x:v>
       </x:c>
       <x:c r="S31" s="3" t="s">
-        <x:v>726</x:v>
+        <x:v>714</x:v>
       </x:c>
       <x:c r="T31" s="3" t="s">
-        <x:v>727</x:v>
+        <x:v>715</x:v>
       </x:c>
       <x:c r="U31" s="3" t="s">
         <x:v>52</x:v>
@@ -10523,19 +10487,19 @@
     </x:row>
     <x:row r="32" ht="93.25" hidden="0">
       <x:c r="A32" s="3" t="s">
-        <x:v>728</x:v>
+        <x:v>716</x:v>
       </x:c>
       <x:c r="B32" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C32" s="3" t="s">
-        <x:v>729</x:v>
+        <x:v>717</x:v>
       </x:c>
       <x:c r="D32" s="3" t="s">
-        <x:v>730</x:v>
+        <x:v>718</x:v>
       </x:c>
       <x:c r="E32" s="3" t="s">
-        <x:v>731</x:v>
+        <x:v>719</x:v>
       </x:c>
       <x:c r="F32" s="3" t="s">
         <x:v>37</x:v>
@@ -10556,31 +10520,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L32" s="3" t="s">
-        <x:v>732</x:v>
+        <x:v>720</x:v>
       </x:c>
       <x:c r="M32" s="3" t="s">
-        <x:v>733</x:v>
+        <x:v>721</x:v>
       </x:c>
       <x:c r="N32" s="3" t="s">
-        <x:v>734</x:v>
+        <x:v>722</x:v>
       </x:c>
       <x:c r="O32" s="3" t="s">
-        <x:v>735</x:v>
+        <x:v>723</x:v>
       </x:c>
       <x:c r="P32" s="3" t="s">
-        <x:v>736</x:v>
+        <x:v>724</x:v>
       </x:c>
       <x:c r="Q32" s="3" t="s">
-        <x:v>737</x:v>
+        <x:v>725</x:v>
       </x:c>
       <x:c r="R32" s="3" t="s">
-        <x:v>738</x:v>
+        <x:v>726</x:v>
       </x:c>
       <x:c r="S32" s="3" t="s">
-        <x:v>739</x:v>
+        <x:v>727</x:v>
       </x:c>
       <x:c r="T32" s="3" t="s">
-        <x:v>740</x:v>
+        <x:v>728</x:v>
       </x:c>
       <x:c r="U32" s="3" t="s">
         <x:v>52</x:v>
@@ -10588,19 +10552,19 @@
     </x:row>
     <x:row r="33" ht="93.25" hidden="0">
       <x:c r="A33" s="3" t="s">
-        <x:v>741</x:v>
+        <x:v>729</x:v>
       </x:c>
       <x:c r="B33" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C33" s="3" t="s">
-        <x:v>742</x:v>
+        <x:v>730</x:v>
       </x:c>
       <x:c r="D33" s="3" t="s">
-        <x:v>743</x:v>
+        <x:v>731</x:v>
       </x:c>
       <x:c r="E33" s="3" t="s">
-        <x:v>744</x:v>
+        <x:v>732</x:v>
       </x:c>
       <x:c r="F33" s="3" t="s">
         <x:v>37</x:v>
@@ -10621,31 +10585,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L33" s="3" t="s">
-        <x:v>745</x:v>
+        <x:v>733</x:v>
       </x:c>
       <x:c r="M33" s="3" t="s">
-        <x:v>746</x:v>
+        <x:v>734</x:v>
       </x:c>
       <x:c r="N33" s="3" t="s">
-        <x:v>747</x:v>
+        <x:v>735</x:v>
       </x:c>
       <x:c r="O33" s="3" t="s">
-        <x:v>748</x:v>
+        <x:v>736</x:v>
       </x:c>
       <x:c r="P33" s="3" t="s">
-        <x:v>749</x:v>
+        <x:v>737</x:v>
       </x:c>
       <x:c r="Q33" s="3" t="s">
-        <x:v>750</x:v>
+        <x:v>738</x:v>
       </x:c>
       <x:c r="R33" s="3" t="s">
-        <x:v>751</x:v>
+        <x:v>739</x:v>
       </x:c>
       <x:c r="S33" s="3" t="s">
-        <x:v>752</x:v>
+        <x:v>740</x:v>
       </x:c>
       <x:c r="T33" s="3" t="s">
-        <x:v>753</x:v>
+        <x:v>741</x:v>
       </x:c>
       <x:c r="U33" s="3" t="s">
         <x:v>52</x:v>
@@ -10653,7 +10617,7 @@
     </x:row>
     <x:row r="34" ht="93.25" hidden="0">
       <x:c r="A34" s="3" t="s">
-        <x:v>754</x:v>
+        <x:v>742</x:v>
       </x:c>
       <x:c r="B34" s="3" t="s">
         <x:v>8</x:v>
@@ -10662,10 +10626,10 @@
         <x:v>313</x:v>
       </x:c>
       <x:c r="D34" s="3" t="s">
-        <x:v>755</x:v>
+        <x:v>743</x:v>
       </x:c>
       <x:c r="E34" s="3" t="s">
-        <x:v>756</x:v>
+        <x:v>744</x:v>
       </x:c>
       <x:c r="F34" s="3" t="s">
         <x:v>37</x:v>
@@ -10686,31 +10650,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="L34" s="3" t="s">
-        <x:v>757</x:v>
+        <x:v>745</x:v>
       </x:c>
       <x:c r="M34" s="3" t="s">
-        <x:v>758</x:v>
+        <x:v>746</x:v>
       </x:c>
       <x:c r="N34" s="3" t="s">
-        <x:v>759</x:v>
+        <x:v>747</x:v>
       </x:c>
       <x:c r="O34" s="3" t="s">
-        <x:v>760</x:v>
+        <x:v>748</x:v>
       </x:c>
       <x:c r="P34" s="3" t="s">
-        <x:v>761</x:v>
+        <x:v>749</x:v>
       </x:c>
       <x:c r="Q34" s="3" t="s">
-        <x:v>762</x:v>
+        <x:v>750</x:v>
       </x:c>
       <x:c r="R34" s="3" t="s">
-        <x:v>763</x:v>
+        <x:v>751</x:v>
       </x:c>
       <x:c r="S34" s="3" t="s">
         <x:v>323</x:v>
       </x:c>
       <x:c r="T34" s="3" t="s">
-        <x:v>764</x:v>
+        <x:v>752</x:v>
       </x:c>
       <x:c r="U34" s="3" t="s">
         <x:v>52</x:v>
@@ -10718,19 +10682,19 @@
     </x:row>
     <x:row r="35" ht="93.25" hidden="0">
       <x:c r="A35" s="3" t="s">
-        <x:v>765</x:v>
+        <x:v>753</x:v>
       </x:c>
       <x:c r="B35" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C35" s="3" t="s">
-        <x:v>766</x:v>
+        <x:v>754</x:v>
       </x:c>
       <x:c r="D35" s="3" t="s">
-        <x:v>767</x:v>
+        <x:v>755</x:v>
       </x:c>
       <x:c r="E35" s="3" t="s">
-        <x:v>768</x:v>
+        <x:v>756</x:v>
       </x:c>
       <x:c r="F35" s="3" t="s">
         <x:v>37</x:v>
@@ -10751,31 +10715,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L35" s="3" t="s">
-        <x:v>769</x:v>
+        <x:v>757</x:v>
       </x:c>
       <x:c r="M35" s="3" t="s">
-        <x:v>770</x:v>
+        <x:v>758</x:v>
       </x:c>
       <x:c r="N35" s="3" t="s">
-        <x:v>771</x:v>
+        <x:v>759</x:v>
       </x:c>
       <x:c r="O35" s="3" t="s">
-        <x:v>546</x:v>
+        <x:v>533</x:v>
       </x:c>
       <x:c r="P35" s="3" t="s">
-        <x:v>772</x:v>
+        <x:v>760</x:v>
       </x:c>
       <x:c r="Q35" s="3" t="s">
-        <x:v>773</x:v>
+        <x:v>761</x:v>
       </x:c>
       <x:c r="R35" s="3" t="s">
-        <x:v>774</x:v>
+        <x:v>762</x:v>
       </x:c>
       <x:c r="S35" s="3" t="s">
-        <x:v>775</x:v>
+        <x:v>763</x:v>
       </x:c>
       <x:c r="T35" s="3" t="s">
-        <x:v>776</x:v>
+        <x:v>764</x:v>
       </x:c>
       <x:c r="U35" s="3" t="s">
         <x:v>52</x:v>
@@ -10783,19 +10747,19 @@
     </x:row>
     <x:row r="36" ht="93.25" hidden="0">
       <x:c r="A36" s="3" t="s">
-        <x:v>777</x:v>
+        <x:v>765</x:v>
       </x:c>
       <x:c r="B36" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C36" s="3" t="s">
-        <x:v>778</x:v>
+        <x:v>766</x:v>
       </x:c>
       <x:c r="D36" s="3" t="s">
-        <x:v>779</x:v>
+        <x:v>767</x:v>
       </x:c>
       <x:c r="E36" s="3" t="s">
-        <x:v>780</x:v>
+        <x:v>768</x:v>
       </x:c>
       <x:c r="F36" s="3" t="s">
         <x:v>37</x:v>
@@ -10816,31 +10780,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L36" s="3" t="s">
-        <x:v>781</x:v>
+        <x:v>769</x:v>
       </x:c>
       <x:c r="M36" s="3" t="s">
         <x:v>446</x:v>
       </x:c>
       <x:c r="N36" s="3" t="s">
-        <x:v>782</x:v>
+        <x:v>770</x:v>
       </x:c>
       <x:c r="O36" s="3" t="s">
-        <x:v>783</x:v>
+        <x:v>771</x:v>
       </x:c>
       <x:c r="P36" s="3" t="s">
-        <x:v>784</x:v>
+        <x:v>772</x:v>
       </x:c>
       <x:c r="Q36" s="3" t="s">
-        <x:v>785</x:v>
+        <x:v>773</x:v>
       </x:c>
       <x:c r="R36" s="3" t="s">
-        <x:v>786</x:v>
+        <x:v>774</x:v>
       </x:c>
       <x:c r="S36" s="3" t="s">
-        <x:v>787</x:v>
+        <x:v>775</x:v>
       </x:c>
       <x:c r="T36" s="3" t="s">
-        <x:v>788</x:v>
+        <x:v>776</x:v>
       </x:c>
       <x:c r="U36" s="3" t="s">
         <x:v>52</x:v>
@@ -10848,19 +10812,19 @@
     </x:row>
     <x:row r="37" ht="93.25" hidden="0">
       <x:c r="A37" s="3" t="s">
-        <x:v>789</x:v>
+        <x:v>777</x:v>
       </x:c>
       <x:c r="B37" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C37" s="3" t="s">
-        <x:v>790</x:v>
+        <x:v>778</x:v>
       </x:c>
       <x:c r="D37" s="3" t="s">
-        <x:v>791</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="E37" s="3" t="s">
-        <x:v>792</x:v>
+        <x:v>780</x:v>
       </x:c>
       <x:c r="F37" s="3" t="s">
         <x:v>37</x:v>
@@ -10881,31 +10845,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L37" s="3" t="s">
-        <x:v>793</x:v>
+        <x:v>781</x:v>
       </x:c>
       <x:c r="M37" s="3" t="s">
-        <x:v>794</x:v>
+        <x:v>782</x:v>
       </x:c>
       <x:c r="N37" s="3" t="s">
-        <x:v>795</x:v>
+        <x:v>783</x:v>
       </x:c>
       <x:c r="O37" s="3" t="s">
-        <x:v>796</x:v>
+        <x:v>784</x:v>
       </x:c>
       <x:c r="P37" s="3" t="s">
-        <x:v>797</x:v>
+        <x:v>785</x:v>
       </x:c>
       <x:c r="Q37" s="3" t="s">
-        <x:v>798</x:v>
+        <x:v>786</x:v>
       </x:c>
       <x:c r="R37" s="3" t="s">
-        <x:v>799</x:v>
+        <x:v>787</x:v>
       </x:c>
       <x:c r="S37" s="3" t="s">
-        <x:v>800</x:v>
+        <x:v>788</x:v>
       </x:c>
       <x:c r="T37" s="3" t="s">
-        <x:v>794</x:v>
+        <x:v>782</x:v>
       </x:c>
       <x:c r="U37" s="3" t="s">
         <x:v>52</x:v>
@@ -10913,19 +10877,19 @@
     </x:row>
     <x:row r="38" ht="93.25" hidden="0">
       <x:c r="A38" s="3" t="s">
-        <x:v>801</x:v>
+        <x:v>789</x:v>
       </x:c>
       <x:c r="B38" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C38" s="3" t="s">
-        <x:v>802</x:v>
+        <x:v>790</x:v>
       </x:c>
       <x:c r="D38" s="3" t="s">
-        <x:v>803</x:v>
+        <x:v>791</x:v>
       </x:c>
       <x:c r="E38" s="3" t="s">
-        <x:v>804</x:v>
+        <x:v>792</x:v>
       </x:c>
       <x:c r="F38" s="3" t="s">
         <x:v>37</x:v>
@@ -10946,31 +10910,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L38" s="3" t="s">
-        <x:v>805</x:v>
+        <x:v>793</x:v>
       </x:c>
       <x:c r="M38" s="3" t="s">
-        <x:v>471</x:v>
+        <x:v>594</x:v>
       </x:c>
       <x:c r="N38" s="3" t="s">
-        <x:v>806</x:v>
+        <x:v>794</x:v>
       </x:c>
       <x:c r="O38" s="3" t="s">
-        <x:v>807</x:v>
+        <x:v>795</x:v>
       </x:c>
       <x:c r="P38" s="3" t="s">
-        <x:v>808</x:v>
+        <x:v>796</x:v>
       </x:c>
       <x:c r="Q38" s="3" t="s">
-        <x:v>809</x:v>
+        <x:v>797</x:v>
       </x:c>
       <x:c r="R38" s="3" t="s">
-        <x:v>810</x:v>
+        <x:v>798</x:v>
       </x:c>
       <x:c r="S38" s="3" t="s">
-        <x:v>811</x:v>
+        <x:v>799</x:v>
       </x:c>
       <x:c r="T38" s="3" t="s">
-        <x:v>812</x:v>
+        <x:v>800</x:v>
       </x:c>
       <x:c r="U38" s="3" t="s">
         <x:v>52</x:v>
@@ -10978,19 +10942,19 @@
     </x:row>
     <x:row r="39" ht="93.25" hidden="0">
       <x:c r="A39" s="3" t="s">
-        <x:v>813</x:v>
+        <x:v>801</x:v>
       </x:c>
       <x:c r="B39" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C39" s="3" t="s">
-        <x:v>814</x:v>
+        <x:v>802</x:v>
       </x:c>
       <x:c r="D39" s="3" t="s">
-        <x:v>815</x:v>
+        <x:v>803</x:v>
       </x:c>
       <x:c r="E39" s="3" t="s">
-        <x:v>816</x:v>
+        <x:v>804</x:v>
       </x:c>
       <x:c r="F39" s="3" t="s">
         <x:v>37</x:v>
@@ -11011,31 +10975,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="L39" s="3" t="s">
-        <x:v>817</x:v>
+        <x:v>805</x:v>
       </x:c>
       <x:c r="M39" s="3" t="s">
         <x:v>446</x:v>
       </x:c>
       <x:c r="N39" s="3" t="s">
-        <x:v>818</x:v>
+        <x:v>806</x:v>
       </x:c>
       <x:c r="O39" s="3" t="s">
-        <x:v>819</x:v>
+        <x:v>807</x:v>
       </x:c>
       <x:c r="P39" s="3" t="s">
-        <x:v>820</x:v>
+        <x:v>808</x:v>
       </x:c>
       <x:c r="Q39" s="3" t="s">
-        <x:v>821</x:v>
+        <x:v>809</x:v>
       </x:c>
       <x:c r="R39" s="3" t="s">
-        <x:v>822</x:v>
+        <x:v>810</x:v>
       </x:c>
       <x:c r="S39" s="3" t="s">
-        <x:v>823</x:v>
+        <x:v>811</x:v>
       </x:c>
       <x:c r="T39" s="3" t="s">
-        <x:v>824</x:v>
+        <x:v>812</x:v>
       </x:c>
       <x:c r="U39" s="3" t="s">
         <x:v>52</x:v>
@@ -11044,7 +11008,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R98eb820354214b08"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2039768eee124d4b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/maliev-feature-user-story-status.xlsx
+++ b/docs/maliev-feature-user-story-status.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R55ec781b4d914d84"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="R875633f7b0ee44f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R04ac7350e4234996"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="R83b31bd731da41ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rcbb80bf8ec4943ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="R2ac7781be66846b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="Rdd0d9d6738084e57"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="Rf20af795d9654764"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1411,64 +1411,31 @@
     <x:t xml:space="preserve">AgentController.cs:271; QuoteAgentLaunchShell.razor</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">QE-011</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Agent attachments</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">As a customer, I can attach uploaded files as context before asking the agent.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Agent attachment endpoint registers uploaded files in session state and the shell previews attachments until sent.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Composer attachments -&gt; AgentController attachments -&gt; SessionStore</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Attachment preview and sent attachment display</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">AgentController POST sessions/{sessionId}/attachments</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QuoteAgentEndpointTests attachment; QuoteAgentLaunchShell source tests | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:t>
+    <x:t xml:space="preserve">QE-012</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Sketch attachments</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">As a customer, I can draw or attach a hand sketch for the agent.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Sketch dialog captures sketch data and posts it to the agent sketch endpoint.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Sketch UI -&gt; AgentController sketches -&gt; SessionStore/artifacts</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Hand sketch dialog/tools</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">AgentController POST sessions/{sessionId}/sketches</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">QuoteAgentEndpointTests sketches; source tests sketch disposal | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">QuoteEngine BFF, SessionStore, Storage</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Session attachment records</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Needs attachment resend/removal browser pass</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">AgentController.cs:203; QuoteAgentLaunchShell.razor</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QE-012</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Sketch attachments</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">As a customer, I can draw or attach a hand sketch for the agent.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Sketch dialog captures sketch data and posts it to the agent sketch endpoint.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Sketch UI -&gt; AgentController sketches -&gt; SessionStore/artifacts</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Hand sketch dialog/tools</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">AgentController POST sessions/{sessionId}/sketches</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QuoteAgentEndpointTests sketches; source tests sketch disposal | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Sketch artifact/context</x:t>
@@ -5021,7 +4988,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4e50346a62624c9d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd2f86f9681414ec9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8437,7 +8404,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rac7c35f8c1ea4ab2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2dd5de2b59ae4583"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9186,85 +9153,85 @@
       </x:c>
     </x:row>
     <x:row r="12" ht="107.25" hidden="0">
-      <x:c r="A12" s="3" t="s">
-        <x:v>466</x:v>
-      </x:c>
-      <x:c r="B12" s="3" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C12" s="3" t="s">
-        <x:v>467</x:v>
-      </x:c>
-      <x:c r="D12" s="3" t="s">
-        <x:v>468</x:v>
-      </x:c>
-      <x:c r="E12" s="3" t="s">
-        <x:v>469</x:v>
-      </x:c>
-      <x:c r="F12" s="3" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="G12" s="3" t="s">
-        <x:v>442</x:v>
-      </x:c>
-      <x:c r="H12" s="3" t="s">
-        <x:v>443</x:v>
-      </x:c>
-      <x:c r="I12" s="3" t="s">
-        <x:v>444</x:v>
-      </x:c>
-      <x:c r="J12" s="3" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="K12" s="3" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="L12" s="3" t="s">
-        <x:v>470</x:v>
-      </x:c>
-      <x:c r="M12" s="3" t="s">
-        <x:v>446</x:v>
-      </x:c>
-      <x:c r="N12" s="3" t="s">
-        <x:v>471</x:v>
-      </x:c>
-      <x:c r="O12" s="3" t="s">
-        <x:v>472</x:v>
-      </x:c>
-      <x:c r="P12" s="3" t="s">
-        <x:v>473</x:v>
-      </x:c>
-      <x:c r="Q12" s="3" t="s">
-        <x:v>474</x:v>
-      </x:c>
-      <x:c r="R12" s="3" t="s">
-        <x:v>475</x:v>
-      </x:c>
-      <x:c r="S12" s="3" t="s">
-        <x:v>476</x:v>
-      </x:c>
-      <x:c r="T12" s="3" t="s">
-        <x:v>477</x:v>
-      </x:c>
-      <x:c r="U12" s="3" t="s">
-        <x:v>52</x:v>
+      <x:c r="A12" s="3" t="str">
+        <x:v>QE-011</x:v>
+      </x:c>
+      <x:c r="B12" s="3" t="str">
+        <x:v>Maliev.QuoteEngine</x:v>
+      </x:c>
+      <x:c r="C12" s="3" t="str">
+        <x:v>Agent attachments</x:v>
+      </x:c>
+      <x:c r="D12" s="3" t="str">
+        <x:v>As a customer, I can attach uploaded files as context before asking the agent.</x:v>
+      </x:c>
+      <x:c r="E12" s="3" t="str">
+        <x:v>Customers can keep uploaded CAD, drawing, photo, sketch, and supplemental files as pending composer attachments until they send a message; the shell shows previews, status, overflow, selection, and removal controls, sends attachment metadata with the customer turn, and the BFF registration endpoint updates session attachment state while distinguishing geometry-gating CAD from supplemental files.</x:v>
+      </x:c>
+      <x:c r="F12" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G12" s="3" t="str">
+        <x:v>Focused current-state agent attachment tests passed 2026-06-24.</x:v>
+      </x:c>
+      <x:c r="H12" s="3" t="str">
+        <x:v>No behavior error observed in focused QuoteEngine attachment retest; live browser resend/removal interaction still not executed in this slice.</x:v>
+      </x:c>
+      <x:c r="I12" s="3" t="str">
+        <x:v>No app fix applied for QE-011; current code path is covered by focused BFF/source tests.</x:v>
+      </x:c>
+      <x:c r="J12" s="3" t="str">
+        <x:v>Passed 5/5 focused tests: CAD attachment registration materializes uploaded part state, supplemental registration stays out of geometry gate, composer previews/removes attachments until send, sent user attachments render outside the neutral message bubble, and shell visual contract remains present.</x:v>
+      </x:c>
+      <x:c r="K12" s="3" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="L12" s="3" t="str">
+        <x:v>QuoteWorkspace upload/sketch events -&gt; QuoteAgentLaunchShell pending composer attachments -&gt; QuoteAgentMessageRequest attachment payload -&gt; QuoteEngineApiClient RegisterAgentAttachmentsAsync -&gt; AgentController sessions/{sessionId}/attachments -&gt; QuoteAgentService -&gt; QuoteAgentSessionStore attachment dedupe and geometry-gate classification</x:v>
+      </x:c>
+      <x:c r="M12" s="3" t="str">
+        <x:v>QuoteAgentLaunchShell.razor; QuoteEngineApiClient; AgentController; QuoteAgentService; QuoteAgentSessionStore; QuoteAgentDtos</x:v>
+      </x:c>
+      <x:c r="N12" s="3" t="str">
+        <x:v>QuoteAgentLaunchShell renders qe-agent-composer-attachments with aria-live status, previews up to five pending attachments, shows upload progress and overflow count, allows selecting an uploaded part, removes pending attachments, clears the pending list on send, and renders sent attachments in the message thread.</x:v>
+      </x:c>
+      <x:c r="O12" s="3" t="str">
+        <x:v>POST quote/v1/agent/sessions/{sessionId}/attachments validates QuoteAgentAttachmentRegisterRequest, normalizes message/language, gets or creates the session, stores customer id when available, adds attachments to session state, dedupes by attachment id or upload id, and marks CAD/geometry/3D attachments as satisfying the geometry gate while supplemental files remain non-geometry context.</x:v>
+      </x:c>
+      <x:c r="P12" s="3" t="str">
+        <x:v>2026-06-24: dotnet test Maliev.QuoteEngine.slnx --filter "FullyQualifiedName~QuoteAgentEndpointTests.Agent_attachment_registration_materializes_uploaded_cad_state|FullyQualifiedName~QuoteAgentEndpointTests.Agent_attachment_registration_keeps_supplemental_files_out_of_geometry_gate|FullyQualifiedName~QuoteAgentEndpointTests.Agent_message_with_supplemental_attachment_preserves_geometry_gate|FullyQualifiedName~QuoteEngineSourceTests.QuoteAgentLaunchShell_previews_attachments_until_customer_sends_message|FullyQualifiedName~QuoteEngineSourceTests.QuoteAgentLaunchShell_renders_sent_user_attachments_outside_neutral_message_bubble|FullyQualifiedName~QuoteEngineSourceTests.QuoteAgentLaunchShell_has_monochrome_chatgpt_like_contract" --verbosity minimal passed 5/5.</x:v>
+      </x:c>
+      <x:c r="Q12" s="3" t="str">
+        <x:v>QuoteEngine Client, QuoteEngine BFF, agent session store, upload/session attachment metadata, chatbot send payload</x:v>
+      </x:c>
+      <x:c r="R12" s="3" t="str">
+        <x:v>Pending composer attachment previews, sent message attachment metadata, QuoteAgentAttachmentDto payloads, session attachment records, generated part/artifact state for CAD uploads, geometry gate state</x:v>
+      </x:c>
+      <x:c r="S12" s="3" t="str">
+        <x:v>Needs live browser retest for attachment preview, selection, removal, overflow, resend, and sent-message rendering against a running QuoteEngine host.</x:v>
+      </x:c>
+      <x:c r="T12" s="3" t="str">
+        <x:v>Maliev.QuoteEngine.Client/Components/QuoteAgent/QuoteAgentLaunchShell.razor:1131,2803,2822,4299,5998; Maliev.QuoteEngine.Client/Services/QuoteEngineApiClient.cs:410; Maliev.QuoteEngine.Bff/Controllers/AgentController.cs:203; Maliev.QuoteEngine.Bff/Services/QuoteAgentService.cs:536; Maliev.QuoteEngine.Bff/Services/QuoteAgentSessionStore.cs:31,258; Maliev.QuoteEngine.Shared/Agent/QuoteAgentDtos.cs:82,138; Maliev.QuoteEngine.Tests/QuoteAgentEndpointTests.cs:1602,1698; Maliev.QuoteEngine.Tests/QuoteEngineSourceTests.cs:1933,1996</x:v>
+      </x:c>
+      <x:c r="U12" s="3" t="str">
+        <x:v>2026-06-24</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="93.25" hidden="0">
       <x:c r="A13" s="3" t="s">
-        <x:v>478</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="B13" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C13" s="3" t="s">
-        <x:v>479</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="D13" s="3" t="s">
-        <x:v>480</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="E13" s="3" t="s">
-        <x:v>481</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="F13" s="3" t="s">
         <x:v>37</x:v>
@@ -9285,31 +9252,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L13" s="3" t="s">
-        <x:v>482</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="M13" s="3" t="s">
         <x:v>446</x:v>
       </x:c>
       <x:c r="N13" s="3" t="s">
-        <x:v>483</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="O13" s="3" t="s">
-        <x:v>484</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="P13" s="3" t="s">
-        <x:v>485</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="Q13" s="3" t="s">
         <x:v>474</x:v>
       </x:c>
       <x:c r="R13" s="3" t="s">
-        <x:v>486</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="S13" s="3" t="s">
-        <x:v>487</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="T13" s="3" t="s">
-        <x:v>488</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="U13" s="3" t="s">
         <x:v>52</x:v>
@@ -9317,19 +9284,19 @@
     </x:row>
     <x:row r="14" ht="93.25" hidden="0">
       <x:c r="A14" s="3" t="s">
-        <x:v>489</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="B14" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C14" s="3" t="s">
-        <x:v>490</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="D14" s="3" t="s">
-        <x:v>491</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="E14" s="3" t="s">
-        <x:v>492</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="F14" s="3" t="s">
         <x:v>37</x:v>
@@ -9350,31 +9317,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L14" s="3" t="s">
-        <x:v>493</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="M14" s="3" t="s">
-        <x:v>494</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="N14" s="3" t="s">
-        <x:v>495</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="O14" s="3" t="s">
-        <x:v>496</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="P14" s="3" t="s">
-        <x:v>497</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="Q14" s="3" t="s">
-        <x:v>498</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="R14" s="3" t="s">
-        <x:v>499</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="S14" s="3" t="s">
-        <x:v>500</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="T14" s="3" t="s">
-        <x:v>501</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="U14" s="3" t="s">
         <x:v>52</x:v>
@@ -9382,19 +9349,19 @@
     </x:row>
     <x:row r="15" ht="107.25" hidden="0">
       <x:c r="A15" s="3" t="s">
-        <x:v>502</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="B15" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C15" s="3" t="s">
-        <x:v>503</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="D15" s="3" t="s">
-        <x:v>504</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="E15" s="3" t="s">
-        <x:v>505</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="F15" s="3" t="s">
         <x:v>37</x:v>
@@ -9415,31 +9382,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L15" s="3" t="s">
-        <x:v>506</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="M15" s="3" t="s">
         <x:v>446</x:v>
       </x:c>
       <x:c r="N15" s="3" t="s">
-        <x:v>507</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="O15" s="3" t="s">
-        <x:v>508</x:v>
+        <x:v>497</x:v>
       </x:c>
       <x:c r="P15" s="3" t="s">
-        <x:v>509</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="Q15" s="3" t="s">
-        <x:v>510</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="R15" s="3" t="s">
-        <x:v>511</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="S15" s="3" t="s">
-        <x:v>512</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="T15" s="3" t="s">
-        <x:v>513</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="U15" s="3" t="s">
         <x:v>52</x:v>
@@ -9447,19 +9414,19 @@
     </x:row>
     <x:row r="16" ht="107.25" hidden="0">
       <x:c r="A16" s="3" t="s">
-        <x:v>514</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="B16" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C16" s="3" t="s">
-        <x:v>515</x:v>
+        <x:v>504</x:v>
       </x:c>
       <x:c r="D16" s="3" t="s">
-        <x:v>516</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="E16" s="3" t="s">
-        <x:v>517</x:v>
+        <x:v>506</x:v>
       </x:c>
       <x:c r="F16" s="3" t="s">
         <x:v>37</x:v>
@@ -9480,31 +9447,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L16" s="3" t="s">
-        <x:v>518</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="M16" s="3" t="s">
         <x:v>446</x:v>
       </x:c>
       <x:c r="N16" s="3" t="s">
-        <x:v>519</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="O16" s="3" t="s">
-        <x:v>520</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="P16" s="3" t="s">
-        <x:v>521</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="Q16" s="3" t="s">
-        <x:v>522</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="R16" s="3" t="s">
-        <x:v>523</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="S16" s="3" t="s">
-        <x:v>524</x:v>
+        <x:v>513</x:v>
       </x:c>
       <x:c r="T16" s="3" t="s">
-        <x:v>525</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="U16" s="3" t="s">
         <x:v>52</x:v>
@@ -9512,19 +9479,19 @@
     </x:row>
     <x:row r="17" ht="93.25" hidden="0">
       <x:c r="A17" s="3" t="s">
-        <x:v>526</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="B17" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C17" s="3" t="s">
-        <x:v>527</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="D17" s="3" t="s">
-        <x:v>528</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="E17" s="3" t="s">
-        <x:v>529</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="F17" s="3" t="s">
         <x:v>37</x:v>
@@ -9545,31 +9512,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L17" s="3" t="s">
-        <x:v>530</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="M17" s="3" t="s">
-        <x:v>531</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="N17" s="3" t="s">
-        <x:v>532</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="O17" s="3" t="s">
-        <x:v>533</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="P17" s="3" t="s">
-        <x:v>534</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="Q17" s="3" t="s">
-        <x:v>535</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="R17" s="3" t="s">
-        <x:v>536</x:v>
+        <x:v>525</x:v>
       </x:c>
       <x:c r="S17" s="3" t="s">
-        <x:v>537</x:v>
+        <x:v>526</x:v>
       </x:c>
       <x:c r="T17" s="3" t="s">
-        <x:v>538</x:v>
+        <x:v>527</x:v>
       </x:c>
       <x:c r="U17" s="3" t="s">
         <x:v>52</x:v>
@@ -9577,19 +9544,19 @@
     </x:row>
     <x:row r="18" ht="93.25" hidden="0">
       <x:c r="A18" s="3" t="s">
-        <x:v>539</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="B18" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C18" s="3" t="s">
-        <x:v>540</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="D18" s="3" t="s">
-        <x:v>541</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="E18" s="3" t="s">
-        <x:v>542</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="F18" s="3" t="s">
         <x:v>37</x:v>
@@ -9610,31 +9577,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L18" s="3" t="s">
-        <x:v>543</x:v>
+        <x:v>532</x:v>
       </x:c>
       <x:c r="M18" s="3" t="s">
-        <x:v>544</x:v>
+        <x:v>533</x:v>
       </x:c>
       <x:c r="N18" s="3" t="s">
-        <x:v>545</x:v>
+        <x:v>534</x:v>
       </x:c>
       <x:c r="O18" s="3" t="s">
-        <x:v>546</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="P18" s="3" t="s">
-        <x:v>547</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="Q18" s="3" t="s">
-        <x:v>548</x:v>
+        <x:v>537</x:v>
       </x:c>
       <x:c r="R18" s="3" t="s">
-        <x:v>549</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="S18" s="3" t="s">
-        <x:v>550</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="T18" s="3" t="s">
-        <x:v>551</x:v>
+        <x:v>540</x:v>
       </x:c>
       <x:c r="U18" s="3" t="s">
         <x:v>52</x:v>
@@ -9642,19 +9609,19 @@
     </x:row>
     <x:row r="19" ht="93.25" hidden="0">
       <x:c r="A19" s="3" t="s">
-        <x:v>552</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="B19" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C19" s="3" t="s">
-        <x:v>553</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="D19" s="3" t="s">
-        <x:v>554</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="E19" s="3" t="s">
-        <x:v>555</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="F19" s="3" t="s">
         <x:v>37</x:v>
@@ -9675,31 +9642,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L19" s="3" t="s">
-        <x:v>556</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="M19" s="3" t="s">
-        <x:v>557</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="N19" s="3" t="s">
-        <x:v>558</x:v>
+        <x:v>547</x:v>
       </x:c>
       <x:c r="O19" s="3" t="s">
-        <x:v>559</x:v>
+        <x:v>548</x:v>
       </x:c>
       <x:c r="P19" s="3" t="s">
-        <x:v>560</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="Q19" s="3" t="s">
-        <x:v>561</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="R19" s="3" t="s">
-        <x:v>562</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="S19" s="3" t="s">
-        <x:v>563</x:v>
+        <x:v>552</x:v>
       </x:c>
       <x:c r="T19" s="3" t="s">
-        <x:v>564</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="U19" s="3" t="s">
         <x:v>52</x:v>
@@ -9707,19 +9674,19 @@
     </x:row>
     <x:row r="20" ht="79.25" hidden="0">
       <x:c r="A20" s="3" t="s">
-        <x:v>565</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="B20" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C20" s="3" t="s">
-        <x:v>566</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="D20" s="3" t="s">
-        <x:v>567</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="E20" s="3" t="s">
-        <x:v>568</x:v>
+        <x:v>557</x:v>
       </x:c>
       <x:c r="F20" s="3" t="s">
         <x:v>37</x:v>
@@ -9740,31 +9707,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L20" s="3" t="s">
-        <x:v>569</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="M20" s="3" t="s">
-        <x:v>570</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="N20" s="3" t="s">
-        <x:v>571</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="O20" s="3" t="s">
-        <x:v>572</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="P20" s="3" t="s">
-        <x:v>573</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="Q20" s="3" t="s">
-        <x:v>574</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="R20" s="3" t="s">
-        <x:v>575</x:v>
+        <x:v>564</x:v>
       </x:c>
       <x:c r="S20" s="3" t="s">
-        <x:v>576</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="T20" s="3" t="s">
-        <x:v>577</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="U20" s="3" t="s">
         <x:v>52</x:v>
@@ -9772,19 +9739,19 @@
     </x:row>
     <x:row r="21" ht="79.25" hidden="0">
       <x:c r="A21" s="3" t="s">
-        <x:v>578</x:v>
+        <x:v>567</x:v>
       </x:c>
       <x:c r="B21" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C21" s="3" t="s">
-        <x:v>579</x:v>
+        <x:v>568</x:v>
       </x:c>
       <x:c r="D21" s="3" t="s">
-        <x:v>580</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="E21" s="3" t="s">
-        <x:v>581</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="F21" s="3" t="s">
         <x:v>37</x:v>
@@ -9805,31 +9772,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L21" s="3" t="s">
-        <x:v>582</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="M21" s="3" t="s">
-        <x:v>583</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="N21" s="3" t="s">
-        <x:v>584</x:v>
+        <x:v>573</x:v>
       </x:c>
       <x:c r="O21" s="3" t="s">
         <x:v>218</x:v>
       </x:c>
       <x:c r="P21" s="3" t="s">
-        <x:v>585</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="Q21" s="3" t="s">
-        <x:v>586</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="R21" s="3" t="s">
         <x:v>221</x:v>
       </x:c>
       <x:c r="S21" s="3" t="s">
-        <x:v>587</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="T21" s="3" t="s">
-        <x:v>588</x:v>
+        <x:v>577</x:v>
       </x:c>
       <x:c r="U21" s="3" t="s">
         <x:v>52</x:v>
@@ -9837,19 +9804,19 @@
     </x:row>
     <x:row r="22" ht="93.25" hidden="0">
       <x:c r="A22" s="3" t="s">
-        <x:v>589</x:v>
+        <x:v>578</x:v>
       </x:c>
       <x:c r="B22" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C22" s="3" t="s">
-        <x:v>590</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="D22" s="3" t="s">
-        <x:v>591</x:v>
+        <x:v>580</x:v>
       </x:c>
       <x:c r="E22" s="3" t="s">
-        <x:v>592</x:v>
+        <x:v>581</x:v>
       </x:c>
       <x:c r="F22" s="3" t="s">
         <x:v>37</x:v>
@@ -9870,31 +9837,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L22" s="3" t="s">
-        <x:v>593</x:v>
+        <x:v>582</x:v>
       </x:c>
       <x:c r="M22" s="3" t="s">
-        <x:v>594</x:v>
+        <x:v>583</x:v>
       </x:c>
       <x:c r="N22" s="3" t="s">
-        <x:v>595</x:v>
+        <x:v>584</x:v>
       </x:c>
       <x:c r="O22" s="3" t="s">
-        <x:v>596</x:v>
+        <x:v>585</x:v>
       </x:c>
       <x:c r="P22" s="3" t="s">
-        <x:v>597</x:v>
+        <x:v>586</x:v>
       </x:c>
       <x:c r="Q22" s="3" t="s">
-        <x:v>598</x:v>
+        <x:v>587</x:v>
       </x:c>
       <x:c r="R22" s="3" t="s">
-        <x:v>599</x:v>
+        <x:v>588</x:v>
       </x:c>
       <x:c r="S22" s="3" t="s">
-        <x:v>600</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="T22" s="3" t="s">
-        <x:v>601</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="U22" s="3" t="s">
         <x:v>52</x:v>
@@ -9902,19 +9869,19 @@
     </x:row>
     <x:row r="23" ht="93.25" hidden="0">
       <x:c r="A23" s="3" t="s">
-        <x:v>602</x:v>
+        <x:v>591</x:v>
       </x:c>
       <x:c r="B23" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C23" s="3" t="s">
-        <x:v>603</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="D23" s="3" t="s">
-        <x:v>604</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="E23" s="3" t="s">
-        <x:v>605</x:v>
+        <x:v>594</x:v>
       </x:c>
       <x:c r="F23" s="3" t="s">
         <x:v>37</x:v>
@@ -9935,31 +9902,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L23" s="3" t="s">
-        <x:v>606</x:v>
+        <x:v>595</x:v>
       </x:c>
       <x:c r="M23" s="3" t="s">
-        <x:v>607</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="N23" s="3" t="s">
-        <x:v>608</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="O23" s="3" t="s">
-        <x:v>609</x:v>
+        <x:v>598</x:v>
       </x:c>
       <x:c r="P23" s="3" t="s">
-        <x:v>610</x:v>
+        <x:v>599</x:v>
       </x:c>
       <x:c r="Q23" s="3" t="s">
-        <x:v>611</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="R23" s="3" t="s">
-        <x:v>612</x:v>
+        <x:v>601</x:v>
       </x:c>
       <x:c r="S23" s="3" t="s">
-        <x:v>613</x:v>
+        <x:v>602</x:v>
       </x:c>
       <x:c r="T23" s="3" t="s">
-        <x:v>614</x:v>
+        <x:v>603</x:v>
       </x:c>
       <x:c r="U23" s="3" t="s">
         <x:v>52</x:v>
@@ -9967,19 +9934,19 @@
     </x:row>
     <x:row r="24" ht="79.25" hidden="0">
       <x:c r="A24" s="3" t="s">
-        <x:v>615</x:v>
+        <x:v>604</x:v>
       </x:c>
       <x:c r="B24" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C24" s="3" t="s">
-        <x:v>616</x:v>
+        <x:v>605</x:v>
       </x:c>
       <x:c r="D24" s="3" t="s">
-        <x:v>617</x:v>
+        <x:v>606</x:v>
       </x:c>
       <x:c r="E24" s="3" t="s">
-        <x:v>618</x:v>
+        <x:v>607</x:v>
       </x:c>
       <x:c r="F24" s="3" t="s">
         <x:v>37</x:v>
@@ -10000,31 +9967,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L24" s="3" t="s">
-        <x:v>619</x:v>
+        <x:v>608</x:v>
       </x:c>
       <x:c r="M24" s="3" t="s">
-        <x:v>583</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="N24" s="3" t="s">
-        <x:v>620</x:v>
+        <x:v>609</x:v>
       </x:c>
       <x:c r="O24" s="3" t="s">
-        <x:v>621</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="P24" s="3" t="s">
-        <x:v>622</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="Q24" s="3" t="s">
-        <x:v>623</x:v>
+        <x:v>612</x:v>
       </x:c>
       <x:c r="R24" s="3" t="s">
-        <x:v>624</x:v>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="S24" s="3" t="s">
-        <x:v>625</x:v>
+        <x:v>614</x:v>
       </x:c>
       <x:c r="T24" s="3" t="s">
-        <x:v>626</x:v>
+        <x:v>615</x:v>
       </x:c>
       <x:c r="U24" s="3" t="s">
         <x:v>52</x:v>
@@ -10032,19 +9999,19 @@
     </x:row>
     <x:row r="25" ht="79.25" hidden="0">
       <x:c r="A25" s="3" t="s">
-        <x:v>627</x:v>
+        <x:v>616</x:v>
       </x:c>
       <x:c r="B25" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C25" s="3" t="s">
-        <x:v>628</x:v>
+        <x:v>617</x:v>
       </x:c>
       <x:c r="D25" s="3" t="s">
-        <x:v>629</x:v>
+        <x:v>618</x:v>
       </x:c>
       <x:c r="E25" s="3" t="s">
-        <x:v>630</x:v>
+        <x:v>619</x:v>
       </x:c>
       <x:c r="F25" s="3" t="s">
         <x:v>37</x:v>
@@ -10065,31 +10032,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L25" s="3" t="s">
-        <x:v>631</x:v>
+        <x:v>620</x:v>
       </x:c>
       <x:c r="M25" s="3" t="s">
-        <x:v>583</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="N25" s="3" t="s">
-        <x:v>632</x:v>
+        <x:v>621</x:v>
       </x:c>
       <x:c r="O25" s="3" t="s">
-        <x:v>633</x:v>
+        <x:v>622</x:v>
       </x:c>
       <x:c r="P25" s="3" t="s">
-        <x:v>634</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="Q25" s="3" t="s">
-        <x:v>635</x:v>
+        <x:v>624</x:v>
       </x:c>
       <x:c r="R25" s="3" t="s">
-        <x:v>636</x:v>
+        <x:v>625</x:v>
       </x:c>
       <x:c r="S25" s="3" t="s">
-        <x:v>637</x:v>
+        <x:v>626</x:v>
       </x:c>
       <x:c r="T25" s="3" t="s">
-        <x:v>638</x:v>
+        <x:v>627</x:v>
       </x:c>
       <x:c r="U25" s="3" t="s">
         <x:v>52</x:v>
@@ -10097,19 +10064,19 @@
     </x:row>
     <x:row r="26" ht="79.25" hidden="0">
       <x:c r="A26" s="3" t="s">
-        <x:v>639</x:v>
+        <x:v>628</x:v>
       </x:c>
       <x:c r="B26" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C26" s="3" t="s">
-        <x:v>640</x:v>
+        <x:v>629</x:v>
       </x:c>
       <x:c r="D26" s="3" t="s">
-        <x:v>641</x:v>
+        <x:v>630</x:v>
       </x:c>
       <x:c r="E26" s="3" t="s">
-        <x:v>642</x:v>
+        <x:v>631</x:v>
       </x:c>
       <x:c r="F26" s="3" t="s">
         <x:v>37</x:v>
@@ -10130,31 +10097,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L26" s="3" t="s">
-        <x:v>643</x:v>
+        <x:v>632</x:v>
       </x:c>
       <x:c r="M26" s="3" t="s">
-        <x:v>644</x:v>
+        <x:v>633</x:v>
       </x:c>
       <x:c r="N26" s="3" t="s">
-        <x:v>645</x:v>
+        <x:v>634</x:v>
       </x:c>
       <x:c r="O26" s="3" t="s">
-        <x:v>646</x:v>
+        <x:v>635</x:v>
       </x:c>
       <x:c r="P26" s="3" t="s">
-        <x:v>647</x:v>
+        <x:v>636</x:v>
       </x:c>
       <x:c r="Q26" s="3" t="s">
-        <x:v>648</x:v>
+        <x:v>637</x:v>
       </x:c>
       <x:c r="R26" s="3" t="s">
-        <x:v>649</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="S26" s="3" t="s">
-        <x:v>650</x:v>
+        <x:v>639</x:v>
       </x:c>
       <x:c r="T26" s="3" t="s">
-        <x:v>651</x:v>
+        <x:v>640</x:v>
       </x:c>
       <x:c r="U26" s="3" t="s">
         <x:v>52</x:v>
@@ -10162,19 +10129,19 @@
     </x:row>
     <x:row r="27" ht="79.25" hidden="0">
       <x:c r="A27" s="3" t="s">
-        <x:v>652</x:v>
+        <x:v>641</x:v>
       </x:c>
       <x:c r="B27" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C27" s="3" t="s">
-        <x:v>653</x:v>
+        <x:v>642</x:v>
       </x:c>
       <x:c r="D27" s="3" t="s">
-        <x:v>654</x:v>
+        <x:v>643</x:v>
       </x:c>
       <x:c r="E27" s="3" t="s">
-        <x:v>655</x:v>
+        <x:v>644</x:v>
       </x:c>
       <x:c r="F27" s="3" t="s">
         <x:v>37</x:v>
@@ -10195,31 +10162,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L27" s="3" t="s">
-        <x:v>656</x:v>
+        <x:v>645</x:v>
       </x:c>
       <x:c r="M27" s="3" t="s">
-        <x:v>657</x:v>
+        <x:v>646</x:v>
       </x:c>
       <x:c r="N27" s="3" t="s">
-        <x:v>658</x:v>
+        <x:v>647</x:v>
       </x:c>
       <x:c r="O27" s="3" t="s">
-        <x:v>659</x:v>
+        <x:v>648</x:v>
       </x:c>
       <x:c r="P27" s="3" t="s">
-        <x:v>660</x:v>
+        <x:v>649</x:v>
       </x:c>
       <x:c r="Q27" s="3" t="s">
-        <x:v>661</x:v>
+        <x:v>650</x:v>
       </x:c>
       <x:c r="R27" s="3" t="s">
-        <x:v>662</x:v>
+        <x:v>651</x:v>
       </x:c>
       <x:c r="S27" s="3" t="s">
-        <x:v>663</x:v>
+        <x:v>652</x:v>
       </x:c>
       <x:c r="T27" s="3" t="s">
-        <x:v>664</x:v>
+        <x:v>653</x:v>
       </x:c>
       <x:c r="U27" s="3" t="s">
         <x:v>52</x:v>
@@ -10227,19 +10194,19 @@
     </x:row>
     <x:row r="28" ht="93.25" hidden="0">
       <x:c r="A28" s="3" t="s">
-        <x:v>665</x:v>
+        <x:v>654</x:v>
       </x:c>
       <x:c r="B28" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C28" s="3" t="s">
-        <x:v>666</x:v>
+        <x:v>655</x:v>
       </x:c>
       <x:c r="D28" s="3" t="s">
-        <x:v>667</x:v>
+        <x:v>656</x:v>
       </x:c>
       <x:c r="E28" s="3" t="s">
-        <x:v>668</x:v>
+        <x:v>657</x:v>
       </x:c>
       <x:c r="F28" s="3" t="s">
         <x:v>37</x:v>
@@ -10260,31 +10227,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L28" s="3" t="s">
-        <x:v>669</x:v>
+        <x:v>658</x:v>
       </x:c>
       <x:c r="M28" s="3" t="s">
-        <x:v>670</x:v>
+        <x:v>659</x:v>
       </x:c>
       <x:c r="N28" s="3" t="s">
-        <x:v>671</x:v>
+        <x:v>660</x:v>
       </x:c>
       <x:c r="O28" s="3" t="s">
-        <x:v>672</x:v>
+        <x:v>661</x:v>
       </x:c>
       <x:c r="P28" s="3" t="s">
-        <x:v>673</x:v>
+        <x:v>662</x:v>
       </x:c>
       <x:c r="Q28" s="3" t="s">
-        <x:v>674</x:v>
+        <x:v>663</x:v>
       </x:c>
       <x:c r="R28" s="3" t="s">
-        <x:v>675</x:v>
+        <x:v>664</x:v>
       </x:c>
       <x:c r="S28" s="3" t="s">
         <x:v>286</x:v>
       </x:c>
       <x:c r="T28" s="3" t="s">
-        <x:v>676</x:v>
+        <x:v>665</x:v>
       </x:c>
       <x:c r="U28" s="3" t="s">
         <x:v>52</x:v>
@@ -10292,19 +10259,19 @@
     </x:row>
     <x:row r="29" ht="93.25" hidden="0">
       <x:c r="A29" s="3" t="s">
-        <x:v>677</x:v>
+        <x:v>666</x:v>
       </x:c>
       <x:c r="B29" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C29" s="3" t="s">
-        <x:v>678</x:v>
+        <x:v>667</x:v>
       </x:c>
       <x:c r="D29" s="3" t="s">
-        <x:v>679</x:v>
+        <x:v>668</x:v>
       </x:c>
       <x:c r="E29" s="3" t="s">
-        <x:v>680</x:v>
+        <x:v>669</x:v>
       </x:c>
       <x:c r="F29" s="3" t="s">
         <x:v>37</x:v>
@@ -10325,31 +10292,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="L29" s="3" t="s">
-        <x:v>681</x:v>
+        <x:v>670</x:v>
       </x:c>
       <x:c r="M29" s="3" t="s">
-        <x:v>682</x:v>
+        <x:v>671</x:v>
       </x:c>
       <x:c r="N29" s="3" t="s">
-        <x:v>683</x:v>
+        <x:v>672</x:v>
       </x:c>
       <x:c r="O29" s="3" t="s">
-        <x:v>684</x:v>
+        <x:v>673</x:v>
       </x:c>
       <x:c r="P29" s="3" t="s">
-        <x:v>685</x:v>
+        <x:v>674</x:v>
       </x:c>
       <x:c r="Q29" s="3" t="s">
-        <x:v>686</x:v>
+        <x:v>675</x:v>
       </x:c>
       <x:c r="R29" s="3" t="s">
-        <x:v>687</x:v>
+        <x:v>676</x:v>
       </x:c>
       <x:c r="S29" s="3" t="s">
-        <x:v>688</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="T29" s="3" t="s">
-        <x:v>689</x:v>
+        <x:v>678</x:v>
       </x:c>
       <x:c r="U29" s="3" t="s">
         <x:v>52</x:v>
@@ -10357,19 +10324,19 @@
     </x:row>
     <x:row r="30" ht="93.25" hidden="0">
       <x:c r="A30" s="3" t="s">
-        <x:v>690</x:v>
+        <x:v>679</x:v>
       </x:c>
       <x:c r="B30" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C30" s="3" t="s">
-        <x:v>691</x:v>
+        <x:v>680</x:v>
       </x:c>
       <x:c r="D30" s="3" t="s">
-        <x:v>692</x:v>
+        <x:v>681</x:v>
       </x:c>
       <x:c r="E30" s="3" t="s">
-        <x:v>693</x:v>
+        <x:v>682</x:v>
       </x:c>
       <x:c r="F30" s="3" t="s">
         <x:v>37</x:v>
@@ -10390,31 +10357,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L30" s="3" t="s">
-        <x:v>694</x:v>
+        <x:v>683</x:v>
       </x:c>
       <x:c r="M30" s="3" t="s">
-        <x:v>695</x:v>
+        <x:v>684</x:v>
       </x:c>
       <x:c r="N30" s="3" t="s">
-        <x:v>696</x:v>
+        <x:v>685</x:v>
       </x:c>
       <x:c r="O30" s="3" t="s">
-        <x:v>697</x:v>
+        <x:v>686</x:v>
       </x:c>
       <x:c r="P30" s="3" t="s">
-        <x:v>698</x:v>
+        <x:v>687</x:v>
       </x:c>
       <x:c r="Q30" s="3" t="s">
-        <x:v>699</x:v>
+        <x:v>688</x:v>
       </x:c>
       <x:c r="R30" s="3" t="s">
-        <x:v>700</x:v>
+        <x:v>689</x:v>
       </x:c>
       <x:c r="S30" s="3" t="s">
-        <x:v>701</x:v>
+        <x:v>690</x:v>
       </x:c>
       <x:c r="T30" s="3" t="s">
-        <x:v>702</x:v>
+        <x:v>691</x:v>
       </x:c>
       <x:c r="U30" s="3" t="s">
         <x:v>52</x:v>
@@ -10422,19 +10389,19 @@
     </x:row>
     <x:row r="31" ht="93.25" hidden="0">
       <x:c r="A31" s="3" t="s">
-        <x:v>703</x:v>
+        <x:v>692</x:v>
       </x:c>
       <x:c r="B31" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C31" s="3" t="s">
-        <x:v>704</x:v>
+        <x:v>693</x:v>
       </x:c>
       <x:c r="D31" s="3" t="s">
-        <x:v>705</x:v>
+        <x:v>694</x:v>
       </x:c>
       <x:c r="E31" s="3" t="s">
-        <x:v>706</x:v>
+        <x:v>695</x:v>
       </x:c>
       <x:c r="F31" s="3" t="s">
         <x:v>37</x:v>
@@ -10455,31 +10422,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="L31" s="3" t="s">
-        <x:v>707</x:v>
+        <x:v>696</x:v>
       </x:c>
       <x:c r="M31" s="3" t="s">
-        <x:v>708</x:v>
+        <x:v>697</x:v>
       </x:c>
       <x:c r="N31" s="3" t="s">
-        <x:v>709</x:v>
+        <x:v>698</x:v>
       </x:c>
       <x:c r="O31" s="3" t="s">
-        <x:v>710</x:v>
+        <x:v>699</x:v>
       </x:c>
       <x:c r="P31" s="3" t="s">
-        <x:v>711</x:v>
+        <x:v>700</x:v>
       </x:c>
       <x:c r="Q31" s="3" t="s">
-        <x:v>712</x:v>
+        <x:v>701</x:v>
       </x:c>
       <x:c r="R31" s="3" t="s">
-        <x:v>713</x:v>
+        <x:v>702</x:v>
       </x:c>
       <x:c r="S31" s="3" t="s">
-        <x:v>714</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="T31" s="3" t="s">
-        <x:v>715</x:v>
+        <x:v>704</x:v>
       </x:c>
       <x:c r="U31" s="3" t="s">
         <x:v>52</x:v>
@@ -10487,19 +10454,19 @@
     </x:row>
     <x:row r="32" ht="93.25" hidden="0">
       <x:c r="A32" s="3" t="s">
-        <x:v>716</x:v>
+        <x:v>705</x:v>
       </x:c>
       <x:c r="B32" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C32" s="3" t="s">
-        <x:v>717</x:v>
+        <x:v>706</x:v>
       </x:c>
       <x:c r="D32" s="3" t="s">
-        <x:v>718</x:v>
+        <x:v>707</x:v>
       </x:c>
       <x:c r="E32" s="3" t="s">
-        <x:v>719</x:v>
+        <x:v>708</x:v>
       </x:c>
       <x:c r="F32" s="3" t="s">
         <x:v>37</x:v>
@@ -10520,31 +10487,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L32" s="3" t="s">
-        <x:v>720</x:v>
+        <x:v>709</x:v>
       </x:c>
       <x:c r="M32" s="3" t="s">
-        <x:v>721</x:v>
+        <x:v>710</x:v>
       </x:c>
       <x:c r="N32" s="3" t="s">
-        <x:v>722</x:v>
+        <x:v>711</x:v>
       </x:c>
       <x:c r="O32" s="3" t="s">
-        <x:v>723</x:v>
+        <x:v>712</x:v>
       </x:c>
       <x:c r="P32" s="3" t="s">
-        <x:v>724</x:v>
+        <x:v>713</x:v>
       </x:c>
       <x:c r="Q32" s="3" t="s">
-        <x:v>725</x:v>
+        <x:v>714</x:v>
       </x:c>
       <x:c r="R32" s="3" t="s">
-        <x:v>726</x:v>
+        <x:v>715</x:v>
       </x:c>
       <x:c r="S32" s="3" t="s">
-        <x:v>727</x:v>
+        <x:v>716</x:v>
       </x:c>
       <x:c r="T32" s="3" t="s">
-        <x:v>728</x:v>
+        <x:v>717</x:v>
       </x:c>
       <x:c r="U32" s="3" t="s">
         <x:v>52</x:v>
@@ -10552,19 +10519,19 @@
     </x:row>
     <x:row r="33" ht="93.25" hidden="0">
       <x:c r="A33" s="3" t="s">
-        <x:v>729</x:v>
+        <x:v>718</x:v>
       </x:c>
       <x:c r="B33" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C33" s="3" t="s">
-        <x:v>730</x:v>
+        <x:v>719</x:v>
       </x:c>
       <x:c r="D33" s="3" t="s">
-        <x:v>731</x:v>
+        <x:v>720</x:v>
       </x:c>
       <x:c r="E33" s="3" t="s">
-        <x:v>732</x:v>
+        <x:v>721</x:v>
       </x:c>
       <x:c r="F33" s="3" t="s">
         <x:v>37</x:v>
@@ -10585,31 +10552,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L33" s="3" t="s">
-        <x:v>733</x:v>
+        <x:v>722</x:v>
       </x:c>
       <x:c r="M33" s="3" t="s">
-        <x:v>734</x:v>
+        <x:v>723</x:v>
       </x:c>
       <x:c r="N33" s="3" t="s">
-        <x:v>735</x:v>
+        <x:v>724</x:v>
       </x:c>
       <x:c r="O33" s="3" t="s">
-        <x:v>736</x:v>
+        <x:v>725</x:v>
       </x:c>
       <x:c r="P33" s="3" t="s">
-        <x:v>737</x:v>
+        <x:v>726</x:v>
       </x:c>
       <x:c r="Q33" s="3" t="s">
-        <x:v>738</x:v>
+        <x:v>727</x:v>
       </x:c>
       <x:c r="R33" s="3" t="s">
-        <x:v>739</x:v>
+        <x:v>728</x:v>
       </x:c>
       <x:c r="S33" s="3" t="s">
-        <x:v>740</x:v>
+        <x:v>729</x:v>
       </x:c>
       <x:c r="T33" s="3" t="s">
-        <x:v>741</x:v>
+        <x:v>730</x:v>
       </x:c>
       <x:c r="U33" s="3" t="s">
         <x:v>52</x:v>
@@ -10617,7 +10584,7 @@
     </x:row>
     <x:row r="34" ht="93.25" hidden="0">
       <x:c r="A34" s="3" t="s">
-        <x:v>742</x:v>
+        <x:v>731</x:v>
       </x:c>
       <x:c r="B34" s="3" t="s">
         <x:v>8</x:v>
@@ -10626,10 +10593,10 @@
         <x:v>313</x:v>
       </x:c>
       <x:c r="D34" s="3" t="s">
-        <x:v>743</x:v>
+        <x:v>732</x:v>
       </x:c>
       <x:c r="E34" s="3" t="s">
-        <x:v>744</x:v>
+        <x:v>733</x:v>
       </x:c>
       <x:c r="F34" s="3" t="s">
         <x:v>37</x:v>
@@ -10650,31 +10617,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="L34" s="3" t="s">
-        <x:v>745</x:v>
+        <x:v>734</x:v>
       </x:c>
       <x:c r="M34" s="3" t="s">
-        <x:v>746</x:v>
+        <x:v>735</x:v>
       </x:c>
       <x:c r="N34" s="3" t="s">
-        <x:v>747</x:v>
+        <x:v>736</x:v>
       </x:c>
       <x:c r="O34" s="3" t="s">
-        <x:v>748</x:v>
+        <x:v>737</x:v>
       </x:c>
       <x:c r="P34" s="3" t="s">
-        <x:v>749</x:v>
+        <x:v>738</x:v>
       </x:c>
       <x:c r="Q34" s="3" t="s">
-        <x:v>750</x:v>
+        <x:v>739</x:v>
       </x:c>
       <x:c r="R34" s="3" t="s">
-        <x:v>751</x:v>
+        <x:v>740</x:v>
       </x:c>
       <x:c r="S34" s="3" t="s">
         <x:v>323</x:v>
       </x:c>
       <x:c r="T34" s="3" t="s">
-        <x:v>752</x:v>
+        <x:v>741</x:v>
       </x:c>
       <x:c r="U34" s="3" t="s">
         <x:v>52</x:v>
@@ -10682,19 +10649,19 @@
     </x:row>
     <x:row r="35" ht="93.25" hidden="0">
       <x:c r="A35" s="3" t="s">
-        <x:v>753</x:v>
+        <x:v>742</x:v>
       </x:c>
       <x:c r="B35" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C35" s="3" t="s">
-        <x:v>754</x:v>
+        <x:v>743</x:v>
       </x:c>
       <x:c r="D35" s="3" t="s">
-        <x:v>755</x:v>
+        <x:v>744</x:v>
       </x:c>
       <x:c r="E35" s="3" t="s">
-        <x:v>756</x:v>
+        <x:v>745</x:v>
       </x:c>
       <x:c r="F35" s="3" t="s">
         <x:v>37</x:v>
@@ -10715,31 +10682,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L35" s="3" t="s">
-        <x:v>757</x:v>
+        <x:v>746</x:v>
       </x:c>
       <x:c r="M35" s="3" t="s">
-        <x:v>758</x:v>
+        <x:v>747</x:v>
       </x:c>
       <x:c r="N35" s="3" t="s">
-        <x:v>759</x:v>
+        <x:v>748</x:v>
       </x:c>
       <x:c r="O35" s="3" t="s">
-        <x:v>533</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="P35" s="3" t="s">
-        <x:v>760</x:v>
+        <x:v>749</x:v>
       </x:c>
       <x:c r="Q35" s="3" t="s">
-        <x:v>761</x:v>
+        <x:v>750</x:v>
       </x:c>
       <x:c r="R35" s="3" t="s">
-        <x:v>762</x:v>
+        <x:v>751</x:v>
       </x:c>
       <x:c r="S35" s="3" t="s">
-        <x:v>763</x:v>
+        <x:v>752</x:v>
       </x:c>
       <x:c r="T35" s="3" t="s">
-        <x:v>764</x:v>
+        <x:v>753</x:v>
       </x:c>
       <x:c r="U35" s="3" t="s">
         <x:v>52</x:v>
@@ -10747,19 +10714,19 @@
     </x:row>
     <x:row r="36" ht="93.25" hidden="0">
       <x:c r="A36" s="3" t="s">
-        <x:v>765</x:v>
+        <x:v>754</x:v>
       </x:c>
       <x:c r="B36" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C36" s="3" t="s">
-        <x:v>766</x:v>
+        <x:v>755</x:v>
       </x:c>
       <x:c r="D36" s="3" t="s">
-        <x:v>767</x:v>
+        <x:v>756</x:v>
       </x:c>
       <x:c r="E36" s="3" t="s">
-        <x:v>768</x:v>
+        <x:v>757</x:v>
       </x:c>
       <x:c r="F36" s="3" t="s">
         <x:v>37</x:v>
@@ -10780,31 +10747,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L36" s="3" t="s">
-        <x:v>769</x:v>
+        <x:v>758</x:v>
       </x:c>
       <x:c r="M36" s="3" t="s">
         <x:v>446</x:v>
       </x:c>
       <x:c r="N36" s="3" t="s">
-        <x:v>770</x:v>
+        <x:v>759</x:v>
       </x:c>
       <x:c r="O36" s="3" t="s">
-        <x:v>771</x:v>
+        <x:v>760</x:v>
       </x:c>
       <x:c r="P36" s="3" t="s">
-        <x:v>772</x:v>
+        <x:v>761</x:v>
       </x:c>
       <x:c r="Q36" s="3" t="s">
-        <x:v>773</x:v>
+        <x:v>762</x:v>
       </x:c>
       <x:c r="R36" s="3" t="s">
-        <x:v>774</x:v>
+        <x:v>763</x:v>
       </x:c>
       <x:c r="S36" s="3" t="s">
-        <x:v>775</x:v>
+        <x:v>764</x:v>
       </x:c>
       <x:c r="T36" s="3" t="s">
-        <x:v>776</x:v>
+        <x:v>765</x:v>
       </x:c>
       <x:c r="U36" s="3" t="s">
         <x:v>52</x:v>
@@ -10812,19 +10779,19 @@
     </x:row>
     <x:row r="37" ht="93.25" hidden="0">
       <x:c r="A37" s="3" t="s">
-        <x:v>777</x:v>
+        <x:v>766</x:v>
       </x:c>
       <x:c r="B37" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C37" s="3" t="s">
-        <x:v>778</x:v>
+        <x:v>767</x:v>
       </x:c>
       <x:c r="D37" s="3" t="s">
-        <x:v>779</x:v>
+        <x:v>768</x:v>
       </x:c>
       <x:c r="E37" s="3" t="s">
-        <x:v>780</x:v>
+        <x:v>769</x:v>
       </x:c>
       <x:c r="F37" s="3" t="s">
         <x:v>37</x:v>
@@ -10845,31 +10812,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L37" s="3" t="s">
-        <x:v>781</x:v>
+        <x:v>770</x:v>
       </x:c>
       <x:c r="M37" s="3" t="s">
-        <x:v>782</x:v>
+        <x:v>771</x:v>
       </x:c>
       <x:c r="N37" s="3" t="s">
-        <x:v>783</x:v>
+        <x:v>772</x:v>
       </x:c>
       <x:c r="O37" s="3" t="s">
-        <x:v>784</x:v>
+        <x:v>773</x:v>
       </x:c>
       <x:c r="P37" s="3" t="s">
-        <x:v>785</x:v>
+        <x:v>774</x:v>
       </x:c>
       <x:c r="Q37" s="3" t="s">
-        <x:v>786</x:v>
+        <x:v>775</x:v>
       </x:c>
       <x:c r="R37" s="3" t="s">
-        <x:v>787</x:v>
+        <x:v>776</x:v>
       </x:c>
       <x:c r="S37" s="3" t="s">
-        <x:v>788</x:v>
+        <x:v>777</x:v>
       </x:c>
       <x:c r="T37" s="3" t="s">
-        <x:v>782</x:v>
+        <x:v>771</x:v>
       </x:c>
       <x:c r="U37" s="3" t="s">
         <x:v>52</x:v>
@@ -10877,19 +10844,19 @@
     </x:row>
     <x:row r="38" ht="93.25" hidden="0">
       <x:c r="A38" s="3" t="s">
-        <x:v>789</x:v>
+        <x:v>778</x:v>
       </x:c>
       <x:c r="B38" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C38" s="3" t="s">
-        <x:v>790</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="D38" s="3" t="s">
-        <x:v>791</x:v>
+        <x:v>780</x:v>
       </x:c>
       <x:c r="E38" s="3" t="s">
-        <x:v>792</x:v>
+        <x:v>781</x:v>
       </x:c>
       <x:c r="F38" s="3" t="s">
         <x:v>37</x:v>
@@ -10910,31 +10877,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L38" s="3" t="s">
-        <x:v>793</x:v>
+        <x:v>782</x:v>
       </x:c>
       <x:c r="M38" s="3" t="s">
-        <x:v>594</x:v>
+        <x:v>583</x:v>
       </x:c>
       <x:c r="N38" s="3" t="s">
-        <x:v>794</x:v>
+        <x:v>783</x:v>
       </x:c>
       <x:c r="O38" s="3" t="s">
-        <x:v>795</x:v>
+        <x:v>784</x:v>
       </x:c>
       <x:c r="P38" s="3" t="s">
-        <x:v>796</x:v>
+        <x:v>785</x:v>
       </x:c>
       <x:c r="Q38" s="3" t="s">
-        <x:v>797</x:v>
+        <x:v>786</x:v>
       </x:c>
       <x:c r="R38" s="3" t="s">
-        <x:v>798</x:v>
+        <x:v>787</x:v>
       </x:c>
       <x:c r="S38" s="3" t="s">
-        <x:v>799</x:v>
+        <x:v>788</x:v>
       </x:c>
       <x:c r="T38" s="3" t="s">
-        <x:v>800</x:v>
+        <x:v>789</x:v>
       </x:c>
       <x:c r="U38" s="3" t="s">
         <x:v>52</x:v>
@@ -10942,19 +10909,19 @@
     </x:row>
     <x:row r="39" ht="93.25" hidden="0">
       <x:c r="A39" s="3" t="s">
-        <x:v>801</x:v>
+        <x:v>790</x:v>
       </x:c>
       <x:c r="B39" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C39" s="3" t="s">
-        <x:v>802</x:v>
+        <x:v>791</x:v>
       </x:c>
       <x:c r="D39" s="3" t="s">
-        <x:v>803</x:v>
+        <x:v>792</x:v>
       </x:c>
       <x:c r="E39" s="3" t="s">
-        <x:v>804</x:v>
+        <x:v>793</x:v>
       </x:c>
       <x:c r="F39" s="3" t="s">
         <x:v>37</x:v>
@@ -10975,31 +10942,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="L39" s="3" t="s">
-        <x:v>805</x:v>
+        <x:v>794</x:v>
       </x:c>
       <x:c r="M39" s="3" t="s">
         <x:v>446</x:v>
       </x:c>
       <x:c r="N39" s="3" t="s">
-        <x:v>806</x:v>
+        <x:v>795</x:v>
       </x:c>
       <x:c r="O39" s="3" t="s">
-        <x:v>807</x:v>
+        <x:v>796</x:v>
       </x:c>
       <x:c r="P39" s="3" t="s">
-        <x:v>808</x:v>
+        <x:v>797</x:v>
       </x:c>
       <x:c r="Q39" s="3" t="s">
-        <x:v>809</x:v>
+        <x:v>798</x:v>
       </x:c>
       <x:c r="R39" s="3" t="s">
-        <x:v>810</x:v>
+        <x:v>799</x:v>
       </x:c>
       <x:c r="S39" s="3" t="s">
-        <x:v>811</x:v>
+        <x:v>800</x:v>
       </x:c>
       <x:c r="T39" s="3" t="s">
-        <x:v>812</x:v>
+        <x:v>801</x:v>
       </x:c>
       <x:c r="U39" s="3" t="s">
         <x:v>52</x:v>
@@ -11008,7 +10975,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2039768eee124d4b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf3665c4158cc4e66"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/maliev-feature-user-story-status.xlsx
+++ b/docs/maliev-feature-user-story-status.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rcbb80bf8ec4943ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="R2ac7781be66846b9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="Rdd0d9d6738084e57"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="Rf20af795d9654764"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Re6fafe2742cb4b66"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="Red9803fe13de4b7e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R5a6fb379673443d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="Rffa4b4af29db4596"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1409,42 +1409,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">AgentController.cs:271; QuoteAgentLaunchShell.razor</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QE-012</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Sketch attachments</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">As a customer, I can draw or attach a hand sketch for the agent.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Sketch dialog captures sketch data and posts it to the agent sketch endpoint.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Sketch UI -&gt; AgentController sketches -&gt; SessionStore/artifacts</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Hand sketch dialog/tools</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">AgentController POST sessions/{sessionId}/sketches</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QuoteAgentEndpointTests sketches; source tests sketch disposal | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">QuoteEngine BFF, SessionStore, Storage</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Sketch artifact/context</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Needs mobile sketch browser pass</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">AgentController.cs:367; QuoteAgentLaunchShell.razor</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">QE-013</x:t>
@@ -4988,7 +4952,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd2f86f9681414ec9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raf030c1f80b44b1e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8404,7 +8368,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2dd5de2b59ae4583"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R733049c3c13f45b6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9218,85 +9182,85 @@
       </x:c>
     </x:row>
     <x:row r="13" ht="93.25" hidden="0">
-      <x:c r="A13" s="3" t="s">
-        <x:v>466</x:v>
-      </x:c>
-      <x:c r="B13" s="3" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C13" s="3" t="s">
-        <x:v>467</x:v>
-      </x:c>
-      <x:c r="D13" s="3" t="s">
-        <x:v>468</x:v>
-      </x:c>
-      <x:c r="E13" s="3" t="s">
-        <x:v>469</x:v>
-      </x:c>
-      <x:c r="F13" s="3" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="G13" s="3" t="s">
-        <x:v>442</x:v>
-      </x:c>
-      <x:c r="H13" s="3" t="s">
-        <x:v>443</x:v>
-      </x:c>
-      <x:c r="I13" s="3" t="s">
-        <x:v>444</x:v>
-      </x:c>
-      <x:c r="J13" s="3" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="K13" s="3" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="L13" s="3" t="s">
-        <x:v>470</x:v>
-      </x:c>
-      <x:c r="M13" s="3" t="s">
-        <x:v>446</x:v>
-      </x:c>
-      <x:c r="N13" s="3" t="s">
-        <x:v>471</x:v>
-      </x:c>
-      <x:c r="O13" s="3" t="s">
-        <x:v>472</x:v>
-      </x:c>
-      <x:c r="P13" s="3" t="s">
-        <x:v>473</x:v>
-      </x:c>
-      <x:c r="Q13" s="3" t="s">
-        <x:v>474</x:v>
-      </x:c>
-      <x:c r="R13" s="3" t="s">
-        <x:v>475</x:v>
-      </x:c>
-      <x:c r="S13" s="3" t="s">
-        <x:v>476</x:v>
-      </x:c>
-      <x:c r="T13" s="3" t="s">
-        <x:v>477</x:v>
-      </x:c>
-      <x:c r="U13" s="3" t="s">
-        <x:v>52</x:v>
+      <x:c r="A13" s="3" t="str">
+        <x:v>QE-012</x:v>
+      </x:c>
+      <x:c r="B13" s="3" t="str">
+        <x:v>Maliev.QuoteEngine</x:v>
+      </x:c>
+      <x:c r="C13" s="3" t="str">
+        <x:v>Sketch attachments</x:v>
+      </x:c>
+      <x:c r="D13" s="3" t="str">
+        <x:v>As a customer, I can draw or attach a hand sketch for the agent.</x:v>
+      </x:c>
+      <x:c r="E13" s="3" t="str">
+        <x:v>Customers can open the hand-sketch dialog from the agent workspace, draw with mouse or pen, erase, undo, redo, insert or paste an image, name the sketch, attach it as a PNG, preview it as a pending composer attachment, and send it as image context without satisfying the CAD geometry gate by itself.</x:v>
+      </x:c>
+      <x:c r="F13" s="3" t="str">
+        <x:v>Current code-derived</x:v>
+      </x:c>
+      <x:c r="G13" s="3" t="str">
+        <x:v>Focused current-state sketch attachment tests passed 2026-06-24.</x:v>
+      </x:c>
+      <x:c r="H13" s="3" t="str">
+        <x:v>No behavior error observed in focused QuoteEngine sketch retest; live mobile/touch sketch browser interaction still not executed in this slice.</x:v>
+      </x:c>
+      <x:c r="I13" s="3" t="str">
+        <x:v>No app fix applied for QE-012; current code path is covered by focused BFF/source tests.</x:v>
+      </x:c>
+      <x:c r="J13" s="3" t="str">
+        <x:v>Passed 6/6 focused tests: session-scoped sketch upload and download redirect, uploaded sketch media inlined for chatbot stream, sketchboard clipboard isolation, sketch canvas disposal, pending attachment preview/send behavior, and shell visual contract.</x:v>
+      </x:c>
+      <x:c r="K13" s="3" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="L13" s="3" t="str">
+        <x:v>QuoteAgentLaunchShell hand-sketch dialog -&gt; quote-agent-sketch.js canvas module -&gt; multipart POST quote/v1/agent/sessions/{sessionId}/sketches -&gt; AgentController UploadSketch -&gt; QuoteAgentService UploadSketchAsync -&gt; UploadService signed URL -&gt; pending ComposerAttachmentPreview -&gt; QuoteAgentMessageRequest image attachment</x:v>
+      </x:c>
+      <x:c r="M13" s="3" t="str">
+        <x:v>QuoteAgentLaunchShell.razor; quote-agent-sketch.js; quote-upload.js; AgentController; QuoteAgentService; UploadSketchResponse; QuoteAgentDtos</x:v>
+      </x:c>
+      <x:c r="N13" s="3" t="str">
+        <x:v>QuoteAgentLaunchShell renders a modal hand-sketch canvas with title, color swatches, eraser, undo, redo, image insert, clear, and attach controls; it initializes /js/quote-agent-sketch.js, exports the canvas, uploads a PNG, queues a sketch ComposerAttachmentPreview, disposes the canvas on close/dispose, and refreshes the pending attachment preview.</x:v>
+      </x:c>
+      <x:c r="O13" s="3" t="str">
+        <x:v>POST quote/v1/agent/sessions/{sessionId}/sketches requires a non-empty image file, copies the multipart file to memory, stores it through UploadService at agent/sketches/{sessionId:N}/{fileName}, streams bytes with Content-Range, returns UploadSketchResponse with uploadId/storagePath/signed URL, and artifact download only redirects for the same session-owned sketch path.</x:v>
+      </x:c>
+      <x:c r="P13" s="3" t="str">
+        <x:v>2026-06-24: dotnet test Maliev.QuoteEngine.slnx --filter "FullyQualifiedName~QuoteAgentEndpointTests.Agent_sketch_upload_returns_signed_url_and_download_redirect_is_session_scoped|FullyQualifiedName~QuoteAgentEndpointTests.Agent_message_stream_with_uploaded_sketch_inlines_storage_media_for_chatbot|FullyQualifiedName~QuoteEngineSourceTests.QuoteUploadJs_does_not_steal_sketchboard_clipboard_images|FullyQualifiedName~QuoteEngineSourceTests.QuoteAgentLaunchShell_disposes_sketch_canvas_when_component_is_disposed|FullyQualifiedName~QuoteEngineSourceTests.QuoteAgentLaunchShell_previews_attachments_until_customer_sends_message|FullyQualifiedName~QuoteEngineSourceTests.QuoteAgentLaunchShell_has_monochrome_chatgpt_like_contract" --verbosity minimal passed 6/6.</x:v>
+      </x:c>
+      <x:c r="Q13" s="3" t="str">
+        <x:v>QuoteEngine Client, QuoteEngine BFF, UploadService client, agent session state, chatbot stream media payload</x:v>
+      </x:c>
+      <x:c r="R13" s="3" t="str">
+        <x:v>Sketch canvas image bytes, UploadSketchResponse upload id/storage path/signed URL, pending sketch composer attachment, sent image attachment payload, session-scoped sketch artifact download authorization</x:v>
+      </x:c>
+      <x:c r="S13" s="3" t="str">
+        <x:v>Needs live browser retest for mobile/touch drawing, image paste/insert, undo/redo/erase, upload failure UI, pending preview, and send behavior against a running QuoteEngine host.</x:v>
+      </x:c>
+      <x:c r="T13" s="3" t="str">
+        <x:v>Maliev.QuoteEngine.Client/Components/QuoteAgent/QuoteAgentLaunchShell.razor:1386,1457,2665,4533,4693,4722,4731,4766; Maliev.QuoteEngine.Client/wwwroot/js/quote-agent-sketch.js:530,553,562,590,603,620,627; Maliev.QuoteEngine.Client/wwwroot/js/quote-upload.js:205; Maliev.QuoteEngine.Bff/Controllers/AgentController.cs:367; Maliev.QuoteEngine.Bff/Services/QuoteAgentService.cs:1071,6373; Maliev.QuoteEngine.Shared/Agent/QuoteAgentDtos.cs:858; Maliev.QuoteEngine.Tests/QuoteAgentEndpointTests.cs:910,1178; Maliev.QuoteEngine.Tests/QuoteEngineSourceTests.cs:1655,1669,1933</x:v>
+      </x:c>
+      <x:c r="U13" s="3" t="str">
+        <x:v>2026-06-24</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="93.25" hidden="0">
       <x:c r="A14" s="3" t="s">
-        <x:v>478</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="B14" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C14" s="3" t="s">
-        <x:v>479</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="D14" s="3" t="s">
-        <x:v>480</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="E14" s="3" t="s">
-        <x:v>481</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="F14" s="3" t="s">
         <x:v>37</x:v>
@@ -9317,31 +9281,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L14" s="3" t="s">
-        <x:v>482</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="M14" s="3" t="s">
-        <x:v>483</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="N14" s="3" t="s">
-        <x:v>484</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="O14" s="3" t="s">
-        <x:v>485</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="P14" s="3" t="s">
-        <x:v>486</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="Q14" s="3" t="s">
-        <x:v>487</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="R14" s="3" t="s">
-        <x:v>488</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="S14" s="3" t="s">
-        <x:v>489</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="T14" s="3" t="s">
-        <x:v>490</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="U14" s="3" t="s">
         <x:v>52</x:v>
@@ -9349,19 +9313,19 @@
     </x:row>
     <x:row r="15" ht="107.25" hidden="0">
       <x:c r="A15" s="3" t="s">
-        <x:v>491</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="B15" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C15" s="3" t="s">
-        <x:v>492</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="D15" s="3" t="s">
-        <x:v>493</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="E15" s="3" t="s">
-        <x:v>494</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="F15" s="3" t="s">
         <x:v>37</x:v>
@@ -9382,31 +9346,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L15" s="3" t="s">
-        <x:v>495</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="M15" s="3" t="s">
         <x:v>446</x:v>
       </x:c>
       <x:c r="N15" s="3" t="s">
-        <x:v>496</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="O15" s="3" t="s">
-        <x:v>497</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="P15" s="3" t="s">
-        <x:v>498</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="Q15" s="3" t="s">
-        <x:v>499</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="R15" s="3" t="s">
-        <x:v>500</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="S15" s="3" t="s">
-        <x:v>501</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="T15" s="3" t="s">
-        <x:v>502</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="U15" s="3" t="s">
         <x:v>52</x:v>
@@ -9414,19 +9378,19 @@
     </x:row>
     <x:row r="16" ht="107.25" hidden="0">
       <x:c r="A16" s="3" t="s">
-        <x:v>503</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="B16" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C16" s="3" t="s">
-        <x:v>504</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="D16" s="3" t="s">
-        <x:v>505</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="E16" s="3" t="s">
-        <x:v>506</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="F16" s="3" t="s">
         <x:v>37</x:v>
@@ -9447,31 +9411,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L16" s="3" t="s">
-        <x:v>507</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="M16" s="3" t="s">
         <x:v>446</x:v>
       </x:c>
       <x:c r="N16" s="3" t="s">
-        <x:v>508</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="O16" s="3" t="s">
-        <x:v>509</x:v>
+        <x:v>497</x:v>
       </x:c>
       <x:c r="P16" s="3" t="s">
-        <x:v>510</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="Q16" s="3" t="s">
-        <x:v>511</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="R16" s="3" t="s">
-        <x:v>512</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="S16" s="3" t="s">
-        <x:v>513</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="T16" s="3" t="s">
-        <x:v>514</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="U16" s="3" t="s">
         <x:v>52</x:v>
@@ -9479,19 +9443,19 @@
     </x:row>
     <x:row r="17" ht="93.25" hidden="0">
       <x:c r="A17" s="3" t="s">
-        <x:v>515</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="B17" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C17" s="3" t="s">
-        <x:v>516</x:v>
+        <x:v>504</x:v>
       </x:c>
       <x:c r="D17" s="3" t="s">
-        <x:v>517</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="E17" s="3" t="s">
-        <x:v>518</x:v>
+        <x:v>506</x:v>
       </x:c>
       <x:c r="F17" s="3" t="s">
         <x:v>37</x:v>
@@ -9512,31 +9476,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L17" s="3" t="s">
-        <x:v>519</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="M17" s="3" t="s">
-        <x:v>520</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="N17" s="3" t="s">
-        <x:v>521</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="O17" s="3" t="s">
-        <x:v>522</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="P17" s="3" t="s">
-        <x:v>523</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="Q17" s="3" t="s">
-        <x:v>524</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="R17" s="3" t="s">
-        <x:v>525</x:v>
+        <x:v>513</x:v>
       </x:c>
       <x:c r="S17" s="3" t="s">
-        <x:v>526</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="T17" s="3" t="s">
-        <x:v>527</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="U17" s="3" t="s">
         <x:v>52</x:v>
@@ -9544,19 +9508,19 @@
     </x:row>
     <x:row r="18" ht="93.25" hidden="0">
       <x:c r="A18" s="3" t="s">
-        <x:v>528</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="B18" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C18" s="3" t="s">
-        <x:v>529</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="D18" s="3" t="s">
-        <x:v>530</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="E18" s="3" t="s">
-        <x:v>531</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="F18" s="3" t="s">
         <x:v>37</x:v>
@@ -9577,31 +9541,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L18" s="3" t="s">
-        <x:v>532</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="M18" s="3" t="s">
-        <x:v>533</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="N18" s="3" t="s">
-        <x:v>534</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="O18" s="3" t="s">
-        <x:v>535</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="P18" s="3" t="s">
-        <x:v>536</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="Q18" s="3" t="s">
-        <x:v>537</x:v>
+        <x:v>525</x:v>
       </x:c>
       <x:c r="R18" s="3" t="s">
-        <x:v>538</x:v>
+        <x:v>526</x:v>
       </x:c>
       <x:c r="S18" s="3" t="s">
-        <x:v>539</x:v>
+        <x:v>527</x:v>
       </x:c>
       <x:c r="T18" s="3" t="s">
-        <x:v>540</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="U18" s="3" t="s">
         <x:v>52</x:v>
@@ -9609,19 +9573,19 @@
     </x:row>
     <x:row r="19" ht="93.25" hidden="0">
       <x:c r="A19" s="3" t="s">
-        <x:v>541</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="B19" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C19" s="3" t="s">
-        <x:v>542</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="D19" s="3" t="s">
-        <x:v>543</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="E19" s="3" t="s">
-        <x:v>544</x:v>
+        <x:v>532</x:v>
       </x:c>
       <x:c r="F19" s="3" t="s">
         <x:v>37</x:v>
@@ -9642,31 +9606,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L19" s="3" t="s">
-        <x:v>545</x:v>
+        <x:v>533</x:v>
       </x:c>
       <x:c r="M19" s="3" t="s">
-        <x:v>546</x:v>
+        <x:v>534</x:v>
       </x:c>
       <x:c r="N19" s="3" t="s">
-        <x:v>547</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="O19" s="3" t="s">
-        <x:v>548</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="P19" s="3" t="s">
-        <x:v>549</x:v>
+        <x:v>537</x:v>
       </x:c>
       <x:c r="Q19" s="3" t="s">
-        <x:v>550</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="R19" s="3" t="s">
-        <x:v>551</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="S19" s="3" t="s">
-        <x:v>552</x:v>
+        <x:v>540</x:v>
       </x:c>
       <x:c r="T19" s="3" t="s">
-        <x:v>553</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="U19" s="3" t="s">
         <x:v>52</x:v>
@@ -9674,19 +9638,19 @@
     </x:row>
     <x:row r="20" ht="79.25" hidden="0">
       <x:c r="A20" s="3" t="s">
-        <x:v>554</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="B20" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C20" s="3" t="s">
-        <x:v>555</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="D20" s="3" t="s">
-        <x:v>556</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="E20" s="3" t="s">
-        <x:v>557</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="F20" s="3" t="s">
         <x:v>37</x:v>
@@ -9707,31 +9671,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L20" s="3" t="s">
-        <x:v>558</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="M20" s="3" t="s">
-        <x:v>559</x:v>
+        <x:v>547</x:v>
       </x:c>
       <x:c r="N20" s="3" t="s">
-        <x:v>560</x:v>
+        <x:v>548</x:v>
       </x:c>
       <x:c r="O20" s="3" t="s">
-        <x:v>561</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="P20" s="3" t="s">
-        <x:v>562</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="Q20" s="3" t="s">
-        <x:v>563</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="R20" s="3" t="s">
-        <x:v>564</x:v>
+        <x:v>552</x:v>
       </x:c>
       <x:c r="S20" s="3" t="s">
-        <x:v>565</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="T20" s="3" t="s">
-        <x:v>566</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="U20" s="3" t="s">
         <x:v>52</x:v>
@@ -9739,19 +9703,19 @@
     </x:row>
     <x:row r="21" ht="79.25" hidden="0">
       <x:c r="A21" s="3" t="s">
-        <x:v>567</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="B21" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C21" s="3" t="s">
-        <x:v>568</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="D21" s="3" t="s">
-        <x:v>569</x:v>
+        <x:v>557</x:v>
       </x:c>
       <x:c r="E21" s="3" t="s">
-        <x:v>570</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="F21" s="3" t="s">
         <x:v>37</x:v>
@@ -9772,31 +9736,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L21" s="3" t="s">
-        <x:v>571</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="M21" s="3" t="s">
-        <x:v>572</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="N21" s="3" t="s">
-        <x:v>573</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="O21" s="3" t="s">
         <x:v>218</x:v>
       </x:c>
       <x:c r="P21" s="3" t="s">
-        <x:v>574</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="Q21" s="3" t="s">
-        <x:v>575</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="R21" s="3" t="s">
         <x:v>221</x:v>
       </x:c>
       <x:c r="S21" s="3" t="s">
-        <x:v>576</x:v>
+        <x:v>564</x:v>
       </x:c>
       <x:c r="T21" s="3" t="s">
-        <x:v>577</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="U21" s="3" t="s">
         <x:v>52</x:v>
@@ -9804,19 +9768,19 @@
     </x:row>
     <x:row r="22" ht="93.25" hidden="0">
       <x:c r="A22" s="3" t="s">
-        <x:v>578</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="B22" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C22" s="3" t="s">
-        <x:v>579</x:v>
+        <x:v>567</x:v>
       </x:c>
       <x:c r="D22" s="3" t="s">
-        <x:v>580</x:v>
+        <x:v>568</x:v>
       </x:c>
       <x:c r="E22" s="3" t="s">
-        <x:v>581</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="F22" s="3" t="s">
         <x:v>37</x:v>
@@ -9837,31 +9801,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L22" s="3" t="s">
-        <x:v>582</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="M22" s="3" t="s">
-        <x:v>583</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="N22" s="3" t="s">
-        <x:v>584</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="O22" s="3" t="s">
-        <x:v>585</x:v>
+        <x:v>573</x:v>
       </x:c>
       <x:c r="P22" s="3" t="s">
-        <x:v>586</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="Q22" s="3" t="s">
-        <x:v>587</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="R22" s="3" t="s">
-        <x:v>588</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="S22" s="3" t="s">
-        <x:v>589</x:v>
+        <x:v>577</x:v>
       </x:c>
       <x:c r="T22" s="3" t="s">
-        <x:v>590</x:v>
+        <x:v>578</x:v>
       </x:c>
       <x:c r="U22" s="3" t="s">
         <x:v>52</x:v>
@@ -9869,19 +9833,19 @@
     </x:row>
     <x:row r="23" ht="93.25" hidden="0">
       <x:c r="A23" s="3" t="s">
-        <x:v>591</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="B23" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C23" s="3" t="s">
-        <x:v>592</x:v>
+        <x:v>580</x:v>
       </x:c>
       <x:c r="D23" s="3" t="s">
-        <x:v>593</x:v>
+        <x:v>581</x:v>
       </x:c>
       <x:c r="E23" s="3" t="s">
-        <x:v>594</x:v>
+        <x:v>582</x:v>
       </x:c>
       <x:c r="F23" s="3" t="s">
         <x:v>37</x:v>
@@ -9902,31 +9866,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L23" s="3" t="s">
-        <x:v>595</x:v>
+        <x:v>583</x:v>
       </x:c>
       <x:c r="M23" s="3" t="s">
-        <x:v>596</x:v>
+        <x:v>584</x:v>
       </x:c>
       <x:c r="N23" s="3" t="s">
-        <x:v>597</x:v>
+        <x:v>585</x:v>
       </x:c>
       <x:c r="O23" s="3" t="s">
-        <x:v>598</x:v>
+        <x:v>586</x:v>
       </x:c>
       <x:c r="P23" s="3" t="s">
-        <x:v>599</x:v>
+        <x:v>587</x:v>
       </x:c>
       <x:c r="Q23" s="3" t="s">
-        <x:v>600</x:v>
+        <x:v>588</x:v>
       </x:c>
       <x:c r="R23" s="3" t="s">
-        <x:v>601</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="S23" s="3" t="s">
-        <x:v>602</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="T23" s="3" t="s">
-        <x:v>603</x:v>
+        <x:v>591</x:v>
       </x:c>
       <x:c r="U23" s="3" t="s">
         <x:v>52</x:v>
@@ -9934,19 +9898,19 @@
     </x:row>
     <x:row r="24" ht="79.25" hidden="0">
       <x:c r="A24" s="3" t="s">
-        <x:v>604</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="B24" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C24" s="3" t="s">
-        <x:v>605</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="D24" s="3" t="s">
-        <x:v>606</x:v>
+        <x:v>594</x:v>
       </x:c>
       <x:c r="E24" s="3" t="s">
-        <x:v>607</x:v>
+        <x:v>595</x:v>
       </x:c>
       <x:c r="F24" s="3" t="s">
         <x:v>37</x:v>
@@ -9967,31 +9931,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L24" s="3" t="s">
-        <x:v>608</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="M24" s="3" t="s">
-        <x:v>572</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="N24" s="3" t="s">
-        <x:v>609</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="O24" s="3" t="s">
-        <x:v>610</x:v>
+        <x:v>598</x:v>
       </x:c>
       <x:c r="P24" s="3" t="s">
-        <x:v>611</x:v>
+        <x:v>599</x:v>
       </x:c>
       <x:c r="Q24" s="3" t="s">
-        <x:v>612</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="R24" s="3" t="s">
-        <x:v>613</x:v>
+        <x:v>601</x:v>
       </x:c>
       <x:c r="S24" s="3" t="s">
-        <x:v>614</x:v>
+        <x:v>602</x:v>
       </x:c>
       <x:c r="T24" s="3" t="s">
-        <x:v>615</x:v>
+        <x:v>603</x:v>
       </x:c>
       <x:c r="U24" s="3" t="s">
         <x:v>52</x:v>
@@ -9999,19 +9963,19 @@
     </x:row>
     <x:row r="25" ht="79.25" hidden="0">
       <x:c r="A25" s="3" t="s">
-        <x:v>616</x:v>
+        <x:v>604</x:v>
       </x:c>
       <x:c r="B25" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C25" s="3" t="s">
-        <x:v>617</x:v>
+        <x:v>605</x:v>
       </x:c>
       <x:c r="D25" s="3" t="s">
-        <x:v>618</x:v>
+        <x:v>606</x:v>
       </x:c>
       <x:c r="E25" s="3" t="s">
-        <x:v>619</x:v>
+        <x:v>607</x:v>
       </x:c>
       <x:c r="F25" s="3" t="s">
         <x:v>37</x:v>
@@ -10032,31 +9996,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L25" s="3" t="s">
-        <x:v>620</x:v>
+        <x:v>608</x:v>
       </x:c>
       <x:c r="M25" s="3" t="s">
-        <x:v>572</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="N25" s="3" t="s">
-        <x:v>621</x:v>
+        <x:v>609</x:v>
       </x:c>
       <x:c r="O25" s="3" t="s">
-        <x:v>622</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="P25" s="3" t="s">
-        <x:v>623</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="Q25" s="3" t="s">
-        <x:v>624</x:v>
+        <x:v>612</x:v>
       </x:c>
       <x:c r="R25" s="3" t="s">
-        <x:v>625</x:v>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="S25" s="3" t="s">
-        <x:v>626</x:v>
+        <x:v>614</x:v>
       </x:c>
       <x:c r="T25" s="3" t="s">
-        <x:v>627</x:v>
+        <x:v>615</x:v>
       </x:c>
       <x:c r="U25" s="3" t="s">
         <x:v>52</x:v>
@@ -10064,19 +10028,19 @@
     </x:row>
     <x:row r="26" ht="79.25" hidden="0">
       <x:c r="A26" s="3" t="s">
-        <x:v>628</x:v>
+        <x:v>616</x:v>
       </x:c>
       <x:c r="B26" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C26" s="3" t="s">
-        <x:v>629</x:v>
+        <x:v>617</x:v>
       </x:c>
       <x:c r="D26" s="3" t="s">
-        <x:v>630</x:v>
+        <x:v>618</x:v>
       </x:c>
       <x:c r="E26" s="3" t="s">
-        <x:v>631</x:v>
+        <x:v>619</x:v>
       </x:c>
       <x:c r="F26" s="3" t="s">
         <x:v>37</x:v>
@@ -10097,31 +10061,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L26" s="3" t="s">
-        <x:v>632</x:v>
+        <x:v>620</x:v>
       </x:c>
       <x:c r="M26" s="3" t="s">
-        <x:v>633</x:v>
+        <x:v>621</x:v>
       </x:c>
       <x:c r="N26" s="3" t="s">
-        <x:v>634</x:v>
+        <x:v>622</x:v>
       </x:c>
       <x:c r="O26" s="3" t="s">
-        <x:v>635</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="P26" s="3" t="s">
-        <x:v>636</x:v>
+        <x:v>624</x:v>
       </x:c>
       <x:c r="Q26" s="3" t="s">
-        <x:v>637</x:v>
+        <x:v>625</x:v>
       </x:c>
       <x:c r="R26" s="3" t="s">
-        <x:v>638</x:v>
+        <x:v>626</x:v>
       </x:c>
       <x:c r="S26" s="3" t="s">
-        <x:v>639</x:v>
+        <x:v>627</x:v>
       </x:c>
       <x:c r="T26" s="3" t="s">
-        <x:v>640</x:v>
+        <x:v>628</x:v>
       </x:c>
       <x:c r="U26" s="3" t="s">
         <x:v>52</x:v>
@@ -10129,19 +10093,19 @@
     </x:row>
     <x:row r="27" ht="79.25" hidden="0">
       <x:c r="A27" s="3" t="s">
-        <x:v>641</x:v>
+        <x:v>629</x:v>
       </x:c>
       <x:c r="B27" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C27" s="3" t="s">
-        <x:v>642</x:v>
+        <x:v>630</x:v>
       </x:c>
       <x:c r="D27" s="3" t="s">
-        <x:v>643</x:v>
+        <x:v>631</x:v>
       </x:c>
       <x:c r="E27" s="3" t="s">
-        <x:v>644</x:v>
+        <x:v>632</x:v>
       </x:c>
       <x:c r="F27" s="3" t="s">
         <x:v>37</x:v>
@@ -10162,31 +10126,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L27" s="3" t="s">
-        <x:v>645</x:v>
+        <x:v>633</x:v>
       </x:c>
       <x:c r="M27" s="3" t="s">
-        <x:v>646</x:v>
+        <x:v>634</x:v>
       </x:c>
       <x:c r="N27" s="3" t="s">
-        <x:v>647</x:v>
+        <x:v>635</x:v>
       </x:c>
       <x:c r="O27" s="3" t="s">
-        <x:v>648</x:v>
+        <x:v>636</x:v>
       </x:c>
       <x:c r="P27" s="3" t="s">
-        <x:v>649</x:v>
+        <x:v>637</x:v>
       </x:c>
       <x:c r="Q27" s="3" t="s">
-        <x:v>650</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="R27" s="3" t="s">
-        <x:v>651</x:v>
+        <x:v>639</x:v>
       </x:c>
       <x:c r="S27" s="3" t="s">
-        <x:v>652</x:v>
+        <x:v>640</x:v>
       </x:c>
       <x:c r="T27" s="3" t="s">
-        <x:v>653</x:v>
+        <x:v>641</x:v>
       </x:c>
       <x:c r="U27" s="3" t="s">
         <x:v>52</x:v>
@@ -10194,19 +10158,19 @@
     </x:row>
     <x:row r="28" ht="93.25" hidden="0">
       <x:c r="A28" s="3" t="s">
-        <x:v>654</x:v>
+        <x:v>642</x:v>
       </x:c>
       <x:c r="B28" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C28" s="3" t="s">
-        <x:v>655</x:v>
+        <x:v>643</x:v>
       </x:c>
       <x:c r="D28" s="3" t="s">
-        <x:v>656</x:v>
+        <x:v>644</x:v>
       </x:c>
       <x:c r="E28" s="3" t="s">
-        <x:v>657</x:v>
+        <x:v>645</x:v>
       </x:c>
       <x:c r="F28" s="3" t="s">
         <x:v>37</x:v>
@@ -10227,31 +10191,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L28" s="3" t="s">
-        <x:v>658</x:v>
+        <x:v>646</x:v>
       </x:c>
       <x:c r="M28" s="3" t="s">
-        <x:v>659</x:v>
+        <x:v>647</x:v>
       </x:c>
       <x:c r="N28" s="3" t="s">
-        <x:v>660</x:v>
+        <x:v>648</x:v>
       </x:c>
       <x:c r="O28" s="3" t="s">
-        <x:v>661</x:v>
+        <x:v>649</x:v>
       </x:c>
       <x:c r="P28" s="3" t="s">
-        <x:v>662</x:v>
+        <x:v>650</x:v>
       </x:c>
       <x:c r="Q28" s="3" t="s">
-        <x:v>663</x:v>
+        <x:v>651</x:v>
       </x:c>
       <x:c r="R28" s="3" t="s">
-        <x:v>664</x:v>
+        <x:v>652</x:v>
       </x:c>
       <x:c r="S28" s="3" t="s">
         <x:v>286</x:v>
       </x:c>
       <x:c r="T28" s="3" t="s">
-        <x:v>665</x:v>
+        <x:v>653</x:v>
       </x:c>
       <x:c r="U28" s="3" t="s">
         <x:v>52</x:v>
@@ -10259,19 +10223,19 @@
     </x:row>
     <x:row r="29" ht="93.25" hidden="0">
       <x:c r="A29" s="3" t="s">
-        <x:v>666</x:v>
+        <x:v>654</x:v>
       </x:c>
       <x:c r="B29" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C29" s="3" t="s">
-        <x:v>667</x:v>
+        <x:v>655</x:v>
       </x:c>
       <x:c r="D29" s="3" t="s">
-        <x:v>668</x:v>
+        <x:v>656</x:v>
       </x:c>
       <x:c r="E29" s="3" t="s">
-        <x:v>669</x:v>
+        <x:v>657</x:v>
       </x:c>
       <x:c r="F29" s="3" t="s">
         <x:v>37</x:v>
@@ -10292,31 +10256,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="L29" s="3" t="s">
-        <x:v>670</x:v>
+        <x:v>658</x:v>
       </x:c>
       <x:c r="M29" s="3" t="s">
-        <x:v>671</x:v>
+        <x:v>659</x:v>
       </x:c>
       <x:c r="N29" s="3" t="s">
-        <x:v>672</x:v>
+        <x:v>660</x:v>
       </x:c>
       <x:c r="O29" s="3" t="s">
-        <x:v>673</x:v>
+        <x:v>661</x:v>
       </x:c>
       <x:c r="P29" s="3" t="s">
-        <x:v>674</x:v>
+        <x:v>662</x:v>
       </x:c>
       <x:c r="Q29" s="3" t="s">
-        <x:v>675</x:v>
+        <x:v>663</x:v>
       </x:c>
       <x:c r="R29" s="3" t="s">
-        <x:v>676</x:v>
+        <x:v>664</x:v>
       </x:c>
       <x:c r="S29" s="3" t="s">
-        <x:v>677</x:v>
+        <x:v>665</x:v>
       </x:c>
       <x:c r="T29" s="3" t="s">
-        <x:v>678</x:v>
+        <x:v>666</x:v>
       </x:c>
       <x:c r="U29" s="3" t="s">
         <x:v>52</x:v>
@@ -10324,19 +10288,19 @@
     </x:row>
     <x:row r="30" ht="93.25" hidden="0">
       <x:c r="A30" s="3" t="s">
-        <x:v>679</x:v>
+        <x:v>667</x:v>
       </x:c>
       <x:c r="B30" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C30" s="3" t="s">
-        <x:v>680</x:v>
+        <x:v>668</x:v>
       </x:c>
       <x:c r="D30" s="3" t="s">
-        <x:v>681</x:v>
+        <x:v>669</x:v>
       </x:c>
       <x:c r="E30" s="3" t="s">
-        <x:v>682</x:v>
+        <x:v>670</x:v>
       </x:c>
       <x:c r="F30" s="3" t="s">
         <x:v>37</x:v>
@@ -10357,31 +10321,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L30" s="3" t="s">
-        <x:v>683</x:v>
+        <x:v>671</x:v>
       </x:c>
       <x:c r="M30" s="3" t="s">
-        <x:v>684</x:v>
+        <x:v>672</x:v>
       </x:c>
       <x:c r="N30" s="3" t="s">
-        <x:v>685</x:v>
+        <x:v>673</x:v>
       </x:c>
       <x:c r="O30" s="3" t="s">
-        <x:v>686</x:v>
+        <x:v>674</x:v>
       </x:c>
       <x:c r="P30" s="3" t="s">
-        <x:v>687</x:v>
+        <x:v>675</x:v>
       </x:c>
       <x:c r="Q30" s="3" t="s">
-        <x:v>688</x:v>
+        <x:v>676</x:v>
       </x:c>
       <x:c r="R30" s="3" t="s">
-        <x:v>689</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="S30" s="3" t="s">
-        <x:v>690</x:v>
+        <x:v>678</x:v>
       </x:c>
       <x:c r="T30" s="3" t="s">
-        <x:v>691</x:v>
+        <x:v>679</x:v>
       </x:c>
       <x:c r="U30" s="3" t="s">
         <x:v>52</x:v>
@@ -10389,19 +10353,19 @@
     </x:row>
     <x:row r="31" ht="93.25" hidden="0">
       <x:c r="A31" s="3" t="s">
-        <x:v>692</x:v>
+        <x:v>680</x:v>
       </x:c>
       <x:c r="B31" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C31" s="3" t="s">
-        <x:v>693</x:v>
+        <x:v>681</x:v>
       </x:c>
       <x:c r="D31" s="3" t="s">
-        <x:v>694</x:v>
+        <x:v>682</x:v>
       </x:c>
       <x:c r="E31" s="3" t="s">
-        <x:v>695</x:v>
+        <x:v>683</x:v>
       </x:c>
       <x:c r="F31" s="3" t="s">
         <x:v>37</x:v>
@@ -10422,31 +10386,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="L31" s="3" t="s">
-        <x:v>696</x:v>
+        <x:v>684</x:v>
       </x:c>
       <x:c r="M31" s="3" t="s">
-        <x:v>697</x:v>
+        <x:v>685</x:v>
       </x:c>
       <x:c r="N31" s="3" t="s">
-        <x:v>698</x:v>
+        <x:v>686</x:v>
       </x:c>
       <x:c r="O31" s="3" t="s">
-        <x:v>699</x:v>
+        <x:v>687</x:v>
       </x:c>
       <x:c r="P31" s="3" t="s">
-        <x:v>700</x:v>
+        <x:v>688</x:v>
       </x:c>
       <x:c r="Q31" s="3" t="s">
-        <x:v>701</x:v>
+        <x:v>689</x:v>
       </x:c>
       <x:c r="R31" s="3" t="s">
-        <x:v>702</x:v>
+        <x:v>690</x:v>
       </x:c>
       <x:c r="S31" s="3" t="s">
-        <x:v>703</x:v>
+        <x:v>691</x:v>
       </x:c>
       <x:c r="T31" s="3" t="s">
-        <x:v>704</x:v>
+        <x:v>692</x:v>
       </x:c>
       <x:c r="U31" s="3" t="s">
         <x:v>52</x:v>
@@ -10454,19 +10418,19 @@
     </x:row>
     <x:row r="32" ht="93.25" hidden="0">
       <x:c r="A32" s="3" t="s">
-        <x:v>705</x:v>
+        <x:v>693</x:v>
       </x:c>
       <x:c r="B32" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C32" s="3" t="s">
-        <x:v>706</x:v>
+        <x:v>694</x:v>
       </x:c>
       <x:c r="D32" s="3" t="s">
-        <x:v>707</x:v>
+        <x:v>695</x:v>
       </x:c>
       <x:c r="E32" s="3" t="s">
-        <x:v>708</x:v>
+        <x:v>696</x:v>
       </x:c>
       <x:c r="F32" s="3" t="s">
         <x:v>37</x:v>
@@ -10487,31 +10451,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L32" s="3" t="s">
-        <x:v>709</x:v>
+        <x:v>697</x:v>
       </x:c>
       <x:c r="M32" s="3" t="s">
-        <x:v>710</x:v>
+        <x:v>698</x:v>
       </x:c>
       <x:c r="N32" s="3" t="s">
-        <x:v>711</x:v>
+        <x:v>699</x:v>
       </x:c>
       <x:c r="O32" s="3" t="s">
-        <x:v>712</x:v>
+        <x:v>700</x:v>
       </x:c>
       <x:c r="P32" s="3" t="s">
-        <x:v>713</x:v>
+        <x:v>701</x:v>
       </x:c>
       <x:c r="Q32" s="3" t="s">
-        <x:v>714</x:v>
+        <x:v>702</x:v>
       </x:c>
       <x:c r="R32" s="3" t="s">
-        <x:v>715</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="S32" s="3" t="s">
-        <x:v>716</x:v>
+        <x:v>704</x:v>
       </x:c>
       <x:c r="T32" s="3" t="s">
-        <x:v>717</x:v>
+        <x:v>705</x:v>
       </x:c>
       <x:c r="U32" s="3" t="s">
         <x:v>52</x:v>
@@ -10519,19 +10483,19 @@
     </x:row>
     <x:row r="33" ht="93.25" hidden="0">
       <x:c r="A33" s="3" t="s">
-        <x:v>718</x:v>
+        <x:v>706</x:v>
       </x:c>
       <x:c r="B33" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C33" s="3" t="s">
-        <x:v>719</x:v>
+        <x:v>707</x:v>
       </x:c>
       <x:c r="D33" s="3" t="s">
-        <x:v>720</x:v>
+        <x:v>708</x:v>
       </x:c>
       <x:c r="E33" s="3" t="s">
-        <x:v>721</x:v>
+        <x:v>709</x:v>
       </x:c>
       <x:c r="F33" s="3" t="s">
         <x:v>37</x:v>
@@ -10552,31 +10516,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L33" s="3" t="s">
-        <x:v>722</x:v>
+        <x:v>710</x:v>
       </x:c>
       <x:c r="M33" s="3" t="s">
-        <x:v>723</x:v>
+        <x:v>711</x:v>
       </x:c>
       <x:c r="N33" s="3" t="s">
-        <x:v>724</x:v>
+        <x:v>712</x:v>
       </x:c>
       <x:c r="O33" s="3" t="s">
-        <x:v>725</x:v>
+        <x:v>713</x:v>
       </x:c>
       <x:c r="P33" s="3" t="s">
-        <x:v>726</x:v>
+        <x:v>714</x:v>
       </x:c>
       <x:c r="Q33" s="3" t="s">
-        <x:v>727</x:v>
+        <x:v>715</x:v>
       </x:c>
       <x:c r="R33" s="3" t="s">
-        <x:v>728</x:v>
+        <x:v>716</x:v>
       </x:c>
       <x:c r="S33" s="3" t="s">
-        <x:v>729</x:v>
+        <x:v>717</x:v>
       </x:c>
       <x:c r="T33" s="3" t="s">
-        <x:v>730</x:v>
+        <x:v>718</x:v>
       </x:c>
       <x:c r="U33" s="3" t="s">
         <x:v>52</x:v>
@@ -10584,7 +10548,7 @@
     </x:row>
     <x:row r="34" ht="93.25" hidden="0">
       <x:c r="A34" s="3" t="s">
-        <x:v>731</x:v>
+        <x:v>719</x:v>
       </x:c>
       <x:c r="B34" s="3" t="s">
         <x:v>8</x:v>
@@ -10593,10 +10557,10 @@
         <x:v>313</x:v>
       </x:c>
       <x:c r="D34" s="3" t="s">
-        <x:v>732</x:v>
+        <x:v>720</x:v>
       </x:c>
       <x:c r="E34" s="3" t="s">
-        <x:v>733</x:v>
+        <x:v>721</x:v>
       </x:c>
       <x:c r="F34" s="3" t="s">
         <x:v>37</x:v>
@@ -10617,31 +10581,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="L34" s="3" t="s">
-        <x:v>734</x:v>
+        <x:v>722</x:v>
       </x:c>
       <x:c r="M34" s="3" t="s">
-        <x:v>735</x:v>
+        <x:v>723</x:v>
       </x:c>
       <x:c r="N34" s="3" t="s">
-        <x:v>736</x:v>
+        <x:v>724</x:v>
       </x:c>
       <x:c r="O34" s="3" t="s">
-        <x:v>737</x:v>
+        <x:v>725</x:v>
       </x:c>
       <x:c r="P34" s="3" t="s">
-        <x:v>738</x:v>
+        <x:v>726</x:v>
       </x:c>
       <x:c r="Q34" s="3" t="s">
-        <x:v>739</x:v>
+        <x:v>727</x:v>
       </x:c>
       <x:c r="R34" s="3" t="s">
-        <x:v>740</x:v>
+        <x:v>728</x:v>
       </x:c>
       <x:c r="S34" s="3" t="s">
         <x:v>323</x:v>
       </x:c>
       <x:c r="T34" s="3" t="s">
-        <x:v>741</x:v>
+        <x:v>729</x:v>
       </x:c>
       <x:c r="U34" s="3" t="s">
         <x:v>52</x:v>
@@ -10649,19 +10613,19 @@
     </x:row>
     <x:row r="35" ht="93.25" hidden="0">
       <x:c r="A35" s="3" t="s">
-        <x:v>742</x:v>
+        <x:v>730</x:v>
       </x:c>
       <x:c r="B35" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C35" s="3" t="s">
-        <x:v>743</x:v>
+        <x:v>731</x:v>
       </x:c>
       <x:c r="D35" s="3" t="s">
-        <x:v>744</x:v>
+        <x:v>732</x:v>
       </x:c>
       <x:c r="E35" s="3" t="s">
-        <x:v>745</x:v>
+        <x:v>733</x:v>
       </x:c>
       <x:c r="F35" s="3" t="s">
         <x:v>37</x:v>
@@ -10682,31 +10646,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L35" s="3" t="s">
-        <x:v>746</x:v>
+        <x:v>734</x:v>
       </x:c>
       <x:c r="M35" s="3" t="s">
-        <x:v>747</x:v>
+        <x:v>735</x:v>
       </x:c>
       <x:c r="N35" s="3" t="s">
-        <x:v>748</x:v>
+        <x:v>736</x:v>
       </x:c>
       <x:c r="O35" s="3" t="s">
-        <x:v>522</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="P35" s="3" t="s">
-        <x:v>749</x:v>
+        <x:v>737</x:v>
       </x:c>
       <x:c r="Q35" s="3" t="s">
-        <x:v>750</x:v>
+        <x:v>738</x:v>
       </x:c>
       <x:c r="R35" s="3" t="s">
-        <x:v>751</x:v>
+        <x:v>739</x:v>
       </x:c>
       <x:c r="S35" s="3" t="s">
-        <x:v>752</x:v>
+        <x:v>740</x:v>
       </x:c>
       <x:c r="T35" s="3" t="s">
-        <x:v>753</x:v>
+        <x:v>741</x:v>
       </x:c>
       <x:c r="U35" s="3" t="s">
         <x:v>52</x:v>
@@ -10714,19 +10678,19 @@
     </x:row>
     <x:row r="36" ht="93.25" hidden="0">
       <x:c r="A36" s="3" t="s">
-        <x:v>754</x:v>
+        <x:v>742</x:v>
       </x:c>
       <x:c r="B36" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C36" s="3" t="s">
-        <x:v>755</x:v>
+        <x:v>743</x:v>
       </x:c>
       <x:c r="D36" s="3" t="s">
-        <x:v>756</x:v>
+        <x:v>744</x:v>
       </x:c>
       <x:c r="E36" s="3" t="s">
-        <x:v>757</x:v>
+        <x:v>745</x:v>
       </x:c>
       <x:c r="F36" s="3" t="s">
         <x:v>37</x:v>
@@ -10747,31 +10711,31 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="L36" s="3" t="s">
-        <x:v>758</x:v>
+        <x:v>746</x:v>
       </x:c>
       <x:c r="M36" s="3" t="s">
         <x:v>446</x:v>
       </x:c>
       <x:c r="N36" s="3" t="s">
-        <x:v>759</x:v>
+        <x:v>747</x:v>
       </x:c>
       <x:c r="O36" s="3" t="s">
-        <x:v>760</x:v>
+        <x:v>748</x:v>
       </x:c>
       <x:c r="P36" s="3" t="s">
-        <x:v>761</x:v>
+        <x:v>749</x:v>
       </x:c>
       <x:c r="Q36" s="3" t="s">
-        <x:v>762</x:v>
+        <x:v>750</x:v>
       </x:c>
       <x:c r="R36" s="3" t="s">
-        <x:v>763</x:v>
+        <x:v>751</x:v>
       </x:c>
       <x:c r="S36" s="3" t="s">
-        <x:v>764</x:v>
+        <x:v>752</x:v>
       </x:c>
       <x:c r="T36" s="3" t="s">
-        <x:v>765</x:v>
+        <x:v>753</x:v>
       </x:c>
       <x:c r="U36" s="3" t="s">
         <x:v>52</x:v>
@@ -10779,19 +10743,19 @@
     </x:row>
     <x:row r="37" ht="93.25" hidden="0">
       <x:c r="A37" s="3" t="s">
-        <x:v>766</x:v>
+        <x:v>754</x:v>
       </x:c>
       <x:c r="B37" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C37" s="3" t="s">
-        <x:v>767</x:v>
+        <x:v>755</x:v>
       </x:c>
       <x:c r="D37" s="3" t="s">
-        <x:v>768</x:v>
+        <x:v>756</x:v>
       </x:c>
       <x:c r="E37" s="3" t="s">
-        <x:v>769</x:v>
+        <x:v>757</x:v>
       </x:c>
       <x:c r="F37" s="3" t="s">
         <x:v>37</x:v>
@@ -10812,31 +10776,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L37" s="3" t="s">
-        <x:v>770</x:v>
+        <x:v>758</x:v>
       </x:c>
       <x:c r="M37" s="3" t="s">
-        <x:v>771</x:v>
+        <x:v>759</x:v>
       </x:c>
       <x:c r="N37" s="3" t="s">
-        <x:v>772</x:v>
+        <x:v>760</x:v>
       </x:c>
       <x:c r="O37" s="3" t="s">
-        <x:v>773</x:v>
+        <x:v>761</x:v>
       </x:c>
       <x:c r="P37" s="3" t="s">
-        <x:v>774</x:v>
+        <x:v>762</x:v>
       </x:c>
       <x:c r="Q37" s="3" t="s">
-        <x:v>775</x:v>
+        <x:v>763</x:v>
       </x:c>
       <x:c r="R37" s="3" t="s">
-        <x:v>776</x:v>
+        <x:v>764</x:v>
       </x:c>
       <x:c r="S37" s="3" t="s">
-        <x:v>777</x:v>
+        <x:v>765</x:v>
       </x:c>
       <x:c r="T37" s="3" t="s">
-        <x:v>771</x:v>
+        <x:v>759</x:v>
       </x:c>
       <x:c r="U37" s="3" t="s">
         <x:v>52</x:v>
@@ -10844,19 +10808,19 @@
     </x:row>
     <x:row r="38" ht="93.25" hidden="0">
       <x:c r="A38" s="3" t="s">
-        <x:v>778</x:v>
+        <x:v>766</x:v>
       </x:c>
       <x:c r="B38" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C38" s="3" t="s">
-        <x:v>779</x:v>
+        <x:v>767</x:v>
       </x:c>
       <x:c r="D38" s="3" t="s">
-        <x:v>780</x:v>
+        <x:v>768</x:v>
       </x:c>
       <x:c r="E38" s="3" t="s">
-        <x:v>781</x:v>
+        <x:v>769</x:v>
       </x:c>
       <x:c r="F38" s="3" t="s">
         <x:v>37</x:v>
@@ -10877,31 +10841,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L38" s="3" t="s">
-        <x:v>782</x:v>
+        <x:v>770</x:v>
       </x:c>
       <x:c r="M38" s="3" t="s">
-        <x:v>583</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="N38" s="3" t="s">
-        <x:v>783</x:v>
+        <x:v>771</x:v>
       </x:c>
       <x:c r="O38" s="3" t="s">
-        <x:v>784</x:v>
+        <x:v>772</x:v>
       </x:c>
       <x:c r="P38" s="3" t="s">
-        <x:v>785</x:v>
+        <x:v>773</x:v>
       </x:c>
       <x:c r="Q38" s="3" t="s">
-        <x:v>786</x:v>
+        <x:v>774</x:v>
       </x:c>
       <x:c r="R38" s="3" t="s">
-        <x:v>787</x:v>
+        <x:v>775</x:v>
       </x:c>
       <x:c r="S38" s="3" t="s">
-        <x:v>788</x:v>
+        <x:v>776</x:v>
       </x:c>
       <x:c r="T38" s="3" t="s">
-        <x:v>789</x:v>
+        <x:v>777</x:v>
       </x:c>
       <x:c r="U38" s="3" t="s">
         <x:v>52</x:v>
@@ -10909,19 +10873,19 @@
     </x:row>
     <x:row r="39" ht="93.25" hidden="0">
       <x:c r="A39" s="3" t="s">
-        <x:v>790</x:v>
+        <x:v>778</x:v>
       </x:c>
       <x:c r="B39" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C39" s="3" t="s">
-        <x:v>791</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="D39" s="3" t="s">
-        <x:v>792</x:v>
+        <x:v>780</x:v>
       </x:c>
       <x:c r="E39" s="3" t="s">
-        <x:v>793</x:v>
+        <x:v>781</x:v>
       </x:c>
       <x:c r="F39" s="3" t="s">
         <x:v>37</x:v>
@@ -10942,31 +10906,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="L39" s="3" t="s">
-        <x:v>794</x:v>
+        <x:v>782</x:v>
       </x:c>
       <x:c r="M39" s="3" t="s">
         <x:v>446</x:v>
       </x:c>
       <x:c r="N39" s="3" t="s">
-        <x:v>795</x:v>
+        <x:v>783</x:v>
       </x:c>
       <x:c r="O39" s="3" t="s">
-        <x:v>796</x:v>
+        <x:v>784</x:v>
       </x:c>
       <x:c r="P39" s="3" t="s">
-        <x:v>797</x:v>
+        <x:v>785</x:v>
       </x:c>
       <x:c r="Q39" s="3" t="s">
-        <x:v>798</x:v>
+        <x:v>786</x:v>
       </x:c>
       <x:c r="R39" s="3" t="s">
-        <x:v>799</x:v>
+        <x:v>787</x:v>
       </x:c>
       <x:c r="S39" s="3" t="s">
-        <x:v>800</x:v>
+        <x:v>788</x:v>
       </x:c>
       <x:c r="T39" s="3" t="s">
-        <x:v>801</x:v>
+        <x:v>789</x:v>
       </x:c>
       <x:c r="U39" s="3" t="s">
         <x:v>52</x:v>
@@ -10975,7 +10939,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf3665c4158cc4e66"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4d86a2a394f341b3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/maliev-feature-user-story-status.xlsx
+++ b/docs/maliev-feature-user-story-status.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R3f2a93bb0f704916"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="R05c25e21206b4dfd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="Ra6b23a2c131e47f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="R2ba32506083540da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rf7b2e44ef5514cf4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="R1d2df020d1f64acb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R532363df82634b29"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="R0ef2c3c78f0040ae"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3919,7 +3919,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd4ef8c8477924da3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8a59603307d444c8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9519,7 +9519,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Recb4e4dcf1d8456e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R045242ff3d294c9f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10541,55 +10541,55 @@
         <x:v>As a customer, I can give feedback on generated previews/artifacts.</x:v>
       </x:c>
       <x:c r="E16" s="8" t="str">
-        <x:v>Inline viewer feedback posts sentiment/text feedback and reflects memory observation status.</x:v>
+        <x:v>Customers can give thumbs-up or thumbs-down feedback on generated 3D preview artifacts from the inline viewer. Choosing a thumb reveals an optional comment box, sentiment-only feedback is accepted, comments are trimmed and sanitized before reuse, the BFF records artifact metadata and status, successful customer-memory observation is reflected in the response and UI status, and feedback is included in later agent context even when durable memory observation is unavailable.</x:v>
       </x:c>
       <x:c r="F16" s="8" t="str">
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G16" s="8" t="str">
-        <x:v>Automated QuoteEngine suite passed 2026-06-23 after workspace cleanup</x:v>
+        <x:v>Focused current-code artifact feedback tests passed 2026-06-24.</x:v>
       </x:c>
       <x:c r="H16" s="8" t="str">
-        <x:v>No behavior error observed in current QuoteEngine automated retest.</x:v>
+        <x:v>No behavior error observed in focused QuoteEngine artifact feedback retest; live browser feedback interaction still not executed in this slice.</x:v>
       </x:c>
       <x:c r="I16" s="8" t="str">
-        <x:v>No fix needed for this story from current QuoteEngine automated retest.</x:v>
+        <x:v>No app fix applied for QE-015; current code path is covered by focused BFF/source tests.</x:v>
       </x:c>
       <x:c r="J16" s="8" t="str">
-        <x:v>Current automated suite passed.</x:v>
+        <x:v>Passed 12 focused tests: feedback records artifact metadata and customer memory, feedback still records when memory observation fails, whitespace comments become sentiment-only feedback, observed memory appears in the next agent turn, prompt override text is sanitized from memory and next-turn context, session feedback is reused when memory observation fails, sentiment-only feedback is reused, memory-aware UI status text is present, sentiment-only submit gate is present, thumb buttons expose pressed state and isolate clicks, feedback text is hidden until sentiment is selected, and thumb buttons are borderless.</x:v>
       </x:c>
       <x:c r="K16" s="8" t="str">
         <x:v>P1</x:v>
       </x:c>
       <x:c r="L16" s="8" t="str">
-        <x:v>Inline feedback UI -&gt; AgentController artifact-feedback -&gt; QuoteAgentService</x:v>
+        <x:v>QuoteAgentLaunchShell inline viewer feedback UI -&gt; POST quote/v1/agent/sessions/{sessionId}/artifacts/{artifactId}/feedback -&gt; AgentController model validation/problem details -&gt; QuoteAgentService RecordPreviewFeedbackAsync -&gt; QuoteAgentPreviewFeedbackRequest/Response DTOs -&gt; QuoteAgentArtifactDto metadata/status -&gt; CustomerService ObserveCustomerMemoryAsync -&gt; next-turn QuoteAgentService context injection</x:v>
       </x:c>
       <x:c r="M16" s="8" t="str">
-        <x:v>QuoteAgentLaunchShell.razor</x:v>
+        <x:v>QuoteAgentLaunchShell.razor; AgentController; QuoteAgentService; QuoteAgentDtos; CustomerService client</x:v>
       </x:c>
       <x:c r="N16" s="8" t="str">
-        <x:v>Thumb feedback and optional text</x:v>
+        <x:v>QuoteAgentLaunchShell renders qe-inline-viewer-feedback with thumb up/down buttons, aria-pressed state, click isolation, hidden comment form until a sentiment is selected, optional 1200-character comment textarea, and a Send action that posts to /quote/v1/agent/sessions/{sessionId}/artifacts/{artifactId}/feedback and updates feedback status from MemoryObserved.</x:v>
       </x:c>
       <x:c r="O16" s="8" t="str">
-        <x:v>AgentController POST artifacts/{artifactId}/feedback</x:v>
+        <x:v>POST quote/v1/agent/sessions/{sessionId}/artifacts/{artifactId}/feedback accepts QuoteAgentPreviewFeedbackRequest with required Sentiment up/down and optional Comment. QuoteAgentService rejects missing/non-generated viewer artifacts, stores customerSentiment, optional sanitized customerComment, feedbackObservedAt, customerApproved, and customer_approved or issue_reported status, attempts make_studio_feedback memory observation, marks feedbackMemoryObserved when successful, returns updated state, and builds generated-preview feedback context for later agent turns.</x:v>
       </x:c>
       <x:c r="P16" s="8" t="str">
-        <x:v>QuoteEngineSourceTests feedback; QuoteAgentEndpointTests feedback | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:v>
+        <x:v>dotnet test Maliev.QuoteEngine.slnx --filter "FullyQualifiedName~QuoteAgentEndpointTests.Agent_preview_feedback_records_artifact_feedback_and_observes_customer_memory|FullyQualifiedName~QuoteAgentEndpointTests.Agent_preview_feedback_records_artifact_feedback_when_memory_observation_fails|FullyQualifiedName~QuoteAgentEndpointTests.Agent_preview_feedback_records_whitespace_comment_as_sentiment_only_feedback|FullyQualifiedName~QuoteAgentEndpointTests.Agent_message_after_preview_feedback_includes_observed_feedback_memory|FullyQualifiedName~QuoteAgentEndpointTests.Agent_preview_feedback_does_not_replay_prompt_override_text_into_memory_or_next_turn|FullyQualifiedName~QuoteAgentEndpointTests.Agent_message_after_preview_feedback_includes_session_feedback_when_memory_observation_fails|FullyQualifiedName~QuoteAgentEndpointTests.Agent_message_after_sentiment_only_preview_feedback_includes_session_sentiment|FullyQualifiedName~QuoteEngineSourceTests.QuoteAgentLaunchShell_feedback_status_reflects_memory_observation|FullyQualifiedName~QuoteEngineSourceTests.QuoteAgentLaunchShell_allows_sentiment_only_generated_preview_feedback|FullyQualifiedName~QuoteEngineSourceTests.QuoteAgentLaunchShell_thumb_buttons_expose_pressed_state_and_isolate_clicks|FullyQualifiedName~QuoteEngineSourceTests.QuoteAgentLaunchShell_hides_inline_viewer_feedback_text_until_sentiment_is_selected|FullyQualifiedName~QuoteEngineSourceTests.QuoteAgentLaunchShell_uses_borderless_inline_viewer_thumb_buttons" --verbosity minimal passed 12/12 on 2026-06-24.</x:v>
       </x:c>
       <x:c r="Q16" s="8" t="str">
-        <x:v>QuoteEngine BFF, Agent service, Customer memory</x:v>
+        <x:v>QuoteEngine Client, QuoteEngine BFF, QuoteAgentService, QuoteAgentSessionStore, CustomerService memory observation, ChatbotService next-turn context</x:v>
       </x:c>
       <x:c r="R16" s="8" t="str">
-        <x:v>Feedback records/memory observations</x:v>
+        <x:v>Generated viewer artifact feedback metadata, artifact status, feedbackObservedAt timestamp, customerApproved flag, feedbackMemoryObserved flag, customer memory observation record, next-turn generated-preview feedback context</x:v>
       </x:c>
       <x:c r="S16" s="8" t="str">
-        <x:v>Needs feedback persistence retest</x:v>
+        <x:v>Needs live browser retest for thumb selection, comment reveal, sentiment-only submit, failed-save status, successful-save status, and follow-up agent response behavior against a running QuoteEngine host.</x:v>
       </x:c>
       <x:c r="T16" s="8" t="str">
-        <x:v>AgentController.cs:240; QuoteAgentService.cs</x:v>
+        <x:v>Maliev.QuoteEngine.Client/Components/QuoteAgent/QuoteAgentLaunchShell.razor:669,670,675,690,692,701,4917,4923,4955,4966,4974,4986,5000,5009; Maliev.QuoteEngine.Bff/Controllers/AgentController.cs:240; Maliev.QuoteEngine.Bff/Services/QuoteAgentService.cs:670,678,692,705,715,724,729,748,774,5773,5922,6032; Maliev.QuoteEngine.Shared/Agent/QuoteAgentDtos.cs:515,518,523,530,538; Maliev.QuoteEngine.Tests/QuoteAgentEndpointTests.cs:8775,8843,8907,9047,9115,9187,9261; Maliev.QuoteEngine.Tests/QuoteEngineSourceTests.cs:5110,5140,5158,5181,5199</x:v>
       </x:c>
       <x:c r="U16" s="8" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-24</x:v>
       </x:c>
     </x:row>
     <x:row r="17" s="6" customFormat="1" ht="93.25" customHeight="1">
@@ -12090,7 +12090,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec5f0297565844e0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1640becbd8ad40fd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/maliev-feature-user-story-status.xlsx
+++ b/docs/maliev-feature-user-story-status.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rf7b2e44ef5514cf4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="R1d2df020d1f64acb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R532363df82634b29"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="R0ef2c3c78f0040ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R82e53614d15f4a57"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="R0e8929f6e3ec4591"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R64029884b0294103"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="R058668de7b1f4c27"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3919,7 +3919,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8a59603307d444c8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R60ce2ae7ee35414d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9519,7 +9519,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R045242ff3d294c9f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R61b955ab6efd4ffe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10603,58 +10603,58 @@
         <x:v>3D part viewer</x:v>
       </x:c>
       <x:c r="D17" s="8" t="str">
-        <x:v>As a customer, I can inspect uploaded/generated parts in a 3D viewer.</x:v>
+        <x:v>As a customer, I can inspect uploaded and agent-generated parts in a 3D viewer.</x:v>
       </x:c>
       <x:c r="E17" s="8" t="str">
-        <x:v>Part viewer loads GLB/viewer URLs, applies viewer settings, and pushes process/material/runtime state to JS.</x:v>
+        <x:v>Customers can inspect uploaded CAD/mesh files and generated preview artifacts in the QuoteEngine 3D viewer. The artifact drawer and part detail card render QePartViewer when viewer metadata is available, pass GLB/viewer URLs, file extension, browser file handles, storage path, process/material/finish/roughness, viewer settings, dark mode, and local geometry callbacks into the browser viewer, and fall back to safe preview states when a file is not renderable.</x:v>
       </x:c>
       <x:c r="F17" s="8" t="str">
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G17" s="8" t="str">
-        <x:v>Automated QuoteEngine suite passed 2026-06-23 after workspace cleanup</x:v>
+        <x:v>Focused current-code 3D viewer tests passed 2026-06-24.</x:v>
       </x:c>
       <x:c r="H17" s="8" t="str">
-        <x:v>No behavior error observed in current QuoteEngine automated retest.</x:v>
+        <x:v>No behavior error observed in focused QuoteEngine 3D viewer retest; live browser canvas smoke still not executed in this slice.</x:v>
       </x:c>
       <x:c r="I17" s="8" t="str">
-        <x:v>No fix needed for this story from current QuoteEngine automated retest.</x:v>
+        <x:v>No app fix applied for QE-016; current code path is covered by focused source and endpoint tests.</x:v>
       </x:c>
       <x:c r="J17" s="8" t="str">
-        <x:v>Current automated suite passed.</x:v>
+        <x:v>Passed 22/22 focused tests covering BFF geometry runtime manifest/assets/telemetry, QePartViewer and QePartDetailCard local DFM wiring, artifact drawer uploaded-part viewer rendering, and inline generated preview resource/error guards.</x:v>
       </x:c>
       <x:c r="K17" s="8" t="str">
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L17" s="8" t="str">
-        <x:v>QePartViewer -&gt; geometry runtime assets/telemetry -&gt; browser viewer</x:v>
+        <x:v>QuoteAgentLaunchShell artifact drawer and QePartDetailCard -&gt; QePartViewer -&gt; quote-part-viewer.js browser viewer and local geometry callbacks -&gt; QuoteWorkspace/agent part state -&gt; GeometryRuntimeController manifest/assets/telemetry</x:v>
       </x:c>
       <x:c r="M17" s="8" t="str">
-        <x:v>QePartViewer.razor; QePartDetailCard.razor</x:v>
+        <x:v>QePartViewer.razor; QePartDetailCard.razor; QuoteAgentLaunchShell.razor; QeInlinePartViewer.razor; quote-part-viewer.js; quote-inline-viewer.js; GeometryRuntimeController</x:v>
       </x:c>
       <x:c r="N17" s="8" t="str">
-        <x:v>3D Model tab, artifact drawer viewer</x:v>
+        <x:v>Part detail model tab keeps the Babylon viewer mounted across mode changes; artifact drawer renders the selected uploaded-part 3D viewer; assistant messages can render inline generated previews; toolbar exposes camera, render mode, projection, grid, edges, bounds, section, measure, thickness, rotate, and reset controls.</x:v>
       </x:c>
       <x:c r="O17" s="8" t="str">
-        <x:v>GeometryRuntimeController manifest/assets/telemetry</x:v>
+        <x:v>QePartViewer imports quote-part-viewer.js, initializes the canvas with viewer settings and file/runtime metadata, runs browser local geometry through quoteEngineUploads, and reports started/complete/unavailable callbacks. GeometryRuntimeController exposes anonymous quote/v1/geometry/runtime/manifest, assets/{assetName}, and telemetry endpoints with packaged runtime fallback and analysis-status hydration.</x:v>
       </x:c>
       <x:c r="P17" s="8" t="str">
-        <x:v>QuoteEngineSourceTests viewer/runtime | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:v>
+        <x:v>2026-06-24: dotnet test Maliev.QuoteEngine.slnx --filter focused QE-016 viewer/runtime set --verbosity minimal passed 22/22. Covered geometry runtime manifest/assets/telemetry endpoint tests, QePartViewer/detail-card source tests, artifact drawer viewer source test, and inline preview source tests.</x:v>
       </x:c>
       <x:c r="Q17" s="8" t="str">
-        <x:v>QuoteEngine client/BFF, Geometry runtime</x:v>
+        <x:v>QuoteEngine Client, QuoteEngine BFF, browser geometry/runtime assets, UploadService/analysis metadata, agent session local DFM sync</x:v>
       </x:c>
       <x:c r="R17" s="8" t="str">
-        <x:v>Viewer settings/telemetry</x:v>
+        <x:v>Viewer settings, selected part state, browser file identifiers, local geometry runtime status/result, DFM reports, overlay GLB URLs, runtime telemetry, inline preview command payloads</x:v>
       </x:c>
       <x:c r="S17" s="8" t="str">
-        <x:v>Needs visual canvas smoke</x:v>
+        <x:v>Needs live browser canvas smoke for uploaded GLB/STL/STEP, generated inline preview, toolbar interaction, dark/light mode, and local geometry callback behavior against a running QuoteEngine host.</x:v>
       </x:c>
       <x:c r="T17" s="8" t="str">
-        <x:v>QePartViewer.razor; QePartDetailCard.razor; GeometryRuntimeController.cs</x:v>
+        <x:v>QePartViewer.razor:6,21,150,207,284,370,443; QePartDetailCard.razor:92,95,228,271; QuoteAgentLaunchShell.razor:665,1631,1644,4220; QuoteEngineDtos.cs:164,304,341; GeometryRuntimeController.cs:18,39,74,214; quote-part-viewer.js:1915,3721,3734,3746; quote-inline-viewer.js:371</x:v>
       </x:c>
       <x:c r="U17" s="8" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-24</x:v>
       </x:c>
     </x:row>
     <x:row r="18" s="6" customFormat="1" ht="93.25" customHeight="1">
@@ -12090,7 +12090,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1640becbd8ad40fd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb034090643b54609"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/maliev-feature-user-story-status.xlsx
+++ b/docs/maliev-feature-user-story-status.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R82e53614d15f4a57"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="R0e8929f6e3ec4591"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R64029884b0294103"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="R058668de7b1f4c27"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R8bbed84910c04d4f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="R2897ba0727184eda"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R92dd9e0a46454f8d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="R5f5227a2a26a4753"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3919,7 +3919,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R60ce2ae7ee35414d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R335da5755d054031"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9519,7 +9519,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R61b955ab6efd4ffe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc0c54c32a7204ecf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10671,55 +10671,55 @@
         <x:v>As a customer, I can review manufacturability checks for FDM, SLA, and CNC.</x:v>
       </x:c>
       <x:c r="E18" s="8" t="str">
-        <x:v>DFM tab renders process-specific report types and the agent can apply DFM reports to session state.</x:v>
+        <x:v>Customers can open the DFM tab for a selected part and see pending, passed, or failed manufacturability checks for mesh integrity, body count, and the selected manufacturing process. FDM reports cover thin walls, overhang/support need, and small features; SLA reports cover thin walls, resin trapping, suction, and hollow regions; CNC reports cover sharp internal corners, undercuts, drill holes, EDM, grinding, and turnability. Browser-local DFM results update the matching process report, preserve accepted local results when later status refreshes have no report, feed issue overlays into the viewer, and can be acknowledged before formal quote/order gates proceed.</x:v>
       </x:c>
       <x:c r="F18" s="8" t="str">
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G18" s="8" t="str">
-        <x:v>Automated QuoteEngine suite passed 2026-06-23 after workspace cleanup</x:v>
+        <x:v>Focused current-code DFM reporting tests passed 2026-06-24.</x:v>
       </x:c>
       <x:c r="H18" s="8" t="str">
-        <x:v>No behavior error observed in current QuoteEngine automated retest.</x:v>
+        <x:v>No behavior error observed in focused QuoteEngine DFM retest; live browser DFM runtime and overlay interaction smoke still not executed in this slice.</x:v>
       </x:c>
       <x:c r="I18" s="8" t="str">
-        <x:v>No fix needed for this story from current QuoteEngine automated retest.</x:v>
+        <x:v>No app fix applied for QE-017; current code path is covered by focused source, endpoint, status-store, and gate tests.</x:v>
       </x:c>
       <x:c r="J18" s="8" t="str">
-        <x:v>Current automated suite passed.</x:v>
+        <x:v>Passed 22/22 focused tests covering DFM DTO round trips, local mapper process matching and report preservation, status-store merge behavior, DFM SignalR handling, DFM tab/source contracts, overlay status copy, local DFM session hydration, draft duplication preservation, and quote/order/agent gates for unacknowledged issues.</x:v>
       </x:c>
       <x:c r="K18" s="8" t="str">
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L18" s="8" t="str">
-        <x:v>QeDfmTab/QePartDetailCard -&gt; AgentController dfm -&gt; SessionStore</x:v>
+        <x:v>QePartDetailCard DFM tab and overlay panel -&gt; QeDfmTab/QeDfmOverlayPanel/QePartConfigSidebar -&gt; QeLocalDfmMapper -&gt; QuoteAgentLaunchShell local DFM submission -&gt; QuoteEngineApiClient -&gt; AgentController sessions/{sessionId}/dfm -&gt; QuoteAgentService and QuoteFileAnalysisStatusService -&gt; shared DFM DTOs</x:v>
       </x:c>
       <x:c r="M18" s="8" t="str">
-        <x:v>QeDfmTab.razor; QePartDetailCard.razor</x:v>
+        <x:v>QeDfmTab.razor; QePartDetailCard.razor; QeDfmOverlayPanel.razor; QePartConfigSidebar.razor; QeLocalDfmMapper.cs; QuoteAgentLaunchShell.razor; QuoteEngineApiClient.cs; AgentController.cs; QuoteAgentService.cs; QeDfmDtos.cs</x:v>
       </x:c>
       <x:c r="N18" s="8" t="str">
-        <x:v>DFM tab and issue acknowledgement</x:v>
+        <x:v>Part detail DFM tab shows pass/fail/pending badges and process tabs; DFM overlay panel shows analyzing, local analyzing, unavailable, all-clear, and issue states; issue rows toggle viewer overlays; DFM acknowledgement can be made from the overlay or part configuration sidebar.</x:v>
       </x:c>
       <x:c r="O18" s="8" t="str">
-        <x:v>AgentController POST sessions/{sessionId}/dfm; QeDfmDtos</x:v>
+        <x:v>POST quote/v1/agent/sessions/{sessionId}/dfm accepts QuoteAgentLocalDfmRequest, writes metrics and process reports to the authoritative analysis-status store, hydrates session parts back from that store, and returns QuoteAgentStateResponse so the assistant sees the same DFM issues as the customer UI.</x:v>
       </x:c>
       <x:c r="P18" s="8" t="str">
-        <x:v>QuoteEngineSourceTests DFM | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:v>
+        <x:v>2026-06-24: dotnet test Maliev.QuoteEngine.slnx --filter focused QE-017 DFM set --verbosity minimal passed 22/22. Covered DFM DTOs, mapper, SignalR/status-store merge, source contracts, local DFM endpoint hydration, draft preservation, and quote/order/agent acknowledgement gates.</x:v>
       </x:c>
       <x:c r="Q18" s="8" t="str">
-        <x:v>QuoteEngine BFF, Geometry/DFM, SessionStore</x:v>
+        <x:v>QuoteEngine Client, QuoteEngine BFF, QuoteAgentService, QuoteFileAnalysisStatusService, browser local geometry runtime, SignalR analysis notifications, formal quote/order gates</x:v>
       </x:c>
       <x:c r="R18" s="8" t="str">
-        <x:v>DFM reports and acknowledgement state</x:v>
+        <x:v>FDM/SLA/CNC DFM reports, DFM issue items, overlay GLB URLs, local runtime status fields, non-manifold reason, body count, part acknowledgement state, session part DFM state, quote/order gate state</x:v>
       </x:c>
       <x:c r="S18" s="8" t="str">
-        <x:v>Needs process-specific fixture coverage</x:v>
+        <x:v>Needs live browser DFM runtime smoke with representative FDM, SLA, and CNC files, overlay toggle rendering, acknowledgement interaction, and formal quote/order gating against a running QuoteEngine host.</x:v>
       </x:c>
       <x:c r="T18" s="8" t="str">
-        <x:v>QeDfmTab.razor; QePartDetailCard.razor; AgentController.cs:221</x:v>
+        <x:v>QeDfmTab.razor:4,37,47,134,150,223; QeLocalDfmMapper.cs:17,73,97,106,127,193,207; QePartDetailCard.razor:39,62,153,216,271,337,349,365; QeDfmOverlayPanel.razor:1,12,23,34,70,120; QePartConfigSidebar.razor:585,963; QuoteAgentLaunchShell.razor:3428,4220,4247; QuoteEngineApiClient.cs:421; AgentController.cs:221; QuoteAgentService.cs:561,580,598,638; QeDfmDtos.cs:10,16,25,33</x:v>
       </x:c>
       <x:c r="U18" s="8" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-24</x:v>
       </x:c>
     </x:row>
     <x:row r="19" s="6" customFormat="1" ht="93.25" customHeight="1">
@@ -12090,7 +12090,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb034090643b54609"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd325f058835b4392"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/maliev-feature-user-story-status.xlsx
+++ b/docs/maliev-feature-user-story-status.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R8bbed84910c04d4f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="R2897ba0727184eda"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="R92dd9e0a46454f8d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="R5f5227a2a26a4753"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R6b379c98333b4bd1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Web" sheetId="2" r:id="R79b65ba8a56d4daa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.Intranet" sheetId="3" r:id="Refa46d087f604d81"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maliev.QuoteEngine" sheetId="4" r:id="R5cb2dd8fcba940f0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3919,7 +3919,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R335da5755d054031"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8577feca60e84528"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9519,7 +9519,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc0c54c32a7204ecf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0887e75454734b9d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10733,58 +10733,58 @@
         <x:v>Part configuration sidebar</x:v>
       </x:c>
       <x:c r="D19" s="8" t="str">
-        <x:v>As a customer, I can select process, material, color, finish, tolerance, quantity, and options.</x:v>
+        <x:v>As a customer, I can configure process, material, finish, tolerance, inspection, quantity, notes, and manufacturing options for each uploaded part.</x:v>
       </x:c>
       <x:c r="E19" s="8" t="str">
-        <x:v>Configuration sidebar filters reference data and emits changes for quote estimation.</x:v>
+        <x:v>Customers can configure the selected part from the QuoteEngine chat workspace sidebar using process search/cards, material and color choices, surface finish and finish options, tolerance, CNC roughness, threaded-hole and insert details, process-specific options, inspection level, quantity stepper/presets/input, DFM acknowledgement, and production notes. Changing process or material clears dependent configuration, applies Project New-style catalog defaults from current reference data, resets stale DFM acknowledgement/runtime state when the process changes, and emits part-change callbacks so estimates, drafts, formal quotes, orders, and agent state use the same QuotePartDraftDto fields.</x:v>
       </x:c>
       <x:c r="F19" s="8" t="str">
         <x:v>Current code-derived</x:v>
       </x:c>
       <x:c r="G19" s="8" t="str">
-        <x:v>Automated QuoteEngine suite passed 2026-06-23 after workspace cleanup</x:v>
+        <x:v>Focused current-code part configuration tests passed 2026-06-24.</x:v>
       </x:c>
       <x:c r="H19" s="8" t="str">
-        <x:v>No behavior error observed in current QuoteEngine automated retest.</x:v>
+        <x:v>No behavior error observed in focused QuoteEngine part configuration retest; live keyboard/browser accessibility pass was not executed in this slice.</x:v>
       </x:c>
       <x:c r="I19" s="8" t="str">
-        <x:v>No fix needed for this story from current QuoteEngine automated retest.</x:v>
+        <x:v>No app fix applied for QE-018; current code path is covered by focused source, endpoint, and DTO tests.</x:v>
       </x:c>
       <x:c r="J19" s="8" t="str">
-        <x:v>Current automated suite passed.</x:v>
+        <x:v>Retested 2026-06-24 with 13 focused QuoteEngine tests covering part configuration sidebar card/source contract, process/material default clearing, DTO round-trip, reference-data exposure, and configured estimate pricing.</x:v>
       </x:c>
       <x:c r="K19" s="8" t="str">
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L19" s="8" t="str">
-        <x:v>QePartConfigSidebar -&gt; reference-data/estimate DTOs</x:v>
+        <x:v>QePartConfigSidebar controls -&gt; QuotePartViewModel process/material/defaulting and ToDraft -&gt; QuoteWorkspace estimate/draft/formal quote/order requests -&gt; QuotePartDraftDto/QuoteEstimateRequest -&gt; QuoteController estimate/projects/draft/formal quote/order endpoints.</x:v>
       </x:c>
       <x:c r="M19" s="8" t="str">
-        <x:v>QePartConfigSidebar.razor</x:v>
+        <x:v>Maliev.QuoteEngine.Client/Components/QuoteEngine/QePartConfigSidebar.razor; Maliev.QuoteEngine.Client/Models/QuotePartViewModel.cs; Maliev.QuoteEngine.Client/Pages/QuoteWorkspace.razor; Maliev.QuoteEngine.Shared/Quotes/QuoteEngineDtos.cs; Maliev.QuoteEngine.Bff/Controllers/QuoteController.cs.</x:v>
       </x:c>
       <x:c r="N19" s="8" t="str">
-        <x:v>Part configuration controls</x:v>
+        <x:v>QuoteWorkspace renders QePartConfigSidebar for the selected uploaded part. Sidebar sections include manufacturing process search/cards, material, material color, surface finish, finish options, tolerance, CNC roughness, part features, process options, inspection, quantity, DFM reviewed checkbox, and production notes.</x:v>
       </x:c>
       <x:c r="O19" s="8" t="str">
-        <x:v>QuoteController reference-data/estimate</x:v>
+        <x:v>GET quote/v1/reference-data supplies processes/materials/finishes/tolerances/inspection/roughness/colors/options. POST quote/v1/estimate prices configured QuotePartDraftDto fields. POST quote/v1/projects/draft persists request.Parts; formal quote and order requests reuse ToDraft parts.</x:v>
       </x:c>
       <x:c r="P19" s="8" t="str">
-        <x:v>QuoteEngineSourceTests config sidebar | Current suite: dotnet test Maliev.QuoteEngine.slnx --verbosity minimal passed 539/539 on 2026-06-23 after workspace cleanup. Initial full run failed 3/539 on QuoteEngineSourceTests stale sample-only workspace expectations.</x:v>
+        <x:v>dotnet test B:/maliev/Maliev.QuoteEngine/Maliev.QuoteEngine.slnx --filter part-configuration focused filter --verbosity minimal passed 2026-06-24: 13 passed, 0 failed.</x:v>
       </x:c>
       <x:c r="Q19" s="8" t="str">
-        <x:v>QuoteEngine client/BFF, Pricing/Material services</x:v>
+        <x:v>QuoteEngine Client, QuoteEngine BFF, reference data, project, pricing, formal quote, and order service boundaries.</x:v>
       </x:c>
       <x:c r="R19" s="8" t="str">
-        <x:v>Part configuration state</x:v>
+        <x:v>Selected part process, material, finish, tolerance, inspection, roughness, color, process option values, threaded-hole and insert fields, quantity, DFM acknowledgement, notes, and QuotePartDraftDto payload fields.</x:v>
       </x:c>
       <x:c r="S19" s="8" t="str">
-        <x:v>Needs keyboard/accessibility check</x:v>
+        <x:v>Needs live keyboard and screen-reader pass for process search, card groups, color picker, quantity stepper, DFM checkbox, and notes against a running QuoteEngine host.</x:v>
       </x:c>
       <x:c r="T19" s="8" t="str">
-        <x:v>QePartConfigSidebar.razor; QuoteController.cs:47,301</x:v>
+        <x:v>QePartConfigSidebar.razor:1-80,608-994,1026-1053; QuotePartViewModel.cs:65-179,195-238; QuoteWorkspace.razor:332-343,878-908,930-936,1028-1033; QuoteEngineDtos.cs:233-354; QuoteController.cs:301-460,502-540,1227-1255; QuoteEngineSourceTests.cs:121-159,421-498,3774-3975; QuoteEngineEndpointTests.cs:2102-2114,2630-2715.</x:v>
       </x:c>
       <x:c r="U19" s="8" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-24</x:v>
       </x:c>
     </x:row>
     <x:row r="20" s="6" customFormat="1" ht="79.25" customHeight="1">
@@ -12090,7 +12090,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd325f058835b4392"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R96292127832f4c43"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/maliev-feature-user-story-status.xlsx
+++ b/docs/maliev-feature-user-story-status.xlsx
@@ -193,7 +193,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:U31" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:U40" headerRowCount="1">
   <tableColumns count="21">
     <tableColumn id="1" name="Story ID"/>
     <tableColumn id="2" name="App Surface"/>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" ht="16.64999961853027" customHeight="1" s="6">
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>120</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" ht="31.60000038146973" customHeight="1" s="6">
@@ -566,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U31"/>
+  <dimension ref="A1:U40"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.8359375" defaultRowHeight="21.95000076293945"/>
   <cols>
     <col width="12.47000026702881" customWidth="1" style="5" min="1" max="1"/>
@@ -3907,6 +3907,969 @@
       <c r="U31" s="8" t="inlineStr">
         <is>
           <t>2026-06-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="73.44999694824219" customHeight="1" s="6">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>WEB-031</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>Maliev.Web</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>Landing hero and ad-targeted copy</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>As a visitor arriving from an ad or public link, I see a localized Make Studio hero that matches my intent and routes me into the live workspace.</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>The home page resolves an explicit ad target from the URL when present, otherwise uses the default hero profile, chooses and persists a localized hero-copy variant for prerender/interactive consistency, shows crawlable manufacturing metrics enhanced by count-up animation, renders an animated Make Studio conversation preview for sketch, CAD, photo, and text scenarios, and keeps primary CTAs wired to Make Studio and contact paths.</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>Current code-derived</t>
+        </is>
+      </c>
+      <c r="G32" s="8" t="inlineStr">
+        <is>
+          <t>Mapped to current source tests; not executed in this workbook pass.</t>
+        </is>
+      </c>
+      <c r="H32" s="8" t="inlineStr">
+        <is>
+          <t>No behavior error documented in this spreadsheet pass.</t>
+        </is>
+      </c>
+      <c r="I32" s="8" t="inlineStr">
+        <is>
+          <t>No app fix applied; spreadsheet row added from current code evidence only.</t>
+        </is>
+      </c>
+      <c r="J32" s="8" t="inlineStr">
+        <is>
+          <t>Existing tests cover ad-targeted hero copy, Make Studio animation, metrics count-up, Make Studio CTAs, responsive hero composition, and reduced-motion freeze guards.</t>
+        </is>
+      </c>
+      <c r="K32" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L32" s="8" t="inlineStr">
+        <is>
+          <t>Home.razor hero state -&gt; HeroCopyCatalog ad target/variant selection -&gt; PersistentComponentState -&gt; SiteContent MakeStudioUrl/contact links -&gt; maliev-make-studio-hero.js animation and app.css responsive styles</t>
+        </is>
+      </c>
+      <c r="M32" s="8" t="inlineStr">
+        <is>
+          <t>Home.razor; HeroCopyCatalog.cs; SiteContent.cs; maliev-make-studio-hero.js; app.css; HeroLayoutSourceTests.cs; HeroCopyCatalogTests.cs</t>
+        </is>
+      </c>
+      <c r="N32" s="8" t="inlineStr">
+        <is>
+          <t>Home renders landing-hero, data-count-up metrics, data-make-studio-hero ms-hero scenes, Start in Make Studio and Talk to MALIEV links, and final Make Studio CTA; InitializeHeroCopy resolves URL targets and persists selected variants.</t>
+        </is>
+      </c>
+      <c r="O32" s="8" t="inlineStr">
+        <is>
+          <t>No BFF write boundary; public page uses static content, persisted component state, browser animation JavaScript, and QuoteEngine URL from SiteContent.</t>
+        </is>
+      </c>
+      <c r="P32" s="8" t="inlineStr">
+        <is>
+          <t>HeroLayoutSourceTests.HomeHeroShowsAnimatedMakeStudioWindow; MakeStudioHeroDoesNotStopForReducedMotion; HomeHeroMetricsUseCountUpEnhancement; HomeHeroUsesAdTargetedLocalizedCopyRotation; HomeHeroAndFinalCtaLinkToLiveMakeStudio; HeroCopyCatalogTests.*</t>
+        </is>
+      </c>
+      <c r="Q32" s="8" t="inlineStr">
+        <is>
+          <t>Maliev.Web Client, BFF static assets, QuoteEngine public workspace link</t>
+        </is>
+      </c>
+      <c r="R32" s="8" t="inlineStr">
+        <is>
+          <t>Client-side hero copy selection state, persisted component state keys for hero variant, no durable customer data mutation</t>
+        </is>
+      </c>
+      <c r="S32" s="8" t="inlineStr">
+        <is>
+          <t>Needs live browser verification for animated scene cycling, count-up timing, ad-target query behavior, and CTA navigation across desktop/mobile.</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>Maliev.Web.Client/Pages/Home.razor:11,32,47,724; Maliev.Web.Client/Content/HeroCopyCatalog.cs:8,359,364,370; Maliev.Web.Bff/wwwroot/js/maliev-make-studio-hero.js:7; Maliev.Web.Tests/HeroLayoutSourceTests.cs:13,409,1288; Maliev.Web.Tests/HeroCopyCatalogTests.cs:1</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="73.44999694824219" customHeight="1" s="6">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>WEB-032</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>Maliev.Web</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>Home workflow, services, and machine configurator</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>As a visitor, I can explore MALIEV workflows, service fit, and a workshop-made machine package from the home page before taking action.</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>The home page lets visitors select workflow steps, switch manufacturing service tabs, open service details, view randomized case-study/news cards, choose a pneumatic injection machine size, toggle an optional air compressor, see updated localized stats/images/package labels, and follow the configured package link into the shop product route with variant and compressor query parameters.</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>Current code-derived</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t>Mapped to current source tests; not executed in this workbook pass.</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="inlineStr">
+        <is>
+          <t>No behavior error documented in this spreadsheet pass.</t>
+        </is>
+      </c>
+      <c r="I33" s="8" t="inlineStr">
+        <is>
+          <t>No app fix applied; spreadsheet row added from current code evidence only.</t>
+        </is>
+      </c>
+      <c r="J33" s="8" t="inlineStr">
+        <is>
+          <t>Existing tests cover workflow layout, home services rotation, machine configurator selection/compressor add-on, prepared machine images, finished manufacturing sections, and responsive layout rules.</t>
+        </is>
+      </c>
+      <c r="K33" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L33" s="8" t="inlineStr">
+        <is>
+          <t>Home.razor UI state -&gt; SiteContent service/case/blog data -&gt; machine variant records -&gt; product-detail shop URL query -&gt; browser scroll helper for selected workflow target</t>
+        </is>
+      </c>
+      <c r="M33" s="8" t="inlineStr">
+        <is>
+          <t>Home.razor; SiteContent.cs; app.css; WorkflowLayoutSourceTests.cs; HeroLayoutSourceTests.cs</t>
+        </is>
+      </c>
+      <c r="N33" s="8" t="inlineStr">
+        <is>
+          <t>Home renders process-grid workflow buttons, home-services tabs/panel, case/blog cards, machine-feature section with data-selected-variant and data-compressor-included, MachineVariant radio buttons, compressor toggle, configured package summary, and Configure link.</t>
+        </is>
+      </c>
+      <c r="O33" s="8" t="inlineStr">
+        <is>
+          <t>No BFF write boundary; public page state is client-side and links into /services/{slug}, /case-studies/{slug}, /blog/{slug}, and /shop/pneumatic-injection-molding-machine query routes.</t>
+        </is>
+      </c>
+      <c r="P33" s="8" t="inlineStr">
+        <is>
+          <t>WorkflowLayoutSourceTests.WorkflowStepsUseFullWidthTrackForConsistentColumnAlignment; HeroLayoutSourceTests.HomeServicesRotateGenericHighlightAndPinExplicitServiceTargets; HomeMachineConfiguratorLimitsMachineSelectionAndCompressorAddon; HomeUsesFinishedManufacturingAndNewsSections</t>
+        </is>
+      </c>
+      <c r="Q33" s="8" t="inlineStr">
+        <is>
+          <t>Maliev.Web Client, content model, shop route</t>
+        </is>
+      </c>
+      <c r="R33" s="8" t="inlineStr">
+        <is>
+          <t>Selected workflow accent, selected home service slug, selected machine variant, compressor toggle, persisted order state for randomized home cards</t>
+        </is>
+      </c>
+      <c r="S33" s="8" t="inlineStr">
+        <is>
+          <t>Needs live browser verification for keyboard/assistive behavior, service tab state, machine configure link query, and responsive home layout.</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>Maliev.Web.Client/Pages/Home.razor:197,224,300,310,334,354,606,633,645; Maliev.Web.Tests/WorkflowLayoutSourceTests.cs:1; Maliev.Web.Tests/HeroLayoutSourceTests.cs:718,756,1122</t>
+        </is>
+      </c>
+      <c r="U33" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="73.44999694824219" customHeight="1" s="6">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>WEB-033</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>Maliev.Web</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>Public quote dropzone format picker</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>As a visitor, I can understand supported quote file formats and open Make Studio from public quote entry points.</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>Public quote dropzones render as keyboard-focusable upload targets with a hidden multi-file input, display supported CAD and mesh formats in an interactive popover, prevent child controls from triggering the dropzone, register JavaScript handlers for click/drag file handoff, dismiss the format popover when clicking outside, and route selected files through the configured Make Studio/QuoteEngine handoff URL.</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t>Current code-derived</t>
+        </is>
+      </c>
+      <c r="G34" s="8" t="inlineStr">
+        <is>
+          <t>Mapped to current source tests; not executed in this workbook pass.</t>
+        </is>
+      </c>
+      <c r="H34" s="8" t="inlineStr">
+        <is>
+          <t>No behavior error documented in this spreadsheet pass.</t>
+        </is>
+      </c>
+      <c r="I34" s="8" t="inlineStr">
+        <is>
+          <t>No app fix applied; spreadsheet row added from current code evidence only.</t>
+        </is>
+      </c>
+      <c r="J34" s="8" t="inlineStr">
+        <is>
+          <t>Existing source tests cover supported format list, JS registration, drag/drop file capture, interactive child guards, and public entry points.</t>
+        </is>
+      </c>
+      <c r="K34" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L34" s="8" t="inlineStr">
+        <is>
+          <t>QuoteDropzone.razor component -&gt; maliev-quote-dropzone.js browser registration -&gt; public quote links -&gt; Web quote upload/handoff endpoints -&gt; QuoteEngine workspace URL</t>
+        </is>
+      </c>
+      <c r="M34" s="8" t="inlineStr">
+        <is>
+          <t>QuoteDropzone.razor; maliev-quote-dropzone.js; Quote.razor; Home.razor; HeroLayoutSourceTests.cs; WebBffEndpointTests.cs</t>
+        </is>
+      </c>
+      <c r="N34" s="8" t="inlineStr">
+        <is>
+          <t>QuoteDropzone renders type=file, accept list, role=button surface, supported-format button/popover, JSInvokable CloseFormatsAsync, malievQuoteDropzone.register, and registerFormatDismissal; quote entry points no longer point at disabled quote actions.</t>
+        </is>
+      </c>
+      <c r="O34" s="8" t="inlineStr">
+        <is>
+          <t>When files are selected, JavaScript routes to the handoff URL; upload and token validation are handled by web/v1/quote uploads/resumable, complete, analysis-status, and uploads/handoff-token endpoints already tracked by WEB-013/WEB-012.</t>
+        </is>
+      </c>
+      <c r="P34" s="8" t="inlineStr">
+        <is>
+          <t>HeroLayoutSourceTests.QuoteDropzoneRoutesSelectedFilesToQuoteEngine; PublicQuoteEntryPointsAreLive; WebBffEndpointTests.POST_QuoteUploadInitiation_*; POST_QuoteUploadHandoffToken_*</t>
+        </is>
+      </c>
+      <c r="Q34" s="8" t="inlineStr">
+        <is>
+          <t>Maliev.Web Client, BFF quote upload endpoints, QuoteEngine handoff destination, browser JS</t>
+        </is>
+      </c>
+      <c r="R34" s="8" t="inlineStr">
+        <is>
+          <t>Browser-selected files, supported format popover state, upload session IDs and signed handoff token via existing quote upload rows</t>
+        </is>
+      </c>
+      <c r="S34" s="8" t="inlineStr">
+        <is>
+          <t>Needs live browser verification for drag/drop, format popover dismissal, keyboard activation, and selected-file handoff into QuoteEngine.</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>Maliev.Web.Client/Components/Quote/QuoteDropzone.razor:3,5,15,27,37,57,118; Maliev.Web.Bff/wwwroot/js/maliev-quote-dropzone.js; Maliev.Web.Tests/HeroLayoutSourceTests.cs:300; Maliev.Web.Bff/Controllers/QuoteController.cs:66,170</t>
+        </is>
+      </c>
+      <c r="U34" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="73.44999694824219" customHeight="1" s="6">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>WEB-034</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>Maliev.Web</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>Product media gallery and variant purchase</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>As a shopper, I can inspect product media, select an available variant, and add the product to my cart.</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>The product detail route loads a product by handle, shows thumbnail media when multiple images exist, crossfades the selected main image, initializes the first available variant, disables unavailable variants, displays lead time/inventory/quantity, enables Add to cart only for buyable published stock with a valid price and available variant, and offers a Make Studio link for custom-part requests.</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t>Current code-derived</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="inlineStr">
+        <is>
+          <t>Mapped to current source tests; not executed in this workbook pass.</t>
+        </is>
+      </c>
+      <c r="H35" s="8" t="inlineStr">
+        <is>
+          <t>No behavior error documented in this spreadsheet pass.</t>
+        </is>
+      </c>
+      <c r="I35" s="8" t="inlineStr">
+        <is>
+          <t>No app fix applied; spreadsheet row added from current code evidence only.</t>
+        </is>
+      </c>
+      <c r="J35" s="8" t="inlineStr">
+        <is>
+          <t>Existing tests cover media-grid layout, thumbnail strip, crossfade state fields/classes, selected image method, and catalog product detail contract.</t>
+        </is>
+      </c>
+      <c r="K35" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L35" s="8" t="inlineStr">
+        <is>
+          <t>ProductDetail.razor route handle -&gt; MalievApiClient.GetProductAsync -&gt; CatalogController products/{handle} -&gt; Commerce catalog service -&gt; CartState.AddAsync for selected variant</t>
+        </is>
+      </c>
+      <c r="M35" s="8" t="inlineStr">
+        <is>
+          <t>ProductDetail.razor; ProductGrid.razor; CartState.cs; CatalogController.cs; ProductDetailMediaSourceTests.cs; CommerceCatalogBoundaryTests.cs</t>
+        </is>
+      </c>
+      <c r="N35" s="8" t="inlineStr">
+        <is>
+          <t>ProductDetail renders media-strip thumbnail buttons, product-detail-media-main crossfade images, variant select with disabled unavailable options, lead time/inventory/quantity specs, Add to cart button, and custom-part Make Studio link.</t>
+        </is>
+      </c>
+      <c r="O35" s="8" t="inlineStr">
+        <is>
+          <t>GET web/v1/catalog/products/{handle} maps catalog detail data; cart mutation is client-side CartState for the browser session.</t>
+        </is>
+      </c>
+      <c r="P35" s="8" t="inlineStr">
+        <is>
+          <t>ProductDetailMediaSourceTests.*; CommerceCatalogBoundaryTests.GET_CatalogProduct_MapsCommerceServiceProductDetail; WebBffEndpointTests.GET_CatalogProducts_ReturnsCatalogProducts</t>
+        </is>
+      </c>
+      <c r="Q35" s="8" t="inlineStr">
+        <is>
+          <t>Maliev.Web Client, Web BFF catalog endpoints, CommerceService catalog, browser cart state</t>
+        </is>
+      </c>
+      <c r="R35" s="8" t="inlineStr">
+        <is>
+          <t>Displayed/fading product image state, selected variant SKU, cart item state in browser/session storage</t>
+        </is>
+      </c>
+      <c r="S35" s="8" t="inlineStr">
+        <is>
+          <t>Needs live browser verification for thumbnail crossfade timing, variant disabled state, cart count update, and missing-product recovery.</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
+        <is>
+          <t>Maliev.Web.Client/Pages/ProductDetail.razor:1,19,25,31,42,52,68,74,121; Maliev.Web.Tests/ProductDetailMediaSourceTests.cs:7,79,94; Maliev.Web.Bff/Controllers/CatalogController.cs:87</t>
+        </is>
+      </c>
+      <c r="U35" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="73.44999694824219" customHeight="1" s="6">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>WEB-035</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>Maliev.Web</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>Blog discovery and article tools</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>As a visitor, I can search, filter, page through, read, and export manufacturing notes.</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>The blog library route supports query-string search, multi-topic category chips with clear filters, result counts, paged cards, previous/next page links, article detail pages with checkl